--- a/Result/analyze_2.xlsx
+++ b/Result/analyze_2.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
     </row>
@@ -503,37 +503,37 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>378.61661185</v>
+        <v>127.95919719</v>
       </c>
       <c r="D2" t="n">
-        <v>127.96018674</v>
+        <v>203.49289</v>
       </c>
       <c r="E2" t="n">
-        <v>203.4922117</v>
+        <v>-276.35023151</v>
       </c>
       <c r="F2" t="n">
-        <v>-276.3497376</v>
+        <v>158.97995833</v>
       </c>
       <c r="G2" t="n">
-        <v>158.97929835</v>
+        <v>273.16832933</v>
       </c>
       <c r="H2" t="n">
-        <v>273.16651717</v>
+        <v>109.07201334</v>
       </c>
       <c r="I2" t="n">
-        <v>109.07201822</v>
+        <v>397.81500457</v>
       </c>
       <c r="J2" t="n">
-        <v>397.80846612</v>
+        <v>-15.39561179000001</v>
       </c>
       <c r="K2" t="n">
-        <v>-15.41230627000001</v>
+        <v>227.93637408</v>
       </c>
       <c r="L2" t="n">
-        <v>227.9379437</v>
+        <v>613.8424225</v>
       </c>
       <c r="M2" t="n">
-        <v>613.84583642</v>
+        <v>670.9141331700001</v>
       </c>
     </row>
     <row r="3">
@@ -544,37 +544,37 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>28.20313922</v>
+        <v>-54.91244948000001</v>
       </c>
       <c r="D3" t="n">
-        <v>-53.75805347</v>
+        <v>-74.32056421000001</v>
       </c>
       <c r="E3" t="n">
-        <v>-72.71582455000001</v>
+        <v>-175.84137512</v>
       </c>
       <c r="F3" t="n">
-        <v>-175.50961481</v>
+        <v>4.470229860000002</v>
       </c>
       <c r="G3" t="n">
-        <v>5.416809699999999</v>
+        <v>65.91919256</v>
       </c>
       <c r="H3" t="n">
-        <v>67.93627185000001</v>
+        <v>148.60531562</v>
       </c>
       <c r="I3" t="n">
-        <v>149.17134376</v>
+        <v>216.59486601</v>
       </c>
       <c r="J3" t="n">
-        <v>217.7331842</v>
+        <v>120.05869735</v>
       </c>
       <c r="K3" t="n">
-        <v>119.52700887</v>
+        <v>183.62103201</v>
       </c>
       <c r="L3" t="n">
-        <v>190.78776386</v>
+        <v>19.38308904</v>
       </c>
       <c r="M3" t="n">
-        <v>22.53308388</v>
+        <v>5.290656840000007</v>
       </c>
     </row>
     <row r="4">
@@ -585,37 +585,37 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>425.4531639</v>
+        <v>547.71554956</v>
       </c>
       <c r="D4" t="n">
-        <v>546.560164</v>
+        <v>479.93782586</v>
       </c>
       <c r="E4" t="n">
-        <v>478.3337645</v>
+        <v>-34.43076157000001</v>
       </c>
       <c r="F4" t="n">
-        <v>-34.76301579</v>
+        <v>-125.8413677</v>
       </c>
       <c r="G4" t="n">
-        <v>-126.78728756</v>
+        <v>107.71665762</v>
       </c>
       <c r="H4" t="n">
-        <v>105.70139049</v>
+        <v>-41.65350639999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-42.21953942</v>
+        <v>-76.10564045999999</v>
       </c>
       <c r="J4" t="n">
-        <v>-77.2374202</v>
+        <v>-184.43235699</v>
       </c>
       <c r="K4" t="n">
-        <v>-183.88397403</v>
+        <v>-55.80883295000001</v>
       </c>
       <c r="L4" t="n">
-        <v>-62.97713442000001</v>
+        <v>-169.1393089</v>
       </c>
       <c r="M4" t="n">
-        <v>-172.29271766</v>
+        <v>-220.1144846</v>
       </c>
     </row>
     <row r="5">
@@ -626,37 +626,37 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>-65.29147432000001</v>
+        <v>-80.57878520999999</v>
       </c>
       <c r="D5" t="n">
-        <v>-80.57878520999999</v>
+        <v>-41.82454427</v>
       </c>
       <c r="E5" t="n">
-        <v>-41.82454427</v>
+        <v>-198.68212282</v>
       </c>
       <c r="F5" t="n">
-        <v>-198.68212282</v>
+        <v>-126.15321476</v>
       </c>
       <c r="G5" t="n">
-        <v>-126.15321476</v>
+        <v>186.82817224</v>
       </c>
       <c r="H5" t="n">
-        <v>186.82817224</v>
+        <v>467.84870192</v>
       </c>
       <c r="I5" t="n">
-        <v>467.84870192</v>
+        <v>758.27998281</v>
       </c>
       <c r="J5" t="n">
-        <v>758.27998281</v>
+        <v>802.10581856</v>
       </c>
       <c r="K5" t="n">
-        <v>802.10581856</v>
+        <v>1311.67911888</v>
       </c>
       <c r="L5" t="n">
-        <v>1311.67911888</v>
+        <v>1402.61016698</v>
       </c>
       <c r="M5" t="n">
-        <v>1402.61016698</v>
+        <v>947.17840165</v>
       </c>
     </row>
     <row r="6">
@@ -667,37 +667,37 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>67.66474070999999</v>
+        <v>-30.20119688</v>
       </c>
       <c r="D6" t="n">
-        <v>-16.71685492</v>
+        <v>-17.18114108</v>
       </c>
       <c r="E6" t="n">
-        <v>-4.810381969999997</v>
+        <v>-109.22155964</v>
       </c>
       <c r="F6" t="n">
-        <v>-102.92022365</v>
+        <v>52.46751640000001</v>
       </c>
       <c r="G6" t="n">
-        <v>64.02042153000001</v>
+        <v>36.99258923000001</v>
       </c>
       <c r="H6" t="n">
-        <v>45.2817945</v>
+        <v>-15.6315426</v>
       </c>
       <c r="I6" t="n">
-        <v>-10.42032348</v>
+        <v>-37.31116809</v>
       </c>
       <c r="J6" t="n">
-        <v>-36.58453509</v>
+        <v>-50.83876026999999</v>
       </c>
       <c r="K6" t="n">
-        <v>-45.18726547999999</v>
+        <v>-51.95025489999999</v>
       </c>
       <c r="L6" t="n">
-        <v>-42.80451564999999</v>
+        <v>-141.17693016</v>
       </c>
       <c r="M6" t="n">
-        <v>-142.23888348</v>
+        <v>-65.94550987</v>
       </c>
     </row>
     <row r="7">
@@ -708,37 +708,37 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>4.904085130000001</v>
+        <v>-0.9401508499999987</v>
       </c>
       <c r="D7" t="n">
-        <v>-14.42449281</v>
+        <v>30.22284465</v>
       </c>
       <c r="E7" t="n">
-        <v>17.85208554</v>
+        <v>17.14304371</v>
       </c>
       <c r="F7" t="n">
-        <v>10.84170772</v>
+        <v>45.93011667</v>
       </c>
       <c r="G7" t="n">
-        <v>34.37721154</v>
+        <v>34.89399661</v>
       </c>
       <c r="H7" t="n">
-        <v>26.60479134</v>
+        <v>24.4647333</v>
       </c>
       <c r="I7" t="n">
-        <v>19.25351418</v>
+        <v>18.88294978</v>
       </c>
       <c r="J7" t="n">
-        <v>18.15631678</v>
+        <v>13.23002471</v>
       </c>
       <c r="K7" t="n">
-        <v>7.578529919999998</v>
+        <v>24.15559624</v>
       </c>
       <c r="L7" t="n">
-        <v>15.00985699</v>
+        <v>8.516418289999999</v>
       </c>
       <c r="M7" t="n">
-        <v>9.57837161</v>
+        <v>8.717809850000004</v>
       </c>
     </row>
     <row r="8">
@@ -749,37 +749,37 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>-406.71345692</v>
+        <v>1195.38538558</v>
       </c>
       <c r="D8" t="n">
-        <v>1195.38305168</v>
+        <v>556.4589227300002</v>
       </c>
       <c r="E8" t="n">
-        <v>556.4632063500002</v>
+        <v>-1944.2599113</v>
       </c>
       <c r="F8" t="n">
-        <v>-1944.24913114</v>
+        <v>-599.6152991099999</v>
       </c>
       <c r="G8" t="n">
-        <v>-599.6078130999999</v>
+        <v>1548.76478186</v>
       </c>
       <c r="H8" t="n">
-        <v>1548.77045769</v>
+        <v>1718.89143472</v>
       </c>
       <c r="I8" t="n">
-        <v>1718.89840521</v>
+        <v>1803.15963861</v>
       </c>
       <c r="J8" t="n">
-        <v>1803.16711039</v>
+        <v>300.95168602</v>
       </c>
       <c r="K8" t="n">
-        <v>300.96101766</v>
+        <v>-118.262187</v>
       </c>
       <c r="L8" t="n">
-        <v>-118.25303632</v>
+        <v>1443.76986541</v>
       </c>
       <c r="M8" t="n">
-        <v>1443.77885708</v>
+        <v>2180.66499101</v>
       </c>
     </row>
     <row r="9">
@@ -788,41 +788,39 @@
           <t>其他電子業右下</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>58.68647769</v>
+        <v>21.84615598</v>
       </c>
       <c r="D9" t="n">
-        <v>21.84577745</v>
+        <v>75.89871953000001</v>
       </c>
       <c r="E9" t="n">
-        <v>75.89854339</v>
+        <v>5.860238190000002</v>
       </c>
       <c r="F9" t="n">
-        <v>5.860496940000003</v>
+        <v>68.36908266999998</v>
       </c>
       <c r="G9" t="n">
-        <v>68.36892299</v>
+        <v>64.52141722</v>
       </c>
       <c r="H9" t="n">
-        <v>64.52139552</v>
+        <v>24.17054145</v>
       </c>
       <c r="I9" t="n">
-        <v>24.17067021</v>
+        <v>-2.58511499</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.58524676</v>
+        <v>5.02297822</v>
       </c>
       <c r="K9" t="n">
-        <v>5.022933399999999</v>
+        <v>17.57920718</v>
       </c>
       <c r="L9" t="n">
-        <v>17.57913757</v>
+        <v>-18.75978422</v>
       </c>
       <c r="M9" t="n">
-        <v>-18.76011516</v>
+        <v>37.68639279</v>
       </c>
     </row>
     <row r="10">
@@ -833,37 +831,37 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>17.25505467</v>
+        <v>186.37600926</v>
       </c>
       <c r="D10" t="n">
-        <v>186.37342242</v>
+        <v>72.46610762</v>
       </c>
       <c r="E10" t="n">
-        <v>72.45016692999999</v>
+        <v>-127.30960734</v>
       </c>
       <c r="F10" t="n">
-        <v>-127.32324488</v>
+        <v>-22.11584877</v>
       </c>
       <c r="G10" t="n">
-        <v>-22.12720129</v>
+        <v>80.74255992000001</v>
       </c>
       <c r="H10" t="n">
-        <v>80.73240184999999</v>
+        <v>-23.83148457</v>
       </c>
       <c r="I10" t="n">
-        <v>-23.84007115</v>
+        <v>-43.34589346</v>
       </c>
       <c r="J10" t="n">
-        <v>-43.35579865</v>
+        <v>-111.72759535</v>
       </c>
       <c r="K10" t="n">
-        <v>-111.73703211</v>
+        <v>-54.28320683</v>
       </c>
       <c r="L10" t="n">
-        <v>-54.29285776</v>
+        <v>-18.55405404</v>
       </c>
       <c r="M10" t="n">
-        <v>-18.56100346</v>
+        <v>104.89008214</v>
       </c>
     </row>
     <row r="11">
@@ -874,37 +872,37 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>44.87738397</v>
+        <v>21.06413663</v>
       </c>
       <c r="D11" t="n">
-        <v>21.00343256</v>
+        <v>18.10102991</v>
       </c>
       <c r="E11" t="n">
-        <v>18.0848753</v>
+        <v>4.557968200000001</v>
       </c>
       <c r="F11" t="n">
-        <v>4.574126350000001</v>
+        <v>25.1602354</v>
       </c>
       <c r="G11" t="n">
-        <v>25.16208922</v>
+        <v>32.84137479</v>
       </c>
       <c r="H11" t="n">
-        <v>32.86414364</v>
+        <v>35.49912004999999</v>
       </c>
       <c r="I11" t="n">
-        <v>35.530148</v>
+        <v>70.59165781</v>
       </c>
       <c r="J11" t="n">
-        <v>70.60011512999999</v>
+        <v>12.96211003</v>
       </c>
       <c r="K11" t="n">
-        <v>12.99880258</v>
+        <v>60.57403519</v>
       </c>
       <c r="L11" t="n">
-        <v>60.59191811</v>
+        <v>133.73712991</v>
       </c>
       <c r="M11" t="n">
-        <v>133.72659956</v>
+        <v>63.03845849</v>
       </c>
     </row>
     <row r="12">
@@ -913,41 +911,39 @@
           <t>化學工業右下</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>255.1624458</v>
+        <v>195.34927787</v>
       </c>
       <c r="D12" t="n">
-        <v>195.34927787</v>
+        <v>248.90957013</v>
       </c>
       <c r="E12" t="n">
-        <v>248.90957013</v>
+        <v>38.94469194999999</v>
       </c>
       <c r="F12" t="n">
-        <v>38.94469194999999</v>
+        <v>43.88918375</v>
       </c>
       <c r="G12" t="n">
-        <v>43.88918375</v>
+        <v>181.12827274</v>
       </c>
       <c r="H12" t="n">
-        <v>181.12827274</v>
+        <v>62.28709359</v>
       </c>
       <c r="I12" t="n">
-        <v>62.28709359</v>
+        <v>47.51182313</v>
       </c>
       <c r="J12" t="n">
-        <v>47.51182313</v>
+        <v>-67.86251213</v>
       </c>
       <c r="K12" t="n">
-        <v>-67.86251213</v>
+        <v>117.04709593</v>
       </c>
       <c r="L12" t="n">
-        <v>117.04709593</v>
+        <v>1.19653822</v>
       </c>
       <c r="M12" t="n">
-        <v>1.19653822</v>
+        <v>-83.11722171000001</v>
       </c>
     </row>
     <row r="13">
@@ -958,37 +954,37 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>2.24015463</v>
+        <v>0.6288524099999997</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6288524099999997</v>
+        <v>-0.3505743700000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.3505743700000001</v>
+        <v>-3.3437935</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.3437935</v>
+        <v>0.7640100200000001</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7640100200000001</v>
+        <v>-0.38818104</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.38818104</v>
+        <v>-0.2997979300000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2997979300000001</v>
+        <v>-0.55539505</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.55539505</v>
+        <v>-0.1066688500000001</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.1066688500000001</v>
+        <v>1.73731473</v>
       </c>
       <c r="L13" t="n">
-        <v>1.73731473</v>
+        <v>2.49062023</v>
       </c>
       <c r="M13" t="n">
-        <v>2.49062023</v>
+        <v>1.4928339</v>
       </c>
     </row>
     <row r="14">
@@ -999,37 +995,37 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>889.125306</v>
+        <v>6025.853046519999</v>
       </c>
       <c r="D14" t="n">
-        <v>6025.89210489</v>
+        <v>82.44883361000001</v>
       </c>
       <c r="E14" t="n">
-        <v>82.49690215000001</v>
+        <v>-6433.896442570001</v>
       </c>
       <c r="F14" t="n">
-        <v>-6433.807900040001</v>
+        <v>-2269.84513997</v>
       </c>
       <c r="G14" t="n">
-        <v>-2269.82829864</v>
+        <v>-3003.78359303</v>
       </c>
       <c r="H14" t="n">
-        <v>-3003.79887517</v>
+        <v>-6021.93955622</v>
       </c>
       <c r="I14" t="n">
-        <v>-6021.936051839999</v>
+        <v>-8049.94423817</v>
       </c>
       <c r="J14" t="n">
-        <v>-8049.950096809999</v>
+        <v>-11793.53571359</v>
       </c>
       <c r="K14" t="n">
-        <v>-11793.52532823</v>
+        <v>-5709.79791283</v>
       </c>
       <c r="L14" t="n">
-        <v>-5709.79689543</v>
+        <v>-682.4450672300004</v>
       </c>
       <c r="M14" t="n">
-        <v>-682.4340131200005</v>
+        <v>-4494.947423600001</v>
       </c>
     </row>
     <row r="15">
@@ -1042,37 +1038,37 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>1289.14150812</v>
+        <v>785.9075450199999</v>
       </c>
       <c r="D15" t="n">
-        <v>785.59069522</v>
+        <v>597.56706706</v>
       </c>
       <c r="E15" t="n">
-        <v>597.1110878</v>
+        <v>-55.82149363999999</v>
       </c>
       <c r="F15" t="n">
-        <v>-56.41452704999998</v>
+        <v>767.96032906</v>
       </c>
       <c r="G15" t="n">
-        <v>767.40585058</v>
+        <v>424.02397229</v>
       </c>
       <c r="H15" t="n">
-        <v>423.69385963</v>
+        <v>575.7483816</v>
       </c>
       <c r="I15" t="n">
-        <v>575.51332106</v>
+        <v>493.0651961</v>
       </c>
       <c r="J15" t="n">
-        <v>492.70111098</v>
+        <v>2.393348989999978</v>
       </c>
       <c r="K15" t="n">
-        <v>1.909775269999973</v>
+        <v>140.80085853</v>
       </c>
       <c r="L15" t="n">
-        <v>140.65200284</v>
+        <v>-526.47618612</v>
       </c>
       <c r="M15" t="n">
-        <v>-526.73016978</v>
+        <v>-85.15016720999999</v>
       </c>
     </row>
     <row r="16">
@@ -1083,37 +1079,37 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>574.4144663300001</v>
+        <v>214.83832883</v>
       </c>
       <c r="D16" t="n">
-        <v>183.03776191</v>
+        <v>37.86505968999997</v>
       </c>
       <c r="E16" t="n">
-        <v>39.86543381</v>
+        <v>-478.29208159</v>
       </c>
       <c r="F16" t="n">
-        <v>-272.42137909</v>
+        <v>120.78985269</v>
       </c>
       <c r="G16" t="n">
-        <v>502.37758097</v>
+        <v>-264.1486009</v>
       </c>
       <c r="H16" t="n">
-        <v>-105.01844</v>
+        <v>-215.14933885</v>
       </c>
       <c r="I16" t="n">
-        <v>-165.18720851</v>
+        <v>-38.16499436</v>
       </c>
       <c r="J16" t="n">
-        <v>-58.06536476999999</v>
+        <v>197.35254887</v>
       </c>
       <c r="K16" t="n">
-        <v>258.60728782</v>
+        <v>-366.17817746</v>
       </c>
       <c r="L16" t="n">
-        <v>-380.87343823</v>
+        <v>-207.15442516</v>
       </c>
       <c r="M16" t="n">
-        <v>-216.09828325</v>
+        <v>219.69826482</v>
       </c>
     </row>
     <row r="17">
@@ -1124,37 +1120,37 @@
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
-        <v>0.09921713</v>
+        <v>0.12858354</v>
       </c>
       <c r="D17" t="n">
-        <v>0.00181601</v>
+        <v>-0.26640583</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0470121</v>
+        <v>-0.55064815</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.10620948</v>
+        <v>0.02769861000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.12663608</v>
+        <v>0.34979235</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.12881972</v>
+        <v>0.55659024</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.11435322</v>
+        <v>0.56842657</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.10262431</v>
+        <v>0.62029989</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.09241648</v>
+        <v>0.79269335</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.03466036</v>
+        <v>1.35239712</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.04070153</v>
+        <v>2.728404</v>
       </c>
     </row>
     <row r="18">
@@ -1165,37 +1161,37 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>343.07053434</v>
+        <v>514.5168238700001</v>
       </c>
       <c r="D18" t="n">
-        <v>514.5168238700001</v>
+        <v>533.24000686</v>
       </c>
       <c r="E18" t="n">
-        <v>533.24000686</v>
+        <v>338.87725289</v>
       </c>
       <c r="F18" t="n">
-        <v>338.87725289</v>
+        <v>494.0830853900001</v>
       </c>
       <c r="G18" t="n">
-        <v>494.0830853900001</v>
+        <v>317.7273254</v>
       </c>
       <c r="H18" t="n">
-        <v>317.7273254</v>
+        <v>283.6058508000001</v>
       </c>
       <c r="I18" t="n">
-        <v>283.6058508000001</v>
+        <v>797.0432088700001</v>
       </c>
       <c r="J18" t="n">
-        <v>797.0432088700001</v>
+        <v>-142.28295233</v>
       </c>
       <c r="K18" t="n">
-        <v>-142.28295233</v>
+        <v>949.17323245</v>
       </c>
       <c r="L18" t="n">
-        <v>949.17323245</v>
+        <v>786.6830428600001</v>
       </c>
       <c r="M18" t="n">
-        <v>786.6830428600001</v>
+        <v>-272.85884179</v>
       </c>
     </row>
     <row r="19">
@@ -1206,37 +1202,37 @@
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>-9.12601766</v>
+        <v>-15.49992431</v>
       </c>
       <c r="D19" t="n">
-        <v>-15.37315678</v>
+        <v>-9.88241236</v>
       </c>
       <c r="E19" t="n">
-        <v>-10.10180609</v>
+        <v>-14.82229246</v>
       </c>
       <c r="F19" t="n">
-        <v>-15.26673113</v>
+        <v>-9.676539879999998</v>
       </c>
       <c r="G19" t="n">
-        <v>-9.522205189999999</v>
+        <v>-12.01174231</v>
       </c>
       <c r="H19" t="n">
-        <v>-11.53313024</v>
+        <v>-11.46147546</v>
       </c>
       <c r="I19" t="n">
-        <v>-10.790532</v>
+        <v>-4.65901074</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.98795986</v>
+        <v>-9.6175397</v>
       </c>
       <c r="K19" t="n">
-        <v>-8.904823329999999</v>
+        <v>-3.18361447</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.35626076</v>
+        <v>-6.06011432</v>
       </c>
       <c r="M19" t="n">
-        <v>-4.66701567</v>
+        <v>-6.603619350000001</v>
       </c>
     </row>
     <row r="20">
@@ -1247,37 +1243,37 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>24.76270936</v>
+        <v>7.97299625</v>
       </c>
       <c r="D20" t="n">
-        <v>7.97299625</v>
+        <v>19.83993459</v>
       </c>
       <c r="E20" t="n">
-        <v>19.83993459</v>
+        <v>5.16841279</v>
       </c>
       <c r="F20" t="n">
-        <v>5.16841279</v>
+        <v>34.60344654</v>
       </c>
       <c r="G20" t="n">
-        <v>34.60344654</v>
+        <v>39.71568626000001</v>
       </c>
       <c r="H20" t="n">
-        <v>39.71568626000001</v>
+        <v>46.16644797999999</v>
       </c>
       <c r="I20" t="n">
-        <v>46.16644797999999</v>
+        <v>49.78897659</v>
       </c>
       <c r="J20" t="n">
-        <v>49.78897659</v>
+        <v>15.83594655</v>
       </c>
       <c r="K20" t="n">
-        <v>15.83594655</v>
+        <v>43.34008297</v>
       </c>
       <c r="L20" t="n">
-        <v>43.34008297</v>
+        <v>-20.57462681</v>
       </c>
       <c r="M20" t="n">
-        <v>-20.57462681</v>
+        <v>-26.64046678</v>
       </c>
     </row>
     <row r="21">
@@ -1288,37 +1284,37 @@
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
-        <v>2.56037766</v>
+        <v>2.43208974</v>
       </c>
       <c r="D21" t="n">
-        <v>2.43208269</v>
+        <v>1.63599599</v>
       </c>
       <c r="E21" t="n">
-        <v>1.6359992</v>
+        <v>-4.00738585</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.00741161</v>
+        <v>-3.14724232</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.14728261</v>
+        <v>0.02344989000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>0.02342975000000012</v>
+        <v>-0.5171800299999999</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.51720213</v>
+        <v>0.5340939699999999</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5341018799999999</v>
+        <v>-1.83215267</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.83215981</v>
+        <v>0.3099200500000001</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3099193600000001</v>
+        <v>-0.9929724099999999</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9929858899999999</v>
+        <v>2.02429566</v>
       </c>
     </row>
     <row r="22">
@@ -1329,37 +1325,37 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>-1.97520458</v>
+        <v>-1.0244927</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0244927</v>
+        <v>-0.6595057899999999</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6595057899999999</v>
+        <v>-1.09703113</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.09703113</v>
+        <v>-1.32421772</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.32421772</v>
+        <v>-1.19789102</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.19789102</v>
+        <v>-0.22544212</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.22544212</v>
+        <v>0.34446533</v>
       </c>
       <c r="J22" t="n">
-        <v>0.34446533</v>
+        <v>0.34050782</v>
       </c>
       <c r="K22" t="n">
-        <v>0.34050782</v>
+        <v>0.8254902999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>0.8254902999999999</v>
+        <v>0.9942745200000001</v>
       </c>
       <c r="M22" t="n">
-        <v>0.9942745200000001</v>
+        <v>1.48964297</v>
       </c>
     </row>
     <row r="23">
@@ -1370,37 +1366,37 @@
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
-        <v>7.199305039999998</v>
+        <v>5.973501690000004</v>
       </c>
       <c r="D23" t="n">
-        <v>5.973501690000004</v>
+        <v>-19.30938348</v>
       </c>
       <c r="E23" t="n">
-        <v>-19.30938348</v>
+        <v>-47.97882261</v>
       </c>
       <c r="F23" t="n">
-        <v>-47.97882261</v>
+        <v>8.745241110000002</v>
       </c>
       <c r="G23" t="n">
-        <v>8.745241110000002</v>
+        <v>27.49038917</v>
       </c>
       <c r="H23" t="n">
-        <v>27.49038917</v>
+        <v>16.16811983</v>
       </c>
       <c r="I23" t="n">
-        <v>16.16811983</v>
+        <v>-1.360895950000001</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.360895950000001</v>
+        <v>-43.29145326</v>
       </c>
       <c r="K23" t="n">
-        <v>-43.29145326</v>
+        <v>-21.43741021</v>
       </c>
       <c r="L23" t="n">
-        <v>-21.43741021</v>
+        <v>-26.59232129</v>
       </c>
       <c r="M23" t="n">
-        <v>-26.59232129</v>
+        <v>-11.85148476</v>
       </c>
     </row>
     <row r="24">
@@ -1409,39 +1405,41 @@
           <t>建材營造右下</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
       <c r="C24" t="n">
-        <v>-17.68025344</v>
+        <v>-3.911297130000002</v>
       </c>
       <c r="D24" t="n">
-        <v>12.14566036</v>
+        <v>-15.46504402</v>
       </c>
       <c r="E24" t="n">
-        <v>12.60496075</v>
+        <v>-61.87304864</v>
       </c>
       <c r="F24" t="n">
-        <v>-13.28790449999999</v>
+        <v>-67.5022307</v>
       </c>
       <c r="G24" t="n">
-        <v>-27.78802093</v>
+        <v>-80.79731274</v>
       </c>
       <c r="H24" t="n">
-        <v>-64.10408142999999</v>
+        <v>-81.7727792</v>
       </c>
       <c r="I24" t="n">
-        <v>-80.14216914000001</v>
+        <v>-79.22005263000001</v>
       </c>
       <c r="J24" t="n">
-        <v>-91.37586913000001</v>
+        <v>-82.78374704000001</v>
       </c>
       <c r="K24" t="n">
-        <v>-102.78971623</v>
+        <v>-54.01685006</v>
       </c>
       <c r="L24" t="n">
-        <v>-64.27183072</v>
+        <v>-34.59311788</v>
       </c>
       <c r="M24" t="n">
-        <v>-51.47628779</v>
+        <v>4.853175940000001</v>
       </c>
     </row>
     <row r="25">
@@ -1452,37 +1450,37 @@
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>91.54239308</v>
+        <v>36.513033</v>
       </c>
       <c r="D25" t="n">
-        <v>20.71448455</v>
+        <v>58.36001469999999</v>
       </c>
       <c r="E25" t="n">
-        <v>30.23455397</v>
+        <v>24.46986895000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-24.16343742</v>
+        <v>83.05171048000001</v>
       </c>
       <c r="G25" t="n">
-        <v>43.51571899</v>
+        <v>36.59002219999999</v>
       </c>
       <c r="H25" t="n">
-        <v>20.16268498</v>
+        <v>-16.21405976</v>
       </c>
       <c r="I25" t="n">
-        <v>-17.54900672</v>
+        <v>-59.42012654</v>
       </c>
       <c r="J25" t="n">
-        <v>-47.07229194999999</v>
+        <v>-96.51404439</v>
       </c>
       <c r="K25" t="n">
-        <v>-76.4608657</v>
+        <v>-66.26645638000001</v>
       </c>
       <c r="L25" t="n">
-        <v>-55.89865595000001</v>
+        <v>-88.72979714</v>
       </c>
       <c r="M25" t="n">
-        <v>-71.80397762</v>
+        <v>-14.44773436</v>
       </c>
     </row>
     <row r="26">
@@ -1493,37 +1491,37 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>96.53054100000001</v>
+        <v>137.02059128</v>
       </c>
       <c r="D26" t="n">
-        <v>137.02059128</v>
+        <v>80.11023591</v>
       </c>
       <c r="E26" t="n">
-        <v>80.11023591</v>
+        <v>14.96755027</v>
       </c>
       <c r="F26" t="n">
-        <v>14.96755027</v>
+        <v>60.78673921</v>
       </c>
       <c r="G26" t="n">
-        <v>60.78673921</v>
+        <v>106.4159577</v>
       </c>
       <c r="H26" t="n">
-        <v>106.4159577</v>
+        <v>30.45080732</v>
       </c>
       <c r="I26" t="n">
-        <v>30.45080732</v>
+        <v>27.11465835</v>
       </c>
       <c r="J26" t="n">
-        <v>27.11465835</v>
+        <v>-15.9721707</v>
       </c>
       <c r="K26" t="n">
-        <v>-15.9721707</v>
+        <v>-11.47404628</v>
       </c>
       <c r="L26" t="n">
-        <v>-11.47404628</v>
+        <v>-0.59206841</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.59206841</v>
+        <v>20.2350177</v>
       </c>
     </row>
     <row r="27">
@@ -1532,39 +1530,41 @@
           <t>數位雲端右下</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
       <c r="C27" t="n">
-        <v>15.88582579</v>
+        <v>15.98260868</v>
       </c>
       <c r="D27" t="n">
-        <v>15.98242234</v>
+        <v>5.80081306</v>
       </c>
       <c r="E27" t="n">
-        <v>5.7988271</v>
+        <v>-5.07146912</v>
       </c>
       <c r="F27" t="n">
-        <v>-5.0766208</v>
+        <v>19.81744912</v>
       </c>
       <c r="G27" t="n">
-        <v>19.81470604</v>
+        <v>26.50836019999999</v>
       </c>
       <c r="H27" t="n">
-        <v>26.50384610999999</v>
+        <v>12.37337787</v>
       </c>
       <c r="I27" t="n">
-        <v>12.3678567</v>
+        <v>16.88589567</v>
       </c>
       <c r="J27" t="n">
-        <v>16.88242132</v>
+        <v>5.175073139999999</v>
       </c>
       <c r="K27" t="n">
-        <v>5.169652749999999</v>
+        <v>10.2050075</v>
       </c>
       <c r="L27" t="n">
-        <v>10.18806125</v>
+        <v>5.18855116</v>
       </c>
       <c r="M27" t="n">
-        <v>5.148170700000001</v>
+        <v>12.3688821</v>
       </c>
     </row>
     <row r="28">
@@ -1575,37 +1575,37 @@
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>1.05148289</v>
+        <v>0.15505805</v>
       </c>
       <c r="D28" t="n">
-        <v>0.15727784</v>
+        <v>-0.39483859</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.39045239</v>
+        <v>-0.53778595</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.5318428399999999</v>
+        <v>-0.26137895</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.25765854</v>
+        <v>-0.52308184</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.5159487899999999</v>
+        <v>-0.20881999</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.20053678</v>
+        <v>-0.3587911</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.35401137</v>
+        <v>-0.39895759</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.3935179</v>
+        <v>-0.11373782</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.09701660000000001</v>
+        <v>-0.18190578</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.14210904</v>
+        <v>-0.09283578000000001</v>
       </c>
     </row>
     <row r="29">
@@ -1616,37 +1616,37 @@
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>-0.01768001</v>
+        <v>-0.03888696</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.03888696</v>
+        <v>-0.03401444999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.03401444999999999</v>
+        <v>-0.03154172</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.03154172</v>
+        <v>-0.01295868</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.01295868</v>
+        <v>-0.00221319</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.00221319</v>
+        <v>-0.00056724</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.00056724</v>
+        <v>0.00672136</v>
       </c>
       <c r="J29" t="n">
-        <v>0.00672136</v>
+        <v>-0.00145954</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.00145954</v>
+        <v>0.006492230000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>0.006492230000000001</v>
+        <v>0.01229479</v>
       </c>
       <c r="M29" t="n">
-        <v>0.01229479</v>
+        <v>0.01976942</v>
       </c>
     </row>
     <row r="30">
@@ -1657,37 +1657,37 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>-0.01583309</v>
+        <v>-0.01467411</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.01467411</v>
+        <v>-0.006610240000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.006610240000000001</v>
+        <v>-0.0134701</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.0134701</v>
+        <v>-0.0001509699999999998</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.0001509699999999998</v>
+        <v>-0.00248782</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.00248782</v>
+        <v>0.00563157</v>
       </c>
       <c r="I30" t="n">
-        <v>0.00563157</v>
+        <v>0.0038025</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0038025</v>
+        <v>-0.0011534</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.0011534</v>
+        <v>0.00062989</v>
       </c>
       <c r="L30" t="n">
-        <v>0.00062989</v>
+        <v>-0.005775890000000001</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.005775890000000001</v>
+        <v>0.0001075200000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1698,37 +1698,37 @@
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>-0.09526194</v>
+        <v>-0.14618367</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.14618367</v>
+        <v>-0.15061427</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.15061427</v>
+        <v>-0.21081572</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.21081572</v>
+        <v>0.03445644</v>
       </c>
       <c r="G31" t="n">
-        <v>0.03445644</v>
+        <v>-0.0509551</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.0509551</v>
+        <v>0.04199869000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>0.04199869000000001</v>
+        <v>0.005081129999999999</v>
       </c>
       <c r="J31" t="n">
-        <v>0.005081129999999999</v>
+        <v>-0.04898686</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.04898686</v>
+        <v>-0.07565420999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.07565420999999999</v>
+        <v>0.03133109000000001</v>
       </c>
       <c r="M31" t="n">
-        <v>0.03133109000000001</v>
+        <v>-0.00056753</v>
       </c>
     </row>
     <row r="32">
@@ -1739,37 +1739,37 @@
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>1.46103388</v>
+        <v>2.14088619</v>
       </c>
       <c r="D32" t="n">
-        <v>2.14088619</v>
+        <v>-0.19341137</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.19341137</v>
+        <v>-1.58173283</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.58173283</v>
+        <v>0.79667627</v>
       </c>
       <c r="G32" t="n">
-        <v>0.79667627</v>
+        <v>-0.8938292</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.8938292</v>
+        <v>0.26859018</v>
       </c>
       <c r="I32" t="n">
-        <v>0.26859018</v>
+        <v>-1.1550498</v>
       </c>
       <c r="J32" t="n">
-        <v>-1.1550498</v>
+        <v>0.19597777</v>
       </c>
       <c r="K32" t="n">
-        <v>0.19597777</v>
+        <v>0.93832401</v>
       </c>
       <c r="L32" t="n">
-        <v>0.93832401</v>
+        <v>-0.60581137</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.60581137</v>
+        <v>-0.18124846</v>
       </c>
     </row>
     <row r="33">
@@ -1780,37 +1780,37 @@
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
-        <v>59.56377501</v>
+        <v>26.07414317</v>
       </c>
       <c r="D33" t="n">
-        <v>26.07414317</v>
+        <v>46.49768424000001</v>
       </c>
       <c r="E33" t="n">
-        <v>46.49768424000001</v>
+        <v>1.71917202</v>
       </c>
       <c r="F33" t="n">
-        <v>1.71917202</v>
+        <v>51.11736981</v>
       </c>
       <c r="G33" t="n">
-        <v>51.11736981</v>
+        <v>74.52305657000001</v>
       </c>
       <c r="H33" t="n">
-        <v>74.52305657000001</v>
+        <v>28.77819571</v>
       </c>
       <c r="I33" t="n">
-        <v>28.77819571</v>
+        <v>47.13405325</v>
       </c>
       <c r="J33" t="n">
-        <v>47.13405325</v>
+        <v>17.62821512</v>
       </c>
       <c r="K33" t="n">
-        <v>17.62821512</v>
+        <v>9.357429240000002</v>
       </c>
       <c r="L33" t="n">
-        <v>9.357429240000002</v>
+        <v>-23.28926443</v>
       </c>
       <c r="M33" t="n">
-        <v>-23.28926443</v>
+        <v>-15.50397747</v>
       </c>
     </row>
     <row r="34">
@@ -1821,37 +1821,37 @@
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
-        <v>1.19789814</v>
+        <v>1.28537791</v>
       </c>
       <c r="D34" t="n">
-        <v>1.28537791</v>
+        <v>0.6885503099999999</v>
       </c>
       <c r="E34" t="n">
-        <v>0.6885503099999999</v>
+        <v>0.03085148000000001</v>
       </c>
       <c r="F34" t="n">
-        <v>0.03085148000000001</v>
+        <v>0.6241331099999999</v>
       </c>
       <c r="G34" t="n">
-        <v>0.6241331099999999</v>
+        <v>0.6281405</v>
       </c>
       <c r="H34" t="n">
-        <v>0.6281405</v>
+        <v>0.5322796400000001</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5322796400000001</v>
+        <v>0.66688402</v>
       </c>
       <c r="J34" t="n">
-        <v>0.66688402</v>
+        <v>0.39455165</v>
       </c>
       <c r="K34" t="n">
-        <v>0.39455165</v>
+        <v>0.7616216099999999</v>
       </c>
       <c r="L34" t="n">
-        <v>0.7616216099999999</v>
+        <v>0.68170787</v>
       </c>
       <c r="M34" t="n">
-        <v>0.68170787</v>
+        <v>0.03184879000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1862,37 +1862,37 @@
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
-        <v>-158.616183</v>
+        <v>-32.78750292</v>
       </c>
       <c r="D35" t="n">
-        <v>-32.78750292</v>
+        <v>29.79901899</v>
       </c>
       <c r="E35" t="n">
-        <v>29.79901899</v>
+        <v>191.1411963</v>
       </c>
       <c r="F35" t="n">
-        <v>191.1411963</v>
+        <v>281.70180355</v>
       </c>
       <c r="G35" t="n">
-        <v>281.70180355</v>
+        <v>169.91598432</v>
       </c>
       <c r="H35" t="n">
-        <v>169.91598432</v>
+        <v>151.94936306</v>
       </c>
       <c r="I35" t="n">
-        <v>151.94936306</v>
+        <v>180.3735272</v>
       </c>
       <c r="J35" t="n">
-        <v>180.3735272</v>
+        <v>110.71375524</v>
       </c>
       <c r="K35" t="n">
-        <v>110.71375524</v>
+        <v>152.65296865</v>
       </c>
       <c r="L35" t="n">
-        <v>152.65296865</v>
+        <v>75.59350051</v>
       </c>
       <c r="M35" t="n">
-        <v>75.59350051</v>
+        <v>33.17521386</v>
       </c>
     </row>
     <row r="36">
@@ -1903,37 +1903,37 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>11.69872803</v>
+        <v>44.72266871</v>
       </c>
       <c r="D36" t="n">
-        <v>44.72266871</v>
+        <v>57.7183895</v>
       </c>
       <c r="E36" t="n">
-        <v>57.7183895</v>
+        <v>16.06229448</v>
       </c>
       <c r="F36" t="n">
-        <v>16.06229448</v>
+        <v>64.33256663</v>
       </c>
       <c r="G36" t="n">
-        <v>64.33256663</v>
+        <v>10.04559587</v>
       </c>
       <c r="H36" t="n">
-        <v>10.04559587</v>
+        <v>-26.98847005</v>
       </c>
       <c r="I36" t="n">
-        <v>-26.98847005</v>
+        <v>-56.02270716</v>
       </c>
       <c r="J36" t="n">
-        <v>-56.02270716</v>
+        <v>-66.06686309</v>
       </c>
       <c r="K36" t="n">
-        <v>-66.06686309</v>
+        <v>-35.53463518</v>
       </c>
       <c r="L36" t="n">
-        <v>-35.53463518</v>
+        <v>5.89095571</v>
       </c>
       <c r="M36" t="n">
-        <v>5.89095571</v>
+        <v>-9.68118084</v>
       </c>
     </row>
     <row r="37">
@@ -1944,37 +1944,37 @@
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>11.51803531</v>
+        <v>52.08126556000001</v>
       </c>
       <c r="D37" t="n">
-        <v>56.16649016</v>
+        <v>41.51401431</v>
       </c>
       <c r="E37" t="n">
-        <v>46.18684118</v>
+        <v>-11.49951154</v>
       </c>
       <c r="F37" t="n">
-        <v>-10.93528</v>
+        <v>80.82614101</v>
       </c>
       <c r="G37" t="n">
-        <v>82.55782090000001</v>
+        <v>66.01691722999999</v>
       </c>
       <c r="H37" t="n">
-        <v>68.09249739999998</v>
+        <v>48.47841772</v>
       </c>
       <c r="I37" t="n">
-        <v>48.2288916</v>
+        <v>53.14321922</v>
       </c>
       <c r="J37" t="n">
-        <v>51.51172708</v>
+        <v>29.27277965</v>
       </c>
       <c r="K37" t="n">
-        <v>26.68500857</v>
+        <v>73.12264562</v>
       </c>
       <c r="L37" t="n">
-        <v>72.13048381</v>
+        <v>-12.08264623</v>
       </c>
       <c r="M37" t="n">
-        <v>-15.6013143</v>
+        <v>14.60630841</v>
       </c>
     </row>
     <row r="38">
@@ -1985,37 +1985,37 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>54.56274334</v>
+        <v>17.92583462</v>
       </c>
       <c r="D38" t="n">
-        <v>13.84061002</v>
+        <v>76.40466408</v>
       </c>
       <c r="E38" t="n">
-        <v>71.73183721000001</v>
+        <v>-66.09117928999999</v>
       </c>
       <c r="F38" t="n">
-        <v>-66.65541082999999</v>
+        <v>33.53088707</v>
       </c>
       <c r="G38" t="n">
-        <v>31.79920718</v>
+        <v>48.96045531</v>
       </c>
       <c r="H38" t="n">
-        <v>46.88487514</v>
+        <v>3.12731607</v>
       </c>
       <c r="I38" t="n">
-        <v>3.376842190000001</v>
+        <v>-31.92339557</v>
       </c>
       <c r="J38" t="n">
-        <v>-30.29190343</v>
+        <v>-64.28269378</v>
       </c>
       <c r="K38" t="n">
-        <v>-61.69492270000001</v>
+        <v>-3.518179410000001</v>
       </c>
       <c r="L38" t="n">
-        <v>-2.526017600000001</v>
+        <v>-37.97274526</v>
       </c>
       <c r="M38" t="n">
-        <v>-34.45407719</v>
+        <v>-7.511398109999999</v>
       </c>
     </row>
     <row r="39">
@@ -2026,37 +2026,37 @@
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
-        <v>1.21801833</v>
+        <v>31.88991085</v>
       </c>
       <c r="D39" t="n">
-        <v>33.36404843</v>
+        <v>38.42099165</v>
       </c>
       <c r="E39" t="n">
-        <v>40.54742183</v>
+        <v>11.11791429</v>
       </c>
       <c r="F39" t="n">
-        <v>12.34076062</v>
+        <v>32.60895456999999</v>
       </c>
       <c r="G39" t="n">
-        <v>34.05617272</v>
+        <v>56.67209458</v>
       </c>
       <c r="H39" t="n">
-        <v>58.04914093</v>
+        <v>17.94407397</v>
       </c>
       <c r="I39" t="n">
-        <v>21.56711507</v>
+        <v>33.68792604</v>
       </c>
       <c r="J39" t="n">
-        <v>37.4368935</v>
+        <v>4.108083939999999</v>
       </c>
       <c r="K39" t="n">
-        <v>6.89583663</v>
+        <v>73.39446294</v>
       </c>
       <c r="L39" t="n">
-        <v>75.56064378000001</v>
+        <v>168.35310772</v>
       </c>
       <c r="M39" t="n">
-        <v>169.94903149</v>
+        <v>54.65563677999999</v>
       </c>
     </row>
     <row r="40">
@@ -2067,37 +2067,37 @@
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>13.72143673</v>
+        <v>15.27198214</v>
       </c>
       <c r="D40" t="n">
-        <v>13.79784456</v>
+        <v>18.70547509</v>
       </c>
       <c r="E40" t="n">
-        <v>16.57904491</v>
+        <v>6.664288</v>
       </c>
       <c r="F40" t="n">
-        <v>5.44144167</v>
+        <v>7.2135412</v>
       </c>
       <c r="G40" t="n">
-        <v>5.76632305</v>
+        <v>0.08460432999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.29244202</v>
+        <v>-3.21255832</v>
       </c>
       <c r="I40" t="n">
-        <v>-6.83559942</v>
+        <v>-6.40072734</v>
       </c>
       <c r="J40" t="n">
-        <v>-10.1496948</v>
+        <v>-3.77333719</v>
       </c>
       <c r="K40" t="n">
-        <v>-6.561089880000001</v>
+        <v>1.57257904</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.5936018000000001</v>
+        <v>-2.42404502</v>
       </c>
       <c r="M40" t="n">
-        <v>-4.01996879</v>
+        <v>-1.22188635</v>
       </c>
     </row>
     <row r="41">
@@ -2108,37 +2108,37 @@
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
-        <v>-60.12340589</v>
+        <v>-78.61716095999999</v>
       </c>
       <c r="D41" t="n">
-        <v>-78.61716095999999</v>
+        <v>-63.09958463</v>
       </c>
       <c r="E41" t="n">
-        <v>-63.09958463</v>
+        <v>-76.87109083</v>
       </c>
       <c r="F41" t="n">
-        <v>-76.87109083</v>
+        <v>85.15477465000001</v>
       </c>
       <c r="G41" t="n">
-        <v>85.15477465000001</v>
+        <v>307.60971191</v>
       </c>
       <c r="H41" t="n">
-        <v>307.60971191</v>
+        <v>433.81361385</v>
       </c>
       <c r="I41" t="n">
-        <v>433.81361385</v>
+        <v>668.62466564</v>
       </c>
       <c r="J41" t="n">
-        <v>668.62466564</v>
+        <v>244.91801602</v>
       </c>
       <c r="K41" t="n">
-        <v>244.91801602</v>
+        <v>320.90370974</v>
       </c>
       <c r="L41" t="n">
-        <v>320.90370974</v>
+        <v>479.18507195</v>
       </c>
       <c r="M41" t="n">
-        <v>479.18507195</v>
+        <v>759.412483</v>
       </c>
     </row>
     <row r="42">
@@ -2149,37 +2149,37 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>3.43977374</v>
+        <v>2.38658788</v>
       </c>
       <c r="D42" t="n">
-        <v>2.38658788</v>
+        <v>2.76879612</v>
       </c>
       <c r="E42" t="n">
-        <v>2.76879612</v>
+        <v>1.39195655</v>
       </c>
       <c r="F42" t="n">
-        <v>1.39195655</v>
+        <v>3.33996648</v>
       </c>
       <c r="G42" t="n">
-        <v>3.33996648</v>
+        <v>4.04519709</v>
       </c>
       <c r="H42" t="n">
-        <v>4.04519709</v>
+        <v>4.39753474</v>
       </c>
       <c r="I42" t="n">
-        <v>4.39753474</v>
+        <v>5.01754811</v>
       </c>
       <c r="J42" t="n">
-        <v>5.01754811</v>
+        <v>5.69713828</v>
       </c>
       <c r="K42" t="n">
-        <v>5.69713828</v>
+        <v>14.7458941</v>
       </c>
       <c r="L42" t="n">
-        <v>14.7458941</v>
+        <v>7.43637919</v>
       </c>
       <c r="M42" t="n">
-        <v>7.43637919</v>
+        <v>9.030643980000001</v>
       </c>
     </row>
     <row r="43">
@@ -2190,37 +2190,37 @@
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
-        <v>0.77833895</v>
+        <v>-0.64378347</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.64378347</v>
+        <v>-0.38199066</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.38199066</v>
+        <v>-1.4309121</v>
       </c>
       <c r="F43" t="n">
-        <v>-1.4309121</v>
+        <v>1.94254906</v>
       </c>
       <c r="G43" t="n">
-        <v>1.94254906</v>
+        <v>9.474221210000001</v>
       </c>
       <c r="H43" t="n">
-        <v>9.474221210000001</v>
+        <v>3.52060646</v>
       </c>
       <c r="I43" t="n">
-        <v>3.52060646</v>
+        <v>7.11610011</v>
       </c>
       <c r="J43" t="n">
-        <v>7.11610011</v>
+        <v>3.20700107</v>
       </c>
       <c r="K43" t="n">
-        <v>3.20700107</v>
+        <v>1.61384816</v>
       </c>
       <c r="L43" t="n">
-        <v>1.61384816</v>
+        <v>0.5450071499999999</v>
       </c>
       <c r="M43" t="n">
-        <v>0.5450071499999999</v>
+        <v>2.44174181</v>
       </c>
     </row>
     <row r="44">
@@ -2231,37 +2231,37 @@
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>108.72090109</v>
+        <v>190.33483352</v>
       </c>
       <c r="D44" t="n">
-        <v>190.33483352</v>
+        <v>121.65825754</v>
       </c>
       <c r="E44" t="n">
-        <v>121.65825754</v>
+        <v>-30.99881446</v>
       </c>
       <c r="F44" t="n">
-        <v>-30.99881446</v>
+        <v>87.01359362000001</v>
       </c>
       <c r="G44" t="n">
-        <v>87.01359362000001</v>
+        <v>69.61852187000001</v>
       </c>
       <c r="H44" t="n">
-        <v>69.61852187000001</v>
+        <v>-24.77563102</v>
       </c>
       <c r="I44" t="n">
-        <v>-24.77563102</v>
+        <v>12.27685316</v>
       </c>
       <c r="J44" t="n">
-        <v>12.27685316</v>
+        <v>-117.81225534</v>
       </c>
       <c r="K44" t="n">
-        <v>-117.81225534</v>
+        <v>-107.77603948</v>
       </c>
       <c r="L44" t="n">
-        <v>-107.77603948</v>
+        <v>-42.36237779</v>
       </c>
       <c r="M44" t="n">
-        <v>-42.36237779</v>
+        <v>71.38909197</v>
       </c>
     </row>
     <row r="45">
@@ -2274,37 +2274,37 @@
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>96.32136340000001</v>
+        <v>53.14560842</v>
       </c>
       <c r="D45" t="n">
-        <v>63.91983587999999</v>
+        <v>-29.26108884000001</v>
       </c>
       <c r="E45" t="n">
-        <v>-19.92177758</v>
+        <v>-597.49573645</v>
       </c>
       <c r="F45" t="n">
-        <v>-586.16837607</v>
+        <v>-104.10864394</v>
       </c>
       <c r="G45" t="n">
-        <v>-93.00898807999998</v>
+        <v>141.14766511</v>
       </c>
       <c r="H45" t="n">
-        <v>149.01439169</v>
+        <v>272.19530525</v>
       </c>
       <c r="I45" t="n">
-        <v>278.1995933</v>
+        <v>-26.17901317</v>
       </c>
       <c r="J45" t="n">
-        <v>-18.26627923</v>
+        <v>-232.600864</v>
       </c>
       <c r="K45" t="n">
-        <v>-227.26252445</v>
+        <v>-348.26249207</v>
       </c>
       <c r="L45" t="n">
-        <v>-345.47236651</v>
+        <v>-324.45211075</v>
       </c>
       <c r="M45" t="n">
-        <v>-323.12190539</v>
+        <v>-311.36017096</v>
       </c>
     </row>
     <row r="46">
@@ -2315,37 +2315,37 @@
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>116.67126073</v>
+        <v>62.95070912999999</v>
       </c>
       <c r="D46" t="n">
-        <v>51.56284805999999</v>
+        <v>6.310727320000001</v>
       </c>
       <c r="E46" t="n">
-        <v>-3.308200009999998</v>
+        <v>-56.74143730999999</v>
       </c>
       <c r="F46" t="n">
-        <v>-67.44318901000001</v>
+        <v>6.502091459999999</v>
       </c>
       <c r="G46" t="n">
-        <v>-4.670221300000001</v>
+        <v>-46.1849935</v>
       </c>
       <c r="H46" t="n">
-        <v>-53.8883098</v>
+        <v>-105.69346251</v>
       </c>
       <c r="I46" t="n">
-        <v>-111.50270141</v>
+        <v>-121.53073867</v>
       </c>
       <c r="J46" t="n">
-        <v>-129.13552162</v>
+        <v>-148.94011808</v>
       </c>
       <c r="K46" t="n">
-        <v>-153.85499081</v>
+        <v>-153.63024872</v>
       </c>
       <c r="L46" t="n">
-        <v>-156.3513999</v>
+        <v>-163.39371761</v>
       </c>
       <c r="M46" t="n">
-        <v>-164.60097871</v>
+        <v>-20.50349563</v>
       </c>
     </row>
     <row r="47">
@@ -2356,37 +2356,37 @@
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>-1.34980283</v>
+        <v>-3.321631309999999</v>
       </c>
       <c r="D47" t="n">
-        <v>-3.32161227</v>
+        <v>-3.11363331</v>
       </c>
       <c r="E47" t="n">
-        <v>-3.11364565</v>
+        <v>-4.72339887</v>
       </c>
       <c r="F47" t="n">
-        <v>-4.72335562</v>
+        <v>-1.49148739</v>
       </c>
       <c r="G47" t="n">
-        <v>-1.49149481</v>
+        <v>2.33220014</v>
       </c>
       <c r="H47" t="n">
-        <v>2.33218234</v>
+        <v>-2.68896906</v>
       </c>
       <c r="I47" t="n">
-        <v>-2.68934393</v>
+        <v>-6.34562959</v>
       </c>
       <c r="J47" t="n">
-        <v>-6.34563964</v>
+        <v>-8.065714099999999</v>
       </c>
       <c r="K47" t="n">
-        <v>-8.06577257</v>
+        <v>-5.8884915</v>
       </c>
       <c r="L47" t="n">
-        <v>-5.88842813</v>
+        <v>-5.95645232</v>
       </c>
       <c r="M47" t="n">
-        <v>-5.95638258</v>
+        <v>-5.16068395</v>
       </c>
     </row>
     <row r="48">
@@ -2397,37 +2397,37 @@
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
-        <v>12.69149004</v>
+        <v>-9.719348770000002</v>
       </c>
       <c r="D48" t="n">
-        <v>-9.719348770000002</v>
+        <v>87.66968166999999</v>
       </c>
       <c r="E48" t="n">
-        <v>87.66968166999999</v>
+        <v>-110.19884231</v>
       </c>
       <c r="F48" t="n">
-        <v>-110.19884231</v>
+        <v>51.74861537</v>
       </c>
       <c r="G48" t="n">
-        <v>51.74861537</v>
+        <v>112.36569676</v>
       </c>
       <c r="H48" t="n">
-        <v>112.36569676</v>
+        <v>53.50560005</v>
       </c>
       <c r="I48" t="n">
-        <v>53.50560005</v>
+        <v>95.05480141</v>
       </c>
       <c r="J48" t="n">
-        <v>95.05480141</v>
+        <v>9.371867360000001</v>
       </c>
       <c r="K48" t="n">
-        <v>9.371867360000001</v>
+        <v>39.77664651000001</v>
       </c>
       <c r="L48" t="n">
-        <v>39.77664651000001</v>
+        <v>5.021144390000001</v>
       </c>
       <c r="M48" t="n">
-        <v>5.021144390000001</v>
+        <v>20.83421519</v>
       </c>
     </row>
     <row r="49">
@@ -2438,37 +2438,37 @@
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>0.76822078</v>
+        <v>0.8912484000000001</v>
       </c>
       <c r="D49" t="n">
-        <v>0.89122936</v>
+        <v>0.7885891500000001</v>
       </c>
       <c r="E49" t="n">
-        <v>0.78860149</v>
+        <v>0.42070623</v>
       </c>
       <c r="F49" t="n">
-        <v>0.42066298</v>
+        <v>0.5480494499999999</v>
       </c>
       <c r="G49" t="n">
-        <v>0.54805687</v>
+        <v>0.34096733</v>
       </c>
       <c r="H49" t="n">
-        <v>0.34098513</v>
+        <v>0.50162335</v>
       </c>
       <c r="I49" t="n">
-        <v>0.5019982199999999</v>
+        <v>0.28499248</v>
       </c>
       <c r="J49" t="n">
-        <v>0.28500253</v>
+        <v>0.06329543000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>0.0633539</v>
+        <v>-0.02356351</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.02362688</v>
+        <v>-0.16403953</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.16410927</v>
+        <v>-0.03927072</v>
       </c>
     </row>
     <row r="50">
@@ -2479,37 +2479,37 @@
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
-        <v>93.7245678</v>
+        <v>32.85024001</v>
       </c>
       <c r="D50" t="n">
-        <v>32.91358118</v>
+        <v>0.2943598800000006</v>
       </c>
       <c r="E50" t="n">
-        <v>0.1132715900000005</v>
+        <v>-39.79114603</v>
       </c>
       <c r="F50" t="n">
-        <v>-39.89386621</v>
+        <v>-25.86812985</v>
       </c>
       <c r="G50" t="n">
-        <v>-25.72227665</v>
+        <v>-15.37702207</v>
       </c>
       <c r="H50" t="n">
-        <v>-15.21344484</v>
+        <v>-21.86573385</v>
       </c>
       <c r="I50" t="n">
-        <v>-21.58523652</v>
+        <v>-5.271030309999998</v>
       </c>
       <c r="J50" t="n">
-        <v>-5.0023913</v>
+        <v>10.19355404</v>
       </c>
       <c r="K50" t="n">
-        <v>10.4383156</v>
+        <v>-56.44455119</v>
       </c>
       <c r="L50" t="n">
-        <v>-56.09961231</v>
+        <v>-46.45714444000001</v>
       </c>
       <c r="M50" t="n">
-        <v>-46.16405787000001</v>
+        <v>-43.83128722999999</v>
       </c>
     </row>
     <row r="51">
@@ -2520,37 +2520,37 @@
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>8.37252496</v>
+        <v>-8.697055900000002</v>
       </c>
       <c r="D51" t="n">
-        <v>-29.51015281</v>
+        <v>7.78556319</v>
       </c>
       <c r="E51" t="n">
-        <v>-34.6721315</v>
+        <v>-26.75564822</v>
       </c>
       <c r="F51" t="n">
-        <v>-69.96659522</v>
+        <v>-29.6747849</v>
       </c>
       <c r="G51" t="n">
-        <v>-69.96006340999999</v>
+        <v>-9.074995439999997</v>
       </c>
       <c r="H51" t="n">
-        <v>-47.35630138</v>
+        <v>-6.02440684</v>
       </c>
       <c r="I51" t="n">
-        <v>-45.2927249</v>
+        <v>-10.76360972</v>
       </c>
       <c r="J51" t="n">
-        <v>-50.38190491</v>
+        <v>-6.295704290000001</v>
       </c>
       <c r="K51" t="n">
-        <v>0.4480022499999993</v>
+        <v>4.70272614</v>
       </c>
       <c r="L51" t="n">
-        <v>-1.855433589999999</v>
+        <v>-5.524311600000001</v>
       </c>
       <c r="M51" t="n">
-        <v>-19.65939032</v>
+        <v>2.53485937</v>
       </c>
     </row>
     <row r="52">
@@ -2561,37 +2561,37 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>-48.83193012</v>
+        <v>-86.09051647</v>
       </c>
       <c r="D52" t="n">
-        <v>-65.34076073</v>
+        <v>-94.17343725000001</v>
       </c>
       <c r="E52" t="n">
-        <v>-51.53465427</v>
+        <v>-90.38974037</v>
       </c>
       <c r="F52" t="n">
-        <v>-47.07607319</v>
+        <v>-46.76736808</v>
       </c>
       <c r="G52" t="n">
-        <v>-6.62794277</v>
+        <v>-18.80448768</v>
       </c>
       <c r="H52" t="n">
-        <v>19.31324103</v>
+        <v>-3.937506679999998</v>
       </c>
       <c r="I52" t="n">
-        <v>35.05031405</v>
+        <v>-28.13410102</v>
       </c>
       <c r="J52" t="n">
-        <v>11.21555516</v>
+        <v>7.48600141</v>
       </c>
       <c r="K52" t="n">
-        <v>0.4975333099999996</v>
+        <v>-7.01302978</v>
       </c>
       <c r="L52" t="n">
-        <v>-0.7998089300000011</v>
+        <v>-24.94529791</v>
       </c>
       <c r="M52" t="n">
-        <v>-11.10330576</v>
+        <v>30.8624361</v>
       </c>
     </row>
     <row r="53">
@@ -2602,37 +2602,37 @@
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>797.8072010300001</v>
+        <v>311.1603595</v>
       </c>
       <c r="D53" t="n">
-        <v>311.1603595</v>
+        <v>48.50273705999999</v>
       </c>
       <c r="E53" t="n">
-        <v>48.50273705999999</v>
+        <v>-201.80258542</v>
       </c>
       <c r="F53" t="n">
-        <v>-201.80258542</v>
+        <v>34.01816414</v>
       </c>
       <c r="G53" t="n">
-        <v>34.01816414</v>
+        <v>305.24566593</v>
       </c>
       <c r="H53" t="n">
-        <v>305.24566593</v>
+        <v>287.84307047</v>
       </c>
       <c r="I53" t="n">
-        <v>287.84307047</v>
+        <v>17.41187099</v>
       </c>
       <c r="J53" t="n">
-        <v>17.41187099</v>
+        <v>-101.62390288</v>
       </c>
       <c r="K53" t="n">
-        <v>-101.62390288</v>
+        <v>10.99956778</v>
       </c>
       <c r="L53" t="n">
-        <v>10.99956778</v>
+        <v>-143.08080159</v>
       </c>
       <c r="M53" t="n">
-        <v>-143.08080159</v>
+        <v>189.49350051</v>
       </c>
     </row>
     <row r="54">
@@ -2643,37 +2643,37 @@
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>-21.14697515</v>
+        <v>-87.98130128</v>
       </c>
       <c r="D54" t="n">
-        <v>-88.26067630000001</v>
+        <v>-131.82160819</v>
       </c>
       <c r="E54" t="n">
-        <v>-131.82460177</v>
+        <v>-186.39584642</v>
       </c>
       <c r="F54" t="n">
-        <v>-186.77167783</v>
+        <v>-23.6370268</v>
       </c>
       <c r="G54" t="n">
-        <v>-23.62684924</v>
+        <v>93.53855481999999</v>
       </c>
       <c r="H54" t="n">
-        <v>94.02638623</v>
+        <v>211.94004658</v>
       </c>
       <c r="I54" t="n">
-        <v>212.92140005</v>
+        <v>90.15219676000001</v>
       </c>
       <c r="J54" t="n">
-        <v>90.77975588000001</v>
+        <v>45.78623981999999</v>
       </c>
       <c r="K54" t="n">
-        <v>45.93233127</v>
+        <v>143.74285746</v>
       </c>
       <c r="L54" t="n">
-        <v>144.17853408</v>
+        <v>11.27958262</v>
       </c>
       <c r="M54" t="n">
-        <v>11.27132376</v>
+        <v>-16.07919225</v>
       </c>
     </row>
     <row r="55">
@@ -2684,37 +2684,37 @@
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>421.21623473</v>
+        <v>271.22984223</v>
       </c>
       <c r="D55" t="n">
-        <v>271.50921725</v>
+        <v>129.3010729</v>
       </c>
       <c r="E55" t="n">
-        <v>129.30406648</v>
+        <v>-60.07452256999999</v>
       </c>
       <c r="F55" t="n">
-        <v>-59.69869116</v>
+        <v>216.25447787</v>
       </c>
       <c r="G55" t="n">
-        <v>216.24430031</v>
+        <v>557.7889049199999</v>
       </c>
       <c r="H55" t="n">
-        <v>557.30107351</v>
+        <v>689.9486379299999</v>
       </c>
       <c r="I55" t="n">
-        <v>688.9672844600001</v>
+        <v>348.99156036</v>
       </c>
       <c r="J55" t="n">
-        <v>348.36400124</v>
+        <v>121.16221999</v>
       </c>
       <c r="K55" t="n">
-        <v>121.01612854</v>
+        <v>88.94171418000001</v>
       </c>
       <c r="L55" t="n">
-        <v>88.50603756</v>
+        <v>-117.22571863</v>
       </c>
       <c r="M55" t="n">
-        <v>-117.21745977</v>
+        <v>78.54214308</v>
       </c>
     </row>
     <row r="56">
@@ -2725,37 +2725,37 @@
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>-0.5950342600000001</v>
+        <v>-21.67176996</v>
       </c>
       <c r="D56" t="n">
-        <v>-21.67183352</v>
+        <v>-33.83319698</v>
       </c>
       <c r="E56" t="n">
-        <v>-33.8333781</v>
+        <v>-16.22676241</v>
       </c>
       <c r="F56" t="n">
-        <v>-16.2270108</v>
+        <v>-8.50384698</v>
       </c>
       <c r="G56" t="n">
-        <v>-8.503983470000001</v>
+        <v>-10.13554798</v>
       </c>
       <c r="H56" t="n">
-        <v>-10.13564548</v>
+        <v>-5.02773301</v>
       </c>
       <c r="I56" t="n">
-        <v>-5.0278013</v>
+        <v>4.61939667</v>
       </c>
       <c r="J56" t="n">
-        <v>4.619251460000001</v>
+        <v>0.32767565</v>
       </c>
       <c r="K56" t="n">
-        <v>0.32751644</v>
+        <v>-1.13437554</v>
       </c>
       <c r="L56" t="n">
-        <v>-1.13427911</v>
+        <v>-9.10632041</v>
       </c>
       <c r="M56" t="n">
-        <v>-9.106385620000001</v>
+        <v>2.08130507</v>
       </c>
     </row>
     <row r="57">
@@ -2766,37 +2766,37 @@
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
-        <v>-1.64724033</v>
+        <v>-2.42438873</v>
       </c>
       <c r="D57" t="n">
-        <v>-18.46042381</v>
+        <v>-1.02980451</v>
       </c>
       <c r="E57" t="n">
-        <v>-8.57775857</v>
+        <v>-2.59555918</v>
       </c>
       <c r="F57" t="n">
-        <v>-12.92365245</v>
+        <v>-0.4973752299999999</v>
       </c>
       <c r="G57" t="n">
-        <v>-2.50102366</v>
+        <v>-3.799829690000001</v>
       </c>
       <c r="H57" t="n">
-        <v>-12.04683458</v>
+        <v>-3.02146857</v>
       </c>
       <c r="I57" t="n">
-        <v>-10.68232485</v>
+        <v>-3.0873309</v>
       </c>
       <c r="J57" t="n">
-        <v>-2.06311068</v>
+        <v>-3.15688858</v>
       </c>
       <c r="K57" t="n">
-        <v>-7.646386179999999</v>
+        <v>-1.54356494</v>
       </c>
       <c r="L57" t="n">
-        <v>-7.730809809999999</v>
+        <v>-4.72126344</v>
       </c>
       <c r="M57" t="n">
-        <v>-13.07119152</v>
+        <v>-3.36291249</v>
       </c>
     </row>
     <row r="58">
@@ -2807,37 +2807,37 @@
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>-22.33104893</v>
+        <v>-45.84164924</v>
       </c>
       <c r="D58" t="n">
-        <v>-29.8055506</v>
+        <v>-34.24924694</v>
       </c>
       <c r="E58" t="n">
-        <v>-26.70111176</v>
+        <v>-43.39532768</v>
       </c>
       <c r="F58" t="n">
-        <v>-33.06698602</v>
+        <v>-36.66191066</v>
       </c>
       <c r="G58" t="n">
-        <v>-34.65812574</v>
+        <v>-40.85378132</v>
       </c>
       <c r="H58" t="n">
-        <v>-32.60667893</v>
+        <v>-33.23532115</v>
       </c>
       <c r="I58" t="n">
-        <v>-25.57439658</v>
+        <v>-1.87354589</v>
       </c>
       <c r="J58" t="n">
-        <v>-2.8976209</v>
+        <v>-8.467964469999998</v>
       </c>
       <c r="K58" t="n">
-        <v>-3.97830766</v>
+        <v>1.73251277</v>
       </c>
       <c r="L58" t="n">
-        <v>7.91966121</v>
+        <v>-3.28163647</v>
       </c>
       <c r="M58" t="n">
-        <v>5.06835682</v>
+        <v>15.7512569</v>
       </c>
     </row>
     <row r="59">
@@ -2848,37 +2848,37 @@
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
-        <v>-20.14105945999999</v>
+        <v>-47.58373863</v>
       </c>
       <c r="D59" t="n">
-        <v>-47.58373863</v>
+        <v>-6.848567779999997</v>
       </c>
       <c r="E59" t="n">
-        <v>-6.848567779999997</v>
+        <v>-40.2240581</v>
       </c>
       <c r="F59" t="n">
-        <v>-40.2240581</v>
+        <v>9.468226549999999</v>
       </c>
       <c r="G59" t="n">
-        <v>9.468226549999999</v>
+        <v>-7.980154839999999</v>
       </c>
       <c r="H59" t="n">
-        <v>-7.980154839999999</v>
+        <v>-34.98440709</v>
       </c>
       <c r="I59" t="n">
-        <v>-34.98440709</v>
+        <v>-56.78136198999999</v>
       </c>
       <c r="J59" t="n">
-        <v>-56.78136198999999</v>
+        <v>-68.2518347</v>
       </c>
       <c r="K59" t="n">
-        <v>-68.2518347</v>
+        <v>-7.668320309999999</v>
       </c>
       <c r="L59" t="n">
-        <v>-7.668320309999999</v>
+        <v>-47.89530137000001</v>
       </c>
       <c r="M59" t="n">
-        <v>-47.89530137000001</v>
+        <v>6.97709691</v>
       </c>
     </row>
     <row r="60">
@@ -2889,37 +2889,37 @@
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
-        <v>-0.00737333</v>
+        <v>-0.02360963</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.02360963</v>
+        <v>0.01021073</v>
       </c>
       <c r="E60" t="n">
-        <v>0.01021073</v>
+        <v>0.008976989999999999</v>
       </c>
       <c r="F60" t="n">
-        <v>0.008976989999999999</v>
+        <v>0.00535379</v>
       </c>
       <c r="G60" t="n">
-        <v>0.00535379</v>
+        <v>0.00779849</v>
       </c>
       <c r="H60" t="n">
-        <v>0.00779849</v>
+        <v>0.00313796</v>
       </c>
       <c r="I60" t="n">
-        <v>0.00313796</v>
+        <v>0.004106569999999999</v>
       </c>
       <c r="J60" t="n">
-        <v>0.004106569999999999</v>
+        <v>0.00161991</v>
       </c>
       <c r="K60" t="n">
-        <v>0.00161991</v>
+        <v>-0.00451898</v>
       </c>
       <c r="L60" t="n">
-        <v>-0.00451898</v>
+        <v>-0.00031755</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.00031755</v>
+        <v>0.01810178</v>
       </c>
     </row>
     <row r="61">
@@ -2930,37 +2930,37 @@
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
-        <v>6.308863690000001</v>
+        <v>18.75386397</v>
       </c>
       <c r="D61" t="n">
-        <v>18.75386397</v>
+        <v>-13.81184612</v>
       </c>
       <c r="E61" t="n">
-        <v>-13.81184612</v>
+        <v>-72.81740354999999</v>
       </c>
       <c r="F61" t="n">
-        <v>-72.81740354999999</v>
+        <v>-43.80328412</v>
       </c>
       <c r="G61" t="n">
-        <v>-43.80328412</v>
+        <v>-59.54090667</v>
       </c>
       <c r="H61" t="n">
-        <v>-59.54090667</v>
+        <v>-59.82930822</v>
       </c>
       <c r="I61" t="n">
-        <v>-59.82930822</v>
+        <v>-20.0936324</v>
       </c>
       <c r="J61" t="n">
-        <v>-20.0936324</v>
+        <v>-30.92306802</v>
       </c>
       <c r="K61" t="n">
-        <v>-30.92306802</v>
+        <v>-15.12147089</v>
       </c>
       <c r="L61" t="n">
-        <v>-15.12147089</v>
+        <v>19.01830041</v>
       </c>
       <c r="M61" t="n">
-        <v>19.01830041</v>
+        <v>32.19726349</v>
       </c>
     </row>
     <row r="62">
@@ -2971,37 +2971,37 @@
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>0.01630225</v>
+        <v>0.01025229</v>
       </c>
       <c r="D62" t="n">
-        <v>0.01026355</v>
+        <v>0.00055136</v>
       </c>
       <c r="E62" t="n">
-        <v>0.00059986</v>
+        <v>-0.00691126</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.00685134</v>
+        <v>-0.0001974500000000001</v>
       </c>
       <c r="G62" t="n">
-        <v>7.956999999999988e-05</v>
+        <v>-0.00328995</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.00301473</v>
+        <v>-0.00367163</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.00353536</v>
+        <v>-0.00149519</v>
       </c>
       <c r="J62" t="n">
-        <v>-0.00140903</v>
+        <v>-0.0044427</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.00438388</v>
+        <v>-0.00424425</v>
       </c>
       <c r="L62" t="n">
-        <v>-0.00429559</v>
+        <v>-0.00749634</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.00773218</v>
+        <v>-0.0031783</v>
       </c>
     </row>
     <row r="63">
@@ -3012,37 +3012,37 @@
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>0.4035366300000002</v>
+        <v>13.26275676</v>
       </c>
       <c r="D63" t="n">
-        <v>13.2627455</v>
+        <v>-4.546467850000001</v>
       </c>
       <c r="E63" t="n">
-        <v>-4.546516350000001</v>
+        <v>-50.08833026</v>
       </c>
       <c r="F63" t="n">
-        <v>-50.08839018</v>
+        <v>3.88198186</v>
       </c>
       <c r="G63" t="n">
-        <v>3.88170484</v>
+        <v>-6.97381204</v>
       </c>
       <c r="H63" t="n">
-        <v>-6.97408726</v>
+        <v>-18.18737138</v>
       </c>
       <c r="I63" t="n">
-        <v>-18.18750765</v>
+        <v>54.93229337</v>
       </c>
       <c r="J63" t="n">
-        <v>54.93220721</v>
+        <v>-0.1344427499999995</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.1345015699999995</v>
+        <v>15.73493082</v>
       </c>
       <c r="L63" t="n">
-        <v>15.73498216</v>
+        <v>-2.454337439999999</v>
       </c>
       <c r="M63" t="n">
-        <v>-2.4541016</v>
+        <v>28.65151394</v>
       </c>
     </row>
     <row r="64">
@@ -3053,37 +3053,37 @@
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
-        <v>-0.00021559</v>
+        <v>-0.0001136</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.0001136</v>
+        <v>-0.00047737</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.00047737</v>
+        <v>-0.0001746</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.0001746</v>
+        <v>0.00012031</v>
       </c>
       <c r="G64" t="n">
-        <v>0.00012031</v>
+        <v>-2.134999999999999e-05</v>
       </c>
       <c r="H64" t="n">
-        <v>-2.134999999999999e-05</v>
+        <v>0.00012761</v>
       </c>
       <c r="I64" t="n">
-        <v>0.00012761</v>
+        <v>0.00014581</v>
       </c>
       <c r="J64" t="n">
-        <v>0.00014581</v>
+        <v>0.00033086</v>
       </c>
       <c r="K64" t="n">
-        <v>0.00033086</v>
+        <v>0.0004248200000000001</v>
       </c>
       <c r="L64" t="n">
-        <v>0.0004248200000000001</v>
+        <v>0.00090755</v>
       </c>
       <c r="M64" t="n">
-        <v>0.00090755</v>
+        <v>0.00103174</v>
       </c>
     </row>
     <row r="65">
@@ -3094,37 +3094,37 @@
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
-        <v>7.334999999999999e-05</v>
+        <v>0.00015227</v>
       </c>
       <c r="D65" t="n">
-        <v>0.00015227</v>
+        <v>-5.835999999999999e-05</v>
       </c>
       <c r="E65" t="n">
-        <v>-5.835999999999999e-05</v>
+        <v>-0.00037977</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.00037977</v>
+        <v>-0.00013752</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.00013752</v>
+        <v>-0.00019394</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.00019394</v>
+        <v>-0.00018756</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.00018756</v>
+        <v>-0.00024988</v>
       </c>
       <c r="J65" t="n">
-        <v>-0.00024988</v>
+        <v>-0.00027272</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.00027272</v>
+        <v>-0.0002611</v>
       </c>
       <c r="L65" t="n">
-        <v>-0.0002611</v>
+        <v>-0.00027651</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.00027651</v>
+        <v>-0.0002609000000000001</v>
       </c>
     </row>
     <row r="66">
@@ -3135,37 +3135,37 @@
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>-304.8079042499999</v>
+        <v>227.064571</v>
       </c>
       <c r="D66" t="n">
-        <v>222.96632187</v>
+        <v>387.1266204199999</v>
       </c>
       <c r="E66" t="n">
-        <v>382.5060045399999</v>
+        <v>806.6555600600001</v>
       </c>
       <c r="F66" t="n">
-        <v>808.1893105500001</v>
+        <v>455.93493763</v>
       </c>
       <c r="G66" t="n">
-        <v>455.72640316</v>
+        <v>660.62955631</v>
       </c>
       <c r="H66" t="n">
-        <v>651.60334046</v>
+        <v>618.7149716599999</v>
       </c>
       <c r="I66" t="n">
-        <v>591.3442807500001</v>
+        <v>1100.53461035</v>
       </c>
       <c r="J66" t="n">
-        <v>1065.57218717</v>
+        <v>916.5280950800001</v>
       </c>
       <c r="K66" t="n">
-        <v>900.64843911</v>
+        <v>224.54199671</v>
       </c>
       <c r="L66" t="n">
-        <v>218.45362839</v>
+        <v>440.73232269</v>
       </c>
       <c r="M66" t="n">
-        <v>442.97819351</v>
+        <v>4.049852369999998</v>
       </c>
     </row>
     <row r="67">
@@ -3176,37 +3176,37 @@
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>255.17645497</v>
+        <v>120.54782873</v>
       </c>
       <c r="D67" t="n">
-        <v>129.68261296</v>
+        <v>44.24762443</v>
       </c>
       <c r="E67" t="n">
-        <v>57.69811906</v>
+        <v>-36.1709015</v>
       </c>
       <c r="F67" t="n">
-        <v>-39.51086015</v>
+        <v>1.71373009</v>
       </c>
       <c r="G67" t="n">
-        <v>7.84265502</v>
+        <v>19.83420643</v>
       </c>
       <c r="H67" t="n">
-        <v>31.32679715</v>
+        <v>16.35510931</v>
       </c>
       <c r="I67" t="n">
-        <v>31.18938849</v>
+        <v>14.86053108</v>
       </c>
       <c r="J67" t="n">
-        <v>33.8760864</v>
+        <v>19.65957699</v>
       </c>
       <c r="K67" t="n">
-        <v>44.29930263</v>
+        <v>-17.0962329</v>
       </c>
       <c r="L67" t="n">
-        <v>29.08729437</v>
+        <v>-53.13388309</v>
       </c>
       <c r="M67" t="n">
-        <v>0.4100098399999969</v>
+        <v>-4.002099009999999</v>
       </c>
     </row>
     <row r="68">
@@ -3217,37 +3217,37 @@
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>103.28013344</v>
+        <v>109.69128697</v>
       </c>
       <c r="D68" t="n">
-        <v>104.65475187</v>
+        <v>259.88125488</v>
       </c>
       <c r="E68" t="n">
-        <v>251.05137613</v>
+        <v>-70.13250491999999</v>
       </c>
       <c r="F68" t="n">
-        <v>-68.32629675999999</v>
+        <v>210.03472047</v>
       </c>
       <c r="G68" t="n">
-        <v>204.11433001</v>
+        <v>189.41176577</v>
       </c>
       <c r="H68" t="n">
-        <v>186.9453909</v>
+        <v>497.0239474000001</v>
       </c>
       <c r="I68" t="n">
-        <v>509.5603591300001</v>
+        <v>817.77069839</v>
       </c>
       <c r="J68" t="n">
-        <v>833.71756625</v>
+        <v>282.87084422</v>
       </c>
       <c r="K68" t="n">
-        <v>274.11077455</v>
+        <v>290.47120023</v>
       </c>
       <c r="L68" t="n">
-        <v>250.37604128</v>
+        <v>141.03527287</v>
       </c>
       <c r="M68" t="n">
-        <v>85.24550911999999</v>
+        <v>355.89689385</v>
       </c>
     </row>
     <row r="69">
@@ -3258,37 +3258,37 @@
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>1.96469934</v>
+        <v>10.78952622</v>
       </c>
       <c r="D69" t="n">
-        <v>10.78952622</v>
+        <v>6.005808959999999</v>
       </c>
       <c r="E69" t="n">
-        <v>6.005808959999999</v>
+        <v>1.48615941</v>
       </c>
       <c r="F69" t="n">
-        <v>1.48615941</v>
+        <v>6.954071790000001</v>
       </c>
       <c r="G69" t="n">
-        <v>6.954071790000001</v>
+        <v>8.895559609999999</v>
       </c>
       <c r="H69" t="n">
-        <v>8.895559609999999</v>
+        <v>25.77768484</v>
       </c>
       <c r="I69" t="n">
-        <v>25.77768484</v>
+        <v>7.5358798</v>
       </c>
       <c r="J69" t="n">
-        <v>7.5358798</v>
+        <v>-2.18453111</v>
       </c>
       <c r="K69" t="n">
-        <v>-2.18453111</v>
+        <v>-4.28064262</v>
       </c>
       <c r="L69" t="n">
-        <v>-4.28064262</v>
+        <v>-9.848016550000001</v>
       </c>
       <c r="M69" t="n">
-        <v>-9.848016550000001</v>
+        <v>-11.75977663</v>
       </c>
     </row>
     <row r="70">
@@ -3299,37 +3299,37 @@
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>-1.08469633</v>
+        <v>-2.25176163</v>
       </c>
       <c r="D70" t="n">
-        <v>-2.25176163</v>
+        <v>-1.21277104</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.21277104</v>
+        <v>-3.03497446</v>
       </c>
       <c r="F70" t="n">
-        <v>-3.03497446</v>
+        <v>-1.57228821</v>
       </c>
       <c r="G70" t="n">
-        <v>-1.57228821</v>
+        <v>-0.33839224</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.33839224</v>
+        <v>-1.43394215</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.43394215</v>
+        <v>-1.69268373</v>
       </c>
       <c r="J70" t="n">
-        <v>-1.69268373</v>
+        <v>-3.23010772</v>
       </c>
       <c r="K70" t="n">
-        <v>-3.23010772</v>
+        <v>-3.39045584</v>
       </c>
       <c r="L70" t="n">
-        <v>-3.39045584</v>
+        <v>-4.06147909</v>
       </c>
       <c r="M70" t="n">
-        <v>-4.06147909</v>
+        <v>-3.60733925</v>
       </c>
     </row>
     <row r="71">
@@ -3340,37 +3340,37 @@
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
-        <v>-6.51519358</v>
+        <v>-9.829484189999999</v>
       </c>
       <c r="D71" t="n">
-        <v>-9.829484189999999</v>
+        <v>-14.93550311</v>
       </c>
       <c r="E71" t="n">
-        <v>-14.93550311</v>
+        <v>-19.17963443</v>
       </c>
       <c r="F71" t="n">
-        <v>-19.17963443</v>
+        <v>-4.231608599999999</v>
       </c>
       <c r="G71" t="n">
-        <v>-4.231608599999999</v>
+        <v>-4.30055992</v>
       </c>
       <c r="H71" t="n">
-        <v>-4.30055992</v>
+        <v>-3.592882920000001</v>
       </c>
       <c r="I71" t="n">
-        <v>-3.592882920000001</v>
+        <v>-6.801680230000001</v>
       </c>
       <c r="J71" t="n">
-        <v>-6.801680230000001</v>
+        <v>-13.86701406</v>
       </c>
       <c r="K71" t="n">
-        <v>-13.86701406</v>
+        <v>1.46514716</v>
       </c>
       <c r="L71" t="n">
-        <v>1.46514716</v>
+        <v>0.14055349</v>
       </c>
       <c r="M71" t="n">
-        <v>0.14055349</v>
+        <v>7.1486433</v>
       </c>
     </row>
     <row r="72">
@@ -3381,37 +3381,37 @@
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>36.48567583</v>
+        <v>-49.00740580000001</v>
       </c>
       <c r="D72" t="n">
-        <v>-43.25389258000001</v>
+        <v>36.20031953</v>
       </c>
       <c r="E72" t="n">
-        <v>47.88964175</v>
+        <v>-67.66731897</v>
       </c>
       <c r="F72" t="n">
-        <v>-63.73493999</v>
+        <v>86.08082459000001</v>
       </c>
       <c r="G72" t="n">
-        <v>90.96197023000001</v>
+        <v>65.03796482999999</v>
       </c>
       <c r="H72" t="n">
-        <v>66.47659118999999</v>
+        <v>7.475289409999997</v>
       </c>
       <c r="I72" t="n">
-        <v>6.500239739999999</v>
+        <v>-64.07427258999999</v>
       </c>
       <c r="J72" t="n">
-        <v>-66.40334514</v>
+        <v>-115.50237892</v>
       </c>
       <c r="K72" t="n">
-        <v>-114.75350115</v>
+        <v>-11.79256974999999</v>
       </c>
       <c r="L72" t="n">
-        <v>-10.32054621999999</v>
+        <v>-141.47987787</v>
       </c>
       <c r="M72" t="n">
-        <v>-143.2717555</v>
+        <v>-101.90599359</v>
       </c>
     </row>
     <row r="73">
@@ -3422,37 +3422,37 @@
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
-        <v>16.25091608</v>
+        <v>12.37816619</v>
       </c>
       <c r="D73" t="n">
-        <v>6.624652970000001</v>
+        <v>29.61557151</v>
       </c>
       <c r="E73" t="n">
-        <v>17.92624929</v>
+        <v>-16.74761519</v>
       </c>
       <c r="F73" t="n">
-        <v>-20.67999417</v>
+        <v>12.69931131</v>
       </c>
       <c r="G73" t="n">
-        <v>7.81816567</v>
+        <v>3.78296577</v>
       </c>
       <c r="H73" t="n">
-        <v>2.34433941</v>
+        <v>-8.953148180000001</v>
       </c>
       <c r="I73" t="n">
-        <v>-7.978098510000001</v>
+        <v>-9.151913179999999</v>
       </c>
       <c r="J73" t="n">
-        <v>-6.82284063</v>
+        <v>-18.43159092</v>
       </c>
       <c r="K73" t="n">
-        <v>-19.18046869</v>
+        <v>-8.639121230000001</v>
       </c>
       <c r="L73" t="n">
-        <v>-10.11114476</v>
+        <v>-18.10617875</v>
       </c>
       <c r="M73" t="n">
-        <v>-16.31430112</v>
+        <v>-0.7691315999999999</v>
       </c>
     </row>
     <row r="74">
@@ -3463,37 +3463,37 @@
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
-        <v>-507.9878969</v>
+        <v>-1008.07010514</v>
       </c>
       <c r="D74" t="n">
-        <v>-969.2779692900001</v>
+        <v>-1537.60609394</v>
       </c>
       <c r="E74" t="n">
-        <v>-1476.29869168</v>
+        <v>-1300.60484244</v>
       </c>
       <c r="F74" t="n">
-        <v>-1210.75677447</v>
+        <v>-446.7146776000001</v>
       </c>
       <c r="G74" t="n">
-        <v>-431.0473437</v>
+        <v>-782.3819385199999</v>
       </c>
       <c r="H74" t="n">
-        <v>-848.3152573899999</v>
+        <v>-1081.01944222</v>
       </c>
       <c r="I74" t="n">
-        <v>-1101.91752823</v>
+        <v>-1391.75995319</v>
       </c>
       <c r="J74" t="n">
-        <v>-1385.0147538</v>
+        <v>-1580.93302348</v>
       </c>
       <c r="K74" t="n">
-        <v>-1537.42281634</v>
+        <v>-563.61207497</v>
       </c>
       <c r="L74" t="n">
-        <v>-584.60167899</v>
+        <v>-1021.23222964</v>
       </c>
       <c r="M74" t="n">
-        <v>-983.24788187</v>
+        <v>32.26943954999999</v>
       </c>
     </row>
     <row r="75">
@@ -3504,37 +3504,37 @@
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
-        <v>384.2826500200001</v>
+        <v>-60.65922219999999</v>
       </c>
       <c r="D75" t="n">
-        <v>-60.65922219999999</v>
+        <v>-260.44258382</v>
       </c>
       <c r="E75" t="n">
-        <v>-260.44258382</v>
+        <v>-368.46173542</v>
       </c>
       <c r="F75" t="n">
-        <v>-368.46173542</v>
+        <v>-257.34234104</v>
       </c>
       <c r="G75" t="n">
-        <v>-257.34234104</v>
+        <v>-885.79771207</v>
       </c>
       <c r="H75" t="n">
-        <v>-885.79771207</v>
+        <v>-150.17356266</v>
       </c>
       <c r="I75" t="n">
-        <v>-150.17356266</v>
+        <v>-451.01320442</v>
       </c>
       <c r="J75" t="n">
-        <v>-451.01320442</v>
+        <v>-639.4418898500001</v>
       </c>
       <c r="K75" t="n">
-        <v>-639.4418898500001</v>
+        <v>-343.7357963100001</v>
       </c>
       <c r="L75" t="n">
-        <v>-343.7357963100001</v>
+        <v>-358.27958259</v>
       </c>
       <c r="M75" t="n">
-        <v>-358.27958259</v>
+        <v>-339.09543789</v>
       </c>
     </row>
     <row r="76">
@@ -3545,37 +3545,37 @@
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>201.15438429</v>
+        <v>108.00936268</v>
       </c>
       <c r="D76" t="n">
-        <v>69.21722683000002</v>
+        <v>19.06414180000001</v>
       </c>
       <c r="E76" t="n">
-        <v>-42.24326045999999</v>
+        <v>-36.27459351</v>
       </c>
       <c r="F76" t="n">
-        <v>-126.12266148</v>
+        <v>60.51338413</v>
       </c>
       <c r="G76" t="n">
-        <v>44.84605023</v>
+        <v>-14.83326694</v>
       </c>
       <c r="H76" t="n">
-        <v>51.10005193</v>
+        <v>-38.65199278</v>
       </c>
       <c r="I76" t="n">
-        <v>-17.75390677</v>
+        <v>-81.31538531</v>
       </c>
       <c r="J76" t="n">
-        <v>-88.06058470000001</v>
+        <v>-113.49396267</v>
       </c>
       <c r="K76" t="n">
-        <v>-157.00416981</v>
+        <v>-9.233541829999998</v>
       </c>
       <c r="L76" t="n">
-        <v>11.75606219</v>
+        <v>-62.41240477000001</v>
       </c>
       <c r="M76" t="n">
-        <v>-100.39675254</v>
+        <v>40.32641878</v>
       </c>
     </row>
     <row r="77">
@@ -3586,37 +3586,37 @@
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="n">
-        <v>7.779000000000001e-05</v>
+        <v>0.00048183</v>
       </c>
       <c r="D77" t="n">
-        <v>0.00048183</v>
+        <v>-0.00035228</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.00035228</v>
+        <v>-0.0010076</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.0010076</v>
+        <v>-0.00018871</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.00018871</v>
+        <v>-0.00053725</v>
       </c>
       <c r="H77" t="n">
-        <v>-0.00053725</v>
+        <v>-0.00057684</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.00057684</v>
+        <v>-0.0006594299999999999</v>
       </c>
       <c r="J77" t="n">
-        <v>-0.0006594299999999999</v>
+        <v>-0.00071329</v>
       </c>
       <c r="K77" t="n">
-        <v>-0.00071329</v>
+        <v>-0.0003751</v>
       </c>
       <c r="L77" t="n">
-        <v>-0.0003751</v>
+        <v>-0.00072667</v>
       </c>
       <c r="M77" t="n">
-        <v>-0.00072667</v>
+        <v>-0.00031853</v>
       </c>
     </row>
     <row r="78">
@@ -3627,37 +3627,37 @@
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
-        <v>0.00113808</v>
+        <v>0.0028904</v>
       </c>
       <c r="D78" t="n">
-        <v>0.0028904</v>
+        <v>0.00127502</v>
       </c>
       <c r="E78" t="n">
-        <v>0.00127502</v>
+        <v>-0.00110649</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.00110649</v>
+        <v>0.0006396900000000001</v>
       </c>
       <c r="G78" t="n">
-        <v>0.0006396900000000001</v>
+        <v>0.00368509</v>
       </c>
       <c r="H78" t="n">
-        <v>0.00368509</v>
+        <v>0.004119070000000001</v>
       </c>
       <c r="I78" t="n">
-        <v>0.004119070000000001</v>
+        <v>0.00104634</v>
       </c>
       <c r="J78" t="n">
-        <v>0.00104634</v>
+        <v>-0.00267286</v>
       </c>
       <c r="K78" t="n">
-        <v>-0.00267286</v>
+        <v>-9.306000000000001e-05</v>
       </c>
       <c r="L78" t="n">
-        <v>-9.306000000000001e-05</v>
+        <v>-0.00439828</v>
       </c>
       <c r="M78" t="n">
-        <v>-0.00439828</v>
+        <v>-0.005935770000000001</v>
       </c>
     </row>
     <row r="79">
@@ -3668,37 +3668,37 @@
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="n">
-        <v>5.295999999999999e-05</v>
+        <v>-4.426999999999998e-05</v>
       </c>
       <c r="D79" t="n">
-        <v>-4.426999999999998e-05</v>
+        <v>-0.00031949</v>
       </c>
       <c r="E79" t="n">
-        <v>-0.00031949</v>
+        <v>-0.00080643</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.00080643</v>
+        <v>-0.00053355</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.00053355</v>
+        <v>-0.0004297</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.0004297</v>
+        <v>-0.00048908</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.00048908</v>
+        <v>-0.00026955</v>
       </c>
       <c r="J79" t="n">
-        <v>-0.00026955</v>
+        <v>-0.00035725</v>
       </c>
       <c r="K79" t="n">
-        <v>-0.00035725</v>
+        <v>-0.00052145</v>
       </c>
       <c r="L79" t="n">
-        <v>-0.00052145</v>
+        <v>-0.00052038</v>
       </c>
       <c r="M79" t="n">
-        <v>-0.00052038</v>
+        <v>-0.00049876</v>
       </c>
     </row>
     <row r="80">
@@ -3709,37 +3709,37 @@
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="n">
-        <v>4.15302783</v>
+        <v>2.61099361</v>
       </c>
       <c r="D80" t="n">
-        <v>2.61099361</v>
+        <v>23.15279365</v>
       </c>
       <c r="E80" t="n">
-        <v>23.15279365</v>
+        <v>3.53747368</v>
       </c>
       <c r="F80" t="n">
-        <v>3.53747368</v>
+        <v>3.37237859</v>
       </c>
       <c r="G80" t="n">
-        <v>3.37237859</v>
+        <v>12.60022255</v>
       </c>
       <c r="H80" t="n">
-        <v>12.60022255</v>
+        <v>28.00022631</v>
       </c>
       <c r="I80" t="n">
-        <v>28.00022631</v>
+        <v>3.68878533</v>
       </c>
       <c r="J80" t="n">
-        <v>3.68878533</v>
+        <v>-6.56068165</v>
       </c>
       <c r="K80" t="n">
-        <v>-6.56068165</v>
+        <v>5.127412570000001</v>
       </c>
       <c r="L80" t="n">
-        <v>5.127412570000001</v>
+        <v>0.3745234199999999</v>
       </c>
       <c r="M80" t="n">
-        <v>0.3745234199999999</v>
+        <v>-13.08952523</v>
       </c>
     </row>
     <row r="81">
@@ -3748,39 +3748,41 @@
           <t>鋼鐵工業右下</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr"/>
+      <c r="B81" t="n">
+        <v>0</v>
+      </c>
       <c r="C81" t="n">
-        <v>57.84019353</v>
+        <v>11.94355438</v>
       </c>
       <c r="D81" t="n">
-        <v>14.19445558</v>
+        <v>44.30325269</v>
       </c>
       <c r="E81" t="n">
-        <v>45.19376998000001</v>
+        <v>56.83459901000001</v>
       </c>
       <c r="F81" t="n">
-        <v>55.3360788</v>
+        <v>188.94294104</v>
       </c>
       <c r="G81" t="n">
-        <v>188.1240479</v>
+        <v>60.27513024</v>
       </c>
       <c r="H81" t="n">
-        <v>61.19985670000001</v>
+        <v>36.77150214</v>
       </c>
       <c r="I81" t="n">
-        <v>36.8115511</v>
+        <v>-46.30174972</v>
       </c>
       <c r="J81" t="n">
-        <v>-44.42130979</v>
+        <v>-85.81048893000001</v>
       </c>
       <c r="K81" t="n">
-        <v>-85.83761873</v>
+        <v>4.43261345</v>
       </c>
       <c r="L81" t="n">
-        <v>4.2730069</v>
+        <v>-72.10663736999999</v>
       </c>
       <c r="M81" t="n">
-        <v>-70.87105361999998</v>
+        <v>-104.95248059</v>
       </c>
     </row>
     <row r="82">
@@ -3791,37 +3793,37 @@
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
-        <v>66.66401304</v>
+        <v>29.91834361</v>
       </c>
       <c r="D82" t="n">
-        <v>27.92816723999999</v>
+        <v>36.51244642</v>
       </c>
       <c r="E82" t="n">
-        <v>35.55277909</v>
+        <v>97.64502983000001</v>
       </c>
       <c r="F82" t="n">
-        <v>97.91762933000001</v>
+        <v>253.67546433</v>
       </c>
       <c r="G82" t="n">
-        <v>254.63680657</v>
+        <v>106.78659576</v>
       </c>
       <c r="H82" t="n">
-        <v>105.10418892</v>
+        <v>356.41528479</v>
       </c>
       <c r="I82" t="n">
-        <v>356.3969255000001</v>
+        <v>506.88955911</v>
       </c>
       <c r="J82" t="n">
-        <v>504.75618342</v>
+        <v>775.7932965800001</v>
       </c>
       <c r="K82" t="n">
-        <v>775.38497423</v>
+        <v>803.9262191600001</v>
       </c>
       <c r="L82" t="n">
-        <v>804.40523495</v>
+        <v>245.7090147</v>
       </c>
       <c r="M82" t="n">
-        <v>243.92214045</v>
+        <v>6.74061814</v>
       </c>
     </row>
     <row r="83">
@@ -3832,37 +3834,37 @@
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>9.089367230000001</v>
+        <v>76.29529208</v>
       </c>
       <c r="D83" t="n">
-        <v>76.29529208</v>
+        <v>23.28468532</v>
       </c>
       <c r="E83" t="n">
-        <v>23.28468532</v>
+        <v>-16.2538581</v>
       </c>
       <c r="F83" t="n">
-        <v>-16.2538581</v>
+        <v>-12.95625808</v>
       </c>
       <c r="G83" t="n">
-        <v>-12.95625808</v>
+        <v>-9.47706786</v>
       </c>
       <c r="H83" t="n">
-        <v>-9.47706786</v>
+        <v>-3.909404330000002</v>
       </c>
       <c r="I83" t="n">
-        <v>-3.909404330000002</v>
+        <v>-14.46518195</v>
       </c>
       <c r="J83" t="n">
-        <v>-14.46518195</v>
+        <v>37.21932350000001</v>
       </c>
       <c r="K83" t="n">
-        <v>37.21932350000001</v>
+        <v>68.03134521</v>
       </c>
       <c r="L83" t="n">
-        <v>68.03134521</v>
+        <v>-2.350372119999999</v>
       </c>
       <c r="M83" t="n">
-        <v>-2.350372119999999</v>
+        <v>-4.571539939999999</v>
       </c>
     </row>
     <row r="84">
@@ -3873,37 +3875,37 @@
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
-        <v>10.47940253</v>
+        <v>40.35862178</v>
       </c>
       <c r="D84" t="n">
-        <v>36.22894215</v>
+        <v>68.37247169999999</v>
       </c>
       <c r="E84" t="n">
-        <v>70.09217058</v>
+        <v>3.416822149999998</v>
       </c>
       <c r="F84" t="n">
-        <v>16.23243836</v>
+        <v>43.73037651000001</v>
       </c>
       <c r="G84" t="n">
-        <v>46.0244771</v>
+        <v>0.8549038500000001</v>
       </c>
       <c r="H84" t="n">
-        <v>10.70405304</v>
+        <v>-20.28244063</v>
       </c>
       <c r="I84" t="n">
-        <v>-5.995419249999999</v>
+        <v>-7.13288485</v>
       </c>
       <c r="J84" t="n">
-        <v>7.19164066</v>
+        <v>-11.15250674</v>
       </c>
       <c r="K84" t="n">
-        <v>-6.73843708</v>
+        <v>107.81488663</v>
       </c>
       <c r="L84" t="n">
-        <v>102.04970245</v>
+        <v>-119.17231353</v>
       </c>
       <c r="M84" t="n">
-        <v>-116.03762182</v>
+        <v>-149.47758541</v>
       </c>
     </row>
     <row r="85">
@@ -3914,37 +3916,37 @@
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>2.51148734</v>
+        <v>14.5085341</v>
       </c>
       <c r="D85" t="n">
-        <v>18.63821373</v>
+        <v>20.15684346</v>
       </c>
       <c r="E85" t="n">
-        <v>18.43714458</v>
+        <v>-1.24360454</v>
       </c>
       <c r="F85" t="n">
-        <v>-14.05922075</v>
+        <v>6.66986342</v>
       </c>
       <c r="G85" t="n">
-        <v>4.37576283</v>
+        <v>-6.613553349999999</v>
       </c>
       <c r="H85" t="n">
-        <v>-16.46270254</v>
+        <v>-13.39359848</v>
       </c>
       <c r="I85" t="n">
-        <v>-27.68061986</v>
+        <v>-9.00979353</v>
       </c>
       <c r="J85" t="n">
-        <v>-23.33431904</v>
+        <v>-13.60499768</v>
       </c>
       <c r="K85" t="n">
-        <v>-18.01906734</v>
+        <v>-6.87317825</v>
       </c>
       <c r="L85" t="n">
-        <v>-1.10799407</v>
+        <v>-16.67037756</v>
       </c>
       <c r="M85" t="n">
-        <v>-19.80506927</v>
+        <v>-18.67401923</v>
       </c>
     </row>
     <row r="86">
@@ -3955,37 +3957,37 @@
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
-        <v>169.26384426</v>
+        <v>99.26279117999999</v>
       </c>
       <c r="D86" t="n">
-        <v>98.81335047</v>
+        <v>82.10264262000001</v>
       </c>
       <c r="E86" t="n">
-        <v>84.78180712999999</v>
+        <v>-0.5536843900000029</v>
       </c>
       <c r="F86" t="n">
-        <v>5.239100129999997</v>
+        <v>35.31476152</v>
       </c>
       <c r="G86" t="n">
-        <v>37.95854161</v>
+        <v>2.312927219999999</v>
       </c>
       <c r="H86" t="n">
-        <v>6.337415530000002</v>
+        <v>-14.73780212</v>
       </c>
       <c r="I86" t="n">
-        <v>-14.77173878</v>
+        <v>45.55591851</v>
       </c>
       <c r="J86" t="n">
-        <v>42.12402878</v>
+        <v>20.93663418</v>
       </c>
       <c r="K86" t="n">
-        <v>24.19335857</v>
+        <v>83.75538558</v>
       </c>
       <c r="L86" t="n">
-        <v>81.89622543999999</v>
+        <v>31.50825829</v>
       </c>
       <c r="M86" t="n">
-        <v>36.94664319</v>
+        <v>43.48443047</v>
       </c>
     </row>
     <row r="87">
@@ -3996,37 +3998,37 @@
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>32.94701889</v>
+        <v>25.20733403</v>
       </c>
       <c r="D87" t="n">
-        <v>26.51973603</v>
+        <v>22.32559712</v>
       </c>
       <c r="E87" t="n">
-        <v>24.11018693</v>
+        <v>6.20539317</v>
       </c>
       <c r="F87" t="n">
-        <v>6.10786008</v>
+        <v>19.57465763</v>
       </c>
       <c r="G87" t="n">
-        <v>20.87429374</v>
+        <v>19.41548498</v>
       </c>
       <c r="H87" t="n">
-        <v>19.51212332</v>
+        <v>15.32622302</v>
       </c>
       <c r="I87" t="n">
-        <v>14.66728639</v>
+        <v>21.24192985</v>
       </c>
       <c r="J87" t="n">
-        <v>20.14334333</v>
+        <v>2.4630607</v>
       </c>
       <c r="K87" t="n">
-        <v>1.00411063</v>
+        <v>3.62088127</v>
       </c>
       <c r="L87" t="n">
-        <v>1.80195043</v>
+        <v>-6.0015291</v>
       </c>
       <c r="M87" t="n">
-        <v>-8.905567599999999</v>
+        <v>-2.04589291</v>
       </c>
     </row>
     <row r="88">
@@ -4037,37 +4039,37 @@
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
-        <v>114.80381599</v>
+        <v>-7.25654832</v>
       </c>
       <c r="D88" t="n">
-        <v>-8.11950961</v>
+        <v>-11.46735275</v>
       </c>
       <c r="E88" t="n">
-        <v>-15.93110706999999</v>
+        <v>-163.74735214</v>
       </c>
       <c r="F88" t="n">
-        <v>-169.44260357</v>
+        <v>-3.85048578</v>
       </c>
       <c r="G88" t="n">
-        <v>-7.793901979999998</v>
+        <v>-82.65326964999998</v>
       </c>
       <c r="H88" t="n">
-        <v>-86.77439629999999</v>
+        <v>-36.3711009</v>
       </c>
       <c r="I88" t="n">
-        <v>-35.67822761</v>
+        <v>20.28814212</v>
       </c>
       <c r="J88" t="n">
-        <v>24.81861837</v>
+        <v>-48.29431101</v>
       </c>
       <c r="K88" t="n">
-        <v>-50.09208533</v>
+        <v>12.16911801</v>
       </c>
       <c r="L88" t="n">
-        <v>15.84720899</v>
+        <v>-68.14740863</v>
       </c>
       <c r="M88" t="n">
-        <v>-70.68175503000001</v>
+        <v>-28.11776397</v>
       </c>
     </row>
     <row r="89">
@@ -4078,37 +4080,37 @@
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>1257.78768424</v>
+        <v>2906.52286037</v>
       </c>
       <c r="D89" t="n">
-        <v>2795.92344442</v>
+        <v>3041.85862625</v>
       </c>
       <c r="E89" t="n">
-        <v>3037.413368</v>
+        <v>-50.91332269000007</v>
       </c>
       <c r="F89" t="n">
-        <v>-182.62646979</v>
+        <v>1440.99283615</v>
       </c>
       <c r="G89" t="n">
-        <v>1449.69273732</v>
+        <v>2091.2588738</v>
       </c>
       <c r="H89" t="n">
-        <v>2183.23606896</v>
+        <v>650.42892814</v>
       </c>
       <c r="I89" t="n">
-        <v>807.3481759899998</v>
+        <v>2555.91236937</v>
       </c>
       <c r="J89" t="n">
-        <v>2695.0084778</v>
+        <v>1482.30721553</v>
       </c>
       <c r="K89" t="n">
-        <v>1479.9531464</v>
+        <v>587.08496215</v>
       </c>
       <c r="L89" t="n">
-        <v>707.1543839499999</v>
+        <v>1888.36280674</v>
       </c>
       <c r="M89" t="n">
-        <v>2034.8912422</v>
+        <v>2863.27898597</v>
       </c>
     </row>
     <row r="90">
@@ -4119,37 +4121,37 @@
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>840.1348328400002</v>
+        <v>-39.30927771999999</v>
       </c>
       <c r="D90" t="n">
-        <v>-36.61286150999999</v>
+        <v>5.541886310000004</v>
       </c>
       <c r="E90" t="n">
-        <v>8.60068389000001</v>
+        <v>-812.85023669</v>
       </c>
       <c r="F90" t="n">
-        <v>-809.9343282</v>
+        <v>-209.20355873</v>
       </c>
       <c r="G90" t="n">
-        <v>-207.85397643</v>
+        <v>23.2753109</v>
       </c>
       <c r="H90" t="n">
-        <v>18.83528317000001</v>
+        <v>-392.10574716</v>
       </c>
       <c r="I90" t="n">
-        <v>-401.20175874</v>
+        <v>-86.06334828999998</v>
       </c>
       <c r="J90" t="n">
-        <v>-93.50089285999999</v>
+        <v>926.9330168199999</v>
       </c>
       <c r="K90" t="n">
-        <v>918.3623095999999</v>
+        <v>1129.75807729</v>
       </c>
       <c r="L90" t="n">
-        <v>1081.86905297</v>
+        <v>67.15083111</v>
       </c>
       <c r="M90" t="n">
-        <v>62.58371018999999</v>
+        <v>111.41716165</v>
       </c>
     </row>
     <row r="91">
@@ -4160,37 +4162,37 @@
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>604.84468883</v>
+        <v>872.4743653200001</v>
       </c>
       <c r="D91" t="n">
-        <v>980.3773650600001</v>
+        <v>352.59548411</v>
       </c>
       <c r="E91" t="n">
-        <v>353.98194478</v>
+        <v>-437.59402655</v>
       </c>
       <c r="F91" t="n">
-        <v>-308.7967879399999</v>
+        <v>437.77691794</v>
       </c>
       <c r="G91" t="n">
-        <v>427.72743447</v>
+        <v>518.40491737</v>
       </c>
       <c r="H91" t="n">
-        <v>430.86774994</v>
+        <v>712.4984515499999</v>
       </c>
       <c r="I91" t="n">
-        <v>564.67521528</v>
+        <v>793.92868294</v>
       </c>
       <c r="J91" t="n">
-        <v>662.2701190800001</v>
+        <v>38.35306098999999</v>
       </c>
       <c r="K91" t="n">
-        <v>49.27783733999998</v>
+        <v>-171.32649259</v>
       </c>
       <c r="L91" t="n">
-        <v>-243.50689007</v>
+        <v>-455.7695278999999</v>
       </c>
       <c r="M91" t="n">
-        <v>-597.7308424400001</v>
+        <v>-526.24604949</v>
       </c>
     </row>
     <row r="92">
@@ -4201,37 +4203,37 @@
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>76.46651637000004</v>
+        <v>450.1374404300001</v>
       </c>
       <c r="D92" t="n">
-        <v>430.23063587</v>
+        <v>230.8343588500001</v>
       </c>
       <c r="E92" t="n">
-        <v>196.37744021</v>
+        <v>193.42815452</v>
       </c>
       <c r="F92" t="n">
-        <v>198.37992527</v>
+        <v>1368.7163708</v>
       </c>
       <c r="G92" t="n">
-        <v>1348.26549426</v>
+        <v>-244.27991623</v>
       </c>
       <c r="H92" t="n">
-        <v>-236.79206187</v>
+        <v>-1063.7628104</v>
       </c>
       <c r="I92" t="n">
-        <v>-1042.70124102</v>
+        <v>-416.69328563</v>
       </c>
       <c r="J92" t="n">
-        <v>-387.84962513</v>
+        <v>-246.4158350100001</v>
       </c>
       <c r="K92" t="n">
-        <v>-245.5531098</v>
+        <v>-263.547706</v>
       </c>
       <c r="L92" t="n">
-        <v>-250.22542046</v>
+        <v>-117.21702503</v>
       </c>
       <c r="M92" t="n">
-        <v>-149.2554709</v>
+        <v>254.06105455</v>
       </c>
     </row>
     <row r="93">
@@ -4242,37 +4244,37 @@
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>67.77470189</v>
+        <v>-139.77033695</v>
       </c>
       <c r="D93" t="n">
-        <v>-139.76904567</v>
+        <v>28.58933824</v>
       </c>
       <c r="E93" t="n">
-        <v>28.59097033</v>
+        <v>-107.07951807</v>
       </c>
       <c r="F93" t="n">
-        <v>-107.08081999</v>
+        <v>121.21020237</v>
       </c>
       <c r="G93" t="n">
-        <v>121.21167898</v>
+        <v>91.21977593999999</v>
       </c>
       <c r="H93" t="n">
-        <v>91.22181734999999</v>
+        <v>-54.60765974</v>
       </c>
       <c r="I93" t="n">
-        <v>-54.60380649</v>
+        <v>-43.35784784</v>
       </c>
       <c r="J93" t="n">
-        <v>-43.35495179999999</v>
+        <v>-87.54705163</v>
       </c>
       <c r="K93" t="n">
-        <v>-87.54330586</v>
+        <v>57.4009534</v>
       </c>
       <c r="L93" t="n">
-        <v>57.40429852999999</v>
+        <v>-52.61122439</v>
       </c>
       <c r="M93" t="n">
-        <v>-52.60672143</v>
+        <v>-101.21467454</v>
       </c>
     </row>
     <row r="94">
@@ -4283,37 +4285,37 @@
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>-114.08428263</v>
+        <v>-76.74787737999999</v>
       </c>
       <c r="D94" t="n">
-        <v>-56.8423641</v>
+        <v>-50.85289054</v>
       </c>
       <c r="E94" t="n">
-        <v>-16.39760398999999</v>
+        <v>-159.14422832</v>
       </c>
       <c r="F94" t="n">
-        <v>-164.09469715</v>
+        <v>62.98996203</v>
       </c>
       <c r="G94" t="n">
-        <v>83.43936196000001</v>
+        <v>128.22662341</v>
       </c>
       <c r="H94" t="n">
-        <v>120.73672764</v>
+        <v>412.83655354</v>
       </c>
       <c r="I94" t="n">
-        <v>391.77113091</v>
+        <v>467.60502446</v>
       </c>
       <c r="J94" t="n">
-        <v>438.75846792</v>
+        <v>72.62953129</v>
       </c>
       <c r="K94" t="n">
-        <v>71.76306031</v>
+        <v>149.6861809</v>
       </c>
       <c r="L94" t="n">
-        <v>136.36055023</v>
+        <v>291.08983047</v>
       </c>
       <c r="M94" t="n">
-        <v>323.12377338</v>
+        <v>88.94080502</v>
       </c>
     </row>
     <row r="95">
@@ -4324,37 +4326,37 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>-1102.79360577</v>
+        <v>1814.27344033</v>
       </c>
       <c r="D95" t="n">
-        <v>1761.49441303</v>
+        <v>1190.51089312</v>
       </c>
       <c r="E95" t="n">
-        <v>1169.88175455</v>
+        <v>323.3601261200004</v>
       </c>
       <c r="F95" t="n">
-        <v>318.3636925599999</v>
+        <v>-814.9015840400001</v>
       </c>
       <c r="G95" t="n">
-        <v>-828.4938808800001</v>
+        <v>678.04168456</v>
       </c>
       <c r="H95" t="n">
-        <v>675.65692934</v>
+        <v>-201.49401636</v>
       </c>
       <c r="I95" t="n">
-        <v>-197.66187764</v>
+        <v>1189.33098974</v>
       </c>
       <c r="J95" t="n">
-        <v>1192.6070228</v>
+        <v>709.2095474999999</v>
       </c>
       <c r="K95" t="n">
-        <v>716.2717947199999</v>
+        <v>956.1483032399999</v>
       </c>
       <c r="L95" t="n">
-        <v>965.6994616499999</v>
+        <v>3033.12208602</v>
       </c>
       <c r="M95" t="n">
-        <v>3040.2639893</v>
+        <v>2681.58312908</v>
       </c>
     </row>
     <row r="96">
@@ -4365,37 +4367,37 @@
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>88.38893640000001</v>
+        <v>64.72300055999999</v>
       </c>
       <c r="D96" t="n">
-        <v>26.45710478</v>
+        <v>131.70823582</v>
       </c>
       <c r="E96" t="n">
-        <v>198.41968851</v>
+        <v>-143.09228886</v>
       </c>
       <c r="F96" t="n">
-        <v>-181.93677505</v>
+        <v>39.32826783</v>
       </c>
       <c r="G96" t="n">
-        <v>40.84103192</v>
+        <v>52.68948845</v>
       </c>
       <c r="H96" t="n">
-        <v>72.52729771</v>
+        <v>69.56662471999999</v>
       </c>
       <c r="I96" t="n">
-        <v>48.91160651000001</v>
+        <v>81.71908187000001</v>
       </c>
       <c r="J96" t="n">
-        <v>93.21302844</v>
+        <v>-12.04564383</v>
       </c>
       <c r="K96" t="n">
-        <v>-55.76650856000001</v>
+        <v>57.64531502000001</v>
       </c>
       <c r="L96" t="n">
-        <v>44.22864608</v>
+        <v>19.70511214</v>
       </c>
       <c r="M96" t="n">
-        <v>-38.08494090000001</v>
+        <v>2.184672839999996</v>
       </c>
     </row>
     <row r="97">
@@ -4406,37 +4408,37 @@
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>249.51558479</v>
+        <v>264.91728899</v>
       </c>
       <c r="D97" t="n">
-        <v>355.96221207</v>
+        <v>470.6439971099999</v>
       </c>
       <c r="E97" t="n">
-        <v>424.56168299</v>
+        <v>5.818737989999997</v>
       </c>
       <c r="F97" t="n">
-        <v>49.65965774</v>
+        <v>165.53992615</v>
       </c>
       <c r="G97" t="n">
-        <v>177.6194589</v>
+        <v>87.4352246</v>
       </c>
       <c r="H97" t="n">
-        <v>69.98217056</v>
+        <v>-40.84549997</v>
       </c>
       <c r="I97" t="n">
-        <v>-24.02262048</v>
+        <v>77.24785016</v>
       </c>
       <c r="J97" t="n">
-        <v>62.47787053</v>
+        <v>-175.42829405</v>
       </c>
       <c r="K97" t="n">
-        <v>-138.76967654</v>
+        <v>-231.61454649</v>
       </c>
       <c r="L97" t="n">
-        <v>-227.74903596</v>
+        <v>-98.17657771</v>
       </c>
       <c r="M97" t="n">
-        <v>-47.52842795</v>
+        <v>-1.719338979999999</v>
       </c>
     </row>
     <row r="98">
@@ -4447,37 +4449,37 @@
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
-        <v>-20.60593856</v>
+        <v>-52.95175765</v>
       </c>
       <c r="D98" t="n">
-        <v>-52.87930635</v>
+        <v>-75.60989875999999</v>
       </c>
       <c r="E98" t="n">
-        <v>-74.84192003999999</v>
+        <v>-89.46311981999999</v>
       </c>
       <c r="F98" t="n">
-        <v>-89.75941349999999</v>
+        <v>-56.04701719000001</v>
       </c>
       <c r="G98" t="n">
-        <v>-55.51367920000001</v>
+        <v>-57.87665437</v>
       </c>
       <c r="H98" t="n">
-        <v>-57.70773954</v>
+        <v>-36.62885614</v>
       </c>
       <c r="I98" t="n">
-        <v>-36.45684124</v>
+        <v>-32.91272461</v>
       </c>
       <c r="J98" t="n">
-        <v>-33.17751057</v>
+        <v>-31.98487371</v>
       </c>
       <c r="K98" t="n">
-        <v>-32.66692659</v>
+        <v>-28.05827051</v>
       </c>
       <c r="L98" t="n">
-        <v>-28.58669746</v>
+        <v>-31.36616687</v>
       </c>
       <c r="M98" t="n">
-        <v>-32.48884227</v>
+        <v>-10.44515264</v>
       </c>
     </row>
     <row r="99">
@@ -4488,37 +4490,37 @@
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>17.8093649</v>
+        <v>20.89206484</v>
       </c>
       <c r="D99" t="n">
-        <v>20.89138356</v>
+        <v>4.255960159999999</v>
       </c>
       <c r="E99" t="n">
-        <v>4.255614609999999</v>
+        <v>-13.81783122</v>
       </c>
       <c r="F99" t="n">
-        <v>-13.8180535</v>
+        <v>8.902682299999999</v>
       </c>
       <c r="G99" t="n">
-        <v>8.90267367</v>
+        <v>-7.00097985</v>
       </c>
       <c r="H99" t="n">
-        <v>-7.00088521</v>
+        <v>-8.586387240000001</v>
       </c>
       <c r="I99" t="n">
-        <v>-8.586196810000001</v>
+        <v>-10.56307657</v>
       </c>
       <c r="J99" t="n">
-        <v>-10.56292261</v>
+        <v>-11.32923905</v>
       </c>
       <c r="K99" t="n">
-        <v>-11.32881665</v>
+        <v>2.98401102</v>
       </c>
       <c r="L99" t="n">
-        <v>2.98430139</v>
+        <v>1.30875266</v>
       </c>
       <c r="M99" t="n">
-        <v>1.3088601</v>
+        <v>-3.510710399999999</v>
       </c>
     </row>
     <row r="100">
@@ -4529,37 +4531,37 @@
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="n">
-        <v>43.38163308</v>
+        <v>65.07351196</v>
       </c>
       <c r="D100" t="n">
-        <v>65.00174194</v>
+        <v>78.41909075999999</v>
       </c>
       <c r="E100" t="n">
-        <v>77.65145758999999</v>
+        <v>92.08884234999999</v>
       </c>
       <c r="F100" t="n">
-        <v>92.38535831</v>
+        <v>-53.37163051</v>
       </c>
       <c r="G100" t="n">
-        <v>-53.90495987000001</v>
+        <v>-138.98959363</v>
       </c>
       <c r="H100" t="n">
-        <v>-139.1586031</v>
+        <v>-186.96238045</v>
       </c>
       <c r="I100" t="n">
-        <v>-187.13458578</v>
+        <v>-263.10589982</v>
       </c>
       <c r="J100" t="n">
-        <v>-262.84126782</v>
+        <v>-271.70482822</v>
       </c>
       <c r="K100" t="n">
-        <v>-271.02319774</v>
+        <v>-157.31249025</v>
       </c>
       <c r="L100" t="n">
-        <v>-156.78435367</v>
+        <v>-223.51401407</v>
       </c>
       <c r="M100" t="n">
-        <v>-222.39144611</v>
+        <v>-120.79845952</v>
       </c>
     </row>
   </sheetData>

--- a/Result/analyze_2.xlsx
+++ b/Result/analyze_2.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-04</t>
         </is>
       </c>
     </row>
@@ -503,37 +503,37 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>127.95919719</v>
+        <v>203.49008685</v>
       </c>
       <c r="D2" t="n">
-        <v>203.49289</v>
+        <v>-276.35701626</v>
       </c>
       <c r="E2" t="n">
-        <v>-276.35023151</v>
+        <v>158.97861774</v>
       </c>
       <c r="F2" t="n">
-        <v>158.97995833</v>
+        <v>273.1721498</v>
       </c>
       <c r="G2" t="n">
-        <v>273.16832933</v>
+        <v>109.07311689</v>
       </c>
       <c r="H2" t="n">
-        <v>109.07201334</v>
+        <v>397.81934154</v>
       </c>
       <c r="I2" t="n">
-        <v>397.81500457</v>
+        <v>-15.38801818000001</v>
       </c>
       <c r="J2" t="n">
-        <v>-15.39561179000001</v>
+        <v>227.952527</v>
       </c>
       <c r="K2" t="n">
-        <v>227.93637408</v>
+        <v>613.87092129</v>
       </c>
       <c r="L2" t="n">
-        <v>613.8424225</v>
+        <v>670.9315105500001</v>
       </c>
       <c r="M2" t="n">
-        <v>670.9141331700001</v>
+        <v>931.5625464399998</v>
       </c>
     </row>
     <row r="3">
@@ -544,37 +544,37 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>-54.91244948000001</v>
+        <v>-67.23004175</v>
       </c>
       <c r="D3" t="n">
-        <v>-74.32056421000001</v>
+        <v>-166.33005423</v>
       </c>
       <c r="E3" t="n">
-        <v>-175.84137512</v>
+        <v>6.232973830000001</v>
       </c>
       <c r="F3" t="n">
-        <v>4.470229860000002</v>
+        <v>65.41039418</v>
       </c>
       <c r="G3" t="n">
-        <v>65.91919256</v>
+        <v>149.15657245</v>
       </c>
       <c r="H3" t="n">
-        <v>148.60531562</v>
+        <v>212.78266681</v>
       </c>
       <c r="I3" t="n">
-        <v>216.59486601</v>
+        <v>119.32230385</v>
       </c>
       <c r="J3" t="n">
-        <v>120.05869735</v>
+        <v>181.43881515</v>
       </c>
       <c r="K3" t="n">
-        <v>183.62103201</v>
+        <v>21.08890903</v>
       </c>
       <c r="L3" t="n">
-        <v>19.38308904</v>
+        <v>6.802920000000005</v>
       </c>
       <c r="M3" t="n">
-        <v>5.290656840000007</v>
+        <v>147.95318511</v>
       </c>
     </row>
     <row r="4">
@@ -585,37 +585,37 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>547.71554956</v>
+        <v>472.85010655</v>
       </c>
       <c r="D4" t="n">
-        <v>479.93782586</v>
+        <v>-43.93529771</v>
       </c>
       <c r="E4" t="n">
-        <v>-34.43076157000001</v>
+        <v>-127.60277108</v>
       </c>
       <c r="F4" t="n">
-        <v>-125.8413677</v>
+        <v>108.22163553</v>
       </c>
       <c r="G4" t="n">
-        <v>107.71665762</v>
+        <v>-42.20586677999999</v>
       </c>
       <c r="H4" t="n">
-        <v>-41.65350639999999</v>
+        <v>-72.29777823000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-76.10564045999999</v>
+        <v>-183.7035571</v>
       </c>
       <c r="J4" t="n">
-        <v>-184.43235699</v>
+        <v>-53.64276901</v>
       </c>
       <c r="K4" t="n">
-        <v>-55.80883295000001</v>
+        <v>-170.87362768</v>
       </c>
       <c r="L4" t="n">
-        <v>-169.1393089</v>
+        <v>-222.20792707</v>
       </c>
       <c r="M4" t="n">
-        <v>-220.1144846</v>
+        <v>-46.49547533</v>
       </c>
     </row>
     <row r="5">
@@ -626,37 +626,37 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>-80.57878520999999</v>
+        <v>-41.82464505999999</v>
       </c>
       <c r="D5" t="n">
-        <v>-41.82454427</v>
+        <v>-198.68233339</v>
       </c>
       <c r="E5" t="n">
-        <v>-198.68212282</v>
+        <v>-126.15324289</v>
       </c>
       <c r="F5" t="n">
-        <v>-126.15321476</v>
+        <v>186.82804932</v>
       </c>
       <c r="G5" t="n">
-        <v>186.82817224</v>
+        <v>467.84842782</v>
       </c>
       <c r="H5" t="n">
-        <v>467.84870192</v>
+        <v>758.27957524</v>
       </c>
       <c r="I5" t="n">
-        <v>758.27998281</v>
+        <v>802.1054623700001</v>
       </c>
       <c r="J5" t="n">
-        <v>802.10581856</v>
+        <v>1311.67882669</v>
       </c>
       <c r="K5" t="n">
-        <v>1311.67911888</v>
+        <v>1402.60993889</v>
       </c>
       <c r="L5" t="n">
-        <v>1402.61016698</v>
+        <v>947.17838006</v>
       </c>
       <c r="M5" t="n">
-        <v>947.17840165</v>
+        <v>633.9200583099999</v>
       </c>
     </row>
     <row r="6">
@@ -667,37 +667,37 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>-30.20119688</v>
+        <v>-17.12550561</v>
       </c>
       <c r="D6" t="n">
-        <v>-17.18114108</v>
+        <v>-110.01340852</v>
       </c>
       <c r="E6" t="n">
-        <v>-109.22155964</v>
+        <v>55.37835390999999</v>
       </c>
       <c r="F6" t="n">
-        <v>52.46751640000001</v>
+        <v>36.31399072</v>
       </c>
       <c r="G6" t="n">
-        <v>36.99258923000001</v>
+        <v>-15.07146657</v>
       </c>
       <c r="H6" t="n">
-        <v>-15.6315426</v>
+        <v>-36.4982224</v>
       </c>
       <c r="I6" t="n">
-        <v>-37.31116809</v>
+        <v>-50.54148856</v>
       </c>
       <c r="J6" t="n">
-        <v>-50.83876026999999</v>
+        <v>-51.15717497</v>
       </c>
       <c r="K6" t="n">
-        <v>-51.95025489999999</v>
+        <v>-140.94454075</v>
       </c>
       <c r="L6" t="n">
-        <v>-141.17693016</v>
+        <v>-65.32947157999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-65.94550987</v>
+        <v>61.93062826000001</v>
       </c>
     </row>
     <row r="7">
@@ -708,37 +708,37 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>-0.9401508499999987</v>
+        <v>30.16730997</v>
       </c>
       <c r="D7" t="n">
-        <v>30.22284465</v>
+        <v>17.93510316</v>
       </c>
       <c r="E7" t="n">
-        <v>17.14304371</v>
+        <v>43.01930729000001</v>
       </c>
       <c r="F7" t="n">
-        <v>45.93011667</v>
+        <v>35.57271804000001</v>
       </c>
       <c r="G7" t="n">
-        <v>34.89399661</v>
+        <v>23.90493137</v>
       </c>
       <c r="H7" t="n">
-        <v>24.4647333</v>
+        <v>18.07041166</v>
       </c>
       <c r="I7" t="n">
-        <v>18.88294978</v>
+        <v>12.93310919</v>
       </c>
       <c r="J7" t="n">
-        <v>13.23002471</v>
+        <v>23.3628085</v>
       </c>
       <c r="K7" t="n">
-        <v>24.15559624</v>
+        <v>8.284256969999999</v>
       </c>
       <c r="L7" t="n">
-        <v>8.516418289999999</v>
+        <v>8.101793150000002</v>
       </c>
       <c r="M7" t="n">
-        <v>8.717809850000004</v>
+        <v>10.61864305</v>
       </c>
     </row>
     <row r="8">
@@ -749,37 +749,37 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>1195.38538558</v>
+        <v>600.11167478</v>
       </c>
       <c r="D8" t="n">
-        <v>556.4589227300002</v>
+        <v>-1954.76384583</v>
       </c>
       <c r="E8" t="n">
-        <v>-1944.2599113</v>
+        <v>-601.3486867599999</v>
       </c>
       <c r="F8" t="n">
-        <v>-599.6152991099999</v>
+        <v>1553.77214451</v>
       </c>
       <c r="G8" t="n">
-        <v>1548.76478186</v>
+        <v>1727.70582126</v>
       </c>
       <c r="H8" t="n">
-        <v>1718.89143472</v>
+        <v>1816.7779131</v>
       </c>
       <c r="I8" t="n">
-        <v>1803.15963861</v>
+        <v>294.4739660700001</v>
       </c>
       <c r="J8" t="n">
-        <v>300.95168602</v>
+        <v>-133.97107088</v>
       </c>
       <c r="K8" t="n">
-        <v>-118.262187</v>
+        <v>1435.74773577</v>
       </c>
       <c r="L8" t="n">
-        <v>1443.76986541</v>
+        <v>2186.03386589</v>
       </c>
       <c r="M8" t="n">
-        <v>2180.66499101</v>
+        <v>1070.4454373</v>
       </c>
     </row>
     <row r="9">
@@ -790,37 +790,37 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>21.84615598</v>
+        <v>74.59893966</v>
       </c>
       <c r="D9" t="n">
-        <v>75.89871953000001</v>
+        <v>5.405164230000001</v>
       </c>
       <c r="E9" t="n">
-        <v>5.860238190000002</v>
+        <v>67.87233653</v>
       </c>
       <c r="F9" t="n">
-        <v>68.36908266999998</v>
+        <v>64.29641302</v>
       </c>
       <c r="G9" t="n">
-        <v>64.52141722</v>
+        <v>24.04309969</v>
       </c>
       <c r="H9" t="n">
-        <v>24.17054145</v>
+        <v>-2.54958474</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.58511499</v>
+        <v>5.40583608</v>
       </c>
       <c r="J9" t="n">
-        <v>5.02297822</v>
+        <v>17.64058429</v>
       </c>
       <c r="K9" t="n">
-        <v>17.57920718</v>
+        <v>-18.94115622</v>
       </c>
       <c r="L9" t="n">
-        <v>-18.75978422</v>
+        <v>37.6286003</v>
       </c>
       <c r="M9" t="n">
-        <v>37.68639279</v>
+        <v>35.63607057</v>
       </c>
     </row>
     <row r="10">
@@ -831,37 +831,37 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>186.37600926</v>
+        <v>30.11313543999999</v>
       </c>
       <c r="D10" t="n">
-        <v>72.46610762</v>
+        <v>-116.35059885</v>
       </c>
       <c r="E10" t="n">
-        <v>-127.30960734</v>
+        <v>-19.88571498</v>
       </c>
       <c r="F10" t="n">
-        <v>-22.11584877</v>
+        <v>75.96020147</v>
       </c>
       <c r="G10" t="n">
-        <v>80.74255992000001</v>
+        <v>-32.51842934999999</v>
       </c>
       <c r="H10" t="n">
-        <v>-23.83148457</v>
+        <v>-56.9996982</v>
       </c>
       <c r="I10" t="n">
-        <v>-43.34589346</v>
+        <v>-105.63273326</v>
       </c>
       <c r="J10" t="n">
-        <v>-111.72759535</v>
+        <v>-38.63570006</v>
       </c>
       <c r="K10" t="n">
-        <v>-54.28320683</v>
+        <v>-10.3505524</v>
       </c>
       <c r="L10" t="n">
-        <v>-18.55405404</v>
+        <v>99.57899974999999</v>
       </c>
       <c r="M10" t="n">
-        <v>104.89008214</v>
+        <v>45.90581191</v>
       </c>
     </row>
     <row r="11">
@@ -872,37 +872,37 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>21.06413663</v>
+        <v>16.45993232</v>
       </c>
       <c r="D11" t="n">
-        <v>18.10102991</v>
+        <v>2.859002090000001</v>
       </c>
       <c r="E11" t="n">
-        <v>4.557968200000001</v>
+        <v>23.8488836</v>
       </c>
       <c r="F11" t="n">
-        <v>25.1602354</v>
+        <v>31.95600483</v>
       </c>
       <c r="G11" t="n">
-        <v>32.84137479</v>
+        <v>36.40751091</v>
       </c>
       <c r="H11" t="n">
-        <v>35.49912004999999</v>
+        <v>70.07194070999999</v>
       </c>
       <c r="I11" t="n">
-        <v>70.59165781</v>
+        <v>11.69021167</v>
       </c>
       <c r="J11" t="n">
-        <v>12.96211003</v>
+        <v>59.84247325</v>
       </c>
       <c r="K11" t="n">
-        <v>60.57403519</v>
+        <v>132.53821739</v>
       </c>
       <c r="L11" t="n">
-        <v>133.73712991</v>
+        <v>62.3192098</v>
       </c>
       <c r="M11" t="n">
-        <v>63.03845849</v>
+        <v>59.63880218</v>
       </c>
     </row>
     <row r="12">
@@ -913,37 +913,37 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>195.34927787</v>
+        <v>248.90957013</v>
       </c>
       <c r="D12" t="n">
-        <v>248.90957013</v>
+        <v>38.94469194999999</v>
       </c>
       <c r="E12" t="n">
-        <v>38.94469194999999</v>
+        <v>43.88918375</v>
       </c>
       <c r="F12" t="n">
-        <v>43.88918375</v>
+        <v>181.12827274</v>
       </c>
       <c r="G12" t="n">
-        <v>181.12827274</v>
+        <v>62.28709359</v>
       </c>
       <c r="H12" t="n">
-        <v>62.28709359</v>
+        <v>47.51182313</v>
       </c>
       <c r="I12" t="n">
-        <v>47.51182313</v>
+        <v>-67.86251213</v>
       </c>
       <c r="J12" t="n">
-        <v>-67.86251213</v>
+        <v>117.04709593</v>
       </c>
       <c r="K12" t="n">
-        <v>117.04709593</v>
+        <v>1.19653822</v>
       </c>
       <c r="L12" t="n">
-        <v>1.19653822</v>
+        <v>-83.11722171000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-83.11722171000001</v>
+        <v>-44.36274827</v>
       </c>
     </row>
     <row r="13">
@@ -954,37 +954,37 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>0.6288524099999997</v>
+        <v>1.29052322</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.3505743700000001</v>
+        <v>-1.64482739</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.3437935</v>
+        <v>2.07536182</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7640100200000001</v>
+        <v>0.49718892</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.38818104</v>
+        <v>-1.20818879</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.2997979300000001</v>
+        <v>-0.03567795000000003</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.55539505</v>
+        <v>1.16522951</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.1066688500000001</v>
+        <v>2.46887667</v>
       </c>
       <c r="K13" t="n">
-        <v>1.73731473</v>
+        <v>3.68953275</v>
       </c>
       <c r="L13" t="n">
-        <v>2.49062023</v>
+        <v>2.212082590000001</v>
       </c>
       <c r="M13" t="n">
-        <v>1.4928339</v>
+        <v>2.475399079999999</v>
       </c>
     </row>
     <row r="14">
@@ -995,37 +995,37 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>6025.853046519999</v>
+        <v>-73.80787921000001</v>
       </c>
       <c r="D14" t="n">
-        <v>82.44883361000001</v>
+        <v>-6404.986798970001</v>
       </c>
       <c r="E14" t="n">
-        <v>-6433.896442570001</v>
+        <v>-2387.28499942</v>
       </c>
       <c r="F14" t="n">
-        <v>-2269.84513997</v>
+        <v>-3210.22790721</v>
       </c>
       <c r="G14" t="n">
-        <v>-3003.78359303</v>
+        <v>-6061.21163653</v>
       </c>
       <c r="H14" t="n">
-        <v>-6021.93955622</v>
+        <v>-8186.855044399999</v>
       </c>
       <c r="I14" t="n">
-        <v>-8049.94423817</v>
+        <v>-11815.19871817</v>
       </c>
       <c r="J14" t="n">
-        <v>-11793.53571359</v>
+        <v>-5578.29502055</v>
       </c>
       <c r="K14" t="n">
-        <v>-5709.79791283</v>
+        <v>-719.4418733800004</v>
       </c>
       <c r="L14" t="n">
-        <v>-682.4450672300004</v>
+        <v>-4048.66307044</v>
       </c>
       <c r="M14" t="n">
-        <v>-4494.947423600001</v>
+        <v>-6007.02146868</v>
       </c>
     </row>
     <row r="15">
@@ -1038,37 +1038,37 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>785.9075450199999</v>
+        <v>597.56649538</v>
       </c>
       <c r="D15" t="n">
-        <v>597.56706706</v>
+        <v>-55.82158261999998</v>
       </c>
       <c r="E15" t="n">
-        <v>-55.82149363999999</v>
+        <v>767.9598315500001</v>
       </c>
       <c r="F15" t="n">
-        <v>767.96032906</v>
+        <v>424.02378399</v>
       </c>
       <c r="G15" t="n">
-        <v>424.02397229</v>
+        <v>575.7480783</v>
       </c>
       <c r="H15" t="n">
-        <v>575.7483816</v>
+        <v>493.0647100100001</v>
       </c>
       <c r="I15" t="n">
-        <v>493.0651961</v>
+        <v>2.393189149999978</v>
       </c>
       <c r="J15" t="n">
-        <v>2.393348989999978</v>
+        <v>140.80050117</v>
       </c>
       <c r="K15" t="n">
-        <v>140.80085853</v>
+        <v>-526.47615674</v>
       </c>
       <c r="L15" t="n">
-        <v>-526.47618612</v>
+        <v>-84.51514500999998</v>
       </c>
       <c r="M15" t="n">
-        <v>-85.15016720999999</v>
+        <v>125.42301085</v>
       </c>
     </row>
     <row r="16">
@@ -1079,37 +1079,37 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>214.83832883</v>
+        <v>195.75642651</v>
       </c>
       <c r="D16" t="n">
-        <v>37.86505968999997</v>
+        <v>-301.8312480700001</v>
       </c>
       <c r="E16" t="n">
-        <v>-478.29208159</v>
+        <v>619.2252684399999</v>
       </c>
       <c r="F16" t="n">
-        <v>120.78985269</v>
+        <v>100.98110874</v>
       </c>
       <c r="G16" t="n">
-        <v>-264.1486009</v>
+        <v>-126.15191792</v>
       </c>
       <c r="H16" t="n">
-        <v>-215.14933885</v>
+        <v>78.47394292000003</v>
       </c>
       <c r="I16" t="n">
-        <v>-38.16499436</v>
+        <v>279.82426251</v>
       </c>
       <c r="J16" t="n">
-        <v>197.35254887</v>
+        <v>-512.62341522</v>
       </c>
       <c r="K16" t="n">
-        <v>-366.17817746</v>
+        <v>-179.45931426</v>
       </c>
       <c r="L16" t="n">
-        <v>-207.15442516</v>
+        <v>-287.0601313499999</v>
       </c>
       <c r="M16" t="n">
-        <v>219.69826482</v>
+        <v>-955.2026000599999</v>
       </c>
     </row>
     <row r="17">
@@ -1120,37 +1120,37 @@
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
-        <v>0.12858354</v>
+        <v>-0.26640583</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.26640583</v>
+        <v>-0.55064815</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.55064815</v>
+        <v>0.02769861000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>0.02769861000000001</v>
+        <v>0.34979235</v>
       </c>
       <c r="G17" t="n">
-        <v>0.34979235</v>
+        <v>0.55659024</v>
       </c>
       <c r="H17" t="n">
-        <v>0.55659024</v>
+        <v>0.56842657</v>
       </c>
       <c r="I17" t="n">
-        <v>0.56842657</v>
+        <v>0.62029989</v>
       </c>
       <c r="J17" t="n">
-        <v>0.62029989</v>
+        <v>0.79269335</v>
       </c>
       <c r="K17" t="n">
-        <v>0.79269335</v>
+        <v>1.35239712</v>
       </c>
       <c r="L17" t="n">
-        <v>1.35239712</v>
+        <v>2.728404</v>
       </c>
       <c r="M17" t="n">
-        <v>2.728404</v>
+        <v>0.8800688800000001</v>
       </c>
     </row>
     <row r="18">
@@ -1161,37 +1161,37 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>514.5168238700001</v>
+        <v>533.24000686</v>
       </c>
       <c r="D18" t="n">
-        <v>533.24000686</v>
+        <v>338.87725289</v>
       </c>
       <c r="E18" t="n">
-        <v>338.87725289</v>
+        <v>494.0830853900001</v>
       </c>
       <c r="F18" t="n">
-        <v>494.0830853900001</v>
+        <v>317.7273254</v>
       </c>
       <c r="G18" t="n">
-        <v>317.7273254</v>
+        <v>283.6058508000001</v>
       </c>
       <c r="H18" t="n">
-        <v>283.6058508000001</v>
+        <v>797.0432088700001</v>
       </c>
       <c r="I18" t="n">
-        <v>797.0432088700001</v>
+        <v>-142.28295233</v>
       </c>
       <c r="J18" t="n">
-        <v>-142.28295233</v>
+        <v>949.17323245</v>
       </c>
       <c r="K18" t="n">
-        <v>949.17323245</v>
+        <v>786.6830428600001</v>
       </c>
       <c r="L18" t="n">
-        <v>786.6830428600001</v>
+        <v>-272.85884179</v>
       </c>
       <c r="M18" t="n">
-        <v>-272.85884179</v>
+        <v>-871.1229194199999</v>
       </c>
     </row>
     <row r="19">
@@ -1202,37 +1202,37 @@
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>-15.49992431</v>
+        <v>-9.88241236</v>
       </c>
       <c r="D19" t="n">
-        <v>-9.88241236</v>
+        <v>-14.82229246</v>
       </c>
       <c r="E19" t="n">
-        <v>-14.82229246</v>
+        <v>-9.676539879999998</v>
       </c>
       <c r="F19" t="n">
-        <v>-9.676539879999998</v>
+        <v>-12.01174231</v>
       </c>
       <c r="G19" t="n">
-        <v>-12.01174231</v>
+        <v>-11.46147546</v>
       </c>
       <c r="H19" t="n">
-        <v>-11.46147546</v>
+        <v>-4.65901074</v>
       </c>
       <c r="I19" t="n">
-        <v>-4.65901074</v>
+        <v>-9.6175397</v>
       </c>
       <c r="J19" t="n">
-        <v>-9.6175397</v>
+        <v>-3.18361447</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.18361447</v>
+        <v>-6.06011432</v>
       </c>
       <c r="L19" t="n">
-        <v>-6.06011432</v>
+        <v>-6.603619350000001</v>
       </c>
       <c r="M19" t="n">
-        <v>-6.603619350000001</v>
+        <v>-1.86834617</v>
       </c>
     </row>
     <row r="20">
@@ -1243,37 +1243,37 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>7.97299625</v>
+        <v>19.83993459</v>
       </c>
       <c r="D20" t="n">
-        <v>19.83993459</v>
+        <v>5.16841279</v>
       </c>
       <c r="E20" t="n">
-        <v>5.16841279</v>
+        <v>34.60344654</v>
       </c>
       <c r="F20" t="n">
-        <v>34.60344654</v>
+        <v>39.71568626000001</v>
       </c>
       <c r="G20" t="n">
-        <v>39.71568626000001</v>
+        <v>46.16644797999999</v>
       </c>
       <c r="H20" t="n">
-        <v>46.16644797999999</v>
+        <v>49.78897659</v>
       </c>
       <c r="I20" t="n">
-        <v>49.78897659</v>
+        <v>15.83594655</v>
       </c>
       <c r="J20" t="n">
-        <v>15.83594655</v>
+        <v>43.34008297</v>
       </c>
       <c r="K20" t="n">
-        <v>43.34008297</v>
+        <v>-20.57462681</v>
       </c>
       <c r="L20" t="n">
-        <v>-20.57462681</v>
+        <v>-26.64046678</v>
       </c>
       <c r="M20" t="n">
-        <v>-26.64046678</v>
+        <v>-8.66289199</v>
       </c>
     </row>
     <row r="21">
@@ -1284,37 +1284,37 @@
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
-        <v>2.43208974</v>
+        <v>1.92116228</v>
       </c>
       <c r="D21" t="n">
-        <v>1.63599599</v>
+        <v>-2.44418154</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.00738585</v>
+        <v>-2.90937825</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.14724232</v>
+        <v>-0.6914854</v>
       </c>
       <c r="G21" t="n">
-        <v>0.02344989000000001</v>
+        <v>-0.87016615</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5171800299999999</v>
+        <v>0.47642728</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5340939699999999</v>
+        <v>-1.38489539</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.83215267</v>
+        <v>1.01578957</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3099200500000001</v>
+        <v>-0.08695448000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.9929724099999999</v>
+        <v>1.98383284</v>
       </c>
       <c r="M21" t="n">
-        <v>2.02429566</v>
+        <v>2.625483</v>
       </c>
     </row>
     <row r="22">
@@ -1325,37 +1325,37 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>-1.0244927</v>
+        <v>-0.9446688699999999</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6595057899999999</v>
+        <v>-2.6602612</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.09703113</v>
+        <v>-1.56212208</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.32421772</v>
+        <v>-0.48297587</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.19789102</v>
+        <v>0.1275219</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.22544212</v>
+        <v>0.40213993</v>
       </c>
       <c r="I22" t="n">
-        <v>0.34446533</v>
+        <v>-0.1067566</v>
       </c>
       <c r="J22" t="n">
-        <v>0.34050782</v>
+        <v>0.11962009</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8254902999999999</v>
+        <v>0.08824311000000006</v>
       </c>
       <c r="L22" t="n">
-        <v>0.9942745200000001</v>
+        <v>1.53011789</v>
       </c>
       <c r="M22" t="n">
-        <v>1.48964297</v>
+        <v>2.46088503</v>
       </c>
     </row>
     <row r="23">
@@ -1366,37 +1366,37 @@
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
-        <v>5.973501690000004</v>
+        <v>-20.02007137</v>
       </c>
       <c r="D23" t="n">
-        <v>-19.30938348</v>
+        <v>-49.58400418</v>
       </c>
       <c r="E23" t="n">
-        <v>-47.97882261</v>
+        <v>8.735795679999999</v>
       </c>
       <c r="F23" t="n">
-        <v>8.745241110000002</v>
+        <v>26.99976877</v>
       </c>
       <c r="G23" t="n">
-        <v>27.49038917</v>
+        <v>15.13909586</v>
       </c>
       <c r="H23" t="n">
-        <v>16.16811983</v>
+        <v>-1.688928360000001</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.360895950000001</v>
+        <v>-42.37913560000001</v>
       </c>
       <c r="J23" t="n">
-        <v>-43.29145326</v>
+        <v>-18.23225077</v>
       </c>
       <c r="K23" t="n">
-        <v>-21.43741021</v>
+        <v>-27.17241243</v>
       </c>
       <c r="L23" t="n">
-        <v>-26.59232129</v>
+        <v>-9.696450990000002</v>
       </c>
       <c r="M23" t="n">
-        <v>-11.85148476</v>
+        <v>57.26541241</v>
       </c>
     </row>
     <row r="24">
@@ -1405,41 +1405,39 @@
           <t>建材營造右下</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
-        <v>-3.911297130000002</v>
+        <v>-15.04512446</v>
       </c>
       <c r="D24" t="n">
-        <v>-15.46504402</v>
+        <v>-59.08562743</v>
       </c>
       <c r="E24" t="n">
-        <v>-61.87304864</v>
+        <v>-66.95218318999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-67.5022307</v>
+        <v>-81.1055707</v>
       </c>
       <c r="G24" t="n">
-        <v>-80.79731274</v>
+        <v>-84.15877762000001</v>
       </c>
       <c r="H24" t="n">
-        <v>-81.7727792</v>
+        <v>-84.14077758000001</v>
       </c>
       <c r="I24" t="n">
-        <v>-79.22005263000001</v>
+        <v>-82.8272675</v>
       </c>
       <c r="J24" t="n">
-        <v>-82.78374704000001</v>
+        <v>-54.6127678</v>
       </c>
       <c r="K24" t="n">
-        <v>-54.01685006</v>
+        <v>-33.53495641</v>
       </c>
       <c r="L24" t="n">
-        <v>-34.59311788</v>
+        <v>2.644124560000001</v>
       </c>
       <c r="M24" t="n">
-        <v>4.853175940000001</v>
+        <v>45.01555479</v>
       </c>
     </row>
     <row r="25">
@@ -1450,37 +1448,37 @@
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>36.513033</v>
+        <v>58.59532707</v>
       </c>
       <c r="D25" t="n">
-        <v>58.36001469999999</v>
+        <v>23.23946708</v>
       </c>
       <c r="E25" t="n">
-        <v>24.46986895000001</v>
+        <v>82.68932667999999</v>
       </c>
       <c r="F25" t="n">
-        <v>83.05171048000001</v>
+        <v>37.65479465</v>
       </c>
       <c r="G25" t="n">
-        <v>36.59002219999999</v>
+        <v>-12.50337427</v>
       </c>
       <c r="H25" t="n">
-        <v>-16.21405976</v>
+        <v>-53.97935109</v>
       </c>
       <c r="I25" t="n">
-        <v>-59.42012654</v>
+        <v>-97.33563208999999</v>
       </c>
       <c r="J25" t="n">
-        <v>-96.51404439</v>
+        <v>-68.76287831</v>
       </c>
       <c r="K25" t="n">
-        <v>-66.26645638000001</v>
+        <v>-89.16521786</v>
       </c>
       <c r="L25" t="n">
-        <v>-88.72979714</v>
+        <v>-14.55081096</v>
       </c>
       <c r="M25" t="n">
-        <v>-14.44773436</v>
+        <v>74.04329942</v>
       </c>
     </row>
     <row r="26">
@@ -1491,37 +1489,37 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>137.02059128</v>
+        <v>80.11023591</v>
       </c>
       <c r="D26" t="n">
-        <v>80.11023591</v>
+        <v>14.96755027</v>
       </c>
       <c r="E26" t="n">
-        <v>14.96755027</v>
+        <v>60.78673921</v>
       </c>
       <c r="F26" t="n">
-        <v>60.78673921</v>
+        <v>106.4159577</v>
       </c>
       <c r="G26" t="n">
-        <v>106.4159577</v>
+        <v>30.45080732</v>
       </c>
       <c r="H26" t="n">
-        <v>30.45080732</v>
+        <v>27.11465835</v>
       </c>
       <c r="I26" t="n">
-        <v>27.11465835</v>
+        <v>-15.9721707</v>
       </c>
       <c r="J26" t="n">
-        <v>-15.9721707</v>
+        <v>-11.45883006</v>
       </c>
       <c r="K26" t="n">
-        <v>-11.47404628</v>
+        <v>-0.55266821</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.59206841</v>
+        <v>20.27945308</v>
       </c>
       <c r="M26" t="n">
-        <v>20.2350177</v>
+        <v>-15.82722061</v>
       </c>
     </row>
     <row r="27">
@@ -1530,41 +1528,39 @@
           <t>數位雲端右下</t>
         </is>
       </c>
-      <c r="B27" t="n">
-        <v>0</v>
-      </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>15.98260868</v>
+        <v>5.80081306</v>
       </c>
       <c r="D27" t="n">
-        <v>5.80081306</v>
+        <v>-5.07146912</v>
       </c>
       <c r="E27" t="n">
-        <v>-5.07146912</v>
+        <v>19.81744912</v>
       </c>
       <c r="F27" t="n">
-        <v>19.81744912</v>
+        <v>26.50836019999999</v>
       </c>
       <c r="G27" t="n">
-        <v>26.50836019999999</v>
+        <v>12.37337787</v>
       </c>
       <c r="H27" t="n">
-        <v>12.37337787</v>
+        <v>16.88589567</v>
       </c>
       <c r="I27" t="n">
-        <v>16.88589567</v>
+        <v>5.175073139999999</v>
       </c>
       <c r="J27" t="n">
-        <v>5.175073139999999</v>
+        <v>10.18979128</v>
       </c>
       <c r="K27" t="n">
-        <v>10.2050075</v>
+        <v>5.14915096</v>
       </c>
       <c r="L27" t="n">
-        <v>5.18855116</v>
+        <v>12.32444672</v>
       </c>
       <c r="M27" t="n">
-        <v>12.3688821</v>
+        <v>7.234856349999998</v>
       </c>
     </row>
     <row r="28">
@@ -1575,37 +1571,37 @@
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>0.15505805</v>
+        <v>-0.39243835</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.39483859</v>
+        <v>-0.53699452</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.53778595</v>
+        <v>-0.26040162</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.26137895</v>
+        <v>-0.52046288</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.52308184</v>
+        <v>-0.20605795</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.20881999</v>
+        <v>-0.35748572</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.3587911</v>
+        <v>-0.39893829</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.39895759</v>
+        <v>-0.11396285</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.11373782</v>
+        <v>-0.1824895</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.18190578</v>
+        <v>-0.09413411000000002</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.09283578000000001</v>
+        <v>0.162016</v>
       </c>
     </row>
     <row r="29">
@@ -1616,37 +1612,37 @@
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>-0.03888696</v>
+        <v>-0.03307111</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.03401444999999999</v>
+        <v>-0.03255481</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.03154172</v>
+        <v>-0.01281979</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.01295868</v>
+        <v>-0.00154904</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.00221319</v>
+        <v>-0.00032023</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.00056724</v>
+        <v>0.00658342</v>
       </c>
       <c r="I29" t="n">
-        <v>0.00672136</v>
+        <v>-0.00477515</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.00145954</v>
+        <v>0.004036490000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>0.006492230000000001</v>
+        <v>0.01033713</v>
       </c>
       <c r="L29" t="n">
-        <v>0.01229479</v>
+        <v>0.01825068</v>
       </c>
       <c r="M29" t="n">
-        <v>0.01976942</v>
+        <v>0.02746755</v>
       </c>
     </row>
     <row r="30">
@@ -1657,37 +1653,37 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>-0.01467411</v>
+        <v>-0.006610240000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.006610240000000001</v>
+        <v>-0.0134701</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0134701</v>
+        <v>-0.0001509699999999998</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.0001509699999999998</v>
+        <v>-0.00248782</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.00248782</v>
+        <v>0.00563157</v>
       </c>
       <c r="H30" t="n">
-        <v>0.00563157</v>
+        <v>0.0038025</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0038025</v>
+        <v>-0.0011534</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.0011534</v>
+        <v>0.00062989</v>
       </c>
       <c r="K30" t="n">
-        <v>0.00062989</v>
+        <v>-0.005775890000000001</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.005775890000000001</v>
+        <v>0.0001075200000000001</v>
       </c>
       <c r="M30" t="n">
-        <v>0.0001075200000000001</v>
+        <v>0.009618040000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1698,37 +1694,37 @@
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>-0.14618367</v>
+        <v>-0.15155761</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.15061427</v>
+        <v>-0.20980263</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.21081572</v>
+        <v>0.03431755</v>
       </c>
       <c r="F31" t="n">
-        <v>0.03445644</v>
+        <v>-0.05161925</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.0509551</v>
+        <v>0.04175168</v>
       </c>
       <c r="H31" t="n">
-        <v>0.04199869000000001</v>
+        <v>0.00521907</v>
       </c>
       <c r="I31" t="n">
-        <v>0.005081129999999999</v>
+        <v>-0.04567125</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.04898686</v>
+        <v>-0.07319847</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.07565420999999999</v>
+        <v>0.03328875</v>
       </c>
       <c r="L31" t="n">
-        <v>0.03133109000000001</v>
+        <v>0.0009512100000000007</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.00056753</v>
+        <v>0.09886003</v>
       </c>
     </row>
     <row r="32">
@@ -1739,37 +1735,37 @@
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>2.14088619</v>
+        <v>-0.19341137</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.19341137</v>
+        <v>-1.58173283</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.58173283</v>
+        <v>0.79667627</v>
       </c>
       <c r="F32" t="n">
-        <v>0.79667627</v>
+        <v>-0.8938292</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.8938292</v>
+        <v>0.26859018</v>
       </c>
       <c r="H32" t="n">
-        <v>0.26859018</v>
+        <v>-1.1550498</v>
       </c>
       <c r="I32" t="n">
-        <v>-1.1550498</v>
+        <v>0.19597777</v>
       </c>
       <c r="J32" t="n">
-        <v>0.19597777</v>
+        <v>0.93832401</v>
       </c>
       <c r="K32" t="n">
-        <v>0.93832401</v>
+        <v>-0.60581137</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.60581137</v>
+        <v>-0.18124846</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.18124846</v>
+        <v>0.6026511899999999</v>
       </c>
     </row>
     <row r="33">
@@ -1780,37 +1776,37 @@
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
-        <v>26.07414317</v>
+        <v>46.49768424000001</v>
       </c>
       <c r="D33" t="n">
-        <v>46.49768424000001</v>
+        <v>1.71917202</v>
       </c>
       <c r="E33" t="n">
-        <v>1.71917202</v>
+        <v>51.11736981</v>
       </c>
       <c r="F33" t="n">
-        <v>51.11736981</v>
+        <v>74.52305657000001</v>
       </c>
       <c r="G33" t="n">
-        <v>74.52305657000001</v>
+        <v>28.77819571</v>
       </c>
       <c r="H33" t="n">
-        <v>28.77819571</v>
+        <v>47.13405325</v>
       </c>
       <c r="I33" t="n">
-        <v>47.13405325</v>
+        <v>17.62821512</v>
       </c>
       <c r="J33" t="n">
-        <v>17.62821512</v>
+        <v>9.357429240000002</v>
       </c>
       <c r="K33" t="n">
-        <v>9.357429240000002</v>
+        <v>-23.28926443</v>
       </c>
       <c r="L33" t="n">
-        <v>-23.28926443</v>
+        <v>-15.50397747</v>
       </c>
       <c r="M33" t="n">
-        <v>-15.50397747</v>
+        <v>-7.671519279999999</v>
       </c>
     </row>
     <row r="34">
@@ -1821,37 +1817,37 @@
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
-        <v>1.28537791</v>
+        <v>0.6885503099999999</v>
       </c>
       <c r="D34" t="n">
-        <v>0.6885503099999999</v>
+        <v>0.03085148000000001</v>
       </c>
       <c r="E34" t="n">
-        <v>0.03085148000000001</v>
+        <v>0.6241331099999999</v>
       </c>
       <c r="F34" t="n">
-        <v>0.6241331099999999</v>
+        <v>0.6281405</v>
       </c>
       <c r="G34" t="n">
-        <v>0.6281405</v>
+        <v>0.5322796400000001</v>
       </c>
       <c r="H34" t="n">
-        <v>0.5322796400000001</v>
+        <v>0.66688402</v>
       </c>
       <c r="I34" t="n">
-        <v>0.66688402</v>
+        <v>0.39455165</v>
       </c>
       <c r="J34" t="n">
-        <v>0.39455165</v>
+        <v>0.7616216099999999</v>
       </c>
       <c r="K34" t="n">
-        <v>0.7616216099999999</v>
+        <v>0.68170787</v>
       </c>
       <c r="L34" t="n">
-        <v>0.68170787</v>
+        <v>0.03184879000000001</v>
       </c>
       <c r="M34" t="n">
-        <v>0.03184879000000001</v>
+        <v>-0.05228055</v>
       </c>
     </row>
     <row r="35">
@@ -1862,37 +1858,37 @@
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
-        <v>-32.78750292</v>
+        <v>29.79901899</v>
       </c>
       <c r="D35" t="n">
-        <v>29.79901899</v>
+        <v>191.1411963</v>
       </c>
       <c r="E35" t="n">
-        <v>191.1411963</v>
+        <v>281.70180355</v>
       </c>
       <c r="F35" t="n">
-        <v>281.70180355</v>
+        <v>169.91598432</v>
       </c>
       <c r="G35" t="n">
-        <v>169.91598432</v>
+        <v>151.94936306</v>
       </c>
       <c r="H35" t="n">
-        <v>151.94936306</v>
+        <v>180.3735272</v>
       </c>
       <c r="I35" t="n">
-        <v>180.3735272</v>
+        <v>110.71375524</v>
       </c>
       <c r="J35" t="n">
-        <v>110.71375524</v>
+        <v>152.65296865</v>
       </c>
       <c r="K35" t="n">
-        <v>152.65296865</v>
+        <v>75.59350051</v>
       </c>
       <c r="L35" t="n">
-        <v>75.59350051</v>
+        <v>33.17521386</v>
       </c>
       <c r="M35" t="n">
-        <v>33.17521386</v>
+        <v>20.83055937</v>
       </c>
     </row>
     <row r="36">
@@ -1903,37 +1899,37 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>44.72266871</v>
+        <v>82.34751310999999</v>
       </c>
       <c r="D36" t="n">
-        <v>57.7183895</v>
+        <v>-20.24144777</v>
       </c>
       <c r="E36" t="n">
-        <v>16.06229448</v>
+        <v>25.74357816000001</v>
       </c>
       <c r="F36" t="n">
-        <v>64.33256663</v>
+        <v>-23.20394607</v>
       </c>
       <c r="G36" t="n">
-        <v>10.04559587</v>
+        <v>-46.50593372</v>
       </c>
       <c r="H36" t="n">
-        <v>-26.98847005</v>
+        <v>-73.58654622</v>
       </c>
       <c r="I36" t="n">
-        <v>-56.02270716</v>
+        <v>-69.61487504999999</v>
       </c>
       <c r="J36" t="n">
-        <v>-66.06686309</v>
+        <v>-38.2629963</v>
       </c>
       <c r="K36" t="n">
-        <v>-35.53463518</v>
+        <v>2.09840131</v>
       </c>
       <c r="L36" t="n">
-        <v>5.89095571</v>
+        <v>4.881436730000001</v>
       </c>
       <c r="M36" t="n">
-        <v>-9.68118084</v>
+        <v>41.34069034</v>
       </c>
     </row>
     <row r="37">
@@ -1944,37 +1940,37 @@
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>52.08126556000001</v>
+        <v>9.633830980000003</v>
       </c>
       <c r="D37" t="n">
-        <v>41.51401431</v>
+        <v>-23.40385333</v>
       </c>
       <c r="E37" t="n">
-        <v>-11.49951154</v>
+        <v>57.54664698</v>
       </c>
       <c r="F37" t="n">
-        <v>80.82614101</v>
+        <v>59.14021824</v>
       </c>
       <c r="G37" t="n">
-        <v>66.01691722999999</v>
+        <v>51.38866752999999</v>
       </c>
       <c r="H37" t="n">
-        <v>48.47841772</v>
+        <v>50.08324433999999</v>
       </c>
       <c r="I37" t="n">
-        <v>53.14321922</v>
+        <v>32.01164784</v>
       </c>
       <c r="J37" t="n">
-        <v>29.27277965</v>
+        <v>65.08389405</v>
       </c>
       <c r="K37" t="n">
-        <v>73.12264562</v>
+        <v>-5.245381119999999</v>
       </c>
       <c r="L37" t="n">
-        <v>-12.08264623</v>
+        <v>0.09162379999999946</v>
       </c>
       <c r="M37" t="n">
-        <v>14.60630841</v>
+        <v>23.55432724</v>
       </c>
     </row>
     <row r="38">
@@ -1985,37 +1981,37 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>17.92583462</v>
+        <v>83.65572380000002</v>
       </c>
       <c r="D38" t="n">
-        <v>76.40466408</v>
+        <v>-17.88309525</v>
       </c>
       <c r="E38" t="n">
-        <v>-66.09117928999999</v>
+        <v>95.39936956999999</v>
       </c>
       <c r="F38" t="n">
-        <v>33.53088707</v>
+        <v>89.08669624000001</v>
       </c>
       <c r="G38" t="n">
-        <v>48.96045531</v>
+        <v>19.73452993</v>
       </c>
       <c r="H38" t="n">
-        <v>3.12731607</v>
+        <v>-11.29958163</v>
       </c>
       <c r="I38" t="n">
-        <v>-31.92339557</v>
+        <v>-63.47355001</v>
       </c>
       <c r="J38" t="n">
-        <v>-64.28269378</v>
+        <v>7.24893328</v>
       </c>
       <c r="K38" t="n">
-        <v>-3.518179410000001</v>
+        <v>-41.01745597</v>
       </c>
       <c r="L38" t="n">
-        <v>-37.97274526</v>
+        <v>-7.559331070000001</v>
       </c>
       <c r="M38" t="n">
-        <v>-7.511398109999999</v>
+        <v>38.06963589</v>
       </c>
     </row>
     <row r="39">
@@ -2026,37 +2022,37 @@
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
-        <v>31.88991085</v>
+        <v>38.42099165</v>
       </c>
       <c r="D39" t="n">
-        <v>38.42099165</v>
+        <v>11.11791429</v>
       </c>
       <c r="E39" t="n">
-        <v>11.11791429</v>
+        <v>32.60895456999999</v>
       </c>
       <c r="F39" t="n">
-        <v>32.60895456999999</v>
+        <v>56.67209458</v>
       </c>
       <c r="G39" t="n">
-        <v>56.67209458</v>
+        <v>17.94407397</v>
       </c>
       <c r="H39" t="n">
-        <v>17.94407397</v>
+        <v>33.68792604</v>
       </c>
       <c r="I39" t="n">
-        <v>33.68792604</v>
+        <v>4.108083939999999</v>
       </c>
       <c r="J39" t="n">
-        <v>4.108083939999999</v>
+        <v>73.39446294</v>
       </c>
       <c r="K39" t="n">
-        <v>73.39446294</v>
+        <v>168.35310772</v>
       </c>
       <c r="L39" t="n">
-        <v>168.35310772</v>
+        <v>54.65563677999999</v>
       </c>
       <c r="M39" t="n">
-        <v>54.65563677999999</v>
+        <v>-40.04566426</v>
       </c>
     </row>
     <row r="40">
@@ -2067,37 +2063,37 @@
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>15.27198214</v>
+        <v>18.70547509</v>
       </c>
       <c r="D40" t="n">
-        <v>18.70547509</v>
+        <v>6.664288</v>
       </c>
       <c r="E40" t="n">
-        <v>6.664288</v>
+        <v>7.2135412</v>
       </c>
       <c r="F40" t="n">
-        <v>7.2135412</v>
+        <v>0.08460432999999999</v>
       </c>
       <c r="G40" t="n">
-        <v>0.08460432999999999</v>
+        <v>-3.21255832</v>
       </c>
       <c r="H40" t="n">
-        <v>-3.21255832</v>
+        <v>-6.40072734</v>
       </c>
       <c r="I40" t="n">
-        <v>-6.40072734</v>
+        <v>-3.77333719</v>
       </c>
       <c r="J40" t="n">
-        <v>-3.77333719</v>
+        <v>1.57257904</v>
       </c>
       <c r="K40" t="n">
-        <v>1.57257904</v>
+        <v>-2.42404502</v>
       </c>
       <c r="L40" t="n">
-        <v>-2.42404502</v>
+        <v>-1.22188635</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.22188635</v>
+        <v>2.19978092</v>
       </c>
     </row>
     <row r="41">
@@ -2108,37 +2104,37 @@
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
-        <v>-78.61716095999999</v>
+        <v>-63.09958463</v>
       </c>
       <c r="D41" t="n">
-        <v>-63.09958463</v>
+        <v>-76.87109083</v>
       </c>
       <c r="E41" t="n">
-        <v>-76.87109083</v>
+        <v>85.15477465000001</v>
       </c>
       <c r="F41" t="n">
-        <v>85.15477465000001</v>
+        <v>307.60971191</v>
       </c>
       <c r="G41" t="n">
-        <v>307.60971191</v>
+        <v>433.81361385</v>
       </c>
       <c r="H41" t="n">
-        <v>433.81361385</v>
+        <v>668.62466564</v>
       </c>
       <c r="I41" t="n">
-        <v>668.62466564</v>
+        <v>244.91801602</v>
       </c>
       <c r="J41" t="n">
-        <v>244.91801602</v>
+        <v>320.90370974</v>
       </c>
       <c r="K41" t="n">
-        <v>320.90370974</v>
+        <v>479.18507195</v>
       </c>
       <c r="L41" t="n">
-        <v>479.18507195</v>
+        <v>759.412483</v>
       </c>
       <c r="M41" t="n">
-        <v>759.412483</v>
+        <v>264.18557726</v>
       </c>
     </row>
     <row r="42">
@@ -2149,37 +2145,37 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>2.38658788</v>
+        <v>2.76879612</v>
       </c>
       <c r="D42" t="n">
-        <v>2.76879612</v>
+        <v>1.39195655</v>
       </c>
       <c r="E42" t="n">
-        <v>1.39195655</v>
+        <v>3.33996648</v>
       </c>
       <c r="F42" t="n">
-        <v>3.33996648</v>
+        <v>4.04519709</v>
       </c>
       <c r="G42" t="n">
-        <v>4.04519709</v>
+        <v>4.39753474</v>
       </c>
       <c r="H42" t="n">
-        <v>4.39753474</v>
+        <v>5.01754811</v>
       </c>
       <c r="I42" t="n">
-        <v>5.01754811</v>
+        <v>5.69713828</v>
       </c>
       <c r="J42" t="n">
-        <v>5.69713828</v>
+        <v>14.7458941</v>
       </c>
       <c r="K42" t="n">
-        <v>14.7458941</v>
+        <v>7.43637919</v>
       </c>
       <c r="L42" t="n">
-        <v>7.43637919</v>
+        <v>9.030643980000001</v>
       </c>
       <c r="M42" t="n">
-        <v>9.030643980000001</v>
+        <v>7.387953179999999</v>
       </c>
     </row>
     <row r="43">
@@ -2190,37 +2186,37 @@
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
-        <v>-0.64378347</v>
+        <v>-0.38199066</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.38199066</v>
+        <v>-1.4309121</v>
       </c>
       <c r="E43" t="n">
-        <v>-1.4309121</v>
+        <v>1.94254906</v>
       </c>
       <c r="F43" t="n">
-        <v>1.94254906</v>
+        <v>9.474221210000001</v>
       </c>
       <c r="G43" t="n">
-        <v>9.474221210000001</v>
+        <v>3.52060646</v>
       </c>
       <c r="H43" t="n">
-        <v>3.52060646</v>
+        <v>7.11610011</v>
       </c>
       <c r="I43" t="n">
-        <v>7.11610011</v>
+        <v>3.20700107</v>
       </c>
       <c r="J43" t="n">
-        <v>3.20700107</v>
+        <v>1.61384816</v>
       </c>
       <c r="K43" t="n">
-        <v>1.61384816</v>
+        <v>0.5450071499999999</v>
       </c>
       <c r="L43" t="n">
-        <v>0.5450071499999999</v>
+        <v>2.44174181</v>
       </c>
       <c r="M43" t="n">
-        <v>2.44174181</v>
+        <v>-0.2750045700000001</v>
       </c>
     </row>
     <row r="44">
@@ -2231,37 +2227,37 @@
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>190.33483352</v>
+        <v>79.85056292</v>
       </c>
       <c r="D44" t="n">
-        <v>121.65825754</v>
+        <v>1.62948498</v>
       </c>
       <c r="E44" t="n">
-        <v>-30.99881446</v>
+        <v>28.40165868</v>
       </c>
       <c r="F44" t="n">
-        <v>87.01359362000001</v>
+        <v>65.65651996</v>
       </c>
       <c r="G44" t="n">
-        <v>69.61852187000001</v>
+        <v>5.88662527</v>
       </c>
       <c r="H44" t="n">
-        <v>-24.77563102</v>
+        <v>-37.47173023</v>
       </c>
       <c r="I44" t="n">
-        <v>12.27685316</v>
+        <v>-78.36247659999999</v>
       </c>
       <c r="J44" t="n">
-        <v>-117.81225534</v>
+        <v>-11.41209755</v>
       </c>
       <c r="K44" t="n">
-        <v>-107.77603948</v>
+        <v>-12.36702131</v>
       </c>
       <c r="L44" t="n">
-        <v>-42.36237779</v>
+        <v>4.168181860000002</v>
       </c>
       <c r="M44" t="n">
-        <v>71.38909197</v>
+        <v>-19.49896853</v>
       </c>
     </row>
     <row r="45">
@@ -2270,41 +2266,39 @@
           <t>生技醫療業右下</t>
         </is>
       </c>
-      <c r="B45" t="n">
-        <v>0</v>
-      </c>
+      <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
-        <v>53.14560842</v>
+        <v>-30.00020119</v>
       </c>
       <c r="D45" t="n">
-        <v>-29.26108884000001</v>
+        <v>-597.35391013</v>
       </c>
       <c r="E45" t="n">
-        <v>-597.49573645</v>
+        <v>-104.84622099</v>
       </c>
       <c r="F45" t="n">
-        <v>-104.10864394</v>
+        <v>140.48645098</v>
       </c>
       <c r="G45" t="n">
-        <v>141.14766511</v>
+        <v>271.73166425</v>
       </c>
       <c r="H45" t="n">
-        <v>272.19530525</v>
+        <v>-26.51753093</v>
       </c>
       <c r="I45" t="n">
-        <v>-26.17901317</v>
+        <v>-232.1853368</v>
       </c>
       <c r="J45" t="n">
-        <v>-232.600864</v>
+        <v>-348.8411457399999</v>
       </c>
       <c r="K45" t="n">
-        <v>-348.26249207</v>
+        <v>-324.03077307</v>
       </c>
       <c r="L45" t="n">
-        <v>-324.45211075</v>
+        <v>-311.6297213</v>
       </c>
       <c r="M45" t="n">
-        <v>-311.36017096</v>
+        <v>-65.95265696999999</v>
       </c>
     </row>
     <row r="46">
@@ -2315,37 +2309,37 @@
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>62.95070912999999</v>
+        <v>48.85730937</v>
       </c>
       <c r="D46" t="n">
-        <v>6.310727320000001</v>
+        <v>-89.51192533999999</v>
       </c>
       <c r="E46" t="n">
-        <v>-56.74143730999999</v>
+        <v>65.85137101000001</v>
       </c>
       <c r="F46" t="n">
-        <v>6.502091459999999</v>
+        <v>-41.56200412</v>
       </c>
       <c r="G46" t="n">
-        <v>-46.1849935</v>
+        <v>-135.892264</v>
       </c>
       <c r="H46" t="n">
-        <v>-105.69346251</v>
+        <v>-71.44401619</v>
       </c>
       <c r="I46" t="n">
-        <v>-121.53073867</v>
+        <v>-188.8055999</v>
       </c>
       <c r="J46" t="n">
-        <v>-148.94011808</v>
+        <v>-249.41551529</v>
       </c>
       <c r="K46" t="n">
-        <v>-153.63024872</v>
+        <v>-193.81034374</v>
       </c>
       <c r="L46" t="n">
-        <v>-163.39371761</v>
+        <v>46.98716446</v>
       </c>
       <c r="M46" t="n">
-        <v>-20.50349563</v>
+        <v>3.458085520000008</v>
       </c>
     </row>
     <row r="47">
@@ -2356,37 +2350,37 @@
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>-3.321631309999999</v>
+        <v>-3.11363331</v>
       </c>
       <c r="D47" t="n">
-        <v>-3.11363331</v>
+        <v>-4.72339887</v>
       </c>
       <c r="E47" t="n">
-        <v>-4.72339887</v>
+        <v>-1.49148739</v>
       </c>
       <c r="F47" t="n">
-        <v>-1.49148739</v>
+        <v>2.33220014</v>
       </c>
       <c r="G47" t="n">
-        <v>2.33220014</v>
+        <v>-2.68896906</v>
       </c>
       <c r="H47" t="n">
-        <v>-2.68896906</v>
+        <v>-6.34562959</v>
       </c>
       <c r="I47" t="n">
-        <v>-6.34562959</v>
+        <v>-8.065714099999999</v>
       </c>
       <c r="J47" t="n">
-        <v>-8.065714099999999</v>
+        <v>-5.8884915</v>
       </c>
       <c r="K47" t="n">
-        <v>-5.8884915</v>
+        <v>-5.95645232</v>
       </c>
       <c r="L47" t="n">
-        <v>-5.95645232</v>
+        <v>-5.16068395</v>
       </c>
       <c r="M47" t="n">
-        <v>-5.16068395</v>
+        <v>-5.24392124</v>
       </c>
     </row>
     <row r="48">
@@ -2397,37 +2391,37 @@
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
-        <v>-9.719348770000002</v>
+        <v>87.60524620999999</v>
       </c>
       <c r="D48" t="n">
-        <v>87.66968166999999</v>
+        <v>-110.25147541</v>
       </c>
       <c r="E48" t="n">
-        <v>-110.19884231</v>
+        <v>51.69443244</v>
       </c>
       <c r="F48" t="n">
-        <v>51.74861537</v>
+        <v>112.31552985</v>
       </c>
       <c r="G48" t="n">
-        <v>112.36569676</v>
+        <v>53.45619471</v>
       </c>
       <c r="H48" t="n">
-        <v>53.50560005</v>
+        <v>95.04986186999999</v>
       </c>
       <c r="I48" t="n">
-        <v>95.05480141</v>
+        <v>9.407378970000002</v>
       </c>
       <c r="J48" t="n">
-        <v>9.371867360000001</v>
+        <v>39.68573421</v>
       </c>
       <c r="K48" t="n">
-        <v>39.77664651000001</v>
+        <v>4.959421839999997</v>
       </c>
       <c r="L48" t="n">
-        <v>5.021144390000001</v>
+        <v>20.79778082</v>
       </c>
       <c r="M48" t="n">
-        <v>20.83421519</v>
+        <v>26.43966846</v>
       </c>
     </row>
     <row r="49">
@@ -2438,37 +2432,37 @@
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>0.8912484000000001</v>
+        <v>0.85302461</v>
       </c>
       <c r="D49" t="n">
-        <v>0.7885891500000001</v>
+        <v>0.47333933</v>
       </c>
       <c r="E49" t="n">
-        <v>0.42070623</v>
+        <v>0.60223238</v>
       </c>
       <c r="F49" t="n">
-        <v>0.5480494499999999</v>
+        <v>0.39113424</v>
       </c>
       <c r="G49" t="n">
-        <v>0.34096733</v>
+        <v>0.55102869</v>
       </c>
       <c r="H49" t="n">
-        <v>0.50162335</v>
+        <v>0.28993202</v>
       </c>
       <c r="I49" t="n">
-        <v>0.28499248</v>
+        <v>0.02778382</v>
       </c>
       <c r="J49" t="n">
-        <v>0.06329543000000001</v>
+        <v>0.06734879000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.02356351</v>
+        <v>-0.10231698</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.16403953</v>
+        <v>-0.002836350000000003</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.03927072</v>
+        <v>1.65312477</v>
       </c>
     </row>
     <row r="50">
@@ -2479,37 +2473,37 @@
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
-        <v>32.85024001</v>
+        <v>0.2943598800000006</v>
       </c>
       <c r="D50" t="n">
-        <v>0.2943598800000006</v>
+        <v>-39.79114603</v>
       </c>
       <c r="E50" t="n">
-        <v>-39.79114603</v>
+        <v>-25.86812985</v>
       </c>
       <c r="F50" t="n">
-        <v>-25.86812985</v>
+        <v>-15.37702207</v>
       </c>
       <c r="G50" t="n">
-        <v>-15.37702207</v>
+        <v>-21.86573385</v>
       </c>
       <c r="H50" t="n">
-        <v>-21.86573385</v>
+        <v>-5.271030309999998</v>
       </c>
       <c r="I50" t="n">
-        <v>-5.271030309999998</v>
+        <v>10.19355404</v>
       </c>
       <c r="J50" t="n">
-        <v>10.19355404</v>
+        <v>-56.44455119</v>
       </c>
       <c r="K50" t="n">
-        <v>-56.44455119</v>
+        <v>-46.45714444000001</v>
       </c>
       <c r="L50" t="n">
-        <v>-46.45714444000001</v>
+        <v>-43.83128722999999</v>
       </c>
       <c r="M50" t="n">
-        <v>-43.83128722999999</v>
+        <v>-124.85406477</v>
       </c>
     </row>
     <row r="51">
@@ -2520,37 +2514,37 @@
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>-8.697055900000002</v>
+        <v>-33.79822566</v>
       </c>
       <c r="D51" t="n">
-        <v>7.78556319</v>
+        <v>-70.03717603</v>
       </c>
       <c r="E51" t="n">
-        <v>-26.75564822</v>
+        <v>-71.05295369</v>
       </c>
       <c r="F51" t="n">
-        <v>-29.6747849</v>
+        <v>-51.54037922</v>
       </c>
       <c r="G51" t="n">
-        <v>-9.074995439999997</v>
+        <v>-48.17214372</v>
       </c>
       <c r="H51" t="n">
-        <v>-6.02440684</v>
+        <v>-51.77891822</v>
       </c>
       <c r="I51" t="n">
-        <v>-10.76360972</v>
+        <v>1.437679659999999</v>
       </c>
       <c r="J51" t="n">
-        <v>-6.295704290000001</v>
+        <v>-1.732621739999999</v>
       </c>
       <c r="K51" t="n">
-        <v>4.70272614</v>
+        <v>-17.61133436</v>
       </c>
       <c r="L51" t="n">
-        <v>-5.524311600000001</v>
+        <v>13.32211765</v>
       </c>
       <c r="M51" t="n">
-        <v>2.53485937</v>
+        <v>-0.8307196999999994</v>
       </c>
     </row>
     <row r="52">
@@ -2561,37 +2555,37 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>-86.09051647</v>
+        <v>-52.5896484</v>
       </c>
       <c r="D52" t="n">
-        <v>-94.17343725000001</v>
+        <v>-47.10821256000001</v>
       </c>
       <c r="E52" t="n">
-        <v>-90.38974037</v>
+        <v>-5.38919929</v>
       </c>
       <c r="F52" t="n">
-        <v>-46.76736808</v>
+        <v>23.6608961</v>
       </c>
       <c r="G52" t="n">
-        <v>-18.80448768</v>
+        <v>38.21023020000001</v>
       </c>
       <c r="H52" t="n">
-        <v>-3.937506679999998</v>
+        <v>12.88120748</v>
       </c>
       <c r="I52" t="n">
-        <v>-28.13410102</v>
+        <v>-0.2473825400000005</v>
       </c>
       <c r="J52" t="n">
-        <v>7.48600141</v>
+        <v>-0.5776819000000004</v>
       </c>
       <c r="K52" t="n">
-        <v>-7.01302978</v>
+        <v>-12.85827515</v>
       </c>
       <c r="L52" t="n">
-        <v>-24.94529791</v>
+        <v>20.07517782</v>
       </c>
       <c r="M52" t="n">
-        <v>30.8624361</v>
+        <v>9.366192829999999</v>
       </c>
     </row>
     <row r="53">
@@ -2602,37 +2596,37 @@
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>311.1603595</v>
+        <v>51.29219449999999</v>
       </c>
       <c r="D53" t="n">
-        <v>48.50273705999999</v>
+        <v>-202.43466048</v>
       </c>
       <c r="E53" t="n">
-        <v>-201.80258542</v>
+        <v>42.45403700999999</v>
       </c>
       <c r="F53" t="n">
-        <v>34.01816414</v>
+        <v>353.5626931</v>
       </c>
       <c r="G53" t="n">
-        <v>305.24566593</v>
+        <v>373.92728289</v>
       </c>
       <c r="H53" t="n">
-        <v>287.84307047</v>
+        <v>97.26785201</v>
       </c>
       <c r="I53" t="n">
-        <v>17.41187099</v>
+        <v>-4.230439369999997</v>
       </c>
       <c r="J53" t="n">
-        <v>-101.62390288</v>
+        <v>105.44977854</v>
       </c>
       <c r="K53" t="n">
-        <v>10.99956778</v>
+        <v>-103.48180697</v>
       </c>
       <c r="L53" t="n">
-        <v>-143.08080159</v>
+        <v>214.35774299</v>
       </c>
       <c r="M53" t="n">
-        <v>189.49350051</v>
+        <v>147.19409253</v>
       </c>
     </row>
     <row r="54">
@@ -2643,37 +2637,37 @@
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>-87.98130128</v>
+        <v>-131.82460177</v>
       </c>
       <c r="D54" t="n">
-        <v>-131.82160819</v>
+        <v>-186.77167783</v>
       </c>
       <c r="E54" t="n">
-        <v>-186.39584642</v>
+        <v>-23.62684924</v>
       </c>
       <c r="F54" t="n">
-        <v>-23.6370268</v>
+        <v>94.02638623</v>
       </c>
       <c r="G54" t="n">
-        <v>93.53855481999999</v>
+        <v>212.92140005</v>
       </c>
       <c r="H54" t="n">
-        <v>211.94004658</v>
+        <v>90.77975588000001</v>
       </c>
       <c r="I54" t="n">
-        <v>90.15219676000001</v>
+        <v>45.93233127</v>
       </c>
       <c r="J54" t="n">
-        <v>45.78623981999999</v>
+        <v>144.17853408</v>
       </c>
       <c r="K54" t="n">
-        <v>143.74285746</v>
+        <v>11.27132376</v>
       </c>
       <c r="L54" t="n">
-        <v>11.27958262</v>
+        <v>-15.60971781</v>
       </c>
       <c r="M54" t="n">
-        <v>-16.07919225</v>
+        <v>65.76456664</v>
       </c>
     </row>
     <row r="55">
@@ -2684,37 +2678,37 @@
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>271.22984223</v>
+        <v>126.51460904</v>
       </c>
       <c r="D55" t="n">
-        <v>129.3010729</v>
+        <v>-59.0666161</v>
       </c>
       <c r="E55" t="n">
-        <v>-60.07452256999999</v>
+        <v>207.80842744</v>
       </c>
       <c r="F55" t="n">
-        <v>216.25447787</v>
+        <v>508.98404634</v>
       </c>
       <c r="G55" t="n">
-        <v>557.7889049199999</v>
+        <v>602.88307204</v>
       </c>
       <c r="H55" t="n">
-        <v>689.9486379299999</v>
+        <v>268.50802022</v>
       </c>
       <c r="I55" t="n">
-        <v>348.99156036</v>
+        <v>23.62266503</v>
       </c>
       <c r="J55" t="n">
-        <v>121.16221999</v>
+        <v>-5.944173200000003</v>
       </c>
       <c r="K55" t="n">
-        <v>88.94171418000001</v>
+        <v>-156.81645439</v>
       </c>
       <c r="L55" t="n">
-        <v>-117.22571863</v>
+        <v>53.20842615999999</v>
       </c>
       <c r="M55" t="n">
-        <v>78.54214308</v>
+        <v>59.87525717999999</v>
       </c>
     </row>
     <row r="56">
@@ -2725,37 +2719,37 @@
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>-21.67176996</v>
+        <v>-33.83319698</v>
       </c>
       <c r="D56" t="n">
-        <v>-33.83319698</v>
+        <v>-16.22676241</v>
       </c>
       <c r="E56" t="n">
-        <v>-16.22676241</v>
+        <v>-8.50384698</v>
       </c>
       <c r="F56" t="n">
-        <v>-8.50384698</v>
+        <v>-10.13554798</v>
       </c>
       <c r="G56" t="n">
-        <v>-10.13554798</v>
+        <v>-5.02773301</v>
       </c>
       <c r="H56" t="n">
-        <v>-5.02773301</v>
+        <v>4.61939667</v>
       </c>
       <c r="I56" t="n">
-        <v>4.61939667</v>
+        <v>0.32767565</v>
       </c>
       <c r="J56" t="n">
-        <v>0.32767565</v>
+        <v>-1.13437554</v>
       </c>
       <c r="K56" t="n">
-        <v>-1.13437554</v>
+        <v>-9.10632041</v>
       </c>
       <c r="L56" t="n">
-        <v>-9.10632041</v>
+        <v>2.08130507</v>
       </c>
       <c r="M56" t="n">
-        <v>2.08130507</v>
+        <v>-7.27956868</v>
       </c>
     </row>
     <row r="57">
@@ -2766,37 +2760,37 @@
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
-        <v>-2.42438873</v>
+        <v>-1.0301193</v>
       </c>
       <c r="D57" t="n">
-        <v>-1.02980451</v>
+        <v>-2.59580502</v>
       </c>
       <c r="E57" t="n">
-        <v>-2.59555918</v>
+        <v>-0.4970161599999999</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.4973752299999999</v>
+        <v>-3.79917129</v>
       </c>
       <c r="G57" t="n">
-        <v>-3.799829690000001</v>
+        <v>-3.020980170000001</v>
       </c>
       <c r="H57" t="n">
-        <v>-3.02146857</v>
+        <v>-3.08701631</v>
       </c>
       <c r="I57" t="n">
-        <v>-3.0873309</v>
+        <v>-3.15672715</v>
       </c>
       <c r="J57" t="n">
-        <v>-3.15688858</v>
+        <v>-1.54350305</v>
       </c>
       <c r="K57" t="n">
-        <v>-1.54356494</v>
+        <v>-4.72110351</v>
       </c>
       <c r="L57" t="n">
-        <v>-4.72126344</v>
+        <v>-3.3628632</v>
       </c>
       <c r="M57" t="n">
-        <v>-3.36291249</v>
+        <v>3.84713373</v>
       </c>
     </row>
     <row r="58">
@@ -2807,37 +2801,37 @@
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>-45.84164924</v>
+        <v>-34.24893215</v>
       </c>
       <c r="D58" t="n">
-        <v>-34.24924694</v>
+        <v>-43.39508184</v>
       </c>
       <c r="E58" t="n">
-        <v>-43.39532768</v>
+        <v>-36.66226973000001</v>
       </c>
       <c r="F58" t="n">
-        <v>-36.66191066</v>
+        <v>-40.85443972</v>
       </c>
       <c r="G58" t="n">
-        <v>-40.85378132</v>
+        <v>-33.23580955</v>
       </c>
       <c r="H58" t="n">
-        <v>-33.23532115</v>
+        <v>-1.87386048</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.87354589</v>
+        <v>-8.4681259</v>
       </c>
       <c r="J58" t="n">
-        <v>-8.467964469999998</v>
+        <v>1.73245088</v>
       </c>
       <c r="K58" t="n">
-        <v>1.73251277</v>
+        <v>-3.2817964</v>
       </c>
       <c r="L58" t="n">
-        <v>-3.28163647</v>
+        <v>15.75120761</v>
       </c>
       <c r="M58" t="n">
-        <v>15.7512569</v>
+        <v>55.11926591</v>
       </c>
     </row>
     <row r="59">
@@ -2848,37 +2842,37 @@
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
-        <v>-47.58373863</v>
+        <v>-7.666390959999998</v>
       </c>
       <c r="D59" t="n">
-        <v>-6.848567779999997</v>
+        <v>-41.64196783</v>
       </c>
       <c r="E59" t="n">
-        <v>-40.2240581</v>
+        <v>7.818857879999999</v>
       </c>
       <c r="F59" t="n">
-        <v>9.468226549999999</v>
+        <v>-8.73737841</v>
       </c>
       <c r="G59" t="n">
-        <v>-7.980154839999999</v>
+        <v>-35.23401704</v>
       </c>
       <c r="H59" t="n">
-        <v>-34.98440709</v>
+        <v>-57.93461414</v>
       </c>
       <c r="I59" t="n">
-        <v>-56.78136198999999</v>
+        <v>-68.29465833</v>
       </c>
       <c r="J59" t="n">
-        <v>-68.2518347</v>
+        <v>-8.434151510000001</v>
       </c>
       <c r="K59" t="n">
-        <v>-7.668320309999999</v>
+        <v>-47.65870399000001</v>
       </c>
       <c r="L59" t="n">
-        <v>-47.89530137000001</v>
+        <v>7.714702559999999</v>
       </c>
       <c r="M59" t="n">
-        <v>6.97709691</v>
+        <v>41.99995511</v>
       </c>
     </row>
     <row r="60">
@@ -2889,37 +2883,37 @@
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
-        <v>-0.02360963</v>
+        <v>0.82803391</v>
       </c>
       <c r="D60" t="n">
-        <v>0.01021073</v>
+        <v>1.42688672</v>
       </c>
       <c r="E60" t="n">
-        <v>0.008976989999999999</v>
+        <v>1.65472246</v>
       </c>
       <c r="F60" t="n">
-        <v>0.00535379</v>
+        <v>0.7650220599999999</v>
       </c>
       <c r="G60" t="n">
-        <v>0.00779849</v>
+        <v>0.25274791</v>
       </c>
       <c r="H60" t="n">
-        <v>0.00313796</v>
+        <v>1.15735872</v>
       </c>
       <c r="I60" t="n">
-        <v>0.004106569999999999</v>
+        <v>0.04444354</v>
       </c>
       <c r="J60" t="n">
-        <v>0.00161991</v>
+        <v>0.76131222</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.00451898</v>
+        <v>-0.23691493</v>
       </c>
       <c r="L60" t="n">
-        <v>-0.00031755</v>
+        <v>-0.71950387</v>
       </c>
       <c r="M60" t="n">
-        <v>0.01810178</v>
+        <v>0.5766634</v>
       </c>
     </row>
     <row r="61">
@@ -2930,37 +2924,37 @@
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
-        <v>18.75386397</v>
+        <v>-13.81200569</v>
       </c>
       <c r="D61" t="n">
-        <v>-13.81184612</v>
+        <v>-72.81674255</v>
       </c>
       <c r="E61" t="n">
-        <v>-72.81740354999999</v>
+        <v>-43.8031604</v>
       </c>
       <c r="F61" t="n">
-        <v>-43.80328412</v>
+        <v>-59.54142404</v>
       </c>
       <c r="G61" t="n">
-        <v>-59.54090667</v>
+        <v>-59.83005539</v>
       </c>
       <c r="H61" t="n">
-        <v>-59.82930822</v>
+        <v>-20.09492938</v>
       </c>
       <c r="I61" t="n">
-        <v>-20.0936324</v>
+        <v>-30.92644828</v>
       </c>
       <c r="J61" t="n">
-        <v>-30.92306802</v>
+        <v>-15.12639888</v>
       </c>
       <c r="K61" t="n">
-        <v>-15.12147089</v>
+        <v>19.01507966</v>
       </c>
       <c r="L61" t="n">
-        <v>19.01830041</v>
+        <v>32.19573076</v>
       </c>
       <c r="M61" t="n">
-        <v>32.19726349</v>
+        <v>66.0028885</v>
       </c>
     </row>
     <row r="62">
@@ -2971,37 +2965,37 @@
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>0.01025229</v>
+        <v>0.00055136</v>
       </c>
       <c r="D62" t="n">
-        <v>0.00055136</v>
+        <v>-0.00691126</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.00691126</v>
+        <v>-0.0001974500000000001</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.0001974500000000001</v>
+        <v>-0.00328995</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.00328995</v>
+        <v>-0.00367163</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.00367163</v>
+        <v>-0.00149519</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.00149519</v>
+        <v>-0.0044427</v>
       </c>
       <c r="J62" t="n">
-        <v>-0.0044427</v>
+        <v>-0.00424425</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.00424425</v>
+        <v>-0.00749634</v>
       </c>
       <c r="L62" t="n">
-        <v>-0.00749634</v>
+        <v>-0.0031783</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.0031783</v>
+        <v>-0.00248349</v>
       </c>
     </row>
     <row r="63">
@@ -3012,37 +3006,37 @@
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>13.26275676</v>
+        <v>-4.54630828</v>
       </c>
       <c r="D63" t="n">
-        <v>-4.546467850000001</v>
+        <v>-50.08899126</v>
       </c>
       <c r="E63" t="n">
-        <v>-50.08833026</v>
+        <v>3.88185814</v>
       </c>
       <c r="F63" t="n">
-        <v>3.88198186</v>
+        <v>-6.97329467</v>
       </c>
       <c r="G63" t="n">
-        <v>-6.97381204</v>
+        <v>-18.18662421</v>
       </c>
       <c r="H63" t="n">
-        <v>-18.18737138</v>
+        <v>54.93359035</v>
       </c>
       <c r="I63" t="n">
-        <v>54.93229337</v>
+        <v>-0.1310624899999998</v>
       </c>
       <c r="J63" t="n">
-        <v>-0.1344427499999995</v>
+        <v>15.73985881</v>
       </c>
       <c r="K63" t="n">
-        <v>15.73493082</v>
+        <v>-2.45111669</v>
       </c>
       <c r="L63" t="n">
-        <v>-2.454337439999999</v>
+        <v>28.65304667</v>
       </c>
       <c r="M63" t="n">
-        <v>28.65151394</v>
+        <v>47.66631501</v>
       </c>
     </row>
     <row r="64">
@@ -3053,37 +3047,37 @@
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
-        <v>-0.0001136</v>
+        <v>-0.00047737</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.00047737</v>
+        <v>-0.0001746</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.0001746</v>
+        <v>0.00012031</v>
       </c>
       <c r="F64" t="n">
-        <v>0.00012031</v>
+        <v>-2.134999999999999e-05</v>
       </c>
       <c r="G64" t="n">
-        <v>-2.134999999999999e-05</v>
+        <v>0.00012761</v>
       </c>
       <c r="H64" t="n">
-        <v>0.00012761</v>
+        <v>0.00014581</v>
       </c>
       <c r="I64" t="n">
-        <v>0.00014581</v>
+        <v>0.00033086</v>
       </c>
       <c r="J64" t="n">
-        <v>0.00033086</v>
+        <v>0.0004248200000000001</v>
       </c>
       <c r="K64" t="n">
-        <v>0.0004248200000000001</v>
+        <v>0.00090755</v>
       </c>
       <c r="L64" t="n">
-        <v>0.00090755</v>
+        <v>0.00103174</v>
       </c>
       <c r="M64" t="n">
-        <v>0.00103174</v>
+        <v>0.0009914099999999999</v>
       </c>
     </row>
     <row r="65">
@@ -3094,37 +3088,37 @@
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
-        <v>0.00015227</v>
+        <v>-5.835999999999999e-05</v>
       </c>
       <c r="D65" t="n">
-        <v>-5.835999999999999e-05</v>
+        <v>-0.00037977</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.00037977</v>
+        <v>-0.00013752</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.00013752</v>
+        <v>-0.00019394</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.00019394</v>
+        <v>-0.00018756</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.00018756</v>
+        <v>-0.00024988</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.00024988</v>
+        <v>-0.00027272</v>
       </c>
       <c r="J65" t="n">
-        <v>-0.00027272</v>
+        <v>-0.0002611</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.0002611</v>
+        <v>-0.00027651</v>
       </c>
       <c r="L65" t="n">
-        <v>-0.00027651</v>
+        <v>-0.0002609000000000001</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.0002609000000000001</v>
+        <v>5.814e-05</v>
       </c>
     </row>
     <row r="66">
@@ -3135,37 +3129,37 @@
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>227.064571</v>
+        <v>384.86742887</v>
       </c>
       <c r="D66" t="n">
-        <v>387.1266204199999</v>
+        <v>806.4506068800001</v>
       </c>
       <c r="E66" t="n">
-        <v>806.6555600600001</v>
+        <v>455.55609816</v>
       </c>
       <c r="F66" t="n">
-        <v>455.93493763</v>
+        <v>660.9538407099999</v>
       </c>
       <c r="G66" t="n">
-        <v>660.62955631</v>
+        <v>619.66636562</v>
       </c>
       <c r="H66" t="n">
-        <v>618.7149716599999</v>
+        <v>1094.86919271</v>
       </c>
       <c r="I66" t="n">
-        <v>1100.53461035</v>
+        <v>889.82394895</v>
       </c>
       <c r="J66" t="n">
-        <v>916.5280950800001</v>
+        <v>146.74014652</v>
       </c>
       <c r="K66" t="n">
-        <v>224.54199671</v>
+        <v>412.43538744</v>
       </c>
       <c r="L66" t="n">
-        <v>440.73232269</v>
+        <v>2.34032129999999</v>
       </c>
       <c r="M66" t="n">
-        <v>4.049852369999998</v>
+        <v>183.76378024</v>
       </c>
     </row>
     <row r="67">
@@ -3176,37 +3170,37 @@
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>120.54782873</v>
+        <v>44.24718054</v>
       </c>
       <c r="D67" t="n">
-        <v>44.24762443</v>
+        <v>-36.17068275</v>
       </c>
       <c r="E67" t="n">
-        <v>-36.1709015</v>
+        <v>1.7136654</v>
       </c>
       <c r="F67" t="n">
-        <v>1.71373009</v>
+        <v>19.83441227</v>
       </c>
       <c r="G67" t="n">
-        <v>19.83420643</v>
+        <v>16.35549202</v>
       </c>
       <c r="H67" t="n">
-        <v>16.35510931</v>
+        <v>14.86122769</v>
       </c>
       <c r="I67" t="n">
-        <v>14.86053108</v>
+        <v>19.66030109</v>
       </c>
       <c r="J67" t="n">
-        <v>19.65957699</v>
+        <v>-17.09602854</v>
       </c>
       <c r="K67" t="n">
-        <v>-17.0962329</v>
+        <v>-53.13334783000001</v>
       </c>
       <c r="L67" t="n">
-        <v>-53.13388309</v>
+        <v>-4.00198585</v>
       </c>
       <c r="M67" t="n">
-        <v>-4.002099009999999</v>
+        <v>33.33020905</v>
       </c>
     </row>
     <row r="68">
@@ -3217,37 +3211,37 @@
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>109.69128697</v>
+        <v>262.14089032</v>
       </c>
       <c r="D68" t="n">
-        <v>259.88125488</v>
+        <v>-69.92777048999999</v>
       </c>
       <c r="E68" t="n">
-        <v>-70.13250491999999</v>
+        <v>210.41362463</v>
       </c>
       <c r="F68" t="n">
-        <v>210.03472047</v>
+        <v>189.08727553</v>
       </c>
       <c r="G68" t="n">
-        <v>189.41176577</v>
+        <v>496.0721707300001</v>
       </c>
       <c r="H68" t="n">
-        <v>497.0239474000001</v>
+        <v>823.4354194200001</v>
       </c>
       <c r="I68" t="n">
-        <v>817.77069839</v>
+        <v>309.57426625</v>
       </c>
       <c r="J68" t="n">
-        <v>282.87084422</v>
+        <v>368.27284606</v>
       </c>
       <c r="K68" t="n">
-        <v>290.47120023</v>
+        <v>169.33167286</v>
       </c>
       <c r="L68" t="n">
-        <v>141.03527287</v>
+        <v>357.60631176</v>
       </c>
       <c r="M68" t="n">
-        <v>355.89689385</v>
+        <v>126.61057411</v>
       </c>
     </row>
     <row r="69">
@@ -3258,37 +3252,37 @@
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>10.78952622</v>
+        <v>6.005808959999999</v>
       </c>
       <c r="D69" t="n">
-        <v>6.005808959999999</v>
+        <v>1.48615941</v>
       </c>
       <c r="E69" t="n">
-        <v>1.48615941</v>
+        <v>6.954071790000001</v>
       </c>
       <c r="F69" t="n">
-        <v>6.954071790000001</v>
+        <v>8.895559609999999</v>
       </c>
       <c r="G69" t="n">
-        <v>8.895559609999999</v>
+        <v>25.77768484</v>
       </c>
       <c r="H69" t="n">
-        <v>25.77768484</v>
+        <v>7.5358798</v>
       </c>
       <c r="I69" t="n">
-        <v>7.5358798</v>
+        <v>-2.18453111</v>
       </c>
       <c r="J69" t="n">
-        <v>-2.18453111</v>
+        <v>-4.28064262</v>
       </c>
       <c r="K69" t="n">
-        <v>-4.28064262</v>
+        <v>-9.848016550000001</v>
       </c>
       <c r="L69" t="n">
-        <v>-9.848016550000001</v>
+        <v>-11.75977663</v>
       </c>
       <c r="M69" t="n">
-        <v>-11.75977663</v>
+        <v>-14.45543988</v>
       </c>
     </row>
     <row r="70">
@@ -3299,37 +3293,37 @@
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>-2.25176163</v>
+        <v>-1.21277104</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.21277104</v>
+        <v>-3.03497446</v>
       </c>
       <c r="E70" t="n">
-        <v>-3.03497446</v>
+        <v>-1.57228821</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.57228821</v>
+        <v>-0.33839224</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.33839224</v>
+        <v>-1.43394215</v>
       </c>
       <c r="H70" t="n">
-        <v>-1.43394215</v>
+        <v>-1.69268373</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.69268373</v>
+        <v>-3.23010772</v>
       </c>
       <c r="J70" t="n">
-        <v>-3.23010772</v>
+        <v>-3.39045584</v>
       </c>
       <c r="K70" t="n">
-        <v>-3.39045584</v>
+        <v>-4.06147909</v>
       </c>
       <c r="L70" t="n">
-        <v>-4.06147909</v>
+        <v>-3.60733925</v>
       </c>
       <c r="M70" t="n">
-        <v>-3.60733925</v>
+        <v>-1.16033294</v>
       </c>
     </row>
     <row r="71">
@@ -3340,37 +3334,37 @@
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
-        <v>-9.829484189999999</v>
+        <v>-0.7912245499999994</v>
       </c>
       <c r="D71" t="n">
-        <v>-14.93550311</v>
+        <v>-38.04768629</v>
       </c>
       <c r="E71" t="n">
-        <v>-19.17963443</v>
+        <v>5.646526350000001</v>
       </c>
       <c r="F71" t="n">
-        <v>-4.231608599999999</v>
+        <v>1.152489290000001</v>
       </c>
       <c r="G71" t="n">
-        <v>-4.30055992</v>
+        <v>-9.541564510000001</v>
       </c>
       <c r="H71" t="n">
-        <v>-3.592882920000001</v>
+        <v>-10.24703036</v>
       </c>
       <c r="I71" t="n">
-        <v>-6.801680230000001</v>
+        <v>-29.03830542</v>
       </c>
       <c r="J71" t="n">
-        <v>-13.86701406</v>
+        <v>-7.31066034</v>
       </c>
       <c r="K71" t="n">
-        <v>1.46514716</v>
+        <v>-16.28726425</v>
       </c>
       <c r="L71" t="n">
-        <v>0.14055349</v>
+        <v>6.2073744</v>
       </c>
       <c r="M71" t="n">
-        <v>7.1486433</v>
+        <v>33.59447604</v>
       </c>
     </row>
     <row r="72">
@@ -3381,37 +3375,37 @@
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>-49.00740580000001</v>
+        <v>36.20031953</v>
       </c>
       <c r="D72" t="n">
-        <v>36.20031953</v>
+        <v>-67.66731897</v>
       </c>
       <c r="E72" t="n">
-        <v>-67.66731897</v>
+        <v>86.08082459000001</v>
       </c>
       <c r="F72" t="n">
-        <v>86.08082459000001</v>
+        <v>65.03796482999999</v>
       </c>
       <c r="G72" t="n">
-        <v>65.03796482999999</v>
+        <v>7.475289409999997</v>
       </c>
       <c r="H72" t="n">
-        <v>7.475289409999997</v>
+        <v>-64.07427258999999</v>
       </c>
       <c r="I72" t="n">
-        <v>-64.07427258999999</v>
+        <v>-115.50237892</v>
       </c>
       <c r="J72" t="n">
-        <v>-115.50237892</v>
+        <v>-11.79256974999999</v>
       </c>
       <c r="K72" t="n">
-        <v>-11.79256974999999</v>
+        <v>-141.47987787</v>
       </c>
       <c r="L72" t="n">
-        <v>-141.47987787</v>
+        <v>-101.90599359</v>
       </c>
       <c r="M72" t="n">
-        <v>-101.90599359</v>
+        <v>-27.86393122</v>
       </c>
     </row>
     <row r="73">
@@ -3422,37 +3416,37 @@
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
-        <v>12.37816619</v>
+        <v>15.47129295</v>
       </c>
       <c r="D73" t="n">
-        <v>29.61557151</v>
+        <v>2.12043667</v>
       </c>
       <c r="E73" t="n">
-        <v>-16.74761519</v>
+        <v>2.82117636</v>
       </c>
       <c r="F73" t="n">
-        <v>12.69931131</v>
+        <v>-1.67008344</v>
       </c>
       <c r="G73" t="n">
-        <v>3.78296577</v>
+        <v>-3.00446659</v>
       </c>
       <c r="H73" t="n">
-        <v>-8.953148180000001</v>
+        <v>-5.70656305</v>
       </c>
       <c r="I73" t="n">
-        <v>-9.151913179999999</v>
+        <v>-3.26029956</v>
       </c>
       <c r="J73" t="n">
-        <v>-18.43159092</v>
+        <v>0.1366862700000001</v>
       </c>
       <c r="K73" t="n">
-        <v>-8.639121230000001</v>
+        <v>-1.67836101</v>
       </c>
       <c r="L73" t="n">
-        <v>-18.10617875</v>
+        <v>0.1721373</v>
       </c>
       <c r="M73" t="n">
-        <v>-0.7691315999999999</v>
+        <v>0.3790449200000002</v>
       </c>
     </row>
     <row r="74">
@@ -3463,37 +3457,37 @@
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
-        <v>-1008.07010514</v>
+        <v>-1537.60609394</v>
       </c>
       <c r="D74" t="n">
-        <v>-1537.60609394</v>
+        <v>-1300.60484244</v>
       </c>
       <c r="E74" t="n">
-        <v>-1300.60484244</v>
+        <v>-446.7146776000001</v>
       </c>
       <c r="F74" t="n">
-        <v>-446.7146776000001</v>
+        <v>-782.3819385199999</v>
       </c>
       <c r="G74" t="n">
-        <v>-782.3819385199999</v>
+        <v>-1081.01944222</v>
       </c>
       <c r="H74" t="n">
-        <v>-1081.01944222</v>
+        <v>-1391.75995319</v>
       </c>
       <c r="I74" t="n">
-        <v>-1391.75995319</v>
+        <v>-1580.93302348</v>
       </c>
       <c r="J74" t="n">
-        <v>-1580.93302348</v>
+        <v>-563.61207497</v>
       </c>
       <c r="K74" t="n">
-        <v>-563.61207497</v>
+        <v>-1021.23222964</v>
       </c>
       <c r="L74" t="n">
-        <v>-1021.23222964</v>
+        <v>32.26943954999999</v>
       </c>
       <c r="M74" t="n">
-        <v>32.26943954999999</v>
+        <v>961.0002153400001</v>
       </c>
     </row>
     <row r="75">
@@ -3504,37 +3498,37 @@
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
-        <v>-60.65922219999999</v>
+        <v>-260.44258382</v>
       </c>
       <c r="D75" t="n">
-        <v>-260.44258382</v>
+        <v>-368.46173542</v>
       </c>
       <c r="E75" t="n">
-        <v>-368.46173542</v>
+        <v>-257.34234104</v>
       </c>
       <c r="F75" t="n">
-        <v>-257.34234104</v>
+        <v>-885.79771207</v>
       </c>
       <c r="G75" t="n">
-        <v>-885.79771207</v>
+        <v>-150.17356266</v>
       </c>
       <c r="H75" t="n">
-        <v>-150.17356266</v>
+        <v>-451.01320442</v>
       </c>
       <c r="I75" t="n">
-        <v>-451.01320442</v>
+        <v>-639.4418898500001</v>
       </c>
       <c r="J75" t="n">
-        <v>-639.4418898500001</v>
+        <v>-343.7357963100001</v>
       </c>
       <c r="K75" t="n">
-        <v>-343.7357963100001</v>
+        <v>-358.27958259</v>
       </c>
       <c r="L75" t="n">
-        <v>-358.27958259</v>
+        <v>-339.09543789</v>
       </c>
       <c r="M75" t="n">
-        <v>-339.09543789</v>
+        <v>-134.39403601</v>
       </c>
     </row>
     <row r="76">
@@ -3545,37 +3539,37 @@
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>108.00936268</v>
+        <v>19.06414180000001</v>
       </c>
       <c r="D76" t="n">
-        <v>19.06414180000001</v>
+        <v>-36.27459351</v>
       </c>
       <c r="E76" t="n">
-        <v>-36.27459351</v>
+        <v>60.51338413</v>
       </c>
       <c r="F76" t="n">
-        <v>60.51338413</v>
+        <v>-14.83326694</v>
       </c>
       <c r="G76" t="n">
-        <v>-14.83326694</v>
+        <v>-38.65199278</v>
       </c>
       <c r="H76" t="n">
-        <v>-38.65199278</v>
+        <v>-81.31538531</v>
       </c>
       <c r="I76" t="n">
-        <v>-81.31538531</v>
+        <v>-113.49396267</v>
       </c>
       <c r="J76" t="n">
-        <v>-113.49396267</v>
+        <v>-9.233541829999998</v>
       </c>
       <c r="K76" t="n">
-        <v>-9.233541829999998</v>
+        <v>-62.41240477000001</v>
       </c>
       <c r="L76" t="n">
-        <v>-62.41240477000001</v>
+        <v>40.32641878</v>
       </c>
       <c r="M76" t="n">
-        <v>40.32641878</v>
+        <v>121.04976112</v>
       </c>
     </row>
     <row r="77">
@@ -3586,37 +3580,37 @@
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="n">
-        <v>0.00048183</v>
+        <v>-0.00035228</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.00035228</v>
+        <v>-0.0010076</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.0010076</v>
+        <v>-0.00018871</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.00018871</v>
+        <v>-0.00053725</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.00053725</v>
+        <v>-0.00057684</v>
       </c>
       <c r="H77" t="n">
-        <v>-0.00057684</v>
+        <v>-0.0006594299999999999</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.0006594299999999999</v>
+        <v>-0.00071329</v>
       </c>
       <c r="J77" t="n">
-        <v>-0.00071329</v>
+        <v>-0.0003751</v>
       </c>
       <c r="K77" t="n">
-        <v>-0.0003751</v>
+        <v>-0.00072667</v>
       </c>
       <c r="L77" t="n">
-        <v>-0.00072667</v>
+        <v>-0.00031853</v>
       </c>
       <c r="M77" t="n">
-        <v>-0.00031853</v>
+        <v>-0.00042214</v>
       </c>
     </row>
     <row r="78">
@@ -3627,37 +3621,37 @@
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
-        <v>0.0028904</v>
+        <v>0.00127502</v>
       </c>
       <c r="D78" t="n">
-        <v>0.00127502</v>
+        <v>-0.00110649</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.00110649</v>
+        <v>0.0006396900000000001</v>
       </c>
       <c r="F78" t="n">
-        <v>0.0006396900000000001</v>
+        <v>0.00368509</v>
       </c>
       <c r="G78" t="n">
-        <v>0.00368509</v>
+        <v>0.004119070000000001</v>
       </c>
       <c r="H78" t="n">
-        <v>0.004119070000000001</v>
+        <v>0.00104634</v>
       </c>
       <c r="I78" t="n">
-        <v>0.00104634</v>
+        <v>-0.00267286</v>
       </c>
       <c r="J78" t="n">
-        <v>-0.00267286</v>
+        <v>-9.306000000000001e-05</v>
       </c>
       <c r="K78" t="n">
-        <v>-9.306000000000001e-05</v>
+        <v>-0.00439828</v>
       </c>
       <c r="L78" t="n">
-        <v>-0.00439828</v>
+        <v>-0.005935770000000001</v>
       </c>
       <c r="M78" t="n">
-        <v>-0.005935770000000001</v>
+        <v>-0.006376339999999999</v>
       </c>
     </row>
     <row r="79">
@@ -3668,37 +3662,37 @@
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="n">
-        <v>-4.426999999999998e-05</v>
+        <v>-0.00031949</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.00031949</v>
+        <v>-0.00080643</v>
       </c>
       <c r="E79" t="n">
-        <v>-0.00080643</v>
+        <v>-0.00053355</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.00053355</v>
+        <v>-0.0004297</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.0004297</v>
+        <v>-0.00048908</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.00048908</v>
+        <v>-0.00026955</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.00026955</v>
+        <v>-0.00035725</v>
       </c>
       <c r="J79" t="n">
-        <v>-0.00035725</v>
+        <v>-0.00052145</v>
       </c>
       <c r="K79" t="n">
-        <v>-0.00052145</v>
+        <v>-0.00052038</v>
       </c>
       <c r="L79" t="n">
-        <v>-0.00052038</v>
+        <v>-0.00049876</v>
       </c>
       <c r="M79" t="n">
-        <v>-0.00049876</v>
+        <v>-0.00010349</v>
       </c>
     </row>
     <row r="80">
@@ -3709,37 +3703,37 @@
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="n">
-        <v>2.61099361</v>
+        <v>22.97207093</v>
       </c>
       <c r="D80" t="n">
-        <v>23.15279365</v>
+        <v>3.51672797</v>
       </c>
       <c r="E80" t="n">
-        <v>3.53747368</v>
+        <v>3.13082996</v>
       </c>
       <c r="F80" t="n">
-        <v>3.37237859</v>
+        <v>12.50540977</v>
       </c>
       <c r="G80" t="n">
-        <v>12.60022255</v>
+        <v>27.84336579</v>
       </c>
       <c r="H80" t="n">
-        <v>28.00022631</v>
+        <v>3.57885056</v>
       </c>
       <c r="I80" t="n">
-        <v>3.68878533</v>
+        <v>-6.574561549999999</v>
       </c>
       <c r="J80" t="n">
-        <v>-6.56068165</v>
+        <v>5.12920975</v>
       </c>
       <c r="K80" t="n">
-        <v>5.127412570000001</v>
+        <v>0.3989783500000001</v>
       </c>
       <c r="L80" t="n">
-        <v>0.3745234199999999</v>
+        <v>-13.06068005</v>
       </c>
       <c r="M80" t="n">
-        <v>-13.08952523</v>
+        <v>-4.237776240000001</v>
       </c>
     </row>
     <row r="81">
@@ -3748,41 +3742,39 @@
           <t>鋼鐵工業右下</t>
         </is>
       </c>
-      <c r="B81" t="n">
-        <v>0</v>
-      </c>
+      <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>11.94355438</v>
+        <v>44.23416758</v>
       </c>
       <c r="D81" t="n">
-        <v>44.30325269</v>
+        <v>55.60871175</v>
       </c>
       <c r="E81" t="n">
-        <v>56.83459901000001</v>
+        <v>189.08545711</v>
       </c>
       <c r="F81" t="n">
-        <v>188.94294104</v>
+        <v>59.51750321</v>
       </c>
       <c r="G81" t="n">
-        <v>60.27513024</v>
+        <v>36.79329722999999</v>
       </c>
       <c r="H81" t="n">
-        <v>36.77150214</v>
+        <v>-46.55458285</v>
       </c>
       <c r="I81" t="n">
-        <v>-46.30174972</v>
+        <v>-86.24587647</v>
       </c>
       <c r="J81" t="n">
-        <v>-85.81048893000001</v>
+        <v>4.752140270000001</v>
       </c>
       <c r="K81" t="n">
-        <v>4.43261345</v>
+        <v>-72.65755283</v>
       </c>
       <c r="L81" t="n">
-        <v>-72.10663736999999</v>
+        <v>-104.70529256</v>
       </c>
       <c r="M81" t="n">
-        <v>-104.95248059</v>
+        <v>-114.0303431</v>
       </c>
     </row>
     <row r="82">
@@ -3793,37 +3785,37 @@
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
-        <v>29.91834361</v>
+        <v>36.69310421000001</v>
       </c>
       <c r="D82" t="n">
-        <v>36.51244642</v>
+        <v>97.66574208999999</v>
       </c>
       <c r="E82" t="n">
-        <v>97.64502983000001</v>
+        <v>253.91694599</v>
       </c>
       <c r="F82" t="n">
-        <v>253.67546433</v>
+        <v>106.88135519</v>
       </c>
       <c r="G82" t="n">
-        <v>106.78659576</v>
+        <v>356.57203989</v>
       </c>
       <c r="H82" t="n">
-        <v>356.41528479</v>
+        <v>506.99939125</v>
       </c>
       <c r="I82" t="n">
-        <v>506.88955911</v>
+        <v>775.8071118700001</v>
       </c>
       <c r="J82" t="n">
-        <v>775.7932965800001</v>
+        <v>803.9243044000001</v>
       </c>
       <c r="K82" t="n">
-        <v>803.9262191600001</v>
+        <v>245.68418473</v>
       </c>
       <c r="L82" t="n">
-        <v>245.7090147</v>
+        <v>6.711370079999998</v>
       </c>
       <c r="M82" t="n">
-        <v>6.74061814</v>
+        <v>101.28355863</v>
       </c>
     </row>
     <row r="83">
@@ -3834,37 +3826,37 @@
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>76.29529208</v>
+        <v>23.28468532</v>
       </c>
       <c r="D83" t="n">
-        <v>23.28468532</v>
+        <v>-16.2538581</v>
       </c>
       <c r="E83" t="n">
-        <v>-16.2538581</v>
+        <v>-12.95625808</v>
       </c>
       <c r="F83" t="n">
-        <v>-12.95625808</v>
+        <v>-9.47706786</v>
       </c>
       <c r="G83" t="n">
-        <v>-9.47706786</v>
+        <v>-3.909404330000002</v>
       </c>
       <c r="H83" t="n">
-        <v>-3.909404330000002</v>
+        <v>-14.46518195</v>
       </c>
       <c r="I83" t="n">
-        <v>-14.46518195</v>
+        <v>37.21932350000001</v>
       </c>
       <c r="J83" t="n">
-        <v>37.21932350000001</v>
+        <v>68.03134521</v>
       </c>
       <c r="K83" t="n">
-        <v>68.03134521</v>
+        <v>-2.350372119999999</v>
       </c>
       <c r="L83" t="n">
-        <v>-2.350372119999999</v>
+        <v>-4.571539939999999</v>
       </c>
       <c r="M83" t="n">
-        <v>-4.571539939999999</v>
+        <v>39.14585281</v>
       </c>
     </row>
     <row r="84">
@@ -3875,37 +3867,37 @@
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
-        <v>40.35862178</v>
+        <v>68.89752422999999</v>
       </c>
       <c r="D84" t="n">
-        <v>68.37247169999999</v>
+        <v>15.56912003</v>
       </c>
       <c r="E84" t="n">
-        <v>3.416822149999998</v>
+        <v>45.51657396</v>
       </c>
       <c r="F84" t="n">
-        <v>43.73037651000001</v>
+        <v>10.48380609</v>
       </c>
       <c r="G84" t="n">
-        <v>0.8549038500000001</v>
+        <v>-6.200965539999999</v>
       </c>
       <c r="H84" t="n">
-        <v>-20.28244063</v>
+        <v>7.24073577</v>
       </c>
       <c r="I84" t="n">
-        <v>-7.13288485</v>
+        <v>-6.584472399999999</v>
       </c>
       <c r="J84" t="n">
-        <v>-11.15250674</v>
+        <v>102.05294481</v>
       </c>
       <c r="K84" t="n">
-        <v>107.81488663</v>
+        <v>-115.80624809</v>
       </c>
       <c r="L84" t="n">
-        <v>-119.17231353</v>
+        <v>-143.58805289</v>
       </c>
       <c r="M84" t="n">
-        <v>-149.47758541</v>
+        <v>-122.466744</v>
       </c>
     </row>
     <row r="85">
@@ -3916,37 +3908,37 @@
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>14.5085341</v>
+        <v>19.63179093</v>
       </c>
       <c r="D85" t="n">
-        <v>20.15684346</v>
+        <v>-13.39590242</v>
       </c>
       <c r="E85" t="n">
-        <v>-1.24360454</v>
+        <v>4.88366597</v>
       </c>
       <c r="F85" t="n">
-        <v>6.66986342</v>
+        <v>-16.24245559</v>
       </c>
       <c r="G85" t="n">
-        <v>-6.613553349999999</v>
+        <v>-27.47507357</v>
       </c>
       <c r="H85" t="n">
-        <v>-13.39359848</v>
+        <v>-23.38341415</v>
       </c>
       <c r="I85" t="n">
-        <v>-9.00979353</v>
+        <v>-18.17303202</v>
       </c>
       <c r="J85" t="n">
-        <v>-13.60499768</v>
+        <v>-1.11123643</v>
       </c>
       <c r="K85" t="n">
-        <v>-6.87317825</v>
+        <v>-20.036443</v>
       </c>
       <c r="L85" t="n">
-        <v>-16.67037756</v>
+        <v>-24.56355175</v>
       </c>
       <c r="M85" t="n">
-        <v>-18.67401923</v>
+        <v>-6.497919510000001</v>
       </c>
     </row>
     <row r="86">
@@ -3957,37 +3949,37 @@
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
-        <v>99.26279117999999</v>
+        <v>84.78180712999999</v>
       </c>
       <c r="D86" t="n">
-        <v>82.10264262000001</v>
+        <v>5.239100129999997</v>
       </c>
       <c r="E86" t="n">
-        <v>-0.5536843900000029</v>
+        <v>37.95854161</v>
       </c>
       <c r="F86" t="n">
-        <v>35.31476152</v>
+        <v>6.337415530000002</v>
       </c>
       <c r="G86" t="n">
-        <v>2.312927219999999</v>
+        <v>-14.77173878</v>
       </c>
       <c r="H86" t="n">
-        <v>-14.73780212</v>
+        <v>42.12402878</v>
       </c>
       <c r="I86" t="n">
-        <v>45.55591851</v>
+        <v>24.19335857</v>
       </c>
       <c r="J86" t="n">
-        <v>20.93663418</v>
+        <v>81.89622543999999</v>
       </c>
       <c r="K86" t="n">
-        <v>83.75538558</v>
+        <v>36.94664319</v>
       </c>
       <c r="L86" t="n">
-        <v>31.50825829</v>
+        <v>39.92671712</v>
       </c>
       <c r="M86" t="n">
-        <v>43.48443047</v>
+        <v>-7.647300829999998</v>
       </c>
     </row>
     <row r="87">
@@ -3998,37 +3990,37 @@
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>25.20733403</v>
+        <v>22.32559712</v>
       </c>
       <c r="D87" t="n">
-        <v>22.32559712</v>
+        <v>6.20539317</v>
       </c>
       <c r="E87" t="n">
-        <v>6.20539317</v>
+        <v>19.57465763</v>
       </c>
       <c r="F87" t="n">
-        <v>19.57465763</v>
+        <v>19.41548498</v>
       </c>
       <c r="G87" t="n">
-        <v>19.41548498</v>
+        <v>15.32622302</v>
       </c>
       <c r="H87" t="n">
-        <v>15.32622302</v>
+        <v>21.24192985</v>
       </c>
       <c r="I87" t="n">
-        <v>21.24192985</v>
+        <v>2.4630607</v>
       </c>
       <c r="J87" t="n">
-        <v>2.4630607</v>
+        <v>3.62088127</v>
       </c>
       <c r="K87" t="n">
-        <v>3.62088127</v>
+        <v>-6.0015291</v>
       </c>
       <c r="L87" t="n">
-        <v>-6.0015291</v>
+        <v>-2.04589291</v>
       </c>
       <c r="M87" t="n">
-        <v>-2.04589291</v>
+        <v>3.85967725</v>
       </c>
     </row>
     <row r="88">
@@ -4039,37 +4031,37 @@
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
-        <v>-7.25654832</v>
+        <v>-14.14651726</v>
       </c>
       <c r="D88" t="n">
-        <v>-11.46735275</v>
+        <v>-169.54013666</v>
       </c>
       <c r="E88" t="n">
-        <v>-163.74735214</v>
+        <v>-6.49426587</v>
       </c>
       <c r="F88" t="n">
-        <v>-3.85048578</v>
+        <v>-86.67775795999999</v>
       </c>
       <c r="G88" t="n">
-        <v>-82.65326964999998</v>
+        <v>-36.33716424</v>
       </c>
       <c r="H88" t="n">
-        <v>-36.3711009</v>
+        <v>23.72003185</v>
       </c>
       <c r="I88" t="n">
-        <v>20.28814212</v>
+        <v>-51.5510354</v>
       </c>
       <c r="J88" t="n">
-        <v>-48.29431101</v>
+        <v>14.02827815</v>
       </c>
       <c r="K88" t="n">
-        <v>12.16911801</v>
+        <v>-73.58579353</v>
       </c>
       <c r="L88" t="n">
-        <v>-68.14740863</v>
+        <v>-28.11776397</v>
       </c>
       <c r="M88" t="n">
-        <v>-28.11776397</v>
+        <v>17.17881818</v>
       </c>
     </row>
     <row r="89">
@@ -4080,37 +4072,37 @@
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>2906.52286037</v>
+        <v>3045.12153567</v>
       </c>
       <c r="D89" t="n">
-        <v>3041.85862625</v>
+        <v>-185.6210225900001</v>
       </c>
       <c r="E89" t="n">
-        <v>-50.91332269000007</v>
+        <v>1450.16954711</v>
       </c>
       <c r="F89" t="n">
-        <v>1440.99283615</v>
+        <v>2181.7213222</v>
       </c>
       <c r="G89" t="n">
-        <v>2091.2588738</v>
+        <v>800.8896557599999</v>
       </c>
       <c r="H89" t="n">
-        <v>650.42892814</v>
+        <v>2692.81628791</v>
       </c>
       <c r="I89" t="n">
-        <v>2555.91236937</v>
+        <v>1485.24470595</v>
       </c>
       <c r="J89" t="n">
-        <v>1482.30721553</v>
+        <v>707.3239357199999</v>
       </c>
       <c r="K89" t="n">
-        <v>587.08496215</v>
+        <v>2029.26073542</v>
       </c>
       <c r="L89" t="n">
-        <v>1888.36280674</v>
+        <v>2841.68157912</v>
       </c>
       <c r="M89" t="n">
-        <v>2863.27898597</v>
+        <v>310.9182969999999</v>
       </c>
     </row>
     <row r="90">
@@ -4121,37 +4113,37 @@
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>-39.30927771999999</v>
+        <v>2.463848020000004</v>
       </c>
       <c r="D90" t="n">
-        <v>5.541886310000004</v>
+        <v>-811.15952119</v>
       </c>
       <c r="E90" t="n">
-        <v>-812.85023669</v>
+        <v>-208.916076</v>
       </c>
       <c r="F90" t="n">
-        <v>-209.20355873</v>
+        <v>19.51218682</v>
       </c>
       <c r="G90" t="n">
-        <v>23.2753109</v>
+        <v>-394.97740607</v>
       </c>
       <c r="H90" t="n">
-        <v>-392.10574716</v>
+        <v>-84.82093649000001</v>
       </c>
       <c r="I90" t="n">
-        <v>-86.06334828999998</v>
+        <v>932.39330921</v>
       </c>
       <c r="J90" t="n">
-        <v>926.9330168199999</v>
+        <v>1127.05188189</v>
       </c>
       <c r="K90" t="n">
-        <v>1129.75807729</v>
+        <v>74.69056523</v>
       </c>
       <c r="L90" t="n">
-        <v>67.15083111</v>
+        <v>121.71188574</v>
       </c>
       <c r="M90" t="n">
-        <v>111.41716165</v>
+        <v>-324.48483771</v>
       </c>
     </row>
     <row r="91">
@@ -4162,37 +4154,37 @@
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>872.4743653200001</v>
+        <v>352.41061298</v>
       </c>
       <c r="D91" t="n">
-        <v>352.59548411</v>
+        <v>-304.57704215</v>
       </c>
       <c r="E91" t="n">
-        <v>-437.59402655</v>
+        <v>428.31272425</v>
       </c>
       <c r="F91" t="n">
-        <v>437.77691794</v>
+        <v>431.70559305</v>
       </c>
       <c r="G91" t="n">
-        <v>518.40491737</v>
+        <v>564.9093828399998</v>
       </c>
       <c r="H91" t="n">
-        <v>712.4984515499999</v>
+        <v>655.7823525999999</v>
       </c>
       <c r="I91" t="n">
-        <v>793.92868294</v>
+        <v>29.95527817999999</v>
       </c>
       <c r="J91" t="n">
-        <v>38.35306098999999</v>
+        <v>-288.85927076</v>
       </c>
       <c r="K91" t="n">
-        <v>-171.32649259</v>
+        <v>-604.2071907000001</v>
       </c>
       <c r="L91" t="n">
-        <v>-455.7695278999999</v>
+        <v>-516.20697965</v>
       </c>
       <c r="M91" t="n">
-        <v>-526.24604949</v>
+        <v>-454.6967065100001</v>
       </c>
     </row>
     <row r="92">
@@ -4203,37 +4195,37 @@
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>450.1374404300001</v>
+        <v>231.7437846000001</v>
       </c>
       <c r="D92" t="n">
-        <v>230.8343588500001</v>
+        <v>187.93600482</v>
       </c>
       <c r="E92" t="n">
-        <v>193.42815452</v>
+        <v>1374.52805904</v>
       </c>
       <c r="F92" t="n">
-        <v>1368.7163708</v>
+        <v>-196.0247448</v>
       </c>
       <c r="G92" t="n">
-        <v>-244.27991623</v>
+        <v>-960.59430022</v>
       </c>
       <c r="H92" t="n">
-        <v>-1063.7628104</v>
+        <v>-381.9727258300001</v>
       </c>
       <c r="I92" t="n">
-        <v>-416.69328563</v>
+        <v>-279.90565688</v>
       </c>
       <c r="J92" t="n">
-        <v>-246.4158350100001</v>
+        <v>-266.3651420100001</v>
       </c>
       <c r="K92" t="n">
-        <v>-263.547706</v>
+        <v>-137.75917843</v>
       </c>
       <c r="L92" t="n">
-        <v>-117.21702503</v>
+        <v>229.70470534</v>
       </c>
       <c r="M92" t="n">
-        <v>254.06105455</v>
+        <v>-1071.52023388</v>
       </c>
     </row>
     <row r="93">
@@ -4242,39 +4234,41 @@
           <t>電機機械右下</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr"/>
+      <c r="B93" t="n">
+        <v>0</v>
+      </c>
       <c r="C93" t="n">
-        <v>-139.77033695</v>
+        <v>29.38402996</v>
       </c>
       <c r="D93" t="n">
-        <v>28.58933824</v>
+        <v>-103.78599573</v>
       </c>
       <c r="E93" t="n">
-        <v>-107.07951807</v>
+        <v>122.62280393</v>
       </c>
       <c r="F93" t="n">
-        <v>121.21020237</v>
+        <v>91.51325279</v>
       </c>
       <c r="G93" t="n">
-        <v>91.21977593999999</v>
+        <v>-52.62472325</v>
       </c>
       <c r="H93" t="n">
-        <v>-54.60765974</v>
+        <v>-40.00084902</v>
       </c>
       <c r="I93" t="n">
-        <v>-43.35784784</v>
+        <v>-83.57264979999999</v>
       </c>
       <c r="J93" t="n">
-        <v>-87.54705163</v>
+        <v>59.78373489</v>
       </c>
       <c r="K93" t="n">
-        <v>57.4009534</v>
+        <v>-48.406199</v>
       </c>
       <c r="L93" t="n">
-        <v>-52.61122439</v>
+        <v>-27.57179608000001</v>
       </c>
       <c r="M93" t="n">
-        <v>-101.21467454</v>
+        <v>-25.6795375</v>
       </c>
     </row>
     <row r="94">
@@ -4285,37 +4279,37 @@
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>-76.74787737999999</v>
+        <v>-52.55055714</v>
       </c>
       <c r="D94" t="n">
-        <v>-50.85289054</v>
+        <v>-156.93598863</v>
       </c>
       <c r="E94" t="n">
-        <v>-159.14422832</v>
+        <v>55.77096381</v>
       </c>
       <c r="F94" t="n">
-        <v>62.98996203</v>
+        <v>79.68027279</v>
       </c>
       <c r="G94" t="n">
-        <v>128.22662341</v>
+        <v>307.6798681500001</v>
       </c>
       <c r="H94" t="n">
-        <v>412.83655354</v>
+        <v>429.53010238</v>
       </c>
       <c r="I94" t="n">
-        <v>467.60502446</v>
+        <v>102.15070965</v>
       </c>
       <c r="J94" t="n">
-        <v>72.62953129</v>
+        <v>150.12609553</v>
       </c>
       <c r="K94" t="n">
-        <v>149.6861809</v>
+        <v>307.43325086</v>
       </c>
       <c r="L94" t="n">
-        <v>291.08983047</v>
+        <v>111.64712743</v>
       </c>
       <c r="M94" t="n">
-        <v>88.94080502</v>
+        <v>-8.731056049999998</v>
       </c>
     </row>
     <row r="95">
@@ -4326,37 +4320,37 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>1814.27344033</v>
+        <v>1199.23969039</v>
       </c>
       <c r="D95" t="n">
-        <v>1190.51089312</v>
+        <v>326.13459925</v>
       </c>
       <c r="E95" t="n">
-        <v>323.3601261200004</v>
+        <v>-811.6942932100002</v>
       </c>
       <c r="F95" t="n">
-        <v>-814.9015840400001</v>
+        <v>681.95792121</v>
       </c>
       <c r="G95" t="n">
-        <v>678.04168456</v>
+        <v>-200.73019715</v>
       </c>
       <c r="H95" t="n">
-        <v>-201.49401636</v>
+        <v>1210.48328601</v>
       </c>
       <c r="I95" t="n">
-        <v>1189.33098974</v>
+        <v>730.77928545</v>
       </c>
       <c r="J95" t="n">
-        <v>709.2095474999999</v>
+        <v>965.6002825499999</v>
       </c>
       <c r="K95" t="n">
-        <v>956.1483032399999</v>
+        <v>3035.47126514</v>
       </c>
       <c r="L95" t="n">
-        <v>3033.12208602</v>
+        <v>2685.63241132</v>
       </c>
       <c r="M95" t="n">
-        <v>2681.58312908</v>
+        <v>401.58927457</v>
       </c>
     </row>
     <row r="96">
@@ -4367,37 +4361,37 @@
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>64.72300055999999</v>
+        <v>132.29966174</v>
       </c>
       <c r="D96" t="n">
-        <v>131.70823582</v>
+        <v>-141.30775993</v>
       </c>
       <c r="E96" t="n">
-        <v>-143.09228886</v>
+        <v>39.64208135</v>
       </c>
       <c r="F96" t="n">
-        <v>39.32826783</v>
+        <v>52.17459030999999</v>
       </c>
       <c r="G96" t="n">
-        <v>52.68948845</v>
+        <v>69.41372987999999</v>
       </c>
       <c r="H96" t="n">
-        <v>69.56662471999999</v>
+        <v>81.05502186</v>
       </c>
       <c r="I96" t="n">
-        <v>81.71908187000001</v>
+        <v>-13.09397059</v>
       </c>
       <c r="J96" t="n">
-        <v>-12.04564383</v>
+        <v>56.25579081</v>
       </c>
       <c r="K96" t="n">
-        <v>57.64531502000001</v>
+        <v>19.28692427</v>
       </c>
       <c r="L96" t="n">
-        <v>19.70511214</v>
+        <v>2.439667629999996</v>
       </c>
       <c r="M96" t="n">
-        <v>2.184672839999996</v>
+        <v>23.74875729999999</v>
       </c>
     </row>
     <row r="97">
@@ -4408,37 +4402,37 @@
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>264.91728899</v>
+        <v>461.32377392</v>
       </c>
       <c r="D97" t="n">
-        <v>470.6439971099999</v>
+        <v>1.259735930000003</v>
       </c>
       <c r="E97" t="n">
-        <v>5.818737989999997</v>
+        <v>162.0188218</v>
       </c>
       <c r="F97" t="n">
-        <v>165.53992615</v>
+        <v>84.03388609</v>
       </c>
       <c r="G97" t="n">
-        <v>87.4352246</v>
+        <v>-41.45642434000001</v>
       </c>
       <c r="H97" t="n">
-        <v>-40.84549997</v>
+        <v>56.75961389999999</v>
       </c>
       <c r="I97" t="n">
-        <v>77.24785016</v>
+        <v>-195.94970524</v>
       </c>
       <c r="J97" t="n">
-        <v>-175.42829405</v>
+        <v>-239.67700159</v>
       </c>
       <c r="K97" t="n">
-        <v>-231.61454649</v>
+        <v>-100.10756896</v>
       </c>
       <c r="L97" t="n">
-        <v>-98.17657771</v>
+        <v>-6.023616009999998</v>
       </c>
       <c r="M97" t="n">
-        <v>-1.719338979999999</v>
+        <v>-53.42532436</v>
       </c>
     </row>
     <row r="98">
@@ -4449,37 +4443,37 @@
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
-        <v>-52.95175765</v>
+        <v>-75.60989875999999</v>
       </c>
       <c r="D98" t="n">
-        <v>-75.60989875999999</v>
+        <v>-89.46311981999999</v>
       </c>
       <c r="E98" t="n">
-        <v>-89.46311981999999</v>
+        <v>-56.04701719000001</v>
       </c>
       <c r="F98" t="n">
-        <v>-56.04701719000001</v>
+        <v>-57.87665437</v>
       </c>
       <c r="G98" t="n">
-        <v>-57.87665437</v>
+        <v>-36.62885614</v>
       </c>
       <c r="H98" t="n">
-        <v>-36.62885614</v>
+        <v>-32.91272461</v>
       </c>
       <c r="I98" t="n">
-        <v>-32.91272461</v>
+        <v>-31.98487371</v>
       </c>
       <c r="J98" t="n">
-        <v>-31.98487371</v>
+        <v>-28.05827051</v>
       </c>
       <c r="K98" t="n">
-        <v>-28.05827051</v>
+        <v>-31.36616687</v>
       </c>
       <c r="L98" t="n">
-        <v>-31.36616687</v>
+        <v>-10.44515264</v>
       </c>
       <c r="M98" t="n">
-        <v>-10.44515264</v>
+        <v>26.32759989</v>
       </c>
     </row>
     <row r="99">
@@ -4490,37 +4484,37 @@
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>20.89206484</v>
+        <v>4.182556519999999</v>
       </c>
       <c r="D99" t="n">
-        <v>4.255960159999999</v>
+        <v>-13.43138844</v>
       </c>
       <c r="E99" t="n">
-        <v>-13.81783122</v>
+        <v>9.332435159999999</v>
       </c>
       <c r="F99" t="n">
-        <v>8.902682299999999</v>
+        <v>-5.543312350000001</v>
       </c>
       <c r="G99" t="n">
-        <v>-7.00097985</v>
+        <v>-7.712997290000001</v>
       </c>
       <c r="H99" t="n">
-        <v>-8.586387240000001</v>
+        <v>-9.903047969999999</v>
       </c>
       <c r="I99" t="n">
-        <v>-10.56307657</v>
+        <v>-10.66132324</v>
       </c>
       <c r="J99" t="n">
-        <v>-11.32923905</v>
+        <v>2.86535633</v>
       </c>
       <c r="K99" t="n">
-        <v>2.98401102</v>
+        <v>0.8721114700000003</v>
       </c>
       <c r="L99" t="n">
-        <v>1.30875266</v>
+        <v>-4.212167819999999</v>
       </c>
       <c r="M99" t="n">
-        <v>-3.510710399999999</v>
+        <v>9.207686730000001</v>
       </c>
     </row>
     <row r="100">
@@ -4531,37 +4525,37 @@
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="n">
-        <v>65.07351196</v>
+        <v>78.49249439999998</v>
       </c>
       <c r="D100" t="n">
-        <v>78.41909075999999</v>
+        <v>91.70239957</v>
       </c>
       <c r="E100" t="n">
-        <v>92.08884234999999</v>
+        <v>-53.80138337</v>
       </c>
       <c r="F100" t="n">
-        <v>-53.37163051</v>
+        <v>-140.44726113</v>
       </c>
       <c r="G100" t="n">
-        <v>-138.98959363</v>
+        <v>-187.8357704</v>
       </c>
       <c r="H100" t="n">
-        <v>-186.96238045</v>
+        <v>-263.76592842</v>
       </c>
       <c r="I100" t="n">
-        <v>-263.10589982</v>
+        <v>-272.37274403</v>
       </c>
       <c r="J100" t="n">
-        <v>-271.70482822</v>
+        <v>-157.19383556</v>
       </c>
       <c r="K100" t="n">
-        <v>-157.31249025</v>
+        <v>-223.07737288</v>
       </c>
       <c r="L100" t="n">
-        <v>-223.51401407</v>
+        <v>-120.0970021</v>
       </c>
       <c r="M100" t="n">
-        <v>-120.79845952</v>
+        <v>-51.04361056</v>
       </c>
     </row>
   </sheetData>

--- a/Result/analyze_2.xlsx
+++ b/Result/analyze_2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M100"/>
+  <dimension ref="A1:M99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
     </row>
@@ -503,37 +503,37 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>203.49008685</v>
+        <v>-322.22722522</v>
       </c>
       <c r="D2" t="n">
-        <v>-276.35701626</v>
+        <v>135.20217909</v>
       </c>
       <c r="E2" t="n">
-        <v>158.97861774</v>
+        <v>242.65630684</v>
       </c>
       <c r="F2" t="n">
-        <v>273.1721498</v>
+        <v>67.46913453000001</v>
       </c>
       <c r="G2" t="n">
-        <v>109.07311689</v>
+        <v>357.82759385</v>
       </c>
       <c r="H2" t="n">
-        <v>397.81934154</v>
+        <v>-35.08082859000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-15.38801818000001</v>
+        <v>249.84557716</v>
       </c>
       <c r="J2" t="n">
-        <v>227.952527</v>
+        <v>605.31840901</v>
       </c>
       <c r="K2" t="n">
-        <v>613.87092129</v>
+        <v>657.13890401</v>
       </c>
       <c r="L2" t="n">
-        <v>670.9315105500001</v>
+        <v>945.81373646</v>
       </c>
       <c r="M2" t="n">
-        <v>931.5625464399998</v>
+        <v>1855.06915177</v>
       </c>
     </row>
     <row r="3">
@@ -544,37 +544,37 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>-67.23004175</v>
+        <v>-159.44846938</v>
       </c>
       <c r="D3" t="n">
-        <v>-166.33005423</v>
+        <v>2.863513359999999</v>
       </c>
       <c r="E3" t="n">
-        <v>6.232973830000001</v>
+        <v>55.44046901999999</v>
       </c>
       <c r="F3" t="n">
-        <v>65.41039418</v>
+        <v>140.1150031</v>
       </c>
       <c r="G3" t="n">
-        <v>149.15657245</v>
+        <v>203.34787115</v>
       </c>
       <c r="H3" t="n">
-        <v>212.78266681</v>
+        <v>116.11038237</v>
       </c>
       <c r="I3" t="n">
-        <v>119.32230385</v>
+        <v>168.18807658</v>
       </c>
       <c r="J3" t="n">
-        <v>181.43881515</v>
+        <v>10.60851722</v>
       </c>
       <c r="K3" t="n">
-        <v>21.08890903</v>
+        <v>-11.69896874</v>
       </c>
       <c r="L3" t="n">
-        <v>6.802920000000005</v>
+        <v>111.92963868</v>
       </c>
       <c r="M3" t="n">
-        <v>147.95318511</v>
+        <v>150.94500049</v>
       </c>
     </row>
     <row r="4">
@@ -585,37 +585,37 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>472.85010655</v>
+        <v>-4.946673600000003</v>
       </c>
       <c r="D4" t="n">
-        <v>-43.93529771</v>
+        <v>-100.45687196</v>
       </c>
       <c r="E4" t="n">
-        <v>-127.60277108</v>
+        <v>148.70740365</v>
       </c>
       <c r="F4" t="n">
-        <v>108.22163553</v>
+        <v>8.439684930000006</v>
       </c>
       <c r="G4" t="n">
-        <v>-42.20586677999999</v>
+        <v>-22.87123488000001</v>
       </c>
       <c r="H4" t="n">
-        <v>-72.29777823000001</v>
+        <v>-160.79882521</v>
       </c>
       <c r="I4" t="n">
-        <v>-183.7035571</v>
+        <v>-62.2850806</v>
       </c>
       <c r="J4" t="n">
-        <v>-53.64276901</v>
+        <v>-151.84072359</v>
       </c>
       <c r="K4" t="n">
-        <v>-170.87362768</v>
+        <v>-186.41994278</v>
       </c>
       <c r="L4" t="n">
-        <v>-222.20792707</v>
+        <v>-24.90480189000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-46.49547533</v>
+        <v>161.79591693</v>
       </c>
     </row>
     <row r="5">
@@ -626,37 +626,37 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>-41.82464505999999</v>
+        <v>-198.68202118</v>
       </c>
       <c r="D5" t="n">
-        <v>-198.68233339</v>
+        <v>-126.15315298</v>
       </c>
       <c r="E5" t="n">
-        <v>-126.15324289</v>
+        <v>186.82811691</v>
       </c>
       <c r="F5" t="n">
-        <v>186.82804932</v>
+        <v>467.8486097100001</v>
       </c>
       <c r="G5" t="n">
-        <v>467.84842782</v>
+        <v>758.27988239</v>
       </c>
       <c r="H5" t="n">
-        <v>758.27957524</v>
+        <v>802.10536136</v>
       </c>
       <c r="I5" t="n">
-        <v>802.1054623700001</v>
+        <v>1311.67929021</v>
       </c>
       <c r="J5" t="n">
-        <v>1311.67882669</v>
+        <v>1402.60968035</v>
       </c>
       <c r="K5" t="n">
-        <v>1402.60993889</v>
+        <v>947.1777888099999</v>
       </c>
       <c r="L5" t="n">
-        <v>947.17838006</v>
+        <v>633.92100185</v>
       </c>
       <c r="M5" t="n">
-        <v>633.9200583099999</v>
+        <v>146.03438519</v>
       </c>
     </row>
     <row r="6">
@@ -667,37 +667,37 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>-17.12550561</v>
+        <v>-110.01241395</v>
       </c>
       <c r="D6" t="n">
-        <v>-110.01340852</v>
+        <v>55.37822946</v>
       </c>
       <c r="E6" t="n">
-        <v>55.37835390999999</v>
+        <v>36.31491508</v>
       </c>
       <c r="F6" t="n">
-        <v>36.31399072</v>
+        <v>-15.07054057</v>
       </c>
       <c r="G6" t="n">
-        <v>-15.07146657</v>
+        <v>-36.497304</v>
       </c>
       <c r="H6" t="n">
-        <v>-36.4982224</v>
+        <v>-50.54118899</v>
       </c>
       <c r="I6" t="n">
-        <v>-50.54148856</v>
+        <v>-51.15767825</v>
       </c>
       <c r="J6" t="n">
-        <v>-51.15717497</v>
+        <v>-140.94539252</v>
       </c>
       <c r="K6" t="n">
-        <v>-140.94454075</v>
+        <v>-65.33151304</v>
       </c>
       <c r="L6" t="n">
-        <v>-65.32947157999999</v>
+        <v>61.9280458</v>
       </c>
       <c r="M6" t="n">
-        <v>61.93062826000001</v>
+        <v>11.71011091</v>
       </c>
     </row>
     <row r="7">
@@ -708,37 +708,37 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>30.16730997</v>
+        <v>17.93379638</v>
       </c>
       <c r="D7" t="n">
-        <v>17.93510316</v>
+        <v>43.01934182999999</v>
       </c>
       <c r="E7" t="n">
-        <v>43.01930729000001</v>
+        <v>35.57172609000001</v>
       </c>
       <c r="F7" t="n">
-        <v>35.57271804000001</v>
+        <v>23.90382348</v>
       </c>
       <c r="G7" t="n">
-        <v>23.90493137</v>
+        <v>18.06918611</v>
       </c>
       <c r="H7" t="n">
-        <v>18.07041166</v>
+        <v>12.93291063</v>
       </c>
       <c r="I7" t="n">
-        <v>12.93310919</v>
+        <v>23.36284826</v>
       </c>
       <c r="J7" t="n">
-        <v>23.3628085</v>
+        <v>8.285367280000001</v>
       </c>
       <c r="K7" t="n">
-        <v>8.284256969999999</v>
+        <v>8.104425859999999</v>
       </c>
       <c r="L7" t="n">
-        <v>8.101793150000002</v>
+        <v>10.62028197</v>
       </c>
       <c r="M7" t="n">
-        <v>10.61864305</v>
+        <v>11.86706585</v>
       </c>
     </row>
     <row r="8">
@@ -749,37 +749,37 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>600.11167478</v>
+        <v>-2015.17474928</v>
       </c>
       <c r="D8" t="n">
-        <v>-1954.76384583</v>
+        <v>-576.1517193</v>
       </c>
       <c r="E8" t="n">
-        <v>-601.3486867599999</v>
+        <v>1605.08533393</v>
       </c>
       <c r="F8" t="n">
-        <v>1553.77214451</v>
+        <v>1699.48898073</v>
       </c>
       <c r="G8" t="n">
-        <v>1727.70582126</v>
+        <v>1760.30099883</v>
       </c>
       <c r="H8" t="n">
-        <v>1816.7779131</v>
+        <v>258.82277212</v>
       </c>
       <c r="I8" t="n">
-        <v>294.4739660700001</v>
+        <v>-136.10115485</v>
       </c>
       <c r="J8" t="n">
-        <v>-133.97107088</v>
+        <v>1519.8498465</v>
       </c>
       <c r="K8" t="n">
-        <v>1435.74773577</v>
+        <v>2333.54672179</v>
       </c>
       <c r="L8" t="n">
-        <v>2186.03386589</v>
+        <v>1156.50518768</v>
       </c>
       <c r="M8" t="n">
-        <v>1070.4454373</v>
+        <v>1287.23069345</v>
       </c>
     </row>
     <row r="9">
@@ -790,37 +790,37 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>74.59893966</v>
+        <v>5.40532031</v>
       </c>
       <c r="D9" t="n">
-        <v>5.405164230000001</v>
+        <v>67.87246501</v>
       </c>
       <c r="E9" t="n">
-        <v>67.87233653</v>
+        <v>64.29666813999999</v>
       </c>
       <c r="F9" t="n">
-        <v>64.29641302</v>
+        <v>24.04332181</v>
       </c>
       <c r="G9" t="n">
-        <v>24.04309969</v>
+        <v>-2.54936097</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.54958474</v>
+        <v>5.406092370000001</v>
       </c>
       <c r="I9" t="n">
-        <v>5.40583608</v>
+        <v>17.64058343</v>
       </c>
       <c r="J9" t="n">
-        <v>17.64058429</v>
+        <v>-18.94161434</v>
       </c>
       <c r="K9" t="n">
-        <v>-18.94115622</v>
+        <v>37.62844630000001</v>
       </c>
       <c r="L9" t="n">
-        <v>37.6286003</v>
+        <v>35.63573011</v>
       </c>
       <c r="M9" t="n">
-        <v>35.63607057</v>
+        <v>39.53914933</v>
       </c>
     </row>
     <row r="10">
@@ -831,37 +831,37 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>30.11313543999999</v>
+        <v>-80.77079300000001</v>
       </c>
       <c r="D10" t="n">
-        <v>-116.35059885</v>
+        <v>-16.45917164</v>
       </c>
       <c r="E10" t="n">
-        <v>-19.88571498</v>
+        <v>45.5686809</v>
       </c>
       <c r="F10" t="n">
-        <v>75.96020147</v>
+        <v>11.50130725</v>
       </c>
       <c r="G10" t="n">
-        <v>-32.51842934999999</v>
+        <v>11.54029648</v>
       </c>
       <c r="H10" t="n">
-        <v>-56.9996982</v>
+        <v>-26.15984913</v>
       </c>
       <c r="I10" t="n">
-        <v>-105.63273326</v>
+        <v>3.02895754</v>
       </c>
       <c r="J10" t="n">
-        <v>-38.63570006</v>
+        <v>-16.71430331</v>
       </c>
       <c r="K10" t="n">
-        <v>-10.3505524</v>
+        <v>39.20265944</v>
       </c>
       <c r="L10" t="n">
-        <v>99.57899974999999</v>
+        <v>56.81217666</v>
       </c>
       <c r="M10" t="n">
-        <v>45.90581191</v>
+        <v>76.48051932000001</v>
       </c>
     </row>
     <row r="11">
@@ -872,37 +872,37 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>16.45993232</v>
+        <v>2.859002090000001</v>
       </c>
       <c r="D11" t="n">
-        <v>2.859002090000001</v>
+        <v>23.8488836</v>
       </c>
       <c r="E11" t="n">
-        <v>23.8488836</v>
+        <v>31.95600483</v>
       </c>
       <c r="F11" t="n">
-        <v>31.95600483</v>
+        <v>36.40751091</v>
       </c>
       <c r="G11" t="n">
-        <v>36.40751091</v>
+        <v>70.07194070999999</v>
       </c>
       <c r="H11" t="n">
-        <v>70.07194070999999</v>
+        <v>11.69021167</v>
       </c>
       <c r="I11" t="n">
-        <v>11.69021167</v>
+        <v>59.84247325</v>
       </c>
       <c r="J11" t="n">
-        <v>59.84247325</v>
+        <v>132.53821739</v>
       </c>
       <c r="K11" t="n">
-        <v>132.53821739</v>
+        <v>62.3192098</v>
       </c>
       <c r="L11" t="n">
-        <v>62.3192098</v>
+        <v>59.63880218</v>
       </c>
       <c r="M11" t="n">
-        <v>59.63880218</v>
+        <v>-16.82507837</v>
       </c>
     </row>
     <row r="12">
@@ -913,37 +913,37 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>248.90957013</v>
+        <v>38.94469194999999</v>
       </c>
       <c r="D12" t="n">
-        <v>38.94469194999999</v>
+        <v>43.88918375</v>
       </c>
       <c r="E12" t="n">
-        <v>43.88918375</v>
+        <v>181.12827274</v>
       </c>
       <c r="F12" t="n">
-        <v>181.12827274</v>
+        <v>62.28709359</v>
       </c>
       <c r="G12" t="n">
-        <v>62.28709359</v>
+        <v>47.51182313</v>
       </c>
       <c r="H12" t="n">
-        <v>47.51182313</v>
+        <v>-67.86251213</v>
       </c>
       <c r="I12" t="n">
-        <v>-67.86251213</v>
+        <v>117.04709593</v>
       </c>
       <c r="J12" t="n">
-        <v>117.04709593</v>
+        <v>1.19653822</v>
       </c>
       <c r="K12" t="n">
-        <v>1.19653822</v>
+        <v>-83.11722171000001</v>
       </c>
       <c r="L12" t="n">
-        <v>-83.11722171000001</v>
+        <v>-44.36274827</v>
       </c>
       <c r="M12" t="n">
-        <v>-44.36274827</v>
+        <v>-99.14298217</v>
       </c>
     </row>
     <row r="13">
@@ -954,37 +954,37 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>1.29052322</v>
+        <v>-1.64482739</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.64482739</v>
+        <v>2.07536182</v>
       </c>
       <c r="E13" t="n">
-        <v>2.07536182</v>
+        <v>0.49718892</v>
       </c>
       <c r="F13" t="n">
-        <v>0.49718892</v>
+        <v>-1.20818879</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.20818879</v>
+        <v>-0.03567795000000003</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.03567795000000003</v>
+        <v>1.16522951</v>
       </c>
       <c r="I13" t="n">
-        <v>1.16522951</v>
+        <v>2.46887667</v>
       </c>
       <c r="J13" t="n">
-        <v>2.46887667</v>
+        <v>3.68953275</v>
       </c>
       <c r="K13" t="n">
-        <v>3.68953275</v>
+        <v>2.212082590000001</v>
       </c>
       <c r="L13" t="n">
-        <v>2.212082590000001</v>
+        <v>2.475399079999999</v>
       </c>
       <c r="M13" t="n">
-        <v>2.475399079999999</v>
+        <v>0.5298702900000001</v>
       </c>
     </row>
     <row r="14">
@@ -995,37 +995,37 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>-73.80787921000001</v>
+        <v>-6456.45545905</v>
       </c>
       <c r="D14" t="n">
-        <v>-6404.986798970001</v>
+        <v>-2412.35071206</v>
       </c>
       <c r="E14" t="n">
-        <v>-2387.28499942</v>
+        <v>-3231.9633218</v>
       </c>
       <c r="F14" t="n">
-        <v>-3210.22790721</v>
+        <v>-6067.096989799999</v>
       </c>
       <c r="G14" t="n">
-        <v>-6061.21163653</v>
+        <v>-8165.36055333</v>
       </c>
       <c r="H14" t="n">
-        <v>-8186.855044399999</v>
+        <v>-11808.0342604</v>
       </c>
       <c r="I14" t="n">
-        <v>-11815.19871817</v>
+        <v>-5565.214608</v>
       </c>
       <c r="J14" t="n">
-        <v>-5578.29502055</v>
+        <v>-693.9481102300002</v>
       </c>
       <c r="K14" t="n">
-        <v>-719.4418733800004</v>
+        <v>-4033.15507835</v>
       </c>
       <c r="L14" t="n">
-        <v>-4048.66307044</v>
+        <v>-5990.6567424</v>
       </c>
       <c r="M14" t="n">
-        <v>-6007.02146868</v>
+        <v>-1118.12726076</v>
       </c>
     </row>
     <row r="15">
@@ -1034,41 +1034,39 @@
           <t>半導體業右下</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>597.56649538</v>
+        <v>-55.75599463999998</v>
       </c>
       <c r="D15" t="n">
-        <v>-55.82158261999998</v>
+        <v>768.03967224</v>
       </c>
       <c r="E15" t="n">
-        <v>767.9598315500001</v>
+        <v>424.0897906</v>
       </c>
       <c r="F15" t="n">
-        <v>424.02378399</v>
+        <v>575.79890386</v>
       </c>
       <c r="G15" t="n">
-        <v>575.7480783</v>
+        <v>493.11082581</v>
       </c>
       <c r="H15" t="n">
-        <v>493.0647100100001</v>
+        <v>2.431007869999977</v>
       </c>
       <c r="I15" t="n">
-        <v>2.393189149999978</v>
+        <v>140.82586865</v>
       </c>
       <c r="J15" t="n">
-        <v>140.80050117</v>
+        <v>-526.45670635</v>
       </c>
       <c r="K15" t="n">
-        <v>-526.47615674</v>
+        <v>-85.14885054</v>
       </c>
       <c r="L15" t="n">
-        <v>-84.51514500999998</v>
+        <v>124.88546237</v>
       </c>
       <c r="M15" t="n">
-        <v>125.42301085</v>
+        <v>726.86992059</v>
       </c>
     </row>
     <row r="16">
@@ -1079,37 +1077,37 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>195.75642651</v>
+        <v>-250.4489123</v>
       </c>
       <c r="D16" t="n">
-        <v>-301.8312480700001</v>
+        <v>644.3022150199999</v>
       </c>
       <c r="E16" t="n">
-        <v>619.2252684399999</v>
+        <v>122.79713917</v>
       </c>
       <c r="F16" t="n">
-        <v>100.98110874</v>
+        <v>-120.27460381</v>
       </c>
       <c r="G16" t="n">
-        <v>-126.15191792</v>
+        <v>56.98240913000001</v>
       </c>
       <c r="H16" t="n">
-        <v>78.47394292000003</v>
+        <v>272.61525249</v>
       </c>
       <c r="I16" t="n">
-        <v>279.82426251</v>
+        <v>-525.64720146</v>
       </c>
       <c r="J16" t="n">
-        <v>-512.62341522</v>
+        <v>-204.80521879</v>
       </c>
       <c r="K16" t="n">
-        <v>-179.45931426</v>
+        <v>-302.53034958</v>
       </c>
       <c r="L16" t="n">
-        <v>-287.0601313499999</v>
+        <v>-971.59696974</v>
       </c>
       <c r="M16" t="n">
-        <v>-955.2026000599999</v>
+        <v>-807.61602896</v>
       </c>
     </row>
     <row r="17">
@@ -1120,37 +1118,37 @@
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
-        <v>-0.26640583</v>
+        <v>-0.5506804200000001</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.55064815</v>
+        <v>0.02769227000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>0.02769861000000001</v>
+        <v>0.34978601</v>
       </c>
       <c r="F17" t="n">
-        <v>0.34979235</v>
+        <v>0.55657781</v>
       </c>
       <c r="G17" t="n">
-        <v>0.55659024</v>
+        <v>0.5684159599999999</v>
       </c>
       <c r="H17" t="n">
-        <v>0.56842657</v>
+        <v>0.6202892800000001</v>
       </c>
       <c r="I17" t="n">
-        <v>0.62029989</v>
+        <v>0.7926845100000001</v>
       </c>
       <c r="J17" t="n">
-        <v>0.79269335</v>
+        <v>1.35238512</v>
       </c>
       <c r="K17" t="n">
-        <v>1.35239712</v>
+        <v>2.728392</v>
       </c>
       <c r="L17" t="n">
-        <v>2.728404</v>
+        <v>0.88005688</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8800688800000001</v>
+        <v>0.9546220400000001</v>
       </c>
     </row>
     <row r="18">
@@ -1161,37 +1159,37 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>533.24000686</v>
+        <v>338.87725289</v>
       </c>
       <c r="D18" t="n">
-        <v>338.87725289</v>
+        <v>494.0830853900001</v>
       </c>
       <c r="E18" t="n">
-        <v>494.0830853900001</v>
+        <v>317.7273254</v>
       </c>
       <c r="F18" t="n">
-        <v>317.7273254</v>
+        <v>283.6058508000001</v>
       </c>
       <c r="G18" t="n">
-        <v>283.6058508000001</v>
+        <v>797.0432088700001</v>
       </c>
       <c r="H18" t="n">
-        <v>797.0432088700001</v>
+        <v>-142.28295233</v>
       </c>
       <c r="I18" t="n">
-        <v>-142.28295233</v>
+        <v>949.17323245</v>
       </c>
       <c r="J18" t="n">
-        <v>949.17323245</v>
+        <v>786.6830428600001</v>
       </c>
       <c r="K18" t="n">
-        <v>786.6830428600001</v>
+        <v>-188.6316088</v>
       </c>
       <c r="L18" t="n">
-        <v>-272.85884179</v>
+        <v>-747.85914215</v>
       </c>
       <c r="M18" t="n">
-        <v>-871.1229194199999</v>
+        <v>-949.2131747899999</v>
       </c>
     </row>
     <row r="19">
@@ -1202,37 +1200,37 @@
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>-9.88241236</v>
+        <v>-14.82226019</v>
       </c>
       <c r="D19" t="n">
-        <v>-14.82229246</v>
+        <v>-9.676533539999999</v>
       </c>
       <c r="E19" t="n">
-        <v>-9.676539879999998</v>
+        <v>-12.01173597</v>
       </c>
       <c r="F19" t="n">
-        <v>-12.01174231</v>
+        <v>-11.46146303</v>
       </c>
       <c r="G19" t="n">
-        <v>-11.46147546</v>
+        <v>-4.65900013</v>
       </c>
       <c r="H19" t="n">
-        <v>-4.65901074</v>
+        <v>-9.61752909</v>
       </c>
       <c r="I19" t="n">
-        <v>-9.6175397</v>
+        <v>-3.18360563</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.18361447</v>
+        <v>-6.06010232</v>
       </c>
       <c r="K19" t="n">
-        <v>-6.06011432</v>
+        <v>-6.603607350000001</v>
       </c>
       <c r="L19" t="n">
-        <v>-6.603619350000001</v>
+        <v>-1.86833417</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.86834617</v>
+        <v>-3.4926213</v>
       </c>
     </row>
     <row r="20">
@@ -1243,37 +1241,37 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>19.83993459</v>
+        <v>5.16841279</v>
       </c>
       <c r="D20" t="n">
-        <v>5.16841279</v>
+        <v>34.60344654</v>
       </c>
       <c r="E20" t="n">
-        <v>34.60344654</v>
+        <v>39.71568626000001</v>
       </c>
       <c r="F20" t="n">
-        <v>39.71568626000001</v>
+        <v>46.16644797999999</v>
       </c>
       <c r="G20" t="n">
-        <v>46.16644797999999</v>
+        <v>49.78897659</v>
       </c>
       <c r="H20" t="n">
-        <v>49.78897659</v>
+        <v>15.83594655</v>
       </c>
       <c r="I20" t="n">
-        <v>15.83594655</v>
+        <v>43.34008297</v>
       </c>
       <c r="J20" t="n">
-        <v>43.34008297</v>
+        <v>-20.57462681</v>
       </c>
       <c r="K20" t="n">
-        <v>-20.57462681</v>
+        <v>-26.64046678</v>
       </c>
       <c r="L20" t="n">
-        <v>-26.64046678</v>
+        <v>-8.66289199</v>
       </c>
       <c r="M20" t="n">
-        <v>-8.66289199</v>
+        <v>6.307098380000001</v>
       </c>
     </row>
     <row r="21">
@@ -1282,39 +1280,41 @@
           <t>居家生活右下</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
       <c r="C21" t="n">
-        <v>1.92116228</v>
+        <v>-2.44418154</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.44418154</v>
+        <v>-2.90937825</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.90937825</v>
+        <v>-0.6914854</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6914854</v>
+        <v>-0.87016615</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.87016615</v>
+        <v>0.47642728</v>
       </c>
       <c r="H21" t="n">
-        <v>0.47642728</v>
+        <v>-1.38489539</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.38489539</v>
+        <v>1.01578957</v>
       </c>
       <c r="J21" t="n">
-        <v>1.01578957</v>
+        <v>-0.08695448000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.08695448000000001</v>
+        <v>1.98383284</v>
       </c>
       <c r="L21" t="n">
-        <v>1.98383284</v>
+        <v>2.625483</v>
       </c>
       <c r="M21" t="n">
-        <v>2.625483</v>
+        <v>2.3940447</v>
       </c>
     </row>
     <row r="22">
@@ -1325,37 +1325,37 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>-0.9446688699999999</v>
+        <v>-2.65920272</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6602612</v>
+        <v>-1.56090563</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.56212208</v>
+        <v>-0.4818726700000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.48297587</v>
+        <v>0.12802714</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1275219</v>
+        <v>0.40218884</v>
       </c>
       <c r="H22" t="n">
-        <v>0.40213993</v>
+        <v>-0.10679337</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1067566</v>
+        <v>0.11954587</v>
       </c>
       <c r="J22" t="n">
-        <v>0.11962009</v>
+        <v>0.08807710000000005</v>
       </c>
       <c r="K22" t="n">
-        <v>0.08824311000000006</v>
+        <v>1.5294618</v>
       </c>
       <c r="L22" t="n">
-        <v>1.53011789</v>
+        <v>2.46055779</v>
       </c>
       <c r="M22" t="n">
-        <v>2.46088503</v>
+        <v>1.59732101</v>
       </c>
     </row>
     <row r="23">
@@ -1366,37 +1366,37 @@
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
-        <v>-20.02007137</v>
+        <v>-35.27000823</v>
       </c>
       <c r="D23" t="n">
-        <v>-49.58400418</v>
+        <v>9.438695200000002</v>
       </c>
       <c r="E23" t="n">
-        <v>8.735795679999999</v>
+        <v>29.14204919</v>
       </c>
       <c r="F23" t="n">
-        <v>26.99976877</v>
+        <v>18.78984363</v>
       </c>
       <c r="G23" t="n">
-        <v>15.13909586</v>
+        <v>11.99700128</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.688928360000001</v>
+        <v>-21.51542892</v>
       </c>
       <c r="I23" t="n">
-        <v>-42.37913560000001</v>
+        <v>3.234019390000002</v>
       </c>
       <c r="J23" t="n">
-        <v>-18.23225077</v>
+        <v>1.317080060000002</v>
       </c>
       <c r="K23" t="n">
-        <v>-27.17241243</v>
+        <v>-8.2388408</v>
       </c>
       <c r="L23" t="n">
-        <v>-9.696450990000002</v>
+        <v>30.90360521</v>
       </c>
       <c r="M23" t="n">
-        <v>57.26541241</v>
+        <v>28.25559642</v>
       </c>
     </row>
     <row r="24">
@@ -1407,37 +1407,37 @@
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
-        <v>-15.04512446</v>
+        <v>-59.08562743</v>
       </c>
       <c r="D24" t="n">
-        <v>-59.08562743</v>
+        <v>-66.95218318999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-66.95218318999999</v>
+        <v>-81.1055707</v>
       </c>
       <c r="F24" t="n">
-        <v>-81.1055707</v>
+        <v>-84.15877762000001</v>
       </c>
       <c r="G24" t="n">
-        <v>-84.15877762000001</v>
+        <v>-84.14077758000001</v>
       </c>
       <c r="H24" t="n">
-        <v>-84.14077758000001</v>
+        <v>-82.8272675</v>
       </c>
       <c r="I24" t="n">
-        <v>-82.8272675</v>
+        <v>-54.6127678</v>
       </c>
       <c r="J24" t="n">
-        <v>-54.6127678</v>
+        <v>-33.53495641</v>
       </c>
       <c r="K24" t="n">
-        <v>-33.53495641</v>
+        <v>2.644124560000001</v>
       </c>
       <c r="L24" t="n">
-        <v>2.644124560000001</v>
+        <v>45.01555479</v>
       </c>
       <c r="M24" t="n">
-        <v>45.01555479</v>
+        <v>38.81457239</v>
       </c>
     </row>
     <row r="25">
@@ -1448,37 +1448,37 @@
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>58.59532707</v>
+        <v>8.92547113</v>
       </c>
       <c r="D25" t="n">
-        <v>23.23946708</v>
+        <v>81.98642715999999</v>
       </c>
       <c r="E25" t="n">
-        <v>82.68932667999999</v>
+        <v>35.51251422999999</v>
       </c>
       <c r="F25" t="n">
-        <v>37.65479465</v>
+        <v>-16.15412204</v>
       </c>
       <c r="G25" t="n">
-        <v>-12.50337427</v>
+        <v>-67.66528073000001</v>
       </c>
       <c r="H25" t="n">
-        <v>-53.97935109</v>
+        <v>-118.19933877</v>
       </c>
       <c r="I25" t="n">
-        <v>-97.33563208999999</v>
+        <v>-90.22914847</v>
       </c>
       <c r="J25" t="n">
-        <v>-68.76287831</v>
+        <v>-117.65471035</v>
       </c>
       <c r="K25" t="n">
-        <v>-89.16521786</v>
+        <v>-16.00842115</v>
       </c>
       <c r="L25" t="n">
-        <v>-14.55081096</v>
+        <v>100.40510662</v>
       </c>
       <c r="M25" t="n">
-        <v>74.04329942</v>
+        <v>9.99010182</v>
       </c>
     </row>
     <row r="26">
@@ -1489,37 +1489,37 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>80.11023591</v>
+        <v>14.92712717</v>
       </c>
       <c r="D26" t="n">
-        <v>14.96755027</v>
+        <v>60.74444865</v>
       </c>
       <c r="E26" t="n">
-        <v>60.78673921</v>
+        <v>106.37604668</v>
       </c>
       <c r="F26" t="n">
-        <v>106.4159577</v>
+        <v>30.41413148</v>
       </c>
       <c r="G26" t="n">
-        <v>30.45080732</v>
+        <v>27.07538775</v>
       </c>
       <c r="H26" t="n">
-        <v>27.11465835</v>
+        <v>-16.00512611</v>
       </c>
       <c r="I26" t="n">
-        <v>-15.9721707</v>
+        <v>-11.48791496</v>
       </c>
       <c r="J26" t="n">
-        <v>-11.45883006</v>
+        <v>-0.5816431699999999</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.55266821</v>
+        <v>20.25448622</v>
       </c>
       <c r="L26" t="n">
-        <v>20.27945308</v>
+        <v>-15.84902005</v>
       </c>
       <c r="M26" t="n">
-        <v>-15.82722061</v>
+        <v>12.53861818</v>
       </c>
     </row>
     <row r="27">
@@ -1530,37 +1530,37 @@
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>5.80081306</v>
+        <v>-5.07148308</v>
       </c>
       <c r="D27" t="n">
-        <v>-5.07146912</v>
+        <v>19.81733471</v>
       </c>
       <c r="E27" t="n">
-        <v>19.81744912</v>
+        <v>26.50834888</v>
       </c>
       <c r="F27" t="n">
-        <v>26.50836019999999</v>
+        <v>12.3732266</v>
       </c>
       <c r="G27" t="n">
-        <v>12.37337787</v>
+        <v>16.88570324</v>
       </c>
       <c r="H27" t="n">
-        <v>16.88589567</v>
+        <v>5.174999509999999</v>
       </c>
       <c r="I27" t="n">
-        <v>5.175073139999999</v>
+        <v>10.18965648</v>
       </c>
       <c r="J27" t="n">
-        <v>10.18979128</v>
+        <v>5.14904886</v>
       </c>
       <c r="K27" t="n">
-        <v>5.14915096</v>
+        <v>12.32428043</v>
       </c>
       <c r="L27" t="n">
-        <v>12.32444672</v>
+        <v>7.23473412</v>
       </c>
       <c r="M27" t="n">
-        <v>7.234856349999998</v>
+        <v>21.39711191</v>
       </c>
     </row>
     <row r="28">
@@ -1571,37 +1571,37 @@
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>-0.39243835</v>
+        <v>-0.49655746</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.53699452</v>
+        <v>-0.21799665</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.26040162</v>
+        <v>-0.48054054</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.52046288</v>
+        <v>-0.16923084</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.20605795</v>
+        <v>-0.31802269</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.35748572</v>
+        <v>-0.36590925</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.39893829</v>
+        <v>-0.08474315</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.11396285</v>
+        <v>-0.15341244</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.1824895</v>
+        <v>-0.06900096</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.09413411000000002</v>
+        <v>0.18393767</v>
       </c>
       <c r="M28" t="n">
-        <v>0.162016</v>
+        <v>0.38545393</v>
       </c>
     </row>
     <row r="29">
@@ -1612,37 +1612,37 @@
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>-0.03307111</v>
+        <v>-0.03255481</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.03255481</v>
+        <v>-0.01281979</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.01281979</v>
+        <v>-0.00154904</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.00154904</v>
+        <v>-0.00032023</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.00032023</v>
+        <v>0.00658342</v>
       </c>
       <c r="H29" t="n">
-        <v>0.00658342</v>
+        <v>-0.00477515</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.00477515</v>
+        <v>0.004036490000000001</v>
       </c>
       <c r="J29" t="n">
-        <v>0.004036490000000001</v>
+        <v>0.01033713</v>
       </c>
       <c r="K29" t="n">
-        <v>0.01033713</v>
+        <v>0.01825068</v>
       </c>
       <c r="L29" t="n">
-        <v>0.01825068</v>
+        <v>0.02746755</v>
       </c>
       <c r="M29" t="n">
-        <v>0.02746755</v>
+        <v>0.08414062</v>
       </c>
     </row>
     <row r="30">
@@ -1653,37 +1653,37 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>-0.006610240000000001</v>
+        <v>-0.01385127</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0134701</v>
+        <v>-0.0008485099999999998</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0001509699999999998</v>
+        <v>-0.0025532</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.00248782</v>
+        <v>0.00442858</v>
       </c>
       <c r="G30" t="n">
-        <v>0.00563157</v>
+        <v>-0.0001344399999999998</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0038025</v>
+        <v>-0.00311901</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0011534</v>
+        <v>-0.00135107</v>
       </c>
       <c r="J30" t="n">
-        <v>0.00062989</v>
+        <v>-0.00645304</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.005775890000000001</v>
+        <v>-0.0007993899999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>0.0001075200000000001</v>
+        <v>0.008251139999999999</v>
       </c>
       <c r="M30" t="n">
-        <v>0.009618040000000001</v>
+        <v>0.009377439999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1694,37 +1694,37 @@
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>-0.15155761</v>
+        <v>-0.20942146</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.20980263</v>
+        <v>0.03501509000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>0.03431755</v>
+        <v>-0.05155387</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.05161925</v>
+        <v>0.04295467</v>
       </c>
       <c r="G31" t="n">
-        <v>0.04175168</v>
+        <v>0.009156010000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>0.00521907</v>
+        <v>-0.04370564</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.04567125</v>
+        <v>-0.07121751</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.07319847</v>
+        <v>0.0339659</v>
       </c>
       <c r="K31" t="n">
-        <v>0.03328875</v>
+        <v>0.001858120000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>0.0009512100000000007</v>
+        <v>0.10022693</v>
       </c>
       <c r="M31" t="n">
-        <v>0.09886003</v>
+        <v>0.21841852</v>
       </c>
     </row>
     <row r="32">
@@ -1735,37 +1735,37 @@
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>-0.19341137</v>
+        <v>-1.58173283</v>
       </c>
       <c r="D32" t="n">
-        <v>-1.58173283</v>
+        <v>0.79667627</v>
       </c>
       <c r="E32" t="n">
-        <v>0.79667627</v>
+        <v>-0.8938292</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.8938292</v>
+        <v>0.26859018</v>
       </c>
       <c r="G32" t="n">
-        <v>0.26859018</v>
+        <v>-1.1550498</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.1550498</v>
+        <v>0.19597777</v>
       </c>
       <c r="I32" t="n">
-        <v>0.19597777</v>
+        <v>0.93832401</v>
       </c>
       <c r="J32" t="n">
-        <v>0.93832401</v>
+        <v>-0.60581137</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.60581137</v>
+        <v>-0.18124846</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.18124846</v>
+        <v>0.6026511899999999</v>
       </c>
       <c r="M32" t="n">
-        <v>0.6026511899999999</v>
+        <v>2.12415212</v>
       </c>
     </row>
     <row r="33">
@@ -1776,37 +1776,37 @@
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
-        <v>46.49768424000001</v>
+        <v>1.71917202</v>
       </c>
       <c r="D33" t="n">
-        <v>1.71917202</v>
+        <v>51.11736981</v>
       </c>
       <c r="E33" t="n">
-        <v>51.11736981</v>
+        <v>74.52305657000001</v>
       </c>
       <c r="F33" t="n">
-        <v>74.52305657000001</v>
+        <v>28.77819571</v>
       </c>
       <c r="G33" t="n">
-        <v>28.77819571</v>
+        <v>47.13405325</v>
       </c>
       <c r="H33" t="n">
-        <v>47.13405325</v>
+        <v>17.62821512</v>
       </c>
       <c r="I33" t="n">
-        <v>17.62821512</v>
+        <v>9.357429240000002</v>
       </c>
       <c r="J33" t="n">
-        <v>9.357429240000002</v>
+        <v>-23.28926443</v>
       </c>
       <c r="K33" t="n">
-        <v>-23.28926443</v>
+        <v>-15.50397747</v>
       </c>
       <c r="L33" t="n">
-        <v>-15.50397747</v>
+        <v>-7.671519279999999</v>
       </c>
       <c r="M33" t="n">
-        <v>-7.671519279999999</v>
+        <v>-12.56496135</v>
       </c>
     </row>
     <row r="34">
@@ -1817,37 +1817,37 @@
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
-        <v>0.6885503099999999</v>
+        <v>0.03085148000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>0.03085148000000001</v>
+        <v>0.6241331099999999</v>
       </c>
       <c r="E34" t="n">
-        <v>0.6241331099999999</v>
+        <v>0.6281405</v>
       </c>
       <c r="F34" t="n">
-        <v>0.6281405</v>
+        <v>0.5322796400000001</v>
       </c>
       <c r="G34" t="n">
-        <v>0.5322796400000001</v>
+        <v>0.66688402</v>
       </c>
       <c r="H34" t="n">
-        <v>0.66688402</v>
+        <v>0.39455165</v>
       </c>
       <c r="I34" t="n">
-        <v>0.39455165</v>
+        <v>0.7616216099999999</v>
       </c>
       <c r="J34" t="n">
-        <v>0.7616216099999999</v>
+        <v>0.68170787</v>
       </c>
       <c r="K34" t="n">
-        <v>0.68170787</v>
+        <v>0.03184879000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>0.03184879000000001</v>
+        <v>-0.05228055</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.05228055</v>
+        <v>-0.22602753</v>
       </c>
     </row>
     <row r="35">
@@ -1858,37 +1858,37 @@
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
-        <v>29.79901899</v>
+        <v>191.1411963</v>
       </c>
       <c r="D35" t="n">
-        <v>191.1411963</v>
+        <v>281.70180355</v>
       </c>
       <c r="E35" t="n">
-        <v>281.70180355</v>
+        <v>169.91598432</v>
       </c>
       <c r="F35" t="n">
-        <v>169.91598432</v>
+        <v>151.94936306</v>
       </c>
       <c r="G35" t="n">
-        <v>151.94936306</v>
+        <v>180.3735272</v>
       </c>
       <c r="H35" t="n">
-        <v>180.3735272</v>
+        <v>110.71375524</v>
       </c>
       <c r="I35" t="n">
-        <v>110.71375524</v>
+        <v>152.65296865</v>
       </c>
       <c r="J35" t="n">
-        <v>152.65296865</v>
+        <v>75.59350051</v>
       </c>
       <c r="K35" t="n">
-        <v>75.59350051</v>
+        <v>33.17521386</v>
       </c>
       <c r="L35" t="n">
-        <v>33.17521386</v>
+        <v>20.83055937</v>
       </c>
       <c r="M35" t="n">
-        <v>20.83055937</v>
+        <v>33.4962376</v>
       </c>
     </row>
     <row r="36">
@@ -1899,37 +1899,37 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>82.34751310999999</v>
+        <v>-13.62434275</v>
       </c>
       <c r="D36" t="n">
-        <v>-20.24144777</v>
+        <v>44.67745786</v>
       </c>
       <c r="E36" t="n">
-        <v>25.74357816000001</v>
+        <v>59.54918461</v>
       </c>
       <c r="F36" t="n">
-        <v>-23.20394607</v>
+        <v>10.97615903</v>
       </c>
       <c r="G36" t="n">
-        <v>-46.50593372</v>
+        <v>-27.80501389</v>
       </c>
       <c r="H36" t="n">
-        <v>-73.58654622</v>
+        <v>-59.6302486</v>
       </c>
       <c r="I36" t="n">
-        <v>-69.61487504999999</v>
+        <v>-13.99488734</v>
       </c>
       <c r="J36" t="n">
-        <v>-38.2629963</v>
+        <v>-16.70895106</v>
       </c>
       <c r="K36" t="n">
-        <v>2.09840131</v>
+        <v>14.60214181</v>
       </c>
       <c r="L36" t="n">
-        <v>4.881436730000001</v>
+        <v>48.93507795999999</v>
       </c>
       <c r="M36" t="n">
-        <v>41.34069034</v>
+        <v>150.56891356</v>
       </c>
     </row>
     <row r="37">
@@ -1938,39 +1938,41 @@
           <t>汽車工業右下</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
       <c r="C37" t="n">
-        <v>9.633830980000003</v>
+        <v>-26.29271288</v>
       </c>
       <c r="D37" t="n">
-        <v>-23.40385333</v>
+        <v>55.89401399</v>
       </c>
       <c r="E37" t="n">
-        <v>57.54664698</v>
+        <v>57.36199072</v>
       </c>
       <c r="F37" t="n">
-        <v>59.14021824</v>
+        <v>50.70589786</v>
       </c>
       <c r="G37" t="n">
-        <v>51.38866752999999</v>
+        <v>50.21233335</v>
       </c>
       <c r="H37" t="n">
-        <v>50.08324433999999</v>
+        <v>31.40989619</v>
       </c>
       <c r="I37" t="n">
-        <v>32.01164784</v>
+        <v>72.00956927</v>
       </c>
       <c r="J37" t="n">
-        <v>65.08389405</v>
+        <v>-5.285111869999999</v>
       </c>
       <c r="K37" t="n">
-        <v>-5.245381119999999</v>
+        <v>1.539300029999999</v>
       </c>
       <c r="L37" t="n">
-        <v>0.09162379999999946</v>
+        <v>26.40051155</v>
       </c>
       <c r="M37" t="n">
-        <v>23.55432724</v>
+        <v>40.88328293</v>
       </c>
     </row>
     <row r="38">
@@ -1981,37 +1983,37 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>83.65572380000002</v>
+        <v>-21.53170029</v>
       </c>
       <c r="D38" t="n">
-        <v>-17.88309525</v>
+        <v>77.96595423999999</v>
       </c>
       <c r="E38" t="n">
-        <v>95.39936956999999</v>
+        <v>7.912929220000001</v>
       </c>
       <c r="F38" t="n">
-        <v>89.08669624000001</v>
+        <v>-37.16771344</v>
       </c>
       <c r="G38" t="n">
-        <v>19.73452993</v>
+        <v>-57.37401867000001</v>
       </c>
       <c r="H38" t="n">
-        <v>-11.29958163</v>
+        <v>-72.93299465999999</v>
       </c>
       <c r="I38" t="n">
-        <v>-63.47355001</v>
+        <v>-23.94618323</v>
       </c>
       <c r="J38" t="n">
-        <v>7.24893328</v>
+        <v>-22.10185019</v>
       </c>
       <c r="K38" t="n">
-        <v>-41.01745597</v>
+        <v>-18.76744058</v>
       </c>
       <c r="L38" t="n">
-        <v>-7.559331070000001</v>
+        <v>27.4358461</v>
       </c>
       <c r="M38" t="n">
-        <v>38.06963589</v>
+        <v>82.26197866</v>
       </c>
     </row>
     <row r="39">
@@ -2022,37 +2024,37 @@
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
-        <v>38.42099165</v>
+        <v>11.11791429</v>
       </c>
       <c r="D39" t="n">
-        <v>11.11791429</v>
+        <v>32.60895456999999</v>
       </c>
       <c r="E39" t="n">
-        <v>32.60895456999999</v>
+        <v>56.67209458</v>
       </c>
       <c r="F39" t="n">
-        <v>56.67209458</v>
+        <v>17.94407397</v>
       </c>
       <c r="G39" t="n">
-        <v>17.94407397</v>
+        <v>33.68792604</v>
       </c>
       <c r="H39" t="n">
-        <v>33.68792604</v>
+        <v>4.108083939999999</v>
       </c>
       <c r="I39" t="n">
-        <v>4.108083939999999</v>
+        <v>73.39446294</v>
       </c>
       <c r="J39" t="n">
-        <v>73.39446294</v>
+        <v>168.35310772</v>
       </c>
       <c r="K39" t="n">
-        <v>168.35310772</v>
+        <v>54.65563677999999</v>
       </c>
       <c r="L39" t="n">
-        <v>54.65563677999999</v>
+        <v>-40.04566426</v>
       </c>
       <c r="M39" t="n">
-        <v>-40.04566426</v>
+        <v>-65.28418285000001</v>
       </c>
     </row>
     <row r="40">
@@ -2063,37 +2065,37 @@
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>18.70547509</v>
+        <v>6.664288</v>
       </c>
       <c r="D40" t="n">
-        <v>6.664288</v>
+        <v>7.2135412</v>
       </c>
       <c r="E40" t="n">
-        <v>7.2135412</v>
+        <v>0.08460432999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>0.08460432999999999</v>
+        <v>-3.21255832</v>
       </c>
       <c r="G40" t="n">
-        <v>-3.21255832</v>
+        <v>-6.40072734</v>
       </c>
       <c r="H40" t="n">
-        <v>-6.40072734</v>
+        <v>-3.77333719</v>
       </c>
       <c r="I40" t="n">
-        <v>-3.77333719</v>
+        <v>1.57257904</v>
       </c>
       <c r="J40" t="n">
-        <v>1.57257904</v>
+        <v>-2.42404502</v>
       </c>
       <c r="K40" t="n">
-        <v>-2.42404502</v>
+        <v>-1.22188635</v>
       </c>
       <c r="L40" t="n">
-        <v>-1.22188635</v>
+        <v>2.19978092</v>
       </c>
       <c r="M40" t="n">
-        <v>2.19978092</v>
+        <v>3.24473775</v>
       </c>
     </row>
     <row r="41">
@@ -2104,2458 +2106,2425 @@
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
-        <v>-63.09958463</v>
+        <v>-76.87109083</v>
       </c>
       <c r="D41" t="n">
-        <v>-76.87109083</v>
+        <v>85.15477465000001</v>
       </c>
       <c r="E41" t="n">
-        <v>85.15477465000001</v>
+        <v>307.60971191</v>
       </c>
       <c r="F41" t="n">
-        <v>307.60971191</v>
+        <v>433.81361385</v>
       </c>
       <c r="G41" t="n">
-        <v>433.81361385</v>
+        <v>668.62466564</v>
       </c>
       <c r="H41" t="n">
-        <v>668.62466564</v>
+        <v>244.91801602</v>
       </c>
       <c r="I41" t="n">
-        <v>244.91801602</v>
+        <v>320.90370974</v>
       </c>
       <c r="J41" t="n">
-        <v>320.90370974</v>
+        <v>479.18507195</v>
       </c>
       <c r="K41" t="n">
-        <v>479.18507195</v>
+        <v>759.412483</v>
       </c>
       <c r="L41" t="n">
-        <v>759.412483</v>
+        <v>264.18557726</v>
       </c>
       <c r="M41" t="n">
-        <v>264.18557726</v>
+        <v>-87.18150326999999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右下</t>
+          <t>玻璃陶瓷平</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>2.76879612</v>
+        <v>-0.03895554999999994</v>
       </c>
       <c r="D42" t="n">
-        <v>1.39195655</v>
+        <v>5.28251554</v>
       </c>
       <c r="E42" t="n">
-        <v>3.33996648</v>
+        <v>13.5194183</v>
       </c>
       <c r="F42" t="n">
-        <v>4.04519709</v>
+        <v>7.9181412</v>
       </c>
       <c r="G42" t="n">
-        <v>4.39753474</v>
+        <v>12.13364822</v>
       </c>
       <c r="H42" t="n">
-        <v>5.01754811</v>
+        <v>8.904139349999999</v>
       </c>
       <c r="I42" t="n">
-        <v>5.69713828</v>
+        <v>16.35974226</v>
       </c>
       <c r="J42" t="n">
-        <v>14.7458941</v>
+        <v>7.98138634</v>
       </c>
       <c r="K42" t="n">
-        <v>7.43637919</v>
+        <v>11.47238579</v>
       </c>
       <c r="L42" t="n">
-        <v>9.030643980000001</v>
+        <v>7.112948609999999</v>
       </c>
       <c r="M42" t="n">
-        <v>7.387953179999999</v>
+        <v>19.89156343000001</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷平</t>
+          <t>生技醫療業右上</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
-        <v>-0.38199066</v>
+        <v>-6.59199424</v>
       </c>
       <c r="D43" t="n">
-        <v>-1.4309121</v>
+        <v>-0.7743389900000001</v>
       </c>
       <c r="E43" t="n">
-        <v>1.94254906</v>
+        <v>-2.06491569</v>
       </c>
       <c r="F43" t="n">
-        <v>9.474221210000001</v>
+        <v>-3.50783653</v>
       </c>
       <c r="G43" t="n">
-        <v>3.52060646</v>
+        <v>-4.53812706</v>
       </c>
       <c r="H43" t="n">
-        <v>7.11610011</v>
+        <v>-14.41317415</v>
       </c>
       <c r="I43" t="n">
-        <v>3.20700107</v>
+        <v>-1.510929369999999</v>
       </c>
       <c r="J43" t="n">
-        <v>1.61384816</v>
+        <v>12.8331323</v>
       </c>
       <c r="K43" t="n">
-        <v>0.5450071499999999</v>
+        <v>11.29758388</v>
       </c>
       <c r="L43" t="n">
-        <v>2.44174181</v>
+        <v>16.35342315</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.2750045700000001</v>
+        <v>15.72564051</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右上</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
+          <t>生技醫療業右下</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0</v>
+      </c>
       <c r="C44" t="n">
-        <v>79.85056292</v>
+        <v>-589.01427738</v>
       </c>
       <c r="D44" t="n">
-        <v>1.62948498</v>
+        <v>-98.77886527999999</v>
       </c>
       <c r="E44" t="n">
-        <v>28.40165868</v>
+        <v>145.3450004</v>
       </c>
       <c r="F44" t="n">
-        <v>65.65651996</v>
+        <v>277.55423926</v>
       </c>
       <c r="G44" t="n">
-        <v>5.88662527</v>
+        <v>-19.27807085</v>
       </c>
       <c r="H44" t="n">
-        <v>-37.47173023</v>
+        <v>-223.77106371</v>
       </c>
       <c r="I44" t="n">
-        <v>-78.36247659999999</v>
+        <v>-341.37744412</v>
       </c>
       <c r="J44" t="n">
-        <v>-11.41209755</v>
+        <v>-315.56075778</v>
       </c>
       <c r="K44" t="n">
-        <v>-12.36702131</v>
+        <v>-305.12043534</v>
       </c>
       <c r="L44" t="n">
-        <v>4.168181860000002</v>
+        <v>-63.14953864</v>
       </c>
       <c r="M44" t="n">
-        <v>-19.49896853</v>
+        <v>24.78475663000001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右下</t>
+          <t>生技醫療業平</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
-        <v>-30.00020119</v>
+        <v>-90.36117743999999</v>
       </c>
       <c r="D45" t="n">
-        <v>-597.35391013</v>
+        <v>87.60529484</v>
       </c>
       <c r="E45" t="n">
-        <v>-104.84622099</v>
+        <v>17.93952776000001</v>
       </c>
       <c r="F45" t="n">
-        <v>140.48645098</v>
+        <v>-135.60866987</v>
       </c>
       <c r="G45" t="n">
-        <v>271.73166425</v>
+        <v>-113.10474484</v>
       </c>
       <c r="H45" t="n">
-        <v>-26.51753093</v>
+        <v>-261.00454043</v>
       </c>
       <c r="I45" t="n">
-        <v>-232.1853368</v>
+        <v>-266.93876518</v>
       </c>
       <c r="J45" t="n">
-        <v>-348.8411457399999</v>
+        <v>-226.46165</v>
       </c>
       <c r="K45" t="n">
-        <v>-324.03077307</v>
+        <v>33.38496002000001</v>
       </c>
       <c r="L45" t="n">
-        <v>-311.6297213</v>
+        <v>-36.41886179</v>
       </c>
       <c r="M45" t="n">
-        <v>-65.95265696999999</v>
+        <v>78.03912475999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業平</t>
+          <t>紡織纖維右上</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>48.85730937</v>
+        <v>-4.72339887</v>
       </c>
       <c r="D46" t="n">
-        <v>-89.51192533999999</v>
+        <v>-1.49148739</v>
       </c>
       <c r="E46" t="n">
-        <v>65.85137101000001</v>
+        <v>2.33220014</v>
       </c>
       <c r="F46" t="n">
-        <v>-41.56200412</v>
+        <v>-2.68896906</v>
       </c>
       <c r="G46" t="n">
-        <v>-135.892264</v>
+        <v>-6.34562959</v>
       </c>
       <c r="H46" t="n">
-        <v>-71.44401619</v>
+        <v>-8.065714099999999</v>
       </c>
       <c r="I46" t="n">
-        <v>-188.8055999</v>
+        <v>-5.8884915</v>
       </c>
       <c r="J46" t="n">
-        <v>-249.41551529</v>
+        <v>-5.95645232</v>
       </c>
       <c r="K46" t="n">
-        <v>-193.81034374</v>
+        <v>-5.16068395</v>
       </c>
       <c r="L46" t="n">
-        <v>46.98716446</v>
+        <v>-5.24392124</v>
       </c>
       <c r="M46" t="n">
-        <v>3.458085520000008</v>
+        <v>-1.42682006</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右上</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
+          <t>紡織纖維右下</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0</v>
+      </c>
       <c r="C47" t="n">
-        <v>-3.11363331</v>
+        <v>-106.93869348</v>
       </c>
       <c r="D47" t="n">
-        <v>-4.72339887</v>
+        <v>50.50353103</v>
       </c>
       <c r="E47" t="n">
-        <v>-1.49148739</v>
+        <v>116.03655748</v>
       </c>
       <c r="F47" t="n">
-        <v>2.33220014</v>
+        <v>57.72593153</v>
       </c>
       <c r="G47" t="n">
-        <v>-2.68896906</v>
+        <v>95.37074805999998</v>
       </c>
       <c r="H47" t="n">
-        <v>-6.34562959</v>
+        <v>11.02279836</v>
       </c>
       <c r="I47" t="n">
-        <v>-8.065714099999999</v>
+        <v>34.5949691</v>
       </c>
       <c r="J47" t="n">
-        <v>-5.8884915</v>
+        <v>4.375589389999996</v>
       </c>
       <c r="K47" t="n">
-        <v>-5.95645232</v>
+        <v>21.94380789</v>
       </c>
       <c r="L47" t="n">
-        <v>-5.16068395</v>
+        <v>26.94948555</v>
       </c>
       <c r="M47" t="n">
-        <v>-5.24392124</v>
+        <v>2.943271589999999</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右下</t>
+          <t>紡織纖維平</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
-        <v>87.60524620999999</v>
+        <v>-0.03830798</v>
       </c>
       <c r="D48" t="n">
-        <v>-110.25147541</v>
+        <v>0.05300252</v>
       </c>
       <c r="E48" t="n">
-        <v>51.69443244</v>
+        <v>0.13976307</v>
       </c>
       <c r="F48" t="n">
-        <v>112.31552985</v>
+        <v>0.48577608</v>
       </c>
       <c r="G48" t="n">
-        <v>53.45619471</v>
+        <v>0.27865859</v>
       </c>
       <c r="H48" t="n">
-        <v>95.04986186999999</v>
+        <v>0.05937113000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>9.407378970000002</v>
+        <v>0.09258559</v>
       </c>
       <c r="J48" t="n">
-        <v>39.68573421</v>
+        <v>-0.04205779</v>
       </c>
       <c r="K48" t="n">
-        <v>4.959421839999997</v>
+        <v>-0.10030131</v>
       </c>
       <c r="L48" t="n">
-        <v>20.79778082</v>
+        <v>0.2635332</v>
       </c>
       <c r="M48" t="n">
-        <v>26.43966846</v>
+        <v>0.7852534600000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維平</t>
+          <t>綠能環保右上</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>0.85302461</v>
+        <v>-39.79114603</v>
       </c>
       <c r="D49" t="n">
-        <v>0.47333933</v>
+        <v>-25.86812985</v>
       </c>
       <c r="E49" t="n">
-        <v>0.60223238</v>
+        <v>-15.37702207</v>
       </c>
       <c r="F49" t="n">
-        <v>0.39113424</v>
+        <v>-21.86573385</v>
       </c>
       <c r="G49" t="n">
-        <v>0.55102869</v>
+        <v>-5.271030309999998</v>
       </c>
       <c r="H49" t="n">
-        <v>0.28993202</v>
+        <v>10.19355404</v>
       </c>
       <c r="I49" t="n">
-        <v>0.02778382</v>
+        <v>-56.44455119</v>
       </c>
       <c r="J49" t="n">
-        <v>0.06734879000000001</v>
+        <v>-46.45714444000001</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.10231698</v>
+        <v>-43.83128722999999</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.002836350000000003</v>
+        <v>-124.85406477</v>
       </c>
       <c r="M49" t="n">
-        <v>1.65312477</v>
+        <v>-35.45945545</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右上</t>
+          <t>綠能環保右下</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
-        <v>0.2943598800000006</v>
+        <v>-26.75564822</v>
       </c>
       <c r="D50" t="n">
-        <v>-39.79114603</v>
+        <v>-29.6747849</v>
       </c>
       <c r="E50" t="n">
-        <v>-25.86812985</v>
+        <v>-9.074995439999997</v>
       </c>
       <c r="F50" t="n">
-        <v>-15.37702207</v>
+        <v>-6.02440684</v>
       </c>
       <c r="G50" t="n">
-        <v>-21.86573385</v>
+        <v>-10.76360972</v>
       </c>
       <c r="H50" t="n">
-        <v>-5.271030309999998</v>
+        <v>-6.295704290000001</v>
       </c>
       <c r="I50" t="n">
-        <v>10.19355404</v>
+        <v>4.70272614</v>
       </c>
       <c r="J50" t="n">
-        <v>-56.44455119</v>
+        <v>-5.524311600000001</v>
       </c>
       <c r="K50" t="n">
-        <v>-46.45714444000001</v>
+        <v>2.53485937</v>
       </c>
       <c r="L50" t="n">
-        <v>-43.83128722999999</v>
+        <v>-2.54366476</v>
       </c>
       <c r="M50" t="n">
-        <v>-124.85406477</v>
+        <v>4.03323023</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右下</t>
+          <t>綠能環保平</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>-33.79822566</v>
+        <v>-90.38974037</v>
       </c>
       <c r="D51" t="n">
-        <v>-70.03717603</v>
+        <v>-46.76736808</v>
       </c>
       <c r="E51" t="n">
-        <v>-71.05295369</v>
+        <v>-18.80448768</v>
       </c>
       <c r="F51" t="n">
-        <v>-51.54037922</v>
+        <v>-3.937506679999998</v>
       </c>
       <c r="G51" t="n">
-        <v>-48.17214372</v>
+        <v>-28.13410102</v>
       </c>
       <c r="H51" t="n">
-        <v>-51.77891822</v>
+        <v>7.48600141</v>
       </c>
       <c r="I51" t="n">
-        <v>1.437679659999999</v>
+        <v>-7.01302978</v>
       </c>
       <c r="J51" t="n">
-        <v>-1.732621739999999</v>
+        <v>-24.94529791</v>
       </c>
       <c r="K51" t="n">
-        <v>-17.61133436</v>
+        <v>30.8624361</v>
       </c>
       <c r="L51" t="n">
-        <v>13.32211765</v>
+        <v>11.07913789</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.8307196999999994</v>
+        <v>52.57312343</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>綠能環保平</t>
+          <t>航運業右上</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>-52.5896484</v>
+        <v>-202.43466048</v>
       </c>
       <c r="D52" t="n">
-        <v>-47.10821256000001</v>
+        <v>42.45403700999999</v>
       </c>
       <c r="E52" t="n">
-        <v>-5.38919929</v>
+        <v>353.5626931</v>
       </c>
       <c r="F52" t="n">
-        <v>23.6608961</v>
+        <v>373.92728289</v>
       </c>
       <c r="G52" t="n">
-        <v>38.21023020000001</v>
+        <v>97.26785201</v>
       </c>
       <c r="H52" t="n">
-        <v>12.88120748</v>
+        <v>-4.230439369999997</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.2473825400000005</v>
+        <v>105.44977854</v>
       </c>
       <c r="J52" t="n">
-        <v>-0.5776819000000004</v>
+        <v>-103.48180697</v>
       </c>
       <c r="K52" t="n">
-        <v>-12.85827515</v>
+        <v>214.35774299</v>
       </c>
       <c r="L52" t="n">
-        <v>20.07517782</v>
+        <v>147.19409253</v>
       </c>
       <c r="M52" t="n">
-        <v>9.366192829999999</v>
+        <v>463.05754523</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>航運業右上</t>
+          <t>航運業右下</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>51.29219449999999</v>
+        <v>-186.39561258</v>
       </c>
       <c r="D53" t="n">
-        <v>-202.43466048</v>
+        <v>-23.63700619</v>
       </c>
       <c r="E53" t="n">
-        <v>42.45403700999999</v>
+        <v>93.53864661</v>
       </c>
       <c r="F53" t="n">
-        <v>353.5626931</v>
+        <v>211.94002794</v>
       </c>
       <c r="G53" t="n">
-        <v>373.92728289</v>
+        <v>90.15224259</v>
       </c>
       <c r="H53" t="n">
-        <v>97.26785201</v>
+        <v>45.78636706</v>
       </c>
       <c r="I53" t="n">
-        <v>-4.230439369999997</v>
+        <v>143.7428402</v>
       </c>
       <c r="J53" t="n">
-        <v>105.44977854</v>
+        <v>11.27969625</v>
       </c>
       <c r="K53" t="n">
-        <v>-103.48180697</v>
+        <v>-16.07925227</v>
       </c>
       <c r="L53" t="n">
-        <v>214.35774299</v>
+        <v>65.65411177</v>
       </c>
       <c r="M53" t="n">
-        <v>147.19409253</v>
+        <v>28.22066404999999</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>航運業右下</t>
+          <t>航運業平</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>-131.82460177</v>
+        <v>-59.44268134999999</v>
       </c>
       <c r="D54" t="n">
-        <v>-186.77167783</v>
+        <v>207.81858439</v>
       </c>
       <c r="E54" t="n">
-        <v>-23.62684924</v>
+        <v>509.47178596</v>
       </c>
       <c r="F54" t="n">
-        <v>94.02638623</v>
+        <v>603.8644441499999</v>
       </c>
       <c r="G54" t="n">
-        <v>212.92140005</v>
+        <v>269.13553351</v>
       </c>
       <c r="H54" t="n">
-        <v>90.77975588000001</v>
+        <v>23.76862924</v>
       </c>
       <c r="I54" t="n">
-        <v>45.93233127</v>
+        <v>-5.508479319999998</v>
       </c>
       <c r="J54" t="n">
-        <v>144.17853408</v>
+        <v>-156.82482688</v>
       </c>
       <c r="K54" t="n">
-        <v>11.27132376</v>
+        <v>53.67796062</v>
       </c>
       <c r="L54" t="n">
-        <v>-15.60971781</v>
+        <v>59.98571205</v>
       </c>
       <c r="M54" t="n">
-        <v>65.76456664</v>
+        <v>161.97887557</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>航運業平</t>
+          <t>觀光事業右上</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>126.51460904</v>
+        <v>-49.27642904</v>
       </c>
       <c r="D55" t="n">
-        <v>-59.0666161</v>
+        <v>-43.15241365</v>
       </c>
       <c r="E55" t="n">
-        <v>207.80842744</v>
+        <v>-42.73856727</v>
       </c>
       <c r="F55" t="n">
-        <v>508.98404634</v>
+        <v>-30.59709092</v>
       </c>
       <c r="G55" t="n">
-        <v>602.88307204</v>
+        <v>1.71896167</v>
       </c>
       <c r="H55" t="n">
-        <v>268.50802022</v>
+        <v>-3.66064519</v>
       </c>
       <c r="I55" t="n">
-        <v>23.62266503</v>
+        <v>6.780631179999999</v>
       </c>
       <c r="J55" t="n">
-        <v>-5.944173200000003</v>
+        <v>-4.03954524</v>
       </c>
       <c r="K55" t="n">
-        <v>-156.81645439</v>
+        <v>17.6737899</v>
       </c>
       <c r="L55" t="n">
-        <v>53.20842615999999</v>
+        <v>27.54426674</v>
       </c>
       <c r="M55" t="n">
-        <v>59.87525717999999</v>
+        <v>42.05846305</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右上</t>
+          <t>觀光事業右下</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>-33.83319698</v>
+        <v>-2.59580502</v>
       </c>
       <c r="D56" t="n">
-        <v>-16.22676241</v>
+        <v>-0.4970161599999999</v>
       </c>
       <c r="E56" t="n">
-        <v>-8.50384698</v>
+        <v>-3.79917129</v>
       </c>
       <c r="F56" t="n">
-        <v>-10.13554798</v>
+        <v>-3.020980170000001</v>
       </c>
       <c r="G56" t="n">
-        <v>-5.02773301</v>
+        <v>-3.08701631</v>
       </c>
       <c r="H56" t="n">
-        <v>4.61939667</v>
+        <v>-3.15672715</v>
       </c>
       <c r="I56" t="n">
-        <v>0.32767565</v>
+        <v>-1.54350305</v>
       </c>
       <c r="J56" t="n">
-        <v>-1.13437554</v>
+        <v>-4.72110351</v>
       </c>
       <c r="K56" t="n">
-        <v>-9.10632041</v>
+        <v>-3.3628632</v>
       </c>
       <c r="L56" t="n">
-        <v>2.08130507</v>
+        <v>3.84713373</v>
       </c>
       <c r="M56" t="n">
-        <v>-7.27956868</v>
+        <v>7.88635447</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右下</t>
+          <t>觀光事業平</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
-        <v>-1.0301193</v>
+        <v>-10.34541521</v>
       </c>
       <c r="D57" t="n">
-        <v>-2.59580502</v>
+        <v>-2.01370306</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.4970161599999999</v>
+        <v>-8.25142043</v>
       </c>
       <c r="F57" t="n">
-        <v>-3.79917129</v>
+        <v>-7.666451640000001</v>
       </c>
       <c r="G57" t="n">
-        <v>-3.020980170000001</v>
+        <v>1.02657452</v>
       </c>
       <c r="H57" t="n">
-        <v>-3.08701631</v>
+        <v>-4.479805059999999</v>
       </c>
       <c r="I57" t="n">
-        <v>-3.15672715</v>
+        <v>-6.18255584</v>
       </c>
       <c r="J57" t="n">
-        <v>-1.54350305</v>
+        <v>-8.348571570000001</v>
       </c>
       <c r="K57" t="n">
-        <v>-4.72110351</v>
+        <v>0.15872278</v>
       </c>
       <c r="L57" t="n">
-        <v>-3.3628632</v>
+        <v>20.29543049</v>
       </c>
       <c r="M57" t="n">
-        <v>3.84713373</v>
+        <v>11.76125342</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>觀光事業平</t>
+          <t>貿易百貨右下</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>-34.24893215</v>
+        <v>-41.64196783</v>
       </c>
       <c r="D58" t="n">
-        <v>-43.39508184</v>
+        <v>7.818857879999999</v>
       </c>
       <c r="E58" t="n">
-        <v>-36.66226973000001</v>
+        <v>-8.73737841</v>
       </c>
       <c r="F58" t="n">
-        <v>-40.85443972</v>
+        <v>-35.23401704</v>
       </c>
       <c r="G58" t="n">
-        <v>-33.23580955</v>
+        <v>-57.93461414</v>
       </c>
       <c r="H58" t="n">
-        <v>-1.87386048</v>
+        <v>-68.29465833</v>
       </c>
       <c r="I58" t="n">
-        <v>-8.4681259</v>
+        <v>-8.434151510000001</v>
       </c>
       <c r="J58" t="n">
-        <v>1.73245088</v>
+        <v>-47.65870399000001</v>
       </c>
       <c r="K58" t="n">
-        <v>-3.2817964</v>
+        <v>7.33809499</v>
       </c>
       <c r="L58" t="n">
-        <v>15.75120761</v>
+        <v>15.97438006</v>
       </c>
       <c r="M58" t="n">
-        <v>55.11926591</v>
+        <v>20.44942311</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨右下</t>
+          <t>貿易百貨平</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
-        <v>-7.666390959999998</v>
+        <v>1.42688672</v>
       </c>
       <c r="D59" t="n">
-        <v>-41.64196783</v>
+        <v>1.65472246</v>
       </c>
       <c r="E59" t="n">
-        <v>7.818857879999999</v>
+        <v>0.7650220599999999</v>
       </c>
       <c r="F59" t="n">
-        <v>-8.73737841</v>
+        <v>0.25274791</v>
       </c>
       <c r="G59" t="n">
-        <v>-35.23401704</v>
+        <v>1.15735872</v>
       </c>
       <c r="H59" t="n">
-        <v>-57.93461414</v>
+        <v>0.04444354</v>
       </c>
       <c r="I59" t="n">
-        <v>-68.29465833</v>
+        <v>0.76131222</v>
       </c>
       <c r="J59" t="n">
-        <v>-8.434151510000001</v>
+        <v>-0.23691493</v>
       </c>
       <c r="K59" t="n">
-        <v>-47.65870399000001</v>
+        <v>-0.71950387</v>
       </c>
       <c r="L59" t="n">
-        <v>7.714702559999999</v>
+        <v>0.5766634</v>
       </c>
       <c r="M59" t="n">
-        <v>41.99995511</v>
+        <v>1.15600886</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨平</t>
+          <t>資訊服務業右上</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
-        <v>0.82803391</v>
+        <v>-72.81776050000001</v>
       </c>
       <c r="D60" t="n">
-        <v>1.42688672</v>
+        <v>-43.80409290999999</v>
       </c>
       <c r="E60" t="n">
-        <v>1.65472246</v>
+        <v>-59.54131665</v>
       </c>
       <c r="F60" t="n">
-        <v>0.7650220599999999</v>
+        <v>-59.82970831</v>
       </c>
       <c r="G60" t="n">
-        <v>0.25274791</v>
+        <v>-20.09390547</v>
       </c>
       <c r="H60" t="n">
-        <v>1.15735872</v>
+        <v>-30.92586359</v>
       </c>
       <c r="I60" t="n">
-        <v>0.04444354</v>
+        <v>-15.12555268</v>
       </c>
       <c r="J60" t="n">
-        <v>0.76131222</v>
+        <v>19.01608918</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.23691493</v>
+        <v>32.19645122</v>
       </c>
       <c r="L60" t="n">
-        <v>-0.71950387</v>
+        <v>66.00356958</v>
       </c>
       <c r="M60" t="n">
-        <v>0.5766634</v>
+        <v>95.20248759</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右上</t>
+          <t>資訊服務業右下</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
-        <v>-13.81200569</v>
+        <v>-0.00691126</v>
       </c>
       <c r="D61" t="n">
-        <v>-72.81674255</v>
+        <v>-0.0001974500000000001</v>
       </c>
       <c r="E61" t="n">
-        <v>-43.8031604</v>
+        <v>-0.00328995</v>
       </c>
       <c r="F61" t="n">
-        <v>-59.54142404</v>
+        <v>-0.00367163</v>
       </c>
       <c r="G61" t="n">
-        <v>-59.83005539</v>
+        <v>-0.00149519</v>
       </c>
       <c r="H61" t="n">
-        <v>-20.09492938</v>
+        <v>-0.0044427</v>
       </c>
       <c r="I61" t="n">
-        <v>-30.92644828</v>
+        <v>-0.00424425</v>
       </c>
       <c r="J61" t="n">
-        <v>-15.12639888</v>
+        <v>-0.00749634</v>
       </c>
       <c r="K61" t="n">
-        <v>19.01507966</v>
+        <v>-0.0031783</v>
       </c>
       <c r="L61" t="n">
-        <v>32.19573076</v>
+        <v>-0.00248349</v>
       </c>
       <c r="M61" t="n">
-        <v>66.0028885</v>
+        <v>0.00740013</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右下</t>
+          <t>資訊服務業平</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>0.00055136</v>
+        <v>-50.08831059</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.00691126</v>
+        <v>3.88192015</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.0001974500000000001</v>
+        <v>-6.974047229999999</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.00328995</v>
+        <v>-18.18771042</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.00367163</v>
+        <v>54.93208556</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.00149519</v>
+        <v>-0.1346072799999995</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.0044427</v>
+        <v>15.73484465</v>
       </c>
       <c r="J62" t="n">
-        <v>-0.00424425</v>
+        <v>-2.45423797</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.00749634</v>
+        <v>28.65151699</v>
       </c>
       <c r="L62" t="n">
-        <v>-0.0031783</v>
+        <v>47.66554514</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.00248349</v>
+        <v>94.86275925</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業平</t>
+          <t>農業科技業右上</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>-4.54630828</v>
+        <v>-0.0001746</v>
       </c>
       <c r="D63" t="n">
-        <v>-50.08899126</v>
+        <v>0.00012031</v>
       </c>
       <c r="E63" t="n">
-        <v>3.88185814</v>
+        <v>-2.134999999999999e-05</v>
       </c>
       <c r="F63" t="n">
-        <v>-6.97329467</v>
+        <v>0.00012761</v>
       </c>
       <c r="G63" t="n">
-        <v>-18.18662421</v>
+        <v>0.00014581</v>
       </c>
       <c r="H63" t="n">
-        <v>54.93359035</v>
+        <v>0.00033086</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.1310624899999998</v>
+        <v>0.0004248200000000001</v>
       </c>
       <c r="J63" t="n">
-        <v>15.73985881</v>
+        <v>0.00090755</v>
       </c>
       <c r="K63" t="n">
-        <v>-2.45111669</v>
+        <v>0.00103174</v>
       </c>
       <c r="L63" t="n">
-        <v>28.65304667</v>
+        <v>0.0009914099999999999</v>
       </c>
       <c r="M63" t="n">
-        <v>47.66631501</v>
+        <v>6.247e-05</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右上</t>
+          <t>農業科技業右下</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
-        <v>-0.00047737</v>
+        <v>-0.00037977</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.0001746</v>
+        <v>-0.00013752</v>
       </c>
       <c r="E64" t="n">
-        <v>0.00012031</v>
+        <v>-0.00019394</v>
       </c>
       <c r="F64" t="n">
-        <v>-2.134999999999999e-05</v>
+        <v>-0.00018756</v>
       </c>
       <c r="G64" t="n">
-        <v>0.00012761</v>
+        <v>-0.00024988</v>
       </c>
       <c r="H64" t="n">
-        <v>0.00014581</v>
+        <v>-0.00027272</v>
       </c>
       <c r="I64" t="n">
-        <v>0.00033086</v>
+        <v>-0.0002611</v>
       </c>
       <c r="J64" t="n">
-        <v>0.0004248200000000001</v>
+        <v>-0.00027651</v>
       </c>
       <c r="K64" t="n">
-        <v>0.00090755</v>
+        <v>-0.0002609000000000001</v>
       </c>
       <c r="L64" t="n">
-        <v>0.00103174</v>
+        <v>5.814e-05</v>
       </c>
       <c r="M64" t="n">
-        <v>0.0009914099999999999</v>
+        <v>0.00018835</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右下</t>
+          <t>通信網路業右上</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
-        <v>-5.835999999999999e-05</v>
+        <v>806.41169386</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.00037977</v>
+        <v>455.92403099</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.00013752</v>
+        <v>660.73977532</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.00019394</v>
+        <v>618.75750132</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.00018756</v>
+        <v>1100.74911451</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.00024988</v>
+        <v>916.6325839000001</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.00027272</v>
+        <v>224.78400483</v>
       </c>
       <c r="J65" t="n">
-        <v>-0.0002611</v>
+        <v>441.09990429</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.00027651</v>
+        <v>4.457560460000001</v>
       </c>
       <c r="L65" t="n">
-        <v>-0.0002609000000000001</v>
+        <v>173.71186101</v>
       </c>
       <c r="M65" t="n">
-        <v>5.814e-05</v>
+        <v>727.45402683</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右上</t>
+          <t>通信網路業右下</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>384.86742887</v>
+        <v>-35.84064752</v>
       </c>
       <c r="D66" t="n">
-        <v>806.4506068800001</v>
+        <v>1.80769688</v>
       </c>
       <c r="E66" t="n">
-        <v>455.55609816</v>
+        <v>19.80204006</v>
       </c>
       <c r="F66" t="n">
-        <v>660.9538407099999</v>
+        <v>16.11997608</v>
       </c>
       <c r="G66" t="n">
-        <v>619.66636562</v>
+        <v>15.01740377</v>
       </c>
       <c r="H66" t="n">
-        <v>1094.86919271</v>
+        <v>19.88991495</v>
       </c>
       <c r="I66" t="n">
-        <v>889.82394895</v>
+        <v>-17.26272065</v>
       </c>
       <c r="J66" t="n">
-        <v>146.74014652</v>
+        <v>-53.03456827</v>
       </c>
       <c r="K66" t="n">
-        <v>412.43538744</v>
+        <v>-4.480187010000003</v>
       </c>
       <c r="L66" t="n">
-        <v>2.34032129999999</v>
+        <v>31.26898156</v>
       </c>
       <c r="M66" t="n">
-        <v>183.76378024</v>
+        <v>-1.41045304</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右下</t>
+          <t>通信網路業平</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>44.24718054</v>
+        <v>-70.21889269999998</v>
       </c>
       <c r="D67" t="n">
-        <v>-36.17068275</v>
+        <v>209.95166032</v>
       </c>
       <c r="E67" t="n">
-        <v>1.7136654</v>
+        <v>189.33371313</v>
       </c>
       <c r="F67" t="n">
-        <v>19.83441227</v>
+        <v>497.2165509700001</v>
       </c>
       <c r="G67" t="n">
-        <v>16.35549202</v>
+        <v>817.3993215400001</v>
       </c>
       <c r="H67" t="n">
-        <v>14.86122769</v>
+        <v>282.53601744</v>
       </c>
       <c r="I67" t="n">
-        <v>19.66030109</v>
+        <v>290.39567986</v>
       </c>
       <c r="J67" t="n">
-        <v>-17.09602854</v>
+        <v>140.56837645</v>
       </c>
       <c r="K67" t="n">
-        <v>-53.13334783000001</v>
+        <v>355.81218004</v>
       </c>
       <c r="L67" t="n">
-        <v>-4.00198585</v>
+        <v>138.70086394</v>
       </c>
       <c r="M67" t="n">
-        <v>33.33020905</v>
+        <v>147.23973732</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>通信網路業平</t>
+          <t>造紙工業右下</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>262.14089032</v>
+        <v>1.48615941</v>
       </c>
       <c r="D68" t="n">
-        <v>-69.92777048999999</v>
+        <v>6.954071790000001</v>
       </c>
       <c r="E68" t="n">
-        <v>210.41362463</v>
+        <v>8.895559609999999</v>
       </c>
       <c r="F68" t="n">
-        <v>189.08727553</v>
+        <v>25.77768484</v>
       </c>
       <c r="G68" t="n">
-        <v>496.0721707300001</v>
+        <v>7.5358798</v>
       </c>
       <c r="H68" t="n">
-        <v>823.4354194200001</v>
+        <v>-2.18453111</v>
       </c>
       <c r="I68" t="n">
-        <v>309.57426625</v>
+        <v>-4.28064262</v>
       </c>
       <c r="J68" t="n">
-        <v>368.27284606</v>
+        <v>-9.848016550000001</v>
       </c>
       <c r="K68" t="n">
-        <v>169.33167286</v>
+        <v>-11.75977663</v>
       </c>
       <c r="L68" t="n">
-        <v>357.60631176</v>
+        <v>-14.45543988</v>
       </c>
       <c r="M68" t="n">
-        <v>126.61057411</v>
+        <v>-8.60103045</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>造紙工業右下</t>
+          <t>造紙工業平</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>6.005808959999999</v>
+        <v>-3.03497446</v>
       </c>
       <c r="D69" t="n">
-        <v>1.48615941</v>
+        <v>-1.57228821</v>
       </c>
       <c r="E69" t="n">
-        <v>6.954071790000001</v>
+        <v>-0.33839224</v>
       </c>
       <c r="F69" t="n">
-        <v>8.895559609999999</v>
+        <v>-1.43394215</v>
       </c>
       <c r="G69" t="n">
-        <v>25.77768484</v>
+        <v>-1.69268373</v>
       </c>
       <c r="H69" t="n">
-        <v>7.5358798</v>
+        <v>-3.23010772</v>
       </c>
       <c r="I69" t="n">
-        <v>-2.18453111</v>
+        <v>-3.39045584</v>
       </c>
       <c r="J69" t="n">
-        <v>-4.28064262</v>
+        <v>-4.06147909</v>
       </c>
       <c r="K69" t="n">
-        <v>-9.848016550000001</v>
+        <v>-3.60733925</v>
       </c>
       <c r="L69" t="n">
-        <v>-11.75977663</v>
+        <v>-1.16033294</v>
       </c>
       <c r="M69" t="n">
-        <v>-14.45543988</v>
+        <v>-1.55525517</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>造紙工業平</t>
+          <t>運動休閒右上</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>-1.21277104</v>
+        <v>-38.78366583</v>
       </c>
       <c r="D70" t="n">
-        <v>-3.03497446</v>
+        <v>-10.01798231</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.57228821</v>
+        <v>-16.91394174</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.33839224</v>
+        <v>-16.82706139</v>
       </c>
       <c r="G70" t="n">
-        <v>-1.43394215</v>
+        <v>-21.49287157</v>
       </c>
       <c r="H70" t="n">
-        <v>-1.69268373</v>
+        <v>-29.75249595</v>
       </c>
       <c r="I70" t="n">
-        <v>-3.23010772</v>
+        <v>-5.49167339</v>
       </c>
       <c r="J70" t="n">
-        <v>-3.39045584</v>
+        <v>-6.985563310000001</v>
       </c>
       <c r="K70" t="n">
-        <v>-4.06147909</v>
+        <v>6.14054282</v>
       </c>
       <c r="L70" t="n">
-        <v>-3.60733925</v>
+        <v>22.89727625</v>
       </c>
       <c r="M70" t="n">
-        <v>-1.16033294</v>
+        <v>39.58487804</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右上</t>
+          <t>運動休閒右下</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
-        <v>-0.7912245499999994</v>
+        <v>-67.66731897</v>
       </c>
       <c r="D71" t="n">
-        <v>-38.04768629</v>
+        <v>86.08082459000001</v>
       </c>
       <c r="E71" t="n">
-        <v>5.646526350000001</v>
+        <v>65.03796482999999</v>
       </c>
       <c r="F71" t="n">
-        <v>1.152489290000001</v>
+        <v>7.475289409999997</v>
       </c>
       <c r="G71" t="n">
-        <v>-9.541564510000001</v>
+        <v>-64.07427258999999</v>
       </c>
       <c r="H71" t="n">
-        <v>-10.24703036</v>
+        <v>-115.50237892</v>
       </c>
       <c r="I71" t="n">
-        <v>-29.03830542</v>
+        <v>-11.79256974999999</v>
       </c>
       <c r="J71" t="n">
-        <v>-7.31066034</v>
+        <v>-141.47987787</v>
       </c>
       <c r="K71" t="n">
-        <v>-16.28726425</v>
+        <v>-101.90599359</v>
       </c>
       <c r="L71" t="n">
-        <v>6.2073744</v>
+        <v>-27.86393122</v>
       </c>
       <c r="M71" t="n">
-        <v>33.59447604</v>
+        <v>-19.72376035</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右下</t>
+          <t>運動休閒平</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>36.20031953</v>
+        <v>2.85641621</v>
       </c>
       <c r="D72" t="n">
-        <v>-67.66731897</v>
+        <v>18.48568502</v>
       </c>
       <c r="E72" t="n">
-        <v>86.08082459000001</v>
+        <v>16.39634759</v>
       </c>
       <c r="F72" t="n">
-        <v>65.03796482999999</v>
+        <v>4.281030289999999</v>
       </c>
       <c r="G72" t="n">
-        <v>7.475289409999997</v>
+        <v>5.539278160000001</v>
       </c>
       <c r="H72" t="n">
-        <v>-64.07427258999999</v>
+        <v>-2.54610903</v>
       </c>
       <c r="I72" t="n">
-        <v>-115.50237892</v>
+        <v>-1.68230068</v>
       </c>
       <c r="J72" t="n">
-        <v>-11.79256974999999</v>
+        <v>-10.98006195</v>
       </c>
       <c r="K72" t="n">
-        <v>-141.47987787</v>
+        <v>0.2389688799999998</v>
       </c>
       <c r="L72" t="n">
-        <v>-101.90599359</v>
+        <v>11.07624471</v>
       </c>
       <c r="M72" t="n">
-        <v>-27.86393122</v>
+        <v>3.90076889</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>運動休閒平</t>
+          <t>金融保險右上</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
-        <v>15.47129295</v>
+        <v>-1283.68705536</v>
       </c>
       <c r="D73" t="n">
-        <v>2.12043667</v>
+        <v>-482.7115760200001</v>
       </c>
       <c r="E73" t="n">
-        <v>2.82117636</v>
+        <v>-765.1041760999999</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.67008344</v>
+        <v>-1040.79625587</v>
       </c>
       <c r="G73" t="n">
-        <v>-3.00446659</v>
+        <v>-1324.62340848</v>
       </c>
       <c r="H73" t="n">
-        <v>-5.70656305</v>
+        <v>-1494.22065455</v>
       </c>
       <c r="I73" t="n">
-        <v>-3.26029956</v>
+        <v>-477.25509582</v>
       </c>
       <c r="J73" t="n">
-        <v>0.1366862700000001</v>
+        <v>-922.0717805799999</v>
       </c>
       <c r="K73" t="n">
-        <v>-1.67836101</v>
+        <v>63.64246134</v>
       </c>
       <c r="L73" t="n">
-        <v>0.1721373</v>
+        <v>898.8864829000001</v>
       </c>
       <c r="M73" t="n">
-        <v>0.3790449200000002</v>
+        <v>790.9240111800001</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>金融保險右上</t>
+          <t>金融保險右下</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
-        <v>-1537.60609394</v>
+        <v>-367.06678437</v>
       </c>
       <c r="D74" t="n">
-        <v>-1300.60484244</v>
+        <v>-250.69924983</v>
       </c>
       <c r="E74" t="n">
-        <v>-446.7146776000001</v>
+        <v>-872.0283148399999</v>
       </c>
       <c r="F74" t="n">
-        <v>-782.3819385199999</v>
+        <v>-139.73695014</v>
       </c>
       <c r="G74" t="n">
-        <v>-1081.01944222</v>
+        <v>-442.97575951</v>
       </c>
       <c r="H74" t="n">
-        <v>-1391.75995319</v>
+        <v>-633.39512414</v>
       </c>
       <c r="I74" t="n">
-        <v>-1580.93302348</v>
+        <v>-341.20493453</v>
       </c>
       <c r="J74" t="n">
-        <v>-563.61207497</v>
+        <v>-356.22095996</v>
       </c>
       <c r="K74" t="n">
-        <v>-1021.23222964</v>
+        <v>-337.45108135</v>
       </c>
       <c r="L74" t="n">
-        <v>32.26943954999999</v>
+        <v>-134.7466928</v>
       </c>
       <c r="M74" t="n">
-        <v>961.0002153400001</v>
+        <v>37.79193381</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>金融保險右下</t>
+          <t>金融保險平</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
-        <v>-260.44258382</v>
+        <v>-54.58733164</v>
       </c>
       <c r="D75" t="n">
-        <v>-368.46173542</v>
+        <v>89.86719134000001</v>
       </c>
       <c r="E75" t="n">
-        <v>-257.34234104</v>
+        <v>-45.88042659000001</v>
       </c>
       <c r="F75" t="n">
-        <v>-885.79771207</v>
+        <v>-89.31179165</v>
       </c>
       <c r="G75" t="n">
-        <v>-150.17356266</v>
+        <v>-156.48937493</v>
       </c>
       <c r="H75" t="n">
-        <v>-451.01320442</v>
+        <v>-206.25309731</v>
       </c>
       <c r="I75" t="n">
-        <v>-639.4418898500001</v>
+        <v>-98.12138276</v>
       </c>
       <c r="J75" t="n">
-        <v>-343.7357963100001</v>
+        <v>-163.63147646</v>
       </c>
       <c r="K75" t="n">
-        <v>-358.27958259</v>
+        <v>7.309040450000002</v>
       </c>
       <c r="L75" t="n">
-        <v>-339.09543789</v>
+        <v>183.51615035</v>
       </c>
       <c r="M75" t="n">
-        <v>-134.39403601</v>
+        <v>140.16921331</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>金融保險平</t>
+          <t>金融業右上</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>19.06414180000001</v>
+        <v>-0.0010076</v>
       </c>
       <c r="D76" t="n">
-        <v>-36.27459351</v>
+        <v>-0.00018871</v>
       </c>
       <c r="E76" t="n">
-        <v>60.51338413</v>
+        <v>-0.00053725</v>
       </c>
       <c r="F76" t="n">
-        <v>-14.83326694</v>
+        <v>-0.00057684</v>
       </c>
       <c r="G76" t="n">
-        <v>-38.65199278</v>
+        <v>-0.0006594299999999999</v>
       </c>
       <c r="H76" t="n">
-        <v>-81.31538531</v>
+        <v>-0.00071329</v>
       </c>
       <c r="I76" t="n">
-        <v>-113.49396267</v>
+        <v>-0.0003751</v>
       </c>
       <c r="J76" t="n">
-        <v>-9.233541829999998</v>
+        <v>-0.00072667</v>
       </c>
       <c r="K76" t="n">
-        <v>-62.41240477000001</v>
+        <v>-0.00031853</v>
       </c>
       <c r="L76" t="n">
-        <v>40.32641878</v>
+        <v>-0.00042214</v>
       </c>
       <c r="M76" t="n">
-        <v>121.04976112</v>
+        <v>0.00035191</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>金融業右上</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr"/>
+          <t>金融業右下</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>0</v>
+      </c>
       <c r="C77" t="n">
-        <v>-0.00035228</v>
+        <v>-0.00133008</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.0010076</v>
+        <v>0.00026628</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.00018871</v>
+        <v>0.00350767</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.00053725</v>
+        <v>0.00375462</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.00057684</v>
+        <v>0.00100754</v>
       </c>
       <c r="H77" t="n">
-        <v>-0.0006594299999999999</v>
+        <v>-0.00254034</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.00071329</v>
+        <v>-0.0002606299999999999</v>
       </c>
       <c r="J77" t="n">
-        <v>-0.0003751</v>
+        <v>-0.00411787</v>
       </c>
       <c r="K77" t="n">
-        <v>-0.00072667</v>
+        <v>-0.00544981</v>
       </c>
       <c r="L77" t="n">
-        <v>-0.00031853</v>
+        <v>-0.006712269999999999</v>
       </c>
       <c r="M77" t="n">
-        <v>-0.00042214</v>
+        <v>-0.0022721</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>金融業右下</t>
+          <t>金融業平</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
-        <v>0.00127502</v>
+        <v>-0.00080643</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.00110649</v>
+        <v>-0.00053355</v>
       </c>
       <c r="E78" t="n">
-        <v>0.0006396900000000001</v>
+        <v>-0.0004297</v>
       </c>
       <c r="F78" t="n">
-        <v>0.00368509</v>
+        <v>-0.00048908</v>
       </c>
       <c r="G78" t="n">
-        <v>0.004119070000000001</v>
+        <v>-0.00026955</v>
       </c>
       <c r="H78" t="n">
-        <v>0.00104634</v>
+        <v>-0.00035725</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.00267286</v>
+        <v>-0.00052145</v>
       </c>
       <c r="J78" t="n">
-        <v>-9.306000000000001e-05</v>
+        <v>-0.00052038</v>
       </c>
       <c r="K78" t="n">
-        <v>-0.00439828</v>
+        <v>-0.00049876</v>
       </c>
       <c r="L78" t="n">
-        <v>-0.005935770000000001</v>
+        <v>-0.00010349</v>
       </c>
       <c r="M78" t="n">
-        <v>-0.006376339999999999</v>
+        <v>0.00149008</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>金融業平</t>
+          <t>鋼鐵工業右上</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="n">
-        <v>-0.00031949</v>
+        <v>3.51672797</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.00080643</v>
+        <v>3.13082996</v>
       </c>
       <c r="E79" t="n">
-        <v>-0.00053355</v>
+        <v>12.50540977</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.0004297</v>
+        <v>27.84336579</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.00048908</v>
+        <v>3.57885056</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.00026955</v>
+        <v>-6.574561549999999</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.00035725</v>
+        <v>5.12920975</v>
       </c>
       <c r="J79" t="n">
-        <v>-0.00052145</v>
+        <v>0.3989783500000001</v>
       </c>
       <c r="K79" t="n">
-        <v>-0.00052038</v>
+        <v>-0.85045757</v>
       </c>
       <c r="L79" t="n">
-        <v>-0.00049876</v>
+        <v>-2.06183055</v>
       </c>
       <c r="M79" t="n">
-        <v>-0.00010349</v>
+        <v>-1.27944524</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上</t>
+          <t>鋼鐵工業右下</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="n">
-        <v>22.97207093</v>
+        <v>55.6086783</v>
       </c>
       <c r="D80" t="n">
-        <v>3.51672797</v>
+        <v>189.08539014</v>
       </c>
       <c r="E80" t="n">
-        <v>3.13082996</v>
+        <v>59.51744986</v>
       </c>
       <c r="F80" t="n">
-        <v>12.50540977</v>
+        <v>36.79319181</v>
       </c>
       <c r="G80" t="n">
-        <v>27.84336579</v>
+        <v>-46.55468548</v>
       </c>
       <c r="H80" t="n">
-        <v>3.57885056</v>
+        <v>-86.24594107999999</v>
       </c>
       <c r="I80" t="n">
-        <v>-6.574561549999999</v>
+        <v>4.75202269</v>
       </c>
       <c r="J80" t="n">
-        <v>5.12920975</v>
+        <v>-72.65792786999999</v>
       </c>
       <c r="K80" t="n">
-        <v>0.3989783500000001</v>
+        <v>-104.70569544</v>
       </c>
       <c r="L80" t="n">
-        <v>-13.06068005</v>
+        <v>-114.03055386</v>
       </c>
       <c r="M80" t="n">
-        <v>-4.237776240000001</v>
+        <v>-68.98960509</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下</t>
+          <t>鋼鐵工業平</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>44.23416758</v>
+        <v>97.66577554</v>
       </c>
       <c r="D81" t="n">
-        <v>55.60871175</v>
+        <v>253.91701296</v>
       </c>
       <c r="E81" t="n">
-        <v>189.08545711</v>
+        <v>106.88140854</v>
       </c>
       <c r="F81" t="n">
-        <v>59.51750321</v>
+        <v>356.57214531</v>
       </c>
       <c r="G81" t="n">
-        <v>36.79329722999999</v>
+        <v>506.99949388</v>
       </c>
       <c r="H81" t="n">
-        <v>-46.55458285</v>
+        <v>775.8071764800002</v>
       </c>
       <c r="I81" t="n">
-        <v>-86.24587647</v>
+        <v>803.92442198</v>
       </c>
       <c r="J81" t="n">
-        <v>4.752140270000001</v>
+        <v>245.68455977</v>
       </c>
       <c r="K81" t="n">
-        <v>-72.65755283</v>
+        <v>6.711772959999993</v>
       </c>
       <c r="L81" t="n">
-        <v>-104.70529256</v>
+        <v>101.28376939</v>
       </c>
       <c r="M81" t="n">
-        <v>-114.0303431</v>
+        <v>-46.22985675999999</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業平</t>
+          <t>電器電纜右上</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
-        <v>36.69310421000001</v>
+        <v>-16.2538581</v>
       </c>
       <c r="D82" t="n">
-        <v>97.66574208999999</v>
+        <v>-12.95625808</v>
       </c>
       <c r="E82" t="n">
-        <v>253.91694599</v>
+        <v>-9.47706786</v>
       </c>
       <c r="F82" t="n">
-        <v>106.88135519</v>
+        <v>-3.909404330000002</v>
       </c>
       <c r="G82" t="n">
-        <v>356.57203989</v>
+        <v>-14.46518195</v>
       </c>
       <c r="H82" t="n">
-        <v>506.99939125</v>
+        <v>37.21932350000001</v>
       </c>
       <c r="I82" t="n">
-        <v>775.8071118700001</v>
+        <v>68.03134521</v>
       </c>
       <c r="J82" t="n">
-        <v>803.9243044000001</v>
+        <v>-2.350372119999999</v>
       </c>
       <c r="K82" t="n">
-        <v>245.68418473</v>
+        <v>-4.571539939999999</v>
       </c>
       <c r="L82" t="n">
-        <v>6.711370079999998</v>
+        <v>39.14585281</v>
       </c>
       <c r="M82" t="n">
-        <v>101.28355863</v>
+        <v>87.22141015999999</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右上</t>
+          <t>電器電纜右下</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>23.28468532</v>
+        <v>16.23269398</v>
       </c>
       <c r="D83" t="n">
-        <v>-16.2538581</v>
+        <v>46.02478503</v>
       </c>
       <c r="E83" t="n">
-        <v>-12.95625808</v>
+        <v>10.70422737</v>
       </c>
       <c r="F83" t="n">
-        <v>-9.47706786</v>
+        <v>-5.995241029999999</v>
       </c>
       <c r="G83" t="n">
-        <v>-3.909404330000002</v>
+        <v>7.19180515</v>
       </c>
       <c r="H83" t="n">
-        <v>-14.46518195</v>
+        <v>-6.73828916</v>
       </c>
       <c r="I83" t="n">
-        <v>37.21932350000001</v>
+        <v>102.04973315</v>
       </c>
       <c r="J83" t="n">
-        <v>68.03134521</v>
+        <v>-116.03766855</v>
       </c>
       <c r="K83" t="n">
-        <v>-2.350372119999999</v>
+        <v>-143.59839725</v>
       </c>
       <c r="L83" t="n">
-        <v>-4.571539939999999</v>
+        <v>-122.34910587</v>
       </c>
       <c r="M83" t="n">
-        <v>39.14585281</v>
+        <v>-54.08839686000001</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右下</t>
+          <t>電器電纜平</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
-        <v>68.89752422999999</v>
+        <v>-14.05947637</v>
       </c>
       <c r="D84" t="n">
-        <v>15.56912003</v>
+        <v>4.3754549</v>
       </c>
       <c r="E84" t="n">
-        <v>45.51657396</v>
+        <v>-16.46287687</v>
       </c>
       <c r="F84" t="n">
-        <v>10.48380609</v>
+        <v>-27.68079808</v>
       </c>
       <c r="G84" t="n">
-        <v>-6.200965539999999</v>
+        <v>-23.33448353</v>
       </c>
       <c r="H84" t="n">
-        <v>7.24073577</v>
+        <v>-18.01921526</v>
       </c>
       <c r="I84" t="n">
-        <v>-6.584472399999999</v>
+        <v>-1.10802477</v>
       </c>
       <c r="J84" t="n">
-        <v>102.05294481</v>
+        <v>-19.80502254</v>
       </c>
       <c r="K84" t="n">
-        <v>-115.80624809</v>
+        <v>-24.55320739</v>
       </c>
       <c r="L84" t="n">
-        <v>-143.58805289</v>
+        <v>-6.61555764</v>
       </c>
       <c r="M84" t="n">
-        <v>-122.466744</v>
+        <v>11.71935781</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>電器電纜平</t>
+          <t>電子通路業右上</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>19.63179093</v>
+        <v>-0.5536843900000029</v>
       </c>
       <c r="D85" t="n">
-        <v>-13.39590242</v>
+        <v>35.31476152</v>
       </c>
       <c r="E85" t="n">
-        <v>4.88366597</v>
+        <v>2.312927219999999</v>
       </c>
       <c r="F85" t="n">
-        <v>-16.24245559</v>
+        <v>-14.73780212</v>
       </c>
       <c r="G85" t="n">
-        <v>-27.47507357</v>
+        <v>45.55591851</v>
       </c>
       <c r="H85" t="n">
-        <v>-23.38341415</v>
+        <v>20.93663418</v>
       </c>
       <c r="I85" t="n">
-        <v>-18.17303202</v>
+        <v>83.75538558</v>
       </c>
       <c r="J85" t="n">
-        <v>-1.11123643</v>
+        <v>31.50825829</v>
       </c>
       <c r="K85" t="n">
-        <v>-20.036443</v>
+        <v>43.48443047</v>
       </c>
       <c r="L85" t="n">
-        <v>-24.56355175</v>
+        <v>13.09829768</v>
       </c>
       <c r="M85" t="n">
-        <v>-6.497919510000001</v>
+        <v>98.23389636000002</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右上</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr"/>
+          <t>電子通路業右下</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>0</v>
+      </c>
       <c r="C86" t="n">
-        <v>84.78180712999999</v>
+        <v>5.08139875</v>
       </c>
       <c r="D86" t="n">
-        <v>5.239100129999997</v>
+        <v>14.30721738</v>
       </c>
       <c r="E86" t="n">
-        <v>37.95854161</v>
+        <v>17.21231996</v>
       </c>
       <c r="F86" t="n">
-        <v>6.337415530000002</v>
+        <v>9.666825319999999</v>
       </c>
       <c r="G86" t="n">
-        <v>-14.77173878</v>
+        <v>13.81801526</v>
       </c>
       <c r="H86" t="n">
-        <v>42.12402878</v>
+        <v>0.01406337</v>
       </c>
       <c r="I86" t="n">
-        <v>24.19335857</v>
+        <v>3.64720106</v>
       </c>
       <c r="J86" t="n">
-        <v>81.89622543999999</v>
+        <v>-2.23925099</v>
       </c>
       <c r="K86" t="n">
-        <v>36.94664319</v>
+        <v>2.45052868</v>
       </c>
       <c r="L86" t="n">
-        <v>39.92671712</v>
+        <v>5.204550360000001</v>
       </c>
       <c r="M86" t="n">
-        <v>-7.647300829999998</v>
+        <v>8.83929865</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右下</t>
+          <t>電子通路業平</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>22.32559712</v>
+        <v>-162.62400307</v>
       </c>
       <c r="D87" t="n">
-        <v>6.20539317</v>
+        <v>1.415673110000001</v>
       </c>
       <c r="E87" t="n">
-        <v>19.57465763</v>
+        <v>-80.45172776999999</v>
       </c>
       <c r="F87" t="n">
-        <v>19.41548498</v>
+        <v>-30.71248296</v>
       </c>
       <c r="G87" t="n">
-        <v>15.32622302</v>
+        <v>27.71139969</v>
       </c>
       <c r="H87" t="n">
-        <v>21.24192985</v>
+        <v>-45.84580746</v>
       </c>
       <c r="I87" t="n">
-        <v>2.4630607</v>
+        <v>12.1419908</v>
       </c>
       <c r="J87" t="n">
-        <v>3.62088127</v>
+        <v>-71.91019874000001</v>
       </c>
       <c r="K87" t="n">
-        <v>-6.0015291</v>
+        <v>-32.61515799</v>
       </c>
       <c r="L87" t="n">
-        <v>-2.04589291</v>
+        <v>15.83261637</v>
       </c>
       <c r="M87" t="n">
-        <v>3.85967725</v>
+        <v>67.43947752</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>電子通路業平</t>
+          <t>電子零組件業右上</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
-        <v>-14.14651726</v>
+        <v>-185.6210225900001</v>
       </c>
       <c r="D88" t="n">
-        <v>-169.54013666</v>
+        <v>1450.16954711</v>
       </c>
       <c r="E88" t="n">
-        <v>-6.49426587</v>
+        <v>2181.7213222</v>
       </c>
       <c r="F88" t="n">
-        <v>-86.67775795999999</v>
+        <v>800.8896557599999</v>
       </c>
       <c r="G88" t="n">
-        <v>-36.33716424</v>
+        <v>2692.81628791</v>
       </c>
       <c r="H88" t="n">
-        <v>23.72003185</v>
+        <v>1485.24470595</v>
       </c>
       <c r="I88" t="n">
-        <v>-51.5510354</v>
+        <v>707.3239357199999</v>
       </c>
       <c r="J88" t="n">
-        <v>14.02827815</v>
+        <v>2029.26073542</v>
       </c>
       <c r="K88" t="n">
-        <v>-73.58579353</v>
+        <v>2841.68157912</v>
       </c>
       <c r="L88" t="n">
-        <v>-28.11776397</v>
+        <v>310.9182969999999</v>
       </c>
       <c r="M88" t="n">
-        <v>17.17881818</v>
+        <v>2951.08125892</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右上</t>
+          <t>電子零組件業右下</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>3045.12153567</v>
+        <v>-883.24209911</v>
       </c>
       <c r="D89" t="n">
-        <v>-185.6210225900001</v>
+        <v>-201.52397087</v>
       </c>
       <c r="E89" t="n">
-        <v>1450.16954711</v>
+        <v>-8.732740339999999</v>
       </c>
       <c r="F89" t="n">
-        <v>2181.7213222</v>
+        <v>-435.81774409</v>
       </c>
       <c r="G89" t="n">
-        <v>800.8896557599999</v>
+        <v>-102.3107785</v>
       </c>
       <c r="H89" t="n">
-        <v>2692.81628791</v>
+        <v>896.3284795599999</v>
       </c>
       <c r="I89" t="n">
-        <v>1485.24470595</v>
+        <v>1111.10497579</v>
       </c>
       <c r="J89" t="n">
-        <v>707.3239357199999</v>
+        <v>50.44890780999999</v>
       </c>
       <c r="K89" t="n">
-        <v>2029.26073542</v>
+        <v>-14.56728938000001</v>
       </c>
       <c r="L89" t="n">
-        <v>2841.68157912</v>
+        <v>-5.564253769999999</v>
       </c>
       <c r="M89" t="n">
-        <v>310.9182969999999</v>
+        <v>-19.6759302</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右下</t>
+          <t>電子零組件業平</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>2.463848020000004</v>
+        <v>-232.4944642299999</v>
       </c>
       <c r="D90" t="n">
-        <v>-811.15952119</v>
+        <v>420.92061912</v>
       </c>
       <c r="E90" t="n">
-        <v>-208.916076</v>
+        <v>459.95052021</v>
       </c>
       <c r="F90" t="n">
-        <v>19.51218682</v>
+        <v>605.7497208599999</v>
       </c>
       <c r="G90" t="n">
-        <v>-394.97740607</v>
+        <v>673.2721946099999</v>
       </c>
       <c r="H90" t="n">
-        <v>-84.82093649000001</v>
+        <v>66.02010782999999</v>
       </c>
       <c r="I90" t="n">
-        <v>932.39330921</v>
+        <v>-272.91236466</v>
       </c>
       <c r="J90" t="n">
-        <v>1127.05188189</v>
+        <v>-579.9655332799999</v>
       </c>
       <c r="K90" t="n">
-        <v>74.69056523</v>
+        <v>-509.24311207</v>
       </c>
       <c r="L90" t="n">
-        <v>121.71188574</v>
+        <v>-465.41948481</v>
       </c>
       <c r="M90" t="n">
-        <v>-324.48483771</v>
+        <v>115.73875425</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業平</t>
+          <t>電機機械右上</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>352.41061298</v>
+        <v>184.87326695</v>
       </c>
       <c r="D91" t="n">
-        <v>-304.57704215</v>
+        <v>1368.35983017</v>
       </c>
       <c r="E91" t="n">
-        <v>428.31272425</v>
+        <v>-196.54083268</v>
       </c>
       <c r="F91" t="n">
-        <v>431.70559305</v>
+        <v>-957.50121358</v>
       </c>
       <c r="G91" t="n">
-        <v>564.9093828399998</v>
+        <v>-381.6503944</v>
       </c>
       <c r="H91" t="n">
-        <v>655.7823525999999</v>
+        <v>-279.9177601100001</v>
       </c>
       <c r="I91" t="n">
-        <v>29.95527817999999</v>
+        <v>-263.24742637</v>
       </c>
       <c r="J91" t="n">
-        <v>-288.85927076</v>
+        <v>-135.88497402</v>
       </c>
       <c r="K91" t="n">
-        <v>-604.2071907000001</v>
+        <v>232.56698152</v>
       </c>
       <c r="L91" t="n">
-        <v>-516.20697965</v>
+        <v>-1066.21545203</v>
       </c>
       <c r="M91" t="n">
-        <v>-454.6967065100001</v>
+        <v>-1047.51645464</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>電機機械右上</t>
+          <t>電機機械右下</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>231.7437846000001</v>
+        <v>-103.78597877</v>
       </c>
       <c r="D92" t="n">
-        <v>187.93600482</v>
+        <v>122.6228198</v>
       </c>
       <c r="E92" t="n">
-        <v>1374.52805904</v>
+        <v>91.51325189999999</v>
       </c>
       <c r="F92" t="n">
-        <v>-196.0247448</v>
+        <v>-52.62472093</v>
       </c>
       <c r="G92" t="n">
-        <v>-960.59430022</v>
+        <v>-40.00084953</v>
       </c>
       <c r="H92" t="n">
-        <v>-381.9727258300001</v>
+        <v>-83.57265513</v>
       </c>
       <c r="I92" t="n">
-        <v>-279.90565688</v>
+        <v>59.78372129</v>
       </c>
       <c r="J92" t="n">
-        <v>-266.3651420100001</v>
+        <v>-48.40620964</v>
       </c>
       <c r="K92" t="n">
-        <v>-137.75917843</v>
+        <v>-27.57179441000001</v>
       </c>
       <c r="L92" t="n">
-        <v>229.70470534</v>
+        <v>-25.67954601</v>
       </c>
       <c r="M92" t="n">
-        <v>-1071.52023388</v>
+        <v>43.66854344</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>電機機械右下</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>0</v>
-      </c>
+          <t>電機機械平</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>29.38402996</v>
+        <v>-153.88288005</v>
       </c>
       <c r="D93" t="n">
-        <v>-103.78599573</v>
+        <v>61.93388523</v>
       </c>
       <c r="E93" t="n">
-        <v>122.62280393</v>
+        <v>80.1940639</v>
       </c>
       <c r="F93" t="n">
-        <v>91.51325279</v>
+        <v>304.59201791</v>
       </c>
       <c r="G93" t="n">
-        <v>-52.62472325</v>
+        <v>429.20513492</v>
       </c>
       <c r="H93" t="n">
-        <v>-40.00084902</v>
+        <v>102.15705989</v>
       </c>
       <c r="I93" t="n">
-        <v>-83.57264979999999</v>
+        <v>147.00313338</v>
       </c>
       <c r="J93" t="n">
-        <v>59.78373489</v>
+        <v>305.55276471</v>
       </c>
       <c r="K93" t="n">
-        <v>-48.406199</v>
+        <v>108.78128855</v>
       </c>
       <c r="L93" t="n">
-        <v>-27.57179608000001</v>
+        <v>-14.03852316</v>
       </c>
       <c r="M93" t="n">
-        <v>-25.6795375</v>
+        <v>-109.0583996</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>電機機械平</t>
+          <t>電腦及週邊設備業右上</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>-52.55055714</v>
+        <v>324.9204341100001</v>
       </c>
       <c r="D94" t="n">
-        <v>-156.93598863</v>
+        <v>-812.2786350600001</v>
       </c>
       <c r="E94" t="n">
-        <v>55.77096381</v>
+        <v>683.4299987600001</v>
       </c>
       <c r="F94" t="n">
-        <v>79.68027279</v>
+        <v>-196.7993444</v>
       </c>
       <c r="G94" t="n">
-        <v>307.6798681500001</v>
+        <v>1230.67429305</v>
       </c>
       <c r="H94" t="n">
-        <v>429.53010238</v>
+        <v>736.97943814</v>
       </c>
       <c r="I94" t="n">
-        <v>102.15070965</v>
+        <v>980.9976145999998</v>
       </c>
       <c r="J94" t="n">
-        <v>150.12609553</v>
+        <v>3039.80295137</v>
       </c>
       <c r="K94" t="n">
-        <v>307.43325086</v>
+        <v>2684.70702195</v>
       </c>
       <c r="L94" t="n">
-        <v>111.64712743</v>
+        <v>405.27107273</v>
       </c>
       <c r="M94" t="n">
-        <v>-8.731056049999998</v>
+        <v>4022.20344772</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr"/>
+          <t>電腦及週邊設備業右下</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>0</v>
+      </c>
       <c r="C95" t="n">
-        <v>1199.23969039</v>
+        <v>-132.46080242</v>
       </c>
       <c r="D95" t="n">
-        <v>326.13459925</v>
+        <v>34.85056729</v>
       </c>
       <c r="E95" t="n">
-        <v>-811.6942932100002</v>
+        <v>55.01980351</v>
       </c>
       <c r="F95" t="n">
-        <v>681.95792121</v>
+        <v>74.50069306</v>
       </c>
       <c r="G95" t="n">
-        <v>-200.73019715</v>
+        <v>80.53706909</v>
       </c>
       <c r="H95" t="n">
-        <v>1210.48328601</v>
+        <v>-8.93303306</v>
       </c>
       <c r="I95" t="n">
-        <v>730.77928545</v>
+        <v>58.02319511</v>
       </c>
       <c r="J95" t="n">
-        <v>965.6002825499999</v>
+        <v>35.29578411000001</v>
       </c>
       <c r="K95" t="n">
-        <v>3035.47126514</v>
+        <v>7.858454199999987</v>
       </c>
       <c r="L95" t="n">
-        <v>2685.63241132</v>
+        <v>28.23256805999999</v>
       </c>
       <c r="M95" t="n">
-        <v>401.58927457</v>
+        <v>208.04570502</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下</t>
+          <t>電腦及週邊設備業平</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>132.29966174</v>
+        <v>-4.141184909999997</v>
       </c>
       <c r="D96" t="n">
-        <v>-141.30775993</v>
+        <v>166.47330958</v>
       </c>
       <c r="E96" t="n">
-        <v>39.64208135</v>
+        <v>80.32533663</v>
       </c>
       <c r="F96" t="n">
-        <v>52.17459030999999</v>
+        <v>-51.44705072</v>
       </c>
       <c r="G96" t="n">
-        <v>69.41372987999999</v>
+        <v>34.72257917</v>
       </c>
       <c r="H96" t="n">
-        <v>81.05502186</v>
+        <v>-207.45357874</v>
       </c>
       <c r="I96" t="n">
-        <v>-13.09397059</v>
+        <v>-257.04887386</v>
       </c>
       <c r="J96" t="n">
-        <v>56.25579081</v>
+        <v>-118.52267815</v>
       </c>
       <c r="K96" t="n">
-        <v>19.28692427</v>
+        <v>-10.78382667</v>
       </c>
       <c r="L96" t="n">
-        <v>2.439667629999996</v>
+        <v>-63.24544184000001</v>
       </c>
       <c r="M96" t="n">
-        <v>23.74875729999999</v>
+        <v>176.69736419</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平</t>
+          <t>食品工業右上</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>461.32377392</v>
+        <v>-89.75941349999999</v>
       </c>
       <c r="D97" t="n">
-        <v>1.259735930000003</v>
+        <v>-55.51367920000001</v>
       </c>
       <c r="E97" t="n">
-        <v>162.0188218</v>
+        <v>-57.70773954</v>
       </c>
       <c r="F97" t="n">
-        <v>84.03388609</v>
+        <v>-36.45684124</v>
       </c>
       <c r="G97" t="n">
-        <v>-41.45642434000001</v>
+        <v>-33.17751057</v>
       </c>
       <c r="H97" t="n">
-        <v>56.75961389999999</v>
+        <v>-32.66692659</v>
       </c>
       <c r="I97" t="n">
-        <v>-195.94970524</v>
+        <v>-28.58669746</v>
       </c>
       <c r="J97" t="n">
-        <v>-239.67700159</v>
+        <v>-32.48884227</v>
       </c>
       <c r="K97" t="n">
-        <v>-100.10756896</v>
+        <v>-12.6336774</v>
       </c>
       <c r="L97" t="n">
-        <v>-6.023616009999998</v>
+        <v>26.64727957</v>
       </c>
       <c r="M97" t="n">
-        <v>-53.42532436</v>
+        <v>55.86739919</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>食品工業右上</t>
+          <t>食品工業右下</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
-        <v>-75.60989875999999</v>
+        <v>-13.81783122</v>
       </c>
       <c r="D98" t="n">
-        <v>-89.46311981999999</v>
+        <v>8.902682299999999</v>
       </c>
       <c r="E98" t="n">
-        <v>-56.04701719000001</v>
+        <v>-7.00097985</v>
       </c>
       <c r="F98" t="n">
-        <v>-57.87665437</v>
+        <v>-8.586387240000001</v>
       </c>
       <c r="G98" t="n">
-        <v>-36.62885614</v>
+        <v>-10.56307657</v>
       </c>
       <c r="H98" t="n">
-        <v>-32.91272461</v>
+        <v>-11.32923905</v>
       </c>
       <c r="I98" t="n">
-        <v>-31.98487371</v>
+        <v>2.98401102</v>
       </c>
       <c r="J98" t="n">
-        <v>-28.05827051</v>
+        <v>1.30875266</v>
       </c>
       <c r="K98" t="n">
-        <v>-31.36616687</v>
+        <v>-3.510710399999999</v>
       </c>
       <c r="L98" t="n">
-        <v>-10.44515264</v>
+        <v>10.10491649</v>
       </c>
       <c r="M98" t="n">
-        <v>26.32759989</v>
+        <v>13.23640147</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>食品工業右下</t>
+          <t>食品工業平</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>4.182556519999999</v>
+        <v>92.38513603</v>
       </c>
       <c r="D99" t="n">
-        <v>-13.43138844</v>
+        <v>-53.9049685</v>
       </c>
       <c r="E99" t="n">
-        <v>9.332435159999999</v>
+        <v>-139.15850846</v>
       </c>
       <c r="F99" t="n">
-        <v>-5.543312350000001</v>
+        <v>-187.13439535</v>
       </c>
       <c r="G99" t="n">
-        <v>-7.712997290000001</v>
+        <v>-262.84111386</v>
       </c>
       <c r="H99" t="n">
-        <v>-9.903047969999999</v>
+        <v>-271.02277534</v>
       </c>
       <c r="I99" t="n">
-        <v>-10.66132324</v>
+        <v>-156.7840633</v>
       </c>
       <c r="J99" t="n">
-        <v>2.86535633</v>
+        <v>-222.39133867</v>
       </c>
       <c r="K99" t="n">
-        <v>0.8721114700000003</v>
+        <v>-118.60993476</v>
       </c>
       <c r="L99" t="n">
-        <v>-4.212167819999999</v>
+        <v>-52.26052</v>
       </c>
       <c r="M99" t="n">
-        <v>9.207686730000001</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="1" t="inlineStr">
-        <is>
-          <t>食品工業平</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr"/>
-      <c r="C100" t="n">
-        <v>78.49249439999998</v>
-      </c>
-      <c r="D100" t="n">
-        <v>91.70239957</v>
-      </c>
-      <c r="E100" t="n">
-        <v>-53.80138337</v>
-      </c>
-      <c r="F100" t="n">
-        <v>-140.44726113</v>
-      </c>
-      <c r="G100" t="n">
-        <v>-187.8357704</v>
-      </c>
-      <c r="H100" t="n">
-        <v>-263.76592842</v>
-      </c>
-      <c r="I100" t="n">
-        <v>-272.37274403</v>
-      </c>
-      <c r="J100" t="n">
-        <v>-157.19383556</v>
-      </c>
-      <c r="K100" t="n">
-        <v>-223.07737288</v>
-      </c>
-      <c r="L100" t="n">
-        <v>-120.0970021</v>
-      </c>
-      <c r="M100" t="n">
-        <v>-51.04361056</v>
+        <v>-89.94657139</v>
       </c>
     </row>
   </sheetData>

--- a/Result/analyze_2.xlsx
+++ b/Result/analyze_2.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
     </row>
@@ -503,37 +503,37 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>-322.22722522</v>
+        <v>133.06912042</v>
       </c>
       <c r="D2" t="n">
-        <v>135.20217909</v>
+        <v>239.95090942</v>
       </c>
       <c r="E2" t="n">
-        <v>242.65630684</v>
+        <v>66.00250505</v>
       </c>
       <c r="F2" t="n">
-        <v>67.46913453000001</v>
+        <v>355.45804248</v>
       </c>
       <c r="G2" t="n">
-        <v>357.82759385</v>
+        <v>-34.51162536</v>
       </c>
       <c r="H2" t="n">
-        <v>-35.08082859000001</v>
+        <v>245.46158357</v>
       </c>
       <c r="I2" t="n">
-        <v>249.84557716</v>
+        <v>602.6152474099999</v>
       </c>
       <c r="J2" t="n">
-        <v>605.31840901</v>
+        <v>653.42568023</v>
       </c>
       <c r="K2" t="n">
-        <v>657.13890401</v>
+        <v>930.2711050599999</v>
       </c>
       <c r="L2" t="n">
-        <v>945.81373646</v>
+        <v>1827.6733201</v>
       </c>
       <c r="M2" t="n">
-        <v>1855.06915177</v>
+        <v>1069.4091092</v>
       </c>
     </row>
     <row r="3">
@@ -542,39 +542,41 @@
           <t>光電業右下</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
       <c r="C3" t="n">
-        <v>-159.44846938</v>
+        <v>7.490133159999999</v>
       </c>
       <c r="D3" t="n">
-        <v>2.863513359999999</v>
+        <v>67.49101417</v>
       </c>
       <c r="E3" t="n">
-        <v>55.44046901999999</v>
+        <v>148.36239801</v>
       </c>
       <c r="F3" t="n">
-        <v>140.1150031</v>
+        <v>210.99623909</v>
       </c>
       <c r="G3" t="n">
-        <v>203.34787115</v>
+        <v>118.84403687</v>
       </c>
       <c r="H3" t="n">
-        <v>116.11038237</v>
+        <v>180.66622047</v>
       </c>
       <c r="I3" t="n">
-        <v>168.18807658</v>
+        <v>18.8222692</v>
       </c>
       <c r="J3" t="n">
-        <v>10.60851722</v>
+        <v>-2.444914739999998</v>
       </c>
       <c r="K3" t="n">
-        <v>-11.69896874</v>
+        <v>124.75165192</v>
       </c>
       <c r="L3" t="n">
-        <v>111.92963868</v>
+        <v>229.66293875</v>
       </c>
       <c r="M3" t="n">
-        <v>150.94500049</v>
+        <v>149.41176898</v>
       </c>
     </row>
     <row r="4">
@@ -585,37 +587,37 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>-4.946673600000003</v>
+        <v>-89.41343711</v>
       </c>
       <c r="D4" t="n">
-        <v>-100.45687196</v>
+        <v>134.16845386</v>
       </c>
       <c r="E4" t="n">
-        <v>148.70740365</v>
+        <v>2.515372209999999</v>
       </c>
       <c r="F4" t="n">
-        <v>8.439684930000006</v>
+        <v>-22.27804234</v>
       </c>
       <c r="G4" t="n">
-        <v>-22.87123488000001</v>
+        <v>-154.32680326</v>
       </c>
       <c r="H4" t="n">
-        <v>-160.79882521</v>
+        <v>-69.50281128</v>
       </c>
       <c r="I4" t="n">
-        <v>-62.2850806</v>
+        <v>-119.78544769</v>
       </c>
       <c r="J4" t="n">
-        <v>-151.84072359</v>
+        <v>-156.06544249</v>
       </c>
       <c r="K4" t="n">
-        <v>-186.41994278</v>
+        <v>11.83680254</v>
       </c>
       <c r="L4" t="n">
-        <v>-24.90480189000001</v>
+        <v>120.80687653</v>
       </c>
       <c r="M4" t="n">
-        <v>161.79591693</v>
+        <v>70.28602769999999</v>
       </c>
     </row>
     <row r="5">
@@ -626,37 +628,37 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>-198.68202118</v>
+        <v>-126.15321476</v>
       </c>
       <c r="D5" t="n">
-        <v>-126.15315298</v>
+        <v>186.82817224</v>
       </c>
       <c r="E5" t="n">
-        <v>186.82811691</v>
+        <v>467.84870192</v>
       </c>
       <c r="F5" t="n">
-        <v>467.8486097100001</v>
+        <v>758.27998281</v>
       </c>
       <c r="G5" t="n">
-        <v>758.27988239</v>
+        <v>802.10581856</v>
       </c>
       <c r="H5" t="n">
-        <v>802.10536136</v>
+        <v>1311.67911888</v>
       </c>
       <c r="I5" t="n">
-        <v>1311.67929021</v>
+        <v>1402.61016698</v>
       </c>
       <c r="J5" t="n">
-        <v>1402.60968035</v>
+        <v>947.17840165</v>
       </c>
       <c r="K5" t="n">
-        <v>947.1777888099999</v>
+        <v>633.91989454</v>
       </c>
       <c r="L5" t="n">
-        <v>633.92100185</v>
+        <v>146.03084003</v>
       </c>
       <c r="M5" t="n">
-        <v>146.03438519</v>
+        <v>-38.63562939</v>
       </c>
     </row>
     <row r="6">
@@ -665,39 +667,41 @@
           <t>其他右下</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
       <c r="C6" t="n">
-        <v>-110.01241395</v>
+        <v>55.37460995</v>
       </c>
       <c r="D6" t="n">
-        <v>55.37822946</v>
+        <v>36.25041112</v>
       </c>
       <c r="E6" t="n">
-        <v>36.31491508</v>
+        <v>-15.16688701</v>
       </c>
       <c r="F6" t="n">
-        <v>-15.07054057</v>
+        <v>-36.62205257</v>
       </c>
       <c r="G6" t="n">
-        <v>-36.497304</v>
+        <v>-50.67505064</v>
       </c>
       <c r="H6" t="n">
-        <v>-50.54118899</v>
+        <v>-51.24585219999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-51.15767825</v>
+        <v>-140.84742715</v>
       </c>
       <c r="J6" t="n">
-        <v>-140.94539252</v>
+        <v>-65.15703855999999</v>
       </c>
       <c r="K6" t="n">
-        <v>-65.33151304</v>
+        <v>62.16016367999999</v>
       </c>
       <c r="L6" t="n">
-        <v>61.9280458</v>
+        <v>11.80711865</v>
       </c>
       <c r="M6" t="n">
-        <v>11.71011091</v>
+        <v>17.54515394</v>
       </c>
     </row>
     <row r="7">
@@ -708,37 +712,37 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>17.93379638</v>
+        <v>43.00683966</v>
       </c>
       <c r="D7" t="n">
-        <v>43.01934182999999</v>
+        <v>35.62588602</v>
       </c>
       <c r="E7" t="n">
-        <v>35.57172609000001</v>
+        <v>23.99754846</v>
       </c>
       <c r="F7" t="n">
-        <v>23.90382348</v>
+        <v>18.20177115</v>
       </c>
       <c r="G7" t="n">
-        <v>18.06918611</v>
+        <v>13.10214007</v>
       </c>
       <c r="H7" t="n">
-        <v>12.93291063</v>
+        <v>23.47973366</v>
       </c>
       <c r="I7" t="n">
-        <v>23.36284826</v>
+        <v>8.216738310000002</v>
       </c>
       <c r="J7" t="n">
-        <v>8.285367280000001</v>
+        <v>7.962291460000001</v>
       </c>
       <c r="K7" t="n">
-        <v>8.104425859999999</v>
+        <v>10.42012994</v>
       </c>
       <c r="L7" t="n">
-        <v>10.62028197</v>
+        <v>11.80106688</v>
       </c>
       <c r="M7" t="n">
-        <v>11.86706585</v>
+        <v>20.27382046</v>
       </c>
     </row>
     <row r="8">
@@ -749,37 +753,37 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>-2015.17474928</v>
+        <v>-603.01014801</v>
       </c>
       <c r="D8" t="n">
-        <v>-576.1517193</v>
+        <v>1579.16335035</v>
       </c>
       <c r="E8" t="n">
-        <v>1605.08533393</v>
+        <v>1674.90332042</v>
       </c>
       <c r="F8" t="n">
-        <v>1699.48898073</v>
+        <v>1734.66238881</v>
       </c>
       <c r="G8" t="n">
-        <v>1760.30099883</v>
+        <v>221.52990653</v>
       </c>
       <c r="H8" t="n">
-        <v>258.82277212</v>
+        <v>-159.8729158599999</v>
       </c>
       <c r="I8" t="n">
-        <v>-136.10115485</v>
+        <v>1450.18502182</v>
       </c>
       <c r="J8" t="n">
-        <v>1519.8498465</v>
+        <v>2241.0766307</v>
       </c>
       <c r="K8" t="n">
-        <v>2333.54672179</v>
+        <v>1043.10318778</v>
       </c>
       <c r="L8" t="n">
-        <v>1156.50518768</v>
+        <v>1207.88001607</v>
       </c>
       <c r="M8" t="n">
-        <v>1287.23069345</v>
+        <v>1211.52543326</v>
       </c>
     </row>
     <row r="9">
@@ -790,37 +794,37 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>5.40532031</v>
+        <v>67.87246501</v>
       </c>
       <c r="D9" t="n">
-        <v>67.87246501</v>
+        <v>64.29666813999999</v>
       </c>
       <c r="E9" t="n">
-        <v>64.29666813999999</v>
+        <v>24.04332181</v>
       </c>
       <c r="F9" t="n">
-        <v>24.04332181</v>
+        <v>-2.54936097</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.54936097</v>
+        <v>5.406092370000001</v>
       </c>
       <c r="H9" t="n">
-        <v>5.406092370000001</v>
+        <v>17.64058343</v>
       </c>
       <c r="I9" t="n">
-        <v>17.64058343</v>
+        <v>-18.94161434</v>
       </c>
       <c r="J9" t="n">
-        <v>-18.94161434</v>
+        <v>37.62844630000001</v>
       </c>
       <c r="K9" t="n">
-        <v>37.62844630000001</v>
+        <v>35.63573011</v>
       </c>
       <c r="L9" t="n">
-        <v>35.63573011</v>
+        <v>39.53914933</v>
       </c>
       <c r="M9" t="n">
-        <v>39.53914933</v>
+        <v>-2.46165883</v>
       </c>
     </row>
     <row r="10">
@@ -831,37 +835,37 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>-80.77079300000001</v>
+        <v>-18.22438221</v>
       </c>
       <c r="D10" t="n">
-        <v>-16.45917164</v>
+        <v>50.56874051</v>
       </c>
       <c r="E10" t="n">
-        <v>45.5686809</v>
+        <v>20.28384937</v>
       </c>
       <c r="F10" t="n">
-        <v>11.50130725</v>
+        <v>25.11560232</v>
       </c>
       <c r="G10" t="n">
-        <v>11.54029648</v>
+        <v>-32.68893001</v>
       </c>
       <c r="H10" t="n">
-        <v>-26.15984913</v>
+        <v>-12.73385422</v>
       </c>
       <c r="I10" t="n">
-        <v>3.02895754</v>
+        <v>-24.78738033</v>
       </c>
       <c r="J10" t="n">
-        <v>-16.71430331</v>
+        <v>44.53638893999999</v>
       </c>
       <c r="K10" t="n">
-        <v>39.20265944</v>
+        <v>73.24840189</v>
       </c>
       <c r="L10" t="n">
-        <v>56.81217666</v>
+        <v>102.50783511</v>
       </c>
       <c r="M10" t="n">
-        <v>76.48051932000001</v>
+        <v>31.43955407</v>
       </c>
     </row>
     <row r="11">
@@ -872,37 +876,37 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>2.859002090000001</v>
+        <v>23.99637591</v>
       </c>
       <c r="D11" t="n">
-        <v>23.8488836</v>
+        <v>32.21424429</v>
       </c>
       <c r="E11" t="n">
-        <v>31.95600483</v>
+        <v>36.53843114</v>
       </c>
       <c r="F11" t="n">
-        <v>36.40751091</v>
+        <v>70.10710927</v>
       </c>
       <c r="G11" t="n">
-        <v>70.07194070999999</v>
+        <v>11.6701371</v>
       </c>
       <c r="H11" t="n">
-        <v>11.69021167</v>
+        <v>59.80061635</v>
       </c>
       <c r="I11" t="n">
-        <v>59.84247325</v>
+        <v>132.46617671</v>
       </c>
       <c r="J11" t="n">
-        <v>132.53821739</v>
+        <v>62.27960491</v>
       </c>
       <c r="K11" t="n">
-        <v>62.3192098</v>
+        <v>59.58881277</v>
       </c>
       <c r="L11" t="n">
-        <v>59.63880218</v>
+        <v>-16.88295119</v>
       </c>
       <c r="M11" t="n">
-        <v>-16.82507837</v>
+        <v>-59.73766403</v>
       </c>
     </row>
     <row r="12">
@@ -911,39 +915,41 @@
           <t>化學工業右下</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
       <c r="C12" t="n">
-        <v>38.94469194999999</v>
+        <v>42.88371942</v>
       </c>
       <c r="D12" t="n">
-        <v>43.88918375</v>
+        <v>188.66706368</v>
       </c>
       <c r="E12" t="n">
-        <v>181.12827274</v>
+        <v>74.9607798</v>
       </c>
       <c r="F12" t="n">
-        <v>62.28709359</v>
+        <v>61.98297435</v>
       </c>
       <c r="G12" t="n">
-        <v>47.51182313</v>
+        <v>-50.61483504</v>
       </c>
       <c r="H12" t="n">
-        <v>-67.86251213</v>
+        <v>120.26081568</v>
       </c>
       <c r="I12" t="n">
-        <v>117.04709593</v>
+        <v>17.05747791</v>
       </c>
       <c r="J12" t="n">
-        <v>1.19653822</v>
+        <v>-76.68317665000001</v>
       </c>
       <c r="K12" t="n">
-        <v>-83.11722171000001</v>
+        <v>-47.9890768</v>
       </c>
       <c r="L12" t="n">
-        <v>-44.36274827</v>
+        <v>-105.84590131</v>
       </c>
       <c r="M12" t="n">
-        <v>-99.14298217</v>
+        <v>-119.01839249</v>
       </c>
     </row>
     <row r="13">
@@ -954,37 +960,37 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>-1.64482739</v>
+        <v>1.92786951</v>
       </c>
       <c r="D13" t="n">
-        <v>2.07536182</v>
+        <v>0.23894946</v>
       </c>
       <c r="E13" t="n">
-        <v>0.49718892</v>
+        <v>-1.33910902</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.20818879</v>
+        <v>-0.07084651000000003</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.03567795000000003</v>
+        <v>1.18530408</v>
       </c>
       <c r="H13" t="n">
-        <v>1.16522951</v>
+        <v>2.51073357</v>
       </c>
       <c r="I13" t="n">
-        <v>2.46887667</v>
+        <v>3.76157343</v>
       </c>
       <c r="J13" t="n">
-        <v>3.68953275</v>
+        <v>2.25168748</v>
       </c>
       <c r="K13" t="n">
-        <v>2.212082590000001</v>
+        <v>2.52538849</v>
       </c>
       <c r="L13" t="n">
-        <v>2.475399079999999</v>
+        <v>0.5877431100000001</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5298702900000001</v>
+        <v>2.16125695</v>
       </c>
     </row>
     <row r="14">
@@ -995,37 +1001,37 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>-6456.45545905</v>
+        <v>-2412.34696072</v>
       </c>
       <c r="D14" t="n">
-        <v>-2412.35071206</v>
+        <v>-3231.96074722</v>
       </c>
       <c r="E14" t="n">
-        <v>-3231.9633218</v>
+        <v>-6067.088565769999</v>
       </c>
       <c r="F14" t="n">
-        <v>-6067.096989799999</v>
+        <v>-8165.36847638</v>
       </c>
       <c r="G14" t="n">
-        <v>-8165.36055333</v>
+        <v>-11808.03381456</v>
       </c>
       <c r="H14" t="n">
-        <v>-11808.0342604</v>
+        <v>-5565.23629961</v>
       </c>
       <c r="I14" t="n">
-        <v>-5565.214608</v>
+        <v>-693.9620924800003</v>
       </c>
       <c r="J14" t="n">
-        <v>-693.9481102300002</v>
+        <v>-4033.19627708</v>
       </c>
       <c r="K14" t="n">
-        <v>-4033.15507835</v>
+        <v>-5990.70254144</v>
       </c>
       <c r="L14" t="n">
-        <v>-5990.6567424</v>
+        <v>-1118.14855647</v>
       </c>
       <c r="M14" t="n">
-        <v>-1118.12726076</v>
+        <v>-3900.45259813</v>
       </c>
     </row>
     <row r="15">
@@ -1036,37 +1042,37 @@
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>-55.75599463999998</v>
+        <v>812.15122491</v>
       </c>
       <c r="D15" t="n">
-        <v>768.03967224</v>
+        <v>402.44684952</v>
       </c>
       <c r="E15" t="n">
-        <v>424.0897906</v>
+        <v>541.1435638200001</v>
       </c>
       <c r="F15" t="n">
-        <v>575.79890386</v>
+        <v>439.24256852</v>
       </c>
       <c r="G15" t="n">
-        <v>493.11082581</v>
+        <v>-44.79142044000002</v>
       </c>
       <c r="H15" t="n">
-        <v>2.431007869999977</v>
+        <v>9.620809680000001</v>
       </c>
       <c r="I15" t="n">
-        <v>140.82586865</v>
+        <v>-648.95806506</v>
       </c>
       <c r="J15" t="n">
-        <v>-526.45670635</v>
+        <v>-168.25121481</v>
       </c>
       <c r="K15" t="n">
-        <v>-85.14885054</v>
+        <v>46.79415958999996</v>
       </c>
       <c r="L15" t="n">
-        <v>124.88546237</v>
+        <v>646.75366428</v>
       </c>
       <c r="M15" t="n">
-        <v>726.86992059</v>
+        <v>59.03503605</v>
       </c>
     </row>
     <row r="16">
@@ -1077,37 +1083,37 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>-250.4489123</v>
+        <v>600.18656244</v>
       </c>
       <c r="D16" t="n">
-        <v>644.3022150199999</v>
+        <v>144.43725266</v>
       </c>
       <c r="E16" t="n">
-        <v>122.79713917</v>
+        <v>-85.62799044999998</v>
       </c>
       <c r="F16" t="n">
-        <v>-120.27460381</v>
+        <v>110.85824884</v>
       </c>
       <c r="G16" t="n">
-        <v>56.98240913000001</v>
+        <v>319.83708784</v>
       </c>
       <c r="H16" t="n">
-        <v>272.61525249</v>
+        <v>-394.42067262</v>
       </c>
       <c r="I16" t="n">
-        <v>-525.64720146</v>
+        <v>-82.29011108</v>
       </c>
       <c r="J16" t="n">
-        <v>-204.80521879</v>
+        <v>-219.38681919</v>
       </c>
       <c r="K16" t="n">
-        <v>-302.53034958</v>
+        <v>-893.4597658600001</v>
       </c>
       <c r="L16" t="n">
-        <v>-971.59696974</v>
+        <v>-727.47811351</v>
       </c>
       <c r="M16" t="n">
-        <v>-807.61602896</v>
+        <v>-1102.49217596</v>
       </c>
     </row>
     <row r="17">
@@ -1118,37 +1124,37 @@
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
-        <v>-0.5506804200000001</v>
+        <v>0.02769227000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>0.02769227000000001</v>
+        <v>0.34978601</v>
       </c>
       <c r="E17" t="n">
-        <v>0.34978601</v>
+        <v>0.55657781</v>
       </c>
       <c r="F17" t="n">
-        <v>0.55657781</v>
+        <v>0.5684159599999999</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5684159599999999</v>
+        <v>0.6202892800000001</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6202892800000001</v>
+        <v>0.7926845100000001</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7926845100000001</v>
+        <v>1.35238512</v>
       </c>
       <c r="J17" t="n">
-        <v>1.35238512</v>
+        <v>2.728392</v>
       </c>
       <c r="K17" t="n">
-        <v>2.728392</v>
+        <v>0.88005688</v>
       </c>
       <c r="L17" t="n">
-        <v>0.88005688</v>
+        <v>0.9546220400000001</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9546220400000001</v>
+        <v>0.84933839</v>
       </c>
     </row>
     <row r="18">
@@ -1159,37 +1165,37 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>338.87725289</v>
+        <v>494.05920309</v>
       </c>
       <c r="D18" t="n">
-        <v>494.0830853900001</v>
+        <v>317.71777002</v>
       </c>
       <c r="E18" t="n">
-        <v>317.7273254</v>
+        <v>283.5817899</v>
       </c>
       <c r="F18" t="n">
-        <v>283.6058508000001</v>
+        <v>797.0976046799999</v>
       </c>
       <c r="G18" t="n">
-        <v>797.0432088700001</v>
+        <v>-142.24816027</v>
       </c>
       <c r="H18" t="n">
-        <v>-142.28295233</v>
+        <v>949.19824843</v>
       </c>
       <c r="I18" t="n">
-        <v>949.17323245</v>
+        <v>786.71530309</v>
       </c>
       <c r="J18" t="n">
-        <v>786.6830428600001</v>
+        <v>-272.89082989</v>
       </c>
       <c r="K18" t="n">
-        <v>-188.6316088</v>
+        <v>-871.1452639</v>
       </c>
       <c r="L18" t="n">
-        <v>-747.85914215</v>
+        <v>-1069.80177573</v>
       </c>
       <c r="M18" t="n">
-        <v>-949.2131747899999</v>
+        <v>-452.59567873</v>
       </c>
     </row>
     <row r="19">
@@ -1200,37 +1206,37 @@
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>-14.82226019</v>
+        <v>-9.652651240000001</v>
       </c>
       <c r="D19" t="n">
-        <v>-9.676533539999999</v>
+        <v>-12.00218059</v>
       </c>
       <c r="E19" t="n">
-        <v>-12.01173597</v>
+        <v>-11.43740213</v>
       </c>
       <c r="F19" t="n">
-        <v>-11.46146303</v>
+        <v>-4.71339594</v>
       </c>
       <c r="G19" t="n">
-        <v>-4.65900013</v>
+        <v>-9.652321150000001</v>
       </c>
       <c r="H19" t="n">
-        <v>-9.61752909</v>
+        <v>-3.20862161</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.18360563</v>
+        <v>-6.092362550000001</v>
       </c>
       <c r="J19" t="n">
-        <v>-6.06010232</v>
+        <v>-6.57161925</v>
       </c>
       <c r="K19" t="n">
-        <v>-6.603607350000001</v>
+        <v>-1.84598969</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.86833417</v>
+        <v>-3.50220299</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.4926213</v>
+        <v>-0.44663556</v>
       </c>
     </row>
     <row r="20">
@@ -1241,37 +1247,37 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>5.16841279</v>
+        <v>34.60076571</v>
       </c>
       <c r="D20" t="n">
-        <v>34.60344654</v>
+        <v>39.71449008</v>
       </c>
       <c r="E20" t="n">
-        <v>39.71568626000001</v>
+        <v>46.16666094</v>
       </c>
       <c r="F20" t="n">
-        <v>46.16644797999999</v>
+        <v>49.79008475</v>
       </c>
       <c r="G20" t="n">
-        <v>49.78897659</v>
+        <v>15.83800044</v>
       </c>
       <c r="H20" t="n">
-        <v>15.83594655</v>
+        <v>43.3430995</v>
       </c>
       <c r="I20" t="n">
-        <v>43.34008297</v>
+        <v>-20.57441159</v>
       </c>
       <c r="J20" t="n">
-        <v>-20.57462681</v>
+        <v>-26.64291881</v>
       </c>
       <c r="K20" t="n">
-        <v>-26.64046678</v>
+        <v>-8.67058585</v>
       </c>
       <c r="L20" t="n">
-        <v>-8.66289199</v>
+        <v>6.293730170000001</v>
       </c>
       <c r="M20" t="n">
-        <v>6.307098380000001</v>
+        <v>-11.39545</v>
       </c>
     </row>
     <row r="21">
@@ -1280,41 +1286,39 @@
           <t>居家生活右下</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
-        <v>-2.44418154</v>
+        <v>-2.90937825</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.90937825</v>
+        <v>-0.6914854</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6914854</v>
+        <v>-0.87016615</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.87016615</v>
+        <v>0.47642728</v>
       </c>
       <c r="G21" t="n">
-        <v>0.47642728</v>
+        <v>-1.38489539</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.38489539</v>
+        <v>1.01578957</v>
       </c>
       <c r="I21" t="n">
-        <v>1.01578957</v>
+        <v>-0.08695448000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.08695448000000001</v>
+        <v>1.98383284</v>
       </c>
       <c r="K21" t="n">
-        <v>1.98383284</v>
+        <v>2.625483</v>
       </c>
       <c r="L21" t="n">
-        <v>2.625483</v>
+        <v>2.3940447</v>
       </c>
       <c r="M21" t="n">
-        <v>2.3940447</v>
+        <v>2.61609992</v>
       </c>
     </row>
     <row r="22">
@@ -1325,37 +1329,37 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>-2.65920272</v>
+        <v>-1.55944125</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.56090563</v>
+        <v>-0.48177969</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4818726700000001</v>
+        <v>0.12730894</v>
       </c>
       <c r="F22" t="n">
-        <v>0.12802714</v>
+        <v>0.40103177</v>
       </c>
       <c r="G22" t="n">
-        <v>0.40218884</v>
+        <v>-0.10881049</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.10679337</v>
+        <v>0.11660356</v>
       </c>
       <c r="I22" t="n">
-        <v>0.11954587</v>
+        <v>0.08802789000000008</v>
       </c>
       <c r="J22" t="n">
-        <v>0.08807710000000005</v>
+        <v>1.53256992</v>
       </c>
       <c r="K22" t="n">
-        <v>1.5294618</v>
+        <v>2.46857889</v>
       </c>
       <c r="L22" t="n">
-        <v>2.46055779</v>
+        <v>1.61133271</v>
       </c>
       <c r="M22" t="n">
-        <v>1.59732101</v>
+        <v>1.84956147</v>
       </c>
     </row>
     <row r="23">
@@ -1366,37 +1370,37 @@
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
-        <v>-35.27000823</v>
+        <v>9.438695200000002</v>
       </c>
       <c r="D23" t="n">
-        <v>9.438695200000002</v>
+        <v>29.14204919</v>
       </c>
       <c r="E23" t="n">
-        <v>29.14204919</v>
+        <v>18.78984363</v>
       </c>
       <c r="F23" t="n">
-        <v>18.78984363</v>
+        <v>11.99700128</v>
       </c>
       <c r="G23" t="n">
-        <v>11.99700128</v>
+        <v>-21.51542892</v>
       </c>
       <c r="H23" t="n">
-        <v>-21.51542892</v>
+        <v>3.234019390000002</v>
       </c>
       <c r="I23" t="n">
-        <v>3.234019390000002</v>
+        <v>1.317080060000002</v>
       </c>
       <c r="J23" t="n">
-        <v>1.317080060000002</v>
+        <v>-8.2388408</v>
       </c>
       <c r="K23" t="n">
-        <v>-8.2388408</v>
+        <v>30.90360521</v>
       </c>
       <c r="L23" t="n">
-        <v>30.90360521</v>
+        <v>28.25559642</v>
       </c>
       <c r="M23" t="n">
-        <v>28.25559642</v>
+        <v>13.04442215</v>
       </c>
     </row>
     <row r="24">
@@ -1407,37 +1411,37 @@
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
-        <v>-59.08562743</v>
+        <v>-65.19009097999999</v>
       </c>
       <c r="D24" t="n">
-        <v>-66.95218318999999</v>
+        <v>-78.71996444</v>
       </c>
       <c r="E24" t="n">
-        <v>-81.1055707</v>
+        <v>-82.29528092000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-84.15877762000001</v>
+        <v>-82.69341238000001</v>
       </c>
       <c r="G24" t="n">
-        <v>-84.14077758000001</v>
+        <v>-81.77471033000002</v>
       </c>
       <c r="H24" t="n">
-        <v>-82.8272675</v>
+        <v>-54.70296398</v>
       </c>
       <c r="I24" t="n">
-        <v>-54.6127678</v>
+        <v>-34.20043623</v>
       </c>
       <c r="J24" t="n">
-        <v>-33.53495641</v>
+        <v>3.396011510000001</v>
       </c>
       <c r="K24" t="n">
-        <v>2.644124560000001</v>
+        <v>45.497298</v>
       </c>
       <c r="L24" t="n">
-        <v>45.01555479</v>
+        <v>38.02832282</v>
       </c>
       <c r="M24" t="n">
-        <v>38.81457239</v>
+        <v>58.68137049</v>
       </c>
     </row>
     <row r="25">
@@ -1448,37 +1452,37 @@
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>8.92547113</v>
+        <v>80.22433495</v>
       </c>
       <c r="D25" t="n">
-        <v>81.98642715999999</v>
+        <v>33.12690797</v>
       </c>
       <c r="E25" t="n">
-        <v>35.51251422999999</v>
+        <v>-18.01761874</v>
       </c>
       <c r="F25" t="n">
-        <v>-16.15412204</v>
+        <v>-69.11264593</v>
       </c>
       <c r="G25" t="n">
-        <v>-67.66528073000001</v>
+        <v>-119.25189594</v>
       </c>
       <c r="H25" t="n">
-        <v>-118.19933877</v>
+        <v>-90.13895229000001</v>
       </c>
       <c r="I25" t="n">
-        <v>-90.22914847</v>
+        <v>-116.98923053</v>
       </c>
       <c r="J25" t="n">
-        <v>-117.65471035</v>
+        <v>-16.7603081</v>
       </c>
       <c r="K25" t="n">
-        <v>-16.00842115</v>
+        <v>99.92336340999999</v>
       </c>
       <c r="L25" t="n">
-        <v>100.40510662</v>
+        <v>10.77635139</v>
       </c>
       <c r="M25" t="n">
-        <v>9.99010182</v>
+        <v>-0.9253528999999954</v>
       </c>
     </row>
     <row r="26">
@@ -1489,37 +1493,37 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>14.92712717</v>
+        <v>60.53162531</v>
       </c>
       <c r="D26" t="n">
-        <v>60.74444865</v>
+        <v>105.90485355</v>
       </c>
       <c r="E26" t="n">
-        <v>106.37604668</v>
+        <v>30.24814522</v>
       </c>
       <c r="F26" t="n">
-        <v>30.41413148</v>
+        <v>26.76396136</v>
       </c>
       <c r="G26" t="n">
-        <v>27.07538775</v>
+        <v>-16.35696898</v>
       </c>
       <c r="H26" t="n">
-        <v>-16.00512611</v>
+        <v>-11.57917922</v>
       </c>
       <c r="I26" t="n">
-        <v>-11.48791496</v>
+        <v>-0.76419575</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.5816431699999999</v>
+        <v>20.13668719</v>
       </c>
       <c r="K26" t="n">
-        <v>20.25448622</v>
+        <v>-15.72170868</v>
       </c>
       <c r="L26" t="n">
-        <v>-15.84902005</v>
+        <v>12.89942112</v>
       </c>
       <c r="M26" t="n">
-        <v>12.53861818</v>
+        <v>-21.76483932</v>
       </c>
     </row>
     <row r="27">
@@ -1530,37 +1534,37 @@
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>-5.07148308</v>
+        <v>19.81733471</v>
       </c>
       <c r="D27" t="n">
-        <v>19.81733471</v>
+        <v>26.50834888</v>
       </c>
       <c r="E27" t="n">
-        <v>26.50834888</v>
+        <v>12.3732266</v>
       </c>
       <c r="F27" t="n">
-        <v>12.3732266</v>
+        <v>16.88570324</v>
       </c>
       <c r="G27" t="n">
-        <v>16.88570324</v>
+        <v>5.174999509999999</v>
       </c>
       <c r="H27" t="n">
-        <v>5.174999509999999</v>
+        <v>10.18965648</v>
       </c>
       <c r="I27" t="n">
-        <v>10.18965648</v>
+        <v>5.14904886</v>
       </c>
       <c r="J27" t="n">
-        <v>5.14904886</v>
+        <v>12.32428043</v>
       </c>
       <c r="K27" t="n">
-        <v>12.32428043</v>
+        <v>7.23473412</v>
       </c>
       <c r="L27" t="n">
-        <v>7.23473412</v>
+        <v>21.39711191</v>
       </c>
       <c r="M27" t="n">
-        <v>21.39711191</v>
+        <v>9.234505710000002</v>
       </c>
     </row>
     <row r="28">
@@ -1571,37 +1575,37 @@
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>-0.49655746</v>
+        <v>-0.00517331</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.21799665</v>
+        <v>-0.00934741</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.48054054</v>
+        <v>-0.00324458</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.16923084</v>
+        <v>-0.006596299999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.31802269</v>
+        <v>-0.01406638</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.36590925</v>
+        <v>0.00652111</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.08474315</v>
+        <v>0.02914014</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.15341244</v>
+        <v>0.04879807</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.06900096</v>
+        <v>0.0566263</v>
       </c>
       <c r="L28" t="n">
-        <v>0.18393767</v>
+        <v>0.02465099</v>
       </c>
       <c r="M28" t="n">
-        <v>0.38545393</v>
+        <v>-0.00128256</v>
       </c>
     </row>
     <row r="29">
@@ -1612,37 +1616,37 @@
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>-0.03255481</v>
+        <v>-0.01281979</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.01281979</v>
+        <v>-0.00154904</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.00154904</v>
+        <v>-0.00032023</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.00032023</v>
+        <v>0.00658342</v>
       </c>
       <c r="G29" t="n">
-        <v>0.00658342</v>
+        <v>-0.00477515</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.00477515</v>
+        <v>0.004036490000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>0.004036490000000001</v>
+        <v>0.01033713</v>
       </c>
       <c r="J29" t="n">
-        <v>0.01033713</v>
+        <v>0.01825068</v>
       </c>
       <c r="K29" t="n">
-        <v>0.01825068</v>
+        <v>0.02746755</v>
       </c>
       <c r="L29" t="n">
-        <v>0.02746755</v>
+        <v>0.08414062</v>
       </c>
       <c r="M29" t="n">
-        <v>0.08414062</v>
+        <v>0.07506878</v>
       </c>
     </row>
     <row r="30">
@@ -1653,37 +1657,37 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>-0.01385127</v>
+        <v>-0.0008485099999999998</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0008485099999999998</v>
+        <v>-0.0025532</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0025532</v>
+        <v>0.00442858</v>
       </c>
       <c r="F30" t="n">
-        <v>0.00442858</v>
+        <v>-0.0001344399999999998</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.0001344399999999998</v>
+        <v>-0.00311901</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.00311901</v>
+        <v>-0.00135107</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.00135107</v>
+        <v>-0.00645304</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.00645304</v>
+        <v>-0.0007993899999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.0007993899999999999</v>
+        <v>0.008251139999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>0.008251139999999999</v>
+        <v>0.009377439999999999</v>
       </c>
       <c r="M30" t="n">
-        <v>0.009377439999999999</v>
+        <v>0.00523351</v>
       </c>
     </row>
     <row r="31">
@@ -1694,37 +1698,37 @@
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>-0.20942146</v>
+        <v>0.03501509000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>0.03501509000000001</v>
+        <v>-0.05155387</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.05155387</v>
+        <v>0.04295467</v>
       </c>
       <c r="F31" t="n">
-        <v>0.04295467</v>
+        <v>0.009156010000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>0.009156010000000001</v>
+        <v>-0.04370564</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.04370564</v>
+        <v>-0.07121751</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.07121751</v>
+        <v>0.0339659</v>
       </c>
       <c r="J31" t="n">
-        <v>0.0339659</v>
+        <v>0.001858120000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0.001858120000000001</v>
+        <v>0.10022693</v>
       </c>
       <c r="L31" t="n">
-        <v>0.10022693</v>
+        <v>0.21841852</v>
       </c>
       <c r="M31" t="n">
-        <v>0.21841852</v>
+        <v>0.10951461</v>
       </c>
     </row>
     <row r="32">
@@ -1735,37 +1739,37 @@
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>-1.58173283</v>
+        <v>0.79667627</v>
       </c>
       <c r="D32" t="n">
-        <v>0.79667627</v>
+        <v>-0.8938292</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.8938292</v>
+        <v>0.26859018</v>
       </c>
       <c r="F32" t="n">
-        <v>0.26859018</v>
+        <v>-1.1550498</v>
       </c>
       <c r="G32" t="n">
-        <v>-1.1550498</v>
+        <v>0.19597777</v>
       </c>
       <c r="H32" t="n">
-        <v>0.19597777</v>
+        <v>0.93832401</v>
       </c>
       <c r="I32" t="n">
-        <v>0.93832401</v>
+        <v>-0.60581137</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.60581137</v>
+        <v>-0.18124846</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.18124846</v>
+        <v>0.6026511899999999</v>
       </c>
       <c r="L32" t="n">
-        <v>0.6026511899999999</v>
+        <v>2.12415212</v>
       </c>
       <c r="M32" t="n">
-        <v>2.12415212</v>
+        <v>3.00018044</v>
       </c>
     </row>
     <row r="33">
@@ -1776,37 +1780,37 @@
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
-        <v>1.71917202</v>
+        <v>39.80493465</v>
       </c>
       <c r="D33" t="n">
-        <v>51.11736981</v>
+        <v>57.11406416</v>
       </c>
       <c r="E33" t="n">
-        <v>74.52305657000001</v>
+        <v>20.94755421</v>
       </c>
       <c r="F33" t="n">
-        <v>28.77819571</v>
+        <v>40.21449492</v>
       </c>
       <c r="G33" t="n">
-        <v>47.13405325</v>
+        <v>16.5613197</v>
       </c>
       <c r="H33" t="n">
-        <v>17.62821512</v>
+        <v>7.29471993</v>
       </c>
       <c r="I33" t="n">
-        <v>9.357429240000002</v>
+        <v>-17.72897884</v>
       </c>
       <c r="J33" t="n">
-        <v>-23.28926443</v>
+        <v>-12.77400785</v>
       </c>
       <c r="K33" t="n">
-        <v>-15.50397747</v>
+        <v>-8.503892480000001</v>
       </c>
       <c r="L33" t="n">
-        <v>-7.671519279999999</v>
+        <v>-15.01818866</v>
       </c>
       <c r="M33" t="n">
-        <v>-12.56496135</v>
+        <v>-18.7437909</v>
       </c>
     </row>
     <row r="34">
@@ -1817,37 +1821,37 @@
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
-        <v>0.03085148000000001</v>
+        <v>11.93656827</v>
       </c>
       <c r="D34" t="n">
-        <v>0.6241331099999999</v>
+        <v>18.03713291</v>
       </c>
       <c r="E34" t="n">
-        <v>0.6281405</v>
+        <v>8.362921139999999</v>
       </c>
       <c r="F34" t="n">
-        <v>0.5322796400000001</v>
+        <v>7.58644235</v>
       </c>
       <c r="G34" t="n">
-        <v>0.66688402</v>
+        <v>1.46144707</v>
       </c>
       <c r="H34" t="n">
-        <v>0.39455165</v>
+        <v>2.82433092</v>
       </c>
       <c r="I34" t="n">
-        <v>0.7616216099999999</v>
+        <v>-4.87857772</v>
       </c>
       <c r="J34" t="n">
-        <v>0.68170787</v>
+        <v>-2.69812083</v>
       </c>
       <c r="K34" t="n">
-        <v>0.03184879000000001</v>
+        <v>0.7800926499999999</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.05228055</v>
+        <v>2.22719978</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.22602753</v>
+        <v>19.154741</v>
       </c>
     </row>
     <row r="35">
@@ -1858,37 +1862,37 @@
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
-        <v>191.1411963</v>
+        <v>281.70180355</v>
       </c>
       <c r="D35" t="n">
-        <v>281.70180355</v>
+        <v>169.91598432</v>
       </c>
       <c r="E35" t="n">
-        <v>169.91598432</v>
+        <v>151.94936306</v>
       </c>
       <c r="F35" t="n">
-        <v>151.94936306</v>
+        <v>180.3735272</v>
       </c>
       <c r="G35" t="n">
-        <v>180.3735272</v>
+        <v>110.71375524</v>
       </c>
       <c r="H35" t="n">
-        <v>110.71375524</v>
+        <v>152.65296865</v>
       </c>
       <c r="I35" t="n">
-        <v>152.65296865</v>
+        <v>75.59350051</v>
       </c>
       <c r="J35" t="n">
-        <v>75.59350051</v>
+        <v>33.17521386</v>
       </c>
       <c r="K35" t="n">
-        <v>33.17521386</v>
+        <v>20.83055937</v>
       </c>
       <c r="L35" t="n">
-        <v>20.83055937</v>
+        <v>33.4962376</v>
       </c>
       <c r="M35" t="n">
-        <v>33.4962376</v>
+        <v>52.14474697</v>
       </c>
     </row>
     <row r="36">
@@ -1899,37 +1903,37 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>-13.62434275</v>
+        <v>-10.36056243</v>
       </c>
       <c r="D36" t="n">
-        <v>44.67745786</v>
+        <v>-17.9699727</v>
       </c>
       <c r="E36" t="n">
-        <v>59.54918461</v>
+        <v>-19.50289189</v>
       </c>
       <c r="F36" t="n">
-        <v>10.97615903</v>
+        <v>-28.50744565999999</v>
       </c>
       <c r="G36" t="n">
-        <v>-27.80501389</v>
+        <v>-22.80401095</v>
       </c>
       <c r="H36" t="n">
-        <v>-59.6302486</v>
+        <v>-20.90837859</v>
       </c>
       <c r="I36" t="n">
-        <v>-13.99488734</v>
+        <v>-1.72982895</v>
       </c>
       <c r="J36" t="n">
-        <v>-16.70895106</v>
+        <v>40.46050624</v>
       </c>
       <c r="K36" t="n">
-        <v>14.60214181</v>
+        <v>77.56024153</v>
       </c>
       <c r="L36" t="n">
-        <v>48.93507795999999</v>
+        <v>148.03386053</v>
       </c>
       <c r="M36" t="n">
-        <v>150.56891356</v>
+        <v>197.16667387</v>
       </c>
     </row>
     <row r="37">
@@ -1938,41 +1942,39 @@
           <t>汽車工業右下</t>
         </is>
       </c>
-      <c r="B37" t="n">
-        <v>0</v>
-      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>-26.29271288</v>
+        <v>48.5683695</v>
       </c>
       <c r="D37" t="n">
-        <v>55.89401399</v>
+        <v>49.76717430999999</v>
       </c>
       <c r="E37" t="n">
-        <v>57.36199072</v>
+        <v>53.62179476999999</v>
       </c>
       <c r="F37" t="n">
-        <v>50.70589786</v>
+        <v>51.38894450999999</v>
       </c>
       <c r="G37" t="n">
-        <v>50.21233335</v>
+        <v>31.34874639</v>
       </c>
       <c r="H37" t="n">
-        <v>31.40989619</v>
+        <v>57.0445669</v>
       </c>
       <c r="I37" t="n">
-        <v>72.00956927</v>
+        <v>5.79384727</v>
       </c>
       <c r="J37" t="n">
-        <v>-5.285111869999999</v>
+        <v>-5.19538949</v>
       </c>
       <c r="K37" t="n">
-        <v>1.539300029999999</v>
+        <v>9.171724370000002</v>
       </c>
       <c r="L37" t="n">
-        <v>26.40051155</v>
+        <v>26.86938084</v>
       </c>
       <c r="M37" t="n">
-        <v>40.88328293</v>
+        <v>29.86593954</v>
       </c>
     </row>
     <row r="38">
@@ -1983,37 +1985,37 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>-21.53170029</v>
+        <v>129.12775155</v>
       </c>
       <c r="D38" t="n">
-        <v>77.96595423999999</v>
+        <v>79.48442993</v>
       </c>
       <c r="E38" t="n">
-        <v>7.912929220000001</v>
+        <v>-14.19438346</v>
       </c>
       <c r="F38" t="n">
-        <v>-37.16771344</v>
+        <v>-65.42173446000001</v>
       </c>
       <c r="G38" t="n">
-        <v>-57.37401867000001</v>
+        <v>-109.56498236</v>
       </c>
       <c r="H38" t="n">
-        <v>-72.93299465999999</v>
+        <v>-12.6418104</v>
       </c>
       <c r="I38" t="n">
-        <v>-23.94618323</v>
+        <v>-36.88875274</v>
       </c>
       <c r="J38" t="n">
-        <v>-22.10185019</v>
+        <v>-41.23637979999999</v>
       </c>
       <c r="K38" t="n">
-        <v>-18.76744058</v>
+        <v>6.901248259999999</v>
       </c>
       <c r="L38" t="n">
-        <v>27.4358461</v>
+        <v>88.42745904</v>
       </c>
       <c r="M38" t="n">
-        <v>82.26197866</v>
+        <v>67.53254963000001</v>
       </c>
     </row>
     <row r="39">
@@ -2024,37 +2026,37 @@
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
-        <v>11.11791429</v>
+        <v>32.60895456999999</v>
       </c>
       <c r="D39" t="n">
-        <v>32.60895456999999</v>
+        <v>56.67209458</v>
       </c>
       <c r="E39" t="n">
-        <v>56.67209458</v>
+        <v>17.94407397</v>
       </c>
       <c r="F39" t="n">
-        <v>17.94407397</v>
+        <v>33.68792604</v>
       </c>
       <c r="G39" t="n">
-        <v>33.68792604</v>
+        <v>4.108083939999999</v>
       </c>
       <c r="H39" t="n">
-        <v>4.108083939999999</v>
+        <v>73.39446294</v>
       </c>
       <c r="I39" t="n">
-        <v>73.39446294</v>
+        <v>168.35310772</v>
       </c>
       <c r="J39" t="n">
-        <v>168.35310772</v>
+        <v>54.65563677999999</v>
       </c>
       <c r="K39" t="n">
-        <v>54.65563677999999</v>
+        <v>-40.04566426</v>
       </c>
       <c r="L39" t="n">
-        <v>-40.04566426</v>
+        <v>-65.28418285000001</v>
       </c>
       <c r="M39" t="n">
-        <v>-65.28418285000001</v>
+        <v>-32.76076323</v>
       </c>
     </row>
     <row r="40">
@@ -2065,37 +2067,37 @@
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>6.664288</v>
+        <v>7.2135412</v>
       </c>
       <c r="D40" t="n">
-        <v>7.2135412</v>
+        <v>0.08460432999999999</v>
       </c>
       <c r="E40" t="n">
-        <v>0.08460432999999999</v>
+        <v>-3.21255832</v>
       </c>
       <c r="F40" t="n">
-        <v>-3.21255832</v>
+        <v>-6.40072734</v>
       </c>
       <c r="G40" t="n">
-        <v>-6.40072734</v>
+        <v>-3.77333719</v>
       </c>
       <c r="H40" t="n">
-        <v>-3.77333719</v>
+        <v>1.57257904</v>
       </c>
       <c r="I40" t="n">
-        <v>1.57257904</v>
+        <v>-2.42404502</v>
       </c>
       <c r="J40" t="n">
-        <v>-2.42404502</v>
+        <v>-1.22188635</v>
       </c>
       <c r="K40" t="n">
-        <v>-1.22188635</v>
+        <v>2.19978092</v>
       </c>
       <c r="L40" t="n">
-        <v>2.19978092</v>
+        <v>3.24473775</v>
       </c>
       <c r="M40" t="n">
-        <v>3.24473775</v>
+        <v>8.124041649999999</v>
       </c>
     </row>
     <row r="41">
@@ -2106,37 +2108,37 @@
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
-        <v>-76.87109083</v>
+        <v>85.15477465000001</v>
       </c>
       <c r="D41" t="n">
-        <v>85.15477465000001</v>
+        <v>307.60971191</v>
       </c>
       <c r="E41" t="n">
-        <v>307.60971191</v>
+        <v>433.81361385</v>
       </c>
       <c r="F41" t="n">
-        <v>433.81361385</v>
+        <v>668.62466564</v>
       </c>
       <c r="G41" t="n">
-        <v>668.62466564</v>
+        <v>244.91801602</v>
       </c>
       <c r="H41" t="n">
-        <v>244.91801602</v>
+        <v>320.90370974</v>
       </c>
       <c r="I41" t="n">
-        <v>320.90370974</v>
+        <v>479.18507195</v>
       </c>
       <c r="J41" t="n">
-        <v>479.18507195</v>
+        <v>759.412483</v>
       </c>
       <c r="K41" t="n">
-        <v>759.412483</v>
+        <v>264.18557726</v>
       </c>
       <c r="L41" t="n">
-        <v>264.18557726</v>
+        <v>-87.18150326999999</v>
       </c>
       <c r="M41" t="n">
-        <v>-87.18150326999999</v>
+        <v>-42.95356518</v>
       </c>
     </row>
     <row r="42">
@@ -2147,37 +2149,37 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>-0.03895554999999994</v>
+        <v>5.28251554</v>
       </c>
       <c r="D42" t="n">
-        <v>5.28251554</v>
+        <v>13.5194183</v>
       </c>
       <c r="E42" t="n">
-        <v>13.5194183</v>
+        <v>7.9181412</v>
       </c>
       <c r="F42" t="n">
-        <v>7.9181412</v>
+        <v>12.13364822</v>
       </c>
       <c r="G42" t="n">
-        <v>12.13364822</v>
+        <v>8.904139349999999</v>
       </c>
       <c r="H42" t="n">
-        <v>8.904139349999999</v>
+        <v>16.35974226</v>
       </c>
       <c r="I42" t="n">
-        <v>16.35974226</v>
+        <v>7.98138634</v>
       </c>
       <c r="J42" t="n">
-        <v>7.98138634</v>
+        <v>11.47238579</v>
       </c>
       <c r="K42" t="n">
-        <v>11.47238579</v>
+        <v>7.112948609999999</v>
       </c>
       <c r="L42" t="n">
-        <v>7.112948609999999</v>
+        <v>19.89156343000001</v>
       </c>
       <c r="M42" t="n">
-        <v>19.89156343000001</v>
+        <v>18.45296431</v>
       </c>
     </row>
     <row r="43">
@@ -2188,37 +2190,37 @@
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
-        <v>-6.59199424</v>
+        <v>-0.7687650100000001</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.7743389900000001</v>
+        <v>-2.06135951</v>
       </c>
       <c r="E43" t="n">
-        <v>-2.06491569</v>
+        <v>-3.50289991</v>
       </c>
       <c r="F43" t="n">
-        <v>-3.50783653</v>
+        <v>-4.535342749999999</v>
       </c>
       <c r="G43" t="n">
-        <v>-4.53812706</v>
+        <v>-14.41262187</v>
       </c>
       <c r="H43" t="n">
-        <v>-14.41317415</v>
+        <v>-1.50831191</v>
       </c>
       <c r="I43" t="n">
-        <v>-1.510929369999999</v>
+        <v>12.83596378</v>
       </c>
       <c r="J43" t="n">
-        <v>12.8331323</v>
+        <v>11.3006092</v>
       </c>
       <c r="K43" t="n">
-        <v>11.29758388</v>
+        <v>16.35830021</v>
       </c>
       <c r="L43" t="n">
-        <v>16.35342315</v>
+        <v>15.73164693</v>
       </c>
       <c r="M43" t="n">
-        <v>15.72564051</v>
+        <v>16.78381093</v>
       </c>
     </row>
     <row r="44">
@@ -2231,37 +2233,37 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>-589.01427738</v>
+        <v>-104.39741896</v>
       </c>
       <c r="D44" t="n">
-        <v>-98.77886527999999</v>
+        <v>140.65027581</v>
       </c>
       <c r="E44" t="n">
-        <v>145.3450004</v>
+        <v>272.08639937</v>
       </c>
       <c r="F44" t="n">
-        <v>277.55423926</v>
+        <v>-25.901574</v>
       </c>
       <c r="G44" t="n">
-        <v>-19.27807085</v>
+        <v>-232.02450076</v>
       </c>
       <c r="H44" t="n">
-        <v>-223.77106371</v>
+        <v>-348.26715623</v>
       </c>
       <c r="I44" t="n">
-        <v>-341.37744412</v>
+        <v>-324.04951756</v>
       </c>
       <c r="J44" t="n">
-        <v>-315.56075778</v>
+        <v>-311.3992895</v>
       </c>
       <c r="K44" t="n">
-        <v>-305.12043534</v>
+        <v>-64.48894854</v>
       </c>
       <c r="L44" t="n">
-        <v>-63.14953864</v>
+        <v>21.50698964</v>
       </c>
       <c r="M44" t="n">
-        <v>24.78475663000001</v>
+        <v>64.43262997000001</v>
       </c>
     </row>
     <row r="45">
@@ -2272,37 +2274,37 @@
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
-        <v>-90.36117743999999</v>
+        <v>94.57192746</v>
       </c>
       <c r="D45" t="n">
-        <v>87.60529484</v>
+        <v>25.9908039</v>
       </c>
       <c r="E45" t="n">
-        <v>17.93952776000001</v>
+        <v>-126.85865153</v>
       </c>
       <c r="F45" t="n">
-        <v>-135.60866987</v>
+        <v>-104.9969829</v>
       </c>
       <c r="G45" t="n">
-        <v>-113.10474484</v>
+        <v>-252.91666599</v>
       </c>
       <c r="H45" t="n">
-        <v>-261.00454043</v>
+        <v>-259.89493722</v>
       </c>
       <c r="I45" t="n">
-        <v>-266.93876518</v>
+        <v>-218.99351342</v>
       </c>
       <c r="J45" t="n">
-        <v>-226.46165</v>
+        <v>39.62431711000001</v>
       </c>
       <c r="K45" t="n">
-        <v>33.38496002000001</v>
+        <v>-33.8640699</v>
       </c>
       <c r="L45" t="n">
-        <v>-36.41886179</v>
+        <v>78.35728603999999</v>
       </c>
       <c r="M45" t="n">
-        <v>78.03912475999999</v>
+        <v>-35.08354371</v>
       </c>
     </row>
     <row r="46">
@@ -2313,37 +2315,37 @@
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>-4.72339887</v>
+        <v>-1.49148739</v>
       </c>
       <c r="D46" t="n">
-        <v>-1.49148739</v>
+        <v>2.33220014</v>
       </c>
       <c r="E46" t="n">
-        <v>2.33220014</v>
+        <v>-2.68896906</v>
       </c>
       <c r="F46" t="n">
-        <v>-2.68896906</v>
+        <v>-6.34562959</v>
       </c>
       <c r="G46" t="n">
-        <v>-6.34562959</v>
+        <v>-8.065714099999999</v>
       </c>
       <c r="H46" t="n">
-        <v>-8.065714099999999</v>
+        <v>-5.8884915</v>
       </c>
       <c r="I46" t="n">
-        <v>-5.8884915</v>
+        <v>-5.95645232</v>
       </c>
       <c r="J46" t="n">
-        <v>-5.95645232</v>
+        <v>-5.16068395</v>
       </c>
       <c r="K46" t="n">
-        <v>-5.16068395</v>
+        <v>-5.24392124</v>
       </c>
       <c r="L46" t="n">
-        <v>-5.24392124</v>
+        <v>-1.42682006</v>
       </c>
       <c r="M46" t="n">
-        <v>-1.42682006</v>
+        <v>-1.55756925</v>
       </c>
     </row>
     <row r="47">
@@ -2352,41 +2354,39 @@
           <t>紡織纖維右下</t>
         </is>
       </c>
-      <c r="B47" t="n">
-        <v>0</v>
-      </c>
+      <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>-106.93869348</v>
+        <v>51.69443244</v>
       </c>
       <c r="D47" t="n">
-        <v>50.50353103</v>
+        <v>112.31552985</v>
       </c>
       <c r="E47" t="n">
-        <v>116.03655748</v>
+        <v>53.45619471</v>
       </c>
       <c r="F47" t="n">
-        <v>57.72593153</v>
+        <v>95.04986186999999</v>
       </c>
       <c r="G47" t="n">
-        <v>95.37074805999998</v>
+        <v>9.407378970000002</v>
       </c>
       <c r="H47" t="n">
-        <v>11.02279836</v>
+        <v>39.68573421</v>
       </c>
       <c r="I47" t="n">
-        <v>34.5949691</v>
+        <v>4.959421839999997</v>
       </c>
       <c r="J47" t="n">
-        <v>4.375589389999996</v>
+        <v>20.79778082</v>
       </c>
       <c r="K47" t="n">
-        <v>21.94380789</v>
+        <v>26.43966846</v>
       </c>
       <c r="L47" t="n">
-        <v>26.94948555</v>
+        <v>2.098726649999999</v>
       </c>
       <c r="M47" t="n">
-        <v>2.943271589999999</v>
+        <v>-22.66043861</v>
       </c>
     </row>
     <row r="48">
@@ -2397,37 +2397,37 @@
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
-        <v>-0.03830798</v>
+        <v>0.60223238</v>
       </c>
       <c r="D48" t="n">
-        <v>0.05300252</v>
+        <v>0.39113424</v>
       </c>
       <c r="E48" t="n">
-        <v>0.13976307</v>
+        <v>0.55102869</v>
       </c>
       <c r="F48" t="n">
-        <v>0.48577608</v>
+        <v>0.28993202</v>
       </c>
       <c r="G48" t="n">
-        <v>0.27865859</v>
+        <v>0.02778382</v>
       </c>
       <c r="H48" t="n">
-        <v>0.05937113000000001</v>
+        <v>0.06734879000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>0.09258559</v>
+        <v>-0.10231698</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.04205779</v>
+        <v>-0.002836350000000003</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.10030131</v>
+        <v>1.65312477</v>
       </c>
       <c r="L48" t="n">
-        <v>0.2635332</v>
+        <v>1.32675854</v>
       </c>
       <c r="M48" t="n">
-        <v>0.7852534600000001</v>
+        <v>0.2550852199999999</v>
       </c>
     </row>
     <row r="49">
@@ -2438,37 +2438,37 @@
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>-39.79114603</v>
+        <v>-25.86812985</v>
       </c>
       <c r="D49" t="n">
-        <v>-25.86812985</v>
+        <v>-15.37702207</v>
       </c>
       <c r="E49" t="n">
-        <v>-15.37702207</v>
+        <v>-21.86573385</v>
       </c>
       <c r="F49" t="n">
-        <v>-21.86573385</v>
+        <v>-5.271030309999998</v>
       </c>
       <c r="G49" t="n">
-        <v>-5.271030309999998</v>
+        <v>10.19355404</v>
       </c>
       <c r="H49" t="n">
-        <v>10.19355404</v>
+        <v>-56.44455119</v>
       </c>
       <c r="I49" t="n">
-        <v>-56.44455119</v>
+        <v>-46.45714444000001</v>
       </c>
       <c r="J49" t="n">
-        <v>-46.45714444000001</v>
+        <v>-43.83128722999999</v>
       </c>
       <c r="K49" t="n">
-        <v>-43.83128722999999</v>
+        <v>-124.85406477</v>
       </c>
       <c r="L49" t="n">
-        <v>-124.85406477</v>
+        <v>-35.45945545</v>
       </c>
       <c r="M49" t="n">
-        <v>-35.45945545</v>
+        <v>-130.49968955</v>
       </c>
     </row>
     <row r="50">
@@ -2479,37 +2479,37 @@
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
-        <v>-26.75564822</v>
+        <v>-29.6747849</v>
       </c>
       <c r="D50" t="n">
-        <v>-29.6747849</v>
+        <v>-9.074995439999997</v>
       </c>
       <c r="E50" t="n">
-        <v>-9.074995439999997</v>
+        <v>-6.02440684</v>
       </c>
       <c r="F50" t="n">
-        <v>-6.02440684</v>
+        <v>-10.76360972</v>
       </c>
       <c r="G50" t="n">
-        <v>-10.76360972</v>
+        <v>-6.295704290000001</v>
       </c>
       <c r="H50" t="n">
-        <v>-6.295704290000001</v>
+        <v>4.70272614</v>
       </c>
       <c r="I50" t="n">
-        <v>4.70272614</v>
+        <v>-5.524311600000001</v>
       </c>
       <c r="J50" t="n">
-        <v>-5.524311600000001</v>
+        <v>2.53485937</v>
       </c>
       <c r="K50" t="n">
-        <v>2.53485937</v>
+        <v>-2.54366476</v>
       </c>
       <c r="L50" t="n">
-        <v>-2.54366476</v>
+        <v>4.03323023</v>
       </c>
       <c r="M50" t="n">
-        <v>4.03323023</v>
+        <v>-4.208008479999999</v>
       </c>
     </row>
     <row r="51">
@@ -2520,37 +2520,37 @@
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>-90.38974037</v>
+        <v>-46.76736808</v>
       </c>
       <c r="D51" t="n">
-        <v>-46.76736808</v>
+        <v>-18.80448768</v>
       </c>
       <c r="E51" t="n">
-        <v>-18.80448768</v>
+        <v>-3.937506679999998</v>
       </c>
       <c r="F51" t="n">
-        <v>-3.937506679999998</v>
+        <v>-28.13410102</v>
       </c>
       <c r="G51" t="n">
-        <v>-28.13410102</v>
+        <v>7.48600141</v>
       </c>
       <c r="H51" t="n">
-        <v>7.48600141</v>
+        <v>-7.01302978</v>
       </c>
       <c r="I51" t="n">
-        <v>-7.01302978</v>
+        <v>-24.94529791</v>
       </c>
       <c r="J51" t="n">
-        <v>-24.94529791</v>
+        <v>30.8624361</v>
       </c>
       <c r="K51" t="n">
-        <v>30.8624361</v>
+        <v>11.07913789</v>
       </c>
       <c r="L51" t="n">
-        <v>11.07913789</v>
+        <v>52.57312343</v>
       </c>
       <c r="M51" t="n">
-        <v>52.57312343</v>
+        <v>37.14575924</v>
       </c>
     </row>
     <row r="52">
@@ -2561,37 +2561,37 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>-202.43466048</v>
+        <v>62.50215</v>
       </c>
       <c r="D52" t="n">
-        <v>42.45403700999999</v>
+        <v>426.79006651</v>
       </c>
       <c r="E52" t="n">
-        <v>353.5626931</v>
+        <v>557.9386459900001</v>
       </c>
       <c r="F52" t="n">
-        <v>373.92728289</v>
+        <v>166.34689068</v>
       </c>
       <c r="G52" t="n">
-        <v>97.26785201</v>
+        <v>-33.08596268</v>
       </c>
       <c r="H52" t="n">
-        <v>-4.230439369999997</v>
+        <v>10.94663334000001</v>
       </c>
       <c r="I52" t="n">
-        <v>105.44977854</v>
+        <v>-242.48694746</v>
       </c>
       <c r="J52" t="n">
-        <v>-103.48180697</v>
+        <v>176.69649829</v>
       </c>
       <c r="K52" t="n">
-        <v>214.35774299</v>
+        <v>173.3919018</v>
       </c>
       <c r="L52" t="n">
-        <v>147.19409253</v>
+        <v>534.26192584</v>
       </c>
       <c r="M52" t="n">
-        <v>463.05754523</v>
+        <v>553.1683261099998</v>
       </c>
     </row>
     <row r="53">
@@ -2602,37 +2602,37 @@
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>-186.39561258</v>
+        <v>0.5799572000000005</v>
       </c>
       <c r="D53" t="n">
-        <v>-23.63700619</v>
+        <v>10.35363797</v>
       </c>
       <c r="E53" t="n">
-        <v>93.53864661</v>
+        <v>57.30598314999999</v>
       </c>
       <c r="F53" t="n">
-        <v>211.94002794</v>
+        <v>29.58738631</v>
       </c>
       <c r="G53" t="n">
-        <v>90.15224259</v>
+        <v>-1.887194979999999</v>
       </c>
       <c r="H53" t="n">
-        <v>45.78636706</v>
+        <v>3.32307619</v>
       </c>
       <c r="I53" t="n">
-        <v>143.7428402</v>
+        <v>-21.73914643</v>
       </c>
       <c r="J53" t="n">
-        <v>11.27969625</v>
+        <v>-5.15073246</v>
       </c>
       <c r="K53" t="n">
-        <v>-16.07925227</v>
+        <v>4.636715280000002</v>
       </c>
       <c r="L53" t="n">
-        <v>65.65411177</v>
+        <v>-6.085364190000002</v>
       </c>
       <c r="M53" t="n">
-        <v>28.22066404999999</v>
+        <v>14.57276881</v>
       </c>
     </row>
     <row r="54">
@@ -2643,37 +2643,37 @@
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>-59.44268134999999</v>
+        <v>163.55350801</v>
       </c>
       <c r="D54" t="n">
-        <v>207.81858439</v>
+        <v>519.42942119</v>
       </c>
       <c r="E54" t="n">
-        <v>509.47178596</v>
+        <v>574.4871258400001</v>
       </c>
       <c r="F54" t="n">
-        <v>603.8644441499999</v>
+        <v>260.62135112</v>
       </c>
       <c r="G54" t="n">
-        <v>269.13553351</v>
+        <v>100.29771459</v>
       </c>
       <c r="H54" t="n">
-        <v>23.76862924</v>
+        <v>229.41442989</v>
       </c>
       <c r="I54" t="n">
-        <v>-5.508479319999998</v>
+        <v>15.19915629</v>
       </c>
       <c r="J54" t="n">
-        <v>-156.82482688</v>
+        <v>80.41068551000001</v>
       </c>
       <c r="K54" t="n">
-        <v>53.67796062</v>
+        <v>94.80529926999999</v>
       </c>
       <c r="L54" t="n">
-        <v>59.98571205</v>
+        <v>125.0805232</v>
       </c>
       <c r="M54" t="n">
-        <v>161.97887557</v>
+        <v>265.36350072</v>
       </c>
     </row>
     <row r="55">
@@ -2684,37 +2684,37 @@
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>-49.27642904</v>
+        <v>-43.16208043</v>
       </c>
       <c r="D55" t="n">
-        <v>-43.15241365</v>
+        <v>-42.74174993</v>
       </c>
       <c r="E55" t="n">
-        <v>-42.73856727</v>
+        <v>-30.60167928</v>
       </c>
       <c r="F55" t="n">
-        <v>-30.59709092</v>
+        <v>1.722041200000001</v>
       </c>
       <c r="G55" t="n">
-        <v>1.71896167</v>
+        <v>-3.650744</v>
       </c>
       <c r="H55" t="n">
-        <v>-3.66064519</v>
+        <v>6.78482776</v>
       </c>
       <c r="I55" t="n">
-        <v>6.780631179999999</v>
+        <v>-4.03840124</v>
       </c>
       <c r="J55" t="n">
-        <v>-4.03954524</v>
+        <v>17.67687168</v>
       </c>
       <c r="K55" t="n">
-        <v>17.6737899</v>
+        <v>27.55673009</v>
       </c>
       <c r="L55" t="n">
-        <v>27.54426674</v>
+        <v>42.07247027</v>
       </c>
       <c r="M55" t="n">
-        <v>42.05846305</v>
+        <v>41.65727162</v>
       </c>
     </row>
     <row r="56">
@@ -2725,37 +2725,37 @@
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>-2.59580502</v>
+        <v>-0.4970161599999999</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.4970161599999999</v>
+        <v>-3.79917129</v>
       </c>
       <c r="E56" t="n">
-        <v>-3.79917129</v>
+        <v>-3.020980170000001</v>
       </c>
       <c r="F56" t="n">
-        <v>-3.020980170000001</v>
+        <v>-3.08701631</v>
       </c>
       <c r="G56" t="n">
-        <v>-3.08701631</v>
+        <v>-3.15672715</v>
       </c>
       <c r="H56" t="n">
-        <v>-3.15672715</v>
+        <v>-1.54350305</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.54350305</v>
+        <v>-4.72110351</v>
       </c>
       <c r="J56" t="n">
-        <v>-4.72110351</v>
+        <v>-3.36279103</v>
       </c>
       <c r="K56" t="n">
-        <v>-3.3628632</v>
+        <v>3.84718283</v>
       </c>
       <c r="L56" t="n">
-        <v>3.84713373</v>
+        <v>7.88656417</v>
       </c>
       <c r="M56" t="n">
-        <v>7.88635447</v>
+        <v>3.20005212</v>
       </c>
     </row>
     <row r="57">
@@ -2766,37 +2766,37 @@
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
-        <v>-10.34541521</v>
+        <v>-2.00403628</v>
       </c>
       <c r="D57" t="n">
-        <v>-2.01370306</v>
+        <v>-8.248237769999999</v>
       </c>
       <c r="E57" t="n">
-        <v>-8.25142043</v>
+        <v>-7.66186328</v>
       </c>
       <c r="F57" t="n">
-        <v>-7.666451640000001</v>
+        <v>1.02349499</v>
       </c>
       <c r="G57" t="n">
-        <v>1.02657452</v>
+        <v>-4.48970625</v>
       </c>
       <c r="H57" t="n">
-        <v>-4.479805059999999</v>
+        <v>-6.18675242</v>
       </c>
       <c r="I57" t="n">
-        <v>-6.18255584</v>
+        <v>-8.349715570000001</v>
       </c>
       <c r="J57" t="n">
-        <v>-8.348571570000001</v>
+        <v>0.155641</v>
       </c>
       <c r="K57" t="n">
-        <v>0.15872278</v>
+        <v>20.28296714</v>
       </c>
       <c r="L57" t="n">
-        <v>20.29543049</v>
+        <v>11.7472462</v>
       </c>
       <c r="M57" t="n">
-        <v>11.76125342</v>
+        <v>6.32177035</v>
       </c>
     </row>
     <row r="58">
@@ -2807,37 +2807,37 @@
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>-41.64196783</v>
+        <v>7.82421167</v>
       </c>
       <c r="D58" t="n">
-        <v>7.818857879999999</v>
+        <v>-8.729579919999999</v>
       </c>
       <c r="E58" t="n">
-        <v>-8.73737841</v>
+        <v>-35.23087908</v>
       </c>
       <c r="F58" t="n">
-        <v>-35.23401704</v>
+        <v>-57.93050757</v>
       </c>
       <c r="G58" t="n">
-        <v>-57.93461414</v>
+        <v>-68.29303842</v>
       </c>
       <c r="H58" t="n">
-        <v>-68.29465833</v>
+        <v>-8.43867049</v>
       </c>
       <c r="I58" t="n">
-        <v>-8.434151510000001</v>
+        <v>-47.65902154</v>
       </c>
       <c r="J58" t="n">
-        <v>-47.65870399000001</v>
+        <v>7.732804339999999</v>
       </c>
       <c r="K58" t="n">
-        <v>7.33809499</v>
+        <v>42.01228871</v>
       </c>
       <c r="L58" t="n">
-        <v>15.97438006</v>
+        <v>64.01109449</v>
       </c>
       <c r="M58" t="n">
-        <v>20.44942311</v>
+        <v>37.16176833999999</v>
       </c>
     </row>
     <row r="59">
@@ -2848,37 +2848,37 @@
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
-        <v>1.42688672</v>
+        <v>1.64936867</v>
       </c>
       <c r="D59" t="n">
-        <v>1.65472246</v>
+        <v>0.75722357</v>
       </c>
       <c r="E59" t="n">
-        <v>0.7650220599999999</v>
+        <v>0.24960995</v>
       </c>
       <c r="F59" t="n">
-        <v>0.25274791</v>
+        <v>1.15325215</v>
       </c>
       <c r="G59" t="n">
-        <v>1.15735872</v>
+        <v>0.04282362999999999</v>
       </c>
       <c r="H59" t="n">
-        <v>0.04444354</v>
+        <v>0.7658311999999999</v>
       </c>
       <c r="I59" t="n">
-        <v>0.76131222</v>
+        <v>-0.23659738</v>
       </c>
       <c r="J59" t="n">
-        <v>-0.23691493</v>
+        <v>-0.73760565</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.71950387</v>
+        <v>0.5643298</v>
       </c>
       <c r="L59" t="n">
-        <v>0.5766634</v>
+        <v>1.16138393</v>
       </c>
       <c r="M59" t="n">
-        <v>1.15600886</v>
+        <v>1.87547844</v>
       </c>
     </row>
     <row r="60">
@@ -2889,37 +2889,37 @@
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
-        <v>-72.81776050000001</v>
+        <v>-43.80415462</v>
       </c>
       <c r="D60" t="n">
-        <v>-43.80409290999999</v>
+        <v>-59.54155184</v>
       </c>
       <c r="E60" t="n">
-        <v>-59.54131665</v>
+        <v>-59.83004735</v>
       </c>
       <c r="F60" t="n">
-        <v>-59.82970831</v>
+        <v>-20.09411328</v>
       </c>
       <c r="G60" t="n">
-        <v>-20.09390547</v>
+        <v>-30.92602812</v>
       </c>
       <c r="H60" t="n">
-        <v>-30.92586359</v>
+        <v>-15.12563885</v>
       </c>
       <c r="I60" t="n">
-        <v>-15.12555268</v>
+        <v>19.01618865</v>
       </c>
       <c r="J60" t="n">
-        <v>19.01608918</v>
+        <v>32.19645427</v>
       </c>
       <c r="K60" t="n">
-        <v>32.19645122</v>
+        <v>66.00343606</v>
       </c>
       <c r="L60" t="n">
-        <v>66.00356958</v>
+        <v>95.20223728000001</v>
       </c>
       <c r="M60" t="n">
-        <v>95.20248759</v>
+        <v>52.08611158</v>
       </c>
     </row>
     <row r="61">
@@ -2930,37 +2930,37 @@
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
-        <v>-0.00691126</v>
+        <v>0.0007849500000000001</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.0001974500000000001</v>
+        <v>-0.0023249</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.00328995</v>
+        <v>-0.00285701</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.00367163</v>
+        <v>-0.0007670700000000002</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.00149519</v>
+        <v>-0.00377332</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.0044427</v>
+        <v>-0.00373142</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.00424425</v>
+        <v>-0.00726259</v>
       </c>
       <c r="J61" t="n">
-        <v>-0.00749634</v>
+        <v>-0.0029527</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.0031783</v>
+        <v>-0.00233591</v>
       </c>
       <c r="L61" t="n">
-        <v>-0.00248349</v>
+        <v>0.007300940000000001</v>
       </c>
       <c r="M61" t="n">
-        <v>0.00740013</v>
+        <v>0.00539476</v>
       </c>
     </row>
     <row r="62">
@@ -2971,37 +2971,37 @@
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>-50.08831059</v>
+        <v>3.88186996</v>
       </c>
       <c r="D62" t="n">
-        <v>3.88192015</v>
+        <v>-6.97413192</v>
       </c>
       <c r="E62" t="n">
-        <v>-6.974047229999999</v>
+        <v>-18.18744687</v>
       </c>
       <c r="F62" t="n">
-        <v>-18.18771042</v>
+        <v>54.93204613</v>
       </c>
       <c r="G62" t="n">
-        <v>54.93208556</v>
+        <v>-0.1321520299999996</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.1346072799999995</v>
+        <v>15.73858595</v>
       </c>
       <c r="I62" t="n">
-        <v>15.73484465</v>
+        <v>-2.45245943</v>
       </c>
       <c r="J62" t="n">
-        <v>-2.45423797</v>
+        <v>28.65209756</v>
       </c>
       <c r="K62" t="n">
-        <v>28.65151699</v>
+        <v>47.66561987</v>
       </c>
       <c r="L62" t="n">
-        <v>47.66554514</v>
+        <v>94.8631642</v>
       </c>
       <c r="M62" t="n">
-        <v>94.86275925</v>
+        <v>46.74765190000001</v>
       </c>
     </row>
     <row r="63">
@@ -3012,37 +3012,37 @@
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>-0.0001746</v>
+        <v>0.00012031</v>
       </c>
       <c r="D63" t="n">
-        <v>0.00012031</v>
+        <v>-2.134999999999999e-05</v>
       </c>
       <c r="E63" t="n">
-        <v>-2.134999999999999e-05</v>
+        <v>0.00012761</v>
       </c>
       <c r="F63" t="n">
-        <v>0.00012761</v>
+        <v>0.00014581</v>
       </c>
       <c r="G63" t="n">
-        <v>0.00014581</v>
+        <v>0.00033086</v>
       </c>
       <c r="H63" t="n">
-        <v>0.00033086</v>
+        <v>0.0004248200000000001</v>
       </c>
       <c r="I63" t="n">
-        <v>0.0004248200000000001</v>
+        <v>0.00090755</v>
       </c>
       <c r="J63" t="n">
-        <v>0.00090755</v>
+        <v>0.00103174</v>
       </c>
       <c r="K63" t="n">
-        <v>0.00103174</v>
+        <v>0.0009914099999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>0.0009914099999999999</v>
+        <v>6.247e-05</v>
       </c>
       <c r="M63" t="n">
-        <v>6.247e-05</v>
+        <v>0.0004044</v>
       </c>
     </row>
     <row r="64">
@@ -3053,37 +3053,37 @@
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
-        <v>-0.00037977</v>
+        <v>-0.00013752</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.00013752</v>
+        <v>-0.00019394</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.00019394</v>
+        <v>-0.00018756</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.00018756</v>
+        <v>-0.00024988</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.00024988</v>
+        <v>-0.00027272</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.00027272</v>
+        <v>-0.0002611</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.0002611</v>
+        <v>-0.00027651</v>
       </c>
       <c r="J64" t="n">
-        <v>-0.00027651</v>
+        <v>-0.0002609000000000001</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.0002609000000000001</v>
+        <v>5.814e-05</v>
       </c>
       <c r="L64" t="n">
-        <v>5.814e-05</v>
+        <v>0.00018835</v>
       </c>
       <c r="M64" t="n">
-        <v>0.00018835</v>
+        <v>2.243e-05</v>
       </c>
     </row>
     <row r="65">
@@ -3094,37 +3094,37 @@
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
-        <v>806.41169386</v>
+        <v>466.0886352000001</v>
       </c>
       <c r="D65" t="n">
-        <v>455.92403099</v>
+        <v>639.80339804</v>
       </c>
       <c r="E65" t="n">
-        <v>660.73977532</v>
+        <v>565.26139745</v>
       </c>
       <c r="F65" t="n">
-        <v>618.75750132</v>
+        <v>1107.65330267</v>
       </c>
       <c r="G65" t="n">
-        <v>1100.74911451</v>
+        <v>908.9790999300001</v>
       </c>
       <c r="H65" t="n">
-        <v>916.6325839000001</v>
+        <v>245.79030677</v>
       </c>
       <c r="I65" t="n">
-        <v>224.78400483</v>
+        <v>523.4402324600001</v>
       </c>
       <c r="J65" t="n">
-        <v>441.09990429</v>
+        <v>30.59805887999999</v>
       </c>
       <c r="K65" t="n">
-        <v>4.457560460000001</v>
+        <v>205.16998145</v>
       </c>
       <c r="L65" t="n">
-        <v>173.71186101</v>
+        <v>749.09681401</v>
       </c>
       <c r="M65" t="n">
-        <v>727.45402683</v>
+        <v>201.40933403</v>
       </c>
     </row>
     <row r="66">
@@ -3133,39 +3133,41 @@
           <t>通信網路業右下</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr"/>
+      <c r="B66" t="n">
+        <v>0</v>
+      </c>
       <c r="C66" t="n">
-        <v>-35.84064752</v>
+        <v>1.80144518</v>
       </c>
       <c r="D66" t="n">
-        <v>1.80769688</v>
+        <v>19.8069366</v>
       </c>
       <c r="E66" t="n">
-        <v>19.80204006</v>
+        <v>16.12262531</v>
       </c>
       <c r="F66" t="n">
-        <v>16.11997608</v>
+        <v>15.01315617</v>
       </c>
       <c r="G66" t="n">
-        <v>15.01740377</v>
+        <v>19.88208755</v>
       </c>
       <c r="H66" t="n">
-        <v>19.88991495</v>
+        <v>-17.25743567</v>
       </c>
       <c r="I66" t="n">
-        <v>-17.26272065</v>
+        <v>-53.04367808</v>
       </c>
       <c r="J66" t="n">
-        <v>-53.03456827</v>
+        <v>-4.322311980000001</v>
       </c>
       <c r="K66" t="n">
-        <v>-4.480187010000003</v>
+        <v>31.29953269</v>
       </c>
       <c r="L66" t="n">
-        <v>31.26898156</v>
+        <v>-1.56919705</v>
       </c>
       <c r="M66" t="n">
-        <v>-1.41045304</v>
+        <v>0.9433941799999992</v>
       </c>
     </row>
     <row r="67">
@@ -3176,37 +3178,37 @@
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>-70.21889269999998</v>
+        <v>261.10249401</v>
       </c>
       <c r="D67" t="n">
-        <v>209.95166032</v>
+        <v>234.53640338</v>
       </c>
       <c r="E67" t="n">
-        <v>189.33371313</v>
+        <v>554.9897066300001</v>
       </c>
       <c r="F67" t="n">
-        <v>497.2165509700001</v>
+        <v>795.63674016</v>
       </c>
       <c r="G67" t="n">
-        <v>817.3993215400001</v>
+        <v>300.45455142</v>
       </c>
       <c r="H67" t="n">
-        <v>282.53601744</v>
+        <v>288.66631953</v>
       </c>
       <c r="I67" t="n">
-        <v>290.39567986</v>
+        <v>56.95423210999999</v>
       </c>
       <c r="J67" t="n">
-        <v>140.56837645</v>
+        <v>319.39536125</v>
       </c>
       <c r="K67" t="n">
-        <v>355.81218004</v>
+        <v>111.32482997</v>
       </c>
       <c r="L67" t="n">
-        <v>138.70086394</v>
+        <v>106.38826172</v>
       </c>
       <c r="M67" t="n">
-        <v>147.23973732</v>
+        <v>143.20773013</v>
       </c>
     </row>
     <row r="68">
@@ -3217,37 +3219,37 @@
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>1.48615941</v>
+        <v>6.954071790000001</v>
       </c>
       <c r="D68" t="n">
-        <v>6.954071790000001</v>
+        <v>8.895559609999999</v>
       </c>
       <c r="E68" t="n">
-        <v>8.895559609999999</v>
+        <v>25.77768484</v>
       </c>
       <c r="F68" t="n">
-        <v>25.77768484</v>
+        <v>7.5358798</v>
       </c>
       <c r="G68" t="n">
-        <v>7.5358798</v>
+        <v>-2.18453111</v>
       </c>
       <c r="H68" t="n">
-        <v>-2.18453111</v>
+        <v>-4.28064262</v>
       </c>
       <c r="I68" t="n">
-        <v>-4.28064262</v>
+        <v>-9.848016550000001</v>
       </c>
       <c r="J68" t="n">
-        <v>-9.848016550000001</v>
+        <v>-11.75977663</v>
       </c>
       <c r="K68" t="n">
-        <v>-11.75977663</v>
+        <v>-14.45543988</v>
       </c>
       <c r="L68" t="n">
-        <v>-14.45543988</v>
+        <v>-8.60103045</v>
       </c>
       <c r="M68" t="n">
-        <v>-8.60103045</v>
+        <v>1.481096</v>
       </c>
     </row>
     <row r="69">
@@ -3258,37 +3260,37 @@
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>-3.03497446</v>
+        <v>-1.57228821</v>
       </c>
       <c r="D69" t="n">
-        <v>-1.57228821</v>
+        <v>-0.33839224</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.33839224</v>
+        <v>-1.43394215</v>
       </c>
       <c r="F69" t="n">
-        <v>-1.43394215</v>
+        <v>-1.69268373</v>
       </c>
       <c r="G69" t="n">
-        <v>-1.69268373</v>
+        <v>-3.23010772</v>
       </c>
       <c r="H69" t="n">
-        <v>-3.23010772</v>
+        <v>-3.39045584</v>
       </c>
       <c r="I69" t="n">
-        <v>-3.39045584</v>
+        <v>-4.06147909</v>
       </c>
       <c r="J69" t="n">
-        <v>-4.06147909</v>
+        <v>-3.60733925</v>
       </c>
       <c r="K69" t="n">
-        <v>-3.60733925</v>
+        <v>-1.16033294</v>
       </c>
       <c r="L69" t="n">
-        <v>-1.16033294</v>
+        <v>-1.55525517</v>
       </c>
       <c r="M69" t="n">
-        <v>-1.55525517</v>
+        <v>0.15859867</v>
       </c>
     </row>
     <row r="70">
@@ -3299,37 +3301,37 @@
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>-38.78366583</v>
+        <v>-10.01798231</v>
       </c>
       <c r="D70" t="n">
-        <v>-10.01798231</v>
+        <v>-16.91394174</v>
       </c>
       <c r="E70" t="n">
-        <v>-16.91394174</v>
+        <v>-16.82706139</v>
       </c>
       <c r="F70" t="n">
-        <v>-16.82706139</v>
+        <v>-21.49287157</v>
       </c>
       <c r="G70" t="n">
-        <v>-21.49287157</v>
+        <v>-29.75249595</v>
       </c>
       <c r="H70" t="n">
-        <v>-29.75249595</v>
+        <v>-5.49167339</v>
       </c>
       <c r="I70" t="n">
-        <v>-5.49167339</v>
+        <v>-6.985563310000001</v>
       </c>
       <c r="J70" t="n">
-        <v>-6.985563310000001</v>
+        <v>6.14054282</v>
       </c>
       <c r="K70" t="n">
-        <v>6.14054282</v>
+        <v>22.89727625</v>
       </c>
       <c r="L70" t="n">
-        <v>22.89727625</v>
+        <v>39.58487804</v>
       </c>
       <c r="M70" t="n">
-        <v>39.58487804</v>
+        <v>49.03197814</v>
       </c>
     </row>
     <row r="71">
@@ -3340,37 +3342,37 @@
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
-        <v>-67.66731897</v>
+        <v>86.08082459000001</v>
       </c>
       <c r="D71" t="n">
-        <v>86.08082459000001</v>
+        <v>65.03796482999999</v>
       </c>
       <c r="E71" t="n">
-        <v>65.03796482999999</v>
+        <v>7.475289409999997</v>
       </c>
       <c r="F71" t="n">
-        <v>7.475289409999997</v>
+        <v>-64.07427258999999</v>
       </c>
       <c r="G71" t="n">
-        <v>-64.07427258999999</v>
+        <v>-115.50237892</v>
       </c>
       <c r="H71" t="n">
-        <v>-115.50237892</v>
+        <v>-11.79256974999999</v>
       </c>
       <c r="I71" t="n">
-        <v>-11.79256974999999</v>
+        <v>-141.47987787</v>
       </c>
       <c r="J71" t="n">
-        <v>-141.47987787</v>
+        <v>-101.90599359</v>
       </c>
       <c r="K71" t="n">
-        <v>-101.90599359</v>
+        <v>-27.86393122</v>
       </c>
       <c r="L71" t="n">
-        <v>-27.86393122</v>
+        <v>-19.72376035</v>
       </c>
       <c r="M71" t="n">
-        <v>-19.72376035</v>
+        <v>-80.99866675</v>
       </c>
     </row>
     <row r="72">
@@ -3381,37 +3383,37 @@
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>2.85641621</v>
+        <v>18.48568502</v>
       </c>
       <c r="D72" t="n">
-        <v>18.48568502</v>
+        <v>16.39634759</v>
       </c>
       <c r="E72" t="n">
-        <v>16.39634759</v>
+        <v>4.281030289999999</v>
       </c>
       <c r="F72" t="n">
-        <v>4.281030289999999</v>
+        <v>5.539278160000001</v>
       </c>
       <c r="G72" t="n">
-        <v>5.539278160000001</v>
+        <v>-2.54610903</v>
       </c>
       <c r="H72" t="n">
-        <v>-2.54610903</v>
+        <v>-1.68230068</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.68230068</v>
+        <v>-10.98006195</v>
       </c>
       <c r="J72" t="n">
-        <v>-10.98006195</v>
+        <v>0.2389688799999998</v>
       </c>
       <c r="K72" t="n">
-        <v>0.2389688799999998</v>
+        <v>11.07624471</v>
       </c>
       <c r="L72" t="n">
-        <v>11.07624471</v>
+        <v>3.90076889</v>
       </c>
       <c r="M72" t="n">
-        <v>3.90076889</v>
+        <v>-10.60413652</v>
       </c>
     </row>
     <row r="73">
@@ -3422,37 +3424,37 @@
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
-        <v>-1283.68705536</v>
+        <v>-479.96587393</v>
       </c>
       <c r="D73" t="n">
-        <v>-482.7115760200001</v>
+        <v>-775.45050197</v>
       </c>
       <c r="E73" t="n">
-        <v>-765.1041760999999</v>
+        <v>-1055.71776824</v>
       </c>
       <c r="F73" t="n">
-        <v>-1040.79625587</v>
+        <v>-1344.25654867</v>
       </c>
       <c r="G73" t="n">
-        <v>-1324.62340848</v>
+        <v>-1513.10008246</v>
       </c>
       <c r="H73" t="n">
-        <v>-1494.22065455</v>
+        <v>-486.52127426</v>
       </c>
       <c r="I73" t="n">
-        <v>-477.25509582</v>
+        <v>-936.91281313</v>
       </c>
       <c r="J73" t="n">
-        <v>-922.0717805799999</v>
+        <v>59.42146735</v>
       </c>
       <c r="K73" t="n">
-        <v>63.64246134</v>
+        <v>903.2323206300001</v>
       </c>
       <c r="L73" t="n">
-        <v>898.8864829000001</v>
+        <v>800.7780561700001</v>
       </c>
       <c r="M73" t="n">
-        <v>790.9240111800001</v>
+        <v>1167.48715472</v>
       </c>
     </row>
     <row r="74">
@@ -3463,37 +3465,37 @@
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
-        <v>-367.06678437</v>
+        <v>-250.80931058</v>
       </c>
       <c r="D74" t="n">
-        <v>-250.69924983</v>
+        <v>-871.11949227</v>
       </c>
       <c r="E74" t="n">
-        <v>-872.0283148399999</v>
+        <v>-140.20681045</v>
       </c>
       <c r="F74" t="n">
-        <v>-139.73695014</v>
+        <v>-444.35116709</v>
       </c>
       <c r="G74" t="n">
-        <v>-442.97575951</v>
+        <v>-637.1793570799999</v>
       </c>
       <c r="H74" t="n">
-        <v>-633.39512414</v>
+        <v>-352.1735925200001</v>
       </c>
       <c r="I74" t="n">
-        <v>-341.20493453</v>
+        <v>-360.48232321</v>
       </c>
       <c r="J74" t="n">
-        <v>-356.22095996</v>
+        <v>-337.9095999</v>
       </c>
       <c r="K74" t="n">
-        <v>-337.45108135</v>
+        <v>-136.63508772</v>
       </c>
       <c r="L74" t="n">
-        <v>-134.7466928</v>
+        <v>35.29096643</v>
       </c>
       <c r="M74" t="n">
-        <v>37.79193381</v>
+        <v>110.83660003</v>
       </c>
     </row>
     <row r="75">
@@ -3504,37 +3506,37 @@
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
-        <v>-54.58733164</v>
+        <v>87.23155</v>
       </c>
       <c r="D75" t="n">
-        <v>89.86719134000001</v>
+        <v>-36.44292329</v>
       </c>
       <c r="E75" t="n">
-        <v>-45.88042659000001</v>
+        <v>-73.92041897</v>
       </c>
       <c r="F75" t="n">
-        <v>-89.31179165</v>
+        <v>-135.48082716</v>
       </c>
       <c r="G75" t="n">
-        <v>-156.48937493</v>
+        <v>-183.58943646</v>
       </c>
       <c r="H75" t="n">
-        <v>-206.25309731</v>
+        <v>-77.88654633</v>
       </c>
       <c r="I75" t="n">
-        <v>-98.12138276</v>
+        <v>-144.52908066</v>
       </c>
       <c r="J75" t="n">
-        <v>-163.63147646</v>
+        <v>11.98855299</v>
       </c>
       <c r="K75" t="n">
-        <v>7.309040450000002</v>
+        <v>181.05870754</v>
       </c>
       <c r="L75" t="n">
-        <v>183.51615035</v>
+        <v>132.8161357</v>
       </c>
       <c r="M75" t="n">
-        <v>140.16921331</v>
+        <v>163.36198118</v>
       </c>
     </row>
     <row r="76">
@@ -3545,37 +3547,37 @@
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>-0.0010076</v>
+        <v>-0.00018871</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.00018871</v>
+        <v>-0.00053725</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.00053725</v>
+        <v>-0.00057684</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.00057684</v>
+        <v>-0.0006594299999999999</v>
       </c>
       <c r="G76" t="n">
-        <v>-0.0006594299999999999</v>
+        <v>-0.00071329</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.00071329</v>
+        <v>-0.0003751</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.0003751</v>
+        <v>-0.00072667</v>
       </c>
       <c r="J76" t="n">
-        <v>-0.00072667</v>
+        <v>-0.00031853</v>
       </c>
       <c r="K76" t="n">
-        <v>-0.00031853</v>
+        <v>-0.00042214</v>
       </c>
       <c r="L76" t="n">
-        <v>-0.00042214</v>
+        <v>0.00035191</v>
       </c>
       <c r="M76" t="n">
-        <v>0.00035191</v>
+        <v>0.0006016</v>
       </c>
     </row>
     <row r="77">
@@ -3584,41 +3586,39 @@
           <t>金融業右下</t>
         </is>
       </c>
-      <c r="B77" t="n">
-        <v>0</v>
-      </c>
+      <c r="B77" t="inlineStr"/>
       <c r="C77" t="n">
-        <v>-0.00133008</v>
+        <v>0.0006396900000000001</v>
       </c>
       <c r="D77" t="n">
-        <v>0.00026628</v>
+        <v>0.00368509</v>
       </c>
       <c r="E77" t="n">
-        <v>0.00350767</v>
+        <v>0.004119070000000001</v>
       </c>
       <c r="F77" t="n">
-        <v>0.00375462</v>
+        <v>0.00104634</v>
       </c>
       <c r="G77" t="n">
-        <v>0.00100754</v>
+        <v>-0.00267286</v>
       </c>
       <c r="H77" t="n">
-        <v>-0.00254034</v>
+        <v>-9.306000000000001e-05</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.0002606299999999999</v>
+        <v>-0.00439828</v>
       </c>
       <c r="J77" t="n">
-        <v>-0.00411787</v>
+        <v>-0.005935770000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>-0.00544981</v>
+        <v>-0.006376339999999999</v>
       </c>
       <c r="L77" t="n">
-        <v>-0.006712269999999999</v>
+        <v>-0.00146164</v>
       </c>
       <c r="M77" t="n">
-        <v>-0.0022721</v>
+        <v>0.0001785999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -3629,37 +3629,37 @@
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
-        <v>-0.00080643</v>
+        <v>-0.00053355</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.00053355</v>
+        <v>-0.0004297</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.0004297</v>
+        <v>-0.00048908</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.00048908</v>
+        <v>-0.00026955</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.00026955</v>
+        <v>-0.00035725</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.00035725</v>
+        <v>-0.00052145</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.00052145</v>
+        <v>-0.00052038</v>
       </c>
       <c r="J78" t="n">
-        <v>-0.00052038</v>
+        <v>-0.00049876</v>
       </c>
       <c r="K78" t="n">
-        <v>-0.00049876</v>
+        <v>-0.00010349</v>
       </c>
       <c r="L78" t="n">
-        <v>-0.00010349</v>
+        <v>0.00149008</v>
       </c>
       <c r="M78" t="n">
-        <v>0.00149008</v>
+        <v>0.00167124</v>
       </c>
     </row>
     <row r="79">
@@ -3670,37 +3670,37 @@
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="n">
-        <v>3.51672797</v>
+        <v>3.13082996</v>
       </c>
       <c r="D79" t="n">
-        <v>3.13082996</v>
+        <v>12.50540977</v>
       </c>
       <c r="E79" t="n">
-        <v>12.50540977</v>
+        <v>27.84336579</v>
       </c>
       <c r="F79" t="n">
-        <v>27.84336579</v>
+        <v>3.57885056</v>
       </c>
       <c r="G79" t="n">
-        <v>3.57885056</v>
+        <v>-6.574561549999999</v>
       </c>
       <c r="H79" t="n">
-        <v>-6.574561549999999</v>
+        <v>5.12920975</v>
       </c>
       <c r="I79" t="n">
-        <v>5.12920975</v>
+        <v>0.3989783500000001</v>
       </c>
       <c r="J79" t="n">
-        <v>0.3989783500000001</v>
+        <v>-13.06068005</v>
       </c>
       <c r="K79" t="n">
-        <v>-0.85045757</v>
+        <v>-4.237776240000001</v>
       </c>
       <c r="L79" t="n">
-        <v>-2.06183055</v>
+        <v>-10.05923</v>
       </c>
       <c r="M79" t="n">
-        <v>-1.27944524</v>
+        <v>8.441145179999999</v>
       </c>
     </row>
     <row r="80">
@@ -3711,37 +3711,37 @@
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="n">
-        <v>55.6086783</v>
+        <v>189.01949834</v>
       </c>
       <c r="D80" t="n">
-        <v>189.08539014</v>
+        <v>59.36770919</v>
       </c>
       <c r="E80" t="n">
-        <v>59.51744986</v>
+        <v>36.53568006</v>
       </c>
       <c r="F80" t="n">
-        <v>36.79319181</v>
+        <v>-46.66810387</v>
       </c>
       <c r="G80" t="n">
-        <v>-46.55468548</v>
+        <v>-86.27307861</v>
       </c>
       <c r="H80" t="n">
-        <v>-86.24594107999999</v>
+        <v>4.663124380000001</v>
       </c>
       <c r="I80" t="n">
-        <v>4.75202269</v>
+        <v>-72.56750855</v>
       </c>
       <c r="J80" t="n">
-        <v>-72.65792786999999</v>
+        <v>-104.41170928</v>
       </c>
       <c r="K80" t="n">
-        <v>-104.70569544</v>
+        <v>-113.93601583</v>
       </c>
       <c r="L80" t="n">
-        <v>-114.03055386</v>
+        <v>-69.00746740999999</v>
       </c>
       <c r="M80" t="n">
-        <v>-68.98960509</v>
+        <v>-46.30035985</v>
       </c>
     </row>
     <row r="81">
@@ -3752,37 +3752,37 @@
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>97.66577554</v>
+        <v>253.98290476</v>
       </c>
       <c r="D81" t="n">
-        <v>253.91701296</v>
+        <v>107.03114921</v>
       </c>
       <c r="E81" t="n">
-        <v>106.88140854</v>
+        <v>356.82965706</v>
       </c>
       <c r="F81" t="n">
-        <v>356.57214531</v>
+        <v>507.11291227</v>
       </c>
       <c r="G81" t="n">
-        <v>506.99949388</v>
+        <v>775.8343140100001</v>
       </c>
       <c r="H81" t="n">
-        <v>775.8071764800002</v>
+        <v>804.0133202900001</v>
       </c>
       <c r="I81" t="n">
-        <v>803.92442198</v>
+        <v>245.59414045</v>
       </c>
       <c r="J81" t="n">
-        <v>245.68455977</v>
+        <v>6.417786799999997</v>
       </c>
       <c r="K81" t="n">
-        <v>6.711772959999993</v>
+        <v>101.18923136</v>
       </c>
       <c r="L81" t="n">
-        <v>101.28376939</v>
+        <v>-46.21199444</v>
       </c>
       <c r="M81" t="n">
-        <v>-46.22985675999999</v>
+        <v>3.214839009999998</v>
       </c>
     </row>
     <row r="82">
@@ -3793,37 +3793,37 @@
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
-        <v>-16.2538581</v>
+        <v>-13.58472732</v>
       </c>
       <c r="D82" t="n">
-        <v>-12.95625808</v>
+        <v>-10.64403632</v>
       </c>
       <c r="E82" t="n">
-        <v>-9.47706786</v>
+        <v>-5.600883880000002</v>
       </c>
       <c r="F82" t="n">
-        <v>-3.909404330000002</v>
+        <v>-16.1009798</v>
       </c>
       <c r="G82" t="n">
-        <v>-14.46518195</v>
+        <v>35.45646956</v>
       </c>
       <c r="H82" t="n">
-        <v>37.21932350000001</v>
+        <v>68.03330789</v>
       </c>
       <c r="I82" t="n">
-        <v>68.03134521</v>
+        <v>-4.41017006</v>
       </c>
       <c r="J82" t="n">
-        <v>-2.350372119999999</v>
+        <v>-6.688197980000001</v>
       </c>
       <c r="K82" t="n">
-        <v>-4.571539939999999</v>
+        <v>39.15618257</v>
       </c>
       <c r="L82" t="n">
-        <v>39.14585281</v>
+        <v>88.37693567999999</v>
       </c>
       <c r="M82" t="n">
-        <v>87.22141015999999</v>
+        <v>173.80208869</v>
       </c>
     </row>
     <row r="83">
@@ -3834,37 +3834,37 @@
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>16.23269398</v>
+        <v>45.51688189</v>
       </c>
       <c r="D83" t="n">
-        <v>46.02478503</v>
+        <v>10.48398042</v>
       </c>
       <c r="E83" t="n">
-        <v>10.70422737</v>
+        <v>-6.200787319999999</v>
       </c>
       <c r="F83" t="n">
-        <v>-5.995241029999999</v>
+        <v>7.24090026</v>
       </c>
       <c r="G83" t="n">
-        <v>7.19180515</v>
+        <v>-6.584324479999999</v>
       </c>
       <c r="H83" t="n">
-        <v>-6.73828916</v>
+        <v>102.05297551</v>
       </c>
       <c r="I83" t="n">
-        <v>102.04973315</v>
+        <v>-115.80629482</v>
       </c>
       <c r="J83" t="n">
-        <v>-116.03766855</v>
+        <v>-143.5880583</v>
       </c>
       <c r="K83" t="n">
-        <v>-143.59839725</v>
+        <v>-122.46679617</v>
       </c>
       <c r="L83" t="n">
-        <v>-122.34910587</v>
+        <v>-54.09129918000001</v>
       </c>
       <c r="M83" t="n">
-        <v>-54.08839686000001</v>
+        <v>-10.37837567</v>
       </c>
     </row>
     <row r="84">
@@ -3875,37 +3875,37 @@
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
-        <v>-14.05947637</v>
+        <v>5.51182728</v>
       </c>
       <c r="D84" t="n">
-        <v>4.3754549</v>
+        <v>-15.07566146</v>
       </c>
       <c r="E84" t="n">
-        <v>-16.46287687</v>
+        <v>-25.78377224</v>
       </c>
       <c r="F84" t="n">
-        <v>-27.68079808</v>
+        <v>-21.74778079</v>
       </c>
       <c r="G84" t="n">
-        <v>-23.33448353</v>
+        <v>-16.410326</v>
       </c>
       <c r="H84" t="n">
-        <v>-18.01921526</v>
+        <v>-1.11322981</v>
       </c>
       <c r="I84" t="n">
-        <v>-1.10802477</v>
+        <v>-17.97659833</v>
       </c>
       <c r="J84" t="n">
-        <v>-19.80502254</v>
+        <v>-22.4468883</v>
       </c>
       <c r="K84" t="n">
-        <v>-24.55320739</v>
+        <v>-6.5081971</v>
       </c>
       <c r="L84" t="n">
-        <v>-6.61555764</v>
+        <v>10.56673461</v>
       </c>
       <c r="M84" t="n">
-        <v>11.71935781</v>
+        <v>91.63808985999999</v>
       </c>
     </row>
     <row r="85">
@@ -3916,37 +3916,37 @@
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>-0.5536843900000029</v>
+        <v>35.31476152</v>
       </c>
       <c r="D85" t="n">
-        <v>35.31476152</v>
+        <v>2.312927219999999</v>
       </c>
       <c r="E85" t="n">
-        <v>2.312927219999999</v>
+        <v>-14.73780212</v>
       </c>
       <c r="F85" t="n">
-        <v>-14.73780212</v>
+        <v>45.55591851</v>
       </c>
       <c r="G85" t="n">
-        <v>45.55591851</v>
+        <v>20.93663418</v>
       </c>
       <c r="H85" t="n">
-        <v>20.93663418</v>
+        <v>83.75538558</v>
       </c>
       <c r="I85" t="n">
-        <v>83.75538558</v>
+        <v>31.50825829</v>
       </c>
       <c r="J85" t="n">
-        <v>31.50825829</v>
+        <v>43.48443047</v>
       </c>
       <c r="K85" t="n">
-        <v>43.48443047</v>
+        <v>13.09829768</v>
       </c>
       <c r="L85" t="n">
-        <v>13.09829768</v>
+        <v>98.23389636000002</v>
       </c>
       <c r="M85" t="n">
-        <v>98.23389636000002</v>
+        <v>22.42436713</v>
       </c>
     </row>
     <row r="86">
@@ -3955,41 +3955,39 @@
           <t>電子通路業右下</t>
         </is>
       </c>
-      <c r="B86" t="n">
-        <v>0</v>
-      </c>
+      <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
-        <v>5.08139875</v>
+        <v>14.30691095</v>
       </c>
       <c r="D86" t="n">
-        <v>14.30721738</v>
+        <v>17.21217532</v>
       </c>
       <c r="E86" t="n">
-        <v>17.21231996</v>
+        <v>9.6667656</v>
       </c>
       <c r="F86" t="n">
-        <v>9.666825319999999</v>
+        <v>13.81802202</v>
       </c>
       <c r="G86" t="n">
-        <v>13.81801526</v>
+        <v>0.01408597999999998</v>
       </c>
       <c r="H86" t="n">
-        <v>0.01406337</v>
+        <v>3.64727612</v>
       </c>
       <c r="I86" t="n">
-        <v>3.64720106</v>
+        <v>-2.23915729</v>
       </c>
       <c r="J86" t="n">
-        <v>-2.23925099</v>
+        <v>2.45049239</v>
       </c>
       <c r="K86" t="n">
-        <v>2.45052868</v>
+        <v>5.20443463</v>
       </c>
       <c r="L86" t="n">
-        <v>5.204550360000001</v>
+        <v>8.837787029999999</v>
       </c>
       <c r="M86" t="n">
-        <v>8.83929865</v>
+        <v>9.958617460000001</v>
       </c>
     </row>
     <row r="87">
@@ -4000,37 +3998,37 @@
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>-162.62400307</v>
+        <v>1.417260900000001</v>
       </c>
       <c r="D87" t="n">
-        <v>1.415673110000001</v>
+        <v>-80.44995999</v>
       </c>
       <c r="E87" t="n">
-        <v>-80.45172776999999</v>
+        <v>-30.71164348</v>
       </c>
       <c r="F87" t="n">
-        <v>-30.71248296</v>
+        <v>27.71204995</v>
       </c>
       <c r="G87" t="n">
-        <v>27.71139969</v>
+        <v>-45.84533629</v>
       </c>
       <c r="H87" t="n">
-        <v>-45.84580746</v>
+        <v>12.14272316</v>
       </c>
       <c r="I87" t="n">
-        <v>12.1419908</v>
+        <v>-71.90978043999999</v>
       </c>
       <c r="J87" t="n">
-        <v>-71.91019874000001</v>
+        <v>-32.61414927000001</v>
       </c>
       <c r="K87" t="n">
-        <v>-32.61515799</v>
+        <v>15.8340608</v>
       </c>
       <c r="L87" t="n">
-        <v>15.83261637</v>
+        <v>67.44172266</v>
       </c>
       <c r="M87" t="n">
-        <v>67.43947752</v>
+        <v>91.12355039000001</v>
       </c>
     </row>
     <row r="88">
@@ -4041,37 +4039,37 @@
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
-        <v>-185.6210225900001</v>
+        <v>1469.03355356</v>
       </c>
       <c r="D88" t="n">
-        <v>1450.16954711</v>
+        <v>2192.38968272</v>
       </c>
       <c r="E88" t="n">
-        <v>2181.7213222</v>
+        <v>796.7331753599999</v>
       </c>
       <c r="F88" t="n">
-        <v>800.8896557599999</v>
+        <v>2711.92330755</v>
       </c>
       <c r="G88" t="n">
-        <v>2692.81628791</v>
+        <v>1458.58061226</v>
       </c>
       <c r="H88" t="n">
-        <v>1485.24470595</v>
+        <v>670.5646738299999</v>
       </c>
       <c r="I88" t="n">
-        <v>707.3239357199999</v>
+        <v>2015.23936833</v>
       </c>
       <c r="J88" t="n">
-        <v>2029.26073542</v>
+        <v>2827.54758005</v>
       </c>
       <c r="K88" t="n">
-        <v>2841.68157912</v>
+        <v>282.75142694</v>
       </c>
       <c r="L88" t="n">
-        <v>310.9182969999999</v>
+        <v>2979.97262876</v>
       </c>
       <c r="M88" t="n">
-        <v>2951.08125892</v>
+        <v>1281.51913489</v>
       </c>
     </row>
     <row r="89">
@@ -4082,37 +4080,37 @@
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>-883.24209911</v>
+        <v>-207.57083162</v>
       </c>
       <c r="D89" t="n">
-        <v>-201.52397087</v>
+        <v>22.89105058000001</v>
       </c>
       <c r="E89" t="n">
-        <v>-8.732740339999999</v>
+        <v>-393.01372625</v>
       </c>
       <c r="F89" t="n">
-        <v>-435.81774409</v>
+        <v>-84.66222935999997</v>
       </c>
       <c r="G89" t="n">
-        <v>-102.3107785</v>
+        <v>931.52277498</v>
       </c>
       <c r="H89" t="n">
-        <v>896.3284795599999</v>
+        <v>1129.91593369</v>
       </c>
       <c r="I89" t="n">
-        <v>1111.10497579</v>
+        <v>75.35369751</v>
       </c>
       <c r="J89" t="n">
-        <v>50.44890780999999</v>
+        <v>123.92895526</v>
       </c>
       <c r="K89" t="n">
-        <v>-14.56728938000001</v>
+        <v>-315.90783049</v>
       </c>
       <c r="L89" t="n">
-        <v>-5.564253769999999</v>
+        <v>-262.85001529</v>
       </c>
       <c r="M89" t="n">
-        <v>-19.6759302</v>
+        <v>-596.34841211</v>
       </c>
     </row>
     <row r="90">
@@ -4123,37 +4121,37 @@
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>-232.4944642299999</v>
+        <v>415.33194817</v>
       </c>
       <c r="D90" t="n">
-        <v>420.92061912</v>
+        <v>502.50672949</v>
       </c>
       <c r="E90" t="n">
-        <v>459.95052021</v>
+        <v>713.8885992099999</v>
       </c>
       <c r="F90" t="n">
-        <v>605.7497208599999</v>
+        <v>788.71285189</v>
       </c>
       <c r="G90" t="n">
-        <v>673.2721946099999</v>
+        <v>112.24879993</v>
       </c>
       <c r="H90" t="n">
-        <v>66.02010782999999</v>
+        <v>-152.73262748</v>
       </c>
       <c r="I90" t="n">
-        <v>-272.91236466</v>
+        <v>-432.85711792</v>
       </c>
       <c r="J90" t="n">
-        <v>-579.9655332799999</v>
+        <v>-467.08175312</v>
       </c>
       <c r="K90" t="n">
-        <v>-509.24311207</v>
+        <v>-365.40042852</v>
       </c>
       <c r="L90" t="n">
-        <v>-465.41948481</v>
+        <v>195.5472825</v>
       </c>
       <c r="M90" t="n">
-        <v>115.73875425</v>
+        <v>-469.65131659</v>
       </c>
     </row>
     <row r="91">
@@ -4164,37 +4162,37 @@
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>184.87326695</v>
+        <v>1374.52931941</v>
       </c>
       <c r="D91" t="n">
-        <v>1368.35983017</v>
+        <v>-196.01497756</v>
       </c>
       <c r="E91" t="n">
-        <v>-196.54083268</v>
+        <v>-960.5770264</v>
       </c>
       <c r="F91" t="n">
-        <v>-957.50121358</v>
+        <v>-381.97723422</v>
       </c>
       <c r="G91" t="n">
-        <v>-381.6503944</v>
+        <v>-279.8947880800001</v>
       </c>
       <c r="H91" t="n">
-        <v>-279.9177601100001</v>
+        <v>-266.33976855</v>
       </c>
       <c r="I91" t="n">
-        <v>-263.24742637</v>
+        <v>-137.76573277</v>
       </c>
       <c r="J91" t="n">
-        <v>-135.88497402</v>
+        <v>229.69125497</v>
       </c>
       <c r="K91" t="n">
-        <v>232.56698152</v>
+        <v>-1071.53426478</v>
       </c>
       <c r="L91" t="n">
-        <v>-1066.21545203</v>
+        <v>-1052.8689742</v>
       </c>
       <c r="M91" t="n">
-        <v>-1047.51645464</v>
+        <v>-302.7896797499999</v>
       </c>
     </row>
     <row r="92">
@@ -4203,39 +4201,41 @@
           <t>電機機械右下</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr"/>
+      <c r="B92" t="n">
+        <v>0</v>
+      </c>
       <c r="C92" t="n">
-        <v>-103.78597877</v>
+        <v>122.39367207</v>
       </c>
       <c r="D92" t="n">
-        <v>122.6228198</v>
+        <v>91.62158169</v>
       </c>
       <c r="E92" t="n">
-        <v>91.51325189999999</v>
+        <v>-52.15505964</v>
       </c>
       <c r="F92" t="n">
-        <v>-52.62472093</v>
+        <v>-40.56079284999999</v>
       </c>
       <c r="G92" t="n">
-        <v>-40.00084953</v>
+        <v>-83.17373404999999</v>
       </c>
       <c r="H92" t="n">
-        <v>-83.57265513</v>
+        <v>58.18204148</v>
       </c>
       <c r="I92" t="n">
-        <v>59.78372129</v>
+        <v>-48.50096176</v>
       </c>
       <c r="J92" t="n">
-        <v>-48.40620964</v>
+        <v>-28.45410904000001</v>
       </c>
       <c r="K92" t="n">
-        <v>-27.57179441000001</v>
+        <v>-26.98770348</v>
       </c>
       <c r="L92" t="n">
-        <v>-25.67954601</v>
+        <v>42.02259498999999</v>
       </c>
       <c r="M92" t="n">
-        <v>43.66854344</v>
+        <v>-82.26534513000001</v>
       </c>
     </row>
     <row r="93">
@@ -4246,37 +4246,37 @@
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>-153.88288005</v>
+        <v>55.76439599</v>
       </c>
       <c r="D93" t="n">
-        <v>61.93388523</v>
+        <v>79.66820878</v>
       </c>
       <c r="E93" t="n">
-        <v>80.1940639</v>
+        <v>307.66783073</v>
       </c>
       <c r="F93" t="n">
-        <v>304.59201791</v>
+        <v>429.53197474</v>
       </c>
       <c r="G93" t="n">
-        <v>429.20513492</v>
+        <v>102.13408786</v>
       </c>
       <c r="H93" t="n">
-        <v>102.15705989</v>
+        <v>150.09547556</v>
       </c>
       <c r="I93" t="n">
-        <v>147.00313338</v>
+        <v>307.43352346</v>
       </c>
       <c r="J93" t="n">
-        <v>305.55276471</v>
+        <v>111.6570151</v>
       </c>
       <c r="K93" t="n">
-        <v>108.78128855</v>
+        <v>-8.719710409999996</v>
       </c>
       <c r="L93" t="n">
-        <v>-14.03852316</v>
+        <v>-103.70588004</v>
       </c>
       <c r="M93" t="n">
-        <v>-109.0583996</v>
+        <v>15.97168822</v>
       </c>
     </row>
     <row r="94">
@@ -4287,37 +4287,37 @@
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>324.9204341100001</v>
+        <v>-812.2786350600001</v>
       </c>
       <c r="D94" t="n">
-        <v>-812.2786350600001</v>
+        <v>683.4299987600001</v>
       </c>
       <c r="E94" t="n">
-        <v>683.4299987600001</v>
+        <v>-196.7993444</v>
       </c>
       <c r="F94" t="n">
-        <v>-196.7993444</v>
+        <v>1230.67429305</v>
       </c>
       <c r="G94" t="n">
-        <v>1230.67429305</v>
+        <v>736.97943814</v>
       </c>
       <c r="H94" t="n">
-        <v>736.97943814</v>
+        <v>980.9976145999998</v>
       </c>
       <c r="I94" t="n">
-        <v>980.9976145999998</v>
+        <v>3039.80295137</v>
       </c>
       <c r="J94" t="n">
-        <v>3039.80295137</v>
+        <v>2684.70702195</v>
       </c>
       <c r="K94" t="n">
-        <v>2684.70702195</v>
+        <v>405.27107273</v>
       </c>
       <c r="L94" t="n">
-        <v>405.27107273</v>
+        <v>4022.20344772</v>
       </c>
       <c r="M94" t="n">
-        <v>4022.20344772</v>
+        <v>1787.99012331</v>
       </c>
     </row>
     <row r="95">
@@ -4326,41 +4326,39 @@
           <t>電腦及週邊設備業右下</t>
         </is>
       </c>
-      <c r="B95" t="n">
-        <v>0</v>
-      </c>
+      <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>-132.46080242</v>
+        <v>39.63236597</v>
       </c>
       <c r="D95" t="n">
-        <v>34.85056729</v>
+        <v>52.16923741999999</v>
       </c>
       <c r="E95" t="n">
-        <v>55.01980351</v>
+        <v>69.4114786</v>
       </c>
       <c r="F95" t="n">
-        <v>74.50069306</v>
+        <v>81.05528531</v>
       </c>
       <c r="G95" t="n">
-        <v>80.53706909</v>
+        <v>-13.09141086</v>
       </c>
       <c r="H95" t="n">
-        <v>-8.93303306</v>
+        <v>56.25626138000001</v>
       </c>
       <c r="I95" t="n">
-        <v>58.02319511</v>
+        <v>19.28790825</v>
       </c>
       <c r="J95" t="n">
-        <v>35.29578411000001</v>
+        <v>2.439236129999996</v>
       </c>
       <c r="K95" t="n">
-        <v>7.858454199999987</v>
+        <v>23.74705774</v>
       </c>
       <c r="L95" t="n">
-        <v>28.23256805999999</v>
+        <v>212.57975408</v>
       </c>
       <c r="M95" t="n">
-        <v>208.04570502</v>
+        <v>25.10469356999999</v>
       </c>
     </row>
     <row r="96">
@@ -4371,37 +4369,37 @@
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>-4.141184909999997</v>
+        <v>162.61287903</v>
       </c>
       <c r="D96" t="n">
-        <v>166.47330958</v>
+        <v>82.56716143</v>
       </c>
       <c r="E96" t="n">
-        <v>80.32533663</v>
+        <v>-45.38502581</v>
       </c>
       <c r="F96" t="n">
-        <v>-51.44705072</v>
+        <v>36.56834340999999</v>
       </c>
       <c r="G96" t="n">
-        <v>34.72257917</v>
+        <v>-202.15241766</v>
       </c>
       <c r="H96" t="n">
-        <v>-207.45357874</v>
+        <v>-255.07480421</v>
       </c>
       <c r="I96" t="n">
-        <v>-257.04887386</v>
+        <v>-104.44023917</v>
       </c>
       <c r="J96" t="n">
-        <v>-118.52267815</v>
+        <v>-5.097795139999999</v>
       </c>
       <c r="K96" t="n">
-        <v>-10.78382667</v>
+        <v>-57.10542296000001</v>
       </c>
       <c r="L96" t="n">
-        <v>-63.24544184000001</v>
+        <v>175.52919447</v>
       </c>
       <c r="M96" t="n">
-        <v>176.69736419</v>
+        <v>-51.77220392000001</v>
       </c>
     </row>
     <row r="97">
@@ -4412,37 +4410,37 @@
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>-89.75941349999999</v>
+        <v>-56.04735297</v>
       </c>
       <c r="D97" t="n">
-        <v>-55.51367920000001</v>
+        <v>-57.87707799</v>
       </c>
       <c r="E97" t="n">
-        <v>-57.70773954</v>
+        <v>-36.62934033</v>
       </c>
       <c r="F97" t="n">
-        <v>-36.45684124</v>
+        <v>-32.91337125</v>
       </c>
       <c r="G97" t="n">
-        <v>-33.17751057</v>
+        <v>-31.98540542</v>
       </c>
       <c r="H97" t="n">
-        <v>-32.66692659</v>
+        <v>-28.05852503</v>
       </c>
       <c r="I97" t="n">
-        <v>-28.58669746</v>
+        <v>-31.36661549</v>
       </c>
       <c r="J97" t="n">
-        <v>-32.48884227</v>
+        <v>-10.44575734</v>
       </c>
       <c r="K97" t="n">
-        <v>-12.6336774</v>
+        <v>26.3273587</v>
       </c>
       <c r="L97" t="n">
-        <v>26.64727957</v>
+        <v>54.67085678</v>
       </c>
       <c r="M97" t="n">
-        <v>55.86739919</v>
+        <v>42.46093398</v>
       </c>
     </row>
     <row r="98">
@@ -4453,37 +4451,37 @@
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
-        <v>-13.81783122</v>
+        <v>8.902682299999999</v>
       </c>
       <c r="D98" t="n">
-        <v>8.902682299999999</v>
+        <v>-7.00097985</v>
       </c>
       <c r="E98" t="n">
-        <v>-7.00097985</v>
+        <v>-8.586387240000001</v>
       </c>
       <c r="F98" t="n">
-        <v>-8.586387240000001</v>
+        <v>-10.56307657</v>
       </c>
       <c r="G98" t="n">
-        <v>-10.56307657</v>
+        <v>-11.32923905</v>
       </c>
       <c r="H98" t="n">
-        <v>-11.32923905</v>
+        <v>2.98401102</v>
       </c>
       <c r="I98" t="n">
-        <v>2.98401102</v>
+        <v>1.30875266</v>
       </c>
       <c r="J98" t="n">
-        <v>1.30875266</v>
+        <v>-3.510710399999999</v>
       </c>
       <c r="K98" t="n">
-        <v>-3.510710399999999</v>
+        <v>10.10491649</v>
       </c>
       <c r="L98" t="n">
-        <v>10.10491649</v>
+        <v>13.23640147</v>
       </c>
       <c r="M98" t="n">
-        <v>13.23640147</v>
+        <v>17.26166795</v>
       </c>
     </row>
     <row r="99">
@@ -4494,37 +4492,37 @@
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>92.38513603</v>
+        <v>-53.37129473</v>
       </c>
       <c r="D99" t="n">
-        <v>-53.9049685</v>
+        <v>-138.98917001</v>
       </c>
       <c r="E99" t="n">
-        <v>-139.15850846</v>
+        <v>-186.96189626</v>
       </c>
       <c r="F99" t="n">
-        <v>-187.13439535</v>
+        <v>-263.10525318</v>
       </c>
       <c r="G99" t="n">
-        <v>-262.84111386</v>
+        <v>-271.70429651</v>
       </c>
       <c r="H99" t="n">
-        <v>-271.02277534</v>
+        <v>-157.31223573</v>
       </c>
       <c r="I99" t="n">
-        <v>-156.7840633</v>
+        <v>-223.51356545</v>
       </c>
       <c r="J99" t="n">
-        <v>-222.39133867</v>
+        <v>-120.79785482</v>
       </c>
       <c r="K99" t="n">
-        <v>-118.60993476</v>
+        <v>-51.94059913</v>
       </c>
       <c r="L99" t="n">
-        <v>-52.26052</v>
+        <v>-88.75002898</v>
       </c>
       <c r="M99" t="n">
-        <v>-89.94657139</v>
+        <v>-109.41664061</v>
       </c>
     </row>
   </sheetData>

--- a/Result/analyze_2.xlsx
+++ b/Result/analyze_2.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
     </row>
@@ -503,37 +503,37 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>133.06912042</v>
+        <v>226.69442662</v>
       </c>
       <c r="D2" t="n">
-        <v>239.95090942</v>
+        <v>52.37458780999999</v>
       </c>
       <c r="E2" t="n">
-        <v>66.00250505</v>
+        <v>346.3266347</v>
       </c>
       <c r="F2" t="n">
-        <v>355.45804248</v>
+        <v>-46.92070764000001</v>
       </c>
       <c r="G2" t="n">
-        <v>-34.51162536</v>
+        <v>245.1040941</v>
       </c>
       <c r="H2" t="n">
-        <v>245.46158357</v>
+        <v>595.52490181</v>
       </c>
       <c r="I2" t="n">
-        <v>602.6152474099999</v>
+        <v>655.98303823</v>
       </c>
       <c r="J2" t="n">
-        <v>653.42568023</v>
+        <v>928.59263271</v>
       </c>
       <c r="K2" t="n">
-        <v>930.2711050599999</v>
+        <v>1831.29052201</v>
       </c>
       <c r="L2" t="n">
-        <v>1827.6733201</v>
+        <v>1078.39506312</v>
       </c>
       <c r="M2" t="n">
-        <v>1069.4091092</v>
+        <v>140.45337218</v>
       </c>
     </row>
     <row r="3">
@@ -546,37 +546,37 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>7.490133159999999</v>
+        <v>64.97403704999999</v>
       </c>
       <c r="D3" t="n">
-        <v>67.49101417</v>
+        <v>146.86998653</v>
       </c>
       <c r="E3" t="n">
-        <v>148.36239801</v>
+        <v>212.41895508</v>
       </c>
       <c r="F3" t="n">
-        <v>210.99623909</v>
+        <v>119.19690213</v>
       </c>
       <c r="G3" t="n">
-        <v>118.84403687</v>
+        <v>180.68861742</v>
       </c>
       <c r="H3" t="n">
-        <v>180.66622047</v>
+        <v>18.85457105</v>
       </c>
       <c r="I3" t="n">
-        <v>18.8222692</v>
+        <v>-2.291154179999999</v>
       </c>
       <c r="J3" t="n">
-        <v>-2.444914739999998</v>
+        <v>126.95353454</v>
       </c>
       <c r="K3" t="n">
-        <v>124.75165192</v>
+        <v>238.00361817</v>
       </c>
       <c r="L3" t="n">
-        <v>229.66293875</v>
+        <v>153.37178115</v>
       </c>
       <c r="M3" t="n">
-        <v>149.41176898</v>
+        <v>43.75407812</v>
       </c>
     </row>
     <row r="4">
@@ -587,37 +587,37 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>-89.41343711</v>
+        <v>155.14548277</v>
       </c>
       <c r="D4" t="n">
-        <v>134.16845386</v>
+        <v>16.79314675</v>
       </c>
       <c r="E4" t="n">
-        <v>2.515372209999999</v>
+        <v>-20.42905813</v>
       </c>
       <c r="F4" t="n">
-        <v>-22.27804234</v>
+        <v>-152.03154317</v>
       </c>
       <c r="G4" t="n">
-        <v>-154.32680326</v>
+        <v>-70.02958740000001</v>
       </c>
       <c r="H4" t="n">
-        <v>-69.50281128</v>
+        <v>-150.27702911</v>
       </c>
       <c r="I4" t="n">
-        <v>-119.78544769</v>
+        <v>-197.58998783</v>
       </c>
       <c r="J4" t="n">
-        <v>-156.06544249</v>
+        <v>-21.7445414</v>
       </c>
       <c r="K4" t="n">
-        <v>11.83680254</v>
+        <v>102.14636438</v>
       </c>
       <c r="L4" t="n">
-        <v>120.80687653</v>
+        <v>46.30012961999999</v>
       </c>
       <c r="M4" t="n">
-        <v>70.28602769999999</v>
+        <v>237.66588987</v>
       </c>
     </row>
     <row r="5">
@@ -628,37 +628,37 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>-126.15321476</v>
+        <v>186.82811691</v>
       </c>
       <c r="D5" t="n">
-        <v>186.82817224</v>
+        <v>467.8486097100001</v>
       </c>
       <c r="E5" t="n">
-        <v>467.84870192</v>
+        <v>758.27988239</v>
       </c>
       <c r="F5" t="n">
-        <v>758.27998281</v>
+        <v>802.10536136</v>
       </c>
       <c r="G5" t="n">
-        <v>802.10581856</v>
+        <v>1311.67929021</v>
       </c>
       <c r="H5" t="n">
-        <v>1311.67911888</v>
+        <v>1402.60968035</v>
       </c>
       <c r="I5" t="n">
-        <v>1402.61016698</v>
+        <v>947.1777888099999</v>
       </c>
       <c r="J5" t="n">
-        <v>947.17840165</v>
+        <v>633.92100185</v>
       </c>
       <c r="K5" t="n">
-        <v>633.91989454</v>
+        <v>146.03438519</v>
       </c>
       <c r="L5" t="n">
-        <v>146.03084003</v>
+        <v>-38.63471579000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-38.63562939</v>
+        <v>-259.31947403</v>
       </c>
     </row>
     <row r="6">
@@ -667,41 +667,39 @@
           <t>其他右下</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>55.37460995</v>
+        <v>36.31469387999999</v>
       </c>
       <c r="D6" t="n">
-        <v>36.25041112</v>
+        <v>-15.0706052</v>
       </c>
       <c r="E6" t="n">
-        <v>-15.16688701</v>
+        <v>-36.497385</v>
       </c>
       <c r="F6" t="n">
-        <v>-36.62205257</v>
+        <v>-50.54128249</v>
       </c>
       <c r="G6" t="n">
-        <v>-50.67505064</v>
+        <v>-51.15769783</v>
       </c>
       <c r="H6" t="n">
-        <v>-51.24585219999999</v>
+        <v>-140.94534825</v>
       </c>
       <c r="I6" t="n">
-        <v>-140.84742715</v>
+        <v>-65.33151937999999</v>
       </c>
       <c r="J6" t="n">
-        <v>-65.15703855999999</v>
+        <v>61.92808129000001</v>
       </c>
       <c r="K6" t="n">
-        <v>62.16016367999999</v>
+        <v>11.71021567</v>
       </c>
       <c r="L6" t="n">
-        <v>11.80711865</v>
+        <v>17.56998252</v>
       </c>
       <c r="M6" t="n">
-        <v>17.54515394</v>
+        <v>63.34027448999999</v>
       </c>
     </row>
     <row r="7">
@@ -712,37 +710,37 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>43.00683966</v>
+        <v>35.57194729</v>
       </c>
       <c r="D7" t="n">
-        <v>35.62588602</v>
+        <v>23.90388811</v>
       </c>
       <c r="E7" t="n">
-        <v>23.99754846</v>
+        <v>18.06926711</v>
       </c>
       <c r="F7" t="n">
-        <v>18.20177115</v>
+        <v>12.93300413</v>
       </c>
       <c r="G7" t="n">
-        <v>13.10214007</v>
+        <v>23.36286784</v>
       </c>
       <c r="H7" t="n">
-        <v>23.47973366</v>
+        <v>8.285323009999999</v>
       </c>
       <c r="I7" t="n">
-        <v>8.216738310000002</v>
+        <v>8.104432200000002</v>
       </c>
       <c r="J7" t="n">
-        <v>7.962291460000001</v>
+        <v>10.62024648</v>
       </c>
       <c r="K7" t="n">
-        <v>10.42012994</v>
+        <v>11.86696109</v>
       </c>
       <c r="L7" t="n">
-        <v>11.80106688</v>
+        <v>20.20766957</v>
       </c>
       <c r="M7" t="n">
-        <v>20.27382046</v>
+        <v>0.2825462599999979</v>
       </c>
     </row>
     <row r="8">
@@ -753,37 +751,37 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>-603.01014801</v>
+        <v>1584.29256748</v>
       </c>
       <c r="D8" t="n">
-        <v>1579.16335035</v>
+        <v>1683.81233496</v>
       </c>
       <c r="E8" t="n">
-        <v>1674.90332042</v>
+        <v>1748.64659283</v>
       </c>
       <c r="F8" t="n">
-        <v>1734.66238881</v>
+        <v>215.04205531</v>
       </c>
       <c r="G8" t="n">
-        <v>221.52990653</v>
+        <v>-175.62021034</v>
       </c>
       <c r="H8" t="n">
-        <v>-159.8729158599999</v>
+        <v>1440.97706319</v>
       </c>
       <c r="I8" t="n">
-        <v>1450.18502182</v>
+        <v>2243.01446221</v>
       </c>
       <c r="J8" t="n">
-        <v>2241.0766307</v>
+        <v>1059.07981602</v>
       </c>
       <c r="K8" t="n">
-        <v>1043.10318778</v>
+        <v>1234.60981361</v>
       </c>
       <c r="L8" t="n">
-        <v>1207.88001607</v>
+        <v>1217.94262096</v>
       </c>
       <c r="M8" t="n">
-        <v>1211.52543326</v>
+        <v>3045.32173068</v>
       </c>
     </row>
     <row r="9">
@@ -792,39 +790,41 @@
           <t>其他電子業右下</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
       <c r="C9" t="n">
-        <v>67.87246501</v>
+        <v>64.29671705</v>
       </c>
       <c r="D9" t="n">
-        <v>64.29666813999999</v>
+        <v>24.0433653</v>
       </c>
       <c r="E9" t="n">
-        <v>24.04332181</v>
+        <v>-2.54934967</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.54936097</v>
+        <v>5.40608709</v>
       </c>
       <c r="G9" t="n">
-        <v>5.406092370000001</v>
+        <v>17.64058699</v>
       </c>
       <c r="H9" t="n">
-        <v>17.64058343</v>
+        <v>-18.94161078</v>
       </c>
       <c r="I9" t="n">
-        <v>-18.94161434</v>
+        <v>37.6284706</v>
       </c>
       <c r="J9" t="n">
-        <v>37.62844630000001</v>
+        <v>35.63575449</v>
       </c>
       <c r="K9" t="n">
-        <v>35.63573011</v>
+        <v>39.53916686</v>
       </c>
       <c r="L9" t="n">
-        <v>39.53914933</v>
+        <v>-2.4616413</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.46165883</v>
+        <v>12.69502643</v>
       </c>
     </row>
     <row r="10">
@@ -835,37 +835,37 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>-18.22438221</v>
+        <v>45.38712386</v>
       </c>
       <c r="D10" t="n">
-        <v>50.56874051</v>
+        <v>11.35598687</v>
       </c>
       <c r="E10" t="n">
-        <v>20.28384937</v>
+        <v>11.13688639</v>
       </c>
       <c r="F10" t="n">
-        <v>25.11560232</v>
+        <v>-26.20296021</v>
       </c>
       <c r="G10" t="n">
-        <v>-32.68893001</v>
+        <v>2.97769681</v>
       </c>
       <c r="H10" t="n">
-        <v>-12.73385422</v>
+        <v>-15.58408941</v>
       </c>
       <c r="I10" t="n">
-        <v>-24.78738033</v>
+        <v>42.61125878</v>
       </c>
       <c r="J10" t="n">
-        <v>44.53638893999999</v>
+        <v>57.29643747999999</v>
       </c>
       <c r="K10" t="n">
-        <v>73.24840189</v>
+        <v>75.79364984</v>
       </c>
       <c r="L10" t="n">
-        <v>102.50783511</v>
+        <v>25.06164219</v>
       </c>
       <c r="M10" t="n">
-        <v>31.43955407</v>
+        <v>53.01065138</v>
       </c>
     </row>
     <row r="11">
@@ -876,37 +876,37 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>23.99637591</v>
+        <v>33.45564705</v>
       </c>
       <c r="D11" t="n">
-        <v>32.21424429</v>
+        <v>36.78153094</v>
       </c>
       <c r="E11" t="n">
-        <v>36.53843114</v>
+        <v>73.32758289</v>
       </c>
       <c r="F11" t="n">
-        <v>70.10710927</v>
+        <v>16.3233625</v>
       </c>
       <c r="G11" t="n">
-        <v>11.6701371</v>
+        <v>61.35117289</v>
       </c>
       <c r="H11" t="n">
-        <v>59.80061635</v>
+        <v>130.87621041</v>
       </c>
       <c r="I11" t="n">
-        <v>132.46617671</v>
+        <v>56.54414629999999</v>
       </c>
       <c r="J11" t="n">
-        <v>62.27960491</v>
+        <v>55.50389919000001</v>
       </c>
       <c r="K11" t="n">
-        <v>59.58881277</v>
+        <v>-2.38883577</v>
       </c>
       <c r="L11" t="n">
-        <v>-16.88295119</v>
+        <v>-58.09566982</v>
       </c>
       <c r="M11" t="n">
-        <v>-59.73766403</v>
+        <v>-77.91717035000001</v>
       </c>
     </row>
     <row r="12">
@@ -919,37 +919,37 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>42.88371942</v>
+        <v>181.12827274</v>
       </c>
       <c r="D12" t="n">
-        <v>188.66706368</v>
+        <v>62.28709359</v>
       </c>
       <c r="E12" t="n">
-        <v>74.9607798</v>
+        <v>47.51182313</v>
       </c>
       <c r="F12" t="n">
-        <v>61.98297435</v>
+        <v>-67.86251213</v>
       </c>
       <c r="G12" t="n">
-        <v>-50.61483504</v>
+        <v>117.04709593</v>
       </c>
       <c r="H12" t="n">
-        <v>120.26081568</v>
+        <v>1.19653822</v>
       </c>
       <c r="I12" t="n">
-        <v>17.05747791</v>
+        <v>-83.11722171000001</v>
       </c>
       <c r="J12" t="n">
-        <v>-76.68317665000001</v>
+        <v>-44.36274827</v>
       </c>
       <c r="K12" t="n">
-        <v>-47.9890768</v>
+        <v>-99.14298217</v>
       </c>
       <c r="L12" t="n">
-        <v>-105.84590131</v>
+        <v>-108.40102338</v>
       </c>
       <c r="M12" t="n">
-        <v>-119.01839249</v>
+        <v>-19.45438872999999</v>
       </c>
     </row>
     <row r="13">
@@ -960,37 +960,37 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>1.92786951</v>
+        <v>-0.6464205</v>
       </c>
       <c r="D13" t="n">
-        <v>0.23894946</v>
+        <v>-0.4307181600000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.33910902</v>
+        <v>-0.59056361</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.07084651000000003</v>
+        <v>-0.08659428000000007</v>
       </c>
       <c r="G13" t="n">
-        <v>1.18530408</v>
+        <v>1.77917163</v>
       </c>
       <c r="H13" t="n">
-        <v>2.51073357</v>
+        <v>2.56266091</v>
       </c>
       <c r="I13" t="n">
-        <v>3.76157343</v>
+        <v>1.53243879</v>
       </c>
       <c r="J13" t="n">
-        <v>2.25168748</v>
+        <v>9.202618049999998</v>
       </c>
       <c r="K13" t="n">
-        <v>2.52538849</v>
+        <v>-4.19720024</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5877431100000001</v>
+        <v>-3.09010341</v>
       </c>
       <c r="M13" t="n">
-        <v>2.16125695</v>
+        <v>-4.3289317</v>
       </c>
     </row>
     <row r="14">
@@ -1001,37 +1001,37 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>-2412.34696072</v>
+        <v>-3231.97946945</v>
       </c>
       <c r="D14" t="n">
-        <v>-3231.96074722</v>
+        <v>-6067.10652506</v>
       </c>
       <c r="E14" t="n">
-        <v>-6067.088565769999</v>
+        <v>-8165.38337648</v>
       </c>
       <c r="F14" t="n">
-        <v>-8165.36847638</v>
+        <v>-11808.04818822</v>
       </c>
       <c r="G14" t="n">
-        <v>-11808.03381456</v>
+        <v>-5565.24977255</v>
       </c>
       <c r="H14" t="n">
-        <v>-5565.23629961</v>
+        <v>-693.9748023900003</v>
       </c>
       <c r="I14" t="n">
-        <v>-693.9620924800003</v>
+        <v>-4033.2061213</v>
       </c>
       <c r="J14" t="n">
-        <v>-4033.19627708</v>
+        <v>-5990.71076214</v>
       </c>
       <c r="K14" t="n">
-        <v>-5990.70254144</v>
+        <v>-1118.15655134</v>
       </c>
       <c r="L14" t="n">
-        <v>-1118.14855647</v>
+        <v>-3900.457885</v>
       </c>
       <c r="M14" t="n">
-        <v>-3900.45259813</v>
+        <v>5225.866922259999</v>
       </c>
     </row>
     <row r="15">
@@ -1042,37 +1042,37 @@
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>812.15122491</v>
+        <v>415.17671171</v>
       </c>
       <c r="D15" t="n">
-        <v>402.44684952</v>
+        <v>525.40998389</v>
       </c>
       <c r="E15" t="n">
-        <v>541.1435638200001</v>
+        <v>447.02976782</v>
       </c>
       <c r="F15" t="n">
-        <v>439.24256852</v>
+        <v>-31.13990355000003</v>
       </c>
       <c r="G15" t="n">
-        <v>-44.79142044000002</v>
+        <v>23.42403106000001</v>
       </c>
       <c r="H15" t="n">
-        <v>9.620809680000001</v>
+        <v>-632.2839042999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-648.95806506</v>
+        <v>-165.3706187</v>
       </c>
       <c r="J15" t="n">
-        <v>-168.25121481</v>
+        <v>51.25846262999996</v>
       </c>
       <c r="K15" t="n">
-        <v>46.79415958999996</v>
+        <v>677.0458991900001</v>
       </c>
       <c r="L15" t="n">
-        <v>646.75366428</v>
+        <v>83.05033821999999</v>
       </c>
       <c r="M15" t="n">
-        <v>59.03503605</v>
+        <v>-148.23056635</v>
       </c>
     </row>
     <row r="16">
@@ -1083,37 +1083,37 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>600.18656244</v>
+        <v>131.7261127</v>
       </c>
       <c r="D16" t="n">
-        <v>144.43725266</v>
+        <v>-69.87645122999997</v>
       </c>
       <c r="E16" t="n">
-        <v>-85.62799044999998</v>
+        <v>103.08594964</v>
       </c>
       <c r="F16" t="n">
-        <v>110.85824884</v>
+        <v>306.19994461</v>
       </c>
       <c r="G16" t="n">
-        <v>319.83708784</v>
+        <v>-408.21042106</v>
       </c>
       <c r="H16" t="n">
-        <v>-394.42067262</v>
+        <v>-98.95156192999997</v>
       </c>
       <c r="I16" t="n">
-        <v>-82.29011108</v>
+        <v>-222.25757108</v>
       </c>
       <c r="J16" t="n">
-        <v>-219.38681919</v>
+        <v>-897.9158482</v>
       </c>
       <c r="K16" t="n">
-        <v>-893.4597658600001</v>
+        <v>-757.7623535499999</v>
       </c>
       <c r="L16" t="n">
-        <v>-727.47811351</v>
+        <v>-1126.50219126</v>
       </c>
       <c r="M16" t="n">
-        <v>-1102.49217596</v>
+        <v>-422.5661715</v>
       </c>
     </row>
     <row r="17">
@@ -1124,37 +1124,37 @@
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
-        <v>0.02769227000000001</v>
+        <v>0.34978601</v>
       </c>
       <c r="D17" t="n">
-        <v>0.34978601</v>
+        <v>0.55657781</v>
       </c>
       <c r="E17" t="n">
-        <v>0.55657781</v>
+        <v>0.5684159599999999</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5684159599999999</v>
+        <v>0.6202892800000001</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6202892800000001</v>
+        <v>0.7926845100000001</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7926845100000001</v>
+        <v>1.35238512</v>
       </c>
       <c r="I17" t="n">
-        <v>1.35238512</v>
+        <v>2.728392</v>
       </c>
       <c r="J17" t="n">
-        <v>2.728392</v>
+        <v>0.88005688</v>
       </c>
       <c r="K17" t="n">
-        <v>0.88005688</v>
+        <v>0.9546220400000001</v>
       </c>
       <c r="L17" t="n">
-        <v>0.9546220400000001</v>
+        <v>0.84933839</v>
       </c>
       <c r="M17" t="n">
-        <v>0.84933839</v>
+        <v>-0.12916396</v>
       </c>
     </row>
     <row r="18">
@@ -1165,37 +1165,37 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>494.05920309</v>
+        <v>317.71777002</v>
       </c>
       <c r="D18" t="n">
-        <v>317.71777002</v>
+        <v>283.5817899</v>
       </c>
       <c r="E18" t="n">
-        <v>283.5817899</v>
+        <v>797.0976046799999</v>
       </c>
       <c r="F18" t="n">
-        <v>797.0976046799999</v>
+        <v>-142.24816027</v>
       </c>
       <c r="G18" t="n">
-        <v>-142.24816027</v>
+        <v>949.19824843</v>
       </c>
       <c r="H18" t="n">
-        <v>949.19824843</v>
+        <v>786.71530309</v>
       </c>
       <c r="I18" t="n">
-        <v>786.71530309</v>
+        <v>-272.89082989</v>
       </c>
       <c r="J18" t="n">
-        <v>-272.89082989</v>
+        <v>-871.1452639</v>
       </c>
       <c r="K18" t="n">
-        <v>-871.1452639</v>
+        <v>-1069.80177573</v>
       </c>
       <c r="L18" t="n">
-        <v>-1069.80177573</v>
+        <v>-452.59567873</v>
       </c>
       <c r="M18" t="n">
-        <v>-452.59567873</v>
+        <v>-531.6740625399999</v>
       </c>
     </row>
     <row r="19">
@@ -1206,37 +1206,37 @@
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>-9.652651240000001</v>
+        <v>-12.00218059</v>
       </c>
       <c r="D19" t="n">
-        <v>-12.00218059</v>
+        <v>-11.43740213</v>
       </c>
       <c r="E19" t="n">
-        <v>-11.43740213</v>
+        <v>-4.71339594</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.71339594</v>
+        <v>-9.652321150000001</v>
       </c>
       <c r="G19" t="n">
-        <v>-9.652321150000001</v>
+        <v>-3.20862161</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.20862161</v>
+        <v>-6.092362550000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-6.092362550000001</v>
+        <v>-6.57161925</v>
       </c>
       <c r="J19" t="n">
-        <v>-6.57161925</v>
+        <v>-1.84598969</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.84598969</v>
+        <v>-3.50220299</v>
       </c>
       <c r="L19" t="n">
-        <v>-3.50220299</v>
+        <v>-0.44663556</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.44663556</v>
+        <v>-5.08226272</v>
       </c>
     </row>
     <row r="20">
@@ -1247,37 +1247,37 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>34.60076571</v>
+        <v>39.71331186</v>
       </c>
       <c r="D20" t="n">
-        <v>39.71449008</v>
+        <v>46.16474276</v>
       </c>
       <c r="E20" t="n">
-        <v>46.16666094</v>
+        <v>49.79108182</v>
       </c>
       <c r="F20" t="n">
-        <v>49.79008475</v>
+        <v>15.83999259</v>
       </c>
       <c r="G20" t="n">
-        <v>15.83800044</v>
+        <v>43.34600284999999</v>
       </c>
       <c r="H20" t="n">
-        <v>43.3430995</v>
+        <v>-20.57369556</v>
       </c>
       <c r="I20" t="n">
-        <v>-20.57441159</v>
+        <v>-26.64337471</v>
       </c>
       <c r="J20" t="n">
-        <v>-26.64291881</v>
+        <v>-8.6719104</v>
       </c>
       <c r="K20" t="n">
-        <v>-8.67058585</v>
+        <v>6.29112816</v>
       </c>
       <c r="L20" t="n">
-        <v>6.293730170000001</v>
+        <v>-11.38791094</v>
       </c>
       <c r="M20" t="n">
-        <v>-11.39545</v>
+        <v>39.90390299</v>
       </c>
     </row>
     <row r="21">
@@ -1288,37 +1288,37 @@
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
-        <v>-2.90937825</v>
+        <v>-0.6914854</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6914854</v>
+        <v>-0.87016615</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.87016615</v>
+        <v>0.47642728</v>
       </c>
       <c r="F21" t="n">
-        <v>0.47642728</v>
+        <v>-1.38489539</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.38489539</v>
+        <v>1.01578957</v>
       </c>
       <c r="H21" t="n">
-        <v>1.01578957</v>
+        <v>-0.08695448000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.08695448000000001</v>
+        <v>1.98383284</v>
       </c>
       <c r="J21" t="n">
-        <v>1.98383284</v>
+        <v>2.625483</v>
       </c>
       <c r="K21" t="n">
-        <v>2.625483</v>
+        <v>2.3940447</v>
       </c>
       <c r="L21" t="n">
-        <v>2.3940447</v>
+        <v>2.61609992</v>
       </c>
       <c r="M21" t="n">
-        <v>2.61609992</v>
+        <v>1.28616441</v>
       </c>
     </row>
     <row r="22">
@@ -1329,37 +1329,37 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>-1.55944125</v>
+        <v>-0.48060147</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.48177969</v>
+        <v>0.12922712</v>
       </c>
       <c r="E22" t="n">
-        <v>0.12730894</v>
+        <v>0.4000347</v>
       </c>
       <c r="F22" t="n">
-        <v>0.40103177</v>
+        <v>-0.11080264</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.10881049</v>
+        <v>0.11370021</v>
       </c>
       <c r="H22" t="n">
-        <v>0.11660356</v>
+        <v>0.08731186000000006</v>
       </c>
       <c r="I22" t="n">
-        <v>0.08802789000000008</v>
+        <v>1.53302582</v>
       </c>
       <c r="J22" t="n">
-        <v>1.53256992</v>
+        <v>2.46990344</v>
       </c>
       <c r="K22" t="n">
-        <v>2.46857889</v>
+        <v>1.61393472</v>
       </c>
       <c r="L22" t="n">
-        <v>1.61133271</v>
+        <v>1.84202241</v>
       </c>
       <c r="M22" t="n">
-        <v>1.84956147</v>
+        <v>2.06787124</v>
       </c>
     </row>
     <row r="23">
@@ -1370,37 +1370,37 @@
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
-        <v>9.438695200000002</v>
+        <v>29.14204919</v>
       </c>
       <c r="D23" t="n">
-        <v>29.14204919</v>
+        <v>18.78984363</v>
       </c>
       <c r="E23" t="n">
-        <v>18.78984363</v>
+        <v>11.99700128</v>
       </c>
       <c r="F23" t="n">
-        <v>11.99700128</v>
+        <v>-21.51542892</v>
       </c>
       <c r="G23" t="n">
-        <v>-21.51542892</v>
+        <v>3.234019390000002</v>
       </c>
       <c r="H23" t="n">
-        <v>3.234019390000002</v>
+        <v>1.317080060000002</v>
       </c>
       <c r="I23" t="n">
-        <v>1.317080060000002</v>
+        <v>-8.2388408</v>
       </c>
       <c r="J23" t="n">
-        <v>-8.2388408</v>
+        <v>30.90360521</v>
       </c>
       <c r="K23" t="n">
-        <v>30.90360521</v>
+        <v>28.25559642</v>
       </c>
       <c r="L23" t="n">
-        <v>28.25559642</v>
+        <v>13.04442215</v>
       </c>
       <c r="M23" t="n">
-        <v>13.04442215</v>
+        <v>-0.4080909000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1411,37 +1411,37 @@
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
-        <v>-65.19009097999999</v>
+        <v>-53.50370855</v>
       </c>
       <c r="D24" t="n">
-        <v>-78.71996444</v>
+        <v>-74.26896387000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-82.29528092000001</v>
+        <v>-90.23747162000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-82.69341238000001</v>
+        <v>-97.42394762000001</v>
       </c>
       <c r="G24" t="n">
-        <v>-81.77471033000002</v>
+        <v>-74.46318362999999</v>
       </c>
       <c r="H24" t="n">
-        <v>-54.70296398</v>
+        <v>-59.42508056</v>
       </c>
       <c r="I24" t="n">
-        <v>-34.20043623</v>
+        <v>-3.668862659999999</v>
       </c>
       <c r="J24" t="n">
-        <v>3.396011510000001</v>
+        <v>58.36625415</v>
       </c>
       <c r="K24" t="n">
-        <v>45.497298</v>
+        <v>28.29321428</v>
       </c>
       <c r="L24" t="n">
-        <v>38.02832282</v>
+        <v>20.81821146000001</v>
       </c>
       <c r="M24" t="n">
-        <v>58.68137049</v>
+        <v>-5.424017260000002</v>
       </c>
     </row>
     <row r="25">
@@ -1452,37 +1452,37 @@
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>80.22433495</v>
+        <v>7.910652079999999</v>
       </c>
       <c r="D25" t="n">
-        <v>33.12690797</v>
+        <v>-26.04393579</v>
       </c>
       <c r="E25" t="n">
-        <v>-18.01761874</v>
+        <v>-61.56858669</v>
       </c>
       <c r="F25" t="n">
-        <v>-69.11264593</v>
+        <v>-103.60265865</v>
       </c>
       <c r="G25" t="n">
-        <v>-119.25189594</v>
+        <v>-70.37873264</v>
       </c>
       <c r="H25" t="n">
-        <v>-90.13895229000001</v>
+        <v>-91.7645862</v>
       </c>
       <c r="I25" t="n">
-        <v>-116.98923053</v>
+        <v>-9.695433929999998</v>
       </c>
       <c r="J25" t="n">
-        <v>-16.7603081</v>
+        <v>87.05440726</v>
       </c>
       <c r="K25" t="n">
-        <v>99.92336340999999</v>
+        <v>20.51145993</v>
       </c>
       <c r="L25" t="n">
-        <v>10.77635139</v>
+        <v>36.93780613000001</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.9253528999999954</v>
+        <v>30.1453996</v>
       </c>
     </row>
     <row r="26">
@@ -1493,37 +1493,37 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>60.53162531</v>
+        <v>105.86494253</v>
       </c>
       <c r="D26" t="n">
-        <v>105.90485355</v>
+        <v>30.21146938</v>
       </c>
       <c r="E26" t="n">
-        <v>30.24814522</v>
+        <v>26.72469076</v>
       </c>
       <c r="F26" t="n">
-        <v>26.76396136</v>
+        <v>-16.38992439</v>
       </c>
       <c r="G26" t="n">
-        <v>-16.35696898</v>
+        <v>-11.60826412</v>
       </c>
       <c r="H26" t="n">
-        <v>-11.57917922</v>
+        <v>-0.7931707099999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.76419575</v>
+        <v>20.11172033</v>
       </c>
       <c r="J26" t="n">
-        <v>20.13668719</v>
+        <v>-15.74350812</v>
       </c>
       <c r="K26" t="n">
-        <v>-15.72170868</v>
+        <v>12.88097516</v>
       </c>
       <c r="L26" t="n">
-        <v>12.89942112</v>
+        <v>-21.7842918</v>
       </c>
       <c r="M26" t="n">
-        <v>-21.76483932</v>
+        <v>-40.05969073999999</v>
       </c>
     </row>
     <row r="27">
@@ -1534,37 +1534,37 @@
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>19.81733471</v>
+        <v>26.50834888</v>
       </c>
       <c r="D27" t="n">
-        <v>26.50834888</v>
+        <v>12.3732266</v>
       </c>
       <c r="E27" t="n">
-        <v>12.3732266</v>
+        <v>16.88570324</v>
       </c>
       <c r="F27" t="n">
-        <v>16.88570324</v>
+        <v>5.174999509999999</v>
       </c>
       <c r="G27" t="n">
-        <v>5.174999509999999</v>
+        <v>7.23050988</v>
       </c>
       <c r="H27" t="n">
-        <v>10.18965648</v>
+        <v>-1.83191157</v>
       </c>
       <c r="I27" t="n">
-        <v>5.14904886</v>
+        <v>-0.1112072000000002</v>
       </c>
       <c r="J27" t="n">
-        <v>12.32428043</v>
+        <v>-8.636969779999999</v>
       </c>
       <c r="K27" t="n">
-        <v>7.23473412</v>
+        <v>-0.6313917000000004</v>
       </c>
       <c r="L27" t="n">
-        <v>21.39711191</v>
+        <v>-12.47592114</v>
       </c>
       <c r="M27" t="n">
-        <v>9.234505710000002</v>
+        <v>-3.23110746</v>
       </c>
     </row>
     <row r="28">
@@ -1575,37 +1575,37 @@
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>-0.00517331</v>
+        <v>0.03056361</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.00934741</v>
+        <v>0.03343126</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.00324458</v>
+        <v>0.0326743</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.006596299999999999</v>
+        <v>0.01888903</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.01406638</v>
+        <v>2.99475261</v>
       </c>
       <c r="H28" t="n">
-        <v>0.00652111</v>
+        <v>7.039075529999999</v>
       </c>
       <c r="I28" t="n">
-        <v>0.02914014</v>
+        <v>12.50925256</v>
       </c>
       <c r="J28" t="n">
-        <v>0.04879807</v>
+        <v>15.95012964</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0566263</v>
+        <v>22.07160056</v>
       </c>
       <c r="L28" t="n">
-        <v>0.02465099</v>
+        <v>21.72859677</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.00128256</v>
+        <v>24.10372721</v>
       </c>
     </row>
     <row r="29">
@@ -1616,37 +1616,37 @@
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>-0.01281979</v>
+        <v>-0.0015445</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.00154904</v>
+        <v>-0.0003015200000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.00032023</v>
+        <v>0.006606399999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>0.00658342</v>
+        <v>-0.004734899999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.00477515</v>
+        <v>0.004098840000000001</v>
       </c>
       <c r="H29" t="n">
-        <v>0.004036490000000001</v>
+        <v>0.01038032</v>
       </c>
       <c r="I29" t="n">
-        <v>0.01033713</v>
+        <v>0.01827796</v>
       </c>
       <c r="J29" t="n">
-        <v>0.01825068</v>
+        <v>0.02748128</v>
       </c>
       <c r="K29" t="n">
-        <v>0.02746755</v>
+        <v>0.08417767</v>
       </c>
       <c r="L29" t="n">
-        <v>0.08414062</v>
+        <v>0.07505073</v>
       </c>
       <c r="M29" t="n">
-        <v>0.07506878</v>
+        <v>0.03327574</v>
       </c>
     </row>
     <row r="30">
@@ -1657,37 +1657,37 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>-0.0008485099999999998</v>
+        <v>-0.0025532</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0025532</v>
+        <v>0.00442858</v>
       </c>
       <c r="E30" t="n">
-        <v>0.00442858</v>
+        <v>-0.0001344399999999998</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.0001344399999999998</v>
+        <v>-0.00311901</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.00311901</v>
+        <v>-0.00135107</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.00135107</v>
+        <v>-0.00645304</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.00645304</v>
+        <v>-0.0007993899999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.0007993899999999999</v>
+        <v>0.008251139999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>0.008251139999999999</v>
+        <v>0.009377439999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>0.009377439999999999</v>
+        <v>0.00523351</v>
       </c>
       <c r="M30" t="n">
-        <v>0.00523351</v>
+        <v>0.01145842</v>
       </c>
     </row>
     <row r="31">
@@ -1698,37 +1698,37 @@
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>0.03501509000000001</v>
+        <v>-0.05155841000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.05155387</v>
+        <v>0.04293596</v>
       </c>
       <c r="E31" t="n">
-        <v>0.04295467</v>
+        <v>0.009133029999999999</v>
       </c>
       <c r="F31" t="n">
-        <v>0.009156010000000001</v>
+        <v>-0.04374589</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.04370564</v>
+        <v>-0.07127986</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.07121751</v>
+        <v>0.03392271</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0339659</v>
+        <v>0.001830840000000001</v>
       </c>
       <c r="J31" t="n">
-        <v>0.001858120000000001</v>
+        <v>0.1002132</v>
       </c>
       <c r="K31" t="n">
-        <v>0.10022693</v>
+        <v>0.21838147</v>
       </c>
       <c r="L31" t="n">
-        <v>0.21841852</v>
+        <v>0.10953266</v>
       </c>
       <c r="M31" t="n">
-        <v>0.10951461</v>
+        <v>0.03985052000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1739,37 +1739,37 @@
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>0.79667627</v>
+        <v>-0.8938292</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8938292</v>
+        <v>0.26859018</v>
       </c>
       <c r="E32" t="n">
-        <v>0.26859018</v>
+        <v>-1.1550498</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.1550498</v>
+        <v>0.19597777</v>
       </c>
       <c r="G32" t="n">
-        <v>0.19597777</v>
+        <v>0.93832401</v>
       </c>
       <c r="H32" t="n">
-        <v>0.93832401</v>
+        <v>-0.60581137</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.60581137</v>
+        <v>-0.18124846</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.18124846</v>
+        <v>0.6026511899999999</v>
       </c>
       <c r="K32" t="n">
-        <v>0.6026511899999999</v>
+        <v>2.12415212</v>
       </c>
       <c r="L32" t="n">
-        <v>2.12415212</v>
+        <v>3.00018044</v>
       </c>
       <c r="M32" t="n">
-        <v>3.00018044</v>
+        <v>0.8008101</v>
       </c>
     </row>
     <row r="33">
@@ -1780,37 +1780,37 @@
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
-        <v>39.80493465</v>
+        <v>74.52305657000001</v>
       </c>
       <c r="D33" t="n">
-        <v>57.11406416</v>
+        <v>28.77819571</v>
       </c>
       <c r="E33" t="n">
-        <v>20.94755421</v>
+        <v>47.13405325</v>
       </c>
       <c r="F33" t="n">
-        <v>40.21449492</v>
+        <v>17.62821512</v>
       </c>
       <c r="G33" t="n">
-        <v>16.5613197</v>
+        <v>9.357429240000002</v>
       </c>
       <c r="H33" t="n">
-        <v>7.29471993</v>
+        <v>-23.28926443</v>
       </c>
       <c r="I33" t="n">
-        <v>-17.72897884</v>
+        <v>-15.50397747</v>
       </c>
       <c r="J33" t="n">
-        <v>-12.77400785</v>
+        <v>-7.671519279999999</v>
       </c>
       <c r="K33" t="n">
-        <v>-8.503892480000001</v>
+        <v>-12.56496135</v>
       </c>
       <c r="L33" t="n">
-        <v>-15.01818866</v>
+        <v>0.4845926899999997</v>
       </c>
       <c r="M33" t="n">
-        <v>-18.7437909</v>
+        <v>-20.67803373</v>
       </c>
     </row>
     <row r="34">
@@ -1821,37 +1821,37 @@
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
-        <v>11.93656827</v>
+        <v>0.6281405</v>
       </c>
       <c r="D34" t="n">
-        <v>18.03713291</v>
+        <v>0.5322796400000001</v>
       </c>
       <c r="E34" t="n">
-        <v>8.362921139999999</v>
+        <v>0.66688402</v>
       </c>
       <c r="F34" t="n">
-        <v>7.58644235</v>
+        <v>0.39455165</v>
       </c>
       <c r="G34" t="n">
-        <v>1.46144707</v>
+        <v>0.7616216099999999</v>
       </c>
       <c r="H34" t="n">
-        <v>2.82433092</v>
+        <v>0.68170787</v>
       </c>
       <c r="I34" t="n">
-        <v>-4.87857772</v>
+        <v>0.03184879000000001</v>
       </c>
       <c r="J34" t="n">
-        <v>-2.69812083</v>
+        <v>-0.05228055</v>
       </c>
       <c r="K34" t="n">
-        <v>0.7800926499999999</v>
+        <v>-0.22602753</v>
       </c>
       <c r="L34" t="n">
-        <v>2.22719978</v>
+        <v>-0.07364258999999999</v>
       </c>
       <c r="M34" t="n">
-        <v>19.154741</v>
+        <v>-0.3195109</v>
       </c>
     </row>
     <row r="35">
@@ -1860,39 +1860,41 @@
           <t>水泥工業右下</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
       <c r="C35" t="n">
-        <v>281.70180355</v>
+        <v>170.80982995</v>
       </c>
       <c r="D35" t="n">
-        <v>169.91598432</v>
+        <v>150.4790605</v>
       </c>
       <c r="E35" t="n">
-        <v>151.94936306</v>
+        <v>180.35446419</v>
       </c>
       <c r="F35" t="n">
-        <v>180.3735272</v>
+        <v>111.88970622</v>
       </c>
       <c r="G35" t="n">
-        <v>110.71375524</v>
+        <v>152.7060144</v>
       </c>
       <c r="H35" t="n">
-        <v>152.65296865</v>
+        <v>77.88811109999999</v>
       </c>
       <c r="I35" t="n">
-        <v>75.59350051</v>
+        <v>33.94075736</v>
       </c>
       <c r="J35" t="n">
-        <v>33.17521386</v>
+        <v>21.68277256</v>
       </c>
       <c r="K35" t="n">
-        <v>20.83055937</v>
+        <v>34.33086562</v>
       </c>
       <c r="L35" t="n">
-        <v>33.4962376</v>
+        <v>53.02693882</v>
       </c>
       <c r="M35" t="n">
-        <v>52.14474697</v>
+        <v>23.33522736</v>
       </c>
     </row>
     <row r="36">
@@ -1903,37 +1905,37 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>-10.36056243</v>
+        <v>-17.9699727</v>
       </c>
       <c r="D36" t="n">
-        <v>-17.9699727</v>
+        <v>-19.50289189</v>
       </c>
       <c r="E36" t="n">
-        <v>-19.50289189</v>
+        <v>-28.50744565999999</v>
       </c>
       <c r="F36" t="n">
-        <v>-28.50744565999999</v>
+        <v>-22.80401095</v>
       </c>
       <c r="G36" t="n">
-        <v>-22.80401095</v>
+        <v>-20.90837859</v>
       </c>
       <c r="H36" t="n">
-        <v>-20.90837859</v>
+        <v>-1.72982895</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.72982895</v>
+        <v>40.46050624</v>
       </c>
       <c r="J36" t="n">
-        <v>40.46050624</v>
+        <v>77.56024153</v>
       </c>
       <c r="K36" t="n">
-        <v>77.56024153</v>
+        <v>148.03386053</v>
       </c>
       <c r="L36" t="n">
-        <v>148.03386053</v>
+        <v>197.16667387</v>
       </c>
       <c r="M36" t="n">
-        <v>197.16667387</v>
+        <v>110.25012848</v>
       </c>
     </row>
     <row r="37">
@@ -1942,39 +1944,41 @@
           <t>汽車工業右下</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
       <c r="C37" t="n">
-        <v>48.5683695</v>
+        <v>60.3508302</v>
       </c>
       <c r="D37" t="n">
-        <v>49.76717430999999</v>
+        <v>55.00207715</v>
       </c>
       <c r="E37" t="n">
-        <v>53.62179476999999</v>
+        <v>57.56681279999999</v>
       </c>
       <c r="F37" t="n">
-        <v>51.38894450999999</v>
+        <v>31.50297334</v>
       </c>
       <c r="G37" t="n">
-        <v>31.34874639</v>
+        <v>66.61318238</v>
       </c>
       <c r="H37" t="n">
-        <v>57.0445669</v>
+        <v>-5.174916559999999</v>
       </c>
       <c r="I37" t="n">
-        <v>5.79384727</v>
+        <v>-0.8484202900000013</v>
       </c>
       <c r="J37" t="n">
-        <v>-5.19538949</v>
+        <v>17.82853616</v>
       </c>
       <c r="K37" t="n">
-        <v>9.171724370000002</v>
+        <v>38.37265259</v>
       </c>
       <c r="L37" t="n">
-        <v>26.86938084</v>
+        <v>45.696401</v>
       </c>
       <c r="M37" t="n">
-        <v>29.86593954</v>
+        <v>52.00953003</v>
       </c>
     </row>
     <row r="38">
@@ -1985,37 +1989,37 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>129.12775155</v>
+        <v>80.14216560000001</v>
       </c>
       <c r="D38" t="n">
-        <v>79.48442993</v>
+        <v>-13.82458601</v>
       </c>
       <c r="E38" t="n">
-        <v>-14.19438346</v>
+        <v>-65.26758768000001</v>
       </c>
       <c r="F38" t="n">
-        <v>-65.42173446000001</v>
+        <v>-109.62146376</v>
       </c>
       <c r="G38" t="n">
-        <v>-109.56498236</v>
+        <v>-12.84797867</v>
       </c>
       <c r="H38" t="n">
-        <v>-12.6418104</v>
+        <v>-37.14346511</v>
       </c>
       <c r="I38" t="n">
-        <v>-36.88875274</v>
+        <v>-41.53191139</v>
       </c>
       <c r="J38" t="n">
-        <v>-41.23637979999999</v>
+        <v>7.015621090000004</v>
       </c>
       <c r="K38" t="n">
-        <v>6.901248259999999</v>
+        <v>88.53171814</v>
       </c>
       <c r="L38" t="n">
-        <v>88.42745904</v>
+        <v>67.46006622000002</v>
       </c>
       <c r="M38" t="n">
-        <v>67.53254963000001</v>
+        <v>-27.28584806</v>
       </c>
     </row>
     <row r="39">
@@ -2026,37 +2030,37 @@
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
-        <v>32.60895456999999</v>
+        <v>56.67209458</v>
       </c>
       <c r="D39" t="n">
-        <v>56.67209458</v>
+        <v>17.94407397</v>
       </c>
       <c r="E39" t="n">
-        <v>17.94407397</v>
+        <v>33.68792604</v>
       </c>
       <c r="F39" t="n">
-        <v>33.68792604</v>
+        <v>4.108083939999999</v>
       </c>
       <c r="G39" t="n">
-        <v>4.108083939999999</v>
+        <v>73.39446294</v>
       </c>
       <c r="H39" t="n">
-        <v>73.39446294</v>
+        <v>168.35310772</v>
       </c>
       <c r="I39" t="n">
-        <v>168.35310772</v>
+        <v>54.65563677999999</v>
       </c>
       <c r="J39" t="n">
-        <v>54.65563677999999</v>
+        <v>-40.04566426</v>
       </c>
       <c r="K39" t="n">
-        <v>-40.04566426</v>
+        <v>-65.28418285000001</v>
       </c>
       <c r="L39" t="n">
-        <v>-65.28418285000001</v>
+        <v>-32.76076323</v>
       </c>
       <c r="M39" t="n">
-        <v>-32.76076323</v>
+        <v>-17.83607626</v>
       </c>
     </row>
     <row r="40">
@@ -2067,37 +2071,37 @@
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>7.2135412</v>
+        <v>0.08460432999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>0.08460432999999999</v>
+        <v>-3.21255832</v>
       </c>
       <c r="E40" t="n">
-        <v>-3.21255832</v>
+        <v>-6.40072734</v>
       </c>
       <c r="F40" t="n">
-        <v>-6.40072734</v>
+        <v>-3.77333719</v>
       </c>
       <c r="G40" t="n">
-        <v>-3.77333719</v>
+        <v>1.57257904</v>
       </c>
       <c r="H40" t="n">
-        <v>1.57257904</v>
+        <v>-2.42404502</v>
       </c>
       <c r="I40" t="n">
-        <v>-2.42404502</v>
+        <v>-1.22188635</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.22188635</v>
+        <v>2.19978092</v>
       </c>
       <c r="K40" t="n">
-        <v>2.19978092</v>
+        <v>3.24473775</v>
       </c>
       <c r="L40" t="n">
-        <v>3.24473775</v>
+        <v>8.124041649999999</v>
       </c>
       <c r="M40" t="n">
-        <v>8.124041649999999</v>
+        <v>0.408039</v>
       </c>
     </row>
     <row r="41">
@@ -2108,37 +2112,37 @@
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
-        <v>85.15477465000001</v>
+        <v>307.60971191</v>
       </c>
       <c r="D41" t="n">
-        <v>307.60971191</v>
+        <v>433.81361385</v>
       </c>
       <c r="E41" t="n">
-        <v>433.81361385</v>
+        <v>668.62466564</v>
       </c>
       <c r="F41" t="n">
-        <v>668.62466564</v>
+        <v>244.91801602</v>
       </c>
       <c r="G41" t="n">
-        <v>244.91801602</v>
+        <v>320.90370974</v>
       </c>
       <c r="H41" t="n">
-        <v>320.90370974</v>
+        <v>479.18507195</v>
       </c>
       <c r="I41" t="n">
-        <v>479.18507195</v>
+        <v>759.412483</v>
       </c>
       <c r="J41" t="n">
-        <v>759.412483</v>
+        <v>264.18557726</v>
       </c>
       <c r="K41" t="n">
-        <v>264.18557726</v>
+        <v>-87.18150326999999</v>
       </c>
       <c r="L41" t="n">
-        <v>-87.18150326999999</v>
+        <v>-42.95356518</v>
       </c>
       <c r="M41" t="n">
-        <v>-42.95356518</v>
+        <v>-209.92976809</v>
       </c>
     </row>
     <row r="42">
@@ -2149,37 +2153,37 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>5.28251554</v>
+        <v>13.5194183</v>
       </c>
       <c r="D42" t="n">
-        <v>13.5194183</v>
+        <v>7.9181412</v>
       </c>
       <c r="E42" t="n">
-        <v>7.9181412</v>
+        <v>12.13364822</v>
       </c>
       <c r="F42" t="n">
-        <v>12.13364822</v>
+        <v>8.904139349999999</v>
       </c>
       <c r="G42" t="n">
-        <v>8.904139349999999</v>
+        <v>16.35974226</v>
       </c>
       <c r="H42" t="n">
-        <v>16.35974226</v>
+        <v>7.98138634</v>
       </c>
       <c r="I42" t="n">
-        <v>7.98138634</v>
+        <v>11.47238579</v>
       </c>
       <c r="J42" t="n">
-        <v>11.47238579</v>
+        <v>7.112948609999999</v>
       </c>
       <c r="K42" t="n">
-        <v>7.112948609999999</v>
+        <v>19.89156343000001</v>
       </c>
       <c r="L42" t="n">
-        <v>19.89156343000001</v>
+        <v>18.45296431</v>
       </c>
       <c r="M42" t="n">
-        <v>18.45296431</v>
+        <v>5.039715139999999</v>
       </c>
     </row>
     <row r="43">
@@ -2190,37 +2194,37 @@
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
-        <v>-0.7687650100000001</v>
+        <v>-2.06152237</v>
       </c>
       <c r="D43" t="n">
-        <v>-2.06135951</v>
+        <v>-3.503046229999999</v>
       </c>
       <c r="E43" t="n">
-        <v>-3.50289991</v>
+        <v>-4.535445409999999</v>
       </c>
       <c r="F43" t="n">
-        <v>-4.535342749999999</v>
+        <v>-14.41254868</v>
       </c>
       <c r="G43" t="n">
-        <v>-14.41262187</v>
+        <v>-1.50810463</v>
       </c>
       <c r="H43" t="n">
-        <v>-1.50831191</v>
+        <v>12.8362347</v>
       </c>
       <c r="I43" t="n">
-        <v>12.83596378</v>
+        <v>11.30074539</v>
       </c>
       <c r="J43" t="n">
-        <v>11.3006092</v>
+        <v>16.35838766</v>
       </c>
       <c r="K43" t="n">
-        <v>16.35830021</v>
+        <v>15.7316962</v>
       </c>
       <c r="L43" t="n">
-        <v>15.73164693</v>
+        <v>16.78350014</v>
       </c>
       <c r="M43" t="n">
-        <v>16.78381093</v>
+        <v>6.063495510000001</v>
       </c>
     </row>
     <row r="44">
@@ -2229,41 +2233,39 @@
           <t>生技醫療業右下</t>
         </is>
       </c>
-      <c r="B44" t="n">
-        <v>0</v>
-      </c>
+      <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>-104.39741896</v>
+        <v>137.43356436</v>
       </c>
       <c r="D44" t="n">
-        <v>140.65027581</v>
+        <v>267.91917575</v>
       </c>
       <c r="E44" t="n">
-        <v>272.08639937</v>
+        <v>-28.46582557999999</v>
       </c>
       <c r="F44" t="n">
-        <v>-25.901574</v>
+        <v>-233.05188301</v>
       </c>
       <c r="G44" t="n">
-        <v>-232.02450076</v>
+        <v>-348.24805795</v>
       </c>
       <c r="H44" t="n">
-        <v>-348.26715623</v>
+        <v>-325.33619197</v>
       </c>
       <c r="I44" t="n">
-        <v>-324.04951756</v>
+        <v>-311.01459162</v>
       </c>
       <c r="J44" t="n">
-        <v>-311.3992895</v>
+        <v>-66.67316493</v>
       </c>
       <c r="K44" t="n">
-        <v>-64.48894854</v>
+        <v>7.325962460000008</v>
       </c>
       <c r="L44" t="n">
-        <v>21.50698964</v>
+        <v>30.03925212</v>
       </c>
       <c r="M44" t="n">
-        <v>64.43262997000001</v>
+        <v>116.27639912</v>
       </c>
     </row>
     <row r="45">
@@ -2274,37 +2276,37 @@
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
-        <v>94.57192746</v>
+        <v>29.20899821</v>
       </c>
       <c r="D45" t="n">
-        <v>25.9908039</v>
+        <v>-122.68992729</v>
       </c>
       <c r="E45" t="n">
-        <v>-126.85865153</v>
+        <v>-102.43163424</v>
       </c>
       <c r="F45" t="n">
-        <v>-104.9969829</v>
+        <v>-251.88889818</v>
       </c>
       <c r="G45" t="n">
-        <v>-252.91666599</v>
+        <v>-259.91249699</v>
       </c>
       <c r="H45" t="n">
-        <v>-259.89493722</v>
+        <v>-217.70816821</v>
       </c>
       <c r="I45" t="n">
-        <v>-218.99351342</v>
+        <v>39.23945844000001</v>
       </c>
       <c r="J45" t="n">
-        <v>39.62431711000001</v>
+        <v>-31.67881664</v>
       </c>
       <c r="K45" t="n">
-        <v>-33.8640699</v>
+        <v>92.538398</v>
       </c>
       <c r="L45" t="n">
-        <v>78.35728603999999</v>
+        <v>-0.6899875800000015</v>
       </c>
       <c r="M45" t="n">
-        <v>-35.08354371</v>
+        <v>77.88738393999999</v>
       </c>
     </row>
     <row r="46">
@@ -2315,37 +2317,37 @@
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>-1.49148739</v>
+        <v>2.33218234</v>
       </c>
       <c r="D46" t="n">
-        <v>2.33220014</v>
+        <v>-2.68934393</v>
       </c>
       <c r="E46" t="n">
-        <v>-2.68896906</v>
+        <v>-6.34563964</v>
       </c>
       <c r="F46" t="n">
-        <v>-6.34562959</v>
+        <v>-8.06577257</v>
       </c>
       <c r="G46" t="n">
-        <v>-8.065714099999999</v>
+        <v>-5.88842813</v>
       </c>
       <c r="H46" t="n">
-        <v>-5.8884915</v>
+        <v>-5.95638258</v>
       </c>
       <c r="I46" t="n">
-        <v>-5.95645232</v>
+        <v>-5.16063128</v>
       </c>
       <c r="J46" t="n">
-        <v>-5.16068395</v>
+        <v>-5.243901949999999</v>
       </c>
       <c r="K46" t="n">
-        <v>-5.24392124</v>
+        <v>-1.42678741</v>
       </c>
       <c r="L46" t="n">
-        <v>-1.42682006</v>
+        <v>-1.55751561</v>
       </c>
       <c r="M46" t="n">
-        <v>-1.55756925</v>
+        <v>0.21300419</v>
       </c>
     </row>
     <row r="47">
@@ -2356,37 +2358,37 @@
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>51.69443244</v>
+        <v>112.31552985</v>
       </c>
       <c r="D47" t="n">
-        <v>112.31552985</v>
+        <v>53.45619471</v>
       </c>
       <c r="E47" t="n">
-        <v>53.45619471</v>
+        <v>95.04986186999999</v>
       </c>
       <c r="F47" t="n">
-        <v>95.04986186999999</v>
+        <v>9.407378970000002</v>
       </c>
       <c r="G47" t="n">
-        <v>9.407378970000002</v>
+        <v>39.68573421</v>
       </c>
       <c r="H47" t="n">
-        <v>39.68573421</v>
+        <v>4.959421839999997</v>
       </c>
       <c r="I47" t="n">
-        <v>4.959421839999997</v>
+        <v>20.79778082</v>
       </c>
       <c r="J47" t="n">
-        <v>20.79778082</v>
+        <v>26.43966846</v>
       </c>
       <c r="K47" t="n">
-        <v>26.43966846</v>
+        <v>2.098726649999999</v>
       </c>
       <c r="L47" t="n">
-        <v>2.098726649999999</v>
+        <v>-22.66043861</v>
       </c>
       <c r="M47" t="n">
-        <v>-22.66043861</v>
+        <v>-14.22419143</v>
       </c>
     </row>
     <row r="48">
@@ -2397,37 +2399,37 @@
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
-        <v>0.60223238</v>
+        <v>0.39115204</v>
       </c>
       <c r="D48" t="n">
-        <v>0.39113424</v>
+        <v>0.5514035599999999</v>
       </c>
       <c r="E48" t="n">
-        <v>0.55102869</v>
+        <v>0.28994207</v>
       </c>
       <c r="F48" t="n">
-        <v>0.28993202</v>
+        <v>0.02784229000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>0.02778382</v>
+        <v>0.06728542</v>
       </c>
       <c r="H48" t="n">
-        <v>0.06734879000000001</v>
+        <v>-0.10238672</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.10231698</v>
+        <v>-0.002889020000000003</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.002836350000000003</v>
+        <v>1.65310548</v>
       </c>
       <c r="K48" t="n">
-        <v>1.65312477</v>
+        <v>1.32672589</v>
       </c>
       <c r="L48" t="n">
-        <v>1.32675854</v>
+        <v>0.25503158</v>
       </c>
       <c r="M48" t="n">
-        <v>0.2550852199999999</v>
+        <v>-0.002404550000000011</v>
       </c>
     </row>
     <row r="49">
@@ -2438,37 +2440,37 @@
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>-25.86812985</v>
+        <v>-57.67915559</v>
       </c>
       <c r="D49" t="n">
-        <v>-15.37702207</v>
+        <v>-63.73321268000001</v>
       </c>
       <c r="E49" t="n">
-        <v>-21.86573385</v>
+        <v>-46.01752432</v>
       </c>
       <c r="F49" t="n">
-        <v>-5.271030309999998</v>
+        <v>18.17174736</v>
       </c>
       <c r="G49" t="n">
-        <v>10.19355404</v>
+        <v>-62.53515385</v>
       </c>
       <c r="H49" t="n">
-        <v>-56.44455119</v>
+        <v>-58.25113503</v>
       </c>
       <c r="I49" t="n">
-        <v>-46.45714444000001</v>
+        <v>-33.2278322</v>
       </c>
       <c r="J49" t="n">
-        <v>-43.83128722999999</v>
+        <v>-123.32308795</v>
       </c>
       <c r="K49" t="n">
-        <v>-124.85406477</v>
+        <v>-8.951695199999996</v>
       </c>
       <c r="L49" t="n">
-        <v>-35.45945545</v>
+        <v>-117.59873813</v>
       </c>
       <c r="M49" t="n">
-        <v>-130.49968955</v>
+        <v>50.73546306</v>
       </c>
     </row>
     <row r="50">
@@ -2479,37 +2481,37 @@
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
-        <v>-29.6747849</v>
+        <v>-9.074995439999997</v>
       </c>
       <c r="D50" t="n">
-        <v>-9.074995439999997</v>
+        <v>-6.02440684</v>
       </c>
       <c r="E50" t="n">
-        <v>-6.02440684</v>
+        <v>-10.76360972</v>
       </c>
       <c r="F50" t="n">
-        <v>-10.76360972</v>
+        <v>-6.295704290000001</v>
       </c>
       <c r="G50" t="n">
-        <v>-6.295704290000001</v>
+        <v>4.70272614</v>
       </c>
       <c r="H50" t="n">
-        <v>4.70272614</v>
+        <v>-5.524311600000001</v>
       </c>
       <c r="I50" t="n">
-        <v>-5.524311600000001</v>
+        <v>2.53485937</v>
       </c>
       <c r="J50" t="n">
-        <v>2.53485937</v>
+        <v>-2.54366476</v>
       </c>
       <c r="K50" t="n">
-        <v>-2.54366476</v>
+        <v>4.03323023</v>
       </c>
       <c r="L50" t="n">
-        <v>4.03323023</v>
+        <v>-4.208008479999999</v>
       </c>
       <c r="M50" t="n">
-        <v>-4.208008479999999</v>
+        <v>-16.668004</v>
       </c>
     </row>
     <row r="51">
@@ -2520,37 +2522,37 @@
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>-46.76736808</v>
+        <v>23.49764584</v>
       </c>
       <c r="D51" t="n">
-        <v>-18.80448768</v>
+        <v>37.92997215</v>
       </c>
       <c r="E51" t="n">
-        <v>-3.937506679999998</v>
+        <v>12.61239299</v>
       </c>
       <c r="F51" t="n">
-        <v>-28.13410102</v>
+        <v>-0.4921919100000006</v>
       </c>
       <c r="G51" t="n">
-        <v>7.48600141</v>
+        <v>-0.922427120000001</v>
       </c>
       <c r="H51" t="n">
-        <v>-7.01302978</v>
+        <v>-13.15130732</v>
       </c>
       <c r="I51" t="n">
-        <v>-24.94529791</v>
+        <v>20.25898107</v>
       </c>
       <c r="J51" t="n">
-        <v>30.8624361</v>
+        <v>9.548161070000001</v>
       </c>
       <c r="K51" t="n">
-        <v>11.07913789</v>
+        <v>26.06536318</v>
       </c>
       <c r="L51" t="n">
-        <v>52.57312343</v>
+        <v>24.24480782</v>
       </c>
       <c r="M51" t="n">
-        <v>37.14575924</v>
+        <v>11.33630351</v>
       </c>
     </row>
     <row r="52">
@@ -2561,37 +2563,37 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>62.50215</v>
+        <v>255.1197481</v>
       </c>
       <c r="D52" t="n">
-        <v>426.79006651</v>
+        <v>334.97889778</v>
       </c>
       <c r="E52" t="n">
-        <v>557.9386459900001</v>
+        <v>109.84570048</v>
       </c>
       <c r="F52" t="n">
-        <v>166.34689068</v>
+        <v>33.61381624000001</v>
       </c>
       <c r="G52" t="n">
-        <v>-33.08596268</v>
+        <v>15.43591371</v>
       </c>
       <c r="H52" t="n">
-        <v>10.94663334000001</v>
+        <v>-113.78998172</v>
       </c>
       <c r="I52" t="n">
-        <v>-242.48694746</v>
+        <v>166.81981741</v>
       </c>
       <c r="J52" t="n">
-        <v>176.69649829</v>
+        <v>318.94946344</v>
       </c>
       <c r="K52" t="n">
-        <v>173.3919018</v>
+        <v>773.50804662</v>
       </c>
       <c r="L52" t="n">
-        <v>534.26192584</v>
+        <v>812.5688147</v>
       </c>
       <c r="M52" t="n">
-        <v>553.1683261099998</v>
+        <v>211.81430302</v>
       </c>
     </row>
     <row r="53">
@@ -2602,37 +2604,37 @@
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>0.5799572000000005</v>
+        <v>32.29490799</v>
       </c>
       <c r="D53" t="n">
-        <v>10.35363797</v>
+        <v>128.09218056</v>
       </c>
       <c r="E53" t="n">
-        <v>57.30598314999999</v>
+        <v>61.64776729</v>
       </c>
       <c r="F53" t="n">
-        <v>29.58738631</v>
+        <v>3.11852082</v>
       </c>
       <c r="G53" t="n">
-        <v>-1.887194979999999</v>
+        <v>27.04329139</v>
       </c>
       <c r="H53" t="n">
-        <v>3.32307619</v>
+        <v>-24.96587078</v>
       </c>
       <c r="I53" t="n">
-        <v>-21.73914643</v>
+        <v>-20.69356391</v>
       </c>
       <c r="J53" t="n">
-        <v>-5.15073246</v>
+        <v>20.21101647</v>
       </c>
       <c r="K53" t="n">
-        <v>4.636715280000002</v>
+        <v>26.50411286999999</v>
       </c>
       <c r="L53" t="n">
-        <v>-6.085364190000002</v>
+        <v>70.6981641</v>
       </c>
       <c r="M53" t="n">
-        <v>14.57276881</v>
+        <v>48.55903931</v>
       </c>
     </row>
     <row r="54">
@@ -2643,37 +2645,37 @@
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>163.55350801</v>
+        <v>669.1584695800001</v>
       </c>
       <c r="D54" t="n">
-        <v>519.42942119</v>
+        <v>726.66067664</v>
       </c>
       <c r="E54" t="n">
-        <v>574.4871258400001</v>
+        <v>285.06216034</v>
       </c>
       <c r="F54" t="n">
-        <v>260.62135112</v>
+        <v>28.59221987</v>
       </c>
       <c r="G54" t="n">
-        <v>100.29771459</v>
+        <v>201.20493432</v>
       </c>
       <c r="H54" t="n">
-        <v>229.41442989</v>
+        <v>-110.2710851</v>
       </c>
       <c r="I54" t="n">
-        <v>15.19915629</v>
+        <v>105.83019784</v>
       </c>
       <c r="J54" t="n">
-        <v>80.41068551000001</v>
+        <v>-66.32656356</v>
       </c>
       <c r="K54" t="n">
-        <v>94.80529926999999</v>
+        <v>-146.75507464</v>
       </c>
       <c r="L54" t="n">
-        <v>125.0805232</v>
+        <v>-50.16238316000002</v>
       </c>
       <c r="M54" t="n">
-        <v>265.36350072</v>
+        <v>-373.51553864</v>
       </c>
     </row>
     <row r="55">
@@ -2684,37 +2686,37 @@
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>-43.16208043</v>
+        <v>-42.73856727</v>
       </c>
       <c r="D55" t="n">
-        <v>-42.74174993</v>
+        <v>-30.59709092</v>
       </c>
       <c r="E55" t="n">
-        <v>-30.60167928</v>
+        <v>1.71896167</v>
       </c>
       <c r="F55" t="n">
-        <v>1.722041200000001</v>
+        <v>-3.66064519</v>
       </c>
       <c r="G55" t="n">
-        <v>-3.650744</v>
+        <v>6.780631179999999</v>
       </c>
       <c r="H55" t="n">
-        <v>6.78482776</v>
+        <v>-4.03954524</v>
       </c>
       <c r="I55" t="n">
-        <v>-4.03840124</v>
+        <v>17.6737899</v>
       </c>
       <c r="J55" t="n">
-        <v>17.67687168</v>
+        <v>27.54426674</v>
       </c>
       <c r="K55" t="n">
-        <v>27.55673009</v>
+        <v>42.05846305</v>
       </c>
       <c r="L55" t="n">
-        <v>42.07247027</v>
+        <v>41.63408625</v>
       </c>
       <c r="M55" t="n">
-        <v>41.65727162</v>
+        <v>24.46272503</v>
       </c>
     </row>
     <row r="56">
@@ -2725,37 +2727,37 @@
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>-0.4970161599999999</v>
+        <v>-12.04617618</v>
       </c>
       <c r="D56" t="n">
-        <v>-3.79917129</v>
+        <v>-10.68183645</v>
       </c>
       <c r="E56" t="n">
-        <v>-3.020980170000001</v>
+        <v>-2.06279609</v>
       </c>
       <c r="F56" t="n">
-        <v>-3.08701631</v>
+        <v>-7.64622475</v>
       </c>
       <c r="G56" t="n">
-        <v>-3.15672715</v>
+        <v>-7.73074792</v>
       </c>
       <c r="H56" t="n">
-        <v>-1.54350305</v>
+        <v>-13.07103159</v>
       </c>
       <c r="I56" t="n">
-        <v>-4.72110351</v>
+        <v>-3.20736873</v>
       </c>
       <c r="J56" t="n">
-        <v>-3.36279103</v>
+        <v>24.12907413</v>
       </c>
       <c r="K56" t="n">
-        <v>3.84718283</v>
+        <v>19.6328924</v>
       </c>
       <c r="L56" t="n">
-        <v>7.88656417</v>
+        <v>9.521610109999999</v>
       </c>
       <c r="M56" t="n">
-        <v>3.20005212</v>
+        <v>-6.49068987</v>
       </c>
     </row>
     <row r="57">
@@ -2766,37 +2768,37 @@
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
-        <v>-2.00403628</v>
+        <v>-0.00441554</v>
       </c>
       <c r="D57" t="n">
-        <v>-8.248237769999999</v>
+        <v>-0.00559536</v>
       </c>
       <c r="E57" t="n">
-        <v>-7.66186328</v>
+        <v>0.0023543</v>
       </c>
       <c r="F57" t="n">
-        <v>1.02349499</v>
+        <v>0.009692540000000001</v>
       </c>
       <c r="G57" t="n">
-        <v>-4.48970625</v>
+        <v>0.004689029999999999</v>
       </c>
       <c r="H57" t="n">
-        <v>-6.18675242</v>
+        <v>0.00135651</v>
       </c>
       <c r="I57" t="n">
-        <v>-8.349715570000001</v>
+        <v>0.00322831</v>
       </c>
       <c r="J57" t="n">
-        <v>0.155641</v>
+        <v>0.01349009</v>
       </c>
       <c r="K57" t="n">
-        <v>20.28296714</v>
+        <v>0.01471549</v>
       </c>
       <c r="L57" t="n">
-        <v>11.7472462</v>
+        <v>0.02311633</v>
       </c>
       <c r="M57" t="n">
-        <v>6.32177035</v>
+        <v>0.006318600000000001</v>
       </c>
     </row>
     <row r="58">
@@ -2807,37 +2809,37 @@
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>7.82421167</v>
+        <v>-8.713049559999998</v>
       </c>
       <c r="D58" t="n">
-        <v>-8.729579919999999</v>
+        <v>-35.22507341000001</v>
       </c>
       <c r="E58" t="n">
-        <v>-35.23087908</v>
+        <v>-57.92342369999999</v>
       </c>
       <c r="F58" t="n">
-        <v>-57.93050757</v>
+        <v>-68.26387203</v>
       </c>
       <c r="G58" t="n">
-        <v>-68.29303842</v>
+        <v>-8.433303890000001</v>
       </c>
       <c r="H58" t="n">
-        <v>-8.43867049</v>
+        <v>-47.65032497000001</v>
       </c>
       <c r="I58" t="n">
-        <v>-47.65902154</v>
+        <v>7.703351639999999</v>
       </c>
       <c r="J58" t="n">
-        <v>7.732804339999999</v>
+        <v>41.98299858</v>
       </c>
       <c r="K58" t="n">
-        <v>42.01228871</v>
+        <v>64.00418524</v>
       </c>
       <c r="L58" t="n">
-        <v>64.01109449</v>
+        <v>37.16416376</v>
       </c>
       <c r="M58" t="n">
-        <v>37.16176833999999</v>
+        <v>48.23396804</v>
       </c>
     </row>
     <row r="59">
@@ -2848,37 +2850,37 @@
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
-        <v>1.64936867</v>
+        <v>0.74069321</v>
       </c>
       <c r="D59" t="n">
-        <v>0.75722357</v>
+        <v>0.24380428</v>
       </c>
       <c r="E59" t="n">
-        <v>0.24960995</v>
+        <v>1.14616828</v>
       </c>
       <c r="F59" t="n">
-        <v>1.15325215</v>
+        <v>0.01365724</v>
       </c>
       <c r="G59" t="n">
-        <v>0.04282362999999999</v>
+        <v>0.7604645999999999</v>
       </c>
       <c r="H59" t="n">
-        <v>0.7658311999999999</v>
+        <v>-0.24529395</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.23659738</v>
+        <v>-0.70815295</v>
       </c>
       <c r="J59" t="n">
-        <v>-0.73760565</v>
+        <v>0.59361993</v>
       </c>
       <c r="K59" t="n">
-        <v>0.5643298</v>
+        <v>1.16829318</v>
       </c>
       <c r="L59" t="n">
-        <v>1.16138393</v>
+        <v>1.87308302</v>
       </c>
       <c r="M59" t="n">
-        <v>1.87547844</v>
+        <v>2.42560356</v>
       </c>
     </row>
     <row r="60">
@@ -2889,37 +2891,37 @@
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
-        <v>-43.80415462</v>
+        <v>-59.54142481</v>
       </c>
       <c r="D60" t="n">
-        <v>-59.54155184</v>
+        <v>-59.83005495</v>
       </c>
       <c r="E60" t="n">
-        <v>-59.83004735</v>
+        <v>-20.09428251</v>
       </c>
       <c r="F60" t="n">
-        <v>-20.09411328</v>
+        <v>-30.92647838</v>
       </c>
       <c r="G60" t="n">
-        <v>-30.92602812</v>
+        <v>-15.12595207</v>
       </c>
       <c r="H60" t="n">
-        <v>-15.12563885</v>
+        <v>19.01596501</v>
       </c>
       <c r="I60" t="n">
-        <v>19.01618865</v>
+        <v>32.19631332</v>
       </c>
       <c r="J60" t="n">
-        <v>32.19645427</v>
+        <v>66.0032384</v>
       </c>
       <c r="K60" t="n">
-        <v>66.00343606</v>
+        <v>95.20201191</v>
       </c>
       <c r="L60" t="n">
-        <v>95.20223728000001</v>
+        <v>52.08602065</v>
       </c>
       <c r="M60" t="n">
-        <v>52.08611158</v>
+        <v>56.26502794</v>
       </c>
     </row>
     <row r="61">
@@ -2930,37 +2932,37 @@
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
-        <v>0.0007849500000000001</v>
+        <v>-0.0023249</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.0023249</v>
+        <v>-0.00285701</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.00285701</v>
+        <v>-0.0007670700000000002</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.0007670700000000002</v>
+        <v>-0.00377332</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.00377332</v>
+        <v>-0.00373142</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.00373142</v>
+        <v>-0.00726259</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.00726259</v>
+        <v>-0.0029527</v>
       </c>
       <c r="J61" t="n">
-        <v>-0.0029527</v>
+        <v>-0.00233591</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.00233591</v>
+        <v>0.007300940000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>0.007300940000000001</v>
+        <v>0.00539476</v>
       </c>
       <c r="M61" t="n">
-        <v>0.00539476</v>
+        <v>0.00131784</v>
       </c>
     </row>
     <row r="62">
@@ -2971,37 +2973,37 @@
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>3.88186996</v>
+        <v>-6.97425895</v>
       </c>
       <c r="D62" t="n">
-        <v>-6.97413192</v>
+        <v>-18.18743927</v>
       </c>
       <c r="E62" t="n">
-        <v>-18.18744687</v>
+        <v>54.93221536000001</v>
       </c>
       <c r="F62" t="n">
-        <v>54.93204613</v>
+        <v>-0.1317017699999996</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.1321520299999996</v>
+        <v>15.73889917</v>
       </c>
       <c r="H62" t="n">
-        <v>15.73858595</v>
+        <v>-2.45223579</v>
       </c>
       <c r="I62" t="n">
-        <v>-2.45245943</v>
+        <v>28.65223851</v>
       </c>
       <c r="J62" t="n">
-        <v>28.65209756</v>
+        <v>47.66581753</v>
       </c>
       <c r="K62" t="n">
-        <v>47.66561987</v>
+        <v>94.86338957</v>
       </c>
       <c r="L62" t="n">
-        <v>94.8631642</v>
+        <v>46.74774283000001</v>
       </c>
       <c r="M62" t="n">
-        <v>46.74765190000001</v>
+        <v>41.24747026</v>
       </c>
     </row>
     <row r="63">
@@ -3012,37 +3014,37 @@
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>0.00012031</v>
+        <v>-2.134999999999999e-05</v>
       </c>
       <c r="D63" t="n">
-        <v>-2.134999999999999e-05</v>
+        <v>0.00012761</v>
       </c>
       <c r="E63" t="n">
-        <v>0.00012761</v>
+        <v>0.00014581</v>
       </c>
       <c r="F63" t="n">
-        <v>0.00014581</v>
+        <v>0.00033086</v>
       </c>
       <c r="G63" t="n">
-        <v>0.00033086</v>
+        <v>0.0004248200000000001</v>
       </c>
       <c r="H63" t="n">
-        <v>0.0004248200000000001</v>
+        <v>0.00090755</v>
       </c>
       <c r="I63" t="n">
-        <v>0.00090755</v>
+        <v>0.00103174</v>
       </c>
       <c r="J63" t="n">
-        <v>0.00103174</v>
+        <v>0.0009914099999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>0.0009914099999999999</v>
+        <v>6.247e-05</v>
       </c>
       <c r="L63" t="n">
-        <v>6.247e-05</v>
+        <v>0.0004044</v>
       </c>
       <c r="M63" t="n">
-        <v>0.0004044</v>
+        <v>0.00072251</v>
       </c>
     </row>
     <row r="64">
@@ -3053,37 +3055,37 @@
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
-        <v>-0.00013752</v>
+        <v>-0.00019394</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.00019394</v>
+        <v>-0.00018756</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.00018756</v>
+        <v>-0.00024988</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.00024988</v>
+        <v>-0.00027272</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.00027272</v>
+        <v>-0.0002611</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.0002611</v>
+        <v>-0.00027651</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.00027651</v>
+        <v>-0.0002609000000000001</v>
       </c>
       <c r="J64" t="n">
-        <v>-0.0002609000000000001</v>
+        <v>5.814e-05</v>
       </c>
       <c r="K64" t="n">
-        <v>5.814e-05</v>
+        <v>0.00018835</v>
       </c>
       <c r="L64" t="n">
-        <v>0.00018835</v>
+        <v>2.243e-05</v>
       </c>
       <c r="M64" t="n">
-        <v>2.243e-05</v>
+        <v>-8.019e-05</v>
       </c>
     </row>
     <row r="65">
@@ -3094,37 +3096,37 @@
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
-        <v>466.0886352000001</v>
+        <v>662.4879303500001</v>
       </c>
       <c r="D65" t="n">
-        <v>639.80339804</v>
+        <v>637.64115263</v>
       </c>
       <c r="E65" t="n">
-        <v>565.26139745</v>
+        <v>1115.98903911</v>
       </c>
       <c r="F65" t="n">
-        <v>1107.65330267</v>
+        <v>915.3000246800001</v>
       </c>
       <c r="G65" t="n">
-        <v>908.9790999300001</v>
+        <v>208.17638257</v>
       </c>
       <c r="H65" t="n">
-        <v>245.79030677</v>
+        <v>489.72836174</v>
       </c>
       <c r="I65" t="n">
-        <v>523.4402324600001</v>
+        <v>57.70085710999999</v>
       </c>
       <c r="J65" t="n">
-        <v>30.59805887999999</v>
+        <v>224.03415516</v>
       </c>
       <c r="K65" t="n">
-        <v>205.16998145</v>
+        <v>719.02437558</v>
       </c>
       <c r="L65" t="n">
-        <v>749.09681401</v>
+        <v>228.66167738</v>
       </c>
       <c r="M65" t="n">
-        <v>201.40933403</v>
+        <v>582.55440177</v>
       </c>
     </row>
     <row r="66">
@@ -3133,41 +3135,39 @@
           <t>通信網路業右下</t>
         </is>
       </c>
-      <c r="B66" t="n">
-        <v>0</v>
-      </c>
+      <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>1.80144518</v>
+        <v>19.83930881</v>
       </c>
       <c r="D66" t="n">
-        <v>19.8069366</v>
+        <v>16.35814125</v>
       </c>
       <c r="E66" t="n">
-        <v>16.12262531</v>
+        <v>14.85698009</v>
       </c>
       <c r="F66" t="n">
-        <v>15.01315617</v>
+        <v>19.65247369</v>
       </c>
       <c r="G66" t="n">
-        <v>19.88208755</v>
+        <v>-17.09074356</v>
       </c>
       <c r="H66" t="n">
-        <v>-17.25743567</v>
+        <v>-53.14245764</v>
       </c>
       <c r="I66" t="n">
-        <v>-53.04367808</v>
+        <v>-3.999204540000001</v>
       </c>
       <c r="J66" t="n">
-        <v>-4.322311980000001</v>
+        <v>33.33790329</v>
       </c>
       <c r="K66" t="n">
-        <v>31.29953269</v>
+        <v>2.42368097</v>
       </c>
       <c r="L66" t="n">
-        <v>-1.56919705</v>
+        <v>1.515334689999999</v>
       </c>
       <c r="M66" t="n">
-        <v>0.9433941799999992</v>
+        <v>-43.93684397</v>
       </c>
     </row>
     <row r="67">
@@ -3178,37 +3178,37 @@
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>261.10249401</v>
+        <v>187.54828935</v>
       </c>
       <c r="D67" t="n">
-        <v>234.53640338</v>
+        <v>478.09473449</v>
       </c>
       <c r="E67" t="n">
-        <v>554.9897066300001</v>
+        <v>802.31982062</v>
       </c>
       <c r="F67" t="n">
-        <v>795.63674016</v>
+        <v>284.10601792</v>
       </c>
       <c r="G67" t="n">
-        <v>300.45455142</v>
+        <v>306.83132503</v>
       </c>
       <c r="H67" t="n">
-        <v>288.66631953</v>
+        <v>92.04780836999998</v>
       </c>
       <c r="I67" t="n">
-        <v>56.95423210999999</v>
+        <v>302.24299464</v>
       </c>
       <c r="J67" t="n">
-        <v>319.39536125</v>
+        <v>86.33250495000001</v>
       </c>
       <c r="K67" t="n">
-        <v>111.32482997</v>
+        <v>151.6696509</v>
       </c>
       <c r="L67" t="n">
-        <v>106.38826172</v>
+        <v>96.78635402999998</v>
       </c>
       <c r="M67" t="n">
-        <v>143.20773013</v>
+        <v>-82.53214648999999</v>
       </c>
     </row>
     <row r="68">
@@ -3219,37 +3219,37 @@
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>6.954071790000001</v>
+        <v>8.895559609999999</v>
       </c>
       <c r="D68" t="n">
-        <v>8.895559609999999</v>
+        <v>25.77768484</v>
       </c>
       <c r="E68" t="n">
-        <v>25.77768484</v>
+        <v>7.5358798</v>
       </c>
       <c r="F68" t="n">
-        <v>7.5358798</v>
+        <v>-2.18453111</v>
       </c>
       <c r="G68" t="n">
-        <v>-2.18453111</v>
+        <v>-4.28064262</v>
       </c>
       <c r="H68" t="n">
-        <v>-4.28064262</v>
+        <v>-9.848016550000001</v>
       </c>
       <c r="I68" t="n">
-        <v>-9.848016550000001</v>
+        <v>-11.75977663</v>
       </c>
       <c r="J68" t="n">
-        <v>-11.75977663</v>
+        <v>-14.45543988</v>
       </c>
       <c r="K68" t="n">
-        <v>-14.45543988</v>
+        <v>-8.60103045</v>
       </c>
       <c r="L68" t="n">
-        <v>-8.60103045</v>
+        <v>1.481096</v>
       </c>
       <c r="M68" t="n">
-        <v>1.481096</v>
+        <v>-2.09694106</v>
       </c>
     </row>
     <row r="69">
@@ -3260,37 +3260,37 @@
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>-1.57228821</v>
+        <v>-0.33839224</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.33839224</v>
+        <v>-1.43394215</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.43394215</v>
+        <v>-1.69268373</v>
       </c>
       <c r="F69" t="n">
-        <v>-1.69268373</v>
+        <v>-3.23010772</v>
       </c>
       <c r="G69" t="n">
-        <v>-3.23010772</v>
+        <v>-3.39045584</v>
       </c>
       <c r="H69" t="n">
-        <v>-3.39045584</v>
+        <v>-4.06147909</v>
       </c>
       <c r="I69" t="n">
-        <v>-4.06147909</v>
+        <v>-3.60733925</v>
       </c>
       <c r="J69" t="n">
-        <v>-3.60733925</v>
+        <v>-1.16033294</v>
       </c>
       <c r="K69" t="n">
-        <v>-1.16033294</v>
+        <v>-1.55525517</v>
       </c>
       <c r="L69" t="n">
-        <v>-1.55525517</v>
+        <v>0.15859867</v>
       </c>
       <c r="M69" t="n">
-        <v>0.15859867</v>
+        <v>-0.01651628</v>
       </c>
     </row>
     <row r="70">
@@ -3301,37 +3301,37 @@
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>-10.01798231</v>
+        <v>-16.91394174</v>
       </c>
       <c r="D70" t="n">
-        <v>-16.91394174</v>
+        <v>-16.82706139</v>
       </c>
       <c r="E70" t="n">
-        <v>-16.82706139</v>
+        <v>-21.49287157</v>
       </c>
       <c r="F70" t="n">
-        <v>-21.49287157</v>
+        <v>-29.75249595</v>
       </c>
       <c r="G70" t="n">
-        <v>-29.75249595</v>
+        <v>-5.49167339</v>
       </c>
       <c r="H70" t="n">
-        <v>-5.49167339</v>
+        <v>-6.985563310000001</v>
       </c>
       <c r="I70" t="n">
-        <v>-6.985563310000001</v>
+        <v>6.14054282</v>
       </c>
       <c r="J70" t="n">
-        <v>6.14054282</v>
+        <v>22.89727625</v>
       </c>
       <c r="K70" t="n">
-        <v>22.89727625</v>
+        <v>39.58487804</v>
       </c>
       <c r="L70" t="n">
-        <v>39.58487804</v>
+        <v>49.03197814</v>
       </c>
       <c r="M70" t="n">
-        <v>49.03197814</v>
+        <v>20.29127258</v>
       </c>
     </row>
     <row r="71">
@@ -3342,37 +3342,37 @@
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
-        <v>86.08082459000001</v>
+        <v>65.03796482999999</v>
       </c>
       <c r="D71" t="n">
-        <v>65.03796482999999</v>
+        <v>7.475289409999997</v>
       </c>
       <c r="E71" t="n">
-        <v>7.475289409999997</v>
+        <v>-64.07427258999999</v>
       </c>
       <c r="F71" t="n">
-        <v>-64.07427258999999</v>
+        <v>-115.50237892</v>
       </c>
       <c r="G71" t="n">
-        <v>-115.50237892</v>
+        <v>-11.79256974999999</v>
       </c>
       <c r="H71" t="n">
-        <v>-11.79256974999999</v>
+        <v>-141.47987787</v>
       </c>
       <c r="I71" t="n">
-        <v>-141.47987787</v>
+        <v>-101.90599359</v>
       </c>
       <c r="J71" t="n">
-        <v>-101.90599359</v>
+        <v>-27.86393122</v>
       </c>
       <c r="K71" t="n">
-        <v>-27.86393122</v>
+        <v>-19.72376035</v>
       </c>
       <c r="L71" t="n">
-        <v>-19.72376035</v>
+        <v>-80.99866675</v>
       </c>
       <c r="M71" t="n">
-        <v>-80.99866675</v>
+        <v>-115.79851781</v>
       </c>
     </row>
     <row r="72">
@@ -3383,37 +3383,37 @@
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>18.48568502</v>
+        <v>16.39634759</v>
       </c>
       <c r="D72" t="n">
-        <v>16.39634759</v>
+        <v>4.281030289999999</v>
       </c>
       <c r="E72" t="n">
-        <v>4.281030289999999</v>
+        <v>5.539278160000001</v>
       </c>
       <c r="F72" t="n">
-        <v>5.539278160000001</v>
+        <v>-2.54610903</v>
       </c>
       <c r="G72" t="n">
-        <v>-2.54610903</v>
+        <v>-1.68230068</v>
       </c>
       <c r="H72" t="n">
-        <v>-1.68230068</v>
+        <v>-10.98006195</v>
       </c>
       <c r="I72" t="n">
-        <v>-10.98006195</v>
+        <v>0.2389688799999998</v>
       </c>
       <c r="J72" t="n">
-        <v>0.2389688799999998</v>
+        <v>11.07624471</v>
       </c>
       <c r="K72" t="n">
-        <v>11.07624471</v>
+        <v>3.90076889</v>
       </c>
       <c r="L72" t="n">
-        <v>3.90076889</v>
+        <v>-10.60413652</v>
       </c>
       <c r="M72" t="n">
-        <v>-10.60413652</v>
+        <v>-10.73076839</v>
       </c>
     </row>
     <row r="73">
@@ -3424,37 +3424,37 @@
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
-        <v>-479.96587393</v>
+        <v>-775.45050197</v>
       </c>
       <c r="D73" t="n">
-        <v>-775.45050197</v>
+        <v>-1055.71776824</v>
       </c>
       <c r="E73" t="n">
-        <v>-1055.71776824</v>
+        <v>-1344.25654867</v>
       </c>
       <c r="F73" t="n">
-        <v>-1344.25654867</v>
+        <v>-1513.10008246</v>
       </c>
       <c r="G73" t="n">
-        <v>-1513.10008246</v>
+        <v>-486.52127426</v>
       </c>
       <c r="H73" t="n">
-        <v>-486.52127426</v>
+        <v>-936.91281313</v>
       </c>
       <c r="I73" t="n">
-        <v>-936.91281313</v>
+        <v>59.42146735</v>
       </c>
       <c r="J73" t="n">
-        <v>59.42146735</v>
+        <v>903.2323206300001</v>
       </c>
       <c r="K73" t="n">
-        <v>903.2323206300001</v>
+        <v>800.7780561700001</v>
       </c>
       <c r="L73" t="n">
-        <v>800.7780561700001</v>
+        <v>1167.48715472</v>
       </c>
       <c r="M73" t="n">
-        <v>1167.48715472</v>
+        <v>823.8283143199999</v>
       </c>
     </row>
     <row r="74">
@@ -3465,37 +3465,37 @@
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
-        <v>-250.80931058</v>
+        <v>-889.3013006599999</v>
       </c>
       <c r="D74" t="n">
-        <v>-871.11949227</v>
+        <v>-155.54415517</v>
       </c>
       <c r="E74" t="n">
-        <v>-140.20681045</v>
+        <v>-454.77151971</v>
       </c>
       <c r="F74" t="n">
-        <v>-444.35116709</v>
+        <v>-641.20146943</v>
       </c>
       <c r="G74" t="n">
-        <v>-637.1793570799999</v>
+        <v>-347.05644305</v>
       </c>
       <c r="H74" t="n">
-        <v>-352.1735925200001</v>
+        <v>-359.8776884299999</v>
       </c>
       <c r="I74" t="n">
-        <v>-360.48232321</v>
+        <v>-343.74413127</v>
       </c>
       <c r="J74" t="n">
-        <v>-337.9095999</v>
+        <v>-136.81080979</v>
       </c>
       <c r="K74" t="n">
-        <v>-136.63508772</v>
+        <v>34.65447583</v>
       </c>
       <c r="L74" t="n">
-        <v>35.29096643</v>
+        <v>112.2585677</v>
       </c>
       <c r="M74" t="n">
-        <v>110.83660003</v>
+        <v>-45.85452738</v>
       </c>
     </row>
     <row r="75">
@@ -3506,37 +3506,37 @@
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
-        <v>87.23155</v>
+        <v>-18.2611149</v>
       </c>
       <c r="D75" t="n">
-        <v>-36.44292329</v>
+        <v>-58.58307425</v>
       </c>
       <c r="E75" t="n">
-        <v>-73.92041897</v>
+        <v>-125.06047454</v>
       </c>
       <c r="F75" t="n">
-        <v>-135.48082716</v>
+        <v>-179.56732411</v>
       </c>
       <c r="G75" t="n">
-        <v>-183.58943646</v>
+        <v>-83.0036958</v>
       </c>
       <c r="H75" t="n">
-        <v>-77.88654633</v>
+        <v>-145.13371544</v>
       </c>
       <c r="I75" t="n">
-        <v>-144.52908066</v>
+        <v>17.82308436</v>
       </c>
       <c r="J75" t="n">
-        <v>11.98855299</v>
+        <v>181.23442961</v>
       </c>
       <c r="K75" t="n">
-        <v>181.05870754</v>
+        <v>133.4526263</v>
       </c>
       <c r="L75" t="n">
-        <v>132.8161357</v>
+        <v>161.94001351</v>
       </c>
       <c r="M75" t="n">
-        <v>163.36198118</v>
+        <v>47.34589182</v>
       </c>
     </row>
     <row r="76">
@@ -3547,37 +3547,37 @@
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>-0.00018871</v>
+        <v>-0.00053725</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.00053725</v>
+        <v>-0.00057684</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.00057684</v>
+        <v>-0.0006594299999999999</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.0006594299999999999</v>
+        <v>-0.00071329</v>
       </c>
       <c r="G76" t="n">
-        <v>-0.00071329</v>
+        <v>-0.0003751</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.0003751</v>
+        <v>-0.00072667</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.00072667</v>
+        <v>-0.00031853</v>
       </c>
       <c r="J76" t="n">
-        <v>-0.00031853</v>
+        <v>-0.00042214</v>
       </c>
       <c r="K76" t="n">
-        <v>-0.00042214</v>
+        <v>0.00035191</v>
       </c>
       <c r="L76" t="n">
-        <v>0.00035191</v>
+        <v>0.0006016</v>
       </c>
       <c r="M76" t="n">
-        <v>0.0006016</v>
+        <v>0.00119589</v>
       </c>
     </row>
     <row r="77">
@@ -3588,37 +3588,37 @@
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="n">
-        <v>0.0006396900000000001</v>
+        <v>0.00368509</v>
       </c>
       <c r="D77" t="n">
-        <v>0.00368509</v>
+        <v>0.004119070000000001</v>
       </c>
       <c r="E77" t="n">
-        <v>0.004119070000000001</v>
+        <v>0.00104634</v>
       </c>
       <c r="F77" t="n">
-        <v>0.00104634</v>
+        <v>-0.00267286</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.00267286</v>
+        <v>-9.306000000000001e-05</v>
       </c>
       <c r="H77" t="n">
-        <v>-9.306000000000001e-05</v>
+        <v>-0.00439828</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.00439828</v>
+        <v>-0.005935770000000001</v>
       </c>
       <c r="J77" t="n">
-        <v>-0.005935770000000001</v>
+        <v>-0.006376339999999999</v>
       </c>
       <c r="K77" t="n">
-        <v>-0.006376339999999999</v>
+        <v>-0.00146164</v>
       </c>
       <c r="L77" t="n">
-        <v>-0.00146164</v>
+        <v>0.0001785999999999999</v>
       </c>
       <c r="M77" t="n">
-        <v>0.0001785999999999999</v>
+        <v>0.00166505</v>
       </c>
     </row>
     <row r="78">
@@ -3629,37 +3629,37 @@
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
-        <v>-0.00053355</v>
+        <v>-0.0004297</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.0004297</v>
+        <v>-0.00048908</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.00048908</v>
+        <v>-0.00026955</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.00026955</v>
+        <v>-0.00035725</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.00035725</v>
+        <v>-0.00052145</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.00052145</v>
+        <v>-0.00052038</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.00052038</v>
+        <v>-0.00049876</v>
       </c>
       <c r="J78" t="n">
-        <v>-0.00049876</v>
+        <v>-0.00010349</v>
       </c>
       <c r="K78" t="n">
-        <v>-0.00010349</v>
+        <v>0.00149008</v>
       </c>
       <c r="L78" t="n">
-        <v>0.00149008</v>
+        <v>0.00167124</v>
       </c>
       <c r="M78" t="n">
-        <v>0.00167124</v>
+        <v>0.00103193</v>
       </c>
     </row>
     <row r="79">
@@ -3670,37 +3670,37 @@
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="n">
-        <v>3.13082996</v>
+        <v>12.60022255</v>
       </c>
       <c r="D79" t="n">
-        <v>12.50540977</v>
+        <v>28.00022631</v>
       </c>
       <c r="E79" t="n">
-        <v>27.84336579</v>
+        <v>3.68878533</v>
       </c>
       <c r="F79" t="n">
-        <v>3.57885056</v>
+        <v>-6.56068165</v>
       </c>
       <c r="G79" t="n">
-        <v>-6.574561549999999</v>
+        <v>5.127412570000001</v>
       </c>
       <c r="H79" t="n">
-        <v>5.12920975</v>
+        <v>0.3745234199999999</v>
       </c>
       <c r="I79" t="n">
-        <v>0.3989783500000001</v>
+        <v>-13.08952523</v>
       </c>
       <c r="J79" t="n">
-        <v>-13.06068005</v>
+        <v>-4.331212519999999</v>
       </c>
       <c r="K79" t="n">
-        <v>-4.237776240000001</v>
+        <v>-10.25827174</v>
       </c>
       <c r="L79" t="n">
-        <v>-10.05923</v>
+        <v>8.421552140000001</v>
       </c>
       <c r="M79" t="n">
-        <v>8.441145179999999</v>
+        <v>-10.13260721</v>
       </c>
     </row>
     <row r="80">
@@ -3711,37 +3711,37 @@
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="n">
-        <v>189.01949834</v>
+        <v>59.36770919</v>
       </c>
       <c r="D80" t="n">
-        <v>59.36770919</v>
+        <v>36.53568006</v>
       </c>
       <c r="E80" t="n">
-        <v>36.53568006</v>
+        <v>-46.66810387</v>
       </c>
       <c r="F80" t="n">
-        <v>-46.66810387</v>
+        <v>-86.27307861</v>
       </c>
       <c r="G80" t="n">
-        <v>-86.27307861</v>
+        <v>4.663124380000001</v>
       </c>
       <c r="H80" t="n">
-        <v>4.663124380000001</v>
+        <v>-72.56750855</v>
       </c>
       <c r="I80" t="n">
-        <v>-72.56750855</v>
+        <v>-104.41170928</v>
       </c>
       <c r="J80" t="n">
-        <v>-104.41170928</v>
+        <v>-113.93601583</v>
       </c>
       <c r="K80" t="n">
-        <v>-113.93601583</v>
+        <v>-69.00746740999999</v>
       </c>
       <c r="L80" t="n">
-        <v>-69.00746740999999</v>
+        <v>-46.30035985</v>
       </c>
       <c r="M80" t="n">
-        <v>-46.30035985</v>
+        <v>-65.86029197000001</v>
       </c>
     </row>
     <row r="81">
@@ -3752,37 +3752,37 @@
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>253.98290476</v>
+        <v>106.93633643</v>
       </c>
       <c r="D81" t="n">
-        <v>107.03114921</v>
+        <v>356.67279654</v>
       </c>
       <c r="E81" t="n">
-        <v>356.82965706</v>
+        <v>507.0029775</v>
       </c>
       <c r="F81" t="n">
-        <v>507.11291227</v>
+        <v>775.8204341100001</v>
       </c>
       <c r="G81" t="n">
-        <v>775.8343140100001</v>
+        <v>804.0151174700002</v>
       </c>
       <c r="H81" t="n">
-        <v>804.0133202900001</v>
+        <v>245.61859538</v>
       </c>
       <c r="I81" t="n">
-        <v>245.59414045</v>
+        <v>6.446631980000004</v>
       </c>
       <c r="J81" t="n">
-        <v>6.417786799999997</v>
+        <v>101.28266764</v>
       </c>
       <c r="K81" t="n">
-        <v>101.18923136</v>
+        <v>-46.01295269999999</v>
       </c>
       <c r="L81" t="n">
-        <v>-46.21199444</v>
+        <v>3.234432050000005</v>
       </c>
       <c r="M81" t="n">
-        <v>3.214839009999998</v>
+        <v>-165.87367631</v>
       </c>
     </row>
     <row r="82">
@@ -3793,37 +3793,37 @@
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
-        <v>-13.58472732</v>
+        <v>-10.64403632</v>
       </c>
       <c r="D82" t="n">
-        <v>-10.64403632</v>
+        <v>-5.600883880000002</v>
       </c>
       <c r="E82" t="n">
-        <v>-5.600883880000002</v>
+        <v>-16.1009798</v>
       </c>
       <c r="F82" t="n">
-        <v>-16.1009798</v>
+        <v>35.45646956</v>
       </c>
       <c r="G82" t="n">
-        <v>35.45646956</v>
+        <v>68.03330789</v>
       </c>
       <c r="H82" t="n">
-        <v>68.03330789</v>
+        <v>-4.41017006</v>
       </c>
       <c r="I82" t="n">
-        <v>-4.41017006</v>
+        <v>-6.688197980000001</v>
       </c>
       <c r="J82" t="n">
-        <v>-6.688197980000001</v>
+        <v>39.15618257</v>
       </c>
       <c r="K82" t="n">
-        <v>39.15618257</v>
+        <v>88.37693567999999</v>
       </c>
       <c r="L82" t="n">
-        <v>88.37693567999999</v>
+        <v>173.80208869</v>
       </c>
       <c r="M82" t="n">
-        <v>173.80208869</v>
+        <v>68.31111571000001</v>
       </c>
     </row>
     <row r="83">
@@ -3834,37 +3834,37 @@
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>45.51688189</v>
+        <v>10.48398042</v>
       </c>
       <c r="D83" t="n">
-        <v>10.48398042</v>
+        <v>-6.200787319999999</v>
       </c>
       <c r="E83" t="n">
-        <v>-6.200787319999999</v>
+        <v>7.24090026</v>
       </c>
       <c r="F83" t="n">
-        <v>7.24090026</v>
+        <v>-6.584324479999999</v>
       </c>
       <c r="G83" t="n">
-        <v>-6.584324479999999</v>
+        <v>102.05297551</v>
       </c>
       <c r="H83" t="n">
-        <v>102.05297551</v>
+        <v>-115.80629482</v>
       </c>
       <c r="I83" t="n">
-        <v>-115.80629482</v>
+        <v>-143.5880583</v>
       </c>
       <c r="J83" t="n">
-        <v>-143.5880583</v>
+        <v>-122.46679617</v>
       </c>
       <c r="K83" t="n">
-        <v>-122.46679617</v>
+        <v>-54.09129918000001</v>
       </c>
       <c r="L83" t="n">
-        <v>-54.09129918000001</v>
+        <v>-10.37837567</v>
       </c>
       <c r="M83" t="n">
-        <v>-10.37837567</v>
+        <v>20.72719751</v>
       </c>
     </row>
     <row r="84">
@@ -3875,37 +3875,37 @@
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
-        <v>5.51182728</v>
+        <v>-15.07566146</v>
       </c>
       <c r="D84" t="n">
-        <v>-15.07566146</v>
+        <v>-25.78377224</v>
       </c>
       <c r="E84" t="n">
-        <v>-25.78377224</v>
+        <v>-21.74778079</v>
       </c>
       <c r="F84" t="n">
-        <v>-21.74778079</v>
+        <v>-16.410326</v>
       </c>
       <c r="G84" t="n">
-        <v>-16.410326</v>
+        <v>-1.11322981</v>
       </c>
       <c r="H84" t="n">
-        <v>-1.11322981</v>
+        <v>-17.97659833</v>
       </c>
       <c r="I84" t="n">
-        <v>-17.97659833</v>
+        <v>-22.4468883</v>
       </c>
       <c r="J84" t="n">
-        <v>-22.4468883</v>
+        <v>-6.5081971</v>
       </c>
       <c r="K84" t="n">
-        <v>-6.5081971</v>
+        <v>10.56673461</v>
       </c>
       <c r="L84" t="n">
-        <v>10.56673461</v>
+        <v>91.63808985999999</v>
       </c>
       <c r="M84" t="n">
-        <v>91.63808985999999</v>
+        <v>307.9549315100001</v>
       </c>
     </row>
     <row r="85">
@@ -3916,37 +3916,37 @@
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>35.31476152</v>
+        <v>2.312927219999999</v>
       </c>
       <c r="D85" t="n">
-        <v>2.312927219999999</v>
+        <v>-14.73780212</v>
       </c>
       <c r="E85" t="n">
-        <v>-14.73780212</v>
+        <v>45.55591851</v>
       </c>
       <c r="F85" t="n">
-        <v>45.55591851</v>
+        <v>20.93663418</v>
       </c>
       <c r="G85" t="n">
-        <v>20.93663418</v>
+        <v>83.75538558</v>
       </c>
       <c r="H85" t="n">
-        <v>83.75538558</v>
+        <v>31.50825829</v>
       </c>
       <c r="I85" t="n">
-        <v>31.50825829</v>
+        <v>43.48443047</v>
       </c>
       <c r="J85" t="n">
-        <v>43.48443047</v>
+        <v>13.09829768</v>
       </c>
       <c r="K85" t="n">
-        <v>13.09829768</v>
+        <v>98.23389636000002</v>
       </c>
       <c r="L85" t="n">
-        <v>98.23389636000002</v>
+        <v>22.42436713</v>
       </c>
       <c r="M85" t="n">
-        <v>22.42436713</v>
+        <v>-73.80742721999999</v>
       </c>
     </row>
     <row r="86">
@@ -3957,37 +3957,37 @@
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
-        <v>14.30691095</v>
+        <v>17.21231996</v>
       </c>
       <c r="D86" t="n">
-        <v>17.21217532</v>
+        <v>9.666825319999999</v>
       </c>
       <c r="E86" t="n">
-        <v>9.6667656</v>
+        <v>13.81801526</v>
       </c>
       <c r="F86" t="n">
-        <v>13.81802202</v>
+        <v>0.01406337</v>
       </c>
       <c r="G86" t="n">
-        <v>0.01408597999999998</v>
+        <v>3.64720106</v>
       </c>
       <c r="H86" t="n">
-        <v>3.64727612</v>
+        <v>-2.23925099</v>
       </c>
       <c r="I86" t="n">
-        <v>-2.23915729</v>
+        <v>2.45052868</v>
       </c>
       <c r="J86" t="n">
-        <v>2.45049239</v>
+        <v>5.204550360000001</v>
       </c>
       <c r="K86" t="n">
-        <v>5.20443463</v>
+        <v>8.83929865</v>
       </c>
       <c r="L86" t="n">
-        <v>8.837787029999999</v>
+        <v>9.964043440000001</v>
       </c>
       <c r="M86" t="n">
-        <v>9.958617460000001</v>
+        <v>13.17166716</v>
       </c>
     </row>
     <row r="87">
@@ -3998,37 +3998,37 @@
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>1.417260900000001</v>
+        <v>-80.45010463</v>
       </c>
       <c r="D87" t="n">
-        <v>-80.44995999</v>
+        <v>-30.7117032</v>
       </c>
       <c r="E87" t="n">
-        <v>-30.71164348</v>
+        <v>27.71205671000001</v>
       </c>
       <c r="F87" t="n">
-        <v>27.71204995</v>
+        <v>-45.84531368</v>
       </c>
       <c r="G87" t="n">
-        <v>-45.84533629</v>
+        <v>12.14279822</v>
       </c>
       <c r="H87" t="n">
-        <v>12.14272316</v>
+        <v>-71.90968674000001</v>
       </c>
       <c r="I87" t="n">
-        <v>-71.90978043999999</v>
+        <v>-32.61418556</v>
       </c>
       <c r="J87" t="n">
-        <v>-32.61414927000001</v>
+        <v>15.83394507</v>
       </c>
       <c r="K87" t="n">
-        <v>15.8340608</v>
+        <v>67.44021103999999</v>
       </c>
       <c r="L87" t="n">
-        <v>67.44172266</v>
+        <v>91.11812440999999</v>
       </c>
       <c r="M87" t="n">
-        <v>91.12355039000001</v>
+        <v>48.69966612</v>
       </c>
     </row>
     <row r="88">
@@ -4039,37 +4039,37 @@
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
-        <v>1469.03355356</v>
+        <v>1996.88248885</v>
       </c>
       <c r="D88" t="n">
-        <v>2192.38968272</v>
+        <v>335.27676698</v>
       </c>
       <c r="E88" t="n">
-        <v>796.7331753599999</v>
+        <v>1948.0038844</v>
       </c>
       <c r="F88" t="n">
-        <v>2711.92330755</v>
+        <v>1153.77468284</v>
       </c>
       <c r="G88" t="n">
-        <v>1458.58061226</v>
+        <v>539.04257491</v>
       </c>
       <c r="H88" t="n">
-        <v>670.5646738299999</v>
+        <v>2122.39441528</v>
       </c>
       <c r="I88" t="n">
-        <v>2015.23936833</v>
+        <v>3114.11401218</v>
       </c>
       <c r="J88" t="n">
-        <v>2827.54758005</v>
+        <v>535.38563185</v>
       </c>
       <c r="K88" t="n">
-        <v>282.75142694</v>
+        <v>2986.65455767</v>
       </c>
       <c r="L88" t="n">
-        <v>2979.97262876</v>
+        <v>1363.49813312</v>
       </c>
       <c r="M88" t="n">
-        <v>1281.51913489</v>
+        <v>1129.59196537</v>
       </c>
     </row>
     <row r="89">
@@ -4080,37 +4080,37 @@
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>-207.57083162</v>
+        <v>23.02808266000001</v>
       </c>
       <c r="D89" t="n">
-        <v>22.89105058000001</v>
+        <v>-393.3110172200001</v>
       </c>
       <c r="E89" t="n">
-        <v>-393.01372625</v>
+        <v>-84.92967764999997</v>
       </c>
       <c r="F89" t="n">
-        <v>-84.66222935999997</v>
+        <v>931.5082035199999</v>
       </c>
       <c r="G89" t="n">
-        <v>931.52277498</v>
+        <v>1129.79374479</v>
       </c>
       <c r="H89" t="n">
-        <v>1129.91593369</v>
+        <v>75.17580845000001</v>
       </c>
       <c r="I89" t="n">
-        <v>75.35369751</v>
+        <v>124.00556606</v>
       </c>
       <c r="J89" t="n">
-        <v>123.92895526</v>
+        <v>-315.54687746</v>
       </c>
       <c r="K89" t="n">
-        <v>-315.90783049</v>
+        <v>-262.35812686</v>
       </c>
       <c r="L89" t="n">
-        <v>-262.85001529</v>
+        <v>-595.77949269</v>
       </c>
       <c r="M89" t="n">
-        <v>-596.34841211</v>
+        <v>-488.48068716</v>
       </c>
     </row>
     <row r="90">
@@ -4121,37 +4121,37 @@
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>415.33194817</v>
+        <v>613.0285305599999</v>
       </c>
       <c r="D90" t="n">
-        <v>502.50672949</v>
+        <v>1028.85588277</v>
       </c>
       <c r="E90" t="n">
-        <v>713.8885992099999</v>
+        <v>1400.70349727</v>
       </c>
       <c r="F90" t="n">
-        <v>788.71285189</v>
+        <v>362.31040698</v>
       </c>
       <c r="G90" t="n">
-        <v>112.24879993</v>
+        <v>-123.31977285</v>
       </c>
       <c r="H90" t="n">
-        <v>-152.73262748</v>
+        <v>-697.82611378</v>
       </c>
       <c r="I90" t="n">
-        <v>-432.85711792</v>
+        <v>-789.66948011</v>
       </c>
       <c r="J90" t="n">
-        <v>-467.08175312</v>
+        <v>-685.6988509600001</v>
       </c>
       <c r="K90" t="n">
-        <v>-365.40042852</v>
+        <v>102.33780019</v>
       </c>
       <c r="L90" t="n">
-        <v>195.5472825</v>
+        <v>-660.33446947</v>
       </c>
       <c r="M90" t="n">
-        <v>-469.65131659</v>
+        <v>-822.70220537</v>
       </c>
     </row>
     <row r="91">
@@ -4162,37 +4162,37 @@
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>1374.52931941</v>
+        <v>-204.85211993</v>
       </c>
       <c r="D91" t="n">
-        <v>-196.01497756</v>
+        <v>-973.5193657500001</v>
       </c>
       <c r="E91" t="n">
-        <v>-960.5770264</v>
+        <v>-396.29097509</v>
       </c>
       <c r="F91" t="n">
-        <v>-381.97723422</v>
+        <v>-273.7276208100001</v>
       </c>
       <c r="G91" t="n">
-        <v>-279.8947880800001</v>
+        <v>-267.98953925</v>
       </c>
       <c r="H91" t="n">
-        <v>-266.33976855</v>
+        <v>-144.3117167</v>
       </c>
       <c r="I91" t="n">
-        <v>-137.76573277</v>
+        <v>236.34830219</v>
       </c>
       <c r="J91" t="n">
-        <v>229.69125497</v>
+        <v>-1051.47495583</v>
       </c>
       <c r="K91" t="n">
-        <v>-1071.53426478</v>
+        <v>-1059.65958156</v>
       </c>
       <c r="L91" t="n">
-        <v>-1052.8689742</v>
+        <v>-274.4274442199999</v>
       </c>
       <c r="M91" t="n">
-        <v>-302.7896797499999</v>
+        <v>842.66042312</v>
       </c>
     </row>
     <row r="92">
@@ -4201,41 +4201,39 @@
           <t>電機機械右下</t>
         </is>
       </c>
-      <c r="B92" t="n">
-        <v>0</v>
-      </c>
+      <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>122.39367207</v>
+        <v>91.51347527999999</v>
       </c>
       <c r="D92" t="n">
-        <v>91.62158169</v>
+        <v>-52.62426496</v>
       </c>
       <c r="E92" t="n">
-        <v>-52.15505964</v>
+        <v>-40.00041285</v>
       </c>
       <c r="F92" t="n">
-        <v>-40.56079284999999</v>
+        <v>-83.57204142000001</v>
       </c>
       <c r="G92" t="n">
-        <v>-83.17373404999999</v>
+        <v>59.78413285</v>
       </c>
       <c r="H92" t="n">
-        <v>58.18204148</v>
+        <v>-48.40594169</v>
       </c>
       <c r="I92" t="n">
-        <v>-48.50096176</v>
+        <v>-27.57166399000001</v>
       </c>
       <c r="J92" t="n">
-        <v>-28.45410904000001</v>
+        <v>-25.67902986999999</v>
       </c>
       <c r="K92" t="n">
-        <v>-26.98770348</v>
+        <v>43.66845514999999</v>
       </c>
       <c r="L92" t="n">
-        <v>42.02259498999999</v>
+        <v>-81.55704404000001</v>
       </c>
       <c r="M92" t="n">
-        <v>-82.26534513000001</v>
+        <v>60.4838282</v>
       </c>
     </row>
     <row r="93">
@@ -4246,37 +4244,37 @@
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>55.76439599</v>
+        <v>88.50512777000002</v>
       </c>
       <c r="D93" t="n">
-        <v>79.66820878</v>
+        <v>320.60971411</v>
       </c>
       <c r="E93" t="n">
-        <v>307.66783073</v>
+        <v>443.84527893</v>
       </c>
       <c r="F93" t="n">
-        <v>429.53197474</v>
+        <v>95.96630688</v>
       </c>
       <c r="G93" t="n">
-        <v>102.13408786</v>
+        <v>151.7448347</v>
       </c>
       <c r="H93" t="n">
-        <v>150.09547556</v>
+        <v>313.97923944</v>
       </c>
       <c r="I93" t="n">
-        <v>307.43352346</v>
+        <v>104.99983746</v>
       </c>
       <c r="J93" t="n">
-        <v>111.6570151</v>
+        <v>-28.7795355</v>
       </c>
       <c r="K93" t="n">
-        <v>-8.719710409999996</v>
+        <v>-96.91518439000001</v>
       </c>
       <c r="L93" t="n">
-        <v>-103.70588004</v>
+        <v>-12.38750471</v>
       </c>
       <c r="M93" t="n">
-        <v>15.97168822</v>
+        <v>108.83205481</v>
       </c>
     </row>
     <row r="94">
@@ -4287,37 +4285,37 @@
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>-812.2786350600001</v>
+        <v>683.4299987600001</v>
       </c>
       <c r="D94" t="n">
-        <v>683.4299987600001</v>
+        <v>-196.7993444</v>
       </c>
       <c r="E94" t="n">
-        <v>-196.7993444</v>
+        <v>1230.67429305</v>
       </c>
       <c r="F94" t="n">
-        <v>1230.67429305</v>
+        <v>736.97943814</v>
       </c>
       <c r="G94" t="n">
-        <v>736.97943814</v>
+        <v>980.9976145999998</v>
       </c>
       <c r="H94" t="n">
-        <v>980.9976145999998</v>
+        <v>3039.80295137</v>
       </c>
       <c r="I94" t="n">
-        <v>3039.80295137</v>
+        <v>2679.37978635</v>
       </c>
       <c r="J94" t="n">
-        <v>2684.70702195</v>
+        <v>398.0836465900001</v>
       </c>
       <c r="K94" t="n">
-        <v>405.27107273</v>
+        <v>4014.61282152</v>
       </c>
       <c r="L94" t="n">
-        <v>4022.20344772</v>
+        <v>1780.16211673</v>
       </c>
       <c r="M94" t="n">
-        <v>1787.99012331</v>
+        <v>2571.08829643</v>
       </c>
     </row>
     <row r="95">
@@ -4328,37 +4326,37 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>39.63236597</v>
+        <v>52.17459030999999</v>
       </c>
       <c r="D95" t="n">
-        <v>52.16923741999999</v>
+        <v>69.41372987999999</v>
       </c>
       <c r="E95" t="n">
-        <v>69.4114786</v>
+        <v>81.05502186</v>
       </c>
       <c r="F95" t="n">
-        <v>81.05528531</v>
+        <v>-13.09397059</v>
       </c>
       <c r="G95" t="n">
-        <v>-13.09141086</v>
+        <v>56.25579081</v>
       </c>
       <c r="H95" t="n">
-        <v>56.25626138000001</v>
+        <v>19.28692427</v>
       </c>
       <c r="I95" t="n">
-        <v>19.28790825</v>
+        <v>2.439667629999996</v>
       </c>
       <c r="J95" t="n">
-        <v>2.439236129999996</v>
+        <v>23.74875729999999</v>
       </c>
       <c r="K95" t="n">
-        <v>23.74705774</v>
+        <v>212.58224952</v>
       </c>
       <c r="L95" t="n">
-        <v>212.57975408</v>
+        <v>25.10754408</v>
       </c>
       <c r="M95" t="n">
-        <v>25.10469356999999</v>
+        <v>-8.521788389999998</v>
       </c>
     </row>
     <row r="96">
@@ -4369,37 +4367,37 @@
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>162.61287903</v>
+        <v>82.56180853999999</v>
       </c>
       <c r="D96" t="n">
-        <v>82.56716143</v>
+        <v>-45.38727709</v>
       </c>
       <c r="E96" t="n">
-        <v>-45.38502581</v>
+        <v>36.56860685999999</v>
       </c>
       <c r="F96" t="n">
-        <v>36.56834340999999</v>
+        <v>-202.14985793</v>
       </c>
       <c r="G96" t="n">
-        <v>-202.15241766</v>
+        <v>-255.07433364</v>
       </c>
       <c r="H96" t="n">
-        <v>-255.07480421</v>
+        <v>-104.43925519</v>
       </c>
       <c r="I96" t="n">
-        <v>-104.44023917</v>
+        <v>0.229008960000001</v>
       </c>
       <c r="J96" t="n">
-        <v>-5.097795139999999</v>
+        <v>-49.91969638000001</v>
       </c>
       <c r="K96" t="n">
-        <v>-57.10542296000001</v>
+        <v>183.11732523</v>
       </c>
       <c r="L96" t="n">
-        <v>175.52919447</v>
+        <v>-43.94704785000001</v>
       </c>
       <c r="M96" t="n">
-        <v>-51.77220392000001</v>
+        <v>88.96946446</v>
       </c>
     </row>
     <row r="97">
@@ -4410,37 +4408,37 @@
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>-56.04735297</v>
+        <v>-57.87665437</v>
       </c>
       <c r="D97" t="n">
-        <v>-57.87707799</v>
+        <v>-36.62885614</v>
       </c>
       <c r="E97" t="n">
-        <v>-36.62934033</v>
+        <v>-32.91272461</v>
       </c>
       <c r="F97" t="n">
-        <v>-32.91337125</v>
+        <v>-31.98487371</v>
       </c>
       <c r="G97" t="n">
-        <v>-31.98540542</v>
+        <v>-28.05827051</v>
       </c>
       <c r="H97" t="n">
-        <v>-28.05852503</v>
+        <v>-31.36616687</v>
       </c>
       <c r="I97" t="n">
-        <v>-31.36661549</v>
+        <v>-10.44515264</v>
       </c>
       <c r="J97" t="n">
-        <v>-10.44575734</v>
+        <v>26.32759989</v>
       </c>
       <c r="K97" t="n">
-        <v>26.3273587</v>
+        <v>54.67073346</v>
       </c>
       <c r="L97" t="n">
-        <v>54.67085678</v>
+        <v>42.46099433</v>
       </c>
       <c r="M97" t="n">
-        <v>42.46093398</v>
+        <v>0.9574884200000013</v>
       </c>
     </row>
     <row r="98">
@@ -4449,39 +4447,41 @@
           <t>食品工業右下</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr"/>
+      <c r="B98" t="n">
+        <v>0</v>
+      </c>
       <c r="C98" t="n">
-        <v>8.902682299999999</v>
+        <v>-6.83742472</v>
       </c>
       <c r="D98" t="n">
-        <v>-7.00097985</v>
+        <v>-8.384741280000002</v>
       </c>
       <c r="E98" t="n">
-        <v>-8.586387240000001</v>
+        <v>-10.39423065</v>
       </c>
       <c r="F98" t="n">
-        <v>-10.56307657</v>
+        <v>-11.35658426</v>
       </c>
       <c r="G98" t="n">
-        <v>-11.32923905</v>
+        <v>2.90771855</v>
       </c>
       <c r="H98" t="n">
-        <v>2.98401102</v>
+        <v>1.30504188</v>
       </c>
       <c r="I98" t="n">
-        <v>1.30875266</v>
+        <v>-3.46681689</v>
       </c>
       <c r="J98" t="n">
-        <v>-3.510710399999999</v>
+        <v>10.1722114</v>
       </c>
       <c r="K98" t="n">
-        <v>10.10491649</v>
+        <v>13.3762424</v>
       </c>
       <c r="L98" t="n">
-        <v>13.23640147</v>
+        <v>17.45927326</v>
       </c>
       <c r="M98" t="n">
-        <v>17.26166795</v>
+        <v>6.2808356</v>
       </c>
     </row>
     <row r="99">
@@ -4492,37 +4492,37 @@
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>-53.37129473</v>
+        <v>-138.98959363</v>
       </c>
       <c r="D99" t="n">
-        <v>-138.98917001</v>
+        <v>-186.96238045</v>
       </c>
       <c r="E99" t="n">
-        <v>-186.96189626</v>
+        <v>-263.10589982</v>
       </c>
       <c r="F99" t="n">
-        <v>-263.10525318</v>
+        <v>-271.70482822</v>
       </c>
       <c r="G99" t="n">
-        <v>-271.70429651</v>
+        <v>-157.31249025</v>
       </c>
       <c r="H99" t="n">
-        <v>-157.31223573</v>
+        <v>-223.51401407</v>
       </c>
       <c r="I99" t="n">
-        <v>-223.51356545</v>
+        <v>-120.79845952</v>
       </c>
       <c r="J99" t="n">
-        <v>-120.79785482</v>
+        <v>-51.94084032</v>
       </c>
       <c r="K99" t="n">
-        <v>-51.94059913</v>
+        <v>-88.74990566</v>
       </c>
       <c r="L99" t="n">
-        <v>-88.75002898</v>
+        <v>-109.41670096</v>
       </c>
       <c r="M99" t="n">
-        <v>-109.41664061</v>
+        <v>-136.86063727</v>
       </c>
     </row>
   </sheetData>

--- a/Result/analyze_2.xlsx
+++ b/Result/analyze_2.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
     </row>
@@ -503,37 +503,37 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>226.69442662</v>
+        <v>66.56199049</v>
       </c>
       <c r="D2" t="n">
-        <v>52.37458780999999</v>
+        <v>356.56633246</v>
       </c>
       <c r="E2" t="n">
-        <v>346.3266347</v>
+        <v>-35.06648140000001</v>
       </c>
       <c r="F2" t="n">
-        <v>-46.92070764000001</v>
+        <v>252.61035904</v>
       </c>
       <c r="G2" t="n">
-        <v>245.1040941</v>
+        <v>605.75553287</v>
       </c>
       <c r="H2" t="n">
-        <v>595.52490181</v>
+        <v>658.30641657</v>
       </c>
       <c r="I2" t="n">
-        <v>655.98303823</v>
+        <v>947.5900919199998</v>
       </c>
       <c r="J2" t="n">
-        <v>928.59263271</v>
+        <v>1854.05646702</v>
       </c>
       <c r="K2" t="n">
-        <v>1831.29052201</v>
+        <v>1081.37279024</v>
       </c>
       <c r="L2" t="n">
-        <v>1078.39506312</v>
+        <v>129.60770167</v>
       </c>
       <c r="M2" t="n">
-        <v>140.45337218</v>
+        <v>631.62990461</v>
       </c>
     </row>
     <row r="3">
@@ -542,41 +542,39 @@
           <t>光電業右下</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>64.97403704999999</v>
+        <v>147.11955259</v>
       </c>
       <c r="D3" t="n">
-        <v>146.86998653</v>
+        <v>213.90499924</v>
       </c>
       <c r="E3" t="n">
-        <v>212.41895508</v>
+        <v>119.41768033</v>
       </c>
       <c r="F3" t="n">
-        <v>119.19690213</v>
+        <v>182.4498646</v>
       </c>
       <c r="G3" t="n">
-        <v>180.68861742</v>
+        <v>17.55563291</v>
       </c>
       <c r="H3" t="n">
-        <v>18.85457105</v>
+        <v>-4.824857839999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.291154179999999</v>
+        <v>127.74288916</v>
       </c>
       <c r="J3" t="n">
-        <v>126.95353454</v>
+        <v>240.46139432</v>
       </c>
       <c r="K3" t="n">
-        <v>238.00361817</v>
+        <v>154.10382631</v>
       </c>
       <c r="L3" t="n">
-        <v>153.37178115</v>
+        <v>42.91116328</v>
       </c>
       <c r="M3" t="n">
-        <v>43.75407812</v>
+        <v>-75.75932651000001</v>
       </c>
     </row>
     <row r="4">
@@ -587,37 +585,37 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>155.14548277</v>
+        <v>2.342279479999998</v>
       </c>
       <c r="D4" t="n">
-        <v>16.79314675</v>
+        <v>-32.16710158000001</v>
       </c>
       <c r="E4" t="n">
-        <v>-20.42905813</v>
+        <v>-164.12047036</v>
       </c>
       <c r="F4" t="n">
-        <v>-152.03154317</v>
+        <v>-79.31165050000001</v>
       </c>
       <c r="G4" t="n">
-        <v>-70.02958740000001</v>
+        <v>-159.22496314</v>
       </c>
       <c r="H4" t="n">
-        <v>-150.27702911</v>
+        <v>-197.39125332</v>
       </c>
       <c r="I4" t="n">
-        <v>-197.58998783</v>
+        <v>-41.53954115</v>
       </c>
       <c r="J4" t="n">
-        <v>-21.7445414</v>
+        <v>76.91706268999999</v>
       </c>
       <c r="K4" t="n">
-        <v>102.14636438</v>
+        <v>42.5827177</v>
       </c>
       <c r="L4" t="n">
-        <v>46.30012961999999</v>
+        <v>249.34874036</v>
       </c>
       <c r="M4" t="n">
-        <v>237.66588987</v>
+        <v>50.02287835999999</v>
       </c>
     </row>
     <row r="5">
@@ -628,37 +626,37 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>186.82811691</v>
+        <v>467.8486097100001</v>
       </c>
       <c r="D5" t="n">
-        <v>467.8486097100001</v>
+        <v>758.27988239</v>
       </c>
       <c r="E5" t="n">
-        <v>758.27988239</v>
+        <v>802.10536136</v>
       </c>
       <c r="F5" t="n">
-        <v>802.10536136</v>
+        <v>1311.67929021</v>
       </c>
       <c r="G5" t="n">
-        <v>1311.67929021</v>
+        <v>1402.60968035</v>
       </c>
       <c r="H5" t="n">
-        <v>1402.60968035</v>
+        <v>947.1777888099999</v>
       </c>
       <c r="I5" t="n">
-        <v>947.1777888099999</v>
+        <v>633.92100185</v>
       </c>
       <c r="J5" t="n">
-        <v>633.92100185</v>
+        <v>146.03438519</v>
       </c>
       <c r="K5" t="n">
-        <v>146.03438519</v>
+        <v>-38.63471579000001</v>
       </c>
       <c r="L5" t="n">
-        <v>-38.63471579000001</v>
+        <v>-259.31947403</v>
       </c>
       <c r="M5" t="n">
-        <v>-259.31947403</v>
+        <v>-387.10504069</v>
       </c>
     </row>
     <row r="6">
@@ -669,37 +667,37 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>36.31469387999999</v>
+        <v>-15.0706052</v>
       </c>
       <c r="D6" t="n">
-        <v>-15.0706052</v>
+        <v>-36.497385</v>
       </c>
       <c r="E6" t="n">
-        <v>-36.497385</v>
+        <v>-50.54128249</v>
       </c>
       <c r="F6" t="n">
-        <v>-50.54128249</v>
+        <v>-51.15769783</v>
       </c>
       <c r="G6" t="n">
-        <v>-51.15769783</v>
+        <v>-140.94534825</v>
       </c>
       <c r="H6" t="n">
-        <v>-140.94534825</v>
+        <v>-65.33151937999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-65.33151937999999</v>
+        <v>61.92808129000001</v>
       </c>
       <c r="J6" t="n">
-        <v>61.92808129000001</v>
+        <v>11.71021567</v>
       </c>
       <c r="K6" t="n">
-        <v>11.71021567</v>
+        <v>17.56998252</v>
       </c>
       <c r="L6" t="n">
-        <v>17.56998252</v>
+        <v>63.34027448999999</v>
       </c>
       <c r="M6" t="n">
-        <v>63.34027448999999</v>
+        <v>80.29391962000001</v>
       </c>
     </row>
     <row r="7">
@@ -710,37 +708,37 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>35.57194729</v>
+        <v>23.90388811</v>
       </c>
       <c r="D7" t="n">
-        <v>23.90388811</v>
+        <v>18.06926711</v>
       </c>
       <c r="E7" t="n">
-        <v>18.06926711</v>
+        <v>12.93300413</v>
       </c>
       <c r="F7" t="n">
-        <v>12.93300413</v>
+        <v>23.36286784</v>
       </c>
       <c r="G7" t="n">
-        <v>23.36286784</v>
+        <v>8.285323009999999</v>
       </c>
       <c r="H7" t="n">
-        <v>8.285323009999999</v>
+        <v>8.104432200000002</v>
       </c>
       <c r="I7" t="n">
-        <v>8.104432200000002</v>
+        <v>10.62024648</v>
       </c>
       <c r="J7" t="n">
-        <v>10.62024648</v>
+        <v>11.86696109</v>
       </c>
       <c r="K7" t="n">
-        <v>11.86696109</v>
+        <v>20.20766957</v>
       </c>
       <c r="L7" t="n">
-        <v>20.20766957</v>
+        <v>0.2825462599999979</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2825462599999979</v>
+        <v>-11.2621924</v>
       </c>
     </row>
     <row r="8">
@@ -751,37 +749,37 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>1584.29256748</v>
+        <v>1683.83113943</v>
       </c>
       <c r="D8" t="n">
-        <v>1683.81233496</v>
+        <v>1748.64109344</v>
       </c>
       <c r="E8" t="n">
-        <v>1748.64659283</v>
+        <v>215.04394201</v>
       </c>
       <c r="F8" t="n">
-        <v>215.04205531</v>
+        <v>-175.58447045</v>
       </c>
       <c r="G8" t="n">
-        <v>-175.62021034</v>
+        <v>1440.98172734</v>
       </c>
       <c r="H8" t="n">
-        <v>1440.97706319</v>
+        <v>2243.00173656</v>
       </c>
       <c r="I8" t="n">
-        <v>2243.01446221</v>
+        <v>1059.05512781</v>
       </c>
       <c r="J8" t="n">
-        <v>1059.07981602</v>
+        <v>1234.59418381</v>
       </c>
       <c r="K8" t="n">
-        <v>1234.60981361</v>
+        <v>1217.90332761</v>
       </c>
       <c r="L8" t="n">
-        <v>1217.94262096</v>
+        <v>3045.29876754</v>
       </c>
       <c r="M8" t="n">
-        <v>3045.32173068</v>
+        <v>3122.67857891</v>
       </c>
     </row>
     <row r="9">
@@ -790,41 +788,39 @@
           <t>其他電子業右下</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>64.29671705</v>
+        <v>23.99344998</v>
       </c>
       <c r="D9" t="n">
-        <v>24.0433653</v>
+        <v>-2.67383328</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.54934967</v>
+        <v>5.24493221</v>
       </c>
       <c r="F9" t="n">
-        <v>5.40608709</v>
+        <v>17.46157312</v>
       </c>
       <c r="G9" t="n">
-        <v>17.64058699</v>
+        <v>-19.11340726</v>
       </c>
       <c r="H9" t="n">
-        <v>-18.94161078</v>
+        <v>37.53061692</v>
       </c>
       <c r="I9" t="n">
-        <v>37.6284706</v>
+        <v>35.45856086</v>
       </c>
       <c r="J9" t="n">
-        <v>35.63575449</v>
+        <v>39.33183526</v>
       </c>
       <c r="K9" t="n">
-        <v>39.53916686</v>
+        <v>-2.70690422</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.4616413</v>
+        <v>12.50393308</v>
       </c>
       <c r="M9" t="n">
-        <v>12.69502643</v>
+        <v>-57.61832385</v>
       </c>
     </row>
     <row r="10">
@@ -835,37 +831,37 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>45.38712386</v>
+        <v>11.40590219</v>
       </c>
       <c r="D10" t="n">
-        <v>11.35598687</v>
+        <v>11.26137</v>
       </c>
       <c r="E10" t="n">
-        <v>11.13688639</v>
+        <v>-26.04180533</v>
       </c>
       <c r="F10" t="n">
-        <v>-26.20296021</v>
+        <v>3.156710680000001</v>
       </c>
       <c r="G10" t="n">
-        <v>2.97769681</v>
+        <v>-15.41229293</v>
       </c>
       <c r="H10" t="n">
-        <v>-15.58408941</v>
+        <v>42.70911246</v>
       </c>
       <c r="I10" t="n">
-        <v>42.61125878</v>
+        <v>57.47363111</v>
       </c>
       <c r="J10" t="n">
-        <v>57.29643747999999</v>
+        <v>76.00098144</v>
       </c>
       <c r="K10" t="n">
-        <v>75.79364984</v>
+        <v>25.30690511</v>
       </c>
       <c r="L10" t="n">
-        <v>25.06164219</v>
+        <v>53.20174472999999</v>
       </c>
       <c r="M10" t="n">
-        <v>53.01065138</v>
+        <v>72.04851831000001</v>
       </c>
     </row>
     <row r="11">
@@ -876,37 +872,37 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>33.45564705</v>
+        <v>16.97882196</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78153094</v>
+        <v>33.95849969</v>
       </c>
       <c r="E11" t="n">
-        <v>73.32758289</v>
+        <v>31.73740261</v>
       </c>
       <c r="F11" t="n">
-        <v>16.3233625</v>
+        <v>63.07150558</v>
       </c>
       <c r="G11" t="n">
-        <v>61.35117289</v>
+        <v>142.43566523</v>
       </c>
       <c r="H11" t="n">
-        <v>130.87621041</v>
+        <v>62.10685783</v>
       </c>
       <c r="I11" t="n">
-        <v>56.54414629999999</v>
+        <v>74.96178202999999</v>
       </c>
       <c r="J11" t="n">
-        <v>55.50389919000001</v>
+        <v>-2.548439399999999</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.38883577</v>
+        <v>-40.94177412</v>
       </c>
       <c r="L11" t="n">
-        <v>-58.09566982</v>
+        <v>-70.05006009</v>
       </c>
       <c r="M11" t="n">
-        <v>-77.91717035000001</v>
+        <v>-55.17203984</v>
       </c>
     </row>
     <row r="12">
@@ -915,41 +911,39 @@
           <t>化學工業右下</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>181.12827274</v>
+        <v>65.88534808999999</v>
       </c>
       <c r="D12" t="n">
-        <v>62.28709359</v>
+        <v>39.67649825</v>
       </c>
       <c r="E12" t="n">
-        <v>47.51182313</v>
+        <v>-59.92998233</v>
       </c>
       <c r="F12" t="n">
-        <v>-67.86251213</v>
+        <v>109.62239728</v>
       </c>
       <c r="G12" t="n">
-        <v>117.04709593</v>
+        <v>-5.024762610000002</v>
       </c>
       <c r="H12" t="n">
-        <v>1.19653822</v>
+        <v>-76.45363953</v>
       </c>
       <c r="I12" t="n">
-        <v>-83.11722171000001</v>
+        <v>-101.38021878</v>
       </c>
       <c r="J12" t="n">
-        <v>-44.36274827</v>
+        <v>-73.76798635999999</v>
       </c>
       <c r="K12" t="n">
-        <v>-99.14298217</v>
+        <v>-49.99167169</v>
       </c>
       <c r="L12" t="n">
-        <v>-108.40102338</v>
+        <v>-69.64462092999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-19.45438872999999</v>
+        <v>253.05612117</v>
       </c>
     </row>
     <row r="13">
@@ -960,37 +954,37 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>-0.6464205</v>
+        <v>14.62224566</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.4307181600000001</v>
+        <v>43.91308795</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.59056361</v>
+        <v>-26.81449123</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.08659428000000007</v>
+        <v>6.66454299</v>
       </c>
       <c r="G13" t="n">
-        <v>1.77917163</v>
+        <v>0.01338574000000022</v>
       </c>
       <c r="H13" t="n">
-        <v>2.56266091</v>
+        <v>-10.66935122</v>
       </c>
       <c r="I13" t="n">
-        <v>1.53243879</v>
+        <v>46.75941797</v>
       </c>
       <c r="J13" t="n">
-        <v>9.202618049999998</v>
+        <v>-29.39136021</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.19720024</v>
+        <v>-78.65453039999998</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.09010341</v>
+        <v>38.06164016</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.3289317</v>
+        <v>88.24941468999999</v>
       </c>
     </row>
     <row r="14">
@@ -1001,37 +995,37 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>-3231.97946945</v>
+        <v>-6065.20683973</v>
       </c>
       <c r="D14" t="n">
-        <v>-6067.10652506</v>
+        <v>-8193.434163939999</v>
       </c>
       <c r="E14" t="n">
-        <v>-8165.38337648</v>
+        <v>-11812.81124464</v>
       </c>
       <c r="F14" t="n">
-        <v>-11808.04818822</v>
+        <v>-5566.08010312</v>
       </c>
       <c r="G14" t="n">
-        <v>-5565.24977255</v>
+        <v>-696.3512316900003</v>
       </c>
       <c r="H14" t="n">
-        <v>-693.9748023900003</v>
+        <v>-4038.89355937</v>
       </c>
       <c r="I14" t="n">
-        <v>-4033.2061213</v>
+        <v>-6004.50905662</v>
       </c>
       <c r="J14" t="n">
-        <v>-5990.71076214</v>
+        <v>-1135.96927128</v>
       </c>
       <c r="K14" t="n">
-        <v>-1118.15655134</v>
+        <v>-3923.88527044</v>
       </c>
       <c r="L14" t="n">
-        <v>-3900.457885</v>
+        <v>5232.32995332</v>
       </c>
       <c r="M14" t="n">
-        <v>5225.866922259999</v>
+        <v>1633.12764074</v>
       </c>
     </row>
     <row r="15">
@@ -1040,39 +1034,41 @@
           <t>半導體業右下</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
       <c r="C15" t="n">
-        <v>415.17671171</v>
+        <v>412.85528441</v>
       </c>
       <c r="D15" t="n">
-        <v>525.40998389</v>
+        <v>367.89360698</v>
       </c>
       <c r="E15" t="n">
-        <v>447.02976782</v>
+        <v>-67.84231548000004</v>
       </c>
       <c r="F15" t="n">
-        <v>-31.13990355000003</v>
+        <v>-12.82006498999999</v>
       </c>
       <c r="G15" t="n">
-        <v>23.42403106000001</v>
+        <v>-667.61270948</v>
       </c>
       <c r="H15" t="n">
-        <v>-632.2839042999999</v>
+        <v>-216.5034258</v>
       </c>
       <c r="I15" t="n">
-        <v>-165.3706187</v>
+        <v>-134.11423201</v>
       </c>
       <c r="J15" t="n">
-        <v>51.25846262999996</v>
+        <v>591.92068205</v>
       </c>
       <c r="K15" t="n">
-        <v>677.0458991900001</v>
+        <v>-55.01668249000003</v>
       </c>
       <c r="L15" t="n">
-        <v>83.05033821999999</v>
+        <v>-311.90614392</v>
       </c>
       <c r="M15" t="n">
-        <v>-148.23056635</v>
+        <v>267.33807119</v>
       </c>
     </row>
     <row r="16">
@@ -1083,37 +1079,37 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>131.7261127</v>
+        <v>1.484374490000025</v>
       </c>
       <c r="D16" t="n">
-        <v>-69.87645122999997</v>
+        <v>170.44589032</v>
       </c>
       <c r="E16" t="n">
-        <v>103.08594964</v>
+        <v>335.24553992</v>
       </c>
       <c r="F16" t="n">
-        <v>306.19994461</v>
+        <v>-383.17638882</v>
       </c>
       <c r="G16" t="n">
-        <v>-408.21042106</v>
+        <v>-53.77780810999995</v>
       </c>
       <c r="H16" t="n">
-        <v>-98.95156192999997</v>
+        <v>-160.89663637</v>
       </c>
       <c r="I16" t="n">
-        <v>-222.25757108</v>
+        <v>-687.9945551600001</v>
       </c>
       <c r="J16" t="n">
-        <v>-897.9158482</v>
+        <v>-638.59429387</v>
       </c>
       <c r="K16" t="n">
-        <v>-757.7623535499999</v>
+        <v>-966.1564845700001</v>
       </c>
       <c r="L16" t="n">
-        <v>-1126.50219126</v>
+        <v>-254.25417468</v>
       </c>
       <c r="M16" t="n">
-        <v>-422.5661715</v>
+        <v>-247.29899022</v>
       </c>
     </row>
     <row r="17">
@@ -1124,37 +1120,37 @@
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
-        <v>0.34978601</v>
+        <v>0.55657781</v>
       </c>
       <c r="D17" t="n">
-        <v>0.55657781</v>
+        <v>0.5684159599999999</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5684159599999999</v>
+        <v>0.6202892800000001</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6202892800000001</v>
+        <v>0.7926845100000001</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7926845100000001</v>
+        <v>1.35238512</v>
       </c>
       <c r="H17" t="n">
-        <v>1.35238512</v>
+        <v>2.728392</v>
       </c>
       <c r="I17" t="n">
-        <v>2.728392</v>
+        <v>0.88005688</v>
       </c>
       <c r="J17" t="n">
-        <v>0.88005688</v>
+        <v>0.9546220400000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9546220400000001</v>
+        <v>0.84933839</v>
       </c>
       <c r="L17" t="n">
-        <v>0.84933839</v>
+        <v>-0.12916396</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.12916396</v>
+        <v>0.18337836</v>
       </c>
     </row>
     <row r="18">
@@ -1165,37 +1161,37 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>317.71777002</v>
+        <v>283.6058508000001</v>
       </c>
       <c r="D18" t="n">
-        <v>283.5817899</v>
+        <v>797.0432088700001</v>
       </c>
       <c r="E18" t="n">
-        <v>797.0976046799999</v>
+        <v>-142.28295233</v>
       </c>
       <c r="F18" t="n">
-        <v>-142.24816027</v>
+        <v>949.17323245</v>
       </c>
       <c r="G18" t="n">
-        <v>949.19824843</v>
+        <v>786.6830428600001</v>
       </c>
       <c r="H18" t="n">
-        <v>786.71530309</v>
+        <v>-272.85884179</v>
       </c>
       <c r="I18" t="n">
-        <v>-272.89082989</v>
+        <v>-871.1229194199999</v>
       </c>
       <c r="J18" t="n">
-        <v>-871.1452639</v>
+        <v>-1069.81135742</v>
       </c>
       <c r="K18" t="n">
-        <v>-1069.80177573</v>
+        <v>-452.58295967</v>
       </c>
       <c r="L18" t="n">
-        <v>-452.59567873</v>
+        <v>-531.6617434799999</v>
       </c>
       <c r="M18" t="n">
-        <v>-531.6740625399999</v>
+        <v>-603.5171211700001</v>
       </c>
     </row>
     <row r="19">
@@ -1206,37 +1202,37 @@
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>-12.00218059</v>
+        <v>-11.46146303</v>
       </c>
       <c r="D19" t="n">
-        <v>-11.43740213</v>
+        <v>-4.65900013</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.71339594</v>
+        <v>-9.61752909</v>
       </c>
       <c r="F19" t="n">
-        <v>-9.652321150000001</v>
+        <v>-3.18360563</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.20862161</v>
+        <v>-6.06010232</v>
       </c>
       <c r="H19" t="n">
-        <v>-6.092362550000001</v>
+        <v>-6.603607350000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-6.57161925</v>
+        <v>-1.86833417</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.84598969</v>
+        <v>-3.4926213</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.50220299</v>
+        <v>-0.45935462</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.44663556</v>
+        <v>-5.09458178</v>
       </c>
       <c r="M19" t="n">
-        <v>-5.08226272</v>
+        <v>-16.04650259</v>
       </c>
     </row>
     <row r="20">
@@ -1247,37 +1243,37 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>39.71331186</v>
+        <v>46.16474276</v>
       </c>
       <c r="D20" t="n">
-        <v>46.16474276</v>
+        <v>49.79108182</v>
       </c>
       <c r="E20" t="n">
-        <v>49.79108182</v>
+        <v>15.83999259</v>
       </c>
       <c r="F20" t="n">
-        <v>15.83999259</v>
+        <v>43.34600284999999</v>
       </c>
       <c r="G20" t="n">
-        <v>43.34600284999999</v>
+        <v>-20.57369556</v>
       </c>
       <c r="H20" t="n">
-        <v>-20.57369556</v>
+        <v>-26.64337471</v>
       </c>
       <c r="I20" t="n">
-        <v>-26.64337471</v>
+        <v>-8.6719104</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.6719104</v>
+        <v>6.29112816</v>
       </c>
       <c r="K20" t="n">
-        <v>6.29112816</v>
+        <v>-11.38791094</v>
       </c>
       <c r="L20" t="n">
-        <v>-11.38791094</v>
+        <v>39.90390299</v>
       </c>
       <c r="M20" t="n">
-        <v>39.90390299</v>
+        <v>-7.499015480000001</v>
       </c>
     </row>
     <row r="21">
@@ -1288,37 +1284,37 @@
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
-        <v>-0.6914854</v>
+        <v>-1.29708368</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.87016615</v>
+        <v>0.52764575</v>
       </c>
       <c r="E21" t="n">
-        <v>0.47642728</v>
+        <v>-0.34250415</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.38489539</v>
+        <v>0.7141913200000001</v>
       </c>
       <c r="G21" t="n">
-        <v>1.01578957</v>
+        <v>0.11302341</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.08695448000000001</v>
+        <v>1.4265115</v>
       </c>
       <c r="I21" t="n">
-        <v>1.98383284</v>
+        <v>2.43182651</v>
       </c>
       <c r="J21" t="n">
-        <v>2.625483</v>
+        <v>1.74384779</v>
       </c>
       <c r="K21" t="n">
-        <v>2.3940447</v>
+        <v>1.74690904</v>
       </c>
       <c r="L21" t="n">
-        <v>2.61609992</v>
+        <v>1.07925432</v>
       </c>
       <c r="M21" t="n">
-        <v>1.28616441</v>
+        <v>-4.11525328</v>
       </c>
     </row>
     <row r="22">
@@ -1329,37 +1325,37 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>-0.48060147</v>
+        <v>0.55614465</v>
       </c>
       <c r="D22" t="n">
-        <v>0.12922712</v>
+        <v>0.3488162300000001</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4000347</v>
+        <v>-1.15319388</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.11080264</v>
+        <v>0.41529846</v>
       </c>
       <c r="G22" t="n">
-        <v>0.11370021</v>
+        <v>-0.11266603</v>
       </c>
       <c r="H22" t="n">
-        <v>0.08731186000000006</v>
+        <v>2.09034716</v>
       </c>
       <c r="I22" t="n">
-        <v>1.53302582</v>
+        <v>2.66355993</v>
       </c>
       <c r="J22" t="n">
-        <v>2.46990344</v>
+        <v>2.26413163</v>
       </c>
       <c r="K22" t="n">
-        <v>1.61393472</v>
+        <v>2.71121329</v>
       </c>
       <c r="L22" t="n">
-        <v>1.84202241</v>
+        <v>2.27478133</v>
       </c>
       <c r="M22" t="n">
-        <v>2.06787124</v>
+        <v>3.80913609</v>
       </c>
     </row>
     <row r="23">
@@ -1370,37 +1366,37 @@
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
-        <v>29.14204919</v>
+        <v>19.8188676</v>
       </c>
       <c r="D23" t="n">
-        <v>18.78984363</v>
+        <v>12.32503369</v>
       </c>
       <c r="E23" t="n">
-        <v>11.99700128</v>
+        <v>-22.42774658</v>
       </c>
       <c r="F23" t="n">
-        <v>-21.51542892</v>
+        <v>0.02885995000000046</v>
       </c>
       <c r="G23" t="n">
-        <v>3.234019390000002</v>
+        <v>1.897171200000003</v>
       </c>
       <c r="H23" t="n">
-        <v>1.317080060000002</v>
+        <v>-10.39387457</v>
       </c>
       <c r="I23" t="n">
-        <v>-8.2388408</v>
+        <v>25.32103064</v>
       </c>
       <c r="J23" t="n">
-        <v>30.90360521</v>
+        <v>28.17905898</v>
       </c>
       <c r="K23" t="n">
-        <v>28.25559642</v>
+        <v>10.22546174</v>
       </c>
       <c r="L23" t="n">
-        <v>13.04442215</v>
+        <v>-0.04797202999999901</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.4080909000000001</v>
+        <v>3.962863350000001</v>
       </c>
     </row>
     <row r="24">
@@ -1411,37 +1407,37 @@
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
-        <v>-53.50370855</v>
+        <v>-75.38246376000001</v>
       </c>
       <c r="D24" t="n">
-        <v>-74.26896387000001</v>
+        <v>-91.82564342000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-90.23747162000001</v>
+        <v>-99.50884896000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-97.42394762000001</v>
+        <v>-75.71592917</v>
       </c>
       <c r="G24" t="n">
-        <v>-74.46318362999999</v>
+        <v>-60.80458005000001</v>
       </c>
       <c r="H24" t="n">
-        <v>-59.42508056</v>
+        <v>-4.086764929999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.668862659999999</v>
+        <v>59.37612749</v>
       </c>
       <c r="J24" t="n">
-        <v>58.36625415</v>
+        <v>28.97021335</v>
       </c>
       <c r="K24" t="n">
-        <v>28.29321428</v>
+        <v>21.71168018000001</v>
       </c>
       <c r="L24" t="n">
-        <v>20.81821146000001</v>
+        <v>-3.889574799999997</v>
       </c>
       <c r="M24" t="n">
-        <v>-5.424017260000002</v>
+        <v>-20.01266644</v>
       </c>
     </row>
     <row r="25">
@@ -1452,37 +1448,37 @@
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>7.910652079999999</v>
+        <v>-25.95945987</v>
       </c>
       <c r="D25" t="n">
-        <v>-26.04393579</v>
+        <v>-60.3084473</v>
       </c>
       <c r="E25" t="n">
-        <v>-61.56858669</v>
+        <v>-100.60543965</v>
       </c>
       <c r="F25" t="n">
-        <v>-103.60265865</v>
+        <v>-65.92082766</v>
       </c>
       <c r="G25" t="n">
-        <v>-70.37873264</v>
+        <v>-90.96517784999999</v>
       </c>
       <c r="H25" t="n">
-        <v>-91.7645862</v>
+        <v>-7.12249789</v>
       </c>
       <c r="I25" t="n">
-        <v>-9.695433929999998</v>
+        <v>91.62710849</v>
       </c>
       <c r="J25" t="n">
-        <v>87.05440726</v>
+        <v>19.9109983</v>
       </c>
       <c r="K25" t="n">
-        <v>20.51145993</v>
+        <v>38.86329782</v>
       </c>
       <c r="L25" t="n">
-        <v>36.93780613000001</v>
+        <v>28.25083827</v>
       </c>
       <c r="M25" t="n">
-        <v>30.1453996</v>
+        <v>-3.23667587</v>
       </c>
     </row>
     <row r="26">
@@ -1493,37 +1489,37 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>105.86494253</v>
+        <v>30.24814522</v>
       </c>
       <c r="D26" t="n">
-        <v>30.21146938</v>
+        <v>26.76396136</v>
       </c>
       <c r="E26" t="n">
-        <v>26.72469076</v>
+        <v>-16.35696898</v>
       </c>
       <c r="F26" t="n">
-        <v>-16.38992439</v>
+        <v>-11.57917922</v>
       </c>
       <c r="G26" t="n">
-        <v>-11.60826412</v>
+        <v>-0.76419575</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.7931707099999999</v>
+        <v>20.13668719</v>
       </c>
       <c r="I26" t="n">
-        <v>20.11172033</v>
+        <v>-15.72170868</v>
       </c>
       <c r="J26" t="n">
-        <v>-15.74350812</v>
+        <v>12.89942112</v>
       </c>
       <c r="K26" t="n">
-        <v>12.88097516</v>
+        <v>-21.76483932</v>
       </c>
       <c r="L26" t="n">
-        <v>-21.7842918</v>
+        <v>-40.04336831</v>
       </c>
       <c r="M26" t="n">
-        <v>-40.05969073999999</v>
+        <v>-74.61596999</v>
       </c>
     </row>
     <row r="27">
@@ -1534,37 +1530,37 @@
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>26.50834888</v>
+        <v>12.3732266</v>
       </c>
       <c r="D27" t="n">
-        <v>12.3732266</v>
+        <v>16.88570324</v>
       </c>
       <c r="E27" t="n">
-        <v>16.88570324</v>
+        <v>5.174999509999999</v>
       </c>
       <c r="F27" t="n">
-        <v>5.174999509999999</v>
+        <v>10.18965648</v>
       </c>
       <c r="G27" t="n">
-        <v>7.23050988</v>
+        <v>5.14904886</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.83191157</v>
+        <v>12.32428043</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.1112072000000002</v>
+        <v>7.23473412</v>
       </c>
       <c r="J27" t="n">
-        <v>-8.636969779999999</v>
+        <v>21.39711191</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.6313917000000004</v>
+        <v>9.234505710000002</v>
       </c>
       <c r="L27" t="n">
-        <v>-12.47592114</v>
+        <v>20.87369368</v>
       </c>
       <c r="M27" t="n">
-        <v>-3.23110746</v>
+        <v>17.72328894</v>
       </c>
     </row>
     <row r="28">
@@ -1575,37 +1571,37 @@
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>0.03056361</v>
+        <v>-0.00324458</v>
       </c>
       <c r="D28" t="n">
-        <v>0.03343126</v>
+        <v>-0.006596299999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0326743</v>
+        <v>-0.01406638</v>
       </c>
       <c r="F28" t="n">
-        <v>0.01888903</v>
+        <v>0.00652111</v>
       </c>
       <c r="G28" t="n">
-        <v>2.99475261</v>
+        <v>0.02914014</v>
       </c>
       <c r="H28" t="n">
-        <v>7.039075529999999</v>
+        <v>0.04879807</v>
       </c>
       <c r="I28" t="n">
-        <v>12.50925256</v>
+        <v>0.0566263</v>
       </c>
       <c r="J28" t="n">
-        <v>15.95012964</v>
+        <v>0.02465099</v>
       </c>
       <c r="K28" t="n">
-        <v>22.07160056</v>
+        <v>-0.00128256</v>
       </c>
       <c r="L28" t="n">
-        <v>21.72859677</v>
+        <v>-0.01739636</v>
       </c>
       <c r="M28" t="n">
-        <v>24.10372721</v>
+        <v>-0.02008268</v>
       </c>
     </row>
     <row r="29">
@@ -1616,37 +1612,37 @@
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>-0.0015445</v>
+        <v>-0.00056724</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.0003015200000000001</v>
+        <v>0.00672136</v>
       </c>
       <c r="E29" t="n">
-        <v>0.006606399999999999</v>
+        <v>-0.00145954</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.004734899999999999</v>
+        <v>0.006492230000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>0.004098840000000001</v>
+        <v>0.01229479</v>
       </c>
       <c r="H29" t="n">
-        <v>0.01038032</v>
+        <v>0.01976942</v>
       </c>
       <c r="I29" t="n">
-        <v>0.01827796</v>
+        <v>0.0273315</v>
       </c>
       <c r="J29" t="n">
-        <v>0.02748128</v>
+        <v>0.08224571999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>0.08417767</v>
+        <v>0.0739363</v>
       </c>
       <c r="L29" t="n">
-        <v>0.07505073</v>
+        <v>0.03168009</v>
       </c>
       <c r="M29" t="n">
-        <v>0.03327574</v>
+        <v>0.00634259</v>
       </c>
     </row>
     <row r="30">
@@ -1657,37 +1653,37 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>-0.0025532</v>
+        <v>0.00442858</v>
       </c>
       <c r="D30" t="n">
-        <v>0.00442858</v>
+        <v>-0.0001344399999999998</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0001344399999999998</v>
+        <v>-0.00311901</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.00311901</v>
+        <v>-0.00135107</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.00135107</v>
+        <v>-0.00645304</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.00645304</v>
+        <v>-0.0007993899999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0007993899999999999</v>
+        <v>0.008251139999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>0.008251139999999999</v>
+        <v>0.009377439999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>0.009377439999999999</v>
+        <v>0.00523351</v>
       </c>
       <c r="L30" t="n">
-        <v>0.00523351</v>
+        <v>0.01145842</v>
       </c>
       <c r="M30" t="n">
-        <v>0.01145842</v>
+        <v>-0.00107374</v>
       </c>
     </row>
     <row r="31">
@@ -1698,37 +1694,37 @@
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>-0.05155841000000001</v>
+        <v>0.04320168</v>
       </c>
       <c r="D31" t="n">
-        <v>0.04293596</v>
+        <v>0.00901807</v>
       </c>
       <c r="E31" t="n">
-        <v>0.009133029999999999</v>
+        <v>-0.04702125</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.04374589</v>
+        <v>-0.07367325</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.07127986</v>
+        <v>0.03200824</v>
       </c>
       <c r="H31" t="n">
-        <v>0.03392271</v>
+        <v>0.0003393799999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>0.001830840000000001</v>
+        <v>0.10036298</v>
       </c>
       <c r="J31" t="n">
-        <v>0.1002132</v>
+        <v>0.22031342</v>
       </c>
       <c r="K31" t="n">
-        <v>0.21838147</v>
+        <v>0.11064709</v>
       </c>
       <c r="L31" t="n">
-        <v>0.10953266</v>
+        <v>0.04144617</v>
       </c>
       <c r="M31" t="n">
-        <v>0.03985052000000001</v>
+        <v>-0.009926669999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1739,37 +1735,37 @@
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>-0.8938292</v>
+        <v>0.26859018</v>
       </c>
       <c r="D32" t="n">
-        <v>0.26859018</v>
+        <v>-1.1550498</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.1550498</v>
+        <v>0.19597777</v>
       </c>
       <c r="F32" t="n">
-        <v>0.19597777</v>
+        <v>0.93832401</v>
       </c>
       <c r="G32" t="n">
-        <v>0.93832401</v>
+        <v>-0.60581137</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.60581137</v>
+        <v>-0.18124846</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.18124846</v>
+        <v>0.6026511899999999</v>
       </c>
       <c r="J32" t="n">
-        <v>0.6026511899999999</v>
+        <v>2.12415212</v>
       </c>
       <c r="K32" t="n">
-        <v>2.12415212</v>
+        <v>3.00018044</v>
       </c>
       <c r="L32" t="n">
-        <v>3.00018044</v>
+        <v>0.8008101</v>
       </c>
       <c r="M32" t="n">
-        <v>0.8008101</v>
+        <v>-0.41351514</v>
       </c>
     </row>
     <row r="33">
@@ -1780,37 +1776,37 @@
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
-        <v>74.52305657000001</v>
+        <v>28.77819571</v>
       </c>
       <c r="D33" t="n">
-        <v>28.77819571</v>
+        <v>47.13405325</v>
       </c>
       <c r="E33" t="n">
-        <v>47.13405325</v>
+        <v>17.62821512</v>
       </c>
       <c r="F33" t="n">
-        <v>17.62821512</v>
+        <v>9.357429240000002</v>
       </c>
       <c r="G33" t="n">
-        <v>9.357429240000002</v>
+        <v>-23.28926443</v>
       </c>
       <c r="H33" t="n">
-        <v>-23.28926443</v>
+        <v>-14.93848151</v>
       </c>
       <c r="I33" t="n">
-        <v>-15.50397747</v>
+        <v>-7.90298542</v>
       </c>
       <c r="J33" t="n">
-        <v>-7.671519279999999</v>
+        <v>-12.45719128</v>
       </c>
       <c r="K33" t="n">
-        <v>-12.56496135</v>
+        <v>0.01885810999999962</v>
       </c>
       <c r="L33" t="n">
-        <v>0.4845926899999997</v>
+        <v>-20.58713198</v>
       </c>
       <c r="M33" t="n">
-        <v>-20.67803373</v>
+        <v>-31.56361012</v>
       </c>
     </row>
     <row r="34">
@@ -1821,37 +1817,37 @@
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
-        <v>0.6281405</v>
+        <v>0.5322796400000001</v>
       </c>
       <c r="D34" t="n">
-        <v>0.5322796400000001</v>
+        <v>0.66688402</v>
       </c>
       <c r="E34" t="n">
-        <v>0.66688402</v>
+        <v>0.39455165</v>
       </c>
       <c r="F34" t="n">
-        <v>0.39455165</v>
+        <v>0.7616216099999999</v>
       </c>
       <c r="G34" t="n">
-        <v>0.7616216099999999</v>
+        <v>0.68170787</v>
       </c>
       <c r="H34" t="n">
-        <v>0.68170787</v>
+        <v>0.03184879000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>0.03184879000000001</v>
+        <v>-0.05228055</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.05228055</v>
+        <v>-0.22602753</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.22602753</v>
+        <v>-0.07364258999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.07364258999999999</v>
+        <v>-0.3195109</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.3195109</v>
+        <v>-0.68960457</v>
       </c>
     </row>
     <row r="35">
@@ -1860,41 +1856,39 @@
           <t>水泥工業右下</t>
         </is>
       </c>
-      <c r="B35" t="n">
-        <v>0</v>
-      </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
-        <v>170.80982995</v>
+        <v>151.94936306</v>
       </c>
       <c r="D35" t="n">
-        <v>150.4790605</v>
+        <v>180.3735272</v>
       </c>
       <c r="E35" t="n">
-        <v>180.35446419</v>
+        <v>110.71375524</v>
       </c>
       <c r="F35" t="n">
-        <v>111.88970622</v>
+        <v>152.65296865</v>
       </c>
       <c r="G35" t="n">
-        <v>152.7060144</v>
+        <v>75.59350051</v>
       </c>
       <c r="H35" t="n">
-        <v>77.88811109999999</v>
+        <v>33.17521386</v>
       </c>
       <c r="I35" t="n">
-        <v>33.94075736</v>
+        <v>20.83055937</v>
       </c>
       <c r="J35" t="n">
-        <v>21.68277256</v>
+        <v>33.4962376</v>
       </c>
       <c r="K35" t="n">
-        <v>34.33086562</v>
+        <v>52.14474697</v>
       </c>
       <c r="L35" t="n">
-        <v>53.02693882</v>
+        <v>22.3438859</v>
       </c>
       <c r="M35" t="n">
-        <v>23.33522736</v>
+        <v>33.47123066</v>
       </c>
     </row>
     <row r="36">
@@ -1905,37 +1899,37 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>-17.9699727</v>
+        <v>-17.63893328</v>
       </c>
       <c r="D36" t="n">
-        <v>-19.50289189</v>
+        <v>-28.45550326999999</v>
       </c>
       <c r="E36" t="n">
-        <v>-28.50744565999999</v>
+        <v>-21.30608457</v>
       </c>
       <c r="F36" t="n">
-        <v>-22.80401095</v>
+        <v>-20.60556336</v>
       </c>
       <c r="G36" t="n">
-        <v>-20.90837859</v>
+        <v>-2.79298842</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.72982895</v>
+        <v>40.76014224</v>
       </c>
       <c r="I36" t="n">
-        <v>40.46050624</v>
+        <v>83.70217395</v>
       </c>
       <c r="J36" t="n">
-        <v>77.56024153</v>
+        <v>167.07701217</v>
       </c>
       <c r="K36" t="n">
-        <v>148.03386053</v>
+        <v>234.36025707</v>
       </c>
       <c r="L36" t="n">
-        <v>197.16667387</v>
+        <v>118.93610006</v>
       </c>
       <c r="M36" t="n">
-        <v>110.25012848</v>
+        <v>217.86082071</v>
       </c>
     </row>
     <row r="37">
@@ -1944,41 +1938,39 @@
           <t>汽車工業右下</t>
         </is>
       </c>
-      <c r="B37" t="n">
-        <v>0</v>
-      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>60.3508302</v>
+        <v>57.69521552</v>
       </c>
       <c r="D37" t="n">
-        <v>55.00207715</v>
+        <v>57.34065769</v>
       </c>
       <c r="E37" t="n">
-        <v>57.56681279999999</v>
+        <v>28.76092641</v>
       </c>
       <c r="F37" t="n">
-        <v>31.50297334</v>
+        <v>66.83402647999999</v>
       </c>
       <c r="G37" t="n">
-        <v>66.61318238</v>
+        <v>-8.809809789999999</v>
       </c>
       <c r="H37" t="n">
-        <v>-5.174916559999999</v>
+        <v>-1.514865390000001</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8484202900000013</v>
+        <v>18.38879085</v>
       </c>
       <c r="J37" t="n">
-        <v>17.82853616</v>
+        <v>37.15833097</v>
       </c>
       <c r="K37" t="n">
-        <v>38.37265259</v>
+        <v>41.52823503</v>
       </c>
       <c r="L37" t="n">
-        <v>45.696401</v>
+        <v>46.73594826000001</v>
       </c>
       <c r="M37" t="n">
-        <v>52.00953003</v>
+        <v>4.982251610000001</v>
       </c>
     </row>
     <row r="38">
@@ -1989,37 +1981,37 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>80.14216560000001</v>
+        <v>-15.43901849999999</v>
       </c>
       <c r="D38" t="n">
-        <v>-13.82458601</v>
+        <v>-63.68803793000001</v>
       </c>
       <c r="E38" t="n">
-        <v>-65.26758768000001</v>
+        <v>-108.53161906</v>
       </c>
       <c r="F38" t="n">
-        <v>-109.62146376</v>
+        <v>-12.15863209</v>
       </c>
       <c r="G38" t="n">
-        <v>-12.84797867</v>
+        <v>-32.56163757</v>
       </c>
       <c r="H38" t="n">
-        <v>-37.14346511</v>
+        <v>-43.82565295</v>
       </c>
       <c r="I38" t="n">
-        <v>-41.53191139</v>
+        <v>-5.797227319999999</v>
       </c>
       <c r="J38" t="n">
-        <v>7.015621090000004</v>
+        <v>59.82878755999999</v>
       </c>
       <c r="K38" t="n">
-        <v>88.53171814</v>
+        <v>27.71253198</v>
       </c>
       <c r="L38" t="n">
-        <v>67.46006622000002</v>
+        <v>-33.6543528</v>
       </c>
       <c r="M38" t="n">
-        <v>-27.28584806</v>
+        <v>-34.99574105</v>
       </c>
     </row>
     <row r="39">
@@ -2030,37 +2022,37 @@
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
-        <v>56.67209458</v>
+        <v>17.90640587</v>
       </c>
       <c r="D39" t="n">
-        <v>17.94407397</v>
+        <v>33.64427106</v>
       </c>
       <c r="E39" t="n">
-        <v>33.68792604</v>
+        <v>4.060433199999999</v>
       </c>
       <c r="F39" t="n">
-        <v>4.108083939999999</v>
+        <v>73.36151039000001</v>
       </c>
       <c r="G39" t="n">
-        <v>73.39446294</v>
+        <v>168.31023809</v>
       </c>
       <c r="H39" t="n">
-        <v>168.35310772</v>
+        <v>54.66244463</v>
       </c>
       <c r="I39" t="n">
-        <v>54.65563677999999</v>
+        <v>-39.94501549</v>
       </c>
       <c r="J39" t="n">
-        <v>-40.04566426</v>
+        <v>-65.26585011</v>
       </c>
       <c r="K39" t="n">
-        <v>-65.28418285000001</v>
+        <v>-32.772473</v>
       </c>
       <c r="L39" t="n">
-        <v>-32.76076323</v>
+        <v>-17.85393562</v>
       </c>
       <c r="M39" t="n">
-        <v>-17.83607626</v>
+        <v>-34.21927984000001</v>
       </c>
     </row>
     <row r="40">
@@ -2071,37 +2063,37 @@
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>0.08460432999999999</v>
+        <v>-3.17489022</v>
       </c>
       <c r="D40" t="n">
-        <v>-3.21255832</v>
+        <v>-6.35707236</v>
       </c>
       <c r="E40" t="n">
-        <v>-6.40072734</v>
+        <v>-3.72568645</v>
       </c>
       <c r="F40" t="n">
-        <v>-3.77333719</v>
+        <v>1.60553159</v>
       </c>
       <c r="G40" t="n">
-        <v>1.57257904</v>
+        <v>-2.38117539</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.42404502</v>
+        <v>-1.2286942</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.22188635</v>
+        <v>2.09913215</v>
       </c>
       <c r="J40" t="n">
-        <v>2.19978092</v>
+        <v>3.22640501</v>
       </c>
       <c r="K40" t="n">
-        <v>3.24473775</v>
+        <v>8.13575142</v>
       </c>
       <c r="L40" t="n">
-        <v>8.124041649999999</v>
+        <v>0.42589836</v>
       </c>
       <c r="M40" t="n">
-        <v>0.408039</v>
+        <v>5.236739259999999</v>
       </c>
     </row>
     <row r="41">
@@ -2112,37 +2104,37 @@
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
-        <v>307.60971191</v>
+        <v>433.81361385</v>
       </c>
       <c r="D41" t="n">
-        <v>433.81361385</v>
+        <v>668.62466564</v>
       </c>
       <c r="E41" t="n">
-        <v>668.62466564</v>
+        <v>244.91801602</v>
       </c>
       <c r="F41" t="n">
-        <v>244.91801602</v>
+        <v>320.90370974</v>
       </c>
       <c r="G41" t="n">
-        <v>320.90370974</v>
+        <v>479.18507195</v>
       </c>
       <c r="H41" t="n">
-        <v>479.18507195</v>
+        <v>759.412483</v>
       </c>
       <c r="I41" t="n">
-        <v>759.412483</v>
+        <v>264.18557726</v>
       </c>
       <c r="J41" t="n">
-        <v>264.18557726</v>
+        <v>-87.18150326999999</v>
       </c>
       <c r="K41" t="n">
-        <v>-87.18150326999999</v>
+        <v>-42.95356518</v>
       </c>
       <c r="L41" t="n">
-        <v>-42.95356518</v>
+        <v>-209.92976809</v>
       </c>
       <c r="M41" t="n">
-        <v>-209.92976809</v>
+        <v>-24.7706204</v>
       </c>
     </row>
     <row r="42">
@@ -2153,37 +2145,37 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>13.5194183</v>
+        <v>7.9181412</v>
       </c>
       <c r="D42" t="n">
-        <v>7.9181412</v>
+        <v>12.13364822</v>
       </c>
       <c r="E42" t="n">
-        <v>12.13364822</v>
+        <v>8.904139349999999</v>
       </c>
       <c r="F42" t="n">
-        <v>8.904139349999999</v>
+        <v>16.35974226</v>
       </c>
       <c r="G42" t="n">
-        <v>16.35974226</v>
+        <v>7.98138634</v>
       </c>
       <c r="H42" t="n">
-        <v>7.98138634</v>
+        <v>10.480544</v>
       </c>
       <c r="I42" t="n">
-        <v>11.47238579</v>
+        <v>7.58023094</v>
       </c>
       <c r="J42" t="n">
-        <v>7.112948609999999</v>
+        <v>19.71741358</v>
       </c>
       <c r="K42" t="n">
-        <v>19.89156343000001</v>
+        <v>19.39813214</v>
       </c>
       <c r="L42" t="n">
-        <v>18.45296431</v>
+        <v>6.97201257</v>
       </c>
       <c r="M42" t="n">
-        <v>5.039715139999999</v>
+        <v>-1.71694579</v>
       </c>
     </row>
     <row r="43">
@@ -2194,37 +2186,37 @@
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
-        <v>-2.06152237</v>
+        <v>-2.13891016</v>
       </c>
       <c r="D43" t="n">
-        <v>-3.503046229999999</v>
+        <v>-1.4135303</v>
       </c>
       <c r="E43" t="n">
-        <v>-4.535445409999999</v>
+        <v>-10.11111371</v>
       </c>
       <c r="F43" t="n">
-        <v>-14.41254868</v>
+        <v>3.275589520000001</v>
       </c>
       <c r="G43" t="n">
-        <v>-1.50810463</v>
+        <v>17.67968448</v>
       </c>
       <c r="H43" t="n">
-        <v>12.8362347</v>
+        <v>12.9045686</v>
       </c>
       <c r="I43" t="n">
-        <v>11.30074539</v>
+        <v>16.89937039</v>
       </c>
       <c r="J43" t="n">
-        <v>16.35838766</v>
+        <v>14.53633061</v>
       </c>
       <c r="K43" t="n">
-        <v>15.7316962</v>
+        <v>16.77966055</v>
       </c>
       <c r="L43" t="n">
-        <v>16.78350014</v>
+        <v>5.133885120000004</v>
       </c>
       <c r="M43" t="n">
-        <v>6.063495510000001</v>
+        <v>11.00030594</v>
       </c>
     </row>
     <row r="44">
@@ -2233,39 +2225,41 @@
           <t>生技醫療業右下</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
+      <c r="B44" t="n">
+        <v>0</v>
+      </c>
       <c r="C44" t="n">
-        <v>137.43356436</v>
+        <v>267.91659222</v>
       </c>
       <c r="D44" t="n">
-        <v>267.91917575</v>
+        <v>-28.46628853</v>
       </c>
       <c r="E44" t="n">
-        <v>-28.46582557999999</v>
+        <v>-233.05138489</v>
       </c>
       <c r="F44" t="n">
-        <v>-233.05188301</v>
+        <v>-348.2472195999999</v>
       </c>
       <c r="G44" t="n">
-        <v>-348.24805795</v>
+        <v>-325.33434396</v>
       </c>
       <c r="H44" t="n">
-        <v>-325.33619197</v>
+        <v>-310.85803781</v>
       </c>
       <c r="I44" t="n">
-        <v>-311.01459162</v>
+        <v>-66.5272892</v>
       </c>
       <c r="J44" t="n">
-        <v>-66.67316493</v>
+        <v>7.323684740000009</v>
       </c>
       <c r="K44" t="n">
-        <v>7.325962460000008</v>
+        <v>30.19368088000001</v>
       </c>
       <c r="L44" t="n">
-        <v>30.03925212</v>
+        <v>116.40958469</v>
       </c>
       <c r="M44" t="n">
-        <v>116.27639912</v>
+        <v>258.70540645</v>
       </c>
     </row>
     <row r="45">
@@ -2276,37 +2270,37 @@
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
-        <v>29.20899821</v>
+        <v>-124.05335568</v>
       </c>
       <c r="D45" t="n">
-        <v>-122.68992729</v>
+        <v>-105.55517871</v>
       </c>
       <c r="E45" t="n">
-        <v>-102.43163424</v>
+        <v>-256.19174892</v>
       </c>
       <c r="F45" t="n">
-        <v>-251.88889818</v>
+        <v>-264.69814601</v>
       </c>
       <c r="G45" t="n">
-        <v>-259.91249699</v>
+        <v>-222.55389545</v>
       </c>
       <c r="H45" t="n">
-        <v>-217.70816821</v>
+        <v>37.63488079</v>
       </c>
       <c r="I45" t="n">
-        <v>39.23945844000001</v>
+        <v>-32.22098995</v>
       </c>
       <c r="J45" t="n">
-        <v>-31.67881664</v>
+        <v>93.7329625</v>
       </c>
       <c r="K45" t="n">
-        <v>92.538398</v>
+        <v>-0.6881097599999998</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.6899875800000015</v>
+        <v>78.81692654</v>
       </c>
       <c r="M45" t="n">
-        <v>77.88738393999999</v>
+        <v>56.04722025</v>
       </c>
     </row>
     <row r="46">
@@ -2317,37 +2311,37 @@
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>2.33218234</v>
+        <v>-2.68934393</v>
       </c>
       <c r="D46" t="n">
-        <v>-2.68934393</v>
+        <v>-6.34563964</v>
       </c>
       <c r="E46" t="n">
-        <v>-6.34563964</v>
+        <v>-8.06577257</v>
       </c>
       <c r="F46" t="n">
-        <v>-8.06577257</v>
+        <v>-5.88842813</v>
       </c>
       <c r="G46" t="n">
-        <v>-5.88842813</v>
+        <v>-5.95638258</v>
       </c>
       <c r="H46" t="n">
-        <v>-5.95638258</v>
+        <v>-5.16063128</v>
       </c>
       <c r="I46" t="n">
-        <v>-5.16063128</v>
+        <v>-5.243901949999999</v>
       </c>
       <c r="J46" t="n">
-        <v>-5.243901949999999</v>
+        <v>-1.42678741</v>
       </c>
       <c r="K46" t="n">
-        <v>-1.42678741</v>
+        <v>-1.55751561</v>
       </c>
       <c r="L46" t="n">
-        <v>-1.55751561</v>
+        <v>0.21300419</v>
       </c>
       <c r="M46" t="n">
-        <v>0.21300419</v>
+        <v>0.11317531</v>
       </c>
     </row>
     <row r="47">
@@ -2358,37 +2352,37 @@
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>112.31552985</v>
+        <v>53.45619471</v>
       </c>
       <c r="D47" t="n">
-        <v>53.45619471</v>
+        <v>95.04986186999999</v>
       </c>
       <c r="E47" t="n">
-        <v>95.04986186999999</v>
+        <v>9.407378970000002</v>
       </c>
       <c r="F47" t="n">
-        <v>9.407378970000002</v>
+        <v>39.68573421</v>
       </c>
       <c r="G47" t="n">
-        <v>39.68573421</v>
+        <v>4.959421839999997</v>
       </c>
       <c r="H47" t="n">
-        <v>4.959421839999997</v>
+        <v>20.79778082</v>
       </c>
       <c r="I47" t="n">
-        <v>20.79778082</v>
+        <v>26.43966846</v>
       </c>
       <c r="J47" t="n">
-        <v>26.43966846</v>
+        <v>2.098726649999999</v>
       </c>
       <c r="K47" t="n">
-        <v>2.098726649999999</v>
+        <v>-22.66043861</v>
       </c>
       <c r="L47" t="n">
-        <v>-22.66043861</v>
+        <v>-14.22419143</v>
       </c>
       <c r="M47" t="n">
-        <v>-14.22419143</v>
+        <v>-101.46831989</v>
       </c>
     </row>
     <row r="48">
@@ -2399,37 +2393,37 @@
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
-        <v>0.39115204</v>
+        <v>0.5514035599999999</v>
       </c>
       <c r="D48" t="n">
-        <v>0.5514035599999999</v>
+        <v>0.28994207</v>
       </c>
       <c r="E48" t="n">
-        <v>0.28994207</v>
+        <v>0.02784229000000001</v>
       </c>
       <c r="F48" t="n">
-        <v>0.02784229000000001</v>
+        <v>0.06728542</v>
       </c>
       <c r="G48" t="n">
-        <v>0.06728542</v>
+        <v>-0.10238672</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.10238672</v>
+        <v>-0.002889020000000003</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.002889020000000003</v>
+        <v>1.65310548</v>
       </c>
       <c r="J48" t="n">
-        <v>1.65310548</v>
+        <v>1.32672589</v>
       </c>
       <c r="K48" t="n">
-        <v>1.32672589</v>
+        <v>0.25503158</v>
       </c>
       <c r="L48" t="n">
-        <v>0.25503158</v>
+        <v>-0.002404550000000011</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.002404550000000011</v>
+        <v>-0.2114317</v>
       </c>
     </row>
     <row r="49">
@@ -2440,37 +2434,37 @@
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>-57.67915559</v>
+        <v>-60.85314679</v>
       </c>
       <c r="D49" t="n">
-        <v>-63.73321268000001</v>
+        <v>-44.6215331</v>
       </c>
       <c r="E49" t="n">
-        <v>-46.01752432</v>
+        <v>17.17839787</v>
       </c>
       <c r="F49" t="n">
-        <v>18.17174736</v>
+        <v>-62.65965742</v>
       </c>
       <c r="G49" t="n">
-        <v>-62.53515385</v>
+        <v>-60.30171099</v>
       </c>
       <c r="H49" t="n">
-        <v>-58.25113503</v>
+        <v>-31.10208839</v>
       </c>
       <c r="I49" t="n">
-        <v>-33.2278322</v>
+        <v>-117.28128842</v>
       </c>
       <c r="J49" t="n">
-        <v>-123.32308795</v>
+        <v>-6.879195419999996</v>
       </c>
       <c r="K49" t="n">
-        <v>-8.951695199999996</v>
+        <v>-117.29680573</v>
       </c>
       <c r="L49" t="n">
-        <v>-117.59873813</v>
+        <v>50.61498453</v>
       </c>
       <c r="M49" t="n">
-        <v>50.73546306</v>
+        <v>-67.84222641999999</v>
       </c>
     </row>
     <row r="50">
@@ -2481,37 +2475,37 @@
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
-        <v>-9.074995439999997</v>
+        <v>-6.02440684</v>
       </c>
       <c r="D50" t="n">
-        <v>-6.02440684</v>
+        <v>-10.76360972</v>
       </c>
       <c r="E50" t="n">
-        <v>-10.76360972</v>
+        <v>-6.295704290000001</v>
       </c>
       <c r="F50" t="n">
-        <v>-6.295704290000001</v>
+        <v>4.70272614</v>
       </c>
       <c r="G50" t="n">
-        <v>4.70272614</v>
+        <v>-5.524311600000001</v>
       </c>
       <c r="H50" t="n">
-        <v>-5.524311600000001</v>
+        <v>2.53485937</v>
       </c>
       <c r="I50" t="n">
-        <v>2.53485937</v>
+        <v>-2.54366476</v>
       </c>
       <c r="J50" t="n">
-        <v>-2.54366476</v>
+        <v>4.03323023</v>
       </c>
       <c r="K50" t="n">
-        <v>4.03323023</v>
+        <v>-4.208008479999999</v>
       </c>
       <c r="L50" t="n">
-        <v>-4.208008479999999</v>
+        <v>-16.668004</v>
       </c>
       <c r="M50" t="n">
-        <v>-16.668004</v>
+        <v>-17.31000216</v>
       </c>
     </row>
     <row r="51">
@@ -2522,37 +2516,37 @@
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>23.49764584</v>
+        <v>35.04990626</v>
       </c>
       <c r="D51" t="n">
-        <v>37.92997215</v>
+        <v>11.21640177</v>
       </c>
       <c r="E51" t="n">
-        <v>12.61239299</v>
+        <v>0.5011575799999991</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.4921919100000006</v>
+        <v>-0.7979235500000009</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.922427120000001</v>
+        <v>-11.10073136</v>
       </c>
       <c r="H51" t="n">
-        <v>-13.15130732</v>
+        <v>18.13323726</v>
       </c>
       <c r="I51" t="n">
-        <v>20.25898107</v>
+        <v>3.50636154</v>
       </c>
       <c r="J51" t="n">
-        <v>9.548161070000001</v>
+        <v>23.9928634</v>
       </c>
       <c r="K51" t="n">
-        <v>26.06536318</v>
+        <v>23.94287542</v>
       </c>
       <c r="L51" t="n">
-        <v>24.24480782</v>
+        <v>11.45678204</v>
       </c>
       <c r="M51" t="n">
-        <v>11.33630351</v>
+        <v>14.87823323</v>
       </c>
     </row>
     <row r="52">
@@ -2563,37 +2557,37 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>255.1197481</v>
+        <v>557.9386459900001</v>
       </c>
       <c r="D52" t="n">
-        <v>334.97889778</v>
+        <v>166.34689068</v>
       </c>
       <c r="E52" t="n">
-        <v>109.84570048</v>
+        <v>-33.08596268</v>
       </c>
       <c r="F52" t="n">
-        <v>33.61381624000001</v>
+        <v>10.94663334000001</v>
       </c>
       <c r="G52" t="n">
-        <v>15.43591371</v>
+        <v>-242.48694746</v>
       </c>
       <c r="H52" t="n">
-        <v>-113.78998172</v>
+        <v>176.69649829</v>
       </c>
       <c r="I52" t="n">
-        <v>166.81981741</v>
+        <v>173.3919018</v>
       </c>
       <c r="J52" t="n">
-        <v>318.94946344</v>
+        <v>534.26192584</v>
       </c>
       <c r="K52" t="n">
-        <v>773.50804662</v>
+        <v>553.1683261099998</v>
       </c>
       <c r="L52" t="n">
-        <v>812.5688147</v>
+        <v>-153.03544707</v>
       </c>
       <c r="M52" t="n">
-        <v>211.81430302</v>
+        <v>23.19576348999999</v>
       </c>
     </row>
     <row r="53">
@@ -2604,37 +2598,37 @@
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>32.29490799</v>
+        <v>29.15036724</v>
       </c>
       <c r="D53" t="n">
-        <v>128.09218056</v>
+        <v>2.022065750000001</v>
       </c>
       <c r="E53" t="n">
-        <v>61.64776729</v>
+        <v>-8.206359429999999</v>
       </c>
       <c r="F53" t="n">
-        <v>3.11852082</v>
+        <v>2.95694848</v>
       </c>
       <c r="G53" t="n">
-        <v>27.04329139</v>
+        <v>-5.68872284</v>
       </c>
       <c r="H53" t="n">
-        <v>-24.96587078</v>
+        <v>-1.43237066</v>
       </c>
       <c r="I53" t="n">
-        <v>-20.69356391</v>
+        <v>9.39389042</v>
       </c>
       <c r="J53" t="n">
-        <v>20.21101647</v>
+        <v>5.81157704</v>
       </c>
       <c r="K53" t="n">
-        <v>26.50411286999999</v>
+        <v>17.87863184</v>
       </c>
       <c r="L53" t="n">
-        <v>70.6981641</v>
+        <v>33.16015233</v>
       </c>
       <c r="M53" t="n">
-        <v>48.55903931</v>
+        <v>31.6322211</v>
       </c>
     </row>
     <row r="54">
@@ -2645,37 +2639,37 @@
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>669.1584695800001</v>
+        <v>602.64274175</v>
       </c>
       <c r="D54" t="n">
-        <v>726.66067664</v>
+        <v>288.18667168</v>
       </c>
       <c r="E54" t="n">
-        <v>285.06216034</v>
+        <v>106.61687904</v>
       </c>
       <c r="F54" t="n">
-        <v>28.59221987</v>
+        <v>229.7805576</v>
       </c>
       <c r="G54" t="n">
-        <v>201.20493432</v>
+        <v>-0.8512672999999965</v>
       </c>
       <c r="H54" t="n">
-        <v>-110.2710851</v>
+        <v>76.69232371000001</v>
       </c>
       <c r="I54" t="n">
-        <v>105.83019784</v>
+        <v>90.04812412999999</v>
       </c>
       <c r="J54" t="n">
-        <v>-66.32656356</v>
+        <v>113.18358197</v>
       </c>
       <c r="K54" t="n">
-        <v>-146.75507464</v>
+        <v>262.05763769</v>
       </c>
       <c r="L54" t="n">
-        <v>-50.16238316000002</v>
+        <v>6.733098430000003</v>
       </c>
       <c r="M54" t="n">
-        <v>-373.51553864</v>
+        <v>395.21610116</v>
       </c>
     </row>
     <row r="55">
@@ -2686,37 +2680,37 @@
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>-42.73856727</v>
+        <v>-30.59709092</v>
       </c>
       <c r="D55" t="n">
-        <v>-30.59709092</v>
+        <v>1.71896167</v>
       </c>
       <c r="E55" t="n">
-        <v>1.71896167</v>
+        <v>-3.66064519</v>
       </c>
       <c r="F55" t="n">
-        <v>-3.66064519</v>
+        <v>6.780631179999999</v>
       </c>
       <c r="G55" t="n">
-        <v>6.780631179999999</v>
+        <v>-4.03954524</v>
       </c>
       <c r="H55" t="n">
-        <v>-4.03954524</v>
+        <v>17.6737899</v>
       </c>
       <c r="I55" t="n">
-        <v>17.6737899</v>
+        <v>27.54426674</v>
       </c>
       <c r="J55" t="n">
-        <v>27.54426674</v>
+        <v>42.05846305</v>
       </c>
       <c r="K55" t="n">
-        <v>42.05846305</v>
+        <v>41.63408625</v>
       </c>
       <c r="L55" t="n">
-        <v>41.63408625</v>
+        <v>24.46272503</v>
       </c>
       <c r="M55" t="n">
-        <v>24.46272503</v>
+        <v>-9.778699180000002</v>
       </c>
     </row>
     <row r="56">
@@ -2727,37 +2721,37 @@
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>-12.04617618</v>
+        <v>-10.68184894</v>
       </c>
       <c r="D56" t="n">
-        <v>-10.68183645</v>
+        <v>-2.0628507</v>
       </c>
       <c r="E56" t="n">
-        <v>-2.06279609</v>
+        <v>-7.6462564</v>
       </c>
       <c r="F56" t="n">
-        <v>-7.64622475</v>
+        <v>-7.730777489999999</v>
       </c>
       <c r="G56" t="n">
-        <v>-7.73074792</v>
+        <v>-13.07100915</v>
       </c>
       <c r="H56" t="n">
-        <v>-13.07103159</v>
+        <v>-3.2074072</v>
       </c>
       <c r="I56" t="n">
-        <v>-3.20736873</v>
+        <v>24.12902713</v>
       </c>
       <c r="J56" t="n">
-        <v>24.12907413</v>
+        <v>19.63279965</v>
       </c>
       <c r="K56" t="n">
-        <v>19.6328924</v>
+        <v>9.521514139999999</v>
       </c>
       <c r="L56" t="n">
-        <v>9.521610109999999</v>
+        <v>-6.49064102</v>
       </c>
       <c r="M56" t="n">
-        <v>-6.49068987</v>
+        <v>-19.63755573</v>
       </c>
     </row>
     <row r="57">
@@ -2768,37 +2762,37 @@
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
-        <v>-0.00441554</v>
+        <v>-0.00558287</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.00559536</v>
+        <v>0.00240891</v>
       </c>
       <c r="E57" t="n">
-        <v>0.0023543</v>
+        <v>0.009724190000000001</v>
       </c>
       <c r="F57" t="n">
-        <v>0.009692540000000001</v>
+        <v>0.0047186</v>
       </c>
       <c r="G57" t="n">
-        <v>0.004689029999999999</v>
+        <v>0.00133407</v>
       </c>
       <c r="H57" t="n">
-        <v>0.00135651</v>
+        <v>0.00326678</v>
       </c>
       <c r="I57" t="n">
-        <v>0.00322831</v>
+        <v>0.01353709</v>
       </c>
       <c r="J57" t="n">
-        <v>0.01349009</v>
+        <v>0.01480824</v>
       </c>
       <c r="K57" t="n">
-        <v>0.01471549</v>
+        <v>0.0232123</v>
       </c>
       <c r="L57" t="n">
-        <v>0.02311633</v>
+        <v>0.006269750000000001</v>
       </c>
       <c r="M57" t="n">
-        <v>0.006318600000000001</v>
+        <v>-0.00380255</v>
       </c>
     </row>
     <row r="58">
@@ -2809,37 +2803,37 @@
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>-8.713049559999998</v>
+        <v>-35.22507341000001</v>
       </c>
       <c r="D58" t="n">
-        <v>-35.22507341000001</v>
+        <v>-57.92342369999999</v>
       </c>
       <c r="E58" t="n">
-        <v>-57.92342369999999</v>
+        <v>-68.26387203</v>
       </c>
       <c r="F58" t="n">
-        <v>-68.26387203</v>
+        <v>-8.433303890000001</v>
       </c>
       <c r="G58" t="n">
-        <v>-8.433303890000001</v>
+        <v>-47.65032497000001</v>
       </c>
       <c r="H58" t="n">
-        <v>-47.65032497000001</v>
+        <v>7.703351639999999</v>
       </c>
       <c r="I58" t="n">
-        <v>7.703351639999999</v>
+        <v>41.98299858</v>
       </c>
       <c r="J58" t="n">
-        <v>41.98299858</v>
+        <v>64.00418524</v>
       </c>
       <c r="K58" t="n">
-        <v>64.00418524</v>
+        <v>37.16416376</v>
       </c>
       <c r="L58" t="n">
-        <v>37.16416376</v>
+        <v>48.23396804</v>
       </c>
       <c r="M58" t="n">
-        <v>48.23396804</v>
+        <v>28.77712765</v>
       </c>
     </row>
     <row r="59">
@@ -2850,37 +2844,37 @@
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
-        <v>0.74069321</v>
+        <v>0.24380428</v>
       </c>
       <c r="D59" t="n">
-        <v>0.24380428</v>
+        <v>1.14616828</v>
       </c>
       <c r="E59" t="n">
-        <v>1.14616828</v>
+        <v>0.01365724</v>
       </c>
       <c r="F59" t="n">
-        <v>0.01365724</v>
+        <v>0.7604645999999999</v>
       </c>
       <c r="G59" t="n">
-        <v>0.7604645999999999</v>
+        <v>-0.24529395</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.24529395</v>
+        <v>-0.70815295</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.70815295</v>
+        <v>0.59361993</v>
       </c>
       <c r="J59" t="n">
-        <v>0.59361993</v>
+        <v>1.16829318</v>
       </c>
       <c r="K59" t="n">
-        <v>1.16829318</v>
+        <v>1.87308302</v>
       </c>
       <c r="L59" t="n">
-        <v>1.87308302</v>
+        <v>2.42560356</v>
       </c>
       <c r="M59" t="n">
-        <v>2.42560356</v>
+        <v>0.7308388099999999</v>
       </c>
     </row>
     <row r="60">
@@ -2891,37 +2885,37 @@
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
-        <v>-59.54142481</v>
+        <v>-59.83005495</v>
       </c>
       <c r="D60" t="n">
-        <v>-59.83005495</v>
+        <v>-20.09428251</v>
       </c>
       <c r="E60" t="n">
-        <v>-20.09428251</v>
+        <v>-30.92647838</v>
       </c>
       <c r="F60" t="n">
-        <v>-30.92647838</v>
+        <v>-15.12595207</v>
       </c>
       <c r="G60" t="n">
-        <v>-15.12595207</v>
+        <v>19.01596501</v>
       </c>
       <c r="H60" t="n">
-        <v>19.01596501</v>
+        <v>32.19631332</v>
       </c>
       <c r="I60" t="n">
-        <v>32.19631332</v>
+        <v>66.0032384</v>
       </c>
       <c r="J60" t="n">
-        <v>66.0032384</v>
+        <v>95.20201191</v>
       </c>
       <c r="K60" t="n">
-        <v>95.20201191</v>
+        <v>52.08602065</v>
       </c>
       <c r="L60" t="n">
-        <v>52.08602065</v>
+        <v>56.26502794</v>
       </c>
       <c r="M60" t="n">
-        <v>56.26502794</v>
+        <v>4.496212889999995</v>
       </c>
     </row>
     <row r="61">
@@ -2932,37 +2926,37 @@
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
-        <v>-0.0023249</v>
+        <v>-0.00363863</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.00285701</v>
+        <v>-0.00167134</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.0007670700000000002</v>
+        <v>-0.00462742</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.00377332</v>
+        <v>-0.00432153</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.00373142</v>
+        <v>-0.007909279999999999</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.00726259</v>
+        <v>-0.00354446</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.0029527</v>
+        <v>-0.00278847</v>
       </c>
       <c r="J61" t="n">
-        <v>-0.00233591</v>
+        <v>0.007145980000000001</v>
       </c>
       <c r="K61" t="n">
-        <v>0.007300940000000001</v>
+        <v>0.00555183</v>
       </c>
       <c r="L61" t="n">
-        <v>0.00539476</v>
+        <v>0.00131319</v>
       </c>
       <c r="M61" t="n">
-        <v>0.00131784</v>
+        <v>0.008997719999999999</v>
       </c>
     </row>
     <row r="62">
@@ -2973,37 +2967,37 @@
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>-6.97425895</v>
+        <v>-18.18665765</v>
       </c>
       <c r="D62" t="n">
-        <v>-18.18743927</v>
+        <v>54.93311962999999</v>
       </c>
       <c r="E62" t="n">
-        <v>54.93221536000001</v>
+        <v>-0.1308476699999995</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.1317017699999996</v>
+        <v>15.73948928</v>
       </c>
       <c r="G62" t="n">
-        <v>15.73889917</v>
+        <v>-2.4515891</v>
       </c>
       <c r="H62" t="n">
-        <v>-2.45223579</v>
+        <v>28.65283027</v>
       </c>
       <c r="I62" t="n">
-        <v>28.65223851</v>
+        <v>47.66627009</v>
       </c>
       <c r="J62" t="n">
-        <v>47.66581753</v>
+        <v>94.86354453</v>
       </c>
       <c r="K62" t="n">
-        <v>94.86338957</v>
+        <v>46.74758576</v>
       </c>
       <c r="L62" t="n">
-        <v>46.74774283000001</v>
+        <v>41.24747490999999</v>
       </c>
       <c r="M62" t="n">
-        <v>41.24747026</v>
+        <v>17.01497226</v>
       </c>
     </row>
     <row r="63">
@@ -3014,37 +3008,37 @@
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>-2.134999999999999e-05</v>
+        <v>0.00012761</v>
       </c>
       <c r="D63" t="n">
-        <v>0.00012761</v>
+        <v>0.00014581</v>
       </c>
       <c r="E63" t="n">
-        <v>0.00014581</v>
+        <v>0.00033086</v>
       </c>
       <c r="F63" t="n">
-        <v>0.00033086</v>
+        <v>0.0004248200000000001</v>
       </c>
       <c r="G63" t="n">
-        <v>0.0004248200000000001</v>
+        <v>0.00090755</v>
       </c>
       <c r="H63" t="n">
-        <v>0.00090755</v>
+        <v>0.00103174</v>
       </c>
       <c r="I63" t="n">
-        <v>0.00103174</v>
+        <v>0.0009914099999999999</v>
       </c>
       <c r="J63" t="n">
-        <v>0.0009914099999999999</v>
+        <v>6.247e-05</v>
       </c>
       <c r="K63" t="n">
-        <v>6.247e-05</v>
+        <v>0.0004044</v>
       </c>
       <c r="L63" t="n">
-        <v>0.0004044</v>
+        <v>0.00072251</v>
       </c>
       <c r="M63" t="n">
-        <v>0.00072251</v>
+        <v>-0.00025412</v>
       </c>
     </row>
     <row r="64">
@@ -3055,37 +3049,37 @@
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
-        <v>-0.00019394</v>
+        <v>-0.00018756</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.00018756</v>
+        <v>-0.00024988</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.00024988</v>
+        <v>-0.00027272</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.00027272</v>
+        <v>-0.0002611</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.0002611</v>
+        <v>-0.00027651</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.00027651</v>
+        <v>-0.0002609000000000001</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.0002609000000000001</v>
+        <v>5.814e-05</v>
       </c>
       <c r="J64" t="n">
-        <v>5.814e-05</v>
+        <v>0.00018835</v>
       </c>
       <c r="K64" t="n">
-        <v>0.00018835</v>
+        <v>2.243e-05</v>
       </c>
       <c r="L64" t="n">
-        <v>2.243e-05</v>
+        <v>-8.019e-05</v>
       </c>
       <c r="M64" t="n">
-        <v>-8.019e-05</v>
+        <v>-3.720999999999999e-05</v>
       </c>
     </row>
     <row r="65">
@@ -3096,37 +3090,37 @@
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
-        <v>662.4879303500001</v>
+        <v>545.52838719</v>
       </c>
       <c r="D65" t="n">
-        <v>637.64115263</v>
+        <v>1076.26157955</v>
       </c>
       <c r="E65" t="n">
-        <v>1115.98903911</v>
+        <v>852.3115199600001</v>
       </c>
       <c r="F65" t="n">
-        <v>915.3000246800001</v>
+        <v>101.008516</v>
       </c>
       <c r="G65" t="n">
-        <v>208.17638257</v>
+        <v>413.7915287</v>
       </c>
       <c r="H65" t="n">
-        <v>489.72836174</v>
+        <v>-28.99580328000001</v>
       </c>
       <c r="I65" t="n">
-        <v>57.70085710999999</v>
+        <v>175.92371544</v>
       </c>
       <c r="J65" t="n">
-        <v>224.03415516</v>
+        <v>709.1590385</v>
       </c>
       <c r="K65" t="n">
-        <v>719.02437558</v>
+        <v>228.75441454</v>
       </c>
       <c r="L65" t="n">
-        <v>228.66167738</v>
+        <v>580.34068565</v>
       </c>
       <c r="M65" t="n">
-        <v>582.55440177</v>
+        <v>763.7509641700001</v>
       </c>
     </row>
     <row r="66">
@@ -3137,37 +3131,37 @@
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>19.83930881</v>
+        <v>31.1887251</v>
       </c>
       <c r="D66" t="n">
-        <v>16.35814125</v>
+        <v>33.87624075999999</v>
       </c>
       <c r="E66" t="n">
-        <v>14.85698009</v>
+        <v>44.29952979999999</v>
       </c>
       <c r="F66" t="n">
-        <v>19.65247369</v>
+        <v>29.08693983</v>
       </c>
       <c r="G66" t="n">
-        <v>-17.09074356</v>
+        <v>0.4105898600000005</v>
       </c>
       <c r="H66" t="n">
-        <v>-53.14245764</v>
+        <v>86.89475669999999</v>
       </c>
       <c r="I66" t="n">
-        <v>-3.999204540000001</v>
+        <v>-34.34445583999999</v>
       </c>
       <c r="J66" t="n">
-        <v>33.33790329</v>
+        <v>-19.90779443</v>
       </c>
       <c r="K66" t="n">
-        <v>2.42368097</v>
+        <v>-40.57344869999999</v>
       </c>
       <c r="L66" t="n">
-        <v>1.515334689999999</v>
+        <v>-96.36349721000001</v>
       </c>
       <c r="M66" t="n">
-        <v>-43.93684397</v>
+        <v>-77.19925556</v>
       </c>
     </row>
     <row r="67">
@@ -3178,37 +3172,37 @@
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>187.54828935</v>
+        <v>555.37691608</v>
       </c>
       <c r="D67" t="n">
-        <v>478.09473449</v>
+        <v>823.02801951</v>
       </c>
       <c r="E67" t="n">
-        <v>802.31982062</v>
+        <v>322.44746653</v>
       </c>
       <c r="F67" t="n">
-        <v>284.10601792</v>
+        <v>367.82150821</v>
       </c>
       <c r="G67" t="n">
-        <v>306.83132503</v>
+        <v>114.43159391</v>
       </c>
       <c r="H67" t="n">
-        <v>92.04780836999998</v>
+        <v>298.04569379</v>
       </c>
       <c r="I67" t="n">
-        <v>302.24299464</v>
+        <v>202.1253038</v>
       </c>
       <c r="J67" t="n">
-        <v>86.33250495000001</v>
+        <v>183.86646338</v>
       </c>
       <c r="K67" t="n">
-        <v>151.6696509</v>
+        <v>138.78240026</v>
       </c>
       <c r="L67" t="n">
-        <v>96.78635402999998</v>
+        <v>-27.89177712999998</v>
       </c>
       <c r="M67" t="n">
-        <v>-82.53214648999999</v>
+        <v>-117.21568837</v>
       </c>
     </row>
     <row r="68">
@@ -3219,37 +3213,37 @@
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>8.895559609999999</v>
+        <v>25.77768484</v>
       </c>
       <c r="D68" t="n">
-        <v>25.77768484</v>
+        <v>7.5358798</v>
       </c>
       <c r="E68" t="n">
-        <v>7.5358798</v>
+        <v>-2.18453111</v>
       </c>
       <c r="F68" t="n">
-        <v>-2.18453111</v>
+        <v>-4.28064262</v>
       </c>
       <c r="G68" t="n">
-        <v>-4.28064262</v>
+        <v>-9.848016550000001</v>
       </c>
       <c r="H68" t="n">
-        <v>-9.848016550000001</v>
+        <v>-11.75977663</v>
       </c>
       <c r="I68" t="n">
-        <v>-11.75977663</v>
+        <v>-14.45543988</v>
       </c>
       <c r="J68" t="n">
-        <v>-14.45543988</v>
+        <v>-8.60103045</v>
       </c>
       <c r="K68" t="n">
-        <v>-8.60103045</v>
+        <v>1.481096</v>
       </c>
       <c r="L68" t="n">
-        <v>1.481096</v>
+        <v>-2.09694106</v>
       </c>
       <c r="M68" t="n">
-        <v>-2.09694106</v>
+        <v>-1.18870531</v>
       </c>
     </row>
     <row r="69">
@@ -3260,37 +3254,37 @@
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>-0.33839224</v>
+        <v>-1.43394215</v>
       </c>
       <c r="D69" t="n">
-        <v>-1.43394215</v>
+        <v>-1.69268373</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.69268373</v>
+        <v>-3.23010772</v>
       </c>
       <c r="F69" t="n">
-        <v>-3.23010772</v>
+        <v>-3.39045584</v>
       </c>
       <c r="G69" t="n">
-        <v>-3.39045584</v>
+        <v>-4.06147909</v>
       </c>
       <c r="H69" t="n">
-        <v>-4.06147909</v>
+        <v>-3.60733925</v>
       </c>
       <c r="I69" t="n">
-        <v>-3.60733925</v>
+        <v>-1.16033294</v>
       </c>
       <c r="J69" t="n">
-        <v>-1.16033294</v>
+        <v>-1.55525517</v>
       </c>
       <c r="K69" t="n">
-        <v>-1.55525517</v>
+        <v>0.15859867</v>
       </c>
       <c r="L69" t="n">
-        <v>0.15859867</v>
+        <v>-0.01651628</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.01651628</v>
+        <v>0.93115824</v>
       </c>
     </row>
     <row r="70">
@@ -3301,37 +3295,37 @@
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>-16.91394174</v>
+        <v>-16.82706139</v>
       </c>
       <c r="D70" t="n">
-        <v>-16.82706139</v>
+        <v>-21.49287157</v>
       </c>
       <c r="E70" t="n">
-        <v>-21.49287157</v>
+        <v>-29.75249595</v>
       </c>
       <c r="F70" t="n">
-        <v>-29.75249595</v>
+        <v>-5.49167339</v>
       </c>
       <c r="G70" t="n">
-        <v>-5.49167339</v>
+        <v>-6.985563310000001</v>
       </c>
       <c r="H70" t="n">
-        <v>-6.985563310000001</v>
+        <v>6.14054282</v>
       </c>
       <c r="I70" t="n">
-        <v>6.14054282</v>
+        <v>22.89727625</v>
       </c>
       <c r="J70" t="n">
-        <v>22.89727625</v>
+        <v>39.58487804</v>
       </c>
       <c r="K70" t="n">
-        <v>39.58487804</v>
+        <v>49.03197814</v>
       </c>
       <c r="L70" t="n">
-        <v>49.03197814</v>
+        <v>20.29127258</v>
       </c>
       <c r="M70" t="n">
-        <v>20.29127258</v>
+        <v>24.00895878</v>
       </c>
     </row>
     <row r="71">
@@ -3342,37 +3336,37 @@
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
-        <v>65.03796482999999</v>
+        <v>7.475289409999997</v>
       </c>
       <c r="D71" t="n">
-        <v>7.475289409999997</v>
+        <v>-64.07427258999999</v>
       </c>
       <c r="E71" t="n">
-        <v>-64.07427258999999</v>
+        <v>-115.50237892</v>
       </c>
       <c r="F71" t="n">
-        <v>-115.50237892</v>
+        <v>-11.79256974999999</v>
       </c>
       <c r="G71" t="n">
-        <v>-11.79256974999999</v>
+        <v>-141.47987787</v>
       </c>
       <c r="H71" t="n">
-        <v>-141.47987787</v>
+        <v>-101.90599359</v>
       </c>
       <c r="I71" t="n">
-        <v>-101.90599359</v>
+        <v>-27.86393122</v>
       </c>
       <c r="J71" t="n">
-        <v>-27.86393122</v>
+        <v>-19.72376035</v>
       </c>
       <c r="K71" t="n">
-        <v>-19.72376035</v>
+        <v>-80.99866675</v>
       </c>
       <c r="L71" t="n">
-        <v>-80.99866675</v>
+        <v>-115.79851781</v>
       </c>
       <c r="M71" t="n">
-        <v>-115.79851781</v>
+        <v>-38.42840705</v>
       </c>
     </row>
     <row r="72">
@@ -3383,37 +3377,37 @@
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>16.39634759</v>
+        <v>4.281030289999999</v>
       </c>
       <c r="D72" t="n">
-        <v>4.281030289999999</v>
+        <v>5.539278160000001</v>
       </c>
       <c r="E72" t="n">
-        <v>5.539278160000001</v>
+        <v>-2.54610903</v>
       </c>
       <c r="F72" t="n">
-        <v>-2.54610903</v>
+        <v>-1.68230068</v>
       </c>
       <c r="G72" t="n">
-        <v>-1.68230068</v>
+        <v>-10.98006195</v>
       </c>
       <c r="H72" t="n">
-        <v>-10.98006195</v>
+        <v>0.2389688799999998</v>
       </c>
       <c r="I72" t="n">
-        <v>0.2389688799999998</v>
+        <v>11.07624471</v>
       </c>
       <c r="J72" t="n">
-        <v>11.07624471</v>
+        <v>3.90076889</v>
       </c>
       <c r="K72" t="n">
-        <v>3.90076889</v>
+        <v>-10.60413652</v>
       </c>
       <c r="L72" t="n">
-        <v>-10.60413652</v>
+        <v>-10.73076839</v>
       </c>
       <c r="M72" t="n">
-        <v>-10.73076839</v>
+        <v>-23.37633456</v>
       </c>
     </row>
     <row r="73">
@@ -3424,37 +3418,37 @@
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
-        <v>-775.45050197</v>
+        <v>-1039.8621816</v>
       </c>
       <c r="D73" t="n">
-        <v>-1055.71776824</v>
+        <v>-1355.62532236</v>
       </c>
       <c r="E73" t="n">
-        <v>-1344.25654867</v>
+        <v>-1508.41550234</v>
       </c>
       <c r="F73" t="n">
-        <v>-1513.10008246</v>
+        <v>-486.04991945</v>
       </c>
       <c r="G73" t="n">
-        <v>-486.52127426</v>
+        <v>-927.54211931</v>
       </c>
       <c r="H73" t="n">
-        <v>-936.91281313</v>
+        <v>49.54949119</v>
       </c>
       <c r="I73" t="n">
-        <v>59.42146735</v>
+        <v>884.7286469300001</v>
       </c>
       <c r="J73" t="n">
-        <v>903.2323206300001</v>
+        <v>779.76484189</v>
       </c>
       <c r="K73" t="n">
-        <v>800.7780561700001</v>
+        <v>1144.01673126</v>
       </c>
       <c r="L73" t="n">
-        <v>1167.48715472</v>
+        <v>804.37010775</v>
       </c>
       <c r="M73" t="n">
-        <v>823.8283143199999</v>
+        <v>647.00666835</v>
       </c>
     </row>
     <row r="74">
@@ -3463,39 +3457,41 @@
           <t>金融保險右下</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr"/>
+      <c r="B74" t="n">
+        <v>0</v>
+      </c>
       <c r="C74" t="n">
-        <v>-889.3013006599999</v>
+        <v>-155.54415517</v>
       </c>
       <c r="D74" t="n">
-        <v>-155.54415517</v>
+        <v>-454.77151971</v>
       </c>
       <c r="E74" t="n">
-        <v>-454.77151971</v>
+        <v>-641.20146943</v>
       </c>
       <c r="F74" t="n">
-        <v>-641.20146943</v>
+        <v>-347.05644305</v>
       </c>
       <c r="G74" t="n">
-        <v>-347.05644305</v>
+        <v>-359.8776884299999</v>
       </c>
       <c r="H74" t="n">
-        <v>-359.8776884299999</v>
+        <v>-343.74413127</v>
       </c>
       <c r="I74" t="n">
-        <v>-343.74413127</v>
+        <v>-136.81080979</v>
       </c>
       <c r="J74" t="n">
-        <v>-136.81080979</v>
+        <v>34.65447583</v>
       </c>
       <c r="K74" t="n">
-        <v>34.65447583</v>
+        <v>112.2585677</v>
       </c>
       <c r="L74" t="n">
-        <v>112.2585677</v>
+        <v>-45.85452738</v>
       </c>
       <c r="M74" t="n">
-        <v>-45.85452738</v>
+        <v>-206.11673481</v>
       </c>
     </row>
     <row r="75">
@@ -3506,37 +3502,37 @@
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
-        <v>-18.2611149</v>
+        <v>-58.58307425</v>
       </c>
       <c r="D75" t="n">
-        <v>-58.58307425</v>
+        <v>-125.06047454</v>
       </c>
       <c r="E75" t="n">
-        <v>-125.06047454</v>
+        <v>-179.56732411</v>
       </c>
       <c r="F75" t="n">
-        <v>-179.56732411</v>
+        <v>-83.0036958</v>
       </c>
       <c r="G75" t="n">
-        <v>-83.0036958</v>
+        <v>-145.13371544</v>
       </c>
       <c r="H75" t="n">
-        <v>-145.13371544</v>
+        <v>17.82308436</v>
       </c>
       <c r="I75" t="n">
-        <v>17.82308436</v>
+        <v>181.23442961</v>
       </c>
       <c r="J75" t="n">
-        <v>181.23442961</v>
+        <v>133.4526263</v>
       </c>
       <c r="K75" t="n">
-        <v>133.4526263</v>
+        <v>161.94001351</v>
       </c>
       <c r="L75" t="n">
-        <v>161.94001351</v>
+        <v>47.34589182</v>
       </c>
       <c r="M75" t="n">
-        <v>47.34589182</v>
+        <v>55.02704358</v>
       </c>
     </row>
     <row r="76">
@@ -3547,37 +3543,37 @@
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>-0.00053725</v>
+        <v>-0.00057684</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.00057684</v>
+        <v>-0.0006594299999999999</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.0006594299999999999</v>
+        <v>-0.00071329</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.00071329</v>
+        <v>-0.0003751</v>
       </c>
       <c r="G76" t="n">
-        <v>-0.0003751</v>
+        <v>-0.00072667</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.00072667</v>
+        <v>-0.00031853</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.00031853</v>
+        <v>-0.00042214</v>
       </c>
       <c r="J76" t="n">
-        <v>-0.00042214</v>
+        <v>0.00035191</v>
       </c>
       <c r="K76" t="n">
-        <v>0.00035191</v>
+        <v>0.0006016</v>
       </c>
       <c r="L76" t="n">
-        <v>0.0006016</v>
+        <v>0.00119589</v>
       </c>
       <c r="M76" t="n">
-        <v>0.00119589</v>
+        <v>0.00222055</v>
       </c>
     </row>
     <row r="77">
@@ -3588,37 +3584,37 @@
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="n">
-        <v>0.00368509</v>
+        <v>0.004119070000000001</v>
       </c>
       <c r="D77" t="n">
-        <v>0.004119070000000001</v>
+        <v>0.00104634</v>
       </c>
       <c r="E77" t="n">
-        <v>0.00104634</v>
+        <v>-0.00267286</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.00267286</v>
+        <v>-9.306000000000001e-05</v>
       </c>
       <c r="G77" t="n">
-        <v>-9.306000000000001e-05</v>
+        <v>-0.00439828</v>
       </c>
       <c r="H77" t="n">
-        <v>-0.00439828</v>
+        <v>-0.005935770000000001</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.005935770000000001</v>
+        <v>-0.006376339999999999</v>
       </c>
       <c r="J77" t="n">
-        <v>-0.006376339999999999</v>
+        <v>-0.00146164</v>
       </c>
       <c r="K77" t="n">
-        <v>-0.00146164</v>
+        <v>0.0001785999999999999</v>
       </c>
       <c r="L77" t="n">
-        <v>0.0001785999999999999</v>
+        <v>0.00166505</v>
       </c>
       <c r="M77" t="n">
-        <v>0.00166505</v>
+        <v>0.00481058</v>
       </c>
     </row>
     <row r="78">
@@ -3629,37 +3625,37 @@
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
-        <v>-0.0004297</v>
+        <v>-0.00048908</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.00048908</v>
+        <v>-0.00026955</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.00026955</v>
+        <v>-0.00035725</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.00035725</v>
+        <v>-0.00052145</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.00052145</v>
+        <v>-0.00052038</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.00052038</v>
+        <v>-0.00049876</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.00049876</v>
+        <v>-0.00010349</v>
       </c>
       <c r="J78" t="n">
-        <v>-0.00010349</v>
+        <v>0.00149008</v>
       </c>
       <c r="K78" t="n">
-        <v>0.00149008</v>
+        <v>0.00167124</v>
       </c>
       <c r="L78" t="n">
-        <v>0.00167124</v>
+        <v>0.00103193</v>
       </c>
       <c r="M78" t="n">
-        <v>0.00103193</v>
+        <v>0.00057835</v>
       </c>
     </row>
     <row r="79">
@@ -3670,37 +3666,37 @@
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="n">
-        <v>12.60022255</v>
+        <v>349.1965062800001</v>
       </c>
       <c r="D79" t="n">
-        <v>28.00022631</v>
+        <v>489.0815217</v>
       </c>
       <c r="E79" t="n">
-        <v>3.68878533</v>
+        <v>750.7487125599999</v>
       </c>
       <c r="F79" t="n">
-        <v>-6.56068165</v>
+        <v>741.8872466500001</v>
       </c>
       <c r="G79" t="n">
-        <v>5.127412570000001</v>
+        <v>201.67650435</v>
       </c>
       <c r="H79" t="n">
-        <v>0.3745234199999999</v>
+        <v>-141.11423658</v>
       </c>
       <c r="I79" t="n">
-        <v>-13.08952523</v>
+        <v>0.7313264700000002</v>
       </c>
       <c r="J79" t="n">
-        <v>-4.331212519999999</v>
+        <v>-176.67389534</v>
       </c>
       <c r="K79" t="n">
-        <v>-10.25827174</v>
+        <v>-79.90343278</v>
       </c>
       <c r="L79" t="n">
-        <v>8.421552140000001</v>
+        <v>-228.13185528</v>
       </c>
       <c r="M79" t="n">
-        <v>-10.13260721</v>
+        <v>74.18891708000001</v>
       </c>
     </row>
     <row r="80">
@@ -3711,37 +3707,37 @@
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="n">
-        <v>59.36770919</v>
+        <v>36.53568006</v>
       </c>
       <c r="D80" t="n">
-        <v>36.53568006</v>
+        <v>-46.66810387</v>
       </c>
       <c r="E80" t="n">
-        <v>-46.66810387</v>
+        <v>-86.27307861</v>
       </c>
       <c r="F80" t="n">
-        <v>-86.27307861</v>
+        <v>4.663124380000001</v>
       </c>
       <c r="G80" t="n">
-        <v>4.663124380000001</v>
+        <v>-72.56750855</v>
       </c>
       <c r="H80" t="n">
-        <v>-72.56750855</v>
+        <v>-103.89955773</v>
       </c>
       <c r="I80" t="n">
-        <v>-104.41170928</v>
+        <v>-113.32769049</v>
       </c>
       <c r="J80" t="n">
-        <v>-113.93601583</v>
+        <v>-68.71882223</v>
       </c>
       <c r="K80" t="n">
-        <v>-69.00746740999999</v>
+        <v>-46.24819579</v>
       </c>
       <c r="L80" t="n">
-        <v>-46.30035985</v>
+        <v>-65.44478223999999</v>
       </c>
       <c r="M80" t="n">
-        <v>-65.86029197000001</v>
+        <v>-39.48523577</v>
       </c>
     </row>
     <row r="81">
@@ -3752,37 +3748,37 @@
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>106.93633643</v>
+        <v>35.47651657</v>
       </c>
       <c r="D81" t="n">
-        <v>356.67279654</v>
+        <v>21.61024113</v>
       </c>
       <c r="E81" t="n">
-        <v>507.0029775</v>
+        <v>18.5110399</v>
       </c>
       <c r="F81" t="n">
-        <v>775.8204341100001</v>
+        <v>67.25528339</v>
       </c>
       <c r="G81" t="n">
-        <v>804.0151174700002</v>
+        <v>44.31661445</v>
       </c>
       <c r="H81" t="n">
-        <v>245.61859538</v>
+        <v>134.51129435</v>
       </c>
       <c r="I81" t="n">
-        <v>6.446631980000004</v>
+        <v>96.13981677</v>
       </c>
       <c r="J81" t="n">
-        <v>101.28266764</v>
+        <v>120.37920766</v>
       </c>
       <c r="K81" t="n">
-        <v>-46.01295269999999</v>
+        <v>91.52392227000001</v>
       </c>
       <c r="L81" t="n">
-        <v>3.234432050000005</v>
+        <v>52.25192397</v>
       </c>
       <c r="M81" t="n">
-        <v>-165.87367631</v>
+        <v>8.08547903</v>
       </c>
     </row>
     <row r="82">
@@ -3793,37 +3789,37 @@
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
-        <v>-10.64403632</v>
+        <v>-5.600883880000002</v>
       </c>
       <c r="D82" t="n">
-        <v>-5.600883880000002</v>
+        <v>-16.1009798</v>
       </c>
       <c r="E82" t="n">
-        <v>-16.1009798</v>
+        <v>35.45646956</v>
       </c>
       <c r="F82" t="n">
-        <v>35.45646956</v>
+        <v>68.03330789</v>
       </c>
       <c r="G82" t="n">
-        <v>68.03330789</v>
+        <v>-4.41017006</v>
       </c>
       <c r="H82" t="n">
-        <v>-4.41017006</v>
+        <v>-6.688197980000001</v>
       </c>
       <c r="I82" t="n">
-        <v>-6.688197980000001</v>
+        <v>39.15618257</v>
       </c>
       <c r="J82" t="n">
-        <v>39.15618257</v>
+        <v>88.37693567999999</v>
       </c>
       <c r="K82" t="n">
-        <v>88.37693567999999</v>
+        <v>173.80208869</v>
       </c>
       <c r="L82" t="n">
-        <v>173.80208869</v>
+        <v>68.31111571000001</v>
       </c>
       <c r="M82" t="n">
-        <v>68.31111571000001</v>
+        <v>-15.21283794</v>
       </c>
     </row>
     <row r="83">
@@ -3834,37 +3830,37 @@
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>10.48398042</v>
+        <v>-5.995241029999999</v>
       </c>
       <c r="D83" t="n">
-        <v>-6.200787319999999</v>
+        <v>7.19180515</v>
       </c>
       <c r="E83" t="n">
-        <v>7.24090026</v>
+        <v>-6.73828916</v>
       </c>
       <c r="F83" t="n">
-        <v>-6.584324479999999</v>
+        <v>102.04973315</v>
       </c>
       <c r="G83" t="n">
-        <v>102.05297551</v>
+        <v>-116.03766855</v>
       </c>
       <c r="H83" t="n">
-        <v>-115.80629482</v>
+        <v>-143.59839725</v>
       </c>
       <c r="I83" t="n">
-        <v>-143.5880583</v>
+        <v>-122.34910587</v>
       </c>
       <c r="J83" t="n">
-        <v>-122.46679617</v>
+        <v>-54.08839686000001</v>
       </c>
       <c r="K83" t="n">
-        <v>-54.09129918000001</v>
+        <v>-10.32371517</v>
       </c>
       <c r="L83" t="n">
-        <v>-10.37837567</v>
+        <v>20.68578092</v>
       </c>
       <c r="M83" t="n">
-        <v>20.72719751</v>
+        <v>50.43591372</v>
       </c>
     </row>
     <row r="84">
@@ -3875,37 +3871,37 @@
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
-        <v>-15.07566146</v>
+        <v>-25.98931853</v>
       </c>
       <c r="D84" t="n">
-        <v>-25.78377224</v>
+        <v>-21.69868568</v>
       </c>
       <c r="E84" t="n">
-        <v>-21.74778079</v>
+        <v>-16.25636132</v>
       </c>
       <c r="F84" t="n">
-        <v>-16.410326</v>
+        <v>-1.10998745</v>
       </c>
       <c r="G84" t="n">
-        <v>-1.11322981</v>
+        <v>-17.7452246</v>
       </c>
       <c r="H84" t="n">
-        <v>-17.97659833</v>
+        <v>-22.43654935</v>
       </c>
       <c r="I84" t="n">
-        <v>-22.4468883</v>
+        <v>-6.625887400000001</v>
       </c>
       <c r="J84" t="n">
-        <v>-6.5081971</v>
+        <v>10.56383229</v>
       </c>
       <c r="K84" t="n">
-        <v>10.56673461</v>
+        <v>91.58342936</v>
       </c>
       <c r="L84" t="n">
-        <v>91.63808985999999</v>
+        <v>307.9963481</v>
       </c>
       <c r="M84" t="n">
-        <v>307.9549315100001</v>
+        <v>127.17968981</v>
       </c>
     </row>
     <row r="85">
@@ -3916,37 +3912,37 @@
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>2.312927219999999</v>
+        <v>-14.73780212</v>
       </c>
       <c r="D85" t="n">
-        <v>-14.73780212</v>
+        <v>45.55591851</v>
       </c>
       <c r="E85" t="n">
-        <v>45.55591851</v>
+        <v>20.93663418</v>
       </c>
       <c r="F85" t="n">
-        <v>20.93663418</v>
+        <v>83.75538558</v>
       </c>
       <c r="G85" t="n">
-        <v>83.75538558</v>
+        <v>31.50825829</v>
       </c>
       <c r="H85" t="n">
-        <v>31.50825829</v>
+        <v>43.48443047</v>
       </c>
       <c r="I85" t="n">
-        <v>43.48443047</v>
+        <v>13.09829768</v>
       </c>
       <c r="J85" t="n">
-        <v>13.09829768</v>
+        <v>98.23389636000002</v>
       </c>
       <c r="K85" t="n">
-        <v>98.23389636000002</v>
+        <v>22.42436713</v>
       </c>
       <c r="L85" t="n">
-        <v>22.42436713</v>
+        <v>-73.80742721999999</v>
       </c>
       <c r="M85" t="n">
-        <v>-73.80742721999999</v>
+        <v>-141.66079415</v>
       </c>
     </row>
     <row r="86">
@@ -3957,37 +3953,37 @@
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
-        <v>17.21231996</v>
+        <v>-2.703178970000001</v>
       </c>
       <c r="D86" t="n">
-        <v>9.666825319999999</v>
+        <v>3.224730260000002</v>
       </c>
       <c r="E86" t="n">
-        <v>13.81801526</v>
+        <v>-21.47029142</v>
       </c>
       <c r="F86" t="n">
-        <v>0.01406337</v>
+        <v>-7.91920331</v>
       </c>
       <c r="G86" t="n">
-        <v>3.64720106</v>
+        <v>-36.21035567</v>
       </c>
       <c r="H86" t="n">
-        <v>-2.23925099</v>
+        <v>-36.17334212999999</v>
       </c>
       <c r="I86" t="n">
-        <v>2.45052868</v>
+        <v>-17.99274967</v>
       </c>
       <c r="J86" t="n">
-        <v>5.204550360000001</v>
+        <v>2.984687119999999</v>
       </c>
       <c r="K86" t="n">
-        <v>8.83929865</v>
+        <v>-5.265299160000001</v>
       </c>
       <c r="L86" t="n">
-        <v>9.964043440000001</v>
+        <v>0.6815553000000008</v>
       </c>
       <c r="M86" t="n">
-        <v>13.17166716</v>
+        <v>-38.59596085</v>
       </c>
     </row>
     <row r="87">
@@ -3998,37 +3994,37 @@
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>-80.45010463</v>
+        <v>-18.34169891</v>
       </c>
       <c r="D87" t="n">
-        <v>-30.7117032</v>
+        <v>38.30534171</v>
       </c>
       <c r="E87" t="n">
-        <v>27.71205671000001</v>
+        <v>-24.36095889</v>
       </c>
       <c r="F87" t="n">
-        <v>-45.84531368</v>
+        <v>23.70920259</v>
       </c>
       <c r="G87" t="n">
-        <v>12.14279822</v>
+        <v>-37.93858206</v>
       </c>
       <c r="H87" t="n">
-        <v>-71.90968674000001</v>
+        <v>6.009685249999998</v>
       </c>
       <c r="I87" t="n">
-        <v>-32.61418556</v>
+        <v>39.0312451</v>
       </c>
       <c r="J87" t="n">
-        <v>15.83394507</v>
+        <v>73.29482257000001</v>
       </c>
       <c r="K87" t="n">
-        <v>67.44021103999999</v>
+        <v>106.34746701</v>
       </c>
       <c r="L87" t="n">
-        <v>91.11812440999999</v>
+        <v>61.18977798</v>
       </c>
       <c r="M87" t="n">
-        <v>48.69966612</v>
+        <v>-6.59081659</v>
       </c>
     </row>
     <row r="88">
@@ -4039,37 +4035,37 @@
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
-        <v>1996.88248885</v>
+        <v>297.72893396</v>
       </c>
       <c r="D88" t="n">
-        <v>335.27676698</v>
+        <v>1915.63000907</v>
       </c>
       <c r="E88" t="n">
-        <v>1948.0038844</v>
+        <v>1121.81336747</v>
       </c>
       <c r="F88" t="n">
-        <v>1153.77468284</v>
+        <v>511.14990518</v>
       </c>
       <c r="G88" t="n">
-        <v>539.04257491</v>
+        <v>2100.27602122</v>
       </c>
       <c r="H88" t="n">
-        <v>2122.39441528</v>
+        <v>3109.51351174</v>
       </c>
       <c r="I88" t="n">
-        <v>3114.11401218</v>
+        <v>534.58430609</v>
       </c>
       <c r="J88" t="n">
-        <v>535.38563185</v>
+        <v>3001.40162512</v>
       </c>
       <c r="K88" t="n">
-        <v>2986.65455767</v>
+        <v>1383.30676836</v>
       </c>
       <c r="L88" t="n">
-        <v>1363.49813312</v>
+        <v>1204.89327901</v>
       </c>
       <c r="M88" t="n">
-        <v>1129.59196537</v>
+        <v>3540.41320232</v>
       </c>
     </row>
     <row r="89">
@@ -4080,37 +4076,37 @@
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>23.02808266000001</v>
+        <v>-393.67012069</v>
       </c>
       <c r="D89" t="n">
-        <v>-393.3110172200001</v>
+        <v>-83.48365996</v>
       </c>
       <c r="E89" t="n">
-        <v>-84.92967764999997</v>
+        <v>931.00139862</v>
       </c>
       <c r="F89" t="n">
-        <v>931.5082035199999</v>
+        <v>1130.62755198</v>
       </c>
       <c r="G89" t="n">
-        <v>1129.79374479</v>
+        <v>77.14323940999999</v>
       </c>
       <c r="H89" t="n">
-        <v>75.17580845000001</v>
+        <v>123.34598509</v>
       </c>
       <c r="I89" t="n">
-        <v>124.00556606</v>
+        <v>-328.50834531</v>
       </c>
       <c r="J89" t="n">
-        <v>-315.54687746</v>
+        <v>-266.28661612</v>
       </c>
       <c r="K89" t="n">
-        <v>-262.35812686</v>
+        <v>-595.46834428</v>
       </c>
       <c r="L89" t="n">
-        <v>-595.77949269</v>
+        <v>-484.0643838399999</v>
       </c>
       <c r="M89" t="n">
-        <v>-488.48068716</v>
+        <v>-380.73167867</v>
       </c>
     </row>
     <row r="90">
@@ -4121,37 +4117,37 @@
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>613.0285305599999</v>
+        <v>1066.76281926</v>
       </c>
       <c r="D90" t="n">
-        <v>1028.85588277</v>
+        <v>1431.63135491</v>
       </c>
       <c r="E90" t="n">
-        <v>1400.70349727</v>
+        <v>394.77852725</v>
       </c>
       <c r="F90" t="n">
-        <v>362.31040698</v>
+        <v>-96.26091031</v>
       </c>
       <c r="G90" t="n">
-        <v>-123.31977285</v>
+        <v>-677.67515068</v>
       </c>
       <c r="H90" t="n">
-        <v>-697.82611378</v>
+        <v>-784.53746871</v>
       </c>
       <c r="I90" t="n">
-        <v>-789.66948011</v>
+        <v>-672.7562283899999</v>
       </c>
       <c r="J90" t="n">
-        <v>-685.6988509600001</v>
+        <v>91.62525670000001</v>
       </c>
       <c r="K90" t="n">
-        <v>102.33780019</v>
+        <v>-680.17910633</v>
       </c>
       <c r="L90" t="n">
-        <v>-660.33446947</v>
+        <v>-902.10415739</v>
       </c>
       <c r="M90" t="n">
-        <v>-822.70220537</v>
+        <v>-606.5519585200001</v>
       </c>
     </row>
     <row r="91">
@@ -4162,37 +4158,37 @@
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>-204.85211993</v>
+        <v>-950.4535898400001</v>
       </c>
       <c r="D91" t="n">
-        <v>-973.5193657500001</v>
+        <v>-380.51576305</v>
       </c>
       <c r="E91" t="n">
-        <v>-396.29097509</v>
+        <v>-284.10655618</v>
       </c>
       <c r="F91" t="n">
-        <v>-273.7276208100001</v>
+        <v>-260.54141641</v>
       </c>
       <c r="G91" t="n">
-        <v>-267.98953925</v>
+        <v>-140.93046016</v>
       </c>
       <c r="H91" t="n">
-        <v>-144.3117167</v>
+        <v>231.47509598</v>
       </c>
       <c r="I91" t="n">
-        <v>236.34830219</v>
+        <v>-1066.58062978</v>
       </c>
       <c r="J91" t="n">
-        <v>-1051.47495583</v>
+        <v>-1058.24624676</v>
       </c>
       <c r="K91" t="n">
-        <v>-1059.65958156</v>
+        <v>-312.1660538899999</v>
       </c>
       <c r="L91" t="n">
-        <v>-274.4274442199999</v>
+        <v>785.87981229</v>
       </c>
       <c r="M91" t="n">
-        <v>842.66042312</v>
+        <v>-13.84784272</v>
       </c>
     </row>
     <row r="92">
@@ -4203,37 +4199,37 @@
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>91.51347527999999</v>
+        <v>-34.19437538</v>
       </c>
       <c r="D92" t="n">
-        <v>-52.62426496</v>
+        <v>-6.14492606</v>
       </c>
       <c r="E92" t="n">
-        <v>-40.00041285</v>
+        <v>-41.9563862</v>
       </c>
       <c r="F92" t="n">
-        <v>-83.57204142000001</v>
+        <v>13.21991144</v>
       </c>
       <c r="G92" t="n">
-        <v>59.78413285</v>
+        <v>-60.03639301</v>
       </c>
       <c r="H92" t="n">
-        <v>-48.40594169</v>
+        <v>-99.56108504000001</v>
       </c>
       <c r="I92" t="n">
-        <v>-27.57166399000001</v>
+        <v>-27.59891615</v>
       </c>
       <c r="J92" t="n">
-        <v>-25.67902986999999</v>
+        <v>-2.575576679999994</v>
       </c>
       <c r="K92" t="n">
-        <v>43.66845514999999</v>
+        <v>-67.59408645000001</v>
       </c>
       <c r="L92" t="n">
-        <v>-81.55704404000001</v>
+        <v>29.72607914</v>
       </c>
       <c r="M92" t="n">
-        <v>60.4838282</v>
+        <v>29.64006926</v>
       </c>
     </row>
     <row r="93">
@@ -4244,37 +4240,37 @@
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>88.50512777000002</v>
+        <v>279.11404862</v>
       </c>
       <c r="D93" t="n">
-        <v>320.60971411</v>
+        <v>394.2145801</v>
       </c>
       <c r="E93" t="n">
-        <v>443.84527893</v>
+        <v>64.72958703</v>
       </c>
       <c r="F93" t="n">
-        <v>95.96630688</v>
+        <v>190.86093327</v>
       </c>
       <c r="G93" t="n">
-        <v>151.7448347</v>
+        <v>322.22843422</v>
       </c>
       <c r="H93" t="n">
-        <v>313.97923944</v>
+        <v>181.86246472</v>
       </c>
       <c r="I93" t="n">
-        <v>104.99983746</v>
+        <v>-11.75397527</v>
       </c>
       <c r="J93" t="n">
-        <v>-28.7795355</v>
+        <v>-52.08448736</v>
       </c>
       <c r="K93" t="n">
-        <v>-96.91518439000001</v>
+        <v>11.38814737</v>
       </c>
       <c r="L93" t="n">
-        <v>-12.38750471</v>
+        <v>196.3704147</v>
       </c>
       <c r="M93" t="n">
-        <v>108.83205481</v>
+        <v>29.85532934000002</v>
       </c>
     </row>
     <row r="94">
@@ -4285,37 +4281,37 @@
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>683.4299987600001</v>
+        <v>-196.7993444</v>
       </c>
       <c r="D94" t="n">
-        <v>-196.7993444</v>
+        <v>1230.67429305</v>
       </c>
       <c r="E94" t="n">
-        <v>1230.67429305</v>
+        <v>736.97943814</v>
       </c>
       <c r="F94" t="n">
-        <v>736.97943814</v>
+        <v>980.9976145999998</v>
       </c>
       <c r="G94" t="n">
-        <v>980.9976145999998</v>
+        <v>3039.80295137</v>
       </c>
       <c r="H94" t="n">
-        <v>3039.80295137</v>
+        <v>2679.37978635</v>
       </c>
       <c r="I94" t="n">
-        <v>2679.37978635</v>
+        <v>398.0836465900001</v>
       </c>
       <c r="J94" t="n">
-        <v>398.0836465900001</v>
+        <v>4014.61282152</v>
       </c>
       <c r="K94" t="n">
-        <v>4014.61282152</v>
+        <v>1780.16211673</v>
       </c>
       <c r="L94" t="n">
-        <v>1780.16211673</v>
+        <v>2571.08829643</v>
       </c>
       <c r="M94" t="n">
-        <v>2571.08829643</v>
+        <v>3368.74259007</v>
       </c>
     </row>
     <row r="95">
@@ -4326,37 +4322,37 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>52.17459030999999</v>
+        <v>48.76066773</v>
       </c>
       <c r="D95" t="n">
-        <v>69.41372987999999</v>
+        <v>92.55334615</v>
       </c>
       <c r="E95" t="n">
-        <v>81.05502186</v>
+        <v>-56.81754067</v>
       </c>
       <c r="F95" t="n">
-        <v>-13.09397059</v>
+        <v>42.84140761</v>
       </c>
       <c r="G95" t="n">
-        <v>56.25579081</v>
+        <v>-38.50834155000001</v>
       </c>
       <c r="H95" t="n">
-        <v>19.28692427</v>
+        <v>-20.42261438</v>
       </c>
       <c r="I95" t="n">
-        <v>2.439667629999996</v>
+        <v>27.43937357999999</v>
       </c>
       <c r="J95" t="n">
-        <v>23.74875729999999</v>
+        <v>249.26542335</v>
       </c>
       <c r="K95" t="n">
-        <v>212.58224952</v>
+        <v>5.814013070000001</v>
       </c>
       <c r="L95" t="n">
-        <v>25.10754408</v>
+        <v>-67.48752768000001</v>
       </c>
       <c r="M95" t="n">
-        <v>-8.521788389999998</v>
+        <v>-298.07951644</v>
       </c>
     </row>
     <row r="96">
@@ -4367,37 +4363,37 @@
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>82.56180853999999</v>
+        <v>-24.73421494</v>
       </c>
       <c r="D96" t="n">
-        <v>-45.38727709</v>
+        <v>25.07028257</v>
       </c>
       <c r="E96" t="n">
-        <v>36.56860685999999</v>
+        <v>-158.42628785</v>
       </c>
       <c r="F96" t="n">
-        <v>-202.14985793</v>
+        <v>-241.65995044</v>
       </c>
       <c r="G96" t="n">
-        <v>-255.07433364</v>
+        <v>-46.64398937</v>
       </c>
       <c r="H96" t="n">
-        <v>-104.43925519</v>
+        <v>23.09129097</v>
       </c>
       <c r="I96" t="n">
-        <v>0.229008960000001</v>
+        <v>-53.61031266000001</v>
       </c>
       <c r="J96" t="n">
-        <v>-49.91969638000001</v>
+        <v>146.4341514</v>
       </c>
       <c r="K96" t="n">
-        <v>183.11732523</v>
+        <v>-24.65351684000001</v>
       </c>
       <c r="L96" t="n">
-        <v>-43.94704785000001</v>
+        <v>147.93520375</v>
       </c>
       <c r="M96" t="n">
-        <v>88.96946446</v>
+        <v>24.74986286</v>
       </c>
     </row>
     <row r="97">
@@ -4408,37 +4404,37 @@
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>-57.87665437</v>
+        <v>-37.07627961999999</v>
       </c>
       <c r="D97" t="n">
-        <v>-36.62885614</v>
+        <v>-30.0684443</v>
       </c>
       <c r="E97" t="n">
-        <v>-32.91272461</v>
+        <v>-26.68637467</v>
       </c>
       <c r="F97" t="n">
-        <v>-31.98487371</v>
+        <v>-23.61144785</v>
       </c>
       <c r="G97" t="n">
-        <v>-28.05827051</v>
+        <v>-20.82561255</v>
       </c>
       <c r="H97" t="n">
-        <v>-31.36616687</v>
+        <v>-15.11323943</v>
       </c>
       <c r="I97" t="n">
-        <v>-10.44515264</v>
+        <v>2.576522849999999</v>
       </c>
       <c r="J97" t="n">
-        <v>26.32759989</v>
+        <v>17.61782424</v>
       </c>
       <c r="K97" t="n">
-        <v>54.67073346</v>
+        <v>27.3651653</v>
       </c>
       <c r="L97" t="n">
-        <v>42.46099433</v>
+        <v>21.46185849</v>
       </c>
       <c r="M97" t="n">
-        <v>0.9574884200000013</v>
+        <v>2.43374669</v>
       </c>
     </row>
     <row r="98">
@@ -4447,41 +4443,39 @@
           <t>食品工業右下</t>
         </is>
       </c>
-      <c r="B98" t="n">
-        <v>0</v>
-      </c>
+      <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
-        <v>-6.83742472</v>
+        <v>-8.586387240000001</v>
       </c>
       <c r="D98" t="n">
-        <v>-8.384741280000002</v>
+        <v>-10.56307657</v>
       </c>
       <c r="E98" t="n">
-        <v>-10.39423065</v>
+        <v>-11.32923905</v>
       </c>
       <c r="F98" t="n">
-        <v>-11.35658426</v>
+        <v>2.98401102</v>
       </c>
       <c r="G98" t="n">
-        <v>2.90771855</v>
+        <v>1.30875266</v>
       </c>
       <c r="H98" t="n">
-        <v>1.30504188</v>
+        <v>-3.510710399999999</v>
       </c>
       <c r="I98" t="n">
-        <v>-3.46681689</v>
+        <v>10.10491649</v>
       </c>
       <c r="J98" t="n">
-        <v>10.1722114</v>
+        <v>13.23640147</v>
       </c>
       <c r="K98" t="n">
-        <v>13.3762424</v>
+        <v>17.26166795</v>
       </c>
       <c r="L98" t="n">
-        <v>17.45927326</v>
+        <v>6.075726189999999</v>
       </c>
       <c r="M98" t="n">
-        <v>6.2808356</v>
+        <v>-1.47041395</v>
       </c>
     </row>
     <row r="99">
@@ -4492,37 +4486,37 @@
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>-138.98959363</v>
+        <v>-186.51495697</v>
       </c>
       <c r="D99" t="n">
-        <v>-186.96238045</v>
+        <v>-265.95018013</v>
       </c>
       <c r="E99" t="n">
-        <v>-263.10589982</v>
+        <v>-277.00332726</v>
       </c>
       <c r="F99" t="n">
-        <v>-271.70482822</v>
+        <v>-161.75931291</v>
       </c>
       <c r="G99" t="n">
-        <v>-157.31249025</v>
+        <v>-234.05456839</v>
       </c>
       <c r="H99" t="n">
-        <v>-223.51401407</v>
+        <v>-116.13037273</v>
       </c>
       <c r="I99" t="n">
-        <v>-120.79845952</v>
+        <v>-28.18976328</v>
       </c>
       <c r="J99" t="n">
-        <v>-51.94084032</v>
+        <v>-51.69699644</v>
       </c>
       <c r="K99" t="n">
-        <v>-88.74990566</v>
+        <v>-94.32087193</v>
       </c>
       <c r="L99" t="n">
-        <v>-109.41670096</v>
+        <v>-157.36500734</v>
       </c>
       <c r="M99" t="n">
-        <v>-136.86063727</v>
+        <v>-218.54955489</v>
       </c>
     </row>
   </sheetData>

--- a/Result/analyze_2.xlsx
+++ b/Result/analyze_2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M99"/>
+  <dimension ref="A1:M101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-11</t>
         </is>
       </c>
     </row>
@@ -503,37 +503,37 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>66.56199049</v>
+        <v>349.94285983</v>
       </c>
       <c r="D2" t="n">
-        <v>356.56633246</v>
+        <v>-50.48565993</v>
       </c>
       <c r="E2" t="n">
-        <v>-35.06648140000001</v>
+        <v>245.94945238</v>
       </c>
       <c r="F2" t="n">
-        <v>252.61035904</v>
+        <v>594.58673208</v>
       </c>
       <c r="G2" t="n">
-        <v>605.75553287</v>
+        <v>666.80052754</v>
       </c>
       <c r="H2" t="n">
-        <v>658.30641657</v>
+        <v>970.63023904</v>
       </c>
       <c r="I2" t="n">
-        <v>947.5900919199998</v>
+        <v>1867.28884575</v>
       </c>
       <c r="J2" t="n">
-        <v>1854.05646702</v>
+        <v>1102.54176427</v>
       </c>
       <c r="K2" t="n">
-        <v>1081.37279024</v>
+        <v>160.36199751</v>
       </c>
       <c r="L2" t="n">
-        <v>129.60770167</v>
+        <v>696.2803910299999</v>
       </c>
       <c r="M2" t="n">
-        <v>631.62990461</v>
+        <v>812.99425622</v>
       </c>
     </row>
     <row r="3">
@@ -544,37 +544,37 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>147.11955259</v>
+        <v>191.87176472</v>
       </c>
       <c r="D3" t="n">
-        <v>213.90499924</v>
+        <v>84.59307114000001</v>
       </c>
       <c r="E3" t="n">
-        <v>119.41768033</v>
+        <v>147.49896984</v>
       </c>
       <c r="F3" t="n">
-        <v>182.4498646</v>
+        <v>0.2643849900000007</v>
       </c>
       <c r="G3" t="n">
-        <v>17.55563291</v>
+        <v>-20.16331824</v>
       </c>
       <c r="H3" t="n">
-        <v>-4.824857839999999</v>
+        <v>108.99614624</v>
       </c>
       <c r="I3" t="n">
-        <v>127.74288916</v>
+        <v>218.62774389</v>
       </c>
       <c r="J3" t="n">
-        <v>240.46139432</v>
+        <v>151.67850938</v>
       </c>
       <c r="K3" t="n">
-        <v>154.10382631</v>
+        <v>50.43801889</v>
       </c>
       <c r="L3" t="n">
-        <v>42.91116328</v>
+        <v>-71.88062519</v>
       </c>
       <c r="M3" t="n">
-        <v>-75.75932651000001</v>
+        <v>18.3918283</v>
       </c>
     </row>
     <row r="4">
@@ -585,37 +585,37 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>2.342279479999998</v>
+        <v>-3.510394429999991</v>
       </c>
       <c r="D4" t="n">
-        <v>-32.16710158000001</v>
+        <v>-113.87668264</v>
       </c>
       <c r="E4" t="n">
-        <v>-164.12047036</v>
+        <v>-37.69984908000001</v>
       </c>
       <c r="F4" t="n">
-        <v>-79.31165050000001</v>
+        <v>-130.76491443</v>
       </c>
       <c r="G4" t="n">
-        <v>-159.22496314</v>
+        <v>-190.54690389</v>
       </c>
       <c r="H4" t="n">
-        <v>-197.39125332</v>
+        <v>-45.83294535</v>
       </c>
       <c r="I4" t="n">
-        <v>-41.53954115</v>
+        <v>85.51833439000001</v>
       </c>
       <c r="J4" t="n">
-        <v>76.91706268999999</v>
+        <v>23.83906059999999</v>
       </c>
       <c r="K4" t="n">
-        <v>42.5827177</v>
+        <v>211.06758891</v>
       </c>
       <c r="L4" t="n">
-        <v>249.34874036</v>
+        <v>-18.50630938</v>
       </c>
       <c r="M4" t="n">
-        <v>50.02287835999999</v>
+        <v>2.863240560000006</v>
       </c>
     </row>
     <row r="5">
@@ -626,37 +626,37 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>467.8486097100001</v>
+        <v>758.27988239</v>
       </c>
       <c r="D5" t="n">
-        <v>758.27988239</v>
+        <v>802.10536136</v>
       </c>
       <c r="E5" t="n">
-        <v>802.10536136</v>
+        <v>1311.67929021</v>
       </c>
       <c r="F5" t="n">
-        <v>1311.67929021</v>
+        <v>1402.60968035</v>
       </c>
       <c r="G5" t="n">
-        <v>1402.60968035</v>
+        <v>947.1777888099999</v>
       </c>
       <c r="H5" t="n">
-        <v>947.1777888099999</v>
+        <v>633.92100185</v>
       </c>
       <c r="I5" t="n">
-        <v>633.92100185</v>
+        <v>146.03438519</v>
       </c>
       <c r="J5" t="n">
-        <v>146.03438519</v>
+        <v>-38.63471579000001</v>
       </c>
       <c r="K5" t="n">
-        <v>-38.63471579000001</v>
+        <v>-259.31947403</v>
       </c>
       <c r="L5" t="n">
-        <v>-259.31947403</v>
+        <v>-387.10504069</v>
       </c>
       <c r="M5" t="n">
-        <v>-387.10504069</v>
+        <v>-428.41081447</v>
       </c>
     </row>
     <row r="6">
@@ -667,37 +667,37 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>-15.0706052</v>
+        <v>-36.48480923</v>
       </c>
       <c r="D6" t="n">
-        <v>-36.497385</v>
+        <v>-50.54285925</v>
       </c>
       <c r="E6" t="n">
-        <v>-50.54128249</v>
+        <v>-51.16288267</v>
       </c>
       <c r="F6" t="n">
-        <v>-51.15769783</v>
+        <v>-140.95221625</v>
       </c>
       <c r="G6" t="n">
-        <v>-140.94534825</v>
+        <v>-65.33410428999998</v>
       </c>
       <c r="H6" t="n">
-        <v>-65.33151937999999</v>
+        <v>61.92312819</v>
       </c>
       <c r="I6" t="n">
-        <v>61.92808129000001</v>
+        <v>11.70978589</v>
       </c>
       <c r="J6" t="n">
-        <v>11.71021567</v>
+        <v>17.56788924</v>
       </c>
       <c r="K6" t="n">
-        <v>17.56998252</v>
+        <v>63.33664330999999</v>
       </c>
       <c r="L6" t="n">
-        <v>63.34027448999999</v>
+        <v>80.28996298999999</v>
       </c>
       <c r="M6" t="n">
-        <v>80.29391962000001</v>
+        <v>82.10961921000001</v>
       </c>
     </row>
     <row r="7">
@@ -708,37 +708,37 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>23.90388811</v>
+        <v>18.05669134</v>
       </c>
       <c r="D7" t="n">
-        <v>18.06926711</v>
+        <v>12.93458089</v>
       </c>
       <c r="E7" t="n">
-        <v>12.93300413</v>
+        <v>23.36805268</v>
       </c>
       <c r="F7" t="n">
-        <v>23.36286784</v>
+        <v>8.29219101</v>
       </c>
       <c r="G7" t="n">
-        <v>8.285323009999999</v>
+        <v>8.107017110000001</v>
       </c>
       <c r="H7" t="n">
-        <v>8.104432200000002</v>
+        <v>10.62519958</v>
       </c>
       <c r="I7" t="n">
-        <v>10.62024648</v>
+        <v>11.86739087</v>
       </c>
       <c r="J7" t="n">
-        <v>11.86696109</v>
+        <v>20.20976285</v>
       </c>
       <c r="K7" t="n">
-        <v>20.20766957</v>
+        <v>0.2861774399999976</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2825462599999979</v>
+        <v>-11.25823577</v>
       </c>
       <c r="M7" t="n">
-        <v>-11.2621924</v>
+        <v>-42.56794475</v>
       </c>
     </row>
     <row r="8">
@@ -749,37 +749,37 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>1683.83113943</v>
+        <v>1786.62327224</v>
       </c>
       <c r="D8" t="n">
-        <v>1748.64109344</v>
+        <v>266.15349545</v>
       </c>
       <c r="E8" t="n">
-        <v>215.04394201</v>
+        <v>-147.9823112199999</v>
       </c>
       <c r="F8" t="n">
-        <v>-175.58447045</v>
+        <v>1475.91380527</v>
       </c>
       <c r="G8" t="n">
-        <v>1440.98172734</v>
+        <v>2294.25615025</v>
       </c>
       <c r="H8" t="n">
-        <v>2243.00173656</v>
+        <v>1074.80943465</v>
       </c>
       <c r="I8" t="n">
-        <v>1059.05512781</v>
+        <v>1225.86441528</v>
       </c>
       <c r="J8" t="n">
-        <v>1234.59418381</v>
+        <v>1237.92462887</v>
       </c>
       <c r="K8" t="n">
-        <v>1217.90332761</v>
+        <v>3053.75359068</v>
       </c>
       <c r="L8" t="n">
-        <v>3045.29876754</v>
+        <v>3150.11538454</v>
       </c>
       <c r="M8" t="n">
-        <v>3122.67857891</v>
+        <v>3699.4158208</v>
       </c>
     </row>
     <row r="9">
@@ -788,39 +788,41 @@
           <t>其他電子業右下</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
       <c r="C9" t="n">
-        <v>23.99344998</v>
+        <v>1.00886186</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.67383328</v>
+        <v>7.754908189999999</v>
       </c>
       <c r="E9" t="n">
-        <v>5.24493221</v>
+        <v>19.5437169</v>
       </c>
       <c r="F9" t="n">
-        <v>17.46157312</v>
+        <v>-16.87157023</v>
       </c>
       <c r="G9" t="n">
-        <v>-19.11340726</v>
+        <v>39.32909103</v>
       </c>
       <c r="H9" t="n">
-        <v>37.53061692</v>
+        <v>36.6410556</v>
       </c>
       <c r="I9" t="n">
-        <v>35.45856086</v>
+        <v>39.82731007</v>
       </c>
       <c r="J9" t="n">
-        <v>39.33183526</v>
+        <v>-1.71674819</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.70690422</v>
+        <v>12.39743227</v>
       </c>
       <c r="L9" t="n">
-        <v>12.50393308</v>
+        <v>-56.67850128</v>
       </c>
       <c r="M9" t="n">
-        <v>-57.61832385</v>
+        <v>-82.45109039000002</v>
       </c>
     </row>
     <row r="10">
@@ -831,37 +833,37 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>11.40590219</v>
+        <v>-30.39800455</v>
       </c>
       <c r="D10" t="n">
-        <v>11.26137</v>
+        <v>-79.66322145000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-26.04180533</v>
+        <v>-26.56333222</v>
       </c>
       <c r="F10" t="n">
-        <v>3.156710680000001</v>
+        <v>-52.59087204000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-15.41229293</v>
+        <v>-10.33104969000001</v>
       </c>
       <c r="H10" t="n">
-        <v>42.70911246</v>
+        <v>40.56151774</v>
       </c>
       <c r="I10" t="n">
-        <v>57.47363111</v>
+        <v>84.25090496</v>
       </c>
       <c r="J10" t="n">
-        <v>76.00098144</v>
+        <v>4.334741170000002</v>
       </c>
       <c r="K10" t="n">
-        <v>25.30690511</v>
+        <v>44.87638554</v>
       </c>
       <c r="L10" t="n">
-        <v>53.20174472999999</v>
+        <v>43.68914278</v>
       </c>
       <c r="M10" t="n">
-        <v>72.04851831000001</v>
+        <v>-14.18799322</v>
       </c>
     </row>
     <row r="11">
@@ -872,37 +874,37 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>16.97882196</v>
+        <v>73.34760937999999</v>
       </c>
       <c r="D11" t="n">
-        <v>33.95849969</v>
+        <v>17.68913908</v>
       </c>
       <c r="E11" t="n">
-        <v>31.73740261</v>
+        <v>64.27134692</v>
       </c>
       <c r="F11" t="n">
-        <v>63.07150558</v>
+        <v>134.93953454</v>
       </c>
       <c r="G11" t="n">
-        <v>142.43566523</v>
+        <v>59.07640434</v>
       </c>
       <c r="H11" t="n">
-        <v>62.10685783</v>
+        <v>58.26191486</v>
       </c>
       <c r="I11" t="n">
-        <v>74.96178202999999</v>
+        <v>-1.60021218</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.548439399999999</v>
+        <v>-56.15711423999999</v>
       </c>
       <c r="K11" t="n">
-        <v>-40.94177412</v>
+        <v>-77.84830054000001</v>
       </c>
       <c r="L11" t="n">
-        <v>-70.05006009</v>
+        <v>-69.04629460000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-55.17203984</v>
+        <v>-25.69211605</v>
       </c>
     </row>
     <row r="12">
@@ -913,37 +915,37 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>65.88534808999999</v>
+        <v>35.07161981</v>
       </c>
       <c r="D12" t="n">
-        <v>39.67649825</v>
+        <v>-55.30950838</v>
       </c>
       <c r="E12" t="n">
-        <v>-59.92998233</v>
+        <v>108.46396057</v>
       </c>
       <c r="F12" t="n">
-        <v>109.62239728</v>
+        <v>-14.9723182</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.024762610000002</v>
+        <v>-75.27318078</v>
       </c>
       <c r="H12" t="n">
-        <v>-76.45363953</v>
+        <v>-101.53357454</v>
       </c>
       <c r="I12" t="n">
-        <v>-101.38021878</v>
+        <v>-80.67289115999999</v>
       </c>
       <c r="J12" t="n">
-        <v>-73.76798635999999</v>
+        <v>-48.53014978</v>
       </c>
       <c r="K12" t="n">
-        <v>-49.99167169</v>
+        <v>-62.99231673999999</v>
       </c>
       <c r="L12" t="n">
-        <v>-69.64462092999999</v>
+        <v>255.29889573</v>
       </c>
       <c r="M12" t="n">
-        <v>253.05612117</v>
+        <v>83.30783427999999</v>
       </c>
     </row>
     <row r="13">
@@ -954,37 +956,37 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>14.62224566</v>
+        <v>9.1288567</v>
       </c>
       <c r="D13" t="n">
-        <v>43.91308795</v>
+        <v>-17.38670165</v>
       </c>
       <c r="E13" t="n">
-        <v>-26.81449123</v>
+        <v>6.62313836</v>
       </c>
       <c r="F13" t="n">
-        <v>6.66454299</v>
+        <v>17.45707202</v>
       </c>
       <c r="G13" t="n">
-        <v>0.01338574000000022</v>
+        <v>-2.38915288</v>
       </c>
       <c r="H13" t="n">
-        <v>-10.66935122</v>
+        <v>61.02311267</v>
       </c>
       <c r="I13" t="n">
-        <v>46.75941797</v>
+        <v>-33.16508691</v>
       </c>
       <c r="J13" t="n">
-        <v>-29.39136021</v>
+        <v>-61.29016644</v>
       </c>
       <c r="K13" t="n">
-        <v>-78.65453039999998</v>
+        <v>36.84192846</v>
       </c>
       <c r="L13" t="n">
-        <v>38.06164016</v>
+        <v>94.80844499</v>
       </c>
       <c r="M13" t="n">
-        <v>88.24941468999999</v>
+        <v>168.00760089</v>
       </c>
     </row>
     <row r="14">
@@ -995,37 +997,37 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>-6065.20683973</v>
+        <v>-8021.18710023</v>
       </c>
       <c r="D14" t="n">
-        <v>-8193.434163939999</v>
+        <v>-11779.66299903</v>
       </c>
       <c r="E14" t="n">
-        <v>-11812.81124464</v>
+        <v>-5670.27156687</v>
       </c>
       <c r="F14" t="n">
-        <v>-5566.08010312</v>
+        <v>-624.0224289900003</v>
       </c>
       <c r="G14" t="n">
-        <v>-696.3512316900003</v>
+        <v>-4448.64816188</v>
       </c>
       <c r="H14" t="n">
-        <v>-4038.89355937</v>
+        <v>-6496.484548560001</v>
       </c>
       <c r="I14" t="n">
-        <v>-6004.50905662</v>
+        <v>-1624.94800481</v>
       </c>
       <c r="J14" t="n">
-        <v>-1135.96927128</v>
+        <v>-4347.44692024</v>
       </c>
       <c r="K14" t="n">
-        <v>-3923.88527044</v>
+        <v>5116.89556286</v>
       </c>
       <c r="L14" t="n">
-        <v>5232.32995332</v>
+        <v>1770.36109075</v>
       </c>
       <c r="M14" t="n">
-        <v>1633.12764074</v>
+        <v>7381.87680709</v>
       </c>
     </row>
     <row r="15">
@@ -1038,37 +1040,37 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>412.85528441</v>
+        <v>415.55163195</v>
       </c>
       <c r="D15" t="n">
-        <v>367.89360698</v>
+        <v>-54.42527297000004</v>
       </c>
       <c r="E15" t="n">
-        <v>-67.84231548000004</v>
+        <v>-6.453203729999995</v>
       </c>
       <c r="F15" t="n">
-        <v>-12.82006498999999</v>
+        <v>-673.9294293300001</v>
       </c>
       <c r="G15" t="n">
-        <v>-667.61270948</v>
+        <v>-224.13764096</v>
       </c>
       <c r="H15" t="n">
-        <v>-216.5034258</v>
+        <v>-180.72158482</v>
       </c>
       <c r="I15" t="n">
-        <v>-134.11423201</v>
+        <v>521.20736035</v>
       </c>
       <c r="J15" t="n">
-        <v>591.92068205</v>
+        <v>-99.65401256000001</v>
       </c>
       <c r="K15" t="n">
-        <v>-55.01668249000003</v>
+        <v>-336.46048777</v>
       </c>
       <c r="L15" t="n">
-        <v>-311.90614392</v>
+        <v>290.82002466</v>
       </c>
       <c r="M15" t="n">
-        <v>267.33807119</v>
+        <v>-151.79652597</v>
       </c>
     </row>
     <row r="16">
@@ -1079,37 +1081,37 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>1.484374490000025</v>
+        <v>-9.631972939999994</v>
       </c>
       <c r="D16" t="n">
-        <v>170.44589032</v>
+        <v>301.10038523</v>
       </c>
       <c r="E16" t="n">
-        <v>335.24553992</v>
+        <v>-273.31100431</v>
       </c>
       <c r="F16" t="n">
-        <v>-383.17638882</v>
+        <v>-127.25782837</v>
       </c>
       <c r="G16" t="n">
-        <v>-53.77780810999995</v>
+        <v>251.95209464</v>
       </c>
       <c r="H16" t="n">
-        <v>-160.89663637</v>
+        <v>-160.16176203</v>
       </c>
       <c r="I16" t="n">
-        <v>-687.9945551600001</v>
+        <v>-95.13206553000003</v>
       </c>
       <c r="J16" t="n">
-        <v>-638.59429387</v>
+        <v>-496.80833901</v>
       </c>
       <c r="K16" t="n">
-        <v>-966.1564845700001</v>
+        <v>-125.36432627</v>
       </c>
       <c r="L16" t="n">
-        <v>-254.25417468</v>
+        <v>-398.24590544</v>
       </c>
       <c r="M16" t="n">
-        <v>-247.29899022</v>
+        <v>-405.94523872</v>
       </c>
     </row>
     <row r="17">
@@ -1120,37 +1122,37 @@
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
-        <v>0.55657781</v>
+        <v>-0.10265735</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5684159599999999</v>
+        <v>-0.09269372000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6202892800000001</v>
+        <v>-0.03467238</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7926845100000001</v>
+        <v>-0.04065686</v>
       </c>
       <c r="G17" t="n">
-        <v>1.35238512</v>
+        <v>0.0011402</v>
       </c>
       <c r="H17" t="n">
-        <v>2.728392</v>
+        <v>0.03352323</v>
       </c>
       <c r="I17" t="n">
-        <v>0.88005688</v>
+        <v>0.00050968</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9546220400000001</v>
+        <v>-0.01056853</v>
       </c>
       <c r="K17" t="n">
-        <v>0.84933839</v>
+        <v>0.00352167</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.12916396</v>
+        <v>0.01775949</v>
       </c>
       <c r="M17" t="n">
-        <v>0.18337836</v>
+        <v>0.0402896</v>
       </c>
     </row>
     <row r="18">
@@ -1161,37 +1163,37 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>283.6058508000001</v>
+        <v>797.0432088700001</v>
       </c>
       <c r="D18" t="n">
-        <v>797.0432088700001</v>
+        <v>-142.28295233</v>
       </c>
       <c r="E18" t="n">
-        <v>-142.28295233</v>
+        <v>949.17323245</v>
       </c>
       <c r="F18" t="n">
-        <v>949.17323245</v>
+        <v>786.6830428600001</v>
       </c>
       <c r="G18" t="n">
-        <v>786.6830428600001</v>
+        <v>-272.85884179</v>
       </c>
       <c r="H18" t="n">
-        <v>-272.85884179</v>
+        <v>-871.1229194199999</v>
       </c>
       <c r="I18" t="n">
-        <v>-871.1229194199999</v>
+        <v>-1069.81135742</v>
       </c>
       <c r="J18" t="n">
-        <v>-1069.81135742</v>
+        <v>-452.58295967</v>
       </c>
       <c r="K18" t="n">
-        <v>-452.58295967</v>
+        <v>-531.6617434799999</v>
       </c>
       <c r="L18" t="n">
-        <v>-531.6617434799999</v>
+        <v>-603.5171211700001</v>
       </c>
       <c r="M18" t="n">
-        <v>-603.5171211700001</v>
+        <v>-1.170012629999998</v>
       </c>
     </row>
     <row r="19">
@@ -1202,37 +1204,37 @@
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>-11.46146303</v>
+        <v>-3.98792682</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.65900013</v>
+        <v>-8.90454609</v>
       </c>
       <c r="E19" t="n">
-        <v>-9.61752909</v>
+        <v>-2.35624874</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.18360563</v>
+        <v>-4.667060340000001</v>
       </c>
       <c r="G19" t="n">
-        <v>-6.06010232</v>
+        <v>-3.87635555</v>
       </c>
       <c r="H19" t="n">
-        <v>-6.603607350000001</v>
+        <v>-1.02180052</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.86833417</v>
+        <v>-2.53850894</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.4926213</v>
+        <v>0.4005523000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.45935462</v>
+        <v>-5.227267410000001</v>
       </c>
       <c r="L19" t="n">
-        <v>-5.09458178</v>
+        <v>-15.88088372</v>
       </c>
       <c r="M19" t="n">
-        <v>-16.04650259</v>
+        <v>-17.52423777</v>
       </c>
     </row>
     <row r="20">
@@ -1243,37 +1245,37 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>46.16474276</v>
+        <v>49.79108182</v>
       </c>
       <c r="D20" t="n">
-        <v>49.79108182</v>
+        <v>15.83999259</v>
       </c>
       <c r="E20" t="n">
-        <v>15.83999259</v>
+        <v>43.34600284999999</v>
       </c>
       <c r="F20" t="n">
-        <v>43.34600284999999</v>
+        <v>-20.57369556</v>
       </c>
       <c r="G20" t="n">
-        <v>-20.57369556</v>
+        <v>-26.64337471</v>
       </c>
       <c r="H20" t="n">
-        <v>-26.64337471</v>
+        <v>-8.6719104</v>
       </c>
       <c r="I20" t="n">
-        <v>-8.6719104</v>
+        <v>6.29112816</v>
       </c>
       <c r="J20" t="n">
-        <v>6.29112816</v>
+        <v>-11.38791094</v>
       </c>
       <c r="K20" t="n">
-        <v>-11.38791094</v>
+        <v>39.90390299</v>
       </c>
       <c r="L20" t="n">
-        <v>39.90390299</v>
+        <v>-7.499015480000001</v>
       </c>
       <c r="M20" t="n">
-        <v>-7.499015480000001</v>
+        <v>-34.65196079</v>
       </c>
     </row>
     <row r="21">
@@ -1284,37 +1286,37 @@
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
-        <v>-1.29708368</v>
+        <v>0.47642728</v>
       </c>
       <c r="D21" t="n">
-        <v>0.52764575</v>
+        <v>-1.38489539</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.34250415</v>
+        <v>1.01578957</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7141913200000001</v>
+        <v>-0.08695448000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>0.11302341</v>
+        <v>1.98383284</v>
       </c>
       <c r="H21" t="n">
-        <v>1.4265115</v>
+        <v>2.625483</v>
       </c>
       <c r="I21" t="n">
-        <v>2.43182651</v>
+        <v>2.3940447</v>
       </c>
       <c r="J21" t="n">
-        <v>1.74384779</v>
+        <v>2.61609992</v>
       </c>
       <c r="K21" t="n">
-        <v>1.74690904</v>
+        <v>1.28616441</v>
       </c>
       <c r="L21" t="n">
-        <v>1.07925432</v>
+        <v>-2.43946403</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.11525328</v>
+        <v>-7.15914957</v>
       </c>
     </row>
     <row r="22">
@@ -1325,37 +1327,37 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>0.55614465</v>
+        <v>0.4000347</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3488162300000001</v>
+        <v>-0.11080264</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.15319388</v>
+        <v>0.11370021</v>
       </c>
       <c r="F22" t="n">
-        <v>0.41529846</v>
+        <v>0.08731186000000006</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.11266603</v>
+        <v>1.53302582</v>
       </c>
       <c r="H22" t="n">
-        <v>2.09034716</v>
+        <v>2.46990344</v>
       </c>
       <c r="I22" t="n">
-        <v>2.66355993</v>
+        <v>1.61393472</v>
       </c>
       <c r="J22" t="n">
-        <v>2.26413163</v>
+        <v>1.84202241</v>
       </c>
       <c r="K22" t="n">
-        <v>2.71121329</v>
+        <v>2.06787124</v>
       </c>
       <c r="L22" t="n">
-        <v>2.27478133</v>
+        <v>2.13334684</v>
       </c>
       <c r="M22" t="n">
-        <v>3.80913609</v>
+        <v>0.9929304</v>
       </c>
     </row>
     <row r="23">
@@ -1366,37 +1368,37 @@
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
-        <v>19.8188676</v>
+        <v>11.84440164</v>
       </c>
       <c r="D23" t="n">
-        <v>12.32503369</v>
+        <v>-23.12302004</v>
       </c>
       <c r="E23" t="n">
-        <v>-22.42774658</v>
+        <v>-0.9094807799999995</v>
       </c>
       <c r="F23" t="n">
-        <v>0.02885995000000046</v>
+        <v>0.5220866800000026</v>
       </c>
       <c r="G23" t="n">
-        <v>1.897171200000003</v>
+        <v>-11.60290924</v>
       </c>
       <c r="H23" t="n">
-        <v>-10.39387457</v>
+        <v>24.20836844</v>
       </c>
       <c r="I23" t="n">
-        <v>25.32103064</v>
+        <v>28.28368726</v>
       </c>
       <c r="J23" t="n">
-        <v>28.17905898</v>
+        <v>11.25997404</v>
       </c>
       <c r="K23" t="n">
-        <v>10.22546174</v>
+        <v>2.312601040000001</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.04797202999999901</v>
+        <v>7.41955448</v>
       </c>
       <c r="M23" t="n">
-        <v>3.962863350000001</v>
+        <v>26.59317097</v>
       </c>
     </row>
     <row r="24">
@@ -1407,37 +1409,37 @@
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
-        <v>-75.38246376000001</v>
+        <v>-93.28730779</v>
       </c>
       <c r="D24" t="n">
-        <v>-91.82564342000001</v>
+        <v>-105.4288386</v>
       </c>
       <c r="E24" t="n">
-        <v>-99.50884896000001</v>
+        <v>-77.88456595000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-75.71592917</v>
+        <v>-65.37887472</v>
       </c>
       <c r="G24" t="n">
-        <v>-60.80458005000001</v>
+        <v>-4.07799874</v>
       </c>
       <c r="H24" t="n">
-        <v>-4.086764929999999</v>
+        <v>63.41788019</v>
       </c>
       <c r="I24" t="n">
-        <v>59.37612749</v>
+        <v>27.87193822</v>
       </c>
       <c r="J24" t="n">
-        <v>28.97021335</v>
+        <v>17.49109479</v>
       </c>
       <c r="K24" t="n">
-        <v>21.71168018000001</v>
+        <v>-11.95157945</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.889574799999997</v>
+        <v>-30.21774896000001</v>
       </c>
       <c r="M24" t="n">
-        <v>-20.01266644</v>
+        <v>-29.35515905</v>
       </c>
     </row>
     <row r="25">
@@ -1448,37 +1450,37 @@
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>-25.95945987</v>
+        <v>-58.36615088</v>
       </c>
       <c r="D25" t="n">
-        <v>-60.3084473</v>
+        <v>-93.99017655</v>
       </c>
       <c r="E25" t="n">
-        <v>-100.60543965</v>
+        <v>-62.81385015</v>
       </c>
       <c r="F25" t="n">
-        <v>-65.92082766</v>
+        <v>-85.01579866</v>
       </c>
       <c r="G25" t="n">
-        <v>-90.96517784999999</v>
+        <v>-5.922229410000001</v>
       </c>
       <c r="H25" t="n">
-        <v>-7.12249789</v>
+        <v>88.69801799</v>
       </c>
       <c r="I25" t="n">
-        <v>91.62710849</v>
+        <v>20.90464515</v>
       </c>
       <c r="J25" t="n">
-        <v>19.9109983</v>
+        <v>42.04937090999999</v>
       </c>
       <c r="K25" t="n">
-        <v>38.86329782</v>
+        <v>33.95226985</v>
       </c>
       <c r="L25" t="n">
-        <v>28.25083827</v>
+        <v>3.511715520000001</v>
       </c>
       <c r="M25" t="n">
-        <v>-3.23667587</v>
+        <v>-6.496830300000003</v>
       </c>
     </row>
     <row r="26">
@@ -1489,37 +1491,37 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>30.24814522</v>
+        <v>-5.3701208</v>
       </c>
       <c r="D26" t="n">
-        <v>26.76396136</v>
+        <v>-4.58681387</v>
       </c>
       <c r="E26" t="n">
-        <v>-16.35696898</v>
+        <v>-0.07064465</v>
       </c>
       <c r="F26" t="n">
-        <v>-11.57917922</v>
+        <v>-0.4004080399999999</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.76419575</v>
+        <v>7.61994909</v>
       </c>
       <c r="H26" t="n">
-        <v>20.13668719</v>
+        <v>3.95032609</v>
       </c>
       <c r="I26" t="n">
-        <v>-15.72170868</v>
+        <v>8.953404039999999</v>
       </c>
       <c r="J26" t="n">
-        <v>12.89942112</v>
+        <v>5.887683269999999</v>
       </c>
       <c r="K26" t="n">
-        <v>-21.76483932</v>
+        <v>7.59334499</v>
       </c>
       <c r="L26" t="n">
-        <v>-40.04336831</v>
+        <v>5.17034791</v>
       </c>
       <c r="M26" t="n">
-        <v>-74.61596999</v>
+        <v>7.59349848</v>
       </c>
     </row>
     <row r="27">
@@ -1530,37 +1532,37 @@
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>12.3732266</v>
+        <v>16.88570324</v>
       </c>
       <c r="D27" t="n">
-        <v>16.88570324</v>
+        <v>5.174999509999999</v>
       </c>
       <c r="E27" t="n">
-        <v>5.174999509999999</v>
+        <v>10.18965648</v>
       </c>
       <c r="F27" t="n">
-        <v>10.18965648</v>
+        <v>5.14904886</v>
       </c>
       <c r="G27" t="n">
-        <v>5.14904886</v>
+        <v>12.32428043</v>
       </c>
       <c r="H27" t="n">
-        <v>12.32428043</v>
+        <v>7.23473412</v>
       </c>
       <c r="I27" t="n">
-        <v>7.23473412</v>
+        <v>21.39711191</v>
       </c>
       <c r="J27" t="n">
-        <v>21.39711191</v>
+        <v>9.234505710000002</v>
       </c>
       <c r="K27" t="n">
-        <v>9.234505710000002</v>
+        <v>20.87369368</v>
       </c>
       <c r="L27" t="n">
-        <v>20.87369368</v>
+        <v>17.72328894</v>
       </c>
       <c r="M27" t="n">
-        <v>17.72328894</v>
+        <v>22.18730068</v>
       </c>
     </row>
     <row r="28">
@@ -1571,37 +1573,37 @@
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>-0.00324458</v>
+        <v>32.12748586</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.006596299999999999</v>
+        <v>-11.78422149</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.01406638</v>
+        <v>-11.50201346</v>
       </c>
       <c r="F28" t="n">
-        <v>0.00652111</v>
+        <v>-0.33464757</v>
       </c>
       <c r="G28" t="n">
-        <v>0.02914014</v>
+        <v>12.56553617</v>
       </c>
       <c r="H28" t="n">
-        <v>0.04879807</v>
+        <v>-19.61540847</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0566263</v>
+        <v>3.97066807</v>
       </c>
       <c r="J28" t="n">
-        <v>0.02465099</v>
+        <v>-27.65380515</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.00128256</v>
+        <v>-47.65410966</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.01739636</v>
+        <v>-79.80640058</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.02008268</v>
+        <v>-109.71341936</v>
       </c>
     </row>
     <row r="29">
@@ -1612,37 +1614,37 @@
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>-0.00056724</v>
+        <v>0.00672136</v>
       </c>
       <c r="D29" t="n">
-        <v>0.00672136</v>
+        <v>-0.00145954</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.00145954</v>
+        <v>0.006492230000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>0.006492230000000001</v>
+        <v>0.01229479</v>
       </c>
       <c r="G29" t="n">
-        <v>0.01229479</v>
+        <v>0.01976942</v>
       </c>
       <c r="H29" t="n">
-        <v>0.01976942</v>
+        <v>0.0273315</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0273315</v>
+        <v>0.08224571999999999</v>
       </c>
       <c r="J29" t="n">
-        <v>0.08224571999999999</v>
+        <v>0.0739363</v>
       </c>
       <c r="K29" t="n">
-        <v>0.0739363</v>
+        <v>0.03168009</v>
       </c>
       <c r="L29" t="n">
-        <v>0.03168009</v>
+        <v>0.00634259</v>
       </c>
       <c r="M29" t="n">
-        <v>0.00634259</v>
+        <v>0.01295552</v>
       </c>
     </row>
     <row r="30">
@@ -1653,37 +1655,37 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>0.00442858</v>
+        <v>-0.0001607799999999998</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.0001344399999999998</v>
+        <v>-0.00308211</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.00311901</v>
+        <v>-0.00131417</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.00135107</v>
+        <v>-0.00648989</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.00645304</v>
+        <v>-0.0008686499999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.0007993899999999999</v>
+        <v>0.008181880000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>0.008251139999999999</v>
+        <v>0.009350769999999998</v>
       </c>
       <c r="J30" t="n">
-        <v>0.009377439999999999</v>
+        <v>0.00520684</v>
       </c>
       <c r="K30" t="n">
-        <v>0.00523351</v>
+        <v>0.01144411</v>
       </c>
       <c r="L30" t="n">
-        <v>0.01145842</v>
+        <v>-0.00111543</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.00107374</v>
+        <v>-0.005250739999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1694,201 +1696,201 @@
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>0.04320168</v>
+        <v>0.009044409999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>0.00901807</v>
+        <v>-0.04705815</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.04702125</v>
+        <v>-0.07371014999999999</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.07367325</v>
+        <v>0.03204509000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>0.03200824</v>
+        <v>0.00040864</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0003393799999999999</v>
+        <v>0.10043224</v>
       </c>
       <c r="I31" t="n">
-        <v>0.10036298</v>
+        <v>0.22034009</v>
       </c>
       <c r="J31" t="n">
-        <v>0.22031342</v>
+        <v>0.11067376</v>
       </c>
       <c r="K31" t="n">
-        <v>0.11064709</v>
+        <v>0.04146048</v>
       </c>
       <c r="L31" t="n">
-        <v>0.04144617</v>
+        <v>-0.009884979999999998</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.009926669999999999</v>
+        <v>-0.05246441</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>橡膠工業右上</t>
+          <t>橡膠工業右下</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>0.26859018</v>
+        <v>47.13405325</v>
       </c>
       <c r="D32" t="n">
-        <v>-1.1550498</v>
+        <v>17.62821512</v>
       </c>
       <c r="E32" t="n">
-        <v>0.19597777</v>
+        <v>9.357429240000002</v>
       </c>
       <c r="F32" t="n">
-        <v>0.93832401</v>
+        <v>-23.28926443</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.60581137</v>
+        <v>-15.50397747</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.18124846</v>
+        <v>-7.671519279999999</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6026511899999999</v>
+        <v>-12.56496135</v>
       </c>
       <c r="J32" t="n">
-        <v>2.12415212</v>
+        <v>0.4845926899999997</v>
       </c>
       <c r="K32" t="n">
-        <v>3.00018044</v>
+        <v>-20.67803373</v>
       </c>
       <c r="L32" t="n">
-        <v>0.8008101</v>
+        <v>-32.15445803</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.41351514</v>
+        <v>-40.28821612</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>橡膠工業右下</t>
+          <t>橡膠工業平</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
-        <v>28.77819571</v>
+        <v>-0.48816578</v>
       </c>
       <c r="D33" t="n">
-        <v>47.13405325</v>
+        <v>0.5905294200000001</v>
       </c>
       <c r="E33" t="n">
-        <v>17.62821512</v>
+        <v>1.69994562</v>
       </c>
       <c r="F33" t="n">
-        <v>9.357429240000002</v>
+        <v>0.07589649999999996</v>
       </c>
       <c r="G33" t="n">
-        <v>-23.28926443</v>
+        <v>-0.14939967</v>
       </c>
       <c r="H33" t="n">
-        <v>-14.93848151</v>
+        <v>0.5503706399999999</v>
       </c>
       <c r="I33" t="n">
-        <v>-7.90298542</v>
+        <v>1.89812459</v>
       </c>
       <c r="J33" t="n">
-        <v>-12.45719128</v>
+        <v>2.92653785</v>
       </c>
       <c r="K33" t="n">
-        <v>0.01885810999999962</v>
+        <v>0.4812992</v>
       </c>
       <c r="L33" t="n">
-        <v>-20.58713198</v>
+        <v>-1.10311971</v>
       </c>
       <c r="M33" t="n">
-        <v>-31.56361012</v>
+        <v>-3.2016798</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>橡膠工業平</t>
+          <t>水泥工業右下</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
-        <v>0.5322796400000001</v>
+        <v>180.37309538</v>
       </c>
       <c r="D34" t="n">
-        <v>0.66688402</v>
+        <v>110.85613396</v>
       </c>
       <c r="E34" t="n">
-        <v>0.39455165</v>
+        <v>152.60252483</v>
       </c>
       <c r="F34" t="n">
-        <v>0.7616216099999999</v>
+        <v>75.68712063</v>
       </c>
       <c r="G34" t="n">
-        <v>0.68170787</v>
+        <v>33.27450068</v>
       </c>
       <c r="H34" t="n">
-        <v>0.03184879000000001</v>
+        <v>20.78368849</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.05228055</v>
+        <v>33.21580698</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.22602753</v>
+        <v>52.12681979</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.07364258999999999</v>
+        <v>22.38281906</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.3195109</v>
+        <v>33.51679171</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.68960457</v>
+        <v>42.04676762</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>水泥工業右下</t>
+          <t>水泥工業平</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
-        <v>151.94936306</v>
+        <v>0.00043182</v>
       </c>
       <c r="D35" t="n">
-        <v>180.3735272</v>
+        <v>-0.14237872</v>
       </c>
       <c r="E35" t="n">
-        <v>110.71375524</v>
+        <v>0.05044382</v>
       </c>
       <c r="F35" t="n">
-        <v>152.65296865</v>
+        <v>-0.09362012</v>
       </c>
       <c r="G35" t="n">
-        <v>75.59350051</v>
+        <v>-0.09928682000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>33.17521386</v>
+        <v>0.04687088</v>
       </c>
       <c r="I35" t="n">
-        <v>20.83055937</v>
+        <v>0.28043062</v>
       </c>
       <c r="J35" t="n">
-        <v>33.4962376</v>
+        <v>0.01792718</v>
       </c>
       <c r="K35" t="n">
-        <v>52.14474697</v>
+        <v>-0.03893316</v>
       </c>
       <c r="L35" t="n">
-        <v>22.3438859</v>
+        <v>-0.04556105000000001</v>
       </c>
       <c r="M35" t="n">
-        <v>33.47123066</v>
+        <v>0.30602701</v>
       </c>
     </row>
     <row r="36">
@@ -1899,37 +1901,37 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>-17.63893328</v>
+        <v>-28.53262185</v>
       </c>
       <c r="D36" t="n">
-        <v>-28.45550326999999</v>
+        <v>-22.32423203</v>
       </c>
       <c r="E36" t="n">
-        <v>-21.30608457</v>
+        <v>-19.84310048</v>
       </c>
       <c r="F36" t="n">
-        <v>-20.60556336</v>
+        <v>-4.70504814</v>
       </c>
       <c r="G36" t="n">
-        <v>-2.79298842</v>
+        <v>40.16238359</v>
       </c>
       <c r="H36" t="n">
-        <v>40.76014224</v>
+        <v>84.05469214</v>
       </c>
       <c r="I36" t="n">
-        <v>83.70217395</v>
+        <v>168.24925684</v>
       </c>
       <c r="J36" t="n">
-        <v>167.07701217</v>
+        <v>236.89254524</v>
       </c>
       <c r="K36" t="n">
-        <v>234.36025707</v>
+        <v>117.94625767</v>
       </c>
       <c r="L36" t="n">
-        <v>118.93610006</v>
+        <v>217.93889327</v>
       </c>
       <c r="M36" t="n">
-        <v>217.86082071</v>
+        <v>352.4427523</v>
       </c>
     </row>
     <row r="37">
@@ -1940,37 +1942,37 @@
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>57.69521552</v>
+        <v>58.97214983</v>
       </c>
       <c r="D37" t="n">
-        <v>57.34065769</v>
+        <v>31.34869749</v>
       </c>
       <c r="E37" t="n">
-        <v>28.76092641</v>
+        <v>67.82618828999999</v>
       </c>
       <c r="F37" t="n">
-        <v>66.83402647999999</v>
+        <v>-5.291141719999999</v>
       </c>
       <c r="G37" t="n">
-        <v>-8.809809789999999</v>
+        <v>-1.55991917</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.514865390000001</v>
+        <v>18.38462999</v>
       </c>
       <c r="I37" t="n">
-        <v>18.38879085</v>
+        <v>37.21148715</v>
       </c>
       <c r="J37" t="n">
-        <v>37.15833097</v>
+        <v>41.54908926</v>
       </c>
       <c r="K37" t="n">
-        <v>41.52823503</v>
+        <v>46.78805196</v>
       </c>
       <c r="L37" t="n">
-        <v>46.73594826000001</v>
+        <v>5.0257426</v>
       </c>
       <c r="M37" t="n">
-        <v>4.982251610000001</v>
+        <v>6.859546159999998</v>
       </c>
     </row>
     <row r="38">
@@ -1981,2542 +1983,2626 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>-15.43901849999999</v>
+        <v>-65.24241149000001</v>
       </c>
       <c r="D38" t="n">
-        <v>-63.68803793000001</v>
+        <v>-110.10124268</v>
       </c>
       <c r="E38" t="n">
-        <v>-108.53161906</v>
+        <v>-13.91325678</v>
       </c>
       <c r="F38" t="n">
-        <v>-12.15863209</v>
+        <v>-34.16824592</v>
       </c>
       <c r="G38" t="n">
-        <v>-32.56163757</v>
+        <v>-41.23378873999999</v>
       </c>
       <c r="H38" t="n">
-        <v>-43.82565295</v>
+        <v>0.5211704800000023</v>
       </c>
       <c r="I38" t="n">
-        <v>-5.797227319999999</v>
+        <v>68.31632182999999</v>
       </c>
       <c r="J38" t="n">
-        <v>59.82878755999999</v>
+        <v>27.73419485000001</v>
       </c>
       <c r="K38" t="n">
-        <v>27.71253198</v>
+        <v>-34.98197725</v>
       </c>
       <c r="L38" t="n">
-        <v>-33.6543528</v>
+        <v>-54.9151605</v>
       </c>
       <c r="M38" t="n">
-        <v>-34.99574105</v>
+        <v>-5.680847629999999</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業右下</t>
+          <t>油電燃氣業右上</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
-        <v>17.90640587</v>
+        <v>-6.3569939</v>
       </c>
       <c r="D39" t="n">
-        <v>33.64427106</v>
+        <v>-3.72633246</v>
       </c>
       <c r="E39" t="n">
-        <v>4.060433199999999</v>
+        <v>1.60522561</v>
       </c>
       <c r="F39" t="n">
-        <v>73.36151039000001</v>
+        <v>-2.38145906</v>
       </c>
       <c r="G39" t="n">
-        <v>168.31023809</v>
+        <v>-1.22895808</v>
       </c>
       <c r="H39" t="n">
-        <v>54.66244463</v>
+        <v>2.09904764</v>
       </c>
       <c r="I39" t="n">
-        <v>-39.94501549</v>
+        <v>3.22631047</v>
       </c>
       <c r="J39" t="n">
-        <v>-65.26585011</v>
+        <v>8.135896049999999</v>
       </c>
       <c r="K39" t="n">
-        <v>-32.772473</v>
+        <v>0.42597227</v>
       </c>
       <c r="L39" t="n">
-        <v>-17.85393562</v>
+        <v>5.236759269999999</v>
       </c>
       <c r="M39" t="n">
-        <v>-34.21927984000001</v>
+        <v>24.80576117</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業平</t>
+          <t>油電燃氣業右下</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>-3.17489022</v>
+        <v>33.64417675</v>
       </c>
       <c r="D40" t="n">
-        <v>-6.35707236</v>
+        <v>4.060389399999999</v>
       </c>
       <c r="E40" t="n">
-        <v>-3.72568645</v>
+        <v>73.36149224</v>
       </c>
       <c r="F40" t="n">
-        <v>1.60553159</v>
+        <v>168.3102298</v>
       </c>
       <c r="G40" t="n">
-        <v>-2.38117539</v>
+        <v>54.66236087999999</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.2286942</v>
+        <v>-39.94506282000001</v>
       </c>
       <c r="I40" t="n">
-        <v>2.09913215</v>
+        <v>-65.26597674</v>
       </c>
       <c r="J40" t="n">
-        <v>3.22640501</v>
+        <v>-32.77254173</v>
       </c>
       <c r="K40" t="n">
-        <v>8.13575142</v>
+        <v>-17.85398609</v>
       </c>
       <c r="L40" t="n">
-        <v>0.42589836</v>
+        <v>-34.21927367</v>
       </c>
       <c r="M40" t="n">
-        <v>5.236739259999999</v>
+        <v>-18.29835111</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右上</t>
+          <t>油電燃氣業平</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
-        <v>433.81361385</v>
+        <v>1.585000000000001e-05</v>
       </c>
       <c r="D41" t="n">
-        <v>668.62466564</v>
+        <v>0.0006898099999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>244.91801602</v>
+        <v>0.00032413</v>
       </c>
       <c r="F41" t="n">
-        <v>320.90370974</v>
+        <v>0.00029196</v>
       </c>
       <c r="G41" t="n">
-        <v>479.18507195</v>
+        <v>0.00034763</v>
       </c>
       <c r="H41" t="n">
-        <v>759.412483</v>
+        <v>0.00013184</v>
       </c>
       <c r="I41" t="n">
-        <v>264.18557726</v>
+        <v>0.00022117</v>
       </c>
       <c r="J41" t="n">
-        <v>-87.18150326999999</v>
+        <v>-7.589999999999999e-05</v>
       </c>
       <c r="K41" t="n">
-        <v>-42.95356518</v>
+        <v>-2.344e-05</v>
       </c>
       <c r="L41" t="n">
-        <v>-209.92976809</v>
+        <v>-2.618e-05</v>
       </c>
       <c r="M41" t="n">
-        <v>-24.7706204</v>
+        <v>7.396e-05</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷平</t>
+          <t>玻璃陶瓷右上</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>7.9181412</v>
+        <v>668.62466564</v>
       </c>
       <c r="D42" t="n">
-        <v>12.13364822</v>
+        <v>244.91801602</v>
       </c>
       <c r="E42" t="n">
-        <v>8.904139349999999</v>
+        <v>320.90370974</v>
       </c>
       <c r="F42" t="n">
-        <v>16.35974226</v>
+        <v>479.18507195</v>
       </c>
       <c r="G42" t="n">
-        <v>7.98138634</v>
+        <v>759.412483</v>
       </c>
       <c r="H42" t="n">
-        <v>10.480544</v>
+        <v>264.18557726</v>
       </c>
       <c r="I42" t="n">
-        <v>7.58023094</v>
+        <v>-87.18150326999999</v>
       </c>
       <c r="J42" t="n">
-        <v>19.71741358</v>
+        <v>-42.95356518</v>
       </c>
       <c r="K42" t="n">
-        <v>19.39813214</v>
+        <v>-209.92976809</v>
       </c>
       <c r="L42" t="n">
-        <v>6.97201257</v>
+        <v>-24.7706204</v>
       </c>
       <c r="M42" t="n">
-        <v>-1.71694579</v>
+        <v>154.56242497</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右上</t>
+          <t>玻璃陶瓷右下</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
-        <v>-2.13891016</v>
+        <v>0.38604138</v>
       </c>
       <c r="D43" t="n">
-        <v>-1.4135303</v>
+        <v>0.7518413900000001</v>
       </c>
       <c r="E43" t="n">
-        <v>-10.11111371</v>
+        <v>0.53861171</v>
       </c>
       <c r="F43" t="n">
-        <v>3.275589520000001</v>
+        <v>-0.02875878</v>
       </c>
       <c r="G43" t="n">
-        <v>17.67968448</v>
+        <v>0.35239102</v>
       </c>
       <c r="H43" t="n">
-        <v>12.9045686</v>
+        <v>0.02480043</v>
       </c>
       <c r="I43" t="n">
-        <v>16.89937039</v>
+        <v>0.14843928</v>
       </c>
       <c r="J43" t="n">
-        <v>14.53633061</v>
+        <v>0.2334175</v>
       </c>
       <c r="K43" t="n">
-        <v>16.77966055</v>
+        <v>0.05061566000000001</v>
       </c>
       <c r="L43" t="n">
-        <v>5.133885120000004</v>
+        <v>8.911000000000001e-05</v>
       </c>
       <c r="M43" t="n">
-        <v>11.00030594</v>
+        <v>-0.46469736</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右下</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>0</v>
-      </c>
+          <t>玻璃陶瓷平</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>267.91659222</v>
+        <v>11.74760684</v>
       </c>
       <c r="D44" t="n">
-        <v>-28.46628853</v>
+        <v>8.15229796</v>
       </c>
       <c r="E44" t="n">
-        <v>-233.05138489</v>
+        <v>15.82113055</v>
       </c>
       <c r="F44" t="n">
-        <v>-348.2472195999999</v>
+        <v>8.010145120000001</v>
       </c>
       <c r="G44" t="n">
-        <v>-325.33434396</v>
+        <v>11.11999477</v>
       </c>
       <c r="H44" t="n">
-        <v>-310.85803781</v>
+        <v>7.08814818</v>
       </c>
       <c r="I44" t="n">
-        <v>-66.5272892</v>
+        <v>19.74312415</v>
       </c>
       <c r="J44" t="n">
-        <v>7.323684740000009</v>
+        <v>18.21954681</v>
       </c>
       <c r="K44" t="n">
-        <v>30.19368088000001</v>
+        <v>4.989099479999999</v>
       </c>
       <c r="L44" t="n">
-        <v>116.40958469</v>
+        <v>-4.016226140000001</v>
       </c>
       <c r="M44" t="n">
-        <v>258.70540645</v>
+        <v>-0.05892154000000004</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業平</t>
+          <t>生技醫療業右上</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
-        <v>-124.05335568</v>
+        <v>-1.69406084</v>
       </c>
       <c r="D45" t="n">
-        <v>-105.55517871</v>
+        <v>-9.704325000000001</v>
       </c>
       <c r="E45" t="n">
-        <v>-256.19174892</v>
+        <v>3.652572440000001</v>
       </c>
       <c r="F45" t="n">
-        <v>-264.69814601</v>
+        <v>18.08799593</v>
       </c>
       <c r="G45" t="n">
-        <v>-222.55389545</v>
+        <v>13.37258108</v>
       </c>
       <c r="H45" t="n">
-        <v>37.63488079</v>
+        <v>15.07971701</v>
       </c>
       <c r="I45" t="n">
-        <v>-32.22098995</v>
+        <v>14.30404653</v>
       </c>
       <c r="J45" t="n">
-        <v>93.7329625</v>
+        <v>16.90830076</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.6881097599999998</v>
+        <v>5.003064830000001</v>
       </c>
       <c r="L45" t="n">
-        <v>78.81692654</v>
+        <v>12.13955481</v>
       </c>
       <c r="M45" t="n">
-        <v>56.04722025</v>
+        <v>12.4494654</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右上</t>
+          <t>生技醫療業右下</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>-2.68934393</v>
+        <v>-28.46534079</v>
       </c>
       <c r="D46" t="n">
-        <v>-6.34563964</v>
+        <v>-233.05222756</v>
       </c>
       <c r="E46" t="n">
-        <v>-8.06577257</v>
+        <v>-348.24858398</v>
       </c>
       <c r="F46" t="n">
-        <v>-5.88842813</v>
+        <v>-325.33811903</v>
       </c>
       <c r="G46" t="n">
-        <v>-5.95638258</v>
+        <v>-311.01762448</v>
       </c>
       <c r="H46" t="n">
-        <v>-5.16063128</v>
+        <v>-66.67090091</v>
       </c>
       <c r="I46" t="n">
-        <v>-5.243901949999999</v>
+        <v>7.325849740000002</v>
       </c>
       <c r="J46" t="n">
-        <v>-1.42678741</v>
+        <v>30.03810668</v>
       </c>
       <c r="K46" t="n">
-        <v>-1.55751561</v>
+        <v>116.27487735</v>
       </c>
       <c r="L46" t="n">
-        <v>0.21300419</v>
+        <v>258.77313968</v>
       </c>
       <c r="M46" t="n">
-        <v>0.11317531</v>
+        <v>93.90679775000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右下</t>
+          <t>生技醫療業平</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>53.45619471</v>
+        <v>-105.27377237</v>
       </c>
       <c r="D47" t="n">
-        <v>95.04986186999999</v>
+        <v>-256.59694877</v>
       </c>
       <c r="E47" t="n">
-        <v>9.407378970000002</v>
+        <v>-265.07278991</v>
       </c>
       <c r="F47" t="n">
-        <v>39.68573421</v>
+        <v>-222.95824788</v>
       </c>
       <c r="G47" t="n">
-        <v>4.959421839999997</v>
+        <v>37.17042832</v>
       </c>
       <c r="H47" t="n">
-        <v>20.79778082</v>
+        <v>-30.40253615</v>
       </c>
       <c r="I47" t="n">
-        <v>26.43966846</v>
+        <v>93.96601003000001</v>
       </c>
       <c r="J47" t="n">
-        <v>2.098726649999999</v>
+        <v>-0.8139572099999953</v>
       </c>
       <c r="K47" t="n">
-        <v>-22.66043861</v>
+        <v>78.94952617999999</v>
       </c>
       <c r="L47" t="n">
-        <v>-14.22419143</v>
+        <v>54.90868887</v>
       </c>
       <c r="M47" t="n">
-        <v>-101.46831989</v>
+        <v>-56.90458671</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維平</t>
+          <t>紡織纖維右上</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
-        <v>0.5514035599999999</v>
+        <v>-6.34542106</v>
       </c>
       <c r="D48" t="n">
-        <v>0.28994207</v>
+        <v>-8.06516886</v>
       </c>
       <c r="E48" t="n">
-        <v>0.02784229000000001</v>
+        <v>-5.88833566</v>
       </c>
       <c r="F48" t="n">
-        <v>0.06728542</v>
+        <v>-5.95651349</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.10238672</v>
+        <v>-5.16051644</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.002889020000000003</v>
+        <v>-5.243580819999999</v>
       </c>
       <c r="I48" t="n">
-        <v>1.65310548</v>
+        <v>-1.42689061</v>
       </c>
       <c r="J48" t="n">
-        <v>1.32672589</v>
+        <v>-1.55805487</v>
       </c>
       <c r="K48" t="n">
-        <v>0.25503158</v>
+        <v>0.2128199</v>
       </c>
       <c r="L48" t="n">
-        <v>-0.002404550000000011</v>
+        <v>0.11380938</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.2114317</v>
+        <v>-1.16393911</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右上</t>
+          <t>紡織纖維右下</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>-60.85314679</v>
+        <v>95.04986186999999</v>
       </c>
       <c r="D49" t="n">
-        <v>-44.6215331</v>
+        <v>9.407378970000002</v>
       </c>
       <c r="E49" t="n">
-        <v>17.17839787</v>
+        <v>39.68573421</v>
       </c>
       <c r="F49" t="n">
-        <v>-62.65965742</v>
+        <v>4.959421839999997</v>
       </c>
       <c r="G49" t="n">
-        <v>-60.30171099</v>
+        <v>20.79778082</v>
       </c>
       <c r="H49" t="n">
-        <v>-31.10208839</v>
+        <v>26.43966846</v>
       </c>
       <c r="I49" t="n">
-        <v>-117.28128842</v>
+        <v>2.098726649999999</v>
       </c>
       <c r="J49" t="n">
-        <v>-6.879195419999996</v>
+        <v>-22.66043861</v>
       </c>
       <c r="K49" t="n">
-        <v>-117.29680573</v>
+        <v>-14.22419143</v>
       </c>
       <c r="L49" t="n">
-        <v>50.61498453</v>
+        <v>-101.46831989</v>
       </c>
       <c r="M49" t="n">
-        <v>-67.84222641999999</v>
+        <v>-165.30252001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右下</t>
+          <t>紡織纖維平</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
-        <v>-6.02440684</v>
+        <v>0.28972349</v>
       </c>
       <c r="D50" t="n">
-        <v>-10.76360972</v>
+        <v>0.02723858000000001</v>
       </c>
       <c r="E50" t="n">
-        <v>-6.295704290000001</v>
+        <v>0.06719295</v>
       </c>
       <c r="F50" t="n">
-        <v>4.70272614</v>
+        <v>-0.10225581</v>
       </c>
       <c r="G50" t="n">
-        <v>-5.524311600000001</v>
+        <v>-0.003003860000000003</v>
       </c>
       <c r="H50" t="n">
-        <v>2.53485937</v>
+        <v>1.65278435</v>
       </c>
       <c r="I50" t="n">
-        <v>-2.54366476</v>
+        <v>1.32682909</v>
       </c>
       <c r="J50" t="n">
-        <v>4.03323023</v>
+        <v>0.25557084</v>
       </c>
       <c r="K50" t="n">
-        <v>-4.208008479999999</v>
+        <v>-0.002220260000000012</v>
       </c>
       <c r="L50" t="n">
-        <v>-16.668004</v>
+        <v>-0.21206577</v>
       </c>
       <c r="M50" t="n">
-        <v>-17.31000216</v>
+        <v>-0.3229723599999999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>綠能環保平</t>
+          <t>綠能環保右上</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>35.04990626</v>
+        <v>-44.42665097</v>
       </c>
       <c r="D51" t="n">
-        <v>11.21640177</v>
+        <v>16.98814198</v>
       </c>
       <c r="E51" t="n">
-        <v>0.5011575799999991</v>
+        <v>-62.84743057</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.7979235500000009</v>
+        <v>-60.72548797</v>
       </c>
       <c r="G51" t="n">
-        <v>-11.10073136</v>
+        <v>-31.76071553</v>
       </c>
       <c r="H51" t="n">
-        <v>18.13323726</v>
+        <v>-116.83585634</v>
       </c>
       <c r="I51" t="n">
-        <v>3.50636154</v>
+        <v>-7.13067809</v>
       </c>
       <c r="J51" t="n">
-        <v>23.9928634</v>
+        <v>-116.51903971</v>
       </c>
       <c r="K51" t="n">
-        <v>23.94287542</v>
+        <v>53.02447994</v>
       </c>
       <c r="L51" t="n">
-        <v>11.45678204</v>
+        <v>-67.05617642999999</v>
       </c>
       <c r="M51" t="n">
-        <v>14.87823323</v>
+        <v>-49.19548277000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>航運業右上</t>
+          <t>綠能環保右下</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>557.9386459900001</v>
+        <v>-10.76360972</v>
       </c>
       <c r="D52" t="n">
-        <v>166.34689068</v>
+        <v>-6.295704290000001</v>
       </c>
       <c r="E52" t="n">
-        <v>-33.08596268</v>
+        <v>4.70272614</v>
       </c>
       <c r="F52" t="n">
-        <v>10.94663334000001</v>
+        <v>-5.524311600000001</v>
       </c>
       <c r="G52" t="n">
-        <v>-242.48694746</v>
+        <v>2.53485937</v>
       </c>
       <c r="H52" t="n">
-        <v>176.69649829</v>
+        <v>-2.54366476</v>
       </c>
       <c r="I52" t="n">
-        <v>173.3919018</v>
+        <v>4.03323023</v>
       </c>
       <c r="J52" t="n">
-        <v>534.26192584</v>
+        <v>-4.208008479999999</v>
       </c>
       <c r="K52" t="n">
-        <v>553.1683261099998</v>
+        <v>-16.668004</v>
       </c>
       <c r="L52" t="n">
-        <v>-153.03544707</v>
+        <v>-17.31000216</v>
       </c>
       <c r="M52" t="n">
-        <v>23.19576348999999</v>
+        <v>-27.00119206</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>航運業右下</t>
+          <t>綠能環保平</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>29.15036724</v>
+        <v>11.02151964</v>
       </c>
       <c r="D53" t="n">
-        <v>2.022065750000001</v>
+        <v>0.6914134699999998</v>
       </c>
       <c r="E53" t="n">
-        <v>-8.206359429999999</v>
+        <v>-0.6101504000000009</v>
       </c>
       <c r="F53" t="n">
-        <v>2.95694848</v>
+        <v>-10.67695438</v>
       </c>
       <c r="G53" t="n">
-        <v>-5.68872284</v>
+        <v>18.7918644</v>
       </c>
       <c r="H53" t="n">
-        <v>-1.43237066</v>
+        <v>3.06092946</v>
       </c>
       <c r="I53" t="n">
-        <v>9.39389042</v>
+        <v>24.24434607</v>
       </c>
       <c r="J53" t="n">
-        <v>5.81157704</v>
+        <v>23.1651094</v>
       </c>
       <c r="K53" t="n">
-        <v>17.87863184</v>
+        <v>9.047286630000002</v>
       </c>
       <c r="L53" t="n">
-        <v>33.16015233</v>
+        <v>14.09218324</v>
       </c>
       <c r="M53" t="n">
-        <v>31.6322211</v>
+        <v>-7.867694850000001</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>航運業平</t>
+          <t>航運業右上</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>602.64274175</v>
+        <v>109.84570048</v>
       </c>
       <c r="D54" t="n">
-        <v>288.18667168</v>
+        <v>33.61381624000001</v>
       </c>
       <c r="E54" t="n">
-        <v>106.61687904</v>
+        <v>15.43591371</v>
       </c>
       <c r="F54" t="n">
-        <v>229.7805576</v>
+        <v>-113.78998172</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.8512672999999965</v>
+        <v>166.81981741</v>
       </c>
       <c r="H54" t="n">
-        <v>76.69232371000001</v>
+        <v>318.94946344</v>
       </c>
       <c r="I54" t="n">
-        <v>90.04812412999999</v>
+        <v>773.50804662</v>
       </c>
       <c r="J54" t="n">
-        <v>113.18358197</v>
+        <v>812.5688147</v>
       </c>
       <c r="K54" t="n">
-        <v>262.05763769</v>
+        <v>211.81430302</v>
       </c>
       <c r="L54" t="n">
-        <v>6.733098430000003</v>
+        <v>163.15365218</v>
       </c>
       <c r="M54" t="n">
-        <v>395.21610116</v>
+        <v>424.97201031</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右上</t>
+          <t>航運業右下</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>-30.59709092</v>
+        <v>2.649624870000001</v>
       </c>
       <c r="D55" t="n">
-        <v>1.71896167</v>
+        <v>-8.060267979999999</v>
       </c>
       <c r="E55" t="n">
-        <v>-3.66064519</v>
+        <v>3.392625100000001</v>
       </c>
       <c r="F55" t="n">
-        <v>6.780631179999999</v>
+        <v>-5.6969817</v>
       </c>
       <c r="G55" t="n">
-        <v>-4.03954524</v>
+        <v>-0.9628962199999999</v>
       </c>
       <c r="H55" t="n">
-        <v>17.6737899</v>
+        <v>9.504409800000001</v>
       </c>
       <c r="I55" t="n">
-        <v>27.54426674</v>
+        <v>6.19122544</v>
       </c>
       <c r="J55" t="n">
-        <v>42.05846305</v>
+        <v>18.44192423</v>
       </c>
       <c r="K55" t="n">
-        <v>41.63408625</v>
+        <v>33.41105407</v>
       </c>
       <c r="L55" t="n">
-        <v>24.46272503</v>
+        <v>32.28942822</v>
       </c>
       <c r="M55" t="n">
-        <v>-9.778699180000002</v>
+        <v>13.83002886</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右下</t>
+          <t>航運業平</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>-10.68184894</v>
+        <v>344.06030276</v>
       </c>
       <c r="D56" t="n">
-        <v>-2.0628507</v>
+        <v>39.77100866999999</v>
       </c>
       <c r="E56" t="n">
-        <v>-7.6462564</v>
+        <v>224.85560061</v>
       </c>
       <c r="F56" t="n">
-        <v>-7.730777489999999</v>
+        <v>-129.53997418</v>
       </c>
       <c r="G56" t="n">
-        <v>-13.07100915</v>
+        <v>86.09953015000001</v>
       </c>
       <c r="H56" t="n">
-        <v>-3.2074072</v>
+        <v>-55.61995688999998</v>
       </c>
       <c r="I56" t="n">
-        <v>24.12902713</v>
+        <v>-126.44218721</v>
       </c>
       <c r="J56" t="n">
-        <v>19.63279965</v>
+        <v>2.093856710000002</v>
       </c>
       <c r="K56" t="n">
-        <v>9.521514139999999</v>
+        <v>-358.3675534</v>
       </c>
       <c r="L56" t="n">
-        <v>-6.49064102</v>
+        <v>254.60100535</v>
       </c>
       <c r="M56" t="n">
-        <v>-19.63755573</v>
+        <v>92.98913580000003</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>觀光事業平</t>
+          <t>觀光事業右上</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
-        <v>-0.00558287</v>
+        <v>4.620033370000001</v>
       </c>
       <c r="D57" t="n">
-        <v>0.00240891</v>
+        <v>0.3289832499999999</v>
       </c>
       <c r="E57" t="n">
-        <v>0.009724190000000001</v>
+        <v>-1.13281235</v>
       </c>
       <c r="F57" t="n">
-        <v>0.0047186</v>
+        <v>-9.10466808</v>
       </c>
       <c r="G57" t="n">
-        <v>0.00133407</v>
+        <v>2.08177039</v>
       </c>
       <c r="H57" t="n">
-        <v>0.00326678</v>
+        <v>-7.27948795</v>
       </c>
       <c r="I57" t="n">
-        <v>0.01353709</v>
+        <v>-1.98132958</v>
       </c>
       <c r="J57" t="n">
-        <v>0.01480824</v>
+        <v>-4.1160601</v>
       </c>
       <c r="K57" t="n">
-        <v>0.0232123</v>
+        <v>4.08058217</v>
       </c>
       <c r="L57" t="n">
-        <v>0.006269750000000001</v>
+        <v>-0.19960646</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.00380255</v>
+        <v>-12.28249493</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨右下</t>
+          <t>觀光事業右下</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>-35.22507341000001</v>
+        <v>-2.06283767</v>
       </c>
       <c r="D58" t="n">
-        <v>-57.92342369999999</v>
+        <v>-7.64623531</v>
       </c>
       <c r="E58" t="n">
-        <v>-68.26387203</v>
+        <v>-7.73076538</v>
       </c>
       <c r="F58" t="n">
-        <v>-8.433303890000001</v>
+        <v>-13.07100979</v>
       </c>
       <c r="G58" t="n">
-        <v>-47.65032497000001</v>
+        <v>-3.20737339</v>
       </c>
       <c r="H58" t="n">
-        <v>7.703351639999999</v>
+        <v>24.12908983</v>
       </c>
       <c r="I58" t="n">
-        <v>41.98299858</v>
+        <v>19.63287374</v>
       </c>
       <c r="J58" t="n">
-        <v>64.00418524</v>
+        <v>9.521552719999999</v>
       </c>
       <c r="K58" t="n">
-        <v>37.16416376</v>
+        <v>-6.49062084</v>
       </c>
       <c r="L58" t="n">
-        <v>48.23396804</v>
+        <v>-19.63753738</v>
       </c>
       <c r="M58" t="n">
-        <v>28.77712765</v>
+        <v>-31.28690505</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨平</t>
+          <t>觀光事業平</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
-        <v>0.24380428</v>
+        <v>-2.89867582</v>
       </c>
       <c r="D59" t="n">
-        <v>1.14616828</v>
+        <v>-3.97992534</v>
       </c>
       <c r="E59" t="n">
-        <v>0.01365724</v>
+        <v>7.918150020000001</v>
       </c>
       <c r="F59" t="n">
-        <v>0.7604645999999999</v>
+        <v>5.06645755</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.24529395</v>
+        <v>15.59525248</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.70815295</v>
+        <v>34.83722908</v>
       </c>
       <c r="I59" t="n">
-        <v>0.59361993</v>
+        <v>44.05452678</v>
       </c>
       <c r="J59" t="n">
-        <v>1.16829318</v>
+        <v>45.77332007</v>
       </c>
       <c r="K59" t="n">
-        <v>1.87308302</v>
+        <v>20.38839243</v>
       </c>
       <c r="L59" t="n">
-        <v>2.42560356</v>
+        <v>-9.582913620000001</v>
       </c>
       <c r="M59" t="n">
-        <v>0.7308388099999999</v>
+        <v>-17.24537549</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右上</t>
+          <t>貿易百貨右下</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
-        <v>-59.83005495</v>
+        <v>-57.92342369999999</v>
       </c>
       <c r="D60" t="n">
-        <v>-20.09428251</v>
+        <v>-68.26387203</v>
       </c>
       <c r="E60" t="n">
-        <v>-30.92647838</v>
+        <v>-8.433303890000001</v>
       </c>
       <c r="F60" t="n">
-        <v>-15.12595207</v>
+        <v>-47.65032497000001</v>
       </c>
       <c r="G60" t="n">
-        <v>19.01596501</v>
+        <v>7.703351639999999</v>
       </c>
       <c r="H60" t="n">
-        <v>32.19631332</v>
+        <v>41.98299858</v>
       </c>
       <c r="I60" t="n">
-        <v>66.0032384</v>
+        <v>64.00418524</v>
       </c>
       <c r="J60" t="n">
-        <v>95.20201191</v>
+        <v>37.16416376</v>
       </c>
       <c r="K60" t="n">
-        <v>52.08602065</v>
+        <v>48.23396804</v>
       </c>
       <c r="L60" t="n">
-        <v>56.26502794</v>
+        <v>28.77712765</v>
       </c>
       <c r="M60" t="n">
-        <v>4.496212889999995</v>
+        <v>3.951017690000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右下</t>
+          <t>貿易百貨平</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
-        <v>-0.00363863</v>
+        <v>1.14616828</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.00167134</v>
+        <v>0.01365724</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.00462742</v>
+        <v>0.7604645999999999</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.00432153</v>
+        <v>-0.24529395</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.007909279999999999</v>
+        <v>-0.70815295</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.00354446</v>
+        <v>0.59361993</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.00278847</v>
+        <v>1.16829318</v>
       </c>
       <c r="J61" t="n">
-        <v>0.007145980000000001</v>
+        <v>1.87308302</v>
       </c>
       <c r="K61" t="n">
-        <v>0.00555183</v>
+        <v>2.42560356</v>
       </c>
       <c r="L61" t="n">
-        <v>0.00131319</v>
+        <v>0.7308388099999999</v>
       </c>
       <c r="M61" t="n">
-        <v>0.008997719999999999</v>
+        <v>-0.17334417</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業平</t>
+          <t>資訊服務業右上</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>-18.18665765</v>
+        <v>-20.09428251</v>
       </c>
       <c r="D62" t="n">
-        <v>54.93311962999999</v>
+        <v>-30.92647838</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.1308476699999995</v>
+        <v>-15.12595207</v>
       </c>
       <c r="F62" t="n">
-        <v>15.73948928</v>
+        <v>19.01596501</v>
       </c>
       <c r="G62" t="n">
-        <v>-2.4515891</v>
+        <v>32.19631332</v>
       </c>
       <c r="H62" t="n">
-        <v>28.65283027</v>
+        <v>66.0032384</v>
       </c>
       <c r="I62" t="n">
-        <v>47.66627009</v>
+        <v>95.20201191</v>
       </c>
       <c r="J62" t="n">
-        <v>94.86354453</v>
+        <v>52.08602065</v>
       </c>
       <c r="K62" t="n">
-        <v>46.74758576</v>
+        <v>56.26502794</v>
       </c>
       <c r="L62" t="n">
-        <v>41.24747490999999</v>
+        <v>4.496212889999995</v>
       </c>
       <c r="M62" t="n">
-        <v>17.01497226</v>
+        <v>16.521687</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右上</t>
+          <t>資訊服務業右下</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>0.00012761</v>
+        <v>-0.0009432200000000003</v>
       </c>
       <c r="D63" t="n">
-        <v>0.00014581</v>
+        <v>-0.00395804</v>
       </c>
       <c r="E63" t="n">
-        <v>0.00033086</v>
+        <v>-0.0038087</v>
       </c>
       <c r="F63" t="n">
-        <v>0.0004248200000000001</v>
+        <v>-0.00767553</v>
       </c>
       <c r="G63" t="n">
-        <v>0.00090755</v>
+        <v>-0.00331886</v>
       </c>
       <c r="H63" t="n">
-        <v>0.00103174</v>
+        <v>-0.00264089</v>
       </c>
       <c r="I63" t="n">
-        <v>0.0009914099999999999</v>
+        <v>0.00704679</v>
       </c>
       <c r="J63" t="n">
-        <v>6.247e-05</v>
+        <v>0.00531042</v>
       </c>
       <c r="K63" t="n">
-        <v>0.0004044</v>
+        <v>0.00115759</v>
       </c>
       <c r="L63" t="n">
-        <v>0.00072251</v>
+        <v>0.009192200000000001</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.00025412</v>
+        <v>0.01654324</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右下</t>
+          <t>資訊服務業平</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
-        <v>-0.00018756</v>
+        <v>54.93303347</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.00024988</v>
+        <v>-0.1309064899999995</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.00027272</v>
+        <v>15.73954062</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.0002611</v>
+        <v>-2.45135326</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.00027651</v>
+        <v>28.65296481</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.0002609000000000001</v>
+        <v>47.66635361</v>
       </c>
       <c r="I64" t="n">
-        <v>5.814e-05</v>
+        <v>94.86368377000001</v>
       </c>
       <c r="J64" t="n">
-        <v>0.00018835</v>
+        <v>46.74773143</v>
       </c>
       <c r="K64" t="n">
-        <v>2.243e-05</v>
+        <v>41.24752671</v>
       </c>
       <c r="L64" t="n">
-        <v>-8.019e-05</v>
+        <v>17.01497371</v>
       </c>
       <c r="M64" t="n">
-        <v>-3.720999999999999e-05</v>
+        <v>18.43894564</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右上</t>
+          <t>農業科技業右上</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
-        <v>545.52838719</v>
+        <v>0.00014581</v>
       </c>
       <c r="D65" t="n">
-        <v>1076.26157955</v>
+        <v>0.00033086</v>
       </c>
       <c r="E65" t="n">
-        <v>852.3115199600001</v>
+        <v>0.0004248200000000001</v>
       </c>
       <c r="F65" t="n">
-        <v>101.008516</v>
+        <v>0.00090755</v>
       </c>
       <c r="G65" t="n">
-        <v>413.7915287</v>
+        <v>0.00103174</v>
       </c>
       <c r="H65" t="n">
-        <v>-28.99580328000001</v>
+        <v>0.0009914099999999999</v>
       </c>
       <c r="I65" t="n">
-        <v>175.92371544</v>
+        <v>6.247e-05</v>
       </c>
       <c r="J65" t="n">
-        <v>709.1590385</v>
+        <v>0.0004044</v>
       </c>
       <c r="K65" t="n">
-        <v>228.75441454</v>
+        <v>0.00072251</v>
       </c>
       <c r="L65" t="n">
-        <v>580.34068565</v>
+        <v>-0.00025412</v>
       </c>
       <c r="M65" t="n">
-        <v>763.7509641700001</v>
+        <v>-0.00126824</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右下</t>
+          <t>農業科技業右下</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>31.1887251</v>
+        <v>-0.00024988</v>
       </c>
       <c r="D66" t="n">
-        <v>33.87624075999999</v>
+        <v>-0.00027272</v>
       </c>
       <c r="E66" t="n">
-        <v>44.29952979999999</v>
+        <v>-0.0002611</v>
       </c>
       <c r="F66" t="n">
-        <v>29.08693983</v>
+        <v>-0.00027651</v>
       </c>
       <c r="G66" t="n">
-        <v>0.4105898600000005</v>
+        <v>-0.0002609000000000001</v>
       </c>
       <c r="H66" t="n">
-        <v>86.89475669999999</v>
+        <v>5.814e-05</v>
       </c>
       <c r="I66" t="n">
-        <v>-34.34445583999999</v>
+        <v>0.00018835</v>
       </c>
       <c r="J66" t="n">
-        <v>-19.90779443</v>
+        <v>2.243e-05</v>
       </c>
       <c r="K66" t="n">
-        <v>-40.57344869999999</v>
+        <v>-8.019e-05</v>
       </c>
       <c r="L66" t="n">
-        <v>-96.36349721000001</v>
+        <v>-3.720999999999999e-05</v>
       </c>
       <c r="M66" t="n">
-        <v>-77.19925556</v>
+        <v>-0.00012853</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>通信網路業平</t>
+          <t>通信網路業右上</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>555.37691608</v>
+        <v>1071.29921391</v>
       </c>
       <c r="D67" t="n">
-        <v>823.02801951</v>
+        <v>847.7265433000001</v>
       </c>
       <c r="E67" t="n">
-        <v>322.44746653</v>
+        <v>96.80285476</v>
       </c>
       <c r="F67" t="n">
-        <v>367.82150821</v>
+        <v>410.20350762</v>
       </c>
       <c r="G67" t="n">
-        <v>114.43159391</v>
+        <v>-30.36561727</v>
       </c>
       <c r="H67" t="n">
-        <v>298.04569379</v>
+        <v>176.70231297</v>
       </c>
       <c r="I67" t="n">
-        <v>202.1253038</v>
+        <v>709.04143488</v>
       </c>
       <c r="J67" t="n">
-        <v>183.86646338</v>
+        <v>231.25709942</v>
       </c>
       <c r="K67" t="n">
-        <v>138.78240026</v>
+        <v>583.75361994</v>
       </c>
       <c r="L67" t="n">
-        <v>-27.89177712999998</v>
+        <v>765.4437038900001</v>
       </c>
       <c r="M67" t="n">
-        <v>-117.21568837</v>
+        <v>919.7423975</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>造紙工業右下</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr"/>
+          <t>通信網路業右下</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>0</v>
+      </c>
       <c r="C68" t="n">
-        <v>25.77768484</v>
+        <v>33.87624075999999</v>
       </c>
       <c r="D68" t="n">
-        <v>7.5358798</v>
+        <v>44.29952979999999</v>
       </c>
       <c r="E68" t="n">
-        <v>-2.18453111</v>
+        <v>29.08693983</v>
       </c>
       <c r="F68" t="n">
-        <v>-4.28064262</v>
+        <v>0.4105898600000005</v>
       </c>
       <c r="G68" t="n">
-        <v>-9.848016550000001</v>
+        <v>86.89475669999999</v>
       </c>
       <c r="H68" t="n">
-        <v>-11.75977663</v>
+        <v>-34.34445583999999</v>
       </c>
       <c r="I68" t="n">
-        <v>-14.45543988</v>
+        <v>-19.90779443</v>
       </c>
       <c r="J68" t="n">
-        <v>-8.60103045</v>
+        <v>-40.57344869999999</v>
       </c>
       <c r="K68" t="n">
-        <v>1.481096</v>
+        <v>-96.36349721000001</v>
       </c>
       <c r="L68" t="n">
-        <v>-2.09694106</v>
+        <v>-77.19925556</v>
       </c>
       <c r="M68" t="n">
-        <v>-1.18870531</v>
+        <v>-56.20752070000001</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>造紙工業平</t>
+          <t>通信網路業平</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>-1.43394215</v>
+        <v>827.99073538</v>
       </c>
       <c r="D69" t="n">
-        <v>-1.69268373</v>
+        <v>327.03278143</v>
       </c>
       <c r="E69" t="n">
-        <v>-3.23010772</v>
+        <v>372.02748297</v>
       </c>
       <c r="F69" t="n">
-        <v>-3.39045584</v>
+        <v>118.01982874</v>
       </c>
       <c r="G69" t="n">
-        <v>-4.06147909</v>
+        <v>299.41572412</v>
       </c>
       <c r="H69" t="n">
-        <v>-3.60733925</v>
+        <v>201.34689884</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.16033294</v>
+        <v>183.9841914</v>
       </c>
       <c r="J69" t="n">
-        <v>-1.55525517</v>
+        <v>136.28002782</v>
       </c>
       <c r="K69" t="n">
-        <v>0.15859867</v>
+        <v>-31.30440671999998</v>
       </c>
       <c r="L69" t="n">
-        <v>-0.01651628</v>
+        <v>-118.90813709</v>
       </c>
       <c r="M69" t="n">
-        <v>0.93115824</v>
+        <v>-93.30377819</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右上</t>
+          <t>造紙工業右下</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>-16.82706139</v>
+        <v>7.5358798</v>
       </c>
       <c r="D70" t="n">
-        <v>-21.49287157</v>
+        <v>-2.18453111</v>
       </c>
       <c r="E70" t="n">
-        <v>-29.75249595</v>
+        <v>-4.28064262</v>
       </c>
       <c r="F70" t="n">
-        <v>-5.49167339</v>
+        <v>-9.848016550000001</v>
       </c>
       <c r="G70" t="n">
-        <v>-6.985563310000001</v>
+        <v>-11.75977663</v>
       </c>
       <c r="H70" t="n">
-        <v>6.14054282</v>
+        <v>-14.45543988</v>
       </c>
       <c r="I70" t="n">
-        <v>22.89727625</v>
+        <v>-8.60103045</v>
       </c>
       <c r="J70" t="n">
-        <v>39.58487804</v>
+        <v>1.481096</v>
       </c>
       <c r="K70" t="n">
-        <v>49.03197814</v>
+        <v>-2.09694106</v>
       </c>
       <c r="L70" t="n">
-        <v>20.29127258</v>
+        <v>-1.18870531</v>
       </c>
       <c r="M70" t="n">
-        <v>24.00895878</v>
+        <v>0.8999840899999999</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右下</t>
+          <t>造紙工業平</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
-        <v>7.475289409999997</v>
+        <v>-1.69268373</v>
       </c>
       <c r="D71" t="n">
-        <v>-64.07427258999999</v>
+        <v>-3.23010772</v>
       </c>
       <c r="E71" t="n">
-        <v>-115.50237892</v>
+        <v>-3.39045584</v>
       </c>
       <c r="F71" t="n">
-        <v>-11.79256974999999</v>
+        <v>-4.06147909</v>
       </c>
       <c r="G71" t="n">
-        <v>-141.47987787</v>
+        <v>-3.60733925</v>
       </c>
       <c r="H71" t="n">
-        <v>-101.90599359</v>
+        <v>-1.16033294</v>
       </c>
       <c r="I71" t="n">
-        <v>-27.86393122</v>
+        <v>-1.55525517</v>
       </c>
       <c r="J71" t="n">
-        <v>-19.72376035</v>
+        <v>0.15859867</v>
       </c>
       <c r="K71" t="n">
-        <v>-80.99866675</v>
+        <v>-0.01651628</v>
       </c>
       <c r="L71" t="n">
-        <v>-115.79851781</v>
+        <v>0.93115824</v>
       </c>
       <c r="M71" t="n">
-        <v>-38.42840705</v>
+        <v>0.15324129</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>運動休閒平</t>
+          <t>運動休閒右上</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>4.281030289999999</v>
+        <v>-21.49287157</v>
       </c>
       <c r="D72" t="n">
-        <v>5.539278160000001</v>
+        <v>-29.75249595</v>
       </c>
       <c r="E72" t="n">
-        <v>-2.54610903</v>
+        <v>-5.49167339</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.68230068</v>
+        <v>-6.985563310000001</v>
       </c>
       <c r="G72" t="n">
-        <v>-10.98006195</v>
+        <v>6.14054282</v>
       </c>
       <c r="H72" t="n">
-        <v>0.2389688799999998</v>
+        <v>22.89727625</v>
       </c>
       <c r="I72" t="n">
-        <v>11.07624471</v>
+        <v>39.58487804</v>
       </c>
       <c r="J72" t="n">
-        <v>3.90076889</v>
+        <v>49.03197814</v>
       </c>
       <c r="K72" t="n">
-        <v>-10.60413652</v>
+        <v>20.29127258</v>
       </c>
       <c r="L72" t="n">
-        <v>-10.73076839</v>
+        <v>24.00895878</v>
       </c>
       <c r="M72" t="n">
-        <v>-23.37633456</v>
+        <v>34.17125779</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>金融保險右上</t>
+          <t>運動休閒右下</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
-        <v>-1039.8621816</v>
+        <v>-69.08854124</v>
       </c>
       <c r="D73" t="n">
-        <v>-1355.62532236</v>
+        <v>-118.02431299</v>
       </c>
       <c r="E73" t="n">
-        <v>-1508.41550234</v>
+        <v>-11.99343319999999</v>
       </c>
       <c r="F73" t="n">
-        <v>-486.04991945</v>
+        <v>-143.94763791</v>
       </c>
       <c r="G73" t="n">
-        <v>-927.54211931</v>
+        <v>-102.25610116</v>
       </c>
       <c r="H73" t="n">
-        <v>49.54949119</v>
+        <v>-27.91482</v>
       </c>
       <c r="I73" t="n">
-        <v>884.7286469300001</v>
+        <v>-17.14059748</v>
       </c>
       <c r="J73" t="n">
-        <v>779.76484189</v>
+        <v>-81.91163204999999</v>
       </c>
       <c r="K73" t="n">
-        <v>1144.01673126</v>
+        <v>-115.31227011</v>
       </c>
       <c r="L73" t="n">
-        <v>804.37010775</v>
+        <v>-37.30362026</v>
       </c>
       <c r="M73" t="n">
-        <v>647.00666835</v>
+        <v>-103.56392674</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>金融保險右下</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
-        <v>0</v>
-      </c>
+          <t>運動休閒平</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
-        <v>-155.54415517</v>
+        <v>10.55354681</v>
       </c>
       <c r="D74" t="n">
-        <v>-454.77151971</v>
+        <v>-0.02417495999999996</v>
       </c>
       <c r="E74" t="n">
-        <v>-641.20146943</v>
+        <v>-1.48143723</v>
       </c>
       <c r="F74" t="n">
-        <v>-347.05644305</v>
+        <v>-8.51230191</v>
       </c>
       <c r="G74" t="n">
-        <v>-359.8776884299999</v>
+        <v>0.58907645</v>
       </c>
       <c r="H74" t="n">
-        <v>-343.74413127</v>
+        <v>11.12713349</v>
       </c>
       <c r="I74" t="n">
-        <v>-136.81080979</v>
+        <v>1.31760602</v>
       </c>
       <c r="J74" t="n">
-        <v>34.65447583</v>
+        <v>-9.691171220000001</v>
       </c>
       <c r="K74" t="n">
-        <v>112.2585677</v>
+        <v>-11.21701609</v>
       </c>
       <c r="L74" t="n">
-        <v>-45.85452738</v>
+        <v>-24.50112135</v>
       </c>
       <c r="M74" t="n">
-        <v>-206.11673481</v>
+        <v>-23.85631305</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>金融保險平</t>
+          <t>金融保險右上</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
-        <v>-58.58307425</v>
+        <v>-1344.25654867</v>
       </c>
       <c r="D75" t="n">
-        <v>-125.06047454</v>
+        <v>-1513.10008246</v>
       </c>
       <c r="E75" t="n">
-        <v>-179.56732411</v>
+        <v>-486.52127426</v>
       </c>
       <c r="F75" t="n">
-        <v>-83.0036958</v>
+        <v>-936.91281313</v>
       </c>
       <c r="G75" t="n">
-        <v>-145.13371544</v>
+        <v>59.42146735</v>
       </c>
       <c r="H75" t="n">
-        <v>17.82308436</v>
+        <v>903.2323206300001</v>
       </c>
       <c r="I75" t="n">
-        <v>181.23442961</v>
+        <v>800.7780561700001</v>
       </c>
       <c r="J75" t="n">
-        <v>133.4526263</v>
+        <v>1167.48715472</v>
       </c>
       <c r="K75" t="n">
-        <v>161.94001351</v>
+        <v>823.8283143199999</v>
       </c>
       <c r="L75" t="n">
-        <v>47.34589182</v>
+        <v>653.6134696299999</v>
       </c>
       <c r="M75" t="n">
-        <v>55.02704358</v>
+        <v>665.12436012</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>金融業右上</t>
+          <t>金融保險右下</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>-0.00057684</v>
+        <v>-454.77151971</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.0006594299999999999</v>
+        <v>-641.20146943</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.00071329</v>
+        <v>-347.05644305</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.0003751</v>
+        <v>-359.8776884299999</v>
       </c>
       <c r="G76" t="n">
-        <v>-0.00072667</v>
+        <v>-343.74413127</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.00031853</v>
+        <v>-136.81080979</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.00042214</v>
+        <v>34.65447583</v>
       </c>
       <c r="J76" t="n">
-        <v>0.00035191</v>
+        <v>112.2585677</v>
       </c>
       <c r="K76" t="n">
-        <v>0.0006016</v>
+        <v>-45.85452738</v>
       </c>
       <c r="L76" t="n">
-        <v>0.00119589</v>
+        <v>-206.11673481</v>
       </c>
       <c r="M76" t="n">
-        <v>0.00222055</v>
+        <v>-343.8864405899999</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>金融業右下</t>
+          <t>金融保險平</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="n">
-        <v>0.004119070000000001</v>
+        <v>-125.06047454</v>
       </c>
       <c r="D77" t="n">
-        <v>0.00104634</v>
+        <v>-179.56732411</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.00267286</v>
+        <v>-83.0036958</v>
       </c>
       <c r="F77" t="n">
-        <v>-9.306000000000001e-05</v>
+        <v>-145.13371544</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.00439828</v>
+        <v>17.82308436</v>
       </c>
       <c r="H77" t="n">
-        <v>-0.005935770000000001</v>
+        <v>181.23442961</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.006376339999999999</v>
+        <v>133.4526263</v>
       </c>
       <c r="J77" t="n">
-        <v>-0.00146164</v>
+        <v>161.94001351</v>
       </c>
       <c r="K77" t="n">
-        <v>0.0001785999999999999</v>
+        <v>47.34589182</v>
       </c>
       <c r="L77" t="n">
-        <v>0.00166505</v>
+        <v>55.02704358</v>
       </c>
       <c r="M77" t="n">
-        <v>0.00481058</v>
+        <v>21.00031481</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>金融業平</t>
+          <t>金融業右上</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
-        <v>-0.00048908</v>
+        <v>-0.0006594299999999999</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.00026955</v>
+        <v>-0.00071329</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.00035725</v>
+        <v>-0.0003751</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.00052145</v>
+        <v>-0.00072667</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.00052038</v>
+        <v>-0.00031853</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.00049876</v>
+        <v>-0.00042214</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.00010349</v>
+        <v>0.00035191</v>
       </c>
       <c r="J78" t="n">
-        <v>0.00149008</v>
+        <v>0.0006016</v>
       </c>
       <c r="K78" t="n">
-        <v>0.00167124</v>
+        <v>0.00119589</v>
       </c>
       <c r="L78" t="n">
-        <v>0.00103193</v>
+        <v>0.00222055</v>
       </c>
       <c r="M78" t="n">
-        <v>0.00057835</v>
+        <v>0.00226234</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上</t>
+          <t>金融業右下</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="n">
-        <v>349.1965062800001</v>
+        <v>0.00104378</v>
       </c>
       <c r="D79" t="n">
-        <v>489.0815217</v>
+        <v>-0.00267729</v>
       </c>
       <c r="E79" t="n">
-        <v>750.7487125599999</v>
+        <v>-7.551999999999998e-05</v>
       </c>
       <c r="F79" t="n">
-        <v>741.8872466500001</v>
+        <v>-0.00437749</v>
       </c>
       <c r="G79" t="n">
-        <v>201.67650435</v>
+        <v>-0.00592591</v>
       </c>
       <c r="H79" t="n">
-        <v>-141.11423658</v>
+        <v>-0.006374369999999999</v>
       </c>
       <c r="I79" t="n">
-        <v>0.7313264700000002</v>
+        <v>-0.00145684</v>
       </c>
       <c r="J79" t="n">
-        <v>-176.67389534</v>
+        <v>0.0001739999999999999</v>
       </c>
       <c r="K79" t="n">
-        <v>-79.90343278</v>
+        <v>0.00166164</v>
       </c>
       <c r="L79" t="n">
-        <v>-228.13185528</v>
+        <v>0.00480599</v>
       </c>
       <c r="M79" t="n">
-        <v>74.18891708000001</v>
+        <v>0.00271667</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下</t>
+          <t>金融業平</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="n">
-        <v>36.53568006</v>
+        <v>-0.00026699</v>
       </c>
       <c r="D80" t="n">
-        <v>-46.66810387</v>
+        <v>-0.00035282</v>
       </c>
       <c r="E80" t="n">
-        <v>-86.27307861</v>
+        <v>-0.00053899</v>
       </c>
       <c r="F80" t="n">
-        <v>4.663124380000001</v>
+        <v>-0.0005411700000000001</v>
       </c>
       <c r="G80" t="n">
-        <v>-72.56750855</v>
+        <v>-0.00050862</v>
       </c>
       <c r="H80" t="n">
-        <v>-103.89955773</v>
+        <v>-0.00010546</v>
       </c>
       <c r="I80" t="n">
-        <v>-113.32769049</v>
+        <v>0.00148528</v>
       </c>
       <c r="J80" t="n">
-        <v>-68.71882223</v>
+        <v>0.00167584</v>
       </c>
       <c r="K80" t="n">
-        <v>-46.24819579</v>
+        <v>0.00103534</v>
       </c>
       <c r="L80" t="n">
-        <v>-65.44478223999999</v>
+        <v>0.0005829400000000001</v>
       </c>
       <c r="M80" t="n">
-        <v>-39.48523577</v>
+        <v>0.000107</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業平</t>
+          <t>鋼鐵工業右上</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>35.47651657</v>
+        <v>489.0815217</v>
       </c>
       <c r="D81" t="n">
-        <v>21.61024113</v>
+        <v>750.7487125599999</v>
       </c>
       <c r="E81" t="n">
-        <v>18.5110399</v>
+        <v>741.8872466500001</v>
       </c>
       <c r="F81" t="n">
-        <v>67.25528339</v>
+        <v>201.67650435</v>
       </c>
       <c r="G81" t="n">
-        <v>44.31661445</v>
+        <v>-141.11423658</v>
       </c>
       <c r="H81" t="n">
-        <v>134.51129435</v>
+        <v>0.7313264700000002</v>
       </c>
       <c r="I81" t="n">
-        <v>96.13981677</v>
+        <v>-176.67389534</v>
       </c>
       <c r="J81" t="n">
-        <v>120.37920766</v>
+        <v>-79.90343278</v>
       </c>
       <c r="K81" t="n">
-        <v>91.52392227000001</v>
+        <v>-228.13185528</v>
       </c>
       <c r="L81" t="n">
-        <v>52.25192397</v>
+        <v>74.18891708000001</v>
       </c>
       <c r="M81" t="n">
-        <v>8.08547903</v>
+        <v>-251.67991232</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右上</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr"/>
+          <t>鋼鐵工業右下</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>0</v>
+      </c>
       <c r="C82" t="n">
-        <v>-5.600883880000002</v>
+        <v>-46.83917436999999</v>
       </c>
       <c r="D82" t="n">
-        <v>-16.1009798</v>
+        <v>-85.97153582999999</v>
       </c>
       <c r="E82" t="n">
-        <v>35.45646956</v>
+        <v>3.881013460000001</v>
       </c>
       <c r="F82" t="n">
-        <v>68.03330789</v>
+        <v>-72.54789876</v>
       </c>
       <c r="G82" t="n">
-        <v>-4.41017006</v>
+        <v>-103.93206944</v>
       </c>
       <c r="H82" t="n">
-        <v>-6.688197980000001</v>
+        <v>-113.73505718</v>
       </c>
       <c r="I82" t="n">
-        <v>39.15618257</v>
+        <v>-68.4080062</v>
       </c>
       <c r="J82" t="n">
-        <v>88.37693567999999</v>
+        <v>-45.60012753</v>
       </c>
       <c r="K82" t="n">
-        <v>173.80208869</v>
+        <v>-65.01996659</v>
       </c>
       <c r="L82" t="n">
-        <v>68.31111571000001</v>
+        <v>-39.60682835</v>
       </c>
       <c r="M82" t="n">
-        <v>-15.21283794</v>
+        <v>-10.18949832</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右下</t>
+          <t>鋼鐵工業平</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>-5.995241029999999</v>
+        <v>21.61024113</v>
       </c>
       <c r="D83" t="n">
-        <v>7.19180515</v>
+        <v>18.5110399</v>
       </c>
       <c r="E83" t="n">
-        <v>-6.73828916</v>
+        <v>67.25528339</v>
       </c>
       <c r="F83" t="n">
-        <v>102.04973315</v>
+        <v>44.31661445</v>
       </c>
       <c r="G83" t="n">
-        <v>-116.03766855</v>
+        <v>134.47134333</v>
       </c>
       <c r="H83" t="n">
-        <v>-143.59839725</v>
+        <v>96.22012865000001</v>
       </c>
       <c r="I83" t="n">
-        <v>-122.34910587</v>
+        <v>120.4026709</v>
       </c>
       <c r="J83" t="n">
-        <v>-54.08839686000001</v>
+        <v>91.55941697</v>
       </c>
       <c r="K83" t="n">
-        <v>-10.32371517</v>
+        <v>52.12557176</v>
       </c>
       <c r="L83" t="n">
-        <v>20.68578092</v>
+        <v>8.03369266</v>
       </c>
       <c r="M83" t="n">
-        <v>50.43591372</v>
+        <v>98.18599175999999</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>電器電纜平</t>
+          <t>電器電纜右上</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
-        <v>-25.98931853</v>
+        <v>-14.46518195</v>
       </c>
       <c r="D84" t="n">
-        <v>-21.69868568</v>
+        <v>37.21932350000001</v>
       </c>
       <c r="E84" t="n">
-        <v>-16.25636132</v>
+        <v>68.03134521</v>
       </c>
       <c r="F84" t="n">
-        <v>-1.10998745</v>
+        <v>-2.350372119999999</v>
       </c>
       <c r="G84" t="n">
-        <v>-17.7452246</v>
+        <v>-4.571539939999999</v>
       </c>
       <c r="H84" t="n">
-        <v>-22.43654935</v>
+        <v>39.14585281</v>
       </c>
       <c r="I84" t="n">
-        <v>-6.625887400000001</v>
+        <v>87.22141015999999</v>
       </c>
       <c r="J84" t="n">
-        <v>10.56383229</v>
+        <v>170.87627227</v>
       </c>
       <c r="K84" t="n">
-        <v>91.58342936</v>
+        <v>64.92778369</v>
       </c>
       <c r="L84" t="n">
-        <v>307.9963481</v>
+        <v>-16.8321213</v>
       </c>
       <c r="M84" t="n">
-        <v>127.17968981</v>
+        <v>-17.33743878</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右上</t>
+          <t>電器電纜右下</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>-14.73780212</v>
+        <v>7.24090026</v>
       </c>
       <c r="D85" t="n">
-        <v>45.55591851</v>
+        <v>-6.584324479999999</v>
       </c>
       <c r="E85" t="n">
-        <v>20.93663418</v>
+        <v>102.05297551</v>
       </c>
       <c r="F85" t="n">
-        <v>83.75538558</v>
+        <v>-115.80629482</v>
       </c>
       <c r="G85" t="n">
-        <v>31.50825829</v>
+        <v>-143.5880583</v>
       </c>
       <c r="H85" t="n">
-        <v>43.48443047</v>
+        <v>-122.46679617</v>
       </c>
       <c r="I85" t="n">
-        <v>13.09829768</v>
+        <v>-54.09129918000001</v>
       </c>
       <c r="J85" t="n">
-        <v>98.23389636000002</v>
+        <v>-10.37837567</v>
       </c>
       <c r="K85" t="n">
-        <v>22.42436713</v>
+        <v>20.72719751</v>
       </c>
       <c r="L85" t="n">
-        <v>-73.80742721999999</v>
+        <v>50.52978478</v>
       </c>
       <c r="M85" t="n">
-        <v>-141.66079415</v>
+        <v>20.65799403</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右下</t>
+          <t>電器電纜平</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
-        <v>-2.703178970000001</v>
+        <v>-23.38357864</v>
       </c>
       <c r="D86" t="n">
-        <v>3.224730260000002</v>
+        <v>-18.17317994</v>
       </c>
       <c r="E86" t="n">
-        <v>-21.47029142</v>
+        <v>-1.11126713</v>
       </c>
       <c r="F86" t="n">
-        <v>-7.91920331</v>
+        <v>-20.03639627</v>
       </c>
       <c r="G86" t="n">
-        <v>-36.21035567</v>
+        <v>-24.56354634</v>
       </c>
       <c r="H86" t="n">
-        <v>-36.17334212999999</v>
+        <v>-6.497867340000001</v>
       </c>
       <c r="I86" t="n">
-        <v>-17.99274967</v>
+        <v>11.72226013</v>
       </c>
       <c r="J86" t="n">
-        <v>2.984687119999999</v>
+        <v>94.56390628</v>
       </c>
       <c r="K86" t="n">
-        <v>-5.265299160000001</v>
+        <v>311.33826353</v>
       </c>
       <c r="L86" t="n">
-        <v>0.6815553000000008</v>
+        <v>128.70510211</v>
       </c>
       <c r="M86" t="n">
-        <v>-38.59596085</v>
+        <v>35.16071363999999</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>電子通路業平</t>
+          <t>電子通路業右上</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>-18.34169891</v>
+        <v>42.12402878</v>
       </c>
       <c r="D87" t="n">
-        <v>38.30534171</v>
+        <v>24.19335857</v>
       </c>
       <c r="E87" t="n">
-        <v>-24.36095889</v>
+        <v>81.89622543999999</v>
       </c>
       <c r="F87" t="n">
-        <v>23.70920259</v>
+        <v>36.94664319</v>
       </c>
       <c r="G87" t="n">
-        <v>-37.93858206</v>
+        <v>39.92671712</v>
       </c>
       <c r="H87" t="n">
-        <v>6.009685249999998</v>
+        <v>-7.647300829999998</v>
       </c>
       <c r="I87" t="n">
-        <v>39.0312451</v>
+        <v>40.5057899</v>
       </c>
       <c r="J87" t="n">
-        <v>73.29482257000001</v>
+        <v>0.2115746600000012</v>
       </c>
       <c r="K87" t="n">
-        <v>106.34746701</v>
+        <v>-73.51357708</v>
       </c>
       <c r="L87" t="n">
-        <v>61.18977798</v>
+        <v>-120.38293081</v>
       </c>
       <c r="M87" t="n">
-        <v>-6.59081659</v>
+        <v>-28.81328676999999</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右上</t>
+          <t>電子通路業右下</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
-        <v>297.72893396</v>
+        <v>7.28057738</v>
       </c>
       <c r="D88" t="n">
-        <v>1915.63000907</v>
+        <v>-21.34147909</v>
       </c>
       <c r="E88" t="n">
-        <v>1121.81336747</v>
+        <v>-9.3358998</v>
       </c>
       <c r="F88" t="n">
-        <v>511.14990518</v>
+        <v>-40.89610144</v>
       </c>
       <c r="G88" t="n">
-        <v>2100.27602122</v>
+        <v>-35.51571165</v>
       </c>
       <c r="H88" t="n">
-        <v>3109.51351174</v>
+        <v>-13.73270536</v>
       </c>
       <c r="I88" t="n">
-        <v>534.58430609</v>
+        <v>8.53210361</v>
       </c>
       <c r="J88" t="n">
-        <v>3001.40162512</v>
+        <v>-7.17190724</v>
       </c>
       <c r="K88" t="n">
-        <v>1383.30676836</v>
+        <v>-3.542795019999999</v>
       </c>
       <c r="L88" t="n">
-        <v>1204.89327901</v>
+        <v>-45.59276418</v>
       </c>
       <c r="M88" t="n">
-        <v>3540.41320232</v>
+        <v>-99.21578414</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右下</t>
+          <t>電子通路業平</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>-393.67012069</v>
+        <v>37.68138432</v>
       </c>
       <c r="D89" t="n">
-        <v>-83.48365996</v>
+        <v>-27.74649561</v>
       </c>
       <c r="E89" t="n">
-        <v>931.00139862</v>
+        <v>26.98505922</v>
       </c>
       <c r="F89" t="n">
-        <v>1130.62755198</v>
+        <v>-38.69122119</v>
       </c>
       <c r="G89" t="n">
-        <v>77.14323940999999</v>
+        <v>8.909768119999999</v>
       </c>
       <c r="H89" t="n">
-        <v>123.34598509</v>
+        <v>55.5167993</v>
       </c>
       <c r="I89" t="n">
-        <v>-328.50834531</v>
+        <v>125.47551254</v>
       </c>
       <c r="J89" t="n">
-        <v>-266.28661612</v>
+        <v>130.46686756</v>
       </c>
       <c r="K89" t="n">
-        <v>-595.46834428</v>
+        <v>65.12027816</v>
       </c>
       <c r="L89" t="n">
-        <v>-484.0643838399999</v>
+        <v>-20.8718766</v>
       </c>
       <c r="M89" t="n">
-        <v>-380.73167867</v>
+        <v>-76.75126703000001</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業平</t>
+          <t>電子零組件業右上</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>1066.76281926</v>
+        <v>2535.16370684</v>
       </c>
       <c r="D90" t="n">
-        <v>1431.63135491</v>
+        <v>1754.35238786</v>
       </c>
       <c r="E90" t="n">
-        <v>394.77852725</v>
+        <v>725.1192927100001</v>
       </c>
       <c r="F90" t="n">
-        <v>-96.26091031</v>
+        <v>1890.14496335</v>
       </c>
       <c r="G90" t="n">
-        <v>-677.67515068</v>
+        <v>2886.93956966</v>
       </c>
       <c r="H90" t="n">
-        <v>-784.53746871</v>
+        <v>409.9676745900001</v>
       </c>
       <c r="I90" t="n">
-        <v>-672.7562283899999</v>
+        <v>3027.59866921</v>
       </c>
       <c r="J90" t="n">
-        <v>91.62525670000001</v>
+        <v>959.4811870999999</v>
       </c>
       <c r="K90" t="n">
-        <v>-680.17910633</v>
+        <v>921.8883400300001</v>
       </c>
       <c r="L90" t="n">
-        <v>-902.10415739</v>
+        <v>3745.82889977</v>
       </c>
       <c r="M90" t="n">
-        <v>-606.5519585200001</v>
+        <v>5233.41588458</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>電機機械右上</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr"/>
+          <t>電子零組件業右下</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>0</v>
+      </c>
       <c r="C91" t="n">
-        <v>-950.4535898400001</v>
+        <v>274.92690075</v>
       </c>
       <c r="D91" t="n">
-        <v>-380.51576305</v>
+        <v>132.4067022</v>
       </c>
       <c r="E91" t="n">
-        <v>-284.10655618</v>
+        <v>164.43456362</v>
       </c>
       <c r="F91" t="n">
-        <v>-260.54141641</v>
+        <v>65.63399751999999</v>
       </c>
       <c r="G91" t="n">
-        <v>-140.93046016</v>
+        <v>-6.879982530000001</v>
       </c>
       <c r="H91" t="n">
-        <v>231.47509598</v>
+        <v>-15.60161395</v>
       </c>
       <c r="I91" t="n">
-        <v>-1066.58062978</v>
+        <v>-16.00762839</v>
       </c>
       <c r="J91" t="n">
-        <v>-1058.24624676</v>
+        <v>-47.2644274</v>
       </c>
       <c r="K91" t="n">
-        <v>-312.1660538899999</v>
+        <v>-124.14966563</v>
       </c>
       <c r="L91" t="n">
-        <v>785.87981229</v>
+        <v>-106.07986476</v>
       </c>
       <c r="M91" t="n">
-        <v>-13.84784272</v>
+        <v>-61.85437630999999</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>電機機械右下</t>
+          <t>電子零組件業平</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>-34.19437538</v>
+        <v>481.77049984</v>
       </c>
       <c r="D92" t="n">
-        <v>-6.14492606</v>
+        <v>746.7007588699998</v>
       </c>
       <c r="E92" t="n">
-        <v>-41.9563862</v>
+        <v>809.64075587</v>
       </c>
       <c r="F92" t="n">
-        <v>13.21991144</v>
+        <v>-346.64333567</v>
       </c>
       <c r="G92" t="n">
-        <v>-60.03639301</v>
+        <v>-227.63665588</v>
       </c>
       <c r="H92" t="n">
-        <v>-99.56108504000001</v>
+        <v>-599.87995288</v>
       </c>
       <c r="I92" t="n">
-        <v>-27.59891615</v>
+        <v>-57.05884498</v>
       </c>
       <c r="J92" t="n">
-        <v>-2.575576679999994</v>
+        <v>-958.1662586899999</v>
       </c>
       <c r="K92" t="n">
-        <v>-67.59408645000001</v>
+        <v>-863.50434671</v>
       </c>
       <c r="L92" t="n">
-        <v>29.72607914</v>
+        <v>-873.4107989400001</v>
       </c>
       <c r="M92" t="n">
-        <v>29.64006926</v>
+        <v>-193.70222852</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>電機機械平</t>
+          <t>電機機械右上</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>279.11404862</v>
+        <v>59.08262594</v>
       </c>
       <c r="D93" t="n">
-        <v>394.2145801</v>
+        <v>-164.69119126</v>
       </c>
       <c r="E93" t="n">
-        <v>64.72958703</v>
+        <v>-128.95365214</v>
       </c>
       <c r="F93" t="n">
-        <v>190.86093327</v>
+        <v>185.34105938</v>
       </c>
       <c r="G93" t="n">
-        <v>322.22843422</v>
+        <v>303.03071299</v>
       </c>
       <c r="H93" t="n">
-        <v>181.86246472</v>
+        <v>-1127.25072354</v>
       </c>
       <c r="I93" t="n">
-        <v>-11.75397527</v>
+        <v>-1206.15067931</v>
       </c>
       <c r="J93" t="n">
-        <v>-52.08448736</v>
+        <v>-387.8413038099999</v>
       </c>
       <c r="K93" t="n">
-        <v>11.38814737</v>
+        <v>815.78799864</v>
       </c>
       <c r="L93" t="n">
-        <v>196.3704147</v>
+        <v>-141.74496392</v>
       </c>
       <c r="M93" t="n">
-        <v>29.85532934000002</v>
+        <v>56.89468007999999</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上</t>
+          <t>電機機械右下</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>-196.7993444</v>
+        <v>-6.14492606</v>
       </c>
       <c r="D94" t="n">
-        <v>1230.67429305</v>
+        <v>-41.9563862</v>
       </c>
       <c r="E94" t="n">
-        <v>736.97943814</v>
+        <v>13.21991144</v>
       </c>
       <c r="F94" t="n">
-        <v>980.9976145999998</v>
+        <v>-60.03639301</v>
       </c>
       <c r="G94" t="n">
-        <v>3039.80295137</v>
+        <v>-99.56108504000001</v>
       </c>
       <c r="H94" t="n">
-        <v>2679.37978635</v>
+        <v>-27.59891615</v>
       </c>
       <c r="I94" t="n">
-        <v>398.0836465900001</v>
+        <v>-2.575576679999994</v>
       </c>
       <c r="J94" t="n">
-        <v>4014.61282152</v>
+        <v>-67.59408645000001</v>
       </c>
       <c r="K94" t="n">
-        <v>1780.16211673</v>
+        <v>29.72607914</v>
       </c>
       <c r="L94" t="n">
-        <v>2571.08829643</v>
+        <v>29.64006926</v>
       </c>
       <c r="M94" t="n">
-        <v>3368.74259007</v>
+        <v>-30.16457714</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下</t>
+          <t>電機機械平</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>48.76066773</v>
+        <v>-45.38380889</v>
       </c>
       <c r="D95" t="n">
-        <v>92.55334615</v>
+        <v>-54.68577789</v>
       </c>
       <c r="E95" t="n">
-        <v>-56.81754067</v>
+        <v>59.273169</v>
       </c>
       <c r="F95" t="n">
-        <v>42.84140761</v>
+        <v>-4.04308532</v>
       </c>
       <c r="G95" t="n">
-        <v>-38.50834155000001</v>
+        <v>110.30684771</v>
       </c>
       <c r="H95" t="n">
-        <v>-20.42261438</v>
+        <v>48.91611849</v>
       </c>
       <c r="I95" t="n">
-        <v>27.43937357999999</v>
+        <v>95.81994519</v>
       </c>
       <c r="J95" t="n">
-        <v>249.26542335</v>
+        <v>87.06339729000001</v>
       </c>
       <c r="K95" t="n">
-        <v>5.814013070000001</v>
+        <v>166.46222835</v>
       </c>
       <c r="L95" t="n">
-        <v>-67.48752768000001</v>
+        <v>157.75245054</v>
       </c>
       <c r="M95" t="n">
-        <v>-298.07951644</v>
+        <v>70.98911336000002</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平</t>
+          <t>電腦及週邊設備業右上</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>-24.73421494</v>
+        <v>1273.52849336</v>
       </c>
       <c r="D96" t="n">
-        <v>25.07028257</v>
+        <v>646.76043126</v>
       </c>
       <c r="E96" t="n">
-        <v>-158.42628785</v>
+        <v>718.6346194299999</v>
       </c>
       <c r="F96" t="n">
-        <v>-241.65995044</v>
+        <v>2942.98355138</v>
       </c>
       <c r="G96" t="n">
-        <v>-46.64398937</v>
+        <v>2681.95247828</v>
       </c>
       <c r="H96" t="n">
-        <v>23.09129097</v>
+        <v>343.3241458</v>
       </c>
       <c r="I96" t="n">
-        <v>-53.61031266000001</v>
+        <v>4030.16582431</v>
       </c>
       <c r="J96" t="n">
-        <v>146.4341514</v>
+        <v>1729.38756114</v>
       </c>
       <c r="K96" t="n">
-        <v>-24.65351684000001</v>
+        <v>2625.1180385</v>
       </c>
       <c r="L96" t="n">
-        <v>147.93520375</v>
+        <v>3441.32132545</v>
       </c>
       <c r="M96" t="n">
-        <v>24.74986286</v>
+        <v>3032.12116609</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>食品工業右上</t>
+          <t>電腦及週邊設備業右下</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>-37.07627961999999</v>
+        <v>93.21859898</v>
       </c>
       <c r="D97" t="n">
-        <v>-30.0684443</v>
+        <v>-55.76555674</v>
       </c>
       <c r="E97" t="n">
-        <v>-26.68637467</v>
+        <v>44.23255601</v>
       </c>
       <c r="F97" t="n">
-        <v>-23.61144785</v>
+        <v>-38.08882206000001</v>
       </c>
       <c r="G97" t="n">
-        <v>-20.82561255</v>
+        <v>-20.67808733</v>
       </c>
       <c r="H97" t="n">
-        <v>-15.11323943</v>
+        <v>27.94534482</v>
       </c>
       <c r="I97" t="n">
-        <v>2.576522849999999</v>
+        <v>250.15528983</v>
       </c>
       <c r="J97" t="n">
-        <v>17.61782424</v>
+        <v>7.289573850000001</v>
       </c>
       <c r="K97" t="n">
-        <v>27.3651653</v>
+        <v>-66.99732744000001</v>
       </c>
       <c r="L97" t="n">
-        <v>21.46185849</v>
+        <v>-298.0557950200001</v>
       </c>
       <c r="M97" t="n">
-        <v>2.43374669</v>
+        <v>-489.15865882</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>食品工業右下</t>
+          <t>電腦及週邊設備業平</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
-        <v>-8.586387240000001</v>
+        <v>-18.44917057</v>
       </c>
       <c r="D98" t="n">
-        <v>-10.56307657</v>
+        <v>-69.25926489999999</v>
       </c>
       <c r="E98" t="n">
-        <v>-11.32923905</v>
+        <v>19.31189633</v>
       </c>
       <c r="F98" t="n">
-        <v>2.98401102</v>
+        <v>49.75589112999999</v>
       </c>
       <c r="G98" t="n">
-        <v>1.30875266</v>
+        <v>20.77407199</v>
       </c>
       <c r="H98" t="n">
-        <v>-3.510710399999999</v>
+        <v>0.6432168899999976</v>
       </c>
       <c r="I98" t="n">
-        <v>10.10491649</v>
+        <v>129.99128213</v>
       </c>
       <c r="J98" t="n">
-        <v>13.23640147</v>
+        <v>24.64547797</v>
       </c>
       <c r="K98" t="n">
-        <v>17.26166795</v>
+        <v>93.41526143999999</v>
       </c>
       <c r="L98" t="n">
-        <v>6.075726189999999</v>
+        <v>-47.85259394</v>
       </c>
       <c r="M98" t="n">
-        <v>-1.47041395</v>
+        <v>-63.48290797</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>食品工業平</t>
+          <t>食品工業右上</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>-186.51495697</v>
+        <v>-30.06779766</v>
       </c>
       <c r="D99" t="n">
-        <v>-265.95018013</v>
+        <v>-26.68584296</v>
       </c>
       <c r="E99" t="n">
-        <v>-277.00332726</v>
+        <v>-23.61119333</v>
       </c>
       <c r="F99" t="n">
-        <v>-161.75931291</v>
+        <v>-20.82516393</v>
       </c>
       <c r="G99" t="n">
-        <v>-234.05456839</v>
+        <v>-15.11263473</v>
       </c>
       <c r="H99" t="n">
-        <v>-116.13037273</v>
+        <v>2.57676404</v>
       </c>
       <c r="I99" t="n">
-        <v>-28.18976328</v>
+        <v>17.61770092</v>
       </c>
       <c r="J99" t="n">
-        <v>-51.69699644</v>
+        <v>27.36522565</v>
       </c>
       <c r="K99" t="n">
-        <v>-94.32087193</v>
+        <v>21.462162</v>
       </c>
       <c r="L99" t="n">
-        <v>-157.36500734</v>
+        <v>2.43355516</v>
       </c>
       <c r="M99" t="n">
-        <v>-218.54955489</v>
+        <v>3.428873750000001</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>食品工業右下</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
+      <c r="C100" t="n">
+        <v>-10.56322777</v>
+      </c>
+      <c r="D100" t="n">
+        <v>-11.32936548</v>
+      </c>
+      <c r="E100" t="n">
+        <v>2.9838397</v>
+      </c>
+      <c r="F100" t="n">
+        <v>1.30858839</v>
+      </c>
+      <c r="G100" t="n">
+        <v>-3.510833229999999</v>
+      </c>
+      <c r="H100" t="n">
+        <v>10.104738</v>
+      </c>
+      <c r="I100" t="n">
+        <v>13.23628785</v>
+      </c>
+      <c r="J100" t="n">
+        <v>17.2616073</v>
+      </c>
+      <c r="K100" t="n">
+        <v>6.075689359999999</v>
+      </c>
+      <c r="L100" t="n">
+        <v>-1.47053638</v>
+      </c>
+      <c r="M100" t="n">
+        <v>-12.68556489</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>食品工業平</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
+      <c r="C101" t="n">
+        <v>-265.95067557</v>
+      </c>
+      <c r="D101" t="n">
+        <v>-277.00373254</v>
+      </c>
+      <c r="E101" t="n">
+        <v>-161.75939611</v>
+      </c>
+      <c r="F101" t="n">
+        <v>-234.05485274</v>
+      </c>
+      <c r="G101" t="n">
+        <v>-116.1308546</v>
+      </c>
+      <c r="H101" t="n">
+        <v>-28.18982598</v>
+      </c>
+      <c r="I101" t="n">
+        <v>-51.69675949999999</v>
+      </c>
+      <c r="J101" t="n">
+        <v>-94.32087163</v>
+      </c>
+      <c r="K101" t="n">
+        <v>-157.36527402</v>
+      </c>
+      <c r="L101" t="n">
+        <v>-218.54924093</v>
+      </c>
+      <c r="M101" t="n">
+        <v>-239.31743868</v>
       </c>
     </row>
   </sheetData>

--- a/Result/analyze_2.xlsx
+++ b/Result/analyze_2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M101"/>
+  <dimension ref="A1:M100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-13</t>
         </is>
       </c>
     </row>
@@ -503,37 +503,37 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>349.94285983</v>
+        <v>262.27963268</v>
       </c>
       <c r="D2" t="n">
-        <v>-50.48565993</v>
+        <v>621.91176462</v>
       </c>
       <c r="E2" t="n">
-        <v>245.94945238</v>
+        <v>674.7170971199999</v>
       </c>
       <c r="F2" t="n">
-        <v>594.58673208</v>
+        <v>970.13274813</v>
       </c>
       <c r="G2" t="n">
-        <v>666.80052754</v>
+        <v>1847.20645299</v>
       </c>
       <c r="H2" t="n">
-        <v>970.63023904</v>
+        <v>1090.09580616</v>
       </c>
       <c r="I2" t="n">
-        <v>1867.28884575</v>
+        <v>152.20944048</v>
       </c>
       <c r="J2" t="n">
-        <v>1102.54176427</v>
+        <v>727.30452817</v>
       </c>
       <c r="K2" t="n">
-        <v>160.36199751</v>
+        <v>787.25271681</v>
       </c>
       <c r="L2" t="n">
-        <v>696.2803910299999</v>
+        <v>709.64192214</v>
       </c>
       <c r="M2" t="n">
-        <v>812.99425622</v>
+        <v>1783.52327864</v>
       </c>
     </row>
     <row r="3">
@@ -544,37 +544,37 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>191.87176472</v>
+        <v>147.49896984</v>
       </c>
       <c r="D3" t="n">
-        <v>84.59307114000001</v>
+        <v>0.2643849900000007</v>
       </c>
       <c r="E3" t="n">
-        <v>147.49896984</v>
+        <v>-20.16331824</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2643849900000007</v>
+        <v>108.99614624</v>
       </c>
       <c r="G3" t="n">
-        <v>-20.16331824</v>
+        <v>218.62774389</v>
       </c>
       <c r="H3" t="n">
-        <v>108.99614624</v>
+        <v>151.67850938</v>
       </c>
       <c r="I3" t="n">
-        <v>218.62774389</v>
+        <v>50.43801889</v>
       </c>
       <c r="J3" t="n">
-        <v>151.67850938</v>
+        <v>-71.88062519</v>
       </c>
       <c r="K3" t="n">
-        <v>50.43801889</v>
+        <v>18.3918283</v>
       </c>
       <c r="L3" t="n">
-        <v>-71.88062519</v>
+        <v>118.11633031</v>
       </c>
       <c r="M3" t="n">
-        <v>18.3918283</v>
+        <v>114.91389364</v>
       </c>
     </row>
     <row r="4">
@@ -585,37 +585,37 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>-3.510394429999991</v>
+        <v>-54.03002938000001</v>
       </c>
       <c r="D4" t="n">
-        <v>-113.87668264</v>
+        <v>-158.08994697</v>
       </c>
       <c r="E4" t="n">
-        <v>-37.69984908000001</v>
+        <v>-198.46347347</v>
       </c>
       <c r="F4" t="n">
-        <v>-130.76491443</v>
+        <v>-45.33545444</v>
       </c>
       <c r="G4" t="n">
-        <v>-190.54690389</v>
+        <v>105.60072715</v>
       </c>
       <c r="H4" t="n">
-        <v>-45.83294535</v>
+        <v>36.28501871</v>
       </c>
       <c r="I4" t="n">
-        <v>85.51833439000001</v>
+        <v>219.22014594</v>
       </c>
       <c r="J4" t="n">
-        <v>23.83906059999999</v>
+        <v>-49.53044652</v>
       </c>
       <c r="K4" t="n">
-        <v>211.06758891</v>
+        <v>28.60477997000001</v>
       </c>
       <c r="L4" t="n">
-        <v>-18.50630938</v>
+        <v>-1.130153140000016</v>
       </c>
       <c r="M4" t="n">
-        <v>2.863240560000006</v>
+        <v>-48.71721795999999</v>
       </c>
     </row>
     <row r="5">
@@ -626,37 +626,37 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>758.27988239</v>
+        <v>1311.6789827</v>
       </c>
       <c r="D5" t="n">
-        <v>802.10536136</v>
+        <v>1402.6094384</v>
       </c>
       <c r="E5" t="n">
-        <v>1311.67929021</v>
+        <v>947.17776913</v>
       </c>
       <c r="F5" t="n">
-        <v>1402.60968035</v>
+        <v>633.9211675299999</v>
       </c>
       <c r="G5" t="n">
-        <v>947.1777888099999</v>
+        <v>146.03440984</v>
       </c>
       <c r="H5" t="n">
-        <v>633.92100185</v>
+        <v>-38.63469054000001</v>
       </c>
       <c r="I5" t="n">
-        <v>146.03438519</v>
+        <v>-259.31952002</v>
       </c>
       <c r="J5" t="n">
-        <v>-38.63471579000001</v>
+        <v>-387.10507082</v>
       </c>
       <c r="K5" t="n">
-        <v>-259.31947403</v>
+        <v>-428.41055059</v>
       </c>
       <c r="L5" t="n">
-        <v>-387.10504069</v>
+        <v>-414.44012063</v>
       </c>
       <c r="M5" t="n">
-        <v>-428.41081447</v>
+        <v>-488.47392939</v>
       </c>
     </row>
     <row r="6">
@@ -667,37 +667,37 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>-36.48480923</v>
+        <v>-51.13695541</v>
       </c>
       <c r="D6" t="n">
-        <v>-50.54285925</v>
+        <v>-141.00929526</v>
       </c>
       <c r="E6" t="n">
-        <v>-51.16288267</v>
+        <v>-65.26154403</v>
       </c>
       <c r="F6" t="n">
-        <v>-140.95221625</v>
+        <v>62.04500406999999</v>
       </c>
       <c r="G6" t="n">
-        <v>-65.33410428999998</v>
+        <v>11.78770847</v>
       </c>
       <c r="H6" t="n">
-        <v>61.92312819</v>
+        <v>18.84798607</v>
       </c>
       <c r="I6" t="n">
-        <v>11.70978589</v>
+        <v>63.41058579</v>
       </c>
       <c r="J6" t="n">
-        <v>17.56788924</v>
+        <v>80.62499681</v>
       </c>
       <c r="K6" t="n">
-        <v>63.33664330999999</v>
+        <v>81.45993682000001</v>
       </c>
       <c r="L6" t="n">
-        <v>80.28996298999999</v>
+        <v>70.53339803</v>
       </c>
       <c r="M6" t="n">
-        <v>82.10961921000001</v>
+        <v>154.79530516</v>
       </c>
     </row>
     <row r="7">
@@ -708,37 +708,37 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>18.05669134</v>
+        <v>23.34243293</v>
       </c>
       <c r="D7" t="n">
-        <v>12.93458089</v>
+        <v>8.34951197</v>
       </c>
       <c r="E7" t="n">
-        <v>23.36805268</v>
+        <v>8.191339730000003</v>
       </c>
       <c r="F7" t="n">
-        <v>8.29219101</v>
+        <v>10.73662403</v>
       </c>
       <c r="G7" t="n">
-        <v>8.107017110000001</v>
+        <v>12.01709187</v>
       </c>
       <c r="H7" t="n">
-        <v>10.62519958</v>
+        <v>19.79486985</v>
       </c>
       <c r="I7" t="n">
-        <v>11.86739087</v>
+        <v>0.6761040199999977</v>
       </c>
       <c r="J7" t="n">
-        <v>20.20976285</v>
+        <v>-11.2907794</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2861774399999976</v>
+        <v>-41.80932144</v>
       </c>
       <c r="L7" t="n">
-        <v>-11.25823577</v>
+        <v>-34.71912384</v>
       </c>
       <c r="M7" t="n">
-        <v>-42.56794475</v>
+        <v>-30.00408671</v>
       </c>
     </row>
     <row r="8">
@@ -749,37 +749,37 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>1786.62327224</v>
+        <v>-148.70606176</v>
       </c>
       <c r="D8" t="n">
-        <v>266.15349545</v>
+        <v>1476.56908614</v>
       </c>
       <c r="E8" t="n">
-        <v>-147.9823112199999</v>
+        <v>2293.90645356</v>
       </c>
       <c r="F8" t="n">
-        <v>1475.91380527</v>
+        <v>1075.83236819</v>
       </c>
       <c r="G8" t="n">
-        <v>2294.25615025</v>
+        <v>1228.30997512</v>
       </c>
       <c r="H8" t="n">
-        <v>1074.80943465</v>
+        <v>1242.73536522</v>
       </c>
       <c r="I8" t="n">
-        <v>1225.86441528</v>
+        <v>3055.28122897</v>
       </c>
       <c r="J8" t="n">
-        <v>1237.92462887</v>
+        <v>3152.68677979</v>
       </c>
       <c r="K8" t="n">
-        <v>3053.75359068</v>
+        <v>3698.39980366</v>
       </c>
       <c r="L8" t="n">
-        <v>3150.11538454</v>
+        <v>840.28728211</v>
       </c>
       <c r="M8" t="n">
-        <v>3699.4158208</v>
+        <v>2512.778153</v>
       </c>
     </row>
     <row r="9">
@@ -788,41 +788,39 @@
           <t>其他電子業右下</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1.00886186</v>
+        <v>19.26401315</v>
       </c>
       <c r="D9" t="n">
-        <v>7.754908189999999</v>
+        <v>-16.93993281</v>
       </c>
       <c r="E9" t="n">
-        <v>19.5437169</v>
+        <v>39.37455131</v>
       </c>
       <c r="F9" t="n">
-        <v>-16.87157023</v>
+        <v>36.7864105</v>
       </c>
       <c r="G9" t="n">
-        <v>39.32909103</v>
+        <v>40.08066302</v>
       </c>
       <c r="H9" t="n">
-        <v>36.6410556</v>
+        <v>-1.64290466</v>
       </c>
       <c r="I9" t="n">
-        <v>39.82731007</v>
+        <v>12.49313254</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.71674819</v>
+        <v>-56.5111112</v>
       </c>
       <c r="K9" t="n">
-        <v>12.39743227</v>
+        <v>-83.09150933000001</v>
       </c>
       <c r="L9" t="n">
-        <v>-56.67850128</v>
+        <v>-91.21407562</v>
       </c>
       <c r="M9" t="n">
-        <v>-82.45109039000002</v>
+        <v>-123.56078289</v>
       </c>
     </row>
     <row r="10">
@@ -833,37 +831,37 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>-30.39800455</v>
+        <v>-25.52413804</v>
       </c>
       <c r="D10" t="n">
-        <v>-79.66322145000001</v>
+        <v>-53.17312618</v>
       </c>
       <c r="E10" t="n">
-        <v>-26.56333222</v>
+        <v>-10.03953893</v>
       </c>
       <c r="F10" t="n">
-        <v>-52.59087204000001</v>
+        <v>39.36854109</v>
       </c>
       <c r="G10" t="n">
-        <v>-10.33104969000001</v>
+        <v>81.53636237000001</v>
       </c>
       <c r="H10" t="n">
-        <v>40.56151774</v>
+        <v>-0.5891320599999984</v>
       </c>
       <c r="I10" t="n">
-        <v>84.25090496</v>
+        <v>43.23008384000001</v>
       </c>
       <c r="J10" t="n">
-        <v>4.334741170000002</v>
+        <v>40.93310478</v>
       </c>
       <c r="K10" t="n">
-        <v>44.87638554</v>
+        <v>-12.55230394</v>
       </c>
       <c r="L10" t="n">
-        <v>43.68914278</v>
+        <v>-62.70918614</v>
       </c>
       <c r="M10" t="n">
-        <v>-14.18799322</v>
+        <v>-55.88911530999999</v>
       </c>
     </row>
     <row r="11">
@@ -874,37 +872,37 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>73.34760937999999</v>
+        <v>65.49933337</v>
       </c>
       <c r="D11" t="n">
-        <v>17.68913908</v>
+        <v>140.90982914</v>
       </c>
       <c r="E11" t="n">
-        <v>64.27134692</v>
+        <v>57.1766969</v>
       </c>
       <c r="F11" t="n">
-        <v>134.93953454</v>
+        <v>65.09250018</v>
       </c>
       <c r="G11" t="n">
-        <v>59.07640434</v>
+        <v>0.5197492700000006</v>
       </c>
       <c r="H11" t="n">
-        <v>58.26191486</v>
+        <v>-62.86999651</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.60021218</v>
+        <v>-89.29810446</v>
       </c>
       <c r="J11" t="n">
-        <v>-56.15711423999999</v>
+        <v>-73.05729255</v>
       </c>
       <c r="K11" t="n">
-        <v>-77.84830054000001</v>
+        <v>-11.72490653000001</v>
       </c>
       <c r="L11" t="n">
-        <v>-69.04629460000001</v>
+        <v>31.05005041</v>
       </c>
       <c r="M11" t="n">
-        <v>-25.69211605</v>
+        <v>-180.95019354</v>
       </c>
     </row>
     <row r="12">
@@ -915,37 +913,37 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>35.07161981</v>
+        <v>121.89913691</v>
       </c>
       <c r="D12" t="n">
-        <v>-55.30950838</v>
+        <v>-3.193201080000001</v>
       </c>
       <c r="E12" t="n">
-        <v>108.46396057</v>
+        <v>-78.9334088</v>
       </c>
       <c r="F12" t="n">
-        <v>-14.9723182</v>
+        <v>-41.43368870999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-75.27318078</v>
+        <v>-102.00764632</v>
       </c>
       <c r="H12" t="n">
-        <v>-101.53357454</v>
+        <v>-106.15040842</v>
       </c>
       <c r="I12" t="n">
-        <v>-80.67289115999999</v>
+        <v>-22.38016029999999</v>
       </c>
       <c r="J12" t="n">
-        <v>-48.53014978</v>
+        <v>360.0173907299999</v>
       </c>
       <c r="K12" t="n">
-        <v>-62.99231673999999</v>
+        <v>239.49133427</v>
       </c>
       <c r="L12" t="n">
-        <v>255.29889573</v>
+        <v>173.03014541</v>
       </c>
       <c r="M12" t="n">
-        <v>83.30783427999999</v>
+        <v>-44.2824068</v>
       </c>
     </row>
     <row r="13">
@@ -956,37 +954,37 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>9.1288567</v>
+        <v>-8.040024430000001</v>
       </c>
       <c r="D13" t="n">
-        <v>-17.38670165</v>
+        <v>-0.2923396999999996</v>
       </c>
       <c r="E13" t="n">
-        <v>6.62313836</v>
+        <v>3.17078258</v>
       </c>
       <c r="F13" t="n">
-        <v>17.45707202</v>
+        <v>-5.907358479999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.38915288</v>
+        <v>-13.9502932</v>
       </c>
       <c r="H13" t="n">
-        <v>61.02311267</v>
+        <v>3.04297447</v>
       </c>
       <c r="I13" t="n">
-        <v>-33.16508691</v>
+        <v>7.67957594</v>
       </c>
       <c r="J13" t="n">
-        <v>-61.29016644</v>
+        <v>-5.899052060000001</v>
       </c>
       <c r="K13" t="n">
-        <v>36.84192846</v>
+        <v>-2.14310862</v>
       </c>
       <c r="L13" t="n">
-        <v>94.80844499</v>
+        <v>21.88574365</v>
       </c>
       <c r="M13" t="n">
-        <v>168.00760089</v>
+        <v>43.17843798</v>
       </c>
     </row>
     <row r="14">
@@ -997,37 +995,37 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>-8021.18710023</v>
+        <v>-5535.98562555</v>
       </c>
       <c r="D14" t="n">
-        <v>-11779.66299903</v>
+        <v>-658.0841553300002</v>
       </c>
       <c r="E14" t="n">
-        <v>-5670.27156687</v>
+        <v>-4001.93109319</v>
       </c>
       <c r="F14" t="n">
-        <v>-624.0224289900003</v>
+        <v>-5978.31957158</v>
       </c>
       <c r="G14" t="n">
-        <v>-4448.64816188</v>
+        <v>-1092.19583828</v>
       </c>
       <c r="H14" t="n">
-        <v>-6496.484548560001</v>
+        <v>-3890.94390022</v>
       </c>
       <c r="I14" t="n">
-        <v>-1624.94800481</v>
+        <v>5256.24524152</v>
       </c>
       <c r="J14" t="n">
-        <v>-4347.44692024</v>
+        <v>1678.88706639</v>
       </c>
       <c r="K14" t="n">
-        <v>5116.89556286</v>
+        <v>7048.85128128</v>
       </c>
       <c r="L14" t="n">
-        <v>1770.36109075</v>
+        <v>3617.835917129999</v>
       </c>
       <c r="M14" t="n">
-        <v>7381.87680709</v>
+        <v>7480.86293599</v>
       </c>
     </row>
     <row r="15">
@@ -1040,37 +1038,37 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>415.55163195</v>
+        <v>-86.36146058</v>
       </c>
       <c r="D15" t="n">
-        <v>-54.42527297000004</v>
+        <v>-602.33041612</v>
       </c>
       <c r="E15" t="n">
-        <v>-6.453203729999995</v>
+        <v>8.812711690000006</v>
       </c>
       <c r="F15" t="n">
-        <v>-673.9294293300001</v>
+        <v>-113.70895621</v>
       </c>
       <c r="G15" t="n">
-        <v>-224.13764096</v>
+        <v>877.88284232</v>
       </c>
       <c r="H15" t="n">
-        <v>-180.72158482</v>
+        <v>1.19436815999998</v>
       </c>
       <c r="I15" t="n">
-        <v>521.20736035</v>
+        <v>-256.58128448</v>
       </c>
       <c r="J15" t="n">
-        <v>-99.65401256000001</v>
+        <v>33.95014528000004</v>
       </c>
       <c r="K15" t="n">
-        <v>-336.46048777</v>
+        <v>-645.3038545400001</v>
       </c>
       <c r="L15" t="n">
-        <v>290.82002466</v>
+        <v>333.00948395</v>
       </c>
       <c r="M15" t="n">
-        <v>-151.79652597</v>
+        <v>-12.58744067999995</v>
       </c>
     </row>
     <row r="16">
@@ -1081,37 +1079,37 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>-9.631972939999994</v>
+        <v>-238.6301166</v>
       </c>
       <c r="D16" t="n">
-        <v>301.10038523</v>
+        <v>30.90868662</v>
       </c>
       <c r="E16" t="n">
-        <v>-273.31100431</v>
+        <v>-213.22392075</v>
       </c>
       <c r="F16" t="n">
-        <v>-127.25782837</v>
+        <v>-546.1150724600001</v>
       </c>
       <c r="G16" t="n">
-        <v>251.95209464</v>
+        <v>-815.9856730299999</v>
       </c>
       <c r="H16" t="n">
-        <v>-160.16176203</v>
+        <v>-900.6945041700001</v>
       </c>
       <c r="I16" t="n">
-        <v>-95.13206553000003</v>
+        <v>-318.48843623</v>
       </c>
       <c r="J16" t="n">
-        <v>-496.80833901</v>
+        <v>-1.957435519999996</v>
       </c>
       <c r="K16" t="n">
-        <v>-125.36432627</v>
+        <v>470.0650154399999</v>
       </c>
       <c r="L16" t="n">
-        <v>-398.24590544</v>
+        <v>335.10144141</v>
       </c>
       <c r="M16" t="n">
-        <v>-405.94523872</v>
+        <v>187.51669966</v>
       </c>
     </row>
     <row r="17">
@@ -1122,37 +1120,37 @@
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
-        <v>-0.10265735</v>
+        <v>-0.03467238</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.09269372000000001</v>
+        <v>-0.04065686</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.03467238</v>
+        <v>0.0011402</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.04065686</v>
+        <v>0.03352323</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0011402</v>
+        <v>0.00050968</v>
       </c>
       <c r="H17" t="n">
-        <v>0.03352323</v>
+        <v>-0.01056853</v>
       </c>
       <c r="I17" t="n">
-        <v>0.00050968</v>
+        <v>0.00352167</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.01056853</v>
+        <v>0.01775949</v>
       </c>
       <c r="K17" t="n">
-        <v>0.00352167</v>
+        <v>0.0402896</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01775949</v>
+        <v>-0.04455849</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0402896</v>
+        <v>0.07666569000000001</v>
       </c>
     </row>
     <row r="18">
@@ -1163,37 +1161,37 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>797.0432088700001</v>
+        <v>949.17323245</v>
       </c>
       <c r="D18" t="n">
-        <v>-142.28295233</v>
+        <v>786.6830428600001</v>
       </c>
       <c r="E18" t="n">
-        <v>949.17323245</v>
+        <v>-272.85884179</v>
       </c>
       <c r="F18" t="n">
-        <v>786.6830428600001</v>
+        <v>-871.1229194199999</v>
       </c>
       <c r="G18" t="n">
-        <v>-272.85884179</v>
+        <v>-1069.81135742</v>
       </c>
       <c r="H18" t="n">
-        <v>-871.1229194199999</v>
+        <v>-452.58295967</v>
       </c>
       <c r="I18" t="n">
-        <v>-1069.81135742</v>
+        <v>-531.6617434799999</v>
       </c>
       <c r="J18" t="n">
-        <v>-452.58295967</v>
+        <v>-603.5171211700001</v>
       </c>
       <c r="K18" t="n">
-        <v>-531.6617434799999</v>
+        <v>-1.170012629999998</v>
       </c>
       <c r="L18" t="n">
-        <v>-603.5171211700001</v>
+        <v>755.74136299</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.170012629999998</v>
+        <v>808.41838966</v>
       </c>
     </row>
     <row r="19">
@@ -1204,37 +1202,37 @@
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>-3.98792682</v>
+        <v>-2.35624874</v>
       </c>
       <c r="D19" t="n">
-        <v>-8.90454609</v>
+        <v>-4.667060340000001</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.35624874</v>
+        <v>-3.87635555</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.667060340000001</v>
+        <v>-1.02180052</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.87635555</v>
+        <v>-2.53850894</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.02180052</v>
+        <v>0.4005523000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.53850894</v>
+        <v>-5.227267410000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4005523000000001</v>
+        <v>-15.88088372</v>
       </c>
       <c r="K19" t="n">
-        <v>-5.227267410000001</v>
+        <v>-17.52423777</v>
       </c>
       <c r="L19" t="n">
-        <v>-15.88088372</v>
+        <v>-10.84451686</v>
       </c>
       <c r="M19" t="n">
-        <v>-17.52423777</v>
+        <v>-2.39038121</v>
       </c>
     </row>
     <row r="20">
@@ -1245,37 +1243,37 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>49.79108182</v>
+        <v>43.34600284999999</v>
       </c>
       <c r="D20" t="n">
-        <v>15.83999259</v>
+        <v>-20.57369556</v>
       </c>
       <c r="E20" t="n">
-        <v>43.34600284999999</v>
+        <v>-26.64337471</v>
       </c>
       <c r="F20" t="n">
-        <v>-20.57369556</v>
+        <v>-8.6719104</v>
       </c>
       <c r="G20" t="n">
-        <v>-26.64337471</v>
+        <v>6.29112816</v>
       </c>
       <c r="H20" t="n">
-        <v>-8.6719104</v>
+        <v>-11.38791094</v>
       </c>
       <c r="I20" t="n">
-        <v>6.29112816</v>
+        <v>39.90390299</v>
       </c>
       <c r="J20" t="n">
-        <v>-11.38791094</v>
+        <v>-7.499015480000001</v>
       </c>
       <c r="K20" t="n">
-        <v>39.90390299</v>
+        <v>-34.65196079</v>
       </c>
       <c r="L20" t="n">
-        <v>-7.499015480000001</v>
+        <v>-20.07586818</v>
       </c>
       <c r="M20" t="n">
-        <v>-34.65196079</v>
+        <v>37.03994246</v>
       </c>
     </row>
     <row r="21">
@@ -1286,37 +1284,37 @@
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
-        <v>0.47642728</v>
+        <v>1.01545869</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.38489539</v>
+        <v>-0.08711676000000002</v>
       </c>
       <c r="E21" t="n">
-        <v>1.01578957</v>
+        <v>1.98363663</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.08695448000000001</v>
+        <v>2.62524275</v>
       </c>
       <c r="G21" t="n">
-        <v>1.98383284</v>
+        <v>2.39378135</v>
       </c>
       <c r="H21" t="n">
-        <v>2.625483</v>
+        <v>2.61607538</v>
       </c>
       <c r="I21" t="n">
-        <v>2.3940447</v>
+        <v>1.28640456</v>
       </c>
       <c r="J21" t="n">
-        <v>2.61609992</v>
+        <v>-2.43901558</v>
       </c>
       <c r="K21" t="n">
-        <v>1.28616441</v>
+        <v>-7.15590988</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.43946403</v>
+        <v>-1.96261004</v>
       </c>
       <c r="M21" t="n">
-        <v>-7.15914957</v>
+        <v>-1.02451533</v>
       </c>
     </row>
     <row r="22">
@@ -1327,37 +1325,37 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>0.4000347</v>
+        <v>0.11370021</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.11080264</v>
+        <v>0.08731186000000006</v>
       </c>
       <c r="E22" t="n">
-        <v>0.11370021</v>
+        <v>1.53302582</v>
       </c>
       <c r="F22" t="n">
-        <v>0.08731186000000006</v>
+        <v>2.46990344</v>
       </c>
       <c r="G22" t="n">
-        <v>1.53302582</v>
+        <v>1.61393472</v>
       </c>
       <c r="H22" t="n">
-        <v>2.46990344</v>
+        <v>1.84202241</v>
       </c>
       <c r="I22" t="n">
-        <v>1.61393472</v>
+        <v>2.06787124</v>
       </c>
       <c r="J22" t="n">
-        <v>1.84202241</v>
+        <v>2.13334684</v>
       </c>
       <c r="K22" t="n">
-        <v>2.06787124</v>
+        <v>0.9929304</v>
       </c>
       <c r="L22" t="n">
-        <v>2.13334684</v>
+        <v>-0.03632950000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>0.9929304</v>
+        <v>0.96950563</v>
       </c>
     </row>
     <row r="23">
@@ -1368,37 +1366,37 @@
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
-        <v>11.84440164</v>
+        <v>2.279171630000002</v>
       </c>
       <c r="D23" t="n">
-        <v>-23.12302004</v>
+        <v>-0.2745837299999978</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.9094807799999995</v>
+        <v>-8.598820600000002</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5220866800000026</v>
+        <v>30.33780378</v>
       </c>
       <c r="G23" t="n">
-        <v>-11.60290924</v>
+        <v>29.55377318</v>
       </c>
       <c r="H23" t="n">
-        <v>24.20836844</v>
+        <v>14.81809427</v>
       </c>
       <c r="I23" t="n">
-        <v>28.28368726</v>
+        <v>2.2237342</v>
       </c>
       <c r="J23" t="n">
-        <v>11.25997404</v>
+        <v>5.296906070000001</v>
       </c>
       <c r="K23" t="n">
-        <v>2.312601040000001</v>
+        <v>25.09193065</v>
       </c>
       <c r="L23" t="n">
-        <v>7.41955448</v>
+        <v>54.47860323</v>
       </c>
       <c r="M23" t="n">
-        <v>26.59317097</v>
+        <v>66.45411108</v>
       </c>
     </row>
     <row r="24">
@@ -1409,37 +1407,37 @@
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
-        <v>-93.28730779</v>
+        <v>-93.22952265000001</v>
       </c>
       <c r="D24" t="n">
-        <v>-105.4288386</v>
+        <v>-90.70000823000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-77.88456595000001</v>
+        <v>-6.2809364</v>
       </c>
       <c r="F24" t="n">
-        <v>-65.37887472</v>
+        <v>86.20473114000001</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.07799874</v>
+        <v>29.54057057</v>
       </c>
       <c r="H24" t="n">
-        <v>63.41788019</v>
+        <v>15.57147579</v>
       </c>
       <c r="I24" t="n">
-        <v>27.87193822</v>
+        <v>-19.0600271</v>
       </c>
       <c r="J24" t="n">
-        <v>17.49109479</v>
+        <v>-41.61633796</v>
       </c>
       <c r="K24" t="n">
-        <v>-11.95157945</v>
+        <v>-42.96796366</v>
       </c>
       <c r="L24" t="n">
-        <v>-30.21774896000001</v>
+        <v>-44.10190735</v>
       </c>
       <c r="M24" t="n">
-        <v>-29.35515905</v>
+        <v>-27.06907343</v>
       </c>
     </row>
     <row r="25">
@@ -1450,37 +1448,37 @@
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>-58.36615088</v>
+        <v>-50.65754586</v>
       </c>
       <c r="D25" t="n">
-        <v>-93.99017655</v>
+        <v>-58.89799474</v>
       </c>
       <c r="E25" t="n">
-        <v>-62.81385015</v>
+        <v>-6.72338039</v>
       </c>
       <c r="F25" t="n">
-        <v>-85.01579866</v>
+        <v>59.7817317</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.922229410000001</v>
+        <v>17.96592688</v>
       </c>
       <c r="H25" t="n">
-        <v>88.69801799</v>
+        <v>40.41086968</v>
       </c>
       <c r="I25" t="n">
-        <v>20.90464515</v>
+        <v>41.14958434</v>
       </c>
       <c r="J25" t="n">
-        <v>42.04937090999999</v>
+        <v>17.03295293</v>
       </c>
       <c r="K25" t="n">
-        <v>33.95226985</v>
+        <v>8.617214629999999</v>
       </c>
       <c r="L25" t="n">
-        <v>3.511715520000001</v>
+        <v>11.34909846</v>
       </c>
       <c r="M25" t="n">
-        <v>-6.496830300000003</v>
+        <v>45.72187033000001</v>
       </c>
     </row>
     <row r="26">
@@ -1491,37 +1489,37 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>-5.3701208</v>
+        <v>0.06516363999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.58681387</v>
+        <v>-0.14909701</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.07064465</v>
+        <v>7.807659770000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.4004080399999999</v>
+        <v>3.90290423</v>
       </c>
       <c r="G26" t="n">
-        <v>7.61994909</v>
+        <v>8.67842671</v>
       </c>
       <c r="H26" t="n">
-        <v>3.95032609</v>
+        <v>5.4001713</v>
       </c>
       <c r="I26" t="n">
-        <v>8.953404039999999</v>
+        <v>6.494961730000001</v>
       </c>
       <c r="J26" t="n">
-        <v>5.887683269999999</v>
+        <v>3.30757135</v>
       </c>
       <c r="K26" t="n">
-        <v>7.59334499</v>
+        <v>5.568523260000001</v>
       </c>
       <c r="L26" t="n">
-        <v>5.17034791</v>
+        <v>16.69468449</v>
       </c>
       <c r="M26" t="n">
-        <v>7.59349848</v>
+        <v>6.11848527</v>
       </c>
     </row>
     <row r="27">
@@ -1530,39 +1528,41 @@
           <t>數位雲端右下</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
       <c r="C27" t="n">
-        <v>16.88570324</v>
+        <v>10.21874138</v>
       </c>
       <c r="D27" t="n">
-        <v>5.174999509999999</v>
+        <v>5.178023819999999</v>
       </c>
       <c r="E27" t="n">
-        <v>10.18965648</v>
+        <v>12.34924729</v>
       </c>
       <c r="F27" t="n">
-        <v>5.14904886</v>
+        <v>7.256533559999999</v>
       </c>
       <c r="G27" t="n">
-        <v>12.32428043</v>
+        <v>21.41555787</v>
       </c>
       <c r="H27" t="n">
-        <v>7.23473412</v>
+        <v>9.253958190000001</v>
       </c>
       <c r="I27" t="n">
-        <v>21.39711191</v>
+        <v>20.89001611</v>
       </c>
       <c r="J27" t="n">
-        <v>9.234505710000002</v>
+        <v>17.74033155</v>
       </c>
       <c r="K27" t="n">
-        <v>20.87369368</v>
+        <v>22.20184127</v>
       </c>
       <c r="L27" t="n">
-        <v>17.72328894</v>
+        <v>32.01865752</v>
       </c>
       <c r="M27" t="n">
-        <v>22.18730068</v>
+        <v>32.91440352</v>
       </c>
     </row>
     <row r="28">
@@ -1573,37 +1573,37 @@
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>32.12748586</v>
+        <v>-11.54655749</v>
       </c>
       <c r="D28" t="n">
-        <v>-11.78422149</v>
+        <v>-0.40340602</v>
       </c>
       <c r="E28" t="n">
-        <v>-11.50201346</v>
+        <v>12.49562452</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.33464757</v>
+        <v>-19.69529798</v>
       </c>
       <c r="G28" t="n">
-        <v>12.56553617</v>
+        <v>3.88484246</v>
       </c>
       <c r="H28" t="n">
-        <v>-19.61540847</v>
+        <v>-27.74305593</v>
       </c>
       <c r="I28" t="n">
-        <v>3.97066807</v>
+        <v>-47.75031722</v>
       </c>
       <c r="J28" t="n">
-        <v>-27.65380515</v>
+        <v>-79.88476525</v>
       </c>
       <c r="K28" t="n">
-        <v>-47.65410966</v>
+        <v>-109.77504311</v>
       </c>
       <c r="L28" t="n">
-        <v>-79.80640058</v>
+        <v>-102.99505801</v>
       </c>
       <c r="M28" t="n">
-        <v>-109.71341936</v>
+        <v>-89.85061942999999</v>
       </c>
     </row>
     <row r="29">
@@ -1614,37 +1614,37 @@
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>0.00672136</v>
+        <v>0.006492230000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.00145954</v>
+        <v>0.01229479</v>
       </c>
       <c r="E29" t="n">
-        <v>0.006492230000000001</v>
+        <v>0.01976942</v>
       </c>
       <c r="F29" t="n">
-        <v>0.01229479</v>
+        <v>0.0273315</v>
       </c>
       <c r="G29" t="n">
-        <v>0.01976942</v>
+        <v>0.08224571999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0273315</v>
+        <v>0.0739363</v>
       </c>
       <c r="I29" t="n">
-        <v>0.08224571999999999</v>
+        <v>0.03168009</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0739363</v>
+        <v>0.00634259</v>
       </c>
       <c r="K29" t="n">
-        <v>0.03168009</v>
+        <v>0.01295552</v>
       </c>
       <c r="L29" t="n">
-        <v>0.00634259</v>
+        <v>-0.00654754</v>
       </c>
       <c r="M29" t="n">
-        <v>0.01295552</v>
+        <v>-0.01613442</v>
       </c>
     </row>
     <row r="30">
@@ -1655,37 +1655,37 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>-0.0001607799999999998</v>
+        <v>-0.00124175</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.00308211</v>
+        <v>-0.00683579</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.00131417</v>
+        <v>-0.00255541</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.00648989</v>
+        <v>0.0079351</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.0008686499999999999</v>
+        <v>0.01028314</v>
       </c>
       <c r="H30" t="n">
-        <v>0.008181880000000001</v>
+        <v>0.00538708</v>
       </c>
       <c r="I30" t="n">
-        <v>0.009350769999999998</v>
+        <v>0.01209633</v>
       </c>
       <c r="J30" t="n">
-        <v>0.00520684</v>
+        <v>0.0008129699999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>0.01144411</v>
+        <v>-0.00467908</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.00111543</v>
+        <v>-0.00565026</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.005250739999999999</v>
+        <v>-0.00688049</v>
       </c>
     </row>
     <row r="31">
@@ -1696,37 +1696,37 @@
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>0.009044409999999999</v>
+        <v>-0.07378256999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.04705815</v>
+        <v>0.03239099</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.07371014999999999</v>
+        <v>0.0020954</v>
       </c>
       <c r="F31" t="n">
-        <v>0.03204509000000001</v>
+        <v>0.10067902</v>
       </c>
       <c r="G31" t="n">
-        <v>0.00040864</v>
+        <v>0.21940772</v>
       </c>
       <c r="H31" t="n">
-        <v>0.10043224</v>
+        <v>0.11049352</v>
       </c>
       <c r="I31" t="n">
-        <v>0.22034009</v>
+        <v>0.04080826</v>
       </c>
       <c r="J31" t="n">
-        <v>0.11067376</v>
+        <v>-0.01181338</v>
       </c>
       <c r="K31" t="n">
-        <v>0.04146048</v>
+        <v>-0.05303607</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.009884979999999998</v>
+        <v>-0.09474384</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.05246441</v>
+        <v>-0.18510753</v>
       </c>
     </row>
     <row r="32">
@@ -1737,37 +1737,37 @@
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>47.13405325</v>
+        <v>9.357429240000002</v>
       </c>
       <c r="D32" t="n">
-        <v>17.62821512</v>
+        <v>-23.28926443</v>
       </c>
       <c r="E32" t="n">
-        <v>9.357429240000002</v>
+        <v>-15.50397747</v>
       </c>
       <c r="F32" t="n">
-        <v>-23.28926443</v>
+        <v>-7.671519279999999</v>
       </c>
       <c r="G32" t="n">
-        <v>-15.50397747</v>
+        <v>-12.56496135</v>
       </c>
       <c r="H32" t="n">
-        <v>-7.671519279999999</v>
+        <v>0.4845926899999997</v>
       </c>
       <c r="I32" t="n">
-        <v>-12.56496135</v>
+        <v>-20.67803373</v>
       </c>
       <c r="J32" t="n">
-        <v>0.4845926899999997</v>
+        <v>-32.15445803</v>
       </c>
       <c r="K32" t="n">
-        <v>-20.67803373</v>
+        <v>-40.28821612</v>
       </c>
       <c r="L32" t="n">
-        <v>-32.15445803</v>
+        <v>-16.20914258</v>
       </c>
       <c r="M32" t="n">
-        <v>-40.28821612</v>
+        <v>-19.13381427</v>
       </c>
     </row>
     <row r="33">
@@ -1778,37 +1778,37 @@
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
-        <v>-0.48816578</v>
+        <v>1.69994562</v>
       </c>
       <c r="D33" t="n">
-        <v>0.5905294200000001</v>
+        <v>0.07589649999999996</v>
       </c>
       <c r="E33" t="n">
-        <v>1.69994562</v>
+        <v>-0.14939967</v>
       </c>
       <c r="F33" t="n">
-        <v>0.07589649999999996</v>
+        <v>0.5503706399999999</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.14939967</v>
+        <v>1.89812459</v>
       </c>
       <c r="H33" t="n">
-        <v>0.5503706399999999</v>
+        <v>2.92653785</v>
       </c>
       <c r="I33" t="n">
-        <v>1.89812459</v>
+        <v>0.4812992</v>
       </c>
       <c r="J33" t="n">
-        <v>2.92653785</v>
+        <v>-1.10311971</v>
       </c>
       <c r="K33" t="n">
-        <v>0.4812992</v>
+        <v>-3.2016798</v>
       </c>
       <c r="L33" t="n">
-        <v>-1.10311971</v>
+        <v>-1.87034995</v>
       </c>
       <c r="M33" t="n">
-        <v>-3.2016798</v>
+        <v>-2.31543645</v>
       </c>
     </row>
     <row r="34">
@@ -1819,37 +1819,37 @@
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
-        <v>180.37309538</v>
+        <v>152.60252483</v>
       </c>
       <c r="D34" t="n">
-        <v>110.85613396</v>
+        <v>75.68712063</v>
       </c>
       <c r="E34" t="n">
-        <v>152.60252483</v>
+        <v>33.27450068</v>
       </c>
       <c r="F34" t="n">
-        <v>75.68712063</v>
+        <v>20.78368849</v>
       </c>
       <c r="G34" t="n">
-        <v>33.27450068</v>
+        <v>33.21580698</v>
       </c>
       <c r="H34" t="n">
-        <v>20.78368849</v>
+        <v>52.12681979</v>
       </c>
       <c r="I34" t="n">
-        <v>33.21580698</v>
+        <v>22.38281906</v>
       </c>
       <c r="J34" t="n">
-        <v>52.12681979</v>
+        <v>33.51679171</v>
       </c>
       <c r="K34" t="n">
-        <v>22.38281906</v>
+        <v>42.04676762</v>
       </c>
       <c r="L34" t="n">
-        <v>33.51679171</v>
+        <v>53.81900047</v>
       </c>
       <c r="M34" t="n">
-        <v>42.04676762</v>
+        <v>78.81126565000001</v>
       </c>
     </row>
     <row r="35">
@@ -1860,37 +1860,37 @@
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
-        <v>0.00043182</v>
+        <v>0.05044382</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.14237872</v>
+        <v>-0.09362012</v>
       </c>
       <c r="E35" t="n">
-        <v>0.05044382</v>
+        <v>-0.09928682000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.09362012</v>
+        <v>0.04687088</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.09928682000000001</v>
+        <v>0.28043062</v>
       </c>
       <c r="H35" t="n">
-        <v>0.04687088</v>
+        <v>0.01792718</v>
       </c>
       <c r="I35" t="n">
-        <v>0.28043062</v>
+        <v>-0.03893316</v>
       </c>
       <c r="J35" t="n">
-        <v>0.01792718</v>
+        <v>-0.04556105000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.03893316</v>
+        <v>0.30602701</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.04556105000000001</v>
+        <v>2.51033113</v>
       </c>
       <c r="M35" t="n">
-        <v>0.30602701</v>
+        <v>1.1068391</v>
       </c>
     </row>
     <row r="36">
@@ -1901,37 +1901,37 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>-28.53262185</v>
+        <v>-19.84310048</v>
       </c>
       <c r="D36" t="n">
-        <v>-22.32423203</v>
+        <v>-4.70504814</v>
       </c>
       <c r="E36" t="n">
-        <v>-19.84310048</v>
+        <v>40.16238359</v>
       </c>
       <c r="F36" t="n">
-        <v>-4.70504814</v>
+        <v>84.05469214</v>
       </c>
       <c r="G36" t="n">
-        <v>40.16238359</v>
+        <v>168.24925684</v>
       </c>
       <c r="H36" t="n">
-        <v>84.05469214</v>
+        <v>236.89254524</v>
       </c>
       <c r="I36" t="n">
-        <v>168.24925684</v>
+        <v>117.94625767</v>
       </c>
       <c r="J36" t="n">
-        <v>236.89254524</v>
+        <v>217.93889327</v>
       </c>
       <c r="K36" t="n">
-        <v>117.94625767</v>
+        <v>352.4427523</v>
       </c>
       <c r="L36" t="n">
-        <v>217.93889327</v>
+        <v>204.10822595</v>
       </c>
       <c r="M36" t="n">
-        <v>352.4427523</v>
+        <v>203.78321979</v>
       </c>
     </row>
     <row r="37">
@@ -1940,39 +1940,41 @@
           <t>汽車工業右下</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
       <c r="C37" t="n">
-        <v>58.97214983</v>
+        <v>66.83402647999999</v>
       </c>
       <c r="D37" t="n">
-        <v>31.34869749</v>
+        <v>-8.809809789999999</v>
       </c>
       <c r="E37" t="n">
-        <v>67.82618828999999</v>
+        <v>-2.004053790000001</v>
       </c>
       <c r="F37" t="n">
-        <v>-5.291141719999999</v>
+        <v>19.77853517</v>
       </c>
       <c r="G37" t="n">
-        <v>-1.55991917</v>
+        <v>39.36001564</v>
       </c>
       <c r="H37" t="n">
-        <v>18.38462999</v>
+        <v>41.24324093</v>
       </c>
       <c r="I37" t="n">
-        <v>37.21148715</v>
+        <v>44.13020765</v>
       </c>
       <c r="J37" t="n">
-        <v>41.54908926</v>
+        <v>-0.2081203699999995</v>
       </c>
       <c r="K37" t="n">
-        <v>46.78805196</v>
+        <v>-1.378526400000002</v>
       </c>
       <c r="L37" t="n">
-        <v>5.0257426</v>
+        <v>31.44334252</v>
       </c>
       <c r="M37" t="n">
-        <v>6.859546159999998</v>
+        <v>2.58619647</v>
       </c>
     </row>
     <row r="38">
@@ -1983,37 +1985,37 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>-65.24241149000001</v>
+        <v>-17.31197655</v>
       </c>
       <c r="D38" t="n">
-        <v>-110.10124268</v>
+        <v>-30.84179741</v>
       </c>
       <c r="E38" t="n">
-        <v>-13.91325678</v>
+        <v>-44.13402555</v>
       </c>
       <c r="F38" t="n">
-        <v>-34.16824592</v>
+        <v>-8.959139569999998</v>
       </c>
       <c r="G38" t="n">
-        <v>-41.23378873999999</v>
+        <v>62.48420981000001</v>
       </c>
       <c r="H38" t="n">
-        <v>0.5211704800000023</v>
+        <v>22.18522692</v>
       </c>
       <c r="I38" t="n">
-        <v>68.31632182999999</v>
+        <v>-33.98069776</v>
       </c>
       <c r="J38" t="n">
-        <v>27.73419485000001</v>
+        <v>-48.80477131</v>
       </c>
       <c r="K38" t="n">
-        <v>-34.98197725</v>
+        <v>6.336184970000002</v>
       </c>
       <c r="L38" t="n">
-        <v>-54.9151605</v>
+        <v>49.13944627</v>
       </c>
       <c r="M38" t="n">
-        <v>-5.680847629999999</v>
+        <v>41.06527597000001</v>
       </c>
     </row>
     <row r="39">
@@ -2024,37 +2026,37 @@
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
-        <v>-6.3569939</v>
+        <v>1.60522561</v>
       </c>
       <c r="D39" t="n">
-        <v>-3.72633246</v>
+        <v>-2.38145906</v>
       </c>
       <c r="E39" t="n">
-        <v>1.60522561</v>
+        <v>-1.22895808</v>
       </c>
       <c r="F39" t="n">
-        <v>-2.38145906</v>
+        <v>2.09904764</v>
       </c>
       <c r="G39" t="n">
-        <v>-1.22895808</v>
+        <v>3.22631047</v>
       </c>
       <c r="H39" t="n">
-        <v>2.09904764</v>
+        <v>8.135896049999999</v>
       </c>
       <c r="I39" t="n">
-        <v>3.22631047</v>
+        <v>0.42597227</v>
       </c>
       <c r="J39" t="n">
-        <v>8.135896049999999</v>
+        <v>5.236759269999999</v>
       </c>
       <c r="K39" t="n">
-        <v>0.42597227</v>
+        <v>24.80576117</v>
       </c>
       <c r="L39" t="n">
-        <v>5.236759269999999</v>
+        <v>21.99748971</v>
       </c>
       <c r="M39" t="n">
-        <v>24.80576117</v>
+        <v>7.5667577</v>
       </c>
     </row>
     <row r="40">
@@ -2063,39 +2065,41 @@
           <t>油電燃氣業右下</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
+      <c r="B40" t="n">
+        <v>0</v>
+      </c>
       <c r="C40" t="n">
-        <v>33.64417675</v>
+        <v>73.39823507000001</v>
       </c>
       <c r="D40" t="n">
-        <v>4.060389399999999</v>
+        <v>168.35615972</v>
       </c>
       <c r="E40" t="n">
-        <v>73.36149224</v>
+        <v>54.65808956999999</v>
       </c>
       <c r="F40" t="n">
-        <v>168.3102298</v>
+        <v>-40.04370454000001</v>
       </c>
       <c r="G40" t="n">
-        <v>54.66236087999999</v>
+        <v>-65.28278445000001</v>
       </c>
       <c r="H40" t="n">
-        <v>-39.94506282000001</v>
+        <v>-32.7596749</v>
       </c>
       <c r="I40" t="n">
-        <v>-65.26597674</v>
+        <v>-17.83517614</v>
       </c>
       <c r="J40" t="n">
-        <v>-32.77254173</v>
+        <v>-34.19477872</v>
       </c>
       <c r="K40" t="n">
-        <v>-17.85398609</v>
+        <v>-18.2753221</v>
       </c>
       <c r="L40" t="n">
-        <v>-34.21927367</v>
+        <v>16.53961087</v>
       </c>
       <c r="M40" t="n">
-        <v>-18.29835111</v>
+        <v>-19.19636158</v>
       </c>
     </row>
     <row r="41">
@@ -2106,37 +2110,37 @@
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
-        <v>1.585000000000001e-05</v>
+        <v>-0.03262842000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0006898099999999999</v>
+        <v>-0.04257767</v>
       </c>
       <c r="E41" t="n">
-        <v>0.00032413</v>
+        <v>0.007155480000000001</v>
       </c>
       <c r="F41" t="n">
-        <v>0.00029196</v>
+        <v>0.10078061</v>
       </c>
       <c r="G41" t="n">
-        <v>0.00034763</v>
+        <v>0.01855391</v>
       </c>
       <c r="H41" t="n">
-        <v>0.00013184</v>
+        <v>-0.01178567</v>
       </c>
       <c r="I41" t="n">
-        <v>0.00022117</v>
+        <v>-0.0178828</v>
       </c>
       <c r="J41" t="n">
-        <v>-7.589999999999999e-05</v>
+        <v>-0.02335537</v>
       </c>
       <c r="K41" t="n">
-        <v>-2.344e-05</v>
+        <v>-0.02156378</v>
       </c>
       <c r="L41" t="n">
-        <v>-2.618e-05</v>
+        <v>-0.01861452</v>
       </c>
       <c r="M41" t="n">
-        <v>7.396e-05</v>
+        <v>-0.01283763</v>
       </c>
     </row>
     <row r="42">
@@ -2147,2462 +2151,2421 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>668.62466564</v>
+        <v>335.6496038400001</v>
       </c>
       <c r="D42" t="n">
-        <v>244.91801602</v>
+        <v>486.62145114</v>
       </c>
       <c r="E42" t="n">
-        <v>320.90370974</v>
+        <v>768.44312698</v>
       </c>
       <c r="F42" t="n">
-        <v>479.18507195</v>
+        <v>271.57353044</v>
       </c>
       <c r="G42" t="n">
-        <v>759.412483</v>
+        <v>-68.75579565</v>
       </c>
       <c r="H42" t="n">
-        <v>264.18557726</v>
+        <v>-25.65882652</v>
       </c>
       <c r="I42" t="n">
-        <v>-87.18150326999999</v>
+        <v>-203.34503687</v>
       </c>
       <c r="J42" t="n">
-        <v>-42.95356518</v>
+        <v>-26.00127152</v>
       </c>
       <c r="K42" t="n">
-        <v>-209.92976809</v>
+        <v>156.76665614</v>
       </c>
       <c r="L42" t="n">
-        <v>-24.7706204</v>
+        <v>578.4989785</v>
       </c>
       <c r="M42" t="n">
-        <v>154.56242497</v>
+        <v>900.52032724</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右下</t>
+          <t>玻璃陶瓷平</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
-        <v>0.38604138</v>
+        <v>1.61384816</v>
       </c>
       <c r="D43" t="n">
-        <v>0.7518413900000001</v>
+        <v>0.5450071499999999</v>
       </c>
       <c r="E43" t="n">
-        <v>0.53861171</v>
+        <v>2.44174181</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.02875878</v>
+        <v>-0.2750045700000001</v>
       </c>
       <c r="G43" t="n">
-        <v>0.35239102</v>
+        <v>1.46585581</v>
       </c>
       <c r="H43" t="n">
-        <v>0.02480043</v>
+        <v>1.15822565</v>
       </c>
       <c r="I43" t="n">
-        <v>0.14843928</v>
+        <v>-1.54501608</v>
       </c>
       <c r="J43" t="n">
-        <v>0.2334175</v>
+        <v>-2.785485910000001</v>
       </c>
       <c r="K43" t="n">
-        <v>0.05061566000000001</v>
+        <v>-2.72785007</v>
       </c>
       <c r="L43" t="n">
-        <v>8.911000000000001e-05</v>
+        <v>3.65355746</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.46469736</v>
+        <v>20.8485932</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷平</t>
+          <t>生技醫療業右上</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>11.74760684</v>
+        <v>-1.133946449999999</v>
       </c>
       <c r="D44" t="n">
-        <v>8.15229796</v>
+        <v>13.24144375</v>
       </c>
       <c r="E44" t="n">
-        <v>15.82113055</v>
+        <v>11.76559636</v>
       </c>
       <c r="F44" t="n">
-        <v>8.010145120000001</v>
+        <v>14.53376977</v>
       </c>
       <c r="G44" t="n">
-        <v>11.11999477</v>
+        <v>15.49335643</v>
       </c>
       <c r="H44" t="n">
-        <v>7.08814818</v>
+        <v>16.90445673</v>
       </c>
       <c r="I44" t="n">
-        <v>19.74312415</v>
+        <v>5.929895040000002</v>
       </c>
       <c r="J44" t="n">
-        <v>18.21954681</v>
+        <v>12.21935185</v>
       </c>
       <c r="K44" t="n">
-        <v>4.989099479999999</v>
+        <v>11.88079468</v>
       </c>
       <c r="L44" t="n">
-        <v>-4.016226140000001</v>
+        <v>12.56105717</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.05892154000000004</v>
+        <v>-6.57284661</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右上</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
+          <t>生技醫療業右下</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0</v>
+      </c>
       <c r="C45" t="n">
-        <v>-1.69406084</v>
+        <v>-340.48951741</v>
       </c>
       <c r="D45" t="n">
-        <v>-9.704325000000001</v>
+        <v>-317.75064965</v>
       </c>
       <c r="E45" t="n">
-        <v>3.652572440000001</v>
+        <v>-304.39042601</v>
       </c>
       <c r="F45" t="n">
-        <v>18.08799593</v>
+        <v>-62.50324634999999</v>
       </c>
       <c r="G45" t="n">
-        <v>13.37258108</v>
+        <v>9.092606350000009</v>
       </c>
       <c r="H45" t="n">
-        <v>15.07971701</v>
+        <v>32.71090707</v>
       </c>
       <c r="I45" t="n">
-        <v>14.30404653</v>
+        <v>119.31041291</v>
       </c>
       <c r="J45" t="n">
-        <v>16.90830076</v>
+        <v>261.59726426</v>
       </c>
       <c r="K45" t="n">
-        <v>5.003064830000001</v>
+        <v>96.41570724000002</v>
       </c>
       <c r="L45" t="n">
-        <v>12.13955481</v>
+        <v>182.21972061</v>
       </c>
       <c r="M45" t="n">
-        <v>12.4494654</v>
+        <v>197.71447</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右下</t>
+          <t>生技醫療業平</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>-28.46534079</v>
+        <v>-268.04503056</v>
       </c>
       <c r="D46" t="n">
-        <v>-233.05222756</v>
+        <v>-225.69859044</v>
       </c>
       <c r="E46" t="n">
-        <v>-348.24858398</v>
+        <v>32.15057442000001</v>
       </c>
       <c r="F46" t="n">
-        <v>-325.33811903</v>
+        <v>-34.02384609000001</v>
       </c>
       <c r="G46" t="n">
-        <v>-311.01762448</v>
+        <v>91.01002581</v>
       </c>
       <c r="H46" t="n">
-        <v>-66.67090091</v>
+        <v>-3.482605619999986</v>
       </c>
       <c r="I46" t="n">
-        <v>7.325849740000002</v>
+        <v>74.98699289999999</v>
       </c>
       <c r="J46" t="n">
-        <v>30.03810668</v>
+        <v>52.00554579</v>
       </c>
       <c r="K46" t="n">
-        <v>116.27487735</v>
+        <v>-58.8440166</v>
       </c>
       <c r="L46" t="n">
-        <v>258.77313968</v>
+        <v>75.63740370000001</v>
       </c>
       <c r="M46" t="n">
-        <v>93.90679775000001</v>
+        <v>104.59265614</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業平</t>
+          <t>紡織纖維右上</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>-105.27377237</v>
+        <v>-5.88827229</v>
       </c>
       <c r="D47" t="n">
-        <v>-256.59694877</v>
+        <v>-5.95644375</v>
       </c>
       <c r="E47" t="n">
-        <v>-265.07278991</v>
+        <v>-5.160463770000001</v>
       </c>
       <c r="F47" t="n">
-        <v>-222.95824788</v>
+        <v>-5.243561529999999</v>
       </c>
       <c r="G47" t="n">
-        <v>37.17042832</v>
+        <v>-1.42685796</v>
       </c>
       <c r="H47" t="n">
-        <v>-30.40253615</v>
+        <v>-1.55800123</v>
       </c>
       <c r="I47" t="n">
-        <v>93.96601003000001</v>
+        <v>0.21287991</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.8139572099999953</v>
+        <v>0.11387768</v>
       </c>
       <c r="K47" t="n">
-        <v>78.94952617999999</v>
+        <v>-1.16397337</v>
       </c>
       <c r="L47" t="n">
-        <v>54.90868887</v>
+        <v>3.26751648</v>
       </c>
       <c r="M47" t="n">
-        <v>-56.90458671</v>
+        <v>1.63974039</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右上</t>
+          <t>紡織纖維右下</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
-        <v>-6.34542106</v>
+        <v>39.68570400999999</v>
       </c>
       <c r="D48" t="n">
-        <v>-8.06516886</v>
+        <v>4.959410939999997</v>
       </c>
       <c r="E48" t="n">
-        <v>-5.88833566</v>
+        <v>20.79775888</v>
       </c>
       <c r="F48" t="n">
-        <v>-5.95651349</v>
+        <v>26.43965689</v>
       </c>
       <c r="G48" t="n">
-        <v>-5.16051644</v>
+        <v>2.09872248</v>
       </c>
       <c r="H48" t="n">
-        <v>-5.243580819999999</v>
+        <v>-22.66043907</v>
       </c>
       <c r="I48" t="n">
-        <v>-1.42689061</v>
+        <v>-14.22418096</v>
       </c>
       <c r="J48" t="n">
-        <v>-1.55805487</v>
+        <v>-101.4682925</v>
       </c>
       <c r="K48" t="n">
-        <v>0.2128199</v>
+        <v>-165.30248956</v>
       </c>
       <c r="L48" t="n">
-        <v>0.11380938</v>
+        <v>-139.3712056</v>
       </c>
       <c r="M48" t="n">
-        <v>-1.16393911</v>
+        <v>-51.9386133</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右下</t>
+          <t>紡織纖維平</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>95.04986186999999</v>
+        <v>0.06715978</v>
       </c>
       <c r="D49" t="n">
-        <v>9.407378970000002</v>
+        <v>-0.10231465</v>
       </c>
       <c r="E49" t="n">
-        <v>39.68573421</v>
+        <v>-0.003034590000000003</v>
       </c>
       <c r="F49" t="n">
-        <v>4.959421839999997</v>
+        <v>1.65277663</v>
       </c>
       <c r="G49" t="n">
-        <v>20.79778082</v>
+        <v>1.32680061</v>
       </c>
       <c r="H49" t="n">
-        <v>26.43966846</v>
+        <v>0.25551766</v>
       </c>
       <c r="I49" t="n">
-        <v>2.098726649999999</v>
+        <v>-0.002290740000000012</v>
       </c>
       <c r="J49" t="n">
-        <v>-22.66043861</v>
+        <v>-0.21216146</v>
       </c>
       <c r="K49" t="n">
-        <v>-14.22419143</v>
+        <v>-0.3229685499999999</v>
       </c>
       <c r="L49" t="n">
-        <v>-101.46831989</v>
+        <v>-0.6423388099999999</v>
       </c>
       <c r="M49" t="n">
-        <v>-165.30252001</v>
+        <v>-0.68793905</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維平</t>
+          <t>綠能環保右上</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
-        <v>0.28972349</v>
+        <v>-62.66401336</v>
       </c>
       <c r="D50" t="n">
-        <v>0.02723858000000001</v>
+        <v>-57.76571075</v>
       </c>
       <c r="E50" t="n">
-        <v>0.06719295</v>
+        <v>-32.92139744</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.10225581</v>
+        <v>-122.83206046</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.003003860000000003</v>
+        <v>-8.516761969999999</v>
       </c>
       <c r="H50" t="n">
-        <v>1.65278435</v>
+        <v>-116.90533009</v>
       </c>
       <c r="I50" t="n">
-        <v>1.32682909</v>
+        <v>51.20665815</v>
       </c>
       <c r="J50" t="n">
-        <v>0.25557084</v>
+        <v>-77.14822511999999</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.002220260000000012</v>
+        <v>-66.42575235000001</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.21206577</v>
+        <v>-59.29735394</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.3229723599999999</v>
+        <v>-112.99623943</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右上</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
+          <t>綠能環保右下</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
       <c r="C51" t="n">
-        <v>-44.42665097</v>
+        <v>4.58012303</v>
       </c>
       <c r="D51" t="n">
-        <v>16.98814198</v>
+        <v>-7.572110350000001</v>
       </c>
       <c r="E51" t="n">
-        <v>-62.84743057</v>
+        <v>2.53484422</v>
       </c>
       <c r="F51" t="n">
-        <v>-60.72548797</v>
+        <v>-2.543530349999999</v>
       </c>
       <c r="G51" t="n">
-        <v>-31.76071553</v>
+        <v>4.033005090000001</v>
       </c>
       <c r="H51" t="n">
-        <v>-116.83585634</v>
+        <v>-4.20817929</v>
       </c>
       <c r="I51" t="n">
-        <v>-7.13067809</v>
+        <v>-16.66796257</v>
       </c>
       <c r="J51" t="n">
-        <v>-116.51903971</v>
+        <v>-17.3098579</v>
       </c>
       <c r="K51" t="n">
-        <v>53.02447994</v>
+        <v>-27.00053969</v>
       </c>
       <c r="L51" t="n">
-        <v>-67.05617642999999</v>
+        <v>-37.85252972</v>
       </c>
       <c r="M51" t="n">
-        <v>-49.19548277000001</v>
+        <v>-40.22146727</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右下</t>
+          <t>綠能環保平</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>-10.76360972</v>
+        <v>-0.6707557600000009</v>
       </c>
       <c r="D52" t="n">
-        <v>-6.295704290000001</v>
+        <v>-11.58867564</v>
       </c>
       <c r="E52" t="n">
-        <v>4.70272614</v>
+        <v>17.82601938</v>
       </c>
       <c r="F52" t="n">
-        <v>-5.524311600000001</v>
+        <v>3.01749032</v>
       </c>
       <c r="G52" t="n">
-        <v>2.53485937</v>
+        <v>23.56122139</v>
       </c>
       <c r="H52" t="n">
-        <v>-2.54366476</v>
+        <v>23.25266108</v>
       </c>
       <c r="I52" t="n">
-        <v>4.03323023</v>
+        <v>10.98587756</v>
       </c>
       <c r="J52" t="n">
-        <v>-4.208008479999999</v>
+        <v>14.37131513</v>
       </c>
       <c r="K52" t="n">
-        <v>-16.668004</v>
+        <v>-7.095445330000001</v>
       </c>
       <c r="L52" t="n">
-        <v>-17.31000216</v>
+        <v>3.773723930000001</v>
       </c>
       <c r="M52" t="n">
-        <v>-27.00119206</v>
+        <v>-0.6006474200000018</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>綠能環保平</t>
+          <t>航運業右上</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>11.02151964</v>
+        <v>10.94663334000001</v>
       </c>
       <c r="D53" t="n">
-        <v>0.6914134699999998</v>
+        <v>-242.48694746</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.6101504000000009</v>
+        <v>176.69649829</v>
       </c>
       <c r="F53" t="n">
-        <v>-10.67695438</v>
+        <v>173.3919018</v>
       </c>
       <c r="G53" t="n">
-        <v>18.7918644</v>
+        <v>534.26192584</v>
       </c>
       <c r="H53" t="n">
-        <v>3.06092946</v>
+        <v>553.1683261099998</v>
       </c>
       <c r="I53" t="n">
-        <v>24.24434607</v>
+        <v>-153.03544707</v>
       </c>
       <c r="J53" t="n">
-        <v>23.1651094</v>
+        <v>23.19576348999999</v>
       </c>
       <c r="K53" t="n">
-        <v>9.047286630000002</v>
+        <v>202.36344017</v>
       </c>
       <c r="L53" t="n">
-        <v>14.09218324</v>
+        <v>368.1468738200001</v>
       </c>
       <c r="M53" t="n">
-        <v>-7.867694850000001</v>
+        <v>697.00617015</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>航運業右上</t>
+          <t>航運業右下</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>109.84570048</v>
+        <v>3.392625100000001</v>
       </c>
       <c r="D54" t="n">
-        <v>33.61381624000001</v>
+        <v>-5.6969817</v>
       </c>
       <c r="E54" t="n">
-        <v>15.43591371</v>
+        <v>-0.9628962199999999</v>
       </c>
       <c r="F54" t="n">
-        <v>-113.78998172</v>
+        <v>9.504409800000001</v>
       </c>
       <c r="G54" t="n">
-        <v>166.81981741</v>
+        <v>6.19122544</v>
       </c>
       <c r="H54" t="n">
-        <v>318.94946344</v>
+        <v>18.44192423</v>
       </c>
       <c r="I54" t="n">
-        <v>773.50804662</v>
+        <v>33.41105407</v>
       </c>
       <c r="J54" t="n">
-        <v>812.5688147</v>
+        <v>32.28942822</v>
       </c>
       <c r="K54" t="n">
-        <v>211.81430302</v>
+        <v>13.83002886</v>
       </c>
       <c r="L54" t="n">
-        <v>163.15365218</v>
+        <v>22.66830127</v>
       </c>
       <c r="M54" t="n">
-        <v>424.97201031</v>
+        <v>11.76082298</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>航運業右下</t>
+          <t>航運業平</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>2.649624870000001</v>
+        <v>229.34488098</v>
       </c>
       <c r="D55" t="n">
-        <v>-8.060267979999999</v>
+        <v>-0.8430084399999972</v>
       </c>
       <c r="E55" t="n">
-        <v>3.392625100000001</v>
+        <v>106.61593814</v>
       </c>
       <c r="F55" t="n">
-        <v>-5.6969817</v>
+        <v>124.87391476</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.9628962199999999</v>
+        <v>151.40139458</v>
       </c>
       <c r="H55" t="n">
-        <v>9.504409800000001</v>
+        <v>285.09222881</v>
       </c>
       <c r="I55" t="n">
-        <v>6.19122544</v>
+        <v>15.57843331</v>
       </c>
       <c r="J55" t="n">
-        <v>18.44192423</v>
+        <v>372.0778595</v>
       </c>
       <c r="K55" t="n">
-        <v>33.41105407</v>
+        <v>327.19522717</v>
       </c>
       <c r="L55" t="n">
-        <v>32.28942822</v>
+        <v>361.80669016</v>
       </c>
       <c r="M55" t="n">
-        <v>13.83002886</v>
+        <v>51.10309794000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>航運業平</t>
+          <t>觀光事業右上</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>344.06030276</v>
+        <v>-1.13279489</v>
       </c>
       <c r="D56" t="n">
-        <v>39.77100866999999</v>
+        <v>-9.104689879999999</v>
       </c>
       <c r="E56" t="n">
-        <v>224.85560061</v>
+        <v>2.08177505</v>
       </c>
       <c r="F56" t="n">
-        <v>-129.53997418</v>
+        <v>-7.279503650000001</v>
       </c>
       <c r="G56" t="n">
-        <v>86.09953015000001</v>
+        <v>-1.98131092</v>
       </c>
       <c r="H56" t="n">
-        <v>-55.61995688999998</v>
+        <v>-4.11600271</v>
       </c>
       <c r="I56" t="n">
-        <v>-126.44218721</v>
+        <v>4.08051314</v>
       </c>
       <c r="J56" t="n">
-        <v>2.093856710000002</v>
+        <v>-0.19955683</v>
       </c>
       <c r="K56" t="n">
-        <v>-358.3675534</v>
+        <v>-12.28203431</v>
       </c>
       <c r="L56" t="n">
-        <v>254.60100535</v>
+        <v>-2.91422361</v>
       </c>
       <c r="M56" t="n">
-        <v>92.98913580000003</v>
+        <v>20.80536127</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右上</t>
+          <t>觀光事業右下</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
-        <v>4.620033370000001</v>
+        <v>-7.73082727</v>
       </c>
       <c r="D57" t="n">
-        <v>0.3289832499999999</v>
+        <v>-13.07116972</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.13281235</v>
+        <v>-3.21768409</v>
       </c>
       <c r="F57" t="n">
-        <v>-9.10466808</v>
+        <v>24.1128248</v>
       </c>
       <c r="G57" t="n">
-        <v>2.08177039</v>
+        <v>19.63663041</v>
       </c>
       <c r="H57" t="n">
-        <v>-7.27948795</v>
+        <v>9.533073910000001</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.98132958</v>
+        <v>-6.476807470000001</v>
       </c>
       <c r="J57" t="n">
-        <v>-4.1160601</v>
+        <v>-19.62278828</v>
       </c>
       <c r="K57" t="n">
-        <v>4.08058217</v>
+        <v>-31.28641675</v>
       </c>
       <c r="L57" t="n">
-        <v>-0.19960646</v>
+        <v>-35.817193</v>
       </c>
       <c r="M57" t="n">
-        <v>-12.28249493</v>
+        <v>-48.82730269</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右下</t>
+          <t>觀光事業平</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>-2.06283767</v>
+        <v>7.918194450000001</v>
       </c>
       <c r="D58" t="n">
-        <v>-7.64623531</v>
+        <v>5.06663928</v>
       </c>
       <c r="E58" t="n">
-        <v>-7.73076538</v>
+        <v>15.59529711</v>
       </c>
       <c r="F58" t="n">
-        <v>-13.07100979</v>
+        <v>34.83699054</v>
       </c>
       <c r="G58" t="n">
-        <v>-3.20737339</v>
+        <v>44.05412936</v>
       </c>
       <c r="H58" t="n">
-        <v>24.12908983</v>
+        <v>45.77293921</v>
       </c>
       <c r="I58" t="n">
-        <v>19.63287374</v>
+        <v>20.388095</v>
       </c>
       <c r="J58" t="n">
-        <v>9.521552719999999</v>
+        <v>-9.583186169999999</v>
       </c>
       <c r="K58" t="n">
-        <v>-6.49062084</v>
+        <v>-17.24602033</v>
       </c>
       <c r="L58" t="n">
-        <v>-19.63753738</v>
+        <v>-34.94951331</v>
       </c>
       <c r="M58" t="n">
-        <v>-31.28690505</v>
+        <v>-42.18687047</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>觀光事業平</t>
+          <t>貿易百貨右下</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
-        <v>-2.89867582</v>
+        <v>-7.66747269</v>
       </c>
       <c r="D59" t="n">
-        <v>-3.97992534</v>
+        <v>-47.88692235000001</v>
       </c>
       <c r="E59" t="n">
-        <v>7.918150020000001</v>
+        <v>6.96574599</v>
       </c>
       <c r="F59" t="n">
-        <v>5.06645755</v>
+        <v>42.54732838</v>
       </c>
       <c r="G59" t="n">
-        <v>15.59525248</v>
+        <v>65.16556917</v>
       </c>
       <c r="H59" t="n">
-        <v>34.83722908</v>
+        <v>39.0396422</v>
       </c>
       <c r="I59" t="n">
-        <v>44.05452678</v>
+        <v>50.5705571</v>
       </c>
       <c r="J59" t="n">
-        <v>45.77332007</v>
+        <v>29.48116599</v>
       </c>
       <c r="K59" t="n">
-        <v>20.38839243</v>
+        <v>3.745202050000001</v>
       </c>
       <c r="L59" t="n">
-        <v>-9.582913620000001</v>
+        <v>-27.11462849</v>
       </c>
       <c r="M59" t="n">
-        <v>-17.24537549</v>
+        <v>-15.70060404</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨右下</t>
+          <t>貿易百貨平</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
-        <v>-57.92342369999999</v>
+        <v>-0.005366599999999999</v>
       </c>
       <c r="D60" t="n">
-        <v>-68.26387203</v>
+        <v>-0.008696569999999999</v>
       </c>
       <c r="E60" t="n">
-        <v>-8.433303890000001</v>
+        <v>0.0294527</v>
       </c>
       <c r="F60" t="n">
-        <v>-47.65032497000001</v>
+        <v>0.02929013</v>
       </c>
       <c r="G60" t="n">
-        <v>7.703351639999999</v>
+        <v>0.00690925</v>
       </c>
       <c r="H60" t="n">
-        <v>41.98299858</v>
+        <v>-0.002395420000000002</v>
       </c>
       <c r="I60" t="n">
-        <v>64.00418524</v>
+        <v>0.0890145</v>
       </c>
       <c r="J60" t="n">
-        <v>37.16416376</v>
+        <v>0.02680047</v>
       </c>
       <c r="K60" t="n">
-        <v>48.23396804</v>
+        <v>0.03247147</v>
       </c>
       <c r="L60" t="n">
-        <v>28.77712765</v>
+        <v>0.03435918</v>
       </c>
       <c r="M60" t="n">
-        <v>3.951017690000001</v>
+        <v>0.0329061</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨平</t>
+          <t>資訊服務業右上</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
-        <v>1.14616828</v>
+        <v>-15.12597921</v>
       </c>
       <c r="D61" t="n">
-        <v>0.01365724</v>
+        <v>19.01627602</v>
       </c>
       <c r="E61" t="n">
-        <v>0.7604645999999999</v>
+        <v>32.19641023</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.24529395</v>
+        <v>66.00317588999999</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.70815295</v>
+        <v>95.2021495</v>
       </c>
       <c r="H61" t="n">
-        <v>0.59361993</v>
+        <v>52.08626254999999</v>
       </c>
       <c r="I61" t="n">
-        <v>1.16829318</v>
+        <v>56.2650797</v>
       </c>
       <c r="J61" t="n">
-        <v>1.87308302</v>
+        <v>4.496617839999995</v>
       </c>
       <c r="K61" t="n">
-        <v>2.42560356</v>
+        <v>16.52188146</v>
       </c>
       <c r="L61" t="n">
-        <v>0.7308388099999999</v>
+        <v>67.27001618000001</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.17334417</v>
+        <v>-16.92923413</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右上</t>
+          <t>資訊服務業右下</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>-20.09428251</v>
+        <v>-0.0038087</v>
       </c>
       <c r="D62" t="n">
-        <v>-30.92647838</v>
+        <v>-0.00767553</v>
       </c>
       <c r="E62" t="n">
-        <v>-15.12595207</v>
+        <v>-0.00331886</v>
       </c>
       <c r="F62" t="n">
-        <v>19.01596501</v>
+        <v>-0.00264089</v>
       </c>
       <c r="G62" t="n">
-        <v>32.19631332</v>
+        <v>0.00704679</v>
       </c>
       <c r="H62" t="n">
-        <v>66.0032384</v>
+        <v>0.00531042</v>
       </c>
       <c r="I62" t="n">
-        <v>95.20201191</v>
+        <v>0.00115759</v>
       </c>
       <c r="J62" t="n">
-        <v>52.08602065</v>
+        <v>0.009192200000000001</v>
       </c>
       <c r="K62" t="n">
-        <v>56.26502794</v>
+        <v>0.01654324</v>
       </c>
       <c r="L62" t="n">
-        <v>4.496212889999995</v>
+        <v>0.02075615</v>
       </c>
       <c r="M62" t="n">
-        <v>16.521687</v>
+        <v>0.02263502</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右下</t>
+          <t>資訊服務業平</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>-0.0009432200000000003</v>
+        <v>15.73900359</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.00395804</v>
+        <v>-2.45213386</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.0038087</v>
+        <v>28.65250776</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.00767553</v>
+        <v>47.66618502</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.00331886</v>
+        <v>94.86350612999999</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.00264089</v>
+        <v>46.74758527</v>
       </c>
       <c r="I63" t="n">
-        <v>0.00704679</v>
+        <v>41.24757875</v>
       </c>
       <c r="J63" t="n">
-        <v>0.00531042</v>
+        <v>17.01437283</v>
       </c>
       <c r="K63" t="n">
-        <v>0.00115759</v>
+        <v>18.43867922</v>
       </c>
       <c r="L63" t="n">
-        <v>0.009192200000000001</v>
+        <v>30.16376739</v>
       </c>
       <c r="M63" t="n">
-        <v>0.01654324</v>
+        <v>29.38237083</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業平</t>
+          <t>農業科技業右上</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
-        <v>54.93303347</v>
+        <v>0.0004248200000000001</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.1309064899999995</v>
+        <v>0.00090755</v>
       </c>
       <c r="E64" t="n">
-        <v>15.73954062</v>
+        <v>0.00103174</v>
       </c>
       <c r="F64" t="n">
-        <v>-2.45135326</v>
+        <v>0.0009914099999999999</v>
       </c>
       <c r="G64" t="n">
-        <v>28.65296481</v>
+        <v>6.247e-05</v>
       </c>
       <c r="H64" t="n">
-        <v>47.66635361</v>
+        <v>0.0004044</v>
       </c>
       <c r="I64" t="n">
-        <v>94.86368377000001</v>
+        <v>0.00072251</v>
       </c>
       <c r="J64" t="n">
-        <v>46.74773143</v>
+        <v>-0.00025412</v>
       </c>
       <c r="K64" t="n">
-        <v>41.24752671</v>
+        <v>-0.00126824</v>
       </c>
       <c r="L64" t="n">
-        <v>17.01497371</v>
+        <v>-0.00052996</v>
       </c>
       <c r="M64" t="n">
-        <v>18.43894564</v>
+        <v>-4.627e-05</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右上</t>
+          <t>農業科技業右下</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
-        <v>0.00014581</v>
+        <v>-0.0002611</v>
       </c>
       <c r="D65" t="n">
-        <v>0.00033086</v>
+        <v>-0.00027651</v>
       </c>
       <c r="E65" t="n">
-        <v>0.0004248200000000001</v>
+        <v>-0.0002609000000000001</v>
       </c>
       <c r="F65" t="n">
-        <v>0.00090755</v>
+        <v>5.814e-05</v>
       </c>
       <c r="G65" t="n">
-        <v>0.00103174</v>
+        <v>0.00018835</v>
       </c>
       <c r="H65" t="n">
-        <v>0.0009914099999999999</v>
+        <v>2.243e-05</v>
       </c>
       <c r="I65" t="n">
-        <v>6.247e-05</v>
+        <v>-8.019e-05</v>
       </c>
       <c r="J65" t="n">
-        <v>0.0004044</v>
+        <v>-3.720999999999999e-05</v>
       </c>
       <c r="K65" t="n">
-        <v>0.00072251</v>
+        <v>-0.00012853</v>
       </c>
       <c r="L65" t="n">
-        <v>-0.00025412</v>
+        <v>-0.00011783</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.00126824</v>
+        <v>-0.00038662</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右下</t>
+          <t>通信網路業右上</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>-0.00024988</v>
+        <v>123.2535663</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.00027272</v>
+        <v>410.13154095</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.0002611</v>
+        <v>11.21869360999999</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.00027651</v>
+        <v>180.39949613</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.0002609000000000001</v>
+        <v>722.05268942</v>
       </c>
       <c r="H66" t="n">
-        <v>5.814e-05</v>
+        <v>196.89899252</v>
       </c>
       <c r="I66" t="n">
-        <v>0.00018835</v>
+        <v>597.94056154</v>
       </c>
       <c r="J66" t="n">
-        <v>2.243e-05</v>
+        <v>739.9888603400001</v>
       </c>
       <c r="K66" t="n">
-        <v>-8.019e-05</v>
+        <v>897.7872426599999</v>
       </c>
       <c r="L66" t="n">
-        <v>-3.720999999999999e-05</v>
+        <v>989.4003378800001</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.00012853</v>
+        <v>1236.14751122</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右上</t>
+          <t>通信網路業右下</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>1071.29921391</v>
+        <v>-17.09105708</v>
       </c>
       <c r="D67" t="n">
-        <v>847.7265433000001</v>
+        <v>-53.14267139</v>
       </c>
       <c r="E67" t="n">
-        <v>96.80285476</v>
+        <v>-3.999420880000002</v>
       </c>
       <c r="F67" t="n">
-        <v>410.20350762</v>
+        <v>33.33771072</v>
       </c>
       <c r="G67" t="n">
-        <v>-30.36561727</v>
+        <v>2.42355657</v>
       </c>
       <c r="H67" t="n">
-        <v>176.70231297</v>
+        <v>1.51502225</v>
       </c>
       <c r="I67" t="n">
-        <v>709.04143488</v>
+        <v>-43.93714867</v>
       </c>
       <c r="J67" t="n">
-        <v>231.25709942</v>
+        <v>-27.1973517</v>
       </c>
       <c r="K67" t="n">
-        <v>583.75361994</v>
+        <v>-8.63181679</v>
       </c>
       <c r="L67" t="n">
-        <v>765.4437038900001</v>
+        <v>45.1348587</v>
       </c>
       <c r="M67" t="n">
-        <v>919.7423975</v>
+        <v>-69.71877004</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右下</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>0</v>
-      </c>
+          <t>通信網路業平</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>33.87624075999999</v>
+        <v>391.75445482</v>
       </c>
       <c r="D68" t="n">
-        <v>44.29952979999999</v>
+        <v>171.64484291</v>
       </c>
       <c r="E68" t="n">
-        <v>29.08693983</v>
+        <v>348.72537448</v>
       </c>
       <c r="F68" t="n">
-        <v>0.4105898600000005</v>
+        <v>129.96735655</v>
       </c>
       <c r="G68" t="n">
-        <v>86.89475669999999</v>
+        <v>148.64146146</v>
       </c>
       <c r="H68" t="n">
-        <v>-34.34445583999999</v>
+        <v>128.54935133</v>
       </c>
       <c r="I68" t="n">
-        <v>-19.90779443</v>
+        <v>-97.91800155999999</v>
       </c>
       <c r="J68" t="n">
-        <v>-40.57344869999999</v>
+        <v>-143.4554884</v>
       </c>
       <c r="K68" t="n">
-        <v>-96.36349721000001</v>
+        <v>-118.92468569</v>
       </c>
       <c r="L68" t="n">
-        <v>-77.19925556</v>
+        <v>-14.14023993</v>
       </c>
       <c r="M68" t="n">
-        <v>-56.20752070000001</v>
+        <v>-118.20082058</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>通信網路業平</t>
+          <t>造紙工業右下</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>827.99073538</v>
+        <v>-4.28064262</v>
       </c>
       <c r="D69" t="n">
-        <v>327.03278143</v>
+        <v>-9.848016550000001</v>
       </c>
       <c r="E69" t="n">
-        <v>372.02748297</v>
+        <v>-11.75977663</v>
       </c>
       <c r="F69" t="n">
-        <v>118.01982874</v>
+        <v>-14.45543988</v>
       </c>
       <c r="G69" t="n">
-        <v>299.41572412</v>
+        <v>-8.60103045</v>
       </c>
       <c r="H69" t="n">
-        <v>201.34689884</v>
+        <v>1.481096</v>
       </c>
       <c r="I69" t="n">
-        <v>183.9841914</v>
+        <v>-2.09694106</v>
       </c>
       <c r="J69" t="n">
-        <v>136.28002782</v>
+        <v>-1.18870531</v>
       </c>
       <c r="K69" t="n">
-        <v>-31.30440671999998</v>
+        <v>0.8999840899999999</v>
       </c>
       <c r="L69" t="n">
-        <v>-118.90813709</v>
+        <v>-1.07992369</v>
       </c>
       <c r="M69" t="n">
-        <v>-93.30377819</v>
+        <v>-8.13542947</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>造紙工業右下</t>
+          <t>造紙工業平</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>7.5358798</v>
+        <v>-3.39045584</v>
       </c>
       <c r="D70" t="n">
-        <v>-2.18453111</v>
+        <v>-4.06147909</v>
       </c>
       <c r="E70" t="n">
-        <v>-4.28064262</v>
+        <v>-3.60733925</v>
       </c>
       <c r="F70" t="n">
-        <v>-9.848016550000001</v>
+        <v>-1.16033294</v>
       </c>
       <c r="G70" t="n">
-        <v>-11.75977663</v>
+        <v>-1.55525517</v>
       </c>
       <c r="H70" t="n">
-        <v>-14.45543988</v>
+        <v>0.15859867</v>
       </c>
       <c r="I70" t="n">
-        <v>-8.60103045</v>
+        <v>-0.01651628</v>
       </c>
       <c r="J70" t="n">
-        <v>1.481096</v>
+        <v>0.93115824</v>
       </c>
       <c r="K70" t="n">
-        <v>-2.09694106</v>
+        <v>0.15324129</v>
       </c>
       <c r="L70" t="n">
-        <v>-1.18870531</v>
+        <v>2.0141396</v>
       </c>
       <c r="M70" t="n">
-        <v>0.8999840899999999</v>
+        <v>0.94456732</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>造紙工業平</t>
+          <t>運動休閒右上</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
-        <v>-1.69268373</v>
+        <v>-5.49167339</v>
       </c>
       <c r="D71" t="n">
-        <v>-3.23010772</v>
+        <v>-6.985563310000001</v>
       </c>
       <c r="E71" t="n">
-        <v>-3.39045584</v>
+        <v>6.14054282</v>
       </c>
       <c r="F71" t="n">
-        <v>-4.06147909</v>
+        <v>22.89727625</v>
       </c>
       <c r="G71" t="n">
-        <v>-3.60733925</v>
+        <v>39.58487804</v>
       </c>
       <c r="H71" t="n">
-        <v>-1.16033294</v>
+        <v>49.03197814</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.55525517</v>
+        <v>20.29127258</v>
       </c>
       <c r="J71" t="n">
-        <v>0.15859867</v>
+        <v>24.00895878</v>
       </c>
       <c r="K71" t="n">
-        <v>-0.01651628</v>
+        <v>34.17125779</v>
       </c>
       <c r="L71" t="n">
-        <v>0.93115824</v>
+        <v>-3.0706811</v>
       </c>
       <c r="M71" t="n">
-        <v>0.15324129</v>
+        <v>-7.127004649999999</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右上</t>
+          <t>運動休閒右下</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>-21.49287157</v>
+        <v>-13.46545672999999</v>
       </c>
       <c r="D72" t="n">
-        <v>-29.75249595</v>
+        <v>-142.15576028</v>
       </c>
       <c r="E72" t="n">
-        <v>-5.49167339</v>
+        <v>-103.65398381</v>
       </c>
       <c r="F72" t="n">
-        <v>-6.985563310000001</v>
+        <v>-29.97898556</v>
       </c>
       <c r="G72" t="n">
-        <v>6.14054282</v>
+        <v>-20.96570658</v>
       </c>
       <c r="H72" t="n">
-        <v>22.89727625</v>
+        <v>-82.82987403</v>
       </c>
       <c r="I72" t="n">
-        <v>39.58487804</v>
+        <v>-117.56860161</v>
       </c>
       <c r="J72" t="n">
-        <v>49.03197814</v>
+        <v>-41.76354069999999</v>
       </c>
       <c r="K72" t="n">
-        <v>20.29127258</v>
+        <v>-96.87037564000001</v>
       </c>
       <c r="L72" t="n">
-        <v>24.00895878</v>
+        <v>-62.8772119</v>
       </c>
       <c r="M72" t="n">
-        <v>34.17125779</v>
+        <v>-12.82282402</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右下</t>
+          <t>運動休閒平</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
-        <v>-69.08854124</v>
+        <v>-0.009413699999999837</v>
       </c>
       <c r="D73" t="n">
-        <v>-118.02431299</v>
+        <v>-10.30417954</v>
       </c>
       <c r="E73" t="n">
-        <v>-11.99343319999999</v>
+        <v>1.9869591</v>
       </c>
       <c r="F73" t="n">
-        <v>-143.94763791</v>
+        <v>13.19129905</v>
       </c>
       <c r="G73" t="n">
-        <v>-102.25610116</v>
+        <v>5.14271512</v>
       </c>
       <c r="H73" t="n">
-        <v>-27.91482</v>
+        <v>-8.77292924</v>
       </c>
       <c r="I73" t="n">
-        <v>-17.14059748</v>
+        <v>-8.96068459</v>
       </c>
       <c r="J73" t="n">
-        <v>-81.91163204999999</v>
+        <v>-20.04120091</v>
       </c>
       <c r="K73" t="n">
-        <v>-115.31227011</v>
+        <v>-30.54986415</v>
       </c>
       <c r="L73" t="n">
-        <v>-37.30362026</v>
+        <v>-15.30492149</v>
       </c>
       <c r="M73" t="n">
-        <v>-103.56392674</v>
+        <v>-8.88836045</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>運動休閒平</t>
+          <t>金融保險右上</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
-        <v>10.55354681</v>
+        <v>-491.5545925</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.02417495999999996</v>
+        <v>-955.75845715</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.48143723</v>
+        <v>77.77591090999999</v>
       </c>
       <c r="F74" t="n">
-        <v>-8.51230191</v>
+        <v>945.98594926</v>
       </c>
       <c r="G74" t="n">
-        <v>0.58907645</v>
+        <v>863.70488928</v>
       </c>
       <c r="H74" t="n">
-        <v>11.12713349</v>
+        <v>1242.79248807</v>
       </c>
       <c r="I74" t="n">
-        <v>1.31760602</v>
+        <v>851.86550735</v>
       </c>
       <c r="J74" t="n">
-        <v>-9.691171220000001</v>
+        <v>703.0305864300001</v>
       </c>
       <c r="K74" t="n">
-        <v>-11.21701609</v>
+        <v>664.72535027</v>
       </c>
       <c r="L74" t="n">
-        <v>-24.50112135</v>
+        <v>656.9999549300001</v>
       </c>
       <c r="M74" t="n">
-        <v>-23.85631305</v>
+        <v>819.4355921499999</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>金融保險右上</t>
+          <t>金融保險右下</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
-        <v>-1344.25654867</v>
+        <v>-375.3300158500001</v>
       </c>
       <c r="D75" t="n">
-        <v>-1513.10008246</v>
+        <v>-399.01998549</v>
       </c>
       <c r="E75" t="n">
-        <v>-486.52127426</v>
+        <v>-351.15875377</v>
       </c>
       <c r="F75" t="n">
-        <v>-936.91281313</v>
+        <v>-120.53167</v>
       </c>
       <c r="G75" t="n">
-        <v>59.42146735</v>
+        <v>71.85420393</v>
       </c>
       <c r="H75" t="n">
-        <v>903.2323206300001</v>
+        <v>166.88105806</v>
       </c>
       <c r="I75" t="n">
-        <v>800.7780561700001</v>
+        <v>-29.24538225</v>
       </c>
       <c r="J75" t="n">
-        <v>1167.48715472</v>
+        <v>-217.03758715</v>
       </c>
       <c r="K75" t="n">
-        <v>823.8283143199999</v>
+        <v>-381.0536326899999</v>
       </c>
       <c r="L75" t="n">
-        <v>653.6134696299999</v>
+        <v>-510.1900488100001</v>
       </c>
       <c r="M75" t="n">
-        <v>665.12436012</v>
+        <v>-257.06344158</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>金融保險右下</t>
+          <t>金融保險平</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>-454.77151971</v>
+        <v>-49.69680476000001</v>
       </c>
       <c r="D76" t="n">
-        <v>-641.20146943</v>
+        <v>-87.14577436000002</v>
       </c>
       <c r="E76" t="n">
-        <v>-347.05644305</v>
+        <v>6.883263300000002</v>
       </c>
       <c r="F76" t="n">
-        <v>-359.8776884299999</v>
+        <v>122.20166119</v>
       </c>
       <c r="G76" t="n">
-        <v>-343.74413127</v>
+        <v>33.32606508999999</v>
       </c>
       <c r="H76" t="n">
-        <v>-136.81080979</v>
+        <v>32.0121898</v>
       </c>
       <c r="I76" t="n">
-        <v>34.65447583</v>
+        <v>2.699553660000002</v>
       </c>
       <c r="J76" t="n">
-        <v>112.2585677</v>
+        <v>16.53077912</v>
       </c>
       <c r="K76" t="n">
-        <v>-45.85452738</v>
+        <v>58.56651676</v>
       </c>
       <c r="L76" t="n">
-        <v>-206.11673481</v>
+        <v>51.54869252</v>
       </c>
       <c r="M76" t="n">
-        <v>-343.8864405899999</v>
+        <v>63.32101605</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>金融保險平</t>
+          <t>金融業右上</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="n">
-        <v>-125.06047454</v>
+        <v>-0.0003751</v>
       </c>
       <c r="D77" t="n">
-        <v>-179.56732411</v>
+        <v>-0.00072667</v>
       </c>
       <c r="E77" t="n">
-        <v>-83.0036958</v>
+        <v>-0.00031853</v>
       </c>
       <c r="F77" t="n">
-        <v>-145.13371544</v>
+        <v>-0.00042214</v>
       </c>
       <c r="G77" t="n">
-        <v>17.82308436</v>
+        <v>0.00035191</v>
       </c>
       <c r="H77" t="n">
-        <v>181.23442961</v>
+        <v>0.0006016</v>
       </c>
       <c r="I77" t="n">
-        <v>133.4526263</v>
+        <v>0.00119589</v>
       </c>
       <c r="J77" t="n">
-        <v>161.94001351</v>
+        <v>0.00222055</v>
       </c>
       <c r="K77" t="n">
-        <v>47.34589182</v>
+        <v>0.00226234</v>
       </c>
       <c r="L77" t="n">
-        <v>55.02704358</v>
+        <v>0.00101082</v>
       </c>
       <c r="M77" t="n">
-        <v>21.00031481</v>
+        <v>9.988e-05</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>金融業右上</t>
+          <t>金融業右下</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
-        <v>-0.0006594299999999999</v>
+        <v>-9.306000000000001e-05</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.00071329</v>
+        <v>-0.00439828</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.0003751</v>
+        <v>-0.005935770000000001</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.00072667</v>
+        <v>-0.006376339999999999</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.00031853</v>
+        <v>-0.00146164</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.00042214</v>
+        <v>0.0001785999999999999</v>
       </c>
       <c r="I78" t="n">
-        <v>0.00035191</v>
+        <v>0.00166505</v>
       </c>
       <c r="J78" t="n">
-        <v>0.0006016</v>
+        <v>0.00481058</v>
       </c>
       <c r="K78" t="n">
-        <v>0.00119589</v>
+        <v>0.00272902</v>
       </c>
       <c r="L78" t="n">
-        <v>0.00222055</v>
+        <v>9.011000000000007e-05</v>
       </c>
       <c r="M78" t="n">
-        <v>0.00226234</v>
+        <v>0.0004795100000000002</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>金融業右下</t>
+          <t>金融業平</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="n">
-        <v>0.00104378</v>
+        <v>-0.00052145</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.00267729</v>
+        <v>-0.00052038</v>
       </c>
       <c r="E79" t="n">
-        <v>-7.551999999999998e-05</v>
+        <v>-0.00049876</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.00437749</v>
+        <v>-0.00010349</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.00592591</v>
+        <v>0.00149008</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.006374369999999999</v>
+        <v>0.00167124</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.00145684</v>
+        <v>0.00103193</v>
       </c>
       <c r="J79" t="n">
-        <v>0.0001739999999999999</v>
+        <v>0.00057835</v>
       </c>
       <c r="K79" t="n">
-        <v>0.00166164</v>
+        <v>9.465e-05</v>
       </c>
       <c r="L79" t="n">
-        <v>0.00480599</v>
+        <v>0.00013897</v>
       </c>
       <c r="M79" t="n">
-        <v>0.00271667</v>
+        <v>6.415e-05</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>金融業平</t>
+          <t>鋼鐵工業右上</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="n">
-        <v>-0.00026699</v>
+        <v>5.127412570000001</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.00035282</v>
+        <v>0.3745234199999999</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.00053899</v>
+        <v>-13.08952523</v>
       </c>
       <c r="F80" t="n">
-        <v>-0.0005411700000000001</v>
+        <v>-4.331212519999999</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.00050862</v>
+        <v>-10.25827174</v>
       </c>
       <c r="H80" t="n">
-        <v>-0.00010546</v>
+        <v>8.421552140000001</v>
       </c>
       <c r="I80" t="n">
-        <v>0.00148528</v>
+        <v>-10.13260721</v>
       </c>
       <c r="J80" t="n">
-        <v>0.00167584</v>
+        <v>-9.68964107</v>
       </c>
       <c r="K80" t="n">
-        <v>0.00103534</v>
+        <v>4.868124629999999</v>
       </c>
       <c r="L80" t="n">
-        <v>0.0005829400000000001</v>
+        <v>12.18883922</v>
       </c>
       <c r="M80" t="n">
-        <v>0.000107</v>
+        <v>-4.46799539</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上</t>
+          <t>鋼鐵工業右下</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>489.0815217</v>
+        <v>6.615816210000001</v>
       </c>
       <c r="D81" t="n">
-        <v>750.7487125599999</v>
+        <v>-60.44946178</v>
       </c>
       <c r="E81" t="n">
-        <v>741.8872466500001</v>
+        <v>-91.46511696</v>
       </c>
       <c r="F81" t="n">
-        <v>201.67650435</v>
+        <v>-106.86700106</v>
       </c>
       <c r="G81" t="n">
-        <v>-141.11423658</v>
+        <v>-61.40586277000001</v>
       </c>
       <c r="H81" t="n">
-        <v>0.7313264700000002</v>
+        <v>-43.15341879</v>
       </c>
       <c r="I81" t="n">
-        <v>-176.67389534</v>
+        <v>-61.66911995</v>
       </c>
       <c r="J81" t="n">
-        <v>-79.90343278</v>
+        <v>-42.28803382</v>
       </c>
       <c r="K81" t="n">
-        <v>-228.13185528</v>
+        <v>-15.58922796</v>
       </c>
       <c r="L81" t="n">
-        <v>74.18891708000001</v>
+        <v>32.84825903000001</v>
       </c>
       <c r="M81" t="n">
-        <v>-251.67991232</v>
+        <v>93.29633133</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
-        <v>0</v>
-      </c>
+          <t>鋼鐵工業平</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
-        <v>-46.83917436999999</v>
+        <v>802.0624256400001</v>
       </c>
       <c r="D82" t="n">
-        <v>-85.97153582999999</v>
+        <v>233.50054861</v>
       </c>
       <c r="E82" t="n">
-        <v>3.881013460000001</v>
+        <v>-6.471851030000002</v>
       </c>
       <c r="F82" t="n">
-        <v>-72.54789876</v>
+        <v>94.32777211</v>
       </c>
       <c r="G82" t="n">
-        <v>-103.93206944</v>
+        <v>-53.45805922999999</v>
       </c>
       <c r="H82" t="n">
-        <v>-113.73505718</v>
+        <v>0.2473854100000039</v>
       </c>
       <c r="I82" t="n">
-        <v>-68.4080062</v>
+        <v>-169.90165851</v>
       </c>
       <c r="J82" t="n">
-        <v>-45.60012753</v>
+        <v>94.84075396999999</v>
       </c>
       <c r="K82" t="n">
-        <v>-65.01996659</v>
+        <v>-153.37305345</v>
       </c>
       <c r="L82" t="n">
-        <v>-39.60682835</v>
+        <v>-343.65384548</v>
       </c>
       <c r="M82" t="n">
-        <v>-10.18949832</v>
+        <v>-547.62890373</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業平</t>
+          <t>電器電纜右上</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>21.61024113</v>
+        <v>68.03330789</v>
       </c>
       <c r="D83" t="n">
-        <v>18.5110399</v>
+        <v>-4.41017006</v>
       </c>
       <c r="E83" t="n">
-        <v>67.25528339</v>
+        <v>-6.688197980000001</v>
       </c>
       <c r="F83" t="n">
-        <v>44.31661445</v>
+        <v>39.15618257</v>
       </c>
       <c r="G83" t="n">
-        <v>134.47134333</v>
+        <v>88.37693567999999</v>
       </c>
       <c r="H83" t="n">
-        <v>96.22012865000001</v>
+        <v>173.80208869</v>
       </c>
       <c r="I83" t="n">
-        <v>120.4026709</v>
+        <v>68.31111571000001</v>
       </c>
       <c r="J83" t="n">
-        <v>91.55941697</v>
+        <v>-15.21283794</v>
       </c>
       <c r="K83" t="n">
-        <v>52.12557176</v>
+        <v>-17.71552102</v>
       </c>
       <c r="L83" t="n">
-        <v>8.03369266</v>
+        <v>-64.05499739</v>
       </c>
       <c r="M83" t="n">
-        <v>98.18599175999999</v>
+        <v>-108.28490628</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右上</t>
+          <t>電器電纜右下</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
-        <v>-14.46518195</v>
+        <v>102.04973315</v>
       </c>
       <c r="D84" t="n">
-        <v>37.21932350000001</v>
+        <v>-116.03766855</v>
       </c>
       <c r="E84" t="n">
-        <v>68.03134521</v>
+        <v>-143.59839725</v>
       </c>
       <c r="F84" t="n">
-        <v>-2.350372119999999</v>
+        <v>-122.34910587</v>
       </c>
       <c r="G84" t="n">
-        <v>-4.571539939999999</v>
+        <v>-54.08839686000001</v>
       </c>
       <c r="H84" t="n">
-        <v>39.14585281</v>
+        <v>-10.32371517</v>
       </c>
       <c r="I84" t="n">
-        <v>87.22141015999999</v>
+        <v>20.68578092</v>
       </c>
       <c r="J84" t="n">
-        <v>170.87627227</v>
+        <v>50.43591372</v>
       </c>
       <c r="K84" t="n">
-        <v>64.92778369</v>
+        <v>20.67704156</v>
       </c>
       <c r="L84" t="n">
-        <v>-16.8321213</v>
+        <v>39.12544062</v>
       </c>
       <c r="M84" t="n">
-        <v>-17.33743878</v>
+        <v>82.69030088000001</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右下</t>
+          <t>電器電纜平</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>7.24090026</v>
+        <v>-1.10998745</v>
       </c>
       <c r="D85" t="n">
-        <v>-6.584324479999999</v>
+        <v>-17.7452246</v>
       </c>
       <c r="E85" t="n">
-        <v>102.05297551</v>
+        <v>-22.43654935</v>
       </c>
       <c r="F85" t="n">
-        <v>-115.80629482</v>
+        <v>-6.625887400000001</v>
       </c>
       <c r="G85" t="n">
-        <v>-143.5880583</v>
+        <v>10.56383229</v>
       </c>
       <c r="H85" t="n">
-        <v>-122.46679617</v>
+        <v>91.58342936</v>
       </c>
       <c r="I85" t="n">
-        <v>-54.09129918000001</v>
+        <v>307.9963481</v>
       </c>
       <c r="J85" t="n">
-        <v>-10.37837567</v>
+        <v>127.17968981</v>
       </c>
       <c r="K85" t="n">
-        <v>20.72719751</v>
+        <v>35.51974835</v>
       </c>
       <c r="L85" t="n">
-        <v>50.52978478</v>
+        <v>-44.38686312000001</v>
       </c>
       <c r="M85" t="n">
-        <v>20.65799403</v>
+        <v>-80.33943861</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>電器電纜平</t>
+          <t>電子通路業右上</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
-        <v>-23.38357864</v>
+        <v>81.89622543999999</v>
       </c>
       <c r="D86" t="n">
-        <v>-18.17317994</v>
+        <v>36.94664319</v>
       </c>
       <c r="E86" t="n">
-        <v>-1.11126713</v>
+        <v>39.92671712</v>
       </c>
       <c r="F86" t="n">
-        <v>-20.03639627</v>
+        <v>-7.647300829999998</v>
       </c>
       <c r="G86" t="n">
-        <v>-24.56354634</v>
+        <v>40.5057899</v>
       </c>
       <c r="H86" t="n">
-        <v>-6.497867340000001</v>
+        <v>0.2115746600000012</v>
       </c>
       <c r="I86" t="n">
-        <v>11.72226013</v>
+        <v>-73.51357708</v>
       </c>
       <c r="J86" t="n">
-        <v>94.56390628</v>
+        <v>-120.38293081</v>
       </c>
       <c r="K86" t="n">
-        <v>311.33826353</v>
+        <v>-28.81328676999999</v>
       </c>
       <c r="L86" t="n">
-        <v>128.70510211</v>
+        <v>26.42893274</v>
       </c>
       <c r="M86" t="n">
-        <v>35.16071363999999</v>
+        <v>-19.94011926</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右上</t>
+          <t>電子通路業右下</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>42.12402878</v>
+        <v>-8.843038400000001</v>
       </c>
       <c r="D87" t="n">
-        <v>24.19335857</v>
+        <v>-41.8310306</v>
       </c>
       <c r="E87" t="n">
-        <v>81.89622543999999</v>
+        <v>-36.82459142</v>
       </c>
       <c r="F87" t="n">
-        <v>36.94664319</v>
+        <v>-13.84526226</v>
       </c>
       <c r="G87" t="n">
-        <v>39.92671712</v>
+        <v>9.219265179999997</v>
       </c>
       <c r="H87" t="n">
-        <v>-7.647300829999998</v>
+        <v>-7.030059699999999</v>
       </c>
       <c r="I87" t="n">
-        <v>40.5057899</v>
+        <v>-4.059091990000001</v>
       </c>
       <c r="J87" t="n">
-        <v>0.2115746600000012</v>
+        <v>-47.29568497</v>
       </c>
       <c r="K87" t="n">
-        <v>-73.51357708</v>
+        <v>-104.1367929</v>
       </c>
       <c r="L87" t="n">
-        <v>-120.38293081</v>
+        <v>-134.84861918</v>
       </c>
       <c r="M87" t="n">
-        <v>-28.81328676999999</v>
+        <v>-125.00312348</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右下</t>
+          <t>電子通路業平</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
-        <v>7.28057738</v>
+        <v>26.49219782</v>
       </c>
       <c r="D88" t="n">
-        <v>-21.34147909</v>
+        <v>-37.75629203</v>
       </c>
       <c r="E88" t="n">
-        <v>-9.3358998</v>
+        <v>10.21864789</v>
       </c>
       <c r="F88" t="n">
-        <v>-40.89610144</v>
+        <v>55.6293562</v>
       </c>
       <c r="G88" t="n">
-        <v>-35.51571165</v>
+        <v>124.78835097</v>
       </c>
       <c r="H88" t="n">
-        <v>-13.73270536</v>
+        <v>130.32502002</v>
       </c>
       <c r="I88" t="n">
-        <v>8.53210361</v>
+        <v>65.63657513</v>
       </c>
       <c r="J88" t="n">
-        <v>-7.17190724</v>
+        <v>-19.16895581</v>
       </c>
       <c r="K88" t="n">
-        <v>-3.542795019999999</v>
+        <v>-71.83025827</v>
       </c>
       <c r="L88" t="n">
-        <v>-45.59276418</v>
+        <v>-44.42444898</v>
       </c>
       <c r="M88" t="n">
-        <v>-99.21578414</v>
+        <v>-63.71747357000001</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>電子通路業平</t>
+          <t>電子零組件業右上</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>37.68138432</v>
+        <v>675.7218513099999</v>
       </c>
       <c r="D89" t="n">
-        <v>-27.74649561</v>
+        <v>1938.81589722</v>
       </c>
       <c r="E89" t="n">
-        <v>26.98505922</v>
+        <v>2721.40570911</v>
       </c>
       <c r="F89" t="n">
-        <v>-38.69122119</v>
+        <v>233.9174681800001</v>
       </c>
       <c r="G89" t="n">
-        <v>8.909768119999999</v>
+        <v>3032.472158439999</v>
       </c>
       <c r="H89" t="n">
-        <v>55.5167993</v>
+        <v>1243.25631578</v>
       </c>
       <c r="I89" t="n">
-        <v>125.47551254</v>
+        <v>826.02914661</v>
       </c>
       <c r="J89" t="n">
-        <v>130.46686756</v>
+        <v>3432.44482566</v>
       </c>
       <c r="K89" t="n">
-        <v>65.12027816</v>
+        <v>5007.490816279999</v>
       </c>
       <c r="L89" t="n">
-        <v>-20.8718766</v>
+        <v>5005.6008972</v>
       </c>
       <c r="M89" t="n">
-        <v>-76.75126703000001</v>
+        <v>5017.250771810001</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右上</t>
+          <t>電子零組件業右下</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>2535.16370684</v>
+        <v>1082.63682107</v>
       </c>
       <c r="D90" t="n">
-        <v>1754.35238786</v>
+        <v>61.51201302</v>
       </c>
       <c r="E90" t="n">
-        <v>725.1192927100001</v>
+        <v>135.01031749</v>
       </c>
       <c r="F90" t="n">
-        <v>1890.14496335</v>
+        <v>-319.59804829</v>
       </c>
       <c r="G90" t="n">
-        <v>2886.93956966</v>
+        <v>-260.44057116</v>
       </c>
       <c r="H90" t="n">
-        <v>409.9676745900001</v>
+        <v>-587.90753496</v>
       </c>
       <c r="I90" t="n">
-        <v>3027.59866921</v>
+        <v>-475.41634619</v>
       </c>
       <c r="J90" t="n">
-        <v>959.4811870999999</v>
+        <v>-368.05320958</v>
       </c>
       <c r="K90" t="n">
-        <v>921.8883400300001</v>
+        <v>-14.35892189</v>
       </c>
       <c r="L90" t="n">
-        <v>3745.82889977</v>
+        <v>-363.26591111</v>
       </c>
       <c r="M90" t="n">
-        <v>5233.41588458</v>
+        <v>-791.49813785</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右下</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>0</v>
-      </c>
+          <t>電子零組件業平</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>274.92690075</v>
+        <v>-212.84212553</v>
       </c>
       <c r="D91" t="n">
-        <v>132.4067022</v>
+        <v>-500.58380029</v>
       </c>
       <c r="E91" t="n">
-        <v>164.43456362</v>
+        <v>-407.9659284700001</v>
       </c>
       <c r="F91" t="n">
-        <v>65.63399751999999</v>
+        <v>-380.1795164600001</v>
       </c>
       <c r="G91" t="n">
-        <v>-6.879982530000001</v>
+        <v>54.60264371999999</v>
       </c>
       <c r="H91" t="n">
-        <v>-15.60161395</v>
+        <v>-547.96460986</v>
       </c>
       <c r="I91" t="n">
-        <v>-16.00762839</v>
+        <v>-532.2037275800001</v>
       </c>
       <c r="J91" t="n">
-        <v>-47.2644274</v>
+        <v>-511.2457994</v>
       </c>
       <c r="K91" t="n">
-        <v>-124.14966563</v>
+        <v>-279.5068743900001</v>
       </c>
       <c r="L91" t="n">
-        <v>-106.07986476</v>
+        <v>-672.4342682499999</v>
       </c>
       <c r="M91" t="n">
-        <v>-61.85437630999999</v>
+        <v>-865.22479599</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業平</t>
+          <t>電機機械右上</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>481.77049984</v>
+        <v>-128.97794832</v>
       </c>
       <c r="D92" t="n">
-        <v>746.7007588699998</v>
+        <v>185.30484018</v>
       </c>
       <c r="E92" t="n">
-        <v>809.64075587</v>
+        <v>303.0147502099999</v>
       </c>
       <c r="F92" t="n">
-        <v>-346.64333567</v>
+        <v>-1127.25673355</v>
       </c>
       <c r="G92" t="n">
-        <v>-227.63665588</v>
+        <v>-1206.15649694</v>
       </c>
       <c r="H92" t="n">
-        <v>-599.87995288</v>
+        <v>-387.8385127399999</v>
       </c>
       <c r="I92" t="n">
-        <v>-57.05884498</v>
+        <v>815.78342775</v>
       </c>
       <c r="J92" t="n">
-        <v>-958.1662586899999</v>
+        <v>-141.77400986</v>
       </c>
       <c r="K92" t="n">
-        <v>-863.50434671</v>
+        <v>56.85748323999998</v>
       </c>
       <c r="L92" t="n">
-        <v>-873.4107989400001</v>
+        <v>-1144.31158492</v>
       </c>
       <c r="M92" t="n">
-        <v>-193.70222852</v>
+        <v>-36.69571987999992</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>電機機械右上</t>
+          <t>電機機械右下</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>59.08262594</v>
+        <v>59.78359257</v>
       </c>
       <c r="D93" t="n">
-        <v>-164.69119126</v>
+        <v>-48.40637532</v>
       </c>
       <c r="E93" t="n">
-        <v>-128.95365214</v>
+        <v>-27.57171820000002</v>
       </c>
       <c r="F93" t="n">
-        <v>185.34105938</v>
+        <v>-25.67948576</v>
       </c>
       <c r="G93" t="n">
-        <v>303.03071299</v>
+        <v>43.66869122</v>
       </c>
       <c r="H93" t="n">
-        <v>-1127.25072354</v>
+        <v>-81.55400834000001</v>
       </c>
       <c r="I93" t="n">
-        <v>-1206.15067931</v>
+        <v>60.49007137</v>
       </c>
       <c r="J93" t="n">
-        <v>-387.8413038099999</v>
+        <v>121.80988964</v>
       </c>
       <c r="K93" t="n">
-        <v>815.78799864</v>
+        <v>71.00693721</v>
       </c>
       <c r="L93" t="n">
-        <v>-141.74496392</v>
+        <v>113.34036996</v>
       </c>
       <c r="M93" t="n">
-        <v>56.89468007999999</v>
+        <v>40.45147514999999</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>電機機械右下</t>
+          <t>電機機械平</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>-6.14492606</v>
+        <v>12.73378405</v>
       </c>
       <c r="D94" t="n">
-        <v>-41.9563862</v>
+        <v>-15.63688381</v>
       </c>
       <c r="E94" t="n">
-        <v>13.21991144</v>
+        <v>38.33344365</v>
       </c>
       <c r="F94" t="n">
-        <v>-60.03639301</v>
+        <v>47.00269811</v>
       </c>
       <c r="G94" t="n">
-        <v>-99.56108504000001</v>
+        <v>49.58149492</v>
       </c>
       <c r="H94" t="n">
-        <v>-27.59891615</v>
+        <v>101.02052811</v>
       </c>
       <c r="I94" t="n">
-        <v>-2.575576679999994</v>
+        <v>135.70280701</v>
       </c>
       <c r="J94" t="n">
-        <v>-67.59408645000001</v>
+        <v>65.6116761</v>
       </c>
       <c r="K94" t="n">
-        <v>29.72607914</v>
+        <v>-30.14520415</v>
       </c>
       <c r="L94" t="n">
-        <v>29.64006926</v>
+        <v>-56.61067838</v>
       </c>
       <c r="M94" t="n">
-        <v>-30.16457714</v>
+        <v>-71.72352194999999</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>電機機械平</t>
+          <t>電腦及週邊設備業右上</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>-45.38380889</v>
+        <v>981.0393276199999</v>
       </c>
       <c r="D95" t="n">
-        <v>-54.68577789</v>
+        <v>3039.78159024</v>
       </c>
       <c r="E95" t="n">
-        <v>59.273169</v>
+        <v>2679.40341063</v>
       </c>
       <c r="F95" t="n">
-        <v>-4.04308532</v>
+        <v>398.16777622</v>
       </c>
       <c r="G95" t="n">
-        <v>110.30684771</v>
+        <v>4014.56995358</v>
       </c>
       <c r="H95" t="n">
-        <v>48.91611849</v>
+        <v>1780.27417029</v>
       </c>
       <c r="I95" t="n">
-        <v>95.81994519</v>
+        <v>2571.2515713</v>
       </c>
       <c r="J95" t="n">
-        <v>87.06339729000001</v>
+        <v>3369.1646542</v>
       </c>
       <c r="K95" t="n">
-        <v>166.46222835</v>
+        <v>2900.04081789</v>
       </c>
       <c r="L95" t="n">
-        <v>157.75245054</v>
+        <v>391.9865974</v>
       </c>
       <c r="M95" t="n">
-        <v>70.98911336000002</v>
+        <v>-3414.60216891</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr"/>
+          <t>電腦及週邊設備業右下</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>0</v>
+      </c>
       <c r="C96" t="n">
-        <v>1273.52849336</v>
+        <v>13.07843566</v>
       </c>
       <c r="D96" t="n">
-        <v>646.76043126</v>
+        <v>-82.78174076000001</v>
       </c>
       <c r="E96" t="n">
-        <v>718.6346194299999</v>
+        <v>-38.17457037</v>
       </c>
       <c r="F96" t="n">
-        <v>2942.98355138</v>
+        <v>30.58266309999999</v>
       </c>
       <c r="G96" t="n">
-        <v>2681.95247828</v>
+        <v>289.99602877</v>
       </c>
       <c r="H96" t="n">
-        <v>343.3241458</v>
+        <v>26.90707316</v>
       </c>
       <c r="I96" t="n">
-        <v>4030.16582431</v>
+        <v>-22.35415357</v>
       </c>
       <c r="J96" t="n">
-        <v>1729.38756114</v>
+        <v>-320.91429934</v>
       </c>
       <c r="K96" t="n">
-        <v>2625.1180385</v>
+        <v>-537.5567834</v>
       </c>
       <c r="L96" t="n">
-        <v>3441.32132545</v>
+        <v>-567.91663938</v>
       </c>
       <c r="M96" t="n">
-        <v>3032.12116609</v>
+        <v>-621.6234280599999</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下</t>
+          <t>電腦及週邊設備業平</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>93.21859898</v>
+        <v>-211.66196497</v>
       </c>
       <c r="D97" t="n">
-        <v>-55.76555674</v>
+        <v>-2.047810939999996</v>
       </c>
       <c r="E97" t="n">
-        <v>44.23255601</v>
+        <v>40.63617187</v>
       </c>
       <c r="F97" t="n">
-        <v>-38.08882206000001</v>
+        <v>-60.09170362</v>
       </c>
       <c r="G97" t="n">
-        <v>-20.67808733</v>
+        <v>101.62346198</v>
       </c>
       <c r="H97" t="n">
-        <v>27.94534482</v>
+        <v>-49.76638192</v>
       </c>
       <c r="I97" t="n">
-        <v>250.15528983</v>
+        <v>103.88289413</v>
       </c>
       <c r="J97" t="n">
-        <v>7.289573850000001</v>
+        <v>49.88564175999999</v>
       </c>
       <c r="K97" t="n">
-        <v>-66.99732744000001</v>
+        <v>120.5395721</v>
       </c>
       <c r="L97" t="n">
-        <v>-298.0557950200001</v>
+        <v>-87.70383674</v>
       </c>
       <c r="M97" t="n">
-        <v>-489.15865882</v>
+        <v>-14.75605133000001</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平</t>
+          <t>食品工業右上</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
-        <v>-18.44917057</v>
+        <v>-23.61119333</v>
       </c>
       <c r="D98" t="n">
-        <v>-69.25926489999999</v>
+        <v>-20.82516393</v>
       </c>
       <c r="E98" t="n">
-        <v>19.31189633</v>
+        <v>-15.11263473</v>
       </c>
       <c r="F98" t="n">
-        <v>49.75589112999999</v>
+        <v>2.57676404</v>
       </c>
       <c r="G98" t="n">
-        <v>20.77407199</v>
+        <v>17.61770092</v>
       </c>
       <c r="H98" t="n">
-        <v>0.6432168899999976</v>
+        <v>27.36522565</v>
       </c>
       <c r="I98" t="n">
-        <v>129.99128213</v>
+        <v>21.462162</v>
       </c>
       <c r="J98" t="n">
-        <v>24.64547797</v>
+        <v>2.43355516</v>
       </c>
       <c r="K98" t="n">
-        <v>93.41526143999999</v>
+        <v>3.428873750000001</v>
       </c>
       <c r="L98" t="n">
-        <v>-47.85259394</v>
+        <v>20.06785335</v>
       </c>
       <c r="M98" t="n">
-        <v>-63.48290797</v>
+        <v>29.26245925</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>食品工業右上</t>
+          <t>食品工業右下</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>-30.06779766</v>
+        <v>2.86518501</v>
       </c>
       <c r="D99" t="n">
-        <v>-26.68584296</v>
+        <v>0.8719472000000004</v>
       </c>
       <c r="E99" t="n">
-        <v>-23.61119333</v>
+        <v>-4.212290649999999</v>
       </c>
       <c r="F99" t="n">
-        <v>-20.82516393</v>
+        <v>9.207508240000001</v>
       </c>
       <c r="G99" t="n">
-        <v>-15.11263473</v>
+        <v>12.72317876</v>
       </c>
       <c r="H99" t="n">
-        <v>2.57676404</v>
+        <v>17.20167136</v>
       </c>
       <c r="I99" t="n">
-        <v>17.61770092</v>
+        <v>5.82127413</v>
       </c>
       <c r="J99" t="n">
-        <v>27.36522565</v>
+        <v>-1.51808174</v>
       </c>
       <c r="K99" t="n">
-        <v>21.462162</v>
+        <v>-12.99658263</v>
       </c>
       <c r="L99" t="n">
-        <v>2.43355516</v>
+        <v>-16.94004654</v>
       </c>
       <c r="M99" t="n">
-        <v>3.428873750000001</v>
+        <v>-11.90809048</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>食品工業右下</t>
+          <t>食品工業平</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="n">
-        <v>-10.56322777</v>
+        <v>-161.64074142</v>
       </c>
       <c r="D100" t="n">
-        <v>-11.32936548</v>
+        <v>-233.61821155</v>
       </c>
       <c r="E100" t="n">
-        <v>2.9838397</v>
+        <v>-115.42939718</v>
       </c>
       <c r="F100" t="n">
-        <v>1.30858839</v>
+        <v>-27.29259622</v>
       </c>
       <c r="G100" t="n">
-        <v>-3.510833229999999</v>
+        <v>-51.18365041</v>
       </c>
       <c r="H100" t="n">
-        <v>10.104738</v>
+        <v>-94.26093568999998</v>
       </c>
       <c r="I100" t="n">
-        <v>13.23628785</v>
+        <v>-157.11085879</v>
       </c>
       <c r="J100" t="n">
-        <v>17.2616073</v>
+        <v>-218.50169557</v>
       </c>
       <c r="K100" t="n">
-        <v>6.075689359999999</v>
+        <v>-239.00642094</v>
       </c>
       <c r="L100" t="n">
-        <v>-1.47053638</v>
+        <v>-229.12936233</v>
       </c>
       <c r="M100" t="n">
-        <v>-12.68556489</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="1" t="inlineStr">
-        <is>
-          <t>食品工業平</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr"/>
-      <c r="C101" t="n">
-        <v>-265.95067557</v>
-      </c>
-      <c r="D101" t="n">
-        <v>-277.00373254</v>
-      </c>
-      <c r="E101" t="n">
-        <v>-161.75939611</v>
-      </c>
-      <c r="F101" t="n">
-        <v>-234.05485274</v>
-      </c>
-      <c r="G101" t="n">
-        <v>-116.1308546</v>
-      </c>
-      <c r="H101" t="n">
-        <v>-28.18982598</v>
-      </c>
-      <c r="I101" t="n">
-        <v>-51.69675949999999</v>
-      </c>
-      <c r="J101" t="n">
-        <v>-94.32087163</v>
-      </c>
-      <c r="K101" t="n">
-        <v>-157.36527402</v>
-      </c>
-      <c r="L101" t="n">
-        <v>-218.54924093</v>
-      </c>
-      <c r="M101" t="n">
-        <v>-239.31743868</v>
+        <v>-222.29646372</v>
       </c>
     </row>
   </sheetData>

--- a/Result/analyze_2.xlsx
+++ b/Result/analyze_2.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
     </row>
@@ -503,37 +503,37 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>262.27963268</v>
+        <v>602.6976485</v>
       </c>
       <c r="D2" t="n">
-        <v>621.91176462</v>
+        <v>669.4584688799999</v>
       </c>
       <c r="E2" t="n">
-        <v>674.7170971199999</v>
+        <v>969.6423881799999</v>
       </c>
       <c r="F2" t="n">
-        <v>970.13274813</v>
+        <v>1849.48860399</v>
       </c>
       <c r="G2" t="n">
-        <v>1847.20645299</v>
+        <v>1085.48359226</v>
       </c>
       <c r="H2" t="n">
-        <v>1090.09580616</v>
+        <v>157.01022691</v>
       </c>
       <c r="I2" t="n">
-        <v>152.20944048</v>
+        <v>735.71064775</v>
       </c>
       <c r="J2" t="n">
-        <v>727.30452817</v>
+        <v>790.5330572400001</v>
       </c>
       <c r="K2" t="n">
-        <v>787.25271681</v>
+        <v>687.6225635699999</v>
       </c>
       <c r="L2" t="n">
-        <v>709.64192214</v>
+        <v>1777.99963127</v>
       </c>
       <c r="M2" t="n">
-        <v>1783.52327864</v>
+        <v>-168.4125216</v>
       </c>
     </row>
     <row r="3">
@@ -542,39 +542,41 @@
           <t>光電業右下</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
       <c r="C3" t="n">
-        <v>147.49896984</v>
+        <v>0.2643849900000007</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2643849900000007</v>
+        <v>-20.16331824</v>
       </c>
       <c r="E3" t="n">
-        <v>-20.16331824</v>
+        <v>108.99614624</v>
       </c>
       <c r="F3" t="n">
-        <v>108.99614624</v>
+        <v>218.62774389</v>
       </c>
       <c r="G3" t="n">
-        <v>218.62774389</v>
+        <v>151.67850938</v>
       </c>
       <c r="H3" t="n">
-        <v>151.67850938</v>
+        <v>50.43801889</v>
       </c>
       <c r="I3" t="n">
-        <v>50.43801889</v>
+        <v>-71.88062519</v>
       </c>
       <c r="J3" t="n">
-        <v>-71.88062519</v>
+        <v>18.3918283</v>
       </c>
       <c r="K3" t="n">
-        <v>18.3918283</v>
+        <v>118.11633031</v>
       </c>
       <c r="L3" t="n">
-        <v>118.11633031</v>
+        <v>114.91389364</v>
       </c>
       <c r="M3" t="n">
-        <v>114.91389364</v>
+        <v>99.37302536</v>
       </c>
     </row>
     <row r="4">
@@ -585,37 +587,37 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>-54.03002938000001</v>
+        <v>-158.07171923</v>
       </c>
       <c r="D4" t="n">
-        <v>-158.08994697</v>
+        <v>-198.42502927</v>
       </c>
       <c r="E4" t="n">
-        <v>-198.46347347</v>
+        <v>-45.27663139</v>
       </c>
       <c r="F4" t="n">
-        <v>-45.33545444</v>
+        <v>105.57078515</v>
       </c>
       <c r="G4" t="n">
-        <v>105.60072715</v>
+        <v>36.23594113</v>
       </c>
       <c r="H4" t="n">
-        <v>36.28501871</v>
+        <v>219.17184839</v>
       </c>
       <c r="I4" t="n">
-        <v>219.22014594</v>
+        <v>-49.55764159</v>
       </c>
       <c r="J4" t="n">
-        <v>-49.53044652</v>
+        <v>28.5783324</v>
       </c>
       <c r="K4" t="n">
-        <v>28.60477997000001</v>
+        <v>-1.138802360000014</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.130153140000016</v>
+        <v>-48.71127217</v>
       </c>
       <c r="M4" t="n">
-        <v>-48.71721795999999</v>
+        <v>-152.7341734</v>
       </c>
     </row>
     <row r="5">
@@ -626,37 +628,37 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1311.6789827</v>
+        <v>1402.66047048</v>
       </c>
       <c r="D5" t="n">
-        <v>1402.6094384</v>
+        <v>946.8620050899999</v>
       </c>
       <c r="E5" t="n">
-        <v>947.17776913</v>
+        <v>633.97876007</v>
       </c>
       <c r="F5" t="n">
-        <v>633.9211675299999</v>
+        <v>145.98154998</v>
       </c>
       <c r="G5" t="n">
-        <v>146.03440984</v>
+        <v>-38.91567496</v>
       </c>
       <c r="H5" t="n">
-        <v>-38.63469054000001</v>
+        <v>-259.11423339</v>
       </c>
       <c r="I5" t="n">
-        <v>-259.31952002</v>
+        <v>-387.0616234</v>
       </c>
       <c r="J5" t="n">
-        <v>-387.10507082</v>
+        <v>-427.89242988</v>
       </c>
       <c r="K5" t="n">
-        <v>-428.41055059</v>
+        <v>-414.13751969</v>
       </c>
       <c r="L5" t="n">
-        <v>-414.44012063</v>
+        <v>-488.4837365</v>
       </c>
       <c r="M5" t="n">
-        <v>-488.47392939</v>
+        <v>-411.74193648</v>
       </c>
     </row>
     <row r="6">
@@ -665,39 +667,41 @@
           <t>其他右下</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
       <c r="C6" t="n">
-        <v>-51.13695541</v>
+        <v>-141.3043893</v>
       </c>
       <c r="D6" t="n">
-        <v>-141.00929526</v>
+        <v>-65.84285428999999</v>
       </c>
       <c r="E6" t="n">
-        <v>-65.26154403</v>
+        <v>61.18649945</v>
       </c>
       <c r="F6" t="n">
-        <v>62.04500406999999</v>
+        <v>11.53724968</v>
       </c>
       <c r="G6" t="n">
-        <v>11.78770847</v>
+        <v>17.98194362</v>
       </c>
       <c r="H6" t="n">
-        <v>18.84798607</v>
+        <v>62.90351154</v>
       </c>
       <c r="I6" t="n">
-        <v>63.41058579</v>
+        <v>80.61587611</v>
       </c>
       <c r="J6" t="n">
-        <v>80.62499681</v>
+        <v>81.29088198000001</v>
       </c>
       <c r="K6" t="n">
-        <v>81.45993682000001</v>
+        <v>70.96316671</v>
       </c>
       <c r="L6" t="n">
-        <v>70.53339803</v>
+        <v>155.55564606</v>
       </c>
       <c r="M6" t="n">
-        <v>154.79530516</v>
+        <v>192.27816816</v>
       </c>
     </row>
     <row r="7">
@@ -708,37 +712,37 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>23.34243293</v>
+        <v>8.593587789999999</v>
       </c>
       <c r="D7" t="n">
-        <v>8.34951197</v>
+        <v>8.931548919999999</v>
       </c>
       <c r="E7" t="n">
-        <v>8.191339730000003</v>
+        <v>11.30406819</v>
       </c>
       <c r="F7" t="n">
-        <v>10.73662403</v>
+        <v>12.0927555</v>
       </c>
       <c r="G7" t="n">
-        <v>12.01709187</v>
+        <v>20.07663934</v>
       </c>
       <c r="H7" t="n">
-        <v>19.79486985</v>
+        <v>0.5140568199999984</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6761040199999977</v>
+        <v>-11.62759703</v>
       </c>
       <c r="J7" t="n">
-        <v>-11.2907794</v>
+        <v>-42.26777828</v>
       </c>
       <c r="K7" t="n">
-        <v>-41.80932144</v>
+        <v>-35.32248623</v>
       </c>
       <c r="L7" t="n">
-        <v>-34.71912384</v>
+        <v>-30.84577259</v>
       </c>
       <c r="M7" t="n">
-        <v>-30.00408671</v>
+        <v>-40.53569926</v>
       </c>
     </row>
     <row r="8">
@@ -749,37 +753,37 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>-148.70606176</v>
+        <v>1462.80068978</v>
       </c>
       <c r="D8" t="n">
-        <v>1476.56908614</v>
+        <v>2288.29119089</v>
       </c>
       <c r="E8" t="n">
-        <v>2293.90645356</v>
+        <v>1082.1776767</v>
       </c>
       <c r="F8" t="n">
-        <v>1075.83236819</v>
+        <v>1217.19830357</v>
       </c>
       <c r="G8" t="n">
-        <v>1228.30997512</v>
+        <v>1224.9719705</v>
       </c>
       <c r="H8" t="n">
-        <v>1242.73536522</v>
+        <v>3053.42235397</v>
       </c>
       <c r="I8" t="n">
-        <v>3055.28122897</v>
+        <v>3202.53595737</v>
       </c>
       <c r="J8" t="n">
-        <v>3152.68677979</v>
+        <v>3796.8887242</v>
       </c>
       <c r="K8" t="n">
-        <v>3698.39980366</v>
+        <v>879.34427735</v>
       </c>
       <c r="L8" t="n">
-        <v>840.28728211</v>
+        <v>2616.39879541</v>
       </c>
       <c r="M8" t="n">
-        <v>2512.778153</v>
+        <v>2457.47873682</v>
       </c>
     </row>
     <row r="9">
@@ -790,37 +794,37 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>19.26401315</v>
+        <v>-16.93995363</v>
       </c>
       <c r="D9" t="n">
-        <v>-16.93993281</v>
+        <v>39.37451661</v>
       </c>
       <c r="E9" t="n">
-        <v>39.37455131</v>
+        <v>36.7863755</v>
       </c>
       <c r="F9" t="n">
-        <v>36.7864105</v>
+        <v>40.08065389</v>
       </c>
       <c r="G9" t="n">
-        <v>40.08066302</v>
+        <v>-1.64293746</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.64290466</v>
+        <v>12.49312112</v>
       </c>
       <c r="I9" t="n">
-        <v>12.49313254</v>
+        <v>-56.51112387000001</v>
       </c>
       <c r="J9" t="n">
-        <v>-56.5111112</v>
+        <v>-83.09151716000001</v>
       </c>
       <c r="K9" t="n">
-        <v>-83.09150933000001</v>
+        <v>-91.21407168</v>
       </c>
       <c r="L9" t="n">
-        <v>-91.21407562</v>
+        <v>-123.56075957</v>
       </c>
       <c r="M9" t="n">
-        <v>-123.56078289</v>
+        <v>-130.50237339</v>
       </c>
     </row>
     <row r="10">
@@ -831,37 +835,37 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>-25.52413804</v>
+        <v>-39.404709</v>
       </c>
       <c r="D10" t="n">
-        <v>-53.17312618</v>
+        <v>-4.424241560000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-10.03953893</v>
+        <v>33.02326758</v>
       </c>
       <c r="F10" t="n">
-        <v>39.36854109</v>
+        <v>92.64804305</v>
       </c>
       <c r="G10" t="n">
-        <v>81.53636237000001</v>
+        <v>17.17429546</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5891320599999984</v>
+        <v>45.08897026</v>
       </c>
       <c r="I10" t="n">
-        <v>43.23008384000001</v>
+        <v>-8.916060129999998</v>
       </c>
       <c r="J10" t="n">
-        <v>40.93310478</v>
+        <v>-111.04121665</v>
       </c>
       <c r="K10" t="n">
-        <v>-12.55230394</v>
+        <v>-101.76618532</v>
       </c>
       <c r="L10" t="n">
-        <v>-62.70918614</v>
+        <v>-139.32909304</v>
       </c>
       <c r="M10" t="n">
-        <v>-55.88911530999999</v>
+        <v>-100.04690397</v>
       </c>
     </row>
     <row r="11">
@@ -872,37 +876,37 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>65.49933337</v>
+        <v>142.10709826</v>
       </c>
       <c r="D11" t="n">
-        <v>140.90982914</v>
+        <v>57.88838204</v>
       </c>
       <c r="E11" t="n">
-        <v>57.1766969</v>
+        <v>58.40439622000001</v>
       </c>
       <c r="F11" t="n">
-        <v>65.09250018</v>
+        <v>5.304335569999999</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5197492700000006</v>
+        <v>-57.6147605</v>
       </c>
       <c r="H11" t="n">
-        <v>-62.86999651</v>
+        <v>-84.49988563000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-89.29810446</v>
+        <v>-71.27958376000001</v>
       </c>
       <c r="J11" t="n">
-        <v>-73.05729255</v>
+        <v>-9.778352530000008</v>
       </c>
       <c r="K11" t="n">
-        <v>-11.72490653000001</v>
+        <v>31.64014183</v>
       </c>
       <c r="L11" t="n">
-        <v>31.05005041</v>
+        <v>-181.89200288</v>
       </c>
       <c r="M11" t="n">
-        <v>-180.95019354</v>
+        <v>-28.50705036000002</v>
       </c>
     </row>
     <row r="12">
@@ -913,37 +917,37 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>121.89913691</v>
+        <v>-3.215999110000002</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.193201080000001</v>
+        <v>-78.93212152</v>
       </c>
       <c r="E12" t="n">
-        <v>-78.9334088</v>
+        <v>-41.43989729</v>
       </c>
       <c r="F12" t="n">
-        <v>-41.43368870999999</v>
+        <v>-102.01485622</v>
       </c>
       <c r="G12" t="n">
-        <v>-102.00764632</v>
+        <v>-106.13760151</v>
       </c>
       <c r="H12" t="n">
-        <v>-106.15040842</v>
+        <v>-22.3740144</v>
       </c>
       <c r="I12" t="n">
-        <v>-22.38016029999999</v>
+        <v>360.00356585</v>
       </c>
       <c r="J12" t="n">
-        <v>360.0173907299999</v>
+        <v>239.47928084</v>
       </c>
       <c r="K12" t="n">
-        <v>239.49133427</v>
+        <v>172.96076883</v>
       </c>
       <c r="L12" t="n">
-        <v>173.03014541</v>
+        <v>-44.249782</v>
       </c>
       <c r="M12" t="n">
-        <v>-44.2824068</v>
+        <v>-22.19598527</v>
       </c>
     </row>
     <row r="13">
@@ -954,37 +958,37 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>-8.040024430000001</v>
+        <v>-1.46681079</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.2923396999999996</v>
+        <v>2.45781016</v>
       </c>
       <c r="E13" t="n">
-        <v>3.17078258</v>
+        <v>0.7869540599999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.907358479999999</v>
+        <v>-18.7276696</v>
       </c>
       <c r="G13" t="n">
-        <v>-13.9502932</v>
+        <v>-2.22506845</v>
       </c>
       <c r="H13" t="n">
-        <v>3.04297447</v>
+        <v>2.87521121</v>
       </c>
       <c r="I13" t="n">
-        <v>7.67957594</v>
+        <v>-7.662935969999999</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.899052060000001</v>
+        <v>-4.07760919</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.14310862</v>
+        <v>21.36502881</v>
       </c>
       <c r="L13" t="n">
-        <v>21.88574365</v>
+        <v>44.08762252</v>
       </c>
       <c r="M13" t="n">
-        <v>43.17843798</v>
+        <v>22.01935964</v>
       </c>
     </row>
     <row r="14">
@@ -995,37 +999,37 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>-5535.98562555</v>
+        <v>-558.0274960500003</v>
       </c>
       <c r="D14" t="n">
-        <v>-658.0841553300002</v>
+        <v>-4031.0308901</v>
       </c>
       <c r="E14" t="n">
-        <v>-4001.93109319</v>
+        <v>-5869.02274616</v>
       </c>
       <c r="F14" t="n">
-        <v>-5978.31957158</v>
+        <v>-1133.26056514</v>
       </c>
       <c r="G14" t="n">
-        <v>-1092.19583828</v>
+        <v>-3705.16582924</v>
       </c>
       <c r="H14" t="n">
-        <v>-3890.94390022</v>
+        <v>5239.739088179999</v>
       </c>
       <c r="I14" t="n">
-        <v>5256.24524152</v>
+        <v>1818.91268169</v>
       </c>
       <c r="J14" t="n">
-        <v>1678.88706639</v>
+        <v>7262.88889412</v>
       </c>
       <c r="K14" t="n">
-        <v>7048.85128128</v>
+        <v>4023.58498686</v>
       </c>
       <c r="L14" t="n">
-        <v>3617.835917129999</v>
+        <v>7564.39810059</v>
       </c>
       <c r="M14" t="n">
-        <v>7480.86293599</v>
+        <v>3973.15930394</v>
       </c>
     </row>
     <row r="15">
@@ -1038,37 +1042,37 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>-86.36146058</v>
+        <v>-441.8664886</v>
       </c>
       <c r="D15" t="n">
-        <v>-602.33041612</v>
+        <v>280.46767513</v>
       </c>
       <c r="E15" t="n">
-        <v>8.812711690000006</v>
+        <v>187.83748074</v>
       </c>
       <c r="F15" t="n">
-        <v>-113.70895621</v>
+        <v>557.79165071</v>
       </c>
       <c r="G15" t="n">
-        <v>877.88284232</v>
+        <v>-142.65581879</v>
       </c>
       <c r="H15" t="n">
-        <v>1.19436815999998</v>
+        <v>-434.42812575</v>
       </c>
       <c r="I15" t="n">
-        <v>-256.58128448</v>
+        <v>313.4371352400001</v>
       </c>
       <c r="J15" t="n">
-        <v>33.95014528000004</v>
+        <v>19.93314023999998</v>
       </c>
       <c r="K15" t="n">
-        <v>-645.3038545400001</v>
+        <v>988.7134929800001</v>
       </c>
       <c r="L15" t="n">
-        <v>333.00948395</v>
+        <v>610.43790317</v>
       </c>
       <c r="M15" t="n">
-        <v>-12.58744067999995</v>
+        <v>920.21499783</v>
       </c>
     </row>
     <row r="16">
@@ -1079,37 +1083,37 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>-238.6301166</v>
+        <v>-425.31854186</v>
       </c>
       <c r="D16" t="n">
-        <v>30.90868662</v>
+        <v>-670.2735597</v>
       </c>
       <c r="E16" t="n">
-        <v>-213.22392075</v>
+        <v>-1156.18405488</v>
       </c>
       <c r="F16" t="n">
-        <v>-546.1150724600001</v>
+        <v>-623.4059272899999</v>
       </c>
       <c r="G16" t="n">
-        <v>-815.9856730299999</v>
+        <v>-1096.09065954</v>
       </c>
       <c r="H16" t="n">
-        <v>-900.6945041700001</v>
+        <v>-150.24100706</v>
       </c>
       <c r="I16" t="n">
-        <v>-318.48843623</v>
+        <v>-469.41605542</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.957435519999996</v>
+        <v>-458.6890040100001</v>
       </c>
       <c r="K16" t="n">
-        <v>470.0650154399999</v>
+        <v>-715.76837278</v>
       </c>
       <c r="L16" t="n">
-        <v>335.10144141</v>
+        <v>-375.38672873</v>
       </c>
       <c r="M16" t="n">
-        <v>187.51669966</v>
+        <v>-114.94700233</v>
       </c>
     </row>
     <row r="17">
@@ -1120,37 +1124,37 @@
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
-        <v>-0.03467238</v>
+        <v>1.35244179</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.04065686</v>
+        <v>2.72845142</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0011402</v>
+        <v>0.8801225899999999</v>
       </c>
       <c r="F17" t="n">
-        <v>0.03352323</v>
+        <v>0.95461918</v>
       </c>
       <c r="G17" t="n">
-        <v>0.00050968</v>
+        <v>0.84933853</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.01056853</v>
+        <v>-0.12911185</v>
       </c>
       <c r="I17" t="n">
-        <v>0.00352167</v>
+        <v>0.18345265</v>
       </c>
       <c r="J17" t="n">
-        <v>0.01775949</v>
+        <v>-0.75565477</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0402896</v>
+        <v>-1.09301157</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.04455849</v>
+        <v>-1.25991411</v>
       </c>
       <c r="M17" t="n">
-        <v>0.07666569000000001</v>
+        <v>0.42586555</v>
       </c>
     </row>
     <row r="18">
@@ -1161,37 +1165,37 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>949.17323245</v>
+        <v>786.6830428600001</v>
       </c>
       <c r="D18" t="n">
-        <v>786.6830428600001</v>
+        <v>-272.85884179</v>
       </c>
       <c r="E18" t="n">
-        <v>-272.85884179</v>
+        <v>-871.1229194199999</v>
       </c>
       <c r="F18" t="n">
-        <v>-871.1229194199999</v>
+        <v>-1069.81135742</v>
       </c>
       <c r="G18" t="n">
-        <v>-1069.81135742</v>
+        <v>-452.58295967</v>
       </c>
       <c r="H18" t="n">
-        <v>-452.58295967</v>
+        <v>-531.6617434799999</v>
       </c>
       <c r="I18" t="n">
-        <v>-531.6617434799999</v>
+        <v>-603.5171211700001</v>
       </c>
       <c r="J18" t="n">
-        <v>-603.5171211700001</v>
+        <v>-1.170012629999998</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.170012629999998</v>
+        <v>755.74136299</v>
       </c>
       <c r="L18" t="n">
-        <v>755.74136299</v>
+        <v>808.41838966</v>
       </c>
       <c r="M18" t="n">
-        <v>808.41838966</v>
+        <v>20.05482964</v>
       </c>
     </row>
     <row r="19">
@@ -1202,37 +1206,37 @@
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>-2.35624874</v>
+        <v>-6.060158990000001</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.667060340000001</v>
+        <v>-6.60366677</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.87635555</v>
+        <v>-1.86839988</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.02180052</v>
+        <v>-3.49261844</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.53850894</v>
+        <v>-0.45935476</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4005523000000001</v>
+        <v>-5.09463389</v>
       </c>
       <c r="I19" t="n">
-        <v>-5.227267410000001</v>
+        <v>-16.04657688</v>
       </c>
       <c r="J19" t="n">
-        <v>-15.88088372</v>
+        <v>-16.7282934</v>
       </c>
       <c r="K19" t="n">
-        <v>-17.52423777</v>
+        <v>-9.796063780000001</v>
       </c>
       <c r="L19" t="n">
-        <v>-10.84451686</v>
+        <v>-1.05380141</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.39038121</v>
+        <v>2.68419108</v>
       </c>
     </row>
     <row r="20">
@@ -1243,37 +1247,37 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>43.34600284999999</v>
+        <v>-20.57369556</v>
       </c>
       <c r="D20" t="n">
-        <v>-20.57369556</v>
+        <v>-26.64337471</v>
       </c>
       <c r="E20" t="n">
-        <v>-26.64337471</v>
+        <v>-8.6719104</v>
       </c>
       <c r="F20" t="n">
-        <v>-8.6719104</v>
+        <v>6.29112816</v>
       </c>
       <c r="G20" t="n">
-        <v>6.29112816</v>
+        <v>-11.38791094</v>
       </c>
       <c r="H20" t="n">
-        <v>-11.38791094</v>
+        <v>39.90390299</v>
       </c>
       <c r="I20" t="n">
-        <v>39.90390299</v>
+        <v>-7.499015480000001</v>
       </c>
       <c r="J20" t="n">
-        <v>-7.499015480000001</v>
+        <v>-34.65196079</v>
       </c>
       <c r="K20" t="n">
-        <v>-34.65196079</v>
+        <v>-20.07586818</v>
       </c>
       <c r="L20" t="n">
-        <v>-20.07586818</v>
+        <v>37.03994246</v>
       </c>
       <c r="M20" t="n">
-        <v>37.03994246</v>
+        <v>61.97440654</v>
       </c>
     </row>
     <row r="21">
@@ -1284,37 +1288,37 @@
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
-        <v>1.01545869</v>
+        <v>0.11204183</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.08711676000000002</v>
+        <v>1.42578982</v>
       </c>
       <c r="E21" t="n">
-        <v>1.98363663</v>
+        <v>2.43176568</v>
       </c>
       <c r="F21" t="n">
-        <v>2.62524275</v>
+        <v>1.74360285</v>
       </c>
       <c r="G21" t="n">
-        <v>2.39378135</v>
+        <v>1.74664979</v>
       </c>
       <c r="H21" t="n">
-        <v>2.61607538</v>
+        <v>1.07891954</v>
       </c>
       <c r="I21" t="n">
-        <v>1.28640456</v>
+        <v>-4.11562551</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.43901558</v>
+        <v>-7.679255199999999</v>
       </c>
       <c r="K21" t="n">
-        <v>-7.15590988</v>
+        <v>-2.84996042</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.96261004</v>
+        <v>-1.06686876</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.02451533</v>
+        <v>0.69414977</v>
       </c>
     </row>
     <row r="22">
@@ -1325,37 +1329,37 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>0.11370021</v>
+        <v>-0.1116844499999999</v>
       </c>
       <c r="D22" t="n">
-        <v>0.08731186000000006</v>
+        <v>2.09106884</v>
       </c>
       <c r="E22" t="n">
-        <v>1.53302582</v>
+        <v>2.66362076</v>
       </c>
       <c r="F22" t="n">
-        <v>2.46990344</v>
+        <v>2.26437657</v>
       </c>
       <c r="G22" t="n">
-        <v>1.61393472</v>
+        <v>2.71147254</v>
       </c>
       <c r="H22" t="n">
-        <v>1.84202241</v>
+        <v>2.27511611</v>
       </c>
       <c r="I22" t="n">
-        <v>2.06787124</v>
+        <v>3.80950832</v>
       </c>
       <c r="J22" t="n">
-        <v>2.13334684</v>
+        <v>1.51303603</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9929304</v>
+        <v>0.84748555</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.03632950000000001</v>
+        <v>1.00912572</v>
       </c>
       <c r="M22" t="n">
-        <v>0.96950563</v>
+        <v>3.30607556</v>
       </c>
     </row>
     <row r="23">
@@ -1366,37 +1370,37 @@
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
-        <v>2.279171630000002</v>
+        <v>16.72892445</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2745837299999978</v>
+        <v>18.21552769</v>
       </c>
       <c r="E23" t="n">
-        <v>-8.598820600000002</v>
+        <v>37.88405859</v>
       </c>
       <c r="F23" t="n">
-        <v>30.33780378</v>
+        <v>24.20960816</v>
       </c>
       <c r="G23" t="n">
-        <v>29.55377318</v>
+        <v>17.34495134</v>
       </c>
       <c r="H23" t="n">
-        <v>14.81809427</v>
+        <v>10.97104816</v>
       </c>
       <c r="I23" t="n">
-        <v>2.2237342</v>
+        <v>14.7137113</v>
       </c>
       <c r="J23" t="n">
-        <v>5.296906070000001</v>
+        <v>25.86115714</v>
       </c>
       <c r="K23" t="n">
-        <v>25.09193065</v>
+        <v>61.50186898999999</v>
       </c>
       <c r="L23" t="n">
-        <v>54.47860323</v>
+        <v>67.72679253</v>
       </c>
       <c r="M23" t="n">
-        <v>66.45411108</v>
+        <v>73.11998154999999</v>
       </c>
     </row>
     <row r="24">
@@ -1407,37 +1411,37 @@
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
-        <v>-93.22952265000001</v>
+        <v>-89.82169067</v>
       </c>
       <c r="D24" t="n">
-        <v>-90.70000823000001</v>
+        <v>-6.62700109</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.2809364</v>
+        <v>83.61085113</v>
       </c>
       <c r="F24" t="n">
-        <v>86.20473114000001</v>
+        <v>26.68614927</v>
       </c>
       <c r="G24" t="n">
-        <v>29.54057057</v>
+        <v>13.31384929</v>
       </c>
       <c r="H24" t="n">
-        <v>15.57147579</v>
+        <v>-21.23921207</v>
       </c>
       <c r="I24" t="n">
-        <v>-19.0600271</v>
+        <v>-42.54438606</v>
       </c>
       <c r="J24" t="n">
-        <v>-41.61633796</v>
+        <v>-44.12641995000001</v>
       </c>
       <c r="K24" t="n">
-        <v>-42.96796366</v>
+        <v>-45.77733627</v>
       </c>
       <c r="L24" t="n">
-        <v>-44.10190735</v>
+        <v>-27.47678849</v>
       </c>
       <c r="M24" t="n">
-        <v>-27.06907343</v>
+        <v>5.553141660000001</v>
       </c>
     </row>
     <row r="25">
@@ -1448,37 +1452,37 @@
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>-50.65754586</v>
+        <v>-76.77982048</v>
       </c>
       <c r="D25" t="n">
-        <v>-58.89799474</v>
+        <v>-33.19166399</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.72338039</v>
+        <v>54.8293569</v>
       </c>
       <c r="F25" t="n">
-        <v>59.7817317</v>
+        <v>26.1645132</v>
       </c>
       <c r="G25" t="n">
-        <v>17.96592688</v>
+        <v>40.14163911</v>
       </c>
       <c r="H25" t="n">
-        <v>40.41086968</v>
+        <v>34.58145535</v>
       </c>
       <c r="I25" t="n">
-        <v>41.14958434</v>
+        <v>8.544195799999995</v>
       </c>
       <c r="J25" t="n">
-        <v>17.03295293</v>
+        <v>9.006444429999998</v>
       </c>
       <c r="K25" t="n">
-        <v>8.617214629999999</v>
+        <v>6.00126162</v>
       </c>
       <c r="L25" t="n">
-        <v>11.34909846</v>
+        <v>44.85690394</v>
       </c>
       <c r="M25" t="n">
-        <v>45.72187033000001</v>
+        <v>48.15734783</v>
       </c>
     </row>
     <row r="26">
@@ -1489,37 +1493,37 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>0.06516363999999999</v>
+        <v>-0.4000247499999999</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.14909701</v>
+        <v>7.620458500000001</v>
       </c>
       <c r="E26" t="n">
-        <v>7.807659770000001</v>
+        <v>3.95086604</v>
       </c>
       <c r="F26" t="n">
-        <v>3.90290423</v>
+        <v>8.954270699999999</v>
       </c>
       <c r="G26" t="n">
-        <v>8.67842671</v>
+        <v>5.88796488</v>
       </c>
       <c r="H26" t="n">
-        <v>5.4001713</v>
+        <v>7.59403203</v>
       </c>
       <c r="I26" t="n">
-        <v>6.494961730000001</v>
+        <v>5.170474019999999</v>
       </c>
       <c r="J26" t="n">
-        <v>3.30757135</v>
+        <v>7.59523152</v>
       </c>
       <c r="K26" t="n">
-        <v>5.568523260000001</v>
+        <v>18.69807133</v>
       </c>
       <c r="L26" t="n">
-        <v>16.69468449</v>
+        <v>6.72828735</v>
       </c>
       <c r="M26" t="n">
-        <v>6.11848527</v>
+        <v>5.82693547</v>
       </c>
     </row>
     <row r="27">
@@ -1528,41 +1532,39 @@
           <t>數位雲端右下</t>
         </is>
       </c>
-      <c r="B27" t="n">
-        <v>0</v>
-      </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>10.21874138</v>
+        <v>5.178023819999999</v>
       </c>
       <c r="D27" t="n">
-        <v>5.178023819999999</v>
+        <v>12.34928412</v>
       </c>
       <c r="E27" t="n">
-        <v>12.34924729</v>
+        <v>7.256554369999998</v>
       </c>
       <c r="F27" t="n">
-        <v>7.256533559999999</v>
+        <v>21.4155872</v>
       </c>
       <c r="G27" t="n">
-        <v>21.41555787</v>
+        <v>9.253985100000001</v>
       </c>
       <c r="H27" t="n">
-        <v>9.253958190000001</v>
+        <v>20.89003487</v>
       </c>
       <c r="I27" t="n">
-        <v>20.89001611</v>
+        <v>17.74032494</v>
       </c>
       <c r="J27" t="n">
-        <v>17.74033155</v>
+        <v>22.20183627</v>
       </c>
       <c r="K27" t="n">
-        <v>22.20184127</v>
+        <v>32.01865252</v>
       </c>
       <c r="L27" t="n">
-        <v>32.01865752</v>
+        <v>32.91414248</v>
       </c>
       <c r="M27" t="n">
-        <v>32.91440352</v>
+        <v>31.90223136</v>
       </c>
     </row>
     <row r="28">
@@ -1573,37 +1575,37 @@
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>-11.54655749</v>
+        <v>-0.3640058200000001</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.40340602</v>
+        <v>12.5400599</v>
       </c>
       <c r="E28" t="n">
-        <v>12.49562452</v>
+        <v>-19.63774786</v>
       </c>
       <c r="F28" t="n">
-        <v>-19.69529798</v>
+        <v>3.95135545</v>
       </c>
       <c r="G28" t="n">
-        <v>3.88484246</v>
+        <v>-27.67353924</v>
       </c>
       <c r="H28" t="n">
-        <v>-27.74305593</v>
+        <v>-47.67111913</v>
       </c>
       <c r="I28" t="n">
-        <v>-47.75031722</v>
+        <v>-79.8235693</v>
       </c>
       <c r="J28" t="n">
-        <v>-79.88476525</v>
+        <v>-109.72969299</v>
       </c>
       <c r="K28" t="n">
-        <v>-109.77504311</v>
+        <v>-102.94515052</v>
       </c>
       <c r="L28" t="n">
-        <v>-102.99505801</v>
+        <v>-89.79466576999999</v>
       </c>
       <c r="M28" t="n">
-        <v>-89.85061942999999</v>
+        <v>-73.93411181</v>
       </c>
     </row>
     <row r="29">
@@ -1614,37 +1616,37 @@
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>0.006492230000000001</v>
+        <v>0.01033713</v>
       </c>
       <c r="D29" t="n">
-        <v>0.01229479</v>
+        <v>0.01825068</v>
       </c>
       <c r="E29" t="n">
-        <v>0.01976942</v>
+        <v>0.02746755</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0273315</v>
+        <v>0.08414062</v>
       </c>
       <c r="G29" t="n">
-        <v>0.08224571999999999</v>
+        <v>0.07506878</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0739363</v>
+        <v>0.03323846</v>
       </c>
       <c r="I29" t="n">
-        <v>0.03168009</v>
+        <v>0.00619917</v>
       </c>
       <c r="J29" t="n">
-        <v>0.00634259</v>
+        <v>0.01277118</v>
       </c>
       <c r="K29" t="n">
-        <v>0.01295552</v>
+        <v>-0.00653676</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.00654754</v>
+        <v>-0.01623805</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.01613442</v>
+        <v>-0.01854561</v>
       </c>
     </row>
     <row r="30">
@@ -1655,37 +1657,37 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>-0.00124175</v>
+        <v>-0.00683579</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.00683579</v>
+        <v>-0.00255541</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.00255541</v>
+        <v>0.0079351</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0079351</v>
+        <v>0.01028314</v>
       </c>
       <c r="G30" t="n">
-        <v>0.01028314</v>
+        <v>0.00538708</v>
       </c>
       <c r="H30" t="n">
-        <v>0.00538708</v>
+        <v>0.01209633</v>
       </c>
       <c r="I30" t="n">
-        <v>0.01209633</v>
+        <v>0.0008129699999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0008129699999999999</v>
+        <v>-0.00467908</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.00467908</v>
+        <v>-0.00565026</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.00565026</v>
+        <v>-0.00688049</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.00688049</v>
+        <v>0.01008529</v>
       </c>
     </row>
     <row r="31">
@@ -1696,37 +1698,37 @@
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>-0.07378256999999999</v>
+        <v>0.03434865</v>
       </c>
       <c r="D31" t="n">
-        <v>0.03239099</v>
+        <v>0.003614140000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0020954</v>
+        <v>0.10054297</v>
       </c>
       <c r="F31" t="n">
-        <v>0.10067902</v>
+        <v>0.21751282</v>
       </c>
       <c r="G31" t="n">
-        <v>0.21940772</v>
+        <v>0.10936104</v>
       </c>
       <c r="H31" t="n">
-        <v>0.11049352</v>
+        <v>0.03924989</v>
       </c>
       <c r="I31" t="n">
-        <v>0.04080826</v>
+        <v>-0.01166996</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.01181338</v>
+        <v>-0.05285173000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.05303607</v>
+        <v>-0.09475462</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.09474384</v>
+        <v>-0.1850039</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.18510753</v>
+        <v>0.0035406</v>
       </c>
     </row>
     <row r="32">
@@ -1737,37 +1739,37 @@
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>9.357429240000002</v>
+        <v>-23.28926443</v>
       </c>
       <c r="D32" t="n">
-        <v>-23.28926443</v>
+        <v>-15.50397747</v>
       </c>
       <c r="E32" t="n">
-        <v>-15.50397747</v>
+        <v>-7.671519279999999</v>
       </c>
       <c r="F32" t="n">
-        <v>-7.671519279999999</v>
+        <v>-12.56496135</v>
       </c>
       <c r="G32" t="n">
-        <v>-12.56496135</v>
+        <v>0.4845926899999997</v>
       </c>
       <c r="H32" t="n">
-        <v>0.4845926899999997</v>
+        <v>-20.67803373</v>
       </c>
       <c r="I32" t="n">
-        <v>-20.67803373</v>
+        <v>-32.15445803</v>
       </c>
       <c r="J32" t="n">
-        <v>-32.15445803</v>
+        <v>-40.28821612</v>
       </c>
       <c r="K32" t="n">
-        <v>-40.28821612</v>
+        <v>-16.20914258</v>
       </c>
       <c r="L32" t="n">
-        <v>-16.20914258</v>
+        <v>-19.13381427</v>
       </c>
       <c r="M32" t="n">
-        <v>-19.13381427</v>
+        <v>-10.30184885</v>
       </c>
     </row>
     <row r="33">
@@ -1778,37 +1780,37 @@
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
-        <v>1.69994562</v>
+        <v>0.07589649999999996</v>
       </c>
       <c r="D33" t="n">
-        <v>0.07589649999999996</v>
+        <v>-0.14939967</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.14939967</v>
+        <v>0.5503706399999999</v>
       </c>
       <c r="F33" t="n">
-        <v>0.5503706399999999</v>
+        <v>1.89812459</v>
       </c>
       <c r="G33" t="n">
-        <v>1.89812459</v>
+        <v>2.92653785</v>
       </c>
       <c r="H33" t="n">
-        <v>2.92653785</v>
+        <v>0.4812992</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4812992</v>
+        <v>-1.10311971</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.10311971</v>
+        <v>-3.2016798</v>
       </c>
       <c r="K33" t="n">
-        <v>-3.2016798</v>
+        <v>-1.87034995</v>
       </c>
       <c r="L33" t="n">
-        <v>-1.87034995</v>
+        <v>-2.31543645</v>
       </c>
       <c r="M33" t="n">
-        <v>-2.31543645</v>
+        <v>-4.02921888</v>
       </c>
     </row>
     <row r="34">
@@ -1819,37 +1821,37 @@
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
-        <v>152.60252483</v>
+        <v>75.68712063</v>
       </c>
       <c r="D34" t="n">
-        <v>75.68712063</v>
+        <v>33.27450068</v>
       </c>
       <c r="E34" t="n">
-        <v>33.27450068</v>
+        <v>20.78368849</v>
       </c>
       <c r="F34" t="n">
-        <v>20.78368849</v>
+        <v>33.21580698</v>
       </c>
       <c r="G34" t="n">
-        <v>33.21580698</v>
+        <v>52.12681979</v>
       </c>
       <c r="H34" t="n">
-        <v>52.12681979</v>
+        <v>22.38281906</v>
       </c>
       <c r="I34" t="n">
-        <v>22.38281906</v>
+        <v>33.51679171</v>
       </c>
       <c r="J34" t="n">
-        <v>33.51679171</v>
+        <v>42.04676762</v>
       </c>
       <c r="K34" t="n">
-        <v>42.04676762</v>
+        <v>53.81900047</v>
       </c>
       <c r="L34" t="n">
-        <v>53.81900047</v>
+        <v>78.81126565000001</v>
       </c>
       <c r="M34" t="n">
-        <v>78.81126565000001</v>
+        <v>-96.49697067</v>
       </c>
     </row>
     <row r="35">
@@ -1860,37 +1862,37 @@
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
-        <v>0.05044382</v>
+        <v>-0.09362012</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.09362012</v>
+        <v>-0.09928682000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.09928682000000001</v>
+        <v>0.04687088</v>
       </c>
       <c r="F35" t="n">
-        <v>0.04687088</v>
+        <v>0.28043062</v>
       </c>
       <c r="G35" t="n">
-        <v>0.28043062</v>
+        <v>0.01792718</v>
       </c>
       <c r="H35" t="n">
-        <v>0.01792718</v>
+        <v>-0.03893316</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.03893316</v>
+        <v>-0.04556105000000001</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.04556105000000001</v>
+        <v>0.30602701</v>
       </c>
       <c r="K35" t="n">
-        <v>0.30602701</v>
+        <v>2.51033113</v>
       </c>
       <c r="L35" t="n">
-        <v>2.51033113</v>
+        <v>1.1068391</v>
       </c>
       <c r="M35" t="n">
-        <v>1.1068391</v>
+        <v>1.56503321</v>
       </c>
     </row>
     <row r="36">
@@ -1901,37 +1903,37 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>-19.84310048</v>
+        <v>-4.70504814</v>
       </c>
       <c r="D36" t="n">
-        <v>-4.70504814</v>
+        <v>40.16238359</v>
       </c>
       <c r="E36" t="n">
-        <v>40.16238359</v>
+        <v>84.05469214</v>
       </c>
       <c r="F36" t="n">
-        <v>84.05469214</v>
+        <v>168.24925684</v>
       </c>
       <c r="G36" t="n">
-        <v>168.24925684</v>
+        <v>236.89254524</v>
       </c>
       <c r="H36" t="n">
-        <v>236.89254524</v>
+        <v>117.94625767</v>
       </c>
       <c r="I36" t="n">
-        <v>117.94625767</v>
+        <v>217.93889327</v>
       </c>
       <c r="J36" t="n">
-        <v>217.93889327</v>
+        <v>352.4427523</v>
       </c>
       <c r="K36" t="n">
-        <v>352.4427523</v>
+        <v>204.10822595</v>
       </c>
       <c r="L36" t="n">
-        <v>204.10822595</v>
+        <v>203.78321979</v>
       </c>
       <c r="M36" t="n">
-        <v>203.78321979</v>
+        <v>-5.257925969999995</v>
       </c>
     </row>
     <row r="37">
@@ -1940,41 +1942,39 @@
           <t>汽車工業右下</t>
         </is>
       </c>
-      <c r="B37" t="n">
-        <v>0</v>
-      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>66.83402647999999</v>
+        <v>-5.291141719999999</v>
       </c>
       <c r="D37" t="n">
-        <v>-8.809809789999999</v>
+        <v>-1.514865390000001</v>
       </c>
       <c r="E37" t="n">
-        <v>-2.004053790000001</v>
+        <v>18.38879085</v>
       </c>
       <c r="F37" t="n">
-        <v>19.77853517</v>
+        <v>37.15833097</v>
       </c>
       <c r="G37" t="n">
-        <v>39.36001564</v>
+        <v>41.52823503</v>
       </c>
       <c r="H37" t="n">
-        <v>41.24324093</v>
+        <v>46.73594826000001</v>
       </c>
       <c r="I37" t="n">
-        <v>44.13020765</v>
+        <v>4.982251610000001</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.2081203699999995</v>
+        <v>6.840031639999999</v>
       </c>
       <c r="K37" t="n">
-        <v>-1.378526400000002</v>
+        <v>35.03138665</v>
       </c>
       <c r="L37" t="n">
-        <v>31.44334252</v>
+        <v>8.22256728</v>
       </c>
       <c r="M37" t="n">
-        <v>2.58619647</v>
+        <v>18.62594352</v>
       </c>
     </row>
     <row r="38">
@@ -1985,37 +1985,37 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>-17.31197655</v>
+        <v>-34.16824592</v>
       </c>
       <c r="D38" t="n">
-        <v>-30.84179741</v>
+        <v>-41.23378873999999</v>
       </c>
       <c r="E38" t="n">
-        <v>-44.13402555</v>
+        <v>0.5211704800000023</v>
       </c>
       <c r="F38" t="n">
-        <v>-8.959139569999998</v>
+        <v>68.31632182999999</v>
       </c>
       <c r="G38" t="n">
-        <v>62.48420981000001</v>
+        <v>27.73419485000001</v>
       </c>
       <c r="H38" t="n">
-        <v>22.18522692</v>
+        <v>-34.98197725</v>
       </c>
       <c r="I38" t="n">
-        <v>-33.98069776</v>
+        <v>-54.9151605</v>
       </c>
       <c r="J38" t="n">
-        <v>-48.80477131</v>
+        <v>-5.680847629999999</v>
       </c>
       <c r="K38" t="n">
-        <v>6.336184970000002</v>
+        <v>41.44173227</v>
       </c>
       <c r="L38" t="n">
-        <v>49.13944627</v>
+        <v>36.47619377</v>
       </c>
       <c r="M38" t="n">
-        <v>41.06527597000001</v>
+        <v>-24.18273323</v>
       </c>
     </row>
     <row r="39">
@@ -2026,37 +2026,37 @@
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
-        <v>1.60522561</v>
+        <v>-2.38145906</v>
       </c>
       <c r="D39" t="n">
-        <v>-2.38145906</v>
+        <v>-1.22895808</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.22895808</v>
+        <v>2.09904764</v>
       </c>
       <c r="F39" t="n">
-        <v>2.09904764</v>
+        <v>3.22631047</v>
       </c>
       <c r="G39" t="n">
-        <v>3.22631047</v>
+        <v>8.135896049999999</v>
       </c>
       <c r="H39" t="n">
-        <v>8.135896049999999</v>
+        <v>0.42597227</v>
       </c>
       <c r="I39" t="n">
-        <v>0.42597227</v>
+        <v>5.236759269999999</v>
       </c>
       <c r="J39" t="n">
-        <v>5.236759269999999</v>
+        <v>24.80576117</v>
       </c>
       <c r="K39" t="n">
-        <v>24.80576117</v>
+        <v>21.99748971</v>
       </c>
       <c r="L39" t="n">
-        <v>21.99748971</v>
+        <v>7.5667577</v>
       </c>
       <c r="M39" t="n">
-        <v>7.5667577</v>
+        <v>-0.39082327</v>
       </c>
     </row>
     <row r="40">
@@ -2065,41 +2065,39 @@
           <t>油電燃氣業右下</t>
         </is>
       </c>
-      <c r="B40" t="n">
-        <v>0</v>
-      </c>
+      <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>73.39823507000001</v>
+        <v>168.35309943</v>
       </c>
       <c r="D40" t="n">
-        <v>168.35615972</v>
+        <v>54.65555302999999</v>
       </c>
       <c r="E40" t="n">
-        <v>54.65808956999999</v>
+        <v>-40.04571159</v>
       </c>
       <c r="F40" t="n">
-        <v>-40.04370454000001</v>
+        <v>-65.28430948</v>
       </c>
       <c r="G40" t="n">
-        <v>-65.28278445000001</v>
+        <v>-32.76083196</v>
       </c>
       <c r="H40" t="n">
-        <v>-32.7596749</v>
+        <v>-17.83612673</v>
       </c>
       <c r="I40" t="n">
-        <v>-17.83517614</v>
+        <v>-34.19594447999999</v>
       </c>
       <c r="J40" t="n">
-        <v>-34.19477872</v>
+        <v>-18.27671337</v>
       </c>
       <c r="K40" t="n">
-        <v>-18.2753221</v>
+        <v>16.53812736</v>
       </c>
       <c r="L40" t="n">
-        <v>16.53961087</v>
+        <v>-19.19792823</v>
       </c>
       <c r="M40" t="n">
-        <v>-19.19636158</v>
+        <v>-76.84975909000001</v>
       </c>
     </row>
     <row r="41">
@@ -2110,37 +2108,37 @@
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
-        <v>-0.03262842000000001</v>
+        <v>-0.04257767</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.04257767</v>
+        <v>0.007155480000000001</v>
       </c>
       <c r="E41" t="n">
-        <v>0.007155480000000001</v>
+        <v>0.10078061</v>
       </c>
       <c r="F41" t="n">
-        <v>0.10078061</v>
+        <v>0.01855391</v>
       </c>
       <c r="G41" t="n">
-        <v>0.01855391</v>
+        <v>-0.01178567</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.01178567</v>
+        <v>-0.0178828</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.0178828</v>
+        <v>-0.02335537</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.02335537</v>
+        <v>-0.02156378</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.02156378</v>
+        <v>-0.01861452</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.01861452</v>
+        <v>-0.01283763</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.01283763</v>
+        <v>-0.01596297</v>
       </c>
     </row>
     <row r="42">
@@ -2151,37 +2149,37 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>335.6496038400001</v>
+        <v>486.62145114</v>
       </c>
       <c r="D42" t="n">
-        <v>486.62145114</v>
+        <v>768.44312698</v>
       </c>
       <c r="E42" t="n">
-        <v>768.44312698</v>
+        <v>271.57353044</v>
       </c>
       <c r="F42" t="n">
-        <v>271.57353044</v>
+        <v>-68.75579565</v>
       </c>
       <c r="G42" t="n">
-        <v>-68.75579565</v>
+        <v>-25.65882652</v>
       </c>
       <c r="H42" t="n">
-        <v>-25.65882652</v>
+        <v>-203.34503687</v>
       </c>
       <c r="I42" t="n">
-        <v>-203.34503687</v>
+        <v>-26.00127152</v>
       </c>
       <c r="J42" t="n">
-        <v>-26.00127152</v>
+        <v>156.76665614</v>
       </c>
       <c r="K42" t="n">
-        <v>156.76665614</v>
+        <v>578.4989785</v>
       </c>
       <c r="L42" t="n">
-        <v>578.4989785</v>
+        <v>900.52032724</v>
       </c>
       <c r="M42" t="n">
-        <v>900.52032724</v>
+        <v>1153.82319753</v>
       </c>
     </row>
     <row r="43">
@@ -2192,37 +2190,37 @@
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
-        <v>1.61384816</v>
+        <v>0.5450071499999999</v>
       </c>
       <c r="D43" t="n">
-        <v>0.5450071499999999</v>
+        <v>2.44174181</v>
       </c>
       <c r="E43" t="n">
-        <v>2.44174181</v>
+        <v>-0.2750045700000001</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.2750045700000001</v>
+        <v>1.46585581</v>
       </c>
       <c r="G43" t="n">
-        <v>1.46585581</v>
+        <v>1.15822565</v>
       </c>
       <c r="H43" t="n">
-        <v>1.15822565</v>
+        <v>-1.54501608</v>
       </c>
       <c r="I43" t="n">
-        <v>-1.54501608</v>
+        <v>-2.785485910000001</v>
       </c>
       <c r="J43" t="n">
-        <v>-2.785485910000001</v>
+        <v>-2.72785007</v>
       </c>
       <c r="K43" t="n">
-        <v>-2.72785007</v>
+        <v>3.65355746</v>
       </c>
       <c r="L43" t="n">
-        <v>3.65355746</v>
+        <v>20.8485932</v>
       </c>
       <c r="M43" t="n">
-        <v>20.8485932</v>
+        <v>34.26722984000001</v>
       </c>
     </row>
     <row r="44">
@@ -2233,37 +2231,37 @@
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>-1.133946449999999</v>
+        <v>-17.9925402</v>
       </c>
       <c r="D44" t="n">
-        <v>13.24144375</v>
+        <v>77.01381998999999</v>
       </c>
       <c r="E44" t="n">
-        <v>11.76559636</v>
+        <v>-54.02000653</v>
       </c>
       <c r="F44" t="n">
-        <v>14.53376977</v>
+        <v>38.02652629</v>
       </c>
       <c r="G44" t="n">
-        <v>15.49335643</v>
+        <v>83.20819602</v>
       </c>
       <c r="H44" t="n">
-        <v>16.90445673</v>
+        <v>82.76183254999999</v>
       </c>
       <c r="I44" t="n">
-        <v>5.929895040000002</v>
+        <v>104.05543862</v>
       </c>
       <c r="J44" t="n">
-        <v>12.21935185</v>
+        <v>28.05805659</v>
       </c>
       <c r="K44" t="n">
-        <v>11.88079468</v>
+        <v>79.00795539000001</v>
       </c>
       <c r="L44" t="n">
-        <v>12.56105717</v>
+        <v>135.77151984</v>
       </c>
       <c r="M44" t="n">
-        <v>-6.57284661</v>
+        <v>171.60848488</v>
       </c>
     </row>
     <row r="45">
@@ -2276,37 +2274,37 @@
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>-340.48951741</v>
+        <v>-317.72873369</v>
       </c>
       <c r="D45" t="n">
-        <v>-317.75064965</v>
+        <v>-304.6201171</v>
       </c>
       <c r="E45" t="n">
-        <v>-304.39042601</v>
+        <v>-63.96852718</v>
       </c>
       <c r="F45" t="n">
-        <v>-62.50324634999999</v>
+        <v>7.646972300000004</v>
       </c>
       <c r="G45" t="n">
-        <v>9.092606350000009</v>
+        <v>31.97162437</v>
       </c>
       <c r="H45" t="n">
-        <v>32.71090707</v>
+        <v>119.09006323</v>
       </c>
       <c r="I45" t="n">
-        <v>119.31041291</v>
+        <v>261.26988149</v>
       </c>
       <c r="J45" t="n">
-        <v>261.59726426</v>
+        <v>96.42507055000002</v>
       </c>
       <c r="K45" t="n">
-        <v>96.41570724000002</v>
+        <v>181.65105055</v>
       </c>
       <c r="L45" t="n">
-        <v>182.21972061</v>
+        <v>198.57951492</v>
       </c>
       <c r="M45" t="n">
-        <v>197.71447</v>
+        <v>293.93786827</v>
       </c>
     </row>
     <row r="46">
@@ -2317,37 +2315,37 @@
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>-268.04503056</v>
+        <v>-194.48683474</v>
       </c>
       <c r="D46" t="n">
-        <v>-225.69859044</v>
+        <v>-32.86805202</v>
       </c>
       <c r="E46" t="n">
-        <v>32.15057442000001</v>
+        <v>35.99495334</v>
       </c>
       <c r="F46" t="n">
-        <v>-34.02384609000001</v>
+        <v>69.92252886</v>
       </c>
       <c r="G46" t="n">
-        <v>91.01002581</v>
+        <v>-69.04706243999999</v>
       </c>
       <c r="H46" t="n">
-        <v>-3.482605619999986</v>
+        <v>-1.624596259999997</v>
       </c>
       <c r="I46" t="n">
-        <v>74.98699289999999</v>
+        <v>-39.50340163000001</v>
       </c>
       <c r="J46" t="n">
-        <v>52.00554579</v>
+        <v>-75.03116486</v>
       </c>
       <c r="K46" t="n">
-        <v>-58.8440166</v>
+        <v>9.758939030000001</v>
       </c>
       <c r="L46" t="n">
-        <v>75.63740370000001</v>
+        <v>-38.61703267000001</v>
       </c>
       <c r="M46" t="n">
-        <v>104.59265614</v>
+        <v>55.03483952000001</v>
       </c>
     </row>
     <row r="47">
@@ -2358,37 +2356,37 @@
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>-5.88827229</v>
+        <v>-5.95651349</v>
       </c>
       <c r="D47" t="n">
-        <v>-5.95644375</v>
+        <v>-5.16051644</v>
       </c>
       <c r="E47" t="n">
-        <v>-5.160463770000001</v>
+        <v>-5.243580819999999</v>
       </c>
       <c r="F47" t="n">
-        <v>-5.243561529999999</v>
+        <v>-1.42689061</v>
       </c>
       <c r="G47" t="n">
-        <v>-1.42685796</v>
+        <v>-1.55805487</v>
       </c>
       <c r="H47" t="n">
-        <v>-1.55800123</v>
+        <v>0.2128199</v>
       </c>
       <c r="I47" t="n">
-        <v>0.21287991</v>
+        <v>0.11380938</v>
       </c>
       <c r="J47" t="n">
-        <v>0.11387768</v>
+        <v>-1.16393911</v>
       </c>
       <c r="K47" t="n">
-        <v>-1.16397337</v>
+        <v>3.26730915</v>
       </c>
       <c r="L47" t="n">
-        <v>3.26751648</v>
+        <v>1.63955288</v>
       </c>
       <c r="M47" t="n">
-        <v>1.63974039</v>
+        <v>0.7404075099999999</v>
       </c>
     </row>
     <row r="48">
@@ -2399,37 +2397,37 @@
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
-        <v>39.68570400999999</v>
+        <v>4.959410939999997</v>
       </c>
       <c r="D48" t="n">
-        <v>4.959410939999997</v>
+        <v>20.79775888</v>
       </c>
       <c r="E48" t="n">
-        <v>20.79775888</v>
+        <v>26.43965689</v>
       </c>
       <c r="F48" t="n">
-        <v>26.43965689</v>
+        <v>2.09872248</v>
       </c>
       <c r="G48" t="n">
-        <v>2.09872248</v>
+        <v>-22.66043907</v>
       </c>
       <c r="H48" t="n">
-        <v>-22.66043907</v>
+        <v>-14.22418096</v>
       </c>
       <c r="I48" t="n">
-        <v>-14.22418096</v>
+        <v>-101.4682925</v>
       </c>
       <c r="J48" t="n">
-        <v>-101.4682925</v>
+        <v>-165.30248956</v>
       </c>
       <c r="K48" t="n">
-        <v>-165.30248956</v>
+        <v>-139.3712056</v>
       </c>
       <c r="L48" t="n">
-        <v>-139.3712056</v>
+        <v>-51.9386133</v>
       </c>
       <c r="M48" t="n">
-        <v>-51.9386133</v>
+        <v>162.00280897</v>
       </c>
     </row>
     <row r="49">
@@ -2440,37 +2438,37 @@
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>0.06715978</v>
+        <v>-0.10224491</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.10231465</v>
+        <v>-0.002981920000000003</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.003034590000000003</v>
+        <v>1.65279592</v>
       </c>
       <c r="F49" t="n">
-        <v>1.65277663</v>
+        <v>1.32683326</v>
       </c>
       <c r="G49" t="n">
-        <v>1.32680061</v>
+        <v>0.2555712999999999</v>
       </c>
       <c r="H49" t="n">
-        <v>0.25551766</v>
+        <v>-0.002230730000000012</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.002290740000000012</v>
+        <v>-0.21209316</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.21216146</v>
+        <v>-0.3230028099999999</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.3229685499999999</v>
+        <v>-0.64213148</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.6423388099999999</v>
+        <v>-0.6877515400000001</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.68793905</v>
+        <v>-0.8016981400000001</v>
       </c>
     </row>
     <row r="50">
@@ -2481,37 +2479,37 @@
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
-        <v>-62.66401336</v>
+        <v>-11.23502624000001</v>
       </c>
       <c r="D50" t="n">
-        <v>-57.76571075</v>
+        <v>0.9214968800000017</v>
       </c>
       <c r="E50" t="n">
-        <v>-32.92139744</v>
+        <v>11.29179383</v>
       </c>
       <c r="F50" t="n">
-        <v>-122.83206046</v>
+        <v>40.39844144</v>
       </c>
       <c r="G50" t="n">
-        <v>-8.516761969999999</v>
+        <v>16.19871256</v>
       </c>
       <c r="H50" t="n">
-        <v>-116.90533009</v>
+        <v>104.70811418</v>
       </c>
       <c r="I50" t="n">
-        <v>51.20665815</v>
+        <v>38.44001472999999</v>
       </c>
       <c r="J50" t="n">
-        <v>-77.14822511999999</v>
+        <v>81.66755676999999</v>
       </c>
       <c r="K50" t="n">
-        <v>-66.42575235000001</v>
+        <v>83.89153795</v>
       </c>
       <c r="L50" t="n">
-        <v>-59.29735394</v>
+        <v>18.31902892</v>
       </c>
       <c r="M50" t="n">
-        <v>-112.99623943</v>
+        <v>80.56754973000001</v>
       </c>
     </row>
     <row r="51">
@@ -2524,37 +2522,37 @@
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>4.58012303</v>
+        <v>-5.524311600000001</v>
       </c>
       <c r="D51" t="n">
-        <v>-7.572110350000001</v>
+        <v>2.53485937</v>
       </c>
       <c r="E51" t="n">
-        <v>2.53484422</v>
+        <v>-2.54366476</v>
       </c>
       <c r="F51" t="n">
-        <v>-2.543530349999999</v>
+        <v>4.03323023</v>
       </c>
       <c r="G51" t="n">
-        <v>4.033005090000001</v>
+        <v>-4.208008479999999</v>
       </c>
       <c r="H51" t="n">
-        <v>-4.20817929</v>
+        <v>-16.668004</v>
       </c>
       <c r="I51" t="n">
-        <v>-16.66796257</v>
+        <v>-17.31000216</v>
       </c>
       <c r="J51" t="n">
-        <v>-17.3098579</v>
+        <v>-27.00119206</v>
       </c>
       <c r="K51" t="n">
-        <v>-27.00053969</v>
+        <v>-37.85262138</v>
       </c>
       <c r="L51" t="n">
-        <v>-37.85252972</v>
+        <v>-40.22165305999999</v>
       </c>
       <c r="M51" t="n">
-        <v>-40.22146727</v>
+        <v>-40.80044587</v>
       </c>
     </row>
     <row r="52">
@@ -2565,37 +2563,37 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>-0.6707557600000009</v>
+        <v>-11.58867564</v>
       </c>
       <c r="D52" t="n">
-        <v>-11.58867564</v>
+        <v>17.82601938</v>
       </c>
       <c r="E52" t="n">
-        <v>17.82601938</v>
+        <v>3.01749032</v>
       </c>
       <c r="F52" t="n">
-        <v>3.01749032</v>
+        <v>23.56122139</v>
       </c>
       <c r="G52" t="n">
-        <v>23.56122139</v>
+        <v>23.25266108</v>
       </c>
       <c r="H52" t="n">
-        <v>23.25266108</v>
+        <v>10.98587756</v>
       </c>
       <c r="I52" t="n">
-        <v>10.98587756</v>
+        <v>14.37131513</v>
       </c>
       <c r="J52" t="n">
-        <v>14.37131513</v>
+        <v>-7.095445330000001</v>
       </c>
       <c r="K52" t="n">
-        <v>-7.095445330000001</v>
+        <v>3.773723930000001</v>
       </c>
       <c r="L52" t="n">
-        <v>3.773723930000001</v>
+        <v>-0.6006474200000018</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.6006474200000018</v>
+        <v>-25.32666663</v>
       </c>
     </row>
     <row r="53">
@@ -2606,37 +2604,37 @@
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>10.94663334000001</v>
+        <v>-242.49142926</v>
       </c>
       <c r="D53" t="n">
-        <v>-242.48694746</v>
+        <v>176.6907841</v>
       </c>
       <c r="E53" t="n">
-        <v>176.69649829</v>
+        <v>173.38863384</v>
       </c>
       <c r="F53" t="n">
-        <v>173.3919018</v>
+        <v>534.25715562</v>
       </c>
       <c r="G53" t="n">
-        <v>534.26192584</v>
+        <v>553.16674841</v>
       </c>
       <c r="H53" t="n">
-        <v>553.1683261099998</v>
+        <v>-153.03526199</v>
       </c>
       <c r="I53" t="n">
-        <v>-153.03544707</v>
+        <v>23.20095008999999</v>
       </c>
       <c r="J53" t="n">
-        <v>23.19576348999999</v>
+        <v>202.3618308</v>
       </c>
       <c r="K53" t="n">
-        <v>202.36344017</v>
+        <v>368.14814455</v>
       </c>
       <c r="L53" t="n">
-        <v>368.1468738200001</v>
+        <v>697.0104023600001</v>
       </c>
       <c r="M53" t="n">
-        <v>697.00617015</v>
+        <v>588.32413694</v>
       </c>
     </row>
     <row r="54">
@@ -2647,37 +2645,37 @@
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>3.392625100000001</v>
+        <v>-5.696196230000001</v>
       </c>
       <c r="D54" t="n">
-        <v>-5.6969817</v>
+        <v>-0.9628130199999999</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.9628962199999999</v>
+        <v>9.50489205</v>
       </c>
       <c r="F54" t="n">
-        <v>9.504409800000001</v>
+        <v>6.19144345</v>
       </c>
       <c r="G54" t="n">
-        <v>6.19122544</v>
+        <v>18.44292239</v>
       </c>
       <c r="H54" t="n">
-        <v>18.44192423</v>
+        <v>33.41217956000001</v>
       </c>
       <c r="I54" t="n">
-        <v>33.41105407</v>
+        <v>32.28907975000001</v>
       </c>
       <c r="J54" t="n">
-        <v>32.28942822</v>
+        <v>13.82758123</v>
       </c>
       <c r="K54" t="n">
-        <v>13.83002886</v>
+        <v>22.66509357</v>
       </c>
       <c r="L54" t="n">
-        <v>22.66830127</v>
+        <v>11.76005505</v>
       </c>
       <c r="M54" t="n">
-        <v>11.76082298</v>
+        <v>15.07171019</v>
       </c>
     </row>
     <row r="55">
@@ -2688,37 +2686,37 @@
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>229.34488098</v>
+        <v>-0.8393121099999971</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.8430084399999972</v>
+        <v>76.22848026000001</v>
       </c>
       <c r="E55" t="n">
-        <v>106.61593814</v>
+        <v>89.94039045999999</v>
       </c>
       <c r="F55" t="n">
-        <v>124.87391476</v>
+        <v>112.80848578</v>
       </c>
       <c r="G55" t="n">
-        <v>151.40139458</v>
+        <v>261.49492484</v>
       </c>
       <c r="H55" t="n">
-        <v>285.09222881</v>
+        <v>6.48088612</v>
       </c>
       <c r="I55" t="n">
-        <v>15.57843331</v>
+        <v>394.55405591</v>
       </c>
       <c r="J55" t="n">
-        <v>372.0778595</v>
+        <v>315.60176294</v>
       </c>
       <c r="K55" t="n">
-        <v>327.19522717</v>
+        <v>368.73117568</v>
       </c>
       <c r="L55" t="n">
-        <v>361.80669016</v>
+        <v>35.39821490000001</v>
       </c>
       <c r="M55" t="n">
-        <v>51.10309794000001</v>
+        <v>15.30677176000001</v>
       </c>
     </row>
     <row r="56">
@@ -2729,37 +2727,37 @@
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>-1.13279489</v>
+        <v>-9.10462467</v>
       </c>
       <c r="D56" t="n">
-        <v>-9.104689879999999</v>
+        <v>2.08191375</v>
       </c>
       <c r="E56" t="n">
-        <v>2.08177505</v>
+        <v>-7.27952517</v>
       </c>
       <c r="F56" t="n">
-        <v>-7.279503650000001</v>
+        <v>-1.98157208</v>
       </c>
       <c r="G56" t="n">
-        <v>-1.98131092</v>
+        <v>-4.11619094</v>
       </c>
       <c r="H56" t="n">
-        <v>-4.11600271</v>
+        <v>4.08045064</v>
       </c>
       <c r="I56" t="n">
-        <v>4.08051314</v>
+        <v>-0.19953913</v>
       </c>
       <c r="J56" t="n">
-        <v>-0.19955683</v>
+        <v>-12.28212704</v>
       </c>
       <c r="K56" t="n">
-        <v>-12.28203431</v>
+        <v>-2.91420292</v>
       </c>
       <c r="L56" t="n">
-        <v>-2.91422361</v>
+        <v>20.80548296</v>
       </c>
       <c r="M56" t="n">
-        <v>20.80536127</v>
+        <v>4.32854381</v>
       </c>
     </row>
     <row r="57">
@@ -2770,37 +2768,37 @@
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
-        <v>-7.73082727</v>
+        <v>-13.07116972</v>
       </c>
       <c r="D57" t="n">
-        <v>-13.07116972</v>
+        <v>-3.20742268</v>
       </c>
       <c r="E57" t="n">
-        <v>-3.21768409</v>
+        <v>24.12934406999999</v>
       </c>
       <c r="F57" t="n">
-        <v>24.1128248</v>
+        <v>19.6332525</v>
       </c>
       <c r="G57" t="n">
-        <v>19.63663041</v>
+        <v>9.521876189999999</v>
       </c>
       <c r="H57" t="n">
-        <v>9.533073910000001</v>
+        <v>-6.49025438</v>
       </c>
       <c r="I57" t="n">
-        <v>-6.476807470000001</v>
+        <v>-19.63731446</v>
       </c>
       <c r="J57" t="n">
-        <v>-19.62278828</v>
+        <v>-31.28672083</v>
       </c>
       <c r="K57" t="n">
-        <v>-31.28641675</v>
+        <v>-35.82230129</v>
       </c>
       <c r="L57" t="n">
-        <v>-35.817193</v>
+        <v>-48.83644887</v>
       </c>
       <c r="M57" t="n">
-        <v>-48.82730269</v>
+        <v>-2.96099005</v>
       </c>
     </row>
     <row r="58">
@@ -2811,37 +2809,37 @@
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>7.918194450000001</v>
+        <v>5.066574070000001</v>
       </c>
       <c r="D58" t="n">
-        <v>5.06663928</v>
+        <v>15.59515841</v>
       </c>
       <c r="E58" t="n">
-        <v>15.59529711</v>
+        <v>34.83701206</v>
       </c>
       <c r="F58" t="n">
-        <v>34.83699054</v>
+        <v>44.05439052</v>
       </c>
       <c r="G58" t="n">
-        <v>44.05412936</v>
+        <v>45.77312744</v>
       </c>
       <c r="H58" t="n">
-        <v>45.77293921</v>
+        <v>20.3881575</v>
       </c>
       <c r="I58" t="n">
-        <v>20.388095</v>
+        <v>-9.58320387</v>
       </c>
       <c r="J58" t="n">
-        <v>-9.583186169999999</v>
+        <v>-17.2459276</v>
       </c>
       <c r="K58" t="n">
-        <v>-17.24602033</v>
+        <v>-34.949534</v>
       </c>
       <c r="L58" t="n">
-        <v>-34.94951331</v>
+        <v>-42.18699216</v>
       </c>
       <c r="M58" t="n">
-        <v>-42.18687047</v>
+        <v>-0.99560861</v>
       </c>
     </row>
     <row r="59">
@@ -2852,37 +2850,37 @@
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
-        <v>-7.66747269</v>
+        <v>-47.88692235000001</v>
       </c>
       <c r="D59" t="n">
-        <v>-47.88692235000001</v>
+        <v>6.96574599</v>
       </c>
       <c r="E59" t="n">
-        <v>6.96574599</v>
+        <v>42.54732838</v>
       </c>
       <c r="F59" t="n">
-        <v>42.54732838</v>
+        <v>65.16556917</v>
       </c>
       <c r="G59" t="n">
-        <v>65.16556917</v>
+        <v>39.0396422</v>
       </c>
       <c r="H59" t="n">
-        <v>39.0396422</v>
+        <v>50.5705571</v>
       </c>
       <c r="I59" t="n">
-        <v>50.5705571</v>
+        <v>29.48116599</v>
       </c>
       <c r="J59" t="n">
-        <v>29.48116599</v>
+        <v>3.745202050000001</v>
       </c>
       <c r="K59" t="n">
-        <v>3.745202050000001</v>
+        <v>-27.11462849</v>
       </c>
       <c r="L59" t="n">
-        <v>-27.11462849</v>
+        <v>-14.54311404</v>
       </c>
       <c r="M59" t="n">
-        <v>-15.70060404</v>
+        <v>-20.20816677</v>
       </c>
     </row>
     <row r="60">
@@ -2893,37 +2891,37 @@
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
-        <v>-0.005366599999999999</v>
+        <v>-0.008696569999999999</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.008696569999999999</v>
+        <v>0.0294527</v>
       </c>
       <c r="E60" t="n">
-        <v>0.0294527</v>
+        <v>0.02929013</v>
       </c>
       <c r="F60" t="n">
-        <v>0.02929013</v>
+        <v>0.00690925</v>
       </c>
       <c r="G60" t="n">
-        <v>0.00690925</v>
+        <v>-0.002395420000000002</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.002395420000000002</v>
+        <v>0.0890145</v>
       </c>
       <c r="I60" t="n">
-        <v>0.0890145</v>
+        <v>0.02680047</v>
       </c>
       <c r="J60" t="n">
-        <v>0.02680047</v>
+        <v>0.03247147</v>
       </c>
       <c r="K60" t="n">
-        <v>0.03247147</v>
+        <v>0.03435918</v>
       </c>
       <c r="L60" t="n">
-        <v>0.03435918</v>
+        <v>0.0329061</v>
       </c>
       <c r="M60" t="n">
-        <v>0.0329061</v>
+        <v>-0.007547529999999998</v>
       </c>
     </row>
     <row r="61">
@@ -2934,37 +2932,37 @@
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
-        <v>-15.12597921</v>
+        <v>19.01627602</v>
       </c>
       <c r="D61" t="n">
-        <v>19.01627602</v>
+        <v>32.19641023</v>
       </c>
       <c r="E61" t="n">
-        <v>32.19641023</v>
+        <v>66.00317588999999</v>
       </c>
       <c r="F61" t="n">
-        <v>66.00317588999999</v>
+        <v>95.2021495</v>
       </c>
       <c r="G61" t="n">
-        <v>95.2021495</v>
+        <v>52.08626254999999</v>
       </c>
       <c r="H61" t="n">
-        <v>52.08626254999999</v>
+        <v>56.2650797</v>
       </c>
       <c r="I61" t="n">
-        <v>56.2650797</v>
+        <v>4.496617839999995</v>
       </c>
       <c r="J61" t="n">
-        <v>4.496617839999995</v>
+        <v>16.52188146</v>
       </c>
       <c r="K61" t="n">
-        <v>16.52188146</v>
+        <v>67.27001618000001</v>
       </c>
       <c r="L61" t="n">
-        <v>67.27001618000001</v>
+        <v>-16.92923413</v>
       </c>
       <c r="M61" t="n">
-        <v>-16.92923413</v>
+        <v>-37.98425285</v>
       </c>
     </row>
     <row r="62">
@@ -2975,37 +2973,37 @@
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>-0.0038087</v>
+        <v>-0.0062889</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.00767553</v>
+        <v>-0.00268161</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.00331886</v>
+        <v>-0.00248998</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.00264089</v>
+        <v>0.006524610000000001</v>
       </c>
       <c r="G62" t="n">
-        <v>0.00704679</v>
+        <v>0.00455783</v>
       </c>
       <c r="H62" t="n">
-        <v>0.00531042</v>
+        <v>0.0007480000000000001</v>
       </c>
       <c r="I62" t="n">
-        <v>0.00115759</v>
+        <v>0.0090934</v>
       </c>
       <c r="J62" t="n">
-        <v>0.009192200000000001</v>
+        <v>0.01658377</v>
       </c>
       <c r="K62" t="n">
-        <v>0.01654324</v>
+        <v>0.01830944</v>
       </c>
       <c r="L62" t="n">
-        <v>0.02075615</v>
+        <v>0.01968591</v>
       </c>
       <c r="M62" t="n">
-        <v>0.02263502</v>
+        <v>0.0123997</v>
       </c>
     </row>
     <row r="63">
@@ -3016,37 +3014,37 @@
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>15.73900359</v>
+        <v>-2.453520489999999</v>
       </c>
       <c r="D63" t="n">
-        <v>-2.45213386</v>
+        <v>28.65187051</v>
       </c>
       <c r="E63" t="n">
-        <v>28.65250776</v>
+        <v>47.66603411</v>
       </c>
       <c r="F63" t="n">
-        <v>47.66618502</v>
+        <v>94.86402831000001</v>
       </c>
       <c r="G63" t="n">
-        <v>94.86350612999999</v>
+        <v>46.74833786</v>
       </c>
       <c r="H63" t="n">
-        <v>46.74758527</v>
+        <v>41.24798834000001</v>
       </c>
       <c r="I63" t="n">
-        <v>41.24757875</v>
+        <v>17.01447163</v>
       </c>
       <c r="J63" t="n">
-        <v>17.01437283</v>
+        <v>18.43863869</v>
       </c>
       <c r="K63" t="n">
-        <v>18.43867922</v>
+        <v>30.1662141</v>
       </c>
       <c r="L63" t="n">
-        <v>30.16376739</v>
+        <v>29.38531994000001</v>
       </c>
       <c r="M63" t="n">
-        <v>29.38237083</v>
+        <v>-1.37473835</v>
       </c>
     </row>
     <row r="64">
@@ -3057,37 +3055,37 @@
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
-        <v>0.0004248200000000001</v>
+        <v>0.00090755</v>
       </c>
       <c r="D64" t="n">
-        <v>0.00090755</v>
+        <v>0.00103174</v>
       </c>
       <c r="E64" t="n">
-        <v>0.00103174</v>
+        <v>0.0009914099999999999</v>
       </c>
       <c r="F64" t="n">
-        <v>0.0009914099999999999</v>
+        <v>6.247e-05</v>
       </c>
       <c r="G64" t="n">
-        <v>6.247e-05</v>
+        <v>0.0004044</v>
       </c>
       <c r="H64" t="n">
-        <v>0.0004044</v>
+        <v>0.00072251</v>
       </c>
       <c r="I64" t="n">
-        <v>0.00072251</v>
+        <v>-0.00025412</v>
       </c>
       <c r="J64" t="n">
-        <v>-0.00025412</v>
+        <v>-0.00126824</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.00126824</v>
+        <v>-0.00052996</v>
       </c>
       <c r="L64" t="n">
-        <v>-0.00052996</v>
+        <v>-4.627e-05</v>
       </c>
       <c r="M64" t="n">
-        <v>-4.627e-05</v>
+        <v>0.00012135</v>
       </c>
     </row>
     <row r="65">
@@ -3098,37 +3096,37 @@
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
-        <v>-0.0002611</v>
+        <v>-0.00027651</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.00027651</v>
+        <v>-0.0002609000000000001</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.0002609000000000001</v>
+        <v>5.814e-05</v>
       </c>
       <c r="F65" t="n">
-        <v>5.814e-05</v>
+        <v>0.00018835</v>
       </c>
       <c r="G65" t="n">
-        <v>0.00018835</v>
+        <v>2.243e-05</v>
       </c>
       <c r="H65" t="n">
-        <v>2.243e-05</v>
+        <v>-8.019e-05</v>
       </c>
       <c r="I65" t="n">
-        <v>-8.019e-05</v>
+        <v>-3.720999999999999e-05</v>
       </c>
       <c r="J65" t="n">
-        <v>-3.720999999999999e-05</v>
+        <v>-0.00012853</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.00012853</v>
+        <v>-0.00011783</v>
       </c>
       <c r="L65" t="n">
-        <v>-0.00011783</v>
+        <v>-0.00038662</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.00038662</v>
+        <v>-0.00020338</v>
       </c>
     </row>
     <row r="66">
@@ -3139,37 +3137,37 @@
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>123.2535663</v>
+        <v>250.33207424</v>
       </c>
       <c r="D66" t="n">
-        <v>410.13154095</v>
+        <v>-71.43827585000001</v>
       </c>
       <c r="E66" t="n">
-        <v>11.21869360999999</v>
+        <v>74.57830126</v>
       </c>
       <c r="F66" t="n">
-        <v>180.39949613</v>
+        <v>587.52380249</v>
       </c>
       <c r="G66" t="n">
-        <v>722.05268942</v>
+        <v>153.62527904</v>
       </c>
       <c r="H66" t="n">
-        <v>196.89899252</v>
+        <v>484.36402765</v>
       </c>
       <c r="I66" t="n">
-        <v>597.94056154</v>
+        <v>563.4345118799999</v>
       </c>
       <c r="J66" t="n">
-        <v>739.9888603400001</v>
+        <v>827.86811563</v>
       </c>
       <c r="K66" t="n">
-        <v>897.7872426599999</v>
+        <v>851.1703980999999</v>
       </c>
       <c r="L66" t="n">
-        <v>989.4003378800001</v>
+        <v>1079.83068439</v>
       </c>
       <c r="M66" t="n">
-        <v>1236.14751122</v>
+        <v>1041.36050229</v>
       </c>
     </row>
     <row r="67">
@@ -3180,37 +3178,37 @@
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>-17.09105708</v>
+        <v>-53.14267139</v>
       </c>
       <c r="D67" t="n">
-        <v>-53.14267139</v>
+        <v>-3.999420880000002</v>
       </c>
       <c r="E67" t="n">
-        <v>-3.999420880000002</v>
+        <v>33.33771072</v>
       </c>
       <c r="F67" t="n">
-        <v>33.33771072</v>
+        <v>2.42355657</v>
       </c>
       <c r="G67" t="n">
-        <v>2.42355657</v>
+        <v>1.51502225</v>
       </c>
       <c r="H67" t="n">
-        <v>1.51502225</v>
+        <v>-43.93714867</v>
       </c>
       <c r="I67" t="n">
-        <v>-43.93714867</v>
+        <v>-27.1973517</v>
       </c>
       <c r="J67" t="n">
-        <v>-27.1973517</v>
+        <v>-8.63181679</v>
       </c>
       <c r="K67" t="n">
-        <v>-8.63181679</v>
+        <v>45.1348587</v>
       </c>
       <c r="L67" t="n">
-        <v>45.1348587</v>
+        <v>-69.71877004</v>
       </c>
       <c r="M67" t="n">
-        <v>-69.71877004</v>
+        <v>42.06810895</v>
       </c>
     </row>
     <row r="68">
@@ -3221,37 +3219,37 @@
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>391.75445482</v>
+        <v>331.44025787</v>
       </c>
       <c r="D68" t="n">
-        <v>171.64484291</v>
+        <v>431.3726510399999</v>
       </c>
       <c r="E68" t="n">
-        <v>348.72537448</v>
+        <v>235.76456954</v>
       </c>
       <c r="F68" t="n">
-        <v>129.96735655</v>
+        <v>283.16068275</v>
       </c>
       <c r="G68" t="n">
-        <v>148.64146146</v>
+        <v>171.8184034</v>
       </c>
       <c r="H68" t="n">
-        <v>128.54935133</v>
+        <v>15.65956619</v>
       </c>
       <c r="I68" t="n">
-        <v>-97.91800155999999</v>
+        <v>33.10447479000002</v>
       </c>
       <c r="J68" t="n">
-        <v>-143.4554884</v>
+        <v>-48.99889076</v>
       </c>
       <c r="K68" t="n">
-        <v>-118.92468569</v>
+        <v>124.08845681</v>
       </c>
       <c r="L68" t="n">
-        <v>-14.14023993</v>
+        <v>40.68521676999999</v>
       </c>
       <c r="M68" t="n">
-        <v>-118.20082058</v>
+        <v>22.86860737</v>
       </c>
     </row>
     <row r="69">
@@ -3262,37 +3260,37 @@
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>-4.28064262</v>
+        <v>-9.848016550000001</v>
       </c>
       <c r="D69" t="n">
-        <v>-9.848016550000001</v>
+        <v>-11.75977663</v>
       </c>
       <c r="E69" t="n">
-        <v>-11.75977663</v>
+        <v>-14.45543988</v>
       </c>
       <c r="F69" t="n">
-        <v>-14.45543988</v>
+        <v>-8.60103045</v>
       </c>
       <c r="G69" t="n">
-        <v>-8.60103045</v>
+        <v>1.481096</v>
       </c>
       <c r="H69" t="n">
-        <v>1.481096</v>
+        <v>-2.09694106</v>
       </c>
       <c r="I69" t="n">
-        <v>-2.09694106</v>
+        <v>-1.18870531</v>
       </c>
       <c r="J69" t="n">
-        <v>-1.18870531</v>
+        <v>0.8999840899999999</v>
       </c>
       <c r="K69" t="n">
-        <v>0.8999840899999999</v>
+        <v>-1.07992369</v>
       </c>
       <c r="L69" t="n">
-        <v>-1.07992369</v>
+        <v>-8.13542947</v>
       </c>
       <c r="M69" t="n">
-        <v>-8.13542947</v>
+        <v>-6.112742610000001</v>
       </c>
     </row>
     <row r="70">
@@ -3303,37 +3301,37 @@
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>-3.39045584</v>
+        <v>-4.06147909</v>
       </c>
       <c r="D70" t="n">
-        <v>-4.06147909</v>
+        <v>-3.60733925</v>
       </c>
       <c r="E70" t="n">
-        <v>-3.60733925</v>
+        <v>-1.16033294</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.16033294</v>
+        <v>-1.55525517</v>
       </c>
       <c r="G70" t="n">
-        <v>-1.55525517</v>
+        <v>0.15859867</v>
       </c>
       <c r="H70" t="n">
-        <v>0.15859867</v>
+        <v>-0.01651628</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.01651628</v>
+        <v>0.93115824</v>
       </c>
       <c r="J70" t="n">
-        <v>0.93115824</v>
+        <v>0.15324129</v>
       </c>
       <c r="K70" t="n">
-        <v>0.15324129</v>
+        <v>2.0141396</v>
       </c>
       <c r="L70" t="n">
-        <v>2.0141396</v>
+        <v>0.94456732</v>
       </c>
       <c r="M70" t="n">
-        <v>0.94456732</v>
+        <v>1.31059385</v>
       </c>
     </row>
     <row r="71">
@@ -3344,37 +3342,37 @@
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
-        <v>-5.49167339</v>
+        <v>-6.985563310000001</v>
       </c>
       <c r="D71" t="n">
-        <v>-6.985563310000001</v>
+        <v>6.14054282</v>
       </c>
       <c r="E71" t="n">
-        <v>6.14054282</v>
+        <v>22.89727625</v>
       </c>
       <c r="F71" t="n">
-        <v>22.89727625</v>
+        <v>39.58487804</v>
       </c>
       <c r="G71" t="n">
-        <v>39.58487804</v>
+        <v>49.03197814</v>
       </c>
       <c r="H71" t="n">
-        <v>49.03197814</v>
+        <v>20.29127258</v>
       </c>
       <c r="I71" t="n">
-        <v>20.29127258</v>
+        <v>24.00895878</v>
       </c>
       <c r="J71" t="n">
-        <v>24.00895878</v>
+        <v>34.17125779</v>
       </c>
       <c r="K71" t="n">
-        <v>34.17125779</v>
+        <v>-3.0706811</v>
       </c>
       <c r="L71" t="n">
-        <v>-3.0706811</v>
+        <v>-7.127004649999999</v>
       </c>
       <c r="M71" t="n">
-        <v>-7.127004649999999</v>
+        <v>-16.45539349</v>
       </c>
     </row>
     <row r="72">
@@ -3385,37 +3383,37 @@
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>-13.46545672999999</v>
+        <v>-142.15576028</v>
       </c>
       <c r="D72" t="n">
-        <v>-142.15576028</v>
+        <v>-103.65398381</v>
       </c>
       <c r="E72" t="n">
-        <v>-103.65398381</v>
+        <v>-29.97898556</v>
       </c>
       <c r="F72" t="n">
-        <v>-29.97898556</v>
+        <v>-20.96570658</v>
       </c>
       <c r="G72" t="n">
-        <v>-20.96570658</v>
+        <v>-82.82987403</v>
       </c>
       <c r="H72" t="n">
-        <v>-82.82987403</v>
+        <v>-117.56860161</v>
       </c>
       <c r="I72" t="n">
-        <v>-117.56860161</v>
+        <v>-41.76354069999999</v>
       </c>
       <c r="J72" t="n">
-        <v>-41.76354069999999</v>
+        <v>-96.87037564000001</v>
       </c>
       <c r="K72" t="n">
-        <v>-96.87037564000001</v>
+        <v>-62.8772119</v>
       </c>
       <c r="L72" t="n">
-        <v>-62.8772119</v>
+        <v>-12.82282402</v>
       </c>
       <c r="M72" t="n">
-        <v>-12.82282402</v>
+        <v>98.85202981</v>
       </c>
     </row>
     <row r="73">
@@ -3426,37 +3424,37 @@
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
-        <v>-0.009413699999999837</v>
+        <v>-10.30417954</v>
       </c>
       <c r="D73" t="n">
-        <v>-10.30417954</v>
+        <v>1.9869591</v>
       </c>
       <c r="E73" t="n">
-        <v>1.9869591</v>
+        <v>13.19129905</v>
       </c>
       <c r="F73" t="n">
-        <v>13.19129905</v>
+        <v>5.14271512</v>
       </c>
       <c r="G73" t="n">
-        <v>5.14271512</v>
+        <v>-8.77292924</v>
       </c>
       <c r="H73" t="n">
-        <v>-8.77292924</v>
+        <v>-8.96068459</v>
       </c>
       <c r="I73" t="n">
-        <v>-8.96068459</v>
+        <v>-20.04120091</v>
       </c>
       <c r="J73" t="n">
-        <v>-20.04120091</v>
+        <v>-30.54986415</v>
       </c>
       <c r="K73" t="n">
-        <v>-30.54986415</v>
+        <v>-15.30492149</v>
       </c>
       <c r="L73" t="n">
-        <v>-15.30492149</v>
+        <v>-8.88836045</v>
       </c>
       <c r="M73" t="n">
-        <v>-8.88836045</v>
+        <v>20.78246032</v>
       </c>
     </row>
     <row r="74">
@@ -3467,37 +3465,37 @@
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
-        <v>-491.5545925</v>
+        <v>-1045.54821239</v>
       </c>
       <c r="D74" t="n">
-        <v>-955.75845715</v>
+        <v>36.53091295999999</v>
       </c>
       <c r="E74" t="n">
-        <v>77.77591090999999</v>
+        <v>989.596008</v>
       </c>
       <c r="F74" t="n">
-        <v>945.98594926</v>
+        <v>825.6772632999999</v>
       </c>
       <c r="G74" t="n">
-        <v>863.70488928</v>
+        <v>1184.45386557</v>
       </c>
       <c r="H74" t="n">
-        <v>1242.79248807</v>
+        <v>782.34708296</v>
       </c>
       <c r="I74" t="n">
-        <v>851.86550735</v>
+        <v>678.97440725</v>
       </c>
       <c r="J74" t="n">
-        <v>703.0305864300001</v>
+        <v>691.18475741</v>
       </c>
       <c r="K74" t="n">
-        <v>664.72535027</v>
+        <v>679.2821239900001</v>
       </c>
       <c r="L74" t="n">
-        <v>656.9999549300001</v>
+        <v>973.4732171100001</v>
       </c>
       <c r="M74" t="n">
-        <v>819.4355921499999</v>
+        <v>1410.22305646</v>
       </c>
     </row>
     <row r="75">
@@ -3506,39 +3504,41 @@
           <t>金融保險右下</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr"/>
+      <c r="B75" t="n">
+        <v>0</v>
+      </c>
       <c r="C75" t="n">
-        <v>-375.3300158500001</v>
+        <v>-396.96136286</v>
       </c>
       <c r="D75" t="n">
-        <v>-399.01998549</v>
+        <v>-349.51439723</v>
       </c>
       <c r="E75" t="n">
-        <v>-351.15875377</v>
+        <v>-120.88432679</v>
       </c>
       <c r="F75" t="n">
-        <v>-120.53167</v>
+        <v>70.24992944999998</v>
       </c>
       <c r="G75" t="n">
-        <v>71.85420393</v>
+        <v>163.48480356</v>
       </c>
       <c r="H75" t="n">
-        <v>166.88105806</v>
+        <v>-31.57288105</v>
       </c>
       <c r="I75" t="n">
-        <v>-29.24538225</v>
+        <v>-217.97355836</v>
       </c>
       <c r="J75" t="n">
-        <v>-217.03758715</v>
+        <v>-383.48576996</v>
       </c>
       <c r="K75" t="n">
-        <v>-381.0536326899999</v>
+        <v>-511.4676543900001</v>
       </c>
       <c r="L75" t="n">
-        <v>-510.1900488100001</v>
+        <v>-257.62854329</v>
       </c>
       <c r="M75" t="n">
-        <v>-257.06344158</v>
+        <v>-17.70767385</v>
       </c>
     </row>
     <row r="76">
@@ -3549,37 +3549,37 @@
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>-49.69680476000001</v>
+        <v>9.95605207</v>
       </c>
       <c r="D76" t="n">
-        <v>-87.14577436000002</v>
+        <v>36.61192854999999</v>
       </c>
       <c r="E76" t="n">
-        <v>6.883263300000002</v>
+        <v>60.44058554</v>
       </c>
       <c r="F76" t="n">
-        <v>122.20166119</v>
+        <v>51.94475127</v>
       </c>
       <c r="G76" t="n">
-        <v>33.32606508999999</v>
+        <v>70.27664334000001</v>
       </c>
       <c r="H76" t="n">
-        <v>32.0121898</v>
+        <v>55.08727028</v>
       </c>
       <c r="I76" t="n">
-        <v>2.699553660000002</v>
+        <v>34.91612823</v>
       </c>
       <c r="J76" t="n">
-        <v>16.53077912</v>
+        <v>40.48346314</v>
       </c>
       <c r="K76" t="n">
-        <v>58.56651676</v>
+        <v>47.28463428</v>
       </c>
       <c r="L76" t="n">
-        <v>51.54869252</v>
+        <v>42.36202298000001</v>
       </c>
       <c r="M76" t="n">
-        <v>63.32101605</v>
+        <v>45.27166862000001</v>
       </c>
     </row>
     <row r="77">
@@ -3590,37 +3590,37 @@
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="n">
-        <v>-0.0003751</v>
+        <v>-0.00072667</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.00072667</v>
+        <v>-0.00031853</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.00031853</v>
+        <v>-0.00042214</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.00042214</v>
+        <v>0.00035191</v>
       </c>
       <c r="G77" t="n">
-        <v>0.00035191</v>
+        <v>0.0006016</v>
       </c>
       <c r="H77" t="n">
-        <v>0.0006016</v>
+        <v>0.00119589</v>
       </c>
       <c r="I77" t="n">
-        <v>0.00119589</v>
+        <v>0.00222055</v>
       </c>
       <c r="J77" t="n">
-        <v>0.00222055</v>
+        <v>0.00226234</v>
       </c>
       <c r="K77" t="n">
-        <v>0.00226234</v>
+        <v>0.00101082</v>
       </c>
       <c r="L77" t="n">
-        <v>0.00101082</v>
+        <v>9.988e-05</v>
       </c>
       <c r="M77" t="n">
-        <v>9.988e-05</v>
+        <v>0.00032912</v>
       </c>
     </row>
     <row r="78">
@@ -3631,37 +3631,37 @@
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
-        <v>-9.306000000000001e-05</v>
+        <v>-0.00439828</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.00439828</v>
+        <v>-0.005935770000000001</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.005935770000000001</v>
+        <v>-0.006376339999999999</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.006376339999999999</v>
+        <v>-0.00146164</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.00146164</v>
+        <v>0.0001785999999999999</v>
       </c>
       <c r="H78" t="n">
-        <v>0.0001785999999999999</v>
+        <v>0.00166505</v>
       </c>
       <c r="I78" t="n">
-        <v>0.00166505</v>
+        <v>0.00481058</v>
       </c>
       <c r="J78" t="n">
-        <v>0.00481058</v>
+        <v>0.00272902</v>
       </c>
       <c r="K78" t="n">
-        <v>0.00272902</v>
+        <v>9.011000000000007e-05</v>
       </c>
       <c r="L78" t="n">
-        <v>9.011000000000007e-05</v>
+        <v>0.0004795100000000002</v>
       </c>
       <c r="M78" t="n">
-        <v>0.0004795100000000002</v>
+        <v>0.00329986</v>
       </c>
     </row>
     <row r="79">
@@ -3672,37 +3672,37 @@
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="n">
-        <v>-0.00052145</v>
+        <v>-0.00052038</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.00052038</v>
+        <v>-0.00049876</v>
       </c>
       <c r="E79" t="n">
-        <v>-0.00049876</v>
+        <v>-0.00010349</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.00010349</v>
+        <v>0.00149008</v>
       </c>
       <c r="G79" t="n">
-        <v>0.00149008</v>
+        <v>0.00167124</v>
       </c>
       <c r="H79" t="n">
-        <v>0.00167124</v>
+        <v>0.00103193</v>
       </c>
       <c r="I79" t="n">
-        <v>0.00103193</v>
+        <v>0.00057835</v>
       </c>
       <c r="J79" t="n">
-        <v>0.00057835</v>
+        <v>9.465e-05</v>
       </c>
       <c r="K79" t="n">
-        <v>9.465e-05</v>
+        <v>0.00013897</v>
       </c>
       <c r="L79" t="n">
-        <v>0.00013897</v>
+        <v>6.415e-05</v>
       </c>
       <c r="M79" t="n">
-        <v>6.415e-05</v>
+        <v>-0.00029419</v>
       </c>
     </row>
     <row r="80">
@@ -3713,37 +3713,37 @@
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="n">
-        <v>5.127412570000001</v>
+        <v>0.3745234199999999</v>
       </c>
       <c r="D80" t="n">
-        <v>0.3745234199999999</v>
+        <v>-13.08952523</v>
       </c>
       <c r="E80" t="n">
-        <v>-13.08952523</v>
+        <v>-4.331212519999999</v>
       </c>
       <c r="F80" t="n">
-        <v>-4.331212519999999</v>
+        <v>-10.25827174</v>
       </c>
       <c r="G80" t="n">
-        <v>-10.25827174</v>
+        <v>8.421552140000001</v>
       </c>
       <c r="H80" t="n">
-        <v>8.421552140000001</v>
+        <v>-10.13260721</v>
       </c>
       <c r="I80" t="n">
-        <v>-10.13260721</v>
+        <v>-9.68964107</v>
       </c>
       <c r="J80" t="n">
-        <v>-9.68964107</v>
+        <v>4.868124629999999</v>
       </c>
       <c r="K80" t="n">
-        <v>4.868124629999999</v>
+        <v>12.18883922</v>
       </c>
       <c r="L80" t="n">
-        <v>12.18883922</v>
+        <v>-4.46799539</v>
       </c>
       <c r="M80" t="n">
-        <v>-4.46799539</v>
+        <v>12.58299348</v>
       </c>
     </row>
     <row r="81">
@@ -3754,37 +3754,37 @@
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>6.615816210000001</v>
+        <v>-59.96519444</v>
       </c>
       <c r="D81" t="n">
-        <v>-60.44946178</v>
+        <v>-91.76253054999999</v>
       </c>
       <c r="E81" t="n">
-        <v>-91.46511696</v>
+        <v>-106.78732313</v>
       </c>
       <c r="F81" t="n">
-        <v>-106.86700106</v>
+        <v>-61.14927203</v>
       </c>
       <c r="G81" t="n">
-        <v>-61.40586277000001</v>
+        <v>-43.25431434999999</v>
       </c>
       <c r="H81" t="n">
-        <v>-43.15341879</v>
+        <v>-61.35135943</v>
       </c>
       <c r="I81" t="n">
-        <v>-61.66911995</v>
+        <v>-43.05485222999999</v>
       </c>
       <c r="J81" t="n">
-        <v>-42.28803382</v>
+        <v>-16.93515817</v>
       </c>
       <c r="K81" t="n">
-        <v>-15.58922796</v>
+        <v>31.37983951</v>
       </c>
       <c r="L81" t="n">
-        <v>32.84825903000001</v>
+        <v>99.07407704000001</v>
       </c>
       <c r="M81" t="n">
-        <v>93.29633133</v>
+        <v>135.88498667</v>
       </c>
     </row>
     <row r="82">
@@ -3795,37 +3795,37 @@
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
-        <v>802.0624256400001</v>
+        <v>233.01628127</v>
       </c>
       <c r="D82" t="n">
-        <v>233.50054861</v>
+        <v>-6.20254675</v>
       </c>
       <c r="E82" t="n">
-        <v>-6.471851030000002</v>
+        <v>94.13397494</v>
       </c>
       <c r="F82" t="n">
-        <v>94.32777211</v>
+        <v>-53.87114807999998</v>
       </c>
       <c r="G82" t="n">
-        <v>-53.45805922999999</v>
+        <v>0.1883865500000045</v>
       </c>
       <c r="H82" t="n">
-        <v>0.2473854100000039</v>
+        <v>-170.38260885</v>
       </c>
       <c r="I82" t="n">
-        <v>-169.90165851</v>
+        <v>95.41136542</v>
       </c>
       <c r="J82" t="n">
-        <v>94.84075396999999</v>
+        <v>-152.1379888</v>
       </c>
       <c r="K82" t="n">
-        <v>-153.37305345</v>
+        <v>-342.33928774</v>
       </c>
       <c r="L82" t="n">
-        <v>-343.65384548</v>
+        <v>-545.95853994</v>
       </c>
       <c r="M82" t="n">
-        <v>-547.62890373</v>
+        <v>-280.96549088</v>
       </c>
     </row>
     <row r="83">
@@ -3836,37 +3836,37 @@
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>68.03330789</v>
+        <v>-19.23454711</v>
       </c>
       <c r="D83" t="n">
-        <v>-4.41017006</v>
+        <v>-23.25895899</v>
       </c>
       <c r="E83" t="n">
-        <v>-6.688197980000001</v>
+        <v>27.87323952</v>
       </c>
       <c r="F83" t="n">
-        <v>39.15618257</v>
+        <v>82.35941356999999</v>
       </c>
       <c r="G83" t="n">
-        <v>88.37693567999999</v>
+        <v>181.83515722</v>
       </c>
       <c r="H83" t="n">
-        <v>173.80208869</v>
+        <v>68.08952595000001</v>
       </c>
       <c r="I83" t="n">
-        <v>68.31111571000001</v>
+        <v>-20.36797773</v>
       </c>
       <c r="J83" t="n">
-        <v>-15.21283794</v>
+        <v>-20.03139617</v>
       </c>
       <c r="K83" t="n">
-        <v>-17.71552102</v>
+        <v>-59.64161756</v>
       </c>
       <c r="L83" t="n">
-        <v>-64.05499739</v>
+        <v>-112.75539681</v>
       </c>
       <c r="M83" t="n">
-        <v>-108.28490628</v>
+        <v>64.56145398</v>
       </c>
     </row>
     <row r="84">
@@ -3877,37 +3877,37 @@
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
-        <v>102.04973315</v>
+        <v>-116.03762182</v>
       </c>
       <c r="D84" t="n">
-        <v>-116.03766855</v>
+        <v>-143.58805289</v>
       </c>
       <c r="E84" t="n">
-        <v>-143.59839725</v>
+        <v>-122.466744</v>
       </c>
       <c r="F84" t="n">
-        <v>-122.34910587</v>
+        <v>-54.09112768000001</v>
       </c>
       <c r="G84" t="n">
-        <v>-54.08839686000001</v>
+        <v>-10.37811915</v>
       </c>
       <c r="H84" t="n">
-        <v>-10.32371517</v>
+        <v>20.72728843</v>
       </c>
       <c r="I84" t="n">
-        <v>20.68578092</v>
+        <v>50.52973096</v>
       </c>
       <c r="J84" t="n">
-        <v>50.43591372</v>
+        <v>20.65790564</v>
       </c>
       <c r="K84" t="n">
-        <v>20.67704156</v>
+        <v>39.26255287</v>
       </c>
       <c r="L84" t="n">
-        <v>39.12544062</v>
+        <v>82.85629460000001</v>
       </c>
       <c r="M84" t="n">
-        <v>82.69030088000001</v>
+        <v>154.58928851</v>
       </c>
     </row>
     <row r="85">
@@ -3918,37 +3918,37 @@
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>-1.10998745</v>
+        <v>-2.92089428</v>
       </c>
       <c r="D85" t="n">
-        <v>-17.7452246</v>
+        <v>-5.86579375</v>
       </c>
       <c r="E85" t="n">
-        <v>-22.43654935</v>
+        <v>4.65700348</v>
       </c>
       <c r="F85" t="n">
-        <v>-6.625887400000001</v>
+        <v>16.5811829</v>
       </c>
       <c r="G85" t="n">
-        <v>10.56383229</v>
+        <v>83.55010430999998</v>
       </c>
       <c r="H85" t="n">
-        <v>91.58342936</v>
+        <v>308.21784694</v>
       </c>
       <c r="I85" t="n">
-        <v>307.9963481</v>
+        <v>132.33488342</v>
       </c>
       <c r="J85" t="n">
-        <v>127.17968981</v>
+        <v>37.83571189</v>
       </c>
       <c r="K85" t="n">
-        <v>35.51974835</v>
+        <v>-48.80012199</v>
       </c>
       <c r="L85" t="n">
-        <v>-44.38686312000001</v>
+        <v>-75.86895855</v>
       </c>
       <c r="M85" t="n">
-        <v>-80.33943861</v>
+        <v>-29.96102533</v>
       </c>
     </row>
     <row r="86">
@@ -3959,37 +3959,37 @@
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
-        <v>81.89622543999999</v>
+        <v>38.98186654</v>
       </c>
       <c r="D86" t="n">
-        <v>36.94664319</v>
+        <v>40.09386715</v>
       </c>
       <c r="E86" t="n">
-        <v>39.92671712</v>
+        <v>-9.095698099999998</v>
       </c>
       <c r="F86" t="n">
-        <v>-7.647300829999998</v>
+        <v>37.72812831</v>
       </c>
       <c r="G86" t="n">
-        <v>40.5057899</v>
+        <v>-0.83850737</v>
       </c>
       <c r="H86" t="n">
-        <v>0.2115746600000012</v>
+        <v>-72.60341334</v>
       </c>
       <c r="I86" t="n">
-        <v>-73.51357708</v>
+        <v>-119.0016073</v>
       </c>
       <c r="J86" t="n">
-        <v>-120.38293081</v>
+        <v>-26.60613834</v>
       </c>
       <c r="K86" t="n">
-        <v>-28.81328676999999</v>
+        <v>29.60181823</v>
       </c>
       <c r="L86" t="n">
-        <v>26.42893274</v>
+        <v>-17.02849766</v>
       </c>
       <c r="M86" t="n">
-        <v>-19.94011926</v>
+        <v>-43.48588267</v>
       </c>
     </row>
     <row r="87">
@@ -3998,39 +3998,41 @@
           <t>電子通路業右下</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr"/>
+      <c r="B87" t="n">
+        <v>0</v>
+      </c>
       <c r="C87" t="n">
-        <v>-8.843038400000001</v>
+        <v>-26.54348754</v>
       </c>
       <c r="D87" t="n">
-        <v>-41.8310306</v>
+        <v>-11.71257476</v>
       </c>
       <c r="E87" t="n">
-        <v>-36.82459142</v>
+        <v>27.59073005</v>
       </c>
       <c r="F87" t="n">
-        <v>-13.84526226</v>
+        <v>78.17267982999999</v>
       </c>
       <c r="G87" t="n">
-        <v>9.219265179999997</v>
+        <v>25.51373005999999</v>
       </c>
       <c r="H87" t="n">
-        <v>-7.030059699999999</v>
+        <v>0.2366620999999996</v>
       </c>
       <c r="I87" t="n">
-        <v>-4.059091990000001</v>
+        <v>-61.34817928</v>
       </c>
       <c r="J87" t="n">
-        <v>-47.29568497</v>
+        <v>-142.1284039</v>
       </c>
       <c r="K87" t="n">
-        <v>-104.1367929</v>
+        <v>-170.64885988</v>
       </c>
       <c r="L87" t="n">
-        <v>-134.84861918</v>
+        <v>-163.99588027</v>
       </c>
       <c r="M87" t="n">
-        <v>-125.00312348</v>
+        <v>-129.46133087</v>
       </c>
     </row>
     <row r="88">
@@ -4041,37 +4043,37 @@
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
-        <v>26.49219782</v>
+        <v>-53.04379301000001</v>
       </c>
       <c r="D88" t="n">
-        <v>-37.75629203</v>
+        <v>-14.89313461</v>
       </c>
       <c r="E88" t="n">
-        <v>10.21864789</v>
+        <v>14.19245187</v>
       </c>
       <c r="F88" t="n">
-        <v>55.6293562</v>
+        <v>55.83540987999999</v>
       </c>
       <c r="G88" t="n">
-        <v>124.78835097</v>
+        <v>97.78185421000001</v>
       </c>
       <c r="H88" t="n">
-        <v>130.32502002</v>
+        <v>61.34033204</v>
       </c>
       <c r="I88" t="n">
-        <v>65.63657513</v>
+        <v>-5.116433789999999</v>
       </c>
       <c r="J88" t="n">
-        <v>-19.16895581</v>
+        <v>-33.83837391</v>
       </c>
       <c r="K88" t="n">
-        <v>-71.83025827</v>
+        <v>-8.624214240000002</v>
       </c>
       <c r="L88" t="n">
-        <v>-44.42444898</v>
+        <v>-24.72450772</v>
       </c>
       <c r="M88" t="n">
-        <v>-63.71747357000001</v>
+        <v>-40.11228814</v>
       </c>
     </row>
     <row r="89">
@@ -4082,37 +4084,37 @@
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>675.7218513099999</v>
+        <v>2038.44906293</v>
       </c>
       <c r="D89" t="n">
-        <v>1938.81589722</v>
+        <v>2785.71638693</v>
       </c>
       <c r="E89" t="n">
-        <v>2721.40570911</v>
+        <v>256.3811546599999</v>
       </c>
       <c r="F89" t="n">
-        <v>233.9174681800001</v>
+        <v>2728.14862403</v>
       </c>
       <c r="G89" t="n">
-        <v>3032.472158439999</v>
+        <v>891.30276728</v>
       </c>
       <c r="H89" t="n">
-        <v>1243.25631578</v>
+        <v>578.0957584399999</v>
       </c>
       <c r="I89" t="n">
-        <v>826.02914661</v>
+        <v>3081.26991417</v>
       </c>
       <c r="J89" t="n">
-        <v>3432.44482566</v>
+        <v>4608.10840054</v>
       </c>
       <c r="K89" t="n">
-        <v>5007.490816279999</v>
+        <v>4483.77360107</v>
       </c>
       <c r="L89" t="n">
-        <v>5005.6008972</v>
+        <v>4805.35057671</v>
       </c>
       <c r="M89" t="n">
-        <v>5017.250771810001</v>
+        <v>4850.32089056</v>
       </c>
     </row>
     <row r="90">
@@ -4121,39 +4123,41 @@
           <t>電子零組件業右下</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr"/>
+      <c r="B90" t="n">
+        <v>0</v>
+      </c>
       <c r="C90" t="n">
-        <v>1082.63682107</v>
+        <v>63.05614875</v>
       </c>
       <c r="D90" t="n">
-        <v>61.51201302</v>
+        <v>132.60557728</v>
       </c>
       <c r="E90" t="n">
-        <v>135.01031749</v>
+        <v>-316.23102769</v>
       </c>
       <c r="F90" t="n">
-        <v>-319.59804829</v>
+        <v>-262.6704543</v>
       </c>
       <c r="G90" t="n">
-        <v>-260.44057116</v>
+        <v>-588.15370719</v>
       </c>
       <c r="H90" t="n">
-        <v>-587.90753496</v>
+        <v>-470.1614567600001</v>
       </c>
       <c r="I90" t="n">
-        <v>-475.41634619</v>
+        <v>-391.8065920600001</v>
       </c>
       <c r="J90" t="n">
-        <v>-368.05320958</v>
+        <v>-8.160727069999995</v>
       </c>
       <c r="K90" t="n">
-        <v>-14.35892189</v>
+        <v>-372.95276079</v>
       </c>
       <c r="L90" t="n">
-        <v>-363.26591111</v>
+        <v>-770.85714174</v>
       </c>
       <c r="M90" t="n">
-        <v>-791.49813785</v>
+        <v>-997.24055418</v>
       </c>
     </row>
     <row r="91">
@@ -4164,37 +4168,37 @@
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>-212.84212553</v>
+        <v>-598.01506698</v>
       </c>
       <c r="D91" t="n">
-        <v>-500.58380029</v>
+        <v>-463.1810605500001</v>
       </c>
       <c r="E91" t="n">
-        <v>-407.9659284700001</v>
+        <v>-367.85249305</v>
       </c>
       <c r="F91" t="n">
-        <v>-380.1795164600001</v>
+        <v>89.34465401999999</v>
       </c>
       <c r="G91" t="n">
-        <v>54.60264371999999</v>
+        <v>-502.57170582</v>
       </c>
       <c r="H91" t="n">
-        <v>-547.96460986</v>
+        <v>-511.83975142</v>
       </c>
       <c r="I91" t="n">
-        <v>-532.2037275800001</v>
+        <v>-525.44626108</v>
       </c>
       <c r="J91" t="n">
-        <v>-511.2457994</v>
+        <v>-295.0103615800001</v>
       </c>
       <c r="K91" t="n">
-        <v>-279.5068743900001</v>
+        <v>-595.9723830899999</v>
       </c>
       <c r="L91" t="n">
-        <v>-672.4342682499999</v>
+        <v>-822.08477513</v>
       </c>
       <c r="M91" t="n">
-        <v>-865.22479599</v>
+        <v>-1012.76483221</v>
       </c>
     </row>
     <row r="92">
@@ -4205,37 +4209,37 @@
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>-128.97794832</v>
+        <v>205.8542734999999</v>
       </c>
       <c r="D92" t="n">
-        <v>185.30484018</v>
+        <v>327.38565675</v>
       </c>
       <c r="E92" t="n">
-        <v>303.0147502099999</v>
+        <v>-1143.72705722</v>
       </c>
       <c r="F92" t="n">
-        <v>-1127.25673355</v>
+        <v>-1241.52012397</v>
       </c>
       <c r="G92" t="n">
-        <v>-1206.15649694</v>
+        <v>-435.94781424</v>
       </c>
       <c r="H92" t="n">
-        <v>-387.8385127399999</v>
+        <v>802.00610026</v>
       </c>
       <c r="I92" t="n">
-        <v>815.78342775</v>
+        <v>-162.91159181</v>
       </c>
       <c r="J92" t="n">
-        <v>-141.77400986</v>
+        <v>58.85484111999997</v>
       </c>
       <c r="K92" t="n">
-        <v>56.85748323999998</v>
+        <v>-1144.83488959</v>
       </c>
       <c r="L92" t="n">
-        <v>-1144.31158492</v>
+        <v>-20.02801225999992</v>
       </c>
       <c r="M92" t="n">
-        <v>-36.69571987999992</v>
+        <v>-124.56689696</v>
       </c>
     </row>
     <row r="93">
@@ -4244,39 +4248,41 @@
           <t>電機機械右下</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr"/>
+      <c r="B93" t="n">
+        <v>0</v>
+      </c>
       <c r="C93" t="n">
-        <v>59.78359257</v>
+        <v>-41.80469665</v>
       </c>
       <c r="D93" t="n">
-        <v>-48.40637532</v>
+        <v>-54.58697853000002</v>
       </c>
       <c r="E93" t="n">
-        <v>-27.57171820000002</v>
+        <v>-153.18902274</v>
       </c>
       <c r="F93" t="n">
-        <v>-25.67948576</v>
+        <v>0.4190695899999994</v>
       </c>
       <c r="G93" t="n">
-        <v>43.66869122</v>
+        <v>-106.67094956</v>
       </c>
       <c r="H93" t="n">
-        <v>-81.55400834000001</v>
+        <v>7.079586339999998</v>
       </c>
       <c r="I93" t="n">
-        <v>60.49007137</v>
+        <v>98.30620274</v>
       </c>
       <c r="J93" t="n">
-        <v>121.80988964</v>
+        <v>68.03748563000001</v>
       </c>
       <c r="K93" t="n">
-        <v>71.00693721</v>
+        <v>-16.9830704</v>
       </c>
       <c r="L93" t="n">
-        <v>113.34036996</v>
+        <v>-136.75676583</v>
       </c>
       <c r="M93" t="n">
-        <v>40.45147514999999</v>
+        <v>-78.07750962</v>
       </c>
     </row>
     <row r="94">
@@ -4287,37 +4293,37 @@
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>12.73378405</v>
+        <v>-42.78836988</v>
       </c>
       <c r="D94" t="n">
-        <v>-15.63688381</v>
+        <v>40.97733781</v>
       </c>
       <c r="E94" t="n">
-        <v>38.33344365</v>
+        <v>190.98204855</v>
       </c>
       <c r="F94" t="n">
-        <v>47.00269811</v>
+        <v>128.19425933</v>
       </c>
       <c r="G94" t="n">
-        <v>49.58149492</v>
+        <v>174.24608435</v>
       </c>
       <c r="H94" t="n">
-        <v>101.02052811</v>
+        <v>202.88977693</v>
       </c>
       <c r="I94" t="n">
-        <v>135.70280701</v>
+        <v>110.25258585</v>
       </c>
       <c r="J94" t="n">
-        <v>65.6116761</v>
+        <v>-29.17319449</v>
       </c>
       <c r="K94" t="n">
-        <v>-30.14520415</v>
+        <v>74.23763863000001</v>
       </c>
       <c r="L94" t="n">
-        <v>-56.61067838</v>
+        <v>88.81858175000001</v>
       </c>
       <c r="M94" t="n">
-        <v>-71.72352194999999</v>
+        <v>158.29159538</v>
       </c>
     </row>
     <row r="95">
@@ -4328,37 +4334,37 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>981.0393276199999</v>
+        <v>3069.92118107</v>
       </c>
       <c r="D95" t="n">
-        <v>3039.78159024</v>
+        <v>2772.51594402</v>
       </c>
       <c r="E95" t="n">
-        <v>2679.40341063</v>
+        <v>522.01829603</v>
       </c>
       <c r="F95" t="n">
-        <v>398.16777622</v>
+        <v>4092.9784752</v>
       </c>
       <c r="G95" t="n">
-        <v>4014.56995358</v>
+        <v>1839.50387616</v>
       </c>
       <c r="H95" t="n">
-        <v>1780.27417029</v>
+        <v>2663.72581026</v>
       </c>
       <c r="I95" t="n">
-        <v>2571.2515713</v>
+        <v>3439.29967521</v>
       </c>
       <c r="J95" t="n">
-        <v>3369.1646542</v>
+        <v>2967.03286289</v>
       </c>
       <c r="K95" t="n">
-        <v>2900.04081789</v>
+        <v>494.5037238999999</v>
       </c>
       <c r="L95" t="n">
-        <v>391.9865974</v>
+        <v>-3248.73856866</v>
       </c>
       <c r="M95" t="n">
-        <v>-3414.60216891</v>
+        <v>-3663.00266384</v>
       </c>
     </row>
     <row r="96">
@@ -4371,37 +4377,37 @@
         <v>0</v>
       </c>
       <c r="C96" t="n">
-        <v>13.07843566</v>
+        <v>-80.75298205000001</v>
       </c>
       <c r="D96" t="n">
-        <v>-82.78174076000001</v>
+        <v>-35.26515296</v>
       </c>
       <c r="E96" t="n">
-        <v>-38.17457037</v>
+        <v>34.77748791999999</v>
       </c>
       <c r="F96" t="n">
-        <v>30.58266309999999</v>
+        <v>293.59366812</v>
       </c>
       <c r="G96" t="n">
-        <v>289.99602877</v>
+        <v>29.92595504</v>
       </c>
       <c r="H96" t="n">
-        <v>26.90707316</v>
+        <v>-25.21789619</v>
       </c>
       <c r="I96" t="n">
-        <v>-22.35415357</v>
+        <v>-321.77418277</v>
       </c>
       <c r="J96" t="n">
-        <v>-320.91429934</v>
+        <v>-540.40644423</v>
       </c>
       <c r="K96" t="n">
-        <v>-537.5567834</v>
+        <v>-566.6008404099999</v>
       </c>
       <c r="L96" t="n">
-        <v>-567.91663938</v>
+        <v>-627.43372863</v>
       </c>
       <c r="M96" t="n">
-        <v>-621.6234280599999</v>
+        <v>-611.38368559</v>
       </c>
     </row>
     <row r="97">
@@ -4412,37 +4418,37 @@
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>-211.66196497</v>
+        <v>-0.04517477999999512</v>
       </c>
       <c r="D97" t="n">
-        <v>-2.047810939999996</v>
+        <v>31.65996122</v>
       </c>
       <c r="E97" t="n">
-        <v>40.63617187</v>
+        <v>-64.52826116</v>
       </c>
       <c r="F97" t="n">
-        <v>-60.09170362</v>
+        <v>107.23571659</v>
       </c>
       <c r="G97" t="n">
-        <v>101.62346198</v>
+        <v>1.012414459999993</v>
       </c>
       <c r="H97" t="n">
-        <v>-49.76638192</v>
+        <v>107.27069085</v>
       </c>
       <c r="I97" t="n">
-        <v>103.88289413</v>
+        <v>40.39906092</v>
       </c>
       <c r="J97" t="n">
-        <v>49.88564175999999</v>
+        <v>103.86640705</v>
       </c>
       <c r="K97" t="n">
-        <v>120.5395721</v>
+        <v>-106.11815169</v>
       </c>
       <c r="L97" t="n">
-        <v>-87.70383674</v>
+        <v>-31.75523302000001</v>
       </c>
       <c r="M97" t="n">
-        <v>-14.75605133000001</v>
+        <v>-203.67266775</v>
       </c>
     </row>
     <row r="98">
@@ -4453,37 +4459,37 @@
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
-        <v>-23.61119333</v>
+        <v>-20.82516393</v>
       </c>
       <c r="D98" t="n">
-        <v>-20.82516393</v>
+        <v>-15.11263473</v>
       </c>
       <c r="E98" t="n">
-        <v>-15.11263473</v>
+        <v>2.57676404</v>
       </c>
       <c r="F98" t="n">
-        <v>2.57676404</v>
+        <v>17.61770092</v>
       </c>
       <c r="G98" t="n">
-        <v>17.61770092</v>
+        <v>27.36522565</v>
       </c>
       <c r="H98" t="n">
-        <v>27.36522565</v>
+        <v>21.462162</v>
       </c>
       <c r="I98" t="n">
-        <v>21.462162</v>
+        <v>2.43355516</v>
       </c>
       <c r="J98" t="n">
-        <v>2.43355516</v>
+        <v>3.428873750000001</v>
       </c>
       <c r="K98" t="n">
-        <v>3.428873750000001</v>
+        <v>20.06785335</v>
       </c>
       <c r="L98" t="n">
-        <v>20.06785335</v>
+        <v>29.26245925</v>
       </c>
       <c r="M98" t="n">
-        <v>29.26245925</v>
+        <v>17.23702606</v>
       </c>
     </row>
     <row r="99">
@@ -4494,37 +4500,37 @@
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>2.86518501</v>
+        <v>0.8721114700000003</v>
       </c>
       <c r="D99" t="n">
-        <v>0.8719472000000004</v>
+        <v>-4.212167819999999</v>
       </c>
       <c r="E99" t="n">
-        <v>-4.212290649999999</v>
+        <v>9.207686730000001</v>
       </c>
       <c r="F99" t="n">
-        <v>9.207508240000001</v>
+        <v>12.72329238</v>
       </c>
       <c r="G99" t="n">
-        <v>12.72317876</v>
+        <v>17.20173201</v>
       </c>
       <c r="H99" t="n">
-        <v>17.20167136</v>
+        <v>5.82131096</v>
       </c>
       <c r="I99" t="n">
-        <v>5.82127413</v>
+        <v>-1.51795931</v>
       </c>
       <c r="J99" t="n">
-        <v>-1.51808174</v>
+        <v>-12.99625281</v>
       </c>
       <c r="K99" t="n">
-        <v>-12.99658263</v>
+        <v>-16.9396746</v>
       </c>
       <c r="L99" t="n">
-        <v>-16.94004654</v>
+        <v>-11.9078638</v>
       </c>
       <c r="M99" t="n">
-        <v>-11.90809048</v>
+        <v>3.03977697</v>
       </c>
     </row>
     <row r="100">
@@ -4535,37 +4541,37 @@
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="n">
-        <v>-161.64074142</v>
+        <v>-233.61837582</v>
       </c>
       <c r="D100" t="n">
-        <v>-233.61821155</v>
+        <v>-115.42952001</v>
       </c>
       <c r="E100" t="n">
-        <v>-115.42939718</v>
+        <v>-27.29277471</v>
       </c>
       <c r="F100" t="n">
-        <v>-27.29259622</v>
+        <v>-51.18376402999999</v>
       </c>
       <c r="G100" t="n">
-        <v>-51.18365041</v>
+        <v>-94.26099633999999</v>
       </c>
       <c r="H100" t="n">
-        <v>-94.26093568999998</v>
+        <v>-157.11089562</v>
       </c>
       <c r="I100" t="n">
-        <v>-157.11085879</v>
+        <v>-218.501818</v>
       </c>
       <c r="J100" t="n">
-        <v>-218.50169557</v>
+        <v>-239.00675076</v>
       </c>
       <c r="K100" t="n">
-        <v>-239.00642094</v>
+        <v>-229.12973427</v>
       </c>
       <c r="L100" t="n">
-        <v>-229.12936233</v>
+        <v>-222.2966904</v>
       </c>
       <c r="M100" t="n">
-        <v>-222.29646372</v>
+        <v>-71.92945067999999</v>
       </c>
     </row>
   </sheetData>

--- a/Result/analyze_2.xlsx
+++ b/Result/analyze_2.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
     </row>
@@ -503,37 +503,37 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>602.6976485</v>
+        <v>674.6886631900001</v>
       </c>
       <c r="D2" t="n">
-        <v>669.4584688799999</v>
+        <v>970.0299840299999</v>
       </c>
       <c r="E2" t="n">
-        <v>969.6423881799999</v>
+        <v>1847.1532232</v>
       </c>
       <c r="F2" t="n">
-        <v>1849.48860399</v>
+        <v>1090.12168094</v>
       </c>
       <c r="G2" t="n">
-        <v>1085.48359226</v>
+        <v>152.27548183</v>
       </c>
       <c r="H2" t="n">
-        <v>157.01022691</v>
+        <v>727.4173344400001</v>
       </c>
       <c r="I2" t="n">
-        <v>735.71064775</v>
+        <v>787.38392211</v>
       </c>
       <c r="J2" t="n">
-        <v>790.5330572400001</v>
+        <v>709.79197376</v>
       </c>
       <c r="K2" t="n">
-        <v>687.6225635699999</v>
+        <v>1783.67454239</v>
       </c>
       <c r="L2" t="n">
-        <v>1777.99963127</v>
+        <v>-145.73187574</v>
       </c>
       <c r="M2" t="n">
-        <v>-168.4125216</v>
+        <v>100.81442348</v>
       </c>
     </row>
     <row r="3">
@@ -542,41 +542,39 @@
           <t>光電業右下</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>0.2643849900000007</v>
+        <v>-57.7376243</v>
       </c>
       <c r="D3" t="n">
-        <v>-20.16331824</v>
+        <v>42.798068</v>
       </c>
       <c r="E3" t="n">
-        <v>108.99614624</v>
+        <v>177.52829294</v>
       </c>
       <c r="F3" t="n">
-        <v>218.62774389</v>
+        <v>135.66154168</v>
       </c>
       <c r="G3" t="n">
-        <v>151.67850938</v>
+        <v>45.71565789</v>
       </c>
       <c r="H3" t="n">
-        <v>50.43801889</v>
+        <v>-63.2461811</v>
       </c>
       <c r="I3" t="n">
-        <v>-71.88062519</v>
+        <v>36.92485858999999</v>
       </c>
       <c r="J3" t="n">
-        <v>18.3918283</v>
+        <v>130.83599664</v>
       </c>
       <c r="K3" t="n">
-        <v>118.11633031</v>
+        <v>121.91977397</v>
       </c>
       <c r="L3" t="n">
-        <v>114.91389364</v>
+        <v>99.40697876</v>
       </c>
       <c r="M3" t="n">
-        <v>99.37302536</v>
+        <v>165.42042423</v>
       </c>
     </row>
     <row r="4">
@@ -587,37 +585,37 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>-158.07171923</v>
+        <v>-160.86073348</v>
       </c>
       <c r="D4" t="n">
-        <v>-198.42502927</v>
+        <v>20.9653879</v>
       </c>
       <c r="E4" t="n">
-        <v>-45.27663139</v>
+        <v>146.75340789</v>
       </c>
       <c r="F4" t="n">
-        <v>105.57078515</v>
+        <v>52.27611163</v>
       </c>
       <c r="G4" t="n">
-        <v>36.23594113</v>
+        <v>223.87646559</v>
       </c>
       <c r="H4" t="n">
-        <v>219.17184839</v>
+        <v>-58.27769687999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-49.55764159</v>
+        <v>9.940544380000002</v>
       </c>
       <c r="J4" t="n">
-        <v>28.5783324</v>
+        <v>-13.99987109000001</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.138802360000014</v>
+        <v>-55.87436203999999</v>
       </c>
       <c r="L4" t="n">
-        <v>-48.71127217</v>
+        <v>-152.91789665</v>
       </c>
       <c r="M4" t="n">
-        <v>-152.7341734</v>
+        <v>-145.96836652</v>
       </c>
     </row>
     <row r="5">
@@ -628,37 +626,37 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1402.66047048</v>
+        <v>945.3156049899999</v>
       </c>
       <c r="D5" t="n">
-        <v>946.8620050899999</v>
+        <v>633.39701284</v>
       </c>
       <c r="E5" t="n">
-        <v>633.97876007</v>
+        <v>145.83107331</v>
       </c>
       <c r="F5" t="n">
-        <v>145.98154998</v>
+        <v>-39.15896537</v>
       </c>
       <c r="G5" t="n">
-        <v>-38.91567496</v>
+        <v>-259.43326067</v>
       </c>
       <c r="H5" t="n">
-        <v>-259.11423339</v>
+        <v>-387.39297887</v>
       </c>
       <c r="I5" t="n">
-        <v>-387.0616234</v>
+        <v>-428.42212264</v>
       </c>
       <c r="J5" t="n">
-        <v>-427.89242988</v>
+        <v>-414.2600325699999</v>
       </c>
       <c r="K5" t="n">
-        <v>-414.13751969</v>
+        <v>-487.77716299</v>
       </c>
       <c r="L5" t="n">
-        <v>-488.4837365</v>
+        <v>-411.36808591</v>
       </c>
       <c r="M5" t="n">
-        <v>-411.74193648</v>
+        <v>-388.16366113</v>
       </c>
     </row>
     <row r="6">
@@ -667,41 +665,39 @@
           <t>其他右下</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>-141.3043893</v>
+        <v>-66.02961714</v>
       </c>
       <c r="D6" t="n">
-        <v>-65.84285428999999</v>
+        <v>59.97732865</v>
       </c>
       <c r="E6" t="n">
-        <v>61.18649945</v>
+        <v>11.23121783</v>
       </c>
       <c r="F6" t="n">
-        <v>11.53724968</v>
+        <v>17.82405653</v>
       </c>
       <c r="G6" t="n">
-        <v>17.98194362</v>
+        <v>63.14145063</v>
       </c>
       <c r="H6" t="n">
-        <v>62.90351154</v>
+        <v>81.07120747999998</v>
       </c>
       <c r="I6" t="n">
-        <v>80.61587611</v>
+        <v>80.90020034</v>
       </c>
       <c r="J6" t="n">
-        <v>81.29088198000001</v>
+        <v>71.14833212000001</v>
       </c>
       <c r="K6" t="n">
-        <v>70.96316671</v>
+        <v>154.44832648</v>
       </c>
       <c r="L6" t="n">
-        <v>155.55564606</v>
+        <v>190.30644914</v>
       </c>
       <c r="M6" t="n">
-        <v>192.27816816</v>
+        <v>31.97720224999999</v>
       </c>
     </row>
     <row r="7">
@@ -712,37 +708,37 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>8.593587789999999</v>
+        <v>10.66471378</v>
       </c>
       <c r="D7" t="n">
-        <v>8.931548919999999</v>
+        <v>13.09498813</v>
       </c>
       <c r="E7" t="n">
-        <v>11.30406819</v>
+        <v>12.54927081</v>
       </c>
       <c r="F7" t="n">
-        <v>12.0927555</v>
+        <v>20.47784514</v>
       </c>
       <c r="G7" t="n">
-        <v>20.07663934</v>
+        <v>0.595156759999998</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5140568199999984</v>
+        <v>-11.75154208</v>
       </c>
       <c r="I7" t="n">
-        <v>-11.62759703</v>
+        <v>-41.34721771</v>
       </c>
       <c r="J7" t="n">
-        <v>-42.26777828</v>
+        <v>-35.38490754</v>
       </c>
       <c r="K7" t="n">
-        <v>-35.32248623</v>
+        <v>-30.44482707</v>
       </c>
       <c r="L7" t="n">
-        <v>-30.84577259</v>
+        <v>-38.93767733999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-40.53569926</v>
+        <v>-19.33931298</v>
       </c>
     </row>
     <row r="8">
@@ -753,37 +749,37 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>1462.80068978</v>
+        <v>2288.2928933</v>
       </c>
       <c r="D8" t="n">
-        <v>2288.29119089</v>
+        <v>1082.17697646</v>
       </c>
       <c r="E8" t="n">
-        <v>1082.1776767</v>
+        <v>1217.20015451</v>
       </c>
       <c r="F8" t="n">
-        <v>1217.19830357</v>
+        <v>1224.98766666</v>
       </c>
       <c r="G8" t="n">
-        <v>1224.9719705</v>
+        <v>3053.41093554</v>
       </c>
       <c r="H8" t="n">
-        <v>3053.42235397</v>
+        <v>3202.5230305</v>
       </c>
       <c r="I8" t="n">
-        <v>3202.53595737</v>
+        <v>3796.87587415</v>
       </c>
       <c r="J8" t="n">
-        <v>3796.8887242</v>
+        <v>879.33300735</v>
       </c>
       <c r="K8" t="n">
-        <v>879.34427735</v>
+        <v>2616.38882237</v>
       </c>
       <c r="L8" t="n">
-        <v>2616.39879541</v>
+        <v>2457.47498701</v>
       </c>
       <c r="M8" t="n">
-        <v>2457.47873682</v>
+        <v>3001.08271769</v>
       </c>
     </row>
     <row r="9">
@@ -794,37 +790,37 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>-16.93995363</v>
+        <v>39.37436597</v>
       </c>
       <c r="D9" t="n">
-        <v>39.37451661</v>
+        <v>36.78591928</v>
       </c>
       <c r="E9" t="n">
-        <v>36.7863755</v>
+        <v>40.08006312000001</v>
       </c>
       <c r="F9" t="n">
-        <v>40.08065389</v>
+        <v>-1.64257977</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.64293746</v>
+        <v>12.49002131</v>
       </c>
       <c r="H9" t="n">
-        <v>12.49312112</v>
+        <v>-56.5152249</v>
       </c>
       <c r="I9" t="n">
-        <v>-56.51112387000001</v>
+        <v>-83.09911693000001</v>
       </c>
       <c r="J9" t="n">
-        <v>-83.09151716000001</v>
+        <v>-91.21725834</v>
       </c>
       <c r="K9" t="n">
-        <v>-91.21407168</v>
+        <v>-123.56119124</v>
       </c>
       <c r="L9" t="n">
-        <v>-123.56075957</v>
+        <v>-130.50494652</v>
       </c>
       <c r="M9" t="n">
-        <v>-130.50237339</v>
+        <v>-119.4984721</v>
       </c>
     </row>
     <row r="10">
@@ -835,37 +831,37 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>-39.404709</v>
+        <v>-4.425793330000002</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.424241560000001</v>
+        <v>33.02442404</v>
       </c>
       <c r="E10" t="n">
-        <v>33.02326758</v>
+        <v>92.64678287999999</v>
       </c>
       <c r="F10" t="n">
-        <v>92.64804305</v>
+        <v>17.15824161</v>
       </c>
       <c r="G10" t="n">
-        <v>17.17429546</v>
+        <v>45.1034885</v>
       </c>
       <c r="H10" t="n">
-        <v>45.08897026</v>
+        <v>-8.899032229999998</v>
       </c>
       <c r="I10" t="n">
-        <v>-8.916060129999998</v>
+        <v>-111.02076683</v>
       </c>
       <c r="J10" t="n">
-        <v>-111.04121665</v>
+        <v>-101.75172866</v>
       </c>
       <c r="K10" t="n">
-        <v>-101.76618532</v>
+        <v>-139.31868833</v>
       </c>
       <c r="L10" t="n">
-        <v>-139.32909304</v>
+        <v>-100.04058103</v>
       </c>
       <c r="M10" t="n">
-        <v>-100.04690397</v>
+        <v>-54.97436146999999</v>
       </c>
     </row>
     <row r="11">
@@ -876,37 +872,37 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>142.10709826</v>
+        <v>59.06884079</v>
       </c>
       <c r="D11" t="n">
-        <v>57.88838204</v>
+        <v>58.25104046</v>
       </c>
       <c r="E11" t="n">
-        <v>58.40439622000001</v>
+        <v>-1.600569230000001</v>
       </c>
       <c r="F11" t="n">
-        <v>5.304335569999999</v>
+        <v>-56.15323858999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-57.6147605</v>
+        <v>-77.84758144</v>
       </c>
       <c r="H11" t="n">
-        <v>-84.49988563000001</v>
+        <v>-69.03680920000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-71.27958376000001</v>
+        <v>-25.6903414</v>
       </c>
       <c r="J11" t="n">
-        <v>-9.778352530000008</v>
+        <v>29.68746072</v>
       </c>
       <c r="K11" t="n">
-        <v>31.64014183</v>
+        <v>-208.16999437</v>
       </c>
       <c r="L11" t="n">
-        <v>-181.89200288</v>
+        <v>-206.94991158</v>
       </c>
       <c r="M11" t="n">
-        <v>-28.50705036000002</v>
+        <v>-108.51393825</v>
       </c>
     </row>
     <row r="12">
@@ -915,39 +911,41 @@
           <t>化學工業右下</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
       <c r="C12" t="n">
-        <v>-3.215999110000002</v>
+        <v>-78.93212152</v>
       </c>
       <c r="D12" t="n">
-        <v>-78.93212152</v>
+        <v>-41.43989729</v>
       </c>
       <c r="E12" t="n">
-        <v>-41.43989729</v>
+        <v>-102.01485622</v>
       </c>
       <c r="F12" t="n">
-        <v>-102.01485622</v>
+        <v>-106.13760151</v>
       </c>
       <c r="G12" t="n">
-        <v>-106.13760151</v>
+        <v>-22.3740144</v>
       </c>
       <c r="H12" t="n">
-        <v>-22.3740144</v>
+        <v>360.00356585</v>
       </c>
       <c r="I12" t="n">
-        <v>360.00356585</v>
+        <v>239.47928084</v>
       </c>
       <c r="J12" t="n">
-        <v>239.47928084</v>
+        <v>172.96076883</v>
       </c>
       <c r="K12" t="n">
-        <v>172.96076883</v>
+        <v>-44.249782</v>
       </c>
       <c r="L12" t="n">
-        <v>-44.249782</v>
+        <v>-22.19598527</v>
       </c>
       <c r="M12" t="n">
-        <v>-22.19598527</v>
+        <v>2.736445330000004</v>
       </c>
     </row>
     <row r="13">
@@ -958,37 +956,37 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>-1.46681079</v>
+        <v>2.45781016</v>
       </c>
       <c r="D13" t="n">
-        <v>2.45781016</v>
+        <v>0.7869540599999999</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7869540599999999</v>
+        <v>-18.7276696</v>
       </c>
       <c r="F13" t="n">
-        <v>-18.7276696</v>
+        <v>-2.22506845</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.22506845</v>
+        <v>2.87521121</v>
       </c>
       <c r="H13" t="n">
-        <v>2.87521121</v>
+        <v>-7.662935969999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-7.662935969999999</v>
+        <v>-4.07760919</v>
       </c>
       <c r="J13" t="n">
-        <v>-4.07760919</v>
+        <v>21.36502881</v>
       </c>
       <c r="K13" t="n">
-        <v>21.36502881</v>
+        <v>44.08762252</v>
       </c>
       <c r="L13" t="n">
-        <v>44.08762252</v>
+        <v>22.01935964</v>
       </c>
       <c r="M13" t="n">
-        <v>22.01935964</v>
+        <v>21.7085099</v>
       </c>
     </row>
     <row r="14">
@@ -999,37 +997,37 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>-558.0274960500003</v>
+        <v>-4030.99020094</v>
       </c>
       <c r="D14" t="n">
-        <v>-4031.0308901</v>
+        <v>-5868.97951287</v>
       </c>
       <c r="E14" t="n">
-        <v>-5869.02274616</v>
+        <v>-1133.26658091</v>
       </c>
       <c r="F14" t="n">
-        <v>-1133.26056514</v>
+        <v>-3705.140555330001</v>
       </c>
       <c r="G14" t="n">
-        <v>-3705.16582924</v>
+        <v>5235.51142395</v>
       </c>
       <c r="H14" t="n">
-        <v>5239.739088179999</v>
+        <v>1804.83180749</v>
       </c>
       <c r="I14" t="n">
-        <v>1818.91268169</v>
+        <v>7248.74316912</v>
       </c>
       <c r="J14" t="n">
-        <v>7262.88889412</v>
+        <v>3995.88190836</v>
       </c>
       <c r="K14" t="n">
-        <v>4023.58498686</v>
+        <v>7523.27648651</v>
       </c>
       <c r="L14" t="n">
-        <v>7564.39810059</v>
+        <v>3953.31127801</v>
       </c>
       <c r="M14" t="n">
-        <v>3973.15930394</v>
+        <v>4481.908409510001</v>
       </c>
     </row>
     <row r="15">
@@ -1038,41 +1036,39 @@
           <t>半導體業右下</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>-441.8664886</v>
+        <v>282.2401762700001</v>
       </c>
       <c r="D15" t="n">
-        <v>280.46767513</v>
+        <v>225.80410349</v>
       </c>
       <c r="E15" t="n">
-        <v>187.83748074</v>
+        <v>610.72651117</v>
       </c>
       <c r="F15" t="n">
-        <v>557.79165071</v>
+        <v>-94.81707577000003</v>
       </c>
       <c r="G15" t="n">
-        <v>-142.65581879</v>
+        <v>-417.5162018699999</v>
       </c>
       <c r="H15" t="n">
-        <v>-434.42812575</v>
+        <v>317.77029651</v>
       </c>
       <c r="I15" t="n">
-        <v>313.4371352400001</v>
+        <v>27.96913816999998</v>
       </c>
       <c r="J15" t="n">
-        <v>19.93314023999998</v>
+        <v>979.1443715299999</v>
       </c>
       <c r="K15" t="n">
-        <v>988.7134929800001</v>
+        <v>577.74898408</v>
       </c>
       <c r="L15" t="n">
-        <v>610.43790317</v>
+        <v>839.39304378</v>
       </c>
       <c r="M15" t="n">
-        <v>920.21499783</v>
+        <v>892.64955362</v>
       </c>
     </row>
     <row r="16">
@@ -1083,37 +1079,37 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>-425.31854186</v>
+        <v>-672.08428641</v>
       </c>
       <c r="D16" t="n">
-        <v>-670.2735597</v>
+        <v>-1194.19273833</v>
       </c>
       <c r="E16" t="n">
-        <v>-1156.18405488</v>
+        <v>-676.33293596</v>
       </c>
       <c r="F16" t="n">
-        <v>-623.4059272899999</v>
+        <v>-1143.95210694</v>
       </c>
       <c r="G16" t="n">
-        <v>-1096.09065954</v>
+        <v>-162.92503767</v>
       </c>
       <c r="H16" t="n">
-        <v>-150.24100706</v>
+        <v>-459.66738414</v>
       </c>
       <c r="I16" t="n">
-        <v>-469.41605542</v>
+        <v>-452.57734768</v>
       </c>
       <c r="J16" t="n">
-        <v>-458.6890040100001</v>
+        <v>-678.4962069400001</v>
       </c>
       <c r="K16" t="n">
-        <v>-715.76837278</v>
+        <v>-301.5696719300001</v>
       </c>
       <c r="L16" t="n">
-        <v>-375.38672873</v>
+        <v>-14.27670384000002</v>
       </c>
       <c r="M16" t="n">
-        <v>-114.94700233</v>
+        <v>-578.11620666</v>
       </c>
     </row>
     <row r="17">
@@ -1124,37 +1120,37 @@
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
-        <v>1.35244179</v>
+        <v>2.72845142</v>
       </c>
       <c r="D17" t="n">
-        <v>2.72845142</v>
+        <v>0.8801225899999999</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8801225899999999</v>
+        <v>0.95461918</v>
       </c>
       <c r="F17" t="n">
-        <v>0.95461918</v>
+        <v>0.84933853</v>
       </c>
       <c r="G17" t="n">
-        <v>0.84933853</v>
+        <v>-0.12911185</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.12911185</v>
+        <v>0.18345265</v>
       </c>
       <c r="I17" t="n">
-        <v>0.18345265</v>
+        <v>-0.75565477</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.75565477</v>
+        <v>-1.09301157</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.09301157</v>
+        <v>-1.25991411</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.25991411</v>
+        <v>0.42586555</v>
       </c>
       <c r="M17" t="n">
-        <v>0.42586555</v>
+        <v>1.11311752</v>
       </c>
     </row>
     <row r="18">
@@ -1165,37 +1161,37 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>786.6830428600001</v>
+        <v>-272.85884179</v>
       </c>
       <c r="D18" t="n">
-        <v>-272.85884179</v>
+        <v>-871.1229194199999</v>
       </c>
       <c r="E18" t="n">
-        <v>-871.1229194199999</v>
+        <v>-1069.81135742</v>
       </c>
       <c r="F18" t="n">
-        <v>-1069.81135742</v>
+        <v>-452.58295967</v>
       </c>
       <c r="G18" t="n">
-        <v>-452.58295967</v>
+        <v>-531.6617434799999</v>
       </c>
       <c r="H18" t="n">
-        <v>-531.6617434799999</v>
+        <v>-603.5171211700001</v>
       </c>
       <c r="I18" t="n">
-        <v>-603.5171211700001</v>
+        <v>-1.170012629999998</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.170012629999998</v>
+        <v>755.74136299</v>
       </c>
       <c r="K18" t="n">
-        <v>755.74136299</v>
+        <v>808.41838966</v>
       </c>
       <c r="L18" t="n">
-        <v>808.41838966</v>
+        <v>20.05482964</v>
       </c>
       <c r="M18" t="n">
-        <v>20.05482964</v>
+        <v>397.91409635</v>
       </c>
     </row>
     <row r="19">
@@ -1206,37 +1202,37 @@
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>-6.060158990000001</v>
+        <v>-6.60366677</v>
       </c>
       <c r="D19" t="n">
-        <v>-6.60366677</v>
+        <v>-1.86839988</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.86839988</v>
+        <v>-3.49261844</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.49261844</v>
+        <v>-0.45935476</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.45935476</v>
+        <v>-5.09463389</v>
       </c>
       <c r="H19" t="n">
-        <v>-5.09463389</v>
+        <v>-16.04657688</v>
       </c>
       <c r="I19" t="n">
-        <v>-16.04657688</v>
+        <v>-16.7282934</v>
       </c>
       <c r="J19" t="n">
-        <v>-16.7282934</v>
+        <v>-9.796063780000001</v>
       </c>
       <c r="K19" t="n">
-        <v>-9.796063780000001</v>
+        <v>-1.05380141</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.05380141</v>
+        <v>2.68419108</v>
       </c>
       <c r="M19" t="n">
-        <v>2.68419108</v>
+        <v>5.168692590000001</v>
       </c>
     </row>
     <row r="20">
@@ -1247,37 +1243,37 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>-20.57369556</v>
+        <v>-26.64337471</v>
       </c>
       <c r="D20" t="n">
-        <v>-26.64337471</v>
+        <v>-8.6719104</v>
       </c>
       <c r="E20" t="n">
-        <v>-8.6719104</v>
+        <v>6.29112816</v>
       </c>
       <c r="F20" t="n">
-        <v>6.29112816</v>
+        <v>-11.38791094</v>
       </c>
       <c r="G20" t="n">
-        <v>-11.38791094</v>
+        <v>39.90390299</v>
       </c>
       <c r="H20" t="n">
-        <v>39.90390299</v>
+        <v>-7.499015480000001</v>
       </c>
       <c r="I20" t="n">
-        <v>-7.499015480000001</v>
+        <v>-34.65196079</v>
       </c>
       <c r="J20" t="n">
-        <v>-34.65196079</v>
+        <v>-20.07586818</v>
       </c>
       <c r="K20" t="n">
-        <v>-20.07586818</v>
+        <v>37.03994246</v>
       </c>
       <c r="L20" t="n">
-        <v>37.03994246</v>
+        <v>61.97440654</v>
       </c>
       <c r="M20" t="n">
-        <v>61.97440654</v>
+        <v>4.784528130000001</v>
       </c>
     </row>
     <row r="21">
@@ -1286,39 +1282,41 @@
           <t>居家生活右下</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
       <c r="C21" t="n">
-        <v>0.11204183</v>
+        <v>1.42652432</v>
       </c>
       <c r="D21" t="n">
-        <v>1.42578982</v>
+        <v>2.43182188</v>
       </c>
       <c r="E21" t="n">
-        <v>2.43176568</v>
+        <v>1.74384658</v>
       </c>
       <c r="F21" t="n">
-        <v>1.74360285</v>
+        <v>1.74691153</v>
       </c>
       <c r="G21" t="n">
-        <v>1.74664979</v>
+        <v>1.07925514</v>
       </c>
       <c r="H21" t="n">
-        <v>1.07891954</v>
+        <v>-4.11525845</v>
       </c>
       <c r="I21" t="n">
-        <v>-4.11562551</v>
+        <v>-7.67941925</v>
       </c>
       <c r="J21" t="n">
-        <v>-7.679255199999999</v>
+        <v>-2.84960067</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.84996042</v>
+        <v>-1.0665493</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.06686876</v>
+        <v>0.6943534300000002</v>
       </c>
       <c r="M21" t="n">
-        <v>0.69414977</v>
+        <v>-0.5864616200000001</v>
       </c>
     </row>
     <row r="22">
@@ -1329,37 +1327,37 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>-0.1116844499999999</v>
+        <v>2.09046991</v>
       </c>
       <c r="D22" t="n">
-        <v>2.09106884</v>
+        <v>2.66346664</v>
       </c>
       <c r="E22" t="n">
-        <v>2.66362076</v>
+        <v>2.26386664</v>
       </c>
       <c r="F22" t="n">
-        <v>2.26437657</v>
+        <v>2.71086744</v>
       </c>
       <c r="G22" t="n">
-        <v>2.71147254</v>
+        <v>2.27450032</v>
       </c>
       <c r="H22" t="n">
-        <v>2.27511611</v>
+        <v>3.80883685</v>
       </c>
       <c r="I22" t="n">
-        <v>3.80950832</v>
+        <v>1.51244877</v>
       </c>
       <c r="J22" t="n">
-        <v>1.51303603</v>
+        <v>0.8467118700000001</v>
       </c>
       <c r="K22" t="n">
-        <v>0.84748555</v>
+        <v>1.00827689</v>
       </c>
       <c r="L22" t="n">
-        <v>1.00912572</v>
+        <v>3.30557361</v>
       </c>
       <c r="M22" t="n">
-        <v>3.30607556</v>
+        <v>4.33944642</v>
       </c>
     </row>
     <row r="23">
@@ -1370,37 +1368,37 @@
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
-        <v>16.72892445</v>
+        <v>18.20302817</v>
       </c>
       <c r="D23" t="n">
-        <v>18.21552769</v>
+        <v>37.92417097</v>
       </c>
       <c r="E23" t="n">
-        <v>37.88405859</v>
+        <v>24.25433136</v>
       </c>
       <c r="F23" t="n">
-        <v>24.20960816</v>
+        <v>17.35399521</v>
       </c>
       <c r="G23" t="n">
-        <v>17.34495134</v>
+        <v>10.91826206</v>
       </c>
       <c r="H23" t="n">
-        <v>10.97104816</v>
+        <v>14.60415864</v>
       </c>
       <c r="I23" t="n">
-        <v>14.7137113</v>
+        <v>25.82796283</v>
       </c>
       <c r="J23" t="n">
-        <v>25.86115714</v>
+        <v>61.49910808</v>
       </c>
       <c r="K23" t="n">
-        <v>61.50186898999999</v>
+        <v>67.77362210000001</v>
       </c>
       <c r="L23" t="n">
-        <v>67.72679253</v>
+        <v>73.12120501999999</v>
       </c>
       <c r="M23" t="n">
-        <v>73.11998154999999</v>
+        <v>134.40800574</v>
       </c>
     </row>
     <row r="24">
@@ -1409,39 +1407,41 @@
           <t>建材營造右下</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
       <c r="C24" t="n">
-        <v>-89.82169067</v>
+        <v>-6.62700109</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.62700109</v>
+        <v>83.61085113</v>
       </c>
       <c r="E24" t="n">
-        <v>83.61085113</v>
+        <v>26.68614927</v>
       </c>
       <c r="F24" t="n">
-        <v>26.68614927</v>
+        <v>13.31384929</v>
       </c>
       <c r="G24" t="n">
-        <v>13.31384929</v>
+        <v>-21.23921207</v>
       </c>
       <c r="H24" t="n">
-        <v>-21.23921207</v>
+        <v>-42.54438606</v>
       </c>
       <c r="I24" t="n">
-        <v>-42.54438606</v>
+        <v>-44.12641995000001</v>
       </c>
       <c r="J24" t="n">
-        <v>-44.12641995000001</v>
+        <v>-45.77733627</v>
       </c>
       <c r="K24" t="n">
-        <v>-45.77733627</v>
+        <v>-27.47678849</v>
       </c>
       <c r="L24" t="n">
-        <v>-27.47678849</v>
+        <v>5.553141660000001</v>
       </c>
       <c r="M24" t="n">
-        <v>5.553141660000001</v>
+        <v>28.34928419</v>
       </c>
     </row>
     <row r="25">
@@ -1452,37 +1452,37 @@
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>-76.77982048</v>
+        <v>-33.08088043999999</v>
       </c>
       <c r="D25" t="n">
-        <v>-33.19166399</v>
+        <v>54.79315186</v>
       </c>
       <c r="E25" t="n">
-        <v>54.8293569</v>
+        <v>26.1645912</v>
       </c>
       <c r="F25" t="n">
-        <v>26.1645132</v>
+        <v>40.18119956</v>
       </c>
       <c r="G25" t="n">
-        <v>40.14163911</v>
+        <v>34.56604312</v>
       </c>
       <c r="H25" t="n">
-        <v>34.58145535</v>
+        <v>8.61558161</v>
       </c>
       <c r="I25" t="n">
-        <v>8.544195799999995</v>
+        <v>8.902622270000002</v>
       </c>
       <c r="J25" t="n">
-        <v>9.006444429999998</v>
+        <v>5.70338004</v>
       </c>
       <c r="K25" t="n">
-        <v>6.00126162</v>
+        <v>44.66285690000001</v>
       </c>
       <c r="L25" t="n">
-        <v>44.85690394</v>
+        <v>48.10175376999999</v>
       </c>
       <c r="M25" t="n">
-        <v>48.15734783</v>
+        <v>37.10647014</v>
       </c>
     </row>
     <row r="26">
@@ -1493,37 +1493,37 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>-0.4000247499999999</v>
+        <v>7.61994909</v>
       </c>
       <c r="D26" t="n">
-        <v>7.620458500000001</v>
+        <v>3.95032609</v>
       </c>
       <c r="E26" t="n">
-        <v>3.95086604</v>
+        <v>8.953404039999999</v>
       </c>
       <c r="F26" t="n">
-        <v>8.954270699999999</v>
+        <v>5.887683269999999</v>
       </c>
       <c r="G26" t="n">
-        <v>5.88796488</v>
+        <v>7.59334499</v>
       </c>
       <c r="H26" t="n">
-        <v>7.59403203</v>
+        <v>5.17034791</v>
       </c>
       <c r="I26" t="n">
-        <v>5.170474019999999</v>
+        <v>7.59349848</v>
       </c>
       <c r="J26" t="n">
-        <v>7.59523152</v>
+        <v>18.69440627</v>
       </c>
       <c r="K26" t="n">
-        <v>18.69807133</v>
+        <v>6.72809566</v>
       </c>
       <c r="L26" t="n">
-        <v>6.72828735</v>
+        <v>5.8262754</v>
       </c>
       <c r="M26" t="n">
-        <v>5.82693547</v>
+        <v>6.19576568</v>
       </c>
     </row>
     <row r="27">
@@ -1534,37 +1534,37 @@
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>5.178023819999999</v>
+        <v>12.34924729</v>
       </c>
       <c r="D27" t="n">
-        <v>12.34928412</v>
+        <v>7.256533559999999</v>
       </c>
       <c r="E27" t="n">
-        <v>7.256554369999998</v>
+        <v>21.41555787</v>
       </c>
       <c r="F27" t="n">
-        <v>21.4155872</v>
+        <v>9.253958190000001</v>
       </c>
       <c r="G27" t="n">
-        <v>9.253985100000001</v>
+        <v>20.89001611</v>
       </c>
       <c r="H27" t="n">
-        <v>20.89003487</v>
+        <v>17.74033155</v>
       </c>
       <c r="I27" t="n">
-        <v>17.74032494</v>
+        <v>22.20184127</v>
       </c>
       <c r="J27" t="n">
-        <v>22.20183627</v>
+        <v>32.01865752</v>
       </c>
       <c r="K27" t="n">
-        <v>32.01865252</v>
+        <v>32.91440352</v>
       </c>
       <c r="L27" t="n">
-        <v>32.91414248</v>
+        <v>31.90241096</v>
       </c>
       <c r="M27" t="n">
-        <v>31.90223136</v>
+        <v>15.84994324</v>
       </c>
     </row>
     <row r="28">
@@ -1575,37 +1575,37 @@
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>-0.3640058200000001</v>
+        <v>12.54056931</v>
       </c>
       <c r="D28" t="n">
-        <v>12.5400599</v>
+        <v>-19.63720791</v>
       </c>
       <c r="E28" t="n">
-        <v>-19.63774786</v>
+        <v>3.95222211</v>
       </c>
       <c r="F28" t="n">
-        <v>3.95135545</v>
+        <v>-27.67325763</v>
       </c>
       <c r="G28" t="n">
-        <v>-27.67353924</v>
+        <v>-47.67043209</v>
       </c>
       <c r="H28" t="n">
-        <v>-47.67111913</v>
+        <v>-79.82344318999999</v>
       </c>
       <c r="I28" t="n">
-        <v>-79.8235693</v>
+        <v>-109.72795995</v>
       </c>
       <c r="J28" t="n">
-        <v>-109.72969299</v>
+        <v>-102.94148546</v>
       </c>
       <c r="K28" t="n">
-        <v>-102.94515052</v>
+        <v>-89.79447408</v>
       </c>
       <c r="L28" t="n">
-        <v>-89.79466576999999</v>
+        <v>-73.93345174000001</v>
       </c>
       <c r="M28" t="n">
-        <v>-73.93411181</v>
+        <v>-58.76420166999999</v>
       </c>
     </row>
     <row r="29">
@@ -1616,37 +1616,37 @@
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>0.01033713</v>
+        <v>0.01825068</v>
       </c>
       <c r="D29" t="n">
-        <v>0.01825068</v>
+        <v>0.02746755</v>
       </c>
       <c r="E29" t="n">
-        <v>0.02746755</v>
+        <v>0.08414062</v>
       </c>
       <c r="F29" t="n">
-        <v>0.08414062</v>
+        <v>0.07506878</v>
       </c>
       <c r="G29" t="n">
-        <v>0.07506878</v>
+        <v>0.03323846</v>
       </c>
       <c r="H29" t="n">
-        <v>0.03323846</v>
+        <v>0.00619917</v>
       </c>
       <c r="I29" t="n">
-        <v>0.00619917</v>
+        <v>0.01277118</v>
       </c>
       <c r="J29" t="n">
-        <v>0.01277118</v>
+        <v>-0.00653676</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.00653676</v>
+        <v>-0.01623805</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.01623805</v>
+        <v>-0.01854561</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.01854561</v>
+        <v>-0.0214375</v>
       </c>
     </row>
     <row r="30">
@@ -1657,37 +1657,37 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>-0.00683579</v>
+        <v>-0.00255541</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.00255541</v>
+        <v>0.0079351</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0079351</v>
+        <v>0.01028314</v>
       </c>
       <c r="F30" t="n">
-        <v>0.01028314</v>
+        <v>0.00538708</v>
       </c>
       <c r="G30" t="n">
-        <v>0.00538708</v>
+        <v>0.01209633</v>
       </c>
       <c r="H30" t="n">
-        <v>0.01209633</v>
+        <v>0.0008129699999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0008129699999999999</v>
+        <v>-0.00467908</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.00467908</v>
+        <v>-0.00565026</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.00565026</v>
+        <v>-0.00688049</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.00688049</v>
+        <v>0.01008529</v>
       </c>
       <c r="M30" t="n">
-        <v>0.01008529</v>
+        <v>0.00215091</v>
       </c>
     </row>
     <row r="31">
@@ -1698,37 +1698,37 @@
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>0.03434865</v>
+        <v>0.003614140000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>0.003614140000000001</v>
+        <v>0.10054297</v>
       </c>
       <c r="E31" t="n">
-        <v>0.10054297</v>
+        <v>0.21751282</v>
       </c>
       <c r="F31" t="n">
-        <v>0.21751282</v>
+        <v>0.10936104</v>
       </c>
       <c r="G31" t="n">
-        <v>0.10936104</v>
+        <v>0.03924989</v>
       </c>
       <c r="H31" t="n">
-        <v>0.03924989</v>
+        <v>-0.01166996</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.01166996</v>
+        <v>-0.05285173000000001</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.05285173000000001</v>
+        <v>-0.09475462</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.09475462</v>
+        <v>-0.1850039</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.1850039</v>
+        <v>0.0035406</v>
       </c>
       <c r="M31" t="n">
-        <v>0.0035406</v>
+        <v>-0.03696819</v>
       </c>
     </row>
     <row r="32">
@@ -1739,37 +1739,37 @@
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>-23.28926443</v>
+        <v>-15.50397747</v>
       </c>
       <c r="D32" t="n">
-        <v>-15.50397747</v>
+        <v>-7.671519279999999</v>
       </c>
       <c r="E32" t="n">
-        <v>-7.671519279999999</v>
+        <v>-12.56496135</v>
       </c>
       <c r="F32" t="n">
-        <v>-12.56496135</v>
+        <v>0.4845926899999997</v>
       </c>
       <c r="G32" t="n">
-        <v>0.4845926899999997</v>
+        <v>-20.67803373</v>
       </c>
       <c r="H32" t="n">
-        <v>-20.67803373</v>
+        <v>-32.15445803</v>
       </c>
       <c r="I32" t="n">
-        <v>-32.15445803</v>
+        <v>-40.28821612</v>
       </c>
       <c r="J32" t="n">
-        <v>-40.28821612</v>
+        <v>-16.20914258</v>
       </c>
       <c r="K32" t="n">
-        <v>-16.20914258</v>
+        <v>-19.13381427</v>
       </c>
       <c r="L32" t="n">
-        <v>-19.13381427</v>
+        <v>-10.30184885</v>
       </c>
       <c r="M32" t="n">
-        <v>-10.30184885</v>
+        <v>-13.95881996</v>
       </c>
     </row>
     <row r="33">
@@ -1780,37 +1780,37 @@
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
-        <v>0.07589649999999996</v>
+        <v>-0.14939967</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.14939967</v>
+        <v>0.5503706399999999</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5503706399999999</v>
+        <v>1.89812459</v>
       </c>
       <c r="F33" t="n">
-        <v>1.89812459</v>
+        <v>2.92653785</v>
       </c>
       <c r="G33" t="n">
-        <v>2.92653785</v>
+        <v>0.4812992</v>
       </c>
       <c r="H33" t="n">
-        <v>0.4812992</v>
+        <v>-1.10311971</v>
       </c>
       <c r="I33" t="n">
-        <v>-1.10311971</v>
+        <v>-3.2016798</v>
       </c>
       <c r="J33" t="n">
-        <v>-3.2016798</v>
+        <v>-1.87034995</v>
       </c>
       <c r="K33" t="n">
-        <v>-1.87034995</v>
+        <v>-2.31543645</v>
       </c>
       <c r="L33" t="n">
-        <v>-2.31543645</v>
+        <v>-4.02921888</v>
       </c>
       <c r="M33" t="n">
-        <v>-4.02921888</v>
+        <v>-1.65893927</v>
       </c>
     </row>
     <row r="34">
@@ -1821,37 +1821,37 @@
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
-        <v>75.68712063</v>
+        <v>34.04004418</v>
       </c>
       <c r="D34" t="n">
-        <v>33.27450068</v>
+        <v>21.63590168</v>
       </c>
       <c r="E34" t="n">
-        <v>20.78368849</v>
+        <v>34.050435</v>
       </c>
       <c r="F34" t="n">
-        <v>33.21580698</v>
+        <v>53.00901164</v>
       </c>
       <c r="G34" t="n">
-        <v>52.12681979</v>
+        <v>23.37416052</v>
       </c>
       <c r="H34" t="n">
-        <v>22.38281906</v>
+        <v>33.49646586</v>
       </c>
       <c r="I34" t="n">
-        <v>33.51679171</v>
+        <v>42.38292683</v>
       </c>
       <c r="J34" t="n">
-        <v>42.04676762</v>
+        <v>53.14078301</v>
       </c>
       <c r="K34" t="n">
-        <v>53.81900047</v>
+        <v>77.31264456</v>
       </c>
       <c r="L34" t="n">
-        <v>78.81126565000001</v>
+        <v>-99.06594910000001</v>
       </c>
       <c r="M34" t="n">
-        <v>-96.49697067</v>
+        <v>-137.71287059</v>
       </c>
     </row>
     <row r="35">
@@ -1862,37 +1862,37 @@
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
-        <v>-0.09362012</v>
+        <v>-0.86483032</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.09928682000000001</v>
+        <v>-0.8053423099999999</v>
       </c>
       <c r="E35" t="n">
-        <v>0.04687088</v>
+        <v>-0.5541974000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>0.28043062</v>
+        <v>-0.86426467</v>
       </c>
       <c r="G35" t="n">
-        <v>0.01792718</v>
+        <v>-1.03027462</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.03893316</v>
+        <v>-0.0252352</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.04556105000000001</v>
+        <v>-0.03013220000000001</v>
       </c>
       <c r="J35" t="n">
-        <v>0.30602701</v>
+        <v>3.18854859</v>
       </c>
       <c r="K35" t="n">
-        <v>2.51033113</v>
+        <v>2.605460190000001</v>
       </c>
       <c r="L35" t="n">
-        <v>1.1068391</v>
+        <v>4.13401164</v>
       </c>
       <c r="M35" t="n">
-        <v>1.56503321</v>
+        <v>4.72190981</v>
       </c>
     </row>
     <row r="36">
@@ -1903,37 +1903,37 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>-4.70504814</v>
+        <v>44.04495778</v>
       </c>
       <c r="D36" t="n">
-        <v>40.16238359</v>
+        <v>85.63237165</v>
       </c>
       <c r="E36" t="n">
-        <v>84.05469214</v>
+        <v>179.98748556</v>
       </c>
       <c r="F36" t="n">
-        <v>168.24925684</v>
+        <v>243.01780536</v>
       </c>
       <c r="G36" t="n">
-        <v>236.89254524</v>
+        <v>120.77072082</v>
       </c>
       <c r="H36" t="n">
-        <v>117.94625767</v>
+        <v>227.54441106</v>
       </c>
       <c r="I36" t="n">
-        <v>217.93889327</v>
+        <v>364.58955555</v>
       </c>
       <c r="J36" t="n">
-        <v>352.4427523</v>
+        <v>215.34440896</v>
       </c>
       <c r="K36" t="n">
-        <v>204.10822595</v>
+        <v>203.11277483</v>
       </c>
       <c r="L36" t="n">
-        <v>203.78321979</v>
+        <v>-9.032017559999998</v>
       </c>
       <c r="M36" t="n">
-        <v>-5.257925969999995</v>
+        <v>184.61897931</v>
       </c>
     </row>
     <row r="37">
@@ -1944,37 +1944,37 @@
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>-5.291141719999999</v>
+        <v>3.358943199999999</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.514865390000001</v>
+        <v>21.65631013</v>
       </c>
       <c r="E37" t="n">
-        <v>18.38879085</v>
+        <v>37.15833097</v>
       </c>
       <c r="F37" t="n">
-        <v>37.15833097</v>
+        <v>41.52823503</v>
       </c>
       <c r="G37" t="n">
-        <v>41.52823503</v>
+        <v>46.73594826000001</v>
       </c>
       <c r="H37" t="n">
-        <v>46.73594826000001</v>
+        <v>4.982251610000001</v>
       </c>
       <c r="I37" t="n">
-        <v>4.982251610000001</v>
+        <v>6.840031639999999</v>
       </c>
       <c r="J37" t="n">
-        <v>6.840031639999999</v>
+        <v>35.03138665</v>
       </c>
       <c r="K37" t="n">
-        <v>35.03138665</v>
+        <v>8.22256728</v>
       </c>
       <c r="L37" t="n">
-        <v>8.22256728</v>
+        <v>18.62594352</v>
       </c>
       <c r="M37" t="n">
-        <v>18.62594352</v>
+        <v>6.7077866</v>
       </c>
     </row>
     <row r="38">
@@ -1985,37 +1985,37 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>-34.16824592</v>
+        <v>-45.11636293</v>
       </c>
       <c r="D38" t="n">
-        <v>-41.23378873999999</v>
+        <v>-1.056509029999998</v>
       </c>
       <c r="E38" t="n">
-        <v>0.5211704800000023</v>
+        <v>56.57809310999999</v>
       </c>
       <c r="F38" t="n">
-        <v>68.31632182999999</v>
+        <v>21.60893473000001</v>
       </c>
       <c r="G38" t="n">
-        <v>27.73419485000001</v>
+        <v>-37.8064404</v>
       </c>
       <c r="H38" t="n">
-        <v>-34.98197725</v>
+        <v>-64.52067828999999</v>
       </c>
       <c r="I38" t="n">
-        <v>-54.9151605</v>
+        <v>-17.82765088</v>
       </c>
       <c r="J38" t="n">
-        <v>-5.680847629999999</v>
+        <v>30.20554926</v>
       </c>
       <c r="K38" t="n">
-        <v>41.44173227</v>
+        <v>37.14663873000001</v>
       </c>
       <c r="L38" t="n">
-        <v>36.47619377</v>
+        <v>-20.40864164</v>
       </c>
       <c r="M38" t="n">
-        <v>-24.18273323</v>
+        <v>2.93989154</v>
       </c>
     </row>
     <row r="39">
@@ -2026,37 +2026,37 @@
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
-        <v>-2.38145906</v>
+        <v>-1.22895808</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.22895808</v>
+        <v>2.09904764</v>
       </c>
       <c r="E39" t="n">
-        <v>2.09904764</v>
+        <v>3.22631047</v>
       </c>
       <c r="F39" t="n">
-        <v>3.22631047</v>
+        <v>8.135896049999999</v>
       </c>
       <c r="G39" t="n">
-        <v>8.135896049999999</v>
+        <v>0.42597227</v>
       </c>
       <c r="H39" t="n">
-        <v>0.42597227</v>
+        <v>5.236759269999999</v>
       </c>
       <c r="I39" t="n">
-        <v>5.236759269999999</v>
+        <v>24.80576117</v>
       </c>
       <c r="J39" t="n">
-        <v>24.80576117</v>
+        <v>21.99748971</v>
       </c>
       <c r="K39" t="n">
-        <v>21.99748971</v>
+        <v>7.5667577</v>
       </c>
       <c r="L39" t="n">
-        <v>7.5667577</v>
+        <v>-0.39082327</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.39082327</v>
+        <v>6.9156605</v>
       </c>
     </row>
     <row r="40">
@@ -2067,37 +2067,37 @@
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>168.35309943</v>
+        <v>54.65563677999999</v>
       </c>
       <c r="D40" t="n">
-        <v>54.65555302999999</v>
+        <v>-40.04566426</v>
       </c>
       <c r="E40" t="n">
-        <v>-40.04571159</v>
+        <v>-65.28418285000001</v>
       </c>
       <c r="F40" t="n">
-        <v>-65.28430948</v>
+        <v>-32.76076323</v>
       </c>
       <c r="G40" t="n">
-        <v>-32.76083196</v>
+        <v>-17.83607626</v>
       </c>
       <c r="H40" t="n">
-        <v>-17.83612673</v>
+        <v>-34.19595065</v>
       </c>
       <c r="I40" t="n">
-        <v>-34.19594447999999</v>
+        <v>-18.27668358</v>
       </c>
       <c r="J40" t="n">
-        <v>-18.27671337</v>
+        <v>16.53820925</v>
       </c>
       <c r="K40" t="n">
-        <v>16.53812736</v>
+        <v>-19.19783037</v>
       </c>
       <c r="L40" t="n">
-        <v>-19.19792823</v>
+        <v>-76.84971587000001</v>
       </c>
       <c r="M40" t="n">
-        <v>-76.84975909000001</v>
+        <v>-32.57665906</v>
       </c>
     </row>
     <row r="41">
@@ -2108,37 +2108,37 @@
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
-        <v>-0.04257767</v>
+        <v>0.007071730000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>0.007155480000000001</v>
+        <v>0.10073328</v>
       </c>
       <c r="E41" t="n">
-        <v>0.10078061</v>
+        <v>0.01842728</v>
       </c>
       <c r="F41" t="n">
-        <v>0.01855391</v>
+        <v>-0.0118544</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.01178567</v>
+        <v>-0.01793327</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.0178828</v>
+        <v>-0.0233492</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.02335537</v>
+        <v>-0.02159357</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.02156378</v>
+        <v>-0.01869641</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.01861452</v>
+        <v>-0.01293549</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.01283763</v>
+        <v>-0.01600619</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.01596297</v>
+        <v>-0.02050284</v>
       </c>
     </row>
     <row r="42">
@@ -2149,37 +2149,37 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>486.62145114</v>
+        <v>769.43496877</v>
       </c>
       <c r="D42" t="n">
-        <v>768.44312698</v>
+        <v>271.10624811</v>
       </c>
       <c r="E42" t="n">
-        <v>271.57353044</v>
+        <v>-68.5816458</v>
       </c>
       <c r="F42" t="n">
-        <v>-68.75579565</v>
+        <v>-26.60399435</v>
       </c>
       <c r="G42" t="n">
-        <v>-25.65882652</v>
+        <v>-205.2773343</v>
       </c>
       <c r="H42" t="n">
-        <v>-203.34503687</v>
+        <v>-28.30046276</v>
       </c>
       <c r="I42" t="n">
-        <v>-26.00127152</v>
+        <v>155.55902704</v>
       </c>
       <c r="J42" t="n">
-        <v>156.76665614</v>
+        <v>582.9563215699999</v>
       </c>
       <c r="K42" t="n">
-        <v>578.4989785</v>
+        <v>919.0814701600001</v>
       </c>
       <c r="L42" t="n">
-        <v>900.52032724</v>
+        <v>1187.41765549</v>
       </c>
       <c r="M42" t="n">
-        <v>1153.82319753</v>
+        <v>1289.85564071</v>
       </c>
     </row>
     <row r="43">
@@ -2190,37 +2190,37 @@
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
-        <v>0.5450071499999999</v>
+        <v>1.44990002</v>
       </c>
       <c r="D43" t="n">
-        <v>2.44174181</v>
+        <v>0.19227776</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.2750045700000001</v>
+        <v>1.29170596</v>
       </c>
       <c r="F43" t="n">
-        <v>1.46585581</v>
+        <v>2.10339348</v>
       </c>
       <c r="G43" t="n">
-        <v>1.15822565</v>
+        <v>0.38728135</v>
       </c>
       <c r="H43" t="n">
-        <v>-1.54501608</v>
+        <v>-0.48629467</v>
       </c>
       <c r="I43" t="n">
-        <v>-2.785485910000001</v>
+        <v>-1.52022097</v>
       </c>
       <c r="J43" t="n">
-        <v>-2.72785007</v>
+        <v>-0.80378561</v>
       </c>
       <c r="K43" t="n">
-        <v>3.65355746</v>
+        <v>2.28745028</v>
       </c>
       <c r="L43" t="n">
-        <v>20.8485932</v>
+        <v>0.67277188</v>
       </c>
       <c r="M43" t="n">
-        <v>34.26722984000001</v>
+        <v>0.93779075</v>
       </c>
     </row>
     <row r="44">
@@ -2231,37 +2231,37 @@
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>-17.9925402</v>
+        <v>80.12160184</v>
       </c>
       <c r="D44" t="n">
-        <v>77.01381998999999</v>
+        <v>-52.86507272</v>
       </c>
       <c r="E44" t="n">
-        <v>-54.02000653</v>
+        <v>37.46158601</v>
       </c>
       <c r="F44" t="n">
-        <v>38.02652629</v>
+        <v>83.43559676999999</v>
       </c>
       <c r="G44" t="n">
-        <v>83.20819602</v>
+        <v>81.79199306</v>
       </c>
       <c r="H44" t="n">
-        <v>82.76183254999999</v>
+        <v>103.719146</v>
       </c>
       <c r="I44" t="n">
-        <v>104.05543862</v>
+        <v>28.17386177</v>
       </c>
       <c r="J44" t="n">
-        <v>28.05805659</v>
+        <v>77.18747601999999</v>
       </c>
       <c r="K44" t="n">
-        <v>79.00795539000001</v>
+        <v>133.43583258</v>
       </c>
       <c r="L44" t="n">
-        <v>135.77151984</v>
+        <v>170.96596239</v>
       </c>
       <c r="M44" t="n">
-        <v>171.60848488</v>
+        <v>26.97087123</v>
       </c>
     </row>
     <row r="45">
@@ -2270,41 +2270,39 @@
           <t>生技醫療業右下</t>
         </is>
       </c>
-      <c r="B45" t="n">
-        <v>0</v>
-      </c>
+      <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
-        <v>-317.72873369</v>
+        <v>-301.92317178</v>
       </c>
       <c r="D45" t="n">
-        <v>-304.6201171</v>
+        <v>-60.52257173</v>
       </c>
       <c r="E45" t="n">
-        <v>-63.96852718</v>
+        <v>12.40978543000001</v>
       </c>
       <c r="F45" t="n">
-        <v>7.646972300000004</v>
+        <v>34.89329313</v>
       </c>
       <c r="G45" t="n">
-        <v>31.97162437</v>
+        <v>122.56977911</v>
       </c>
       <c r="H45" t="n">
-        <v>119.09006323</v>
+        <v>263.33302193</v>
       </c>
       <c r="I45" t="n">
-        <v>261.26988149</v>
+        <v>96.62626367000001</v>
       </c>
       <c r="J45" t="n">
-        <v>96.42507055000002</v>
+        <v>184.2028899</v>
       </c>
       <c r="K45" t="n">
-        <v>181.65105055</v>
+        <v>197.75035785</v>
       </c>
       <c r="L45" t="n">
-        <v>198.57951492</v>
+        <v>293.1900217</v>
       </c>
       <c r="M45" t="n">
-        <v>293.93786827</v>
+        <v>426.00817599</v>
       </c>
     </row>
     <row r="46">
@@ -2315,37 +2313,37 @@
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>-194.48683474</v>
+        <v>-38.67281785</v>
       </c>
       <c r="D46" t="n">
-        <v>-32.86805202</v>
+        <v>31.39405054</v>
       </c>
       <c r="E46" t="n">
-        <v>35.99495334</v>
+        <v>65.72468522</v>
       </c>
       <c r="F46" t="n">
-        <v>69.92252886</v>
+        <v>-72.19612522</v>
       </c>
       <c r="G46" t="n">
-        <v>-69.04706243999999</v>
+        <v>-4.134493600000007</v>
       </c>
       <c r="H46" t="n">
-        <v>-1.624596259999997</v>
+        <v>-41.23027432000001</v>
       </c>
       <c r="I46" t="n">
-        <v>-39.50340163000001</v>
+        <v>-75.34814689</v>
       </c>
       <c r="J46" t="n">
-        <v>-75.03116486</v>
+        <v>9.027543470000003</v>
       </c>
       <c r="K46" t="n">
-        <v>9.758939030000001</v>
+        <v>-35.45215350000001</v>
       </c>
       <c r="L46" t="n">
-        <v>-38.61703267000001</v>
+        <v>56.42522958999999</v>
       </c>
       <c r="M46" t="n">
-        <v>55.03483952000001</v>
+        <v>14.355379</v>
       </c>
     </row>
     <row r="47">
@@ -2356,37 +2354,37 @@
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>-5.95651349</v>
+        <v>-5.16051644</v>
       </c>
       <c r="D47" t="n">
-        <v>-5.16051644</v>
+        <v>-5.243580819999999</v>
       </c>
       <c r="E47" t="n">
-        <v>-5.243580819999999</v>
+        <v>-1.42689061</v>
       </c>
       <c r="F47" t="n">
-        <v>-1.42689061</v>
+        <v>-1.55805487</v>
       </c>
       <c r="G47" t="n">
-        <v>-1.55805487</v>
+        <v>0.2128199</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2128199</v>
+        <v>0.11380938</v>
       </c>
       <c r="I47" t="n">
-        <v>0.11380938</v>
+        <v>-1.16393911</v>
       </c>
       <c r="J47" t="n">
-        <v>-1.16393911</v>
+        <v>3.26730915</v>
       </c>
       <c r="K47" t="n">
-        <v>3.26730915</v>
+        <v>1.63955288</v>
       </c>
       <c r="L47" t="n">
-        <v>1.63955288</v>
+        <v>0.7404075099999999</v>
       </c>
       <c r="M47" t="n">
-        <v>0.7404075099999999</v>
+        <v>2.84180396</v>
       </c>
     </row>
     <row r="48">
@@ -2397,37 +2395,37 @@
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
-        <v>4.959410939999997</v>
+        <v>18.61284379</v>
       </c>
       <c r="D48" t="n">
-        <v>20.79775888</v>
+        <v>26.69718061</v>
       </c>
       <c r="E48" t="n">
-        <v>26.43965689</v>
+        <v>6.876004369999999</v>
       </c>
       <c r="F48" t="n">
-        <v>2.09872248</v>
+        <v>-21.01691388</v>
       </c>
       <c r="G48" t="n">
-        <v>-22.66043907</v>
+        <v>-15.13193809</v>
       </c>
       <c r="H48" t="n">
-        <v>-14.22418096</v>
+        <v>-100.97579443</v>
       </c>
       <c r="I48" t="n">
-        <v>-101.4682925</v>
+        <v>-162.4749122</v>
       </c>
       <c r="J48" t="n">
-        <v>-165.30248956</v>
+        <v>-138.91380902</v>
       </c>
       <c r="K48" t="n">
-        <v>-139.3712056</v>
+        <v>-65.78404603</v>
       </c>
       <c r="L48" t="n">
-        <v>-51.9386133</v>
+        <v>100.66743719</v>
       </c>
       <c r="M48" t="n">
-        <v>162.00280897</v>
+        <v>167.30677723</v>
       </c>
     </row>
     <row r="49">
@@ -2438,37 +2436,37 @@
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>-0.10224491</v>
+        <v>2.18193317</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.002981920000000003</v>
+        <v>1.3952722</v>
       </c>
       <c r="E49" t="n">
-        <v>1.65279592</v>
+        <v>-3.45044863</v>
       </c>
       <c r="F49" t="n">
-        <v>1.32683326</v>
+        <v>-1.38795389</v>
       </c>
       <c r="G49" t="n">
-        <v>0.2555712999999999</v>
+        <v>0.9055264000000001</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.002230730000000012</v>
+        <v>-0.70459123</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.21209316</v>
+        <v>-3.15058017</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.3230028099999999</v>
+        <v>-1.09952806</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.64213148</v>
+        <v>13.15768119</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.6877515400000001</v>
+        <v>60.53367364</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.8016981400000001</v>
+        <v>92.00546668000001</v>
       </c>
     </row>
     <row r="50">
@@ -2479,37 +2477,37 @@
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
-        <v>-11.23502624000001</v>
+        <v>-31.44969937</v>
       </c>
       <c r="D50" t="n">
-        <v>0.9214968800000017</v>
+        <v>-116.33562401</v>
       </c>
       <c r="E50" t="n">
-        <v>11.29179383</v>
+        <v>-6.691790779999997</v>
       </c>
       <c r="F50" t="n">
-        <v>40.39844144</v>
+        <v>-115.82523807</v>
       </c>
       <c r="G50" t="n">
-        <v>16.19871256</v>
+        <v>53.49678095</v>
       </c>
       <c r="H50" t="n">
-        <v>104.70811418</v>
+        <v>-66.54429746</v>
       </c>
       <c r="I50" t="n">
-        <v>38.44001472999999</v>
+        <v>-48.69457564000001</v>
       </c>
       <c r="J50" t="n">
-        <v>81.66755676999999</v>
+        <v>-31.82532077</v>
       </c>
       <c r="K50" t="n">
-        <v>83.89153795</v>
+        <v>-102.22615871</v>
       </c>
       <c r="L50" t="n">
-        <v>18.31902892</v>
+        <v>-21.90862964999999</v>
       </c>
       <c r="M50" t="n">
-        <v>80.56754973000001</v>
+        <v>59.43721305</v>
       </c>
     </row>
     <row r="51">
@@ -2518,41 +2516,39 @@
           <t>綠能環保右下</t>
         </is>
       </c>
-      <c r="B51" t="n">
-        <v>0</v>
-      </c>
+      <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>-5.524311600000001</v>
+        <v>2.53485937</v>
       </c>
       <c r="D51" t="n">
-        <v>2.53485937</v>
+        <v>-2.54366476</v>
       </c>
       <c r="E51" t="n">
-        <v>-2.54366476</v>
+        <v>4.03323023</v>
       </c>
       <c r="F51" t="n">
-        <v>4.03323023</v>
+        <v>-4.208008479999999</v>
       </c>
       <c r="G51" t="n">
-        <v>-4.208008479999999</v>
+        <v>-16.668004</v>
       </c>
       <c r="H51" t="n">
-        <v>-16.668004</v>
+        <v>-17.31000216</v>
       </c>
       <c r="I51" t="n">
-        <v>-17.31000216</v>
+        <v>-27.00119206</v>
       </c>
       <c r="J51" t="n">
-        <v>-27.00119206</v>
+        <v>-37.85262138</v>
       </c>
       <c r="K51" t="n">
-        <v>-37.85262138</v>
+        <v>-40.22165305999999</v>
       </c>
       <c r="L51" t="n">
-        <v>-40.22165305999999</v>
+        <v>-40.80044587</v>
       </c>
       <c r="M51" t="n">
-        <v>-40.80044587</v>
+        <v>-105.72065853</v>
       </c>
     </row>
     <row r="52">
@@ -2563,37 +2559,37 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>-11.58867564</v>
+        <v>18.48084824</v>
       </c>
       <c r="D52" t="n">
-        <v>17.82601938</v>
+        <v>2.56069713</v>
       </c>
       <c r="E52" t="n">
-        <v>3.01749032</v>
+        <v>23.80545876</v>
       </c>
       <c r="F52" t="n">
-        <v>23.56122139</v>
+        <v>22.47130776</v>
       </c>
       <c r="G52" t="n">
-        <v>23.25266108</v>
+        <v>8.574985620000001</v>
       </c>
       <c r="H52" t="n">
-        <v>10.98587756</v>
+        <v>13.58030427</v>
       </c>
       <c r="I52" t="n">
-        <v>14.37131513</v>
+        <v>-8.368601980000001</v>
       </c>
       <c r="J52" t="n">
-        <v>-7.095445330000001</v>
+        <v>0.7310655100000012</v>
       </c>
       <c r="K52" t="n">
-        <v>3.773723930000001</v>
+        <v>-0.2081954600000009</v>
       </c>
       <c r="L52" t="n">
-        <v>-0.6006474200000018</v>
+        <v>-23.608655</v>
       </c>
       <c r="M52" t="n">
-        <v>-25.32666663</v>
+        <v>-24.72453738</v>
       </c>
     </row>
     <row r="53">
@@ -2604,37 +2600,37 @@
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>-242.49142926</v>
+        <v>176.6907841</v>
       </c>
       <c r="D53" t="n">
-        <v>176.6907841</v>
+        <v>173.38863384</v>
       </c>
       <c r="E53" t="n">
-        <v>173.38863384</v>
+        <v>534.25715562</v>
       </c>
       <c r="F53" t="n">
-        <v>534.25715562</v>
+        <v>553.16674841</v>
       </c>
       <c r="G53" t="n">
-        <v>553.16674841</v>
+        <v>-153.03526199</v>
       </c>
       <c r="H53" t="n">
-        <v>-153.03526199</v>
+        <v>23.20095008999999</v>
       </c>
       <c r="I53" t="n">
-        <v>23.20095008999999</v>
+        <v>202.3618308</v>
       </c>
       <c r="J53" t="n">
-        <v>202.3618308</v>
+        <v>368.14814455</v>
       </c>
       <c r="K53" t="n">
-        <v>368.14814455</v>
+        <v>697.0104023600001</v>
       </c>
       <c r="L53" t="n">
-        <v>697.0104023600001</v>
+        <v>588.32413694</v>
       </c>
       <c r="M53" t="n">
-        <v>588.32413694</v>
+        <v>568.4089294300001</v>
       </c>
     </row>
     <row r="54">
@@ -2645,37 +2641,37 @@
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>-5.696196230000001</v>
+        <v>-0.9628130199999999</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.9628130199999999</v>
+        <v>9.50489205</v>
       </c>
       <c r="E54" t="n">
-        <v>9.50489205</v>
+        <v>6.19144345</v>
       </c>
       <c r="F54" t="n">
-        <v>6.19144345</v>
+        <v>18.44292239</v>
       </c>
       <c r="G54" t="n">
-        <v>18.44292239</v>
+        <v>33.41217956000001</v>
       </c>
       <c r="H54" t="n">
-        <v>33.41217956000001</v>
+        <v>32.28907975000001</v>
       </c>
       <c r="I54" t="n">
-        <v>32.28907975000001</v>
+        <v>13.82758123</v>
       </c>
       <c r="J54" t="n">
-        <v>13.82758123</v>
+        <v>22.66509357</v>
       </c>
       <c r="K54" t="n">
-        <v>22.66509357</v>
+        <v>11.76005505</v>
       </c>
       <c r="L54" t="n">
-        <v>11.76005505</v>
+        <v>15.07171019</v>
       </c>
       <c r="M54" t="n">
-        <v>15.07171019</v>
+        <v>11.96384752</v>
       </c>
     </row>
     <row r="55">
@@ -2686,37 +2682,37 @@
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>-0.8393121099999971</v>
+        <v>76.22848026000001</v>
       </c>
       <c r="D55" t="n">
-        <v>76.22848026000001</v>
+        <v>89.94039045999999</v>
       </c>
       <c r="E55" t="n">
-        <v>89.94039045999999</v>
+        <v>112.80848578</v>
       </c>
       <c r="F55" t="n">
-        <v>112.80848578</v>
+        <v>261.49492484</v>
       </c>
       <c r="G55" t="n">
-        <v>261.49492484</v>
+        <v>6.48088612</v>
       </c>
       <c r="H55" t="n">
-        <v>6.48088612</v>
+        <v>394.55405591</v>
       </c>
       <c r="I55" t="n">
-        <v>394.55405591</v>
+        <v>315.60176294</v>
       </c>
       <c r="J55" t="n">
-        <v>315.60176294</v>
+        <v>368.73117568</v>
       </c>
       <c r="K55" t="n">
-        <v>368.73117568</v>
+        <v>35.39821490000001</v>
       </c>
       <c r="L55" t="n">
-        <v>35.39821490000001</v>
+        <v>15.30677176000001</v>
       </c>
       <c r="M55" t="n">
-        <v>15.30677176000001</v>
+        <v>-50.80448778</v>
       </c>
     </row>
     <row r="56">
@@ -2727,37 +2723,37 @@
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>-9.10462467</v>
+        <v>2.08191375</v>
       </c>
       <c r="D56" t="n">
-        <v>2.08191375</v>
+        <v>-7.27952517</v>
       </c>
       <c r="E56" t="n">
-        <v>-7.27952517</v>
+        <v>-1.98157208</v>
       </c>
       <c r="F56" t="n">
-        <v>-1.98157208</v>
+        <v>-4.11619094</v>
       </c>
       <c r="G56" t="n">
-        <v>-4.11619094</v>
+        <v>4.08045064</v>
       </c>
       <c r="H56" t="n">
-        <v>4.08045064</v>
+        <v>-0.19953913</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.19953913</v>
+        <v>-12.28212704</v>
       </c>
       <c r="J56" t="n">
-        <v>-12.28212704</v>
+        <v>-2.91420292</v>
       </c>
       <c r="K56" t="n">
-        <v>-2.91420292</v>
+        <v>20.80548296</v>
       </c>
       <c r="L56" t="n">
-        <v>20.80548296</v>
+        <v>4.32854381</v>
       </c>
       <c r="M56" t="n">
-        <v>4.32854381</v>
+        <v>9.662940969999999</v>
       </c>
     </row>
     <row r="57">
@@ -2766,39 +2762,41 @@
           <t>觀光事業右下</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
+      <c r="B57" t="n">
+        <v>0</v>
+      </c>
       <c r="C57" t="n">
-        <v>-13.07116972</v>
+        <v>-2.52893461</v>
       </c>
       <c r="D57" t="n">
-        <v>-3.20742268</v>
+        <v>23.74879822</v>
       </c>
       <c r="E57" t="n">
-        <v>24.12934406999999</v>
+        <v>18.9220015</v>
       </c>
       <c r="F57" t="n">
-        <v>19.6332525</v>
+        <v>8.37023009</v>
       </c>
       <c r="G57" t="n">
-        <v>9.521876189999999</v>
+        <v>-7.02994692</v>
       </c>
       <c r="H57" t="n">
-        <v>-6.49025438</v>
+        <v>-19.5461556</v>
       </c>
       <c r="I57" t="n">
-        <v>-19.63731446</v>
+        <v>-30.63795106</v>
       </c>
       <c r="J57" t="n">
-        <v>-31.28672083</v>
+        <v>-34.1687701</v>
       </c>
       <c r="K57" t="n">
-        <v>-35.82230129</v>
+        <v>-46.96409482</v>
       </c>
       <c r="L57" t="n">
-        <v>-48.83644887</v>
+        <v>-1.62805522</v>
       </c>
       <c r="M57" t="n">
-        <v>-2.96099005</v>
+        <v>-3.08028842</v>
       </c>
     </row>
     <row r="58">
@@ -2809,37 +2807,37 @@
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>5.066574070000001</v>
+        <v>15.59515841</v>
       </c>
       <c r="D58" t="n">
-        <v>15.59515841</v>
+        <v>34.83701206</v>
       </c>
       <c r="E58" t="n">
-        <v>34.83701206</v>
+        <v>44.05439052</v>
       </c>
       <c r="F58" t="n">
-        <v>44.05439052</v>
+        <v>45.77312744</v>
       </c>
       <c r="G58" t="n">
-        <v>45.77312744</v>
+        <v>20.3881575</v>
       </c>
       <c r="H58" t="n">
-        <v>20.3881575</v>
+        <v>-9.58320387</v>
       </c>
       <c r="I58" t="n">
-        <v>-9.58320387</v>
+        <v>-17.2459276</v>
       </c>
       <c r="J58" t="n">
-        <v>-17.2459276</v>
+        <v>-34.949534</v>
       </c>
       <c r="K58" t="n">
-        <v>-34.949534</v>
+        <v>-42.18699216</v>
       </c>
       <c r="L58" t="n">
-        <v>-42.18699216</v>
+        <v>-0.99560861</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.99560861</v>
+        <v>-6.332915389999999</v>
       </c>
     </row>
     <row r="59">
@@ -2850,37 +2848,37 @@
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
-        <v>-47.88692235000001</v>
+        <v>6.96574599</v>
       </c>
       <c r="D59" t="n">
-        <v>6.96574599</v>
+        <v>42.54732838</v>
       </c>
       <c r="E59" t="n">
-        <v>42.54732838</v>
+        <v>65.16556917</v>
       </c>
       <c r="F59" t="n">
-        <v>65.16556917</v>
+        <v>39.0396422</v>
       </c>
       <c r="G59" t="n">
-        <v>39.0396422</v>
+        <v>50.5705571</v>
       </c>
       <c r="H59" t="n">
-        <v>50.5705571</v>
+        <v>29.48116599</v>
       </c>
       <c r="I59" t="n">
-        <v>29.48116599</v>
+        <v>3.745202050000001</v>
       </c>
       <c r="J59" t="n">
-        <v>3.745202050000001</v>
+        <v>-27.11462849</v>
       </c>
       <c r="K59" t="n">
-        <v>-27.11462849</v>
+        <v>-14.54311404</v>
       </c>
       <c r="L59" t="n">
-        <v>-14.54311404</v>
+        <v>-20.20816677</v>
       </c>
       <c r="M59" t="n">
-        <v>-20.20816677</v>
+        <v>-48.84269329</v>
       </c>
     </row>
     <row r="60">
@@ -2891,37 +2889,37 @@
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
-        <v>-0.008696569999999999</v>
+        <v>0.0294527</v>
       </c>
       <c r="D60" t="n">
-        <v>0.0294527</v>
+        <v>0.02929013</v>
       </c>
       <c r="E60" t="n">
-        <v>0.02929013</v>
+        <v>0.00690925</v>
       </c>
       <c r="F60" t="n">
-        <v>0.00690925</v>
+        <v>-0.002395420000000002</v>
       </c>
       <c r="G60" t="n">
-        <v>-0.002395420000000002</v>
+        <v>0.0890145</v>
       </c>
       <c r="H60" t="n">
-        <v>0.0890145</v>
+        <v>0.02680047</v>
       </c>
       <c r="I60" t="n">
-        <v>0.02680047</v>
+        <v>0.03247147</v>
       </c>
       <c r="J60" t="n">
-        <v>0.03247147</v>
+        <v>0.03435918</v>
       </c>
       <c r="K60" t="n">
-        <v>0.03435918</v>
+        <v>0.0329061</v>
       </c>
       <c r="L60" t="n">
-        <v>0.0329061</v>
+        <v>-0.007547529999999998</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.007547529999999998</v>
+        <v>0.06462674</v>
       </c>
     </row>
     <row r="61">
@@ -2932,37 +2930,37 @@
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
-        <v>19.01627602</v>
+        <v>32.19605009</v>
       </c>
       <c r="D61" t="n">
-        <v>32.19641023</v>
+        <v>66.00294479</v>
       </c>
       <c r="E61" t="n">
-        <v>66.00317588999999</v>
+        <v>95.20210945000001</v>
       </c>
       <c r="F61" t="n">
-        <v>95.2021495</v>
+        <v>52.08635829</v>
       </c>
       <c r="G61" t="n">
-        <v>52.08626254999999</v>
+        <v>56.2651835</v>
       </c>
       <c r="H61" t="n">
-        <v>56.2650797</v>
+        <v>4.496421909999995</v>
       </c>
       <c r="I61" t="n">
-        <v>4.496617839999995</v>
+        <v>16.5218095</v>
       </c>
       <c r="J61" t="n">
-        <v>16.52188146</v>
+        <v>67.27009512000001</v>
       </c>
       <c r="K61" t="n">
-        <v>67.27001618000001</v>
+        <v>-16.92938799</v>
       </c>
       <c r="L61" t="n">
-        <v>-16.92923413</v>
+        <v>-37.98414687</v>
       </c>
       <c r="M61" t="n">
-        <v>-37.98425285</v>
+        <v>-34.65845204999999</v>
       </c>
     </row>
     <row r="62">
@@ -2971,39 +2969,41 @@
           <t>資訊服務業右下</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr"/>
+      <c r="B62" t="n">
+        <v>0</v>
+      </c>
       <c r="C62" t="n">
-        <v>-0.0062889</v>
+        <v>5.92041929</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.00268161</v>
+        <v>6.52392742</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.00248998</v>
+        <v>6.715422149999999</v>
       </c>
       <c r="F62" t="n">
-        <v>0.006524610000000001</v>
+        <v>5.812983760000001</v>
       </c>
       <c r="G62" t="n">
-        <v>0.00455783</v>
+        <v>3.00061214</v>
       </c>
       <c r="H62" t="n">
-        <v>0.0007480000000000001</v>
+        <v>-6.38541483</v>
       </c>
       <c r="I62" t="n">
-        <v>0.0090934</v>
+        <v>-9.712041819999998</v>
       </c>
       <c r="J62" t="n">
-        <v>0.01658377</v>
+        <v>-5.19174317</v>
       </c>
       <c r="K62" t="n">
-        <v>0.01830944</v>
+        <v>-4.46376258</v>
       </c>
       <c r="L62" t="n">
-        <v>0.01968591</v>
+        <v>-3.86283365</v>
       </c>
       <c r="M62" t="n">
-        <v>0.0123997</v>
+        <v>-4.498926060000001</v>
       </c>
     </row>
     <row r="63">
@@ -3014,37 +3014,37 @@
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>-2.453520489999999</v>
+        <v>22.72898805</v>
       </c>
       <c r="D63" t="n">
-        <v>28.65187051</v>
+        <v>41.13900461</v>
       </c>
       <c r="E63" t="n">
-        <v>47.66603411</v>
+        <v>88.15215049</v>
       </c>
       <c r="F63" t="n">
-        <v>94.86402831000001</v>
+        <v>40.93864671</v>
       </c>
       <c r="G63" t="n">
-        <v>46.74833786</v>
+        <v>38.24771547</v>
       </c>
       <c r="H63" t="n">
-        <v>41.24798834000001</v>
+        <v>23.4096762</v>
       </c>
       <c r="I63" t="n">
-        <v>17.01447163</v>
+        <v>28.16626605</v>
       </c>
       <c r="J63" t="n">
-        <v>18.43863869</v>
+        <v>35.37615519</v>
       </c>
       <c r="K63" t="n">
-        <v>30.1662141</v>
+        <v>33.8697661</v>
       </c>
       <c r="L63" t="n">
-        <v>29.38531994000001</v>
+        <v>2.50047791</v>
       </c>
       <c r="M63" t="n">
-        <v>-1.37473835</v>
+        <v>-18.08325091</v>
       </c>
     </row>
     <row r="64">
@@ -3055,37 +3055,37 @@
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
-        <v>0.00090755</v>
+        <v>0.00103174</v>
       </c>
       <c r="D64" t="n">
-        <v>0.00103174</v>
+        <v>0.0009914099999999999</v>
       </c>
       <c r="E64" t="n">
-        <v>0.0009914099999999999</v>
+        <v>6.247e-05</v>
       </c>
       <c r="F64" t="n">
-        <v>6.247e-05</v>
+        <v>0.0004044</v>
       </c>
       <c r="G64" t="n">
-        <v>0.0004044</v>
+        <v>0.00072251</v>
       </c>
       <c r="H64" t="n">
-        <v>0.00072251</v>
+        <v>-0.00025412</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.00025412</v>
+        <v>-0.00126824</v>
       </c>
       <c r="J64" t="n">
-        <v>-0.00126824</v>
+        <v>-0.00052996</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.00052996</v>
+        <v>-4.627e-05</v>
       </c>
       <c r="L64" t="n">
-        <v>-4.627e-05</v>
+        <v>0.00012135</v>
       </c>
       <c r="M64" t="n">
-        <v>0.00012135</v>
+        <v>0.00033795</v>
       </c>
     </row>
     <row r="65">
@@ -3096,37 +3096,37 @@
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
-        <v>-0.00027651</v>
+        <v>-0.0002609000000000001</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.0002609000000000001</v>
+        <v>5.814e-05</v>
       </c>
       <c r="E65" t="n">
-        <v>5.814e-05</v>
+        <v>0.00018835</v>
       </c>
       <c r="F65" t="n">
-        <v>0.00018835</v>
+        <v>2.243e-05</v>
       </c>
       <c r="G65" t="n">
-        <v>2.243e-05</v>
+        <v>-8.019e-05</v>
       </c>
       <c r="H65" t="n">
-        <v>-8.019e-05</v>
+        <v>-3.720999999999999e-05</v>
       </c>
       <c r="I65" t="n">
-        <v>-3.720999999999999e-05</v>
+        <v>-0.00012853</v>
       </c>
       <c r="J65" t="n">
-        <v>-0.00012853</v>
+        <v>-0.00011783</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.00011783</v>
+        <v>-0.00038662</v>
       </c>
       <c r="L65" t="n">
-        <v>-0.00038662</v>
+        <v>-0.00020338</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.00020338</v>
+        <v>2.062999999999999e-05</v>
       </c>
     </row>
     <row r="66">
@@ -3137,37 +3137,37 @@
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>250.33207424</v>
+        <v>-13.98078499000001</v>
       </c>
       <c r="D66" t="n">
-        <v>-71.43827585000001</v>
+        <v>113.82940649</v>
       </c>
       <c r="E66" t="n">
-        <v>74.57830126</v>
+        <v>602.97937943</v>
       </c>
       <c r="F66" t="n">
-        <v>587.52380249</v>
+        <v>164.30663862</v>
       </c>
       <c r="G66" t="n">
-        <v>153.62527904</v>
+        <v>478.95908781</v>
       </c>
       <c r="H66" t="n">
-        <v>484.36402765</v>
+        <v>548.0155602000001</v>
       </c>
       <c r="I66" t="n">
-        <v>563.4345118799999</v>
+        <v>805.81832688</v>
       </c>
       <c r="J66" t="n">
-        <v>827.86811563</v>
+        <v>824.0944196200001</v>
       </c>
       <c r="K66" t="n">
-        <v>851.1703980999999</v>
+        <v>1051.07870633</v>
       </c>
       <c r="L66" t="n">
-        <v>1079.83068439</v>
+        <v>1021.09156123</v>
       </c>
       <c r="M66" t="n">
-        <v>1041.36050229</v>
+        <v>919.67733936</v>
       </c>
     </row>
     <row r="67">
@@ -3176,39 +3176,41 @@
           <t>通信網路業右下</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr"/>
+      <c r="B67" t="n">
+        <v>0</v>
+      </c>
       <c r="C67" t="n">
-        <v>-53.14267139</v>
+        <v>14.35426651</v>
       </c>
       <c r="D67" t="n">
-        <v>-3.999420880000002</v>
+        <v>3.661172020000002</v>
       </c>
       <c r="E67" t="n">
-        <v>33.33771072</v>
+        <v>43.03769867</v>
       </c>
       <c r="F67" t="n">
-        <v>2.42355657</v>
+        <v>-32.84988569</v>
       </c>
       <c r="G67" t="n">
-        <v>1.51502225</v>
+        <v>-44.98339458</v>
       </c>
       <c r="H67" t="n">
-        <v>-43.93714867</v>
+        <v>-50.19198401999999</v>
       </c>
       <c r="I67" t="n">
-        <v>-27.1973517</v>
+        <v>-61.96146647</v>
       </c>
       <c r="J67" t="n">
-        <v>-8.63181679</v>
+        <v>-32.79786634</v>
       </c>
       <c r="K67" t="n">
-        <v>45.1348587</v>
+        <v>-12.77004483</v>
       </c>
       <c r="L67" t="n">
-        <v>-69.71877004</v>
+        <v>-10.69580253</v>
       </c>
       <c r="M67" t="n">
-        <v>42.06810895</v>
+        <v>-9.02277816</v>
       </c>
     </row>
     <row r="68">
@@ -3219,37 +3221,37 @@
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>331.44025787</v>
+        <v>355.56638351</v>
       </c>
       <c r="D68" t="n">
-        <v>431.3726510399999</v>
+        <v>226.21071599</v>
       </c>
       <c r="E68" t="n">
-        <v>235.76456954</v>
+        <v>227.09530235</v>
       </c>
       <c r="F68" t="n">
-        <v>283.16068275</v>
+        <v>195.49797504</v>
       </c>
       <c r="G68" t="n">
-        <v>171.8184034</v>
+        <v>22.10781184</v>
       </c>
       <c r="H68" t="n">
-        <v>15.65956619</v>
+        <v>71.51372678000001</v>
       </c>
       <c r="I68" t="n">
-        <v>33.10447479000002</v>
+        <v>26.37887649</v>
       </c>
       <c r="J68" t="n">
-        <v>-48.99889076</v>
+        <v>229.10723779</v>
       </c>
       <c r="K68" t="n">
-        <v>124.08845681</v>
+        <v>12.50703683999999</v>
       </c>
       <c r="L68" t="n">
-        <v>40.68521676999999</v>
+        <v>95.91743174000001</v>
       </c>
       <c r="M68" t="n">
-        <v>22.86860737</v>
+        <v>264.96250325</v>
       </c>
     </row>
     <row r="69">
@@ -3260,37 +3262,37 @@
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>-9.848016550000001</v>
+        <v>-11.75977663</v>
       </c>
       <c r="D69" t="n">
-        <v>-11.75977663</v>
+        <v>-14.45543988</v>
       </c>
       <c r="E69" t="n">
-        <v>-14.45543988</v>
+        <v>-8.60103045</v>
       </c>
       <c r="F69" t="n">
-        <v>-8.60103045</v>
+        <v>1.481096</v>
       </c>
       <c r="G69" t="n">
-        <v>1.481096</v>
+        <v>-2.09694106</v>
       </c>
       <c r="H69" t="n">
-        <v>-2.09694106</v>
+        <v>-1.18870531</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.18870531</v>
+        <v>0.8999840899999999</v>
       </c>
       <c r="J69" t="n">
-        <v>0.8999840899999999</v>
+        <v>-1.07992369</v>
       </c>
       <c r="K69" t="n">
-        <v>-1.07992369</v>
+        <v>-8.13542947</v>
       </c>
       <c r="L69" t="n">
-        <v>-8.13542947</v>
+        <v>-6.112742610000001</v>
       </c>
       <c r="M69" t="n">
-        <v>-6.112742610000001</v>
+        <v>0.62737845</v>
       </c>
     </row>
     <row r="70">
@@ -3301,37 +3303,37 @@
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>-4.06147909</v>
+        <v>-3.60733925</v>
       </c>
       <c r="D70" t="n">
-        <v>-3.60733925</v>
+        <v>-1.16033294</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.16033294</v>
+        <v>-1.55525517</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.55525517</v>
+        <v>0.15859867</v>
       </c>
       <c r="G70" t="n">
-        <v>0.15859867</v>
+        <v>-0.01651628</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.01651628</v>
+        <v>0.93115824</v>
       </c>
       <c r="I70" t="n">
-        <v>0.93115824</v>
+        <v>0.15324129</v>
       </c>
       <c r="J70" t="n">
-        <v>0.15324129</v>
+        <v>2.0141396</v>
       </c>
       <c r="K70" t="n">
-        <v>2.0141396</v>
+        <v>0.94456732</v>
       </c>
       <c r="L70" t="n">
-        <v>0.94456732</v>
+        <v>1.31059385</v>
       </c>
       <c r="M70" t="n">
-        <v>1.31059385</v>
+        <v>0.44808132</v>
       </c>
     </row>
     <row r="71">
@@ -3342,37 +3344,37 @@
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
-        <v>-6.985563310000001</v>
+        <v>6.14054282</v>
       </c>
       <c r="D71" t="n">
-        <v>6.14054282</v>
+        <v>22.89727625</v>
       </c>
       <c r="E71" t="n">
-        <v>22.89727625</v>
+        <v>39.58487804</v>
       </c>
       <c r="F71" t="n">
-        <v>39.58487804</v>
+        <v>49.03197814</v>
       </c>
       <c r="G71" t="n">
-        <v>49.03197814</v>
+        <v>20.29127258</v>
       </c>
       <c r="H71" t="n">
-        <v>20.29127258</v>
+        <v>24.00895878</v>
       </c>
       <c r="I71" t="n">
-        <v>24.00895878</v>
+        <v>34.17125779</v>
       </c>
       <c r="J71" t="n">
-        <v>34.17125779</v>
+        <v>-3.0706811</v>
       </c>
       <c r="K71" t="n">
-        <v>-3.0706811</v>
+        <v>-7.127004649999999</v>
       </c>
       <c r="L71" t="n">
-        <v>-7.127004649999999</v>
+        <v>-16.45539349</v>
       </c>
       <c r="M71" t="n">
-        <v>-16.45539349</v>
+        <v>-1.46575611</v>
       </c>
     </row>
     <row r="72">
@@ -3383,37 +3385,37 @@
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>-142.15576028</v>
+        <v>-103.65398381</v>
       </c>
       <c r="D72" t="n">
-        <v>-103.65398381</v>
+        <v>-29.97898556</v>
       </c>
       <c r="E72" t="n">
-        <v>-29.97898556</v>
+        <v>-20.96570658</v>
       </c>
       <c r="F72" t="n">
-        <v>-20.96570658</v>
+        <v>-82.82987403</v>
       </c>
       <c r="G72" t="n">
-        <v>-82.82987403</v>
+        <v>-117.56860161</v>
       </c>
       <c r="H72" t="n">
-        <v>-117.56860161</v>
+        <v>-41.76354069999999</v>
       </c>
       <c r="I72" t="n">
-        <v>-41.76354069999999</v>
+        <v>-96.87037564000001</v>
       </c>
       <c r="J72" t="n">
-        <v>-96.87037564000001</v>
+        <v>-62.8772119</v>
       </c>
       <c r="K72" t="n">
-        <v>-62.8772119</v>
+        <v>-12.82282402</v>
       </c>
       <c r="L72" t="n">
-        <v>-12.82282402</v>
+        <v>98.85202981</v>
       </c>
       <c r="M72" t="n">
-        <v>98.85202981</v>
+        <v>106.34325255</v>
       </c>
     </row>
     <row r="73">
@@ -3424,37 +3426,37 @@
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
-        <v>-10.30417954</v>
+        <v>1.9869591</v>
       </c>
       <c r="D73" t="n">
-        <v>1.9869591</v>
+        <v>13.19129905</v>
       </c>
       <c r="E73" t="n">
-        <v>13.19129905</v>
+        <v>5.14271512</v>
       </c>
       <c r="F73" t="n">
-        <v>5.14271512</v>
+        <v>-8.77292924</v>
       </c>
       <c r="G73" t="n">
-        <v>-8.77292924</v>
+        <v>-8.96068459</v>
       </c>
       <c r="H73" t="n">
-        <v>-8.96068459</v>
+        <v>-20.04120091</v>
       </c>
       <c r="I73" t="n">
-        <v>-20.04120091</v>
+        <v>-30.54986415</v>
       </c>
       <c r="J73" t="n">
-        <v>-30.54986415</v>
+        <v>-15.30492149</v>
       </c>
       <c r="K73" t="n">
-        <v>-15.30492149</v>
+        <v>-8.88836045</v>
       </c>
       <c r="L73" t="n">
-        <v>-8.88836045</v>
+        <v>20.78246032</v>
       </c>
       <c r="M73" t="n">
-        <v>20.78246032</v>
+        <v>-2.68761685</v>
       </c>
     </row>
     <row r="74">
@@ -3465,37 +3467,37 @@
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
-        <v>-1045.54821239</v>
+        <v>99.09603653999999</v>
       </c>
       <c r="D74" t="n">
-        <v>36.53091295999999</v>
+        <v>970.65146917</v>
       </c>
       <c r="E74" t="n">
-        <v>989.596008</v>
+        <v>884.16237317</v>
       </c>
       <c r="F74" t="n">
-        <v>825.6772632999999</v>
+        <v>1255.32413101</v>
       </c>
       <c r="G74" t="n">
-        <v>1184.45386557</v>
+        <v>874.8045002699999</v>
       </c>
       <c r="H74" t="n">
-        <v>782.34708296</v>
+        <v>707.7305493600001</v>
       </c>
       <c r="I74" t="n">
-        <v>678.97440725</v>
+        <v>679.97336817</v>
       </c>
       <c r="J74" t="n">
-        <v>691.18475741</v>
+        <v>678.9577422699999</v>
       </c>
       <c r="K74" t="n">
-        <v>679.2821239900001</v>
+        <v>924.3511551399999</v>
       </c>
       <c r="L74" t="n">
-        <v>973.4732171100001</v>
+        <v>1354.0773804</v>
       </c>
       <c r="M74" t="n">
-        <v>1410.22305646</v>
+        <v>461.03885747</v>
       </c>
     </row>
     <row r="75">
@@ -3504,41 +3506,39 @@
           <t>金融保險右下</t>
         </is>
       </c>
-      <c r="B75" t="n">
-        <v>0</v>
-      </c>
+      <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
-        <v>-396.96136286</v>
+        <v>-349.0558786799999</v>
       </c>
       <c r="D75" t="n">
-        <v>-349.51439723</v>
+        <v>-118.99593187</v>
       </c>
       <c r="E75" t="n">
-        <v>-120.88432679</v>
+        <v>72.75089683</v>
       </c>
       <c r="F75" t="n">
-        <v>70.24992944999998</v>
+        <v>167.55188173</v>
       </c>
       <c r="G75" t="n">
-        <v>163.48480356</v>
+        <v>-31.46257298</v>
       </c>
       <c r="H75" t="n">
-        <v>-31.57288105</v>
+        <v>-219.97600686</v>
       </c>
       <c r="I75" t="n">
-        <v>-217.97355836</v>
+        <v>-384.3325941999999</v>
       </c>
       <c r="J75" t="n">
-        <v>-383.48576996</v>
+        <v>-513.9571076200001</v>
       </c>
       <c r="K75" t="n">
-        <v>-511.4676543900001</v>
+        <v>-257.99615698</v>
       </c>
       <c r="L75" t="n">
-        <v>-257.62854329</v>
+        <v>-17.04792302</v>
       </c>
       <c r="M75" t="n">
-        <v>-17.70767385</v>
+        <v>-66.68232792000001</v>
       </c>
     </row>
     <row r="76">
@@ -3549,37 +3549,37 @@
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>9.95605207</v>
+        <v>-12.31874343</v>
       </c>
       <c r="D76" t="n">
-        <v>36.61192854999999</v>
+        <v>91.65456542</v>
       </c>
       <c r="E76" t="n">
-        <v>60.44058554</v>
+        <v>2.117843309999998</v>
       </c>
       <c r="F76" t="n">
-        <v>51.94475127</v>
+        <v>-1.871264110000001</v>
       </c>
       <c r="G76" t="n">
-        <v>70.27664334000001</v>
+        <v>-27.58568966</v>
       </c>
       <c r="H76" t="n">
-        <v>55.08727028</v>
+        <v>10.96223872</v>
       </c>
       <c r="I76" t="n">
-        <v>34.91612823</v>
+        <v>47.73662943</v>
       </c>
       <c r="J76" t="n">
-        <v>40.48346314</v>
+        <v>37.80555489</v>
       </c>
       <c r="K76" t="n">
-        <v>47.28463428</v>
+        <v>60.24445445000001</v>
       </c>
       <c r="L76" t="n">
-        <v>42.36202298000001</v>
+        <v>75.68165750999999</v>
       </c>
       <c r="M76" t="n">
-        <v>45.27166862000001</v>
+        <v>33.39518098</v>
       </c>
     </row>
     <row r="77">
@@ -3590,37 +3590,37 @@
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="n">
-        <v>-0.00072667</v>
+        <v>-0.00031853</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.00031853</v>
+        <v>-0.00042214</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.00042214</v>
+        <v>0.00035191</v>
       </c>
       <c r="F77" t="n">
-        <v>0.00035191</v>
+        <v>0.0006016</v>
       </c>
       <c r="G77" t="n">
-        <v>0.0006016</v>
+        <v>0.00119589</v>
       </c>
       <c r="H77" t="n">
-        <v>0.00119589</v>
+        <v>0.00222055</v>
       </c>
       <c r="I77" t="n">
-        <v>0.00222055</v>
+        <v>0.00226234</v>
       </c>
       <c r="J77" t="n">
-        <v>0.00226234</v>
+        <v>0.00101082</v>
       </c>
       <c r="K77" t="n">
-        <v>0.00101082</v>
+        <v>9.988e-05</v>
       </c>
       <c r="L77" t="n">
-        <v>9.988e-05</v>
+        <v>0.00032912</v>
       </c>
       <c r="M77" t="n">
-        <v>0.00032912</v>
+        <v>-0.00052438</v>
       </c>
     </row>
     <row r="78">
@@ -3631,37 +3631,37 @@
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
-        <v>-0.00439828</v>
+        <v>-0.005935770000000001</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.005935770000000001</v>
+        <v>-0.006376339999999999</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.006376339999999999</v>
+        <v>-0.00146164</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.00146164</v>
+        <v>0.0001785999999999999</v>
       </c>
       <c r="G78" t="n">
-        <v>0.0001785999999999999</v>
+        <v>0.00166505</v>
       </c>
       <c r="H78" t="n">
-        <v>0.00166505</v>
+        <v>0.00481058</v>
       </c>
       <c r="I78" t="n">
-        <v>0.00481058</v>
+        <v>0.00272902</v>
       </c>
       <c r="J78" t="n">
-        <v>0.00272902</v>
+        <v>9.011000000000007e-05</v>
       </c>
       <c r="K78" t="n">
-        <v>9.011000000000007e-05</v>
+        <v>0.0004795100000000002</v>
       </c>
       <c r="L78" t="n">
-        <v>0.0004795100000000002</v>
+        <v>0.00329986</v>
       </c>
       <c r="M78" t="n">
-        <v>0.00329986</v>
+        <v>0.0005099499999999999</v>
       </c>
     </row>
     <row r="79">
@@ -3672,37 +3672,37 @@
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="n">
-        <v>-0.00052038</v>
+        <v>-0.00049876</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.00049876</v>
+        <v>-0.00010349</v>
       </c>
       <c r="E79" t="n">
-        <v>-0.00010349</v>
+        <v>0.00149008</v>
       </c>
       <c r="F79" t="n">
-        <v>0.00149008</v>
+        <v>0.00167124</v>
       </c>
       <c r="G79" t="n">
-        <v>0.00167124</v>
+        <v>0.00103193</v>
       </c>
       <c r="H79" t="n">
-        <v>0.00103193</v>
+        <v>0.00057835</v>
       </c>
       <c r="I79" t="n">
-        <v>0.00057835</v>
+        <v>9.465e-05</v>
       </c>
       <c r="J79" t="n">
-        <v>9.465e-05</v>
+        <v>0.00013897</v>
       </c>
       <c r="K79" t="n">
-        <v>0.00013897</v>
+        <v>6.415e-05</v>
       </c>
       <c r="L79" t="n">
-        <v>6.415e-05</v>
+        <v>-0.00029419</v>
       </c>
       <c r="M79" t="n">
-        <v>-0.00029419</v>
+        <v>0.00019073</v>
       </c>
     </row>
     <row r="80">
@@ -3713,37 +3713,37 @@
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="n">
-        <v>0.3745234199999999</v>
+        <v>-13.08952523</v>
       </c>
       <c r="D80" t="n">
-        <v>-13.08952523</v>
+        <v>-4.331212519999999</v>
       </c>
       <c r="E80" t="n">
-        <v>-4.331212519999999</v>
+        <v>-10.25827174</v>
       </c>
       <c r="F80" t="n">
-        <v>-10.25827174</v>
+        <v>8.421552140000001</v>
       </c>
       <c r="G80" t="n">
-        <v>8.421552140000001</v>
+        <v>-10.13260721</v>
       </c>
       <c r="H80" t="n">
-        <v>-10.13260721</v>
+        <v>-9.68964107</v>
       </c>
       <c r="I80" t="n">
-        <v>-9.68964107</v>
+        <v>4.868124629999999</v>
       </c>
       <c r="J80" t="n">
-        <v>4.868124629999999</v>
+        <v>12.18883922</v>
       </c>
       <c r="K80" t="n">
-        <v>12.18883922</v>
+        <v>-4.46799539</v>
       </c>
       <c r="L80" t="n">
-        <v>-4.46799539</v>
+        <v>12.58299348</v>
       </c>
       <c r="M80" t="n">
-        <v>12.58299348</v>
+        <v>17.39570309</v>
       </c>
     </row>
     <row r="81">
@@ -3754,37 +3754,37 @@
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>-59.96519444</v>
+        <v>-88.87504158</v>
       </c>
       <c r="D81" t="n">
-        <v>-91.76253054999999</v>
+        <v>-103.34398829</v>
       </c>
       <c r="E81" t="n">
-        <v>-106.78732313</v>
+        <v>-57.69436082</v>
       </c>
       <c r="F81" t="n">
-        <v>-61.14927203</v>
+        <v>-41.13783873999999</v>
       </c>
       <c r="G81" t="n">
-        <v>-43.25431434999999</v>
+        <v>-58.76555155999999</v>
       </c>
       <c r="H81" t="n">
-        <v>-61.35135943</v>
+        <v>-40.17196165999999</v>
       </c>
       <c r="I81" t="n">
-        <v>-43.05485222999999</v>
+        <v>-13.61398708</v>
       </c>
       <c r="J81" t="n">
-        <v>-16.93515817</v>
+        <v>34.26378235</v>
       </c>
       <c r="K81" t="n">
-        <v>31.37983951</v>
+        <v>102.02552729</v>
       </c>
       <c r="L81" t="n">
-        <v>99.07407704000001</v>
+        <v>136.86135343</v>
       </c>
       <c r="M81" t="n">
-        <v>135.88498667</v>
+        <v>238.22024326</v>
       </c>
     </row>
     <row r="82">
@@ -3795,37 +3795,37 @@
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
-        <v>233.01628127</v>
+        <v>-9.090035719999999</v>
       </c>
       <c r="D82" t="n">
-        <v>-6.20254675</v>
+        <v>90.6906401</v>
       </c>
       <c r="E82" t="n">
-        <v>94.13397494</v>
+        <v>-57.32605929</v>
       </c>
       <c r="F82" t="n">
-        <v>-53.87114807999998</v>
+        <v>-1.928089060000002</v>
       </c>
       <c r="G82" t="n">
-        <v>0.1883865500000045</v>
+        <v>-172.96841672</v>
       </c>
       <c r="H82" t="n">
-        <v>-170.38260885</v>
+        <v>92.52847485000001</v>
       </c>
       <c r="I82" t="n">
-        <v>95.41136542</v>
+        <v>-155.45915989</v>
       </c>
       <c r="J82" t="n">
-        <v>-152.1379888</v>
+        <v>-345.22323058</v>
       </c>
       <c r="K82" t="n">
-        <v>-342.33928774</v>
+        <v>-548.90999019</v>
       </c>
       <c r="L82" t="n">
-        <v>-545.95853994</v>
+        <v>-281.94185764</v>
       </c>
       <c r="M82" t="n">
-        <v>-280.96549088</v>
+        <v>-159.52405027</v>
       </c>
     </row>
     <row r="83">
@@ -3836,37 +3836,37 @@
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>-19.23454711</v>
+        <v>-6.688197980000001</v>
       </c>
       <c r="D83" t="n">
-        <v>-23.25895899</v>
+        <v>39.15618257</v>
       </c>
       <c r="E83" t="n">
-        <v>27.87323952</v>
+        <v>88.37693567999999</v>
       </c>
       <c r="F83" t="n">
-        <v>82.35941356999999</v>
+        <v>173.80208869</v>
       </c>
       <c r="G83" t="n">
-        <v>181.83515722</v>
+        <v>68.31111571000001</v>
       </c>
       <c r="H83" t="n">
-        <v>68.08952595000001</v>
+        <v>-15.21283794</v>
       </c>
       <c r="I83" t="n">
-        <v>-20.36797773</v>
+        <v>-17.71552102</v>
       </c>
       <c r="J83" t="n">
-        <v>-20.03139617</v>
+        <v>-64.05499739</v>
       </c>
       <c r="K83" t="n">
-        <v>-59.64161756</v>
+        <v>-108.28490628</v>
       </c>
       <c r="L83" t="n">
-        <v>-112.75539681</v>
+        <v>17.23501362</v>
       </c>
       <c r="M83" t="n">
-        <v>64.56145398</v>
+        <v>-42.91166961</v>
       </c>
     </row>
     <row r="84">
@@ -3877,37 +3877,37 @@
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
-        <v>-116.03762182</v>
+        <v>-143.58805289</v>
       </c>
       <c r="D84" t="n">
-        <v>-143.58805289</v>
+        <v>-122.466744</v>
       </c>
       <c r="E84" t="n">
-        <v>-122.466744</v>
+        <v>-54.09112768000001</v>
       </c>
       <c r="F84" t="n">
-        <v>-54.09112768000001</v>
+        <v>-10.37811915</v>
       </c>
       <c r="G84" t="n">
-        <v>-10.37811915</v>
+        <v>20.72728843</v>
       </c>
       <c r="H84" t="n">
-        <v>20.72728843</v>
+        <v>50.52973096</v>
       </c>
       <c r="I84" t="n">
-        <v>50.52973096</v>
+        <v>20.65790564</v>
       </c>
       <c r="J84" t="n">
-        <v>20.65790564</v>
+        <v>39.26255287</v>
       </c>
       <c r="K84" t="n">
-        <v>39.26255287</v>
+        <v>82.85629460000001</v>
       </c>
       <c r="L84" t="n">
-        <v>82.85629460000001</v>
+        <v>154.58928851</v>
       </c>
       <c r="M84" t="n">
-        <v>154.58928851</v>
+        <v>58.48154729</v>
       </c>
     </row>
     <row r="85">
@@ -3918,37 +3918,37 @@
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>-2.92089428</v>
+        <v>-22.44689371</v>
       </c>
       <c r="D85" t="n">
-        <v>-5.86579375</v>
+        <v>-6.50824927</v>
       </c>
       <c r="E85" t="n">
-        <v>4.65700348</v>
+        <v>10.56656311</v>
       </c>
       <c r="F85" t="n">
-        <v>16.5811829</v>
+        <v>91.63783333999999</v>
       </c>
       <c r="G85" t="n">
-        <v>83.55010430999998</v>
+        <v>307.9548405900001</v>
       </c>
       <c r="H85" t="n">
-        <v>308.21784694</v>
+        <v>127.08587257</v>
       </c>
       <c r="I85" t="n">
-        <v>132.33488342</v>
+        <v>35.53888427</v>
       </c>
       <c r="J85" t="n">
-        <v>37.83571189</v>
+        <v>-44.52397537</v>
       </c>
       <c r="K85" t="n">
-        <v>-48.80012199</v>
+        <v>-80.50543233</v>
       </c>
       <c r="L85" t="n">
-        <v>-75.86895855</v>
+        <v>17.37158543</v>
       </c>
       <c r="M85" t="n">
-        <v>-29.96102533</v>
+        <v>-21.99522969</v>
       </c>
     </row>
     <row r="86">
@@ -3959,37 +3959,37 @@
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
-        <v>38.98186654</v>
+        <v>39.92671712</v>
       </c>
       <c r="D86" t="n">
-        <v>40.09386715</v>
+        <v>-7.647300829999998</v>
       </c>
       <c r="E86" t="n">
-        <v>-9.095698099999998</v>
+        <v>40.5057899</v>
       </c>
       <c r="F86" t="n">
-        <v>37.72812831</v>
+        <v>0.2115746600000012</v>
       </c>
       <c r="G86" t="n">
-        <v>-0.83850737</v>
+        <v>-73.51357708</v>
       </c>
       <c r="H86" t="n">
-        <v>-72.60341334</v>
+        <v>-120.38293081</v>
       </c>
       <c r="I86" t="n">
-        <v>-119.0016073</v>
+        <v>-28.81328676999999</v>
       </c>
       <c r="J86" t="n">
-        <v>-26.60613834</v>
+        <v>26.42893274</v>
       </c>
       <c r="K86" t="n">
-        <v>29.60181823</v>
+        <v>-19.94011926</v>
       </c>
       <c r="L86" t="n">
-        <v>-17.02849766</v>
+        <v>-44.01715513000001</v>
       </c>
       <c r="M86" t="n">
-        <v>-43.48588267</v>
+        <v>-47.84157947</v>
       </c>
     </row>
     <row r="87">
@@ -3998,41 +3998,39 @@
           <t>電子通路業右下</t>
         </is>
       </c>
-      <c r="B87" t="n">
-        <v>0</v>
-      </c>
+      <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>-26.54348754</v>
+        <v>-33.26785071</v>
       </c>
       <c r="D87" t="n">
-        <v>-11.71257476</v>
+        <v>6.899450400000001</v>
       </c>
       <c r="E87" t="n">
-        <v>27.59073005</v>
+        <v>66.94732356</v>
       </c>
       <c r="F87" t="n">
-        <v>78.17267982999999</v>
+        <v>15.18315901</v>
       </c>
       <c r="G87" t="n">
-        <v>25.51373005999999</v>
+        <v>-4.35202075</v>
       </c>
       <c r="H87" t="n">
-        <v>0.2366620999999996</v>
+        <v>-68.57304669</v>
       </c>
       <c r="I87" t="n">
-        <v>-61.34817928</v>
+        <v>-151.21501754</v>
       </c>
       <c r="J87" t="n">
-        <v>-142.1284039</v>
+        <v>-178.71603407</v>
       </c>
       <c r="K87" t="n">
-        <v>-170.64885988</v>
+        <v>-165.20199526</v>
       </c>
       <c r="L87" t="n">
-        <v>-163.99588027</v>
+        <v>-124.5411635</v>
       </c>
       <c r="M87" t="n">
-        <v>-129.46133087</v>
+        <v>-106.78033262</v>
       </c>
     </row>
     <row r="88">
@@ -4043,37 +4041,37 @@
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
-        <v>-53.04379301000001</v>
+        <v>6.661907179999998</v>
       </c>
       <c r="D88" t="n">
-        <v>-14.89313461</v>
+        <v>34.88464354</v>
       </c>
       <c r="E88" t="n">
-        <v>14.19245187</v>
+        <v>67.06029259</v>
       </c>
       <c r="F88" t="n">
-        <v>55.83540987999999</v>
+        <v>108.11180131</v>
       </c>
       <c r="G88" t="n">
-        <v>97.78185421000001</v>
+        <v>65.92950389000001</v>
       </c>
       <c r="H88" t="n">
-        <v>61.34033204</v>
+        <v>2.10840591</v>
       </c>
       <c r="I88" t="n">
-        <v>-5.116433789999999</v>
+        <v>-24.75203363</v>
       </c>
       <c r="J88" t="n">
-        <v>-33.83837391</v>
+        <v>-0.5570340900000017</v>
       </c>
       <c r="K88" t="n">
-        <v>-8.624214240000002</v>
+        <v>-23.51860179</v>
       </c>
       <c r="L88" t="n">
-        <v>-24.72450772</v>
+        <v>-45.03233113</v>
       </c>
       <c r="M88" t="n">
-        <v>-40.11228814</v>
+        <v>-38.22943602</v>
       </c>
     </row>
     <row r="89">
@@ -4084,37 +4082,37 @@
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>2038.44906293</v>
+        <v>2783.39345016</v>
       </c>
       <c r="D89" t="n">
-        <v>2785.71638693</v>
+        <v>215.5806035</v>
       </c>
       <c r="E89" t="n">
-        <v>256.3811546599999</v>
+        <v>2982.67742872</v>
       </c>
       <c r="F89" t="n">
-        <v>2728.14862403</v>
+        <v>1180.78229041</v>
       </c>
       <c r="G89" t="n">
-        <v>891.30276728</v>
+        <v>793.649512</v>
       </c>
       <c r="H89" t="n">
-        <v>578.0957584399999</v>
+        <v>3437.09900703</v>
       </c>
       <c r="I89" t="n">
-        <v>3081.26991417</v>
+        <v>5003.80231401</v>
       </c>
       <c r="J89" t="n">
-        <v>4608.10840054</v>
+        <v>4907.06809745</v>
       </c>
       <c r="K89" t="n">
-        <v>4483.77360107</v>
+        <v>5011.02327398</v>
       </c>
       <c r="L89" t="n">
-        <v>4805.35057671</v>
+        <v>4978.62790089</v>
       </c>
       <c r="M89" t="n">
-        <v>4850.32089056</v>
+        <v>3566.86714986</v>
       </c>
     </row>
     <row r="90">
@@ -4127,37 +4125,37 @@
         <v>0</v>
       </c>
       <c r="C90" t="n">
-        <v>63.05614875</v>
+        <v>114.871394</v>
       </c>
       <c r="D90" t="n">
-        <v>132.60557728</v>
+        <v>-321.46475975</v>
       </c>
       <c r="E90" t="n">
-        <v>-316.23102769</v>
+        <v>-259.42360324</v>
       </c>
       <c r="F90" t="n">
-        <v>-262.6704543</v>
+        <v>-580.3061901999999</v>
       </c>
       <c r="G90" t="n">
-        <v>-588.15370719</v>
+        <v>-464.38819778</v>
       </c>
       <c r="H90" t="n">
-        <v>-470.1614567600001</v>
+        <v>-366.0556037000001</v>
       </c>
       <c r="I90" t="n">
-        <v>-391.8065920600001</v>
+        <v>-5.243127309999995</v>
       </c>
       <c r="J90" t="n">
-        <v>-8.160727069999995</v>
+        <v>-354.20319953</v>
       </c>
       <c r="K90" t="n">
-        <v>-372.95276079</v>
+        <v>-784.57410473</v>
       </c>
       <c r="L90" t="n">
-        <v>-770.85714174</v>
+        <v>-1020.75804413</v>
       </c>
       <c r="M90" t="n">
-        <v>-997.24055418</v>
+        <v>-1127.69522433</v>
       </c>
     </row>
     <row r="91">
@@ -4168,37 +4166,37 @@
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>-598.01506698</v>
+        <v>-449.80729223</v>
       </c>
       <c r="D91" t="n">
-        <v>-463.1810605500001</v>
+        <v>-359.9600526300001</v>
       </c>
       <c r="E91" t="n">
-        <v>-367.85249305</v>
+        <v>103.40258845</v>
       </c>
       <c r="F91" t="n">
-        <v>89.34465401999999</v>
+        <v>-493.07000123</v>
       </c>
       <c r="G91" t="n">
-        <v>-502.57170582</v>
+        <v>-510.84168123</v>
       </c>
       <c r="H91" t="n">
-        <v>-511.83975142</v>
+        <v>-517.89728523</v>
       </c>
       <c r="I91" t="n">
-        <v>-525.44626108</v>
+        <v>-284.9405972600001</v>
       </c>
       <c r="J91" t="n">
-        <v>-295.0103615800001</v>
+        <v>-583.04451753</v>
       </c>
       <c r="K91" t="n">
-        <v>-595.9723830899999</v>
+        <v>-797.12358419</v>
       </c>
       <c r="L91" t="n">
-        <v>-822.08477513</v>
+        <v>-998.21052736</v>
       </c>
       <c r="M91" t="n">
-        <v>-1012.76483221</v>
+        <v>-991.88876777</v>
       </c>
     </row>
     <row r="92">
@@ -4209,37 +4207,37 @@
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>205.8542734999999</v>
+        <v>327.53786522</v>
       </c>
       <c r="D92" t="n">
-        <v>327.38565675</v>
+        <v>-1136.41872908</v>
       </c>
       <c r="E92" t="n">
-        <v>-1143.72705722</v>
+        <v>-1245.16251958</v>
       </c>
       <c r="F92" t="n">
-        <v>-1241.52012397</v>
+        <v>-443.0947849599999</v>
       </c>
       <c r="G92" t="n">
-        <v>-435.94781424</v>
+        <v>793.4250831000001</v>
       </c>
       <c r="H92" t="n">
-        <v>802.00610026</v>
+        <v>-164.21426872</v>
       </c>
       <c r="I92" t="n">
-        <v>-162.91159181</v>
+        <v>31.72998852999997</v>
       </c>
       <c r="J92" t="n">
-        <v>58.85484111999997</v>
+        <v>-1157.49170408</v>
       </c>
       <c r="K92" t="n">
-        <v>-1144.83488959</v>
+        <v>-9.335778799999908</v>
       </c>
       <c r="L92" t="n">
-        <v>-20.02801225999992</v>
+        <v>-123.20143785</v>
       </c>
       <c r="M92" t="n">
-        <v>-124.56689696</v>
+        <v>-443.73774572</v>
       </c>
     </row>
     <row r="93">
@@ -4252,37 +4250,37 @@
         <v>0</v>
       </c>
       <c r="C93" t="n">
-        <v>-41.80469665</v>
+        <v>-54.44380702</v>
       </c>
       <c r="D93" t="n">
-        <v>-54.58697853000002</v>
+        <v>-153.00815105</v>
       </c>
       <c r="E93" t="n">
-        <v>-153.18902274</v>
+        <v>0.6957613299999942</v>
       </c>
       <c r="F93" t="n">
-        <v>0.4190695899999994</v>
+        <v>-106.30556185</v>
       </c>
       <c r="G93" t="n">
-        <v>-106.67094956</v>
+        <v>7.431064629999999</v>
       </c>
       <c r="H93" t="n">
-        <v>7.079586339999998</v>
+        <v>98.67010714000001</v>
       </c>
       <c r="I93" t="n">
-        <v>98.30620274</v>
+        <v>68.31838794000001</v>
       </c>
       <c r="J93" t="n">
-        <v>68.03748563000001</v>
+        <v>-16.79744466</v>
       </c>
       <c r="K93" t="n">
-        <v>-16.9830704</v>
+        <v>-136.91026723</v>
       </c>
       <c r="L93" t="n">
-        <v>-136.75676583</v>
+        <v>-78.38075546</v>
       </c>
       <c r="M93" t="n">
-        <v>-78.07750962</v>
+        <v>3.436960939999999</v>
       </c>
     </row>
     <row r="94">
@@ -4293,37 +4291,37 @@
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>-42.78836988</v>
+        <v>40.82373081999999</v>
       </c>
       <c r="D94" t="n">
-        <v>40.97733781</v>
+        <v>183.67215091</v>
       </c>
       <c r="E94" t="n">
-        <v>190.98204855</v>
+        <v>131.83445524</v>
       </c>
       <c r="F94" t="n">
-        <v>128.19425933</v>
+        <v>181.39244916</v>
       </c>
       <c r="G94" t="n">
-        <v>174.24608435</v>
+        <v>211.46973347</v>
       </c>
       <c r="H94" t="n">
-        <v>202.88977693</v>
+        <v>111.55350454</v>
       </c>
       <c r="I94" t="n">
-        <v>110.25258585</v>
+        <v>-2.048849939999999</v>
       </c>
       <c r="J94" t="n">
-        <v>-29.17319449</v>
+        <v>86.89526453000002</v>
       </c>
       <c r="K94" t="n">
-        <v>74.23763863000001</v>
+        <v>78.12434784</v>
       </c>
       <c r="L94" t="n">
-        <v>88.81858175000001</v>
+        <v>156.91687895</v>
       </c>
       <c r="M94" t="n">
-        <v>158.29159538</v>
+        <v>211.45213399</v>
       </c>
     </row>
     <row r="95">
@@ -4334,37 +4332,37 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>3069.92118107</v>
+        <v>2685.65049112</v>
       </c>
       <c r="D95" t="n">
-        <v>2772.51594402</v>
+        <v>401.66842728</v>
       </c>
       <c r="E95" t="n">
-        <v>522.01829603</v>
+        <v>4009.46578054</v>
       </c>
       <c r="F95" t="n">
-        <v>4092.9784752</v>
+        <v>1730.40432885</v>
       </c>
       <c r="G95" t="n">
-        <v>1839.50387616</v>
+        <v>2569.44557358</v>
       </c>
       <c r="H95" t="n">
-        <v>2663.72581026</v>
+        <v>3376.77160564</v>
       </c>
       <c r="I95" t="n">
-        <v>3439.29967521</v>
+        <v>2916.05091773</v>
       </c>
       <c r="J95" t="n">
-        <v>2967.03286289</v>
+        <v>409.17178916</v>
       </c>
       <c r="K95" t="n">
-        <v>494.5037238999999</v>
+        <v>-3393.207893069999</v>
       </c>
       <c r="L95" t="n">
-        <v>-3248.73856866</v>
+        <v>-3802.88474447</v>
       </c>
       <c r="M95" t="n">
-        <v>-3663.00266384</v>
+        <v>-3113.12340659</v>
       </c>
     </row>
     <row r="96">
@@ -4373,41 +4371,39 @@
           <t>電腦及週邊設備業右下</t>
         </is>
       </c>
-      <c r="B96" t="n">
-        <v>0</v>
-      </c>
+      <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>-80.75298205000001</v>
+        <v>-34.4090199</v>
       </c>
       <c r="D96" t="n">
-        <v>-35.26515296</v>
+        <v>40.3709417</v>
       </c>
       <c r="E96" t="n">
-        <v>34.77748791999999</v>
+        <v>304.38397094</v>
       </c>
       <c r="F96" t="n">
-        <v>293.59366812</v>
+        <v>36.22071315</v>
       </c>
       <c r="G96" t="n">
-        <v>29.92595504</v>
+        <v>-20.63448973000001</v>
       </c>
       <c r="H96" t="n">
-        <v>-25.21789619</v>
+        <v>-317.5745386</v>
       </c>
       <c r="I96" t="n">
-        <v>-321.77418277</v>
+        <v>-538.8407471</v>
       </c>
       <c r="J96" t="n">
-        <v>-540.40644423</v>
+        <v>-573.10052565</v>
       </c>
       <c r="K96" t="n">
-        <v>-566.6008404099999</v>
+        <v>-620.52603838</v>
       </c>
       <c r="L96" t="n">
-        <v>-627.43372863</v>
+        <v>-630.9166388</v>
       </c>
       <c r="M96" t="n">
-        <v>-611.38368559</v>
+        <v>-429.82889656</v>
       </c>
     </row>
     <row r="97">
@@ -4418,37 +4414,37 @@
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>-0.04517477999999512</v>
+        <v>30.80699172</v>
       </c>
       <c r="D97" t="n">
-        <v>31.65996122</v>
+        <v>-70.12666147</v>
       </c>
       <c r="E97" t="n">
-        <v>-64.52826116</v>
+        <v>96.46264479000001</v>
       </c>
       <c r="F97" t="n">
-        <v>107.23571659</v>
+        <v>-5.302429040000006</v>
       </c>
       <c r="G97" t="n">
-        <v>1.012414459999993</v>
+        <v>102.72488865</v>
       </c>
       <c r="H97" t="n">
-        <v>107.27069085</v>
+        <v>36.21586944999999</v>
       </c>
       <c r="I97" t="n">
-        <v>40.39906092</v>
+        <v>102.26942867</v>
       </c>
       <c r="J97" t="n">
-        <v>103.86640705</v>
+        <v>-99.61859397999999</v>
       </c>
       <c r="K97" t="n">
-        <v>-106.11815169</v>
+        <v>-38.74008789000001</v>
       </c>
       <c r="L97" t="n">
-        <v>-31.75523302000001</v>
+        <v>-184.17612756</v>
       </c>
       <c r="M97" t="n">
-        <v>-203.67266775</v>
+        <v>-330.8791778300001</v>
       </c>
     </row>
     <row r="98">
@@ -4459,37 +4455,37 @@
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
-        <v>-20.82516393</v>
+        <v>-15.11263473</v>
       </c>
       <c r="D98" t="n">
-        <v>-15.11263473</v>
+        <v>2.57676404</v>
       </c>
       <c r="E98" t="n">
-        <v>2.57676404</v>
+        <v>17.61770092</v>
       </c>
       <c r="F98" t="n">
-        <v>17.61770092</v>
+        <v>27.36522565</v>
       </c>
       <c r="G98" t="n">
-        <v>27.36522565</v>
+        <v>21.462162</v>
       </c>
       <c r="H98" t="n">
-        <v>21.462162</v>
+        <v>2.43355516</v>
       </c>
       <c r="I98" t="n">
-        <v>2.43355516</v>
+        <v>3.428873750000001</v>
       </c>
       <c r="J98" t="n">
-        <v>3.428873750000001</v>
+        <v>20.06785335</v>
       </c>
       <c r="K98" t="n">
-        <v>20.06785335</v>
+        <v>29.26245925</v>
       </c>
       <c r="L98" t="n">
-        <v>29.26245925</v>
+        <v>17.23702606</v>
       </c>
       <c r="M98" t="n">
-        <v>17.23702606</v>
+        <v>24.66836485</v>
       </c>
     </row>
     <row r="99">
@@ -4500,37 +4496,37 @@
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>0.8721114700000003</v>
+        <v>-4.212167819999999</v>
       </c>
       <c r="D99" t="n">
-        <v>-4.212167819999999</v>
+        <v>9.207686730000001</v>
       </c>
       <c r="E99" t="n">
-        <v>9.207686730000001</v>
+        <v>12.72329238</v>
       </c>
       <c r="F99" t="n">
-        <v>12.72329238</v>
+        <v>17.20173201</v>
       </c>
       <c r="G99" t="n">
-        <v>17.20173201</v>
+        <v>5.82131096</v>
       </c>
       <c r="H99" t="n">
-        <v>5.82131096</v>
+        <v>-1.51795931</v>
       </c>
       <c r="I99" t="n">
-        <v>-1.51795931</v>
+        <v>-12.99625281</v>
       </c>
       <c r="J99" t="n">
-        <v>-12.99625281</v>
+        <v>-16.9396746</v>
       </c>
       <c r="K99" t="n">
-        <v>-16.9396746</v>
+        <v>-11.9078638</v>
       </c>
       <c r="L99" t="n">
-        <v>-11.9078638</v>
+        <v>3.03977697</v>
       </c>
       <c r="M99" t="n">
-        <v>3.03977697</v>
+        <v>2.450260839999999</v>
       </c>
     </row>
     <row r="100">
@@ -4541,37 +4537,37 @@
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="n">
-        <v>-233.61837582</v>
+        <v>-115.42952001</v>
       </c>
       <c r="D100" t="n">
-        <v>-115.42952001</v>
+        <v>-27.29277471</v>
       </c>
       <c r="E100" t="n">
-        <v>-27.29277471</v>
+        <v>-51.18376402999999</v>
       </c>
       <c r="F100" t="n">
-        <v>-51.18376402999999</v>
+        <v>-94.26099633999999</v>
       </c>
       <c r="G100" t="n">
-        <v>-94.26099633999999</v>
+        <v>-157.11089562</v>
       </c>
       <c r="H100" t="n">
-        <v>-157.11089562</v>
+        <v>-218.501818</v>
       </c>
       <c r="I100" t="n">
-        <v>-218.501818</v>
+        <v>-239.00675076</v>
       </c>
       <c r="J100" t="n">
-        <v>-239.00675076</v>
+        <v>-229.12973427</v>
       </c>
       <c r="K100" t="n">
-        <v>-229.12973427</v>
+        <v>-222.2966904</v>
       </c>
       <c r="L100" t="n">
-        <v>-222.2966904</v>
+        <v>-71.92945067999999</v>
       </c>
       <c r="M100" t="n">
-        <v>-71.92945067999999</v>
+        <v>16.47066413</v>
       </c>
     </row>
   </sheetData>

--- a/Result/analyze_2.xlsx
+++ b/Result/analyze_2.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-18</t>
         </is>
       </c>
     </row>
@@ -503,37 +503,37 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>674.6886631900001</v>
+        <v>968.4364153299999</v>
       </c>
       <c r="D2" t="n">
-        <v>970.0299840299999</v>
+        <v>1850.81626807</v>
       </c>
       <c r="E2" t="n">
-        <v>1847.1532232</v>
+        <v>1099.0453445</v>
       </c>
       <c r="F2" t="n">
-        <v>1090.12168094</v>
+        <v>166.23606728</v>
       </c>
       <c r="G2" t="n">
-        <v>152.27548183</v>
+        <v>727.0432599100001</v>
       </c>
       <c r="H2" t="n">
-        <v>727.4173344400001</v>
+        <v>821.58169307</v>
       </c>
       <c r="I2" t="n">
-        <v>787.38392211</v>
+        <v>747.65041722</v>
       </c>
       <c r="J2" t="n">
-        <v>709.79197376</v>
+        <v>1788.2746322</v>
       </c>
       <c r="K2" t="n">
-        <v>1783.67454239</v>
+        <v>-150.25167875</v>
       </c>
       <c r="L2" t="n">
-        <v>-145.73187574</v>
+        <v>99.59722605</v>
       </c>
       <c r="M2" t="n">
-        <v>100.81442348</v>
+        <v>214.21690205</v>
       </c>
     </row>
     <row r="3">
@@ -544,37 +544,37 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>-57.7376243</v>
+        <v>40.93185249</v>
       </c>
       <c r="D3" t="n">
-        <v>42.798068</v>
+        <v>167.42852347</v>
       </c>
       <c r="E3" t="n">
-        <v>177.52829294</v>
+        <v>131.20067092</v>
       </c>
       <c r="F3" t="n">
-        <v>135.66154168</v>
+        <v>47.32288347</v>
       </c>
       <c r="G3" t="n">
-        <v>45.71565789</v>
+        <v>-54.27841157</v>
       </c>
       <c r="H3" t="n">
-        <v>-63.2461811</v>
+        <v>44.99788483999998</v>
       </c>
       <c r="I3" t="n">
-        <v>36.92485858999999</v>
+        <v>133.55249681</v>
       </c>
       <c r="J3" t="n">
-        <v>130.83599664</v>
+        <v>127.84452171</v>
       </c>
       <c r="K3" t="n">
-        <v>121.91977397</v>
+        <v>95.93423469</v>
       </c>
       <c r="L3" t="n">
-        <v>99.40697876</v>
+        <v>164.72193823</v>
       </c>
       <c r="M3" t="n">
-        <v>165.42042423</v>
+        <v>252.21287347</v>
       </c>
     </row>
     <row r="4">
@@ -585,37 +585,37 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>-160.86073348</v>
+        <v>24.36349545</v>
       </c>
       <c r="D4" t="n">
-        <v>20.9653879</v>
+        <v>152.98839114</v>
       </c>
       <c r="E4" t="n">
-        <v>146.75340789</v>
+        <v>47.75745193</v>
       </c>
       <c r="F4" t="n">
-        <v>52.27611163</v>
+        <v>208.36690609</v>
       </c>
       <c r="G4" t="n">
-        <v>223.87646559</v>
+        <v>-66.71195385</v>
       </c>
       <c r="H4" t="n">
-        <v>-58.27769687999999</v>
+        <v>-32.01071431</v>
       </c>
       <c r="I4" t="n">
-        <v>9.940544380000002</v>
+        <v>-53.69707771000002</v>
       </c>
       <c r="J4" t="n">
-        <v>-13.99987109000001</v>
+        <v>-65.40194232</v>
       </c>
       <c r="K4" t="n">
-        <v>-55.87436203999999</v>
+        <v>-145.16365585</v>
       </c>
       <c r="L4" t="n">
-        <v>-152.91789665</v>
+        <v>-143.95420855</v>
       </c>
       <c r="M4" t="n">
-        <v>-145.96836652</v>
+        <v>119.33263953</v>
       </c>
     </row>
     <row r="5">
@@ -626,37 +626,37 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>945.3156049899999</v>
+        <v>633.9211675299999</v>
       </c>
       <c r="D5" t="n">
-        <v>633.39701284</v>
+        <v>146.03440984</v>
       </c>
       <c r="E5" t="n">
-        <v>145.83107331</v>
+        <v>-38.63469054000001</v>
       </c>
       <c r="F5" t="n">
-        <v>-39.15896537</v>
+        <v>-259.31952002</v>
       </c>
       <c r="G5" t="n">
-        <v>-259.43326067</v>
+        <v>-387.10507082</v>
       </c>
       <c r="H5" t="n">
-        <v>-387.39297887</v>
+        <v>-428.41055059</v>
       </c>
       <c r="I5" t="n">
-        <v>-428.42212264</v>
+        <v>-414.44012063</v>
       </c>
       <c r="J5" t="n">
-        <v>-414.2600325699999</v>
+        <v>-488.47392939</v>
       </c>
       <c r="K5" t="n">
-        <v>-487.77716299</v>
+        <v>-416.8720858</v>
       </c>
       <c r="L5" t="n">
-        <v>-411.36808591</v>
+        <v>-354.1363623</v>
       </c>
       <c r="M5" t="n">
-        <v>-388.16366113</v>
+        <v>-250.13332917</v>
       </c>
     </row>
     <row r="6">
@@ -667,37 +667,37 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>-66.02961714</v>
+        <v>59.98246195999999</v>
       </c>
       <c r="D6" t="n">
-        <v>59.97732865</v>
+        <v>11.23192045</v>
       </c>
       <c r="E6" t="n">
-        <v>11.23121783</v>
+        <v>17.82646754</v>
       </c>
       <c r="F6" t="n">
-        <v>17.82405653</v>
+        <v>63.14545295000001</v>
       </c>
       <c r="G6" t="n">
-        <v>63.14145063</v>
+        <v>81.07541612999999</v>
       </c>
       <c r="H6" t="n">
-        <v>81.07120747999998</v>
+        <v>80.90591445</v>
       </c>
       <c r="I6" t="n">
-        <v>80.90020034</v>
+        <v>71.1532433</v>
       </c>
       <c r="J6" t="n">
-        <v>71.14833212000001</v>
+        <v>154.45330816</v>
       </c>
       <c r="K6" t="n">
-        <v>154.44832648</v>
+        <v>190.3080599</v>
       </c>
       <c r="L6" t="n">
-        <v>190.30644914</v>
+        <v>31.98070368999999</v>
       </c>
       <c r="M6" t="n">
-        <v>31.97720224999999</v>
+        <v>68.25413482999998</v>
       </c>
     </row>
     <row r="7">
@@ -708,37 +708,37 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>10.66471378</v>
+        <v>12.56570013</v>
       </c>
       <c r="D7" t="n">
-        <v>13.09498813</v>
+        <v>12.34523166</v>
       </c>
       <c r="E7" t="n">
-        <v>12.54927081</v>
+        <v>19.9511593</v>
       </c>
       <c r="F7" t="n">
-        <v>20.47784514</v>
+        <v>0.4774137899999991</v>
       </c>
       <c r="G7" t="n">
-        <v>0.595156759999998</v>
+        <v>-12.04365878</v>
       </c>
       <c r="H7" t="n">
-        <v>-11.75154208</v>
+        <v>-41.36450387000001</v>
       </c>
       <c r="I7" t="n">
-        <v>-41.34721771</v>
+        <v>-35.20973066000001</v>
       </c>
       <c r="J7" t="n">
-        <v>-35.38490754</v>
+        <v>-29.75304235</v>
       </c>
       <c r="K7" t="n">
-        <v>-30.44482707</v>
+        <v>-33.43528821</v>
       </c>
       <c r="L7" t="n">
-        <v>-38.93767733999999</v>
+        <v>-53.37011325000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-19.33931298</v>
+        <v>-29.23449371</v>
       </c>
     </row>
     <row r="8">
@@ -749,37 +749,37 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>2288.2928933</v>
+        <v>1082.17697646</v>
       </c>
       <c r="D8" t="n">
-        <v>1082.17697646</v>
+        <v>1217.20015451</v>
       </c>
       <c r="E8" t="n">
-        <v>1217.20015451</v>
+        <v>1224.98766666</v>
       </c>
       <c r="F8" t="n">
-        <v>1224.98766666</v>
+        <v>3053.41093554</v>
       </c>
       <c r="G8" t="n">
-        <v>3053.41093554</v>
+        <v>3202.5230305</v>
       </c>
       <c r="H8" t="n">
-        <v>3202.5230305</v>
+        <v>3796.87587415</v>
       </c>
       <c r="I8" t="n">
-        <v>3796.87587415</v>
+        <v>879.33300735</v>
       </c>
       <c r="J8" t="n">
-        <v>879.33300735</v>
+        <v>2616.38882237</v>
       </c>
       <c r="K8" t="n">
-        <v>2616.38882237</v>
+        <v>2457.47498701</v>
       </c>
       <c r="L8" t="n">
-        <v>2457.47498701</v>
+        <v>3001.08271769</v>
       </c>
       <c r="M8" t="n">
-        <v>3001.08271769</v>
+        <v>2854.80565398</v>
       </c>
     </row>
     <row r="9">
@@ -788,39 +788,41 @@
           <t>其他電子業右下</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
       <c r="C9" t="n">
-        <v>39.37436597</v>
+        <v>36.96293905</v>
       </c>
       <c r="D9" t="n">
-        <v>36.78591928</v>
+        <v>40.28744362</v>
       </c>
       <c r="E9" t="n">
-        <v>40.08006312000001</v>
+        <v>-1.39741973</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.64257977</v>
+        <v>12.6818208</v>
       </c>
       <c r="G9" t="n">
-        <v>12.49002131</v>
+        <v>-56.32023273</v>
       </c>
       <c r="H9" t="n">
-        <v>-56.5152249</v>
+        <v>-82.96138404000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-83.09911693000001</v>
+        <v>-91.10828211000002</v>
       </c>
       <c r="J9" t="n">
-        <v>-91.21725834</v>
+        <v>-123.47710028</v>
       </c>
       <c r="K9" t="n">
-        <v>-123.56119124</v>
+        <v>-130.42492004</v>
       </c>
       <c r="L9" t="n">
-        <v>-130.50494652</v>
+        <v>-119.44557031</v>
       </c>
       <c r="M9" t="n">
-        <v>-119.4984721</v>
+        <v>-109.62339764</v>
       </c>
     </row>
     <row r="10">
@@ -831,37 +833,37 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>-4.425793330000002</v>
+        <v>32.8467998</v>
       </c>
       <c r="D10" t="n">
-        <v>33.02442404</v>
+        <v>92.43947256</v>
       </c>
       <c r="E10" t="n">
-        <v>92.64678287999999</v>
+        <v>16.91286693</v>
       </c>
       <c r="F10" t="n">
-        <v>17.15824161</v>
+        <v>44.91212201</v>
       </c>
       <c r="G10" t="n">
-        <v>45.1034885</v>
+        <v>-9.094254979999999</v>
       </c>
       <c r="H10" t="n">
-        <v>-8.899032229999998</v>
+        <v>-111.15845621</v>
       </c>
       <c r="I10" t="n">
-        <v>-111.02076683</v>
+        <v>-101.86097063</v>
       </c>
       <c r="J10" t="n">
-        <v>-101.75172866</v>
+        <v>-139.40380109</v>
       </c>
       <c r="K10" t="n">
-        <v>-139.31868833</v>
+        <v>-100.12251588</v>
       </c>
       <c r="L10" t="n">
-        <v>-100.04058103</v>
+        <v>-55.02909974999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-54.97436146999999</v>
+        <v>21.31738405000002</v>
       </c>
     </row>
     <row r="11">
@@ -872,37 +874,37 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>59.06884079</v>
+        <v>58.40428007</v>
       </c>
       <c r="D11" t="n">
-        <v>58.25104046</v>
+        <v>5.30423225</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.600569230000001</v>
+        <v>-57.61486382</v>
       </c>
       <c r="F11" t="n">
-        <v>-56.15323858999999</v>
+        <v>-84.49990516000001</v>
       </c>
       <c r="G11" t="n">
-        <v>-77.84758144</v>
+        <v>-71.27952607</v>
       </c>
       <c r="H11" t="n">
-        <v>-69.03680920000001</v>
+        <v>-9.778319470000007</v>
       </c>
       <c r="I11" t="n">
-        <v>-25.6903414</v>
+        <v>31.64017136999999</v>
       </c>
       <c r="J11" t="n">
-        <v>29.68746072</v>
+        <v>-181.89193455</v>
       </c>
       <c r="K11" t="n">
-        <v>-208.16999437</v>
+        <v>-28.50699865000001</v>
       </c>
       <c r="L11" t="n">
-        <v>-206.94991158</v>
+        <v>309.12090261</v>
       </c>
       <c r="M11" t="n">
-        <v>-108.51393825</v>
+        <v>653.33942918</v>
       </c>
     </row>
     <row r="12">
@@ -911,41 +913,39 @@
           <t>化學工業右下</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>-78.93212152</v>
+        <v>-40.60041190999999</v>
       </c>
       <c r="D12" t="n">
-        <v>-41.43989729</v>
+        <v>-102.18770138</v>
       </c>
       <c r="E12" t="n">
-        <v>-102.01485622</v>
+        <v>-108.24216567</v>
       </c>
       <c r="F12" t="n">
-        <v>-106.13760151</v>
+        <v>-30.29425106</v>
       </c>
       <c r="G12" t="n">
-        <v>-22.3740144</v>
+        <v>360.7339206099999</v>
       </c>
       <c r="H12" t="n">
-        <v>360.00356585</v>
+        <v>243.27156338</v>
       </c>
       <c r="I12" t="n">
-        <v>239.47928084</v>
+        <v>170.82302881</v>
       </c>
       <c r="J12" t="n">
-        <v>172.96076883</v>
+        <v>-59.30385586</v>
       </c>
       <c r="K12" t="n">
-        <v>-44.249782</v>
+        <v>-39.19330053</v>
       </c>
       <c r="L12" t="n">
-        <v>-22.19598527</v>
+        <v>-18.61229305</v>
       </c>
       <c r="M12" t="n">
-        <v>2.736445330000004</v>
+        <v>14.54049766</v>
       </c>
     </row>
     <row r="13">
@@ -956,37 +956,37 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>2.45781016</v>
+        <v>-0.05241517000000009</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7869540599999999</v>
+        <v>-18.55472112</v>
       </c>
       <c r="E13" t="n">
-        <v>-18.7276696</v>
+        <v>-0.1204009700000007</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.22506845</v>
+        <v>10.7954674</v>
       </c>
       <c r="G13" t="n">
-        <v>2.87521121</v>
+        <v>-8.393348420000001</v>
       </c>
       <c r="H13" t="n">
-        <v>-7.662935969999999</v>
+        <v>-7.869924789999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.07760919</v>
+        <v>23.50273929</v>
       </c>
       <c r="J13" t="n">
-        <v>21.36502881</v>
+        <v>59.14162804999999</v>
       </c>
       <c r="K13" t="n">
-        <v>44.08762252</v>
+        <v>39.01662319</v>
       </c>
       <c r="L13" t="n">
-        <v>22.01935964</v>
+        <v>43.05718475</v>
       </c>
       <c r="M13" t="n">
-        <v>21.7085099</v>
+        <v>74.575863</v>
       </c>
     </row>
     <row r="14">
@@ -997,37 +997,37 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>-4030.99020094</v>
+        <v>-6594.14844021</v>
       </c>
       <c r="D14" t="n">
-        <v>-5868.97951287</v>
+        <v>-1898.4734454</v>
       </c>
       <c r="E14" t="n">
-        <v>-1133.26658091</v>
+        <v>-4366.75783154</v>
       </c>
       <c r="F14" t="n">
-        <v>-3705.140555330001</v>
+        <v>4873.196510209999</v>
       </c>
       <c r="G14" t="n">
-        <v>5235.51142395</v>
+        <v>1756.55389994</v>
       </c>
       <c r="H14" t="n">
-        <v>1804.83180749</v>
+        <v>7627.41346733</v>
       </c>
       <c r="I14" t="n">
-        <v>7248.74316912</v>
+        <v>4133.37325492</v>
       </c>
       <c r="J14" t="n">
-        <v>3995.88190836</v>
+        <v>7781.72777513</v>
       </c>
       <c r="K14" t="n">
-        <v>7523.27648651</v>
+        <v>3994.91937618</v>
       </c>
       <c r="L14" t="n">
-        <v>3953.31127801</v>
+        <v>4395.53537626</v>
       </c>
       <c r="M14" t="n">
-        <v>4481.908409510001</v>
+        <v>1742.02967083</v>
       </c>
     </row>
     <row r="15">
@@ -1036,39 +1036,41 @@
           <t>半導體業右下</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
       <c r="C15" t="n">
-        <v>282.2401762700001</v>
+        <v>225.8095879299999</v>
       </c>
       <c r="D15" t="n">
-        <v>225.80410349</v>
+        <v>610.7338875</v>
       </c>
       <c r="E15" t="n">
-        <v>610.72651117</v>
+        <v>-94.80977159000003</v>
       </c>
       <c r="F15" t="n">
-        <v>-94.81707577000003</v>
+        <v>-417.50653784</v>
       </c>
       <c r="G15" t="n">
-        <v>-417.5162018699999</v>
+        <v>317.7782638200001</v>
       </c>
       <c r="H15" t="n">
-        <v>317.77029651</v>
+        <v>27.97551376999998</v>
       </c>
       <c r="I15" t="n">
-        <v>27.96913816999998</v>
+        <v>979.1516323300001</v>
       </c>
       <c r="J15" t="n">
-        <v>979.1443715299999</v>
+        <v>577.7574768100001</v>
       </c>
       <c r="K15" t="n">
-        <v>577.74898408</v>
+        <v>839.4041663200001</v>
       </c>
       <c r="L15" t="n">
-        <v>839.39304378</v>
+        <v>892.65652936</v>
       </c>
       <c r="M15" t="n">
-        <v>892.64955362</v>
+        <v>419.4552546799999</v>
       </c>
     </row>
     <row r="16">
@@ -1079,37 +1081,37 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>-672.08428641</v>
+        <v>-477.72881351</v>
       </c>
       <c r="D16" t="n">
-        <v>-1194.19273833</v>
+        <v>-196.34137564</v>
       </c>
       <c r="E16" t="n">
-        <v>-676.33293596</v>
+        <v>-499.35299213</v>
       </c>
       <c r="F16" t="n">
-        <v>-1143.95210694</v>
+        <v>87.5208913</v>
       </c>
       <c r="G16" t="n">
-        <v>-162.92503767</v>
+        <v>-151.84973796</v>
       </c>
       <c r="H16" t="n">
-        <v>-459.66738414</v>
+        <v>-301.49532814</v>
       </c>
       <c r="I16" t="n">
-        <v>-452.57734768</v>
+        <v>-249.4660041</v>
       </c>
       <c r="J16" t="n">
-        <v>-678.4962069400001</v>
+        <v>100.37929446</v>
       </c>
       <c r="K16" t="n">
-        <v>-301.5696719300001</v>
+        <v>193.60964602</v>
       </c>
       <c r="L16" t="n">
-        <v>-14.27670384000002</v>
+        <v>-248.13278948</v>
       </c>
       <c r="M16" t="n">
-        <v>-578.11620666</v>
+        <v>-36.99389134000001</v>
       </c>
     </row>
     <row r="17">
@@ -1120,37 +1122,37 @@
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
-        <v>2.72845142</v>
+        <v>0.8801225899999999</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8801225899999999</v>
+        <v>0.95461918</v>
       </c>
       <c r="E17" t="n">
-        <v>0.95461918</v>
+        <v>0.84933853</v>
       </c>
       <c r="F17" t="n">
-        <v>0.84933853</v>
+        <v>-0.12911185</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.12911185</v>
+        <v>0.18345265</v>
       </c>
       <c r="H17" t="n">
-        <v>0.18345265</v>
+        <v>-0.75565477</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.75565477</v>
+        <v>-1.09301157</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.09301157</v>
+        <v>-1.25991411</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.25991411</v>
+        <v>0.42586555</v>
       </c>
       <c r="L17" t="n">
-        <v>0.42586555</v>
+        <v>1.11311752</v>
       </c>
       <c r="M17" t="n">
-        <v>1.11311752</v>
+        <v>0.08433128999999999</v>
       </c>
     </row>
     <row r="18">
@@ -1161,37 +1163,37 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>-272.85884179</v>
+        <v>-613.08167041</v>
       </c>
       <c r="D18" t="n">
-        <v>-871.1229194199999</v>
+        <v>-580.6133292200001</v>
       </c>
       <c r="E18" t="n">
-        <v>-1069.81135742</v>
+        <v>-247.38925816</v>
       </c>
       <c r="F18" t="n">
-        <v>-452.58295967</v>
+        <v>-214.90409677</v>
       </c>
       <c r="G18" t="n">
-        <v>-531.6617434799999</v>
+        <v>-217.08732924</v>
       </c>
       <c r="H18" t="n">
-        <v>-603.5171211700001</v>
+        <v>-9.226010169999997</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.170012629999998</v>
+        <v>290.48966357</v>
       </c>
       <c r="J18" t="n">
-        <v>755.74136299</v>
+        <v>54.82167167</v>
       </c>
       <c r="K18" t="n">
-        <v>808.41838966</v>
+        <v>-54.16778170999999</v>
       </c>
       <c r="L18" t="n">
-        <v>20.05482964</v>
+        <v>89.1547312</v>
       </c>
       <c r="M18" t="n">
-        <v>397.91409635</v>
+        <v>243.45978075</v>
       </c>
     </row>
     <row r="19">
@@ -1202,37 +1204,37 @@
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>-6.60366677</v>
+        <v>-259.90964889</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.86839988</v>
+        <v>-492.69064664</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.49261844</v>
+        <v>-205.65305627</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.45935476</v>
+        <v>-321.8522806</v>
       </c>
       <c r="G19" t="n">
-        <v>-5.09463389</v>
+        <v>-402.47636881</v>
       </c>
       <c r="H19" t="n">
-        <v>-16.04657688</v>
+        <v>-8.67229586</v>
       </c>
       <c r="I19" t="n">
-        <v>-16.7282934</v>
+        <v>455.45563564</v>
       </c>
       <c r="J19" t="n">
-        <v>-9.796063780000001</v>
+        <v>752.54291658</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.05380141</v>
+        <v>76.90680243</v>
       </c>
       <c r="L19" t="n">
-        <v>2.68419108</v>
+        <v>313.9280577399999</v>
       </c>
       <c r="M19" t="n">
-        <v>5.168692590000001</v>
+        <v>698.9222146000001</v>
       </c>
     </row>
     <row r="20">
@@ -1243,37 +1245,37 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>-26.64337471</v>
+        <v>-8.6719104</v>
       </c>
       <c r="D20" t="n">
-        <v>-8.6719104</v>
+        <v>6.29112816</v>
       </c>
       <c r="E20" t="n">
-        <v>6.29112816</v>
+        <v>-11.38791094</v>
       </c>
       <c r="F20" t="n">
-        <v>-11.38791094</v>
+        <v>39.90390299</v>
       </c>
       <c r="G20" t="n">
-        <v>39.90390299</v>
+        <v>-7.499015480000001</v>
       </c>
       <c r="H20" t="n">
-        <v>-7.499015480000001</v>
+        <v>-34.65196079</v>
       </c>
       <c r="I20" t="n">
-        <v>-34.65196079</v>
+        <v>-20.07586818</v>
       </c>
       <c r="J20" t="n">
-        <v>-20.07586818</v>
+        <v>37.03994246</v>
       </c>
       <c r="K20" t="n">
-        <v>37.03994246</v>
+        <v>61.97440654</v>
       </c>
       <c r="L20" t="n">
-        <v>61.97440654</v>
+        <v>4.784528130000001</v>
       </c>
       <c r="M20" t="n">
-        <v>4.784528130000001</v>
+        <v>-26.57971293</v>
       </c>
     </row>
     <row r="21">
@@ -1282,41 +1284,39 @@
           <t>居家生活右下</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
-        <v>1.42652432</v>
+        <v>2.43176105</v>
       </c>
       <c r="D21" t="n">
-        <v>2.43182188</v>
+        <v>1.74360164</v>
       </c>
       <c r="E21" t="n">
-        <v>1.74384658</v>
+        <v>1.74665228</v>
       </c>
       <c r="F21" t="n">
-        <v>1.74691153</v>
+        <v>1.07892036</v>
       </c>
       <c r="G21" t="n">
-        <v>1.07925514</v>
+        <v>-4.11563068</v>
       </c>
       <c r="H21" t="n">
-        <v>-4.11525845</v>
+        <v>-7.67926037</v>
       </c>
       <c r="I21" t="n">
-        <v>-7.67941925</v>
+        <v>-2.84996866</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.84960067</v>
+        <v>-1.066877</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.0665493</v>
+        <v>0.69413256</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6943534300000002</v>
+        <v>-0.5863826000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5864616200000001</v>
+        <v>-1.04495596</v>
       </c>
     </row>
     <row r="22">
@@ -1327,37 +1327,37 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>2.09046991</v>
+        <v>2.66362539</v>
       </c>
       <c r="D22" t="n">
-        <v>2.66346664</v>
+        <v>2.26437778</v>
       </c>
       <c r="E22" t="n">
-        <v>2.26386664</v>
+        <v>2.71147005</v>
       </c>
       <c r="F22" t="n">
-        <v>2.71086744</v>
+        <v>2.27511529</v>
       </c>
       <c r="G22" t="n">
-        <v>2.27450032</v>
+        <v>3.80951349</v>
       </c>
       <c r="H22" t="n">
-        <v>3.80883685</v>
+        <v>1.5130412</v>
       </c>
       <c r="I22" t="n">
-        <v>1.51244877</v>
+        <v>0.84749379</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8467118700000001</v>
+        <v>1.00913396</v>
       </c>
       <c r="K22" t="n">
-        <v>1.00827689</v>
+        <v>3.30609277</v>
       </c>
       <c r="L22" t="n">
-        <v>3.30557361</v>
+        <v>4.33970527</v>
       </c>
       <c r="M22" t="n">
-        <v>4.33944642</v>
+        <v>1.19769344</v>
       </c>
     </row>
     <row r="23">
@@ -1368,37 +1368,37 @@
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
-        <v>18.20302817</v>
+        <v>37.88405859</v>
       </c>
       <c r="D23" t="n">
-        <v>37.92417097</v>
+        <v>24.20960816</v>
       </c>
       <c r="E23" t="n">
-        <v>24.25433136</v>
+        <v>17.34495134</v>
       </c>
       <c r="F23" t="n">
-        <v>17.35399521</v>
+        <v>10.97104816</v>
       </c>
       <c r="G23" t="n">
-        <v>10.91826206</v>
+        <v>14.7137113</v>
       </c>
       <c r="H23" t="n">
-        <v>14.60415864</v>
+        <v>25.86115714</v>
       </c>
       <c r="I23" t="n">
-        <v>25.82796283</v>
+        <v>61.50186898999999</v>
       </c>
       <c r="J23" t="n">
-        <v>61.49910808</v>
+        <v>67.72679253</v>
       </c>
       <c r="K23" t="n">
-        <v>67.77362210000001</v>
+        <v>73.11998154999999</v>
       </c>
       <c r="L23" t="n">
-        <v>73.12120501999999</v>
+        <v>134.38158645</v>
       </c>
       <c r="M23" t="n">
-        <v>134.40800574</v>
+        <v>128.60766598</v>
       </c>
     </row>
     <row r="24">
@@ -1407,41 +1407,39 @@
           <t>建材營造右下</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
-        <v>-6.62700109</v>
+        <v>83.64050492</v>
       </c>
       <c r="D24" t="n">
-        <v>83.61085113</v>
+        <v>26.71992094</v>
       </c>
       <c r="E24" t="n">
-        <v>26.68614927</v>
+        <v>13.29203751000001</v>
       </c>
       <c r="F24" t="n">
-        <v>13.31384929</v>
+        <v>-21.13706619</v>
       </c>
       <c r="G24" t="n">
-        <v>-21.23921207</v>
+        <v>-42.5733706</v>
       </c>
       <c r="H24" t="n">
-        <v>-42.54438606</v>
+        <v>-44.01588298</v>
       </c>
       <c r="I24" t="n">
-        <v>-44.12641995000001</v>
+        <v>-45.47459771</v>
       </c>
       <c r="J24" t="n">
-        <v>-45.77733627</v>
+        <v>-27.29051669</v>
       </c>
       <c r="K24" t="n">
-        <v>-27.47678849</v>
+        <v>5.65131877</v>
       </c>
       <c r="L24" t="n">
-        <v>5.553141660000001</v>
+        <v>28.50662747</v>
       </c>
       <c r="M24" t="n">
-        <v>28.34928419</v>
+        <v>38.06157995</v>
       </c>
     </row>
     <row r="25">
@@ -1452,37 +1450,37 @@
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>-33.08088043999999</v>
+        <v>54.79970311</v>
       </c>
       <c r="D25" t="n">
-        <v>54.79315186</v>
+        <v>26.13074153</v>
       </c>
       <c r="E25" t="n">
-        <v>26.1645912</v>
+        <v>40.16345089</v>
       </c>
       <c r="F25" t="n">
-        <v>40.18119956</v>
+        <v>34.47930947</v>
       </c>
       <c r="G25" t="n">
-        <v>34.56604312</v>
+        <v>8.573180339999997</v>
       </c>
       <c r="H25" t="n">
-        <v>8.61558161</v>
+        <v>8.895907459999998</v>
       </c>
       <c r="I25" t="n">
-        <v>8.902622270000002</v>
+        <v>5.698523059999999</v>
       </c>
       <c r="J25" t="n">
-        <v>5.70338004</v>
+        <v>44.67063214</v>
       </c>
       <c r="K25" t="n">
-        <v>44.66285690000001</v>
+        <v>48.05917072</v>
       </c>
       <c r="L25" t="n">
-        <v>48.10175376999999</v>
+        <v>36.97969401</v>
       </c>
       <c r="M25" t="n">
-        <v>37.10647014</v>
+        <v>37.81591028</v>
       </c>
     </row>
     <row r="26">
@@ -1493,37 +1491,37 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>7.61994909</v>
+        <v>3.95032609</v>
       </c>
       <c r="D26" t="n">
-        <v>3.95032609</v>
+        <v>8.953404039999999</v>
       </c>
       <c r="E26" t="n">
-        <v>8.953404039999999</v>
+        <v>5.887683269999999</v>
       </c>
       <c r="F26" t="n">
-        <v>5.887683269999999</v>
+        <v>7.59334499</v>
       </c>
       <c r="G26" t="n">
-        <v>7.59334499</v>
+        <v>5.17034791</v>
       </c>
       <c r="H26" t="n">
-        <v>5.17034791</v>
+        <v>7.59349848</v>
       </c>
       <c r="I26" t="n">
-        <v>7.59349848</v>
+        <v>18.69440627</v>
       </c>
       <c r="J26" t="n">
-        <v>18.69440627</v>
+        <v>6.72809566</v>
       </c>
       <c r="K26" t="n">
-        <v>6.72809566</v>
+        <v>5.8262754</v>
       </c>
       <c r="L26" t="n">
-        <v>5.8262754</v>
+        <v>6.19576568</v>
       </c>
       <c r="M26" t="n">
-        <v>6.19576568</v>
+        <v>7.534156789999999</v>
       </c>
     </row>
     <row r="27">
@@ -1534,37 +1532,37 @@
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>12.34924729</v>
+        <v>7.256533559999999</v>
       </c>
       <c r="D27" t="n">
-        <v>7.256533559999999</v>
+        <v>21.41555787</v>
       </c>
       <c r="E27" t="n">
-        <v>21.41555787</v>
+        <v>9.253958190000001</v>
       </c>
       <c r="F27" t="n">
-        <v>9.253958190000001</v>
+        <v>20.89001611</v>
       </c>
       <c r="G27" t="n">
-        <v>20.89001611</v>
+        <v>17.74033155</v>
       </c>
       <c r="H27" t="n">
-        <v>17.74033155</v>
+        <v>22.20184127</v>
       </c>
       <c r="I27" t="n">
-        <v>22.20184127</v>
+        <v>32.01865752</v>
       </c>
       <c r="J27" t="n">
-        <v>32.01865752</v>
+        <v>32.91440352</v>
       </c>
       <c r="K27" t="n">
-        <v>32.91440352</v>
+        <v>31.90241096</v>
       </c>
       <c r="L27" t="n">
-        <v>31.90241096</v>
+        <v>15.84994324</v>
       </c>
       <c r="M27" t="n">
-        <v>15.84994324</v>
+        <v>15.5021924</v>
       </c>
     </row>
     <row r="28">
@@ -1575,37 +1573,37 @@
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>12.54056931</v>
+        <v>-19.63720791</v>
       </c>
       <c r="D28" t="n">
-        <v>-19.63720791</v>
+        <v>3.95222211</v>
       </c>
       <c r="E28" t="n">
-        <v>3.95222211</v>
+        <v>-27.67325763</v>
       </c>
       <c r="F28" t="n">
-        <v>-27.67325763</v>
+        <v>-47.67043209</v>
       </c>
       <c r="G28" t="n">
-        <v>-47.67043209</v>
+        <v>-79.82344318999999</v>
       </c>
       <c r="H28" t="n">
-        <v>-79.82344318999999</v>
+        <v>-109.72795995</v>
       </c>
       <c r="I28" t="n">
-        <v>-109.72795995</v>
+        <v>-102.94148546</v>
       </c>
       <c r="J28" t="n">
-        <v>-102.94148546</v>
+        <v>-89.79447408</v>
       </c>
       <c r="K28" t="n">
-        <v>-89.79447408</v>
+        <v>-73.93345174000001</v>
       </c>
       <c r="L28" t="n">
-        <v>-73.93345174000001</v>
+        <v>-58.76420166999999</v>
       </c>
       <c r="M28" t="n">
-        <v>-58.76420166999999</v>
+        <v>-32.14115353</v>
       </c>
     </row>
     <row r="29">
@@ -1616,37 +1614,37 @@
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>0.01825068</v>
+        <v>0.02746755</v>
       </c>
       <c r="D29" t="n">
-        <v>0.02746755</v>
+        <v>0.08414062</v>
       </c>
       <c r="E29" t="n">
-        <v>0.08414062</v>
+        <v>0.07506878</v>
       </c>
       <c r="F29" t="n">
-        <v>0.07506878</v>
+        <v>0.03323846</v>
       </c>
       <c r="G29" t="n">
-        <v>0.03323846</v>
+        <v>0.00619917</v>
       </c>
       <c r="H29" t="n">
-        <v>0.00619917</v>
+        <v>0.01277118</v>
       </c>
       <c r="I29" t="n">
-        <v>0.01277118</v>
+        <v>-0.00653676</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.00653676</v>
+        <v>-0.01623805</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.01623805</v>
+        <v>-0.01854561</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.01854561</v>
+        <v>-0.0214375</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.0214375</v>
+        <v>-0.00590779</v>
       </c>
     </row>
     <row r="30">
@@ -1657,37 +1655,37 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>-0.00255541</v>
+        <v>0.0079351</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0079351</v>
+        <v>0.01028314</v>
       </c>
       <c r="E30" t="n">
-        <v>0.01028314</v>
+        <v>0.00538708</v>
       </c>
       <c r="F30" t="n">
-        <v>0.00538708</v>
+        <v>0.01209633</v>
       </c>
       <c r="G30" t="n">
-        <v>0.01209633</v>
+        <v>0.0008129699999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0008129699999999999</v>
+        <v>-0.00467908</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.00467908</v>
+        <v>-0.00565026</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.00565026</v>
+        <v>-0.00688049</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.00688049</v>
+        <v>0.01008529</v>
       </c>
       <c r="L30" t="n">
-        <v>0.01008529</v>
+        <v>0.00215091</v>
       </c>
       <c r="M30" t="n">
-        <v>0.00215091</v>
+        <v>0.003591480000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1698,37 +1696,37 @@
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>0.003614140000000001</v>
+        <v>0.10054297</v>
       </c>
       <c r="D31" t="n">
-        <v>0.10054297</v>
+        <v>0.21751282</v>
       </c>
       <c r="E31" t="n">
-        <v>0.21751282</v>
+        <v>0.10936104</v>
       </c>
       <c r="F31" t="n">
-        <v>0.10936104</v>
+        <v>0.03924989</v>
       </c>
       <c r="G31" t="n">
-        <v>0.03924989</v>
+        <v>-0.01166996</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.01166996</v>
+        <v>-0.05285173000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.05285173000000001</v>
+        <v>-0.09475462</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.09475462</v>
+        <v>-0.1850039</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.1850039</v>
+        <v>0.0035406</v>
       </c>
       <c r="L31" t="n">
-        <v>0.0035406</v>
+        <v>-0.03696819</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.03696819</v>
+        <v>0.20996728</v>
       </c>
     </row>
     <row r="32">
@@ -1739,37 +1737,37 @@
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>-15.50397747</v>
+        <v>-8.503892480000001</v>
       </c>
       <c r="D32" t="n">
-        <v>-7.671519279999999</v>
+        <v>-15.01818866</v>
       </c>
       <c r="E32" t="n">
-        <v>-12.56496135</v>
+        <v>-18.7437909</v>
       </c>
       <c r="F32" t="n">
-        <v>0.4845926899999997</v>
+        <v>-21.51308012</v>
       </c>
       <c r="G32" t="n">
-        <v>-20.67803373</v>
+        <v>-26.23204626999999</v>
       </c>
       <c r="H32" t="n">
-        <v>-32.15445803</v>
+        <v>-28.63820698</v>
       </c>
       <c r="I32" t="n">
-        <v>-40.28821612</v>
+        <v>-10.76783712</v>
       </c>
       <c r="J32" t="n">
-        <v>-16.20914258</v>
+        <v>-20.0377565</v>
       </c>
       <c r="K32" t="n">
-        <v>-19.13381427</v>
+        <v>-6.47922948</v>
       </c>
       <c r="L32" t="n">
-        <v>-10.30184885</v>
+        <v>-21.67391496</v>
       </c>
       <c r="M32" t="n">
-        <v>-13.95881996</v>
+        <v>5.52792584</v>
       </c>
     </row>
     <row r="33">
@@ -1780,37 +1778,37 @@
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
-        <v>-0.14939967</v>
+        <v>1.38274384</v>
       </c>
       <c r="D33" t="n">
-        <v>0.5503706399999999</v>
+        <v>4.3513519</v>
       </c>
       <c r="E33" t="n">
-        <v>1.89812459</v>
+        <v>22.15492144</v>
       </c>
       <c r="F33" t="n">
-        <v>2.92653785</v>
+        <v>1.31634559</v>
       </c>
       <c r="G33" t="n">
-        <v>0.4812992</v>
+        <v>-7.02553147</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.10311971</v>
+        <v>-14.85168894</v>
       </c>
       <c r="I33" t="n">
-        <v>-3.2016798</v>
+        <v>-7.31165541</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.87034995</v>
+        <v>-1.41149422</v>
       </c>
       <c r="K33" t="n">
-        <v>-2.31543645</v>
+        <v>-7.85183825</v>
       </c>
       <c r="L33" t="n">
-        <v>-4.02921888</v>
+        <v>6.05615573</v>
       </c>
       <c r="M33" t="n">
-        <v>-1.65893927</v>
+        <v>10.38013217</v>
       </c>
     </row>
     <row r="34">
@@ -1821,37 +1819,37 @@
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
-        <v>34.04004418</v>
+        <v>21.63590168</v>
       </c>
       <c r="D34" t="n">
-        <v>21.63590168</v>
+        <v>34.050435</v>
       </c>
       <c r="E34" t="n">
-        <v>34.050435</v>
+        <v>53.00901164</v>
       </c>
       <c r="F34" t="n">
-        <v>53.00901164</v>
+        <v>23.37416052</v>
       </c>
       <c r="G34" t="n">
-        <v>23.37416052</v>
+        <v>33.49646586</v>
       </c>
       <c r="H34" t="n">
-        <v>33.49646586</v>
+        <v>42.38292683</v>
       </c>
       <c r="I34" t="n">
-        <v>42.38292683</v>
+        <v>53.14078301</v>
       </c>
       <c r="J34" t="n">
-        <v>53.14078301</v>
+        <v>77.31264456</v>
       </c>
       <c r="K34" t="n">
-        <v>77.31264456</v>
+        <v>-99.06594910000001</v>
       </c>
       <c r="L34" t="n">
-        <v>-99.06594910000001</v>
+        <v>-137.71287059</v>
       </c>
       <c r="M34" t="n">
-        <v>-137.71287059</v>
+        <v>-36.98264507</v>
       </c>
     </row>
     <row r="35">
@@ -1862,37 +1860,37 @@
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
-        <v>-0.86483032</v>
+        <v>-0.8053423099999999</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8053423099999999</v>
+        <v>-0.5541974000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.5541974000000001</v>
+        <v>-0.86426467</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.86426467</v>
+        <v>-1.03027462</v>
       </c>
       <c r="G35" t="n">
-        <v>-1.03027462</v>
+        <v>-0.0252352</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.0252352</v>
+        <v>-0.03013220000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.03013220000000001</v>
+        <v>3.18854859</v>
       </c>
       <c r="J35" t="n">
-        <v>3.18854859</v>
+        <v>2.605460190000001</v>
       </c>
       <c r="K35" t="n">
-        <v>2.605460190000001</v>
+        <v>4.13401164</v>
       </c>
       <c r="L35" t="n">
-        <v>4.13401164</v>
+        <v>4.72190981</v>
       </c>
       <c r="M35" t="n">
-        <v>4.72190981</v>
+        <v>5.98762434</v>
       </c>
     </row>
     <row r="36">
@@ -1903,37 +1901,37 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>44.04495778</v>
+        <v>85.63237165</v>
       </c>
       <c r="D36" t="n">
-        <v>85.63237165</v>
+        <v>179.98748556</v>
       </c>
       <c r="E36" t="n">
-        <v>179.98748556</v>
+        <v>243.01780536</v>
       </c>
       <c r="F36" t="n">
-        <v>243.01780536</v>
+        <v>120.77072082</v>
       </c>
       <c r="G36" t="n">
-        <v>120.77072082</v>
+        <v>227.54441106</v>
       </c>
       <c r="H36" t="n">
-        <v>227.54441106</v>
+        <v>364.58955555</v>
       </c>
       <c r="I36" t="n">
-        <v>364.58955555</v>
+        <v>215.34440896</v>
       </c>
       <c r="J36" t="n">
-        <v>215.34440896</v>
+        <v>203.11277483</v>
       </c>
       <c r="K36" t="n">
-        <v>203.11277483</v>
+        <v>-9.032017559999998</v>
       </c>
       <c r="L36" t="n">
-        <v>-9.032017559999998</v>
+        <v>184.61897931</v>
       </c>
       <c r="M36" t="n">
-        <v>184.61897931</v>
+        <v>5.011323659999997</v>
       </c>
     </row>
     <row r="37">
@@ -1944,37 +1942,37 @@
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>3.358943199999999</v>
+        <v>12.32487082</v>
       </c>
       <c r="D37" t="n">
-        <v>21.65631013</v>
+        <v>26.76512174</v>
       </c>
       <c r="E37" t="n">
-        <v>37.15833097</v>
+        <v>29.93842295</v>
       </c>
       <c r="F37" t="n">
-        <v>41.52823503</v>
+        <v>34.89785375</v>
       </c>
       <c r="G37" t="n">
-        <v>46.73594826000001</v>
+        <v>5.251687500000002</v>
       </c>
       <c r="H37" t="n">
-        <v>4.982251610000001</v>
+        <v>-1.198131249999999</v>
       </c>
       <c r="I37" t="n">
-        <v>6.840031639999999</v>
+        <v>25.6866078</v>
       </c>
       <c r="J37" t="n">
-        <v>35.03138665</v>
+        <v>11.81555731</v>
       </c>
       <c r="K37" t="n">
-        <v>8.22256728</v>
+        <v>15.79877344</v>
       </c>
       <c r="L37" t="n">
-        <v>18.62594352</v>
+        <v>14.04205434</v>
       </c>
       <c r="M37" t="n">
-        <v>6.7077866</v>
+        <v>44.0899897</v>
       </c>
     </row>
     <row r="38">
@@ -1985,37 +1983,37 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>-45.11636293</v>
+        <v>-1.056509029999998</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.056509029999998</v>
+        <v>56.57809310999999</v>
       </c>
       <c r="E38" t="n">
-        <v>56.57809310999999</v>
+        <v>21.60893473000001</v>
       </c>
       <c r="F38" t="n">
-        <v>21.60893473000001</v>
+        <v>-37.8064404</v>
       </c>
       <c r="G38" t="n">
-        <v>-37.8064404</v>
+        <v>-64.52067828999999</v>
       </c>
       <c r="H38" t="n">
-        <v>-64.52067828999999</v>
+        <v>-17.82765088</v>
       </c>
       <c r="I38" t="n">
-        <v>-17.82765088</v>
+        <v>30.20554926</v>
       </c>
       <c r="J38" t="n">
-        <v>30.20554926</v>
+        <v>37.14663873000001</v>
       </c>
       <c r="K38" t="n">
-        <v>37.14663873000001</v>
+        <v>-20.40864164</v>
       </c>
       <c r="L38" t="n">
-        <v>-20.40864164</v>
+        <v>2.93989154</v>
       </c>
       <c r="M38" t="n">
-        <v>2.93989154</v>
+        <v>-48.22699395</v>
       </c>
     </row>
     <row r="39">
@@ -2026,37 +2024,37 @@
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
-        <v>-1.22895808</v>
+        <v>2.09904764</v>
       </c>
       <c r="D39" t="n">
-        <v>2.09904764</v>
+        <v>3.22631047</v>
       </c>
       <c r="E39" t="n">
-        <v>3.22631047</v>
+        <v>8.135896049999999</v>
       </c>
       <c r="F39" t="n">
-        <v>8.135896049999999</v>
+        <v>0.42597227</v>
       </c>
       <c r="G39" t="n">
-        <v>0.42597227</v>
+        <v>5.236759269999999</v>
       </c>
       <c r="H39" t="n">
-        <v>5.236759269999999</v>
+        <v>24.80576117</v>
       </c>
       <c r="I39" t="n">
-        <v>24.80576117</v>
+        <v>21.99748971</v>
       </c>
       <c r="J39" t="n">
-        <v>21.99748971</v>
+        <v>7.5667577</v>
       </c>
       <c r="K39" t="n">
-        <v>7.5667577</v>
+        <v>-0.39082327</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.39082327</v>
+        <v>6.9156605</v>
       </c>
       <c r="M39" t="n">
-        <v>6.9156605</v>
+        <v>-3.65105099</v>
       </c>
     </row>
     <row r="40">
@@ -2067,37 +2065,37 @@
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>54.65563677999999</v>
+        <v>-39.94501549</v>
       </c>
       <c r="D40" t="n">
-        <v>-40.04566426</v>
+        <v>-65.26585011</v>
       </c>
       <c r="E40" t="n">
-        <v>-65.28418285000001</v>
+        <v>-32.772473</v>
       </c>
       <c r="F40" t="n">
-        <v>-32.76076323</v>
+        <v>-17.85393562</v>
       </c>
       <c r="G40" t="n">
-        <v>-17.83607626</v>
+        <v>-34.21927984000001</v>
       </c>
       <c r="H40" t="n">
-        <v>-34.19595065</v>
+        <v>-18.29832132</v>
       </c>
       <c r="I40" t="n">
-        <v>-18.27668358</v>
+        <v>16.51942199</v>
       </c>
       <c r="J40" t="n">
-        <v>16.53820925</v>
+        <v>-19.21069481</v>
       </c>
       <c r="K40" t="n">
-        <v>-19.19783037</v>
+        <v>-76.86549835</v>
       </c>
       <c r="L40" t="n">
-        <v>-76.84971587000001</v>
+        <v>-32.5970419</v>
       </c>
       <c r="M40" t="n">
-        <v>-32.57665906</v>
+        <v>-50.29811102</v>
       </c>
     </row>
     <row r="41">
@@ -2108,37 +2106,37 @@
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
-        <v>0.007071730000000001</v>
+        <v>8.451e-05</v>
       </c>
       <c r="D41" t="n">
-        <v>0.10073328</v>
+        <v>9.454000000000001e-05</v>
       </c>
       <c r="E41" t="n">
-        <v>0.01842728</v>
+        <v>-0.00014463</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.0118544</v>
+        <v>-7.391e-05</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.01793327</v>
+        <v>-2.001e-05</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.0233492</v>
+        <v>4.417e-05</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.02159357</v>
+        <v>9.085e-05</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.01869641</v>
+        <v>-7.104999999999999e-05</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.01293549</v>
+        <v>-0.00022371</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.01600619</v>
+        <v>-0.00012</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.02050284</v>
+        <v>-0.00023445</v>
       </c>
     </row>
     <row r="42">
@@ -2149,37 +2147,37 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>769.43496877</v>
+        <v>271.10624811</v>
       </c>
       <c r="D42" t="n">
-        <v>271.10624811</v>
+        <v>-68.5816458</v>
       </c>
       <c r="E42" t="n">
-        <v>-68.5816458</v>
+        <v>-26.60399435</v>
       </c>
       <c r="F42" t="n">
-        <v>-26.60399435</v>
+        <v>-205.2773343</v>
       </c>
       <c r="G42" t="n">
-        <v>-205.2773343</v>
+        <v>-28.30046276</v>
       </c>
       <c r="H42" t="n">
-        <v>-28.30046276</v>
+        <v>155.55902704</v>
       </c>
       <c r="I42" t="n">
-        <v>155.55902704</v>
+        <v>582.9563215699999</v>
       </c>
       <c r="J42" t="n">
-        <v>582.9563215699999</v>
+        <v>919.0814701600001</v>
       </c>
       <c r="K42" t="n">
-        <v>919.0814701600001</v>
+        <v>1187.41765549</v>
       </c>
       <c r="L42" t="n">
-        <v>1187.41765549</v>
+        <v>1289.85564071</v>
       </c>
       <c r="M42" t="n">
-        <v>1289.85564071</v>
+        <v>1322.24512202</v>
       </c>
     </row>
     <row r="43">
@@ -2190,37 +2188,37 @@
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
-        <v>1.44990002</v>
+        <v>0.19227776</v>
       </c>
       <c r="D43" t="n">
-        <v>0.19227776</v>
+        <v>1.29170596</v>
       </c>
       <c r="E43" t="n">
-        <v>1.29170596</v>
+        <v>2.10339348</v>
       </c>
       <c r="F43" t="n">
-        <v>2.10339348</v>
+        <v>0.38728135</v>
       </c>
       <c r="G43" t="n">
-        <v>0.38728135</v>
+        <v>-0.48629467</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.48629467</v>
+        <v>-1.52022097</v>
       </c>
       <c r="I43" t="n">
-        <v>-1.52022097</v>
+        <v>-0.80378561</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.80378561</v>
+        <v>2.28745028</v>
       </c>
       <c r="K43" t="n">
-        <v>2.28745028</v>
+        <v>0.67277188</v>
       </c>
       <c r="L43" t="n">
-        <v>0.67277188</v>
+        <v>0.93779075</v>
       </c>
       <c r="M43" t="n">
-        <v>0.93779075</v>
+        <v>1.58338164</v>
       </c>
     </row>
     <row r="44">
@@ -2231,37 +2229,37 @@
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>80.12160184</v>
+        <v>15.68920713</v>
       </c>
       <c r="D44" t="n">
-        <v>-52.86507272</v>
+        <v>14.92937701</v>
       </c>
       <c r="E44" t="n">
-        <v>37.46158601</v>
+        <v>17.13186568</v>
       </c>
       <c r="F44" t="n">
-        <v>83.43559676999999</v>
+        <v>4.961326819999999</v>
       </c>
       <c r="G44" t="n">
-        <v>81.79199306</v>
+        <v>11.88330336</v>
       </c>
       <c r="H44" t="n">
-        <v>103.719146</v>
+        <v>11.99597497</v>
       </c>
       <c r="I44" t="n">
-        <v>28.17386177</v>
+        <v>10.73997102</v>
       </c>
       <c r="J44" t="n">
-        <v>77.18747601999999</v>
+        <v>-8.907961029999999</v>
       </c>
       <c r="K44" t="n">
-        <v>133.43583258</v>
+        <v>-21.06636615</v>
       </c>
       <c r="L44" t="n">
-        <v>170.96596239</v>
+        <v>-25.51100199</v>
       </c>
       <c r="M44" t="n">
-        <v>26.97087123</v>
+        <v>-20.91638637</v>
       </c>
     </row>
     <row r="45">
@@ -2270,39 +2268,41 @@
           <t>生技醫療業右下</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
+      <c r="B45" t="n">
+        <v>0</v>
+      </c>
       <c r="C45" t="n">
-        <v>-301.92317178</v>
+        <v>-60.83971186</v>
       </c>
       <c r="D45" t="n">
-        <v>-60.52257173</v>
+        <v>7.91255782</v>
       </c>
       <c r="E45" t="n">
-        <v>12.40978543000001</v>
+        <v>27.53252192</v>
       </c>
       <c r="F45" t="n">
-        <v>34.89329313</v>
+        <v>114.64316707</v>
       </c>
       <c r="G45" t="n">
-        <v>122.56977911</v>
+        <v>263.10772292</v>
       </c>
       <c r="H45" t="n">
-        <v>263.33302193</v>
+        <v>100.07117049</v>
       </c>
       <c r="I45" t="n">
-        <v>96.62626367000001</v>
+        <v>184.39132701</v>
       </c>
       <c r="J45" t="n">
-        <v>184.2028899</v>
+        <v>200.1556611</v>
       </c>
       <c r="K45" t="n">
-        <v>197.75035785</v>
+        <v>282.17230585</v>
       </c>
       <c r="L45" t="n">
-        <v>293.1900217</v>
+        <v>413.65452745</v>
       </c>
       <c r="M45" t="n">
-        <v>426.00817599</v>
+        <v>542.3939973099999</v>
       </c>
     </row>
     <row r="46">
@@ -2313,37 +2313,37 @@
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>-38.67281785</v>
+        <v>-36.90118062</v>
       </c>
       <c r="D46" t="n">
-        <v>31.39405054</v>
+        <v>92.74919083</v>
       </c>
       <c r="E46" t="n">
-        <v>65.72468522</v>
+        <v>1.34486754000001</v>
       </c>
       <c r="F46" t="n">
-        <v>-72.19612522</v>
+        <v>80.49257423999998</v>
       </c>
       <c r="G46" t="n">
-        <v>-4.134493600000007</v>
+        <v>50.73410844999999</v>
       </c>
       <c r="H46" t="n">
-        <v>-41.23027432000001</v>
+        <v>-62.64354142</v>
       </c>
       <c r="I46" t="n">
-        <v>-75.34814689</v>
+        <v>75.29830637000001</v>
       </c>
       <c r="J46" t="n">
-        <v>9.027543470000003</v>
+        <v>104.42617998</v>
       </c>
       <c r="K46" t="n">
-        <v>-35.45215350000001</v>
+        <v>259.50226107</v>
       </c>
       <c r="L46" t="n">
-        <v>56.42522958999999</v>
+        <v>79.21859855</v>
       </c>
       <c r="M46" t="n">
-        <v>14.355379</v>
+        <v>-48.40696312000001</v>
       </c>
     </row>
     <row r="47">
@@ -2354,37 +2354,37 @@
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>-5.16051644</v>
+        <v>-5.50110454</v>
       </c>
       <c r="D47" t="n">
-        <v>-5.243580819999999</v>
+        <v>-6.2041725</v>
       </c>
       <c r="E47" t="n">
-        <v>-1.42689061</v>
+        <v>-3.20158006</v>
       </c>
       <c r="F47" t="n">
-        <v>-1.55805487</v>
+        <v>1.12057703</v>
       </c>
       <c r="G47" t="n">
-        <v>0.2128199</v>
+        <v>-0.37868869</v>
       </c>
       <c r="H47" t="n">
-        <v>0.11380938</v>
+        <v>-3.99151647</v>
       </c>
       <c r="I47" t="n">
-        <v>-1.16393911</v>
+        <v>2.80991257</v>
       </c>
       <c r="J47" t="n">
-        <v>3.26730915</v>
+        <v>15.48498561</v>
       </c>
       <c r="K47" t="n">
-        <v>1.63955288</v>
+        <v>62.07577929</v>
       </c>
       <c r="L47" t="n">
-        <v>0.7404075099999999</v>
+        <v>95.45228308</v>
       </c>
       <c r="M47" t="n">
-        <v>2.84180396</v>
+        <v>201.70015159</v>
       </c>
     </row>
     <row r="48">
@@ -2395,37 +2395,37 @@
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
-        <v>18.61284379</v>
+        <v>26.69719218</v>
       </c>
       <c r="D48" t="n">
-        <v>26.69718061</v>
+        <v>6.876008539999998</v>
       </c>
       <c r="E48" t="n">
-        <v>6.876004369999999</v>
+        <v>-21.01691342</v>
       </c>
       <c r="F48" t="n">
-        <v>-21.01691388</v>
+        <v>-15.13194856</v>
       </c>
       <c r="G48" t="n">
-        <v>-15.13193809</v>
+        <v>-100.97582182</v>
       </c>
       <c r="H48" t="n">
-        <v>-100.97579443</v>
+        <v>-162.47494265</v>
       </c>
       <c r="I48" t="n">
-        <v>-162.4749122</v>
+        <v>-138.91383049</v>
       </c>
       <c r="J48" t="n">
-        <v>-138.91380902</v>
+        <v>-65.78406750000001</v>
       </c>
       <c r="K48" t="n">
-        <v>-65.78404603</v>
+        <v>100.66741346</v>
       </c>
       <c r="L48" t="n">
-        <v>100.66743719</v>
+        <v>167.30680064</v>
       </c>
       <c r="M48" t="n">
-        <v>167.30677723</v>
+        <v>94.00985389</v>
       </c>
     </row>
     <row r="49">
@@ -2436,37 +2436,37 @@
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>2.18193317</v>
+        <v>1.65278435</v>
       </c>
       <c r="D49" t="n">
-        <v>1.3952722</v>
+        <v>1.32682909</v>
       </c>
       <c r="E49" t="n">
-        <v>-3.45044863</v>
+        <v>0.25557084</v>
       </c>
       <c r="F49" t="n">
-        <v>-1.38795389</v>
+        <v>-0.002220260000000012</v>
       </c>
       <c r="G49" t="n">
-        <v>0.9055264000000001</v>
+        <v>-0.21206577</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.70459123</v>
+        <v>-0.3229723599999999</v>
       </c>
       <c r="I49" t="n">
-        <v>-3.15058017</v>
+        <v>-0.64211001</v>
       </c>
       <c r="J49" t="n">
-        <v>-1.09952806</v>
+        <v>-0.68773007</v>
       </c>
       <c r="K49" t="n">
-        <v>13.15768119</v>
+        <v>-0.8016744100000001</v>
       </c>
       <c r="L49" t="n">
-        <v>60.53367364</v>
+        <v>-0.6050358499999999</v>
       </c>
       <c r="M49" t="n">
-        <v>92.00546668000001</v>
+        <v>-0.16058108</v>
       </c>
     </row>
     <row r="50">
@@ -2477,37 +2477,37 @@
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
-        <v>-31.44969937</v>
+        <v>-116.33562401</v>
       </c>
       <c r="D50" t="n">
-        <v>-116.33562401</v>
+        <v>-6.691790779999997</v>
       </c>
       <c r="E50" t="n">
-        <v>-6.691790779999997</v>
+        <v>-115.82523807</v>
       </c>
       <c r="F50" t="n">
-        <v>-115.82523807</v>
+        <v>53.49678095</v>
       </c>
       <c r="G50" t="n">
-        <v>53.49678095</v>
+        <v>-66.54429746</v>
       </c>
       <c r="H50" t="n">
-        <v>-66.54429746</v>
+        <v>-48.69457564000001</v>
       </c>
       <c r="I50" t="n">
-        <v>-48.69457564000001</v>
+        <v>-31.82532077</v>
       </c>
       <c r="J50" t="n">
-        <v>-31.82532077</v>
+        <v>-102.22615871</v>
       </c>
       <c r="K50" t="n">
-        <v>-102.22615871</v>
+        <v>-21.90862964999999</v>
       </c>
       <c r="L50" t="n">
-        <v>-21.90862964999999</v>
+        <v>59.43721305</v>
       </c>
       <c r="M50" t="n">
-        <v>59.43721305</v>
+        <v>46.93449081</v>
       </c>
     </row>
     <row r="51">
@@ -2516,39 +2516,41 @@
           <t>綠能環保右下</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
       <c r="C51" t="n">
-        <v>2.53485937</v>
+        <v>-2.5437199</v>
       </c>
       <c r="D51" t="n">
-        <v>-2.54366476</v>
+        <v>4.033055200000001</v>
       </c>
       <c r="E51" t="n">
-        <v>4.03323023</v>
+        <v>-4.20818115</v>
       </c>
       <c r="F51" t="n">
-        <v>-4.208008479999999</v>
+        <v>-16.66827323</v>
       </c>
       <c r="G51" t="n">
-        <v>-16.668004</v>
+        <v>-17.31015195</v>
       </c>
       <c r="H51" t="n">
-        <v>-17.31000216</v>
+        <v>-27.00139775</v>
       </c>
       <c r="I51" t="n">
-        <v>-27.00119206</v>
+        <v>-37.85275703</v>
       </c>
       <c r="J51" t="n">
-        <v>-37.85262138</v>
+        <v>-40.22167216</v>
       </c>
       <c r="K51" t="n">
-        <v>-40.22165305999999</v>
+        <v>-40.80030042</v>
       </c>
       <c r="L51" t="n">
-        <v>-40.80044587</v>
+        <v>-105.72039485</v>
       </c>
       <c r="M51" t="n">
-        <v>-105.72065853</v>
+        <v>-88.20195445</v>
       </c>
     </row>
     <row r="52">
@@ -2559,37 +2561,37 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>18.48084824</v>
+        <v>0.99142799</v>
       </c>
       <c r="D52" t="n">
-        <v>2.56069713</v>
+        <v>23.8068687</v>
       </c>
       <c r="E52" t="n">
-        <v>23.80545876</v>
+        <v>22.08568782</v>
       </c>
       <c r="F52" t="n">
-        <v>22.47130776</v>
+        <v>7.470954930000001</v>
       </c>
       <c r="G52" t="n">
-        <v>8.574985620000001</v>
+        <v>11.96612713</v>
       </c>
       <c r="H52" t="n">
-        <v>13.58030427</v>
+        <v>-8.497503110000002</v>
       </c>
       <c r="I52" t="n">
-        <v>-8.368601980000001</v>
+        <v>-0.7377022899999989</v>
       </c>
       <c r="J52" t="n">
-        <v>0.7310655100000012</v>
+        <v>1.139528689999999</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.2081954600000009</v>
+        <v>-21.90009003</v>
       </c>
       <c r="L52" t="n">
-        <v>-23.608655</v>
+        <v>-24.02962719</v>
       </c>
       <c r="M52" t="n">
-        <v>-24.72453738</v>
+        <v>-4.317856819999998</v>
       </c>
     </row>
     <row r="53">
@@ -2600,37 +2602,37 @@
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>176.6907841</v>
+        <v>142.87783066</v>
       </c>
       <c r="D53" t="n">
-        <v>173.38863384</v>
+        <v>508.6557417999999</v>
       </c>
       <c r="E53" t="n">
-        <v>534.25715562</v>
+        <v>566.7019476200001</v>
       </c>
       <c r="F53" t="n">
-        <v>553.16674841</v>
+        <v>-209.21155652</v>
       </c>
       <c r="G53" t="n">
-        <v>-153.03526199</v>
+        <v>2.472013799999998</v>
       </c>
       <c r="H53" t="n">
-        <v>23.20095008999999</v>
+        <v>181.3128095</v>
       </c>
       <c r="I53" t="n">
-        <v>202.3618308</v>
+        <v>409.82417843</v>
       </c>
       <c r="J53" t="n">
-        <v>368.14814455</v>
+        <v>679.7734486099999</v>
       </c>
       <c r="K53" t="n">
-        <v>697.0104023600001</v>
+        <v>585.0456973400001</v>
       </c>
       <c r="L53" t="n">
-        <v>588.32413694</v>
+        <v>589.5573766699999</v>
       </c>
       <c r="M53" t="n">
-        <v>568.4089294300001</v>
+        <v>716.6848599800001</v>
       </c>
     </row>
     <row r="54">
@@ -2641,37 +2643,37 @@
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>-0.9628130199999999</v>
+        <v>12.23336543</v>
       </c>
       <c r="D54" t="n">
-        <v>9.50489205</v>
+        <v>7.459217189999999</v>
       </c>
       <c r="E54" t="n">
-        <v>6.19144345</v>
+        <v>20.46282913</v>
       </c>
       <c r="F54" t="n">
-        <v>18.44292239</v>
+        <v>34.59465452000001</v>
       </c>
       <c r="G54" t="n">
-        <v>33.41217956000001</v>
+        <v>30.05918976</v>
       </c>
       <c r="H54" t="n">
-        <v>32.28907975000001</v>
+        <v>15.45659664</v>
       </c>
       <c r="I54" t="n">
-        <v>13.82758123</v>
+        <v>22.21853231</v>
       </c>
       <c r="J54" t="n">
-        <v>22.66509357</v>
+        <v>15.38179527</v>
       </c>
       <c r="K54" t="n">
-        <v>11.76005505</v>
+        <v>9.58508578</v>
       </c>
       <c r="L54" t="n">
-        <v>15.07171019</v>
+        <v>0.4767019700000001</v>
       </c>
       <c r="M54" t="n">
-        <v>11.96384752</v>
+        <v>13.22037048</v>
       </c>
     </row>
     <row r="55">
@@ -2682,37 +2684,37 @@
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>76.22848026000001</v>
+        <v>117.72272026</v>
       </c>
       <c r="D55" t="n">
-        <v>89.94039045999999</v>
+        <v>137.14212586</v>
       </c>
       <c r="E55" t="n">
-        <v>112.80848578</v>
+        <v>245.93981889</v>
       </c>
       <c r="F55" t="n">
-        <v>261.49492484</v>
+        <v>61.47470569</v>
       </c>
       <c r="G55" t="n">
-        <v>6.48088612</v>
+        <v>417.51288219</v>
       </c>
       <c r="H55" t="n">
-        <v>394.55405591</v>
+        <v>335.02176883</v>
       </c>
       <c r="I55" t="n">
-        <v>315.60176294</v>
+        <v>327.50170306</v>
       </c>
       <c r="J55" t="n">
-        <v>368.73117568</v>
+        <v>49.01342843</v>
       </c>
       <c r="K55" t="n">
-        <v>35.39821490000001</v>
+        <v>24.07183576999999</v>
       </c>
       <c r="L55" t="n">
-        <v>15.30677176000001</v>
+        <v>-60.46578947</v>
       </c>
       <c r="M55" t="n">
-        <v>-50.80448778</v>
+        <v>107.76169173</v>
       </c>
     </row>
     <row r="56">
@@ -2723,37 +2725,37 @@
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>2.08191375</v>
+        <v>-7.278711120000001</v>
       </c>
       <c r="D56" t="n">
-        <v>-7.27952517</v>
+        <v>-1.98096138</v>
       </c>
       <c r="E56" t="n">
-        <v>-1.98157208</v>
+        <v>-4.11638705</v>
       </c>
       <c r="F56" t="n">
-        <v>-4.11619094</v>
+        <v>4.08089557</v>
       </c>
       <c r="G56" t="n">
-        <v>4.08045064</v>
+        <v>-0.1995485</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.19953913</v>
+        <v>-12.28237295</v>
       </c>
       <c r="I56" t="n">
-        <v>-12.28212704</v>
+        <v>-2.91487422</v>
       </c>
       <c r="J56" t="n">
-        <v>-2.91420292</v>
+        <v>20.8052581</v>
       </c>
       <c r="K56" t="n">
-        <v>20.80548296</v>
+        <v>4.32875445</v>
       </c>
       <c r="L56" t="n">
-        <v>4.32854381</v>
+        <v>9.664215899999999</v>
       </c>
       <c r="M56" t="n">
-        <v>9.662940969999999</v>
+        <v>19.0901028</v>
       </c>
     </row>
     <row r="57">
@@ -2762,41 +2764,39 @@
           <t>觀光事業右下</t>
         </is>
       </c>
-      <c r="B57" t="n">
-        <v>0</v>
-      </c>
+      <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
-        <v>-2.52893461</v>
+        <v>24.12932168</v>
       </c>
       <c r="D57" t="n">
-        <v>23.74879822</v>
+        <v>19.6332461</v>
       </c>
       <c r="E57" t="n">
-        <v>18.9220015</v>
+        <v>9.52188091</v>
       </c>
       <c r="F57" t="n">
-        <v>8.37023009</v>
+        <v>-6.490226310000001</v>
       </c>
       <c r="G57" t="n">
-        <v>-7.02994692</v>
+        <v>-19.63733982</v>
       </c>
       <c r="H57" t="n">
-        <v>-19.5461556</v>
+        <v>-31.28678731</v>
       </c>
       <c r="I57" t="n">
-        <v>-30.63795106</v>
+        <v>-35.8224009</v>
       </c>
       <c r="J57" t="n">
-        <v>-34.1687701</v>
+        <v>-48.83657307</v>
       </c>
       <c r="K57" t="n">
-        <v>-46.96409482</v>
+        <v>-2.96100229</v>
       </c>
       <c r="L57" t="n">
-        <v>-1.62805522</v>
+        <v>-4.13295156</v>
       </c>
       <c r="M57" t="n">
-        <v>-3.08028842</v>
+        <v>-6.76115287</v>
       </c>
     </row>
     <row r="58">
@@ -2807,37 +2807,37 @@
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>15.59515841</v>
+        <v>34.83619801</v>
       </c>
       <c r="D58" t="n">
-        <v>34.83701206</v>
+        <v>44.05377982</v>
       </c>
       <c r="E58" t="n">
-        <v>44.05439052</v>
+        <v>45.77332355000001</v>
       </c>
       <c r="F58" t="n">
-        <v>45.77312744</v>
+        <v>20.38771257</v>
       </c>
       <c r="G58" t="n">
-        <v>20.3881575</v>
+        <v>-9.583194499999999</v>
       </c>
       <c r="H58" t="n">
-        <v>-9.58320387</v>
+        <v>-17.24568169</v>
       </c>
       <c r="I58" t="n">
-        <v>-17.2459276</v>
+        <v>-34.94886270000001</v>
       </c>
       <c r="J58" t="n">
-        <v>-34.949534</v>
+        <v>-42.1867673</v>
       </c>
       <c r="K58" t="n">
-        <v>-42.18699216</v>
+        <v>-0.99581925</v>
       </c>
       <c r="L58" t="n">
-        <v>-0.99560861</v>
+        <v>-6.33419032</v>
       </c>
       <c r="M58" t="n">
-        <v>-6.332915389999999</v>
+        <v>8.21714162</v>
       </c>
     </row>
     <row r="59">
@@ -2848,37 +2848,37 @@
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
-        <v>6.96574599</v>
+        <v>42.54732838</v>
       </c>
       <c r="D59" t="n">
-        <v>42.54732838</v>
+        <v>65.16556917</v>
       </c>
       <c r="E59" t="n">
-        <v>65.16556917</v>
+        <v>39.0396422</v>
       </c>
       <c r="F59" t="n">
-        <v>39.0396422</v>
+        <v>50.5705571</v>
       </c>
       <c r="G59" t="n">
-        <v>50.5705571</v>
+        <v>29.48116599</v>
       </c>
       <c r="H59" t="n">
-        <v>29.48116599</v>
+        <v>3.745202050000001</v>
       </c>
       <c r="I59" t="n">
-        <v>3.745202050000001</v>
+        <v>-27.11462849</v>
       </c>
       <c r="J59" t="n">
-        <v>-27.11462849</v>
+        <v>-14.54311404</v>
       </c>
       <c r="K59" t="n">
-        <v>-14.54311404</v>
+        <v>-20.20816677</v>
       </c>
       <c r="L59" t="n">
-        <v>-20.20816677</v>
+        <v>-48.84269329</v>
       </c>
       <c r="M59" t="n">
-        <v>-48.84269329</v>
+        <v>-21.3959596</v>
       </c>
     </row>
     <row r="60">
@@ -2889,37 +2889,37 @@
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
-        <v>0.0294527</v>
+        <v>0.02929013</v>
       </c>
       <c r="D60" t="n">
-        <v>0.02929013</v>
+        <v>0.00690925</v>
       </c>
       <c r="E60" t="n">
-        <v>0.00690925</v>
+        <v>-0.002395420000000002</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.002395420000000002</v>
+        <v>0.0890145</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0890145</v>
+        <v>0.02680047</v>
       </c>
       <c r="H60" t="n">
-        <v>0.02680047</v>
+        <v>0.03247147</v>
       </c>
       <c r="I60" t="n">
-        <v>0.03247147</v>
+        <v>0.03435918</v>
       </c>
       <c r="J60" t="n">
-        <v>0.03435918</v>
+        <v>0.0329061</v>
       </c>
       <c r="K60" t="n">
-        <v>0.0329061</v>
+        <v>-0.007547529999999998</v>
       </c>
       <c r="L60" t="n">
-        <v>-0.007547529999999998</v>
+        <v>0.06462674</v>
       </c>
       <c r="M60" t="n">
-        <v>0.06462674</v>
+        <v>-0.03165479</v>
       </c>
     </row>
     <row r="61">
@@ -2930,37 +2930,37 @@
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
-        <v>32.19605009</v>
+        <v>65.72478599999999</v>
       </c>
       <c r="D61" t="n">
-        <v>66.00294479</v>
+        <v>94.84815691</v>
       </c>
       <c r="E61" t="n">
-        <v>95.20210945000001</v>
+        <v>51.98647528</v>
       </c>
       <c r="F61" t="n">
-        <v>52.08635829</v>
+        <v>56.01972017</v>
       </c>
       <c r="G61" t="n">
-        <v>56.2651835</v>
+        <v>4.570142489999996</v>
       </c>
       <c r="H61" t="n">
-        <v>4.496421909999995</v>
+        <v>16.01686962</v>
       </c>
       <c r="I61" t="n">
-        <v>16.5218095</v>
+        <v>67.11095942</v>
       </c>
       <c r="J61" t="n">
-        <v>67.27009512000001</v>
+        <v>-17.12267397</v>
       </c>
       <c r="K61" t="n">
-        <v>-16.92938799</v>
+        <v>-37.94971968</v>
       </c>
       <c r="L61" t="n">
-        <v>-37.98414687</v>
+        <v>-34.75882616</v>
       </c>
       <c r="M61" t="n">
-        <v>-34.65845204999999</v>
+        <v>-52.83354714</v>
       </c>
     </row>
     <row r="62">
@@ -2969,41 +2969,39 @@
           <t>資訊服務業右下</t>
         </is>
       </c>
-      <c r="B62" t="n">
-        <v>0</v>
-      </c>
+      <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>5.92041929</v>
+        <v>6.52392742</v>
       </c>
       <c r="D62" t="n">
-        <v>6.52392742</v>
+        <v>6.715422149999999</v>
       </c>
       <c r="E62" t="n">
-        <v>6.715422149999999</v>
+        <v>5.812983760000001</v>
       </c>
       <c r="F62" t="n">
-        <v>5.812983760000001</v>
+        <v>3.00061214</v>
       </c>
       <c r="G62" t="n">
-        <v>3.00061214</v>
+        <v>-6.38541483</v>
       </c>
       <c r="H62" t="n">
-        <v>-6.38541483</v>
+        <v>-9.712041819999998</v>
       </c>
       <c r="I62" t="n">
-        <v>-9.712041819999998</v>
+        <v>-5.19174317</v>
       </c>
       <c r="J62" t="n">
-        <v>-5.19174317</v>
+        <v>-4.46376258</v>
       </c>
       <c r="K62" t="n">
-        <v>-4.46376258</v>
+        <v>-3.86283365</v>
       </c>
       <c r="L62" t="n">
-        <v>-3.86283365</v>
+        <v>-4.498926060000001</v>
       </c>
       <c r="M62" t="n">
-        <v>-4.498926060000001</v>
+        <v>-1.64025771</v>
       </c>
     </row>
     <row r="63">
@@ -3014,37 +3012,37 @@
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>22.72898805</v>
+        <v>41.13984781</v>
       </c>
       <c r="D63" t="n">
-        <v>41.13900461</v>
+        <v>88.15517082</v>
       </c>
       <c r="E63" t="n">
-        <v>88.15215049</v>
+        <v>40.93981619</v>
       </c>
       <c r="F63" t="n">
-        <v>40.93864671</v>
+        <v>38.2480204</v>
       </c>
       <c r="G63" t="n">
-        <v>38.24771547</v>
+        <v>23.40917579</v>
       </c>
       <c r="H63" t="n">
-        <v>23.4096762</v>
+        <v>28.16733624</v>
       </c>
       <c r="I63" t="n">
-        <v>28.16626605</v>
+        <v>35.37618777</v>
       </c>
       <c r="J63" t="n">
-        <v>35.37615519</v>
+        <v>33.86892229</v>
       </c>
       <c r="K63" t="n">
-        <v>33.8697661</v>
+        <v>2.500389020000001</v>
       </c>
       <c r="L63" t="n">
-        <v>2.50047791</v>
+        <v>-18.08390008</v>
       </c>
       <c r="M63" t="n">
-        <v>-18.08325091</v>
+        <v>-15.90958686</v>
       </c>
     </row>
     <row r="64">
@@ -3055,37 +3053,37 @@
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
-        <v>0.00103174</v>
+        <v>0.0009914099999999999</v>
       </c>
       <c r="D64" t="n">
-        <v>0.0009914099999999999</v>
+        <v>6.247e-05</v>
       </c>
       <c r="E64" t="n">
-        <v>6.247e-05</v>
+        <v>0.0004044</v>
       </c>
       <c r="F64" t="n">
-        <v>0.0004044</v>
+        <v>0.00072251</v>
       </c>
       <c r="G64" t="n">
-        <v>0.00072251</v>
+        <v>-0.00025412</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.00025412</v>
+        <v>-0.00126824</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.00126824</v>
+        <v>-0.00052996</v>
       </c>
       <c r="J64" t="n">
-        <v>-0.00052996</v>
+        <v>-4.627e-05</v>
       </c>
       <c r="K64" t="n">
-        <v>-4.627e-05</v>
+        <v>0.00012135</v>
       </c>
       <c r="L64" t="n">
-        <v>0.00012135</v>
+        <v>0.00033795</v>
       </c>
       <c r="M64" t="n">
-        <v>0.00033795</v>
+        <v>0.0007966399999999999</v>
       </c>
     </row>
     <row r="65">
@@ -3096,37 +3094,37 @@
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
-        <v>-0.0002609000000000001</v>
+        <v>5.814e-05</v>
       </c>
       <c r="D65" t="n">
-        <v>5.814e-05</v>
+        <v>0.00018835</v>
       </c>
       <c r="E65" t="n">
-        <v>0.00018835</v>
+        <v>2.243e-05</v>
       </c>
       <c r="F65" t="n">
-        <v>2.243e-05</v>
+        <v>-8.019e-05</v>
       </c>
       <c r="G65" t="n">
-        <v>-8.019e-05</v>
+        <v>-3.720999999999999e-05</v>
       </c>
       <c r="H65" t="n">
-        <v>-3.720999999999999e-05</v>
+        <v>-0.00012853</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.00012853</v>
+        <v>-0.00011783</v>
       </c>
       <c r="J65" t="n">
-        <v>-0.00011783</v>
+        <v>-0.00038662</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.00038662</v>
+        <v>-0.00020338</v>
       </c>
       <c r="L65" t="n">
-        <v>-0.00020338</v>
+        <v>2.062999999999999e-05</v>
       </c>
       <c r="M65" t="n">
-        <v>2.062999999999999e-05</v>
+        <v>7.988999999999998e-05</v>
       </c>
     </row>
     <row r="66">
@@ -3137,37 +3135,37 @@
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>-13.98078499000001</v>
+        <v>211.45186433</v>
       </c>
       <c r="D66" t="n">
-        <v>113.82940649</v>
+        <v>743.00310366</v>
       </c>
       <c r="E66" t="n">
-        <v>602.97937943</v>
+        <v>222.93098923</v>
       </c>
       <c r="F66" t="n">
-        <v>164.30663862</v>
+        <v>590.68221964</v>
       </c>
       <c r="G66" t="n">
-        <v>478.95908781</v>
+        <v>737.59955096</v>
       </c>
       <c r="H66" t="n">
-        <v>548.0155602000001</v>
+        <v>898.0649092000001</v>
       </c>
       <c r="I66" t="n">
-        <v>805.81832688</v>
+        <v>967.1187534999999</v>
       </c>
       <c r="J66" t="n">
-        <v>824.0944196200001</v>
+        <v>1194.77040763</v>
       </c>
       <c r="K66" t="n">
-        <v>1051.07870633</v>
+        <v>1051.66219636</v>
       </c>
       <c r="L66" t="n">
-        <v>1021.09156123</v>
+        <v>1086.08204445</v>
       </c>
       <c r="M66" t="n">
-        <v>919.67733936</v>
+        <v>1610.76237197</v>
       </c>
     </row>
     <row r="67">
@@ -3176,41 +3174,39 @@
           <t>通信網路業右下</t>
         </is>
       </c>
-      <c r="B67" t="n">
-        <v>0</v>
-      </c>
+      <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>14.35426651</v>
+        <v>3.661172020000002</v>
       </c>
       <c r="D67" t="n">
-        <v>3.661172020000002</v>
+        <v>43.03769867</v>
       </c>
       <c r="E67" t="n">
-        <v>43.03769867</v>
+        <v>-32.84988569</v>
       </c>
       <c r="F67" t="n">
-        <v>-32.84988569</v>
+        <v>-44.98339458</v>
       </c>
       <c r="G67" t="n">
-        <v>-44.98339458</v>
+        <v>-50.19198401999999</v>
       </c>
       <c r="H67" t="n">
-        <v>-50.19198401999999</v>
+        <v>-61.96146647</v>
       </c>
       <c r="I67" t="n">
-        <v>-61.96146647</v>
+        <v>-32.79786634</v>
       </c>
       <c r="J67" t="n">
-        <v>-32.79786634</v>
+        <v>-12.77004483</v>
       </c>
       <c r="K67" t="n">
-        <v>-12.77004483</v>
+        <v>-10.69580253</v>
       </c>
       <c r="L67" t="n">
-        <v>-10.69580253</v>
+        <v>-9.02277816</v>
       </c>
       <c r="M67" t="n">
-        <v>-9.02277816</v>
+        <v>18.34720585</v>
       </c>
     </row>
     <row r="68">
@@ -3221,37 +3217,37 @@
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>355.56638351</v>
+        <v>128.59152705</v>
       </c>
       <c r="D68" t="n">
-        <v>226.21071599</v>
+        <v>87.07690512000001</v>
       </c>
       <c r="E68" t="n">
-        <v>227.09530235</v>
+        <v>136.88226256</v>
       </c>
       <c r="F68" t="n">
-        <v>195.49797504</v>
+        <v>-89.61341375000001</v>
       </c>
       <c r="G68" t="n">
-        <v>22.10781184</v>
+        <v>-118.0715467</v>
       </c>
       <c r="H68" t="n">
-        <v>71.51372678000001</v>
+        <v>-65.87270255</v>
       </c>
       <c r="I68" t="n">
-        <v>26.37887649</v>
+        <v>86.07406949000001</v>
       </c>
       <c r="J68" t="n">
-        <v>229.10723779</v>
+        <v>-131.19495372</v>
       </c>
       <c r="K68" t="n">
-        <v>12.50703683999999</v>
+        <v>65.34373241999999</v>
       </c>
       <c r="L68" t="n">
-        <v>95.91743174000001</v>
+        <v>98.55402330000001</v>
       </c>
       <c r="M68" t="n">
-        <v>264.96250325</v>
+        <v>175.35373227</v>
       </c>
     </row>
     <row r="69">
@@ -3262,37 +3258,37 @@
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>-11.75977663</v>
+        <v>-14.45543988</v>
       </c>
       <c r="D69" t="n">
-        <v>-14.45543988</v>
+        <v>-8.60103045</v>
       </c>
       <c r="E69" t="n">
-        <v>-8.60103045</v>
+        <v>1.481096</v>
       </c>
       <c r="F69" t="n">
-        <v>1.481096</v>
+        <v>-2.09694106</v>
       </c>
       <c r="G69" t="n">
-        <v>-2.09694106</v>
+        <v>-1.18870531</v>
       </c>
       <c r="H69" t="n">
-        <v>-1.18870531</v>
+        <v>0.8999840899999999</v>
       </c>
       <c r="I69" t="n">
-        <v>0.8999840899999999</v>
+        <v>-1.07992369</v>
       </c>
       <c r="J69" t="n">
-        <v>-1.07992369</v>
+        <v>-8.13542947</v>
       </c>
       <c r="K69" t="n">
-        <v>-8.13542947</v>
+        <v>-6.112742610000001</v>
       </c>
       <c r="L69" t="n">
-        <v>-6.112742610000001</v>
+        <v>0.62737845</v>
       </c>
       <c r="M69" t="n">
-        <v>0.62737845</v>
+        <v>-1.39124728</v>
       </c>
     </row>
     <row r="70">
@@ -3303,37 +3299,37 @@
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>-3.60733925</v>
+        <v>-1.16033294</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.16033294</v>
+        <v>-1.55525517</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.55525517</v>
+        <v>0.15859867</v>
       </c>
       <c r="F70" t="n">
-        <v>0.15859867</v>
+        <v>-0.01651628</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.01651628</v>
+        <v>0.93115824</v>
       </c>
       <c r="H70" t="n">
-        <v>0.93115824</v>
+        <v>0.15324129</v>
       </c>
       <c r="I70" t="n">
-        <v>0.15324129</v>
+        <v>2.0141396</v>
       </c>
       <c r="J70" t="n">
-        <v>2.0141396</v>
+        <v>0.94456732</v>
       </c>
       <c r="K70" t="n">
-        <v>0.94456732</v>
+        <v>1.31059385</v>
       </c>
       <c r="L70" t="n">
-        <v>1.31059385</v>
+        <v>0.44808132</v>
       </c>
       <c r="M70" t="n">
-        <v>0.44808132</v>
+        <v>1.02481299</v>
       </c>
     </row>
     <row r="71">
@@ -3344,37 +3340,37 @@
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
-        <v>6.14054282</v>
+        <v>22.89727625</v>
       </c>
       <c r="D71" t="n">
-        <v>22.89727625</v>
+        <v>39.58487804</v>
       </c>
       <c r="E71" t="n">
-        <v>39.58487804</v>
+        <v>49.03197814</v>
       </c>
       <c r="F71" t="n">
-        <v>49.03197814</v>
+        <v>20.29127258</v>
       </c>
       <c r="G71" t="n">
-        <v>20.29127258</v>
+        <v>24.00895878</v>
       </c>
       <c r="H71" t="n">
-        <v>24.00895878</v>
+        <v>34.17125779</v>
       </c>
       <c r="I71" t="n">
-        <v>34.17125779</v>
+        <v>-3.0706811</v>
       </c>
       <c r="J71" t="n">
-        <v>-3.0706811</v>
+        <v>-7.127004649999999</v>
       </c>
       <c r="K71" t="n">
-        <v>-7.127004649999999</v>
+        <v>-16.45539349</v>
       </c>
       <c r="L71" t="n">
-        <v>-16.45539349</v>
+        <v>-1.46575611</v>
       </c>
       <c r="M71" t="n">
-        <v>-1.46575611</v>
+        <v>-28.70342079</v>
       </c>
     </row>
     <row r="72">
@@ -3385,37 +3381,37 @@
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>-103.65398381</v>
+        <v>-29.97898556</v>
       </c>
       <c r="D72" t="n">
-        <v>-29.97898556</v>
+        <v>-20.96570658</v>
       </c>
       <c r="E72" t="n">
-        <v>-20.96570658</v>
+        <v>-82.82987403</v>
       </c>
       <c r="F72" t="n">
-        <v>-82.82987403</v>
+        <v>-117.56860161</v>
       </c>
       <c r="G72" t="n">
-        <v>-117.56860161</v>
+        <v>-41.76354069999999</v>
       </c>
       <c r="H72" t="n">
-        <v>-41.76354069999999</v>
+        <v>-96.87037564000001</v>
       </c>
       <c r="I72" t="n">
-        <v>-96.87037564000001</v>
+        <v>-62.8772119</v>
       </c>
       <c r="J72" t="n">
-        <v>-62.8772119</v>
+        <v>-12.82282402</v>
       </c>
       <c r="K72" t="n">
-        <v>-12.82282402</v>
+        <v>98.85202981</v>
       </c>
       <c r="L72" t="n">
-        <v>98.85202981</v>
+        <v>106.34325255</v>
       </c>
       <c r="M72" t="n">
-        <v>106.34325255</v>
+        <v>-1.836550060000001</v>
       </c>
     </row>
     <row r="73">
@@ -3426,37 +3422,37 @@
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
-        <v>1.9869591</v>
+        <v>13.19129905</v>
       </c>
       <c r="D73" t="n">
-        <v>13.19129905</v>
+        <v>5.14271512</v>
       </c>
       <c r="E73" t="n">
-        <v>5.14271512</v>
+        <v>-8.77292924</v>
       </c>
       <c r="F73" t="n">
-        <v>-8.77292924</v>
+        <v>-8.96068459</v>
       </c>
       <c r="G73" t="n">
-        <v>-8.96068459</v>
+        <v>-20.04120091</v>
       </c>
       <c r="H73" t="n">
-        <v>-20.04120091</v>
+        <v>-30.54986415</v>
       </c>
       <c r="I73" t="n">
-        <v>-30.54986415</v>
+        <v>-15.30492149</v>
       </c>
       <c r="J73" t="n">
-        <v>-15.30492149</v>
+        <v>-8.88836045</v>
       </c>
       <c r="K73" t="n">
-        <v>-8.88836045</v>
+        <v>20.78246032</v>
       </c>
       <c r="L73" t="n">
-        <v>20.78246032</v>
+        <v>-2.68761685</v>
       </c>
       <c r="M73" t="n">
-        <v>-2.68761685</v>
+        <v>-23.26769997</v>
       </c>
     </row>
     <row r="74">
@@ -3467,37 +3463,37 @@
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
-        <v>99.09603653999999</v>
+        <v>974.9973069000001</v>
       </c>
       <c r="D74" t="n">
-        <v>970.65146917</v>
+        <v>894.0164181600001</v>
       </c>
       <c r="E74" t="n">
-        <v>884.16237317</v>
+        <v>1276.00511831</v>
       </c>
       <c r="F74" t="n">
-        <v>1255.32413101</v>
+        <v>884.3679413999999</v>
       </c>
       <c r="G74" t="n">
-        <v>874.8045002699999</v>
+        <v>711.53754654</v>
       </c>
       <c r="H74" t="n">
-        <v>707.7305493600001</v>
+        <v>678.83419911</v>
       </c>
       <c r="I74" t="n">
-        <v>679.97336817</v>
+        <v>674.51015137</v>
       </c>
       <c r="J74" t="n">
-        <v>678.9577422699999</v>
+        <v>926.41732815</v>
       </c>
       <c r="K74" t="n">
-        <v>924.3511551399999</v>
+        <v>1369.02894179</v>
       </c>
       <c r="L74" t="n">
-        <v>1354.0773804</v>
+        <v>463.72510052</v>
       </c>
       <c r="M74" t="n">
-        <v>461.03885747</v>
+        <v>314.75285627</v>
       </c>
     </row>
     <row r="75">
@@ -3508,37 +3504,37 @@
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
-        <v>-349.0558786799999</v>
+        <v>-118.64327508</v>
       </c>
       <c r="D75" t="n">
-        <v>-118.99593187</v>
+        <v>74.35517131</v>
       </c>
       <c r="E75" t="n">
-        <v>72.75089683</v>
+        <v>170.94813623</v>
       </c>
       <c r="F75" t="n">
-        <v>167.55188173</v>
+        <v>-29.13507418</v>
       </c>
       <c r="G75" t="n">
-        <v>-31.46257298</v>
+        <v>-219.04003565</v>
       </c>
       <c r="H75" t="n">
-        <v>-219.97600686</v>
+        <v>-381.90045693</v>
       </c>
       <c r="I75" t="n">
-        <v>-384.3325941999999</v>
+        <v>-512.67950204</v>
       </c>
       <c r="J75" t="n">
-        <v>-513.9571076200001</v>
+        <v>-257.43105527</v>
       </c>
       <c r="K75" t="n">
-        <v>-257.99615698</v>
+        <v>-15.00335476</v>
       </c>
       <c r="L75" t="n">
-        <v>-17.04792302</v>
+        <v>-65.23920036</v>
       </c>
       <c r="M75" t="n">
-        <v>-66.68232792000001</v>
+        <v>40.41807481999999</v>
       </c>
     </row>
     <row r="76">
@@ -3549,37 +3545,37 @@
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>-12.31874343</v>
+        <v>91.30190863</v>
       </c>
       <c r="D76" t="n">
-        <v>91.65456542</v>
+        <v>0.5135688299999975</v>
       </c>
       <c r="E76" t="n">
-        <v>2.117843309999998</v>
+        <v>-5.267518610000002</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.871264110000001</v>
+        <v>-29.91318846</v>
       </c>
       <c r="G76" t="n">
-        <v>-27.58568966</v>
+        <v>10.02626751</v>
       </c>
       <c r="H76" t="n">
-        <v>10.96223872</v>
+        <v>45.30449216</v>
       </c>
       <c r="I76" t="n">
-        <v>47.73662943</v>
+        <v>36.52794931</v>
       </c>
       <c r="J76" t="n">
-        <v>37.80555489</v>
+        <v>59.67935274</v>
       </c>
       <c r="K76" t="n">
-        <v>60.24445445000001</v>
+        <v>73.63708925</v>
       </c>
       <c r="L76" t="n">
-        <v>75.68165750999999</v>
+        <v>31.95205342</v>
       </c>
       <c r="M76" t="n">
-        <v>33.39518098</v>
+        <v>12.76365991</v>
       </c>
     </row>
     <row r="77">
@@ -3590,37 +3586,37 @@
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="n">
-        <v>-0.00031853</v>
+        <v>-0.00042214</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.00042214</v>
+        <v>0.00035191</v>
       </c>
       <c r="E77" t="n">
-        <v>0.00035191</v>
+        <v>0.0006016</v>
       </c>
       <c r="F77" t="n">
-        <v>0.0006016</v>
+        <v>0.00119589</v>
       </c>
       <c r="G77" t="n">
-        <v>0.00119589</v>
+        <v>0.00222055</v>
       </c>
       <c r="H77" t="n">
-        <v>0.00222055</v>
+        <v>0.00226234</v>
       </c>
       <c r="I77" t="n">
-        <v>0.00226234</v>
+        <v>0.00101082</v>
       </c>
       <c r="J77" t="n">
-        <v>0.00101082</v>
+        <v>9.988e-05</v>
       </c>
       <c r="K77" t="n">
-        <v>9.988e-05</v>
+        <v>0.00032912</v>
       </c>
       <c r="L77" t="n">
-        <v>0.00032912</v>
+        <v>-0.00052438</v>
       </c>
       <c r="M77" t="n">
-        <v>-0.00052438</v>
+        <v>-9.99e-05</v>
       </c>
     </row>
     <row r="78">
@@ -3631,37 +3627,37 @@
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
-        <v>-0.005935770000000001</v>
+        <v>-0.006376339999999999</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.006376339999999999</v>
+        <v>-0.00146164</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.00146164</v>
+        <v>0.0001785999999999999</v>
       </c>
       <c r="F78" t="n">
-        <v>0.0001785999999999999</v>
+        <v>0.00166505</v>
       </c>
       <c r="G78" t="n">
-        <v>0.00166505</v>
+        <v>0.00481058</v>
       </c>
       <c r="H78" t="n">
-        <v>0.00481058</v>
+        <v>0.00272902</v>
       </c>
       <c r="I78" t="n">
-        <v>0.00272902</v>
+        <v>9.011000000000007e-05</v>
       </c>
       <c r="J78" t="n">
-        <v>9.011000000000007e-05</v>
+        <v>0.0004795100000000002</v>
       </c>
       <c r="K78" t="n">
-        <v>0.0004795100000000002</v>
+        <v>0.00329986</v>
       </c>
       <c r="L78" t="n">
-        <v>0.00329986</v>
+        <v>0.0005099499999999999</v>
       </c>
       <c r="M78" t="n">
-        <v>0.0005099499999999999</v>
+        <v>-0.0007658099999999999</v>
       </c>
     </row>
     <row r="79">
@@ -3672,37 +3668,37 @@
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="n">
-        <v>-0.00049876</v>
+        <v>-0.00010349</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.00010349</v>
+        <v>0.00149008</v>
       </c>
       <c r="E79" t="n">
-        <v>0.00149008</v>
+        <v>0.00167124</v>
       </c>
       <c r="F79" t="n">
-        <v>0.00167124</v>
+        <v>0.00103193</v>
       </c>
       <c r="G79" t="n">
-        <v>0.00103193</v>
+        <v>0.00057835</v>
       </c>
       <c r="H79" t="n">
-        <v>0.00057835</v>
+        <v>9.465e-05</v>
       </c>
       <c r="I79" t="n">
-        <v>9.465e-05</v>
+        <v>0.00013897</v>
       </c>
       <c r="J79" t="n">
-        <v>0.00013897</v>
+        <v>6.415e-05</v>
       </c>
       <c r="K79" t="n">
-        <v>6.415e-05</v>
+        <v>-0.00029419</v>
       </c>
       <c r="L79" t="n">
-        <v>-0.00029419</v>
+        <v>0.00019073</v>
       </c>
       <c r="M79" t="n">
-        <v>0.00019073</v>
+        <v>-2.111999999999998e-05</v>
       </c>
     </row>
     <row r="80">
@@ -3713,37 +3709,37 @@
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="n">
-        <v>-13.08952523</v>
+        <v>-4.332121809999999</v>
       </c>
       <c r="D80" t="n">
-        <v>-4.331212519999999</v>
+        <v>-10.26026165</v>
       </c>
       <c r="E80" t="n">
-        <v>-10.25827174</v>
+        <v>8.420322020000002</v>
       </c>
       <c r="F80" t="n">
-        <v>8.421552140000001</v>
+        <v>-10.13479723</v>
       </c>
       <c r="G80" t="n">
-        <v>-10.13260721</v>
+        <v>-9.688284559999998</v>
       </c>
       <c r="H80" t="n">
-        <v>-9.68964107</v>
+        <v>4.870666569999999</v>
       </c>
       <c r="I80" t="n">
-        <v>4.868124629999999</v>
+        <v>12.18966626</v>
       </c>
       <c r="J80" t="n">
-        <v>12.18883922</v>
+        <v>-4.46977351</v>
       </c>
       <c r="K80" t="n">
-        <v>-4.46799539</v>
+        <v>12.58217618</v>
       </c>
       <c r="L80" t="n">
-        <v>12.58299348</v>
+        <v>17.39556762</v>
       </c>
       <c r="M80" t="n">
-        <v>17.39570309</v>
+        <v>13.14819293</v>
       </c>
     </row>
     <row r="81">
@@ -3754,37 +3750,37 @@
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>-88.87504158</v>
+        <v>-103.34398829</v>
       </c>
       <c r="D81" t="n">
-        <v>-103.34398829</v>
+        <v>-57.69436082</v>
       </c>
       <c r="E81" t="n">
-        <v>-57.69436082</v>
+        <v>-41.13783873999999</v>
       </c>
       <c r="F81" t="n">
-        <v>-41.13783873999999</v>
+        <v>-58.76555155999999</v>
       </c>
       <c r="G81" t="n">
-        <v>-58.76555155999999</v>
+        <v>-40.17196165999999</v>
       </c>
       <c r="H81" t="n">
-        <v>-40.17196165999999</v>
+        <v>-13.61398708</v>
       </c>
       <c r="I81" t="n">
-        <v>-13.61398708</v>
+        <v>34.26378235</v>
       </c>
       <c r="J81" t="n">
-        <v>34.26378235</v>
+        <v>102.02552729</v>
       </c>
       <c r="K81" t="n">
-        <v>102.02552729</v>
+        <v>136.86135343</v>
       </c>
       <c r="L81" t="n">
-        <v>136.86135343</v>
+        <v>238.22024326</v>
       </c>
       <c r="M81" t="n">
-        <v>238.22024326</v>
+        <v>139.12935513</v>
       </c>
     </row>
     <row r="82">
@@ -3795,37 +3791,37 @@
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
-        <v>-9.090035719999999</v>
+        <v>90.69154939000001</v>
       </c>
       <c r="D82" t="n">
-        <v>90.6906401</v>
+        <v>-57.32406938000001</v>
       </c>
       <c r="E82" t="n">
-        <v>-57.32605929</v>
+        <v>-1.926858940000005</v>
       </c>
       <c r="F82" t="n">
-        <v>-1.928089060000002</v>
+        <v>-172.9662267</v>
       </c>
       <c r="G82" t="n">
-        <v>-172.96841672</v>
+        <v>92.52711834</v>
       </c>
       <c r="H82" t="n">
-        <v>92.52847485000001</v>
+        <v>-155.46170183</v>
       </c>
       <c r="I82" t="n">
-        <v>-155.45915989</v>
+        <v>-345.22405762</v>
       </c>
       <c r="J82" t="n">
-        <v>-345.22323058</v>
+        <v>-548.9082120700001</v>
       </c>
       <c r="K82" t="n">
-        <v>-548.90999019</v>
+        <v>-281.94104034</v>
       </c>
       <c r="L82" t="n">
-        <v>-281.94185764</v>
+        <v>-159.5239148</v>
       </c>
       <c r="M82" t="n">
-        <v>-159.52405027</v>
+        <v>63.48032186</v>
       </c>
     </row>
     <row r="83">
@@ -3836,37 +3832,37 @@
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>-6.688197980000001</v>
+        <v>27.87323952</v>
       </c>
       <c r="D83" t="n">
-        <v>39.15618257</v>
+        <v>82.35941356999999</v>
       </c>
       <c r="E83" t="n">
-        <v>88.37693567999999</v>
+        <v>181.83515722</v>
       </c>
       <c r="F83" t="n">
-        <v>173.80208869</v>
+        <v>68.08952595000001</v>
       </c>
       <c r="G83" t="n">
-        <v>68.31111571000001</v>
+        <v>-20.36797773</v>
       </c>
       <c r="H83" t="n">
-        <v>-15.21283794</v>
+        <v>-20.03139617</v>
       </c>
       <c r="I83" t="n">
-        <v>-17.71552102</v>
+        <v>-59.64161756</v>
       </c>
       <c r="J83" t="n">
-        <v>-64.05499739</v>
+        <v>-112.75539681</v>
       </c>
       <c r="K83" t="n">
-        <v>-108.28490628</v>
+        <v>64.56145398</v>
       </c>
       <c r="L83" t="n">
-        <v>17.23501362</v>
+        <v>-54.95076079</v>
       </c>
       <c r="M83" t="n">
-        <v>-42.91166961</v>
+        <v>-5.751428920000002</v>
       </c>
     </row>
     <row r="84">
@@ -3877,37 +3873,37 @@
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
-        <v>-143.58805289</v>
+        <v>-122.3490537</v>
       </c>
       <c r="D84" t="n">
-        <v>-122.466744</v>
+        <v>-54.08822536000001</v>
       </c>
       <c r="E84" t="n">
-        <v>-54.09112768000001</v>
+        <v>-10.32345865</v>
       </c>
       <c r="F84" t="n">
-        <v>-10.37811915</v>
+        <v>20.68587184</v>
       </c>
       <c r="G84" t="n">
-        <v>20.72728843</v>
+        <v>50.4358599</v>
       </c>
       <c r="H84" t="n">
-        <v>50.52973096</v>
+        <v>20.67695317</v>
       </c>
       <c r="I84" t="n">
-        <v>20.65790564</v>
+        <v>39.12531966</v>
       </c>
       <c r="J84" t="n">
-        <v>39.26255287</v>
+        <v>82.69031135000002</v>
       </c>
       <c r="K84" t="n">
-        <v>82.85629460000001</v>
+        <v>154.59545891</v>
       </c>
       <c r="L84" t="n">
-        <v>154.58928851</v>
+        <v>58.71590928</v>
       </c>
       <c r="M84" t="n">
-        <v>58.48154729</v>
+        <v>121.63718761</v>
       </c>
     </row>
     <row r="85">
@@ -3918,37 +3914,37 @@
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>-22.44689371</v>
+        <v>4.65700348</v>
       </c>
       <c r="D85" t="n">
-        <v>-6.50824927</v>
+        <v>16.5811829</v>
       </c>
       <c r="E85" t="n">
-        <v>10.56656311</v>
+        <v>83.55010430999998</v>
       </c>
       <c r="F85" t="n">
-        <v>91.63783333999999</v>
+        <v>308.21784694</v>
       </c>
       <c r="G85" t="n">
-        <v>307.9548405900001</v>
+        <v>132.33488342</v>
       </c>
       <c r="H85" t="n">
-        <v>127.08587257</v>
+        <v>37.83571189</v>
       </c>
       <c r="I85" t="n">
-        <v>35.53888427</v>
+        <v>-48.80012199</v>
       </c>
       <c r="J85" t="n">
-        <v>-44.52397537</v>
+        <v>-75.86895855</v>
       </c>
       <c r="K85" t="n">
-        <v>-80.50543233</v>
+        <v>-29.96102533</v>
       </c>
       <c r="L85" t="n">
-        <v>17.37158543</v>
+        <v>-10.1905005</v>
       </c>
       <c r="M85" t="n">
-        <v>-21.99522969</v>
+        <v>26.19259462</v>
       </c>
     </row>
     <row r="86">
@@ -3959,37 +3955,37 @@
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
-        <v>39.92671712</v>
+        <v>-7.647300829999998</v>
       </c>
       <c r="D86" t="n">
-        <v>-7.647300829999998</v>
+        <v>40.5057899</v>
       </c>
       <c r="E86" t="n">
-        <v>40.5057899</v>
+        <v>0.2115746600000012</v>
       </c>
       <c r="F86" t="n">
-        <v>0.2115746600000012</v>
+        <v>-73.51357708</v>
       </c>
       <c r="G86" t="n">
-        <v>-73.51357708</v>
+        <v>-120.38293081</v>
       </c>
       <c r="H86" t="n">
-        <v>-120.38293081</v>
+        <v>-28.81328676999999</v>
       </c>
       <c r="I86" t="n">
-        <v>-28.81328676999999</v>
+        <v>26.42893274</v>
       </c>
       <c r="J86" t="n">
-        <v>26.42893274</v>
+        <v>-19.94011926</v>
       </c>
       <c r="K86" t="n">
-        <v>-19.94011926</v>
+        <v>-44.01715513000001</v>
       </c>
       <c r="L86" t="n">
-        <v>-44.01715513000001</v>
+        <v>-47.84157947</v>
       </c>
       <c r="M86" t="n">
-        <v>-47.84157947</v>
+        <v>-49.89369227</v>
       </c>
     </row>
     <row r="87">
@@ -3998,39 +3994,41 @@
           <t>電子通路業右下</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr"/>
+      <c r="B87" t="n">
+        <v>0</v>
+      </c>
       <c r="C87" t="n">
-        <v>-33.26785071</v>
+        <v>9.40449473</v>
       </c>
       <c r="D87" t="n">
-        <v>6.899450400000001</v>
+        <v>61.57701271</v>
       </c>
       <c r="E87" t="n">
-        <v>66.94732356</v>
+        <v>20.08251324</v>
       </c>
       <c r="F87" t="n">
-        <v>15.18315901</v>
+        <v>3.54886275</v>
       </c>
       <c r="G87" t="n">
-        <v>-4.35202075</v>
+        <v>-33.63304152</v>
       </c>
       <c r="H87" t="n">
-        <v>-68.57304669</v>
+        <v>-78.28551906999999</v>
       </c>
       <c r="I87" t="n">
-        <v>-151.21501754</v>
+        <v>-80.95774643</v>
       </c>
       <c r="J87" t="n">
-        <v>-178.71603407</v>
+        <v>-76.5308065</v>
       </c>
       <c r="K87" t="n">
-        <v>-165.20199526</v>
+        <v>-51.41952109</v>
       </c>
       <c r="L87" t="n">
-        <v>-124.5411635</v>
+        <v>-47.21596209</v>
       </c>
       <c r="M87" t="n">
-        <v>-106.78033262</v>
+        <v>-35.58194683</v>
       </c>
     </row>
     <row r="88">
@@ -4041,37 +4039,37 @@
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
-        <v>6.661907179999998</v>
+        <v>34.88464354</v>
       </c>
       <c r="D88" t="n">
-        <v>34.88464354</v>
+        <v>67.06029259</v>
       </c>
       <c r="E88" t="n">
-        <v>67.06029259</v>
+        <v>108.11180131</v>
       </c>
       <c r="F88" t="n">
-        <v>108.11180131</v>
+        <v>65.92950389000001</v>
       </c>
       <c r="G88" t="n">
-        <v>65.92950389000001</v>
+        <v>2.10840591</v>
       </c>
       <c r="H88" t="n">
-        <v>2.10840591</v>
+        <v>-24.75203363</v>
       </c>
       <c r="I88" t="n">
-        <v>-24.75203363</v>
+        <v>-0.5570340900000017</v>
       </c>
       <c r="J88" t="n">
-        <v>-0.5570340900000017</v>
+        <v>-23.51860179</v>
       </c>
       <c r="K88" t="n">
-        <v>-23.51860179</v>
+        <v>-45.03233113</v>
       </c>
       <c r="L88" t="n">
-        <v>-45.03233113</v>
+        <v>-38.22943602</v>
       </c>
       <c r="M88" t="n">
-        <v>-38.22943602</v>
+        <v>-4.498579950000001</v>
       </c>
     </row>
     <row r="89">
@@ -4082,37 +4080,37 @@
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>2783.39345016</v>
+        <v>212.40817085</v>
       </c>
       <c r="D89" t="n">
-        <v>215.5806035</v>
+        <v>2990.31880572</v>
       </c>
       <c r="E89" t="n">
-        <v>2982.67742872</v>
+        <v>1186.80735137</v>
       </c>
       <c r="F89" t="n">
-        <v>1180.78229041</v>
+        <v>794.00660127</v>
       </c>
       <c r="G89" t="n">
-        <v>793.649512</v>
+        <v>3445.63541345</v>
       </c>
       <c r="H89" t="n">
-        <v>3437.09900703</v>
+        <v>5028.74955195</v>
       </c>
       <c r="I89" t="n">
-        <v>5003.80231401</v>
+        <v>4932.12340164</v>
       </c>
       <c r="J89" t="n">
-        <v>4907.06809745</v>
+        <v>5056.04785329</v>
       </c>
       <c r="K89" t="n">
-        <v>5011.02327398</v>
+        <v>5015.056826280001</v>
       </c>
       <c r="L89" t="n">
-        <v>4978.62790089</v>
+        <v>3596.91904878</v>
       </c>
       <c r="M89" t="n">
-        <v>3566.86714986</v>
+        <v>5119.45468342</v>
       </c>
     </row>
     <row r="90">
@@ -4121,41 +4119,39 @@
           <t>電子零組件業右下</t>
         </is>
       </c>
-      <c r="B90" t="n">
-        <v>0</v>
-      </c>
+      <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>114.871394</v>
+        <v>-14.22535454</v>
       </c>
       <c r="D90" t="n">
-        <v>-321.46475975</v>
+        <v>-7.938487430000005</v>
       </c>
       <c r="E90" t="n">
-        <v>-259.42360324</v>
+        <v>-49.59893637</v>
       </c>
       <c r="F90" t="n">
-        <v>-580.3061901999999</v>
+        <v>-124.42277984</v>
       </c>
       <c r="G90" t="n">
-        <v>-464.38819778</v>
+        <v>-109.69509236</v>
       </c>
       <c r="H90" t="n">
-        <v>-366.0556037000001</v>
+        <v>-69.58334395</v>
       </c>
       <c r="I90" t="n">
-        <v>-5.243127309999995</v>
+        <v>-0.2716190900000023</v>
       </c>
       <c r="J90" t="n">
-        <v>-354.20319953</v>
+        <v>-83.76383537999999</v>
       </c>
       <c r="K90" t="n">
-        <v>-784.57410473</v>
+        <v>-41.75871842999999</v>
       </c>
       <c r="L90" t="n">
-        <v>-1020.75804413</v>
+        <v>-17.05357446999999</v>
       </c>
       <c r="M90" t="n">
-        <v>-1127.69522433</v>
+        <v>74.16510740000001</v>
       </c>
     </row>
     <row r="91">
@@ -4166,37 +4162,37 @@
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>-449.80729223</v>
+        <v>-664.04291288</v>
       </c>
       <c r="D91" t="n">
-        <v>-359.9600526300001</v>
+        <v>-155.74608729</v>
       </c>
       <c r="E91" t="n">
-        <v>103.40258845</v>
+        <v>-1029.82424404</v>
       </c>
       <c r="F91" t="n">
-        <v>-493.07000123</v>
+        <v>-851.17474859</v>
       </c>
       <c r="G91" t="n">
-        <v>-510.84168123</v>
+        <v>-782.7945044100001</v>
       </c>
       <c r="H91" t="n">
-        <v>-517.89728523</v>
+        <v>-245.541188</v>
       </c>
       <c r="I91" t="n">
-        <v>-284.9405972600001</v>
+        <v>-961.95106471</v>
       </c>
       <c r="J91" t="n">
-        <v>-583.04451753</v>
+        <v>-1542.95742309</v>
       </c>
       <c r="K91" t="n">
-        <v>-797.12358419</v>
+        <v>-2013.65992858</v>
       </c>
       <c r="L91" t="n">
-        <v>-998.21052736</v>
+        <v>-2132.58183584</v>
       </c>
       <c r="M91" t="n">
-        <v>-991.88876777</v>
+        <v>-617.2388345000001</v>
       </c>
     </row>
     <row r="92">
@@ -4207,37 +4203,37 @@
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>327.53786522</v>
+        <v>-1119.94840541</v>
       </c>
       <c r="D92" t="n">
-        <v>-1136.41872908</v>
+        <v>-1209.79889255</v>
       </c>
       <c r="E92" t="n">
-        <v>-1245.16251958</v>
+        <v>-394.9854834599999</v>
       </c>
       <c r="F92" t="n">
-        <v>-443.0947849599999</v>
+        <v>807.20241059</v>
       </c>
       <c r="G92" t="n">
-        <v>793.4250831000001</v>
+        <v>-143.07668677</v>
       </c>
       <c r="H92" t="n">
-        <v>-164.21426872</v>
+        <v>29.73263064999998</v>
       </c>
       <c r="I92" t="n">
-        <v>31.72998852999997</v>
+        <v>-1156.96839941</v>
       </c>
       <c r="J92" t="n">
-        <v>-1157.49170408</v>
+        <v>-26.00348641999991</v>
       </c>
       <c r="K92" t="n">
-        <v>-9.335778799999908</v>
+        <v>-147.75120938</v>
       </c>
       <c r="L92" t="n">
-        <v>-123.20143785</v>
+        <v>-473.74963365</v>
       </c>
       <c r="M92" t="n">
-        <v>-443.73774572</v>
+        <v>527.4095368100001</v>
       </c>
     </row>
     <row r="93">
@@ -4250,37 +4246,37 @@
         <v>0</v>
       </c>
       <c r="C93" t="n">
-        <v>-54.44380702</v>
+        <v>-155.10822174</v>
       </c>
       <c r="D93" t="n">
-        <v>-153.00815105</v>
+        <v>-45.82354711</v>
       </c>
       <c r="E93" t="n">
-        <v>0.6957613299999942</v>
+        <v>-92.70913264000002</v>
       </c>
       <c r="F93" t="n">
-        <v>-106.30556185</v>
+        <v>-23.68235597</v>
       </c>
       <c r="G93" t="n">
-        <v>7.431064629999999</v>
+        <v>6.1374519</v>
       </c>
       <c r="H93" t="n">
-        <v>98.67010714000001</v>
+        <v>-33.13408994</v>
       </c>
       <c r="I93" t="n">
-        <v>68.31838794000001</v>
+        <v>-49.35878334</v>
       </c>
       <c r="J93" t="n">
-        <v>-16.79744466</v>
+        <v>-60.85396212999999</v>
       </c>
       <c r="K93" t="n">
-        <v>-136.91026723</v>
+        <v>16.57186501</v>
       </c>
       <c r="L93" t="n">
-        <v>-78.38075546</v>
+        <v>14.50032759</v>
       </c>
       <c r="M93" t="n">
-        <v>3.436960939999999</v>
+        <v>13.5528489</v>
       </c>
     </row>
     <row r="94">
@@ -4291,37 +4287,37 @@
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>40.82373081999999</v>
+        <v>169.123142</v>
       </c>
       <c r="D94" t="n">
-        <v>183.67215091</v>
+        <v>142.71602724</v>
       </c>
       <c r="E94" t="n">
-        <v>131.83445524</v>
+        <v>119.32277019</v>
       </c>
       <c r="F94" t="n">
-        <v>181.39244916</v>
+        <v>228.45661413</v>
       </c>
       <c r="G94" t="n">
-        <v>211.46973347</v>
+        <v>182.58705834</v>
       </c>
       <c r="H94" t="n">
-        <v>111.55350454</v>
+        <v>101.12114545</v>
       </c>
       <c r="I94" t="n">
-        <v>-2.048849939999999</v>
+        <v>118.74585852</v>
       </c>
       <c r="J94" t="n">
-        <v>86.89526453000002</v>
+        <v>18.89004940999999</v>
       </c>
       <c r="K94" t="n">
-        <v>78.12434784</v>
+        <v>86.82549297</v>
       </c>
       <c r="L94" t="n">
-        <v>156.91687895</v>
+        <v>230.56657783</v>
       </c>
       <c r="M94" t="n">
-        <v>211.45213399</v>
+        <v>274.15330595</v>
       </c>
     </row>
     <row r="95">
@@ -4332,37 +4328,37 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>2685.65049112</v>
+        <v>416.44109066</v>
       </c>
       <c r="D95" t="n">
-        <v>401.66842728</v>
+        <v>4058.27390463</v>
       </c>
       <c r="E95" t="n">
-        <v>4009.46578054</v>
+        <v>1802.97024758</v>
       </c>
       <c r="F95" t="n">
-        <v>1730.40432885</v>
+        <v>2588.30203534</v>
       </c>
       <c r="G95" t="n">
-        <v>2569.44557358</v>
+        <v>3407.84381268</v>
       </c>
       <c r="H95" t="n">
-        <v>3376.77160564</v>
+        <v>2918.26632337</v>
       </c>
       <c r="I95" t="n">
-        <v>2916.05091773</v>
+        <v>392.76594471</v>
       </c>
       <c r="J95" t="n">
-        <v>409.17178916</v>
+        <v>-3427.24280729</v>
       </c>
       <c r="K95" t="n">
-        <v>-3393.207893069999</v>
+        <v>-3829.12475877</v>
       </c>
       <c r="L95" t="n">
-        <v>-3802.88474447</v>
+        <v>-3124.25803953</v>
       </c>
       <c r="M95" t="n">
-        <v>-3113.12340659</v>
+        <v>-3099.23420779</v>
       </c>
     </row>
     <row r="96">
@@ -4371,39 +4367,41 @@
           <t>電腦及週邊設備業右下</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr"/>
+      <c r="B96" t="n">
+        <v>0</v>
+      </c>
       <c r="C96" t="n">
-        <v>-34.4090199</v>
+        <v>41.31179470999999</v>
       </c>
       <c r="D96" t="n">
-        <v>40.3709417</v>
+        <v>303.85865835</v>
       </c>
       <c r="E96" t="n">
-        <v>304.38397094</v>
+        <v>35.3318436</v>
       </c>
       <c r="F96" t="n">
-        <v>36.22071315</v>
+        <v>-22.25389299</v>
       </c>
       <c r="G96" t="n">
-        <v>-20.63448973000001</v>
+        <v>-315.7113619</v>
       </c>
       <c r="H96" t="n">
-        <v>-317.5745386</v>
+        <v>-538.14640064</v>
       </c>
       <c r="I96" t="n">
-        <v>-538.8407471</v>
+        <v>-571.8712749299999</v>
       </c>
       <c r="J96" t="n">
-        <v>-573.10052565</v>
+        <v>-624.8439679099999</v>
       </c>
       <c r="K96" t="n">
-        <v>-620.52603838</v>
+        <v>-657.73119352</v>
       </c>
       <c r="L96" t="n">
-        <v>-630.9166388</v>
+        <v>-438.96181825</v>
       </c>
       <c r="M96" t="n">
-        <v>-429.82889656</v>
+        <v>-464.35261563</v>
       </c>
     </row>
     <row r="97">
@@ -4414,37 +4412,37 @@
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>30.80699172</v>
+        <v>-85.92268896</v>
       </c>
       <c r="D97" t="n">
-        <v>-70.12666147</v>
+        <v>48.26396369</v>
       </c>
       <c r="E97" t="n">
-        <v>96.46264479000001</v>
+        <v>-76.90205049000001</v>
       </c>
       <c r="F97" t="n">
-        <v>-5.302429040000006</v>
+        <v>85.5031202</v>
       </c>
       <c r="G97" t="n">
-        <v>102.72488865</v>
+        <v>3.221822799999994</v>
       </c>
       <c r="H97" t="n">
-        <v>36.21586944999999</v>
+        <v>99.35405415999999</v>
       </c>
       <c r="I97" t="n">
-        <v>102.26942867</v>
+        <v>-84.42280314</v>
       </c>
       <c r="J97" t="n">
-        <v>-99.61859397999999</v>
+        <v>-0.3987063000000081</v>
       </c>
       <c r="K97" t="n">
-        <v>-38.74008789000001</v>
+        <v>-131.11918459</v>
       </c>
       <c r="L97" t="n">
-        <v>-184.17612756</v>
+        <v>-310.60347696</v>
       </c>
       <c r="M97" t="n">
-        <v>-330.8791778300001</v>
+        <v>-111.28280038</v>
       </c>
     </row>
     <row r="98">
@@ -4455,37 +4453,37 @@
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
-        <v>-15.11263473</v>
+        <v>2.57707229</v>
       </c>
       <c r="D98" t="n">
-        <v>2.57676404</v>
+        <v>17.61837582</v>
       </c>
       <c r="E98" t="n">
-        <v>17.61770092</v>
+        <v>27.36598622</v>
       </c>
       <c r="F98" t="n">
-        <v>27.36522565</v>
+        <v>21.46284854</v>
       </c>
       <c r="G98" t="n">
-        <v>21.462162</v>
+        <v>2.43384234</v>
       </c>
       <c r="H98" t="n">
-        <v>2.43355516</v>
+        <v>3.42921125</v>
       </c>
       <c r="I98" t="n">
-        <v>3.428873750000001</v>
+        <v>20.06839899</v>
       </c>
       <c r="J98" t="n">
-        <v>20.06785335</v>
+        <v>29.26418117</v>
       </c>
       <c r="K98" t="n">
-        <v>29.26245925</v>
+        <v>17.238713</v>
       </c>
       <c r="L98" t="n">
-        <v>17.23702606</v>
+        <v>24.67003403</v>
       </c>
       <c r="M98" t="n">
-        <v>24.66836485</v>
+        <v>34.21972625</v>
       </c>
     </row>
     <row r="99">
@@ -4496,37 +4494,37 @@
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>-4.212167819999999</v>
+        <v>9.207686730000001</v>
       </c>
       <c r="D99" t="n">
-        <v>9.207686730000001</v>
+        <v>12.72329238</v>
       </c>
       <c r="E99" t="n">
-        <v>12.72329238</v>
+        <v>17.20173201</v>
       </c>
       <c r="F99" t="n">
-        <v>17.20173201</v>
+        <v>5.82131096</v>
       </c>
       <c r="G99" t="n">
-        <v>5.82131096</v>
+        <v>-1.51795931</v>
       </c>
       <c r="H99" t="n">
-        <v>-1.51795931</v>
+        <v>-12.99625281</v>
       </c>
       <c r="I99" t="n">
-        <v>-12.99625281</v>
+        <v>-16.9396746</v>
       </c>
       <c r="J99" t="n">
-        <v>-16.9396746</v>
+        <v>-11.9078638</v>
       </c>
       <c r="K99" t="n">
-        <v>-11.9078638</v>
+        <v>3.03977697</v>
       </c>
       <c r="L99" t="n">
-        <v>3.03977697</v>
+        <v>2.450260839999999</v>
       </c>
       <c r="M99" t="n">
-        <v>2.450260839999999</v>
+        <v>4.71740638</v>
       </c>
     </row>
     <row r="100">
@@ -4537,37 +4535,37 @@
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="n">
-        <v>-115.42952001</v>
+        <v>-27.29308296</v>
       </c>
       <c r="D100" t="n">
-        <v>-27.29277471</v>
+        <v>-51.18443892999999</v>
       </c>
       <c r="E100" t="n">
-        <v>-51.18376402999999</v>
+        <v>-94.26175691</v>
       </c>
       <c r="F100" t="n">
-        <v>-94.26099633999999</v>
+        <v>-157.11158216</v>
       </c>
       <c r="G100" t="n">
-        <v>-157.11089562</v>
+        <v>-218.50210518</v>
       </c>
       <c r="H100" t="n">
-        <v>-218.501818</v>
+        <v>-239.00708826</v>
       </c>
       <c r="I100" t="n">
-        <v>-239.00675076</v>
+        <v>-229.13027991</v>
       </c>
       <c r="J100" t="n">
-        <v>-229.12973427</v>
+        <v>-222.29841232</v>
       </c>
       <c r="K100" t="n">
-        <v>-222.2966904</v>
+        <v>-71.93113762</v>
       </c>
       <c r="L100" t="n">
-        <v>-71.92945067999999</v>
+        <v>16.46899495</v>
       </c>
       <c r="M100" t="n">
-        <v>16.47066413</v>
+        <v>-17.34270298</v>
       </c>
     </row>
   </sheetData>

--- a/Result/analyze_2.xlsx
+++ b/Result/analyze_2.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
     </row>
@@ -503,37 +503,37 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>968.4364153299999</v>
+        <v>1829.87179314</v>
       </c>
       <c r="D2" t="n">
-        <v>1850.81626807</v>
+        <v>1056.78821396</v>
       </c>
       <c r="E2" t="n">
-        <v>1099.0453445</v>
+        <v>38.44985315000002</v>
       </c>
       <c r="F2" t="n">
-        <v>166.23606728</v>
+        <v>605.9506780400001</v>
       </c>
       <c r="G2" t="n">
-        <v>727.0432599100001</v>
+        <v>731.2417069400001</v>
       </c>
       <c r="H2" t="n">
-        <v>821.58169307</v>
+        <v>697.19497599</v>
       </c>
       <c r="I2" t="n">
-        <v>747.65041722</v>
+        <v>1824.4696739</v>
       </c>
       <c r="J2" t="n">
-        <v>1788.2746322</v>
+        <v>-152.05894289</v>
       </c>
       <c r="K2" t="n">
-        <v>-150.25167875</v>
+        <v>-67.89374619999998</v>
       </c>
       <c r="L2" t="n">
-        <v>99.59722605</v>
+        <v>-85.87499314000002</v>
       </c>
       <c r="M2" t="n">
-        <v>214.21690205</v>
+        <v>-192.88029105</v>
       </c>
     </row>
     <row r="3">
@@ -542,39 +542,41 @@
           <t>光電業右下</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
       <c r="C3" t="n">
-        <v>40.93185249</v>
+        <v>169.23619934</v>
       </c>
       <c r="D3" t="n">
-        <v>167.42852347</v>
+        <v>124.14557469</v>
       </c>
       <c r="E3" t="n">
-        <v>131.20067092</v>
+        <v>54.23512341</v>
       </c>
       <c r="F3" t="n">
-        <v>47.32288347</v>
+        <v>-31.05750398999999</v>
       </c>
       <c r="G3" t="n">
-        <v>-54.27841157</v>
+        <v>50.52273997</v>
       </c>
       <c r="H3" t="n">
-        <v>44.99788483999998</v>
+        <v>130.79247186</v>
       </c>
       <c r="I3" t="n">
-        <v>133.55249681</v>
+        <v>140.16408121</v>
       </c>
       <c r="J3" t="n">
-        <v>127.84452171</v>
+        <v>130.03350426</v>
       </c>
       <c r="K3" t="n">
-        <v>95.93423469</v>
+        <v>213.75028653</v>
       </c>
       <c r="L3" t="n">
-        <v>164.72193823</v>
+        <v>273.34038471</v>
       </c>
       <c r="M3" t="n">
-        <v>252.21287347</v>
+        <v>186.63607038</v>
       </c>
     </row>
     <row r="4">
@@ -585,37 +587,37 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>24.36349545</v>
+        <v>155.003109</v>
       </c>
       <c r="D4" t="n">
-        <v>152.98839114</v>
+        <v>63.79301953</v>
       </c>
       <c r="E4" t="n">
-        <v>47.75745193</v>
+        <v>215.36167827</v>
       </c>
       <c r="F4" t="n">
-        <v>208.36690609</v>
+        <v>-90.39439253</v>
       </c>
       <c r="G4" t="n">
-        <v>-66.71195385</v>
+        <v>-3.575122609999999</v>
       </c>
       <c r="H4" t="n">
-        <v>-32.01071431</v>
+        <v>-13.82677621000002</v>
       </c>
       <c r="I4" t="n">
-        <v>-53.69707771000002</v>
+        <v>-73.98470615000001</v>
       </c>
       <c r="J4" t="n">
-        <v>-65.40194232</v>
+        <v>-183.42682176</v>
       </c>
       <c r="K4" t="n">
-        <v>-145.16365585</v>
+        <v>-194.17610375</v>
       </c>
       <c r="L4" t="n">
-        <v>-143.95420855</v>
+        <v>105.10033907</v>
       </c>
       <c r="M4" t="n">
-        <v>119.33263953</v>
+        <v>198.25096442</v>
       </c>
     </row>
     <row r="5">
@@ -626,37 +628,37 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>633.9211675299999</v>
+        <v>146.0345752</v>
       </c>
       <c r="D5" t="n">
-        <v>146.03440984</v>
+        <v>-38.63452967</v>
       </c>
       <c r="E5" t="n">
-        <v>-38.63469054000001</v>
+        <v>-259.31952884</v>
       </c>
       <c r="F5" t="n">
-        <v>-259.31952002</v>
+        <v>-387.10508165</v>
       </c>
       <c r="G5" t="n">
-        <v>-387.10507082</v>
+        <v>-428.41046551</v>
       </c>
       <c r="H5" t="n">
-        <v>-428.41055059</v>
+        <v>-414.44000099</v>
       </c>
       <c r="I5" t="n">
-        <v>-414.44012063</v>
+        <v>-488.4738502000001</v>
       </c>
       <c r="J5" t="n">
-        <v>-488.47392939</v>
+        <v>-416.8719373800001</v>
       </c>
       <c r="K5" t="n">
-        <v>-416.8720858</v>
+        <v>-354.13634132</v>
       </c>
       <c r="L5" t="n">
-        <v>-354.1363623</v>
+        <v>-250.13333523</v>
       </c>
       <c r="M5" t="n">
-        <v>-250.13332917</v>
+        <v>-355.59155334</v>
       </c>
     </row>
     <row r="6">
@@ -665,39 +667,41 @@
           <t>其他右下</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
       <c r="C6" t="n">
-        <v>59.98246195999999</v>
+        <v>11.56633733</v>
       </c>
       <c r="D6" t="n">
-        <v>11.23192045</v>
+        <v>23.38891836</v>
       </c>
       <c r="E6" t="n">
-        <v>17.82646754</v>
+        <v>61.75983711</v>
       </c>
       <c r="F6" t="n">
-        <v>63.14545295000001</v>
+        <v>75.86807717000001</v>
       </c>
       <c r="G6" t="n">
-        <v>81.07541612999999</v>
+        <v>71.68095057000001</v>
       </c>
       <c r="H6" t="n">
-        <v>80.90591445</v>
+        <v>61.51880339</v>
       </c>
       <c r="I6" t="n">
-        <v>71.1532433</v>
+        <v>150.92365386</v>
       </c>
       <c r="J6" t="n">
-        <v>154.45330816</v>
+        <v>191.78965058</v>
       </c>
       <c r="K6" t="n">
-        <v>190.3080599</v>
+        <v>29.44580001999999</v>
       </c>
       <c r="L6" t="n">
-        <v>31.98070368999999</v>
+        <v>62.21572828999999</v>
       </c>
       <c r="M6" t="n">
-        <v>68.25413482999998</v>
+        <v>-16.40639453999999</v>
       </c>
     </row>
     <row r="7">
@@ -708,37 +712,37 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>12.56570013</v>
+        <v>12.0110792</v>
       </c>
       <c r="D7" t="n">
-        <v>12.34523166</v>
+        <v>14.39064089</v>
       </c>
       <c r="E7" t="n">
-        <v>19.9511593</v>
+        <v>1.866669629999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4774137899999991</v>
+        <v>-6.83235236</v>
       </c>
       <c r="G7" t="n">
-        <v>-12.04365878</v>
+        <v>-32.13406114</v>
       </c>
       <c r="H7" t="n">
-        <v>-41.36450387000001</v>
+        <v>-25.57055793</v>
       </c>
       <c r="I7" t="n">
-        <v>-35.20973066000001</v>
+        <v>-26.21872809</v>
       </c>
       <c r="J7" t="n">
-        <v>-29.75304235</v>
+        <v>-34.91576833</v>
       </c>
       <c r="K7" t="n">
-        <v>-33.43528821</v>
+        <v>-50.83131593</v>
       </c>
       <c r="L7" t="n">
-        <v>-53.37011325000001</v>
+        <v>-23.19731798</v>
       </c>
       <c r="M7" t="n">
-        <v>-29.23449371</v>
+        <v>-7.337062079999998</v>
       </c>
     </row>
     <row r="8">
@@ -749,37 +753,37 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>1082.17697646</v>
+        <v>1216.91979688</v>
       </c>
       <c r="D8" t="n">
-        <v>1217.20015451</v>
+        <v>1224.70182488</v>
       </c>
       <c r="E8" t="n">
-        <v>1224.98766666</v>
+        <v>3053.45058058</v>
       </c>
       <c r="F8" t="n">
-        <v>3053.41093554</v>
+        <v>3202.47206384</v>
       </c>
       <c r="G8" t="n">
-        <v>3202.5230305</v>
+        <v>3797.04277677</v>
       </c>
       <c r="H8" t="n">
-        <v>3796.87587415</v>
+        <v>875.06135877</v>
       </c>
       <c r="I8" t="n">
-        <v>879.33300735</v>
+        <v>2608.67093669</v>
       </c>
       <c r="J8" t="n">
-        <v>2616.38882237</v>
+        <v>2447.64286738</v>
       </c>
       <c r="K8" t="n">
-        <v>2457.47498701</v>
+        <v>2990.65970583</v>
       </c>
       <c r="L8" t="n">
-        <v>3001.08271769</v>
+        <v>2850.23196878</v>
       </c>
       <c r="M8" t="n">
-        <v>2854.80565398</v>
+        <v>-845.7175441999999</v>
       </c>
     </row>
     <row r="9">
@@ -788,41 +792,39 @@
           <t>其他電子業右下</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>36.96293905</v>
+        <v>40.08045371000001</v>
       </c>
       <c r="D9" t="n">
-        <v>40.28744362</v>
+        <v>-1.64155862</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.39741973</v>
+        <v>12.49106397</v>
       </c>
       <c r="F9" t="n">
-        <v>12.6818208</v>
+        <v>-56.51378705</v>
       </c>
       <c r="G9" t="n">
-        <v>-56.32023273</v>
+        <v>-83.09307722</v>
       </c>
       <c r="H9" t="n">
-        <v>-82.96138404000001</v>
+        <v>-91.20032823999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-91.10828211000002</v>
+        <v>-123.55814704</v>
       </c>
       <c r="J9" t="n">
-        <v>-123.47710028</v>
+        <v>-130.50766605</v>
       </c>
       <c r="K9" t="n">
-        <v>-130.42492004</v>
+        <v>-119.50554787</v>
       </c>
       <c r="L9" t="n">
-        <v>-119.44557031</v>
+        <v>-109.67401669</v>
       </c>
       <c r="M9" t="n">
-        <v>-109.62339764</v>
+        <v>-113.21363326</v>
       </c>
     </row>
     <row r="10">
@@ -833,37 +835,37 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>32.8467998</v>
+        <v>92.92674992000001</v>
       </c>
       <c r="D10" t="n">
-        <v>92.43947256</v>
+        <v>17.44306224</v>
       </c>
       <c r="E10" t="n">
-        <v>16.91286693</v>
+        <v>45.06280080000001</v>
       </c>
       <c r="F10" t="n">
-        <v>44.91212201</v>
+        <v>-8.84950342</v>
       </c>
       <c r="G10" t="n">
-        <v>-9.094254979999999</v>
+        <v>-111.19370916</v>
       </c>
       <c r="H10" t="n">
-        <v>-111.15845621</v>
+        <v>-97.49701018</v>
       </c>
       <c r="I10" t="n">
-        <v>-101.86097063</v>
+        <v>-131.60384685</v>
       </c>
       <c r="J10" t="n">
-        <v>-139.40380109</v>
+        <v>-90.20574187000001</v>
       </c>
       <c r="K10" t="n">
-        <v>-100.12251588</v>
+        <v>-44.54427384</v>
       </c>
       <c r="L10" t="n">
-        <v>-55.02909974999999</v>
+        <v>25.94232598000002</v>
       </c>
       <c r="M10" t="n">
-        <v>21.31738405000002</v>
+        <v>-59.67607909</v>
       </c>
     </row>
     <row r="11">
@@ -874,37 +876,37 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>58.40428007</v>
+        <v>-4.426172029999999</v>
       </c>
       <c r="D11" t="n">
-        <v>5.30423225</v>
+        <v>-54.00431807</v>
       </c>
       <c r="E11" t="n">
-        <v>-57.61486382</v>
+        <v>-86.86555312</v>
       </c>
       <c r="F11" t="n">
-        <v>-84.49990516000001</v>
+        <v>-76.35197597000001</v>
       </c>
       <c r="G11" t="n">
-        <v>-71.27952607</v>
+        <v>-15.33443696000001</v>
       </c>
       <c r="H11" t="n">
-        <v>-9.778319470000007</v>
+        <v>30.12201213</v>
       </c>
       <c r="I11" t="n">
-        <v>31.64017136999999</v>
+        <v>-180.83661576</v>
       </c>
       <c r="J11" t="n">
-        <v>-181.89193455</v>
+        <v>-28.02151100000001</v>
       </c>
       <c r="K11" t="n">
-        <v>-28.50699865000001</v>
+        <v>312.29508241</v>
       </c>
       <c r="L11" t="n">
-        <v>309.12090261</v>
+        <v>658.2697451700001</v>
       </c>
       <c r="M11" t="n">
-        <v>653.33942918</v>
+        <v>242.28540973</v>
       </c>
     </row>
     <row r="12">
@@ -915,37 +917,37 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>-40.60041190999999</v>
+        <v>-101.9594561</v>
       </c>
       <c r="D12" t="n">
-        <v>-102.18770138</v>
+        <v>-105.76762729</v>
       </c>
       <c r="E12" t="n">
-        <v>-108.24216567</v>
+        <v>-24.18409051999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-30.29425106</v>
+        <v>360.8863256</v>
       </c>
       <c r="G12" t="n">
-        <v>360.7339206099999</v>
+        <v>240.79125821</v>
       </c>
       <c r="H12" t="n">
-        <v>243.27156338</v>
+        <v>174.4546849</v>
       </c>
       <c r="I12" t="n">
-        <v>170.82302881</v>
+        <v>-44.78824605</v>
       </c>
       <c r="J12" t="n">
-        <v>-59.30385586</v>
+        <v>-24.95834715</v>
       </c>
       <c r="K12" t="n">
-        <v>-39.19330053</v>
+        <v>-1.651111749999998</v>
       </c>
       <c r="L12" t="n">
-        <v>-18.61229305</v>
+        <v>48.41734252000001</v>
       </c>
       <c r="M12" t="n">
-        <v>14.54049766</v>
+        <v>-29.50577848</v>
       </c>
     </row>
     <row r="13">
@@ -956,37 +958,37 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>-0.05241517000000009</v>
+        <v>-9.052562119999999</v>
       </c>
       <c r="D13" t="n">
-        <v>-18.55472112</v>
+        <v>-6.205485100000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1204009700000007</v>
+        <v>7.050954819999999</v>
       </c>
       <c r="F13" t="n">
-        <v>10.7954674</v>
+        <v>-3.47330351</v>
       </c>
       <c r="G13" t="n">
-        <v>-8.393348420000001</v>
+        <v>0.1664978700000001</v>
       </c>
       <c r="H13" t="n">
-        <v>-7.869924789999999</v>
+        <v>21.38924244</v>
       </c>
       <c r="I13" t="n">
-        <v>23.50273929</v>
+        <v>43.57069945000001</v>
       </c>
       <c r="J13" t="n">
-        <v>59.14162804999999</v>
+        <v>24.29618216</v>
       </c>
       <c r="K13" t="n">
-        <v>39.01662319</v>
+        <v>22.92182365</v>
       </c>
       <c r="L13" t="n">
-        <v>43.05718475</v>
+        <v>35.76870215</v>
       </c>
       <c r="M13" t="n">
-        <v>74.575863</v>
+        <v>21.2768524</v>
       </c>
     </row>
     <row r="14">
@@ -997,37 +999,37 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>-6594.14844021</v>
+        <v>-1366.25182753</v>
       </c>
       <c r="D14" t="n">
-        <v>-1898.4734454</v>
+        <v>-3909.35918457</v>
       </c>
       <c r="E14" t="n">
-        <v>-4366.75783154</v>
+        <v>5013.90762208</v>
       </c>
       <c r="F14" t="n">
-        <v>4873.196510209999</v>
+        <v>1659.55785566</v>
       </c>
       <c r="G14" t="n">
-        <v>1756.55389994</v>
+        <v>7284.156148679999</v>
       </c>
       <c r="H14" t="n">
-        <v>7627.41346733</v>
+        <v>4018.80423298</v>
       </c>
       <c r="I14" t="n">
-        <v>4133.37325492</v>
+        <v>7510.388950680001</v>
       </c>
       <c r="J14" t="n">
-        <v>7781.72777513</v>
+        <v>3887.31917214</v>
       </c>
       <c r="K14" t="n">
-        <v>3994.91937618</v>
+        <v>4387.32142908</v>
       </c>
       <c r="L14" t="n">
-        <v>4395.53537626</v>
+        <v>1575.79333564</v>
       </c>
       <c r="M14" t="n">
-        <v>1742.02967083</v>
+        <v>607.00186777</v>
       </c>
     </row>
     <row r="15">
@@ -1040,37 +1042,37 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>225.8095879299999</v>
+        <v>405.65647524</v>
       </c>
       <c r="D15" t="n">
-        <v>610.7338875</v>
+        <v>-169.3662312</v>
       </c>
       <c r="E15" t="n">
-        <v>-94.80977159000003</v>
+        <v>-342.01578111</v>
       </c>
       <c r="F15" t="n">
-        <v>-417.50653784</v>
+        <v>213.58401075</v>
       </c>
       <c r="G15" t="n">
-        <v>317.7782638200001</v>
+        <v>-24.42671701</v>
       </c>
       <c r="H15" t="n">
-        <v>27.97551376999998</v>
+        <v>830.46147178</v>
       </c>
       <c r="I15" t="n">
-        <v>979.1516323300001</v>
+        <v>341.12004153</v>
       </c>
       <c r="J15" t="n">
-        <v>577.7574768100001</v>
+        <v>570.66117303</v>
       </c>
       <c r="K15" t="n">
-        <v>839.4041663200001</v>
+        <v>563.44598555</v>
       </c>
       <c r="L15" t="n">
-        <v>892.65652936</v>
+        <v>315.28214846</v>
       </c>
       <c r="M15" t="n">
-        <v>419.4552546799999</v>
+        <v>-48.89996611000002</v>
       </c>
     </row>
     <row r="16">
@@ -1081,37 +1083,37 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>-477.72881351</v>
+        <v>-401.11096956</v>
       </c>
       <c r="D16" t="n">
-        <v>-196.34137564</v>
+        <v>-898.7240468700001</v>
       </c>
       <c r="E16" t="n">
-        <v>-499.35299213</v>
+        <v>78.75591238</v>
       </c>
       <c r="F16" t="n">
-        <v>87.5208913</v>
+        <v>-300.91909334</v>
       </c>
       <c r="G16" t="n">
-        <v>-151.84973796</v>
+        <v>-472.0598458800001</v>
       </c>
       <c r="H16" t="n">
-        <v>-301.49532814</v>
+        <v>-700.5296005499999</v>
       </c>
       <c r="I16" t="n">
-        <v>-249.4660041</v>
+        <v>-291.1882918599999</v>
       </c>
       <c r="J16" t="n">
-        <v>100.37929446</v>
+        <v>35.47685648999999</v>
       </c>
       <c r="K16" t="n">
-        <v>193.60964602</v>
+        <v>-487.94771527</v>
       </c>
       <c r="L16" t="n">
-        <v>-248.13278948</v>
+        <v>-122.07344023</v>
       </c>
       <c r="M16" t="n">
-        <v>-36.99389134000001</v>
+        <v>-545.2346220099998</v>
       </c>
     </row>
     <row r="17">
@@ -1122,37 +1124,37 @@
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
-        <v>0.8801225899999999</v>
+        <v>0.95461918</v>
       </c>
       <c r="D17" t="n">
-        <v>0.95461918</v>
+        <v>0.84933853</v>
       </c>
       <c r="E17" t="n">
-        <v>0.84933853</v>
+        <v>-0.12911185</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.12911185</v>
+        <v>0.18345265</v>
       </c>
       <c r="G17" t="n">
-        <v>0.18345265</v>
+        <v>-0.75565477</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.75565477</v>
+        <v>-1.09301157</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.09301157</v>
+        <v>-1.25991411</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.25991411</v>
+        <v>0.42586555</v>
       </c>
       <c r="K17" t="n">
-        <v>0.42586555</v>
+        <v>1.11311752</v>
       </c>
       <c r="L17" t="n">
-        <v>1.11311752</v>
+        <v>0.08433128999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>0.08433128999999999</v>
+        <v>-0.35153504</v>
       </c>
     </row>
     <row r="18">
@@ -1163,37 +1165,37 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>-613.08167041</v>
+        <v>-1069.80177573</v>
       </c>
       <c r="D18" t="n">
-        <v>-580.6133292200001</v>
+        <v>-452.59567873</v>
       </c>
       <c r="E18" t="n">
-        <v>-247.38925816</v>
+        <v>-531.6740625399999</v>
       </c>
       <c r="F18" t="n">
-        <v>-214.90409677</v>
+        <v>-603.34921862</v>
       </c>
       <c r="G18" t="n">
-        <v>-217.08732924</v>
+        <v>-1.127325219999998</v>
       </c>
       <c r="H18" t="n">
-        <v>-9.226010169999997</v>
+        <v>755.78596021</v>
       </c>
       <c r="I18" t="n">
-        <v>290.48966357</v>
+        <v>808.41952552</v>
       </c>
       <c r="J18" t="n">
-        <v>54.82167167</v>
+        <v>20.00698698</v>
       </c>
       <c r="K18" t="n">
-        <v>-54.16778170999999</v>
+        <v>397.85688729</v>
       </c>
       <c r="L18" t="n">
-        <v>89.1547312</v>
+        <v>941.7538826699999</v>
       </c>
       <c r="M18" t="n">
-        <v>243.45978075</v>
+        <v>-199.19026018</v>
       </c>
     </row>
     <row r="19">
@@ -1204,37 +1206,37 @@
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>-259.90964889</v>
+        <v>-3.50220013</v>
       </c>
       <c r="D19" t="n">
-        <v>-492.69064664</v>
+        <v>-0.4466357</v>
       </c>
       <c r="E19" t="n">
-        <v>-205.65305627</v>
+        <v>-5.082314830000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-321.8522806</v>
+        <v>-16.21447943</v>
       </c>
       <c r="G19" t="n">
-        <v>-402.47636881</v>
+        <v>-16.77098081</v>
       </c>
       <c r="H19" t="n">
-        <v>-8.67229586</v>
+        <v>-9.840661000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>455.45563564</v>
+        <v>-1.05493727</v>
       </c>
       <c r="J19" t="n">
-        <v>752.54291658</v>
+        <v>2.73203374</v>
       </c>
       <c r="K19" t="n">
-        <v>76.90680243</v>
+        <v>5.22590165</v>
       </c>
       <c r="L19" t="n">
-        <v>313.9280577399999</v>
+        <v>0.6281126800000002</v>
       </c>
       <c r="M19" t="n">
-        <v>698.9222146000001</v>
+        <v>-0.7541094099999999</v>
       </c>
     </row>
     <row r="20">
@@ -1245,37 +1247,37 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>-8.6719104</v>
+        <v>6.29112816</v>
       </c>
       <c r="D20" t="n">
-        <v>6.29112816</v>
+        <v>-11.38791094</v>
       </c>
       <c r="E20" t="n">
-        <v>-11.38791094</v>
+        <v>39.90390299</v>
       </c>
       <c r="F20" t="n">
-        <v>39.90390299</v>
+        <v>-7.499015480000001</v>
       </c>
       <c r="G20" t="n">
-        <v>-7.499015480000001</v>
+        <v>-34.65196079</v>
       </c>
       <c r="H20" t="n">
-        <v>-34.65196079</v>
+        <v>-20.07586818</v>
       </c>
       <c r="I20" t="n">
-        <v>-20.07586818</v>
+        <v>37.03994246</v>
       </c>
       <c r="J20" t="n">
-        <v>37.03994246</v>
+        <v>61.97440654</v>
       </c>
       <c r="K20" t="n">
-        <v>61.97440654</v>
+        <v>4.784528130000001</v>
       </c>
       <c r="L20" t="n">
-        <v>4.784528130000001</v>
+        <v>-26.57971293</v>
       </c>
       <c r="M20" t="n">
-        <v>-26.57971293</v>
+        <v>-51.94192612000001</v>
       </c>
     </row>
     <row r="21">
@@ -1284,39 +1286,41 @@
           <t>居家生活右下</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
       <c r="C21" t="n">
-        <v>2.43176105</v>
+        <v>1.74384863</v>
       </c>
       <c r="D21" t="n">
-        <v>1.74360164</v>
+        <v>1.74691358</v>
       </c>
       <c r="E21" t="n">
-        <v>1.74665228</v>
+        <v>1.07924872</v>
       </c>
       <c r="F21" t="n">
-        <v>1.07892036</v>
+        <v>-4.11526546</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.11563068</v>
+        <v>-7.67942267</v>
       </c>
       <c r="H21" t="n">
-        <v>-7.67926037</v>
+        <v>-2.84958627</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.84996866</v>
+        <v>-1.06654168</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.066877</v>
+        <v>0.6943522100000002</v>
       </c>
       <c r="K21" t="n">
-        <v>0.69413256</v>
+        <v>-0.5864628399999998</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5863826000000001</v>
+        <v>-1.04684694</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.04495596</v>
+        <v>-1.56026058</v>
       </c>
     </row>
     <row r="22">
@@ -1327,37 +1331,37 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>2.66362539</v>
+        <v>2.26413284</v>
       </c>
       <c r="D22" t="n">
-        <v>2.26437778</v>
+        <v>2.7112108</v>
       </c>
       <c r="E22" t="n">
-        <v>2.71147005</v>
+        <v>2.27478051</v>
       </c>
       <c r="F22" t="n">
-        <v>2.27511529</v>
+        <v>3.80914126</v>
       </c>
       <c r="G22" t="n">
-        <v>3.80951349</v>
+        <v>1.51320008</v>
       </c>
       <c r="H22" t="n">
-        <v>1.5130412</v>
+        <v>0.8471258</v>
       </c>
       <c r="I22" t="n">
-        <v>0.84749379</v>
+        <v>1.00880626</v>
       </c>
       <c r="J22" t="n">
-        <v>1.00913396</v>
+        <v>3.3058719</v>
       </c>
       <c r="K22" t="n">
-        <v>3.30609277</v>
+        <v>4.33978429</v>
       </c>
       <c r="L22" t="n">
-        <v>4.33970527</v>
+        <v>1.19746172</v>
       </c>
       <c r="M22" t="n">
-        <v>1.19769344</v>
+        <v>1.25147485</v>
       </c>
     </row>
     <row r="23">
@@ -1368,37 +1372,37 @@
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
-        <v>37.88405859</v>
+        <v>24.20960816</v>
       </c>
       <c r="D23" t="n">
-        <v>24.20960816</v>
+        <v>17.34495134</v>
       </c>
       <c r="E23" t="n">
-        <v>17.34495134</v>
+        <v>10.97104816</v>
       </c>
       <c r="F23" t="n">
-        <v>10.97104816</v>
+        <v>14.7137113</v>
       </c>
       <c r="G23" t="n">
-        <v>14.7137113</v>
+        <v>25.86115714</v>
       </c>
       <c r="H23" t="n">
-        <v>25.86115714</v>
+        <v>61.50186898999999</v>
       </c>
       <c r="I23" t="n">
-        <v>61.50186898999999</v>
+        <v>67.72679253</v>
       </c>
       <c r="J23" t="n">
-        <v>67.72679253</v>
+        <v>73.11998154999999</v>
       </c>
       <c r="K23" t="n">
-        <v>73.11998154999999</v>
+        <v>134.38158645</v>
       </c>
       <c r="L23" t="n">
-        <v>134.38158645</v>
+        <v>128.60766598</v>
       </c>
       <c r="M23" t="n">
-        <v>128.60766598</v>
+        <v>54.72915059</v>
       </c>
     </row>
     <row r="24">
@@ -1409,37 +1413,37 @@
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
-        <v>83.64050492</v>
+        <v>25.4033357</v>
       </c>
       <c r="D24" t="n">
-        <v>26.71992094</v>
+        <v>9.407099060000002</v>
       </c>
       <c r="E24" t="n">
-        <v>13.29203751000001</v>
+        <v>-28.60478166</v>
       </c>
       <c r="F24" t="n">
-        <v>-21.13706619</v>
+        <v>-52.17398673</v>
       </c>
       <c r="G24" t="n">
-        <v>-42.5733706</v>
+        <v>-56.72933906</v>
       </c>
       <c r="H24" t="n">
-        <v>-44.01588298</v>
+        <v>-58.07142467</v>
       </c>
       <c r="I24" t="n">
-        <v>-45.47459771</v>
+        <v>7.94764037</v>
       </c>
       <c r="J24" t="n">
-        <v>-27.29051669</v>
+        <v>15.47102482</v>
       </c>
       <c r="K24" t="n">
-        <v>5.65131877</v>
+        <v>30.43583354</v>
       </c>
       <c r="L24" t="n">
-        <v>28.50662747</v>
+        <v>34.01798669</v>
       </c>
       <c r="M24" t="n">
-        <v>38.06157995</v>
+        <v>20.54550917</v>
       </c>
     </row>
     <row r="25">
@@ -1450,37 +1454,37 @@
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>54.79970311</v>
+        <v>27.44718895</v>
       </c>
       <c r="D25" t="n">
-        <v>26.13074153</v>
+        <v>44.0481345</v>
       </c>
       <c r="E25" t="n">
-        <v>40.16345089</v>
+        <v>41.94677165</v>
       </c>
       <c r="F25" t="n">
-        <v>34.47930947</v>
+        <v>18.17364713</v>
       </c>
       <c r="G25" t="n">
-        <v>8.573180339999997</v>
+        <v>21.60931035</v>
       </c>
       <c r="H25" t="n">
-        <v>8.895907459999998</v>
+        <v>18.29554628</v>
       </c>
       <c r="I25" t="n">
-        <v>5.698523059999999</v>
+        <v>9.43256483</v>
       </c>
       <c r="J25" t="n">
-        <v>44.67063214</v>
+        <v>38.23987602</v>
       </c>
       <c r="K25" t="n">
-        <v>48.05917072</v>
+        <v>35.05095730000001</v>
       </c>
       <c r="L25" t="n">
-        <v>36.97969401</v>
+        <v>41.8600014</v>
       </c>
       <c r="M25" t="n">
-        <v>37.81591028</v>
+        <v>-13.67264728</v>
       </c>
     </row>
     <row r="26">
@@ -1491,37 +1495,37 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>3.95032609</v>
+        <v>8.953501469999999</v>
       </c>
       <c r="D26" t="n">
-        <v>8.953404039999999</v>
+        <v>5.88787313</v>
       </c>
       <c r="E26" t="n">
-        <v>5.887683269999999</v>
+        <v>7.593937100000001</v>
       </c>
       <c r="F26" t="n">
-        <v>7.59334499</v>
+        <v>5.17181729</v>
       </c>
       <c r="G26" t="n">
-        <v>5.17034791</v>
+        <v>7.592146520000001</v>
       </c>
       <c r="H26" t="n">
-        <v>7.59349848</v>
+        <v>18.69060947</v>
       </c>
       <c r="I26" t="n">
-        <v>18.69440627</v>
+        <v>6.72654781</v>
       </c>
       <c r="J26" t="n">
-        <v>6.72809566</v>
+        <v>5.82618834</v>
       </c>
       <c r="K26" t="n">
-        <v>5.8262754</v>
+        <v>6.19496605</v>
       </c>
       <c r="L26" t="n">
-        <v>6.19576568</v>
+        <v>7.53425048</v>
       </c>
       <c r="M26" t="n">
-        <v>7.534156789999999</v>
+        <v>1.57906642</v>
       </c>
     </row>
     <row r="27">
@@ -1532,37 +1536,37 @@
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>7.256533559999999</v>
+        <v>21.41594651</v>
       </c>
       <c r="D27" t="n">
-        <v>21.41555787</v>
+        <v>9.254340819999999</v>
       </c>
       <c r="E27" t="n">
-        <v>9.253958190000001</v>
+        <v>20.89016642</v>
       </c>
       <c r="F27" t="n">
-        <v>20.89001611</v>
+        <v>17.74083201</v>
       </c>
       <c r="G27" t="n">
-        <v>17.74033155</v>
+        <v>22.20219834</v>
       </c>
       <c r="H27" t="n">
-        <v>22.20184127</v>
+        <v>32.01863252</v>
       </c>
       <c r="I27" t="n">
-        <v>32.01865752</v>
+        <v>32.91413802</v>
       </c>
       <c r="J27" t="n">
-        <v>32.91440352</v>
+        <v>31.9022584</v>
       </c>
       <c r="K27" t="n">
-        <v>31.90241096</v>
+        <v>15.84968732</v>
       </c>
       <c r="L27" t="n">
-        <v>15.84994324</v>
+        <v>15.5018982</v>
       </c>
       <c r="M27" t="n">
-        <v>15.5021924</v>
+        <v>7.184865029999999</v>
       </c>
     </row>
     <row r="28">
@@ -1573,37 +1577,37 @@
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>-19.63720791</v>
+        <v>3.95173604</v>
       </c>
       <c r="D28" t="n">
-        <v>3.95222211</v>
+        <v>-27.67383012</v>
       </c>
       <c r="E28" t="n">
-        <v>-27.67325763</v>
+        <v>-47.67117451</v>
       </c>
       <c r="F28" t="n">
-        <v>-47.67043209</v>
+        <v>-79.82541303000001</v>
       </c>
       <c r="G28" t="n">
-        <v>-79.82344318999999</v>
+        <v>-109.72696506</v>
       </c>
       <c r="H28" t="n">
-        <v>-109.72795995</v>
+        <v>-102.93766366</v>
       </c>
       <c r="I28" t="n">
-        <v>-102.94148546</v>
+        <v>-89.79266072999999</v>
       </c>
       <c r="J28" t="n">
-        <v>-89.79447408</v>
+        <v>-73.93321212000001</v>
       </c>
       <c r="K28" t="n">
-        <v>-73.93345174000001</v>
+        <v>-58.76314611999999</v>
       </c>
       <c r="L28" t="n">
-        <v>-58.76420166999999</v>
+        <v>-32.14095302</v>
       </c>
       <c r="M28" t="n">
-        <v>-32.14115353</v>
+        <v>-29.38440493</v>
       </c>
     </row>
     <row r="29">
@@ -1614,37 +1618,37 @@
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>0.02746755</v>
+        <v>0.08414062</v>
       </c>
       <c r="D29" t="n">
-        <v>0.08414062</v>
+        <v>0.07506878</v>
       </c>
       <c r="E29" t="n">
-        <v>0.07506878</v>
+        <v>0.03323846</v>
       </c>
       <c r="F29" t="n">
-        <v>0.03323846</v>
+        <v>0.00619917</v>
       </c>
       <c r="G29" t="n">
-        <v>0.00619917</v>
+        <v>0.01277118</v>
       </c>
       <c r="H29" t="n">
-        <v>0.01277118</v>
+        <v>-0.00653676</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.00653676</v>
+        <v>-0.01623805</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.01623805</v>
+        <v>-0.01854561</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.01854561</v>
+        <v>-0.0214375</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.0214375</v>
+        <v>-0.00590779</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.00590779</v>
+        <v>0.007246020000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1653,39 +1657,41 @@
           <t>文化創意業右下</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
       <c r="C30" t="n">
-        <v>0.0079351</v>
+        <v>0.0102936</v>
       </c>
       <c r="D30" t="n">
-        <v>0.01028314</v>
+        <v>0.005392780000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>0.00538708</v>
+        <v>0.01211806</v>
       </c>
       <c r="F30" t="n">
-        <v>0.01209633</v>
+        <v>0.00088056</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0008129699999999999</v>
+        <v>-0.00458671</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.00467908</v>
+        <v>-0.00565963</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.00565026</v>
+        <v>-0.006874069999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.00688049</v>
+        <v>0.01007853</v>
       </c>
       <c r="K30" t="n">
-        <v>0.01008529</v>
+        <v>0.0022248</v>
       </c>
       <c r="L30" t="n">
-        <v>0.00215091</v>
+        <v>0.003635520000000001</v>
       </c>
       <c r="M30" t="n">
-        <v>0.003591480000000001</v>
+        <v>0.00158488</v>
       </c>
     </row>
     <row r="31">
@@ -1696,37 +1702,37 @@
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>0.10054297</v>
+        <v>0.21751282</v>
       </c>
       <c r="D31" t="n">
-        <v>0.21751282</v>
+        <v>0.10936104</v>
       </c>
       <c r="E31" t="n">
-        <v>0.10936104</v>
+        <v>0.03924989</v>
       </c>
       <c r="F31" t="n">
-        <v>0.03924989</v>
+        <v>-0.01166996</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.01166996</v>
+        <v>-0.05285173000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.05285173000000001</v>
+        <v>-0.09475462</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.09475462</v>
+        <v>-0.1850039</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.1850039</v>
+        <v>0.0035406</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0035406</v>
+        <v>-0.03696819</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.03696819</v>
+        <v>0.20996728</v>
       </c>
       <c r="M31" t="n">
-        <v>0.20996728</v>
+        <v>0.08270688000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1737,37 +1743,37 @@
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>-8.503892480000001</v>
+        <v>-15.01818866</v>
       </c>
       <c r="D32" t="n">
-        <v>-15.01818866</v>
+        <v>-18.7437909</v>
       </c>
       <c r="E32" t="n">
-        <v>-18.7437909</v>
+        <v>-21.51308012</v>
       </c>
       <c r="F32" t="n">
-        <v>-21.51308012</v>
+        <v>-26.23204626999999</v>
       </c>
       <c r="G32" t="n">
-        <v>-26.23204626999999</v>
+        <v>-28.63820698</v>
       </c>
       <c r="H32" t="n">
-        <v>-28.63820698</v>
+        <v>-10.76783712</v>
       </c>
       <c r="I32" t="n">
-        <v>-10.76783712</v>
+        <v>-20.0377565</v>
       </c>
       <c r="J32" t="n">
-        <v>-20.0377565</v>
+        <v>-6.47922948</v>
       </c>
       <c r="K32" t="n">
-        <v>-6.47922948</v>
+        <v>-21.67391496</v>
       </c>
       <c r="L32" t="n">
-        <v>-21.67391496</v>
+        <v>5.52792584</v>
       </c>
       <c r="M32" t="n">
-        <v>5.52792584</v>
+        <v>7.32848074</v>
       </c>
     </row>
     <row r="33">
@@ -1778,37 +1784,37 @@
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
-        <v>1.38274384</v>
+        <v>4.3513519</v>
       </c>
       <c r="D33" t="n">
-        <v>4.3513519</v>
+        <v>22.15492144</v>
       </c>
       <c r="E33" t="n">
-        <v>22.15492144</v>
+        <v>1.31634559</v>
       </c>
       <c r="F33" t="n">
-        <v>1.31634559</v>
+        <v>-7.02553147</v>
       </c>
       <c r="G33" t="n">
-        <v>-7.02553147</v>
+        <v>-14.85168894</v>
       </c>
       <c r="H33" t="n">
-        <v>-14.85168894</v>
+        <v>-7.31165541</v>
       </c>
       <c r="I33" t="n">
-        <v>-7.31165541</v>
+        <v>-1.41149422</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.41149422</v>
+        <v>-7.85183825</v>
       </c>
       <c r="K33" t="n">
-        <v>-7.85183825</v>
+        <v>6.05615573</v>
       </c>
       <c r="L33" t="n">
-        <v>6.05615573</v>
+        <v>10.38013217</v>
       </c>
       <c r="M33" t="n">
-        <v>10.38013217</v>
+        <v>14.06584317</v>
       </c>
     </row>
     <row r="34">
@@ -1819,37 +1825,37 @@
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
-        <v>21.63590168</v>
+        <v>34.050435</v>
       </c>
       <c r="D34" t="n">
-        <v>34.050435</v>
+        <v>53.00901164</v>
       </c>
       <c r="E34" t="n">
-        <v>53.00901164</v>
+        <v>23.37416052</v>
       </c>
       <c r="F34" t="n">
-        <v>23.37416052</v>
+        <v>33.49646586</v>
       </c>
       <c r="G34" t="n">
-        <v>33.49646586</v>
+        <v>42.38292683</v>
       </c>
       <c r="H34" t="n">
-        <v>42.38292683</v>
+        <v>53.14078301</v>
       </c>
       <c r="I34" t="n">
-        <v>53.14078301</v>
+        <v>77.31264456</v>
       </c>
       <c r="J34" t="n">
-        <v>77.31264456</v>
+        <v>-99.06594910000001</v>
       </c>
       <c r="K34" t="n">
-        <v>-99.06594910000001</v>
+        <v>-137.71287059</v>
       </c>
       <c r="L34" t="n">
-        <v>-137.71287059</v>
+        <v>-36.98264507</v>
       </c>
       <c r="M34" t="n">
-        <v>-36.98264507</v>
+        <v>-110.28325571</v>
       </c>
     </row>
     <row r="35">
@@ -1860,37 +1866,37 @@
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
-        <v>-0.8053423099999999</v>
+        <v>-0.5541974000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.5541974000000001</v>
+        <v>-0.86426467</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.86426467</v>
+        <v>-1.03027462</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.03027462</v>
+        <v>-0.0252352</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.0252352</v>
+        <v>-0.03013220000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.03013220000000001</v>
+        <v>3.18854859</v>
       </c>
       <c r="I35" t="n">
-        <v>3.18854859</v>
+        <v>2.605460190000001</v>
       </c>
       <c r="J35" t="n">
-        <v>2.605460190000001</v>
+        <v>4.13401164</v>
       </c>
       <c r="K35" t="n">
-        <v>4.13401164</v>
+        <v>4.72190981</v>
       </c>
       <c r="L35" t="n">
-        <v>4.72190981</v>
+        <v>5.98762434</v>
       </c>
       <c r="M35" t="n">
-        <v>5.98762434</v>
+        <v>2.37916882</v>
       </c>
     </row>
     <row r="36">
@@ -1901,37 +1907,37 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>85.63237165</v>
+        <v>179.98748556</v>
       </c>
       <c r="D36" t="n">
-        <v>179.98748556</v>
+        <v>243.01780536</v>
       </c>
       <c r="E36" t="n">
-        <v>243.01780536</v>
+        <v>120.77072082</v>
       </c>
       <c r="F36" t="n">
-        <v>120.77072082</v>
+        <v>227.54441106</v>
       </c>
       <c r="G36" t="n">
-        <v>227.54441106</v>
+        <v>364.58955555</v>
       </c>
       <c r="H36" t="n">
-        <v>364.58955555</v>
+        <v>215.34440896</v>
       </c>
       <c r="I36" t="n">
-        <v>215.34440896</v>
+        <v>203.11277483</v>
       </c>
       <c r="J36" t="n">
-        <v>203.11277483</v>
+        <v>-9.032017559999998</v>
       </c>
       <c r="K36" t="n">
-        <v>-9.032017559999998</v>
+        <v>184.61897931</v>
       </c>
       <c r="L36" t="n">
-        <v>184.61897931</v>
+        <v>4.745168009999998</v>
       </c>
       <c r="M36" t="n">
-        <v>5.011323659999997</v>
+        <v>-97.09928714</v>
       </c>
     </row>
     <row r="37">
@@ -1942,37 +1948,37 @@
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>12.32487082</v>
+        <v>40.78875832</v>
       </c>
       <c r="D37" t="n">
-        <v>26.76512174</v>
+        <v>47.36219706</v>
       </c>
       <c r="E37" t="n">
-        <v>29.93842295</v>
+        <v>48.34040938</v>
       </c>
       <c r="F37" t="n">
-        <v>34.89785375</v>
+        <v>4.062234399999999</v>
       </c>
       <c r="G37" t="n">
-        <v>5.251687500000002</v>
+        <v>3.04155708</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.198131249999999</v>
+        <v>30.92171678</v>
       </c>
       <c r="I37" t="n">
-        <v>25.6866078</v>
+        <v>9.269855889999999</v>
       </c>
       <c r="J37" t="n">
-        <v>11.81555731</v>
+        <v>27.09746122</v>
       </c>
       <c r="K37" t="n">
-        <v>15.79877344</v>
+        <v>7.489372550000001</v>
       </c>
       <c r="L37" t="n">
-        <v>14.04205434</v>
+        <v>29.27701968</v>
       </c>
       <c r="M37" t="n">
-        <v>44.0899897</v>
+        <v>6.686107529999997</v>
       </c>
     </row>
     <row r="38">
@@ -1983,37 +1989,37 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>-1.056509029999998</v>
+        <v>52.94766575999999</v>
       </c>
       <c r="D38" t="n">
-        <v>56.57809310999999</v>
+        <v>15.77497270000001</v>
       </c>
       <c r="E38" t="n">
-        <v>21.60893473000001</v>
+        <v>-39.41090152</v>
       </c>
       <c r="F38" t="n">
-        <v>-37.8064404</v>
+        <v>-63.60066107999999</v>
       </c>
       <c r="G38" t="n">
-        <v>-64.52067828999999</v>
+        <v>-14.02917632</v>
       </c>
       <c r="H38" t="n">
-        <v>-17.82765088</v>
+        <v>34.31521913</v>
       </c>
       <c r="I38" t="n">
-        <v>30.20554926</v>
+        <v>36.09935012</v>
       </c>
       <c r="J38" t="n">
-        <v>37.14663873000001</v>
+        <v>-28.88015934</v>
       </c>
       <c r="K38" t="n">
-        <v>-20.40864164</v>
+        <v>2.15830559</v>
       </c>
       <c r="L38" t="n">
-        <v>2.93989154</v>
+        <v>-45.70276733</v>
       </c>
       <c r="M38" t="n">
-        <v>-48.22699395</v>
+        <v>-110.970004</v>
       </c>
     </row>
     <row r="39">
@@ -2024,37 +2030,37 @@
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
-        <v>2.09904764</v>
+        <v>3.22631047</v>
       </c>
       <c r="D39" t="n">
-        <v>3.22631047</v>
+        <v>8.135896049999999</v>
       </c>
       <c r="E39" t="n">
-        <v>8.135896049999999</v>
+        <v>0.42597227</v>
       </c>
       <c r="F39" t="n">
-        <v>0.42597227</v>
+        <v>5.236759269999999</v>
       </c>
       <c r="G39" t="n">
-        <v>5.236759269999999</v>
+        <v>24.80576117</v>
       </c>
       <c r="H39" t="n">
-        <v>24.80576117</v>
+        <v>21.99748971</v>
       </c>
       <c r="I39" t="n">
-        <v>21.99748971</v>
+        <v>7.5667577</v>
       </c>
       <c r="J39" t="n">
-        <v>7.5667577</v>
+        <v>-0.39082327</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.39082327</v>
+        <v>6.9156605</v>
       </c>
       <c r="L39" t="n">
-        <v>6.9156605</v>
+        <v>-3.65105099</v>
       </c>
       <c r="M39" t="n">
-        <v>-3.65105099</v>
+        <v>5.96885178</v>
       </c>
     </row>
     <row r="40">
@@ -2065,37 +2071,37 @@
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>-39.94501549</v>
+        <v>-65.26585011</v>
       </c>
       <c r="D40" t="n">
-        <v>-65.26585011</v>
+        <v>-32.772473</v>
       </c>
       <c r="E40" t="n">
-        <v>-32.772473</v>
+        <v>-17.85393562</v>
       </c>
       <c r="F40" t="n">
-        <v>-17.85393562</v>
+        <v>-34.21927984000001</v>
       </c>
       <c r="G40" t="n">
-        <v>-34.21927984000001</v>
+        <v>-18.29832132</v>
       </c>
       <c r="H40" t="n">
-        <v>-18.29832132</v>
+        <v>16.51942199</v>
       </c>
       <c r="I40" t="n">
-        <v>16.51942199</v>
+        <v>-19.21069481</v>
       </c>
       <c r="J40" t="n">
-        <v>-19.21069481</v>
+        <v>-76.86549835</v>
       </c>
       <c r="K40" t="n">
-        <v>-76.86549835</v>
+        <v>-32.5970419</v>
       </c>
       <c r="L40" t="n">
-        <v>-32.5970419</v>
+        <v>-50.29811102</v>
       </c>
       <c r="M40" t="n">
-        <v>-50.29811102</v>
+        <v>-89.72822392</v>
       </c>
     </row>
     <row r="41">
@@ -2106,37 +2112,37 @@
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
-        <v>8.451e-05</v>
+        <v>9.454000000000001e-05</v>
       </c>
       <c r="D41" t="n">
-        <v>9.454000000000001e-05</v>
+        <v>-0.00014463</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.00014463</v>
+        <v>-7.391e-05</v>
       </c>
       <c r="F41" t="n">
-        <v>-7.391e-05</v>
+        <v>-2.001e-05</v>
       </c>
       <c r="G41" t="n">
-        <v>-2.001e-05</v>
+        <v>4.417e-05</v>
       </c>
       <c r="H41" t="n">
-        <v>4.417e-05</v>
+        <v>9.085e-05</v>
       </c>
       <c r="I41" t="n">
-        <v>9.085e-05</v>
+        <v>-7.104999999999999e-05</v>
       </c>
       <c r="J41" t="n">
-        <v>-7.104999999999999e-05</v>
+        <v>-0.00022371</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.00022371</v>
+        <v>-0.00012</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.00012</v>
+        <v>-0.00023445</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.00023445</v>
+        <v>-0.00035108</v>
       </c>
     </row>
     <row r="42">
@@ -2147,37 +2153,37 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>271.10624811</v>
+        <v>-68.75579565</v>
       </c>
       <c r="D42" t="n">
-        <v>-68.5816458</v>
+        <v>-25.65882652</v>
       </c>
       <c r="E42" t="n">
-        <v>-26.60399435</v>
+        <v>-203.34503687</v>
       </c>
       <c r="F42" t="n">
-        <v>-205.2773343</v>
+        <v>-26.00127152</v>
       </c>
       <c r="G42" t="n">
-        <v>-28.30046276</v>
+        <v>156.76665614</v>
       </c>
       <c r="H42" t="n">
-        <v>155.55902704</v>
+        <v>578.4989785</v>
       </c>
       <c r="I42" t="n">
-        <v>582.9563215699999</v>
+        <v>900.52032724</v>
       </c>
       <c r="J42" t="n">
-        <v>919.0814701600001</v>
+        <v>1153.82319753</v>
       </c>
       <c r="K42" t="n">
-        <v>1187.41765549</v>
+        <v>1252.18441714</v>
       </c>
       <c r="L42" t="n">
-        <v>1289.85564071</v>
+        <v>1286.18806609</v>
       </c>
       <c r="M42" t="n">
-        <v>1322.24512202</v>
+        <v>-596.5809266700001</v>
       </c>
     </row>
     <row r="43">
@@ -2188,37 +2194,37 @@
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
-        <v>0.19227776</v>
+        <v>1.46585581</v>
       </c>
       <c r="D43" t="n">
-        <v>1.29170596</v>
+        <v>1.15822565</v>
       </c>
       <c r="E43" t="n">
-        <v>2.10339348</v>
+        <v>-1.54501608</v>
       </c>
       <c r="F43" t="n">
-        <v>0.38728135</v>
+        <v>-2.785485910000001</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.48629467</v>
+        <v>-2.72785007</v>
       </c>
       <c r="H43" t="n">
-        <v>-1.52022097</v>
+        <v>3.65355746</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.80378561</v>
+        <v>20.8485932</v>
       </c>
       <c r="J43" t="n">
-        <v>2.28745028</v>
+        <v>34.26722984000001</v>
       </c>
       <c r="K43" t="n">
-        <v>0.67277188</v>
+        <v>38.60901432</v>
       </c>
       <c r="L43" t="n">
-        <v>0.93779075</v>
+        <v>37.64043757</v>
       </c>
       <c r="M43" t="n">
-        <v>1.58338164</v>
+        <v>12.03339149</v>
       </c>
     </row>
     <row r="44">
@@ -2229,37 +2235,37 @@
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>15.68920713</v>
+        <v>14.29967463</v>
       </c>
       <c r="D44" t="n">
-        <v>14.92937701</v>
+        <v>16.9019166</v>
       </c>
       <c r="E44" t="n">
-        <v>17.13186568</v>
+        <v>5.002261640000003</v>
       </c>
       <c r="F44" t="n">
-        <v>4.961326819999999</v>
+        <v>12.13699712</v>
       </c>
       <c r="G44" t="n">
-        <v>11.88330336</v>
+        <v>12.44531902</v>
       </c>
       <c r="H44" t="n">
-        <v>11.99597497</v>
+        <v>10.95086562</v>
       </c>
       <c r="I44" t="n">
-        <v>10.73997102</v>
+        <v>-8.826540080000003</v>
       </c>
       <c r="J44" t="n">
-        <v>-8.907961029999999</v>
+        <v>-21.12212905</v>
       </c>
       <c r="K44" t="n">
-        <v>-21.06636615</v>
+        <v>-25.33887335</v>
       </c>
       <c r="L44" t="n">
-        <v>-25.51100199</v>
+        <v>-20.50910314</v>
       </c>
       <c r="M44" t="n">
-        <v>-20.91638637</v>
+        <v>-9.32173066</v>
       </c>
     </row>
     <row r="45">
@@ -2272,37 +2278,37 @@
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>-60.83971186</v>
+        <v>11.07060200000001</v>
       </c>
       <c r="D45" t="n">
-        <v>7.91255782</v>
+        <v>34.26786155000001</v>
       </c>
       <c r="E45" t="n">
-        <v>27.53252192</v>
+        <v>122.41482328</v>
       </c>
       <c r="F45" t="n">
-        <v>114.64316707</v>
+        <v>263.12835826</v>
       </c>
       <c r="G45" t="n">
-        <v>263.10772292</v>
+        <v>96.53880563000003</v>
       </c>
       <c r="H45" t="n">
-        <v>100.07117049</v>
+        <v>183.63272959</v>
       </c>
       <c r="I45" t="n">
-        <v>184.39132701</v>
+        <v>198.4700732</v>
       </c>
       <c r="J45" t="n">
-        <v>200.1556611</v>
+        <v>293.16865939</v>
       </c>
       <c r="K45" t="n">
-        <v>282.17230585</v>
+        <v>426.18412531</v>
       </c>
       <c r="L45" t="n">
-        <v>413.65452745</v>
+        <v>555.23315785</v>
       </c>
       <c r="M45" t="n">
-        <v>542.3939973099999</v>
+        <v>773.5621615300001</v>
       </c>
     </row>
     <row r="46">
@@ -2313,37 +2319,37 @@
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>-36.90118062</v>
+        <v>90.33122224999998</v>
       </c>
       <c r="D46" t="n">
-        <v>92.74919083</v>
+        <v>-4.924683899999998</v>
       </c>
       <c r="E46" t="n">
-        <v>1.34486754000001</v>
+        <v>72.87505576999999</v>
       </c>
       <c r="F46" t="n">
-        <v>80.49257423999998</v>
+        <v>50.68055956999999</v>
       </c>
       <c r="G46" t="n">
-        <v>50.73410844999999</v>
+        <v>-59.63001799</v>
       </c>
       <c r="H46" t="n">
-        <v>-62.64354142</v>
+        <v>75.83161161</v>
       </c>
       <c r="I46" t="n">
-        <v>75.29830637000001</v>
+        <v>105.94402623</v>
       </c>
       <c r="J46" t="n">
-        <v>104.42617998</v>
+        <v>248.31095814</v>
       </c>
       <c r="K46" t="n">
-        <v>259.50226107</v>
+        <v>66.21656041</v>
       </c>
       <c r="L46" t="n">
-        <v>79.21859855</v>
+        <v>-62.84952854</v>
       </c>
       <c r="M46" t="n">
-        <v>-48.40696312000001</v>
+        <v>-147.24993142</v>
       </c>
     </row>
     <row r="47">
@@ -2354,37 +2360,37 @@
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>-5.50110454</v>
+        <v>-6.2041725</v>
       </c>
       <c r="D47" t="n">
-        <v>-6.2041725</v>
+        <v>-3.20158006</v>
       </c>
       <c r="E47" t="n">
-        <v>-3.20158006</v>
+        <v>1.12057703</v>
       </c>
       <c r="F47" t="n">
-        <v>1.12057703</v>
+        <v>-0.37868869</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.37868869</v>
+        <v>-3.99151647</v>
       </c>
       <c r="H47" t="n">
-        <v>-3.99151647</v>
+        <v>2.80991257</v>
       </c>
       <c r="I47" t="n">
-        <v>2.80991257</v>
+        <v>15.48498561</v>
       </c>
       <c r="J47" t="n">
-        <v>15.48498561</v>
+        <v>62.07577929</v>
       </c>
       <c r="K47" t="n">
-        <v>62.07577929</v>
+        <v>95.45228308</v>
       </c>
       <c r="L47" t="n">
-        <v>95.45228308</v>
+        <v>201.70015159</v>
       </c>
       <c r="M47" t="n">
-        <v>201.70015159</v>
+        <v>314.31583016</v>
       </c>
     </row>
     <row r="48">
@@ -2395,37 +2401,37 @@
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
-        <v>26.69719218</v>
+        <v>6.876008539999998</v>
       </c>
       <c r="D48" t="n">
-        <v>6.876008539999998</v>
+        <v>-21.01691342</v>
       </c>
       <c r="E48" t="n">
-        <v>-21.01691342</v>
+        <v>-15.13194856</v>
       </c>
       <c r="F48" t="n">
-        <v>-15.13194856</v>
+        <v>-100.97582182</v>
       </c>
       <c r="G48" t="n">
-        <v>-100.97582182</v>
+        <v>-162.47494265</v>
       </c>
       <c r="H48" t="n">
-        <v>-162.47494265</v>
+        <v>-138.91383049</v>
       </c>
       <c r="I48" t="n">
-        <v>-138.91383049</v>
+        <v>-65.78406750000001</v>
       </c>
       <c r="J48" t="n">
-        <v>-65.78406750000001</v>
+        <v>100.66741346</v>
       </c>
       <c r="K48" t="n">
-        <v>100.66741346</v>
+        <v>167.30680064</v>
       </c>
       <c r="L48" t="n">
-        <v>167.30680064</v>
+        <v>94.00985389</v>
       </c>
       <c r="M48" t="n">
-        <v>94.00985389</v>
+        <v>31.25882024</v>
       </c>
     </row>
     <row r="49">
@@ -2436,37 +2442,37 @@
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>1.65278435</v>
+        <v>1.32682909</v>
       </c>
       <c r="D49" t="n">
-        <v>1.32682909</v>
+        <v>0.25557084</v>
       </c>
       <c r="E49" t="n">
-        <v>0.25557084</v>
+        <v>-0.002220260000000012</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.002220260000000012</v>
+        <v>-0.21206577</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.21206577</v>
+        <v>-0.3229723599999999</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.3229723599999999</v>
+        <v>-0.64211001</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.64211001</v>
+        <v>-0.68773007</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.68773007</v>
+        <v>-0.8016744100000001</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.8016744100000001</v>
+        <v>-0.6050358499999999</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.6050358499999999</v>
+        <v>-0.16058108</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.16058108</v>
+        <v>-0.4915954</v>
       </c>
     </row>
     <row r="50">
@@ -2477,37 +2483,37 @@
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
-        <v>-116.33562401</v>
+        <v>-6.442285149999996</v>
       </c>
       <c r="D50" t="n">
-        <v>-6.691790779999997</v>
+        <v>-116.60320089</v>
       </c>
       <c r="E50" t="n">
-        <v>-115.82523807</v>
+        <v>51.08673258</v>
       </c>
       <c r="F50" t="n">
-        <v>53.49678095</v>
+        <v>-67.32971089999999</v>
       </c>
       <c r="G50" t="n">
-        <v>-66.54429746</v>
+        <v>-49.9699323</v>
       </c>
       <c r="H50" t="n">
-        <v>-48.69457564000001</v>
+        <v>-34.87113519</v>
       </c>
       <c r="I50" t="n">
-        <v>-31.82532077</v>
+        <v>-101.83529897</v>
       </c>
       <c r="J50" t="n">
-        <v>-102.22615871</v>
+        <v>-20.18952884999999</v>
       </c>
       <c r="K50" t="n">
-        <v>-21.90862964999999</v>
+        <v>60.03399915</v>
       </c>
       <c r="L50" t="n">
-        <v>59.43721305</v>
+        <v>46.57401195000001</v>
       </c>
       <c r="M50" t="n">
-        <v>46.93449081</v>
+        <v>94.33851032</v>
       </c>
     </row>
     <row r="51">
@@ -2516,41 +2522,39 @@
           <t>綠能環保右下</t>
         </is>
       </c>
-      <c r="B51" t="n">
-        <v>0</v>
-      </c>
+      <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>-2.5437199</v>
+        <v>4.03323023</v>
       </c>
       <c r="D51" t="n">
-        <v>4.033055200000001</v>
+        <v>-4.208008479999999</v>
       </c>
       <c r="E51" t="n">
-        <v>-4.20818115</v>
+        <v>-16.668004</v>
       </c>
       <c r="F51" t="n">
-        <v>-16.66827323</v>
+        <v>-17.31000216</v>
       </c>
       <c r="G51" t="n">
-        <v>-17.31015195</v>
+        <v>-27.00119206</v>
       </c>
       <c r="H51" t="n">
-        <v>-27.00139775</v>
+        <v>-37.85262138</v>
       </c>
       <c r="I51" t="n">
-        <v>-37.85275703</v>
+        <v>-40.22165305999999</v>
       </c>
       <c r="J51" t="n">
-        <v>-40.22167216</v>
+        <v>-40.80044587</v>
       </c>
       <c r="K51" t="n">
-        <v>-40.80030042</v>
+        <v>-105.72065853</v>
       </c>
       <c r="L51" t="n">
-        <v>-105.72039485</v>
+        <v>-88.20215075</v>
       </c>
       <c r="M51" t="n">
-        <v>-88.20195445</v>
+        <v>-78.58694362999999</v>
       </c>
     </row>
     <row r="52">
@@ -2561,37 +2565,37 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>0.99142799</v>
+        <v>23.55595313</v>
       </c>
       <c r="D52" t="n">
-        <v>23.8068687</v>
+        <v>23.24927058</v>
       </c>
       <c r="E52" t="n">
-        <v>22.08568782</v>
+        <v>10.98503399</v>
       </c>
       <c r="F52" t="n">
-        <v>7.470954930000001</v>
+        <v>14.36571771</v>
       </c>
       <c r="G52" t="n">
-        <v>11.96612713</v>
+        <v>-7.093245320000001</v>
       </c>
       <c r="H52" t="n">
-        <v>-8.497503110000002</v>
+        <v>3.776879930000002</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.7377022899999989</v>
+        <v>-0.599055200000002</v>
       </c>
       <c r="J52" t="n">
-        <v>1.139528689999999</v>
+        <v>-25.3277558</v>
       </c>
       <c r="K52" t="n">
-        <v>-21.90009003</v>
+        <v>-25.32132348</v>
       </c>
       <c r="L52" t="n">
-        <v>-24.02962719</v>
+        <v>-2.890964619999999</v>
       </c>
       <c r="M52" t="n">
-        <v>-4.317856819999998</v>
+        <v>-8.700042229999999</v>
       </c>
     </row>
     <row r="53">
@@ -2602,37 +2606,37 @@
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>142.87783066</v>
+        <v>734.9058153899999</v>
       </c>
       <c r="D53" t="n">
-        <v>508.6557417999999</v>
+        <v>788.96935349</v>
       </c>
       <c r="E53" t="n">
-        <v>566.7019476200001</v>
+        <v>202.71825148</v>
       </c>
       <c r="F53" t="n">
-        <v>-209.21155652</v>
+        <v>185.63987332</v>
       </c>
       <c r="G53" t="n">
-        <v>2.472013799999998</v>
+        <v>413.37287971</v>
       </c>
       <c r="H53" t="n">
-        <v>181.3128095</v>
+        <v>382.52006728</v>
       </c>
       <c r="I53" t="n">
-        <v>409.82417843</v>
+        <v>788.81984295</v>
       </c>
       <c r="J53" t="n">
-        <v>679.7734486099999</v>
+        <v>536.01880756</v>
       </c>
       <c r="K53" t="n">
-        <v>585.0456973400001</v>
+        <v>663.41942352</v>
       </c>
       <c r="L53" t="n">
-        <v>589.5573766699999</v>
+        <v>832.86466129</v>
       </c>
       <c r="M53" t="n">
-        <v>716.6848599800001</v>
+        <v>148.04517125</v>
       </c>
     </row>
     <row r="54">
@@ -2643,37 +2647,37 @@
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>12.23336543</v>
+        <v>5.94735249</v>
       </c>
       <c r="D54" t="n">
-        <v>7.459217189999999</v>
+        <v>23.83820258</v>
       </c>
       <c r="E54" t="n">
-        <v>20.46282913</v>
+        <v>29.98847398</v>
       </c>
       <c r="F54" t="n">
-        <v>34.59465452000001</v>
+        <v>32.85000479</v>
       </c>
       <c r="G54" t="n">
-        <v>30.05918976</v>
+        <v>27.25000905</v>
       </c>
       <c r="H54" t="n">
-        <v>15.45659664</v>
+        <v>58.22860823000001</v>
       </c>
       <c r="I54" t="n">
-        <v>22.21853231</v>
+        <v>28.42361836</v>
       </c>
       <c r="J54" t="n">
-        <v>15.38179527</v>
+        <v>27.12037651</v>
       </c>
       <c r="K54" t="n">
-        <v>9.58508578</v>
+        <v>4.33543982</v>
       </c>
       <c r="L54" t="n">
-        <v>0.4767019700000001</v>
+        <v>4.657683560000001</v>
       </c>
       <c r="M54" t="n">
-        <v>13.22037048</v>
+        <v>-6.665553060000001</v>
       </c>
     </row>
     <row r="55">
@@ -2684,37 +2688,37 @@
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>117.72272026</v>
+        <v>-87.59608303</v>
       </c>
       <c r="D55" t="n">
-        <v>137.14212586</v>
+        <v>20.29703956999999</v>
       </c>
       <c r="E55" t="n">
-        <v>245.93981889</v>
+        <v>-345.84892177</v>
       </c>
       <c r="F55" t="n">
-        <v>61.47470569</v>
+        <v>231.55420764</v>
       </c>
       <c r="G55" t="n">
-        <v>417.51288219</v>
+        <v>91.16828621000002</v>
       </c>
       <c r="H55" t="n">
-        <v>335.02176883</v>
+        <v>318.79573829</v>
       </c>
       <c r="I55" t="n">
-        <v>327.50170306</v>
+        <v>-73.07478899999998</v>
       </c>
       <c r="J55" t="n">
-        <v>49.01342843</v>
+        <v>55.56343482</v>
       </c>
       <c r="K55" t="n">
-        <v>24.07183576999999</v>
+        <v>-138.18657417</v>
       </c>
       <c r="L55" t="n">
-        <v>-60.46578947</v>
+        <v>0.1445773399999785</v>
       </c>
       <c r="M55" t="n">
-        <v>107.76169173</v>
+        <v>-394.95349135</v>
       </c>
     </row>
     <row r="56">
@@ -2725,37 +2729,37 @@
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>-7.278711120000001</v>
+        <v>-1.98122254</v>
       </c>
       <c r="D56" t="n">
-        <v>-1.98096138</v>
+        <v>-4.11657528</v>
       </c>
       <c r="E56" t="n">
-        <v>-4.11638705</v>
+        <v>4.080833070000001</v>
       </c>
       <c r="F56" t="n">
-        <v>4.08089557</v>
+        <v>-0.1995308</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.1995485</v>
+        <v>-12.28246568</v>
       </c>
       <c r="H56" t="n">
-        <v>-12.28237295</v>
+        <v>-2.91485353</v>
       </c>
       <c r="I56" t="n">
-        <v>-2.91487422</v>
+        <v>20.80537979</v>
       </c>
       <c r="J56" t="n">
-        <v>20.8052581</v>
+        <v>4.328907650000001</v>
       </c>
       <c r="K56" t="n">
-        <v>4.32875445</v>
+        <v>9.664171169999998</v>
       </c>
       <c r="L56" t="n">
-        <v>9.664215899999999</v>
+        <v>19.08999414</v>
       </c>
       <c r="M56" t="n">
-        <v>19.0901028</v>
+        <v>26.43894332</v>
       </c>
     </row>
     <row r="57">
@@ -2766,37 +2770,37 @@
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
-        <v>24.12932168</v>
+        <v>19.63287374</v>
       </c>
       <c r="D57" t="n">
-        <v>19.6332461</v>
+        <v>9.521552719999999</v>
       </c>
       <c r="E57" t="n">
-        <v>9.52188091</v>
+        <v>-6.49062084</v>
       </c>
       <c r="F57" t="n">
-        <v>-6.490226310000001</v>
+        <v>-19.63753738</v>
       </c>
       <c r="G57" t="n">
-        <v>-19.63733982</v>
+        <v>-31.28690505</v>
       </c>
       <c r="H57" t="n">
-        <v>-31.28678731</v>
+        <v>-35.82237618</v>
       </c>
       <c r="I57" t="n">
-        <v>-35.8224009</v>
+        <v>-48.83650657</v>
       </c>
       <c r="J57" t="n">
-        <v>-48.83657307</v>
+        <v>-2.96101949</v>
       </c>
       <c r="K57" t="n">
-        <v>-2.96100229</v>
+        <v>-4.13299422</v>
       </c>
       <c r="L57" t="n">
-        <v>-4.13295156</v>
+        <v>-6.761116970000001</v>
       </c>
       <c r="M57" t="n">
-        <v>-6.76115287</v>
+        <v>-11.20179401</v>
       </c>
     </row>
     <row r="58">
@@ -2807,119 +2811,119 @@
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>34.83619801</v>
+        <v>44.05441974</v>
       </c>
       <c r="D58" t="n">
-        <v>44.05377982</v>
+        <v>45.77383525</v>
       </c>
       <c r="E58" t="n">
-        <v>45.77332355000001</v>
+        <v>20.38814153</v>
       </c>
       <c r="F58" t="n">
-        <v>20.38771257</v>
+        <v>-9.582989280000001</v>
       </c>
       <c r="G58" t="n">
-        <v>-9.583194499999999</v>
+        <v>-17.24540474</v>
       </c>
       <c r="H58" t="n">
-        <v>-17.24568169</v>
+        <v>-34.9488085</v>
       </c>
       <c r="I58" t="n">
-        <v>-34.94886270000001</v>
+        <v>-42.18683129</v>
       </c>
       <c r="J58" t="n">
-        <v>-42.1867673</v>
+        <v>-0.99594301</v>
       </c>
       <c r="K58" t="n">
-        <v>-0.99581925</v>
+        <v>-6.33405912</v>
       </c>
       <c r="L58" t="n">
-        <v>-6.33419032</v>
+        <v>8.217235840000001</v>
       </c>
       <c r="M58" t="n">
-        <v>8.21714162</v>
+        <v>3.55951186</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨右下</t>
+          <t>貿易百貨右上</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
-        <v>42.54732838</v>
+        <v>-0.00537507</v>
       </c>
       <c r="D59" t="n">
-        <v>65.16556917</v>
+        <v>-0.02343861</v>
       </c>
       <c r="E59" t="n">
-        <v>39.0396422</v>
+        <v>0.03144128</v>
       </c>
       <c r="F59" t="n">
-        <v>50.5705571</v>
+        <v>0.01201424</v>
       </c>
       <c r="G59" t="n">
-        <v>29.48116599</v>
+        <v>0.04099756</v>
       </c>
       <c r="H59" t="n">
-        <v>3.745202050000001</v>
+        <v>0.02809802</v>
       </c>
       <c r="I59" t="n">
-        <v>-27.11462849</v>
+        <v>0.04076989</v>
       </c>
       <c r="J59" t="n">
-        <v>-14.54311404</v>
+        <v>-0.02230235</v>
       </c>
       <c r="K59" t="n">
-        <v>-20.20816677</v>
+        <v>0.0121624</v>
       </c>
       <c r="L59" t="n">
-        <v>-48.84269329</v>
+        <v>-0.02442989</v>
       </c>
       <c r="M59" t="n">
-        <v>-21.3959596</v>
+        <v>0.09452125</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨平</t>
+          <t>貿易百貨右下</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
-        <v>0.02929013</v>
+        <v>65.17785349</v>
       </c>
       <c r="D60" t="n">
-        <v>0.00690925</v>
+        <v>39.06068539</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.002395420000000002</v>
+        <v>50.62813032</v>
       </c>
       <c r="F60" t="n">
-        <v>0.0890145</v>
+        <v>29.49595222</v>
       </c>
       <c r="G60" t="n">
-        <v>0.02680047</v>
+        <v>3.736675960000001</v>
       </c>
       <c r="H60" t="n">
-        <v>0.03247147</v>
+        <v>-27.10836733</v>
       </c>
       <c r="I60" t="n">
-        <v>0.03435918</v>
+        <v>-14.55097783</v>
       </c>
       <c r="J60" t="n">
-        <v>0.0329061</v>
+        <v>-20.19341195</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.007547529999999998</v>
+        <v>-48.79022895</v>
       </c>
       <c r="L60" t="n">
-        <v>0.06462674</v>
+        <v>-21.4031845</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.03165479</v>
+        <v>-29.01154994</v>
       </c>
     </row>
     <row r="61">
@@ -2930,37 +2934,37 @@
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
-        <v>65.72478599999999</v>
+        <v>95.20197021</v>
       </c>
       <c r="D61" t="n">
-        <v>94.84815691</v>
+        <v>52.08621262</v>
       </c>
       <c r="E61" t="n">
-        <v>51.98647528</v>
+        <v>56.2651317</v>
       </c>
       <c r="F61" t="n">
-        <v>56.01972017</v>
+        <v>4.496420459999995</v>
       </c>
       <c r="G61" t="n">
-        <v>4.570142489999996</v>
+        <v>16.52153666</v>
       </c>
       <c r="H61" t="n">
-        <v>16.01686962</v>
+        <v>67.26849343000001</v>
       </c>
       <c r="I61" t="n">
-        <v>67.11095942</v>
+        <v>-16.93341359</v>
       </c>
       <c r="J61" t="n">
-        <v>-17.12267397</v>
+        <v>-37.98556158</v>
       </c>
       <c r="K61" t="n">
-        <v>-37.94971968</v>
+        <v>-34.65841320000001</v>
       </c>
       <c r="L61" t="n">
-        <v>-34.75882616</v>
+        <v>-52.24856203</v>
       </c>
       <c r="M61" t="n">
-        <v>-52.83354714</v>
+        <v>-39.37859758</v>
       </c>
     </row>
     <row r="62">
@@ -2971,37 +2975,37 @@
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>6.52392742</v>
+        <v>0.0072971</v>
       </c>
       <c r="D62" t="n">
-        <v>6.715422149999999</v>
+        <v>0.005237070000000001</v>
       </c>
       <c r="E62" t="n">
-        <v>5.812983760000001</v>
+        <v>0.00104507</v>
       </c>
       <c r="F62" t="n">
-        <v>3.00061214</v>
+        <v>0.00898524</v>
       </c>
       <c r="G62" t="n">
-        <v>-6.38541483</v>
+        <v>0.01629072</v>
       </c>
       <c r="H62" t="n">
-        <v>-9.712041819999998</v>
+        <v>0.02050236</v>
       </c>
       <c r="I62" t="n">
-        <v>-5.19174317</v>
+        <v>0.02262908</v>
       </c>
       <c r="J62" t="n">
-        <v>-4.46376258</v>
+        <v>0.01813206</v>
       </c>
       <c r="K62" t="n">
-        <v>-3.86283365</v>
+        <v>0.01316176</v>
       </c>
       <c r="L62" t="n">
-        <v>-4.498926060000001</v>
+        <v>-0.0002601800000000002</v>
       </c>
       <c r="M62" t="n">
-        <v>-1.64025771</v>
+        <v>-0.00714299</v>
       </c>
     </row>
     <row r="63">
@@ -3012,37 +3016,37 @@
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>41.13984781</v>
+        <v>94.86343511</v>
       </c>
       <c r="D63" t="n">
-        <v>88.15517082</v>
+        <v>46.74770855</v>
       </c>
       <c r="E63" t="n">
-        <v>40.93981619</v>
+        <v>41.24763927</v>
       </c>
       <c r="F63" t="n">
-        <v>38.2480204</v>
+        <v>17.01477717</v>
       </c>
       <c r="G63" t="n">
-        <v>23.40917579</v>
+        <v>18.43927654</v>
       </c>
       <c r="H63" t="n">
-        <v>28.16733624</v>
+        <v>30.16554393</v>
       </c>
       <c r="I63" t="n">
-        <v>35.37618777</v>
+        <v>29.38655623</v>
       </c>
       <c r="J63" t="n">
-        <v>33.86892229</v>
+        <v>-1.379161980000001</v>
       </c>
       <c r="K63" t="n">
-        <v>2.500389020000001</v>
+        <v>-22.59602675</v>
       </c>
       <c r="L63" t="n">
-        <v>-18.08390008</v>
+        <v>-17.54911508</v>
       </c>
       <c r="M63" t="n">
-        <v>-15.90958686</v>
+        <v>-29.10383618</v>
       </c>
     </row>
     <row r="64">
@@ -3053,37 +3057,37 @@
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
-        <v>0.0009914099999999999</v>
+        <v>6.247e-05</v>
       </c>
       <c r="D64" t="n">
-        <v>6.247e-05</v>
+        <v>0.0004044</v>
       </c>
       <c r="E64" t="n">
-        <v>0.0004044</v>
+        <v>0.00072251</v>
       </c>
       <c r="F64" t="n">
-        <v>0.00072251</v>
+        <v>-0.00025412</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.00025412</v>
+        <v>-0.00126824</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.00126824</v>
+        <v>-0.00052996</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.00052996</v>
+        <v>-4.627e-05</v>
       </c>
       <c r="J64" t="n">
-        <v>-4.627e-05</v>
+        <v>0.00012135</v>
       </c>
       <c r="K64" t="n">
-        <v>0.00012135</v>
+        <v>0.00033795</v>
       </c>
       <c r="L64" t="n">
-        <v>0.00033795</v>
+        <v>0.0007966399999999999</v>
       </c>
       <c r="M64" t="n">
-        <v>0.0007966399999999999</v>
+        <v>0.00094526</v>
       </c>
     </row>
     <row r="65">
@@ -3094,37 +3098,37 @@
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
-        <v>5.814e-05</v>
+        <v>0.00018835</v>
       </c>
       <c r="D65" t="n">
-        <v>0.00018835</v>
+        <v>2.243e-05</v>
       </c>
       <c r="E65" t="n">
-        <v>2.243e-05</v>
+        <v>-8.019e-05</v>
       </c>
       <c r="F65" t="n">
-        <v>-8.019e-05</v>
+        <v>-3.720999999999999e-05</v>
       </c>
       <c r="G65" t="n">
-        <v>-3.720999999999999e-05</v>
+        <v>-0.00012853</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.00012853</v>
+        <v>-0.00011783</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.00011783</v>
+        <v>-0.00038662</v>
       </c>
       <c r="J65" t="n">
-        <v>-0.00038662</v>
+        <v>-0.00020338</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.00020338</v>
+        <v>2.062999999999999e-05</v>
       </c>
       <c r="L65" t="n">
-        <v>2.062999999999999e-05</v>
+        <v>7.988999999999998e-05</v>
       </c>
       <c r="M65" t="n">
-        <v>7.988999999999998e-05</v>
+        <v>-3.629999999999995e-06</v>
       </c>
     </row>
     <row r="66">
@@ -3135,37 +3139,37 @@
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>211.45186433</v>
+        <v>726.58418074</v>
       </c>
       <c r="D66" t="n">
-        <v>743.00310366</v>
+        <v>219.22811038</v>
       </c>
       <c r="E66" t="n">
-        <v>222.93098923</v>
+        <v>553.06950304</v>
       </c>
       <c r="F66" t="n">
-        <v>590.68221964</v>
+        <v>726.4882705900001</v>
       </c>
       <c r="G66" t="n">
-        <v>737.59955096</v>
+        <v>921.94961616</v>
       </c>
       <c r="H66" t="n">
-        <v>898.0649092000001</v>
+        <v>1026.06143639</v>
       </c>
       <c r="I66" t="n">
-        <v>967.1187534999999</v>
+        <v>1122.80221939</v>
       </c>
       <c r="J66" t="n">
-        <v>1194.77040763</v>
+        <v>1091.18890072</v>
       </c>
       <c r="K66" t="n">
-        <v>1051.66219636</v>
+        <v>1194.06178914</v>
       </c>
       <c r="L66" t="n">
-        <v>1086.08204445</v>
+        <v>1751.61038935</v>
       </c>
       <c r="M66" t="n">
-        <v>1610.76237197</v>
+        <v>599.6731381000001</v>
       </c>
     </row>
     <row r="67">
@@ -3174,39 +3178,41 @@
           <t>通信網路業右下</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr"/>
+      <c r="B67" t="n">
+        <v>0</v>
+      </c>
       <c r="C67" t="n">
-        <v>3.661172020000002</v>
+        <v>43.54210218</v>
       </c>
       <c r="D67" t="n">
-        <v>43.03769867</v>
+        <v>-32.81636228</v>
       </c>
       <c r="E67" t="n">
-        <v>-32.84988569</v>
+        <v>-43.90206674</v>
       </c>
       <c r="F67" t="n">
-        <v>-44.98339458</v>
+        <v>-50.52353451</v>
       </c>
       <c r="G67" t="n">
-        <v>-50.19198401999999</v>
+        <v>-59.86684214</v>
       </c>
       <c r="H67" t="n">
-        <v>-61.96146647</v>
+        <v>-32.44140473</v>
       </c>
       <c r="I67" t="n">
-        <v>-32.79786634</v>
+        <v>-13.85306951</v>
       </c>
       <c r="J67" t="n">
-        <v>-12.77004483</v>
+        <v>-12.01927122</v>
       </c>
       <c r="K67" t="n">
-        <v>-10.69580253</v>
+        <v>-10.69279784</v>
       </c>
       <c r="L67" t="n">
-        <v>-9.02277816</v>
+        <v>16.19583004</v>
       </c>
       <c r="M67" t="n">
-        <v>18.34720585</v>
+        <v>16.22284164</v>
       </c>
     </row>
     <row r="68">
@@ -3217,37 +3223,37 @@
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>128.59152705</v>
+        <v>103.49582804</v>
       </c>
       <c r="D68" t="n">
-        <v>87.07690512000001</v>
+        <v>140.58514141</v>
       </c>
       <c r="E68" t="n">
-        <v>136.88226256</v>
+        <v>-52.00069714999999</v>
       </c>
       <c r="F68" t="n">
-        <v>-89.61341375000001</v>
+        <v>-106.96026633</v>
       </c>
       <c r="G68" t="n">
-        <v>-118.0715467</v>
+        <v>-89.75740950999999</v>
       </c>
       <c r="H68" t="n">
-        <v>-65.87270255</v>
+        <v>27.1313866</v>
       </c>
       <c r="I68" t="n">
-        <v>86.07406949000001</v>
+        <v>-59.22676548</v>
       </c>
       <c r="J68" t="n">
-        <v>-131.19495372</v>
+        <v>25.81702806</v>
       </c>
       <c r="K68" t="n">
-        <v>65.34373241999999</v>
+        <v>-9.425721389999991</v>
       </c>
       <c r="L68" t="n">
-        <v>98.55402330000001</v>
+        <v>34.50571488999998</v>
       </c>
       <c r="M68" t="n">
-        <v>175.35373227</v>
+        <v>-44.29452930000001</v>
       </c>
     </row>
     <row r="69">
@@ -3258,37 +3264,37 @@
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>-14.45543988</v>
+        <v>-8.60103045</v>
       </c>
       <c r="D69" t="n">
-        <v>-8.60103045</v>
+        <v>1.481096</v>
       </c>
       <c r="E69" t="n">
-        <v>1.481096</v>
+        <v>-2.09694106</v>
       </c>
       <c r="F69" t="n">
-        <v>-2.09694106</v>
+        <v>-1.18870531</v>
       </c>
       <c r="G69" t="n">
-        <v>-1.18870531</v>
+        <v>0.8999840899999999</v>
       </c>
       <c r="H69" t="n">
-        <v>0.8999840899999999</v>
+        <v>-1.07992369</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.07992369</v>
+        <v>-8.13542947</v>
       </c>
       <c r="J69" t="n">
-        <v>-8.13542947</v>
+        <v>-6.112742610000001</v>
       </c>
       <c r="K69" t="n">
-        <v>-6.112742610000001</v>
+        <v>0.62737845</v>
       </c>
       <c r="L69" t="n">
-        <v>0.62737845</v>
+        <v>-1.39124728</v>
       </c>
       <c r="M69" t="n">
-        <v>-1.39124728</v>
+        <v>-3.48094111</v>
       </c>
     </row>
     <row r="70">
@@ -3299,37 +3305,37 @@
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>-1.16033294</v>
+        <v>-1.55525517</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.55525517</v>
+        <v>0.15859867</v>
       </c>
       <c r="E70" t="n">
-        <v>0.15859867</v>
+        <v>-0.01651628</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.01651628</v>
+        <v>0.93115824</v>
       </c>
       <c r="G70" t="n">
-        <v>0.93115824</v>
+        <v>0.15324129</v>
       </c>
       <c r="H70" t="n">
-        <v>0.15324129</v>
+        <v>2.0141396</v>
       </c>
       <c r="I70" t="n">
-        <v>2.0141396</v>
+        <v>0.94456732</v>
       </c>
       <c r="J70" t="n">
-        <v>0.94456732</v>
+        <v>1.31059385</v>
       </c>
       <c r="K70" t="n">
-        <v>1.31059385</v>
+        <v>0.44808132</v>
       </c>
       <c r="L70" t="n">
-        <v>0.44808132</v>
+        <v>1.02481299</v>
       </c>
       <c r="M70" t="n">
-        <v>1.02481299</v>
+        <v>0.39879786</v>
       </c>
     </row>
     <row r="71">
@@ -3340,37 +3346,37 @@
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
-        <v>22.89727625</v>
+        <v>39.58487804</v>
       </c>
       <c r="D71" t="n">
-        <v>39.58487804</v>
+        <v>49.03197814</v>
       </c>
       <c r="E71" t="n">
-        <v>49.03197814</v>
+        <v>20.29127258</v>
       </c>
       <c r="F71" t="n">
-        <v>20.29127258</v>
+        <v>24.00895878</v>
       </c>
       <c r="G71" t="n">
-        <v>24.00895878</v>
+        <v>34.17125779</v>
       </c>
       <c r="H71" t="n">
-        <v>34.17125779</v>
+        <v>-3.0706811</v>
       </c>
       <c r="I71" t="n">
-        <v>-3.0706811</v>
+        <v>-7.127004649999999</v>
       </c>
       <c r="J71" t="n">
-        <v>-7.127004649999999</v>
+        <v>-16.45539349</v>
       </c>
       <c r="K71" t="n">
-        <v>-16.45539349</v>
+        <v>-1.46575611</v>
       </c>
       <c r="L71" t="n">
-        <v>-1.46575611</v>
+        <v>-28.70342079</v>
       </c>
       <c r="M71" t="n">
-        <v>-28.70342079</v>
+        <v>-30.10771701</v>
       </c>
     </row>
     <row r="72">
@@ -3381,37 +3387,37 @@
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>-29.97898556</v>
+        <v>-17.14059748</v>
       </c>
       <c r="D72" t="n">
-        <v>-20.96570658</v>
+        <v>-81.91163204999999</v>
       </c>
       <c r="E72" t="n">
-        <v>-82.82987403</v>
+        <v>-115.31227011</v>
       </c>
       <c r="F72" t="n">
-        <v>-117.56860161</v>
+        <v>-37.30362026</v>
       </c>
       <c r="G72" t="n">
-        <v>-41.76354069999999</v>
+        <v>-103.56392674</v>
       </c>
       <c r="H72" t="n">
-        <v>-96.87037564000001</v>
+        <v>-54.40137722999999</v>
       </c>
       <c r="I72" t="n">
-        <v>-62.8772119</v>
+        <v>-0.9121308300000042</v>
       </c>
       <c r="J72" t="n">
-        <v>-12.82282402</v>
+        <v>111.99430636</v>
       </c>
       <c r="K72" t="n">
-        <v>98.85202981</v>
+        <v>111.66897061</v>
       </c>
       <c r="L72" t="n">
-        <v>106.34325255</v>
+        <v>-3.999667890000003</v>
       </c>
       <c r="M72" t="n">
-        <v>-1.836550060000001</v>
+        <v>-119.43980218</v>
       </c>
     </row>
     <row r="73">
@@ -3422,37 +3428,37 @@
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
-        <v>13.19129905</v>
+        <v>1.31760602</v>
       </c>
       <c r="D73" t="n">
-        <v>5.14271512</v>
+        <v>-9.691171220000001</v>
       </c>
       <c r="E73" t="n">
-        <v>-8.77292924</v>
+        <v>-11.21701609</v>
       </c>
       <c r="F73" t="n">
-        <v>-8.96068459</v>
+        <v>-24.50112135</v>
       </c>
       <c r="G73" t="n">
-        <v>-20.04120091</v>
+        <v>-23.85631305</v>
       </c>
       <c r="H73" t="n">
-        <v>-30.54986415</v>
+        <v>-23.78075616</v>
       </c>
       <c r="I73" t="n">
-        <v>-15.30492149</v>
+        <v>-20.79905364</v>
       </c>
       <c r="J73" t="n">
-        <v>-8.88836045</v>
+        <v>7.640183769999999</v>
       </c>
       <c r="K73" t="n">
-        <v>20.78246032</v>
+        <v>-8.013334910000001</v>
       </c>
       <c r="L73" t="n">
-        <v>-2.68761685</v>
+        <v>-21.10458214000001</v>
       </c>
       <c r="M73" t="n">
-        <v>-23.26769997</v>
+        <v>-30.02046044</v>
       </c>
     </row>
     <row r="74">
@@ -3463,37 +3469,37 @@
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
-        <v>974.9973069000001</v>
+        <v>894.0164181600001</v>
       </c>
       <c r="D74" t="n">
-        <v>894.0164181600001</v>
+        <v>1276.00511831</v>
       </c>
       <c r="E74" t="n">
-        <v>1276.00511831</v>
+        <v>884.3679413999999</v>
       </c>
       <c r="F74" t="n">
-        <v>884.3679413999999</v>
+        <v>711.53754654</v>
       </c>
       <c r="G74" t="n">
-        <v>711.53754654</v>
+        <v>678.83419911</v>
       </c>
       <c r="H74" t="n">
-        <v>678.83419911</v>
+        <v>674.51015137</v>
       </c>
       <c r="I74" t="n">
-        <v>674.51015137</v>
+        <v>926.41732815</v>
       </c>
       <c r="J74" t="n">
-        <v>926.41732815</v>
+        <v>1369.02894179</v>
       </c>
       <c r="K74" t="n">
-        <v>1369.02894179</v>
+        <v>463.72510052</v>
       </c>
       <c r="L74" t="n">
-        <v>463.72510052</v>
+        <v>314.75285627</v>
       </c>
       <c r="M74" t="n">
-        <v>314.75285627</v>
+        <v>-267.78573693</v>
       </c>
     </row>
     <row r="75">
@@ -3504,37 +3510,37 @@
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
-        <v>-118.64327508</v>
+        <v>72.75089683</v>
       </c>
       <c r="D75" t="n">
-        <v>74.35517131</v>
+        <v>167.55188173</v>
       </c>
       <c r="E75" t="n">
-        <v>170.94813623</v>
+        <v>-31.46257298</v>
       </c>
       <c r="F75" t="n">
-        <v>-29.13507418</v>
+        <v>-219.97600686</v>
       </c>
       <c r="G75" t="n">
-        <v>-219.04003565</v>
+        <v>-384.3325941999999</v>
       </c>
       <c r="H75" t="n">
-        <v>-381.90045693</v>
+        <v>-513.9571076200001</v>
       </c>
       <c r="I75" t="n">
-        <v>-512.67950204</v>
+        <v>-257.99615698</v>
       </c>
       <c r="J75" t="n">
-        <v>-257.43105527</v>
+        <v>-17.04792302</v>
       </c>
       <c r="K75" t="n">
-        <v>-15.00335476</v>
+        <v>-66.68232792000001</v>
       </c>
       <c r="L75" t="n">
-        <v>-65.23920036</v>
+        <v>39.88375886</v>
       </c>
       <c r="M75" t="n">
-        <v>40.41807481999999</v>
+        <v>5.240855929999999</v>
       </c>
     </row>
     <row r="76">
@@ -3545,37 +3551,37 @@
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>91.30190863</v>
+        <v>2.117843309999998</v>
       </c>
       <c r="D76" t="n">
-        <v>0.5135688299999975</v>
+        <v>-1.871264110000001</v>
       </c>
       <c r="E76" t="n">
-        <v>-5.267518610000002</v>
+        <v>-27.58568966</v>
       </c>
       <c r="F76" t="n">
-        <v>-29.91318846</v>
+        <v>10.96223872</v>
       </c>
       <c r="G76" t="n">
-        <v>10.02626751</v>
+        <v>47.73662943</v>
       </c>
       <c r="H76" t="n">
-        <v>45.30449216</v>
+        <v>37.80555489</v>
       </c>
       <c r="I76" t="n">
-        <v>36.52794931</v>
+        <v>60.24445445000001</v>
       </c>
       <c r="J76" t="n">
-        <v>59.67935274</v>
+        <v>75.68165750999999</v>
       </c>
       <c r="K76" t="n">
-        <v>73.63708925</v>
+        <v>33.39518098</v>
       </c>
       <c r="L76" t="n">
-        <v>31.95205342</v>
+        <v>13.29797587</v>
       </c>
       <c r="M76" t="n">
-        <v>12.76365991</v>
+        <v>-21.45733517</v>
       </c>
     </row>
     <row r="77">
@@ -3586,37 +3592,37 @@
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="n">
-        <v>-0.00042214</v>
+        <v>0.00035191</v>
       </c>
       <c r="D77" t="n">
-        <v>0.00035191</v>
+        <v>0.0006016</v>
       </c>
       <c r="E77" t="n">
-        <v>0.0006016</v>
+        <v>0.00119589</v>
       </c>
       <c r="F77" t="n">
-        <v>0.00119589</v>
+        <v>0.00222055</v>
       </c>
       <c r="G77" t="n">
-        <v>0.00222055</v>
+        <v>0.00226234</v>
       </c>
       <c r="H77" t="n">
-        <v>0.00226234</v>
+        <v>0.00101082</v>
       </c>
       <c r="I77" t="n">
-        <v>0.00101082</v>
+        <v>9.988e-05</v>
       </c>
       <c r="J77" t="n">
-        <v>9.988e-05</v>
+        <v>0.00032912</v>
       </c>
       <c r="K77" t="n">
-        <v>0.00032912</v>
+        <v>-0.00052438</v>
       </c>
       <c r="L77" t="n">
-        <v>-0.00052438</v>
+        <v>-9.99e-05</v>
       </c>
       <c r="M77" t="n">
-        <v>-9.99e-05</v>
+        <v>-0.00069427</v>
       </c>
     </row>
     <row r="78">
@@ -3627,37 +3633,37 @@
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
-        <v>-0.006376339999999999</v>
+        <v>-0.00146164</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.00146164</v>
+        <v>0.0001785999999999999</v>
       </c>
       <c r="E78" t="n">
-        <v>0.0001785999999999999</v>
+        <v>0.00166505</v>
       </c>
       <c r="F78" t="n">
-        <v>0.00166505</v>
+        <v>0.00481058</v>
       </c>
       <c r="G78" t="n">
-        <v>0.00481058</v>
+        <v>0.00272902</v>
       </c>
       <c r="H78" t="n">
-        <v>0.00272902</v>
+        <v>9.011000000000007e-05</v>
       </c>
       <c r="I78" t="n">
-        <v>9.011000000000007e-05</v>
+        <v>0.0004795100000000002</v>
       </c>
       <c r="J78" t="n">
-        <v>0.0004795100000000002</v>
+        <v>0.00329986</v>
       </c>
       <c r="K78" t="n">
-        <v>0.00329986</v>
+        <v>0.0005099499999999999</v>
       </c>
       <c r="L78" t="n">
-        <v>0.0005099499999999999</v>
+        <v>-0.0007658099999999999</v>
       </c>
       <c r="M78" t="n">
-        <v>-0.0007658099999999999</v>
+        <v>0.0034501</v>
       </c>
     </row>
     <row r="79">
@@ -3668,37 +3674,37 @@
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="n">
-        <v>-0.00010349</v>
+        <v>0.00149008</v>
       </c>
       <c r="D79" t="n">
-        <v>0.00149008</v>
+        <v>0.00167124</v>
       </c>
       <c r="E79" t="n">
-        <v>0.00167124</v>
+        <v>0.00103193</v>
       </c>
       <c r="F79" t="n">
-        <v>0.00103193</v>
+        <v>0.00057835</v>
       </c>
       <c r="G79" t="n">
-        <v>0.00057835</v>
+        <v>9.465e-05</v>
       </c>
       <c r="H79" t="n">
-        <v>9.465e-05</v>
+        <v>0.00013897</v>
       </c>
       <c r="I79" t="n">
-        <v>0.00013897</v>
+        <v>6.415e-05</v>
       </c>
       <c r="J79" t="n">
-        <v>6.415e-05</v>
+        <v>-0.00029419</v>
       </c>
       <c r="K79" t="n">
-        <v>-0.00029419</v>
+        <v>0.00019073</v>
       </c>
       <c r="L79" t="n">
-        <v>0.00019073</v>
+        <v>-2.111999999999998e-05</v>
       </c>
       <c r="M79" t="n">
-        <v>-2.111999999999998e-05</v>
+        <v>0.00040195</v>
       </c>
     </row>
     <row r="80">
@@ -3709,37 +3715,37 @@
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="n">
-        <v>-4.332121809999999</v>
+        <v>-10.26026165</v>
       </c>
       <c r="D80" t="n">
-        <v>-10.26026165</v>
+        <v>8.420322020000002</v>
       </c>
       <c r="E80" t="n">
-        <v>8.420322020000002</v>
+        <v>-10.13479723</v>
       </c>
       <c r="F80" t="n">
-        <v>-10.13479723</v>
+        <v>-9.688284559999998</v>
       </c>
       <c r="G80" t="n">
-        <v>-9.688284559999998</v>
+        <v>4.870666569999999</v>
       </c>
       <c r="H80" t="n">
-        <v>4.870666569999999</v>
+        <v>12.18966626</v>
       </c>
       <c r="I80" t="n">
-        <v>12.18966626</v>
+        <v>-4.46977351</v>
       </c>
       <c r="J80" t="n">
-        <v>-4.46977351</v>
+        <v>12.58217618</v>
       </c>
       <c r="K80" t="n">
-        <v>12.58217618</v>
+        <v>17.39556762</v>
       </c>
       <c r="L80" t="n">
-        <v>17.39556762</v>
+        <v>13.14819293</v>
       </c>
       <c r="M80" t="n">
-        <v>13.14819293</v>
+        <v>10.09827181</v>
       </c>
     </row>
     <row r="81">
@@ -3748,39 +3754,41 @@
           <t>鋼鐵工業右下</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr"/>
+      <c r="B81" t="n">
+        <v>0</v>
+      </c>
       <c r="C81" t="n">
-        <v>-103.34398829</v>
+        <v>-57.31861607</v>
       </c>
       <c r="D81" t="n">
-        <v>-57.69436082</v>
+        <v>-40.77116172</v>
       </c>
       <c r="E81" t="n">
-        <v>-41.13783873999999</v>
+        <v>-58.31165084</v>
       </c>
       <c r="F81" t="n">
-        <v>-58.76555155999999</v>
+        <v>-40.10086</v>
       </c>
       <c r="G81" t="n">
-        <v>-40.17196165999999</v>
+        <v>-13.23293289</v>
       </c>
       <c r="H81" t="n">
-        <v>-13.61398708</v>
+        <v>34.28753278</v>
       </c>
       <c r="I81" t="n">
-        <v>34.26378235</v>
+        <v>102.15875626</v>
       </c>
       <c r="J81" t="n">
-        <v>102.02552729</v>
+        <v>136.68336307</v>
       </c>
       <c r="K81" t="n">
-        <v>136.86135343</v>
+        <v>237.45557772</v>
       </c>
       <c r="L81" t="n">
-        <v>238.22024326</v>
+        <v>137.26361639</v>
       </c>
       <c r="M81" t="n">
-        <v>139.12935513</v>
+        <v>45.08298159</v>
       </c>
     </row>
     <row r="82">
@@ -3791,37 +3799,37 @@
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
-        <v>90.69154939000001</v>
+        <v>-50.2547076</v>
       </c>
       <c r="D82" t="n">
-        <v>-57.32406938000001</v>
+        <v>0.6935106799999997</v>
       </c>
       <c r="E82" t="n">
-        <v>-1.926858940000005</v>
+        <v>-169.39214522</v>
       </c>
       <c r="F82" t="n">
-        <v>-172.9662267</v>
+        <v>89.52751352000001</v>
       </c>
       <c r="G82" t="n">
-        <v>92.52711834</v>
+        <v>-160.83174776</v>
       </c>
       <c r="H82" t="n">
-        <v>-155.46170183</v>
+        <v>-351.76678152</v>
       </c>
       <c r="I82" t="n">
-        <v>-345.22405762</v>
+        <v>-559.3531269600001</v>
       </c>
       <c r="J82" t="n">
-        <v>-548.9082120700001</v>
+        <v>-300.64457347</v>
       </c>
       <c r="K82" t="n">
-        <v>-281.94104034</v>
+        <v>-178.50942961</v>
       </c>
       <c r="L82" t="n">
-        <v>-159.5239148</v>
+        <v>63.14910776</v>
       </c>
       <c r="M82" t="n">
-        <v>63.48032186</v>
+        <v>-30.53152689</v>
       </c>
     </row>
     <row r="83">
@@ -3832,37 +3840,37 @@
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>27.87323952</v>
+        <v>82.35941356999999</v>
       </c>
       <c r="D83" t="n">
-        <v>82.35941356999999</v>
+        <v>181.83515722</v>
       </c>
       <c r="E83" t="n">
-        <v>181.83515722</v>
+        <v>68.08952595000001</v>
       </c>
       <c r="F83" t="n">
-        <v>68.08952595000001</v>
+        <v>-20.36797773</v>
       </c>
       <c r="G83" t="n">
-        <v>-20.36797773</v>
+        <v>-20.03139617</v>
       </c>
       <c r="H83" t="n">
-        <v>-20.03139617</v>
+        <v>-59.64161756</v>
       </c>
       <c r="I83" t="n">
-        <v>-59.64161756</v>
+        <v>-112.75539681</v>
       </c>
       <c r="J83" t="n">
-        <v>-112.75539681</v>
+        <v>64.56145398</v>
       </c>
       <c r="K83" t="n">
-        <v>64.56145398</v>
+        <v>-54.95076079</v>
       </c>
       <c r="L83" t="n">
-        <v>-54.95076079</v>
+        <v>-5.751428920000002</v>
       </c>
       <c r="M83" t="n">
-        <v>-5.751428920000002</v>
+        <v>-18.06551288</v>
       </c>
     </row>
     <row r="84">
@@ -3873,37 +3881,37 @@
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
-        <v>-122.3490537</v>
+        <v>-54.08822536000001</v>
       </c>
       <c r="D84" t="n">
-        <v>-54.08822536000001</v>
+        <v>-10.32345865</v>
       </c>
       <c r="E84" t="n">
-        <v>-10.32345865</v>
+        <v>20.68587184</v>
       </c>
       <c r="F84" t="n">
-        <v>20.68587184</v>
+        <v>50.4358599</v>
       </c>
       <c r="G84" t="n">
-        <v>50.4358599</v>
+        <v>20.67695317</v>
       </c>
       <c r="H84" t="n">
-        <v>20.67695317</v>
+        <v>39.12531966</v>
       </c>
       <c r="I84" t="n">
-        <v>39.12531966</v>
+        <v>82.69031135000002</v>
       </c>
       <c r="J84" t="n">
-        <v>82.69031135000002</v>
+        <v>154.59545891</v>
       </c>
       <c r="K84" t="n">
-        <v>154.59545891</v>
+        <v>58.71590928</v>
       </c>
       <c r="L84" t="n">
-        <v>58.71590928</v>
+        <v>121.63718761</v>
       </c>
       <c r="M84" t="n">
-        <v>121.63718761</v>
+        <v>29.61562639</v>
       </c>
     </row>
     <row r="85">
@@ -3914,37 +3922,37 @@
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>4.65700348</v>
+        <v>16.5811829</v>
       </c>
       <c r="D85" t="n">
-        <v>16.5811829</v>
+        <v>83.55010430999998</v>
       </c>
       <c r="E85" t="n">
-        <v>83.55010430999998</v>
+        <v>308.21784694</v>
       </c>
       <c r="F85" t="n">
-        <v>308.21784694</v>
+        <v>132.33488342</v>
       </c>
       <c r="G85" t="n">
-        <v>132.33488342</v>
+        <v>37.83571189</v>
       </c>
       <c r="H85" t="n">
-        <v>37.83571189</v>
+        <v>-48.80012199</v>
       </c>
       <c r="I85" t="n">
-        <v>-48.80012199</v>
+        <v>-75.86895855</v>
       </c>
       <c r="J85" t="n">
-        <v>-75.86895855</v>
+        <v>-29.96102533</v>
       </c>
       <c r="K85" t="n">
-        <v>-29.96102533</v>
+        <v>-10.1905005</v>
       </c>
       <c r="L85" t="n">
-        <v>-10.1905005</v>
+        <v>26.19259462</v>
       </c>
       <c r="M85" t="n">
-        <v>26.19259462</v>
+        <v>-37.08723535</v>
       </c>
     </row>
     <row r="86">
@@ -3955,37 +3963,37 @@
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
-        <v>-7.647300829999998</v>
+        <v>40.5057899</v>
       </c>
       <c r="D86" t="n">
-        <v>40.5057899</v>
+        <v>0.2115746600000012</v>
       </c>
       <c r="E86" t="n">
-        <v>0.2115746600000012</v>
+        <v>-73.51357708</v>
       </c>
       <c r="F86" t="n">
-        <v>-73.51357708</v>
+        <v>-120.38293081</v>
       </c>
       <c r="G86" t="n">
-        <v>-120.38293081</v>
+        <v>-28.81328676999999</v>
       </c>
       <c r="H86" t="n">
-        <v>-28.81328676999999</v>
+        <v>26.42893274</v>
       </c>
       <c r="I86" t="n">
-        <v>26.42893274</v>
+        <v>-19.94011926</v>
       </c>
       <c r="J86" t="n">
-        <v>-19.94011926</v>
+        <v>-44.01715513000001</v>
       </c>
       <c r="K86" t="n">
-        <v>-44.01715513000001</v>
+        <v>-47.84157947</v>
       </c>
       <c r="L86" t="n">
-        <v>-47.84157947</v>
+        <v>-49.89369227</v>
       </c>
       <c r="M86" t="n">
-        <v>-49.89369227</v>
+        <v>-54.41137247</v>
       </c>
     </row>
     <row r="87">
@@ -3994,41 +4002,39 @@
           <t>電子通路業右下</t>
         </is>
       </c>
-      <c r="B87" t="n">
-        <v>0</v>
-      </c>
+      <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>9.40449473</v>
+        <v>72.27875806999999</v>
       </c>
       <c r="D87" t="n">
-        <v>61.57701271</v>
+        <v>17.68104212999999</v>
       </c>
       <c r="E87" t="n">
-        <v>20.08251324</v>
+        <v>-3.41344151</v>
       </c>
       <c r="F87" t="n">
-        <v>3.54886275</v>
+        <v>-68.99595576999999</v>
       </c>
       <c r="G87" t="n">
-        <v>-33.63304152</v>
+        <v>-152.61735534</v>
       </c>
       <c r="H87" t="n">
-        <v>-78.28551906999999</v>
+        <v>-178.63669302</v>
       </c>
       <c r="I87" t="n">
-        <v>-80.95774643</v>
+        <v>-166.39734657</v>
       </c>
       <c r="J87" t="n">
-        <v>-76.5308065</v>
+        <v>-126.75621919</v>
       </c>
       <c r="K87" t="n">
-        <v>-51.41952109</v>
+        <v>-109.66916115</v>
       </c>
       <c r="L87" t="n">
-        <v>-47.21596209</v>
+        <v>-91.38076609000001</v>
       </c>
       <c r="M87" t="n">
-        <v>-35.58194683</v>
+        <v>-87.53814033</v>
       </c>
     </row>
     <row r="88">
@@ -4039,37 +4045,37 @@
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
-        <v>34.88464354</v>
+        <v>61.72885808000001</v>
       </c>
       <c r="D88" t="n">
-        <v>67.06029259</v>
+        <v>105.61391819</v>
       </c>
       <c r="E88" t="n">
-        <v>108.11180131</v>
+        <v>64.99092465</v>
       </c>
       <c r="F88" t="n">
-        <v>65.92950389000001</v>
+        <v>2.53131499</v>
       </c>
       <c r="G88" t="n">
-        <v>2.10840591</v>
+        <v>-23.34969583</v>
       </c>
       <c r="H88" t="n">
-        <v>-24.75203363</v>
+        <v>-0.6363751400000015</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.5570340900000017</v>
+        <v>-22.32325048</v>
       </c>
       <c r="J88" t="n">
-        <v>-23.51860179</v>
+        <v>-42.81727544</v>
       </c>
       <c r="K88" t="n">
-        <v>-45.03233113</v>
+        <v>-35.34060749</v>
       </c>
       <c r="L88" t="n">
-        <v>-38.22943602</v>
+        <v>-4.153807230000002</v>
       </c>
       <c r="M88" t="n">
-        <v>-4.498579950000001</v>
+        <v>20.97149765</v>
       </c>
     </row>
     <row r="89">
@@ -4080,37 +4086,37 @@
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>212.40817085</v>
+        <v>2976.04661351</v>
       </c>
       <c r="D89" t="n">
-        <v>2990.31880572</v>
+        <v>1174.76537281</v>
       </c>
       <c r="E89" t="n">
-        <v>1186.80735137</v>
+        <v>788.47338988</v>
       </c>
       <c r="F89" t="n">
-        <v>794.00660127</v>
+        <v>3439.72712589</v>
       </c>
       <c r="G89" t="n">
-        <v>3445.63541345</v>
+        <v>5018.143648769999</v>
       </c>
       <c r="H89" t="n">
-        <v>5028.74955195</v>
+        <v>4913.86418217</v>
       </c>
       <c r="I89" t="n">
-        <v>4932.12340164</v>
+        <v>5029.14339548</v>
       </c>
       <c r="J89" t="n">
-        <v>5056.04785329</v>
+        <v>5003.88768559</v>
       </c>
       <c r="K89" t="n">
-        <v>5015.056826280001</v>
+        <v>3597.82972113</v>
       </c>
       <c r="L89" t="n">
-        <v>3596.91904878</v>
+        <v>5119.049637009999</v>
       </c>
       <c r="M89" t="n">
-        <v>5119.45468342</v>
+        <v>-39.36253362999983</v>
       </c>
     </row>
     <row r="90">
@@ -4121,37 +4127,37 @@
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>-14.22535454</v>
+        <v>-7.703919789999998</v>
       </c>
       <c r="D90" t="n">
-        <v>-7.938487430000005</v>
+        <v>-52.6155042</v>
       </c>
       <c r="E90" t="n">
-        <v>-49.59893637</v>
+        <v>-129.53775208</v>
       </c>
       <c r="F90" t="n">
-        <v>-124.42277984</v>
+        <v>-109.32306762</v>
       </c>
       <c r="G90" t="n">
-        <v>-109.69509236</v>
+        <v>-71.99148717999999</v>
       </c>
       <c r="H90" t="n">
-        <v>-69.58334395</v>
+        <v>-6.84765444</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2716190900000023</v>
+        <v>-87.32757911</v>
       </c>
       <c r="J90" t="n">
-        <v>-83.76383537999999</v>
+        <v>-38.67162504</v>
       </c>
       <c r="K90" t="n">
-        <v>-41.75871842999999</v>
+        <v>-2.150323739999998</v>
       </c>
       <c r="L90" t="n">
-        <v>-17.05357446999999</v>
+        <v>79.26695736000001</v>
       </c>
       <c r="M90" t="n">
-        <v>74.16510740000001</v>
+        <v>32.94809444</v>
       </c>
     </row>
     <row r="91">
@@ -4162,37 +4168,37 @@
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>-664.04291288</v>
+        <v>-141.70846272</v>
       </c>
       <c r="D91" t="n">
-        <v>-155.74608729</v>
+        <v>-1014.76569765</v>
       </c>
       <c r="E91" t="n">
-        <v>-1029.82424404</v>
+        <v>-840.5265649600001</v>
       </c>
       <c r="F91" t="n">
-        <v>-851.17474859</v>
+        <v>-777.2582415900001</v>
       </c>
       <c r="G91" t="n">
-        <v>-782.7945044100001</v>
+        <v>-232.52714159</v>
       </c>
       <c r="H91" t="n">
-        <v>-245.541188</v>
+        <v>-937.11580989</v>
       </c>
       <c r="I91" t="n">
-        <v>-961.95106471</v>
+        <v>-1512.48922155</v>
       </c>
       <c r="J91" t="n">
-        <v>-1542.95742309</v>
+        <v>-2005.57788128</v>
       </c>
       <c r="K91" t="n">
-        <v>-2013.65992858</v>
+        <v>-2148.39575892</v>
       </c>
       <c r="L91" t="n">
-        <v>-2132.58183584</v>
+        <v>-621.93563805</v>
       </c>
       <c r="M91" t="n">
-        <v>-617.2388345000001</v>
+        <v>-1410.80683404</v>
       </c>
     </row>
     <row r="92">
@@ -4203,37 +4209,37 @@
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>-1119.94840541</v>
+        <v>-1209.79725867</v>
       </c>
       <c r="D92" t="n">
-        <v>-1209.79889255</v>
+        <v>-394.98546916</v>
       </c>
       <c r="E92" t="n">
-        <v>-394.9854834599999</v>
+        <v>807.19972316</v>
       </c>
       <c r="F92" t="n">
-        <v>807.20241059</v>
+        <v>-143.08203782</v>
       </c>
       <c r="G92" t="n">
-        <v>-143.07668677</v>
+        <v>29.72846714999998</v>
       </c>
       <c r="H92" t="n">
-        <v>29.73263064999998</v>
+        <v>-1156.97070077</v>
       </c>
       <c r="I92" t="n">
-        <v>-1156.96839941</v>
+        <v>-26.00681758999992</v>
       </c>
       <c r="J92" t="n">
-        <v>-26.00348641999991</v>
+        <v>-147.75625942</v>
       </c>
       <c r="K92" t="n">
-        <v>-147.75120938</v>
+        <v>-473.75673339</v>
       </c>
       <c r="L92" t="n">
-        <v>-473.74963365</v>
+        <v>527.4104596</v>
       </c>
       <c r="M92" t="n">
-        <v>527.4095368100001</v>
+        <v>-553.7174667100001</v>
       </c>
     </row>
     <row r="93">
@@ -4242,41 +4248,39 @@
           <t>電機機械右下</t>
         </is>
       </c>
-      <c r="B93" t="n">
-        <v>0</v>
-      </c>
+      <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>-155.10822174</v>
+        <v>-3.998096980000008</v>
       </c>
       <c r="D93" t="n">
-        <v>-45.82354711</v>
+        <v>-110.70243297</v>
       </c>
       <c r="E93" t="n">
-        <v>-92.70913264000002</v>
+        <v>6.200496799999999</v>
       </c>
       <c r="F93" t="n">
-        <v>-23.68235597</v>
+        <v>97.14551906</v>
       </c>
       <c r="G93" t="n">
-        <v>6.1374519</v>
+        <v>65.14495000000001</v>
       </c>
       <c r="H93" t="n">
-        <v>-33.13408994</v>
+        <v>-20.06332136</v>
       </c>
       <c r="I93" t="n">
-        <v>-49.35878334</v>
+        <v>-141.52650904</v>
       </c>
       <c r="J93" t="n">
-        <v>-60.85396212999999</v>
+        <v>-80.82240035</v>
       </c>
       <c r="K93" t="n">
-        <v>16.57186501</v>
+        <v>4.54919342</v>
       </c>
       <c r="L93" t="n">
-        <v>14.50032759</v>
+        <v>157.23986864</v>
       </c>
       <c r="M93" t="n">
-        <v>13.5528489</v>
+        <v>-5.068777900000002</v>
       </c>
     </row>
     <row r="94">
@@ -4287,37 +4291,37 @@
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>169.123142</v>
+        <v>100.88904485</v>
       </c>
       <c r="D94" t="n">
-        <v>142.71602724</v>
+        <v>137.31590916</v>
       </c>
       <c r="E94" t="n">
-        <v>119.32277019</v>
+        <v>198.57608617</v>
       </c>
       <c r="F94" t="n">
-        <v>228.45661413</v>
+        <v>91.58407464</v>
       </c>
       <c r="G94" t="n">
-        <v>182.58705834</v>
+        <v>2.84579915</v>
       </c>
       <c r="H94" t="n">
-        <v>101.12114545</v>
+        <v>89.45212879</v>
       </c>
       <c r="I94" t="n">
-        <v>118.74585852</v>
+        <v>99.56555995000001</v>
       </c>
       <c r="J94" t="n">
-        <v>18.89004940999999</v>
+        <v>184.22448881</v>
       </c>
       <c r="K94" t="n">
-        <v>86.82549297</v>
+        <v>240.52444953</v>
       </c>
       <c r="L94" t="n">
-        <v>230.56657783</v>
+        <v>130.46502946</v>
       </c>
       <c r="M94" t="n">
-        <v>274.15330595</v>
+        <v>150.6881894</v>
       </c>
     </row>
     <row r="95">
@@ -4328,37 +4332,37 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>416.44109066</v>
+        <v>3999.20590199</v>
       </c>
       <c r="D95" t="n">
-        <v>4058.27390463</v>
+        <v>1762.63583123</v>
       </c>
       <c r="E95" t="n">
-        <v>1802.97024758</v>
+        <v>2552.71020422</v>
       </c>
       <c r="F95" t="n">
-        <v>2588.30203534</v>
+        <v>3352.5478127</v>
       </c>
       <c r="G95" t="n">
-        <v>3407.84381268</v>
+        <v>2886.99522768</v>
       </c>
       <c r="H95" t="n">
-        <v>2918.26632337</v>
+        <v>398.4060898100001</v>
       </c>
       <c r="I95" t="n">
-        <v>392.76594471</v>
+        <v>-3396.75229127</v>
       </c>
       <c r="J95" t="n">
-        <v>-3427.24280729</v>
+        <v>-3813.35342558</v>
       </c>
       <c r="K95" t="n">
-        <v>-3829.12475877</v>
+        <v>-3126.49078176</v>
       </c>
       <c r="L95" t="n">
-        <v>-3124.25803953</v>
+        <v>-3111.00042372</v>
       </c>
       <c r="M95" t="n">
-        <v>-3099.23420779</v>
+        <v>-3739.27661508</v>
       </c>
     </row>
     <row r="96">
@@ -4367,41 +4371,39 @@
           <t>電腦及週邊設備業右下</t>
         </is>
       </c>
-      <c r="B96" t="n">
-        <v>0</v>
-      </c>
+      <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>41.31179470999999</v>
+        <v>317.72942932</v>
       </c>
       <c r="D96" t="n">
-        <v>303.85865835</v>
+        <v>5.791317389999997</v>
       </c>
       <c r="E96" t="n">
-        <v>35.3318436</v>
+        <v>12.15852532999999</v>
       </c>
       <c r="F96" t="n">
-        <v>-22.25389299</v>
+        <v>-379.72493019</v>
       </c>
       <c r="G96" t="n">
-        <v>-315.7113619</v>
+        <v>-564.06818734</v>
       </c>
       <c r="H96" t="n">
-        <v>-538.14640064</v>
+        <v>-653.8013840599999</v>
       </c>
       <c r="I96" t="n">
-        <v>-571.8712749299999</v>
+        <v>-748.07666977</v>
       </c>
       <c r="J96" t="n">
-        <v>-624.8439679099999</v>
+        <v>-766.2916985000001</v>
       </c>
       <c r="K96" t="n">
-        <v>-657.73119352</v>
+        <v>-583.1377750299999</v>
       </c>
       <c r="L96" t="n">
-        <v>-438.96181825</v>
+        <v>-495.62078918</v>
       </c>
       <c r="M96" t="n">
-        <v>-464.35261563</v>
+        <v>-390.00583392</v>
       </c>
     </row>
     <row r="97">
@@ -4412,37 +4414,37 @@
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>-85.92268896</v>
+        <v>93.37706496000001</v>
       </c>
       <c r="D97" t="n">
-        <v>48.26396369</v>
+        <v>-7.104535660000006</v>
       </c>
       <c r="E97" t="n">
-        <v>-76.90205049000001</v>
+        <v>86.66724294999999</v>
       </c>
       <c r="F97" t="n">
-        <v>85.5031202</v>
+        <v>122.59005398</v>
       </c>
       <c r="G97" t="n">
-        <v>3.221822799999994</v>
+        <v>156.55255896</v>
       </c>
       <c r="H97" t="n">
-        <v>99.35405415999999</v>
+        <v>-8.152036220000001</v>
       </c>
       <c r="I97" t="n">
-        <v>-84.42280314</v>
+        <v>92.3549417</v>
       </c>
       <c r="J97" t="n">
-        <v>-0.3987063000000081</v>
+        <v>-38.33238675</v>
       </c>
       <c r="K97" t="n">
-        <v>-131.11918459</v>
+        <v>-164.20292419</v>
       </c>
       <c r="L97" t="n">
-        <v>-310.60347696</v>
+        <v>-68.25951778</v>
       </c>
       <c r="M97" t="n">
-        <v>-111.28280038</v>
+        <v>-6.200428619999998</v>
       </c>
     </row>
     <row r="98">
@@ -4453,37 +4455,37 @@
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
-        <v>2.57707229</v>
+        <v>17.61837582</v>
       </c>
       <c r="D98" t="n">
-        <v>17.61837582</v>
+        <v>27.36598622</v>
       </c>
       <c r="E98" t="n">
-        <v>27.36598622</v>
+        <v>21.46284854</v>
       </c>
       <c r="F98" t="n">
-        <v>21.46284854</v>
+        <v>2.43384234</v>
       </c>
       <c r="G98" t="n">
-        <v>2.43384234</v>
+        <v>3.42921125</v>
       </c>
       <c r="H98" t="n">
-        <v>3.42921125</v>
+        <v>20.06839899</v>
       </c>
       <c r="I98" t="n">
-        <v>20.06839899</v>
+        <v>29.26418117</v>
       </c>
       <c r="J98" t="n">
-        <v>29.26418117</v>
+        <v>17.238713</v>
       </c>
       <c r="K98" t="n">
-        <v>17.238713</v>
+        <v>24.67003403</v>
       </c>
       <c r="L98" t="n">
-        <v>24.67003403</v>
+        <v>34.21972625</v>
       </c>
       <c r="M98" t="n">
-        <v>34.21972625</v>
+        <v>36.67212921999999</v>
       </c>
     </row>
     <row r="99">
@@ -4494,37 +4496,37 @@
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>9.207686730000001</v>
+        <v>12.72317876</v>
       </c>
       <c r="D99" t="n">
-        <v>12.72329238</v>
+        <v>17.20167136</v>
       </c>
       <c r="E99" t="n">
-        <v>17.20173201</v>
+        <v>5.82127413</v>
       </c>
       <c r="F99" t="n">
-        <v>5.82131096</v>
+        <v>-1.51808174</v>
       </c>
       <c r="G99" t="n">
-        <v>-1.51795931</v>
+        <v>-12.99658263</v>
       </c>
       <c r="H99" t="n">
-        <v>-12.99625281</v>
+        <v>-16.94004654</v>
       </c>
       <c r="I99" t="n">
-        <v>-16.9396746</v>
+        <v>-11.90809048</v>
       </c>
       <c r="J99" t="n">
-        <v>-11.9078638</v>
+        <v>3.03967369</v>
       </c>
       <c r="K99" t="n">
-        <v>3.03977697</v>
+        <v>2.450110249999999</v>
       </c>
       <c r="L99" t="n">
-        <v>2.450260839999999</v>
+        <v>4.71725531</v>
       </c>
       <c r="M99" t="n">
-        <v>4.71740638</v>
+        <v>5.754929999999999</v>
       </c>
     </row>
     <row r="100">
@@ -4535,37 +4537,37 @@
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="n">
-        <v>-27.29308296</v>
+        <v>-51.18432531</v>
       </c>
       <c r="D100" t="n">
-        <v>-51.18443892999999</v>
+        <v>-94.26169625999999</v>
       </c>
       <c r="E100" t="n">
-        <v>-94.26175691</v>
+        <v>-157.11154533</v>
       </c>
       <c r="F100" t="n">
-        <v>-157.11158216</v>
+        <v>-218.50198275</v>
       </c>
       <c r="G100" t="n">
-        <v>-218.50210518</v>
+        <v>-239.00675844</v>
       </c>
       <c r="H100" t="n">
-        <v>-239.00708826</v>
+        <v>-229.12990797</v>
       </c>
       <c r="I100" t="n">
-        <v>-229.13027991</v>
+        <v>-222.29818564</v>
       </c>
       <c r="J100" t="n">
-        <v>-222.29841232</v>
+        <v>-71.93103434</v>
       </c>
       <c r="K100" t="n">
-        <v>-71.93113762</v>
+        <v>16.46914554</v>
       </c>
       <c r="L100" t="n">
-        <v>16.46899495</v>
+        <v>-17.34255191</v>
       </c>
       <c r="M100" t="n">
-        <v>-17.34270298</v>
+        <v>-32.57008549</v>
       </c>
     </row>
   </sheetData>

--- a/Result/analyze_2.xlsx
+++ b/Result/analyze_2.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
     </row>
@@ -503,37 +503,37 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1829.87179314</v>
+        <v>1090.07558463</v>
       </c>
       <c r="D2" t="n">
-        <v>1056.78821396</v>
+        <v>151.91773738</v>
       </c>
       <c r="E2" t="n">
-        <v>38.44985315000002</v>
+        <v>726.90928567</v>
       </c>
       <c r="F2" t="n">
-        <v>605.9506780400001</v>
+        <v>786.60943803</v>
       </c>
       <c r="G2" t="n">
-        <v>731.2417069400001</v>
+        <v>708.8842369299999</v>
       </c>
       <c r="H2" t="n">
-        <v>697.19497599</v>
+        <v>1783.37409329</v>
       </c>
       <c r="I2" t="n">
-        <v>1824.4696739</v>
+        <v>-145.63833015</v>
       </c>
       <c r="J2" t="n">
-        <v>-152.05894289</v>
+        <v>101.2267009</v>
       </c>
       <c r="K2" t="n">
-        <v>-67.89374619999998</v>
+        <v>207.3858346</v>
       </c>
       <c r="L2" t="n">
-        <v>-85.87499314000002</v>
+        <v>-87.39109071</v>
       </c>
       <c r="M2" t="n">
-        <v>-192.88029105</v>
+        <v>-892.0108127399999</v>
       </c>
     </row>
     <row r="3">
@@ -542,41 +542,39 @@
           <t>光電業右下</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>169.23619934</v>
+        <v>140.59546247</v>
       </c>
       <c r="D3" t="n">
-        <v>124.14557469</v>
+        <v>58.50494856</v>
       </c>
       <c r="E3" t="n">
-        <v>54.23512341</v>
+        <v>-47.13305369</v>
       </c>
       <c r="F3" t="n">
-        <v>-31.05750398999999</v>
+        <v>26.35795273</v>
       </c>
       <c r="G3" t="n">
-        <v>50.52273997</v>
+        <v>115.87357209</v>
       </c>
       <c r="H3" t="n">
-        <v>130.79247186</v>
+        <v>128.58963539</v>
       </c>
       <c r="I3" t="n">
-        <v>140.16408121</v>
+        <v>131.89171887</v>
       </c>
       <c r="J3" t="n">
-        <v>130.03350426</v>
+        <v>238.37577133</v>
       </c>
       <c r="K3" t="n">
-        <v>213.75028653</v>
+        <v>307.75556055</v>
       </c>
       <c r="L3" t="n">
-        <v>273.34038471</v>
+        <v>236.10169612</v>
       </c>
       <c r="M3" t="n">
-        <v>186.63607038</v>
+        <v>-24.40457867</v>
       </c>
     </row>
     <row r="4">
@@ -587,37 +585,37 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>155.003109</v>
+        <v>47.41035247</v>
       </c>
       <c r="D4" t="n">
-        <v>63.79301953</v>
+        <v>211.47174397</v>
       </c>
       <c r="E4" t="n">
-        <v>215.36167827</v>
+        <v>-73.86853386999999</v>
       </c>
       <c r="F4" t="n">
-        <v>-90.39439253</v>
+        <v>21.29332980000001</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.575122609999999</v>
+        <v>1.869937859999985</v>
       </c>
       <c r="H4" t="n">
-        <v>-13.82677621000002</v>
+        <v>-62.26718312000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-73.98470615000001</v>
+        <v>-185.50155132</v>
       </c>
       <c r="J4" t="n">
-        <v>-183.42682176</v>
+        <v>-219.33741223</v>
       </c>
       <c r="K4" t="n">
-        <v>-194.17610375</v>
+        <v>70.2855538</v>
       </c>
       <c r="L4" t="n">
-        <v>105.10033907</v>
+        <v>148.44488018</v>
       </c>
       <c r="M4" t="n">
-        <v>198.25096442</v>
+        <v>-107.55015101</v>
       </c>
     </row>
     <row r="5">
@@ -628,37 +626,37 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>146.0345752</v>
+        <v>-38.63470381</v>
       </c>
       <c r="D5" t="n">
-        <v>-38.63452967</v>
+        <v>-259.31952944</v>
       </c>
       <c r="E5" t="n">
-        <v>-259.31952884</v>
+        <v>-387.10508662</v>
       </c>
       <c r="F5" t="n">
-        <v>-387.10508165</v>
+        <v>-428.41056918</v>
       </c>
       <c r="G5" t="n">
-        <v>-428.41046551</v>
+        <v>-414.44013366</v>
       </c>
       <c r="H5" t="n">
-        <v>-414.44000099</v>
+        <v>-488.47393708</v>
       </c>
       <c r="I5" t="n">
-        <v>-488.4738502000001</v>
+        <v>-416.87207636</v>
       </c>
       <c r="J5" t="n">
-        <v>-416.8719373800001</v>
+        <v>-354.1363297</v>
       </c>
       <c r="K5" t="n">
-        <v>-354.13634132</v>
+        <v>-250.13327652</v>
       </c>
       <c r="L5" t="n">
-        <v>-250.13333523</v>
+        <v>-355.59157241</v>
       </c>
       <c r="M5" t="n">
-        <v>-355.59155334</v>
+        <v>-426.40809136</v>
       </c>
     </row>
     <row r="6">
@@ -671,37 +669,37 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>11.56633733</v>
+        <v>23.8340967</v>
       </c>
       <c r="D6" t="n">
-        <v>23.38891836</v>
+        <v>62.44199644</v>
       </c>
       <c r="E6" t="n">
-        <v>61.75983711</v>
+        <v>75.21006885</v>
       </c>
       <c r="F6" t="n">
-        <v>75.86807717000001</v>
+        <v>70.80507362</v>
       </c>
       <c r="G6" t="n">
-        <v>71.68095057000001</v>
+        <v>61.05628663</v>
       </c>
       <c r="H6" t="n">
-        <v>61.51880339</v>
+        <v>148.08338344</v>
       </c>
       <c r="I6" t="n">
-        <v>150.92365386</v>
+        <v>189.98701193</v>
       </c>
       <c r="J6" t="n">
-        <v>191.78965058</v>
+        <v>27.06366671999999</v>
       </c>
       <c r="K6" t="n">
-        <v>29.44580001999999</v>
+        <v>59.43793802</v>
       </c>
       <c r="L6" t="n">
-        <v>62.21572828999999</v>
+        <v>-16.76787345999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-16.40639453999999</v>
+        <v>-82.0723675</v>
       </c>
     </row>
     <row r="7">
@@ -712,37 +710,37 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>12.0110792</v>
+        <v>14.45395505</v>
       </c>
       <c r="D7" t="n">
-        <v>14.39064089</v>
+        <v>1.834345269999998</v>
       </c>
       <c r="E7" t="n">
-        <v>1.866669629999999</v>
+        <v>-6.807581649999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-6.83235236</v>
+        <v>-32.31644055</v>
       </c>
       <c r="G7" t="n">
-        <v>-32.13406114</v>
+        <v>-25.77772236</v>
       </c>
       <c r="H7" t="n">
-        <v>-25.57055793</v>
+        <v>-26.2212407</v>
       </c>
       <c r="I7" t="n">
-        <v>-26.21872809</v>
+        <v>-34.91714055</v>
       </c>
       <c r="J7" t="n">
-        <v>-34.91576833</v>
+        <v>-50.82166224000001</v>
       </c>
       <c r="K7" t="n">
-        <v>-50.83131593</v>
+        <v>-23.0987534</v>
       </c>
       <c r="L7" t="n">
-        <v>-23.19731798</v>
+        <v>-7.21434608</v>
       </c>
       <c r="M7" t="n">
-        <v>-7.337062079999998</v>
+        <v>-16.83103393</v>
       </c>
     </row>
     <row r="8">
@@ -753,37 +751,37 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>1216.91979688</v>
+        <v>1470.79262695</v>
       </c>
       <c r="D8" t="n">
-        <v>1224.70182488</v>
+        <v>2857.49565018</v>
       </c>
       <c r="E8" t="n">
-        <v>3053.45058058</v>
+        <v>2696.70472936</v>
       </c>
       <c r="F8" t="n">
-        <v>3202.47206384</v>
+        <v>3193.33253514</v>
       </c>
       <c r="G8" t="n">
-        <v>3797.04277677</v>
+        <v>783.54376217</v>
       </c>
       <c r="H8" t="n">
-        <v>875.06135877</v>
+        <v>2204.70663249</v>
       </c>
       <c r="I8" t="n">
-        <v>2608.67093669</v>
+        <v>2426.97135045</v>
       </c>
       <c r="J8" t="n">
-        <v>2447.64286738</v>
+        <v>3280.19517416</v>
       </c>
       <c r="K8" t="n">
-        <v>2990.65970583</v>
+        <v>3443.16117847</v>
       </c>
       <c r="L8" t="n">
-        <v>2850.23196878</v>
+        <v>-68.84787009999998</v>
       </c>
       <c r="M8" t="n">
-        <v>-845.7175441999999</v>
+        <v>-4331.160411569999</v>
       </c>
     </row>
     <row r="9">
@@ -792,39 +790,41 @@
           <t>其他電子業右下</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
       <c r="C9" t="n">
-        <v>40.08045371000001</v>
+        <v>-1.71563536</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.64155862</v>
+        <v>12.39496474</v>
       </c>
       <c r="E9" t="n">
-        <v>12.49106397</v>
+        <v>-56.68166504</v>
       </c>
       <c r="F9" t="n">
-        <v>-56.51378705</v>
+        <v>-82.45231404</v>
       </c>
       <c r="G9" t="n">
-        <v>-83.09307722</v>
+        <v>-85.97938264</v>
       </c>
       <c r="H9" t="n">
-        <v>-91.20032823999999</v>
+        <v>-109.82733274</v>
       </c>
       <c r="I9" t="n">
-        <v>-123.55814704</v>
+        <v>-108.80447564</v>
       </c>
       <c r="J9" t="n">
-        <v>-130.50766605</v>
+        <v>-110.69811322</v>
       </c>
       <c r="K9" t="n">
-        <v>-119.50554787</v>
+        <v>-109.39143654</v>
       </c>
       <c r="L9" t="n">
-        <v>-109.67401669</v>
+        <v>-116.10055027</v>
       </c>
       <c r="M9" t="n">
-        <v>-113.21363326</v>
+        <v>-93.26368867999999</v>
       </c>
     </row>
     <row r="10">
@@ -835,37 +835,37 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>92.92674992000001</v>
+        <v>6.833367389999998</v>
       </c>
       <c r="D10" t="n">
-        <v>17.44306224</v>
+        <v>45.76534605</v>
       </c>
       <c r="E10" t="n">
-        <v>45.06280080000001</v>
+        <v>-18.12366639</v>
       </c>
       <c r="F10" t="n">
-        <v>-8.84950342</v>
+        <v>-107.5375859</v>
       </c>
       <c r="G10" t="n">
-        <v>-111.19370916</v>
+        <v>-93.76588418</v>
       </c>
       <c r="H10" t="n">
-        <v>-97.49701018</v>
+        <v>-135.47981988</v>
       </c>
       <c r="I10" t="n">
-        <v>-131.60384685</v>
+        <v>-116.34511689</v>
       </c>
       <c r="J10" t="n">
-        <v>-90.20574187000001</v>
+        <v>-103.29812568</v>
       </c>
       <c r="K10" t="n">
-        <v>-44.54427384</v>
+        <v>-96.95473371999999</v>
       </c>
       <c r="L10" t="n">
-        <v>25.94232598000002</v>
+        <v>-103.92862233</v>
       </c>
       <c r="M10" t="n">
-        <v>-59.67607909</v>
+        <v>-111.97291779</v>
       </c>
     </row>
     <row r="11">
@@ -876,37 +876,37 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>-4.426172029999999</v>
+        <v>-57.61486382</v>
       </c>
       <c r="D11" t="n">
-        <v>-54.00431807</v>
+        <v>-84.49990516000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-86.86555312</v>
+        <v>-71.27952607</v>
       </c>
       <c r="F11" t="n">
-        <v>-76.35197597000001</v>
+        <v>-9.778319470000007</v>
       </c>
       <c r="G11" t="n">
-        <v>-15.33443696000001</v>
+        <v>31.64017136999999</v>
       </c>
       <c r="H11" t="n">
-        <v>30.12201213</v>
+        <v>-181.89193455</v>
       </c>
       <c r="I11" t="n">
-        <v>-180.83661576</v>
+        <v>-28.50699865000001</v>
       </c>
       <c r="J11" t="n">
-        <v>-28.02151100000001</v>
+        <v>309.12090261</v>
       </c>
       <c r="K11" t="n">
-        <v>312.29508241</v>
+        <v>653.33942918</v>
       </c>
       <c r="L11" t="n">
-        <v>658.2697451700001</v>
+        <v>235.03869243</v>
       </c>
       <c r="M11" t="n">
-        <v>242.28540973</v>
+        <v>-34.09932765999999</v>
       </c>
     </row>
     <row r="12">
@@ -915,39 +915,41 @@
           <t>化學工業右下</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
       <c r="C12" t="n">
-        <v>-101.9594561</v>
+        <v>-106.15223612</v>
       </c>
       <c r="D12" t="n">
-        <v>-105.76762729</v>
+        <v>-22.38041667999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-24.18409051999999</v>
+        <v>360.01811206</v>
       </c>
       <c r="F12" t="n">
-        <v>360.8863256</v>
+        <v>239.49278571</v>
       </c>
       <c r="G12" t="n">
-        <v>240.79125821</v>
+        <v>173.02896927</v>
       </c>
       <c r="H12" t="n">
-        <v>174.4546849</v>
+        <v>-44.28497224</v>
       </c>
       <c r="I12" t="n">
-        <v>-44.78824605</v>
+        <v>-22.13560097</v>
       </c>
       <c r="J12" t="n">
-        <v>-24.95834715</v>
+        <v>2.70338473</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.651111749999998</v>
+        <v>58.76884053</v>
       </c>
       <c r="L12" t="n">
-        <v>48.41734252000001</v>
+        <v>-14.08458902</v>
       </c>
       <c r="M12" t="n">
-        <v>-29.50577848</v>
+        <v>-152.02836988</v>
       </c>
     </row>
     <row r="13">
@@ -958,37 +960,37 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>-9.052562119999999</v>
+        <v>-2.21215822</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.205485100000001</v>
+        <v>2.88137664</v>
       </c>
       <c r="E13" t="n">
-        <v>7.050954819999999</v>
+        <v>-7.67681854</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.47330351</v>
+        <v>-4.089695679999999</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1664978700000001</v>
+        <v>21.29562269</v>
       </c>
       <c r="H13" t="n">
-        <v>21.38924244</v>
+        <v>44.12017899</v>
       </c>
       <c r="I13" t="n">
-        <v>43.57069945000001</v>
+        <v>21.95574711</v>
       </c>
       <c r="J13" t="n">
-        <v>24.29618216</v>
+        <v>21.73672541000001</v>
       </c>
       <c r="K13" t="n">
-        <v>22.92182365</v>
+        <v>30.34853865</v>
       </c>
       <c r="L13" t="n">
-        <v>35.76870215</v>
+        <v>13.10436976</v>
       </c>
       <c r="M13" t="n">
-        <v>21.2768524</v>
+        <v>-5.90438728</v>
       </c>
     </row>
     <row r="14">
@@ -999,37 +1001,37 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>-1366.25182753</v>
+        <v>-3741.12802511</v>
       </c>
       <c r="D14" t="n">
-        <v>-3909.35918457</v>
+        <v>5092.684053989999</v>
       </c>
       <c r="E14" t="n">
-        <v>5013.90762208</v>
+        <v>1795.11592831</v>
       </c>
       <c r="F14" t="n">
-        <v>1659.55785566</v>
+        <v>7285.72629368</v>
       </c>
       <c r="G14" t="n">
-        <v>7284.156148679999</v>
+        <v>4052.47761611</v>
       </c>
       <c r="H14" t="n">
-        <v>4018.80423298</v>
+        <v>7580.91730309</v>
       </c>
       <c r="I14" t="n">
-        <v>7510.388950680001</v>
+        <v>4000.9836017</v>
       </c>
       <c r="J14" t="n">
-        <v>3887.31917214</v>
+        <v>4548.563723889999</v>
       </c>
       <c r="K14" t="n">
-        <v>4387.32142908</v>
+        <v>1421.6717039</v>
       </c>
       <c r="L14" t="n">
-        <v>1575.79333564</v>
+        <v>754.4407251499999</v>
       </c>
       <c r="M14" t="n">
-        <v>607.00186777</v>
+        <v>-9345.922801280001</v>
       </c>
     </row>
     <row r="15">
@@ -1042,37 +1044,37 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>405.65647524</v>
+        <v>-118.82287651</v>
       </c>
       <c r="D15" t="n">
-        <v>-169.3662312</v>
+        <v>-325.73320421</v>
       </c>
       <c r="E15" t="n">
-        <v>-342.01578111</v>
+        <v>44.70852931000003</v>
       </c>
       <c r="F15" t="n">
-        <v>213.58401075</v>
+        <v>-517.70621518</v>
       </c>
       <c r="G15" t="n">
-        <v>-24.42671701</v>
+        <v>411.72784859</v>
       </c>
       <c r="H15" t="n">
-        <v>830.46147178</v>
+        <v>-80.12825020999998</v>
       </c>
       <c r="I15" t="n">
-        <v>341.12004153</v>
+        <v>606.13821407</v>
       </c>
       <c r="J15" t="n">
-        <v>570.66117303</v>
+        <v>653.4195649200001</v>
       </c>
       <c r="K15" t="n">
-        <v>563.44598555</v>
+        <v>164.81433669</v>
       </c>
       <c r="L15" t="n">
-        <v>315.28214846</v>
+        <v>-175.78176315</v>
       </c>
       <c r="M15" t="n">
-        <v>-48.89996611000002</v>
+        <v>-122.62350856</v>
       </c>
     </row>
     <row r="16">
@@ -1083,37 +1085,37 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>-401.11096956</v>
+        <v>-1077.63965973</v>
       </c>
       <c r="D16" t="n">
-        <v>-898.7240468700001</v>
+        <v>-102.6001831</v>
       </c>
       <c r="E16" t="n">
-        <v>78.75591238</v>
+        <v>-187.30067927</v>
       </c>
       <c r="F16" t="n">
-        <v>-300.91909334</v>
+        <v>58.27291674000001</v>
       </c>
       <c r="G16" t="n">
-        <v>-472.0598458800001</v>
+        <v>-187.66411075</v>
       </c>
       <c r="H16" t="n">
-        <v>-700.5296005499999</v>
+        <v>273.43466368</v>
       </c>
       <c r="I16" t="n">
-        <v>-291.1882918599999</v>
+        <v>129.63155696</v>
       </c>
       <c r="J16" t="n">
-        <v>35.47685648999999</v>
+        <v>-425.0015046099999</v>
       </c>
       <c r="K16" t="n">
-        <v>-487.94771527</v>
+        <v>282.76584949</v>
       </c>
       <c r="L16" t="n">
-        <v>-122.07344023</v>
+        <v>-364.47517977</v>
       </c>
       <c r="M16" t="n">
-        <v>-545.2346220099998</v>
+        <v>-697.2965504299999</v>
       </c>
     </row>
     <row r="17">
@@ -1124,37 +1126,37 @@
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
-        <v>0.95461918</v>
+        <v>0.84933853</v>
       </c>
       <c r="D17" t="n">
-        <v>0.84933853</v>
+        <v>-0.12911185</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.12911185</v>
+        <v>0.18345265</v>
       </c>
       <c r="F17" t="n">
-        <v>0.18345265</v>
+        <v>-0.75565477</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.75565477</v>
+        <v>-1.09301157</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.09301157</v>
+        <v>-1.25991411</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.25991411</v>
+        <v>0.42586555</v>
       </c>
       <c r="J17" t="n">
-        <v>0.42586555</v>
+        <v>1.11311752</v>
       </c>
       <c r="K17" t="n">
-        <v>1.11311752</v>
+        <v>0.08433128999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>0.08433128999999999</v>
+        <v>-0.35153504</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.35153504</v>
+        <v>-0.7377812500000001</v>
       </c>
     </row>
     <row r="18">
@@ -1165,37 +1167,37 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>-1069.80177573</v>
+        <v>-452.58295967</v>
       </c>
       <c r="D18" t="n">
-        <v>-452.59567873</v>
+        <v>-531.6617434799999</v>
       </c>
       <c r="E18" t="n">
-        <v>-531.6740625399999</v>
+        <v>-603.5171211700001</v>
       </c>
       <c r="F18" t="n">
-        <v>-603.34921862</v>
+        <v>-1.170012629999998</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.127325219999998</v>
+        <v>755.74136299</v>
       </c>
       <c r="H18" t="n">
-        <v>755.78596021</v>
+        <v>808.41838966</v>
       </c>
       <c r="I18" t="n">
-        <v>808.41952552</v>
+        <v>20.05482964</v>
       </c>
       <c r="J18" t="n">
-        <v>20.00698698</v>
+        <v>397.91409635</v>
       </c>
       <c r="K18" t="n">
-        <v>397.85688729</v>
+        <v>941.82636841</v>
       </c>
       <c r="L18" t="n">
-        <v>941.7538826699999</v>
+        <v>-199.10421778</v>
       </c>
       <c r="M18" t="n">
-        <v>-199.19026018</v>
+        <v>-682.83194151</v>
       </c>
     </row>
     <row r="19">
@@ -1206,37 +1208,37 @@
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>-3.50220013</v>
+        <v>-0.45935476</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4466357</v>
+        <v>-5.09463389</v>
       </c>
       <c r="E19" t="n">
-        <v>-5.082314830000001</v>
+        <v>-16.04657688</v>
       </c>
       <c r="F19" t="n">
-        <v>-16.21447943</v>
+        <v>-16.7282934</v>
       </c>
       <c r="G19" t="n">
-        <v>-16.77098081</v>
+        <v>-9.796063780000001</v>
       </c>
       <c r="H19" t="n">
-        <v>-9.840661000000001</v>
+        <v>-1.05380141</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.05493727</v>
+        <v>2.68419108</v>
       </c>
       <c r="J19" t="n">
-        <v>2.73203374</v>
+        <v>5.168692590000001</v>
       </c>
       <c r="K19" t="n">
-        <v>5.22590165</v>
+        <v>0.5556269400000001</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6281126800000002</v>
+        <v>-0.8401518099999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7541094099999999</v>
+        <v>-3.47672728</v>
       </c>
     </row>
     <row r="20">
@@ -1247,37 +1249,37 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>6.29112816</v>
+        <v>-11.38791094</v>
       </c>
       <c r="D20" t="n">
-        <v>-11.38791094</v>
+        <v>39.90390299</v>
       </c>
       <c r="E20" t="n">
-        <v>39.90390299</v>
+        <v>-7.499015480000001</v>
       </c>
       <c r="F20" t="n">
-        <v>-7.499015480000001</v>
+        <v>-34.65196079</v>
       </c>
       <c r="G20" t="n">
-        <v>-34.65196079</v>
+        <v>-20.07586818</v>
       </c>
       <c r="H20" t="n">
-        <v>-20.07586818</v>
+        <v>37.03994246</v>
       </c>
       <c r="I20" t="n">
-        <v>37.03994246</v>
+        <v>61.97440654</v>
       </c>
       <c r="J20" t="n">
-        <v>61.97440654</v>
+        <v>4.784528130000001</v>
       </c>
       <c r="K20" t="n">
-        <v>4.784528130000001</v>
+        <v>-26.57971293</v>
       </c>
       <c r="L20" t="n">
-        <v>-26.57971293</v>
+        <v>-51.94192612000001</v>
       </c>
       <c r="M20" t="n">
-        <v>-51.94192612000001</v>
+        <v>-0.42173321</v>
       </c>
     </row>
     <row r="21">
@@ -1286,41 +1288,39 @@
           <t>居家生活右下</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
-        <v>1.74384863</v>
+        <v>2.61610241</v>
       </c>
       <c r="D21" t="n">
-        <v>1.74691358</v>
+        <v>1.28616523</v>
       </c>
       <c r="E21" t="n">
-        <v>1.07924872</v>
+        <v>-2.4394692</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.11526546</v>
+        <v>-7.15915474</v>
       </c>
       <c r="G21" t="n">
-        <v>-7.67942267</v>
+        <v>-1.96615361</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.84958627</v>
+        <v>-1.02725691</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.06654168</v>
+        <v>2.78603437</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6943522100000002</v>
+        <v>1.57257115</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5864628399999998</v>
+        <v>-0.11746601</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.04684694</v>
+        <v>-1.28445344</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.56026058</v>
+        <v>-3.1639559</v>
       </c>
     </row>
     <row r="22">
@@ -1331,37 +1331,37 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>2.26413284</v>
+        <v>1.84201992</v>
       </c>
       <c r="D22" t="n">
-        <v>2.7112108</v>
+        <v>2.06787042</v>
       </c>
       <c r="E22" t="n">
-        <v>2.27478051</v>
+        <v>2.13335201</v>
       </c>
       <c r="F22" t="n">
-        <v>3.80914126</v>
+        <v>0.99293557</v>
       </c>
       <c r="G22" t="n">
-        <v>1.51320008</v>
+        <v>-0.03632125999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8471258</v>
+        <v>0.96951387</v>
       </c>
       <c r="I22" t="n">
-        <v>1.00880626</v>
+        <v>1.21419096</v>
       </c>
       <c r="J22" t="n">
-        <v>3.3058719</v>
+        <v>2.18075152</v>
       </c>
       <c r="K22" t="n">
-        <v>4.33978429</v>
+        <v>0.27020349</v>
       </c>
       <c r="L22" t="n">
-        <v>1.19746172</v>
+        <v>0.9770878199999999</v>
       </c>
       <c r="M22" t="n">
-        <v>1.25147485</v>
+        <v>-0.11773817</v>
       </c>
     </row>
     <row r="23">
@@ -1372,37 +1372,37 @@
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
-        <v>24.20960816</v>
+        <v>17.34516254</v>
       </c>
       <c r="D23" t="n">
-        <v>17.34495134</v>
+        <v>10.97105729</v>
       </c>
       <c r="E23" t="n">
-        <v>10.97104816</v>
+        <v>14.71366628</v>
       </c>
       <c r="F23" t="n">
-        <v>14.7137113</v>
+        <v>25.86071722</v>
       </c>
       <c r="G23" t="n">
-        <v>25.86115714</v>
+        <v>61.50125926</v>
       </c>
       <c r="H23" t="n">
-        <v>61.50186898999999</v>
+        <v>67.72635014999999</v>
       </c>
       <c r="I23" t="n">
-        <v>67.72679253</v>
+        <v>73.11968537</v>
       </c>
       <c r="J23" t="n">
-        <v>73.11998154999999</v>
+        <v>134.38144712</v>
       </c>
       <c r="K23" t="n">
-        <v>134.38158645</v>
+        <v>128.60747793</v>
       </c>
       <c r="L23" t="n">
-        <v>128.60766598</v>
+        <v>54.72903168000001</v>
       </c>
       <c r="M23" t="n">
-        <v>54.72915059</v>
+        <v>-6.258354399999998</v>
       </c>
     </row>
     <row r="24">
@@ -1411,39 +1411,41 @@
           <t>建材營造右下</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
       <c r="C24" t="n">
-        <v>25.4033357</v>
+        <v>-16.31533705</v>
       </c>
       <c r="D24" t="n">
-        <v>9.407099060000002</v>
+        <v>-46.41851334</v>
       </c>
       <c r="E24" t="n">
-        <v>-28.60478166</v>
+        <v>-61.32108313</v>
       </c>
       <c r="F24" t="n">
-        <v>-52.17398673</v>
+        <v>-68.27193079999999</v>
       </c>
       <c r="G24" t="n">
-        <v>-56.72933906</v>
+        <v>-77.0040529</v>
       </c>
       <c r="H24" t="n">
-        <v>-58.07142467</v>
+        <v>-9.682483549999999</v>
       </c>
       <c r="I24" t="n">
-        <v>7.94764037</v>
+        <v>1.74148469</v>
       </c>
       <c r="J24" t="n">
-        <v>15.47102482</v>
+        <v>13.04511441</v>
       </c>
       <c r="K24" t="n">
-        <v>30.43583354</v>
+        <v>7.141467479999999</v>
       </c>
       <c r="L24" t="n">
-        <v>34.01798669</v>
+        <v>-8.145874860000001</v>
       </c>
       <c r="M24" t="n">
-        <v>20.54550917</v>
+        <v>-43.37187738</v>
       </c>
     </row>
     <row r="25">
@@ -1454,37 +1456,37 @@
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>27.44718895</v>
+        <v>37.12761154</v>
       </c>
       <c r="D25" t="n">
-        <v>44.0481345</v>
+        <v>38.26432395</v>
       </c>
       <c r="E25" t="n">
-        <v>41.94677165</v>
+        <v>13.15924753</v>
       </c>
       <c r="F25" t="n">
-        <v>18.17364713</v>
+        <v>20.67896918</v>
       </c>
       <c r="G25" t="n">
-        <v>21.60931035</v>
+        <v>18.91207722</v>
       </c>
       <c r="H25" t="n">
-        <v>18.29554628</v>
+        <v>5.190265300000001</v>
       </c>
       <c r="I25" t="n">
-        <v>9.43256483</v>
+        <v>29.06947743</v>
       </c>
       <c r="J25" t="n">
-        <v>38.23987602</v>
+        <v>34.67251390000001</v>
       </c>
       <c r="K25" t="n">
-        <v>35.05095730000001</v>
+        <v>48.58322851</v>
       </c>
       <c r="L25" t="n">
-        <v>41.8600014</v>
+        <v>3.014457449999998</v>
       </c>
       <c r="M25" t="n">
-        <v>-13.67264728</v>
+        <v>-49.21154851</v>
       </c>
     </row>
     <row r="26">
@@ -1495,37 +1497,37 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>8.953501469999999</v>
+        <v>5.88787313</v>
       </c>
       <c r="D26" t="n">
-        <v>5.88787313</v>
+        <v>7.593937100000001</v>
       </c>
       <c r="E26" t="n">
-        <v>7.593937100000001</v>
+        <v>5.17181729</v>
       </c>
       <c r="F26" t="n">
-        <v>5.17181729</v>
+        <v>7.592146520000001</v>
       </c>
       <c r="G26" t="n">
-        <v>7.592146520000001</v>
+        <v>18.69060947</v>
       </c>
       <c r="H26" t="n">
-        <v>18.69060947</v>
+        <v>6.72654781</v>
       </c>
       <c r="I26" t="n">
-        <v>6.72654781</v>
+        <v>5.82618834</v>
       </c>
       <c r="J26" t="n">
-        <v>5.82618834</v>
+        <v>6.19496605</v>
       </c>
       <c r="K26" t="n">
-        <v>6.19496605</v>
+        <v>7.53425048</v>
       </c>
       <c r="L26" t="n">
-        <v>7.53425048</v>
+        <v>1.57906642</v>
       </c>
       <c r="M26" t="n">
-        <v>1.57906642</v>
+        <v>-2.91136613</v>
       </c>
     </row>
     <row r="27">
@@ -1536,37 +1538,37 @@
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>21.41594651</v>
+        <v>9.126986050000001</v>
       </c>
       <c r="D27" t="n">
-        <v>9.254340819999999</v>
+        <v>22.17120965</v>
       </c>
       <c r="E27" t="n">
-        <v>20.89016642</v>
+        <v>17.62114185</v>
       </c>
       <c r="F27" t="n">
-        <v>17.74083201</v>
+        <v>22.73835175</v>
       </c>
       <c r="G27" t="n">
-        <v>22.20219834</v>
+        <v>29.64031750000001</v>
       </c>
       <c r="H27" t="n">
-        <v>32.01863252</v>
+        <v>34.23960959</v>
       </c>
       <c r="I27" t="n">
-        <v>32.91413802</v>
+        <v>34.65264778</v>
       </c>
       <c r="J27" t="n">
-        <v>31.9022584</v>
+        <v>21.38763383</v>
       </c>
       <c r="K27" t="n">
-        <v>15.84968732</v>
+        <v>21.65209811</v>
       </c>
       <c r="L27" t="n">
-        <v>15.5018982</v>
+        <v>13.90380849</v>
       </c>
       <c r="M27" t="n">
-        <v>7.184865029999999</v>
+        <v>4.021312670000001</v>
       </c>
     </row>
     <row r="28">
@@ -1577,37 +1579,37 @@
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>3.95173604</v>
+        <v>-27.74334681</v>
       </c>
       <c r="D28" t="n">
-        <v>-27.67383012</v>
+        <v>-47.7503726</v>
       </c>
       <c r="E28" t="n">
-        <v>-47.67117451</v>
+        <v>-79.88660898000001</v>
       </c>
       <c r="F28" t="n">
-        <v>-79.82541303000001</v>
+        <v>-109.77231518</v>
       </c>
       <c r="G28" t="n">
-        <v>-109.72696506</v>
+        <v>-102.98757115</v>
       </c>
       <c r="H28" t="n">
-        <v>-102.93766366</v>
+        <v>-89.84861438999999</v>
       </c>
       <c r="I28" t="n">
-        <v>-89.79266072999999</v>
+        <v>-73.97514631</v>
       </c>
       <c r="J28" t="n">
-        <v>-73.93321212000001</v>
+        <v>-58.79575538</v>
       </c>
       <c r="K28" t="n">
-        <v>-58.76314611999999</v>
+        <v>-32.16641504</v>
       </c>
       <c r="L28" t="n">
-        <v>-32.14095302</v>
+        <v>-29.40265683</v>
       </c>
       <c r="M28" t="n">
-        <v>-29.38440493</v>
+        <v>-32.3931544</v>
       </c>
     </row>
     <row r="29">
@@ -1618,37 +1620,37 @@
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>0.08414062</v>
+        <v>0.07506878</v>
       </c>
       <c r="D29" t="n">
-        <v>0.07506878</v>
+        <v>0.03323846</v>
       </c>
       <c r="E29" t="n">
-        <v>0.03323846</v>
+        <v>0.00619917</v>
       </c>
       <c r="F29" t="n">
-        <v>0.00619917</v>
+        <v>0.01277118</v>
       </c>
       <c r="G29" t="n">
-        <v>0.01277118</v>
+        <v>-0.00653676</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.00653676</v>
+        <v>-0.01623805</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.01623805</v>
+        <v>-0.01854561</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.01854561</v>
+        <v>-0.0214375</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.0214375</v>
+        <v>-0.00590779</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.00590779</v>
+        <v>0.007246020000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>0.007246020000000001</v>
+        <v>0.04125581</v>
       </c>
     </row>
     <row r="30">
@@ -1657,41 +1659,39 @@
           <t>文化創意業右下</t>
         </is>
       </c>
-      <c r="B30" t="n">
-        <v>0</v>
-      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>0.0102936</v>
+        <v>0.00536903</v>
       </c>
       <c r="D30" t="n">
-        <v>0.005392780000000001</v>
+        <v>0.01213361</v>
       </c>
       <c r="E30" t="n">
-        <v>0.01211806</v>
+        <v>0.0007921299999999998</v>
       </c>
       <c r="F30" t="n">
-        <v>0.00088056</v>
+        <v>-0.00470349</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.00458671</v>
+        <v>-0.005675059999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.00565963</v>
+        <v>-0.00690276</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.006874069999999999</v>
+        <v>0.01012549</v>
       </c>
       <c r="J30" t="n">
-        <v>0.01007853</v>
+        <v>0.00217369</v>
       </c>
       <c r="K30" t="n">
-        <v>0.0022248</v>
+        <v>0.00358807</v>
       </c>
       <c r="L30" t="n">
-        <v>0.003635520000000001</v>
+        <v>0.00154582</v>
       </c>
       <c r="M30" t="n">
-        <v>0.00158488</v>
+        <v>-0.0008311099999999996</v>
       </c>
     </row>
     <row r="31">
@@ -1702,37 +1702,37 @@
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>0.21751282</v>
+        <v>0.10937909</v>
       </c>
       <c r="D31" t="n">
-        <v>0.10936104</v>
+        <v>0.03921261</v>
       </c>
       <c r="E31" t="n">
-        <v>0.03924989</v>
+        <v>-0.01164912</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.01166996</v>
+        <v>-0.05282732</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.05285173000000001</v>
+        <v>-0.09472982000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.09475462</v>
+        <v>-0.18498163</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1850039</v>
+        <v>0.003500399999999999</v>
       </c>
       <c r="J31" t="n">
-        <v>0.0035406</v>
+        <v>-0.03699097</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.03696819</v>
+        <v>0.20997069</v>
       </c>
       <c r="L31" t="n">
-        <v>0.20996728</v>
+        <v>0.08271654000000001</v>
       </c>
       <c r="M31" t="n">
-        <v>0.08270688000000001</v>
+        <v>-0.01967012</v>
       </c>
     </row>
     <row r="32">
@@ -1743,37 +1743,37 @@
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>-15.01818866</v>
+        <v>0.4845926899999997</v>
       </c>
       <c r="D32" t="n">
-        <v>-18.7437909</v>
+        <v>-20.67803373</v>
       </c>
       <c r="E32" t="n">
-        <v>-21.51308012</v>
+        <v>-32.15445803</v>
       </c>
       <c r="F32" t="n">
-        <v>-26.23204626999999</v>
+        <v>-40.28821612</v>
       </c>
       <c r="G32" t="n">
-        <v>-28.63820698</v>
+        <v>-16.20914258</v>
       </c>
       <c r="H32" t="n">
-        <v>-10.76783712</v>
+        <v>-19.13381427</v>
       </c>
       <c r="I32" t="n">
-        <v>-20.0377565</v>
+        <v>-10.30184885</v>
       </c>
       <c r="J32" t="n">
-        <v>-6.47922948</v>
+        <v>-13.95881996</v>
       </c>
       <c r="K32" t="n">
-        <v>-21.67391496</v>
+        <v>16.5897552</v>
       </c>
       <c r="L32" t="n">
-        <v>5.52792584</v>
+        <v>21.57479981</v>
       </c>
       <c r="M32" t="n">
-        <v>7.32848074</v>
+        <v>10.77240005</v>
       </c>
     </row>
     <row r="33">
@@ -1784,37 +1784,37 @@
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
-        <v>4.3513519</v>
+        <v>2.92653785</v>
       </c>
       <c r="D33" t="n">
-        <v>22.15492144</v>
+        <v>0.4812992</v>
       </c>
       <c r="E33" t="n">
-        <v>1.31634559</v>
+        <v>-1.10311971</v>
       </c>
       <c r="F33" t="n">
-        <v>-7.02553147</v>
+        <v>-3.2016798</v>
       </c>
       <c r="G33" t="n">
-        <v>-14.85168894</v>
+        <v>-1.87034995</v>
       </c>
       <c r="H33" t="n">
-        <v>-7.31165541</v>
+        <v>-2.31543645</v>
       </c>
       <c r="I33" t="n">
-        <v>-1.41149422</v>
+        <v>-4.02921888</v>
       </c>
       <c r="J33" t="n">
-        <v>-7.85183825</v>
+        <v>-1.65893927</v>
       </c>
       <c r="K33" t="n">
-        <v>6.05615573</v>
+        <v>-0.68169719</v>
       </c>
       <c r="L33" t="n">
-        <v>10.38013217</v>
+        <v>-0.1804759</v>
       </c>
       <c r="M33" t="n">
-        <v>14.06584317</v>
+        <v>-1.24122729</v>
       </c>
     </row>
     <row r="34">
@@ -1825,37 +1825,37 @@
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
-        <v>34.050435</v>
+        <v>53.00901164</v>
       </c>
       <c r="D34" t="n">
-        <v>53.00901164</v>
+        <v>23.37416052</v>
       </c>
       <c r="E34" t="n">
-        <v>23.37416052</v>
+        <v>33.49646586</v>
       </c>
       <c r="F34" t="n">
-        <v>33.49646586</v>
+        <v>42.38292683</v>
       </c>
       <c r="G34" t="n">
-        <v>42.38292683</v>
+        <v>53.14078301</v>
       </c>
       <c r="H34" t="n">
-        <v>53.14078301</v>
+        <v>77.31264456</v>
       </c>
       <c r="I34" t="n">
-        <v>77.31264456</v>
+        <v>-99.06594910000001</v>
       </c>
       <c r="J34" t="n">
-        <v>-99.06594910000001</v>
+        <v>-137.71287059</v>
       </c>
       <c r="K34" t="n">
-        <v>-137.71287059</v>
+        <v>-36.98264507</v>
       </c>
       <c r="L34" t="n">
-        <v>-36.98264507</v>
+        <v>-110.28325571</v>
       </c>
       <c r="M34" t="n">
-        <v>-110.28325571</v>
+        <v>-29.94653585</v>
       </c>
     </row>
     <row r="35">
@@ -1866,37 +1866,37 @@
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
-        <v>-0.5541974000000001</v>
+        <v>-0.86426467</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.86426467</v>
+        <v>-1.03027462</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.03027462</v>
+        <v>-0.0252352</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.0252352</v>
+        <v>-0.03013220000000001</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.03013220000000001</v>
+        <v>3.18854859</v>
       </c>
       <c r="H35" t="n">
-        <v>3.18854859</v>
+        <v>2.605460190000001</v>
       </c>
       <c r="I35" t="n">
-        <v>2.605460190000001</v>
+        <v>4.13401164</v>
       </c>
       <c r="J35" t="n">
-        <v>4.13401164</v>
+        <v>4.72190981</v>
       </c>
       <c r="K35" t="n">
-        <v>4.72190981</v>
+        <v>5.98762434</v>
       </c>
       <c r="L35" t="n">
-        <v>5.98762434</v>
+        <v>2.37916882</v>
       </c>
       <c r="M35" t="n">
-        <v>2.37916882</v>
+        <v>-0.53526386</v>
       </c>
     </row>
     <row r="36">
@@ -1907,37 +1907,37 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>179.98748556</v>
+        <v>205.82422216</v>
       </c>
       <c r="D36" t="n">
-        <v>243.01780536</v>
+        <v>112.08474924</v>
       </c>
       <c r="E36" t="n">
-        <v>120.77072082</v>
+        <v>201.10258552</v>
       </c>
       <c r="F36" t="n">
-        <v>227.54441106</v>
+        <v>264.13111271</v>
       </c>
       <c r="G36" t="n">
-        <v>364.58955555</v>
+        <v>172.4178389</v>
       </c>
       <c r="H36" t="n">
-        <v>215.34440896</v>
+        <v>136.92221049</v>
       </c>
       <c r="I36" t="n">
-        <v>203.11277483</v>
+        <v>18.18229482</v>
       </c>
       <c r="J36" t="n">
-        <v>-9.032017559999998</v>
+        <v>186.7382784</v>
       </c>
       <c r="K36" t="n">
-        <v>184.61897931</v>
+        <v>-26.1190374</v>
       </c>
       <c r="L36" t="n">
-        <v>4.745168009999998</v>
+        <v>-145.80769051</v>
       </c>
       <c r="M36" t="n">
-        <v>-97.09928714</v>
+        <v>-91.33632412999999</v>
       </c>
     </row>
     <row r="37">
@@ -1948,37 +1948,37 @@
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>40.78875832</v>
+        <v>44.36718017</v>
       </c>
       <c r="D37" t="n">
-        <v>47.36219706</v>
+        <v>47.02422203</v>
       </c>
       <c r="E37" t="n">
-        <v>48.34040938</v>
+        <v>-9.668723299999998</v>
       </c>
       <c r="F37" t="n">
-        <v>4.062234399999999</v>
+        <v>10.93613627</v>
       </c>
       <c r="G37" t="n">
-        <v>3.04155708</v>
+        <v>59.2642467</v>
       </c>
       <c r="H37" t="n">
-        <v>30.92171678</v>
+        <v>15.98931635</v>
       </c>
       <c r="I37" t="n">
-        <v>9.269855889999999</v>
+        <v>19.55677792</v>
       </c>
       <c r="J37" t="n">
-        <v>27.09746122</v>
+        <v>2.64621305</v>
       </c>
       <c r="K37" t="n">
-        <v>7.489372550000001</v>
+        <v>25.57220427</v>
       </c>
       <c r="L37" t="n">
-        <v>29.27701968</v>
+        <v>4.312316109999998</v>
       </c>
       <c r="M37" t="n">
-        <v>6.686107529999997</v>
+        <v>-61.2942177</v>
       </c>
     </row>
     <row r="38">
@@ -1989,37 +1989,37 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>52.94766575999999</v>
+        <v>18.76998959000001</v>
       </c>
       <c r="D38" t="n">
-        <v>15.77497270000001</v>
+        <v>-38.09471417</v>
       </c>
       <c r="E38" t="n">
-        <v>-39.41090152</v>
+        <v>-49.86970338</v>
       </c>
       <c r="F38" t="n">
-        <v>-63.60066107999999</v>
+        <v>-21.92375551</v>
       </c>
       <c r="G38" t="n">
-        <v>-14.02917632</v>
+        <v>5.972689210000001</v>
       </c>
       <c r="H38" t="n">
-        <v>34.31521913</v>
+        <v>29.37988966</v>
       </c>
       <c r="I38" t="n">
-        <v>36.09935012</v>
+        <v>-21.33947604</v>
       </c>
       <c r="J38" t="n">
-        <v>-28.88015934</v>
+        <v>7.001465090000003</v>
       </c>
       <c r="K38" t="n">
-        <v>2.15830559</v>
+        <v>-42.26410757</v>
       </c>
       <c r="L38" t="n">
-        <v>-45.70276733</v>
+        <v>-107.25360982</v>
       </c>
       <c r="M38" t="n">
-        <v>-110.970004</v>
+        <v>-125.20318794</v>
       </c>
     </row>
     <row r="39">
@@ -2030,37 +2030,37 @@
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
-        <v>3.22631047</v>
+        <v>8.135896049999999</v>
       </c>
       <c r="D39" t="n">
-        <v>8.135896049999999</v>
+        <v>0.42597227</v>
       </c>
       <c r="E39" t="n">
-        <v>0.42597227</v>
+        <v>5.236759269999999</v>
       </c>
       <c r="F39" t="n">
-        <v>5.236759269999999</v>
+        <v>24.80576117</v>
       </c>
       <c r="G39" t="n">
-        <v>24.80576117</v>
+        <v>21.99748971</v>
       </c>
       <c r="H39" t="n">
-        <v>21.99748971</v>
+        <v>7.5667577</v>
       </c>
       <c r="I39" t="n">
-        <v>7.5667577</v>
+        <v>-0.39082327</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.39082327</v>
+        <v>6.9156605</v>
       </c>
       <c r="K39" t="n">
-        <v>6.9156605</v>
+        <v>-3.65105099</v>
       </c>
       <c r="L39" t="n">
-        <v>-3.65105099</v>
+        <v>5.96885178</v>
       </c>
       <c r="M39" t="n">
-        <v>5.96885178</v>
+        <v>-4.14332239</v>
       </c>
     </row>
     <row r="40">
@@ -2071,37 +2071,37 @@
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>-65.26585011</v>
+        <v>-32.772473</v>
       </c>
       <c r="D40" t="n">
-        <v>-32.772473</v>
+        <v>-17.85393562</v>
       </c>
       <c r="E40" t="n">
-        <v>-17.85393562</v>
+        <v>-34.21927984000001</v>
       </c>
       <c r="F40" t="n">
-        <v>-34.21927984000001</v>
+        <v>-18.29832132</v>
       </c>
       <c r="G40" t="n">
-        <v>-18.29832132</v>
+        <v>16.51942199</v>
       </c>
       <c r="H40" t="n">
-        <v>16.51942199</v>
+        <v>-19.21069481</v>
       </c>
       <c r="I40" t="n">
-        <v>-19.21069481</v>
+        <v>-76.86549835</v>
       </c>
       <c r="J40" t="n">
-        <v>-76.86549835</v>
+        <v>-32.5970419</v>
       </c>
       <c r="K40" t="n">
-        <v>-32.5970419</v>
+        <v>-50.29811102</v>
       </c>
       <c r="L40" t="n">
-        <v>-50.29811102</v>
+        <v>-89.72822392</v>
       </c>
       <c r="M40" t="n">
-        <v>-89.72822392</v>
+        <v>-81.92920619</v>
       </c>
     </row>
     <row r="41">
@@ -2112,37 +2112,37 @@
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
-        <v>9.454000000000001e-05</v>
+        <v>-0.00014463</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.00014463</v>
+        <v>-7.391e-05</v>
       </c>
       <c r="E41" t="n">
-        <v>-7.391e-05</v>
+        <v>-2.001e-05</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.001e-05</v>
+        <v>4.417e-05</v>
       </c>
       <c r="G41" t="n">
-        <v>4.417e-05</v>
+        <v>9.085e-05</v>
       </c>
       <c r="H41" t="n">
-        <v>9.085e-05</v>
+        <v>-7.104999999999999e-05</v>
       </c>
       <c r="I41" t="n">
-        <v>-7.104999999999999e-05</v>
+        <v>-0.00022371</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.00022371</v>
+        <v>-0.00012</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.00012</v>
+        <v>-0.00023445</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.00023445</v>
+        <v>-0.00035108</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.00035108</v>
+        <v>-0.00043212</v>
       </c>
     </row>
     <row r="42">
@@ -2153,37 +2153,37 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>-68.75579565</v>
+        <v>-42.95356518</v>
       </c>
       <c r="D42" t="n">
-        <v>-25.65882652</v>
+        <v>-209.92976809</v>
       </c>
       <c r="E42" t="n">
-        <v>-203.34503687</v>
+        <v>-24.7706204</v>
       </c>
       <c r="F42" t="n">
-        <v>-26.00127152</v>
+        <v>154.56242497</v>
       </c>
       <c r="G42" t="n">
-        <v>156.76665614</v>
+        <v>569.9204095299999</v>
       </c>
       <c r="H42" t="n">
-        <v>578.4989785</v>
+        <v>879.95625971</v>
       </c>
       <c r="I42" t="n">
-        <v>900.52032724</v>
+        <v>1190.48956757</v>
       </c>
       <c r="J42" t="n">
-        <v>1153.82319753</v>
+        <v>1271.44494553</v>
       </c>
       <c r="K42" t="n">
-        <v>1252.18441714</v>
+        <v>1277.79570934</v>
       </c>
       <c r="L42" t="n">
-        <v>1286.18806609</v>
+        <v>-591.18301373</v>
       </c>
       <c r="M42" t="n">
-        <v>-596.5809266700001</v>
+        <v>-815.56774821</v>
       </c>
     </row>
     <row r="43">
@@ -2194,37 +2194,37 @@
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
-        <v>1.46585581</v>
+        <v>18.45296431</v>
       </c>
       <c r="D43" t="n">
-        <v>1.15822565</v>
+        <v>5.039715139999999</v>
       </c>
       <c r="E43" t="n">
-        <v>-1.54501608</v>
+        <v>-4.01613703</v>
       </c>
       <c r="F43" t="n">
-        <v>-2.785485910000001</v>
+        <v>-0.5236189</v>
       </c>
       <c r="G43" t="n">
-        <v>-2.72785007</v>
+        <v>12.23212643</v>
       </c>
       <c r="H43" t="n">
-        <v>3.65355746</v>
+        <v>41.41266073000001</v>
       </c>
       <c r="I43" t="n">
-        <v>20.8485932</v>
+        <v>-2.399140199999998</v>
       </c>
       <c r="J43" t="n">
-        <v>34.26722984000001</v>
+        <v>19.34848593</v>
       </c>
       <c r="K43" t="n">
-        <v>38.60901432</v>
+        <v>46.03279432</v>
       </c>
       <c r="L43" t="n">
-        <v>37.64043757</v>
+        <v>6.63547855</v>
       </c>
       <c r="M43" t="n">
-        <v>12.03339149</v>
+        <v>-12.07906279</v>
       </c>
     </row>
     <row r="44">
@@ -2235,37 +2235,37 @@
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>14.29967463</v>
+        <v>17.13178991</v>
       </c>
       <c r="D44" t="n">
-        <v>16.9019166</v>
+        <v>4.96132119</v>
       </c>
       <c r="E44" t="n">
-        <v>5.002261640000003</v>
+        <v>11.88326792</v>
       </c>
       <c r="F44" t="n">
-        <v>12.13699712</v>
+        <v>11.99605395000001</v>
       </c>
       <c r="G44" t="n">
-        <v>12.44531902</v>
+        <v>10.73998824</v>
       </c>
       <c r="H44" t="n">
-        <v>10.95086562</v>
+        <v>-8.907901220000001</v>
       </c>
       <c r="I44" t="n">
-        <v>-8.826540080000003</v>
+        <v>-21.06634319</v>
       </c>
       <c r="J44" t="n">
-        <v>-21.12212905</v>
+        <v>-25.51101711</v>
       </c>
       <c r="K44" t="n">
-        <v>-25.33887335</v>
+        <v>-20.91638141</v>
       </c>
       <c r="L44" t="n">
-        <v>-20.50910314</v>
+        <v>-9.859126460000001</v>
       </c>
       <c r="M44" t="n">
-        <v>-9.32173066</v>
+        <v>-15.5341533</v>
       </c>
     </row>
     <row r="45">
@@ -2278,37 +2278,37 @@
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>11.07060200000001</v>
+        <v>34.74102881</v>
       </c>
       <c r="D45" t="n">
-        <v>34.26786155000001</v>
+        <v>122.44112911</v>
       </c>
       <c r="E45" t="n">
-        <v>122.41482328</v>
+        <v>263.40352697</v>
       </c>
       <c r="F45" t="n">
-        <v>263.12835826</v>
+        <v>96.87998216000003</v>
       </c>
       <c r="G45" t="n">
-        <v>96.53880563000003</v>
+        <v>184.55389075</v>
       </c>
       <c r="H45" t="n">
-        <v>183.63272959</v>
+        <v>197.80873071</v>
       </c>
       <c r="I45" t="n">
-        <v>198.4700732</v>
+        <v>293.41731848</v>
       </c>
       <c r="J45" t="n">
-        <v>293.16865939</v>
+        <v>426.02240409</v>
       </c>
       <c r="K45" t="n">
-        <v>426.18412531</v>
+        <v>555.4999105099999</v>
       </c>
       <c r="L45" t="n">
-        <v>555.23315785</v>
+        <v>773.0920901900001</v>
       </c>
       <c r="M45" t="n">
-        <v>773.5621615300001</v>
+        <v>1234.26724926</v>
       </c>
     </row>
     <row r="46">
@@ -2319,37 +2319,37 @@
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>90.33122224999998</v>
+        <v>-5.739201689999998</v>
       </c>
       <c r="D46" t="n">
-        <v>-4.924683899999998</v>
+        <v>72.82681453999999</v>
       </c>
       <c r="E46" t="n">
-        <v>72.87505576999999</v>
+        <v>50.53460386999999</v>
       </c>
       <c r="F46" t="n">
-        <v>50.68055956999999</v>
+        <v>-59.42225436</v>
       </c>
       <c r="G46" t="n">
-        <v>-59.63001799</v>
+        <v>75.12495246</v>
       </c>
       <c r="H46" t="n">
-        <v>75.83161161</v>
+        <v>106.8370172</v>
       </c>
       <c r="I46" t="n">
-        <v>105.94402623</v>
+        <v>248.24594157</v>
       </c>
       <c r="J46" t="n">
-        <v>248.31095814</v>
+        <v>66.83976742999999</v>
       </c>
       <c r="K46" t="n">
-        <v>66.21656041</v>
+        <v>-61.59740323</v>
       </c>
       <c r="L46" t="n">
-        <v>-62.84952854</v>
+        <v>-146.5239308</v>
       </c>
       <c r="M46" t="n">
-        <v>-147.24993142</v>
+        <v>-137.20722078</v>
       </c>
     </row>
     <row r="47">
@@ -2360,37 +2360,37 @@
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>-6.2041725</v>
+        <v>-1.55805487</v>
       </c>
       <c r="D47" t="n">
-        <v>-3.20158006</v>
+        <v>0.2128199</v>
       </c>
       <c r="E47" t="n">
-        <v>1.12057703</v>
+        <v>0.11380938</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.37868869</v>
+        <v>-1.16393911</v>
       </c>
       <c r="G47" t="n">
-        <v>-3.99151647</v>
+        <v>3.26730915</v>
       </c>
       <c r="H47" t="n">
-        <v>2.80991257</v>
+        <v>1.63955288</v>
       </c>
       <c r="I47" t="n">
-        <v>15.48498561</v>
+        <v>0.7404075099999999</v>
       </c>
       <c r="J47" t="n">
-        <v>62.07577929</v>
+        <v>2.84180396</v>
       </c>
       <c r="K47" t="n">
-        <v>95.45228308</v>
+        <v>3.94008714</v>
       </c>
       <c r="L47" t="n">
-        <v>201.70015159</v>
+        <v>4.28278438</v>
       </c>
       <c r="M47" t="n">
-        <v>314.31583016</v>
+        <v>1.74077493</v>
       </c>
     </row>
     <row r="48">
@@ -2399,39 +2399,41 @@
           <t>紡織纖維右下</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
+      <c r="B48" t="n">
+        <v>0</v>
+      </c>
       <c r="C48" t="n">
-        <v>6.876008539999998</v>
+        <v>1.470755140000002</v>
       </c>
       <c r="D48" t="n">
-        <v>-21.01691342</v>
+        <v>18.96919007</v>
       </c>
       <c r="E48" t="n">
-        <v>-15.13194856</v>
+        <v>-20.28660042</v>
       </c>
       <c r="F48" t="n">
-        <v>-100.97582182</v>
+        <v>-80.24432846000001</v>
       </c>
       <c r="G48" t="n">
-        <v>-162.47494265</v>
+        <v>-99.69417993</v>
       </c>
       <c r="H48" t="n">
-        <v>-138.91383049</v>
+        <v>-59.87145587</v>
       </c>
       <c r="I48" t="n">
-        <v>-65.78406750000001</v>
+        <v>20.9288823</v>
       </c>
       <c r="J48" t="n">
-        <v>100.66741346</v>
+        <v>46.60395298</v>
       </c>
       <c r="K48" t="n">
-        <v>167.30680064</v>
+        <v>32.49431972</v>
       </c>
       <c r="L48" t="n">
-        <v>94.00985389</v>
+        <v>0.7880856500000022</v>
       </c>
       <c r="M48" t="n">
-        <v>31.25882024</v>
+        <v>15.49087174</v>
       </c>
     </row>
     <row r="49">
@@ -2442,37 +2444,37 @@
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>1.32682909</v>
+        <v>-1.34135238</v>
       </c>
       <c r="D49" t="n">
-        <v>0.25557084</v>
+        <v>0.8862975200000001</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.002220260000000012</v>
+        <v>-0.6830073800000001</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.21206577</v>
+        <v>-3.18095136</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.3229723599999999</v>
+        <v>-1.0886851</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.64211001</v>
+        <v>13.1180532</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.68773007</v>
+        <v>60.53762608</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.8016744100000001</v>
+        <v>92.04177723000001</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.6050358499999999</v>
+        <v>197.69451778</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.16058108</v>
+        <v>309.63768162</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.4915954</v>
+        <v>124.56556053</v>
       </c>
     </row>
     <row r="50">
@@ -2483,37 +2485,37 @@
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
-        <v>-6.442285149999996</v>
+        <v>-118.5355461</v>
       </c>
       <c r="D50" t="n">
-        <v>-116.60320089</v>
+        <v>48.67417623000001</v>
       </c>
       <c r="E50" t="n">
-        <v>51.08673258</v>
+        <v>-68.17846678999999</v>
       </c>
       <c r="F50" t="n">
-        <v>-67.32971089999999</v>
+        <v>-51.11842820000001</v>
       </c>
       <c r="G50" t="n">
-        <v>-49.9699323</v>
+        <v>-32.7785758</v>
       </c>
       <c r="H50" t="n">
-        <v>-34.87113519</v>
+        <v>-99.73463743000001</v>
       </c>
       <c r="I50" t="n">
-        <v>-101.83529897</v>
+        <v>-19.73116191999999</v>
       </c>
       <c r="J50" t="n">
-        <v>-20.18952884999999</v>
+        <v>59.53426253</v>
       </c>
       <c r="K50" t="n">
-        <v>60.03399915</v>
+        <v>46.45680000999999</v>
       </c>
       <c r="L50" t="n">
-        <v>46.57401195000001</v>
+        <v>94.52176788</v>
       </c>
       <c r="M50" t="n">
-        <v>94.33851032</v>
+        <v>-54.93532402</v>
       </c>
     </row>
     <row r="51">
@@ -2524,37 +2526,37 @@
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>4.03323023</v>
+        <v>-4.208008479999999</v>
       </c>
       <c r="D51" t="n">
-        <v>-4.208008479999999</v>
+        <v>-16.668004</v>
       </c>
       <c r="E51" t="n">
-        <v>-16.668004</v>
+        <v>-17.31000216</v>
       </c>
       <c r="F51" t="n">
-        <v>-17.31000216</v>
+        <v>-27.00119206</v>
       </c>
       <c r="G51" t="n">
-        <v>-27.00119206</v>
+        <v>-37.85262138</v>
       </c>
       <c r="H51" t="n">
-        <v>-37.85262138</v>
+        <v>-40.22165305999999</v>
       </c>
       <c r="I51" t="n">
-        <v>-40.22165305999999</v>
+        <v>-40.80044587</v>
       </c>
       <c r="J51" t="n">
-        <v>-40.80044587</v>
+        <v>-105.72065853</v>
       </c>
       <c r="K51" t="n">
-        <v>-105.72065853</v>
+        <v>-88.20215075</v>
       </c>
       <c r="L51" t="n">
-        <v>-88.20215075</v>
+        <v>-78.58694362999999</v>
       </c>
       <c r="M51" t="n">
-        <v>-78.58694362999999</v>
+        <v>-59.1372507</v>
       </c>
     </row>
     <row r="52">
@@ -2565,37 +2567,37 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>23.55595313</v>
+        <v>23.24927058</v>
       </c>
       <c r="D52" t="n">
-        <v>23.24927058</v>
+        <v>10.98503399</v>
       </c>
       <c r="E52" t="n">
-        <v>10.98503399</v>
+        <v>14.36571771</v>
       </c>
       <c r="F52" t="n">
-        <v>14.36571771</v>
+        <v>-7.093245320000001</v>
       </c>
       <c r="G52" t="n">
-        <v>-7.093245320000001</v>
+        <v>3.776879930000002</v>
       </c>
       <c r="H52" t="n">
-        <v>3.776879930000002</v>
+        <v>-0.599055200000002</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.599055200000002</v>
+        <v>-25.3277558</v>
       </c>
       <c r="J52" t="n">
-        <v>-25.3277558</v>
+        <v>-25.32132348</v>
       </c>
       <c r="K52" t="n">
-        <v>-25.32132348</v>
+        <v>-2.890964619999999</v>
       </c>
       <c r="L52" t="n">
-        <v>-2.890964619999999</v>
+        <v>-8.700042229999999</v>
       </c>
       <c r="M52" t="n">
-        <v>-8.700042229999999</v>
+        <v>-18.52731013</v>
       </c>
     </row>
     <row r="53">
@@ -2606,37 +2608,37 @@
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>734.9058153899999</v>
+        <v>788.96935349</v>
       </c>
       <c r="D53" t="n">
-        <v>788.96935349</v>
+        <v>202.71825148</v>
       </c>
       <c r="E53" t="n">
-        <v>202.71825148</v>
+        <v>185.63987332</v>
       </c>
       <c r="F53" t="n">
-        <v>185.63987332</v>
+        <v>413.37287971</v>
       </c>
       <c r="G53" t="n">
-        <v>413.37287971</v>
+        <v>382.52006728</v>
       </c>
       <c r="H53" t="n">
-        <v>382.52006728</v>
+        <v>788.81984295</v>
       </c>
       <c r="I53" t="n">
-        <v>788.81984295</v>
+        <v>536.01880756</v>
       </c>
       <c r="J53" t="n">
-        <v>536.01880756</v>
+        <v>663.41942352</v>
       </c>
       <c r="K53" t="n">
-        <v>663.41942352</v>
+        <v>832.86466129</v>
       </c>
       <c r="L53" t="n">
-        <v>832.86466129</v>
+        <v>148.04517125</v>
       </c>
       <c r="M53" t="n">
-        <v>148.04517125</v>
+        <v>92.40368975999999</v>
       </c>
     </row>
     <row r="54">
@@ -2647,37 +2649,37 @@
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>5.94735249</v>
+        <v>79.96259970999999</v>
       </c>
       <c r="D54" t="n">
-        <v>23.83820258</v>
+        <v>53.38682709</v>
       </c>
       <c r="E54" t="n">
-        <v>29.98847398</v>
+        <v>71.14172211</v>
       </c>
       <c r="F54" t="n">
-        <v>32.85000479</v>
+        <v>5.673030960000003</v>
       </c>
       <c r="G54" t="n">
-        <v>27.25000905</v>
+        <v>29.67370817</v>
       </c>
       <c r="H54" t="n">
-        <v>58.22860823000001</v>
+        <v>45.69961662999999</v>
       </c>
       <c r="I54" t="n">
-        <v>28.42361836</v>
+        <v>81.70161845</v>
       </c>
       <c r="J54" t="n">
-        <v>27.12037651</v>
+        <v>28.41798539</v>
       </c>
       <c r="K54" t="n">
-        <v>4.33543982</v>
+        <v>55.00752722</v>
       </c>
       <c r="L54" t="n">
-        <v>4.657683560000001</v>
+        <v>4.253341999999999</v>
       </c>
       <c r="M54" t="n">
-        <v>-6.665553060000001</v>
+        <v>-55.55444215</v>
       </c>
     </row>
     <row r="55">
@@ -2688,37 +2690,37 @@
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>-87.59608303</v>
+        <v>-35.82735756000002</v>
       </c>
       <c r="D55" t="n">
-        <v>20.29703956999999</v>
+        <v>-369.24727488</v>
       </c>
       <c r="E55" t="n">
-        <v>-345.84892177</v>
+        <v>193.26249032</v>
       </c>
       <c r="F55" t="n">
-        <v>231.55420764</v>
+        <v>112.7452643</v>
       </c>
       <c r="G55" t="n">
-        <v>91.16828621000002</v>
+        <v>347.3506383499999</v>
       </c>
       <c r="H55" t="n">
-        <v>318.79573829</v>
+        <v>-90.35078726999998</v>
       </c>
       <c r="I55" t="n">
-        <v>-73.07478899999998</v>
+        <v>0.9821928799999957</v>
       </c>
       <c r="J55" t="n">
-        <v>55.56343482</v>
+        <v>-162.26911974</v>
       </c>
       <c r="K55" t="n">
-        <v>-138.18657417</v>
+        <v>-50.20526632000001</v>
       </c>
       <c r="L55" t="n">
-        <v>0.1445773399999785</v>
+        <v>-405.87238641</v>
       </c>
       <c r="M55" t="n">
-        <v>-394.95349135</v>
+        <v>-502.9824038</v>
       </c>
     </row>
     <row r="56">
@@ -2729,37 +2731,37 @@
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>-1.98122254</v>
+        <v>-4.11638705</v>
       </c>
       <c r="D56" t="n">
-        <v>-4.11657528</v>
+        <v>4.08089557</v>
       </c>
       <c r="E56" t="n">
-        <v>4.080833070000001</v>
+        <v>-0.1995485</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.1995308</v>
+        <v>-12.28237295</v>
       </c>
       <c r="G56" t="n">
-        <v>-12.28246568</v>
+        <v>-2.91487422</v>
       </c>
       <c r="H56" t="n">
-        <v>-2.91485353</v>
+        <v>20.8052581</v>
       </c>
       <c r="I56" t="n">
-        <v>20.80537979</v>
+        <v>4.32875445</v>
       </c>
       <c r="J56" t="n">
-        <v>4.328907650000001</v>
+        <v>9.664215899999999</v>
       </c>
       <c r="K56" t="n">
-        <v>9.664171169999998</v>
+        <v>19.0901028</v>
       </c>
       <c r="L56" t="n">
-        <v>19.08999414</v>
+        <v>26.43894701</v>
       </c>
       <c r="M56" t="n">
-        <v>26.43894332</v>
+        <v>12.17498731</v>
       </c>
     </row>
     <row r="57">
@@ -2770,37 +2772,37 @@
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
-        <v>19.63287374</v>
+        <v>9.521552719999999</v>
       </c>
       <c r="D57" t="n">
-        <v>9.521552719999999</v>
+        <v>-6.49062084</v>
       </c>
       <c r="E57" t="n">
-        <v>-6.49062084</v>
+        <v>-19.63753738</v>
       </c>
       <c r="F57" t="n">
-        <v>-19.63753738</v>
+        <v>-31.28690505</v>
       </c>
       <c r="G57" t="n">
-        <v>-31.28690505</v>
+        <v>-35.82237618</v>
       </c>
       <c r="H57" t="n">
-        <v>-35.82237618</v>
+        <v>-48.83650657</v>
       </c>
       <c r="I57" t="n">
-        <v>-48.83650657</v>
+        <v>-2.96101949</v>
       </c>
       <c r="J57" t="n">
-        <v>-2.96101949</v>
+        <v>-4.13299422</v>
       </c>
       <c r="K57" t="n">
-        <v>-4.13299422</v>
+        <v>-6.761116970000001</v>
       </c>
       <c r="L57" t="n">
-        <v>-6.761116970000001</v>
+        <v>-11.20179401</v>
       </c>
       <c r="M57" t="n">
-        <v>-11.20179401</v>
+        <v>-1.30365066</v>
       </c>
     </row>
     <row r="58">
@@ -2811,37 +2813,37 @@
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>44.05441974</v>
+        <v>45.77364702000001</v>
       </c>
       <c r="D58" t="n">
-        <v>45.77383525</v>
+        <v>20.38807903</v>
       </c>
       <c r="E58" t="n">
-        <v>20.38814153</v>
+        <v>-9.582971580000001</v>
       </c>
       <c r="F58" t="n">
-        <v>-9.582989280000001</v>
+        <v>-17.24549747</v>
       </c>
       <c r="G58" t="n">
-        <v>-17.24540474</v>
+        <v>-34.94878781</v>
       </c>
       <c r="H58" t="n">
-        <v>-34.9488085</v>
+        <v>-42.18670959999999</v>
       </c>
       <c r="I58" t="n">
-        <v>-42.18683129</v>
+        <v>-0.9957898099999999</v>
       </c>
       <c r="J58" t="n">
-        <v>-0.99594301</v>
+        <v>-6.334103850000001</v>
       </c>
       <c r="K58" t="n">
-        <v>-6.33405912</v>
+        <v>8.21712718</v>
       </c>
       <c r="L58" t="n">
-        <v>8.217235840000001</v>
+        <v>3.55950817</v>
       </c>
       <c r="M58" t="n">
-        <v>3.55951186</v>
+        <v>17.67879739</v>
       </c>
     </row>
     <row r="59">
@@ -2852,37 +2854,37 @@
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
-        <v>-0.00537507</v>
+        <v>-0.02343861</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.02343861</v>
+        <v>0.03144128</v>
       </c>
       <c r="E59" t="n">
-        <v>0.03144128</v>
+        <v>0.01201424</v>
       </c>
       <c r="F59" t="n">
-        <v>0.01201424</v>
+        <v>0.04099756</v>
       </c>
       <c r="G59" t="n">
-        <v>0.04099756</v>
+        <v>0.02809802</v>
       </c>
       <c r="H59" t="n">
-        <v>0.02809802</v>
+        <v>0.04076989</v>
       </c>
       <c r="I59" t="n">
-        <v>0.04076989</v>
+        <v>-0.02230235</v>
       </c>
       <c r="J59" t="n">
-        <v>-0.02230235</v>
+        <v>0.0121624</v>
       </c>
       <c r="K59" t="n">
-        <v>0.0121624</v>
+        <v>-0.02442989</v>
       </c>
       <c r="L59" t="n">
-        <v>-0.02442989</v>
+        <v>0.09452125</v>
       </c>
       <c r="M59" t="n">
-        <v>0.09452125</v>
+        <v>0.12390914</v>
       </c>
     </row>
     <row r="60">
@@ -2893,37 +2895,37 @@
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
-        <v>65.17785349</v>
+        <v>39.06068539</v>
       </c>
       <c r="D60" t="n">
-        <v>39.06068539</v>
+        <v>50.62813032</v>
       </c>
       <c r="E60" t="n">
-        <v>50.62813032</v>
+        <v>29.49595222</v>
       </c>
       <c r="F60" t="n">
-        <v>29.49595222</v>
+        <v>3.736675960000001</v>
       </c>
       <c r="G60" t="n">
-        <v>3.736675960000001</v>
+        <v>-27.10836733</v>
       </c>
       <c r="H60" t="n">
-        <v>-27.10836733</v>
+        <v>-14.55097783</v>
       </c>
       <c r="I60" t="n">
-        <v>-14.55097783</v>
+        <v>-20.19341195</v>
       </c>
       <c r="J60" t="n">
-        <v>-20.19341195</v>
+        <v>-48.79022895</v>
       </c>
       <c r="K60" t="n">
-        <v>-48.79022895</v>
+        <v>-21.4031845</v>
       </c>
       <c r="L60" t="n">
-        <v>-21.4031845</v>
+        <v>-29.01154994</v>
       </c>
       <c r="M60" t="n">
-        <v>-29.01154994</v>
+        <v>-29.79071027</v>
       </c>
     </row>
     <row r="61">
@@ -2934,37 +2936,37 @@
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
-        <v>95.20197021</v>
+        <v>52.08621262</v>
       </c>
       <c r="D61" t="n">
-        <v>52.08621262</v>
+        <v>56.2651317</v>
       </c>
       <c r="E61" t="n">
-        <v>56.2651317</v>
+        <v>4.496420459999995</v>
       </c>
       <c r="F61" t="n">
-        <v>4.496420459999995</v>
+        <v>16.52153666</v>
       </c>
       <c r="G61" t="n">
-        <v>16.52153666</v>
+        <v>67.26849343000001</v>
       </c>
       <c r="H61" t="n">
-        <v>67.26849343000001</v>
+        <v>-16.93341359</v>
       </c>
       <c r="I61" t="n">
-        <v>-16.93341359</v>
+        <v>-37.98556158</v>
       </c>
       <c r="J61" t="n">
-        <v>-37.98556158</v>
+        <v>-34.65841320000001</v>
       </c>
       <c r="K61" t="n">
-        <v>-34.65841320000001</v>
+        <v>-52.24856203</v>
       </c>
       <c r="L61" t="n">
-        <v>-52.24856203</v>
+        <v>-39.37859758</v>
       </c>
       <c r="M61" t="n">
-        <v>-39.37859758</v>
+        <v>-4.036567070000014</v>
       </c>
     </row>
     <row r="62">
@@ -2975,37 +2977,37 @@
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>0.0072971</v>
+        <v>0.005237070000000001</v>
       </c>
       <c r="D62" t="n">
-        <v>0.005237070000000001</v>
+        <v>0.00104507</v>
       </c>
       <c r="E62" t="n">
-        <v>0.00104507</v>
+        <v>0.00898524</v>
       </c>
       <c r="F62" t="n">
-        <v>0.00898524</v>
+        <v>0.01629072</v>
       </c>
       <c r="G62" t="n">
-        <v>0.01629072</v>
+        <v>0.02050236</v>
       </c>
       <c r="H62" t="n">
-        <v>0.02050236</v>
+        <v>0.02262908</v>
       </c>
       <c r="I62" t="n">
-        <v>0.02262908</v>
+        <v>0.01813206</v>
       </c>
       <c r="J62" t="n">
-        <v>0.01813206</v>
+        <v>0.01316176</v>
       </c>
       <c r="K62" t="n">
-        <v>0.01316176</v>
+        <v>-0.0002601800000000002</v>
       </c>
       <c r="L62" t="n">
-        <v>-0.0002601800000000002</v>
+        <v>-0.00714299</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.00714299</v>
+        <v>0.00352127</v>
       </c>
     </row>
     <row r="63">
@@ -3016,37 +3018,37 @@
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>94.86343511</v>
+        <v>48.0678358</v>
       </c>
       <c r="D63" t="n">
-        <v>46.74770855</v>
+        <v>39.22009743</v>
       </c>
       <c r="E63" t="n">
-        <v>41.24763927</v>
+        <v>15.91580701</v>
       </c>
       <c r="F63" t="n">
-        <v>17.01477717</v>
+        <v>18.27737456</v>
       </c>
       <c r="G63" t="n">
-        <v>18.43927654</v>
+        <v>27.18001496</v>
       </c>
       <c r="H63" t="n">
-        <v>30.16554393</v>
+        <v>29.03651708</v>
       </c>
       <c r="I63" t="n">
-        <v>29.38655623</v>
+        <v>-0.5535146500000004</v>
       </c>
       <c r="J63" t="n">
-        <v>-1.379161980000001</v>
+        <v>-21.72210101</v>
       </c>
       <c r="K63" t="n">
-        <v>-22.59602675</v>
+        <v>-16.22650388</v>
       </c>
       <c r="L63" t="n">
-        <v>-17.54911508</v>
+        <v>-27.89734886</v>
       </c>
       <c r="M63" t="n">
-        <v>-29.10383618</v>
+        <v>-0.0972629100000006</v>
       </c>
     </row>
     <row r="64">
@@ -3057,37 +3059,37 @@
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
-        <v>6.247e-05</v>
+        <v>0.0004044</v>
       </c>
       <c r="D64" t="n">
-        <v>0.0004044</v>
+        <v>0.00072251</v>
       </c>
       <c r="E64" t="n">
-        <v>0.00072251</v>
+        <v>-0.00025412</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.00025412</v>
+        <v>-0.00126824</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.00126824</v>
+        <v>-0.00052996</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.00052996</v>
+        <v>-4.627e-05</v>
       </c>
       <c r="I64" t="n">
-        <v>-4.627e-05</v>
+        <v>0.00012135</v>
       </c>
       <c r="J64" t="n">
-        <v>0.00012135</v>
+        <v>0.00033795</v>
       </c>
       <c r="K64" t="n">
-        <v>0.00033795</v>
+        <v>0.0007966399999999999</v>
       </c>
       <c r="L64" t="n">
-        <v>0.0007966399999999999</v>
+        <v>0.00094526</v>
       </c>
       <c r="M64" t="n">
-        <v>0.00094526</v>
+        <v>0.00174454</v>
       </c>
     </row>
     <row r="65">
@@ -3098,37 +3100,37 @@
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
-        <v>0.00018835</v>
+        <v>2.243e-05</v>
       </c>
       <c r="D65" t="n">
-        <v>2.243e-05</v>
+        <v>-8.019e-05</v>
       </c>
       <c r="E65" t="n">
-        <v>-8.019e-05</v>
+        <v>-3.720999999999999e-05</v>
       </c>
       <c r="F65" t="n">
-        <v>-3.720999999999999e-05</v>
+        <v>-0.00012853</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.00012853</v>
+        <v>-0.00011783</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.00011783</v>
+        <v>-0.00038662</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.00038662</v>
+        <v>-0.00020338</v>
       </c>
       <c r="J65" t="n">
-        <v>-0.00020338</v>
+        <v>2.062999999999999e-05</v>
       </c>
       <c r="K65" t="n">
-        <v>2.062999999999999e-05</v>
+        <v>7.988999999999998e-05</v>
       </c>
       <c r="L65" t="n">
-        <v>7.988999999999998e-05</v>
+        <v>-3.629999999999995e-06</v>
       </c>
       <c r="M65" t="n">
-        <v>-3.629999999999995e-06</v>
+        <v>0.00015752</v>
       </c>
     </row>
     <row r="66">
@@ -3139,37 +3141,37 @@
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>726.58418074</v>
+        <v>219.61619982</v>
       </c>
       <c r="D66" t="n">
-        <v>219.22811038</v>
+        <v>553.1703113999999</v>
       </c>
       <c r="E66" t="n">
-        <v>553.06950304</v>
+        <v>726.6980753300001</v>
       </c>
       <c r="F66" t="n">
-        <v>726.4882705900001</v>
+        <v>922.15021687</v>
       </c>
       <c r="G66" t="n">
-        <v>921.94961616</v>
+        <v>1026.32503559</v>
       </c>
       <c r="H66" t="n">
-        <v>1026.06143639</v>
+        <v>1123.08660503</v>
       </c>
       <c r="I66" t="n">
-        <v>1122.80221939</v>
+        <v>1091.51975738</v>
       </c>
       <c r="J66" t="n">
-        <v>1091.18890072</v>
+        <v>1194.06903594</v>
       </c>
       <c r="K66" t="n">
-        <v>1194.06178914</v>
+        <v>1751.09843048</v>
       </c>
       <c r="L66" t="n">
-        <v>1751.61038935</v>
+        <v>599.7315965499999</v>
       </c>
       <c r="M66" t="n">
-        <v>599.6731381000001</v>
+        <v>-1801.28695509</v>
       </c>
     </row>
     <row r="67">
@@ -3178,41 +3180,39 @@
           <t>通信網路業右下</t>
         </is>
       </c>
-      <c r="B67" t="n">
-        <v>0</v>
-      </c>
+      <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>43.54210218</v>
+        <v>-74.88972738000001</v>
       </c>
       <c r="D67" t="n">
-        <v>-32.81636228</v>
+        <v>-97.46323704000001</v>
       </c>
       <c r="E67" t="n">
-        <v>-43.90206674</v>
+        <v>-100.39485247</v>
       </c>
       <c r="F67" t="n">
-        <v>-50.52353451</v>
+        <v>-108.88161837</v>
       </c>
       <c r="G67" t="n">
-        <v>-59.86684214</v>
+        <v>-49.34560721</v>
       </c>
       <c r="H67" t="n">
-        <v>-32.44140473</v>
+        <v>-40.32005366</v>
       </c>
       <c r="I67" t="n">
-        <v>-13.85306951</v>
+        <v>-39.00891055</v>
       </c>
       <c r="J67" t="n">
-        <v>-12.01927122</v>
+        <v>-17.81442497</v>
       </c>
       <c r="K67" t="n">
-        <v>-10.69279784</v>
+        <v>5.999381360000001</v>
       </c>
       <c r="L67" t="n">
-        <v>16.19583004</v>
+        <v>-0.7701470400000022</v>
       </c>
       <c r="M67" t="n">
-        <v>16.22284164</v>
+        <v>-37.88870957</v>
       </c>
     </row>
     <row r="68">
@@ -3223,37 +3223,37 @@
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>103.49582804</v>
+        <v>182.23689366</v>
       </c>
       <c r="D68" t="n">
-        <v>140.58514141</v>
+        <v>0.3783369500000233</v>
       </c>
       <c r="E68" t="n">
-        <v>-52.00069714999999</v>
+        <v>-56.96720261999998</v>
       </c>
       <c r="F68" t="n">
-        <v>-106.96026633</v>
+        <v>-43.03785831999999</v>
       </c>
       <c r="G68" t="n">
-        <v>-89.75740950999999</v>
+        <v>43.41552827</v>
       </c>
       <c r="H68" t="n">
-        <v>27.1313866</v>
+        <v>-31.96114228999999</v>
       </c>
       <c r="I68" t="n">
-        <v>-59.22676548</v>
+        <v>53.79927942</v>
       </c>
       <c r="J68" t="n">
-        <v>25.81702806</v>
+        <v>-0.6413213799999855</v>
       </c>
       <c r="K68" t="n">
-        <v>-9.425721389999991</v>
+        <v>47.36549824999998</v>
       </c>
       <c r="L68" t="n">
-        <v>34.50571488999998</v>
+        <v>-27.16941134000001</v>
       </c>
       <c r="M68" t="n">
-        <v>-44.29452930000001</v>
+        <v>-271.15013425</v>
       </c>
     </row>
     <row r="69">
@@ -3264,37 +3264,37 @@
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>-8.60103045</v>
+        <v>1.481096</v>
       </c>
       <c r="D69" t="n">
-        <v>1.481096</v>
+        <v>-2.09694106</v>
       </c>
       <c r="E69" t="n">
-        <v>-2.09694106</v>
+        <v>-1.18870531</v>
       </c>
       <c r="F69" t="n">
-        <v>-1.18870531</v>
+        <v>0.8999840899999999</v>
       </c>
       <c r="G69" t="n">
-        <v>0.8999840899999999</v>
+        <v>-1.07992369</v>
       </c>
       <c r="H69" t="n">
-        <v>-1.07992369</v>
+        <v>-8.13542947</v>
       </c>
       <c r="I69" t="n">
-        <v>-8.13542947</v>
+        <v>-6.112742610000001</v>
       </c>
       <c r="J69" t="n">
-        <v>-6.112742610000001</v>
+        <v>0.62737845</v>
       </c>
       <c r="K69" t="n">
-        <v>0.62737845</v>
+        <v>-1.39124728</v>
       </c>
       <c r="L69" t="n">
-        <v>-1.39124728</v>
+        <v>-3.48094111</v>
       </c>
       <c r="M69" t="n">
-        <v>-3.48094111</v>
+        <v>-5.56892512</v>
       </c>
     </row>
     <row r="70">
@@ -3305,37 +3305,37 @@
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>-1.55525517</v>
+        <v>0.15859867</v>
       </c>
       <c r="D70" t="n">
-        <v>0.15859867</v>
+        <v>-0.01651628</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.01651628</v>
+        <v>0.93115824</v>
       </c>
       <c r="F70" t="n">
-        <v>0.93115824</v>
+        <v>0.15324129</v>
       </c>
       <c r="G70" t="n">
-        <v>0.15324129</v>
+        <v>2.0141396</v>
       </c>
       <c r="H70" t="n">
-        <v>2.0141396</v>
+        <v>0.94456732</v>
       </c>
       <c r="I70" t="n">
-        <v>0.94456732</v>
+        <v>1.31059385</v>
       </c>
       <c r="J70" t="n">
-        <v>1.31059385</v>
+        <v>0.44808132</v>
       </c>
       <c r="K70" t="n">
-        <v>0.44808132</v>
+        <v>1.02481299</v>
       </c>
       <c r="L70" t="n">
-        <v>1.02481299</v>
+        <v>0.39879786</v>
       </c>
       <c r="M70" t="n">
-        <v>0.39879786</v>
+        <v>-0.4558637</v>
       </c>
     </row>
     <row r="71">
@@ -3346,37 +3346,37 @@
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
-        <v>39.58487804</v>
+        <v>49.03197814</v>
       </c>
       <c r="D71" t="n">
-        <v>49.03197814</v>
+        <v>20.29127258</v>
       </c>
       <c r="E71" t="n">
-        <v>20.29127258</v>
+        <v>24.00895878</v>
       </c>
       <c r="F71" t="n">
-        <v>24.00895878</v>
+        <v>34.17125779</v>
       </c>
       <c r="G71" t="n">
-        <v>34.17125779</v>
+        <v>-3.0706811</v>
       </c>
       <c r="H71" t="n">
-        <v>-3.0706811</v>
+        <v>-7.127004649999999</v>
       </c>
       <c r="I71" t="n">
-        <v>-7.127004649999999</v>
+        <v>-16.45539349</v>
       </c>
       <c r="J71" t="n">
-        <v>-16.45539349</v>
+        <v>-1.46575611</v>
       </c>
       <c r="K71" t="n">
-        <v>-1.46575611</v>
+        <v>-28.70342079</v>
       </c>
       <c r="L71" t="n">
-        <v>-28.70342079</v>
+        <v>-30.10771701</v>
       </c>
       <c r="M71" t="n">
-        <v>-30.10771701</v>
+        <v>-17.75000963</v>
       </c>
     </row>
     <row r="72">
@@ -3385,39 +3385,41 @@
           <t>運動休閒右下</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr"/>
+      <c r="B72" t="n">
+        <v>0</v>
+      </c>
       <c r="C72" t="n">
-        <v>-17.14059748</v>
+        <v>-81.91164641</v>
       </c>
       <c r="D72" t="n">
-        <v>-81.91163204999999</v>
+        <v>-115.31225339</v>
       </c>
       <c r="E72" t="n">
-        <v>-115.31227011</v>
+        <v>-37.30359735</v>
       </c>
       <c r="F72" t="n">
-        <v>-37.30362026</v>
+        <v>-103.56379597</v>
       </c>
       <c r="G72" t="n">
-        <v>-103.56392674</v>
+        <v>-54.40126461</v>
       </c>
       <c r="H72" t="n">
-        <v>-54.40137722999999</v>
+        <v>-0.911962920000004</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.9121308300000042</v>
+        <v>111.99431699</v>
       </c>
       <c r="J72" t="n">
-        <v>111.99430636</v>
+        <v>111.66897828</v>
       </c>
       <c r="K72" t="n">
-        <v>111.66897061</v>
+        <v>-3.999638780000003</v>
       </c>
       <c r="L72" t="n">
-        <v>-3.999667890000003</v>
+        <v>-119.43976164</v>
       </c>
       <c r="M72" t="n">
-        <v>-119.43980218</v>
+        <v>-105.75567819</v>
       </c>
     </row>
     <row r="73">
@@ -3428,37 +3430,37 @@
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
-        <v>1.31760602</v>
+        <v>-9.691171220000001</v>
       </c>
       <c r="D73" t="n">
-        <v>-9.691171220000001</v>
+        <v>-11.21701609</v>
       </c>
       <c r="E73" t="n">
-        <v>-11.21701609</v>
+        <v>-24.50112135</v>
       </c>
       <c r="F73" t="n">
-        <v>-24.50112135</v>
+        <v>-23.85631305</v>
       </c>
       <c r="G73" t="n">
-        <v>-23.85631305</v>
+        <v>-23.78075616</v>
       </c>
       <c r="H73" t="n">
-        <v>-23.78075616</v>
+        <v>-20.79905364</v>
       </c>
       <c r="I73" t="n">
-        <v>-20.79905364</v>
+        <v>7.640183769999999</v>
       </c>
       <c r="J73" t="n">
-        <v>7.640183769999999</v>
+        <v>-8.013334910000001</v>
       </c>
       <c r="K73" t="n">
-        <v>-8.013334910000001</v>
+        <v>-21.10458214000001</v>
       </c>
       <c r="L73" t="n">
-        <v>-21.10458214000001</v>
+        <v>-30.02046044</v>
       </c>
       <c r="M73" t="n">
-        <v>-30.02046044</v>
+        <v>-8.537947050000001</v>
       </c>
     </row>
     <row r="74">
@@ -3469,37 +3471,37 @@
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
-        <v>894.0164181600001</v>
+        <v>1242.79248807</v>
       </c>
       <c r="D74" t="n">
-        <v>1276.00511831</v>
+        <v>851.86550735</v>
       </c>
       <c r="E74" t="n">
-        <v>884.3679413999999</v>
+        <v>703.0305864300001</v>
       </c>
       <c r="F74" t="n">
-        <v>711.53754654</v>
+        <v>664.72535027</v>
       </c>
       <c r="G74" t="n">
-        <v>678.83419911</v>
+        <v>656.9999549300001</v>
       </c>
       <c r="H74" t="n">
-        <v>674.51015137</v>
+        <v>922.40805115</v>
       </c>
       <c r="I74" t="n">
-        <v>926.41732815</v>
+        <v>1352.18679415</v>
       </c>
       <c r="J74" t="n">
-        <v>1369.02894179</v>
+        <v>443.55634693</v>
       </c>
       <c r="K74" t="n">
-        <v>463.72510052</v>
+        <v>296.15320315</v>
       </c>
       <c r="L74" t="n">
-        <v>314.75285627</v>
+        <v>-274.2499456</v>
       </c>
       <c r="M74" t="n">
-        <v>-267.78573693</v>
+        <v>-985.81143814</v>
       </c>
     </row>
     <row r="75">
@@ -3508,39 +3510,41 @@
           <t>金融保險右下</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr"/>
+      <c r="B75" t="n">
+        <v>0</v>
+      </c>
       <c r="C75" t="n">
-        <v>72.75089683</v>
+        <v>166.88105806</v>
       </c>
       <c r="D75" t="n">
-        <v>167.55188173</v>
+        <v>-29.24538225</v>
       </c>
       <c r="E75" t="n">
-        <v>-31.46257298</v>
+        <v>-217.03758715</v>
       </c>
       <c r="F75" t="n">
-        <v>-219.97600686</v>
+        <v>-381.0536326899999</v>
       </c>
       <c r="G75" t="n">
-        <v>-384.3325941999999</v>
+        <v>-510.1900488100001</v>
       </c>
       <c r="H75" t="n">
-        <v>-513.9571076200001</v>
+        <v>-257.06344158</v>
       </c>
       <c r="I75" t="n">
-        <v>-257.99615698</v>
+        <v>-15.66310559</v>
       </c>
       <c r="J75" t="n">
-        <v>-17.04792302</v>
+        <v>-63.22544475999999</v>
       </c>
       <c r="K75" t="n">
-        <v>-66.68232792000001</v>
+        <v>44.96276262999999</v>
       </c>
       <c r="L75" t="n">
-        <v>39.88375886</v>
+        <v>11.43137598</v>
       </c>
       <c r="M75" t="n">
-        <v>5.240855929999999</v>
+        <v>129.33146676</v>
       </c>
     </row>
     <row r="76">
@@ -3551,37 +3555,37 @@
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>2.117843309999998</v>
+        <v>13.71012711</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.871264110000001</v>
+        <v>-5.745900730000001</v>
       </c>
       <c r="E76" t="n">
-        <v>-27.58568966</v>
+        <v>4.30056158</v>
       </c>
       <c r="F76" t="n">
-        <v>10.96223872</v>
+        <v>44.18124179</v>
       </c>
       <c r="G76" t="n">
-        <v>47.73662943</v>
+        <v>30.18417386</v>
       </c>
       <c r="H76" t="n">
-        <v>37.80555489</v>
+        <v>37.38347089</v>
       </c>
       <c r="I76" t="n">
-        <v>60.24445445000001</v>
+        <v>81.34864014999999</v>
       </c>
       <c r="J76" t="n">
-        <v>75.68165750999999</v>
+        <v>50.99804315999999</v>
       </c>
       <c r="K76" t="n">
-        <v>33.39518098</v>
+        <v>16.02535167</v>
       </c>
       <c r="L76" t="n">
-        <v>13.29797587</v>
+        <v>-14.83456122</v>
       </c>
       <c r="M76" t="n">
-        <v>-21.45733517</v>
+        <v>-41.55389577</v>
       </c>
     </row>
     <row r="77">
@@ -3592,37 +3596,37 @@
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="n">
-        <v>0.00035191</v>
+        <v>0.0006016</v>
       </c>
       <c r="D77" t="n">
-        <v>0.0006016</v>
+        <v>0.00119589</v>
       </c>
       <c r="E77" t="n">
-        <v>0.00119589</v>
+        <v>0.00222055</v>
       </c>
       <c r="F77" t="n">
-        <v>0.00222055</v>
+        <v>0.00226234</v>
       </c>
       <c r="G77" t="n">
-        <v>0.00226234</v>
+        <v>0.00101082</v>
       </c>
       <c r="H77" t="n">
-        <v>0.00101082</v>
+        <v>9.988e-05</v>
       </c>
       <c r="I77" t="n">
-        <v>9.988e-05</v>
+        <v>0.00032912</v>
       </c>
       <c r="J77" t="n">
-        <v>0.00032912</v>
+        <v>-0.00052438</v>
       </c>
       <c r="K77" t="n">
-        <v>-0.00052438</v>
+        <v>-9.99e-05</v>
       </c>
       <c r="L77" t="n">
-        <v>-9.99e-05</v>
+        <v>-0.00069427</v>
       </c>
       <c r="M77" t="n">
-        <v>-0.00069427</v>
+        <v>-0.00100544</v>
       </c>
     </row>
     <row r="78">
@@ -3633,37 +3637,37 @@
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
-        <v>-0.00146164</v>
+        <v>0.0001785999999999999</v>
       </c>
       <c r="D78" t="n">
-        <v>0.0001785999999999999</v>
+        <v>0.00166505</v>
       </c>
       <c r="E78" t="n">
-        <v>0.00166505</v>
+        <v>0.00481058</v>
       </c>
       <c r="F78" t="n">
-        <v>0.00481058</v>
+        <v>0.00272902</v>
       </c>
       <c r="G78" t="n">
-        <v>0.00272902</v>
+        <v>9.011000000000007e-05</v>
       </c>
       <c r="H78" t="n">
-        <v>9.011000000000007e-05</v>
+        <v>0.0004795100000000002</v>
       </c>
       <c r="I78" t="n">
-        <v>0.0004795100000000002</v>
+        <v>0.00329986</v>
       </c>
       <c r="J78" t="n">
-        <v>0.00329986</v>
+        <v>0.0005099499999999999</v>
       </c>
       <c r="K78" t="n">
-        <v>0.0005099499999999999</v>
+        <v>-0.0007658099999999999</v>
       </c>
       <c r="L78" t="n">
-        <v>-0.0007658099999999999</v>
+        <v>0.0034501</v>
       </c>
       <c r="M78" t="n">
-        <v>0.0034501</v>
+        <v>0.0005688300000000001</v>
       </c>
     </row>
     <row r="79">
@@ -3674,37 +3678,37 @@
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="n">
-        <v>0.00149008</v>
+        <v>0.00167124</v>
       </c>
       <c r="D79" t="n">
-        <v>0.00167124</v>
+        <v>0.00103193</v>
       </c>
       <c r="E79" t="n">
-        <v>0.00103193</v>
+        <v>0.00057835</v>
       </c>
       <c r="F79" t="n">
-        <v>0.00057835</v>
+        <v>9.465e-05</v>
       </c>
       <c r="G79" t="n">
-        <v>9.465e-05</v>
+        <v>0.00013897</v>
       </c>
       <c r="H79" t="n">
-        <v>0.00013897</v>
+        <v>6.415e-05</v>
       </c>
       <c r="I79" t="n">
-        <v>6.415e-05</v>
+        <v>-0.00029419</v>
       </c>
       <c r="J79" t="n">
-        <v>-0.00029419</v>
+        <v>0.00019073</v>
       </c>
       <c r="K79" t="n">
-        <v>0.00019073</v>
+        <v>-2.111999999999998e-05</v>
       </c>
       <c r="L79" t="n">
-        <v>-2.111999999999998e-05</v>
+        <v>0.00040195</v>
       </c>
       <c r="M79" t="n">
-        <v>0.00040195</v>
+        <v>7.686999999999999e-05</v>
       </c>
     </row>
     <row r="80">
@@ -3715,37 +3719,37 @@
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="n">
-        <v>-10.26026165</v>
+        <v>8.421552140000001</v>
       </c>
       <c r="D80" t="n">
-        <v>8.420322020000002</v>
+        <v>-10.13260721</v>
       </c>
       <c r="E80" t="n">
-        <v>-10.13479723</v>
+        <v>-9.68964107</v>
       </c>
       <c r="F80" t="n">
-        <v>-9.688284559999998</v>
+        <v>4.868124629999999</v>
       </c>
       <c r="G80" t="n">
-        <v>4.870666569999999</v>
+        <v>12.18883922</v>
       </c>
       <c r="H80" t="n">
-        <v>12.18966626</v>
+        <v>-4.46799539</v>
       </c>
       <c r="I80" t="n">
-        <v>-4.46977351</v>
+        <v>12.58299348</v>
       </c>
       <c r="J80" t="n">
-        <v>12.58217618</v>
+        <v>17.39570309</v>
       </c>
       <c r="K80" t="n">
-        <v>17.39556762</v>
+        <v>13.14604495</v>
       </c>
       <c r="L80" t="n">
-        <v>13.14819293</v>
+        <v>10.09760665</v>
       </c>
       <c r="M80" t="n">
-        <v>10.09827181</v>
+        <v>-4.54740078</v>
       </c>
     </row>
     <row r="81">
@@ -3754,41 +3758,39 @@
           <t>鋼鐵工業右下</t>
         </is>
       </c>
-      <c r="B81" t="n">
-        <v>0</v>
-      </c>
+      <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>-57.31861607</v>
+        <v>-43.25435408</v>
       </c>
       <c r="D81" t="n">
-        <v>-40.77116172</v>
+        <v>-61.35160032</v>
       </c>
       <c r="E81" t="n">
-        <v>-58.31165084</v>
+        <v>-43.0562662</v>
       </c>
       <c r="F81" t="n">
-        <v>-40.10086</v>
+        <v>-16.93540232</v>
       </c>
       <c r="G81" t="n">
-        <v>-13.23293289</v>
+        <v>31.38022441</v>
       </c>
       <c r="H81" t="n">
-        <v>34.28753278</v>
+        <v>99.07451711</v>
       </c>
       <c r="I81" t="n">
-        <v>102.15875626</v>
+        <v>135.88422991</v>
       </c>
       <c r="J81" t="n">
-        <v>136.68336307</v>
+        <v>238.91509697</v>
       </c>
       <c r="K81" t="n">
-        <v>237.45557772</v>
+        <v>138.66674355</v>
       </c>
       <c r="L81" t="n">
-        <v>137.26361639</v>
+        <v>49.30860766000001</v>
       </c>
       <c r="M81" t="n">
-        <v>45.08298159</v>
+        <v>-47.82701062</v>
       </c>
     </row>
     <row r="82">
@@ -3799,37 +3801,37 @@
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
-        <v>-50.2547076</v>
+        <v>0.1884262800000012</v>
       </c>
       <c r="D82" t="n">
-        <v>0.6935106799999997</v>
+        <v>-170.38236796</v>
       </c>
       <c r="E82" t="n">
-        <v>-169.39214522</v>
+        <v>95.41277939</v>
       </c>
       <c r="F82" t="n">
-        <v>89.52751352000001</v>
+        <v>-152.13774465</v>
       </c>
       <c r="G82" t="n">
-        <v>-160.83174776</v>
+        <v>-342.33967264</v>
       </c>
       <c r="H82" t="n">
-        <v>-351.76678152</v>
+        <v>-545.95898001</v>
       </c>
       <c r="I82" t="n">
-        <v>-559.3531269600001</v>
+        <v>-280.96473412</v>
       </c>
       <c r="J82" t="n">
-        <v>-300.64457347</v>
+        <v>-160.21890398</v>
       </c>
       <c r="K82" t="n">
-        <v>-178.50942961</v>
+        <v>63.94508142</v>
       </c>
       <c r="L82" t="n">
-        <v>63.14910776</v>
+        <v>-39.29490801000001</v>
       </c>
       <c r="M82" t="n">
-        <v>-30.53152689</v>
+        <v>-182.02364974</v>
       </c>
     </row>
     <row r="83">
@@ -3840,37 +3842,37 @@
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>82.35941356999999</v>
+        <v>173.80208869</v>
       </c>
       <c r="D83" t="n">
-        <v>181.83515722</v>
+        <v>68.31111571000001</v>
       </c>
       <c r="E83" t="n">
-        <v>68.08952595000001</v>
+        <v>-15.21283794</v>
       </c>
       <c r="F83" t="n">
-        <v>-20.36797773</v>
+        <v>-17.71552102</v>
       </c>
       <c r="G83" t="n">
-        <v>-20.03139617</v>
+        <v>-64.05499739</v>
       </c>
       <c r="H83" t="n">
-        <v>-59.64161756</v>
+        <v>-108.28490628</v>
       </c>
       <c r="I83" t="n">
-        <v>-112.75539681</v>
+        <v>17.23501362</v>
       </c>
       <c r="J83" t="n">
-        <v>64.56145398</v>
+        <v>-42.91166961</v>
       </c>
       <c r="K83" t="n">
-        <v>-54.95076079</v>
+        <v>-16.22533502</v>
       </c>
       <c r="L83" t="n">
-        <v>-5.751428920000002</v>
+        <v>-7.978113619999998</v>
       </c>
       <c r="M83" t="n">
-        <v>-18.06551288</v>
+        <v>-41.15140009</v>
       </c>
     </row>
     <row r="84">
@@ -3881,37 +3883,37 @@
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
-        <v>-54.08822536000001</v>
+        <v>-10.32345865</v>
       </c>
       <c r="D84" t="n">
-        <v>-10.32345865</v>
+        <v>20.68587184</v>
       </c>
       <c r="E84" t="n">
-        <v>20.68587184</v>
+        <v>50.4358599</v>
       </c>
       <c r="F84" t="n">
-        <v>50.4358599</v>
+        <v>20.67695317</v>
       </c>
       <c r="G84" t="n">
-        <v>20.67695317</v>
+        <v>39.12531966</v>
       </c>
       <c r="H84" t="n">
-        <v>39.12531966</v>
+        <v>82.69031135000002</v>
       </c>
       <c r="I84" t="n">
-        <v>82.69031135000002</v>
+        <v>154.59545891</v>
       </c>
       <c r="J84" t="n">
-        <v>154.59545891</v>
+        <v>58.71590928</v>
       </c>
       <c r="K84" t="n">
-        <v>58.71590928</v>
+        <v>121.63718761</v>
       </c>
       <c r="L84" t="n">
-        <v>121.63718761</v>
+        <v>29.61562639</v>
       </c>
       <c r="M84" t="n">
-        <v>29.61562639</v>
+        <v>-24.78285621</v>
       </c>
     </row>
     <row r="85">
@@ -3922,37 +3924,37 @@
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>16.5811829</v>
+        <v>91.58317283999999</v>
       </c>
       <c r="D85" t="n">
-        <v>83.55010430999998</v>
+        <v>307.99625718</v>
       </c>
       <c r="E85" t="n">
-        <v>308.21784694</v>
+        <v>127.17974363</v>
       </c>
       <c r="F85" t="n">
-        <v>132.33488342</v>
+        <v>35.51983674</v>
       </c>
       <c r="G85" t="n">
-        <v>37.83571189</v>
+        <v>-44.38674216</v>
       </c>
       <c r="H85" t="n">
-        <v>-48.80012199</v>
+        <v>-80.33944907999999</v>
       </c>
       <c r="I85" t="n">
-        <v>-75.86895855</v>
+        <v>17.36541503</v>
       </c>
       <c r="J85" t="n">
-        <v>-29.96102533</v>
+        <v>-22.22959168</v>
       </c>
       <c r="K85" t="n">
-        <v>-10.1905005</v>
+        <v>36.66650072</v>
       </c>
       <c r="L85" t="n">
-        <v>26.19259462</v>
+        <v>-47.17463461</v>
       </c>
       <c r="M85" t="n">
-        <v>-37.08723535</v>
+        <v>-72.74271278000001</v>
       </c>
     </row>
     <row r="86">
@@ -3963,37 +3965,37 @@
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
-        <v>40.5057899</v>
+        <v>-4.04860231</v>
       </c>
       <c r="D86" t="n">
-        <v>0.2115746600000012</v>
+        <v>-13.91812297</v>
       </c>
       <c r="E86" t="n">
-        <v>-73.51357708</v>
+        <v>-26.74595337</v>
       </c>
       <c r="F86" t="n">
-        <v>-120.38293081</v>
+        <v>6.37891582</v>
       </c>
       <c r="G86" t="n">
-        <v>-28.81328676999999</v>
+        <v>68.23265044</v>
       </c>
       <c r="H86" t="n">
-        <v>26.42893274</v>
+        <v>23.90605647</v>
       </c>
       <c r="I86" t="n">
-        <v>-19.94011926</v>
+        <v>-37.2038651</v>
       </c>
       <c r="J86" t="n">
-        <v>-44.01715513000001</v>
+        <v>-34.68524193</v>
       </c>
       <c r="K86" t="n">
-        <v>-47.84157947</v>
+        <v>-68.94026530999999</v>
       </c>
       <c r="L86" t="n">
-        <v>-49.89369227</v>
+        <v>-56.73407539</v>
       </c>
       <c r="M86" t="n">
-        <v>-54.41137247</v>
+        <v>-15.45230189</v>
       </c>
     </row>
     <row r="87">
@@ -4004,37 +4006,37 @@
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>72.27875806999999</v>
+        <v>90.98057971999999</v>
       </c>
       <c r="D87" t="n">
-        <v>17.68104212999999</v>
+        <v>16.93207719</v>
       </c>
       <c r="E87" t="n">
-        <v>-3.41344151</v>
+        <v>-67.92105245</v>
       </c>
       <c r="F87" t="n">
-        <v>-68.99595576999999</v>
+        <v>-169.6017512</v>
       </c>
       <c r="G87" t="n">
-        <v>-152.61735534</v>
+        <v>-200.60217824</v>
       </c>
       <c r="H87" t="n">
-        <v>-178.63669302</v>
+        <v>-165.28100234</v>
       </c>
       <c r="I87" t="n">
-        <v>-166.39734657</v>
+        <v>-136.35591918</v>
       </c>
       <c r="J87" t="n">
-        <v>-126.75621919</v>
+        <v>-127.41416022</v>
       </c>
       <c r="K87" t="n">
-        <v>-109.66916115</v>
+        <v>-99.86235365</v>
       </c>
       <c r="L87" t="n">
-        <v>-91.38076609000001</v>
+        <v>-99.31666487999999</v>
       </c>
       <c r="M87" t="n">
-        <v>-87.53814033</v>
+        <v>-107.42663417</v>
       </c>
     </row>
     <row r="88">
@@ -4045,37 +4047,37 @@
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
-        <v>61.72885808000001</v>
+        <v>36.57455757</v>
       </c>
       <c r="D88" t="n">
-        <v>105.61391819</v>
+        <v>-14.95004816</v>
       </c>
       <c r="E88" t="n">
-        <v>64.99092465</v>
+        <v>-92.18056577000002</v>
       </c>
       <c r="F88" t="n">
-        <v>2.53131499</v>
+        <v>-41.55750256</v>
       </c>
       <c r="G88" t="n">
-        <v>-23.34969583</v>
+        <v>-20.47460762</v>
       </c>
       <c r="H88" t="n">
-        <v>-0.6363751400000015</v>
+        <v>-67.28577043999999</v>
       </c>
       <c r="I88" t="n">
-        <v>-22.32325048</v>
+        <v>-40.03086548</v>
       </c>
       <c r="J88" t="n">
-        <v>-42.81727544</v>
+        <v>-30.75194596</v>
       </c>
       <c r="K88" t="n">
-        <v>-35.34060749</v>
+        <v>23.37435337</v>
       </c>
       <c r="L88" t="n">
-        <v>-4.153807230000002</v>
+        <v>35.07272512000001</v>
       </c>
       <c r="M88" t="n">
-        <v>20.97149765</v>
+        <v>-27.42918962</v>
       </c>
     </row>
     <row r="89">
@@ -4086,37 +4088,37 @@
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>2976.04661351</v>
+        <v>1182.11866472</v>
       </c>
       <c r="D89" t="n">
-        <v>1174.76537281</v>
+        <v>817.053399</v>
       </c>
       <c r="E89" t="n">
-        <v>788.47338988</v>
+        <v>3457.49698208</v>
       </c>
       <c r="F89" t="n">
-        <v>3439.72712589</v>
+        <v>5025.11440555</v>
       </c>
       <c r="G89" t="n">
-        <v>5018.143648769999</v>
+        <v>4950.6694852</v>
       </c>
       <c r="H89" t="n">
-        <v>4913.86418217</v>
+        <v>5001.32971024</v>
       </c>
       <c r="I89" t="n">
-        <v>5029.14339548</v>
+        <v>4878.45836897</v>
       </c>
       <c r="J89" t="n">
-        <v>5003.88768559</v>
+        <v>3521.836542290001</v>
       </c>
       <c r="K89" t="n">
-        <v>3597.82972113</v>
+        <v>5013.69783426</v>
       </c>
       <c r="L89" t="n">
-        <v>5119.049637009999</v>
+        <v>-169.5068375399998</v>
       </c>
       <c r="M89" t="n">
-        <v>-39.36253362999983</v>
+        <v>-7263.958555890001</v>
       </c>
     </row>
     <row r="90">
@@ -4125,39 +4127,41 @@
           <t>電子零組件業右下</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr"/>
+      <c r="B90" t="n">
+        <v>0</v>
+      </c>
       <c r="C90" t="n">
-        <v>-7.703919789999998</v>
+        <v>-617.9405942899999</v>
       </c>
       <c r="D90" t="n">
-        <v>-52.6155042</v>
+        <v>-512.11831169</v>
       </c>
       <c r="E90" t="n">
-        <v>-129.53775208</v>
+        <v>-402.77212489</v>
       </c>
       <c r="F90" t="n">
-        <v>-109.32306762</v>
+        <v>-36.43205005999999</v>
       </c>
       <c r="G90" t="n">
-        <v>-71.99148717999999</v>
+        <v>-377.95209684</v>
       </c>
       <c r="H90" t="n">
-        <v>-6.84765444</v>
+        <v>-797.10663956</v>
       </c>
       <c r="I90" t="n">
-        <v>-87.32757911</v>
+        <v>-1000.82173937</v>
       </c>
       <c r="J90" t="n">
-        <v>-38.67162504</v>
+        <v>-1098.52798332</v>
       </c>
       <c r="K90" t="n">
-        <v>-2.150323739999998</v>
+        <v>-199.4238228299999</v>
       </c>
       <c r="L90" t="n">
-        <v>79.26695736000001</v>
+        <v>-603.82651206</v>
       </c>
       <c r="M90" t="n">
-        <v>32.94809444</v>
+        <v>-944.82321204</v>
       </c>
     </row>
     <row r="91">
@@ -4168,37 +4172,37 @@
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>-141.70846272</v>
+        <v>-470.74915855</v>
       </c>
       <c r="D91" t="n">
-        <v>-1014.76569765</v>
+        <v>-485.13908238</v>
       </c>
       <c r="E91" t="n">
-        <v>-840.5265649600001</v>
+        <v>-531.52777423</v>
       </c>
       <c r="F91" t="n">
-        <v>-777.2582415900001</v>
+        <v>-279.35505049</v>
       </c>
       <c r="G91" t="n">
-        <v>-232.52714159</v>
+        <v>-577.8359113299999</v>
       </c>
       <c r="H91" t="n">
-        <v>-937.11580989</v>
+        <v>-824.0437270499999</v>
       </c>
       <c r="I91" t="n">
-        <v>-1512.48922155</v>
+        <v>-1055.54506517</v>
       </c>
       <c r="J91" t="n">
-        <v>-2005.57788128</v>
+        <v>-1055.64407792</v>
       </c>
       <c r="K91" t="n">
-        <v>-2148.39575892</v>
+        <v>-326.93291329</v>
       </c>
       <c r="L91" t="n">
-        <v>-621.93563805</v>
+        <v>-685.6039252299998</v>
       </c>
       <c r="M91" t="n">
-        <v>-1410.80683404</v>
+        <v>-874.10051376</v>
       </c>
     </row>
     <row r="92">
@@ -4209,37 +4213,37 @@
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>-1209.79725867</v>
+        <v>-433.73346051</v>
       </c>
       <c r="D92" t="n">
-        <v>-394.98546916</v>
+        <v>806.5171311299999</v>
       </c>
       <c r="E92" t="n">
-        <v>807.19972316</v>
+        <v>-167.88835007</v>
       </c>
       <c r="F92" t="n">
-        <v>-143.08203782</v>
+        <v>-11.75600005000001</v>
       </c>
       <c r="G92" t="n">
-        <v>29.72846714999998</v>
+        <v>-1172.87832086</v>
       </c>
       <c r="H92" t="n">
-        <v>-1156.97070077</v>
+        <v>-35.76254806999992</v>
       </c>
       <c r="I92" t="n">
-        <v>-26.00681758999992</v>
+        <v>-127.70470049</v>
       </c>
       <c r="J92" t="n">
-        <v>-147.75625942</v>
+        <v>-456.25515482</v>
       </c>
       <c r="K92" t="n">
-        <v>-473.75673339</v>
+        <v>512.9469588100001</v>
       </c>
       <c r="L92" t="n">
-        <v>527.4104596</v>
+        <v>-504.77581997</v>
       </c>
       <c r="M92" t="n">
-        <v>-553.7174667100001</v>
+        <v>-1267.46074306</v>
       </c>
     </row>
     <row r="93">
@@ -4250,37 +4254,37 @@
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>-3.998096980000008</v>
+        <v>-110.70001883</v>
       </c>
       <c r="D93" t="n">
-        <v>-110.70243297</v>
+        <v>6.201356979999997</v>
       </c>
       <c r="E93" t="n">
-        <v>6.200496799999999</v>
+        <v>97.14637482000001</v>
       </c>
       <c r="F93" t="n">
-        <v>97.14551906</v>
+        <v>65.14308164000001</v>
       </c>
       <c r="G93" t="n">
-        <v>65.14495000000001</v>
+        <v>-20.06744734</v>
       </c>
       <c r="H93" t="n">
-        <v>-20.06332136</v>
+        <v>-141.52817454</v>
       </c>
       <c r="I93" t="n">
-        <v>-141.52650904</v>
+        <v>-80.82108792</v>
       </c>
       <c r="J93" t="n">
-        <v>-80.82240035</v>
+        <v>4.55315406</v>
       </c>
       <c r="K93" t="n">
-        <v>4.54919342</v>
+        <v>157.24168626</v>
       </c>
       <c r="L93" t="n">
-        <v>157.23986864</v>
+        <v>-5.068348040000001</v>
       </c>
       <c r="M93" t="n">
-        <v>-5.068777900000002</v>
+        <v>-120.02153486</v>
       </c>
     </row>
     <row r="94">
@@ -4291,37 +4295,37 @@
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>100.88904485</v>
+        <v>176.06148637</v>
       </c>
       <c r="D94" t="n">
-        <v>137.31590916</v>
+        <v>199.25781802</v>
       </c>
       <c r="E94" t="n">
-        <v>198.57608617</v>
+        <v>116.38953113</v>
       </c>
       <c r="F94" t="n">
-        <v>91.58407464</v>
+        <v>44.33213470999999</v>
       </c>
       <c r="G94" t="n">
-        <v>2.84579915</v>
+        <v>105.36387486</v>
       </c>
       <c r="H94" t="n">
-        <v>89.45212879</v>
+        <v>109.32295593</v>
       </c>
       <c r="I94" t="n">
-        <v>99.56555995000001</v>
+        <v>164.17161745</v>
       </c>
       <c r="J94" t="n">
-        <v>184.22448881</v>
+        <v>223.01891032</v>
       </c>
       <c r="K94" t="n">
-        <v>240.52444953</v>
+        <v>144.92671263</v>
       </c>
       <c r="L94" t="n">
-        <v>130.46502946</v>
+        <v>101.7461128</v>
       </c>
       <c r="M94" t="n">
-        <v>150.6881894</v>
+        <v>-89.03653050999999</v>
       </c>
     </row>
     <row r="95">
@@ -4332,37 +4336,37 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>3999.20590199</v>
+        <v>884.4743874199997</v>
       </c>
       <c r="D95" t="n">
-        <v>1762.63583123</v>
+        <v>1617.73891508</v>
       </c>
       <c r="E95" t="n">
-        <v>2552.71020422</v>
+        <v>2457.80099751</v>
       </c>
       <c r="F95" t="n">
-        <v>3352.5478127</v>
+        <v>2790.69579102</v>
       </c>
       <c r="G95" t="n">
-        <v>2886.99522768</v>
+        <v>977.25624004</v>
       </c>
       <c r="H95" t="n">
-        <v>398.4060898100001</v>
+        <v>-1482.82945407</v>
       </c>
       <c r="I95" t="n">
-        <v>-3396.75229127</v>
+        <v>-1904.38526962</v>
       </c>
       <c r="J95" t="n">
-        <v>-3813.35342558</v>
+        <v>-1256.94743565</v>
       </c>
       <c r="K95" t="n">
-        <v>-3126.49078176</v>
+        <v>-1397.76517245</v>
       </c>
       <c r="L95" t="n">
-        <v>-3111.00042372</v>
+        <v>-2285.96555667</v>
       </c>
       <c r="M95" t="n">
-        <v>-3739.27661508</v>
+        <v>-5136.93517469</v>
       </c>
     </row>
     <row r="96">
@@ -4373,37 +4377,37 @@
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>317.72942932</v>
+        <v>43.45239911</v>
       </c>
       <c r="D96" t="n">
-        <v>5.791317389999997</v>
+        <v>-24.72223465000001</v>
       </c>
       <c r="E96" t="n">
-        <v>12.15852532999999</v>
+        <v>-328.47747728</v>
       </c>
       <c r="F96" t="n">
-        <v>-379.72493019</v>
+        <v>-548.62950641</v>
       </c>
       <c r="G96" t="n">
-        <v>-564.06818734</v>
+        <v>-582.2291348799999</v>
       </c>
       <c r="H96" t="n">
-        <v>-653.8013840599999</v>
+        <v>-615.6505054400001</v>
       </c>
       <c r="I96" t="n">
-        <v>-748.07666977</v>
+        <v>-621.70691772</v>
       </c>
       <c r="J96" t="n">
-        <v>-766.2916985000001</v>
+        <v>-428.221756</v>
       </c>
       <c r="K96" t="n">
-        <v>-583.1377750299999</v>
+        <v>-447.85606706</v>
       </c>
       <c r="L96" t="n">
-        <v>-495.62078918</v>
+        <v>-331.70381063</v>
       </c>
       <c r="M96" t="n">
-        <v>-390.00583392</v>
+        <v>-463.23062184</v>
       </c>
     </row>
     <row r="97">
@@ -4414,37 +4418,37 @@
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>93.37706496000001</v>
+        <v>833.3958264300001</v>
       </c>
       <c r="D97" t="n">
-        <v>-7.104535660000006</v>
+        <v>1058.51929207</v>
       </c>
       <c r="E97" t="n">
-        <v>86.66724294999999</v>
+        <v>966.08941626</v>
       </c>
       <c r="F97" t="n">
-        <v>122.59005398</v>
+        <v>237.41331469</v>
       </c>
       <c r="G97" t="n">
-        <v>156.55255896</v>
+        <v>-658.57443563</v>
       </c>
       <c r="H97" t="n">
-        <v>-8.152036220000001</v>
+        <v>-1953.99405983</v>
       </c>
       <c r="I97" t="n">
-        <v>92.3549417</v>
+        <v>-2091.88532349</v>
       </c>
       <c r="J97" t="n">
-        <v>-38.33238675</v>
+        <v>-2188.66228933</v>
       </c>
       <c r="K97" t="n">
-        <v>-164.20292419</v>
+        <v>-1829.25949117</v>
       </c>
       <c r="L97" t="n">
-        <v>-68.25951778</v>
+        <v>-1517.81351032</v>
       </c>
       <c r="M97" t="n">
-        <v>-6.200428619999998</v>
+        <v>-1861.93314449</v>
       </c>
     </row>
     <row r="98">
@@ -4455,37 +4459,37 @@
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
-        <v>17.61837582</v>
+        <v>27.36598622</v>
       </c>
       <c r="D98" t="n">
-        <v>27.36598622</v>
+        <v>21.46284854</v>
       </c>
       <c r="E98" t="n">
-        <v>21.46284854</v>
+        <v>2.43384234</v>
       </c>
       <c r="F98" t="n">
-        <v>2.43384234</v>
+        <v>3.42921125</v>
       </c>
       <c r="G98" t="n">
-        <v>3.42921125</v>
+        <v>20.06839899</v>
       </c>
       <c r="H98" t="n">
-        <v>20.06839899</v>
+        <v>29.26418117</v>
       </c>
       <c r="I98" t="n">
-        <v>29.26418117</v>
+        <v>17.238713</v>
       </c>
       <c r="J98" t="n">
-        <v>17.238713</v>
+        <v>24.67003403</v>
       </c>
       <c r="K98" t="n">
-        <v>24.67003403</v>
+        <v>34.21972625</v>
       </c>
       <c r="L98" t="n">
-        <v>34.21972625</v>
+        <v>36.67212921999999</v>
       </c>
       <c r="M98" t="n">
-        <v>36.67212921999999</v>
+        <v>25.20784637</v>
       </c>
     </row>
     <row r="99">
@@ -4496,37 +4500,37 @@
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>12.72317876</v>
+        <v>17.26166795</v>
       </c>
       <c r="D99" t="n">
-        <v>17.20167136</v>
+        <v>6.075726189999999</v>
       </c>
       <c r="E99" t="n">
-        <v>5.82127413</v>
+        <v>-1.47041395</v>
       </c>
       <c r="F99" t="n">
-        <v>-1.51808174</v>
+        <v>-12.68523507</v>
       </c>
       <c r="G99" t="n">
-        <v>-12.99658263</v>
+        <v>-16.25005949</v>
       </c>
       <c r="H99" t="n">
-        <v>-16.94004654</v>
+        <v>-10.87937043</v>
       </c>
       <c r="I99" t="n">
-        <v>-11.90809048</v>
+        <v>4.36138133</v>
       </c>
       <c r="J99" t="n">
-        <v>3.03967369</v>
+        <v>2.550761389999999</v>
       </c>
       <c r="K99" t="n">
-        <v>2.450110249999999</v>
+        <v>5.33204738</v>
       </c>
       <c r="L99" t="n">
-        <v>4.71725531</v>
+        <v>7.818490239999999</v>
       </c>
       <c r="M99" t="n">
-        <v>5.754929999999999</v>
+        <v>-4.54547223</v>
       </c>
     </row>
     <row r="100">
@@ -4537,37 +4541,37 @@
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="n">
-        <v>-51.18432531</v>
+        <v>-94.32169284999999</v>
       </c>
       <c r="D100" t="n">
-        <v>-94.26169625999999</v>
+        <v>-157.36599739</v>
       </c>
       <c r="E100" t="n">
-        <v>-157.11154533</v>
+        <v>-218.54965054</v>
       </c>
       <c r="F100" t="n">
-        <v>-218.50198275</v>
+        <v>-239.318106</v>
       </c>
       <c r="G100" t="n">
-        <v>-239.00675844</v>
+        <v>-229.81989502</v>
       </c>
       <c r="H100" t="n">
-        <v>-229.12990797</v>
+        <v>-223.32690569</v>
       </c>
       <c r="I100" t="n">
-        <v>-222.29818564</v>
+        <v>-73.25274198000001</v>
       </c>
       <c r="J100" t="n">
-        <v>-71.93103434</v>
+        <v>16.3684944</v>
       </c>
       <c r="K100" t="n">
-        <v>16.46914554</v>
+        <v>-17.95734398</v>
       </c>
       <c r="L100" t="n">
-        <v>-17.34255191</v>
+        <v>-34.63364573</v>
       </c>
       <c r="M100" t="n">
-        <v>-32.57008549</v>
+        <v>-47.55095419</v>
       </c>
     </row>
   </sheetData>

--- a/Result/analyze_2.xlsx
+++ b/Result/analyze_2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M100"/>
+  <dimension ref="A1:M101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
     </row>
@@ -503,37 +503,37 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1090.07558463</v>
+        <v>166.33007659</v>
       </c>
       <c r="D2" t="n">
-        <v>151.91773738</v>
+        <v>727.06237172</v>
       </c>
       <c r="E2" t="n">
-        <v>726.90928567</v>
+        <v>821.53641256</v>
       </c>
       <c r="F2" t="n">
-        <v>786.60943803</v>
+        <v>747.53890915</v>
       </c>
       <c r="G2" t="n">
-        <v>708.8842369299999</v>
+        <v>1788.09072544</v>
       </c>
       <c r="H2" t="n">
-        <v>1783.37409329</v>
+        <v>-150.22302371</v>
       </c>
       <c r="I2" t="n">
-        <v>-145.63833015</v>
+        <v>99.50102479999998</v>
       </c>
       <c r="J2" t="n">
-        <v>101.2267009</v>
+        <v>214.34266477</v>
       </c>
       <c r="K2" t="n">
-        <v>207.3858346</v>
+        <v>-90.31634846</v>
       </c>
       <c r="L2" t="n">
-        <v>-87.39109071</v>
+        <v>-899.7044331999999</v>
       </c>
       <c r="M2" t="n">
-        <v>-892.0108127399999</v>
+        <v>-250.37099098</v>
       </c>
     </row>
     <row r="3">
@@ -542,39 +542,41 @@
           <t>光電業右下</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
       <c r="C3" t="n">
-        <v>140.59546247</v>
+        <v>47.23345665999999</v>
       </c>
       <c r="D3" t="n">
-        <v>58.50494856</v>
+        <v>-54.49049336</v>
       </c>
       <c r="E3" t="n">
-        <v>-47.13305369</v>
+        <v>44.67072405</v>
       </c>
       <c r="F3" t="n">
-        <v>26.35795273</v>
+        <v>132.65074532</v>
       </c>
       <c r="G3" t="n">
-        <v>115.87357209</v>
+        <v>126.84044948</v>
       </c>
       <c r="H3" t="n">
-        <v>128.58963539</v>
+        <v>96.03657348999999</v>
       </c>
       <c r="I3" t="n">
-        <v>131.89171887</v>
+        <v>164.64025374</v>
       </c>
       <c r="J3" t="n">
-        <v>238.37577133</v>
+        <v>251.60276894</v>
       </c>
       <c r="K3" t="n">
-        <v>307.75556055</v>
+        <v>186.48798612</v>
       </c>
       <c r="L3" t="n">
-        <v>236.10169612</v>
+        <v>-18.89719598</v>
       </c>
       <c r="M3" t="n">
-        <v>-24.40457867</v>
+        <v>256.36204702</v>
       </c>
     </row>
     <row r="4">
@@ -585,37 +587,37 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>47.41035247</v>
+        <v>208.28268441</v>
       </c>
       <c r="D4" t="n">
-        <v>211.47174397</v>
+        <v>-66.69191041999999</v>
       </c>
       <c r="E4" t="n">
-        <v>-73.86853386999999</v>
+        <v>-31.97543567999999</v>
       </c>
       <c r="F4" t="n">
-        <v>21.29332980000001</v>
+        <v>-53.59916159000001</v>
       </c>
       <c r="G4" t="n">
-        <v>1.869937859999985</v>
+        <v>-65.27981079000001</v>
       </c>
       <c r="H4" t="n">
-        <v>-62.26718312000001</v>
+        <v>-145.09569795</v>
       </c>
       <c r="I4" t="n">
-        <v>-185.50155132</v>
+        <v>-143.8945201</v>
       </c>
       <c r="J4" t="n">
-        <v>-219.33741223</v>
+        <v>119.47234483</v>
       </c>
       <c r="K4" t="n">
-        <v>70.2855538</v>
+        <v>200.95783303</v>
       </c>
       <c r="L4" t="n">
-        <v>148.44488018</v>
+        <v>-105.42714588</v>
       </c>
       <c r="M4" t="n">
-        <v>-107.55015101</v>
+        <v>120.81696595</v>
       </c>
     </row>
     <row r="5">
@@ -626,37 +628,37 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>-38.63470381</v>
+        <v>-259.63819733</v>
       </c>
       <c r="D5" t="n">
-        <v>-259.31952944</v>
+        <v>-387.43622092</v>
       </c>
       <c r="E5" t="n">
-        <v>-387.10508662</v>
+        <v>-428.94029793</v>
       </c>
       <c r="F5" t="n">
-        <v>-428.41056918</v>
+        <v>-414.56281904</v>
       </c>
       <c r="G5" t="n">
-        <v>-414.44013366</v>
+        <v>-487.76732049</v>
       </c>
       <c r="H5" t="n">
-        <v>-488.47393708</v>
+        <v>-416.49802748</v>
       </c>
       <c r="I5" t="n">
-        <v>-416.87207636</v>
+        <v>-353.20717254</v>
       </c>
       <c r="J5" t="n">
-        <v>-354.1363297</v>
+        <v>-249.69010529</v>
       </c>
       <c r="K5" t="n">
-        <v>-250.13327652</v>
+        <v>-355.58396056</v>
       </c>
       <c r="L5" t="n">
-        <v>-355.59157241</v>
+        <v>-426.60047145</v>
       </c>
       <c r="M5" t="n">
-        <v>-426.40809136</v>
+        <v>-314.10521795</v>
       </c>
     </row>
     <row r="6">
@@ -665,41 +667,39 @@
           <t>其他右下</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>23.8340967</v>
+        <v>62.05962845000001</v>
       </c>
       <c r="D6" t="n">
-        <v>62.44199644</v>
+        <v>76.3975702</v>
       </c>
       <c r="E6" t="n">
-        <v>75.21006885</v>
+        <v>71.53023737999999</v>
       </c>
       <c r="F6" t="n">
-        <v>70.80507362</v>
+        <v>61.95066472</v>
       </c>
       <c r="G6" t="n">
-        <v>61.05628663</v>
+        <v>149.9594836</v>
       </c>
       <c r="H6" t="n">
-        <v>148.08338344</v>
+        <v>189.86291276</v>
       </c>
       <c r="I6" t="n">
-        <v>189.98701193</v>
+        <v>26.54004693999999</v>
       </c>
       <c r="J6" t="n">
-        <v>27.06366671999999</v>
+        <v>60.85895278999999</v>
       </c>
       <c r="K6" t="n">
-        <v>59.43793802</v>
+        <v>-16.84304757</v>
       </c>
       <c r="L6" t="n">
-        <v>-16.76787345999999</v>
+        <v>-82.56072512</v>
       </c>
       <c r="M6" t="n">
-        <v>-82.0723675</v>
+        <v>19.95677619000001</v>
       </c>
     </row>
     <row r="7">
@@ -710,37 +710,37 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>14.45395505</v>
+        <v>1.881915599999998</v>
       </c>
       <c r="D7" t="n">
-        <v>1.834345269999998</v>
+        <v>-7.03466275</v>
       </c>
       <c r="E7" t="n">
-        <v>-6.807581649999999</v>
+        <v>-31.45907946</v>
       </c>
       <c r="F7" t="n">
-        <v>-32.31644055</v>
+        <v>-25.88445367</v>
       </c>
       <c r="G7" t="n">
-        <v>-25.77772236</v>
+        <v>-25.96582669</v>
       </c>
       <c r="H7" t="n">
-        <v>-26.2212407</v>
+        <v>-33.36419939</v>
       </c>
       <c r="I7" t="n">
-        <v>-34.91714055</v>
+        <v>-48.85864626000001</v>
       </c>
       <c r="J7" t="n">
-        <v>-50.82166224000001</v>
+        <v>-22.28253555</v>
       </c>
       <c r="K7" t="n">
-        <v>-23.0987534</v>
+        <v>-6.9078939</v>
       </c>
       <c r="L7" t="n">
-        <v>-7.21434608</v>
+        <v>-15.80640138</v>
       </c>
       <c r="M7" t="n">
-        <v>-16.83103393</v>
+        <v>12.60122797</v>
       </c>
     </row>
     <row r="8">
@@ -751,37 +751,37 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>1470.79262695</v>
+        <v>3053.41075554</v>
       </c>
       <c r="D8" t="n">
-        <v>2857.49565018</v>
+        <v>3202.52327572</v>
       </c>
       <c r="E8" t="n">
-        <v>2696.70472936</v>
+        <v>3796.87637317</v>
       </c>
       <c r="F8" t="n">
-        <v>3193.33253514</v>
+        <v>879.33382147</v>
       </c>
       <c r="G8" t="n">
-        <v>783.54376217</v>
+        <v>2616.39038512</v>
       </c>
       <c r="H8" t="n">
-        <v>2204.70663249</v>
+        <v>2457.47533552</v>
       </c>
       <c r="I8" t="n">
-        <v>2426.97135045</v>
+        <v>3001.08307843</v>
       </c>
       <c r="J8" t="n">
-        <v>3280.19517416</v>
+        <v>2854.80618496</v>
       </c>
       <c r="K8" t="n">
-        <v>3443.16117847</v>
+        <v>-845.5506428999998</v>
       </c>
       <c r="L8" t="n">
-        <v>-68.84787009999998</v>
+        <v>-5232.96747133</v>
       </c>
       <c r="M8" t="n">
-        <v>-4331.160411569999</v>
+        <v>-2468.41463208</v>
       </c>
     </row>
     <row r="9">
@@ -794,37 +794,37 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.71563536</v>
+        <v>12.50674636</v>
       </c>
       <c r="D9" t="n">
-        <v>12.39496474</v>
+        <v>-56.48915796</v>
       </c>
       <c r="E9" t="n">
-        <v>-56.68166504</v>
+        <v>-83.07011645</v>
       </c>
       <c r="F9" t="n">
-        <v>-82.45231404</v>
+        <v>-91.20880308</v>
       </c>
       <c r="G9" t="n">
-        <v>-85.97938264</v>
+        <v>-123.59842429</v>
       </c>
       <c r="H9" t="n">
-        <v>-109.82733274</v>
+        <v>-130.50634116</v>
       </c>
       <c r="I9" t="n">
-        <v>-108.80447564</v>
+        <v>-119.54552704</v>
       </c>
       <c r="J9" t="n">
-        <v>-110.69811322</v>
+        <v>-109.75583036</v>
       </c>
       <c r="K9" t="n">
-        <v>-109.39143654</v>
+        <v>-113.58214254</v>
       </c>
       <c r="L9" t="n">
-        <v>-116.10055027</v>
+        <v>-89.98371306999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-93.26368867999999</v>
+        <v>-26.74912995</v>
       </c>
     </row>
     <row r="10">
@@ -835,37 +835,37 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>6.833367389999998</v>
+        <v>41.79643612</v>
       </c>
       <c r="D10" t="n">
-        <v>45.76534605</v>
+        <v>6.572641830000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-18.12366639</v>
+        <v>-11.64130752</v>
       </c>
       <c r="F10" t="n">
-        <v>-107.5375859</v>
+        <v>16.40119805</v>
       </c>
       <c r="G10" t="n">
-        <v>-93.76588418</v>
+        <v>0.2232690600000042</v>
       </c>
       <c r="H10" t="n">
-        <v>-135.47981988</v>
+        <v>22.12872621</v>
       </c>
       <c r="I10" t="n">
-        <v>-116.34511689</v>
+        <v>58.65766656</v>
       </c>
       <c r="J10" t="n">
-        <v>-103.29812568</v>
+        <v>132.67527158</v>
       </c>
       <c r="K10" t="n">
-        <v>-96.95473371999999</v>
+        <v>32.92321401</v>
       </c>
       <c r="L10" t="n">
-        <v>-103.92862233</v>
+        <v>-31.34194308</v>
       </c>
       <c r="M10" t="n">
-        <v>-111.97291779</v>
+        <v>-5.87676717</v>
       </c>
     </row>
     <row r="11">
@@ -876,37 +876,37 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>-57.61486382</v>
+        <v>-84.49990516000001</v>
       </c>
       <c r="D11" t="n">
-        <v>-84.49990516000001</v>
+        <v>-71.27952607</v>
       </c>
       <c r="E11" t="n">
-        <v>-71.27952607</v>
+        <v>-9.778319470000007</v>
       </c>
       <c r="F11" t="n">
-        <v>-9.778319470000007</v>
+        <v>31.64017136999999</v>
       </c>
       <c r="G11" t="n">
-        <v>31.64017136999999</v>
+        <v>-181.89193455</v>
       </c>
       <c r="H11" t="n">
-        <v>-181.89193455</v>
+        <v>-28.50699865000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-28.50699865000001</v>
+        <v>309.12090261</v>
       </c>
       <c r="J11" t="n">
-        <v>309.12090261</v>
+        <v>653.33942918</v>
       </c>
       <c r="K11" t="n">
-        <v>653.33942918</v>
+        <v>235.03869243</v>
       </c>
       <c r="L11" t="n">
-        <v>235.03869243</v>
+        <v>-34.09932765999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-34.09932765999999</v>
+        <v>-55.97849528000001</v>
       </c>
     </row>
     <row r="12">
@@ -915,41 +915,39 @@
           <t>化學工業右下</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>-106.15223612</v>
+        <v>-24.1839077</v>
       </c>
       <c r="D12" t="n">
-        <v>-22.38041667999999</v>
+        <v>360.88587043</v>
       </c>
       <c r="E12" t="n">
-        <v>360.01811206</v>
+        <v>240.79024745</v>
       </c>
       <c r="F12" t="n">
-        <v>239.49278571</v>
+        <v>174.45549045</v>
       </c>
       <c r="G12" t="n">
-        <v>173.02896927</v>
+        <v>-44.77826097</v>
       </c>
       <c r="H12" t="n">
-        <v>-44.28497224</v>
+        <v>-24.94843443</v>
       </c>
       <c r="I12" t="n">
-        <v>-22.13560097</v>
+        <v>-1.646659229999999</v>
       </c>
       <c r="J12" t="n">
-        <v>2.70338473</v>
+        <v>48.42108592</v>
       </c>
       <c r="K12" t="n">
-        <v>58.76884053</v>
+        <v>-29.5051251</v>
       </c>
       <c r="L12" t="n">
-        <v>-14.08458902</v>
+        <v>-158.29387524</v>
       </c>
       <c r="M12" t="n">
-        <v>-152.02836988</v>
+        <v>-58.16080901999999</v>
       </c>
     </row>
     <row r="13">
@@ -960,37 +958,37 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>-2.21215822</v>
+        <v>4.685124039999999</v>
       </c>
       <c r="D13" t="n">
-        <v>2.88137664</v>
+        <v>-8.545298240000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.67681854</v>
+        <v>-5.38860886</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.089695679999999</v>
+        <v>19.87027765</v>
       </c>
       <c r="G13" t="n">
-        <v>21.29562269</v>
+        <v>44.61603315999999</v>
       </c>
       <c r="H13" t="n">
-        <v>44.12017899</v>
+        <v>24.77175709</v>
       </c>
       <c r="I13" t="n">
-        <v>21.95574711</v>
+        <v>26.09155093</v>
       </c>
       <c r="J13" t="n">
-        <v>21.73672541000001</v>
+        <v>40.69527474</v>
       </c>
       <c r="K13" t="n">
-        <v>30.34853865</v>
+        <v>28.52291632</v>
       </c>
       <c r="L13" t="n">
-        <v>13.10436976</v>
+        <v>0.3586162699999996</v>
       </c>
       <c r="M13" t="n">
-        <v>-5.90438728</v>
+        <v>12.62378296</v>
       </c>
     </row>
     <row r="14">
@@ -1001,37 +999,37 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>-3741.12802511</v>
+        <v>5117.54882845</v>
       </c>
       <c r="D14" t="n">
-        <v>5092.684053989999</v>
+        <v>1789.16172274</v>
       </c>
       <c r="E14" t="n">
-        <v>1795.11592831</v>
+        <v>7301.843694679999</v>
       </c>
       <c r="F14" t="n">
-        <v>7285.72629368</v>
+        <v>4082.40427775</v>
       </c>
       <c r="G14" t="n">
-        <v>4052.47761611</v>
+        <v>7624.41259415</v>
       </c>
       <c r="H14" t="n">
-        <v>7580.91730309</v>
+        <v>4044.50392003</v>
       </c>
       <c r="I14" t="n">
-        <v>4000.9836017</v>
+        <v>4572.939547319999</v>
       </c>
       <c r="J14" t="n">
-        <v>4548.563723889999</v>
+        <v>1420.59826702</v>
       </c>
       <c r="K14" t="n">
-        <v>1421.6717039</v>
+        <v>734.4927191700001</v>
       </c>
       <c r="L14" t="n">
-        <v>754.4407251499999</v>
+        <v>-9376.83330516</v>
       </c>
       <c r="M14" t="n">
-        <v>-9345.922801280001</v>
+        <v>-2593.98248721</v>
       </c>
     </row>
     <row r="15">
@@ -1040,41 +1038,39 @@
           <t>半導體業右下</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>-118.82287651</v>
+        <v>-321.5083467700001</v>
       </c>
       <c r="D15" t="n">
-        <v>-325.73320421</v>
+        <v>58.78316310000007</v>
       </c>
       <c r="E15" t="n">
-        <v>44.70852931000003</v>
+        <v>-503.54256198</v>
       </c>
       <c r="F15" t="n">
-        <v>-517.70621518</v>
+        <v>439.29170641</v>
       </c>
       <c r="G15" t="n">
-        <v>411.72784859</v>
+        <v>-39.31170931999996</v>
       </c>
       <c r="H15" t="n">
-        <v>-80.12825020999998</v>
+        <v>625.77616114</v>
       </c>
       <c r="I15" t="n">
-        <v>606.13821407</v>
+        <v>664.08159973</v>
       </c>
       <c r="J15" t="n">
-        <v>653.4195649200001</v>
+        <v>172.22682514</v>
       </c>
       <c r="K15" t="n">
-        <v>164.81433669</v>
+        <v>-169.31351507</v>
       </c>
       <c r="L15" t="n">
-        <v>-175.78176315</v>
+        <v>-111.95180094</v>
       </c>
       <c r="M15" t="n">
-        <v>-122.62350856</v>
+        <v>483.0900513300001</v>
       </c>
     </row>
     <row r="16">
@@ -1085,37 +1081,37 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>-1077.63965973</v>
+        <v>-140.97029727</v>
       </c>
       <c r="D16" t="n">
-        <v>-102.6001831</v>
+        <v>-185.01016598</v>
       </c>
       <c r="E16" t="n">
-        <v>-187.30067927</v>
+        <v>25.83382691000003</v>
       </c>
       <c r="F16" t="n">
-        <v>58.27291674000001</v>
+        <v>-225.16591121</v>
       </c>
       <c r="G16" t="n">
-        <v>-187.66411075</v>
+        <v>214.35491383</v>
       </c>
       <c r="H16" t="n">
-        <v>273.43466368</v>
+        <v>108.14753678</v>
       </c>
       <c r="I16" t="n">
-        <v>129.63155696</v>
+        <v>-440.57939058</v>
       </c>
       <c r="J16" t="n">
-        <v>-425.0015046099999</v>
+        <v>278.6670229699999</v>
       </c>
       <c r="K16" t="n">
-        <v>282.76584949</v>
+        <v>-361.18218617</v>
       </c>
       <c r="L16" t="n">
-        <v>-364.47517977</v>
+        <v>-695.61679127</v>
       </c>
       <c r="M16" t="n">
-        <v>-697.2965504299999</v>
+        <v>-665.33908921</v>
       </c>
     </row>
     <row r="17">
@@ -1126,37 +1122,37 @@
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
-        <v>0.84933853</v>
+        <v>-0.12911185</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.12911185</v>
+        <v>0.18345265</v>
       </c>
       <c r="E17" t="n">
-        <v>0.18345265</v>
+        <v>-0.75565477</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.75565477</v>
+        <v>-1.09301157</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.09301157</v>
+        <v>-1.25991411</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.25991411</v>
+        <v>0.42586555</v>
       </c>
       <c r="I17" t="n">
-        <v>0.42586555</v>
+        <v>1.11311752</v>
       </c>
       <c r="J17" t="n">
-        <v>1.11311752</v>
+        <v>0.08433128999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.08433128999999999</v>
+        <v>-0.35153504</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.35153504</v>
+        <v>-0.7377812500000001</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7377812500000001</v>
+        <v>-0.09023301</v>
       </c>
     </row>
     <row r="18">
@@ -1167,37 +1163,37 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>-452.58295967</v>
+        <v>-531.6617434799999</v>
       </c>
       <c r="D18" t="n">
-        <v>-531.6617434799999</v>
+        <v>-603.5171211700001</v>
       </c>
       <c r="E18" t="n">
-        <v>-603.5171211700001</v>
+        <v>-1.170012629999998</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.170012629999998</v>
+        <v>755.74136299</v>
       </c>
       <c r="G18" t="n">
-        <v>755.74136299</v>
+        <v>808.41838966</v>
       </c>
       <c r="H18" t="n">
-        <v>808.41838966</v>
+        <v>20.05482964</v>
       </c>
       <c r="I18" t="n">
-        <v>20.05482964</v>
+        <v>397.91409635</v>
       </c>
       <c r="J18" t="n">
-        <v>397.91409635</v>
+        <v>941.82636841</v>
       </c>
       <c r="K18" t="n">
-        <v>941.82636841</v>
+        <v>-199.10421778</v>
       </c>
       <c r="L18" t="n">
-        <v>-199.10421778</v>
+        <v>-682.83194151</v>
       </c>
       <c r="M18" t="n">
-        <v>-682.83194151</v>
+        <v>76.18796667000002</v>
       </c>
     </row>
     <row r="19">
@@ -1208,37 +1204,37 @@
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>-0.45935476</v>
+        <v>-5.09463389</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.09463389</v>
+        <v>-16.04657688</v>
       </c>
       <c r="E19" t="n">
-        <v>-16.04657688</v>
+        <v>-16.7282934</v>
       </c>
       <c r="F19" t="n">
-        <v>-16.7282934</v>
+        <v>-9.796063780000001</v>
       </c>
       <c r="G19" t="n">
-        <v>-9.796063780000001</v>
+        <v>-1.05380141</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.05380141</v>
+        <v>2.68419108</v>
       </c>
       <c r="I19" t="n">
-        <v>2.68419108</v>
+        <v>5.168692590000001</v>
       </c>
       <c r="J19" t="n">
-        <v>5.168692590000001</v>
+        <v>0.5556269400000001</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5556269400000001</v>
+        <v>-0.8401518099999999</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.8401518099999999</v>
+        <v>-3.47672728</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.47672728</v>
+        <v>1.25178956</v>
       </c>
     </row>
     <row r="20">
@@ -1249,37 +1245,37 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>-11.38791094</v>
+        <v>39.90392790999999</v>
       </c>
       <c r="D20" t="n">
-        <v>39.90390299</v>
+        <v>-7.49896809</v>
       </c>
       <c r="E20" t="n">
-        <v>-7.499015480000001</v>
+        <v>-34.65192705</v>
       </c>
       <c r="F20" t="n">
-        <v>-34.65196079</v>
+        <v>-20.07589765</v>
       </c>
       <c r="G20" t="n">
-        <v>-20.07586818</v>
+        <v>37.03990992</v>
       </c>
       <c r="H20" t="n">
-        <v>37.03994246</v>
+        <v>61.97436829999999</v>
       </c>
       <c r="I20" t="n">
-        <v>61.97440654</v>
+        <v>4.78448792</v>
       </c>
       <c r="J20" t="n">
-        <v>4.784528130000001</v>
+        <v>-26.5797665</v>
       </c>
       <c r="K20" t="n">
-        <v>-26.57971293</v>
+        <v>-51.94194045</v>
       </c>
       <c r="L20" t="n">
-        <v>-51.94192612000001</v>
+        <v>-0.4217290099999998</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.42173321</v>
+        <v>-23.83090088</v>
       </c>
     </row>
     <row r="21">
@@ -1288,39 +1284,41 @@
           <t>居家生活右下</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
       <c r="C21" t="n">
-        <v>2.61610241</v>
+        <v>1.28583045</v>
       </c>
       <c r="D21" t="n">
-        <v>1.28616523</v>
+        <v>-2.43984143</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4394692</v>
+        <v>-7.15899586</v>
       </c>
       <c r="F21" t="n">
-        <v>-7.15915474</v>
+        <v>-1.9665216</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.96615361</v>
+        <v>-1.02758461</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.02725691</v>
+        <v>2.7858135</v>
       </c>
       <c r="I21" t="n">
-        <v>2.78603437</v>
+        <v>1.57265017</v>
       </c>
       <c r="J21" t="n">
-        <v>1.57257115</v>
+        <v>-0.11769773</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.11746601</v>
+        <v>-1.28430574</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.28445344</v>
+        <v>-3.1636393</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.1639559</v>
+        <v>-3.19371817</v>
       </c>
     </row>
     <row r="22">
@@ -1331,37 +1329,37 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>1.84201992</v>
+        <v>2.0682052</v>
       </c>
       <c r="D22" t="n">
-        <v>2.06787042</v>
+        <v>2.13372424</v>
       </c>
       <c r="E22" t="n">
-        <v>2.13335201</v>
+        <v>0.9927766899999999</v>
       </c>
       <c r="F22" t="n">
-        <v>0.99293557</v>
+        <v>-0.03595326999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.03632125999999999</v>
+        <v>0.96984157</v>
       </c>
       <c r="H22" t="n">
-        <v>0.96951387</v>
+        <v>1.21441183</v>
       </c>
       <c r="I22" t="n">
-        <v>1.21419096</v>
+        <v>2.1806725</v>
       </c>
       <c r="J22" t="n">
-        <v>2.18075152</v>
+        <v>0.27043521</v>
       </c>
       <c r="K22" t="n">
-        <v>0.27020349</v>
+        <v>0.97694012</v>
       </c>
       <c r="L22" t="n">
-        <v>0.9770878199999999</v>
+        <v>-0.11805477</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.11773817</v>
+        <v>1.62020539</v>
       </c>
     </row>
     <row r="23">
@@ -1372,37 +1370,37 @@
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
-        <v>17.34516254</v>
+        <v>14.4164355</v>
       </c>
       <c r="D23" t="n">
-        <v>10.97105729</v>
+        <v>17.70036151</v>
       </c>
       <c r="E23" t="n">
-        <v>14.71366628</v>
+        <v>29.79123508</v>
       </c>
       <c r="F23" t="n">
-        <v>25.86071722</v>
+        <v>65.34342972</v>
       </c>
       <c r="G23" t="n">
-        <v>61.50125926</v>
+        <v>67.63610528999999</v>
       </c>
       <c r="H23" t="n">
-        <v>67.72635014999999</v>
+        <v>69.97203975999999</v>
       </c>
       <c r="I23" t="n">
-        <v>73.11968537</v>
+        <v>133.0464327</v>
       </c>
       <c r="J23" t="n">
-        <v>134.38144712</v>
+        <v>130.6413759</v>
       </c>
       <c r="K23" t="n">
-        <v>128.60747793</v>
+        <v>58.89268668</v>
       </c>
       <c r="L23" t="n">
-        <v>54.72903168000001</v>
+        <v>0.1293569200000017</v>
       </c>
       <c r="M23" t="n">
-        <v>-6.258354399999998</v>
+        <v>-20.18880538</v>
       </c>
     </row>
     <row r="24">
@@ -1411,41 +1409,39 @@
           <t>建材營造右下</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
-        <v>-16.31533705</v>
+        <v>-19.81364729</v>
       </c>
       <c r="D24" t="n">
-        <v>-46.41851334</v>
+        <v>-42.19567303</v>
       </c>
       <c r="E24" t="n">
-        <v>-61.32108313</v>
+        <v>-43.48162687</v>
       </c>
       <c r="F24" t="n">
-        <v>-68.27193079999999</v>
+        <v>-44.82396193</v>
       </c>
       <c r="G24" t="n">
-        <v>-77.0040529</v>
+        <v>-27.54116608</v>
       </c>
       <c r="H24" t="n">
-        <v>-9.682483549999999</v>
+        <v>5.802407629999999</v>
       </c>
       <c r="I24" t="n">
-        <v>1.74148469</v>
+        <v>28.91059504</v>
       </c>
       <c r="J24" t="n">
-        <v>13.04511441</v>
+        <v>38.83488594</v>
       </c>
       <c r="K24" t="n">
-        <v>7.141467479999999</v>
+        <v>27.87649351</v>
       </c>
       <c r="L24" t="n">
-        <v>-8.145874860000001</v>
+        <v>4.830213819999999</v>
       </c>
       <c r="M24" t="n">
-        <v>-43.37187738</v>
+        <v>24.18946009</v>
       </c>
     </row>
     <row r="25">
@@ -1456,37 +1452,37 @@
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>37.12761154</v>
+        <v>28.92968096</v>
       </c>
       <c r="D25" t="n">
-        <v>38.26432395</v>
+        <v>5.039214669999998</v>
       </c>
       <c r="E25" t="n">
-        <v>13.15924753</v>
+        <v>3.045110259999998</v>
       </c>
       <c r="F25" t="n">
-        <v>20.67896918</v>
+        <v>-0.5611396100000007</v>
       </c>
       <c r="G25" t="n">
-        <v>18.91207722</v>
+        <v>43.10616236</v>
       </c>
       <c r="H25" t="n">
-        <v>5.190265300000001</v>
+        <v>48.95726033</v>
       </c>
       <c r="I25" t="n">
-        <v>29.06947743</v>
+        <v>36.84770491</v>
       </c>
       <c r="J25" t="n">
-        <v>34.67251390000001</v>
+        <v>34.9128072</v>
       </c>
       <c r="K25" t="n">
-        <v>48.58322851</v>
+        <v>-24.95374618</v>
       </c>
       <c r="L25" t="n">
-        <v>3.014457449999998</v>
+        <v>-98.21648068</v>
       </c>
       <c r="M25" t="n">
-        <v>-49.21154851</v>
+        <v>-61.90102278</v>
       </c>
     </row>
     <row r="26">
@@ -1497,37 +1493,37 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>5.88787313</v>
+        <v>7.593937100000001</v>
       </c>
       <c r="D26" t="n">
-        <v>7.593937100000001</v>
+        <v>5.17181729</v>
       </c>
       <c r="E26" t="n">
-        <v>5.17181729</v>
+        <v>7.592146520000001</v>
       </c>
       <c r="F26" t="n">
-        <v>7.592146520000001</v>
+        <v>18.69060947</v>
       </c>
       <c r="G26" t="n">
-        <v>18.69060947</v>
+        <v>6.72654781</v>
       </c>
       <c r="H26" t="n">
-        <v>6.72654781</v>
+        <v>5.82618834</v>
       </c>
       <c r="I26" t="n">
-        <v>5.82618834</v>
+        <v>6.19496605</v>
       </c>
       <c r="J26" t="n">
-        <v>6.19496605</v>
+        <v>7.53425048</v>
       </c>
       <c r="K26" t="n">
-        <v>7.53425048</v>
+        <v>1.57906642</v>
       </c>
       <c r="L26" t="n">
-        <v>1.57906642</v>
+        <v>-2.91136613</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.91136613</v>
+        <v>-5.8194749</v>
       </c>
     </row>
     <row r="27">
@@ -1536,39 +1532,41 @@
           <t>數位雲端右下</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
       <c r="C27" t="n">
-        <v>9.126986050000001</v>
+        <v>20.9692142</v>
       </c>
       <c r="D27" t="n">
-        <v>22.17120965</v>
+        <v>17.8015275</v>
       </c>
       <c r="E27" t="n">
-        <v>17.62114185</v>
+        <v>22.24719139</v>
       </c>
       <c r="F27" t="n">
-        <v>22.73835175</v>
+        <v>32.06856501</v>
       </c>
       <c r="G27" t="n">
-        <v>29.64031750000001</v>
+        <v>32.97035718</v>
       </c>
       <c r="H27" t="n">
-        <v>34.23960959</v>
+        <v>31.94434515</v>
       </c>
       <c r="I27" t="n">
-        <v>34.65264778</v>
+        <v>15.8825525</v>
       </c>
       <c r="J27" t="n">
-        <v>21.38763383</v>
+        <v>15.52765442</v>
       </c>
       <c r="K27" t="n">
-        <v>21.65209811</v>
+        <v>7.203424859999999</v>
       </c>
       <c r="L27" t="n">
-        <v>13.90380849</v>
+        <v>-2.98286342</v>
       </c>
       <c r="M27" t="n">
-        <v>4.021312670000001</v>
+        <v>-0.9376528699999984</v>
       </c>
     </row>
     <row r="28">
@@ -1579,37 +1577,37 @@
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>-27.74334681</v>
+        <v>-47.7503726</v>
       </c>
       <c r="D28" t="n">
-        <v>-47.7503726</v>
+        <v>-79.88660898000001</v>
       </c>
       <c r="E28" t="n">
-        <v>-79.88660898000001</v>
+        <v>-109.77231518</v>
       </c>
       <c r="F28" t="n">
-        <v>-109.77231518</v>
+        <v>-102.98757115</v>
       </c>
       <c r="G28" t="n">
-        <v>-102.98757115</v>
+        <v>-89.84861438999999</v>
       </c>
       <c r="H28" t="n">
-        <v>-89.84861438999999</v>
+        <v>-73.97514631</v>
       </c>
       <c r="I28" t="n">
-        <v>-73.97514631</v>
+        <v>-58.79575538</v>
       </c>
       <c r="J28" t="n">
-        <v>-58.79575538</v>
+        <v>-32.16641504</v>
       </c>
       <c r="K28" t="n">
-        <v>-32.16641504</v>
+        <v>-29.40265683</v>
       </c>
       <c r="L28" t="n">
-        <v>-29.40265683</v>
+        <v>-32.3931544</v>
       </c>
       <c r="M28" t="n">
-        <v>-32.3931544</v>
+        <v>-4.516689970000001</v>
       </c>
     </row>
     <row r="29">
@@ -1620,37 +1618,37 @@
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>0.07506878</v>
+        <v>0.03323846</v>
       </c>
       <c r="D29" t="n">
-        <v>0.03323846</v>
+        <v>0.00619917</v>
       </c>
       <c r="E29" t="n">
-        <v>0.00619917</v>
+        <v>0.01277118</v>
       </c>
       <c r="F29" t="n">
-        <v>0.01277118</v>
+        <v>-0.00653676</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.00653676</v>
+        <v>-0.01623805</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.01623805</v>
+        <v>-0.01854561</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.01854561</v>
+        <v>-0.0214375</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.0214375</v>
+        <v>-0.00590779</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.00590779</v>
+        <v>0.007246020000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>0.007246020000000001</v>
+        <v>0.04125581</v>
       </c>
       <c r="M29" t="n">
-        <v>0.04125581</v>
+        <v>0.01170391</v>
       </c>
     </row>
     <row r="30">
@@ -1661,37 +1659,37 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>0.00536903</v>
+        <v>0.01213361</v>
       </c>
       <c r="D30" t="n">
-        <v>0.01213361</v>
+        <v>0.0007921299999999998</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0007921299999999998</v>
+        <v>-0.00470349</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.00470349</v>
+        <v>-0.005675059999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.005675059999999999</v>
+        <v>-0.00690276</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.00690276</v>
+        <v>0.01012549</v>
       </c>
       <c r="I30" t="n">
-        <v>0.01012549</v>
+        <v>0.00217369</v>
       </c>
       <c r="J30" t="n">
-        <v>0.00217369</v>
+        <v>0.00358807</v>
       </c>
       <c r="K30" t="n">
-        <v>0.00358807</v>
+        <v>0.00154582</v>
       </c>
       <c r="L30" t="n">
-        <v>0.00154582</v>
+        <v>-0.0008311099999999996</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.0008311099999999996</v>
+        <v>0.00542619</v>
       </c>
     </row>
     <row r="31">
@@ -1702,37 +1700,37 @@
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>0.10937909</v>
+        <v>0.03921261</v>
       </c>
       <c r="D31" t="n">
-        <v>0.03921261</v>
+        <v>-0.01164912</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.01164912</v>
+        <v>-0.05282732</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.05282732</v>
+        <v>-0.09472982000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.09472982000000001</v>
+        <v>-0.18498163</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.18498163</v>
+        <v>0.003500399999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>0.003500399999999999</v>
+        <v>-0.03699097</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.03699097</v>
+        <v>0.20997069</v>
       </c>
       <c r="K31" t="n">
-        <v>0.20997069</v>
+        <v>0.08271654000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>0.08271654000000001</v>
+        <v>-0.01967012</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.01967012</v>
+        <v>0.08787658</v>
       </c>
     </row>
     <row r="32">
@@ -1743,37 +1741,37 @@
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>0.4845926899999997</v>
+        <v>-20.67803373</v>
       </c>
       <c r="D32" t="n">
-        <v>-20.67803373</v>
+        <v>-32.15445803</v>
       </c>
       <c r="E32" t="n">
-        <v>-32.15445803</v>
+        <v>-40.28821612</v>
       </c>
       <c r="F32" t="n">
-        <v>-40.28821612</v>
+        <v>-16.20914258</v>
       </c>
       <c r="G32" t="n">
-        <v>-16.20914258</v>
+        <v>-19.13381427</v>
       </c>
       <c r="H32" t="n">
-        <v>-19.13381427</v>
+        <v>-10.30184885</v>
       </c>
       <c r="I32" t="n">
-        <v>-10.30184885</v>
+        <v>-13.95881996</v>
       </c>
       <c r="J32" t="n">
-        <v>-13.95881996</v>
+        <v>16.5897552</v>
       </c>
       <c r="K32" t="n">
-        <v>16.5897552</v>
+        <v>21.57479981</v>
       </c>
       <c r="L32" t="n">
-        <v>21.57479981</v>
+        <v>10.77240005</v>
       </c>
       <c r="M32" t="n">
-        <v>10.77240005</v>
+        <v>-3.99943991</v>
       </c>
     </row>
     <row r="33">
@@ -1784,37 +1782,37 @@
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
-        <v>2.92653785</v>
+        <v>0.4812992</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4812992</v>
+        <v>-1.10311971</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.10311971</v>
+        <v>-3.2016798</v>
       </c>
       <c r="F33" t="n">
-        <v>-3.2016798</v>
+        <v>-1.87034995</v>
       </c>
       <c r="G33" t="n">
-        <v>-1.87034995</v>
+        <v>-2.31543645</v>
       </c>
       <c r="H33" t="n">
-        <v>-2.31543645</v>
+        <v>-4.02921888</v>
       </c>
       <c r="I33" t="n">
-        <v>-4.02921888</v>
+        <v>-1.65893927</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.65893927</v>
+        <v>-0.68169719</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.68169719</v>
+        <v>-0.1804759</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.1804759</v>
+        <v>-1.24122729</v>
       </c>
       <c r="M33" t="n">
-        <v>-1.24122729</v>
+        <v>-0.30246939</v>
       </c>
     </row>
     <row r="34">
@@ -1825,37 +1823,37 @@
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
-        <v>53.00901164</v>
+        <v>23.37416052</v>
       </c>
       <c r="D34" t="n">
-        <v>23.37416052</v>
+        <v>33.49646586</v>
       </c>
       <c r="E34" t="n">
-        <v>33.49646586</v>
+        <v>42.38292683</v>
       </c>
       <c r="F34" t="n">
-        <v>42.38292683</v>
+        <v>53.14078301</v>
       </c>
       <c r="G34" t="n">
-        <v>53.14078301</v>
+        <v>77.31264456</v>
       </c>
       <c r="H34" t="n">
-        <v>77.31264456</v>
+        <v>-99.06594910000001</v>
       </c>
       <c r="I34" t="n">
-        <v>-99.06594910000001</v>
+        <v>-137.71287059</v>
       </c>
       <c r="J34" t="n">
-        <v>-137.71287059</v>
+        <v>-36.98264507</v>
       </c>
       <c r="K34" t="n">
-        <v>-36.98264507</v>
+        <v>-110.28325571</v>
       </c>
       <c r="L34" t="n">
-        <v>-110.28325571</v>
+        <v>-29.94653585</v>
       </c>
       <c r="M34" t="n">
-        <v>-29.94653585</v>
+        <v>-75.37832121000001</v>
       </c>
     </row>
     <row r="35">
@@ -1866,37 +1864,37 @@
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
-        <v>-0.86426467</v>
+        <v>-1.03027462</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.03027462</v>
+        <v>-0.0252352</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.0252352</v>
+        <v>-0.03013220000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.03013220000000001</v>
+        <v>3.18854859</v>
       </c>
       <c r="G35" t="n">
-        <v>3.18854859</v>
+        <v>2.605460190000001</v>
       </c>
       <c r="H35" t="n">
-        <v>2.605460190000001</v>
+        <v>4.13401164</v>
       </c>
       <c r="I35" t="n">
-        <v>4.13401164</v>
+        <v>4.72190981</v>
       </c>
       <c r="J35" t="n">
-        <v>4.72190981</v>
+        <v>5.98762434</v>
       </c>
       <c r="K35" t="n">
-        <v>5.98762434</v>
+        <v>2.37916882</v>
       </c>
       <c r="L35" t="n">
-        <v>2.37916882</v>
+        <v>-0.53526386</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.53526386</v>
+        <v>2.64361891</v>
       </c>
     </row>
     <row r="36">
@@ -1907,37 +1905,37 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>205.82422216</v>
+        <v>117.94625767</v>
       </c>
       <c r="D36" t="n">
-        <v>112.08474924</v>
+        <v>217.93889327</v>
       </c>
       <c r="E36" t="n">
-        <v>201.10258552</v>
+        <v>352.4427523</v>
       </c>
       <c r="F36" t="n">
-        <v>264.13111271</v>
+        <v>204.10822595</v>
       </c>
       <c r="G36" t="n">
-        <v>172.4178389</v>
+        <v>203.78321979</v>
       </c>
       <c r="H36" t="n">
-        <v>136.92221049</v>
+        <v>-5.257925969999995</v>
       </c>
       <c r="I36" t="n">
-        <v>18.18229482</v>
+        <v>182.21045032</v>
       </c>
       <c r="J36" t="n">
-        <v>186.7382784</v>
+        <v>0.8376441199999973</v>
       </c>
       <c r="K36" t="n">
-        <v>-26.1190374</v>
+        <v>-109.20080044</v>
       </c>
       <c r="L36" t="n">
-        <v>-145.80769051</v>
+        <v>-113.180397</v>
       </c>
       <c r="M36" t="n">
-        <v>-91.33632412999999</v>
+        <v>-28.44645008</v>
       </c>
     </row>
     <row r="37">
@@ -1946,39 +1944,41 @@
           <t>汽車工業右下</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
       <c r="C37" t="n">
-        <v>44.36718017</v>
+        <v>47.02422203</v>
       </c>
       <c r="D37" t="n">
-        <v>47.02422203</v>
+        <v>-9.668723299999998</v>
       </c>
       <c r="E37" t="n">
-        <v>-9.668723299999998</v>
+        <v>10.93613627</v>
       </c>
       <c r="F37" t="n">
-        <v>10.93613627</v>
+        <v>59.2642467</v>
       </c>
       <c r="G37" t="n">
-        <v>59.2642467</v>
+        <v>15.98931635</v>
       </c>
       <c r="H37" t="n">
-        <v>15.98931635</v>
+        <v>19.55677792</v>
       </c>
       <c r="I37" t="n">
-        <v>19.55677792</v>
+        <v>2.64621305</v>
       </c>
       <c r="J37" t="n">
-        <v>2.64621305</v>
+        <v>25.57220427</v>
       </c>
       <c r="K37" t="n">
-        <v>25.57220427</v>
+        <v>4.312316109999998</v>
       </c>
       <c r="L37" t="n">
-        <v>4.312316109999998</v>
+        <v>-61.2942177</v>
       </c>
       <c r="M37" t="n">
-        <v>-61.2942177</v>
+        <v>-26.64410661</v>
       </c>
     </row>
     <row r="38">
@@ -1989,37 +1989,37 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>18.76998959000001</v>
+        <v>-38.84033998</v>
       </c>
       <c r="D38" t="n">
-        <v>-38.09471417</v>
+        <v>-49.15742052</v>
       </c>
       <c r="E38" t="n">
-        <v>-49.86970338</v>
+        <v>-21.66280968</v>
       </c>
       <c r="F38" t="n">
-        <v>-21.92375551</v>
+        <v>4.321580470000002</v>
       </c>
       <c r="G38" t="n">
-        <v>5.972689210000001</v>
+        <v>31.95571575</v>
       </c>
       <c r="H38" t="n">
-        <v>29.37988966</v>
+        <v>-18.81229593</v>
       </c>
       <c r="I38" t="n">
-        <v>-21.33947604</v>
+        <v>8.607906160000004</v>
       </c>
       <c r="J38" t="n">
-        <v>7.001465090000003</v>
+        <v>-41.90752625</v>
       </c>
       <c r="K38" t="n">
-        <v>-42.26410757</v>
+        <v>-106.27549398</v>
       </c>
       <c r="L38" t="n">
-        <v>-107.25360982</v>
+        <v>-123.81290809</v>
       </c>
       <c r="M38" t="n">
-        <v>-125.20318794</v>
+        <v>-47.08863035</v>
       </c>
     </row>
     <row r="39">
@@ -2030,37 +2030,37 @@
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
-        <v>8.135896049999999</v>
+        <v>0.42597227</v>
       </c>
       <c r="D39" t="n">
-        <v>0.42597227</v>
+        <v>5.236759269999999</v>
       </c>
       <c r="E39" t="n">
-        <v>5.236759269999999</v>
+        <v>24.80576117</v>
       </c>
       <c r="F39" t="n">
-        <v>24.80576117</v>
+        <v>21.99748971</v>
       </c>
       <c r="G39" t="n">
-        <v>21.99748971</v>
+        <v>7.5667577</v>
       </c>
       <c r="H39" t="n">
-        <v>7.5667577</v>
+        <v>-0.39082327</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.39082327</v>
+        <v>6.9156605</v>
       </c>
       <c r="J39" t="n">
-        <v>6.9156605</v>
+        <v>-3.65105099</v>
       </c>
       <c r="K39" t="n">
-        <v>-3.65105099</v>
+        <v>5.96885178</v>
       </c>
       <c r="L39" t="n">
-        <v>5.96885178</v>
+        <v>-4.14332239</v>
       </c>
       <c r="M39" t="n">
-        <v>-4.14332239</v>
+        <v>-1.8353452</v>
       </c>
     </row>
     <row r="40">
@@ -2071,37 +2071,37 @@
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>-32.772473</v>
+        <v>-17.85393562</v>
       </c>
       <c r="D40" t="n">
-        <v>-17.85393562</v>
+        <v>-34.21927984000001</v>
       </c>
       <c r="E40" t="n">
-        <v>-34.21927984000001</v>
+        <v>-18.29832132</v>
       </c>
       <c r="F40" t="n">
-        <v>-18.29832132</v>
+        <v>16.51942199</v>
       </c>
       <c r="G40" t="n">
-        <v>16.51942199</v>
+        <v>-19.21069481</v>
       </c>
       <c r="H40" t="n">
-        <v>-19.21069481</v>
+        <v>-76.86549835</v>
       </c>
       <c r="I40" t="n">
-        <v>-76.86549835</v>
+        <v>-32.5970419</v>
       </c>
       <c r="J40" t="n">
-        <v>-32.5970419</v>
+        <v>-50.29811102</v>
       </c>
       <c r="K40" t="n">
-        <v>-50.29811102</v>
+        <v>-89.72822392</v>
       </c>
       <c r="L40" t="n">
-        <v>-89.72822392</v>
+        <v>-81.92920619</v>
       </c>
       <c r="M40" t="n">
-        <v>-81.92920619</v>
+        <v>5.598820609999998</v>
       </c>
     </row>
     <row r="41">
@@ -2112,37 +2112,37 @@
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
-        <v>-0.00014463</v>
+        <v>-7.391e-05</v>
       </c>
       <c r="D41" t="n">
-        <v>-7.391e-05</v>
+        <v>-2.001e-05</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.001e-05</v>
+        <v>4.417e-05</v>
       </c>
       <c r="F41" t="n">
-        <v>4.417e-05</v>
+        <v>9.085e-05</v>
       </c>
       <c r="G41" t="n">
-        <v>9.085e-05</v>
+        <v>-7.104999999999999e-05</v>
       </c>
       <c r="H41" t="n">
-        <v>-7.104999999999999e-05</v>
+        <v>-0.00022371</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.00022371</v>
+        <v>-0.00012</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.00012</v>
+        <v>-0.00023445</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.00023445</v>
+        <v>-0.00035108</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.00035108</v>
+        <v>-0.00043212</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.00043212</v>
+        <v>-0.00024149</v>
       </c>
     </row>
     <row r="42">
@@ -2153,37 +2153,37 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>-42.95356518</v>
+        <v>-209.92976809</v>
       </c>
       <c r="D42" t="n">
-        <v>-209.92976809</v>
+        <v>-24.7706204</v>
       </c>
       <c r="E42" t="n">
-        <v>-24.7706204</v>
+        <v>154.56242497</v>
       </c>
       <c r="F42" t="n">
-        <v>154.56242497</v>
+        <v>569.9204095299999</v>
       </c>
       <c r="G42" t="n">
-        <v>569.9204095299999</v>
+        <v>879.95625971</v>
       </c>
       <c r="H42" t="n">
-        <v>879.95625971</v>
+        <v>1190.48956757</v>
       </c>
       <c r="I42" t="n">
-        <v>1190.48956757</v>
+        <v>1271.44494553</v>
       </c>
       <c r="J42" t="n">
-        <v>1271.44494553</v>
+        <v>1277.79570934</v>
       </c>
       <c r="K42" t="n">
-        <v>1277.79570934</v>
+        <v>-591.18301373</v>
       </c>
       <c r="L42" t="n">
-        <v>-591.18301373</v>
+        <v>-815.56774821</v>
       </c>
       <c r="M42" t="n">
-        <v>-815.56774821</v>
+        <v>-634.0106390599999</v>
       </c>
     </row>
     <row r="43">
@@ -2194,37 +2194,37 @@
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
-        <v>18.45296431</v>
+        <v>5.039715139999999</v>
       </c>
       <c r="D43" t="n">
-        <v>5.039715139999999</v>
+        <v>-4.01613703</v>
       </c>
       <c r="E43" t="n">
-        <v>-4.01613703</v>
+        <v>-0.5236189</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.5236189</v>
+        <v>12.23212643</v>
       </c>
       <c r="G43" t="n">
-        <v>12.23212643</v>
+        <v>41.41266073000001</v>
       </c>
       <c r="H43" t="n">
-        <v>41.41266073000001</v>
+        <v>-2.399140199999998</v>
       </c>
       <c r="I43" t="n">
-        <v>-2.399140199999998</v>
+        <v>19.34848593</v>
       </c>
       <c r="J43" t="n">
-        <v>19.34848593</v>
+        <v>46.03279432</v>
       </c>
       <c r="K43" t="n">
-        <v>46.03279432</v>
+        <v>6.63547855</v>
       </c>
       <c r="L43" t="n">
-        <v>6.63547855</v>
+        <v>-12.07906279</v>
       </c>
       <c r="M43" t="n">
-        <v>-12.07906279</v>
+        <v>-12.14486849</v>
       </c>
     </row>
     <row r="44">
@@ -2235,37 +2235,37 @@
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>17.13178991</v>
+        <v>5.93654785</v>
       </c>
       <c r="D44" t="n">
-        <v>4.96132119</v>
+        <v>12.21945215</v>
       </c>
       <c r="E44" t="n">
-        <v>11.88326792</v>
+        <v>11.87844405</v>
       </c>
       <c r="F44" t="n">
-        <v>11.99605395000001</v>
+        <v>12.57219764</v>
       </c>
       <c r="G44" t="n">
-        <v>10.73998824</v>
+        <v>-6.55060065</v>
       </c>
       <c r="H44" t="n">
-        <v>-8.907901220000001</v>
+        <v>-20.40168625</v>
       </c>
       <c r="I44" t="n">
-        <v>-21.06634319</v>
+        <v>-26.01189411</v>
       </c>
       <c r="J44" t="n">
-        <v>-25.51101711</v>
+        <v>-20.38139739</v>
       </c>
       <c r="K44" t="n">
-        <v>-20.91638141</v>
+        <v>-8.06726274</v>
       </c>
       <c r="L44" t="n">
-        <v>-9.859126460000001</v>
+        <v>-12.98580715</v>
       </c>
       <c r="M44" t="n">
-        <v>-15.5341533</v>
+        <v>8.8337477</v>
       </c>
     </row>
     <row r="45">
@@ -2274,41 +2274,39 @@
           <t>生技醫療業右下</t>
         </is>
       </c>
-      <c r="B45" t="n">
-        <v>0</v>
-      </c>
+      <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
-        <v>34.74102881</v>
+        <v>122.35161025</v>
       </c>
       <c r="D45" t="n">
-        <v>122.44112911</v>
+        <v>263.00612828</v>
       </c>
       <c r="E45" t="n">
-        <v>263.40352697</v>
+        <v>96.63844107000003</v>
       </c>
       <c r="F45" t="n">
-        <v>96.87998216000003</v>
+        <v>183.6373287</v>
       </c>
       <c r="G45" t="n">
-        <v>184.55389075</v>
+        <v>198.61636008</v>
       </c>
       <c r="H45" t="n">
-        <v>197.80873071</v>
+        <v>293.39242734</v>
       </c>
       <c r="I45" t="n">
-        <v>293.41731848</v>
+        <v>426.4585314</v>
       </c>
       <c r="J45" t="n">
-        <v>426.02240409</v>
+        <v>556.32993176</v>
       </c>
       <c r="K45" t="n">
-        <v>555.4999105099999</v>
+        <v>773.2708335200001</v>
       </c>
       <c r="L45" t="n">
-        <v>773.0920901900001</v>
+        <v>1234.8179569</v>
       </c>
       <c r="M45" t="n">
-        <v>1234.26724926</v>
+        <v>1384.13727577</v>
       </c>
     </row>
     <row r="46">
@@ -2319,37 +2317,37 @@
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>-5.739201689999998</v>
+        <v>71.93912046999999</v>
       </c>
       <c r="D46" t="n">
-        <v>72.82681453999999</v>
+        <v>50.59631318</v>
       </c>
       <c r="E46" t="n">
-        <v>50.53460386999999</v>
+        <v>-59.06490656999999</v>
       </c>
       <c r="F46" t="n">
-        <v>-59.42225436</v>
+        <v>74.20838304999999</v>
       </c>
       <c r="G46" t="n">
-        <v>75.12495246</v>
+        <v>103.6682775</v>
       </c>
       <c r="H46" t="n">
-        <v>106.8370172</v>
+        <v>247.59047259</v>
       </c>
       <c r="I46" t="n">
-        <v>248.24594157</v>
+        <v>66.88778893</v>
       </c>
       <c r="J46" t="n">
-        <v>66.83976742999999</v>
+        <v>-62.97837505</v>
       </c>
       <c r="K46" t="n">
-        <v>-61.59740323</v>
+        <v>-148.50774134</v>
       </c>
       <c r="L46" t="n">
-        <v>-146.5239308</v>
+        <v>-140.3231491</v>
       </c>
       <c r="M46" t="n">
-        <v>-137.20722078</v>
+        <v>-83.65430592</v>
       </c>
     </row>
     <row r="47">
@@ -2360,37 +2358,37 @@
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>-1.55805487</v>
+        <v>1.12070131</v>
       </c>
       <c r="D47" t="n">
-        <v>0.2128199</v>
+        <v>-0.37939106</v>
       </c>
       <c r="E47" t="n">
-        <v>0.11380938</v>
+        <v>-3.99313596</v>
       </c>
       <c r="F47" t="n">
-        <v>-1.16393911</v>
+        <v>2.80756889</v>
       </c>
       <c r="G47" t="n">
-        <v>3.26730915</v>
+        <v>15.48295851</v>
       </c>
       <c r="H47" t="n">
-        <v>1.63955288</v>
+        <v>62.07494209</v>
       </c>
       <c r="I47" t="n">
-        <v>0.7404075099999999</v>
+        <v>95.45295953</v>
       </c>
       <c r="J47" t="n">
-        <v>2.84180396</v>
+        <v>201.7001855</v>
       </c>
       <c r="K47" t="n">
-        <v>3.94008714</v>
+        <v>314.3157432199999</v>
       </c>
       <c r="L47" t="n">
-        <v>4.28278438</v>
+        <v>126.7761244</v>
       </c>
       <c r="M47" t="n">
-        <v>1.74077493</v>
+        <v>117.36460055</v>
       </c>
     </row>
     <row r="48">
@@ -2403,37 +2401,37 @@
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>1.470755140000002</v>
+        <v>-15.0385654</v>
       </c>
       <c r="D48" t="n">
-        <v>18.96919007</v>
+        <v>-100.72078989</v>
       </c>
       <c r="E48" t="n">
-        <v>-20.28660042</v>
+        <v>-162.07263695</v>
       </c>
       <c r="F48" t="n">
-        <v>-80.24432846000001</v>
+        <v>-138.82763643</v>
       </c>
       <c r="G48" t="n">
-        <v>-99.69417993</v>
+        <v>-65.51920985</v>
       </c>
       <c r="H48" t="n">
-        <v>-59.87145587</v>
+        <v>101.05817821</v>
       </c>
       <c r="I48" t="n">
-        <v>20.9288823</v>
+        <v>167.79735666</v>
       </c>
       <c r="J48" t="n">
-        <v>46.60395298</v>
+        <v>94.13843056</v>
       </c>
       <c r="K48" t="n">
-        <v>32.49431972</v>
+        <v>30.77328596000001</v>
       </c>
       <c r="L48" t="n">
-        <v>0.7880856500000022</v>
+        <v>-10.082271</v>
       </c>
       <c r="M48" t="n">
-        <v>15.49087174</v>
+        <v>70.38508037000001</v>
       </c>
     </row>
     <row r="49">
@@ -2444,37 +2442,37 @@
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>-1.34135238</v>
+        <v>-0.002355010000000012</v>
       </c>
       <c r="D49" t="n">
-        <v>0.8862975200000001</v>
+        <v>-0.21139079</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.6830073800000001</v>
+        <v>-0.32138332</v>
       </c>
       <c r="F49" t="n">
-        <v>-3.18095136</v>
+        <v>-0.6397877999999999</v>
       </c>
       <c r="G49" t="n">
-        <v>-1.0886851</v>
+        <v>-0.68572444</v>
       </c>
       <c r="H49" t="n">
-        <v>13.1180532</v>
+        <v>-0.8008609400000001</v>
       </c>
       <c r="I49" t="n">
-        <v>60.53762608</v>
+        <v>-0.60568889</v>
       </c>
       <c r="J49" t="n">
-        <v>92.04177723000001</v>
+        <v>-0.16061175</v>
       </c>
       <c r="K49" t="n">
-        <v>197.69451778</v>
+        <v>-0.49145176</v>
       </c>
       <c r="L49" t="n">
-        <v>309.63768162</v>
+        <v>-0.56404314</v>
       </c>
       <c r="M49" t="n">
-        <v>124.56556053</v>
+        <v>-0.42371904</v>
       </c>
     </row>
     <row r="50">
@@ -2485,37 +2483,37 @@
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
-        <v>-118.5355461</v>
+        <v>51.08673258</v>
       </c>
       <c r="D50" t="n">
-        <v>48.67417623000001</v>
+        <v>-67.32971089999999</v>
       </c>
       <c r="E50" t="n">
-        <v>-68.17846678999999</v>
+        <v>-49.9699323</v>
       </c>
       <c r="F50" t="n">
-        <v>-51.11842820000001</v>
+        <v>-34.87113519</v>
       </c>
       <c r="G50" t="n">
-        <v>-32.7785758</v>
+        <v>-101.83529897</v>
       </c>
       <c r="H50" t="n">
-        <v>-99.73463743000001</v>
+        <v>-20.18952884999999</v>
       </c>
       <c r="I50" t="n">
-        <v>-19.73116191999999</v>
+        <v>60.03399915</v>
       </c>
       <c r="J50" t="n">
-        <v>59.53426253</v>
+        <v>46.57401195000001</v>
       </c>
       <c r="K50" t="n">
-        <v>46.45680000999999</v>
+        <v>94.33851032</v>
       </c>
       <c r="L50" t="n">
-        <v>94.52176788</v>
+        <v>-55.45684779</v>
       </c>
       <c r="M50" t="n">
-        <v>-54.93532402</v>
+        <v>95.27728619</v>
       </c>
     </row>
     <row r="51">
@@ -2526,37 +2524,37 @@
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>-4.208008479999999</v>
+        <v>-16.668004</v>
       </c>
       <c r="D51" t="n">
-        <v>-16.668004</v>
+        <v>-17.31000216</v>
       </c>
       <c r="E51" t="n">
-        <v>-17.31000216</v>
+        <v>-27.00119206</v>
       </c>
       <c r="F51" t="n">
-        <v>-27.00119206</v>
+        <v>-37.85262138</v>
       </c>
       <c r="G51" t="n">
-        <v>-37.85262138</v>
+        <v>-40.22165305999999</v>
       </c>
       <c r="H51" t="n">
-        <v>-40.22165305999999</v>
+        <v>-40.80044587</v>
       </c>
       <c r="I51" t="n">
-        <v>-40.80044587</v>
+        <v>-105.72065853</v>
       </c>
       <c r="J51" t="n">
-        <v>-105.72065853</v>
+        <v>-88.20215075</v>
       </c>
       <c r="K51" t="n">
-        <v>-88.20215075</v>
+        <v>-78.58694362999999</v>
       </c>
       <c r="L51" t="n">
-        <v>-78.58694362999999</v>
+        <v>-59.1372507</v>
       </c>
       <c r="M51" t="n">
-        <v>-59.1372507</v>
+        <v>-20.76584638</v>
       </c>
     </row>
     <row r="52">
@@ -2567,37 +2565,37 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>23.24927058</v>
+        <v>10.98503399</v>
       </c>
       <c r="D52" t="n">
-        <v>10.98503399</v>
+        <v>14.36571771</v>
       </c>
       <c r="E52" t="n">
-        <v>14.36571771</v>
+        <v>-7.093245320000001</v>
       </c>
       <c r="F52" t="n">
-        <v>-7.093245320000001</v>
+        <v>3.776879930000002</v>
       </c>
       <c r="G52" t="n">
-        <v>3.776879930000002</v>
+        <v>-0.599055200000002</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.599055200000002</v>
+        <v>-25.3277558</v>
       </c>
       <c r="I52" t="n">
-        <v>-25.3277558</v>
+        <v>-25.32132348</v>
       </c>
       <c r="J52" t="n">
-        <v>-25.32132348</v>
+        <v>-2.890964619999999</v>
       </c>
       <c r="K52" t="n">
-        <v>-2.890964619999999</v>
+        <v>-8.700042229999999</v>
       </c>
       <c r="L52" t="n">
-        <v>-8.700042229999999</v>
+        <v>-18.52731013</v>
       </c>
       <c r="M52" t="n">
-        <v>-18.52731013</v>
+        <v>-1.47967556</v>
       </c>
     </row>
     <row r="53">
@@ -2608,37 +2606,37 @@
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>788.96935349</v>
+        <v>202.71825148</v>
       </c>
       <c r="D53" t="n">
-        <v>202.71825148</v>
+        <v>185.63987332</v>
       </c>
       <c r="E53" t="n">
-        <v>185.63987332</v>
+        <v>413.37287971</v>
       </c>
       <c r="F53" t="n">
-        <v>413.37287971</v>
+        <v>382.52006728</v>
       </c>
       <c r="G53" t="n">
-        <v>382.52006728</v>
+        <v>788.81984295</v>
       </c>
       <c r="H53" t="n">
-        <v>788.81984295</v>
+        <v>536.01880756</v>
       </c>
       <c r="I53" t="n">
-        <v>536.01880756</v>
+        <v>663.41942352</v>
       </c>
       <c r="J53" t="n">
-        <v>663.41942352</v>
+        <v>832.86466129</v>
       </c>
       <c r="K53" t="n">
-        <v>832.86466129</v>
+        <v>148.04517125</v>
       </c>
       <c r="L53" t="n">
-        <v>148.04517125</v>
+        <v>92.40368975999999</v>
       </c>
       <c r="M53" t="n">
-        <v>92.40368975999999</v>
+        <v>-258.920668</v>
       </c>
     </row>
     <row r="54">
@@ -2649,37 +2647,37 @@
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>79.96259970999999</v>
+        <v>29.98847398</v>
       </c>
       <c r="D54" t="n">
-        <v>53.38682709</v>
+        <v>32.85000479</v>
       </c>
       <c r="E54" t="n">
-        <v>71.14172211</v>
+        <v>27.25000905</v>
       </c>
       <c r="F54" t="n">
-        <v>5.673030960000003</v>
+        <v>58.22860823000001</v>
       </c>
       <c r="G54" t="n">
-        <v>29.67370817</v>
+        <v>28.42361836</v>
       </c>
       <c r="H54" t="n">
-        <v>45.69961662999999</v>
+        <v>27.12037651</v>
       </c>
       <c r="I54" t="n">
-        <v>81.70161845</v>
+        <v>4.33543982</v>
       </c>
       <c r="J54" t="n">
-        <v>28.41798539</v>
+        <v>4.657683560000001</v>
       </c>
       <c r="K54" t="n">
-        <v>55.00752722</v>
+        <v>-6.665553060000001</v>
       </c>
       <c r="L54" t="n">
-        <v>4.253341999999999</v>
+        <v>-27.49233601</v>
       </c>
       <c r="M54" t="n">
-        <v>-55.55444215</v>
+        <v>-4.76262133</v>
       </c>
     </row>
     <row r="55">
@@ -2690,37 +2688,37 @@
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>-35.82735756000002</v>
+        <v>-345.84892177</v>
       </c>
       <c r="D55" t="n">
-        <v>-369.24727488</v>
+        <v>231.55420764</v>
       </c>
       <c r="E55" t="n">
-        <v>193.26249032</v>
+        <v>91.16828621000002</v>
       </c>
       <c r="F55" t="n">
-        <v>112.7452643</v>
+        <v>318.79573829</v>
       </c>
       <c r="G55" t="n">
-        <v>347.3506383499999</v>
+        <v>-73.07478899999998</v>
       </c>
       <c r="H55" t="n">
-        <v>-90.35078726999998</v>
+        <v>55.56343482</v>
       </c>
       <c r="I55" t="n">
-        <v>0.9821928799999957</v>
+        <v>-138.18657417</v>
       </c>
       <c r="J55" t="n">
-        <v>-162.26911974</v>
+        <v>0.1445773399999785</v>
       </c>
       <c r="K55" t="n">
-        <v>-50.20526632000001</v>
+        <v>-394.95349135</v>
       </c>
       <c r="L55" t="n">
-        <v>-405.87238641</v>
+        <v>-531.04450994</v>
       </c>
       <c r="M55" t="n">
-        <v>-502.9824038</v>
+        <v>-143.91073819</v>
       </c>
     </row>
     <row r="56">
@@ -2731,37 +2729,37 @@
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>-4.11638705</v>
+        <v>4.08089557</v>
       </c>
       <c r="D56" t="n">
-        <v>4.08089557</v>
+        <v>-0.1995485</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.1995485</v>
+        <v>-12.28237295</v>
       </c>
       <c r="F56" t="n">
-        <v>-12.28237295</v>
+        <v>-2.91487422</v>
       </c>
       <c r="G56" t="n">
-        <v>-2.91487422</v>
+        <v>20.8052581</v>
       </c>
       <c r="H56" t="n">
-        <v>20.8052581</v>
+        <v>4.32875445</v>
       </c>
       <c r="I56" t="n">
-        <v>4.32875445</v>
+        <v>9.664215899999999</v>
       </c>
       <c r="J56" t="n">
-        <v>9.664215899999999</v>
+        <v>19.0901028</v>
       </c>
       <c r="K56" t="n">
-        <v>19.0901028</v>
+        <v>26.43894701</v>
       </c>
       <c r="L56" t="n">
-        <v>26.43894701</v>
+        <v>12.17498731</v>
       </c>
       <c r="M56" t="n">
-        <v>12.17498731</v>
+        <v>-1.17773524</v>
       </c>
     </row>
     <row r="57">
@@ -2772,37 +2770,37 @@
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
-        <v>9.521552719999999</v>
+        <v>-6.490226310000001</v>
       </c>
       <c r="D57" t="n">
-        <v>-6.49062084</v>
+        <v>-19.63733982</v>
       </c>
       <c r="E57" t="n">
-        <v>-19.63753738</v>
+        <v>-31.28678731</v>
       </c>
       <c r="F57" t="n">
-        <v>-31.28690505</v>
+        <v>-35.8224009</v>
       </c>
       <c r="G57" t="n">
-        <v>-35.82237618</v>
+        <v>-48.83657307</v>
       </c>
       <c r="H57" t="n">
-        <v>-48.83650657</v>
+        <v>-2.96100229</v>
       </c>
       <c r="I57" t="n">
-        <v>-2.96101949</v>
+        <v>-4.13295156</v>
       </c>
       <c r="J57" t="n">
-        <v>-4.13299422</v>
+        <v>-6.76115287</v>
       </c>
       <c r="K57" t="n">
-        <v>-6.761116970000001</v>
+        <v>-11.20171031</v>
       </c>
       <c r="L57" t="n">
-        <v>-11.20179401</v>
+        <v>-1.303506030000001</v>
       </c>
       <c r="M57" t="n">
-        <v>-1.30365066</v>
+        <v>12.02103025</v>
       </c>
     </row>
     <row r="58">
@@ -2813,37 +2811,37 @@
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>45.77364702000001</v>
+        <v>20.38771257</v>
       </c>
       <c r="D58" t="n">
-        <v>20.38807903</v>
+        <v>-9.583194499999999</v>
       </c>
       <c r="E58" t="n">
-        <v>-9.582971580000001</v>
+        <v>-17.24568169</v>
       </c>
       <c r="F58" t="n">
-        <v>-17.24549747</v>
+        <v>-34.94886270000001</v>
       </c>
       <c r="G58" t="n">
-        <v>-34.94878781</v>
+        <v>-42.1867673</v>
       </c>
       <c r="H58" t="n">
-        <v>-42.18670959999999</v>
+        <v>-0.99581925</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.9957898099999999</v>
+        <v>-6.33419032</v>
       </c>
       <c r="J58" t="n">
-        <v>-6.334103850000001</v>
+        <v>8.21714162</v>
       </c>
       <c r="K58" t="n">
-        <v>8.21712718</v>
+        <v>3.55941364</v>
       </c>
       <c r="L58" t="n">
-        <v>3.55950817</v>
+        <v>17.67872486</v>
       </c>
       <c r="M58" t="n">
-        <v>17.67879739</v>
+        <v>28.19804109</v>
       </c>
     </row>
     <row r="59">
@@ -2854,37 +2852,37 @@
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
-        <v>-0.02343861</v>
+        <v>0.03144128</v>
       </c>
       <c r="D59" t="n">
-        <v>0.03144128</v>
+        <v>0.01201424</v>
       </c>
       <c r="E59" t="n">
-        <v>0.01201424</v>
+        <v>0.04099756</v>
       </c>
       <c r="F59" t="n">
-        <v>0.04099756</v>
+        <v>0.02809802</v>
       </c>
       <c r="G59" t="n">
-        <v>0.02809802</v>
+        <v>0.04076989</v>
       </c>
       <c r="H59" t="n">
-        <v>0.04076989</v>
+        <v>-0.02230235</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.02230235</v>
+        <v>0.0121624</v>
       </c>
       <c r="J59" t="n">
-        <v>0.0121624</v>
+        <v>-0.02442989</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.02442989</v>
+        <v>0.09452125</v>
       </c>
       <c r="L59" t="n">
-        <v>0.09452125</v>
+        <v>0.12390914</v>
       </c>
       <c r="M59" t="n">
-        <v>0.12390914</v>
+        <v>0.05750639</v>
       </c>
     </row>
     <row r="60">
@@ -2895,1683 +2893,1718 @@
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
-        <v>39.06068539</v>
+        <v>50.5705571</v>
       </c>
       <c r="D60" t="n">
-        <v>50.62813032</v>
+        <v>29.48116599</v>
       </c>
       <c r="E60" t="n">
-        <v>29.49595222</v>
+        <v>3.745202050000001</v>
       </c>
       <c r="F60" t="n">
-        <v>3.736675960000001</v>
+        <v>-27.11462849</v>
       </c>
       <c r="G60" t="n">
-        <v>-27.10836733</v>
+        <v>-14.54311404</v>
       </c>
       <c r="H60" t="n">
-        <v>-14.55097783</v>
+        <v>-20.20816677</v>
       </c>
       <c r="I60" t="n">
-        <v>-20.19341195</v>
+        <v>-48.84269329</v>
       </c>
       <c r="J60" t="n">
-        <v>-48.79022895</v>
+        <v>-21.3959596</v>
       </c>
       <c r="K60" t="n">
-        <v>-21.4031845</v>
+        <v>-28.9827527</v>
       </c>
       <c r="L60" t="n">
-        <v>-29.01154994</v>
+        <v>-29.74134219</v>
       </c>
       <c r="M60" t="n">
-        <v>-29.79071027</v>
+        <v>13.35674909</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右上</t>
+          <t>貿易百貨平</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
-        <v>52.08621262</v>
+        <v>0.05757322</v>
       </c>
       <c r="D61" t="n">
-        <v>56.2651317</v>
+        <v>0.01478623</v>
       </c>
       <c r="E61" t="n">
-        <v>4.496420459999995</v>
+        <v>-0.00852609</v>
       </c>
       <c r="F61" t="n">
-        <v>16.52153666</v>
+        <v>0.00626116</v>
       </c>
       <c r="G61" t="n">
-        <v>67.26849343000001</v>
+        <v>-0.007863790000000001</v>
       </c>
       <c r="H61" t="n">
-        <v>-16.93341359</v>
+        <v>0.01475482</v>
       </c>
       <c r="I61" t="n">
-        <v>-37.98556158</v>
+        <v>0.05246434</v>
       </c>
       <c r="J61" t="n">
-        <v>-34.65841320000001</v>
+        <v>-0.007224899999999999</v>
       </c>
       <c r="K61" t="n">
-        <v>-52.24856203</v>
+        <v>-0.02879724</v>
       </c>
       <c r="L61" t="n">
-        <v>-39.37859758</v>
+        <v>-0.04936808</v>
       </c>
       <c r="M61" t="n">
-        <v>-4.036567070000014</v>
+        <v>-0.01718104</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右下</t>
+          <t>資訊服務業右上</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>0.005237070000000001</v>
+        <v>56.2651835</v>
       </c>
       <c r="D62" t="n">
-        <v>0.00104507</v>
+        <v>4.496421909999995</v>
       </c>
       <c r="E62" t="n">
-        <v>0.00898524</v>
+        <v>16.5218095</v>
       </c>
       <c r="F62" t="n">
-        <v>0.01629072</v>
+        <v>67.27009512000001</v>
       </c>
       <c r="G62" t="n">
-        <v>0.02050236</v>
+        <v>-16.92938799</v>
       </c>
       <c r="H62" t="n">
-        <v>0.02262908</v>
+        <v>-37.98414687</v>
       </c>
       <c r="I62" t="n">
-        <v>0.01813206</v>
+        <v>-34.65845204999999</v>
       </c>
       <c r="J62" t="n">
-        <v>0.01316176</v>
+        <v>-52.24809272</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.0002601800000000002</v>
+        <v>-39.37894222</v>
       </c>
       <c r="L62" t="n">
-        <v>-0.00714299</v>
+        <v>-4.036571590000014</v>
       </c>
       <c r="M62" t="n">
-        <v>0.00352127</v>
+        <v>175.37555294</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業平</t>
+          <t>資訊服務業右下</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>48.0678358</v>
+        <v>-0.00035637</v>
       </c>
       <c r="D63" t="n">
-        <v>39.22009743</v>
+        <v>0.00206774</v>
       </c>
       <c r="E63" t="n">
-        <v>15.91580701</v>
+        <v>0.007072559999999999</v>
       </c>
       <c r="F63" t="n">
-        <v>18.27737456</v>
+        <v>0.008596049999999999</v>
       </c>
       <c r="G63" t="n">
-        <v>27.18001496</v>
+        <v>0.00958909</v>
       </c>
       <c r="H63" t="n">
-        <v>29.03651708</v>
+        <v>0.00693968</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.5535146500000004</v>
+        <v>0.00426686</v>
       </c>
       <c r="J63" t="n">
-        <v>-21.72210101</v>
+        <v>-0.0024533</v>
       </c>
       <c r="K63" t="n">
-        <v>-16.22650388</v>
+        <v>-0.00572523</v>
       </c>
       <c r="L63" t="n">
-        <v>-27.89734886</v>
+        <v>0.002586119999999999</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.0972629100000006</v>
+        <v>-0.0010712</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右上</t>
+          <t>資訊服務業平</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
-        <v>0.0004044</v>
+        <v>41.24898890999999</v>
       </c>
       <c r="D64" t="n">
-        <v>0.00072251</v>
+        <v>17.02169322</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.00025412</v>
+        <v>18.44822186</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.00126824</v>
+        <v>30.17584855</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.00052996</v>
+        <v>29.39557062</v>
       </c>
       <c r="H64" t="n">
-        <v>-4.627e-05</v>
+        <v>-1.369384310000001</v>
       </c>
       <c r="I64" t="n">
-        <v>0.00012135</v>
+        <v>-22.587093</v>
       </c>
       <c r="J64" t="n">
-        <v>0.00033795</v>
+        <v>-17.54739127</v>
       </c>
       <c r="K64" t="n">
-        <v>0.0007966399999999999</v>
+        <v>-29.1049093</v>
       </c>
       <c r="L64" t="n">
-        <v>0.00094526</v>
+        <v>-2.03305201</v>
       </c>
       <c r="M64" t="n">
-        <v>0.00174454</v>
+        <v>22.95042967</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右下</t>
+          <t>農業科技業右上</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
-        <v>2.243e-05</v>
+        <v>0.00072251</v>
       </c>
       <c r="D65" t="n">
-        <v>-8.019e-05</v>
+        <v>-0.00025412</v>
       </c>
       <c r="E65" t="n">
-        <v>-3.720999999999999e-05</v>
+        <v>-0.00126824</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.00012853</v>
+        <v>-0.00052996</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.00011783</v>
+        <v>-4.627e-05</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.00038662</v>
+        <v>0.00012135</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.00020338</v>
+        <v>0.00033795</v>
       </c>
       <c r="J65" t="n">
-        <v>2.062999999999999e-05</v>
+        <v>0.0007966399999999999</v>
       </c>
       <c r="K65" t="n">
-        <v>7.988999999999998e-05</v>
+        <v>0.00094526</v>
       </c>
       <c r="L65" t="n">
-        <v>-3.629999999999995e-06</v>
+        <v>0.00174454</v>
       </c>
       <c r="M65" t="n">
-        <v>0.00015752</v>
+        <v>0.0028698</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右上</t>
+          <t>農業科技業右下</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>219.61619982</v>
+        <v>-8.019e-05</v>
       </c>
       <c r="D66" t="n">
-        <v>553.1703113999999</v>
+        <v>-3.720999999999999e-05</v>
       </c>
       <c r="E66" t="n">
-        <v>726.6980753300001</v>
+        <v>-0.00012853</v>
       </c>
       <c r="F66" t="n">
-        <v>922.15021687</v>
+        <v>-0.00011783</v>
       </c>
       <c r="G66" t="n">
-        <v>1026.32503559</v>
+        <v>-0.00038662</v>
       </c>
       <c r="H66" t="n">
-        <v>1123.08660503</v>
+        <v>-0.00020338</v>
       </c>
       <c r="I66" t="n">
-        <v>1091.51975738</v>
+        <v>2.062999999999999e-05</v>
       </c>
       <c r="J66" t="n">
-        <v>1194.06903594</v>
+        <v>7.988999999999998e-05</v>
       </c>
       <c r="K66" t="n">
-        <v>1751.09843048</v>
+        <v>-3.629999999999995e-06</v>
       </c>
       <c r="L66" t="n">
-        <v>599.7315965499999</v>
+        <v>0.00015752</v>
       </c>
       <c r="M66" t="n">
-        <v>-1801.28695509</v>
+        <v>0.00021599</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右下</t>
+          <t>通信網路業右上</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>-74.88972738000001</v>
+        <v>657.86009789</v>
       </c>
       <c r="D67" t="n">
-        <v>-97.46323704000001</v>
+        <v>838.4339267500001</v>
       </c>
       <c r="E67" t="n">
-        <v>-100.39485247</v>
+        <v>978.4677195099999</v>
       </c>
       <c r="F67" t="n">
-        <v>-108.88161837</v>
+        <v>1089.04459757</v>
       </c>
       <c r="G67" t="n">
-        <v>-49.34560721</v>
+        <v>1149.20011947</v>
       </c>
       <c r="H67" t="n">
-        <v>-40.32005366</v>
+        <v>1101.85639988</v>
       </c>
       <c r="I67" t="n">
-        <v>-39.00891055</v>
+        <v>1227.01135597</v>
       </c>
       <c r="J67" t="n">
-        <v>-17.81442497</v>
+        <v>1805.3234625</v>
       </c>
       <c r="K67" t="n">
-        <v>5.999381360000001</v>
+        <v>665.9036217</v>
       </c>
       <c r="L67" t="n">
-        <v>-0.7701470400000022</v>
+        <v>-1778.21192228</v>
       </c>
       <c r="M67" t="n">
-        <v>-37.88870957</v>
+        <v>-1147.36090812</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>通信網路業平</t>
+          <t>通信網路業右下</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>182.23689366</v>
+        <v>-97.46323704000001</v>
       </c>
       <c r="D68" t="n">
-        <v>0.3783369500000233</v>
+        <v>-100.39485247</v>
       </c>
       <c r="E68" t="n">
-        <v>-56.96720261999998</v>
+        <v>-108.88161837</v>
       </c>
       <c r="F68" t="n">
-        <v>-43.03785831999999</v>
+        <v>-49.34560721</v>
       </c>
       <c r="G68" t="n">
-        <v>43.41552827</v>
+        <v>-40.32005366</v>
       </c>
       <c r="H68" t="n">
-        <v>-31.96114228999999</v>
+        <v>-39.00891055</v>
       </c>
       <c r="I68" t="n">
-        <v>53.79927942</v>
+        <v>-17.81442497</v>
       </c>
       <c r="J68" t="n">
-        <v>-0.6413213799999855</v>
+        <v>5.999381360000001</v>
       </c>
       <c r="K68" t="n">
-        <v>47.36549824999998</v>
+        <v>-0.7701470400000022</v>
       </c>
       <c r="L68" t="n">
-        <v>-27.16941134000001</v>
+        <v>-37.88870957</v>
       </c>
       <c r="M68" t="n">
-        <v>-271.15013425</v>
+        <v>-10.25846167</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>造紙工業右下</t>
+          <t>通信網路業平</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>1.481096</v>
+        <v>-104.31144954</v>
       </c>
       <c r="D69" t="n">
-        <v>-2.09694106</v>
+        <v>-168.70305404</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.18870531</v>
+        <v>-99.35536096</v>
       </c>
       <c r="F69" t="n">
-        <v>0.8999840899999999</v>
+        <v>-19.30403371000001</v>
       </c>
       <c r="G69" t="n">
-        <v>-1.07992369</v>
+        <v>-58.07465672999999</v>
       </c>
       <c r="H69" t="n">
-        <v>-8.13542947</v>
+        <v>43.46263692</v>
       </c>
       <c r="I69" t="n">
-        <v>-6.112742610000001</v>
+        <v>-33.58364140999999</v>
       </c>
       <c r="J69" t="n">
-        <v>0.62737845</v>
+        <v>-6.859533770000024</v>
       </c>
       <c r="K69" t="n">
-        <v>-1.39124728</v>
+        <v>-93.34143649000001</v>
       </c>
       <c r="L69" t="n">
-        <v>-3.48094111</v>
+        <v>-294.22516706</v>
       </c>
       <c r="M69" t="n">
-        <v>-5.56892512</v>
+        <v>-49.62239208</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>造紙工業平</t>
+          <t>造紙工業右下</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>0.15859867</v>
+        <v>-2.09694106</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.01651628</v>
+        <v>-1.18870531</v>
       </c>
       <c r="E70" t="n">
-        <v>0.93115824</v>
+        <v>0.8999840899999999</v>
       </c>
       <c r="F70" t="n">
-        <v>0.15324129</v>
+        <v>-1.07992369</v>
       </c>
       <c r="G70" t="n">
-        <v>2.0141396</v>
+        <v>-8.13542947</v>
       </c>
       <c r="H70" t="n">
-        <v>0.94456732</v>
+        <v>-6.112742610000001</v>
       </c>
       <c r="I70" t="n">
-        <v>1.31059385</v>
+        <v>0.62737845</v>
       </c>
       <c r="J70" t="n">
-        <v>0.44808132</v>
+        <v>-1.39124728</v>
       </c>
       <c r="K70" t="n">
-        <v>1.02481299</v>
+        <v>-3.48094111</v>
       </c>
       <c r="L70" t="n">
-        <v>0.39879786</v>
+        <v>-5.56892512</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.4558637</v>
+        <v>1.72853993</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右上</t>
+          <t>造紙工業平</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
-        <v>49.03197814</v>
+        <v>-0.01651628</v>
       </c>
       <c r="D71" t="n">
-        <v>20.29127258</v>
+        <v>0.93115824</v>
       </c>
       <c r="E71" t="n">
-        <v>24.00895878</v>
+        <v>0.15324129</v>
       </c>
       <c r="F71" t="n">
-        <v>34.17125779</v>
+        <v>2.0141396</v>
       </c>
       <c r="G71" t="n">
-        <v>-3.0706811</v>
+        <v>0.94456732</v>
       </c>
       <c r="H71" t="n">
-        <v>-7.127004649999999</v>
+        <v>1.31059385</v>
       </c>
       <c r="I71" t="n">
-        <v>-16.45539349</v>
+        <v>0.44808132</v>
       </c>
       <c r="J71" t="n">
-        <v>-1.46575611</v>
+        <v>1.02481299</v>
       </c>
       <c r="K71" t="n">
-        <v>-28.70342079</v>
+        <v>0.39879786</v>
       </c>
       <c r="L71" t="n">
-        <v>-30.10771701</v>
+        <v>-0.4558637</v>
       </c>
       <c r="M71" t="n">
-        <v>-17.75000963</v>
+        <v>0.5983068499999999</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右下</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>0</v>
-      </c>
+          <t>運動休閒右上</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>-81.91164641</v>
+        <v>20.29127258</v>
       </c>
       <c r="D72" t="n">
-        <v>-115.31225339</v>
+        <v>24.00895878</v>
       </c>
       <c r="E72" t="n">
-        <v>-37.30359735</v>
+        <v>34.17125779</v>
       </c>
       <c r="F72" t="n">
-        <v>-103.56379597</v>
+        <v>-3.0706811</v>
       </c>
       <c r="G72" t="n">
-        <v>-54.40126461</v>
+        <v>-7.127004649999999</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.911962920000004</v>
+        <v>-16.45539349</v>
       </c>
       <c r="I72" t="n">
-        <v>111.99431699</v>
+        <v>-1.46575611</v>
       </c>
       <c r="J72" t="n">
-        <v>111.66897828</v>
+        <v>-28.70342079</v>
       </c>
       <c r="K72" t="n">
-        <v>-3.999638780000003</v>
+        <v>-30.10771701</v>
       </c>
       <c r="L72" t="n">
-        <v>-119.43976164</v>
+        <v>-17.75000963</v>
       </c>
       <c r="M72" t="n">
-        <v>-105.75567819</v>
+        <v>-16.20229139</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>運動休閒平</t>
+          <t>運動休閒右下</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
-        <v>-9.691171220000001</v>
+        <v>-115.31227011</v>
       </c>
       <c r="D73" t="n">
-        <v>-11.21701609</v>
+        <v>-37.30362026</v>
       </c>
       <c r="E73" t="n">
-        <v>-24.50112135</v>
+        <v>-103.56392674</v>
       </c>
       <c r="F73" t="n">
-        <v>-23.85631305</v>
+        <v>-54.40137722999999</v>
       </c>
       <c r="G73" t="n">
-        <v>-23.78075616</v>
+        <v>-0.9121308300000042</v>
       </c>
       <c r="H73" t="n">
-        <v>-20.79905364</v>
+        <v>111.99430636</v>
       </c>
       <c r="I73" t="n">
-        <v>7.640183769999999</v>
+        <v>111.66897061</v>
       </c>
       <c r="J73" t="n">
-        <v>-8.013334910000001</v>
+        <v>-3.999667890000003</v>
       </c>
       <c r="K73" t="n">
-        <v>-21.10458214000001</v>
+        <v>-119.43980218</v>
       </c>
       <c r="L73" t="n">
-        <v>-30.02046044</v>
+        <v>-105.75567652</v>
       </c>
       <c r="M73" t="n">
-        <v>-8.537947050000001</v>
+        <v>15.98449054</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>金融保險右上</t>
+          <t>運動休閒平</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
-        <v>1242.79248807</v>
+        <v>-11.21701609</v>
       </c>
       <c r="D74" t="n">
-        <v>851.86550735</v>
+        <v>-24.50112135</v>
       </c>
       <c r="E74" t="n">
-        <v>703.0305864300001</v>
+        <v>-23.85631305</v>
       </c>
       <c r="F74" t="n">
-        <v>664.72535027</v>
+        <v>-23.78075616</v>
       </c>
       <c r="G74" t="n">
-        <v>656.9999549300001</v>
+        <v>-20.79905364</v>
       </c>
       <c r="H74" t="n">
-        <v>922.40805115</v>
+        <v>7.640183769999999</v>
       </c>
       <c r="I74" t="n">
-        <v>1352.18679415</v>
+        <v>-8.013334910000001</v>
       </c>
       <c r="J74" t="n">
-        <v>443.55634693</v>
+        <v>-21.10458214000001</v>
       </c>
       <c r="K74" t="n">
-        <v>296.15320315</v>
+        <v>-30.02046044</v>
       </c>
       <c r="L74" t="n">
-        <v>-274.2499456</v>
+        <v>-8.537947050000001</v>
       </c>
       <c r="M74" t="n">
-        <v>-985.81143814</v>
+        <v>11.30247419</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>金融保險右下</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
-        <v>0</v>
-      </c>
+          <t>金融保險右上</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
-        <v>166.88105806</v>
+        <v>851.86550735</v>
       </c>
       <c r="D75" t="n">
-        <v>-29.24538225</v>
+        <v>703.0305864300001</v>
       </c>
       <c r="E75" t="n">
-        <v>-217.03758715</v>
+        <v>664.72535027</v>
       </c>
       <c r="F75" t="n">
-        <v>-381.0536326899999</v>
+        <v>656.9999549300001</v>
       </c>
       <c r="G75" t="n">
-        <v>-510.1900488100001</v>
+        <v>922.40805115</v>
       </c>
       <c r="H75" t="n">
-        <v>-257.06344158</v>
+        <v>1352.18679415</v>
       </c>
       <c r="I75" t="n">
-        <v>-15.66310559</v>
+        <v>443.55634693</v>
       </c>
       <c r="J75" t="n">
-        <v>-63.22544475999999</v>
+        <v>296.15320315</v>
       </c>
       <c r="K75" t="n">
-        <v>44.96276262999999</v>
+        <v>-274.2499456</v>
       </c>
       <c r="L75" t="n">
-        <v>11.43137598</v>
+        <v>-985.81143814</v>
       </c>
       <c r="M75" t="n">
-        <v>129.33146676</v>
+        <v>-778.2785946499999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>金融保險平</t>
+          <t>金融保險右下</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>13.71012711</v>
+        <v>-29.24538225</v>
       </c>
       <c r="D76" t="n">
-        <v>-5.745900730000001</v>
+        <v>-217.03758715</v>
       </c>
       <c r="E76" t="n">
-        <v>4.30056158</v>
+        <v>-381.0536326899999</v>
       </c>
       <c r="F76" t="n">
-        <v>44.18124179</v>
+        <v>-510.1900488100001</v>
       </c>
       <c r="G76" t="n">
-        <v>30.18417386</v>
+        <v>-257.06344158</v>
       </c>
       <c r="H76" t="n">
-        <v>37.38347089</v>
+        <v>-15.66310559</v>
       </c>
       <c r="I76" t="n">
-        <v>81.34864014999999</v>
+        <v>-63.22544475999999</v>
       </c>
       <c r="J76" t="n">
-        <v>50.99804315999999</v>
+        <v>44.96276262999999</v>
       </c>
       <c r="K76" t="n">
-        <v>16.02535167</v>
+        <v>11.43137598</v>
       </c>
       <c r="L76" t="n">
-        <v>-14.83456122</v>
+        <v>129.33146676</v>
       </c>
       <c r="M76" t="n">
-        <v>-41.55389577</v>
+        <v>200.67327692</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>金融業右上</t>
+          <t>金融保險平</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="n">
-        <v>0.0006016</v>
+        <v>2.699553660000002</v>
       </c>
       <c r="D77" t="n">
-        <v>0.00119589</v>
+        <v>16.53077912</v>
       </c>
       <c r="E77" t="n">
-        <v>0.00222055</v>
+        <v>58.56651676</v>
       </c>
       <c r="F77" t="n">
-        <v>0.00226234</v>
+        <v>51.54869252</v>
       </c>
       <c r="G77" t="n">
-        <v>0.00101082</v>
+        <v>63.32101605</v>
       </c>
       <c r="H77" t="n">
-        <v>9.988e-05</v>
+        <v>91.13898772</v>
       </c>
       <c r="I77" t="n">
-        <v>0.00032912</v>
+        <v>50.10705141</v>
       </c>
       <c r="J77" t="n">
-        <v>-0.00052438</v>
+        <v>26.81862522</v>
       </c>
       <c r="K77" t="n">
-        <v>-9.99e-05</v>
+        <v>-21.18364655</v>
       </c>
       <c r="L77" t="n">
-        <v>-0.00069427</v>
+        <v>-65.44784787</v>
       </c>
       <c r="M77" t="n">
-        <v>-0.00100544</v>
+        <v>-54.15444815</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>金融業右下</t>
+          <t>金融業右上</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
-        <v>0.0001785999999999999</v>
+        <v>0.00119589</v>
       </c>
       <c r="D78" t="n">
-        <v>0.00166505</v>
+        <v>0.00222055</v>
       </c>
       <c r="E78" t="n">
-        <v>0.00481058</v>
+        <v>0.00226234</v>
       </c>
       <c r="F78" t="n">
-        <v>0.00272902</v>
+        <v>0.00101082</v>
       </c>
       <c r="G78" t="n">
-        <v>9.011000000000007e-05</v>
+        <v>9.988e-05</v>
       </c>
       <c r="H78" t="n">
-        <v>0.0004795100000000002</v>
+        <v>0.00032912</v>
       </c>
       <c r="I78" t="n">
-        <v>0.00329986</v>
+        <v>-0.00052438</v>
       </c>
       <c r="J78" t="n">
-        <v>0.0005099499999999999</v>
+        <v>-9.99e-05</v>
       </c>
       <c r="K78" t="n">
-        <v>-0.0007658099999999999</v>
+        <v>-0.00069427</v>
       </c>
       <c r="L78" t="n">
-        <v>0.0034501</v>
+        <v>-0.00100544</v>
       </c>
       <c r="M78" t="n">
-        <v>0.0005688300000000001</v>
+        <v>-0.00044273</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>金融業平</t>
+          <t>金融業右下</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="n">
-        <v>0.00167124</v>
+        <v>0.00166505</v>
       </c>
       <c r="D79" t="n">
-        <v>0.00103193</v>
+        <v>0.00481058</v>
       </c>
       <c r="E79" t="n">
-        <v>0.00057835</v>
+        <v>0.00272902</v>
       </c>
       <c r="F79" t="n">
-        <v>9.465e-05</v>
+        <v>9.011000000000007e-05</v>
       </c>
       <c r="G79" t="n">
-        <v>0.00013897</v>
+        <v>0.0004795100000000002</v>
       </c>
       <c r="H79" t="n">
-        <v>6.415e-05</v>
+        <v>0.00329986</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.00029419</v>
+        <v>0.0005099499999999999</v>
       </c>
       <c r="J79" t="n">
-        <v>0.00019073</v>
+        <v>-0.0007658099999999999</v>
       </c>
       <c r="K79" t="n">
-        <v>-2.111999999999998e-05</v>
+        <v>0.0034501</v>
       </c>
       <c r="L79" t="n">
-        <v>0.00040195</v>
+        <v>0.0005688300000000001</v>
       </c>
       <c r="M79" t="n">
-        <v>7.686999999999999e-05</v>
+        <v>0.00248966</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上</t>
+          <t>金融業平</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="n">
-        <v>8.421552140000001</v>
+        <v>0.00103193</v>
       </c>
       <c r="D80" t="n">
-        <v>-10.13260721</v>
+        <v>0.00057835</v>
       </c>
       <c r="E80" t="n">
-        <v>-9.68964107</v>
+        <v>9.465e-05</v>
       </c>
       <c r="F80" t="n">
-        <v>4.868124629999999</v>
+        <v>0.00013897</v>
       </c>
       <c r="G80" t="n">
-        <v>12.18883922</v>
+        <v>6.415e-05</v>
       </c>
       <c r="H80" t="n">
-        <v>-4.46799539</v>
+        <v>-0.00029419</v>
       </c>
       <c r="I80" t="n">
-        <v>12.58299348</v>
+        <v>0.00019073</v>
       </c>
       <c r="J80" t="n">
-        <v>17.39570309</v>
+        <v>-2.111999999999998e-05</v>
       </c>
       <c r="K80" t="n">
-        <v>13.14604495</v>
+        <v>0.00040195</v>
       </c>
       <c r="L80" t="n">
-        <v>10.09760665</v>
+        <v>7.686999999999999e-05</v>
       </c>
       <c r="M80" t="n">
-        <v>-4.54740078</v>
+        <v>-0.00026166</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下</t>
+          <t>鋼鐵工業右上</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>-43.25435408</v>
+        <v>-10.13260721</v>
       </c>
       <c r="D81" t="n">
-        <v>-61.35160032</v>
+        <v>-9.68964107</v>
       </c>
       <c r="E81" t="n">
-        <v>-43.0562662</v>
+        <v>4.868124629999999</v>
       </c>
       <c r="F81" t="n">
-        <v>-16.93540232</v>
+        <v>12.18883922</v>
       </c>
       <c r="G81" t="n">
-        <v>31.38022441</v>
+        <v>-4.46799539</v>
       </c>
       <c r="H81" t="n">
-        <v>99.07451711</v>
+        <v>12.58299348</v>
       </c>
       <c r="I81" t="n">
-        <v>135.88422991</v>
+        <v>17.39570309</v>
       </c>
       <c r="J81" t="n">
-        <v>238.91509697</v>
+        <v>13.14604495</v>
       </c>
       <c r="K81" t="n">
-        <v>138.66674355</v>
+        <v>10.09760665</v>
       </c>
       <c r="L81" t="n">
-        <v>49.30860766000001</v>
+        <v>-4.54740078</v>
       </c>
       <c r="M81" t="n">
-        <v>-47.82701062</v>
+        <v>-6.45092565</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業平</t>
+          <t>鋼鐵工業右下</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
-        <v>0.1884262800000012</v>
+        <v>-60.41482480999999</v>
       </c>
       <c r="D82" t="n">
-        <v>-170.38236796</v>
+        <v>-42.32554019</v>
       </c>
       <c r="E82" t="n">
-        <v>95.41277939</v>
+        <v>-15.38525421</v>
       </c>
       <c r="F82" t="n">
-        <v>-152.13774465</v>
+        <v>33.22418543000001</v>
       </c>
       <c r="G82" t="n">
-        <v>-342.33967264</v>
+        <v>96.69647368000001</v>
       </c>
       <c r="H82" t="n">
-        <v>-545.95898001</v>
+        <v>135.04251964</v>
       </c>
       <c r="I82" t="n">
-        <v>-280.96473412</v>
+        <v>234.45379825</v>
       </c>
       <c r="J82" t="n">
-        <v>-160.21890398</v>
+        <v>136.95814913</v>
       </c>
       <c r="K82" t="n">
-        <v>63.94508142</v>
+        <v>45.55118494</v>
       </c>
       <c r="L82" t="n">
-        <v>-39.29490801000001</v>
+        <v>-50.25659699000001</v>
       </c>
       <c r="M82" t="n">
-        <v>-182.02364974</v>
+        <v>9.74345312</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右上</t>
+          <t>鋼鐵工業平</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>173.80208869</v>
+        <v>-171.31914347</v>
       </c>
       <c r="D83" t="n">
-        <v>68.31111571000001</v>
+        <v>94.68205338000001</v>
       </c>
       <c r="E83" t="n">
-        <v>-15.21283794</v>
+        <v>-153.68789276</v>
       </c>
       <c r="F83" t="n">
-        <v>-17.71552102</v>
+        <v>-344.18363366</v>
       </c>
       <c r="G83" t="n">
-        <v>-64.05499739</v>
+        <v>-543.5809365800001</v>
       </c>
       <c r="H83" t="n">
-        <v>-108.28490628</v>
+        <v>-280.12302385</v>
       </c>
       <c r="I83" t="n">
-        <v>17.23501362</v>
+        <v>-155.75760526</v>
       </c>
       <c r="J83" t="n">
-        <v>-42.91166961</v>
+        <v>65.65367583999999</v>
       </c>
       <c r="K83" t="n">
-        <v>-16.22533502</v>
+        <v>-35.53748529000001</v>
       </c>
       <c r="L83" t="n">
-        <v>-7.978113619999998</v>
+        <v>-179.59406337</v>
       </c>
       <c r="M83" t="n">
-        <v>-41.15140009</v>
+        <v>-21.58922288000001</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右下</t>
+          <t>電器電纜右上</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
-        <v>-10.32345865</v>
+        <v>68.31111571000001</v>
       </c>
       <c r="D84" t="n">
-        <v>20.68587184</v>
+        <v>-15.21283794</v>
       </c>
       <c r="E84" t="n">
-        <v>50.4358599</v>
+        <v>-17.71552102</v>
       </c>
       <c r="F84" t="n">
-        <v>20.67695317</v>
+        <v>-64.05499739</v>
       </c>
       <c r="G84" t="n">
-        <v>39.12531966</v>
+        <v>-108.28490628</v>
       </c>
       <c r="H84" t="n">
-        <v>82.69031135000002</v>
+        <v>17.23501362</v>
       </c>
       <c r="I84" t="n">
-        <v>154.59545891</v>
+        <v>-42.91166961</v>
       </c>
       <c r="J84" t="n">
-        <v>58.71590928</v>
+        <v>-16.22533502</v>
       </c>
       <c r="K84" t="n">
-        <v>121.63718761</v>
+        <v>-7.978113619999998</v>
       </c>
       <c r="L84" t="n">
-        <v>29.61562639</v>
+        <v>-41.15140009</v>
       </c>
       <c r="M84" t="n">
-        <v>-24.78285621</v>
+        <v>-27.68817933</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>電器電纜平</t>
+          <t>電器電纜右下</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>91.58317283999999</v>
+        <v>20.68587184</v>
       </c>
       <c r="D85" t="n">
-        <v>307.99625718</v>
+        <v>50.4358599</v>
       </c>
       <c r="E85" t="n">
-        <v>127.17974363</v>
+        <v>20.67695317</v>
       </c>
       <c r="F85" t="n">
-        <v>35.51983674</v>
+        <v>39.12531966</v>
       </c>
       <c r="G85" t="n">
-        <v>-44.38674216</v>
+        <v>82.69031135000002</v>
       </c>
       <c r="H85" t="n">
-        <v>-80.33944907999999</v>
+        <v>154.59545891</v>
       </c>
       <c r="I85" t="n">
-        <v>17.36541503</v>
+        <v>58.71590928</v>
       </c>
       <c r="J85" t="n">
-        <v>-22.22959168</v>
+        <v>121.63718761</v>
       </c>
       <c r="K85" t="n">
-        <v>36.66650072</v>
+        <v>29.61562639</v>
       </c>
       <c r="L85" t="n">
-        <v>-47.17463461</v>
+        <v>-24.78285621</v>
       </c>
       <c r="M85" t="n">
-        <v>-72.74271278000001</v>
+        <v>2.232190660000001</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右上</t>
+          <t>電器電纜平</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
-        <v>-4.04860231</v>
+        <v>307.99625718</v>
       </c>
       <c r="D86" t="n">
-        <v>-13.91812297</v>
+        <v>127.17974363</v>
       </c>
       <c r="E86" t="n">
-        <v>-26.74595337</v>
+        <v>35.51983674</v>
       </c>
       <c r="F86" t="n">
-        <v>6.37891582</v>
+        <v>-44.38674216</v>
       </c>
       <c r="G86" t="n">
-        <v>68.23265044</v>
+        <v>-80.33944907999999</v>
       </c>
       <c r="H86" t="n">
-        <v>23.90605647</v>
+        <v>17.36541503</v>
       </c>
       <c r="I86" t="n">
-        <v>-37.2038651</v>
+        <v>-22.22959168</v>
       </c>
       <c r="J86" t="n">
-        <v>-34.68524193</v>
+        <v>36.66650072</v>
       </c>
       <c r="K86" t="n">
-        <v>-68.94026530999999</v>
+        <v>-47.17463461</v>
       </c>
       <c r="L86" t="n">
-        <v>-56.73407539</v>
+        <v>-72.74271278000001</v>
       </c>
       <c r="M86" t="n">
-        <v>-15.45230189</v>
+        <v>-28.99937651</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右下</t>
+          <t>電子通路業右上</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>90.98057971999999</v>
+        <v>-73.51635168999999</v>
       </c>
       <c r="D87" t="n">
-        <v>16.93207719</v>
+        <v>-120.3851038</v>
       </c>
       <c r="E87" t="n">
-        <v>-67.92105245</v>
+        <v>-28.81111416</v>
       </c>
       <c r="F87" t="n">
-        <v>-169.6017512</v>
+        <v>26.43414951</v>
       </c>
       <c r="G87" t="n">
-        <v>-200.60217824</v>
+        <v>-19.93885504</v>
       </c>
       <c r="H87" t="n">
-        <v>-165.28100234</v>
+        <v>-44.01148098</v>
       </c>
       <c r="I87" t="n">
-        <v>-136.35591918</v>
+        <v>-47.83444747999999</v>
       </c>
       <c r="J87" t="n">
-        <v>-127.41416022</v>
+        <v>-49.88869408</v>
       </c>
       <c r="K87" t="n">
-        <v>-99.86235365</v>
+        <v>-54.40387915000001</v>
       </c>
       <c r="L87" t="n">
-        <v>-99.31666487999999</v>
+        <v>-32.84970408</v>
       </c>
       <c r="M87" t="n">
-        <v>-107.42663417</v>
+        <v>-6.346303820000002</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>電子通路業平</t>
+          <t>電子通路業右下</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
-        <v>36.57455757</v>
+        <v>16.93232156</v>
       </c>
       <c r="D88" t="n">
-        <v>-14.95004816</v>
+        <v>-67.92127349</v>
       </c>
       <c r="E88" t="n">
-        <v>-92.18056577000002</v>
+        <v>-169.60221825</v>
       </c>
       <c r="F88" t="n">
-        <v>-41.55750256</v>
+        <v>-200.60278138</v>
       </c>
       <c r="G88" t="n">
-        <v>-20.47460762</v>
+        <v>-165.28038545</v>
       </c>
       <c r="H88" t="n">
-        <v>-67.28577043999999</v>
+        <v>-136.35649575</v>
       </c>
       <c r="I88" t="n">
-        <v>-40.03086548</v>
+        <v>-127.41548752</v>
       </c>
       <c r="J88" t="n">
-        <v>-30.75194596</v>
+        <v>-99.86377270999999</v>
       </c>
       <c r="K88" t="n">
-        <v>23.37435337</v>
+        <v>-99.33268954</v>
       </c>
       <c r="L88" t="n">
-        <v>35.07272512000001</v>
+        <v>-107.43049933</v>
       </c>
       <c r="M88" t="n">
-        <v>-27.42918962</v>
+        <v>-13.84931573</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右上</t>
+          <t>電子通路業平</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>1182.11866472</v>
+        <v>44.64793619</v>
       </c>
       <c r="D89" t="n">
-        <v>817.053399</v>
+        <v>1.458805700000001</v>
       </c>
       <c r="E89" t="n">
-        <v>3457.49698208</v>
+        <v>-6.36700553</v>
       </c>
       <c r="F89" t="n">
-        <v>5025.11440555</v>
+        <v>21.32449645</v>
       </c>
       <c r="G89" t="n">
-        <v>4950.6694852</v>
+        <v>-23.44147582</v>
       </c>
       <c r="H89" t="n">
-        <v>5001.32971024</v>
+        <v>-33.22267303</v>
       </c>
       <c r="I89" t="n">
-        <v>4878.45836897</v>
+        <v>-17.60141311</v>
       </c>
       <c r="J89" t="n">
-        <v>3521.836542290001</v>
+        <v>4.3242012</v>
       </c>
       <c r="K89" t="n">
-        <v>5013.69783426</v>
+        <v>32.75855354</v>
       </c>
       <c r="L89" t="n">
-        <v>-169.5068375399998</v>
+        <v>-10.02792227</v>
       </c>
       <c r="M89" t="n">
-        <v>-7263.958555890001</v>
+        <v>7.924349729999999</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右下</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
-        <v>0</v>
-      </c>
+          <t>電子零組件業右上</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>-617.9405942899999</v>
+        <v>799.1942517</v>
       </c>
       <c r="D90" t="n">
-        <v>-512.11831169</v>
+        <v>3442.96219592</v>
       </c>
       <c r="E90" t="n">
-        <v>-402.77212489</v>
+        <v>5014.323862409999</v>
       </c>
       <c r="F90" t="n">
-        <v>-36.43205005999999</v>
+        <v>4925.21886095</v>
       </c>
       <c r="G90" t="n">
-        <v>-377.95209684</v>
+        <v>5037.87784865</v>
       </c>
       <c r="H90" t="n">
-        <v>-797.10663956</v>
+        <v>4989.59937478</v>
       </c>
       <c r="I90" t="n">
-        <v>-1000.82173937</v>
+        <v>3565.94765664</v>
       </c>
       <c r="J90" t="n">
-        <v>-1098.52798332</v>
+        <v>5065.49505683</v>
       </c>
       <c r="K90" t="n">
-        <v>-199.4238228299999</v>
+        <v>-165.23339115</v>
       </c>
       <c r="L90" t="n">
-        <v>-603.82651206</v>
+        <v>-7286.71586753</v>
       </c>
       <c r="M90" t="n">
-        <v>-944.82321204</v>
+        <v>-2012.07423383</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業平</t>
+          <t>電子零組件業右下</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>-470.74915855</v>
+        <v>-496.29692916</v>
       </c>
       <c r="D91" t="n">
-        <v>-485.13908238</v>
+        <v>-386.03117314</v>
       </c>
       <c r="E91" t="n">
-        <v>-531.52777423</v>
+        <v>-28.98295736</v>
       </c>
       <c r="F91" t="n">
-        <v>-279.35505049</v>
+        <v>-376.07515394</v>
       </c>
       <c r="G91" t="n">
-        <v>-577.8359113299999</v>
+        <v>-804.22655073</v>
       </c>
       <c r="H91" t="n">
-        <v>-824.0437270499999</v>
+        <v>-1021.47958938</v>
       </c>
       <c r="I91" t="n">
-        <v>-1055.54506517</v>
+        <v>-1118.85660026</v>
       </c>
       <c r="J91" t="n">
-        <v>-1055.64407792</v>
+        <v>-228.90670528</v>
       </c>
       <c r="K91" t="n">
-        <v>-326.93291329</v>
+        <v>-614.17846718</v>
       </c>
       <c r="L91" t="n">
-        <v>-685.6039252299998</v>
+        <v>-943.0657091999999</v>
       </c>
       <c r="M91" t="n">
-        <v>-874.10051376</v>
+        <v>-922.04330622</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>電機機械右上</t>
+          <t>電子零組件業平</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>-433.73346051</v>
+        <v>-484.4882497</v>
       </c>
       <c r="D92" t="n">
-        <v>806.5171311299999</v>
+        <v>-503.7852061</v>
       </c>
       <c r="E92" t="n">
-        <v>-167.88835007</v>
+        <v>-271.71588505</v>
       </c>
       <c r="F92" t="n">
-        <v>-11.75600005000001</v>
+        <v>-579.24298917</v>
       </c>
       <c r="G92" t="n">
-        <v>-1172.87832086</v>
+        <v>-804.3247031000001</v>
       </c>
       <c r="H92" t="n">
-        <v>-35.76254806999992</v>
+        <v>-1008.48160613</v>
       </c>
       <c r="I92" t="n">
-        <v>-127.70470049</v>
+        <v>-999.8074179099999</v>
       </c>
       <c r="J92" t="n">
-        <v>-456.25515482</v>
+        <v>-260.20739523</v>
       </c>
       <c r="K92" t="n">
-        <v>512.9469588100001</v>
+        <v>-637.8094149</v>
       </c>
       <c r="L92" t="n">
-        <v>-504.77581997</v>
+        <v>-865.29594535</v>
       </c>
       <c r="M92" t="n">
-        <v>-1267.46074306</v>
+        <v>-268.43406529</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>電機機械右下</t>
+          <t>電機機械右上</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>-110.70001883</v>
+        <v>806.5163776000001</v>
       </c>
       <c r="D93" t="n">
-        <v>6.201356979999997</v>
+        <v>-167.88800253</v>
       </c>
       <c r="E93" t="n">
-        <v>97.14637482000001</v>
+        <v>-11.75632670000002</v>
       </c>
       <c r="F93" t="n">
-        <v>65.14308164000001</v>
+        <v>-1172.87813522</v>
       </c>
       <c r="G93" t="n">
-        <v>-20.06744734</v>
+        <v>-35.76061781999991</v>
       </c>
       <c r="H93" t="n">
-        <v>-141.52817454</v>
+        <v>-127.70024637</v>
       </c>
       <c r="I93" t="n">
-        <v>-80.82108792</v>
+        <v>-456.2485559</v>
       </c>
       <c r="J93" t="n">
-        <v>4.55315406</v>
+        <v>512.9479078700001</v>
       </c>
       <c r="K93" t="n">
-        <v>157.24168626</v>
+        <v>-504.77735899</v>
       </c>
       <c r="L93" t="n">
-        <v>-5.068348040000001</v>
+        <v>-1267.46309763</v>
       </c>
       <c r="M93" t="n">
-        <v>-120.02153486</v>
+        <v>-148.71845313</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>電機機械平</t>
+          <t>電機機械右下</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>176.06148637</v>
+        <v>6.201367509999998</v>
       </c>
       <c r="D94" t="n">
-        <v>199.25781802</v>
+        <v>97.14644838000001</v>
       </c>
       <c r="E94" t="n">
-        <v>116.38953113</v>
+        <v>65.14312098000001</v>
       </c>
       <c r="F94" t="n">
-        <v>44.33213470999999</v>
+        <v>-20.06739709</v>
       </c>
       <c r="G94" t="n">
-        <v>105.36387486</v>
+        <v>-141.52816051</v>
       </c>
       <c r="H94" t="n">
-        <v>109.32295593</v>
+        <v>-80.82108114000002</v>
       </c>
       <c r="I94" t="n">
-        <v>164.17161745</v>
+        <v>4.553131289999999</v>
       </c>
       <c r="J94" t="n">
-        <v>223.01891032</v>
+        <v>157.24166445</v>
       </c>
       <c r="K94" t="n">
-        <v>144.92671263</v>
+        <v>-5.068415730000001</v>
       </c>
       <c r="L94" t="n">
-        <v>101.7461128</v>
+        <v>-120.02159172</v>
       </c>
       <c r="M94" t="n">
-        <v>-89.03653050999999</v>
+        <v>23.6635599</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上</t>
+          <t>電機機械平</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>884.4743874199997</v>
+        <v>199.25856102</v>
       </c>
       <c r="D95" t="n">
-        <v>1617.73891508</v>
+        <v>116.38911003</v>
       </c>
       <c r="E95" t="n">
-        <v>2457.80099751</v>
+        <v>44.33242202</v>
       </c>
       <c r="F95" t="n">
-        <v>2790.69579102</v>
+        <v>105.36363897</v>
       </c>
       <c r="G95" t="n">
-        <v>977.25624004</v>
+        <v>109.32101165</v>
       </c>
       <c r="H95" t="n">
-        <v>-1482.82945407</v>
+        <v>164.16715655</v>
       </c>
       <c r="I95" t="n">
-        <v>-1904.38526962</v>
+        <v>223.01233417</v>
       </c>
       <c r="J95" t="n">
-        <v>-1256.94743565</v>
+        <v>144.92578538</v>
       </c>
       <c r="K95" t="n">
-        <v>-1397.76517245</v>
+        <v>101.74771951</v>
       </c>
       <c r="L95" t="n">
-        <v>-2285.96555667</v>
+        <v>-89.03411908</v>
       </c>
       <c r="M95" t="n">
-        <v>-5136.93517469</v>
+        <v>-25.87040719</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下</t>
+          <t>電腦及週邊設備業右上</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>43.45239911</v>
+        <v>1362.63545905</v>
       </c>
       <c r="D96" t="n">
-        <v>-24.72223465000001</v>
+        <v>2059.87154895</v>
       </c>
       <c r="E96" t="n">
-        <v>-328.47747728</v>
+        <v>1916.12359133</v>
       </c>
       <c r="F96" t="n">
-        <v>-548.62950641</v>
+        <v>788.4595847899999</v>
       </c>
       <c r="G96" t="n">
-        <v>-582.2291348799999</v>
+        <v>-4.285213879999727</v>
       </c>
       <c r="H96" t="n">
-        <v>-615.6505054400001</v>
+        <v>-297.7012908</v>
       </c>
       <c r="I96" t="n">
-        <v>-621.70691772</v>
+        <v>327.4414372199998</v>
       </c>
       <c r="J96" t="n">
-        <v>-428.221756</v>
+        <v>69.97099040000006</v>
       </c>
       <c r="K96" t="n">
-        <v>-447.85606706</v>
+        <v>-1075.39165907</v>
       </c>
       <c r="L96" t="n">
-        <v>-331.70381063</v>
+        <v>-4092.80492937</v>
       </c>
       <c r="M96" t="n">
-        <v>-463.23062184</v>
+        <v>-1317.53712474</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平</t>
+          <t>電腦及週邊設備業右下</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>833.3958264300001</v>
+        <v>7.600439939999993</v>
       </c>
       <c r="D97" t="n">
-        <v>1058.51929207</v>
+        <v>-390.66759332</v>
       </c>
       <c r="E97" t="n">
-        <v>966.08941626</v>
+        <v>-572.8400540499999</v>
       </c>
       <c r="F97" t="n">
-        <v>237.41331469</v>
+        <v>-662.7678312099999</v>
       </c>
       <c r="G97" t="n">
-        <v>-658.57443563</v>
+        <v>-743.8964670800001</v>
       </c>
       <c r="H97" t="n">
-        <v>-1953.99405983</v>
+        <v>-758.00109663</v>
       </c>
       <c r="I97" t="n">
-        <v>-2091.88532349</v>
+        <v>-582.72918838</v>
       </c>
       <c r="J97" t="n">
-        <v>-2188.66228933</v>
+        <v>-492.98203666</v>
       </c>
       <c r="K97" t="n">
-        <v>-1829.25949117</v>
+        <v>-394.55857577</v>
       </c>
       <c r="L97" t="n">
-        <v>-1517.81351032</v>
+        <v>-450.82362474</v>
       </c>
       <c r="M97" t="n">
-        <v>-1861.93314449</v>
+        <v>-195.19934005</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>食品工業右上</t>
+          <t>電腦及週邊設備業平</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
-        <v>27.36598622</v>
+        <v>1281.30007351</v>
       </c>
       <c r="D98" t="n">
-        <v>21.46284854</v>
+        <v>1426.20898086</v>
       </c>
       <c r="E98" t="n">
-        <v>2.43384234</v>
+        <v>1136.19606202</v>
       </c>
       <c r="F98" t="n">
-        <v>3.42921125</v>
+        <v>-389.23908405</v>
       </c>
       <c r="G98" t="n">
-        <v>20.06839899</v>
+        <v>-3304.29233838</v>
       </c>
       <c r="H98" t="n">
-        <v>29.26418117</v>
+        <v>-3562.2751234</v>
       </c>
       <c r="I98" t="n">
-        <v>17.238713</v>
+        <v>-3618.54372982</v>
       </c>
       <c r="J98" t="n">
-        <v>24.67003403</v>
+        <v>-3251.86968442</v>
       </c>
       <c r="K98" t="n">
-        <v>34.21972625</v>
+        <v>-2665.53264278</v>
       </c>
       <c r="L98" t="n">
-        <v>36.67212921999999</v>
+        <v>-2918.47038691</v>
       </c>
       <c r="M98" t="n">
-        <v>25.20784637</v>
+        <v>-2659.5171722</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>食品工業右下</t>
+          <t>食品工業右上</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>17.26166795</v>
+        <v>21.4617507</v>
       </c>
       <c r="D99" t="n">
-        <v>6.075726189999999</v>
+        <v>2.43043327</v>
       </c>
       <c r="E99" t="n">
-        <v>-1.47041395</v>
+        <v>3.42453723</v>
       </c>
       <c r="F99" t="n">
-        <v>-12.68523507</v>
+        <v>20.0696195</v>
       </c>
       <c r="G99" t="n">
-        <v>-16.25005949</v>
+        <v>29.27378089</v>
       </c>
       <c r="H99" t="n">
-        <v>-10.87937043</v>
+        <v>17.24417347</v>
       </c>
       <c r="I99" t="n">
-        <v>4.36138133</v>
+        <v>24.68333282</v>
       </c>
       <c r="J99" t="n">
-        <v>2.550761389999999</v>
+        <v>34.23585004</v>
       </c>
       <c r="K99" t="n">
-        <v>5.33204738</v>
+        <v>36.69660673999999</v>
       </c>
       <c r="L99" t="n">
-        <v>7.818490239999999</v>
+        <v>25.24661327</v>
       </c>
       <c r="M99" t="n">
-        <v>-4.54547223</v>
+        <v>13.11654365</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>食品工業平</t>
+          <t>食品工業右下</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="n">
-        <v>-94.32169284999999</v>
+        <v>6.075689359999999</v>
       </c>
       <c r="D100" t="n">
-        <v>-157.36599739</v>
+        <v>-1.47053638</v>
       </c>
       <c r="E100" t="n">
-        <v>-218.54965054</v>
+        <v>-12.68556489</v>
       </c>
       <c r="F100" t="n">
-        <v>-239.318106</v>
+        <v>-16.25043143</v>
       </c>
       <c r="G100" t="n">
-        <v>-229.81989502</v>
+        <v>-10.87959711</v>
       </c>
       <c r="H100" t="n">
-        <v>-223.32690569</v>
+        <v>4.361278050000001</v>
       </c>
       <c r="I100" t="n">
-        <v>-73.25274198000001</v>
+        <v>2.550610799999999</v>
       </c>
       <c r="J100" t="n">
-        <v>16.3684944</v>
+        <v>5.331896309999999</v>
       </c>
       <c r="K100" t="n">
-        <v>-17.95734398</v>
+        <v>7.818366909999999</v>
       </c>
       <c r="L100" t="n">
-        <v>-34.63364573</v>
+        <v>-4.54547083</v>
       </c>
       <c r="M100" t="n">
-        <v>-47.55095419</v>
+        <v>7.62272642</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>食品工業平</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
+      <c r="C101" t="n">
+        <v>-157.36489955</v>
+      </c>
+      <c r="D101" t="n">
+        <v>-218.54624147</v>
+      </c>
+      <c r="E101" t="n">
+        <v>-239.31343198</v>
+      </c>
+      <c r="F101" t="n">
+        <v>-229.82111553</v>
+      </c>
+      <c r="G101" t="n">
+        <v>-223.33650541</v>
+      </c>
+      <c r="H101" t="n">
+        <v>-73.25820245</v>
+      </c>
+      <c r="I101" t="n">
+        <v>16.35519561</v>
+      </c>
+      <c r="J101" t="n">
+        <v>-17.97346777</v>
+      </c>
+      <c r="K101" t="n">
+        <v>-34.65812325</v>
+      </c>
+      <c r="L101" t="n">
+        <v>-47.58972109</v>
+      </c>
+      <c r="M101" t="n">
+        <v>62.04757827</v>
       </c>
     </row>
   </sheetData>

--- a/Result/analyze_2.xlsx
+++ b/Result/analyze_2.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
     </row>
@@ -503,37 +503,37 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>166.33007659</v>
+        <v>726.59775904</v>
       </c>
       <c r="D2" t="n">
-        <v>727.06237172</v>
+        <v>820.86863382</v>
       </c>
       <c r="E2" t="n">
-        <v>821.53641256</v>
+        <v>746.8328335499999</v>
       </c>
       <c r="F2" t="n">
-        <v>747.53890915</v>
+        <v>1788.01294931</v>
       </c>
       <c r="G2" t="n">
-        <v>1788.09072544</v>
+        <v>-150.05220441</v>
       </c>
       <c r="H2" t="n">
-        <v>-150.22302371</v>
+        <v>99.88912488999999</v>
       </c>
       <c r="I2" t="n">
-        <v>99.50102479999998</v>
+        <v>214.59157862</v>
       </c>
       <c r="J2" t="n">
-        <v>214.34266477</v>
+        <v>-90.01480147999997</v>
       </c>
       <c r="K2" t="n">
-        <v>-90.31634846</v>
+        <v>-899.3455663499999</v>
       </c>
       <c r="L2" t="n">
-        <v>-899.7044331999999</v>
+        <v>-250.21686655</v>
       </c>
       <c r="M2" t="n">
-        <v>-250.37099098</v>
+        <v>-608.34332303</v>
       </c>
     </row>
     <row r="3">
@@ -542,41 +542,39 @@
           <t>光電業右下</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>47.23345665999999</v>
+        <v>-67.11271887999999</v>
       </c>
       <c r="D3" t="n">
-        <v>-54.49049336</v>
+        <v>28.39300053</v>
       </c>
       <c r="E3" t="n">
-        <v>44.67072405</v>
+        <v>127.95262029</v>
       </c>
       <c r="F3" t="n">
-        <v>132.65074532</v>
+        <v>127.46112228</v>
       </c>
       <c r="G3" t="n">
-        <v>126.84044948</v>
+        <v>109.86359024</v>
       </c>
       <c r="H3" t="n">
-        <v>96.03657348999999</v>
+        <v>189.33038072</v>
       </c>
       <c r="I3" t="n">
-        <v>164.64025374</v>
+        <v>288.94924691</v>
       </c>
       <c r="J3" t="n">
-        <v>251.60276894</v>
+        <v>224.37403241</v>
       </c>
       <c r="K3" t="n">
-        <v>186.48798612</v>
+        <v>-7.05730837</v>
       </c>
       <c r="L3" t="n">
-        <v>-18.89719598</v>
+        <v>280.74061183</v>
       </c>
       <c r="M3" t="n">
-        <v>256.36204702</v>
+        <v>-3.10053024</v>
       </c>
     </row>
     <row r="4">
@@ -587,37 +585,37 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>208.28268441</v>
+        <v>-51.35355088999999</v>
       </c>
       <c r="D4" t="n">
-        <v>-66.69191041999999</v>
+        <v>-12.19953421999999</v>
       </c>
       <c r="E4" t="n">
-        <v>-31.97543567999999</v>
+        <v>-44.04936299000002</v>
       </c>
       <c r="F4" t="n">
-        <v>-53.59916159000001</v>
+        <v>-60.92103873</v>
       </c>
       <c r="G4" t="n">
-        <v>-65.27981079000001</v>
+        <v>-157.34427698</v>
       </c>
       <c r="H4" t="n">
-        <v>-145.09569795</v>
+        <v>-174.35180957</v>
       </c>
       <c r="I4" t="n">
-        <v>-143.8945201</v>
+        <v>80.52009355999999</v>
       </c>
       <c r="J4" t="n">
-        <v>119.47234483</v>
+        <v>158.8475164</v>
       </c>
       <c r="K4" t="n">
-        <v>200.95783303</v>
+        <v>-118.36346344</v>
       </c>
       <c r="L4" t="n">
-        <v>-105.42714588</v>
+        <v>93.78226703</v>
       </c>
       <c r="M4" t="n">
-        <v>120.81696595</v>
+        <v>-75.55483414</v>
       </c>
     </row>
     <row r="5">
@@ -628,37 +626,37 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>-259.63819733</v>
+        <v>-387.43622092</v>
       </c>
       <c r="D5" t="n">
-        <v>-387.43622092</v>
+        <v>-428.94029793</v>
       </c>
       <c r="E5" t="n">
-        <v>-428.94029793</v>
+        <v>-414.56281904</v>
       </c>
       <c r="F5" t="n">
-        <v>-414.56281904</v>
+        <v>-487.76732049</v>
       </c>
       <c r="G5" t="n">
-        <v>-487.76732049</v>
+        <v>-416.49802748</v>
       </c>
       <c r="H5" t="n">
-        <v>-416.49802748</v>
+        <v>-353.20717254</v>
       </c>
       <c r="I5" t="n">
-        <v>-353.20717254</v>
+        <v>-249.69010529</v>
       </c>
       <c r="J5" t="n">
-        <v>-249.69010529</v>
+        <v>-355.58396056</v>
       </c>
       <c r="K5" t="n">
-        <v>-355.58396056</v>
+        <v>-426.60047145</v>
       </c>
       <c r="L5" t="n">
-        <v>-426.60047145</v>
+        <v>-314.10521795</v>
       </c>
       <c r="M5" t="n">
-        <v>-314.10521795</v>
+        <v>246.88207098</v>
       </c>
     </row>
     <row r="6">
@@ -669,37 +667,37 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>62.05962845000001</v>
+        <v>75.94226827</v>
       </c>
       <c r="D6" t="n">
-        <v>76.3975702</v>
+        <v>71.92094846000001</v>
       </c>
       <c r="E6" t="n">
-        <v>71.53023737999999</v>
+        <v>61.76552875</v>
       </c>
       <c r="F6" t="n">
-        <v>61.95066472</v>
+        <v>151.06680152</v>
       </c>
       <c r="G6" t="n">
-        <v>149.9594836</v>
+        <v>191.83463543</v>
       </c>
       <c r="H6" t="n">
-        <v>189.86291276</v>
+        <v>29.54374092999998</v>
       </c>
       <c r="I6" t="n">
-        <v>26.54004693999999</v>
+        <v>62.14661844</v>
       </c>
       <c r="J6" t="n">
-        <v>60.85895278999999</v>
+        <v>-16.58250072999999</v>
       </c>
       <c r="K6" t="n">
-        <v>-16.84304757</v>
+        <v>-81.61058306</v>
       </c>
       <c r="L6" t="n">
-        <v>-82.56072512</v>
+        <v>21.42096801000001</v>
       </c>
       <c r="M6" t="n">
-        <v>19.95677619000001</v>
+        <v>-19.56567346</v>
       </c>
     </row>
     <row r="7">
@@ -710,37 +708,37 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1.881915599999998</v>
+        <v>-6.579360819999998</v>
       </c>
       <c r="D7" t="n">
-        <v>-7.03466275</v>
+        <v>-31.84979054</v>
       </c>
       <c r="E7" t="n">
-        <v>-31.45907946</v>
+        <v>-25.6993177</v>
       </c>
       <c r="F7" t="n">
-        <v>-25.88445367</v>
+        <v>-27.07314461</v>
       </c>
       <c r="G7" t="n">
-        <v>-25.96582669</v>
+        <v>-35.33592206</v>
       </c>
       <c r="H7" t="n">
-        <v>-33.36419939</v>
+        <v>-51.86234025</v>
       </c>
       <c r="I7" t="n">
-        <v>-48.85864626000001</v>
+        <v>-23.5702012</v>
       </c>
       <c r="J7" t="n">
-        <v>-22.28253555</v>
+        <v>-7.168440740000002</v>
       </c>
       <c r="K7" t="n">
-        <v>-6.9078939</v>
+        <v>-16.75654344</v>
       </c>
       <c r="L7" t="n">
-        <v>-15.80640138</v>
+        <v>11.13703615</v>
       </c>
       <c r="M7" t="n">
-        <v>12.60122797</v>
+        <v>23.91494567</v>
       </c>
     </row>
     <row r="8">
@@ -751,37 +749,37 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3053.41075554</v>
+        <v>3190.55753981</v>
       </c>
       <c r="D8" t="n">
-        <v>3202.52327572</v>
+        <v>3757.19848391</v>
       </c>
       <c r="E8" t="n">
-        <v>3796.87637317</v>
+        <v>810.0627740900001</v>
       </c>
       <c r="F8" t="n">
-        <v>879.33382147</v>
+        <v>2588.62153626</v>
       </c>
       <c r="G8" t="n">
-        <v>2616.39038512</v>
+        <v>2449.81326305</v>
       </c>
       <c r="H8" t="n">
-        <v>2457.47533552</v>
+        <v>2974.25713672</v>
       </c>
       <c r="I8" t="n">
-        <v>3001.08307843</v>
+        <v>2830.08852827</v>
       </c>
       <c r="J8" t="n">
-        <v>2854.80618496</v>
+        <v>-826.58338838</v>
       </c>
       <c r="K8" t="n">
-        <v>-845.5506428999998</v>
+        <v>-5224.99645793</v>
       </c>
       <c r="L8" t="n">
-        <v>-5232.96747133</v>
+        <v>-2463.53015519</v>
       </c>
       <c r="M8" t="n">
-        <v>-2468.41463208</v>
+        <v>-3607.70749756</v>
       </c>
     </row>
     <row r="9">
@@ -794,37 +792,37 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>12.50674636</v>
+        <v>-72.15499683</v>
       </c>
       <c r="D9" t="n">
-        <v>-56.48915796</v>
+        <v>-181.83829642</v>
       </c>
       <c r="E9" t="n">
-        <v>-83.07011645</v>
+        <v>-204.15006145</v>
       </c>
       <c r="F9" t="n">
-        <v>-91.20880308</v>
+        <v>-249.37394372</v>
       </c>
       <c r="G9" t="n">
-        <v>-123.59842429</v>
+        <v>-230.97140242</v>
       </c>
       <c r="H9" t="n">
-        <v>-130.50634116</v>
+        <v>-224.32334882</v>
       </c>
       <c r="I9" t="n">
-        <v>-119.54552704</v>
+        <v>-220.69860142</v>
       </c>
       <c r="J9" t="n">
-        <v>-109.75583036</v>
+        <v>-208.86674509</v>
       </c>
       <c r="K9" t="n">
-        <v>-113.58214254</v>
+        <v>-173.04271755</v>
       </c>
       <c r="L9" t="n">
-        <v>-89.98371306999999</v>
+        <v>-101.57619926</v>
       </c>
       <c r="M9" t="n">
-        <v>-26.74912995</v>
+        <v>-101.77430725</v>
       </c>
     </row>
     <row r="10">
@@ -835,37 +833,37 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>41.79643612</v>
+        <v>18.7060269</v>
       </c>
       <c r="D10" t="n">
-        <v>6.572641830000001</v>
+        <v>27.39408997</v>
       </c>
       <c r="E10" t="n">
-        <v>-11.64130752</v>
+        <v>80.44882436</v>
       </c>
       <c r="F10" t="n">
-        <v>16.40119805</v>
+        <v>14.25920796</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2232690600000042</v>
+        <v>8.08423681</v>
       </c>
       <c r="H10" t="n">
-        <v>22.12872621</v>
+        <v>76.67273951</v>
       </c>
       <c r="I10" t="n">
-        <v>58.65766656</v>
+        <v>157.10584186</v>
       </c>
       <c r="J10" t="n">
-        <v>132.67527158</v>
+        <v>16.84131357</v>
       </c>
       <c r="K10" t="n">
-        <v>32.92321401</v>
+        <v>-35.19751714</v>
       </c>
       <c r="L10" t="n">
-        <v>-31.34194308</v>
+        <v>-7.48463061</v>
       </c>
       <c r="M10" t="n">
-        <v>-5.87676717</v>
+        <v>-42.84053777</v>
       </c>
     </row>
     <row r="11">
@@ -876,37 +874,37 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>-84.49990516000001</v>
+        <v>-76.35197597000001</v>
       </c>
       <c r="D11" t="n">
-        <v>-71.27952607</v>
+        <v>-15.33443696000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-9.778319470000007</v>
+        <v>30.12201213</v>
       </c>
       <c r="F11" t="n">
-        <v>31.64017136999999</v>
+        <v>-180.83661576</v>
       </c>
       <c r="G11" t="n">
-        <v>-181.89193455</v>
+        <v>-28.02151100000001</v>
       </c>
       <c r="H11" t="n">
-        <v>-28.50699865000001</v>
+        <v>312.29508241</v>
       </c>
       <c r="I11" t="n">
-        <v>309.12090261</v>
+        <v>658.2697451700001</v>
       </c>
       <c r="J11" t="n">
-        <v>653.33942918</v>
+        <v>242.28540973</v>
       </c>
       <c r="K11" t="n">
-        <v>235.03869243</v>
+        <v>-30.65988094999998</v>
       </c>
       <c r="L11" t="n">
-        <v>-34.09932765999999</v>
+        <v>-51.47565085999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-55.97849528000001</v>
+        <v>-120.47050673</v>
       </c>
     </row>
     <row r="12">
@@ -917,37 +915,37 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>-24.1839077</v>
+        <v>360.0174231</v>
       </c>
       <c r="D12" t="n">
-        <v>360.88587043</v>
+        <v>239.49127732</v>
       </c>
       <c r="E12" t="n">
-        <v>240.79024745</v>
+        <v>173.03005152</v>
       </c>
       <c r="F12" t="n">
-        <v>174.45549045</v>
+        <v>-44.28253254</v>
       </c>
       <c r="G12" t="n">
-        <v>-44.77826097</v>
+        <v>-22.13244071</v>
       </c>
       <c r="H12" t="n">
-        <v>-24.94843443</v>
+        <v>2.708196700000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.646659229999999</v>
+        <v>58.76775105</v>
       </c>
       <c r="J12" t="n">
-        <v>48.42108592</v>
+        <v>-14.08652773</v>
       </c>
       <c r="K12" t="n">
-        <v>-29.5051251</v>
+        <v>-152.03090199</v>
       </c>
       <c r="L12" t="n">
-        <v>-158.29387524</v>
+        <v>-52.54308368</v>
       </c>
       <c r="M12" t="n">
-        <v>-58.16080901999999</v>
+        <v>-111.04547971</v>
       </c>
     </row>
     <row r="13">
@@ -958,37 +956,37 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>4.685124039999999</v>
+        <v>-2.60440101</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.545298240000001</v>
+        <v>1.46647876</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.38860886</v>
+        <v>22.81387582</v>
       </c>
       <c r="F13" t="n">
-        <v>19.87027765</v>
+        <v>43.06498594</v>
       </c>
       <c r="G13" t="n">
-        <v>44.61603315999999</v>
+        <v>21.47027572</v>
       </c>
       <c r="H13" t="n">
-        <v>24.77175709</v>
+        <v>18.5625152</v>
       </c>
       <c r="I13" t="n">
-        <v>26.09155093</v>
+        <v>25.41829362</v>
       </c>
       <c r="J13" t="n">
-        <v>40.69527474</v>
+        <v>5.85760165</v>
       </c>
       <c r="K13" t="n">
-        <v>28.52291632</v>
+        <v>-9.34380369</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3586162699999996</v>
+        <v>2.5032132</v>
       </c>
       <c r="M13" t="n">
-        <v>12.62378296</v>
+        <v>-6.25119298</v>
       </c>
     </row>
     <row r="14">
@@ -999,37 +997,37 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>5117.54882845</v>
+        <v>1789.18140469</v>
       </c>
       <c r="D14" t="n">
-        <v>1789.16172274</v>
+        <v>7301.872935879999</v>
       </c>
       <c r="E14" t="n">
-        <v>7301.843694679999</v>
+        <v>4082.49005407</v>
       </c>
       <c r="F14" t="n">
-        <v>4082.40427775</v>
+        <v>7624.440961189999</v>
       </c>
       <c r="G14" t="n">
-        <v>7624.41259415</v>
+        <v>4044.69387813</v>
       </c>
       <c r="H14" t="n">
-        <v>4044.50392003</v>
+        <v>4573.007792179999</v>
       </c>
       <c r="I14" t="n">
-        <v>4572.939547319999</v>
+        <v>1420.60736669</v>
       </c>
       <c r="J14" t="n">
-        <v>1420.59826702</v>
+        <v>734.45577874</v>
       </c>
       <c r="K14" t="n">
-        <v>734.4927191700001</v>
+        <v>-9376.891590069999</v>
       </c>
       <c r="L14" t="n">
-        <v>-9376.83330516</v>
+        <v>-2594.01769678</v>
       </c>
       <c r="M14" t="n">
-        <v>-2593.98248721</v>
+        <v>-5123.20414916</v>
       </c>
     </row>
     <row r="15">
@@ -1040,37 +1038,37 @@
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>-321.5083467700001</v>
+        <v>319.7621053700001</v>
       </c>
       <c r="D15" t="n">
-        <v>58.78316310000007</v>
+        <v>27.97302630000001</v>
       </c>
       <c r="E15" t="n">
-        <v>-503.54256198</v>
+        <v>1006.25770933</v>
       </c>
       <c r="F15" t="n">
-        <v>439.29170641</v>
+        <v>619.7335295600001</v>
       </c>
       <c r="G15" t="n">
-        <v>-39.31170931999996</v>
+        <v>872.96122283</v>
       </c>
       <c r="H15" t="n">
-        <v>625.77616114</v>
+        <v>904.94850161</v>
       </c>
       <c r="I15" t="n">
-        <v>664.08159973</v>
+        <v>421.26157337</v>
       </c>
       <c r="J15" t="n">
-        <v>172.22682514</v>
+        <v>147.32368736</v>
       </c>
       <c r="K15" t="n">
-        <v>-169.31351507</v>
+        <v>228.45976646</v>
       </c>
       <c r="L15" t="n">
-        <v>-111.95180094</v>
+        <v>579.9785662999999</v>
       </c>
       <c r="M15" t="n">
-        <v>483.0900513300001</v>
+        <v>221.0350927799999</v>
       </c>
     </row>
     <row r="16">
@@ -1081,37 +1079,37 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>-140.97029727</v>
+        <v>-446.0087902</v>
       </c>
       <c r="D16" t="n">
-        <v>-185.01016598</v>
+        <v>-505.71100257</v>
       </c>
       <c r="E16" t="n">
-        <v>25.83382691000003</v>
+        <v>-792.2176904500001</v>
       </c>
       <c r="F16" t="n">
-        <v>-225.16591121</v>
+        <v>-444.71869209</v>
       </c>
       <c r="G16" t="n">
-        <v>214.35491383</v>
+        <v>-139.22748301</v>
       </c>
       <c r="H16" t="n">
-        <v>108.14753678</v>
+        <v>-681.51453732</v>
       </c>
       <c r="I16" t="n">
-        <v>-440.57939058</v>
+        <v>29.62317507000003</v>
       </c>
       <c r="J16" t="n">
-        <v>278.6670229699999</v>
+        <v>-677.78244817</v>
       </c>
       <c r="K16" t="n">
-        <v>-361.18218617</v>
+        <v>-1035.97007376</v>
       </c>
       <c r="L16" t="n">
-        <v>-695.61679127</v>
+        <v>-762.1923946100001</v>
       </c>
       <c r="M16" t="n">
-        <v>-665.33908921</v>
+        <v>-376.79985322</v>
       </c>
     </row>
     <row r="17">
@@ -1122,37 +1120,37 @@
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
-        <v>-0.12911185</v>
+        <v>0.18345265</v>
       </c>
       <c r="D17" t="n">
-        <v>0.18345265</v>
+        <v>-0.75565477</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.75565477</v>
+        <v>-1.09301157</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.09301157</v>
+        <v>-1.25991411</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.25991411</v>
+        <v>0.42586555</v>
       </c>
       <c r="H17" t="n">
-        <v>0.42586555</v>
+        <v>1.11311752</v>
       </c>
       <c r="I17" t="n">
-        <v>1.11311752</v>
+        <v>0.08433128999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>0.08433128999999999</v>
+        <v>-0.35153504</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.35153504</v>
+        <v>-0.7377812500000001</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7377812500000001</v>
+        <v>-0.09023301</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.09023301</v>
+        <v>-1.10238635</v>
       </c>
     </row>
     <row r="18">
@@ -1163,37 +1161,37 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>-531.6617434799999</v>
+        <v>-603.5171211700001</v>
       </c>
       <c r="D18" t="n">
-        <v>-603.5171211700001</v>
+        <v>-1.170012629999998</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.170012629999998</v>
+        <v>755.74136299</v>
       </c>
       <c r="F18" t="n">
-        <v>755.74136299</v>
+        <v>808.41838966</v>
       </c>
       <c r="G18" t="n">
-        <v>808.41838966</v>
+        <v>20.05482964</v>
       </c>
       <c r="H18" t="n">
-        <v>20.05482964</v>
+        <v>397.91409635</v>
       </c>
       <c r="I18" t="n">
-        <v>397.91409635</v>
+        <v>941.82636841</v>
       </c>
       <c r="J18" t="n">
-        <v>941.82636841</v>
+        <v>-199.10421778</v>
       </c>
       <c r="K18" t="n">
-        <v>-199.10421778</v>
+        <v>-682.83194151</v>
       </c>
       <c r="L18" t="n">
-        <v>-682.83194151</v>
+        <v>76.18796667000002</v>
       </c>
       <c r="M18" t="n">
-        <v>76.18796667000002</v>
+        <v>-50.12917388</v>
       </c>
     </row>
     <row r="19">
@@ -1204,37 +1202,37 @@
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>-5.09463389</v>
+        <v>-16.04657688</v>
       </c>
       <c r="D19" t="n">
-        <v>-16.04657688</v>
+        <v>-16.7282934</v>
       </c>
       <c r="E19" t="n">
-        <v>-16.7282934</v>
+        <v>-9.796063780000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-9.796063780000001</v>
+        <v>-1.05380141</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.05380141</v>
+        <v>2.68419108</v>
       </c>
       <c r="H19" t="n">
-        <v>2.68419108</v>
+        <v>5.168692590000001</v>
       </c>
       <c r="I19" t="n">
-        <v>5.168692590000001</v>
+        <v>0.5556269400000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5556269400000001</v>
+        <v>-0.8401518099999999</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.8401518099999999</v>
+        <v>-3.47672728</v>
       </c>
       <c r="L19" t="n">
-        <v>-3.47672728</v>
+        <v>1.25178956</v>
       </c>
       <c r="M19" t="n">
-        <v>1.25178956</v>
+        <v>-1.32897545</v>
       </c>
     </row>
     <row r="20">
@@ -1245,37 +1243,37 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>39.90392790999999</v>
+        <v>-7.499015480000001</v>
       </c>
       <c r="D20" t="n">
-        <v>-7.49896809</v>
+        <v>-34.65196079</v>
       </c>
       <c r="E20" t="n">
-        <v>-34.65192705</v>
+        <v>-20.07586818</v>
       </c>
       <c r="F20" t="n">
-        <v>-20.07589765</v>
+        <v>37.03994246</v>
       </c>
       <c r="G20" t="n">
-        <v>37.03990992</v>
+        <v>61.97440654</v>
       </c>
       <c r="H20" t="n">
-        <v>61.97436829999999</v>
+        <v>4.784528130000001</v>
       </c>
       <c r="I20" t="n">
-        <v>4.78448792</v>
+        <v>-26.57971293</v>
       </c>
       <c r="J20" t="n">
-        <v>-26.5797665</v>
+        <v>-51.94192612000001</v>
       </c>
       <c r="K20" t="n">
-        <v>-51.94194045</v>
+        <v>-0.42173321</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.4217290099999998</v>
+        <v>-23.83094442</v>
       </c>
       <c r="M20" t="n">
-        <v>-23.83090088</v>
+        <v>-44.06559479000001</v>
       </c>
     </row>
     <row r="21">
@@ -1284,41 +1282,39 @@
           <t>居家生活右下</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
-        <v>1.28583045</v>
+        <v>-2.43984143</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.43984143</v>
+        <v>-7.15899586</v>
       </c>
       <c r="E21" t="n">
-        <v>-7.15899586</v>
+        <v>-1.9665216</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.9665216</v>
+        <v>-1.02758461</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.02758461</v>
+        <v>2.7858135</v>
       </c>
       <c r="H21" t="n">
-        <v>2.7858135</v>
+        <v>1.57265017</v>
       </c>
       <c r="I21" t="n">
-        <v>1.57265017</v>
+        <v>-0.11769773</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.11769773</v>
+        <v>-1.28430574</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.28430574</v>
+        <v>-3.1636393</v>
       </c>
       <c r="L21" t="n">
-        <v>-3.1636393</v>
+        <v>-3.19371817</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.19371817</v>
+        <v>-3.23149288</v>
       </c>
     </row>
     <row r="22">
@@ -1329,37 +1325,37 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>2.0682052</v>
+        <v>2.13372424</v>
       </c>
       <c r="D22" t="n">
-        <v>2.13372424</v>
+        <v>0.9927766899999999</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9927766899999999</v>
+        <v>-0.03595326999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.03595326999999999</v>
+        <v>0.96984157</v>
       </c>
       <c r="G22" t="n">
-        <v>0.96984157</v>
+        <v>1.21441183</v>
       </c>
       <c r="H22" t="n">
-        <v>1.21441183</v>
+        <v>2.1806725</v>
       </c>
       <c r="I22" t="n">
-        <v>2.1806725</v>
+        <v>0.27043521</v>
       </c>
       <c r="J22" t="n">
-        <v>0.27043521</v>
+        <v>0.97694012</v>
       </c>
       <c r="K22" t="n">
-        <v>0.97694012</v>
+        <v>-0.11805477</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.11805477</v>
+        <v>1.62020539</v>
       </c>
       <c r="M22" t="n">
-        <v>1.62020539</v>
+        <v>0.18215004</v>
       </c>
     </row>
     <row r="23">
@@ -1370,37 +1366,37 @@
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
-        <v>14.4164355</v>
+        <v>17.59080885</v>
       </c>
       <c r="D23" t="n">
-        <v>17.70036151</v>
+        <v>29.75804077</v>
       </c>
       <c r="E23" t="n">
-        <v>29.79123508</v>
+        <v>65.34066881</v>
       </c>
       <c r="F23" t="n">
-        <v>65.34342972</v>
+        <v>67.68293486</v>
       </c>
       <c r="G23" t="n">
-        <v>67.63610528999999</v>
+        <v>69.97326323</v>
       </c>
       <c r="H23" t="n">
-        <v>69.97203975999999</v>
+        <v>133.07285199</v>
       </c>
       <c r="I23" t="n">
-        <v>133.0464327</v>
+        <v>130.6029476</v>
       </c>
       <c r="J23" t="n">
-        <v>130.6413759</v>
+        <v>58.88324328</v>
       </c>
       <c r="K23" t="n">
-        <v>58.89268668</v>
+        <v>0.07820831000000045</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1293569200000017</v>
+        <v>-20.15486628</v>
       </c>
       <c r="M23" t="n">
-        <v>-20.18880538</v>
+        <v>-29.67279385</v>
       </c>
     </row>
     <row r="24">
@@ -1409,39 +1405,41 @@
           <t>建材營造右下</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
       <c r="C24" t="n">
-        <v>-19.81364729</v>
+        <v>-52.17383739</v>
       </c>
       <c r="D24" t="n">
-        <v>-42.19567303</v>
+        <v>-56.72928587000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-43.48162687</v>
+        <v>-58.07162093</v>
       </c>
       <c r="F24" t="n">
-        <v>-44.82396193</v>
+        <v>7.94755062</v>
       </c>
       <c r="G24" t="n">
-        <v>-27.54116608</v>
+        <v>15.47061347</v>
       </c>
       <c r="H24" t="n">
-        <v>5.802407629999999</v>
+        <v>30.43536418</v>
       </c>
       <c r="I24" t="n">
-        <v>28.91059504</v>
+        <v>34.01748883</v>
       </c>
       <c r="J24" t="n">
-        <v>38.83488594</v>
+        <v>20.54502436</v>
       </c>
       <c r="K24" t="n">
-        <v>27.87649351</v>
+        <v>-3.29538761</v>
       </c>
       <c r="L24" t="n">
-        <v>4.830213819999999</v>
+        <v>21.3578411</v>
       </c>
       <c r="M24" t="n">
-        <v>24.18946009</v>
+        <v>4.25500277</v>
       </c>
     </row>
     <row r="25">
@@ -1452,37 +1450,37 @@
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>28.92968096</v>
+        <v>14.67194146999999</v>
       </c>
       <c r="D25" t="n">
-        <v>5.039214669999998</v>
+        <v>16.86454862</v>
       </c>
       <c r="E25" t="n">
-        <v>3.045110259999998</v>
+        <v>13.97013735</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.5611396100000007</v>
+        <v>9.695182310000002</v>
       </c>
       <c r="G25" t="n">
-        <v>43.10616236</v>
+        <v>42.13963317</v>
       </c>
       <c r="H25" t="n">
-        <v>48.95726033</v>
+        <v>37.25146005999999</v>
       </c>
       <c r="I25" t="n">
-        <v>36.84770491</v>
+        <v>39.34517793</v>
       </c>
       <c r="J25" t="n">
-        <v>34.9128072</v>
+        <v>-19.70663816</v>
       </c>
       <c r="K25" t="n">
-        <v>-24.95374618</v>
+        <v>-91.57033662000001</v>
       </c>
       <c r="L25" t="n">
-        <v>-98.21648068</v>
+        <v>-61.19228781</v>
       </c>
       <c r="M25" t="n">
-        <v>-61.90102278</v>
+        <v>-55.51439069999999</v>
       </c>
     </row>
     <row r="26">
@@ -1493,37 +1491,37 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>7.593937100000001</v>
+        <v>3.24784478</v>
       </c>
       <c r="D26" t="n">
-        <v>5.17181729</v>
+        <v>5.521821180000001</v>
       </c>
       <c r="E26" t="n">
-        <v>7.592146520000001</v>
+        <v>16.6409802</v>
       </c>
       <c r="F26" t="n">
-        <v>18.69060947</v>
+        <v>6.06098376</v>
       </c>
       <c r="G26" t="n">
-        <v>6.72654781</v>
+        <v>6.223655750000001</v>
       </c>
       <c r="H26" t="n">
-        <v>5.82618834</v>
+        <v>7.69451413</v>
       </c>
       <c r="I26" t="n">
-        <v>6.19496605</v>
+        <v>9.40402284</v>
       </c>
       <c r="J26" t="n">
-        <v>7.53425048</v>
+        <v>3.51569178</v>
       </c>
       <c r="K26" t="n">
-        <v>1.57906642</v>
+        <v>-0.84665852</v>
       </c>
       <c r="L26" t="n">
-        <v>-2.91136613</v>
+        <v>-3.81098417</v>
       </c>
       <c r="M26" t="n">
-        <v>-5.8194749</v>
+        <v>3.2463298</v>
       </c>
     </row>
     <row r="27">
@@ -1532,41 +1530,39 @@
           <t>數位雲端右下</t>
         </is>
       </c>
-      <c r="B27" t="n">
-        <v>0</v>
-      </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>20.9692142</v>
+        <v>17.74083201</v>
       </c>
       <c r="D27" t="n">
-        <v>17.8015275</v>
+        <v>22.20219834</v>
       </c>
       <c r="E27" t="n">
-        <v>22.24719139</v>
+        <v>32.01863252</v>
       </c>
       <c r="F27" t="n">
-        <v>32.06856501</v>
+        <v>32.91413802</v>
       </c>
       <c r="G27" t="n">
-        <v>32.97035718</v>
+        <v>31.9022584</v>
       </c>
       <c r="H27" t="n">
-        <v>31.94434515</v>
+        <v>15.84968732</v>
       </c>
       <c r="I27" t="n">
-        <v>15.8825525</v>
+        <v>15.5018982</v>
       </c>
       <c r="J27" t="n">
-        <v>15.52765442</v>
+        <v>7.184865029999999</v>
       </c>
       <c r="K27" t="n">
-        <v>7.203424859999999</v>
+        <v>-2.99664855</v>
       </c>
       <c r="L27" t="n">
-        <v>-2.98286342</v>
+        <v>-0.9498302199999979</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.9376528699999984</v>
+        <v>-3.041810339999999</v>
       </c>
     </row>
     <row r="28">
@@ -1577,37 +1573,37 @@
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>-47.7503726</v>
+        <v>-77.90144052000001</v>
       </c>
       <c r="D28" t="n">
-        <v>-79.88660898000001</v>
+        <v>-107.65663972</v>
       </c>
       <c r="E28" t="n">
-        <v>-109.77231518</v>
+        <v>-100.88803439</v>
       </c>
       <c r="F28" t="n">
-        <v>-102.98757115</v>
+        <v>-89.12709667999999</v>
       </c>
       <c r="G28" t="n">
-        <v>-89.84861438999999</v>
+        <v>-74.33067953</v>
       </c>
       <c r="H28" t="n">
-        <v>-73.97514631</v>
+        <v>-60.2626942</v>
       </c>
       <c r="I28" t="n">
-        <v>-58.79575538</v>
+        <v>-34.01072538</v>
       </c>
       <c r="J28" t="n">
-        <v>-32.16641504</v>
+        <v>-31.32103029</v>
       </c>
       <c r="K28" t="n">
-        <v>-29.40265683</v>
+        <v>-34.44437976</v>
       </c>
       <c r="L28" t="n">
-        <v>-32.3931544</v>
+        <v>-6.513479540000001</v>
       </c>
       <c r="M28" t="n">
-        <v>-4.516689970000001</v>
+        <v>-9.898372780000001</v>
       </c>
     </row>
     <row r="29">
@@ -1618,37 +1614,37 @@
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>0.03323846</v>
+        <v>0.00619917</v>
       </c>
       <c r="D29" t="n">
-        <v>0.00619917</v>
+        <v>0.01277118</v>
       </c>
       <c r="E29" t="n">
-        <v>0.01277118</v>
+        <v>-0.00653676</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.00653676</v>
+        <v>-0.01623805</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.01623805</v>
+        <v>-0.01854561</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.01854561</v>
+        <v>-0.0214375</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0214375</v>
+        <v>-0.00590779</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.00590779</v>
+        <v>0.007246020000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>0.007246020000000001</v>
+        <v>0.04125581</v>
       </c>
       <c r="L29" t="n">
-        <v>0.04125581</v>
+        <v>0.01170391</v>
       </c>
       <c r="M29" t="n">
-        <v>0.01170391</v>
+        <v>0.02586367</v>
       </c>
     </row>
     <row r="30">
@@ -1659,37 +1655,37 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>0.01213361</v>
+        <v>0.0007921299999999998</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0007921299999999998</v>
+        <v>-0.00470349</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.00470349</v>
+        <v>-0.005675059999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.005675059999999999</v>
+        <v>-0.00690276</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.00690276</v>
+        <v>0.01012549</v>
       </c>
       <c r="H30" t="n">
-        <v>0.01012549</v>
+        <v>0.00217369</v>
       </c>
       <c r="I30" t="n">
-        <v>0.00217369</v>
+        <v>0.00358807</v>
       </c>
       <c r="J30" t="n">
-        <v>0.00358807</v>
+        <v>0.00154582</v>
       </c>
       <c r="K30" t="n">
-        <v>0.00154582</v>
+        <v>-0.0008311099999999996</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.0008311099999999996</v>
+        <v>0.00542619</v>
       </c>
       <c r="M30" t="n">
-        <v>0.00542619</v>
+        <v>0.007489949999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1700,37 +1696,37 @@
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>0.03921261</v>
+        <v>-0.01164912</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.01164912</v>
+        <v>-0.05282732</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.05282732</v>
+        <v>-0.09472982000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.09472982000000001</v>
+        <v>-0.18498163</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.18498163</v>
+        <v>0.003500399999999999</v>
       </c>
       <c r="H31" t="n">
-        <v>0.003500399999999999</v>
+        <v>-0.03699097</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.03699097</v>
+        <v>0.20997069</v>
       </c>
       <c r="J31" t="n">
-        <v>0.20997069</v>
+        <v>0.08271654000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0.08271654000000001</v>
+        <v>-0.01967012</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.01967012</v>
+        <v>0.08787658</v>
       </c>
       <c r="M31" t="n">
-        <v>0.08787658</v>
+        <v>-0.02011098</v>
       </c>
     </row>
     <row r="32">
@@ -1741,37 +1737,37 @@
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>-20.67803373</v>
+        <v>-32.15445803</v>
       </c>
       <c r="D32" t="n">
-        <v>-32.15445803</v>
+        <v>-40.28821612</v>
       </c>
       <c r="E32" t="n">
-        <v>-40.28821612</v>
+        <v>-16.20914258</v>
       </c>
       <c r="F32" t="n">
-        <v>-16.20914258</v>
+        <v>-19.13381427</v>
       </c>
       <c r="G32" t="n">
-        <v>-19.13381427</v>
+        <v>-10.30184885</v>
       </c>
       <c r="H32" t="n">
-        <v>-10.30184885</v>
+        <v>-13.95881996</v>
       </c>
       <c r="I32" t="n">
-        <v>-13.95881996</v>
+        <v>16.5897552</v>
       </c>
       <c r="J32" t="n">
-        <v>16.5897552</v>
+        <v>21.57479981</v>
       </c>
       <c r="K32" t="n">
-        <v>21.57479981</v>
+        <v>10.77240005</v>
       </c>
       <c r="L32" t="n">
-        <v>10.77240005</v>
+        <v>-3.99943991</v>
       </c>
       <c r="M32" t="n">
-        <v>-3.99943991</v>
+        <v>-16.35895754</v>
       </c>
     </row>
     <row r="33">
@@ -1782,37 +1778,37 @@
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
-        <v>0.4812992</v>
+        <v>-1.10311971</v>
       </c>
       <c r="D33" t="n">
-        <v>-1.10311971</v>
+        <v>-3.2016798</v>
       </c>
       <c r="E33" t="n">
-        <v>-3.2016798</v>
+        <v>-1.87034995</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.87034995</v>
+        <v>-2.31543645</v>
       </c>
       <c r="G33" t="n">
-        <v>-2.31543645</v>
+        <v>-4.02921888</v>
       </c>
       <c r="H33" t="n">
-        <v>-4.02921888</v>
+        <v>-1.65893927</v>
       </c>
       <c r="I33" t="n">
-        <v>-1.65893927</v>
+        <v>-0.68169719</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.68169719</v>
+        <v>-0.1804759</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.1804759</v>
+        <v>-1.24122729</v>
       </c>
       <c r="L33" t="n">
-        <v>-1.24122729</v>
+        <v>-0.30246939</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.30246939</v>
+        <v>-0.96733947</v>
       </c>
     </row>
     <row r="34">
@@ -1823,37 +1819,37 @@
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
-        <v>23.37416052</v>
+        <v>33.49646586</v>
       </c>
       <c r="D34" t="n">
-        <v>33.49646586</v>
+        <v>42.38292683</v>
       </c>
       <c r="E34" t="n">
-        <v>42.38292683</v>
+        <v>53.14078301</v>
       </c>
       <c r="F34" t="n">
-        <v>53.14078301</v>
+        <v>77.31264456</v>
       </c>
       <c r="G34" t="n">
-        <v>77.31264456</v>
+        <v>-99.06594910000001</v>
       </c>
       <c r="H34" t="n">
-        <v>-99.06594910000001</v>
+        <v>-137.71287059</v>
       </c>
       <c r="I34" t="n">
-        <v>-137.71287059</v>
+        <v>-36.98264507</v>
       </c>
       <c r="J34" t="n">
-        <v>-36.98264507</v>
+        <v>-110.28325571</v>
       </c>
       <c r="K34" t="n">
-        <v>-110.28325571</v>
+        <v>-29.94653585</v>
       </c>
       <c r="L34" t="n">
-        <v>-29.94653585</v>
+        <v>-75.37832121000001</v>
       </c>
       <c r="M34" t="n">
-        <v>-75.37832121000001</v>
+        <v>-140.33270771</v>
       </c>
     </row>
     <row r="35">
@@ -1864,37 +1860,37 @@
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
-        <v>-1.03027462</v>
+        <v>-0.0252352</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0252352</v>
+        <v>-0.03013220000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.03013220000000001</v>
+        <v>3.18854859</v>
       </c>
       <c r="F35" t="n">
-        <v>3.18854859</v>
+        <v>2.605460190000001</v>
       </c>
       <c r="G35" t="n">
-        <v>2.605460190000001</v>
+        <v>4.13401164</v>
       </c>
       <c r="H35" t="n">
-        <v>4.13401164</v>
+        <v>4.72190981</v>
       </c>
       <c r="I35" t="n">
-        <v>4.72190981</v>
+        <v>5.98762434</v>
       </c>
       <c r="J35" t="n">
-        <v>5.98762434</v>
+        <v>2.37916882</v>
       </c>
       <c r="K35" t="n">
-        <v>2.37916882</v>
+        <v>-0.53526386</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.53526386</v>
+        <v>2.64361891</v>
       </c>
       <c r="M35" t="n">
-        <v>2.64361891</v>
+        <v>7.38655337</v>
       </c>
     </row>
     <row r="36">
@@ -1905,37 +1901,37 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>117.94625767</v>
+        <v>227.54441106</v>
       </c>
       <c r="D36" t="n">
-        <v>217.93889327</v>
+        <v>364.58955555</v>
       </c>
       <c r="E36" t="n">
-        <v>352.4427523</v>
+        <v>215.34440896</v>
       </c>
       <c r="F36" t="n">
-        <v>204.10822595</v>
+        <v>203.11277483</v>
       </c>
       <c r="G36" t="n">
-        <v>203.78321979</v>
+        <v>-9.032017559999998</v>
       </c>
       <c r="H36" t="n">
-        <v>-5.257925969999995</v>
+        <v>184.61897931</v>
       </c>
       <c r="I36" t="n">
-        <v>182.21045032</v>
+        <v>5.011323659999997</v>
       </c>
       <c r="J36" t="n">
-        <v>0.8376441199999973</v>
+        <v>-98.44188990000001</v>
       </c>
       <c r="K36" t="n">
-        <v>-109.20080044</v>
+        <v>-118.62121267</v>
       </c>
       <c r="L36" t="n">
-        <v>-113.180397</v>
+        <v>-24.10902694</v>
       </c>
       <c r="M36" t="n">
-        <v>-28.44645008</v>
+        <v>-146.27039908</v>
       </c>
     </row>
     <row r="37">
@@ -1948,37 +1944,37 @@
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>47.02422203</v>
+        <v>-30.28023679</v>
       </c>
       <c r="D37" t="n">
-        <v>-9.668723299999998</v>
+        <v>-8.215669760000004</v>
       </c>
       <c r="E37" t="n">
-        <v>10.93613627</v>
+        <v>36.84820709</v>
       </c>
       <c r="F37" t="n">
-        <v>59.2642467</v>
+        <v>10.46549578</v>
       </c>
       <c r="G37" t="n">
-        <v>15.98931635</v>
+        <v>14.34898466</v>
       </c>
       <c r="H37" t="n">
-        <v>19.55677792</v>
+        <v>-3.351310759999999</v>
       </c>
       <c r="I37" t="n">
-        <v>2.64621305</v>
+        <v>19.3954208</v>
       </c>
       <c r="J37" t="n">
-        <v>25.57220427</v>
+        <v>-1.251609470000002</v>
       </c>
       <c r="K37" t="n">
-        <v>4.312316109999998</v>
+        <v>-64.85975591</v>
       </c>
       <c r="L37" t="n">
-        <v>-61.2942177</v>
+        <v>-21.79931408</v>
       </c>
       <c r="M37" t="n">
-        <v>-26.64410661</v>
+        <v>-47.61026725</v>
       </c>
     </row>
     <row r="38">
@@ -1989,37 +1985,37 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>-38.84033998</v>
+        <v>-24.06781791</v>
       </c>
       <c r="D38" t="n">
-        <v>-49.15742052</v>
+        <v>5.446608559999999</v>
       </c>
       <c r="E38" t="n">
-        <v>-21.66280968</v>
+        <v>31.97677294999999</v>
       </c>
       <c r="F38" t="n">
-        <v>4.321580470000002</v>
+        <v>40.54008104</v>
       </c>
       <c r="G38" t="n">
-        <v>31.95571575</v>
+        <v>-19.05366693</v>
       </c>
       <c r="H38" t="n">
-        <v>-18.81229593</v>
+        <v>-0.09933349999999831</v>
       </c>
       <c r="I38" t="n">
-        <v>8.607906160000004</v>
+        <v>-56.30677331</v>
       </c>
       <c r="J38" t="n">
-        <v>-41.90752625</v>
+        <v>-109.62729927</v>
       </c>
       <c r="K38" t="n">
-        <v>-106.27549398</v>
+        <v>-123.04542223</v>
       </c>
       <c r="L38" t="n">
-        <v>-123.81290809</v>
+        <v>-55.16890794</v>
       </c>
       <c r="M38" t="n">
-        <v>-47.08863035</v>
+        <v>-50.89618087</v>
       </c>
     </row>
     <row r="39">
@@ -2030,37 +2026,37 @@
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
-        <v>0.42597227</v>
+        <v>5.236759269999999</v>
       </c>
       <c r="D39" t="n">
-        <v>5.236759269999999</v>
+        <v>24.80576117</v>
       </c>
       <c r="E39" t="n">
-        <v>24.80576117</v>
+        <v>21.99748971</v>
       </c>
       <c r="F39" t="n">
-        <v>21.99748971</v>
+        <v>7.5667577</v>
       </c>
       <c r="G39" t="n">
-        <v>7.5667577</v>
+        <v>-0.39082327</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.39082327</v>
+        <v>6.9156605</v>
       </c>
       <c r="I39" t="n">
-        <v>6.9156605</v>
+        <v>-3.65105099</v>
       </c>
       <c r="J39" t="n">
-        <v>-3.65105099</v>
+        <v>5.96885178</v>
       </c>
       <c r="K39" t="n">
-        <v>5.96885178</v>
+        <v>-4.14332239</v>
       </c>
       <c r="L39" t="n">
-        <v>-4.14332239</v>
+        <v>-1.8353452</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.8353452</v>
+        <v>-7.62116679</v>
       </c>
     </row>
     <row r="40">
@@ -2071,37 +2067,37 @@
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>-17.85393562</v>
+        <v>-34.21927984000001</v>
       </c>
       <c r="D40" t="n">
-        <v>-34.21927984000001</v>
+        <v>-18.29832132</v>
       </c>
       <c r="E40" t="n">
-        <v>-18.29832132</v>
+        <v>16.51942199</v>
       </c>
       <c r="F40" t="n">
-        <v>16.51942199</v>
+        <v>-19.21069481</v>
       </c>
       <c r="G40" t="n">
-        <v>-19.21069481</v>
+        <v>-76.86549835</v>
       </c>
       <c r="H40" t="n">
-        <v>-76.86549835</v>
+        <v>-32.5970419</v>
       </c>
       <c r="I40" t="n">
-        <v>-32.5970419</v>
+        <v>-50.29811102</v>
       </c>
       <c r="J40" t="n">
-        <v>-50.29811102</v>
+        <v>-89.72822392</v>
       </c>
       <c r="K40" t="n">
-        <v>-89.72822392</v>
+        <v>-81.92920619</v>
       </c>
       <c r="L40" t="n">
-        <v>-81.92920619</v>
+        <v>5.598820609999998</v>
       </c>
       <c r="M40" t="n">
-        <v>5.598820609999998</v>
+        <v>45.96694628999999</v>
       </c>
     </row>
     <row r="41">
@@ -2112,37 +2108,37 @@
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
-        <v>-7.391e-05</v>
+        <v>-2.001e-05</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.001e-05</v>
+        <v>4.417e-05</v>
       </c>
       <c r="E41" t="n">
-        <v>4.417e-05</v>
+        <v>9.085e-05</v>
       </c>
       <c r="F41" t="n">
-        <v>9.085e-05</v>
+        <v>-7.104999999999999e-05</v>
       </c>
       <c r="G41" t="n">
-        <v>-7.104999999999999e-05</v>
+        <v>-0.00022371</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.00022371</v>
+        <v>-0.00012</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.00012</v>
+        <v>-0.00023445</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.00023445</v>
+        <v>-0.00035108</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.00035108</v>
+        <v>-0.00043212</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.00043212</v>
+        <v>-0.00024149</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.00024149</v>
+        <v>-0.00030939</v>
       </c>
     </row>
     <row r="42">
@@ -2153,37 +2149,37 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>-209.92976809</v>
+        <v>-24.7706204</v>
       </c>
       <c r="D42" t="n">
-        <v>-24.7706204</v>
+        <v>154.56242497</v>
       </c>
       <c r="E42" t="n">
-        <v>154.56242497</v>
+        <v>569.9204095299999</v>
       </c>
       <c r="F42" t="n">
-        <v>569.9204095299999</v>
+        <v>879.95625971</v>
       </c>
       <c r="G42" t="n">
-        <v>879.95625971</v>
+        <v>1190.48956757</v>
       </c>
       <c r="H42" t="n">
-        <v>1190.48956757</v>
+        <v>1271.44494553</v>
       </c>
       <c r="I42" t="n">
-        <v>1271.44494553</v>
+        <v>1277.79570934</v>
       </c>
       <c r="J42" t="n">
-        <v>1277.79570934</v>
+        <v>-591.18301373</v>
       </c>
       <c r="K42" t="n">
-        <v>-591.18301373</v>
+        <v>-815.56774821</v>
       </c>
       <c r="L42" t="n">
-        <v>-815.56774821</v>
+        <v>-634.0106390599999</v>
       </c>
       <c r="M42" t="n">
-        <v>-634.0106390599999</v>
+        <v>-674.41102839</v>
       </c>
     </row>
     <row r="43">
@@ -2194,37 +2190,37 @@
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
-        <v>5.039715139999999</v>
+        <v>-4.01613703</v>
       </c>
       <c r="D43" t="n">
-        <v>-4.01613703</v>
+        <v>-0.5236189</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.5236189</v>
+        <v>12.23212643</v>
       </c>
       <c r="F43" t="n">
-        <v>12.23212643</v>
+        <v>41.41266073000001</v>
       </c>
       <c r="G43" t="n">
-        <v>41.41266073000001</v>
+        <v>-2.399140199999998</v>
       </c>
       <c r="H43" t="n">
-        <v>-2.399140199999998</v>
+        <v>19.34848593</v>
       </c>
       <c r="I43" t="n">
-        <v>19.34848593</v>
+        <v>46.03279432</v>
       </c>
       <c r="J43" t="n">
-        <v>46.03279432</v>
+        <v>6.63547855</v>
       </c>
       <c r="K43" t="n">
-        <v>6.63547855</v>
+        <v>-12.07906279</v>
       </c>
       <c r="L43" t="n">
-        <v>-12.07906279</v>
+        <v>-12.14486849</v>
       </c>
       <c r="M43" t="n">
-        <v>-12.14486849</v>
+        <v>-25.39634166</v>
       </c>
     </row>
     <row r="44">
@@ -2235,37 +2231,37 @@
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>5.93654785</v>
+        <v>12.22388255</v>
       </c>
       <c r="D44" t="n">
-        <v>12.21945215</v>
+        <v>11.88497066</v>
       </c>
       <c r="E44" t="n">
-        <v>11.87844405</v>
+        <v>12.57494785</v>
       </c>
       <c r="F44" t="n">
-        <v>12.57219764</v>
+        <v>-6.547999999999999</v>
       </c>
       <c r="G44" t="n">
-        <v>-6.55060065</v>
+        <v>-20.40100123</v>
       </c>
       <c r="H44" t="n">
-        <v>-20.40168625</v>
+        <v>-26.01072253</v>
       </c>
       <c r="I44" t="n">
-        <v>-26.01189411</v>
+        <v>-20.37963784</v>
       </c>
       <c r="J44" t="n">
-        <v>-20.38139739</v>
+        <v>-8.065689990000001</v>
       </c>
       <c r="K44" t="n">
-        <v>-8.06726274</v>
+        <v>-12.98331069</v>
       </c>
       <c r="L44" t="n">
-        <v>-12.98580715</v>
+        <v>8.833986980000001</v>
       </c>
       <c r="M44" t="n">
-        <v>8.8337477</v>
+        <v>28.14835708</v>
       </c>
     </row>
     <row r="45">
@@ -2274,39 +2270,41 @@
           <t>生技醫療業右下</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
+      <c r="B45" t="n">
+        <v>0</v>
+      </c>
       <c r="C45" t="n">
-        <v>122.35161025</v>
+        <v>263.97938734</v>
       </c>
       <c r="D45" t="n">
-        <v>263.00612828</v>
+        <v>101.98625517</v>
       </c>
       <c r="E45" t="n">
-        <v>96.63844107000003</v>
+        <v>185.99572339</v>
       </c>
       <c r="F45" t="n">
-        <v>183.6373287</v>
+        <v>201.2759963</v>
       </c>
       <c r="G45" t="n">
-        <v>198.61636008</v>
+        <v>281.41953408</v>
       </c>
       <c r="H45" t="n">
-        <v>293.39242734</v>
+        <v>413.92451083</v>
       </c>
       <c r="I45" t="n">
-        <v>426.4585314</v>
+        <v>543.44303894</v>
       </c>
       <c r="J45" t="n">
-        <v>556.32993176</v>
+        <v>766.9229588500001</v>
       </c>
       <c r="K45" t="n">
-        <v>773.2708335200001</v>
+        <v>1236.46258151</v>
       </c>
       <c r="L45" t="n">
-        <v>1234.8179569</v>
+        <v>1392.33320567</v>
       </c>
       <c r="M45" t="n">
-        <v>1384.13727577</v>
+        <v>428.1873829099999</v>
       </c>
     </row>
     <row r="46">
@@ -2317,37 +2315,37 @@
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>71.93912046999999</v>
+        <v>49.74752404</v>
       </c>
       <c r="D46" t="n">
-        <v>50.59631318</v>
+        <v>-63.33927405000001</v>
       </c>
       <c r="E46" t="n">
-        <v>-59.06490656999999</v>
+        <v>73.38784379000001</v>
       </c>
       <c r="F46" t="n">
-        <v>74.20838304999999</v>
+        <v>100.95624138</v>
       </c>
       <c r="G46" t="n">
-        <v>103.6682775</v>
+        <v>258.43465667</v>
       </c>
       <c r="H46" t="n">
-        <v>247.59047259</v>
+        <v>79.3977781</v>
       </c>
       <c r="I46" t="n">
-        <v>66.88778893</v>
+        <v>-49.21388113999999</v>
       </c>
       <c r="J46" t="n">
-        <v>-62.97837505</v>
+        <v>-142.95711393</v>
       </c>
       <c r="K46" t="n">
-        <v>-148.50774134</v>
+        <v>-141.34832742</v>
       </c>
       <c r="L46" t="n">
-        <v>-140.3231491</v>
+        <v>-92.29837343</v>
       </c>
       <c r="M46" t="n">
-        <v>-83.65430592</v>
+        <v>-116.45669402</v>
       </c>
     </row>
     <row r="47">
@@ -2358,37 +2356,37 @@
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>1.12070131</v>
+        <v>0.11380938</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.37939106</v>
+        <v>-1.16393911</v>
       </c>
       <c r="E47" t="n">
-        <v>-3.99313596</v>
+        <v>3.26730915</v>
       </c>
       <c r="F47" t="n">
-        <v>2.80756889</v>
+        <v>1.63955288</v>
       </c>
       <c r="G47" t="n">
-        <v>15.48295851</v>
+        <v>0.7404075099999999</v>
       </c>
       <c r="H47" t="n">
-        <v>62.07494209</v>
+        <v>2.84180396</v>
       </c>
       <c r="I47" t="n">
-        <v>95.45295953</v>
+        <v>3.94008714</v>
       </c>
       <c r="J47" t="n">
-        <v>201.7001855</v>
+        <v>4.28278438</v>
       </c>
       <c r="K47" t="n">
-        <v>314.3157432199999</v>
+        <v>1.74077493</v>
       </c>
       <c r="L47" t="n">
-        <v>126.7761244</v>
+        <v>2.58748699</v>
       </c>
       <c r="M47" t="n">
-        <v>117.36460055</v>
+        <v>8.3743338</v>
       </c>
     </row>
     <row r="48">
@@ -2397,41 +2395,39 @@
           <t>紡織纖維右下</t>
         </is>
       </c>
-      <c r="B48" t="n">
-        <v>0</v>
-      </c>
+      <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
-        <v>-15.0385654</v>
+        <v>-100.97579443</v>
       </c>
       <c r="D48" t="n">
-        <v>-100.72078989</v>
+        <v>-162.4749122</v>
       </c>
       <c r="E48" t="n">
-        <v>-162.07263695</v>
+        <v>-138.91380902</v>
       </c>
       <c r="F48" t="n">
-        <v>-138.82763643</v>
+        <v>-65.78404603</v>
       </c>
       <c r="G48" t="n">
-        <v>-65.51920985</v>
+        <v>100.66743719</v>
       </c>
       <c r="H48" t="n">
-        <v>101.05817821</v>
+        <v>167.30677723</v>
       </c>
       <c r="I48" t="n">
-        <v>167.79735666</v>
+        <v>94.00985064999999</v>
       </c>
       <c r="J48" t="n">
-        <v>94.13843056</v>
+        <v>31.25876354</v>
       </c>
       <c r="K48" t="n">
-        <v>30.77328596000001</v>
+        <v>-9.365502470000003</v>
       </c>
       <c r="L48" t="n">
-        <v>-10.082271</v>
+        <v>71.67941374999999</v>
       </c>
       <c r="M48" t="n">
-        <v>70.38508037000001</v>
+        <v>41.2511178</v>
       </c>
     </row>
     <row r="49">
@@ -2442,37 +2438,37 @@
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>-0.002355010000000012</v>
+        <v>-0.70459123</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.21139079</v>
+        <v>-3.15058017</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.32138332</v>
+        <v>-1.09952806</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.6397877999999999</v>
+        <v>13.15768119</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.68572444</v>
+        <v>60.53367364</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.8008609400000001</v>
+        <v>92.00546668000001</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.60568889</v>
+        <v>197.59948661</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.16061175</v>
+        <v>309.54150708</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.49145176</v>
+        <v>124.47130633</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.56404314</v>
+        <v>114.35339452</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.42371904</v>
+        <v>8.715188470000001</v>
       </c>
     </row>
     <row r="50">
@@ -2483,37 +2479,37 @@
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
-        <v>51.08673258</v>
+        <v>-67.32971089999999</v>
       </c>
       <c r="D50" t="n">
-        <v>-67.32971089999999</v>
+        <v>-49.9699323</v>
       </c>
       <c r="E50" t="n">
-        <v>-49.9699323</v>
+        <v>-34.87113519</v>
       </c>
       <c r="F50" t="n">
-        <v>-34.87113519</v>
+        <v>-101.83529897</v>
       </c>
       <c r="G50" t="n">
-        <v>-101.83529897</v>
+        <v>-20.18952884999999</v>
       </c>
       <c r="H50" t="n">
-        <v>-20.18952884999999</v>
+        <v>60.03399915</v>
       </c>
       <c r="I50" t="n">
-        <v>60.03399915</v>
+        <v>46.57401195000001</v>
       </c>
       <c r="J50" t="n">
-        <v>46.57401195000001</v>
+        <v>94.33851032</v>
       </c>
       <c r="K50" t="n">
-        <v>94.33851032</v>
+        <v>-55.45684779</v>
       </c>
       <c r="L50" t="n">
-        <v>-55.45684779</v>
+        <v>95.27728619</v>
       </c>
       <c r="M50" t="n">
-        <v>95.27728619</v>
+        <v>351.9052843899999</v>
       </c>
     </row>
     <row r="51">
@@ -2524,37 +2520,37 @@
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>-16.668004</v>
+        <v>-17.31000216</v>
       </c>
       <c r="D51" t="n">
-        <v>-17.31000216</v>
+        <v>-27.00119206</v>
       </c>
       <c r="E51" t="n">
-        <v>-27.00119206</v>
+        <v>-37.85262138</v>
       </c>
       <c r="F51" t="n">
-        <v>-37.85262138</v>
+        <v>-40.22165305999999</v>
       </c>
       <c r="G51" t="n">
-        <v>-40.22165305999999</v>
+        <v>-40.80044587</v>
       </c>
       <c r="H51" t="n">
-        <v>-40.80044587</v>
+        <v>-105.72065853</v>
       </c>
       <c r="I51" t="n">
-        <v>-105.72065853</v>
+        <v>-88.20215075</v>
       </c>
       <c r="J51" t="n">
-        <v>-88.20215075</v>
+        <v>-78.58694362999999</v>
       </c>
       <c r="K51" t="n">
-        <v>-78.58694362999999</v>
+        <v>-59.1372507</v>
       </c>
       <c r="L51" t="n">
-        <v>-59.1372507</v>
+        <v>-20.76584638</v>
       </c>
       <c r="M51" t="n">
-        <v>-20.76584638</v>
+        <v>-9.088962759999999</v>
       </c>
     </row>
     <row r="52">
@@ -2565,37 +2561,37 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>10.98503399</v>
+        <v>14.36571771</v>
       </c>
       <c r="D52" t="n">
-        <v>14.36571771</v>
+        <v>-7.093245320000001</v>
       </c>
       <c r="E52" t="n">
-        <v>-7.093245320000001</v>
+        <v>3.776879930000002</v>
       </c>
       <c r="F52" t="n">
-        <v>3.776879930000002</v>
+        <v>-0.599055200000002</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.599055200000002</v>
+        <v>-25.3277558</v>
       </c>
       <c r="H52" t="n">
-        <v>-25.3277558</v>
+        <v>-25.32132348</v>
       </c>
       <c r="I52" t="n">
-        <v>-25.32132348</v>
+        <v>-2.890964619999999</v>
       </c>
       <c r="J52" t="n">
-        <v>-2.890964619999999</v>
+        <v>-8.700042229999999</v>
       </c>
       <c r="K52" t="n">
-        <v>-8.700042229999999</v>
+        <v>-18.52731013</v>
       </c>
       <c r="L52" t="n">
-        <v>-18.52731013</v>
+        <v>-1.47967556</v>
       </c>
       <c r="M52" t="n">
-        <v>-1.47967556</v>
+        <v>56.65079266999999</v>
       </c>
     </row>
     <row r="53">
@@ -2606,37 +2602,37 @@
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>202.71825148</v>
+        <v>163.15883878</v>
       </c>
       <c r="D53" t="n">
-        <v>185.63987332</v>
+        <v>424.97040094</v>
       </c>
       <c r="E53" t="n">
-        <v>413.37287971</v>
+        <v>375.5975187299999</v>
       </c>
       <c r="F53" t="n">
-        <v>382.52006728</v>
+        <v>804.5212617099999</v>
       </c>
       <c r="G53" t="n">
-        <v>788.81984295</v>
+        <v>529.58728232</v>
       </c>
       <c r="H53" t="n">
-        <v>536.01880756</v>
+        <v>628.00361006</v>
       </c>
       <c r="I53" t="n">
-        <v>663.41942352</v>
+        <v>732.3668886900001</v>
       </c>
       <c r="J53" t="n">
-        <v>832.86466129</v>
+        <v>-1.638960959999991</v>
       </c>
       <c r="K53" t="n">
-        <v>148.04517125</v>
+        <v>45.45170964999999</v>
       </c>
       <c r="L53" t="n">
-        <v>92.40368975999999</v>
+        <v>-304.19498971</v>
       </c>
       <c r="M53" t="n">
-        <v>-258.920668</v>
+        <v>-67.37860953000001</v>
       </c>
     </row>
     <row r="54">
@@ -2647,37 +2643,37 @@
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>29.98847398</v>
+        <v>28.77241789</v>
       </c>
       <c r="D54" t="n">
-        <v>32.85000479</v>
+        <v>22.60990303</v>
       </c>
       <c r="E54" t="n">
-        <v>27.25000905</v>
+        <v>54.14957485000001</v>
       </c>
       <c r="F54" t="n">
-        <v>58.22860823000001</v>
+        <v>27.17223683</v>
       </c>
       <c r="G54" t="n">
-        <v>28.42361836</v>
+        <v>25.4658437</v>
       </c>
       <c r="H54" t="n">
-        <v>27.12037651</v>
+        <v>4.33585233</v>
       </c>
       <c r="I54" t="n">
-        <v>4.33543982</v>
+        <v>3.73578347</v>
       </c>
       <c r="J54" t="n">
-        <v>4.657683560000001</v>
+        <v>-5.769233830000001</v>
       </c>
       <c r="K54" t="n">
-        <v>-6.665553060000001</v>
+        <v>-24.43199912</v>
       </c>
       <c r="L54" t="n">
-        <v>-27.49233601</v>
+        <v>-1.47052552</v>
       </c>
       <c r="M54" t="n">
-        <v>-4.76262133</v>
+        <v>-5.378304119999999</v>
       </c>
     </row>
     <row r="55">
@@ -2688,37 +2684,37 @@
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>-345.84892177</v>
+        <v>-4.354884539999996</v>
       </c>
       <c r="D55" t="n">
-        <v>231.55420764</v>
+        <v>-196.46450063</v>
       </c>
       <c r="E55" t="n">
-        <v>91.16828621000002</v>
+        <v>209.35848273</v>
       </c>
       <c r="F55" t="n">
-        <v>318.79573829</v>
+        <v>-57.53995155999999</v>
       </c>
       <c r="G55" t="n">
-        <v>-73.07478899999998</v>
+        <v>134.58193653</v>
       </c>
       <c r="H55" t="n">
-        <v>55.56343482</v>
+        <v>-16.36566422</v>
       </c>
       <c r="I55" t="n">
-        <v>-138.18657417</v>
+        <v>1.29282777999998</v>
       </c>
       <c r="J55" t="n">
-        <v>0.1445773399999785</v>
+        <v>-160.92167213</v>
       </c>
       <c r="K55" t="n">
-        <v>-394.95349135</v>
+        <v>-322.85291833</v>
       </c>
       <c r="L55" t="n">
-        <v>-531.04450994</v>
+        <v>16.64372226</v>
       </c>
       <c r="M55" t="n">
-        <v>-143.91073819</v>
+        <v>-246.85201093</v>
       </c>
     </row>
     <row r="56">
@@ -2729,37 +2725,37 @@
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>4.08089557</v>
+        <v>-9.779559470000001</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.1995485</v>
+        <v>-29.51420846</v>
       </c>
       <c r="E56" t="n">
-        <v>-12.28237295</v>
+        <v>-37.83837768</v>
       </c>
       <c r="F56" t="n">
-        <v>-2.91487422</v>
+        <v>-21.37096288</v>
       </c>
       <c r="G56" t="n">
-        <v>20.8052581</v>
+        <v>3.36146783</v>
       </c>
       <c r="H56" t="n">
-        <v>4.32875445</v>
+        <v>3.36226849</v>
       </c>
       <c r="I56" t="n">
-        <v>9.664215899999999</v>
+        <v>27.33139818</v>
       </c>
       <c r="J56" t="n">
-        <v>19.0901028</v>
+        <v>30.01617481</v>
       </c>
       <c r="K56" t="n">
-        <v>26.43894701</v>
+        <v>29.86061085</v>
       </c>
       <c r="L56" t="n">
-        <v>12.17498731</v>
+        <v>27.02228676</v>
       </c>
       <c r="M56" t="n">
-        <v>-1.17773524</v>
+        <v>32.18990925</v>
       </c>
     </row>
     <row r="57">
@@ -2770,37 +2766,37 @@
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
-        <v>-6.490226310000001</v>
+        <v>-19.63731446</v>
       </c>
       <c r="D57" t="n">
-        <v>-19.63733982</v>
+        <v>-31.28672083</v>
       </c>
       <c r="E57" t="n">
-        <v>-31.28678731</v>
+        <v>-35.82230129</v>
       </c>
       <c r="F57" t="n">
-        <v>-35.8224009</v>
+        <v>-48.83644887</v>
       </c>
       <c r="G57" t="n">
-        <v>-48.83657307</v>
+        <v>-2.96099005</v>
       </c>
       <c r="H57" t="n">
-        <v>-2.96100229</v>
+        <v>-4.132907749999999</v>
       </c>
       <c r="I57" t="n">
-        <v>-4.13295156</v>
+        <v>-6.76113141</v>
       </c>
       <c r="J57" t="n">
-        <v>-6.76115287</v>
+        <v>-11.20169948</v>
       </c>
       <c r="K57" t="n">
-        <v>-11.20171031</v>
+        <v>-1.30357813</v>
       </c>
       <c r="L57" t="n">
-        <v>-1.303506030000001</v>
+        <v>12.02094224</v>
       </c>
       <c r="M57" t="n">
-        <v>12.02103025</v>
+        <v>1.93671805</v>
       </c>
     </row>
     <row r="58">
@@ -2811,37 +2807,37 @@
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>20.38771257</v>
+        <v>-0.00318353</v>
       </c>
       <c r="D58" t="n">
-        <v>-9.583194499999999</v>
+        <v>-0.01384618</v>
       </c>
       <c r="E58" t="n">
-        <v>-17.24568169</v>
+        <v>-0.02535924</v>
       </c>
       <c r="F58" t="n">
-        <v>-34.94886270000001</v>
+        <v>-0.01054632</v>
       </c>
       <c r="G58" t="n">
-        <v>-42.1867673</v>
+        <v>-0.02853263</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.99581925</v>
+        <v>-0.03224291</v>
       </c>
       <c r="I58" t="n">
-        <v>-6.33419032</v>
+        <v>-0.02415376</v>
       </c>
       <c r="J58" t="n">
-        <v>8.21714162</v>
+        <v>-0.01781416</v>
       </c>
       <c r="K58" t="n">
-        <v>3.55941364</v>
+        <v>-0.006898679999999999</v>
       </c>
       <c r="L58" t="n">
-        <v>17.67872486</v>
+        <v>-0.00198091</v>
       </c>
       <c r="M58" t="n">
-        <v>28.19804109</v>
+        <v>0.00017943</v>
       </c>
     </row>
     <row r="59">
@@ -2852,37 +2848,37 @@
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
-        <v>0.03144128</v>
+        <v>0.01201424</v>
       </c>
       <c r="D59" t="n">
-        <v>0.01201424</v>
+        <v>0.04099756</v>
       </c>
       <c r="E59" t="n">
-        <v>0.04099756</v>
+        <v>0.02809802</v>
       </c>
       <c r="F59" t="n">
-        <v>0.02809802</v>
+        <v>0.04076989</v>
       </c>
       <c r="G59" t="n">
-        <v>0.04076989</v>
+        <v>-0.02230235</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.02230235</v>
+        <v>0.0121624</v>
       </c>
       <c r="I59" t="n">
-        <v>0.0121624</v>
+        <v>-0.02442989</v>
       </c>
       <c r="J59" t="n">
-        <v>-0.02442989</v>
+        <v>0.09452125</v>
       </c>
       <c r="K59" t="n">
-        <v>0.09452125</v>
+        <v>0.12390914</v>
       </c>
       <c r="L59" t="n">
-        <v>0.12390914</v>
+        <v>0.05750639</v>
       </c>
       <c r="M59" t="n">
-        <v>0.05750639</v>
+        <v>0.01196176</v>
       </c>
     </row>
     <row r="60">
@@ -2893,37 +2889,37 @@
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
-        <v>50.5705571</v>
+        <v>29.48116599</v>
       </c>
       <c r="D60" t="n">
-        <v>29.48116599</v>
+        <v>3.745202050000001</v>
       </c>
       <c r="E60" t="n">
-        <v>3.745202050000001</v>
+        <v>-27.11462849</v>
       </c>
       <c r="F60" t="n">
-        <v>-27.11462849</v>
+        <v>-14.54311404</v>
       </c>
       <c r="G60" t="n">
-        <v>-14.54311404</v>
+        <v>-20.20816677</v>
       </c>
       <c r="H60" t="n">
-        <v>-20.20816677</v>
+        <v>-48.84269329</v>
       </c>
       <c r="I60" t="n">
-        <v>-48.84269329</v>
+        <v>-21.3959596</v>
       </c>
       <c r="J60" t="n">
-        <v>-21.3959596</v>
+        <v>-28.9827527</v>
       </c>
       <c r="K60" t="n">
-        <v>-28.9827527</v>
+        <v>-29.74134219</v>
       </c>
       <c r="L60" t="n">
-        <v>-29.74134219</v>
+        <v>13.35674909</v>
       </c>
       <c r="M60" t="n">
-        <v>13.35674909</v>
+        <v>-5.219705279999999</v>
       </c>
     </row>
     <row r="61">
@@ -2934,37 +2930,37 @@
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
-        <v>0.05757322</v>
+        <v>0.01478623</v>
       </c>
       <c r="D61" t="n">
-        <v>0.01478623</v>
+        <v>-0.00852609</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.00852609</v>
+        <v>0.00626116</v>
       </c>
       <c r="F61" t="n">
-        <v>0.00626116</v>
+        <v>-0.007863790000000001</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.007863790000000001</v>
+        <v>0.01475482</v>
       </c>
       <c r="H61" t="n">
-        <v>0.01475482</v>
+        <v>0.05246434</v>
       </c>
       <c r="I61" t="n">
-        <v>0.05246434</v>
+        <v>-0.007224899999999999</v>
       </c>
       <c r="J61" t="n">
-        <v>-0.007224899999999999</v>
+        <v>-0.02879724</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.02879724</v>
+        <v>-0.04936808</v>
       </c>
       <c r="L61" t="n">
-        <v>-0.04936808</v>
+        <v>-0.01718104</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.01718104</v>
+        <v>-0.01882583</v>
       </c>
     </row>
     <row r="62">
@@ -2975,37 +2971,37 @@
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>56.2651835</v>
+        <v>4.496421909999995</v>
       </c>
       <c r="D62" t="n">
-        <v>4.496421909999995</v>
+        <v>16.5218095</v>
       </c>
       <c r="E62" t="n">
-        <v>16.5218095</v>
+        <v>67.27009512000001</v>
       </c>
       <c r="F62" t="n">
-        <v>67.27009512000001</v>
+        <v>-16.92938799</v>
       </c>
       <c r="G62" t="n">
-        <v>-16.92938799</v>
+        <v>-37.98414687</v>
       </c>
       <c r="H62" t="n">
-        <v>-37.98414687</v>
+        <v>-34.65845204999999</v>
       </c>
       <c r="I62" t="n">
-        <v>-34.65845204999999</v>
+        <v>-52.24809272</v>
       </c>
       <c r="J62" t="n">
-        <v>-52.24809272</v>
+        <v>-39.37894222</v>
       </c>
       <c r="K62" t="n">
-        <v>-39.37894222</v>
+        <v>-4.036571590000014</v>
       </c>
       <c r="L62" t="n">
-        <v>-4.036571590000014</v>
+        <v>175.37555294</v>
       </c>
       <c r="M62" t="n">
-        <v>175.37555294</v>
+        <v>175.90300913</v>
       </c>
     </row>
     <row r="63">
@@ -3014,39 +3010,41 @@
           <t>資訊服務業右下</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr"/>
+      <c r="B63" t="n">
+        <v>0</v>
+      </c>
       <c r="C63" t="n">
-        <v>-0.00035637</v>
+        <v>0.0077172</v>
       </c>
       <c r="D63" t="n">
-        <v>0.00206774</v>
+        <v>0.01239022</v>
       </c>
       <c r="E63" t="n">
-        <v>0.007072559999999999</v>
+        <v>0.01840041</v>
       </c>
       <c r="F63" t="n">
-        <v>0.008596049999999999</v>
+        <v>0.02224854</v>
       </c>
       <c r="G63" t="n">
-        <v>0.00958909</v>
+        <v>0.01885111</v>
       </c>
       <c r="H63" t="n">
-        <v>0.00693968</v>
+        <v>0.01559031</v>
       </c>
       <c r="I63" t="n">
-        <v>0.00426686</v>
+        <v>0.00229577</v>
       </c>
       <c r="J63" t="n">
-        <v>-0.0024533</v>
+        <v>-0.004842180000000001</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.00572523</v>
+        <v>-0.00114184</v>
       </c>
       <c r="L63" t="n">
-        <v>0.002586119999999999</v>
+        <v>0.00350196</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.0010712</v>
+        <v>-0.00508045</v>
       </c>
     </row>
     <row r="64">
@@ -3057,37 +3055,37 @@
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
-        <v>41.24898890999999</v>
+        <v>17.01477572</v>
       </c>
       <c r="D64" t="n">
-        <v>17.02169322</v>
+        <v>18.4390037</v>
       </c>
       <c r="E64" t="n">
-        <v>18.44822186</v>
+        <v>30.16394224</v>
       </c>
       <c r="F64" t="n">
-        <v>30.17584855</v>
+        <v>29.38253063</v>
       </c>
       <c r="G64" t="n">
-        <v>29.39557062</v>
+        <v>-1.380576690000001</v>
       </c>
       <c r="H64" t="n">
-        <v>-1.369384310000001</v>
+        <v>-22.5959879</v>
       </c>
       <c r="I64" t="n">
-        <v>-22.587093</v>
+        <v>-17.54958439</v>
       </c>
       <c r="J64" t="n">
-        <v>-17.54739127</v>
+        <v>-29.10349154</v>
       </c>
       <c r="K64" t="n">
-        <v>-29.1049093</v>
+        <v>-2.03398716</v>
       </c>
       <c r="L64" t="n">
-        <v>-2.03305201</v>
+        <v>22.94496679</v>
       </c>
       <c r="M64" t="n">
-        <v>22.95042967</v>
+        <v>4.16137799</v>
       </c>
     </row>
     <row r="65">
@@ -3098,37 +3096,37 @@
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
-        <v>0.00072251</v>
+        <v>-0.00025412</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.00025412</v>
+        <v>-0.00126824</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.00126824</v>
+        <v>-0.00052996</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.00052996</v>
+        <v>-4.627e-05</v>
       </c>
       <c r="G65" t="n">
-        <v>-4.627e-05</v>
+        <v>0.00012135</v>
       </c>
       <c r="H65" t="n">
-        <v>0.00012135</v>
+        <v>0.00033795</v>
       </c>
       <c r="I65" t="n">
-        <v>0.00033795</v>
+        <v>0.0007966399999999999</v>
       </c>
       <c r="J65" t="n">
-        <v>0.0007966399999999999</v>
+        <v>0.00094526</v>
       </c>
       <c r="K65" t="n">
-        <v>0.00094526</v>
+        <v>0.00174454</v>
       </c>
       <c r="L65" t="n">
-        <v>0.00174454</v>
+        <v>0.0028698</v>
       </c>
       <c r="M65" t="n">
-        <v>0.0028698</v>
+        <v>0.00067753</v>
       </c>
     </row>
     <row r="66">
@@ -3139,37 +3137,37 @@
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>-8.019e-05</v>
+        <v>-3.720999999999999e-05</v>
       </c>
       <c r="D66" t="n">
-        <v>-3.720999999999999e-05</v>
+        <v>-0.00012853</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.00012853</v>
+        <v>-0.00011783</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.00011783</v>
+        <v>-0.00038662</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.00038662</v>
+        <v>-0.00020338</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.00020338</v>
+        <v>2.062999999999999e-05</v>
       </c>
       <c r="I66" t="n">
-        <v>2.062999999999999e-05</v>
+        <v>7.988999999999998e-05</v>
       </c>
       <c r="J66" t="n">
-        <v>7.988999999999998e-05</v>
+        <v>-3.629999999999995e-06</v>
       </c>
       <c r="K66" t="n">
-        <v>-3.629999999999995e-06</v>
+        <v>0.00015752</v>
       </c>
       <c r="L66" t="n">
-        <v>0.00015752</v>
+        <v>0.00021599</v>
       </c>
       <c r="M66" t="n">
-        <v>0.00021599</v>
+        <v>0.00017486</v>
       </c>
     </row>
     <row r="67">
@@ -3180,37 +3178,37 @@
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>657.86009789</v>
+        <v>738.88523447</v>
       </c>
       <c r="D67" t="n">
-        <v>838.4339267500001</v>
+        <v>921.47562096</v>
       </c>
       <c r="E67" t="n">
-        <v>978.4677195099999</v>
+        <v>931.3788527099999</v>
       </c>
       <c r="F67" t="n">
-        <v>1089.04459757</v>
+        <v>949.17133917</v>
       </c>
       <c r="G67" t="n">
-        <v>1149.20011947</v>
+        <v>686.0715570999999</v>
       </c>
       <c r="H67" t="n">
-        <v>1101.85639988</v>
+        <v>758.0479669600001</v>
       </c>
       <c r="I67" t="n">
-        <v>1227.01135597</v>
+        <v>1593.71785287</v>
       </c>
       <c r="J67" t="n">
-        <v>1805.3234625</v>
+        <v>419.1833105</v>
       </c>
       <c r="K67" t="n">
-        <v>665.9036217</v>
+        <v>-1811.73895411</v>
       </c>
       <c r="L67" t="n">
-        <v>-1778.21192228</v>
+        <v>-1096.96861131</v>
       </c>
       <c r="M67" t="n">
-        <v>-1147.36090812</v>
+        <v>-886.4390190700001</v>
       </c>
     </row>
     <row r="68">
@@ -3219,39 +3217,41 @@
           <t>通信網路業右下</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr"/>
+      <c r="B68" t="n">
+        <v>0</v>
+      </c>
       <c r="C68" t="n">
-        <v>-97.46323704000001</v>
+        <v>-100.39485247</v>
       </c>
       <c r="D68" t="n">
-        <v>-100.39485247</v>
+        <v>-108.88161837</v>
       </c>
       <c r="E68" t="n">
-        <v>-108.88161837</v>
+        <v>-49.34560721</v>
       </c>
       <c r="F68" t="n">
-        <v>-49.34560721</v>
+        <v>-40.32005366</v>
       </c>
       <c r="G68" t="n">
-        <v>-40.32005366</v>
+        <v>-39.00891055</v>
       </c>
       <c r="H68" t="n">
-        <v>-39.00891055</v>
+        <v>-17.81442497</v>
       </c>
       <c r="I68" t="n">
-        <v>-17.81442497</v>
+        <v>5.999381360000001</v>
       </c>
       <c r="J68" t="n">
-        <v>5.999381360000001</v>
+        <v>-0.7701470400000022</v>
       </c>
       <c r="K68" t="n">
-        <v>-0.7701470400000022</v>
+        <v>-37.88870957</v>
       </c>
       <c r="L68" t="n">
-        <v>-37.88870957</v>
+        <v>-10.25846167</v>
       </c>
       <c r="M68" t="n">
-        <v>-10.25846167</v>
+        <v>-18.96851173</v>
       </c>
     </row>
     <row r="69">
@@ -3262,37 +3262,37 @@
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>-104.31144954</v>
+        <v>-69.15763332999998</v>
       </c>
       <c r="D69" t="n">
-        <v>-168.70305404</v>
+        <v>-42.37237207</v>
       </c>
       <c r="E69" t="n">
-        <v>-99.35536096</v>
+        <v>138.35960054</v>
       </c>
       <c r="F69" t="n">
-        <v>-19.30403371000001</v>
+        <v>141.94986474</v>
       </c>
       <c r="G69" t="n">
-        <v>-58.07465672999999</v>
+        <v>459.24300491</v>
       </c>
       <c r="H69" t="n">
-        <v>43.46263692</v>
+        <v>435.3790516</v>
       </c>
       <c r="I69" t="n">
-        <v>-33.58364140999999</v>
+        <v>204.74831062</v>
       </c>
       <c r="J69" t="n">
-        <v>-6.859533770000024</v>
+        <v>153.38339688</v>
       </c>
       <c r="K69" t="n">
-        <v>-93.34143649000001</v>
+        <v>-260.69525017</v>
       </c>
       <c r="L69" t="n">
-        <v>-294.22516706</v>
+        <v>-100.01273259</v>
       </c>
       <c r="M69" t="n">
-        <v>-49.62239208</v>
+        <v>-176.70412707</v>
       </c>
     </row>
     <row r="70">
@@ -3303,37 +3303,37 @@
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>-2.09694106</v>
+        <v>-1.18870531</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.18870531</v>
+        <v>0.8999840899999999</v>
       </c>
       <c r="E70" t="n">
-        <v>0.8999840899999999</v>
+        <v>-1.07992369</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.07992369</v>
+        <v>-8.13542947</v>
       </c>
       <c r="G70" t="n">
-        <v>-8.13542947</v>
+        <v>-6.112742610000001</v>
       </c>
       <c r="H70" t="n">
-        <v>-6.112742610000001</v>
+        <v>0.62737845</v>
       </c>
       <c r="I70" t="n">
-        <v>0.62737845</v>
+        <v>-1.39124728</v>
       </c>
       <c r="J70" t="n">
-        <v>-1.39124728</v>
+        <v>-3.48094111</v>
       </c>
       <c r="K70" t="n">
-        <v>-3.48094111</v>
+        <v>-5.56892512</v>
       </c>
       <c r="L70" t="n">
-        <v>-5.56892512</v>
+        <v>1.72853993</v>
       </c>
       <c r="M70" t="n">
-        <v>1.72853993</v>
+        <v>-2.4559021</v>
       </c>
     </row>
     <row r="71">
@@ -3344,37 +3344,37 @@
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
-        <v>-0.01651628</v>
+        <v>0.93115824</v>
       </c>
       <c r="D71" t="n">
-        <v>0.93115824</v>
+        <v>0.15324129</v>
       </c>
       <c r="E71" t="n">
-        <v>0.15324129</v>
+        <v>2.0141396</v>
       </c>
       <c r="F71" t="n">
-        <v>2.0141396</v>
+        <v>0.94456732</v>
       </c>
       <c r="G71" t="n">
-        <v>0.94456732</v>
+        <v>1.31059385</v>
       </c>
       <c r="H71" t="n">
-        <v>1.31059385</v>
+        <v>0.44808132</v>
       </c>
       <c r="I71" t="n">
-        <v>0.44808132</v>
+        <v>1.02481299</v>
       </c>
       <c r="J71" t="n">
-        <v>1.02481299</v>
+        <v>0.39879786</v>
       </c>
       <c r="K71" t="n">
-        <v>0.39879786</v>
+        <v>-0.4558637</v>
       </c>
       <c r="L71" t="n">
-        <v>-0.4558637</v>
+        <v>0.5983068499999999</v>
       </c>
       <c r="M71" t="n">
-        <v>0.5983068499999999</v>
+        <v>3.41007278</v>
       </c>
     </row>
     <row r="72">
@@ -3385,37 +3385,37 @@
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>20.29127258</v>
+        <v>2.34425566</v>
       </c>
       <c r="D72" t="n">
-        <v>24.00895878</v>
+        <v>11.79920674</v>
       </c>
       <c r="E72" t="n">
-        <v>34.17125779</v>
+        <v>-0.8933656799999999</v>
       </c>
       <c r="F72" t="n">
-        <v>-3.0706811</v>
+        <v>-11.91034057</v>
       </c>
       <c r="G72" t="n">
-        <v>-7.127004649999999</v>
+        <v>-6.11659849</v>
       </c>
       <c r="H72" t="n">
-        <v>-16.45539349</v>
+        <v>-1.00781589</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.46575611</v>
+        <v>-14.19481265</v>
       </c>
       <c r="J72" t="n">
-        <v>-28.70342079</v>
+        <v>-10.85873646</v>
       </c>
       <c r="K72" t="n">
-        <v>-30.10771701</v>
+        <v>-12.55970872</v>
       </c>
       <c r="L72" t="n">
-        <v>-17.75000963</v>
+        <v>-11.07626771</v>
       </c>
       <c r="M72" t="n">
-        <v>-16.20229139</v>
+        <v>-10.07216436</v>
       </c>
     </row>
     <row r="73">
@@ -3426,37 +3426,37 @@
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
-        <v>-115.31227011</v>
+        <v>-37.30362026</v>
       </c>
       <c r="D73" t="n">
-        <v>-37.30362026</v>
+        <v>-103.56392674</v>
       </c>
       <c r="E73" t="n">
-        <v>-103.56392674</v>
+        <v>-54.40137722999999</v>
       </c>
       <c r="F73" t="n">
-        <v>-54.40137722999999</v>
+        <v>-0.9121308300000042</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.9121308300000042</v>
+        <v>111.99430636</v>
       </c>
       <c r="H73" t="n">
-        <v>111.99430636</v>
+        <v>111.66897061</v>
       </c>
       <c r="I73" t="n">
-        <v>111.66897061</v>
+        <v>-3.999667890000003</v>
       </c>
       <c r="J73" t="n">
-        <v>-3.999667890000003</v>
+        <v>-119.43980218</v>
       </c>
       <c r="K73" t="n">
-        <v>-119.43980218</v>
+        <v>-105.75567652</v>
       </c>
       <c r="L73" t="n">
-        <v>-105.75567652</v>
+        <v>15.98449054</v>
       </c>
       <c r="M73" t="n">
-        <v>15.98449054</v>
+        <v>-0.3143597500000023</v>
       </c>
     </row>
     <row r="74">
@@ -3467,37 +3467,37 @@
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
-        <v>-11.21701609</v>
+        <v>-2.836418229999998</v>
       </c>
       <c r="D74" t="n">
-        <v>-24.50112135</v>
+        <v>-1.484262</v>
       </c>
       <c r="E74" t="n">
-        <v>-23.85631305</v>
+        <v>-25.95807158</v>
       </c>
       <c r="F74" t="n">
-        <v>-23.78075616</v>
+        <v>-16.01571772</v>
       </c>
       <c r="G74" t="n">
-        <v>-20.79905364</v>
+        <v>-2.69861123</v>
       </c>
       <c r="H74" t="n">
-        <v>7.640183769999999</v>
+        <v>-8.47127513</v>
       </c>
       <c r="I74" t="n">
-        <v>-8.013334910000001</v>
+        <v>-35.61319028</v>
       </c>
       <c r="J74" t="n">
-        <v>-21.10458214000001</v>
+        <v>-49.26944099</v>
       </c>
       <c r="K74" t="n">
-        <v>-30.02046044</v>
+        <v>-13.72824796</v>
       </c>
       <c r="L74" t="n">
-        <v>-8.537947050000001</v>
+        <v>6.17645051</v>
       </c>
       <c r="M74" t="n">
-        <v>11.30247419</v>
+        <v>-8.167593669999999</v>
       </c>
     </row>
     <row r="75">
@@ -3508,37 +3508,37 @@
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
-        <v>851.86550735</v>
+        <v>703.0305864300001</v>
       </c>
       <c r="D75" t="n">
-        <v>703.0305864300001</v>
+        <v>664.72535027</v>
       </c>
       <c r="E75" t="n">
-        <v>664.72535027</v>
+        <v>656.9999549300001</v>
       </c>
       <c r="F75" t="n">
-        <v>656.9999549300001</v>
+        <v>922.40805115</v>
       </c>
       <c r="G75" t="n">
-        <v>922.40805115</v>
+        <v>1352.18679415</v>
       </c>
       <c r="H75" t="n">
-        <v>1352.18679415</v>
+        <v>443.55634693</v>
       </c>
       <c r="I75" t="n">
-        <v>443.55634693</v>
+        <v>296.15320315</v>
       </c>
       <c r="J75" t="n">
-        <v>296.15320315</v>
+        <v>-274.2499456</v>
       </c>
       <c r="K75" t="n">
-        <v>-274.2499456</v>
+        <v>-985.81143814</v>
       </c>
       <c r="L75" t="n">
-        <v>-985.81143814</v>
+        <v>-778.2785946499999</v>
       </c>
       <c r="M75" t="n">
-        <v>-778.2785946499999</v>
+        <v>-1087.35782134</v>
       </c>
     </row>
     <row r="76">
@@ -3549,37 +3549,37 @@
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>-29.24538225</v>
+        <v>-204.78989644</v>
       </c>
       <c r="D76" t="n">
-        <v>-217.03758715</v>
+        <v>-366.08115125</v>
       </c>
       <c r="E76" t="n">
-        <v>-381.0536326899999</v>
+        <v>-487.8436765000001</v>
       </c>
       <c r="F76" t="n">
-        <v>-510.1900488100001</v>
+        <v>-231.09819764</v>
       </c>
       <c r="G76" t="n">
-        <v>-257.06344158</v>
+        <v>-6.482741509999999</v>
       </c>
       <c r="H76" t="n">
-        <v>-15.66310559</v>
+        <v>-64.07832381</v>
       </c>
       <c r="I76" t="n">
-        <v>-63.22544475999999</v>
+        <v>54.92950557</v>
       </c>
       <c r="J76" t="n">
-        <v>44.96276262999999</v>
+        <v>3.986776439999998</v>
       </c>
       <c r="K76" t="n">
-        <v>11.43137598</v>
+        <v>105.74435434</v>
       </c>
       <c r="L76" t="n">
-        <v>129.33146676</v>
+        <v>173.2930186</v>
       </c>
       <c r="M76" t="n">
-        <v>200.67327692</v>
+        <v>93.11041993999999</v>
       </c>
     </row>
     <row r="77">
@@ -3590,37 +3590,37 @@
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="n">
-        <v>2.699553660000002</v>
+        <v>4.28308841</v>
       </c>
       <c r="D77" t="n">
-        <v>16.53077912</v>
+        <v>43.59403532</v>
       </c>
       <c r="E77" t="n">
-        <v>58.56651676</v>
+        <v>29.20232021</v>
       </c>
       <c r="F77" t="n">
-        <v>51.54869252</v>
+        <v>37.35577211</v>
       </c>
       <c r="G77" t="n">
-        <v>63.32101605</v>
+        <v>81.95862364</v>
       </c>
       <c r="H77" t="n">
-        <v>91.13898772</v>
+        <v>50.95993046</v>
       </c>
       <c r="I77" t="n">
-        <v>50.10705141</v>
+        <v>16.85188228</v>
       </c>
       <c r="J77" t="n">
-        <v>26.81862522</v>
+        <v>-13.73904701</v>
       </c>
       <c r="K77" t="n">
-        <v>-21.18364655</v>
+        <v>-41.86073545</v>
       </c>
       <c r="L77" t="n">
-        <v>-65.44784787</v>
+        <v>-26.77418983</v>
       </c>
       <c r="M77" t="n">
-        <v>-54.15444815</v>
+        <v>-31.00716944</v>
       </c>
     </row>
     <row r="78">
@@ -3631,37 +3631,37 @@
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
-        <v>0.00119589</v>
+        <v>0.00222055</v>
       </c>
       <c r="D78" t="n">
-        <v>0.00222055</v>
+        <v>0.00226234</v>
       </c>
       <c r="E78" t="n">
-        <v>0.00226234</v>
+        <v>0.00101082</v>
       </c>
       <c r="F78" t="n">
-        <v>0.00101082</v>
+        <v>9.988e-05</v>
       </c>
       <c r="G78" t="n">
-        <v>9.988e-05</v>
+        <v>0.00032912</v>
       </c>
       <c r="H78" t="n">
-        <v>0.00032912</v>
+        <v>-0.00052438</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.00052438</v>
+        <v>-9.99e-05</v>
       </c>
       <c r="J78" t="n">
-        <v>-9.99e-05</v>
+        <v>-0.00069427</v>
       </c>
       <c r="K78" t="n">
-        <v>-0.00069427</v>
+        <v>-0.00100544</v>
       </c>
       <c r="L78" t="n">
-        <v>-0.00100544</v>
+        <v>-0.00044273</v>
       </c>
       <c r="M78" t="n">
-        <v>-0.00044273</v>
+        <v>-0.00079249</v>
       </c>
     </row>
     <row r="79">
@@ -3672,37 +3672,37 @@
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="n">
-        <v>0.00166505</v>
+        <v>0.00481058</v>
       </c>
       <c r="D79" t="n">
-        <v>0.00481058</v>
+        <v>0.00272902</v>
       </c>
       <c r="E79" t="n">
-        <v>0.00272902</v>
+        <v>9.011000000000007e-05</v>
       </c>
       <c r="F79" t="n">
-        <v>9.011000000000007e-05</v>
+        <v>0.0004795100000000002</v>
       </c>
       <c r="G79" t="n">
-        <v>0.0004795100000000002</v>
+        <v>0.00329986</v>
       </c>
       <c r="H79" t="n">
-        <v>0.00329986</v>
+        <v>0.0005099499999999999</v>
       </c>
       <c r="I79" t="n">
-        <v>0.0005099499999999999</v>
+        <v>-0.0007658099999999999</v>
       </c>
       <c r="J79" t="n">
-        <v>-0.0007658099999999999</v>
+        <v>0.0034501</v>
       </c>
       <c r="K79" t="n">
-        <v>0.0034501</v>
+        <v>0.0005688300000000001</v>
       </c>
       <c r="L79" t="n">
-        <v>0.0005688300000000001</v>
+        <v>0.00248966</v>
       </c>
       <c r="M79" t="n">
-        <v>0.00248966</v>
+        <v>0.00048036</v>
       </c>
     </row>
     <row r="80">
@@ -3713,37 +3713,37 @@
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="n">
-        <v>0.00103193</v>
+        <v>0.00057835</v>
       </c>
       <c r="D80" t="n">
-        <v>0.00057835</v>
+        <v>9.465e-05</v>
       </c>
       <c r="E80" t="n">
-        <v>9.465e-05</v>
+        <v>0.00013897</v>
       </c>
       <c r="F80" t="n">
-        <v>0.00013897</v>
+        <v>6.415e-05</v>
       </c>
       <c r="G80" t="n">
-        <v>6.415e-05</v>
+        <v>-0.00029419</v>
       </c>
       <c r="H80" t="n">
-        <v>-0.00029419</v>
+        <v>0.00019073</v>
       </c>
       <c r="I80" t="n">
-        <v>0.00019073</v>
+        <v>-2.111999999999998e-05</v>
       </c>
       <c r="J80" t="n">
-        <v>-2.111999999999998e-05</v>
+        <v>0.00040195</v>
       </c>
       <c r="K80" t="n">
-        <v>0.00040195</v>
+        <v>7.686999999999999e-05</v>
       </c>
       <c r="L80" t="n">
-        <v>7.686999999999999e-05</v>
+        <v>-0.00026166</v>
       </c>
       <c r="M80" t="n">
-        <v>-0.00026166</v>
+        <v>-0.0005340900000000001</v>
       </c>
     </row>
     <row r="81">
@@ -3754,37 +3754,37 @@
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>-10.13260721</v>
+        <v>-9.68964107</v>
       </c>
       <c r="D81" t="n">
-        <v>-9.68964107</v>
+        <v>4.868124629999999</v>
       </c>
       <c r="E81" t="n">
-        <v>4.868124629999999</v>
+        <v>12.18883922</v>
       </c>
       <c r="F81" t="n">
-        <v>12.18883922</v>
+        <v>-4.46799539</v>
       </c>
       <c r="G81" t="n">
-        <v>-4.46799539</v>
+        <v>12.58299348</v>
       </c>
       <c r="H81" t="n">
-        <v>12.58299348</v>
+        <v>17.39570309</v>
       </c>
       <c r="I81" t="n">
-        <v>17.39570309</v>
+        <v>13.14604495</v>
       </c>
       <c r="J81" t="n">
-        <v>13.14604495</v>
+        <v>10.09760665</v>
       </c>
       <c r="K81" t="n">
-        <v>10.09760665</v>
+        <v>-4.54740078</v>
       </c>
       <c r="L81" t="n">
-        <v>-4.54740078</v>
+        <v>-6.45092565</v>
       </c>
       <c r="M81" t="n">
-        <v>-6.45092565</v>
+        <v>6.51069558</v>
       </c>
     </row>
     <row r="82">
@@ -3795,37 +3795,37 @@
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
-        <v>-60.41482480999999</v>
+        <v>-27.20367006</v>
       </c>
       <c r="D82" t="n">
-        <v>-42.32554019</v>
+        <v>-6.816274809999999</v>
       </c>
       <c r="E82" t="n">
-        <v>-15.38525421</v>
+        <v>35.92285662</v>
       </c>
       <c r="F82" t="n">
-        <v>33.22418543000001</v>
+        <v>100.00606942</v>
       </c>
       <c r="G82" t="n">
-        <v>96.69647368000001</v>
+        <v>140.42826357</v>
       </c>
       <c r="H82" t="n">
-        <v>135.04251964</v>
+        <v>246.03555927</v>
       </c>
       <c r="I82" t="n">
-        <v>234.45379825</v>
+        <v>140.30381642</v>
       </c>
       <c r="J82" t="n">
-        <v>136.95814913</v>
+        <v>44.57152598</v>
       </c>
       <c r="K82" t="n">
-        <v>45.55118494</v>
+        <v>-57.69820552</v>
       </c>
       <c r="L82" t="n">
-        <v>-50.25659699000001</v>
+        <v>9.688398300000001</v>
       </c>
       <c r="M82" t="n">
-        <v>9.74345312</v>
+        <v>-54.93659078</v>
       </c>
     </row>
     <row r="83">
@@ -3836,37 +3836,37 @@
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>-171.31914347</v>
+        <v>79.56018324999999</v>
       </c>
       <c r="D83" t="n">
-        <v>94.68205338000001</v>
+        <v>-162.25687216</v>
       </c>
       <c r="E83" t="n">
-        <v>-153.68789276</v>
+        <v>-346.88230485</v>
       </c>
       <c r="F83" t="n">
-        <v>-344.18363366</v>
+        <v>-546.89053232</v>
       </c>
       <c r="G83" t="n">
-        <v>-543.5809365800001</v>
+        <v>-285.50876778</v>
       </c>
       <c r="H83" t="n">
-        <v>-280.12302385</v>
+        <v>-167.33936628</v>
       </c>
       <c r="I83" t="n">
-        <v>-155.75760526</v>
+        <v>62.30800855</v>
       </c>
       <c r="J83" t="n">
-        <v>65.65367583999999</v>
+        <v>-34.55782633</v>
       </c>
       <c r="K83" t="n">
-        <v>-35.53748529000001</v>
+        <v>-172.15245484</v>
       </c>
       <c r="L83" t="n">
-        <v>-179.59406337</v>
+        <v>-21.53416806</v>
       </c>
       <c r="M83" t="n">
-        <v>-21.58922288000001</v>
+        <v>-31.30385702</v>
       </c>
     </row>
     <row r="84">
@@ -3877,37 +3877,37 @@
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
-        <v>68.31111571000001</v>
+        <v>-15.21283794</v>
       </c>
       <c r="D84" t="n">
-        <v>-15.21283794</v>
+        <v>-17.71552102</v>
       </c>
       <c r="E84" t="n">
-        <v>-17.71552102</v>
+        <v>-64.05499739</v>
       </c>
       <c r="F84" t="n">
-        <v>-64.05499739</v>
+        <v>-108.28490628</v>
       </c>
       <c r="G84" t="n">
-        <v>-108.28490628</v>
+        <v>17.23501362</v>
       </c>
       <c r="H84" t="n">
-        <v>17.23501362</v>
+        <v>-42.91166961</v>
       </c>
       <c r="I84" t="n">
-        <v>-42.91166961</v>
+        <v>-16.22533502</v>
       </c>
       <c r="J84" t="n">
-        <v>-16.22533502</v>
+        <v>-7.978113619999998</v>
       </c>
       <c r="K84" t="n">
-        <v>-7.978113619999998</v>
+        <v>-41.15140009</v>
       </c>
       <c r="L84" t="n">
-        <v>-41.15140009</v>
+        <v>-27.68817933</v>
       </c>
       <c r="M84" t="n">
-        <v>-27.68817933</v>
+        <v>80.22766098000001</v>
       </c>
     </row>
     <row r="85">
@@ -3918,37 +3918,37 @@
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>20.68587184</v>
+        <v>50.4358599</v>
       </c>
       <c r="D85" t="n">
-        <v>50.4358599</v>
+        <v>20.67695317</v>
       </c>
       <c r="E85" t="n">
-        <v>20.67695317</v>
+        <v>39.12531966</v>
       </c>
       <c r="F85" t="n">
-        <v>39.12531966</v>
+        <v>82.69031135000002</v>
       </c>
       <c r="G85" t="n">
-        <v>82.69031135000002</v>
+        <v>154.59545891</v>
       </c>
       <c r="H85" t="n">
-        <v>154.59545891</v>
+        <v>58.71590928</v>
       </c>
       <c r="I85" t="n">
-        <v>58.71590928</v>
+        <v>121.63718761</v>
       </c>
       <c r="J85" t="n">
-        <v>121.63718761</v>
+        <v>29.61562639</v>
       </c>
       <c r="K85" t="n">
-        <v>29.61562639</v>
+        <v>-24.78285621</v>
       </c>
       <c r="L85" t="n">
-        <v>-24.78285621</v>
+        <v>2.232190660000001</v>
       </c>
       <c r="M85" t="n">
-        <v>2.232190660000001</v>
+        <v>28.4317957</v>
       </c>
     </row>
     <row r="86">
@@ -3959,37 +3959,37 @@
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
-        <v>307.99625718</v>
+        <v>127.17974363</v>
       </c>
       <c r="D86" t="n">
-        <v>127.17974363</v>
+        <v>35.51983674</v>
       </c>
       <c r="E86" t="n">
-        <v>35.51983674</v>
+        <v>-44.38674216</v>
       </c>
       <c r="F86" t="n">
-        <v>-44.38674216</v>
+        <v>-80.33944907999999</v>
       </c>
       <c r="G86" t="n">
-        <v>-80.33944907999999</v>
+        <v>17.36541503</v>
       </c>
       <c r="H86" t="n">
-        <v>17.36541503</v>
+        <v>-22.22959168</v>
       </c>
       <c r="I86" t="n">
-        <v>-22.22959168</v>
+        <v>36.66650072</v>
       </c>
       <c r="J86" t="n">
-        <v>36.66650072</v>
+        <v>-47.17463461</v>
       </c>
       <c r="K86" t="n">
-        <v>-47.17463461</v>
+        <v>-72.74271278000001</v>
       </c>
       <c r="L86" t="n">
-        <v>-72.74271278000001</v>
+        <v>-28.99937651</v>
       </c>
       <c r="M86" t="n">
-        <v>-28.99937651</v>
+        <v>183.09498563</v>
       </c>
     </row>
     <row r="87">
@@ -4000,37 +4000,37 @@
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>-73.51635168999999</v>
+        <v>-120.38566029</v>
       </c>
       <c r="D87" t="n">
-        <v>-120.3851038</v>
+        <v>-28.81164552</v>
       </c>
       <c r="E87" t="n">
-        <v>-28.81111416</v>
+        <v>26.43296405</v>
       </c>
       <c r="F87" t="n">
-        <v>26.43414951</v>
+        <v>-19.93985403</v>
       </c>
       <c r="G87" t="n">
-        <v>-19.93885504</v>
+        <v>-44.01196087</v>
       </c>
       <c r="H87" t="n">
-        <v>-44.01148098</v>
+        <v>-47.8348988</v>
       </c>
       <c r="I87" t="n">
-        <v>-47.83444747999999</v>
+        <v>-49.88927837</v>
       </c>
       <c r="J87" t="n">
-        <v>-49.88869408</v>
+        <v>-54.40417066000001</v>
       </c>
       <c r="K87" t="n">
-        <v>-54.40387915000001</v>
+        <v>-32.8497037</v>
       </c>
       <c r="L87" t="n">
-        <v>-32.84970408</v>
+        <v>-6.345934729999999</v>
       </c>
       <c r="M87" t="n">
-        <v>-6.346303820000002</v>
+        <v>-1.639802489999999</v>
       </c>
     </row>
     <row r="88">
@@ -4041,37 +4041,37 @@
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
-        <v>16.93232156</v>
+        <v>-68.99436043</v>
       </c>
       <c r="D88" t="n">
-        <v>-67.92127349</v>
+        <v>-152.61663408</v>
       </c>
       <c r="E88" t="n">
-        <v>-169.60221825</v>
+        <v>-178.63626288</v>
       </c>
       <c r="F88" t="n">
-        <v>-200.60278138</v>
+        <v>-166.39774649</v>
       </c>
       <c r="G88" t="n">
-        <v>-165.28038545</v>
+        <v>-126.75647098</v>
       </c>
       <c r="H88" t="n">
-        <v>-136.35649575</v>
+        <v>-109.66933011</v>
       </c>
       <c r="I88" t="n">
-        <v>-127.41548752</v>
+        <v>-91.38142356</v>
       </c>
       <c r="J88" t="n">
-        <v>-99.86377270999999</v>
+        <v>-87.53869095</v>
       </c>
       <c r="K88" t="n">
-        <v>-99.33268954</v>
+        <v>-90.77649375</v>
       </c>
       <c r="L88" t="n">
-        <v>-107.43049933</v>
+        <v>-6.19971842</v>
       </c>
       <c r="M88" t="n">
-        <v>-13.84931573</v>
+        <v>-2.30105065</v>
       </c>
     </row>
     <row r="89">
@@ -4082,37 +4082,37 @@
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>44.64793619</v>
+        <v>2.532449130000001</v>
       </c>
       <c r="D89" t="n">
-        <v>1.458805700000001</v>
+        <v>-23.35205834</v>
       </c>
       <c r="E89" t="n">
-        <v>-6.36700553</v>
+        <v>-0.6408365900000008</v>
       </c>
       <c r="F89" t="n">
-        <v>21.32449645</v>
+        <v>-22.32311579</v>
       </c>
       <c r="G89" t="n">
-        <v>-23.44147582</v>
+        <v>-42.82221791</v>
       </c>
       <c r="H89" t="n">
-        <v>-33.22267303</v>
+        <v>-35.3471192</v>
       </c>
       <c r="I89" t="n">
-        <v>-17.60141311</v>
+        <v>-4.157563660000003</v>
       </c>
       <c r="J89" t="n">
-        <v>4.3242012</v>
+        <v>20.96484646</v>
       </c>
       <c r="K89" t="n">
-        <v>32.75855354</v>
+        <v>-26.68192823</v>
       </c>
       <c r="L89" t="n">
-        <v>-10.02792227</v>
+        <v>0.2743833299999991</v>
       </c>
       <c r="M89" t="n">
-        <v>7.924349729999999</v>
+        <v>-1.53777041</v>
       </c>
     </row>
     <row r="90">
@@ -4123,37 +4123,37 @@
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>799.1942517</v>
+        <v>3437.1076367</v>
       </c>
       <c r="D90" t="n">
-        <v>3442.96219592</v>
+        <v>5003.764407600001</v>
       </c>
       <c r="E90" t="n">
-        <v>5014.323862409999</v>
+        <v>4906.96545566</v>
       </c>
       <c r="F90" t="n">
-        <v>4925.21886095</v>
+        <v>5010.823842260001</v>
       </c>
       <c r="G90" t="n">
-        <v>5037.87784865</v>
+        <v>4978.2651254</v>
       </c>
       <c r="H90" t="n">
-        <v>4989.59937478</v>
+        <v>3566.80830261</v>
       </c>
       <c r="I90" t="n">
-        <v>3565.94765664</v>
+        <v>5064.9559481</v>
       </c>
       <c r="J90" t="n">
-        <v>5065.49505683</v>
+        <v>-157.8201205099999</v>
       </c>
       <c r="K90" t="n">
-        <v>-165.23339115</v>
+        <v>-7292.96027817</v>
       </c>
       <c r="L90" t="n">
-        <v>-7286.71586753</v>
+        <v>-1993.57493408</v>
       </c>
       <c r="M90" t="n">
-        <v>-2012.07423383</v>
+        <v>-1804.29618513</v>
       </c>
     </row>
     <row r="91">
@@ -4164,37 +4164,37 @@
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>-496.29692916</v>
+        <v>-377.24334702</v>
       </c>
       <c r="D91" t="n">
-        <v>-386.03117314</v>
+        <v>-0.1189399000000008</v>
       </c>
       <c r="E91" t="n">
-        <v>-28.98295736</v>
+        <v>-339.12723307</v>
       </c>
       <c r="F91" t="n">
-        <v>-376.07515394</v>
+        <v>-800.1076148299999</v>
       </c>
       <c r="G91" t="n">
-        <v>-804.22655073</v>
+        <v>-1014.25226514</v>
       </c>
       <c r="H91" t="n">
-        <v>-1021.47958938</v>
+        <v>-1121.53466632</v>
       </c>
       <c r="I91" t="n">
-        <v>-1118.85660026</v>
+        <v>-237.92571143</v>
       </c>
       <c r="J91" t="n">
-        <v>-228.90670528</v>
+        <v>-627.0042389600001</v>
       </c>
       <c r="K91" t="n">
-        <v>-614.17846718</v>
+        <v>-962.2922248199999</v>
       </c>
       <c r="L91" t="n">
-        <v>-943.0657091999999</v>
+        <v>-926.08295719</v>
       </c>
       <c r="M91" t="n">
-        <v>-922.04330622</v>
+        <v>-606.1103015699999</v>
       </c>
     </row>
     <row r="92">
@@ -4205,37 +4205,37 @@
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>-484.4882497</v>
+        <v>-506.7184730000001</v>
       </c>
       <c r="D92" t="n">
-        <v>-503.7852061</v>
+        <v>-290.0204477</v>
       </c>
       <c r="E92" t="n">
-        <v>-271.71588505</v>
+        <v>-597.93750475</v>
       </c>
       <c r="F92" t="n">
-        <v>-579.24298917</v>
+        <v>-781.38963261</v>
       </c>
       <c r="G92" t="n">
-        <v>-804.3247031000001</v>
+        <v>-1004.37468099</v>
       </c>
       <c r="H92" t="n">
-        <v>-1008.48160613</v>
+        <v>-997.9899978200001</v>
       </c>
       <c r="I92" t="n">
-        <v>-999.8074179099999</v>
+        <v>-250.64928035</v>
       </c>
       <c r="J92" t="n">
-        <v>-260.20739523</v>
+        <v>-632.39691376</v>
       </c>
       <c r="K92" t="n">
-        <v>-637.8094149</v>
+        <v>-839.82501909</v>
       </c>
       <c r="L92" t="n">
-        <v>-865.29594535</v>
+        <v>-282.89371407</v>
       </c>
       <c r="M92" t="n">
-        <v>-268.43406529</v>
+        <v>112.59140298</v>
       </c>
     </row>
     <row r="93">
@@ -4246,37 +4246,37 @@
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>806.5163776000001</v>
+        <v>-136.1838183</v>
       </c>
       <c r="D93" t="n">
-        <v>-167.88800253</v>
+        <v>27.32669066999999</v>
       </c>
       <c r="E93" t="n">
-        <v>-11.75632670000002</v>
+        <v>-1166.72366356</v>
       </c>
       <c r="F93" t="n">
-        <v>-1172.87813522</v>
+        <v>-134.7618539499999</v>
       </c>
       <c r="G93" t="n">
-        <v>-35.76061781999991</v>
+        <v>-348.45785955</v>
       </c>
       <c r="H93" t="n">
-        <v>-127.70024637</v>
+        <v>-562.59891296</v>
       </c>
       <c r="I93" t="n">
-        <v>-456.2485559</v>
+        <v>388.9696313000001</v>
       </c>
       <c r="J93" t="n">
-        <v>512.9479078700001</v>
+        <v>-551.4057077799999</v>
       </c>
       <c r="K93" t="n">
-        <v>-504.77735899</v>
+        <v>-1249.21055614</v>
       </c>
       <c r="L93" t="n">
-        <v>-1267.46309763</v>
+        <v>-158.11036754</v>
       </c>
       <c r="M93" t="n">
-        <v>-148.71845313</v>
+        <v>585.74591515</v>
       </c>
     </row>
     <row r="94">
@@ -4285,39 +4285,41 @@
           <t>電機機械右下</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr"/>
+      <c r="B94" t="n">
+        <v>0</v>
+      </c>
       <c r="C94" t="n">
-        <v>6.201367509999998</v>
+        <v>97.14610656000001</v>
       </c>
       <c r="D94" t="n">
-        <v>97.14644838000001</v>
+        <v>65.14342585000001</v>
       </c>
       <c r="E94" t="n">
-        <v>65.14312098000001</v>
+        <v>-20.06649955</v>
       </c>
       <c r="F94" t="n">
-        <v>-20.06739709</v>
+        <v>-141.52683754</v>
       </c>
       <c r="G94" t="n">
-        <v>-141.52816051</v>
+        <v>-80.82072712999999</v>
       </c>
       <c r="H94" t="n">
-        <v>-80.82108114000002</v>
+        <v>4.55290634</v>
       </c>
       <c r="I94" t="n">
-        <v>4.553131289999999</v>
+        <v>157.2409152</v>
       </c>
       <c r="J94" t="n">
-        <v>157.24166445</v>
+        <v>-5.070559200000001</v>
       </c>
       <c r="K94" t="n">
-        <v>-5.068415730000001</v>
+        <v>-120.0217427</v>
       </c>
       <c r="L94" t="n">
-        <v>-120.02159172</v>
+        <v>23.66297122</v>
       </c>
       <c r="M94" t="n">
-        <v>23.6635599</v>
+        <v>73.77609545</v>
       </c>
     </row>
     <row r="95">
@@ -4328,37 +4330,37 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>199.25856102</v>
+        <v>95.25114665000001</v>
       </c>
       <c r="D95" t="n">
-        <v>116.38911003</v>
+        <v>46.33083919</v>
       </c>
       <c r="E95" t="n">
-        <v>44.33242202</v>
+        <v>104.84364026</v>
       </c>
       <c r="F95" t="n">
-        <v>105.36363897</v>
+        <v>125.99662354</v>
       </c>
       <c r="G95" t="n">
-        <v>109.32101165</v>
+        <v>188.72893597</v>
       </c>
       <c r="H95" t="n">
-        <v>164.16715655</v>
+        <v>253.03523157</v>
       </c>
       <c r="I95" t="n">
-        <v>223.01233417</v>
+        <v>144.4213577</v>
       </c>
       <c r="J95" t="n">
-        <v>144.92578538</v>
+        <v>149.18000524</v>
       </c>
       <c r="K95" t="n">
-        <v>101.74771951</v>
+        <v>-40.54632524</v>
       </c>
       <c r="L95" t="n">
-        <v>-89.03411908</v>
+        <v>-0.6189107100000008</v>
       </c>
       <c r="M95" t="n">
-        <v>-25.87040719</v>
+        <v>-70.00695528</v>
       </c>
     </row>
     <row r="96">
@@ -4369,37 +4371,37 @@
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>1362.63545905</v>
+        <v>1949.37727356</v>
       </c>
       <c r="D96" t="n">
-        <v>2059.87154895</v>
+        <v>1833.67778779</v>
       </c>
       <c r="E96" t="n">
-        <v>1916.12359133</v>
+        <v>713.9447243099999</v>
       </c>
       <c r="F96" t="n">
-        <v>788.4595847899999</v>
+        <v>-27.01846356999978</v>
       </c>
       <c r="G96" t="n">
-        <v>-4.285213879999727</v>
+        <v>-311.7008039900001</v>
       </c>
       <c r="H96" t="n">
-        <v>-297.7012908</v>
+        <v>330.2456217000001</v>
       </c>
       <c r="I96" t="n">
-        <v>327.4414372199998</v>
+        <v>58.89255754999999</v>
       </c>
       <c r="J96" t="n">
-        <v>69.97099040000006</v>
+        <v>-1052.89750497</v>
       </c>
       <c r="K96" t="n">
-        <v>-1075.39165907</v>
+        <v>-4051.10333506</v>
       </c>
       <c r="L96" t="n">
-        <v>-4092.80492937</v>
+        <v>-1316.24999344</v>
       </c>
       <c r="M96" t="n">
-        <v>-1317.53712474</v>
+        <v>-2562.04027985</v>
       </c>
     </row>
     <row r="97">
@@ -4410,37 +4412,37 @@
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>7.600439939999993</v>
+        <v>-390.66800273</v>
       </c>
       <c r="D97" t="n">
-        <v>-390.66759332</v>
+        <v>-572.8410040900001</v>
       </c>
       <c r="E97" t="n">
-        <v>-572.8400540499999</v>
+        <v>-662.76767952</v>
       </c>
       <c r="F97" t="n">
-        <v>-662.7678312099999</v>
+        <v>-743.89748664</v>
       </c>
       <c r="G97" t="n">
-        <v>-743.8964670800001</v>
+        <v>-758.00109288</v>
       </c>
       <c r="H97" t="n">
-        <v>-758.00109663</v>
+        <v>-582.72498698</v>
       </c>
       <c r="I97" t="n">
-        <v>-582.72918838</v>
+        <v>-492.98747729</v>
       </c>
       <c r="J97" t="n">
-        <v>-492.98203666</v>
+        <v>-394.5598874</v>
       </c>
       <c r="K97" t="n">
-        <v>-394.55857577</v>
+        <v>-450.82742394</v>
       </c>
       <c r="L97" t="n">
-        <v>-450.82362474</v>
+        <v>-195.19992286</v>
       </c>
       <c r="M97" t="n">
-        <v>-195.19934005</v>
+        <v>-103.30729146</v>
       </c>
     </row>
     <row r="98">
@@ -4451,37 +4453,37 @@
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
-        <v>1281.30007351</v>
+        <v>1536.70366566</v>
       </c>
       <c r="D98" t="n">
-        <v>1426.20898086</v>
+        <v>1218.6428156</v>
       </c>
       <c r="E98" t="n">
-        <v>1136.19606202</v>
+        <v>-314.7243752599999</v>
       </c>
       <c r="F98" t="n">
-        <v>-389.23908405</v>
+        <v>-3281.55806913</v>
       </c>
       <c r="G98" t="n">
-        <v>-3304.29233838</v>
+        <v>-3548.27561396</v>
       </c>
       <c r="H98" t="n">
-        <v>-3562.2751234</v>
+        <v>-3621.3521157</v>
       </c>
       <c r="I98" t="n">
-        <v>-3618.54372982</v>
+        <v>-3240.785810939999</v>
       </c>
       <c r="J98" t="n">
-        <v>-3251.86968442</v>
+        <v>-2688.02548525</v>
       </c>
       <c r="K98" t="n">
-        <v>-2665.53264278</v>
+        <v>-2960.16818202</v>
       </c>
       <c r="L98" t="n">
-        <v>-2918.47038691</v>
+        <v>-2660.80372069</v>
       </c>
       <c r="M98" t="n">
-        <v>-2659.5171722</v>
+        <v>-1809.89391656</v>
       </c>
     </row>
     <row r="99">
@@ -4492,37 +4494,37 @@
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>21.4617507</v>
+        <v>2.43043327</v>
       </c>
       <c r="D99" t="n">
-        <v>2.43043327</v>
+        <v>3.42453723</v>
       </c>
       <c r="E99" t="n">
-        <v>3.42453723</v>
+        <v>20.0696195</v>
       </c>
       <c r="F99" t="n">
-        <v>20.0696195</v>
+        <v>29.27378089</v>
       </c>
       <c r="G99" t="n">
-        <v>29.27378089</v>
+        <v>17.24417347</v>
       </c>
       <c r="H99" t="n">
-        <v>17.24417347</v>
+        <v>24.68333282</v>
       </c>
       <c r="I99" t="n">
-        <v>24.68333282</v>
+        <v>34.23585004</v>
       </c>
       <c r="J99" t="n">
-        <v>34.23585004</v>
+        <v>36.69660673999999</v>
       </c>
       <c r="K99" t="n">
-        <v>36.69660673999999</v>
+        <v>25.24661327</v>
       </c>
       <c r="L99" t="n">
-        <v>25.24661327</v>
+        <v>13.11654365</v>
       </c>
       <c r="M99" t="n">
-        <v>13.11654365</v>
+        <v>-6.82524702</v>
       </c>
     </row>
     <row r="100">
@@ -4533,37 +4535,37 @@
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="n">
-        <v>6.075689359999999</v>
+        <v>-1.47041395</v>
       </c>
       <c r="D100" t="n">
-        <v>-1.47053638</v>
+        <v>-12.68523507</v>
       </c>
       <c r="E100" t="n">
-        <v>-12.68556489</v>
+        <v>-16.25005949</v>
       </c>
       <c r="F100" t="n">
-        <v>-16.25043143</v>
+        <v>-10.87937043</v>
       </c>
       <c r="G100" t="n">
-        <v>-10.87959711</v>
+        <v>4.36138133</v>
       </c>
       <c r="H100" t="n">
-        <v>4.361278050000001</v>
+        <v>2.550761389999999</v>
       </c>
       <c r="I100" t="n">
-        <v>2.550610799999999</v>
+        <v>5.33204738</v>
       </c>
       <c r="J100" t="n">
-        <v>5.331896309999999</v>
+        <v>7.818490239999999</v>
       </c>
       <c r="K100" t="n">
-        <v>7.818366909999999</v>
+        <v>-4.54547223</v>
       </c>
       <c r="L100" t="n">
-        <v>-4.54547083</v>
+        <v>7.6226877</v>
       </c>
       <c r="M100" t="n">
-        <v>7.62272642</v>
+        <v>6.635682029999999</v>
       </c>
     </row>
     <row r="101">
@@ -4574,37 +4576,37 @@
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
-        <v>-157.36489955</v>
+        <v>-218.54624147</v>
       </c>
       <c r="D101" t="n">
-        <v>-218.54624147</v>
+        <v>-239.31343198</v>
       </c>
       <c r="E101" t="n">
-        <v>-239.31343198</v>
+        <v>-229.82111553</v>
       </c>
       <c r="F101" t="n">
-        <v>-229.82111553</v>
+        <v>-223.33650541</v>
       </c>
       <c r="G101" t="n">
-        <v>-223.33650541</v>
+        <v>-73.25820245</v>
       </c>
       <c r="H101" t="n">
-        <v>-73.25820245</v>
+        <v>16.35519561</v>
       </c>
       <c r="I101" t="n">
-        <v>16.35519561</v>
+        <v>-17.97346777</v>
       </c>
       <c r="J101" t="n">
-        <v>-17.97346777</v>
+        <v>-34.65812325</v>
       </c>
       <c r="K101" t="n">
-        <v>-34.65812325</v>
+        <v>-47.58972109</v>
       </c>
       <c r="L101" t="n">
-        <v>-47.58972109</v>
+        <v>62.04757827</v>
       </c>
       <c r="M101" t="n">
-        <v>62.04757827</v>
+        <v>17.0858512</v>
       </c>
     </row>
   </sheetData>

--- a/Result/analyze_2.xlsx
+++ b/Result/analyze_2.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-25</t>
         </is>
       </c>
     </row>
@@ -503,37 +503,37 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>726.59775904</v>
+        <v>797.9680631</v>
       </c>
       <c r="D2" t="n">
-        <v>820.86863382</v>
+        <v>756.5434718099999</v>
       </c>
       <c r="E2" t="n">
-        <v>746.8328335499999</v>
+        <v>1795.35936574</v>
       </c>
       <c r="F2" t="n">
-        <v>1788.01294931</v>
+        <v>-149.20933828</v>
       </c>
       <c r="G2" t="n">
-        <v>-150.05220441</v>
+        <v>97.92280796</v>
       </c>
       <c r="H2" t="n">
-        <v>99.88912488999999</v>
+        <v>222.53991865</v>
       </c>
       <c r="I2" t="n">
-        <v>214.59157862</v>
+        <v>-93.61492202999999</v>
       </c>
       <c r="J2" t="n">
-        <v>-90.01480147999997</v>
+        <v>-894.43254129</v>
       </c>
       <c r="K2" t="n">
-        <v>-899.3455663499999</v>
+        <v>-234.40686299</v>
       </c>
       <c r="L2" t="n">
-        <v>-250.21686655</v>
+        <v>-620.9509553400001</v>
       </c>
       <c r="M2" t="n">
-        <v>-608.34332303</v>
+        <v>552.3066825500001</v>
       </c>
     </row>
     <row r="3">
@@ -544,37 +544,37 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>-67.11271887999999</v>
+        <v>32.44665509</v>
       </c>
       <c r="D3" t="n">
-        <v>28.39300053</v>
+        <v>126.68079483</v>
       </c>
       <c r="E3" t="n">
-        <v>127.95262029</v>
+        <v>127.30804794</v>
       </c>
       <c r="F3" t="n">
-        <v>127.46112228</v>
+        <v>106.12652779</v>
       </c>
       <c r="G3" t="n">
-        <v>109.86359024</v>
+        <v>194.37430686</v>
       </c>
       <c r="H3" t="n">
-        <v>189.33038072</v>
+        <v>285.69424378</v>
       </c>
       <c r="I3" t="n">
-        <v>288.94924691</v>
+        <v>221.28333162</v>
       </c>
       <c r="J3" t="n">
-        <v>224.37403241</v>
+        <v>-8.367861130000001</v>
       </c>
       <c r="K3" t="n">
-        <v>-7.05730837</v>
+        <v>278.79872496</v>
       </c>
       <c r="L3" t="n">
-        <v>280.74061183</v>
+        <v>-8.181877210000003</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.10053024</v>
+        <v>64.78335676</v>
       </c>
     </row>
     <row r="4">
@@ -585,37 +585,37 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>-51.35355088999999</v>
+        <v>3.834606890000008</v>
       </c>
       <c r="D4" t="n">
-        <v>-12.19953421999999</v>
+        <v>-56.59616733000001</v>
       </c>
       <c r="E4" t="n">
-        <v>-44.04936299000002</v>
+        <v>-72.94745936000001</v>
       </c>
       <c r="F4" t="n">
-        <v>-60.92103873</v>
+        <v>-156.15998314</v>
       </c>
       <c r="G4" t="n">
-        <v>-157.34427698</v>
+        <v>-172.03063363</v>
       </c>
       <c r="H4" t="n">
-        <v>-174.35180957</v>
+        <v>77.19033728999999</v>
       </c>
       <c r="I4" t="n">
-        <v>80.52009355999999</v>
+        <v>169.48177125</v>
       </c>
       <c r="J4" t="n">
-        <v>158.8475164</v>
+        <v>-121.17329731</v>
       </c>
       <c r="K4" t="n">
-        <v>-118.36346344</v>
+        <v>82.40051088</v>
       </c>
       <c r="L4" t="n">
-        <v>93.78226703</v>
+        <v>-61.24672998</v>
       </c>
       <c r="M4" t="n">
-        <v>-75.55483414</v>
+        <v>80.31131538</v>
       </c>
     </row>
     <row r="5">
@@ -626,37 +626,37 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>-387.43622092</v>
+        <v>-428.94029793</v>
       </c>
       <c r="D5" t="n">
-        <v>-428.94029793</v>
+        <v>-414.56281904</v>
       </c>
       <c r="E5" t="n">
-        <v>-414.56281904</v>
+        <v>-487.76732049</v>
       </c>
       <c r="F5" t="n">
-        <v>-487.76732049</v>
+        <v>-416.49802748</v>
       </c>
       <c r="G5" t="n">
-        <v>-416.49802748</v>
+        <v>-353.20717254</v>
       </c>
       <c r="H5" t="n">
-        <v>-353.20717254</v>
+        <v>-249.69010529</v>
       </c>
       <c r="I5" t="n">
-        <v>-249.69010529</v>
+        <v>-355.58396056</v>
       </c>
       <c r="J5" t="n">
-        <v>-355.58396056</v>
+        <v>-426.60047145</v>
       </c>
       <c r="K5" t="n">
-        <v>-426.60047145</v>
+        <v>-314.10521795</v>
       </c>
       <c r="L5" t="n">
-        <v>-314.10521795</v>
+        <v>246.88207098</v>
       </c>
       <c r="M5" t="n">
-        <v>246.88207098</v>
+        <v>389.30943271</v>
       </c>
     </row>
     <row r="6">
@@ -665,39 +665,41 @@
           <t>其他右下</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
       <c r="C6" t="n">
-        <v>75.94226827</v>
+        <v>71.53026682000001</v>
       </c>
       <c r="D6" t="n">
-        <v>71.92094846000001</v>
+        <v>61.95069416</v>
       </c>
       <c r="E6" t="n">
-        <v>61.76552875</v>
+        <v>149.95948194</v>
       </c>
       <c r="F6" t="n">
-        <v>151.06680152</v>
+        <v>189.86291641</v>
       </c>
       <c r="G6" t="n">
-        <v>191.83463543</v>
+        <v>26.54005540999999</v>
       </c>
       <c r="H6" t="n">
-        <v>29.54374092999998</v>
+        <v>60.85894823</v>
       </c>
       <c r="I6" t="n">
-        <v>62.14661844</v>
+        <v>-16.84305672</v>
       </c>
       <c r="J6" t="n">
-        <v>-16.58250072999999</v>
+        <v>-82.56073731999999</v>
       </c>
       <c r="K6" t="n">
-        <v>-81.61058306</v>
+        <v>19.95676215000001</v>
       </c>
       <c r="L6" t="n">
-        <v>21.42096801000001</v>
+        <v>-20.10041905</v>
       </c>
       <c r="M6" t="n">
-        <v>-19.56567346</v>
+        <v>79.89614155</v>
       </c>
     </row>
     <row r="7">
@@ -708,37 +710,37 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>-6.579360819999998</v>
+        <v>-31.47371011</v>
       </c>
       <c r="D7" t="n">
-        <v>-31.84979054</v>
+        <v>-25.89268865</v>
       </c>
       <c r="E7" t="n">
-        <v>-25.6993177</v>
+        <v>-25.98170246</v>
       </c>
       <c r="F7" t="n">
-        <v>-27.07314461</v>
+        <v>-33.37205148</v>
       </c>
       <c r="G7" t="n">
-        <v>-35.33592206</v>
+        <v>-48.86903072</v>
       </c>
       <c r="H7" t="n">
-        <v>-51.86234025</v>
+        <v>-22.2992774</v>
       </c>
       <c r="I7" t="n">
-        <v>-23.5702012</v>
+        <v>-6.911284380000001</v>
       </c>
       <c r="J7" t="n">
-        <v>-7.168440740000002</v>
+        <v>-15.80152208</v>
       </c>
       <c r="K7" t="n">
-        <v>-16.75654344</v>
+        <v>12.60820129</v>
       </c>
       <c r="L7" t="n">
-        <v>11.13703615</v>
+        <v>24.45883667</v>
       </c>
       <c r="M7" t="n">
-        <v>23.91494567</v>
+        <v>16.33643048</v>
       </c>
     </row>
     <row r="8">
@@ -749,37 +751,37 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3190.55753981</v>
+        <v>3796.85290555</v>
       </c>
       <c r="D8" t="n">
-        <v>3757.19848391</v>
+        <v>879.34148613</v>
       </c>
       <c r="E8" t="n">
-        <v>810.0627740900001</v>
+        <v>2616.42912294</v>
       </c>
       <c r="F8" t="n">
-        <v>2588.62153626</v>
+        <v>2457.4736574</v>
       </c>
       <c r="G8" t="n">
-        <v>2449.81326305</v>
+        <v>3001.12265816</v>
       </c>
       <c r="H8" t="n">
-        <v>2974.25713672</v>
+        <v>2854.8874692</v>
       </c>
       <c r="I8" t="n">
-        <v>2830.08852827</v>
+        <v>-845.1834295299999</v>
       </c>
       <c r="J8" t="n">
-        <v>-826.58338838</v>
+        <v>-5232.13894658</v>
       </c>
       <c r="K8" t="n">
-        <v>-5224.99645793</v>
+        <v>-2467.22388111</v>
       </c>
       <c r="L8" t="n">
-        <v>-2463.53015519</v>
+        <v>-3623.44463932</v>
       </c>
       <c r="M8" t="n">
-        <v>-3607.70749756</v>
+        <v>-1265.08049358</v>
       </c>
     </row>
     <row r="9">
@@ -788,41 +790,39 @@
           <t>其他電子業右下</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>-72.15499683</v>
+        <v>-182.47906743</v>
       </c>
       <c r="D9" t="n">
-        <v>-181.83829642</v>
+        <v>-209.37100311</v>
       </c>
       <c r="E9" t="n">
-        <v>-204.15006145</v>
+        <v>-263.1047347</v>
       </c>
       <c r="F9" t="n">
-        <v>-249.37394372</v>
+        <v>-252.67459755</v>
       </c>
       <c r="G9" t="n">
-        <v>-230.97140242</v>
+        <v>-233.13082217</v>
       </c>
       <c r="H9" t="n">
-        <v>-224.32334882</v>
+        <v>-220.98118002</v>
       </c>
       <c r="I9" t="n">
-        <v>-220.69860142</v>
+        <v>-205.97982787</v>
       </c>
       <c r="J9" t="n">
-        <v>-208.86674509</v>
+        <v>-168.92762387</v>
       </c>
       <c r="K9" t="n">
-        <v>-173.04271755</v>
+        <v>-98.29998353999999</v>
       </c>
       <c r="L9" t="n">
-        <v>-101.57619926</v>
+        <v>-98.09675525</v>
       </c>
       <c r="M9" t="n">
-        <v>-101.77430725</v>
+        <v>64.11305131</v>
       </c>
     </row>
     <row r="10">
@@ -833,37 +833,37 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>18.7060269</v>
+        <v>-11.61784773</v>
       </c>
       <c r="D10" t="n">
-        <v>27.39408997</v>
+        <v>16.39353733</v>
       </c>
       <c r="E10" t="n">
-        <v>80.44882436</v>
+        <v>0.1845545600000026</v>
       </c>
       <c r="F10" t="n">
-        <v>14.25920796</v>
+        <v>22.13039961</v>
       </c>
       <c r="G10" t="n">
-        <v>8.08423681</v>
+        <v>58.61804813000001</v>
       </c>
       <c r="H10" t="n">
-        <v>76.67273951</v>
+        <v>132.59398889</v>
       </c>
       <c r="I10" t="n">
-        <v>157.10584186</v>
+        <v>32.55600085</v>
       </c>
       <c r="J10" t="n">
-        <v>16.84131357</v>
+        <v>-32.17047336</v>
       </c>
       <c r="K10" t="n">
-        <v>-35.19751714</v>
+        <v>-7.06750377</v>
       </c>
       <c r="L10" t="n">
-        <v>-7.48463061</v>
+        <v>-30.78226786</v>
       </c>
       <c r="M10" t="n">
-        <v>-42.84053777</v>
+        <v>-3.5616625</v>
       </c>
     </row>
     <row r="11">
@@ -874,37 +874,37 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>-76.35197597000001</v>
+        <v>-15.33443696000001</v>
       </c>
       <c r="D11" t="n">
-        <v>-15.33443696000001</v>
+        <v>30.12201213</v>
       </c>
       <c r="E11" t="n">
-        <v>30.12201213</v>
+        <v>-180.83661576</v>
       </c>
       <c r="F11" t="n">
-        <v>-180.83661576</v>
+        <v>-28.02151100000001</v>
       </c>
       <c r="G11" t="n">
-        <v>-28.02151100000001</v>
+        <v>312.29508241</v>
       </c>
       <c r="H11" t="n">
-        <v>312.29508241</v>
+        <v>658.2697451700001</v>
       </c>
       <c r="I11" t="n">
-        <v>658.2697451700001</v>
+        <v>242.28540973</v>
       </c>
       <c r="J11" t="n">
-        <v>242.28540973</v>
+        <v>-30.65988094999998</v>
       </c>
       <c r="K11" t="n">
-        <v>-30.65988094999998</v>
+        <v>-51.47565085999999</v>
       </c>
       <c r="L11" t="n">
-        <v>-51.47565085999999</v>
+        <v>-120.47050673</v>
       </c>
       <c r="M11" t="n">
-        <v>-120.47050673</v>
+        <v>1.62506261000001</v>
       </c>
     </row>
     <row r="12">
@@ -915,37 +915,37 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>360.0174231</v>
+        <v>239.49127732</v>
       </c>
       <c r="D12" t="n">
-        <v>239.49127732</v>
+        <v>173.03005152</v>
       </c>
       <c r="E12" t="n">
-        <v>173.03005152</v>
+        <v>-44.28253254</v>
       </c>
       <c r="F12" t="n">
-        <v>-44.28253254</v>
+        <v>-22.13244071</v>
       </c>
       <c r="G12" t="n">
-        <v>-22.13244071</v>
+        <v>2.708196700000001</v>
       </c>
       <c r="H12" t="n">
-        <v>2.708196700000001</v>
+        <v>58.76775105</v>
       </c>
       <c r="I12" t="n">
-        <v>58.76775105</v>
+        <v>-14.08652773</v>
       </c>
       <c r="J12" t="n">
-        <v>-14.08652773</v>
+        <v>-152.03090199</v>
       </c>
       <c r="K12" t="n">
-        <v>-152.03090199</v>
+        <v>-52.54308368</v>
       </c>
       <c r="L12" t="n">
-        <v>-52.54308368</v>
+        <v>-111.04547971</v>
       </c>
       <c r="M12" t="n">
-        <v>-111.04547971</v>
+        <v>31.86454527000001</v>
       </c>
     </row>
     <row r="13">
@@ -956,37 +956,37 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>-2.60440101</v>
+        <v>1.46647876</v>
       </c>
       <c r="D13" t="n">
-        <v>1.46647876</v>
+        <v>22.81387582</v>
       </c>
       <c r="E13" t="n">
-        <v>22.81387582</v>
+        <v>43.06498594</v>
       </c>
       <c r="F13" t="n">
-        <v>43.06498594</v>
+        <v>21.47027572</v>
       </c>
       <c r="G13" t="n">
-        <v>21.47027572</v>
+        <v>18.5625152</v>
       </c>
       <c r="H13" t="n">
-        <v>18.5625152</v>
+        <v>25.41829362</v>
       </c>
       <c r="I13" t="n">
-        <v>25.41829362</v>
+        <v>5.85760165</v>
       </c>
       <c r="J13" t="n">
-        <v>5.85760165</v>
+        <v>-9.34380369</v>
       </c>
       <c r="K13" t="n">
-        <v>-9.34380369</v>
+        <v>2.5032132</v>
       </c>
       <c r="L13" t="n">
-        <v>2.5032132</v>
+        <v>-6.25119298</v>
       </c>
       <c r="M13" t="n">
-        <v>-6.25119298</v>
+        <v>-3.81850446</v>
       </c>
     </row>
     <row r="14">
@@ -997,37 +997,37 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>1789.18140469</v>
+        <v>7318.33156405</v>
       </c>
       <c r="D14" t="n">
-        <v>7301.872935879999</v>
+        <v>3930.5487168</v>
       </c>
       <c r="E14" t="n">
-        <v>4082.49005407</v>
+        <v>7257.10979524</v>
       </c>
       <c r="F14" t="n">
-        <v>7624.440961189999</v>
+        <v>3296.08931944</v>
       </c>
       <c r="G14" t="n">
-        <v>4044.69387813</v>
+        <v>3704.13905733</v>
       </c>
       <c r="H14" t="n">
-        <v>4573.007792179999</v>
+        <v>907.2646100900001</v>
       </c>
       <c r="I14" t="n">
-        <v>1420.60736669</v>
+        <v>338.1748518900001</v>
       </c>
       <c r="J14" t="n">
-        <v>734.45577874</v>
+        <v>-9605.48128622</v>
       </c>
       <c r="K14" t="n">
-        <v>-9376.891590069999</v>
+        <v>-2731.88181618</v>
       </c>
       <c r="L14" t="n">
-        <v>-2594.01769678</v>
+        <v>-5124.80083696</v>
       </c>
       <c r="M14" t="n">
-        <v>-5123.20414916</v>
+        <v>504.54231106</v>
       </c>
     </row>
     <row r="15">
@@ -1036,39 +1036,41 @@
           <t>半導體業右下</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
       <c r="C15" t="n">
-        <v>319.7621053700001</v>
+        <v>32.21266831</v>
       </c>
       <c r="D15" t="n">
-        <v>27.97302630000001</v>
+        <v>977.8892039999999</v>
       </c>
       <c r="E15" t="n">
-        <v>1006.25770933</v>
+        <v>547.21699911</v>
       </c>
       <c r="F15" t="n">
-        <v>619.7335295600001</v>
+        <v>777.07836709</v>
       </c>
       <c r="G15" t="n">
-        <v>872.96122283</v>
+        <v>749.1804924300001</v>
       </c>
       <c r="H15" t="n">
-        <v>904.94850161</v>
+        <v>348.7542246099999</v>
       </c>
       <c r="I15" t="n">
-        <v>421.26157337</v>
+        <v>122.71872522</v>
       </c>
       <c r="J15" t="n">
-        <v>147.32368736</v>
+        <v>194.04073046</v>
       </c>
       <c r="K15" t="n">
-        <v>228.45976646</v>
+        <v>571.22651807</v>
       </c>
       <c r="L15" t="n">
-        <v>579.9785662999999</v>
+        <v>228.89498795</v>
       </c>
       <c r="M15" t="n">
-        <v>221.0350927799999</v>
+        <v>670.29859247</v>
       </c>
     </row>
     <row r="16">
@@ -1079,37 +1081,37 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>-446.0087902</v>
+        <v>-489.76824849</v>
       </c>
       <c r="D16" t="n">
-        <v>-505.71100257</v>
+        <v>-701.90128036</v>
       </c>
       <c r="E16" t="n">
-        <v>-792.2176904500001</v>
+        <v>-287.33511213</v>
       </c>
       <c r="F16" t="n">
-        <v>-444.71869209</v>
+        <v>54.02991229000001</v>
       </c>
       <c r="G16" t="n">
-        <v>-139.22748301</v>
+        <v>-480.7713622000001</v>
       </c>
       <c r="H16" t="n">
-        <v>-681.51453732</v>
+        <v>-119.79053997</v>
       </c>
       <c r="I16" t="n">
-        <v>29.62317507000003</v>
+        <v>-549.7267032</v>
       </c>
       <c r="J16" t="n">
-        <v>-677.78244817</v>
+        <v>-813.76362848</v>
       </c>
       <c r="K16" t="n">
-        <v>-1035.97007376</v>
+        <v>-655.10622357</v>
       </c>
       <c r="L16" t="n">
-        <v>-762.1923946100001</v>
+        <v>-245.06034683</v>
       </c>
       <c r="M16" t="n">
-        <v>-376.79985322</v>
+        <v>913.0013036900001</v>
       </c>
     </row>
     <row r="17">
@@ -1120,37 +1122,37 @@
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
-        <v>0.18345265</v>
+        <v>0.0402896</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.75565477</v>
+        <v>-0.04455849</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.09301157</v>
+        <v>0.07666569000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.25991411</v>
+        <v>0.07677364</v>
       </c>
       <c r="G17" t="n">
-        <v>0.42586555</v>
+        <v>0.0734079</v>
       </c>
       <c r="H17" t="n">
-        <v>1.11311752</v>
+        <v>0.0220497</v>
       </c>
       <c r="I17" t="n">
-        <v>0.08433128999999999</v>
+        <v>-0.00882698</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.35153504</v>
+        <v>0.02347425</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.7377812500000001</v>
+        <v>0.05612575</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.09023301</v>
+        <v>0.0005408300000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.10238635</v>
+        <v>0.03166494</v>
       </c>
     </row>
     <row r="18">
@@ -1161,37 +1163,37 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>-603.5171211700001</v>
+        <v>-1.127325219999998</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.170012629999998</v>
+        <v>755.78596021</v>
       </c>
       <c r="E18" t="n">
-        <v>755.74136299</v>
+        <v>808.41952552</v>
       </c>
       <c r="F18" t="n">
-        <v>808.41838966</v>
+        <v>20.00698698</v>
       </c>
       <c r="G18" t="n">
-        <v>20.05482964</v>
+        <v>397.85688729</v>
       </c>
       <c r="H18" t="n">
-        <v>397.91409635</v>
+        <v>941.7538826699999</v>
       </c>
       <c r="I18" t="n">
-        <v>941.82636841</v>
+        <v>-199.19026018</v>
       </c>
       <c r="J18" t="n">
-        <v>-199.10421778</v>
+        <v>-682.8813332799999</v>
       </c>
       <c r="K18" t="n">
-        <v>-682.83194151</v>
+        <v>76.16105438000001</v>
       </c>
       <c r="L18" t="n">
-        <v>76.18796667000002</v>
+        <v>-50.12597799999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-50.12917388</v>
+        <v>-19.45313958</v>
       </c>
     </row>
     <row r="19">
@@ -1202,37 +1204,37 @@
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>-16.04657688</v>
+        <v>-17.56692518</v>
       </c>
       <c r="D19" t="n">
-        <v>-16.7282934</v>
+        <v>-10.88911408</v>
       </c>
       <c r="E19" t="n">
-        <v>-9.796063780000001</v>
+        <v>-2.39151707</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.05380141</v>
+        <v>3.08112565</v>
       </c>
       <c r="G19" t="n">
-        <v>2.68419108</v>
+        <v>6.265611270000001</v>
       </c>
       <c r="H19" t="n">
-        <v>5.168692590000001</v>
+        <v>0.6903942700000002</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5556269400000001</v>
+        <v>-1.09681747</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.8401518099999999</v>
+        <v>-4.188591010000001</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.47672728</v>
+        <v>1.13234309</v>
       </c>
       <c r="L19" t="n">
-        <v>1.25178956</v>
+        <v>-2.43509851</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.32897545</v>
+        <v>-3.15426258</v>
       </c>
     </row>
     <row r="20">
@@ -1243,37 +1245,37 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>-7.499015480000001</v>
+        <v>-34.65196079</v>
       </c>
       <c r="D20" t="n">
-        <v>-34.65196079</v>
+        <v>-20.07586818</v>
       </c>
       <c r="E20" t="n">
-        <v>-20.07586818</v>
+        <v>37.03994246</v>
       </c>
       <c r="F20" t="n">
-        <v>37.03994246</v>
+        <v>61.97440654</v>
       </c>
       <c r="G20" t="n">
-        <v>61.97440654</v>
+        <v>4.784528130000001</v>
       </c>
       <c r="H20" t="n">
-        <v>4.784528130000001</v>
+        <v>-26.57971293</v>
       </c>
       <c r="I20" t="n">
-        <v>-26.57971293</v>
+        <v>-51.94192612000001</v>
       </c>
       <c r="J20" t="n">
-        <v>-51.94192612000001</v>
+        <v>-0.42173321</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.42173321</v>
+        <v>-23.83094442</v>
       </c>
       <c r="L20" t="n">
-        <v>-23.83094442</v>
+        <v>-44.06559479000001</v>
       </c>
       <c r="M20" t="n">
-        <v>-44.06559479000001</v>
+        <v>-16.18543155</v>
       </c>
     </row>
     <row r="21">
@@ -1284,37 +1286,37 @@
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
-        <v>-2.43984143</v>
+        <v>-7.15899586</v>
       </c>
       <c r="D21" t="n">
-        <v>-7.15899586</v>
+        <v>-1.9665216</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9665216</v>
+        <v>-1.02758461</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.02758461</v>
+        <v>2.7858135</v>
       </c>
       <c r="G21" t="n">
-        <v>2.7858135</v>
+        <v>1.57265017</v>
       </c>
       <c r="H21" t="n">
-        <v>1.57265017</v>
+        <v>-0.11769773</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.11769773</v>
+        <v>-1.28430574</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.28430574</v>
+        <v>-3.1636393</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.1636393</v>
+        <v>-3.19371817</v>
       </c>
       <c r="L21" t="n">
-        <v>-3.19371817</v>
+        <v>-3.23149288</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.23149288</v>
+        <v>-1.73988098</v>
       </c>
     </row>
     <row r="22">
@@ -1325,37 +1327,37 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>2.13372424</v>
+        <v>0.9927766899999999</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9927766899999999</v>
+        <v>-0.03595326999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.03595326999999999</v>
+        <v>0.96984157</v>
       </c>
       <c r="F22" t="n">
-        <v>0.96984157</v>
+        <v>1.21441183</v>
       </c>
       <c r="G22" t="n">
-        <v>1.21441183</v>
+        <v>2.1806725</v>
       </c>
       <c r="H22" t="n">
-        <v>2.1806725</v>
+        <v>0.27043521</v>
       </c>
       <c r="I22" t="n">
-        <v>0.27043521</v>
+        <v>0.97694012</v>
       </c>
       <c r="J22" t="n">
-        <v>0.97694012</v>
+        <v>-0.11805477</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.11805477</v>
+        <v>1.62020539</v>
       </c>
       <c r="L22" t="n">
-        <v>1.62020539</v>
+        <v>0.18215004</v>
       </c>
       <c r="M22" t="n">
-        <v>0.18215004</v>
+        <v>1.30186974</v>
       </c>
     </row>
     <row r="23">
@@ -1366,37 +1368,37 @@
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
-        <v>17.59080885</v>
+        <v>29.79123508</v>
       </c>
       <c r="D23" t="n">
-        <v>29.75804077</v>
+        <v>65.34342972</v>
       </c>
       <c r="E23" t="n">
-        <v>65.34066881</v>
+        <v>67.63610528999999</v>
       </c>
       <c r="F23" t="n">
-        <v>67.68293486</v>
+        <v>69.97203975999999</v>
       </c>
       <c r="G23" t="n">
-        <v>69.97326323</v>
+        <v>133.0464327</v>
       </c>
       <c r="H23" t="n">
-        <v>133.07285199</v>
+        <v>130.6413759</v>
       </c>
       <c r="I23" t="n">
-        <v>130.6029476</v>
+        <v>58.89268668</v>
       </c>
       <c r="J23" t="n">
-        <v>58.88324328</v>
+        <v>0.1293569200000017</v>
       </c>
       <c r="K23" t="n">
-        <v>0.07820831000000045</v>
+        <v>-20.18880538</v>
       </c>
       <c r="L23" t="n">
-        <v>-20.15486628</v>
+        <v>-29.74299028</v>
       </c>
       <c r="M23" t="n">
-        <v>-29.67279385</v>
+        <v>-68.75786970999999</v>
       </c>
     </row>
     <row r="24">
@@ -1405,41 +1407,39 @@
           <t>建材營造右下</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
-        <v>-52.17383739</v>
+        <v>-42.31824303</v>
       </c>
       <c r="D24" t="n">
-        <v>-56.72928587000001</v>
+        <v>-44.79656034000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-58.07162093</v>
+        <v>-22.37138071000001</v>
       </c>
       <c r="F24" t="n">
-        <v>7.94755062</v>
+        <v>16.04445966</v>
       </c>
       <c r="G24" t="n">
-        <v>15.47061347</v>
+        <v>30.46881979</v>
       </c>
       <c r="H24" t="n">
-        <v>30.43536418</v>
+        <v>33.51039145</v>
       </c>
       <c r="I24" t="n">
-        <v>34.01748883</v>
+        <v>10.90981581</v>
       </c>
       <c r="J24" t="n">
-        <v>20.54502436</v>
+        <v>-32.27587199</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.29538761</v>
+        <v>6.558118359999997</v>
       </c>
       <c r="L24" t="n">
-        <v>21.3578411</v>
+        <v>-11.25430171</v>
       </c>
       <c r="M24" t="n">
-        <v>4.25500277</v>
+        <v>1.930407980000002</v>
       </c>
     </row>
     <row r="25">
@@ -1450,37 +1450,37 @@
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>14.67194146999999</v>
+        <v>3.268189569999998</v>
       </c>
       <c r="D25" t="n">
-        <v>16.86454862</v>
+        <v>1.178924959999999</v>
       </c>
       <c r="E25" t="n">
-        <v>13.97013735</v>
+        <v>39.8421834</v>
       </c>
       <c r="F25" t="n">
-        <v>9.695182310000002</v>
+        <v>40.81397162</v>
       </c>
       <c r="G25" t="n">
-        <v>42.13963317</v>
+        <v>36.35265544</v>
       </c>
       <c r="H25" t="n">
-        <v>37.25146005999999</v>
+        <v>40.33338886</v>
       </c>
       <c r="I25" t="n">
-        <v>39.34517793</v>
+        <v>-8.200974820000001</v>
       </c>
       <c r="J25" t="n">
-        <v>-19.70663816</v>
+        <v>-62.05995376</v>
       </c>
       <c r="K25" t="n">
-        <v>-91.57033662000001</v>
+        <v>-45.22501095</v>
       </c>
       <c r="L25" t="n">
-        <v>-61.19228781</v>
+        <v>-39.82703207</v>
       </c>
       <c r="M25" t="n">
-        <v>-55.51439069999999</v>
+        <v>-34.68168123</v>
       </c>
     </row>
     <row r="26">
@@ -1491,37 +1491,37 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>3.24784478</v>
+        <v>5.521821180000001</v>
       </c>
       <c r="D26" t="n">
-        <v>5.521821180000001</v>
+        <v>16.6409802</v>
       </c>
       <c r="E26" t="n">
-        <v>16.6409802</v>
+        <v>6.06098376</v>
       </c>
       <c r="F26" t="n">
-        <v>6.06098376</v>
+        <v>6.223655750000001</v>
       </c>
       <c r="G26" t="n">
-        <v>6.223655750000001</v>
+        <v>7.69451413</v>
       </c>
       <c r="H26" t="n">
-        <v>7.69451413</v>
+        <v>9.40402284</v>
       </c>
       <c r="I26" t="n">
-        <v>9.40402284</v>
+        <v>3.51569178</v>
       </c>
       <c r="J26" t="n">
-        <v>3.51569178</v>
+        <v>-0.84665852</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.84665852</v>
+        <v>-3.81098417</v>
       </c>
       <c r="L26" t="n">
-        <v>-3.81098417</v>
+        <v>3.2463298</v>
       </c>
       <c r="M26" t="n">
-        <v>3.2463298</v>
+        <v>10.10026982</v>
       </c>
     </row>
     <row r="27">
@@ -1532,37 +1532,37 @@
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>17.74083201</v>
+        <v>22.18765775</v>
       </c>
       <c r="D27" t="n">
-        <v>22.20219834</v>
+        <v>32.00669278</v>
       </c>
       <c r="E27" t="n">
-        <v>32.01863252</v>
+        <v>32.90437347</v>
       </c>
       <c r="F27" t="n">
-        <v>32.91413802</v>
+        <v>31.89174097</v>
       </c>
       <c r="G27" t="n">
-        <v>31.9022584</v>
+        <v>15.84071661</v>
       </c>
       <c r="H27" t="n">
-        <v>15.84968732</v>
+        <v>15.49391241</v>
       </c>
       <c r="I27" t="n">
-        <v>15.5018982</v>
+        <v>7.17790168</v>
       </c>
       <c r="J27" t="n">
-        <v>7.184865029999999</v>
+        <v>-3.00251758</v>
       </c>
       <c r="K27" t="n">
-        <v>-2.99664855</v>
+        <v>-0.9558826999999984</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.9498302199999979</v>
+        <v>-3.047840899999999</v>
       </c>
       <c r="M27" t="n">
-        <v>-3.041810339999999</v>
+        <v>3.49603584</v>
       </c>
     </row>
     <row r="28">
@@ -1573,37 +1573,37 @@
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>-77.90144052000001</v>
+        <v>-107.64209913</v>
       </c>
       <c r="D28" t="n">
-        <v>-107.65663972</v>
+        <v>-100.87609465</v>
       </c>
       <c r="E28" t="n">
-        <v>-100.88803439</v>
+        <v>-89.11733212999999</v>
       </c>
       <c r="F28" t="n">
-        <v>-89.12709667999999</v>
+        <v>-74.32016209999999</v>
       </c>
       <c r="G28" t="n">
-        <v>-74.33067953</v>
+        <v>-60.25372348999999</v>
       </c>
       <c r="H28" t="n">
-        <v>-60.2626942</v>
+        <v>-34.00273959</v>
       </c>
       <c r="I28" t="n">
-        <v>-34.01072538</v>
+        <v>-31.31406694</v>
       </c>
       <c r="J28" t="n">
-        <v>-31.32103029</v>
+        <v>-34.43851073</v>
       </c>
       <c r="K28" t="n">
-        <v>-34.44437976</v>
+        <v>-6.507427059999999</v>
       </c>
       <c r="L28" t="n">
-        <v>-6.513479540000001</v>
+        <v>-9.892342220000002</v>
       </c>
       <c r="M28" t="n">
-        <v>-9.898372780000001</v>
+        <v>-10.52663957</v>
       </c>
     </row>
     <row r="29">
@@ -1614,37 +1614,37 @@
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>0.00619917</v>
+        <v>0.01277118</v>
       </c>
       <c r="D29" t="n">
-        <v>0.01277118</v>
+        <v>-0.00653676</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.00653676</v>
+        <v>-0.01623805</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.01623805</v>
+        <v>-0.01854561</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.01854561</v>
+        <v>-0.0214375</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.0214375</v>
+        <v>-0.00590779</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.00590779</v>
+        <v>0.007246020000000001</v>
       </c>
       <c r="J29" t="n">
-        <v>0.007246020000000001</v>
+        <v>0.04125581</v>
       </c>
       <c r="K29" t="n">
-        <v>0.04125581</v>
+        <v>0.01170391</v>
       </c>
       <c r="L29" t="n">
-        <v>0.01170391</v>
+        <v>0.02586367</v>
       </c>
       <c r="M29" t="n">
-        <v>0.02586367</v>
+        <v>0.005801969999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1655,37 +1655,37 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>0.0007921299999999998</v>
+        <v>-0.00467908</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.00470349</v>
+        <v>-0.00565026</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.005675059999999999</v>
+        <v>-0.00688049</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.00690276</v>
+        <v>0.01008529</v>
       </c>
       <c r="G30" t="n">
-        <v>0.01012549</v>
+        <v>0.00215091</v>
       </c>
       <c r="H30" t="n">
-        <v>0.00217369</v>
+        <v>0.003591480000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>0.00358807</v>
+        <v>0.001555480000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>0.00154582</v>
+        <v>-0.0007999199999999996</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.0008311099999999996</v>
+        <v>0.00545615</v>
       </c>
       <c r="L30" t="n">
-        <v>0.00542619</v>
+        <v>0.007495199999999999</v>
       </c>
       <c r="M30" t="n">
-        <v>0.007489949999999999</v>
+        <v>0.003162389999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1696,37 +1696,37 @@
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>-0.01164912</v>
+        <v>-0.05285173000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.05282732</v>
+        <v>-0.09475462</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.09472982000000001</v>
+        <v>-0.1850039</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.18498163</v>
+        <v>0.0035406</v>
       </c>
       <c r="G31" t="n">
-        <v>0.003500399999999999</v>
+        <v>-0.03696819</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.03699097</v>
+        <v>0.20996728</v>
       </c>
       <c r="I31" t="n">
-        <v>0.20997069</v>
+        <v>0.08270688000000001</v>
       </c>
       <c r="J31" t="n">
-        <v>0.08271654000000001</v>
+        <v>-0.01970131</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.01967012</v>
+        <v>0.08784662000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>0.08787658</v>
+        <v>-0.02011623</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.02011098</v>
+        <v>-0.08483896</v>
       </c>
     </row>
     <row r="32">
@@ -1737,37 +1737,37 @@
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>-32.15445803</v>
+        <v>-28.63820698</v>
       </c>
       <c r="D32" t="n">
-        <v>-40.28821612</v>
+        <v>-10.76783712</v>
       </c>
       <c r="E32" t="n">
-        <v>-16.20914258</v>
+        <v>-20.0377565</v>
       </c>
       <c r="F32" t="n">
-        <v>-19.13381427</v>
+        <v>-6.47922948</v>
       </c>
       <c r="G32" t="n">
-        <v>-10.30184885</v>
+        <v>-21.67391496</v>
       </c>
       <c r="H32" t="n">
-        <v>-13.95881996</v>
+        <v>5.52792584</v>
       </c>
       <c r="I32" t="n">
-        <v>16.5897552</v>
+        <v>7.32848074</v>
       </c>
       <c r="J32" t="n">
-        <v>21.57479981</v>
+        <v>15.30775618</v>
       </c>
       <c r="K32" t="n">
-        <v>10.77240005</v>
+        <v>7.30639586</v>
       </c>
       <c r="L32" t="n">
-        <v>-3.99943991</v>
+        <v>-11.85354807</v>
       </c>
       <c r="M32" t="n">
-        <v>-16.35895754</v>
+        <v>-0.6966225100000002</v>
       </c>
     </row>
     <row r="33">
@@ -1778,37 +1778,37 @@
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
-        <v>-1.10311971</v>
+        <v>-14.85168894</v>
       </c>
       <c r="D33" t="n">
-        <v>-3.2016798</v>
+        <v>-7.31165541</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.87034995</v>
+        <v>-1.41149422</v>
       </c>
       <c r="F33" t="n">
-        <v>-2.31543645</v>
+        <v>-7.85183825</v>
       </c>
       <c r="G33" t="n">
-        <v>-4.02921888</v>
+        <v>6.05615573</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.65893927</v>
+        <v>10.38013217</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.68169719</v>
+        <v>14.06584317</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.1804759</v>
+        <v>-5.77658342</v>
       </c>
       <c r="K33" t="n">
-        <v>-1.24122729</v>
+        <v>-11.60830516</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.30246939</v>
+        <v>-5.47274894</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.96733947</v>
+        <v>22.31044223</v>
       </c>
     </row>
     <row r="34">
@@ -1819,37 +1819,37 @@
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
-        <v>33.49646586</v>
+        <v>42.38292683</v>
       </c>
       <c r="D34" t="n">
-        <v>42.38292683</v>
+        <v>53.14078301</v>
       </c>
       <c r="E34" t="n">
-        <v>53.14078301</v>
+        <v>77.31264456</v>
       </c>
       <c r="F34" t="n">
-        <v>77.31264456</v>
+        <v>-99.06594910000001</v>
       </c>
       <c r="G34" t="n">
-        <v>-99.06594910000001</v>
+        <v>-137.71287059</v>
       </c>
       <c r="H34" t="n">
-        <v>-137.71287059</v>
+        <v>-36.98264507</v>
       </c>
       <c r="I34" t="n">
-        <v>-36.98264507</v>
+        <v>-110.28325571</v>
       </c>
       <c r="J34" t="n">
-        <v>-110.28325571</v>
+        <v>-29.94653585</v>
       </c>
       <c r="K34" t="n">
-        <v>-29.94653585</v>
+        <v>-75.37832121000001</v>
       </c>
       <c r="L34" t="n">
-        <v>-75.37832121000001</v>
+        <v>-140.33270771</v>
       </c>
       <c r="M34" t="n">
-        <v>-140.33270771</v>
+        <v>-13.10425446</v>
       </c>
     </row>
     <row r="35">
@@ -1860,37 +1860,37 @@
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
-        <v>-0.0252352</v>
+        <v>-0.03013220000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.03013220000000001</v>
+        <v>3.18854859</v>
       </c>
       <c r="E35" t="n">
-        <v>3.18854859</v>
+        <v>2.605460190000001</v>
       </c>
       <c r="F35" t="n">
-        <v>2.605460190000001</v>
+        <v>4.13401164</v>
       </c>
       <c r="G35" t="n">
-        <v>4.13401164</v>
+        <v>4.72190981</v>
       </c>
       <c r="H35" t="n">
-        <v>4.72190981</v>
+        <v>5.98762434</v>
       </c>
       <c r="I35" t="n">
-        <v>5.98762434</v>
+        <v>2.37916882</v>
       </c>
       <c r="J35" t="n">
-        <v>2.37916882</v>
+        <v>-0.53526386</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.53526386</v>
+        <v>2.64361891</v>
       </c>
       <c r="L35" t="n">
-        <v>2.64361891</v>
+        <v>7.38655337</v>
       </c>
       <c r="M35" t="n">
-        <v>7.38655337</v>
+        <v>7.14443184</v>
       </c>
     </row>
     <row r="36">
@@ -1901,37 +1901,37 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>227.54441106</v>
+        <v>352.4427523</v>
       </c>
       <c r="D36" t="n">
-        <v>364.58955555</v>
+        <v>204.10822595</v>
       </c>
       <c r="E36" t="n">
-        <v>215.34440896</v>
+        <v>203.78321979</v>
       </c>
       <c r="F36" t="n">
-        <v>203.11277483</v>
+        <v>-5.257925969999995</v>
       </c>
       <c r="G36" t="n">
-        <v>-9.032017559999998</v>
+        <v>182.21045032</v>
       </c>
       <c r="H36" t="n">
-        <v>184.61897931</v>
+        <v>0.8376441199999973</v>
       </c>
       <c r="I36" t="n">
-        <v>5.011323659999997</v>
+        <v>-109.20080044</v>
       </c>
       <c r="J36" t="n">
-        <v>-98.44188990000001</v>
+        <v>-113.180397</v>
       </c>
       <c r="K36" t="n">
-        <v>-118.62121267</v>
+        <v>-28.44645008</v>
       </c>
       <c r="L36" t="n">
-        <v>-24.10902694</v>
+        <v>-140.59688302</v>
       </c>
       <c r="M36" t="n">
-        <v>-146.27039908</v>
+        <v>-31.58967633999999</v>
       </c>
     </row>
     <row r="37">
@@ -1940,41 +1940,39 @@
           <t>汽車工業右下</t>
         </is>
       </c>
-      <c r="B37" t="n">
-        <v>0</v>
-      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>-30.28023679</v>
+        <v>-8.201723510000004</v>
       </c>
       <c r="D37" t="n">
-        <v>-8.215669760000004</v>
+        <v>36.93535253</v>
       </c>
       <c r="E37" t="n">
-        <v>36.84820709</v>
+        <v>10.60939206</v>
       </c>
       <c r="F37" t="n">
-        <v>10.46549578</v>
+        <v>14.43491196</v>
       </c>
       <c r="G37" t="n">
-        <v>14.34898466</v>
+        <v>-3.202828459999999</v>
       </c>
       <c r="H37" t="n">
-        <v>-3.351310759999999</v>
+        <v>19.45456314</v>
       </c>
       <c r="I37" t="n">
-        <v>19.3954208</v>
+        <v>-1.084996530000001</v>
       </c>
       <c r="J37" t="n">
-        <v>-1.251609470000002</v>
+        <v>-64.69088463</v>
       </c>
       <c r="K37" t="n">
-        <v>-64.85975591</v>
+        <v>-21.91433284</v>
       </c>
       <c r="L37" t="n">
-        <v>-21.79931408</v>
+        <v>-47.81949567</v>
       </c>
       <c r="M37" t="n">
-        <v>-47.61026725</v>
+        <v>-8.695576079999999</v>
       </c>
     </row>
     <row r="38">
@@ -1985,37 +1983,37 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>-24.06781791</v>
+        <v>9.36090752</v>
       </c>
       <c r="D38" t="n">
-        <v>5.446608559999999</v>
+        <v>39.53776639</v>
       </c>
       <c r="E38" t="n">
-        <v>31.97677294999999</v>
+        <v>34.08936899</v>
       </c>
       <c r="F38" t="n">
-        <v>40.54008104</v>
+        <v>-19.99170167</v>
       </c>
       <c r="G38" t="n">
-        <v>-19.05366693</v>
+        <v>15.25903559</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.09933349999999831</v>
+        <v>-31.9727869</v>
       </c>
       <c r="I38" t="n">
-        <v>-56.30677331</v>
+        <v>-91.09738664</v>
       </c>
       <c r="J38" t="n">
-        <v>-109.62729927</v>
+        <v>-127.24733668</v>
       </c>
       <c r="K38" t="n">
-        <v>-123.04542223</v>
+        <v>-48.2061404</v>
       </c>
       <c r="L38" t="n">
-        <v>-55.16890794</v>
+        <v>-58.21138682000001</v>
       </c>
       <c r="M38" t="n">
-        <v>-50.89618087</v>
+        <v>-7.571502210000003</v>
       </c>
     </row>
     <row r="39">
@@ -2026,37 +2024,37 @@
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
-        <v>5.236759269999999</v>
+        <v>24.80576117</v>
       </c>
       <c r="D39" t="n">
-        <v>24.80576117</v>
+        <v>21.99748971</v>
       </c>
       <c r="E39" t="n">
-        <v>21.99748971</v>
+        <v>7.5667577</v>
       </c>
       <c r="F39" t="n">
-        <v>7.5667577</v>
+        <v>-0.39082327</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.39082327</v>
+        <v>6.9156605</v>
       </c>
       <c r="H39" t="n">
-        <v>6.9156605</v>
+        <v>-3.65105099</v>
       </c>
       <c r="I39" t="n">
-        <v>-3.65105099</v>
+        <v>5.96885178</v>
       </c>
       <c r="J39" t="n">
-        <v>5.96885178</v>
+        <v>-4.14332239</v>
       </c>
       <c r="K39" t="n">
-        <v>-4.14332239</v>
+        <v>-1.8353452</v>
       </c>
       <c r="L39" t="n">
-        <v>-1.8353452</v>
+        <v>-7.62116679</v>
       </c>
       <c r="M39" t="n">
-        <v>-7.62116679</v>
+        <v>-5.07731053</v>
       </c>
     </row>
     <row r="40">
@@ -2067,37 +2065,37 @@
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>-34.21927984000001</v>
+        <v>-18.29832132</v>
       </c>
       <c r="D40" t="n">
-        <v>-18.29832132</v>
+        <v>16.51942199</v>
       </c>
       <c r="E40" t="n">
-        <v>16.51942199</v>
+        <v>-19.21069481</v>
       </c>
       <c r="F40" t="n">
-        <v>-19.21069481</v>
+        <v>-76.86549835</v>
       </c>
       <c r="G40" t="n">
-        <v>-76.86549835</v>
+        <v>-32.5970419</v>
       </c>
       <c r="H40" t="n">
-        <v>-32.5970419</v>
+        <v>-50.29811102</v>
       </c>
       <c r="I40" t="n">
-        <v>-50.29811102</v>
+        <v>-89.72822392</v>
       </c>
       <c r="J40" t="n">
-        <v>-89.72822392</v>
+        <v>-81.92920619</v>
       </c>
       <c r="K40" t="n">
-        <v>-81.92920619</v>
+        <v>5.598820609999998</v>
       </c>
       <c r="L40" t="n">
-        <v>5.598820609999998</v>
+        <v>45.96694628999999</v>
       </c>
       <c r="M40" t="n">
-        <v>45.96694628999999</v>
+        <v>5.63183572</v>
       </c>
     </row>
     <row r="41">
@@ -2108,37 +2106,37 @@
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
-        <v>-2.001e-05</v>
+        <v>4.417e-05</v>
       </c>
       <c r="D41" t="n">
-        <v>4.417e-05</v>
+        <v>9.085e-05</v>
       </c>
       <c r="E41" t="n">
-        <v>9.085e-05</v>
+        <v>-7.104999999999999e-05</v>
       </c>
       <c r="F41" t="n">
-        <v>-7.104999999999999e-05</v>
+        <v>-0.00022371</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.00022371</v>
+        <v>-0.00012</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.00012</v>
+        <v>-0.00023445</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.00023445</v>
+        <v>-0.00035108</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.00035108</v>
+        <v>-0.00043212</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.00043212</v>
+        <v>-0.00024149</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.00024149</v>
+        <v>-0.00030939</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.00030939</v>
+        <v>-0.00037094</v>
       </c>
     </row>
     <row r="42">
@@ -2149,37 +2147,37 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>-24.7706204</v>
+        <v>156.76665614</v>
       </c>
       <c r="D42" t="n">
-        <v>154.56242497</v>
+        <v>578.4989785</v>
       </c>
       <c r="E42" t="n">
-        <v>569.9204095299999</v>
+        <v>900.52032724</v>
       </c>
       <c r="F42" t="n">
-        <v>879.95625971</v>
+        <v>1153.82319753</v>
       </c>
       <c r="G42" t="n">
-        <v>1190.48956757</v>
+        <v>1252.18441714</v>
       </c>
       <c r="H42" t="n">
-        <v>1271.44494553</v>
+        <v>1286.18806609</v>
       </c>
       <c r="I42" t="n">
-        <v>1277.79570934</v>
+        <v>-596.5809266700001</v>
       </c>
       <c r="J42" t="n">
-        <v>-591.18301373</v>
+        <v>-826.9752677900001</v>
       </c>
       <c r="K42" t="n">
-        <v>-815.56774821</v>
+        <v>-639.5127566199999</v>
       </c>
       <c r="L42" t="n">
-        <v>-634.0106390599999</v>
+        <v>-688.69328325</v>
       </c>
       <c r="M42" t="n">
-        <v>-674.41102839</v>
+        <v>-546.8971442000001</v>
       </c>
     </row>
     <row r="43">
@@ -2190,37 +2188,37 @@
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
-        <v>-4.01613703</v>
+        <v>-2.72785007</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.5236189</v>
+        <v>3.65355746</v>
       </c>
       <c r="E43" t="n">
-        <v>12.23212643</v>
+        <v>20.8485932</v>
       </c>
       <c r="F43" t="n">
-        <v>41.41266073000001</v>
+        <v>34.26722984000001</v>
       </c>
       <c r="G43" t="n">
-        <v>-2.399140199999998</v>
+        <v>38.60901432</v>
       </c>
       <c r="H43" t="n">
-        <v>19.34848593</v>
+        <v>37.64043757</v>
       </c>
       <c r="I43" t="n">
-        <v>46.03279432</v>
+        <v>12.03339149</v>
       </c>
       <c r="J43" t="n">
-        <v>6.63547855</v>
+        <v>-0.6715432099999999</v>
       </c>
       <c r="K43" t="n">
-        <v>-12.07906279</v>
+        <v>-6.64275093</v>
       </c>
       <c r="L43" t="n">
-        <v>-12.14486849</v>
+        <v>-11.1140868</v>
       </c>
       <c r="M43" t="n">
-        <v>-25.39634166</v>
+        <v>-13.51905319</v>
       </c>
     </row>
     <row r="44">
@@ -2231,37 +2229,37 @@
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>12.22388255</v>
+        <v>11.62153488</v>
       </c>
       <c r="D44" t="n">
-        <v>11.88497066</v>
+        <v>12.52428829</v>
       </c>
       <c r="E44" t="n">
-        <v>12.57494785</v>
+        <v>-6.29255899</v>
       </c>
       <c r="F44" t="n">
-        <v>-6.547999999999999</v>
+        <v>-19.82934299</v>
       </c>
       <c r="G44" t="n">
-        <v>-20.40100123</v>
+        <v>-25.38328077</v>
       </c>
       <c r="H44" t="n">
-        <v>-26.01072253</v>
+        <v>-19.68425024</v>
       </c>
       <c r="I44" t="n">
-        <v>-20.37963784</v>
+        <v>-7.2754713</v>
       </c>
       <c r="J44" t="n">
-        <v>-8.065689990000001</v>
+        <v>-12.29083748</v>
       </c>
       <c r="K44" t="n">
-        <v>-12.98331069</v>
+        <v>0.4751900600000004</v>
       </c>
       <c r="L44" t="n">
-        <v>8.833986980000001</v>
+        <v>23.01384118</v>
       </c>
       <c r="M44" t="n">
-        <v>28.14835708</v>
+        <v>-15.65109047</v>
       </c>
     </row>
     <row r="45">
@@ -2274,37 +2272,37 @@
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>263.97938734</v>
+        <v>97.33550386000002</v>
       </c>
       <c r="D45" t="n">
-        <v>101.98625517</v>
+        <v>184.27656159</v>
       </c>
       <c r="E45" t="n">
-        <v>185.99572339</v>
+        <v>198.713476</v>
       </c>
       <c r="F45" t="n">
-        <v>201.2759963</v>
+        <v>293.36701458</v>
       </c>
       <c r="G45" t="n">
-        <v>281.41953408</v>
+        <v>426.05552276</v>
       </c>
       <c r="H45" t="n">
-        <v>413.92451083</v>
+        <v>554.8971386100001</v>
       </c>
       <c r="I45" t="n">
-        <v>543.44303894</v>
+        <v>773.22111708</v>
       </c>
       <c r="J45" t="n">
-        <v>766.9229588500001</v>
+        <v>1234.9986829</v>
       </c>
       <c r="K45" t="n">
-        <v>1236.46258151</v>
+        <v>1393.16834543</v>
       </c>
       <c r="L45" t="n">
-        <v>1392.33320567</v>
+        <v>431.49039629</v>
       </c>
       <c r="M45" t="n">
-        <v>428.1873829099999</v>
+        <v>639.90180303</v>
       </c>
     </row>
     <row r="46">
@@ -2315,37 +2313,37 @@
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>49.74752404</v>
+        <v>-59.50473491</v>
       </c>
       <c r="D46" t="n">
-        <v>-63.33927405000001</v>
+        <v>73.61822776999999</v>
       </c>
       <c r="E46" t="n">
-        <v>73.38784379000001</v>
+        <v>103.31493801</v>
       </c>
       <c r="F46" t="n">
-        <v>100.95624138</v>
+        <v>247.04460891</v>
       </c>
       <c r="G46" t="n">
-        <v>258.43465667</v>
+        <v>66.66327029999999</v>
       </c>
       <c r="H46" t="n">
-        <v>79.3977781</v>
+        <v>-62.24306832</v>
       </c>
       <c r="I46" t="n">
-        <v>-49.21388113999999</v>
+        <v>-149.25217461</v>
       </c>
       <c r="J46" t="n">
-        <v>-142.95711393</v>
+        <v>-141.19945651</v>
       </c>
       <c r="K46" t="n">
-        <v>-141.34832742</v>
+        <v>-84.32757759</v>
       </c>
       <c r="L46" t="n">
-        <v>-92.29837343</v>
+        <v>-112.99791711</v>
       </c>
       <c r="M46" t="n">
-        <v>-116.45669402</v>
+        <v>-49.55242153000001</v>
       </c>
     </row>
     <row r="47">
@@ -2356,37 +2354,37 @@
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>0.11380938</v>
+        <v>-1.1655586</v>
       </c>
       <c r="D47" t="n">
-        <v>-1.16393911</v>
+        <v>3.26496547</v>
       </c>
       <c r="E47" t="n">
-        <v>3.26730915</v>
+        <v>1.63752578</v>
       </c>
       <c r="F47" t="n">
-        <v>1.63955288</v>
+        <v>0.73957031</v>
       </c>
       <c r="G47" t="n">
-        <v>0.7404075099999999</v>
+        <v>2.84248041</v>
       </c>
       <c r="H47" t="n">
-        <v>2.84180396</v>
+        <v>3.94012105</v>
       </c>
       <c r="I47" t="n">
-        <v>3.94008714</v>
+        <v>4.282697440000001</v>
       </c>
       <c r="J47" t="n">
-        <v>4.28278438</v>
+        <v>1.74059634</v>
       </c>
       <c r="K47" t="n">
-        <v>1.74077493</v>
+        <v>2.58832362</v>
       </c>
       <c r="L47" t="n">
-        <v>2.58748699</v>
+        <v>8.37476756</v>
       </c>
       <c r="M47" t="n">
-        <v>8.3743338</v>
+        <v>2.66770553</v>
       </c>
     </row>
     <row r="48">
@@ -2397,37 +2395,37 @@
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
-        <v>-100.97579443</v>
+        <v>-161.09871495</v>
       </c>
       <c r="D48" t="n">
-        <v>-162.4749122</v>
+        <v>-138.66368119</v>
       </c>
       <c r="E48" t="n">
-        <v>-138.91380902</v>
+        <v>-66.08023935999999</v>
       </c>
       <c r="F48" t="n">
-        <v>-65.78404603</v>
+        <v>100.64913585</v>
       </c>
       <c r="G48" t="n">
-        <v>100.66743719</v>
+        <v>167.52132607</v>
       </c>
       <c r="H48" t="n">
-        <v>167.30677723</v>
+        <v>93.73160254999999</v>
       </c>
       <c r="I48" t="n">
-        <v>94.00985064999999</v>
+        <v>30.6499759</v>
       </c>
       <c r="J48" t="n">
-        <v>31.25876354</v>
+        <v>-10.20388659</v>
       </c>
       <c r="K48" t="n">
-        <v>-9.365502470000003</v>
+        <v>68.61116697</v>
       </c>
       <c r="L48" t="n">
-        <v>71.67941374999999</v>
+        <v>39.74779179999999</v>
       </c>
       <c r="M48" t="n">
-        <v>41.2511178</v>
+        <v>92.27023935000001</v>
       </c>
     </row>
     <row r="49">
@@ -2438,37 +2436,37 @@
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>-0.70459123</v>
+        <v>-3.14896068</v>
       </c>
       <c r="D49" t="n">
-        <v>-3.15058017</v>
+        <v>-1.09718438</v>
       </c>
       <c r="E49" t="n">
-        <v>-1.09952806</v>
+        <v>13.15970829</v>
       </c>
       <c r="F49" t="n">
-        <v>13.15768119</v>
+        <v>60.53451084</v>
       </c>
       <c r="G49" t="n">
-        <v>60.53367364</v>
+        <v>92.00479023</v>
       </c>
       <c r="H49" t="n">
-        <v>92.00546668000001</v>
+        <v>197.5994527</v>
       </c>
       <c r="I49" t="n">
-        <v>197.59948661</v>
+        <v>309.54159402</v>
       </c>
       <c r="J49" t="n">
-        <v>309.54150708</v>
+        <v>124.47148492</v>
       </c>
       <c r="K49" t="n">
-        <v>124.47130633</v>
+        <v>114.35255789</v>
       </c>
       <c r="L49" t="n">
-        <v>114.35339452</v>
+        <v>8.714754710000001</v>
       </c>
       <c r="M49" t="n">
-        <v>8.715188470000001</v>
+        <v>10.6989212</v>
       </c>
     </row>
     <row r="50">
@@ -2479,37 +2477,37 @@
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
-        <v>-67.32971089999999</v>
+        <v>-49.9699323</v>
       </c>
       <c r="D50" t="n">
-        <v>-49.9699323</v>
+        <v>-34.87113519</v>
       </c>
       <c r="E50" t="n">
-        <v>-34.87113519</v>
+        <v>-101.83529897</v>
       </c>
       <c r="F50" t="n">
-        <v>-101.83529897</v>
+        <v>-20.18952884999999</v>
       </c>
       <c r="G50" t="n">
-        <v>-20.18952884999999</v>
+        <v>60.03399915</v>
       </c>
       <c r="H50" t="n">
-        <v>60.03399915</v>
+        <v>46.57401195000001</v>
       </c>
       <c r="I50" t="n">
-        <v>46.57401195000001</v>
+        <v>94.33851032</v>
       </c>
       <c r="J50" t="n">
-        <v>94.33851032</v>
+        <v>-55.45684779</v>
       </c>
       <c r="K50" t="n">
-        <v>-55.45684779</v>
+        <v>95.27728619</v>
       </c>
       <c r="L50" t="n">
-        <v>95.27728619</v>
+        <v>351.9052843899999</v>
       </c>
       <c r="M50" t="n">
-        <v>351.9052843899999</v>
+        <v>-93.63477472999999</v>
       </c>
     </row>
     <row r="51">
@@ -2520,37 +2518,37 @@
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>-17.31000216</v>
+        <v>-27.0028744</v>
       </c>
       <c r="D51" t="n">
-        <v>-27.00119206</v>
+        <v>-37.85275138</v>
       </c>
       <c r="E51" t="n">
-        <v>-37.85262138</v>
+        <v>-40.22223143</v>
       </c>
       <c r="F51" t="n">
-        <v>-40.22165305999999</v>
+        <v>-40.80161921</v>
       </c>
       <c r="G51" t="n">
-        <v>-40.80044587</v>
+        <v>-105.72028086</v>
       </c>
       <c r="H51" t="n">
-        <v>-105.72065853</v>
+        <v>-88.20309210000001</v>
       </c>
       <c r="I51" t="n">
-        <v>-88.20215075</v>
+        <v>-78.58831128</v>
       </c>
       <c r="J51" t="n">
-        <v>-78.58694362999999</v>
+        <v>-59.1395146</v>
       </c>
       <c r="K51" t="n">
-        <v>-59.1372507</v>
+        <v>-20.76651212</v>
       </c>
       <c r="L51" t="n">
-        <v>-20.76584638</v>
+        <v>-9.090089680000002</v>
       </c>
       <c r="M51" t="n">
-        <v>-9.088962759999999</v>
+        <v>13.2654385</v>
       </c>
     </row>
     <row r="52">
@@ -2561,37 +2559,37 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>14.36571771</v>
+        <v>-7.091562979999999</v>
       </c>
       <c r="D52" t="n">
-        <v>-7.093245320000001</v>
+        <v>3.777009930000002</v>
       </c>
       <c r="E52" t="n">
-        <v>3.776879930000002</v>
+        <v>-0.598476830000001</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.599055200000002</v>
+        <v>-25.32658246</v>
       </c>
       <c r="G52" t="n">
-        <v>-25.3277558</v>
+        <v>-25.32170115</v>
       </c>
       <c r="H52" t="n">
-        <v>-25.32132348</v>
+        <v>-2.890023269999999</v>
       </c>
       <c r="I52" t="n">
-        <v>-2.890964619999999</v>
+        <v>-8.69867458</v>
       </c>
       <c r="J52" t="n">
-        <v>-8.700042229999999</v>
+        <v>-18.52504623</v>
       </c>
       <c r="K52" t="n">
-        <v>-18.52731013</v>
+        <v>-1.479009819999999</v>
       </c>
       <c r="L52" t="n">
-        <v>-1.47967556</v>
+        <v>56.65191959</v>
       </c>
       <c r="M52" t="n">
-        <v>56.65079266999999</v>
+        <v>-7.17928261</v>
       </c>
     </row>
     <row r="53">
@@ -2602,37 +2600,37 @@
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>163.15883878</v>
+        <v>403.92137964</v>
       </c>
       <c r="D53" t="n">
-        <v>424.97040094</v>
+        <v>417.27355261</v>
       </c>
       <c r="E53" t="n">
-        <v>375.5975187299999</v>
+        <v>787.2843079599999</v>
       </c>
       <c r="F53" t="n">
-        <v>804.5212617099999</v>
+        <v>526.30884272</v>
       </c>
       <c r="G53" t="n">
-        <v>529.58728232</v>
+        <v>649.1520573</v>
       </c>
       <c r="H53" t="n">
-        <v>628.00361006</v>
+        <v>849.2582801599999</v>
       </c>
       <c r="I53" t="n">
-        <v>732.3668886900001</v>
+        <v>141.52416834</v>
       </c>
       <c r="J53" t="n">
-        <v>-1.638960959999991</v>
+        <v>78.86956287999999</v>
       </c>
       <c r="K53" t="n">
-        <v>45.45170964999999</v>
+        <v>-258.40794319</v>
       </c>
       <c r="L53" t="n">
-        <v>-304.19498971</v>
+        <v>-109.78883045</v>
       </c>
       <c r="M53" t="n">
-        <v>-67.37860953000001</v>
+        <v>57.96800567000002</v>
       </c>
     </row>
     <row r="54">
@@ -2641,39 +2639,41 @@
           <t>航運業右下</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
+      <c r="B54" t="n">
+        <v>0</v>
+      </c>
       <c r="C54" t="n">
-        <v>28.77241789</v>
+        <v>26.53279652</v>
       </c>
       <c r="D54" t="n">
-        <v>22.60990303</v>
+        <v>54.26527661000001</v>
       </c>
       <c r="E54" t="n">
-        <v>54.14957485000001</v>
+        <v>28.46371281</v>
       </c>
       <c r="F54" t="n">
-        <v>27.17223683</v>
+        <v>28.93043279</v>
       </c>
       <c r="G54" t="n">
-        <v>25.4658437</v>
+        <v>7.67053865</v>
       </c>
       <c r="H54" t="n">
-        <v>4.33585233</v>
+        <v>4.52408931</v>
       </c>
       <c r="I54" t="n">
-        <v>3.73578347</v>
+        <v>-5.367082490000001</v>
       </c>
       <c r="J54" t="n">
-        <v>-5.769233830000001</v>
+        <v>-23.60115783</v>
       </c>
       <c r="K54" t="n">
-        <v>-24.43199912</v>
+        <v>-5.530258799999999</v>
       </c>
       <c r="L54" t="n">
-        <v>-1.47052552</v>
+        <v>-21.78297269</v>
       </c>
       <c r="M54" t="n">
-        <v>-5.378304119999999</v>
+        <v>-29.47139295</v>
       </c>
     </row>
     <row r="55">
@@ -2684,37 +2684,37 @@
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>-4.354884539999996</v>
+        <v>101.43027788</v>
       </c>
       <c r="D55" t="n">
-        <v>-196.46450063</v>
+        <v>287.92907859</v>
       </c>
       <c r="E55" t="n">
-        <v>209.35848273</v>
+        <v>-71.93683267999999</v>
       </c>
       <c r="F55" t="n">
-        <v>-57.53995155999999</v>
+        <v>63.32587674999999</v>
       </c>
       <c r="G55" t="n">
-        <v>134.58193653</v>
+        <v>-126.93757763</v>
       </c>
       <c r="H55" t="n">
-        <v>-16.36566422</v>
+        <v>-15.79360724000001</v>
       </c>
       <c r="I55" t="n">
-        <v>1.29282777999998</v>
+        <v>-389.3578205</v>
       </c>
       <c r="J55" t="n">
-        <v>-160.92167213</v>
+        <v>-521.33185575</v>
       </c>
       <c r="K55" t="n">
-        <v>-322.85291833</v>
+        <v>-143.61005651</v>
       </c>
       <c r="L55" t="n">
-        <v>16.64372226</v>
+        <v>-100.5940344</v>
       </c>
       <c r="M55" t="n">
-        <v>-246.85201093</v>
+        <v>-23.22845730999999</v>
       </c>
     </row>
     <row r="56">
@@ -2725,37 +2725,37 @@
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>-9.779559470000001</v>
+        <v>-29.51420846</v>
       </c>
       <c r="D56" t="n">
-        <v>-29.51420846</v>
+        <v>-37.83837768</v>
       </c>
       <c r="E56" t="n">
-        <v>-37.83837768</v>
+        <v>-21.37096288</v>
       </c>
       <c r="F56" t="n">
-        <v>-21.37096288</v>
+        <v>3.36146783</v>
       </c>
       <c r="G56" t="n">
-        <v>3.36146783</v>
+        <v>3.36226849</v>
       </c>
       <c r="H56" t="n">
-        <v>3.36226849</v>
+        <v>27.33139818</v>
       </c>
       <c r="I56" t="n">
-        <v>27.33139818</v>
+        <v>30.01617481</v>
       </c>
       <c r="J56" t="n">
-        <v>30.01617481</v>
+        <v>29.86061085</v>
       </c>
       <c r="K56" t="n">
-        <v>29.86061085</v>
+        <v>27.02228676</v>
       </c>
       <c r="L56" t="n">
-        <v>27.02228676</v>
+        <v>32.18990925</v>
       </c>
       <c r="M56" t="n">
-        <v>32.18990925</v>
+        <v>16.3956815</v>
       </c>
     </row>
     <row r="57">
@@ -2764,39 +2764,41 @@
           <t>觀光事業右下</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
+      <c r="B57" t="n">
+        <v>0</v>
+      </c>
       <c r="C57" t="n">
-        <v>-19.63731446</v>
+        <v>-31.28732159</v>
       </c>
       <c r="D57" t="n">
-        <v>-31.28672083</v>
+        <v>-35.82188406</v>
       </c>
       <c r="E57" t="n">
-        <v>-35.82230129</v>
+        <v>-48.83523693999999</v>
       </c>
       <c r="F57" t="n">
-        <v>-48.83644887</v>
+        <v>-2.96059799</v>
       </c>
       <c r="G57" t="n">
-        <v>-2.96099005</v>
+        <v>-4.132503679999999</v>
       </c>
       <c r="H57" t="n">
-        <v>-4.132907749999999</v>
+        <v>-6.760800140000001</v>
       </c>
       <c r="I57" t="n">
-        <v>-6.76113141</v>
+        <v>-11.20146937</v>
       </c>
       <c r="J57" t="n">
-        <v>-11.20169948</v>
+        <v>-1.30338222</v>
       </c>
       <c r="K57" t="n">
-        <v>-1.30357813</v>
+        <v>12.0210239</v>
       </c>
       <c r="L57" t="n">
-        <v>12.02094224</v>
+        <v>1.93636077</v>
       </c>
       <c r="M57" t="n">
-        <v>1.93671805</v>
+        <v>5.156443139999999</v>
       </c>
     </row>
     <row r="58">
@@ -2807,37 +2809,37 @@
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>-0.00318353</v>
+        <v>-0.01366196</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.01384618</v>
+        <v>-0.02528435</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.02535924</v>
+        <v>-0.01048862</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.01054632</v>
+        <v>-0.02850319</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.02853263</v>
+        <v>-0.03215644</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.03224291</v>
+        <v>-0.0241682</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.02415376</v>
+        <v>-0.01771963</v>
       </c>
       <c r="J58" t="n">
-        <v>-0.01781416</v>
+        <v>-0.00682615</v>
       </c>
       <c r="K58" t="n">
-        <v>-0.006898679999999999</v>
+        <v>-0.00195043</v>
       </c>
       <c r="L58" t="n">
-        <v>-0.00198091</v>
+        <v>0.0001301400000000001</v>
       </c>
       <c r="M58" t="n">
-        <v>0.00017943</v>
+        <v>0.00370429</v>
       </c>
     </row>
     <row r="59">
@@ -2848,37 +2850,37 @@
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
-        <v>0.01201424</v>
+        <v>0.04099756</v>
       </c>
       <c r="D59" t="n">
-        <v>0.04099756</v>
+        <v>0.02809802</v>
       </c>
       <c r="E59" t="n">
-        <v>0.02809802</v>
+        <v>0.04076989</v>
       </c>
       <c r="F59" t="n">
-        <v>0.04076989</v>
+        <v>-0.02230235</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.02230235</v>
+        <v>0.0121624</v>
       </c>
       <c r="H59" t="n">
-        <v>0.0121624</v>
+        <v>-0.02442989</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.02442989</v>
+        <v>0.09452125</v>
       </c>
       <c r="J59" t="n">
-        <v>0.09452125</v>
+        <v>0.12390914</v>
       </c>
       <c r="K59" t="n">
-        <v>0.12390914</v>
+        <v>0.05750639</v>
       </c>
       <c r="L59" t="n">
-        <v>0.05750639</v>
+        <v>0.01196176</v>
       </c>
       <c r="M59" t="n">
-        <v>0.01196176</v>
+        <v>-0.03147701</v>
       </c>
     </row>
     <row r="60">
@@ -2889,37 +2891,37 @@
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
-        <v>29.48116599</v>
+        <v>3.745202050000001</v>
       </c>
       <c r="D60" t="n">
-        <v>3.745202050000001</v>
+        <v>-27.11462849</v>
       </c>
       <c r="E60" t="n">
-        <v>-27.11462849</v>
+        <v>-14.54311404</v>
       </c>
       <c r="F60" t="n">
-        <v>-14.54311404</v>
+        <v>-20.20816677</v>
       </c>
       <c r="G60" t="n">
-        <v>-20.20816677</v>
+        <v>-48.84269329</v>
       </c>
       <c r="H60" t="n">
-        <v>-48.84269329</v>
+        <v>-21.3959596</v>
       </c>
       <c r="I60" t="n">
-        <v>-21.3959596</v>
+        <v>-28.9827527</v>
       </c>
       <c r="J60" t="n">
-        <v>-28.9827527</v>
+        <v>-29.74134219</v>
       </c>
       <c r="K60" t="n">
-        <v>-29.74134219</v>
+        <v>13.35674909</v>
       </c>
       <c r="L60" t="n">
-        <v>13.35674909</v>
+        <v>-5.219705279999999</v>
       </c>
       <c r="M60" t="n">
-        <v>-5.219705279999999</v>
+        <v>-5.249354970000001</v>
       </c>
     </row>
     <row r="61">
@@ -2930,37 +2932,37 @@
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
-        <v>0.01478623</v>
+        <v>-0.00852609</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.00852609</v>
+        <v>0.00626116</v>
       </c>
       <c r="E61" t="n">
-        <v>0.00626116</v>
+        <v>-0.007863790000000001</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.007863790000000001</v>
+        <v>0.01475482</v>
       </c>
       <c r="G61" t="n">
-        <v>0.01475482</v>
+        <v>0.05246434</v>
       </c>
       <c r="H61" t="n">
-        <v>0.05246434</v>
+        <v>-0.007224899999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.007224899999999999</v>
+        <v>-0.02879724</v>
       </c>
       <c r="J61" t="n">
-        <v>-0.02879724</v>
+        <v>-0.04936808</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.04936808</v>
+        <v>-0.01718104</v>
       </c>
       <c r="L61" t="n">
-        <v>-0.01718104</v>
+        <v>-0.01882583</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.01882583</v>
+        <v>0.05582211</v>
       </c>
     </row>
     <row r="62">
@@ -2971,37 +2973,37 @@
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>4.496421909999995</v>
+        <v>16.52188788</v>
       </c>
       <c r="D62" t="n">
-        <v>16.5218095</v>
+        <v>67.26936631000001</v>
       </c>
       <c r="E62" t="n">
-        <v>67.27009512000001</v>
+        <v>-16.93134559</v>
       </c>
       <c r="F62" t="n">
-        <v>-16.92938799</v>
+        <v>-37.9880055</v>
       </c>
       <c r="G62" t="n">
-        <v>-37.98414687</v>
+        <v>-34.65914282</v>
       </c>
       <c r="H62" t="n">
-        <v>-34.65845204999999</v>
+        <v>-52.24997314</v>
       </c>
       <c r="I62" t="n">
-        <v>-52.24809272</v>
+        <v>-39.37738686</v>
       </c>
       <c r="J62" t="n">
-        <v>-39.37894222</v>
+        <v>-4.033918470000014</v>
       </c>
       <c r="K62" t="n">
-        <v>-4.036571590000014</v>
+        <v>175.37682422</v>
       </c>
       <c r="L62" t="n">
-        <v>175.37555294</v>
+        <v>175.90085929</v>
       </c>
       <c r="M62" t="n">
-        <v>175.90300913</v>
+        <v>136.82315401</v>
       </c>
     </row>
     <row r="63">
@@ -3014,37 +3016,37 @@
         <v>0</v>
       </c>
       <c r="C63" t="n">
-        <v>0.0077172</v>
+        <v>0.0165183</v>
       </c>
       <c r="D63" t="n">
-        <v>0.01239022</v>
+        <v>0.02079566</v>
       </c>
       <c r="E63" t="n">
-        <v>0.01840041</v>
+        <v>0.02295783</v>
       </c>
       <c r="F63" t="n">
-        <v>0.02224854</v>
+        <v>0.01874305</v>
       </c>
       <c r="G63" t="n">
-        <v>0.01885111</v>
+        <v>0.01366509</v>
       </c>
       <c r="H63" t="n">
-        <v>0.01559031</v>
+        <v>0.00024416</v>
       </c>
       <c r="I63" t="n">
-        <v>0.00229577</v>
+        <v>-0.00657713</v>
       </c>
       <c r="J63" t="n">
-        <v>-0.004842180000000001</v>
+        <v>0.00399665</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.00114184</v>
+        <v>0.00442412</v>
       </c>
       <c r="L63" t="n">
-        <v>0.00350196</v>
+        <v>-0.00497683</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.00508045</v>
+        <v>-0.0007074799999999999</v>
       </c>
     </row>
     <row r="64">
@@ -3055,37 +3057,37 @@
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
-        <v>17.01477572</v>
+        <v>18.4390037</v>
       </c>
       <c r="D64" t="n">
-        <v>18.4390037</v>
+        <v>30.16394224</v>
       </c>
       <c r="E64" t="n">
-        <v>30.16394224</v>
+        <v>29.38253063</v>
       </c>
       <c r="F64" t="n">
-        <v>29.38253063</v>
+        <v>-1.380576690000001</v>
       </c>
       <c r="G64" t="n">
-        <v>-1.380576690000001</v>
+        <v>-22.5959879</v>
       </c>
       <c r="H64" t="n">
-        <v>-22.5959879</v>
+        <v>-17.54958439</v>
       </c>
       <c r="I64" t="n">
-        <v>-17.54958439</v>
+        <v>-29.10349154</v>
       </c>
       <c r="J64" t="n">
-        <v>-29.10349154</v>
+        <v>-2.03398716</v>
       </c>
       <c r="K64" t="n">
-        <v>-2.03398716</v>
+        <v>22.94496679</v>
       </c>
       <c r="L64" t="n">
-        <v>22.94496679</v>
+        <v>4.16137799</v>
       </c>
       <c r="M64" t="n">
-        <v>4.16137799</v>
+        <v>35.28482904</v>
       </c>
     </row>
     <row r="65">
@@ -3096,37 +3098,37 @@
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
-        <v>-0.00025412</v>
+        <v>-0.00126824</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.00126824</v>
+        <v>-0.00052996</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.00052996</v>
+        <v>-4.627e-05</v>
       </c>
       <c r="F65" t="n">
-        <v>-4.627e-05</v>
+        <v>0.00012135</v>
       </c>
       <c r="G65" t="n">
-        <v>0.00012135</v>
+        <v>0.00033795</v>
       </c>
       <c r="H65" t="n">
-        <v>0.00033795</v>
+        <v>0.0007966399999999999</v>
       </c>
       <c r="I65" t="n">
-        <v>0.0007966399999999999</v>
+        <v>0.00094526</v>
       </c>
       <c r="J65" t="n">
-        <v>0.00094526</v>
+        <v>0.00174454</v>
       </c>
       <c r="K65" t="n">
-        <v>0.00174454</v>
+        <v>0.0028698</v>
       </c>
       <c r="L65" t="n">
-        <v>0.0028698</v>
+        <v>0.00067753</v>
       </c>
       <c r="M65" t="n">
-        <v>0.00067753</v>
+        <v>-0.00045384</v>
       </c>
     </row>
     <row r="66">
@@ -3137,37 +3139,37 @@
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>-3.720999999999999e-05</v>
+        <v>-0.00012853</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.00012853</v>
+        <v>-0.00011783</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.00011783</v>
+        <v>-0.00038662</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.00038662</v>
+        <v>-0.00020338</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.00020338</v>
+        <v>2.062999999999999e-05</v>
       </c>
       <c r="H66" t="n">
-        <v>2.062999999999999e-05</v>
+        <v>7.988999999999998e-05</v>
       </c>
       <c r="I66" t="n">
-        <v>7.988999999999998e-05</v>
+        <v>-3.629999999999995e-06</v>
       </c>
       <c r="J66" t="n">
-        <v>-3.629999999999995e-06</v>
+        <v>0.00015752</v>
       </c>
       <c r="K66" t="n">
-        <v>0.00015752</v>
+        <v>0.00021599</v>
       </c>
       <c r="L66" t="n">
-        <v>0.00021599</v>
+        <v>0.00017486</v>
       </c>
       <c r="M66" t="n">
-        <v>0.00017486</v>
+        <v>3.101e-05</v>
       </c>
     </row>
     <row r="67">
@@ -3178,37 +3180,37 @@
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>738.88523447</v>
+        <v>922.2366730800001</v>
       </c>
       <c r="D67" t="n">
-        <v>921.47562096</v>
+        <v>1025.05925974</v>
       </c>
       <c r="E67" t="n">
-        <v>931.3788527099999</v>
+        <v>1121.3388571</v>
       </c>
       <c r="F67" t="n">
-        <v>949.17133917</v>
+        <v>1091.38838137</v>
       </c>
       <c r="G67" t="n">
-        <v>686.0715570999999</v>
+        <v>1194.63658561</v>
       </c>
       <c r="H67" t="n">
-        <v>758.0479669600001</v>
+        <v>1752.89016636</v>
       </c>
       <c r="I67" t="n">
-        <v>1593.71785287</v>
+        <v>599.6728452000001</v>
       </c>
       <c r="J67" t="n">
-        <v>419.1833105</v>
+        <v>-1800.9600182</v>
       </c>
       <c r="K67" t="n">
-        <v>-1811.73895411</v>
+        <v>-1190.94781851</v>
       </c>
       <c r="L67" t="n">
-        <v>-1096.96861131</v>
+        <v>-1025.3908286</v>
       </c>
       <c r="M67" t="n">
-        <v>-886.4390190700001</v>
+        <v>-866.6814339</v>
       </c>
     </row>
     <row r="68">
@@ -3217,41 +3219,39 @@
           <t>通信網路業右下</t>
         </is>
       </c>
-      <c r="B68" t="n">
-        <v>0</v>
-      </c>
+      <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>-100.39485247</v>
+        <v>-108.88423967</v>
       </c>
       <c r="D68" t="n">
-        <v>-108.88161837</v>
+        <v>-49.34166707</v>
       </c>
       <c r="E68" t="n">
-        <v>-49.34560721</v>
+        <v>-40.32357138</v>
       </c>
       <c r="F68" t="n">
-        <v>-40.32005366</v>
+        <v>-39.00888978</v>
       </c>
       <c r="G68" t="n">
-        <v>-39.00891055</v>
+        <v>-17.80951091</v>
       </c>
       <c r="H68" t="n">
-        <v>-17.81442497</v>
+        <v>6.000725700000001</v>
       </c>
       <c r="I68" t="n">
-        <v>5.999381360000001</v>
+        <v>-0.7707804100000024</v>
       </c>
       <c r="J68" t="n">
-        <v>-0.7701470400000022</v>
+        <v>-37.88953521</v>
       </c>
       <c r="K68" t="n">
-        <v>-37.88870957</v>
+        <v>-10.25797633</v>
       </c>
       <c r="L68" t="n">
-        <v>-10.25846167</v>
+        <v>-18.96683493</v>
       </c>
       <c r="M68" t="n">
-        <v>-18.96851173</v>
+        <v>16.33818648</v>
       </c>
     </row>
     <row r="69">
@@ -3262,37 +3262,37 @@
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>-69.15763332999998</v>
+        <v>-43.12169323</v>
       </c>
       <c r="D69" t="n">
-        <v>-42.37237207</v>
+        <v>44.67736398</v>
       </c>
       <c r="E69" t="n">
-        <v>138.35960054</v>
+        <v>-30.20987664</v>
       </c>
       <c r="F69" t="n">
-        <v>141.94986474</v>
+        <v>53.93063466</v>
       </c>
       <c r="G69" t="n">
-        <v>459.24300491</v>
+        <v>-1.213785110000001</v>
       </c>
       <c r="H69" t="n">
-        <v>435.3790516</v>
+        <v>45.57241802999999</v>
       </c>
       <c r="I69" t="n">
-        <v>204.74831062</v>
+        <v>-27.11002662000001</v>
       </c>
       <c r="J69" t="n">
-        <v>153.38339688</v>
+        <v>-271.4762455</v>
       </c>
       <c r="K69" t="n">
-        <v>-260.69525017</v>
+        <v>-6.035967030000001</v>
       </c>
       <c r="L69" t="n">
-        <v>-100.01273259</v>
+        <v>-37.75509148</v>
       </c>
       <c r="M69" t="n">
-        <v>-176.70412707</v>
+        <v>-3.085999260000009</v>
       </c>
     </row>
     <row r="70">
@@ -3303,37 +3303,37 @@
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>-1.18870531</v>
+        <v>0.8999840899999999</v>
       </c>
       <c r="D70" t="n">
-        <v>0.8999840899999999</v>
+        <v>-1.07992369</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.07992369</v>
+        <v>-8.13542947</v>
       </c>
       <c r="F70" t="n">
-        <v>-8.13542947</v>
+        <v>-6.112742610000001</v>
       </c>
       <c r="G70" t="n">
-        <v>-6.112742610000001</v>
+        <v>0.62737845</v>
       </c>
       <c r="H70" t="n">
-        <v>0.62737845</v>
+        <v>-1.39124728</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.39124728</v>
+        <v>-3.48094111</v>
       </c>
       <c r="J70" t="n">
-        <v>-3.48094111</v>
+        <v>-5.56892512</v>
       </c>
       <c r="K70" t="n">
-        <v>-5.56892512</v>
+        <v>1.72853993</v>
       </c>
       <c r="L70" t="n">
-        <v>1.72853993</v>
+        <v>-2.4559021</v>
       </c>
       <c r="M70" t="n">
-        <v>-2.4559021</v>
+        <v>-1.44139782</v>
       </c>
     </row>
     <row r="71">
@@ -3344,37 +3344,37 @@
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
-        <v>0.93115824</v>
+        <v>0.15324129</v>
       </c>
       <c r="D71" t="n">
-        <v>0.15324129</v>
+        <v>2.0141396</v>
       </c>
       <c r="E71" t="n">
-        <v>2.0141396</v>
+        <v>0.94456732</v>
       </c>
       <c r="F71" t="n">
-        <v>0.94456732</v>
+        <v>1.31059385</v>
       </c>
       <c r="G71" t="n">
-        <v>1.31059385</v>
+        <v>0.44808132</v>
       </c>
       <c r="H71" t="n">
-        <v>0.44808132</v>
+        <v>1.02481299</v>
       </c>
       <c r="I71" t="n">
-        <v>1.02481299</v>
+        <v>0.39879786</v>
       </c>
       <c r="J71" t="n">
-        <v>0.39879786</v>
+        <v>-0.4558637</v>
       </c>
       <c r="K71" t="n">
-        <v>-0.4558637</v>
+        <v>0.5983068499999999</v>
       </c>
       <c r="L71" t="n">
-        <v>0.5983068499999999</v>
+        <v>3.41007278</v>
       </c>
       <c r="M71" t="n">
-        <v>3.41007278</v>
+        <v>3.07970445</v>
       </c>
     </row>
     <row r="72">
@@ -3385,37 +3385,37 @@
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>2.34425566</v>
+        <v>34.17125779</v>
       </c>
       <c r="D72" t="n">
-        <v>11.79920674</v>
+        <v>-3.0706811</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.8933656799999999</v>
+        <v>-7.127004649999999</v>
       </c>
       <c r="F72" t="n">
-        <v>-11.91034057</v>
+        <v>-16.45539349</v>
       </c>
       <c r="G72" t="n">
-        <v>-6.11659849</v>
+        <v>-1.46575611</v>
       </c>
       <c r="H72" t="n">
-        <v>-1.00781589</v>
+        <v>-28.70342079</v>
       </c>
       <c r="I72" t="n">
-        <v>-14.19481265</v>
+        <v>-30.10771701</v>
       </c>
       <c r="J72" t="n">
-        <v>-10.85873646</v>
+        <v>-17.75000963</v>
       </c>
       <c r="K72" t="n">
-        <v>-12.55970872</v>
+        <v>-16.20229139</v>
       </c>
       <c r="L72" t="n">
-        <v>-11.07626771</v>
+        <v>-16.02781221</v>
       </c>
       <c r="M72" t="n">
-        <v>-10.07216436</v>
+        <v>1.12072129</v>
       </c>
     </row>
     <row r="73">
@@ -3426,37 +3426,37 @@
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
-        <v>-37.30362026</v>
+        <v>-112.44551461</v>
       </c>
       <c r="D73" t="n">
-        <v>-103.56392674</v>
+        <v>-90.06517006999999</v>
       </c>
       <c r="E73" t="n">
-        <v>-54.40137722999999</v>
+        <v>-43.46545776000001</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.9121308300000042</v>
+        <v>51.29491169</v>
       </c>
       <c r="G73" t="n">
-        <v>111.99430636</v>
+        <v>59.22804754</v>
       </c>
       <c r="H73" t="n">
-        <v>111.66897061</v>
+        <v>-19.14230721</v>
       </c>
       <c r="I73" t="n">
-        <v>-3.999667890000003</v>
+        <v>-113.7462762</v>
       </c>
       <c r="J73" t="n">
-        <v>-119.43980218</v>
+        <v>-86.32584292</v>
       </c>
       <c r="K73" t="n">
-        <v>-105.75567652</v>
+        <v>28.64253698</v>
       </c>
       <c r="L73" t="n">
-        <v>15.98449054</v>
+        <v>18.30188621</v>
       </c>
       <c r="M73" t="n">
-        <v>-0.3143597500000023</v>
+        <v>99.68047403</v>
       </c>
     </row>
     <row r="74">
@@ -3467,37 +3467,37 @@
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
-        <v>-2.836418229999998</v>
+        <v>-30.54986415</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.484262</v>
+        <v>-15.30492149</v>
       </c>
       <c r="E74" t="n">
-        <v>-25.95807158</v>
+        <v>-8.88836045</v>
       </c>
       <c r="F74" t="n">
-        <v>-16.01571772</v>
+        <v>20.78246032</v>
       </c>
       <c r="G74" t="n">
-        <v>-2.69861123</v>
+        <v>-2.68761685</v>
       </c>
       <c r="H74" t="n">
-        <v>-8.47127513</v>
+        <v>-23.26769997</v>
       </c>
       <c r="I74" t="n">
-        <v>-35.61319028</v>
+        <v>-37.48475252</v>
       </c>
       <c r="J74" t="n">
-        <v>-49.26944099</v>
+        <v>-21.07048008</v>
       </c>
       <c r="K74" t="n">
-        <v>-13.72824796</v>
+        <v>2.66330312</v>
       </c>
       <c r="L74" t="n">
-        <v>6.17645051</v>
+        <v>-11.01034754</v>
       </c>
       <c r="M74" t="n">
-        <v>-8.167593669999999</v>
+        <v>1.25555076</v>
       </c>
     </row>
     <row r="75">
@@ -3508,37 +3508,37 @@
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
-        <v>703.0305864300001</v>
+        <v>664.72535027</v>
       </c>
       <c r="D75" t="n">
-        <v>664.72535027</v>
+        <v>656.9999549300001</v>
       </c>
       <c r="E75" t="n">
-        <v>656.9999549300001</v>
+        <v>922.40805115</v>
       </c>
       <c r="F75" t="n">
-        <v>922.40805115</v>
+        <v>1352.18679415</v>
       </c>
       <c r="G75" t="n">
-        <v>1352.18679415</v>
+        <v>443.55634693</v>
       </c>
       <c r="H75" t="n">
-        <v>443.55634693</v>
+        <v>296.15320315</v>
       </c>
       <c r="I75" t="n">
-        <v>296.15320315</v>
+        <v>-274.2499456</v>
       </c>
       <c r="J75" t="n">
-        <v>-274.2499456</v>
+        <v>-985.81143814</v>
       </c>
       <c r="K75" t="n">
-        <v>-985.81143814</v>
+        <v>-778.2785946499999</v>
       </c>
       <c r="L75" t="n">
-        <v>-778.2785946499999</v>
+        <v>-1087.35782134</v>
       </c>
       <c r="M75" t="n">
-        <v>-1087.35782134</v>
+        <v>-684.8153055399999</v>
       </c>
     </row>
     <row r="76">
@@ -3549,37 +3549,37 @@
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>-204.78989644</v>
+        <v>-366.08115125</v>
       </c>
       <c r="D76" t="n">
-        <v>-366.08115125</v>
+        <v>-487.8436765000001</v>
       </c>
       <c r="E76" t="n">
-        <v>-487.8436765000001</v>
+        <v>-231.09819764</v>
       </c>
       <c r="F76" t="n">
-        <v>-231.09819764</v>
+        <v>-6.482741509999999</v>
       </c>
       <c r="G76" t="n">
-        <v>-6.482741509999999</v>
+        <v>-64.07832381</v>
       </c>
       <c r="H76" t="n">
-        <v>-64.07832381</v>
+        <v>54.92950557</v>
       </c>
       <c r="I76" t="n">
-        <v>54.92950557</v>
+        <v>3.986776439999998</v>
       </c>
       <c r="J76" t="n">
-        <v>3.986776439999998</v>
+        <v>105.74435434</v>
       </c>
       <c r="K76" t="n">
-        <v>105.74435434</v>
+        <v>173.2930186</v>
       </c>
       <c r="L76" t="n">
-        <v>173.2930186</v>
+        <v>93.11041993999999</v>
       </c>
       <c r="M76" t="n">
-        <v>93.11041993999999</v>
+        <v>105.96609074</v>
       </c>
     </row>
     <row r="77">
@@ -3590,37 +3590,37 @@
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="n">
-        <v>4.28308841</v>
+        <v>43.59403532</v>
       </c>
       <c r="D77" t="n">
-        <v>43.59403532</v>
+        <v>29.20232021</v>
       </c>
       <c r="E77" t="n">
-        <v>29.20232021</v>
+        <v>37.35577211</v>
       </c>
       <c r="F77" t="n">
-        <v>37.35577211</v>
+        <v>81.95862364</v>
       </c>
       <c r="G77" t="n">
-        <v>81.95862364</v>
+        <v>50.95993046</v>
       </c>
       <c r="H77" t="n">
-        <v>50.95993046</v>
+        <v>16.85188228</v>
       </c>
       <c r="I77" t="n">
-        <v>16.85188228</v>
+        <v>-13.73904701</v>
       </c>
       <c r="J77" t="n">
-        <v>-13.73904701</v>
+        <v>-41.86073545</v>
       </c>
       <c r="K77" t="n">
-        <v>-41.86073545</v>
+        <v>-26.77418983</v>
       </c>
       <c r="L77" t="n">
-        <v>-26.77418983</v>
+        <v>-31.00716944</v>
       </c>
       <c r="M77" t="n">
-        <v>-31.00716944</v>
+        <v>19.97785319</v>
       </c>
     </row>
     <row r="78">
@@ -3631,37 +3631,37 @@
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
-        <v>0.00222055</v>
+        <v>0.00226234</v>
       </c>
       <c r="D78" t="n">
-        <v>0.00226234</v>
+        <v>0.00101082</v>
       </c>
       <c r="E78" t="n">
-        <v>0.00101082</v>
+        <v>9.988e-05</v>
       </c>
       <c r="F78" t="n">
-        <v>9.988e-05</v>
+        <v>0.00032912</v>
       </c>
       <c r="G78" t="n">
-        <v>0.00032912</v>
+        <v>-0.00052438</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.00052438</v>
+        <v>-9.99e-05</v>
       </c>
       <c r="I78" t="n">
-        <v>-9.99e-05</v>
+        <v>-0.00069427</v>
       </c>
       <c r="J78" t="n">
-        <v>-0.00069427</v>
+        <v>-0.00100544</v>
       </c>
       <c r="K78" t="n">
-        <v>-0.00100544</v>
+        <v>-0.00044273</v>
       </c>
       <c r="L78" t="n">
-        <v>-0.00044273</v>
+        <v>-0.00079249</v>
       </c>
       <c r="M78" t="n">
-        <v>-0.00079249</v>
+        <v>-0.0010202</v>
       </c>
     </row>
     <row r="79">
@@ -3672,37 +3672,37 @@
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="n">
-        <v>0.00481058</v>
+        <v>0.00272902</v>
       </c>
       <c r="D79" t="n">
-        <v>0.00272902</v>
+        <v>9.011000000000007e-05</v>
       </c>
       <c r="E79" t="n">
-        <v>9.011000000000007e-05</v>
+        <v>0.0004795100000000002</v>
       </c>
       <c r="F79" t="n">
-        <v>0.0004795100000000002</v>
+        <v>0.00329986</v>
       </c>
       <c r="G79" t="n">
-        <v>0.00329986</v>
+        <v>0.0005099499999999999</v>
       </c>
       <c r="H79" t="n">
-        <v>0.0005099499999999999</v>
+        <v>-0.0007658099999999999</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.0007658099999999999</v>
+        <v>0.0034501</v>
       </c>
       <c r="J79" t="n">
-        <v>0.0034501</v>
+        <v>0.0005688300000000001</v>
       </c>
       <c r="K79" t="n">
-        <v>0.0005688300000000001</v>
+        <v>0.00248966</v>
       </c>
       <c r="L79" t="n">
-        <v>0.00248966</v>
+        <v>0.00048036</v>
       </c>
       <c r="M79" t="n">
-        <v>0.00048036</v>
+        <v>0.00267611</v>
       </c>
     </row>
     <row r="80">
@@ -3713,37 +3713,37 @@
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="n">
-        <v>0.00057835</v>
+        <v>9.465e-05</v>
       </c>
       <c r="D80" t="n">
-        <v>9.465e-05</v>
+        <v>0.00013897</v>
       </c>
       <c r="E80" t="n">
-        <v>0.00013897</v>
+        <v>6.415e-05</v>
       </c>
       <c r="F80" t="n">
-        <v>6.415e-05</v>
+        <v>-0.00029419</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.00029419</v>
+        <v>0.00019073</v>
       </c>
       <c r="H80" t="n">
-        <v>0.00019073</v>
+        <v>-2.111999999999998e-05</v>
       </c>
       <c r="I80" t="n">
-        <v>-2.111999999999998e-05</v>
+        <v>0.00040195</v>
       </c>
       <c r="J80" t="n">
-        <v>0.00040195</v>
+        <v>7.686999999999999e-05</v>
       </c>
       <c r="K80" t="n">
-        <v>7.686999999999999e-05</v>
+        <v>-0.00026166</v>
       </c>
       <c r="L80" t="n">
-        <v>-0.00026166</v>
+        <v>-0.0005340900000000001</v>
       </c>
       <c r="M80" t="n">
-        <v>-0.0005340900000000001</v>
+        <v>-0.0005954199999999999</v>
       </c>
     </row>
     <row r="81">
@@ -3754,37 +3754,37 @@
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>-9.68964107</v>
+        <v>4.868124629999999</v>
       </c>
       <c r="D81" t="n">
-        <v>4.868124629999999</v>
+        <v>12.18883922</v>
       </c>
       <c r="E81" t="n">
-        <v>12.18883922</v>
+        <v>-4.46799539</v>
       </c>
       <c r="F81" t="n">
-        <v>-4.46799539</v>
+        <v>12.58299348</v>
       </c>
       <c r="G81" t="n">
-        <v>12.58299348</v>
+        <v>17.39570309</v>
       </c>
       <c r="H81" t="n">
-        <v>17.39570309</v>
+        <v>13.14604495</v>
       </c>
       <c r="I81" t="n">
-        <v>13.14604495</v>
+        <v>10.09760665</v>
       </c>
       <c r="J81" t="n">
-        <v>10.09760665</v>
+        <v>-4.54740078</v>
       </c>
       <c r="K81" t="n">
-        <v>-4.54740078</v>
+        <v>-6.45092565</v>
       </c>
       <c r="L81" t="n">
-        <v>-6.45092565</v>
+        <v>6.51069558</v>
       </c>
       <c r="M81" t="n">
-        <v>6.51069558</v>
+        <v>8.6084934</v>
       </c>
     </row>
     <row r="82">
@@ -3795,37 +3795,37 @@
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
-        <v>-27.20367006</v>
+        <v>-12.37892165</v>
       </c>
       <c r="D82" t="n">
-        <v>-6.816274809999999</v>
+        <v>35.57833775000001</v>
       </c>
       <c r="E82" t="n">
-        <v>35.92285662</v>
+        <v>103.69589147</v>
       </c>
       <c r="F82" t="n">
-        <v>100.00606942</v>
+        <v>139.13297302</v>
       </c>
       <c r="G82" t="n">
-        <v>140.42826357</v>
+        <v>240.71997013</v>
       </c>
       <c r="H82" t="n">
-        <v>246.03555927</v>
+        <v>141.93008833</v>
       </c>
       <c r="I82" t="n">
-        <v>140.30381642</v>
+        <v>51.90220972</v>
       </c>
       <c r="J82" t="n">
-        <v>44.57152598</v>
+        <v>-46.60353782</v>
       </c>
       <c r="K82" t="n">
-        <v>-57.69820552</v>
+        <v>14.43417106</v>
       </c>
       <c r="L82" t="n">
-        <v>9.688398300000001</v>
+        <v>-48.01741027000001</v>
       </c>
       <c r="M82" t="n">
-        <v>-54.93659078</v>
+        <v>-21.48938138</v>
       </c>
     </row>
     <row r="83">
@@ -3836,37 +3836,37 @@
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>79.56018324999999</v>
+        <v>-156.69422532</v>
       </c>
       <c r="D83" t="n">
-        <v>-162.25687216</v>
+        <v>-346.53778598</v>
       </c>
       <c r="E83" t="n">
-        <v>-346.88230485</v>
+        <v>-550.58035437</v>
       </c>
       <c r="F83" t="n">
-        <v>-546.89053232</v>
+        <v>-284.21347723</v>
       </c>
       <c r="G83" t="n">
-        <v>-285.50876778</v>
+        <v>-162.02377714</v>
       </c>
       <c r="H83" t="n">
-        <v>-167.33936628</v>
+        <v>60.68173664</v>
       </c>
       <c r="I83" t="n">
-        <v>62.30800855</v>
+        <v>-41.88851007000001</v>
       </c>
       <c r="J83" t="n">
-        <v>-34.55782633</v>
+        <v>-183.24712254</v>
       </c>
       <c r="K83" t="n">
-        <v>-172.15245484</v>
+        <v>-26.27994081999999</v>
       </c>
       <c r="L83" t="n">
-        <v>-21.53416806</v>
+        <v>-38.22303753</v>
       </c>
       <c r="M83" t="n">
-        <v>-31.30385702</v>
+        <v>-33.87690692</v>
       </c>
     </row>
     <row r="84">
@@ -3877,37 +3877,37 @@
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
-        <v>-15.21283794</v>
+        <v>-20.03139617</v>
       </c>
       <c r="D84" t="n">
-        <v>-17.71552102</v>
+        <v>-59.64161756</v>
       </c>
       <c r="E84" t="n">
-        <v>-64.05499739</v>
+        <v>-112.75539681</v>
       </c>
       <c r="F84" t="n">
-        <v>-108.28490628</v>
+        <v>64.56145398</v>
       </c>
       <c r="G84" t="n">
-        <v>17.23501362</v>
+        <v>-54.95076079</v>
       </c>
       <c r="H84" t="n">
-        <v>-42.91166961</v>
+        <v>-5.751428920000002</v>
       </c>
       <c r="I84" t="n">
-        <v>-16.22533502</v>
+        <v>-18.06551288</v>
       </c>
       <c r="J84" t="n">
-        <v>-7.978113619999998</v>
+        <v>-59.30750037</v>
       </c>
       <c r="K84" t="n">
-        <v>-41.15140009</v>
+        <v>-37.87471119</v>
       </c>
       <c r="L84" t="n">
-        <v>-27.68817933</v>
+        <v>80.34547319000001</v>
       </c>
       <c r="M84" t="n">
-        <v>80.22766098000001</v>
+        <v>11.13889726</v>
       </c>
     </row>
     <row r="85">
@@ -3918,37 +3918,37 @@
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>50.4358599</v>
+        <v>20.67695317</v>
       </c>
       <c r="D85" t="n">
-        <v>20.67695317</v>
+        <v>39.12531966</v>
       </c>
       <c r="E85" t="n">
-        <v>39.12531966</v>
+        <v>82.69031135000002</v>
       </c>
       <c r="F85" t="n">
-        <v>82.69031135000002</v>
+        <v>154.59545891</v>
       </c>
       <c r="G85" t="n">
-        <v>154.59545891</v>
+        <v>58.71590928</v>
       </c>
       <c r="H85" t="n">
-        <v>58.71590928</v>
+        <v>121.63718761</v>
       </c>
       <c r="I85" t="n">
-        <v>121.63718761</v>
+        <v>29.61562639</v>
       </c>
       <c r="J85" t="n">
-        <v>29.61562639</v>
+        <v>-24.78285621</v>
       </c>
       <c r="K85" t="n">
-        <v>-24.78285621</v>
+        <v>2.232190660000001</v>
       </c>
       <c r="L85" t="n">
-        <v>2.232190660000001</v>
+        <v>28.4317957</v>
       </c>
       <c r="M85" t="n">
-        <v>28.4317957</v>
+        <v>57.24179094000001</v>
       </c>
     </row>
     <row r="86">
@@ -3959,37 +3959,37 @@
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
-        <v>127.17974363</v>
+        <v>37.83571189</v>
       </c>
       <c r="D86" t="n">
-        <v>35.51983674</v>
+        <v>-48.80012199</v>
       </c>
       <c r="E86" t="n">
-        <v>-44.38674216</v>
+        <v>-75.86895855</v>
       </c>
       <c r="F86" t="n">
-        <v>-80.33944907999999</v>
+        <v>-29.96102533</v>
       </c>
       <c r="G86" t="n">
-        <v>17.36541503</v>
+        <v>-10.1905005</v>
       </c>
       <c r="H86" t="n">
-        <v>-22.22959168</v>
+        <v>26.19259462</v>
       </c>
       <c r="I86" t="n">
-        <v>36.66650072</v>
+        <v>-37.08723535</v>
       </c>
       <c r="J86" t="n">
-        <v>-47.17463461</v>
+        <v>-54.5866125</v>
       </c>
       <c r="K86" t="n">
-        <v>-72.74271278000001</v>
+        <v>-18.81284465</v>
       </c>
       <c r="L86" t="n">
-        <v>-28.99937651</v>
+        <v>182.97717342</v>
       </c>
       <c r="M86" t="n">
-        <v>183.09498563</v>
+        <v>197.89802178</v>
       </c>
     </row>
     <row r="87">
@@ -4000,37 +4000,37 @@
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>-120.38566029</v>
+        <v>-28.81381812999999</v>
       </c>
       <c r="D87" t="n">
-        <v>-28.81164552</v>
+        <v>26.42774728</v>
       </c>
       <c r="E87" t="n">
-        <v>26.43296405</v>
+        <v>-19.94111825</v>
       </c>
       <c r="F87" t="n">
-        <v>-19.93985403</v>
+        <v>-44.01763501999999</v>
       </c>
       <c r="G87" t="n">
-        <v>-44.01196087</v>
+        <v>-47.84203079000001</v>
       </c>
       <c r="H87" t="n">
-        <v>-47.8348988</v>
+        <v>-49.89427655999999</v>
       </c>
       <c r="I87" t="n">
-        <v>-49.88927837</v>
+        <v>-54.41166398000001</v>
       </c>
       <c r="J87" t="n">
-        <v>-54.40417066000001</v>
+        <v>-32.85760689999999</v>
       </c>
       <c r="K87" t="n">
-        <v>-32.8497037</v>
+        <v>-6.351773119999999</v>
       </c>
       <c r="L87" t="n">
-        <v>-6.345934729999999</v>
+        <v>-1.646291149999999</v>
       </c>
       <c r="M87" t="n">
-        <v>-1.639802489999999</v>
+        <v>-3.378789089999999</v>
       </c>
     </row>
     <row r="88">
@@ -4041,37 +4041,37 @@
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
-        <v>-68.99436043</v>
+        <v>-151.21548459</v>
       </c>
       <c r="D88" t="n">
-        <v>-152.61663408</v>
+        <v>-178.71663721</v>
       </c>
       <c r="E88" t="n">
-        <v>-178.63626288</v>
+        <v>-165.20137837</v>
       </c>
       <c r="F88" t="n">
-        <v>-166.39774649</v>
+        <v>-124.54174007</v>
       </c>
       <c r="G88" t="n">
-        <v>-126.75647098</v>
+        <v>-106.78165992</v>
       </c>
       <c r="H88" t="n">
-        <v>-109.66933011</v>
+        <v>-91.03741243</v>
       </c>
       <c r="I88" t="n">
-        <v>-91.38142356</v>
+        <v>-86.13555061</v>
       </c>
       <c r="J88" t="n">
-        <v>-87.53869095</v>
+        <v>-87.44654795000001</v>
       </c>
       <c r="K88" t="n">
-        <v>-90.77649375</v>
+        <v>-4.868710070000001</v>
       </c>
       <c r="L88" t="n">
-        <v>-6.19971842</v>
+        <v>-2.5670926</v>
       </c>
       <c r="M88" t="n">
-        <v>-2.30105065</v>
+        <v>46.79332676999999</v>
       </c>
     </row>
     <row r="89">
@@ -4082,37 +4082,37 @@
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>2.532449130000001</v>
+        <v>-24.75103522</v>
       </c>
       <c r="D89" t="n">
-        <v>-23.35205834</v>
+        <v>-0.5552454900000002</v>
       </c>
       <c r="E89" t="n">
-        <v>-0.6408365900000008</v>
+        <v>-23.51821969</v>
       </c>
       <c r="F89" t="n">
-        <v>-22.32311579</v>
+        <v>-45.03127467</v>
       </c>
       <c r="G89" t="n">
-        <v>-42.82221791</v>
+        <v>-38.2276574</v>
       </c>
       <c r="H89" t="n">
-        <v>-35.3471192</v>
+        <v>-4.496576600000002</v>
       </c>
       <c r="I89" t="n">
-        <v>-4.157563660000003</v>
+        <v>19.56919944000001</v>
       </c>
       <c r="J89" t="n">
-        <v>20.96484646</v>
+        <v>-30.00397083</v>
       </c>
       <c r="K89" t="n">
-        <v>-26.68192823</v>
+        <v>-1.050786630000001</v>
       </c>
       <c r="L89" t="n">
-        <v>0.2743833299999991</v>
+        <v>-1.2652398</v>
       </c>
       <c r="M89" t="n">
-        <v>-1.53777041</v>
+        <v>31.74611091</v>
       </c>
     </row>
     <row r="90">
@@ -4123,37 +4123,37 @@
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>3437.1076367</v>
+        <v>5013.59351741</v>
       </c>
       <c r="D90" t="n">
-        <v>5003.764407600001</v>
+        <v>4791.73900212</v>
       </c>
       <c r="E90" t="n">
-        <v>4906.96545566</v>
+        <v>4658.85393492</v>
       </c>
       <c r="F90" t="n">
-        <v>5010.823842260001</v>
+        <v>4408.64397935</v>
       </c>
       <c r="G90" t="n">
-        <v>4978.2651254</v>
+        <v>3138.16459025</v>
       </c>
       <c r="H90" t="n">
-        <v>3566.80830261</v>
+        <v>4955.01890784</v>
       </c>
       <c r="I90" t="n">
-        <v>5064.9559481</v>
+        <v>-167.2249789299999</v>
       </c>
       <c r="J90" t="n">
-        <v>-157.8201205099999</v>
+        <v>-7352.57627379</v>
       </c>
       <c r="K90" t="n">
-        <v>-7292.96027817</v>
+        <v>-1795.69875686</v>
       </c>
       <c r="L90" t="n">
-        <v>-1993.57493408</v>
+        <v>-1454.15170394</v>
       </c>
       <c r="M90" t="n">
-        <v>-1804.29618513</v>
+        <v>1616.93093978</v>
       </c>
     </row>
     <row r="91">
@@ -4162,39 +4162,41 @@
           <t>電子零組件業右下</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr"/>
+      <c r="B91" t="n">
+        <v>0</v>
+      </c>
       <c r="C91" t="n">
-        <v>-377.24334702</v>
+        <v>-232.77012718</v>
       </c>
       <c r="D91" t="n">
-        <v>-0.1189399000000008</v>
+        <v>-192.04278906</v>
       </c>
       <c r="E91" t="n">
-        <v>-339.12723307</v>
+        <v>-141.80255674</v>
       </c>
       <c r="F91" t="n">
-        <v>-800.1076148299999</v>
+        <v>-31.47501537999999</v>
       </c>
       <c r="G91" t="n">
-        <v>-1014.25226514</v>
+        <v>-4.792802999999996</v>
       </c>
       <c r="H91" t="n">
-        <v>-1121.53466632</v>
+        <v>70.29331661000001</v>
       </c>
       <c r="I91" t="n">
-        <v>-237.92571143</v>
+        <v>20.1303095</v>
       </c>
       <c r="J91" t="n">
-        <v>-627.0042389600001</v>
+        <v>-151.5226142</v>
       </c>
       <c r="K91" t="n">
-        <v>-962.2922248199999</v>
+        <v>-125.63105268</v>
       </c>
       <c r="L91" t="n">
-        <v>-926.08295719</v>
+        <v>-144.50760609</v>
       </c>
       <c r="M91" t="n">
-        <v>-606.1103015699999</v>
+        <v>-399.04905734</v>
       </c>
     </row>
     <row r="92">
@@ -4205,37 +4207,37 @@
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>-506.7184730000001</v>
+        <v>-59.01995913000001</v>
       </c>
       <c r="D92" t="n">
-        <v>-290.0204477</v>
+        <v>-610.41892137</v>
       </c>
       <c r="E92" t="n">
-        <v>-597.93750475</v>
+        <v>-1129.32971682</v>
       </c>
       <c r="F92" t="n">
-        <v>-781.38963261</v>
+        <v>-1488.31761327</v>
       </c>
       <c r="G92" t="n">
-        <v>-1004.37468099</v>
+        <v>-1713.15918779</v>
       </c>
       <c r="H92" t="n">
-        <v>-997.9899978200001</v>
+        <v>-441.787569</v>
       </c>
       <c r="I92" t="n">
-        <v>-250.64928035</v>
+        <v>-1240.01061707</v>
       </c>
       <c r="J92" t="n">
-        <v>-632.39691376</v>
+        <v>-1522.75062881</v>
       </c>
       <c r="K92" t="n">
-        <v>-839.82501909</v>
+        <v>-1193.92058097</v>
       </c>
       <c r="L92" t="n">
-        <v>-282.89371407</v>
+        <v>-693.45400337</v>
       </c>
       <c r="M92" t="n">
-        <v>112.59140298</v>
+        <v>104.04502505</v>
       </c>
     </row>
     <row r="93">
@@ -4246,37 +4248,37 @@
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>-136.1838183</v>
+        <v>29.71415371999997</v>
       </c>
       <c r="D93" t="n">
-        <v>27.32669066999999</v>
+        <v>-1156.99023944</v>
       </c>
       <c r="E93" t="n">
-        <v>-1166.72366356</v>
+        <v>-26.03845825999992</v>
       </c>
       <c r="F93" t="n">
-        <v>-134.7618539499999</v>
+        <v>-147.76099303</v>
       </c>
       <c r="G93" t="n">
-        <v>-348.45785955</v>
+        <v>-473.76629232</v>
       </c>
       <c r="H93" t="n">
-        <v>-562.59891296</v>
+        <v>527.39559712</v>
       </c>
       <c r="I93" t="n">
-        <v>388.9696313000001</v>
+        <v>-553.72042884</v>
       </c>
       <c r="J93" t="n">
-        <v>-551.4057077799999</v>
+        <v>-1330.18010929</v>
       </c>
       <c r="K93" t="n">
-        <v>-1249.21055614</v>
+        <v>-183.27167003</v>
       </c>
       <c r="L93" t="n">
-        <v>-158.11036754</v>
+        <v>520.01654746</v>
       </c>
       <c r="M93" t="n">
-        <v>585.74591515</v>
+        <v>1617.76196555</v>
       </c>
     </row>
     <row r="94">
@@ -4285,41 +4287,39 @@
           <t>電機機械右下</t>
         </is>
       </c>
-      <c r="B94" t="n">
-        <v>0</v>
-      </c>
+      <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>97.14610656000001</v>
+        <v>-36.02857814</v>
       </c>
       <c r="D94" t="n">
-        <v>65.14342585000001</v>
+        <v>-52.44089580999999</v>
       </c>
       <c r="E94" t="n">
-        <v>-20.06649955</v>
+        <v>-65.62257774999999</v>
       </c>
       <c r="F94" t="n">
-        <v>-141.52683754</v>
+        <v>13.83024299</v>
       </c>
       <c r="G94" t="n">
-        <v>-80.82072712999999</v>
+        <v>15.47936881</v>
       </c>
       <c r="H94" t="n">
-        <v>4.55290634</v>
+        <v>19.90884591</v>
       </c>
       <c r="I94" t="n">
-        <v>157.2409152</v>
+        <v>-18.30392559</v>
       </c>
       <c r="J94" t="n">
-        <v>-5.070559200000001</v>
+        <v>-42.2155003</v>
       </c>
       <c r="K94" t="n">
-        <v>-120.0217427</v>
+        <v>33.96449188</v>
       </c>
       <c r="L94" t="n">
-        <v>23.66297122</v>
+        <v>124.52772625</v>
       </c>
       <c r="M94" t="n">
-        <v>73.77609545</v>
+        <v>297.19095941</v>
       </c>
     </row>
     <row r="95">
@@ -4330,37 +4330,37 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>95.25114665000001</v>
+        <v>104.03364072</v>
       </c>
       <c r="D95" t="n">
-        <v>46.33083919</v>
+        <v>121.84924191</v>
       </c>
       <c r="E95" t="n">
-        <v>104.84364026</v>
+        <v>23.69326932999998</v>
       </c>
       <c r="F95" t="n">
-        <v>125.99662354</v>
+        <v>89.57657908000002</v>
       </c>
       <c r="G95" t="n">
-        <v>188.72893597</v>
+        <v>229.60383307</v>
       </c>
       <c r="H95" t="n">
-        <v>253.03523157</v>
+        <v>267.81091467</v>
       </c>
       <c r="I95" t="n">
-        <v>144.4213577</v>
+        <v>163.92629922</v>
       </c>
       <c r="J95" t="n">
-        <v>149.18000524</v>
+        <v>-104.12319884</v>
       </c>
       <c r="K95" t="n">
-        <v>-40.54632524</v>
+        <v>-1.618122270000001</v>
       </c>
       <c r="L95" t="n">
-        <v>-0.6189107100000008</v>
+        <v>-106.12360277</v>
       </c>
       <c r="M95" t="n">
-        <v>-70.00695528</v>
+        <v>158.26178347</v>
       </c>
     </row>
     <row r="96">
@@ -4371,37 +4371,37 @@
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>1949.37727356</v>
+        <v>2905.05954319</v>
       </c>
       <c r="D96" t="n">
-        <v>1833.67778779</v>
+        <v>401.3709961599999</v>
       </c>
       <c r="E96" t="n">
-        <v>713.9447243099999</v>
+        <v>-3405.02325223</v>
       </c>
       <c r="F96" t="n">
-        <v>-27.01846356999978</v>
+        <v>-3815.60537313</v>
       </c>
       <c r="G96" t="n">
-        <v>-311.7008039900001</v>
+        <v>-3123.93030206</v>
       </c>
       <c r="H96" t="n">
-        <v>330.2456217000001</v>
+        <v>-3084.78117262</v>
       </c>
       <c r="I96" t="n">
-        <v>58.89255754999999</v>
+        <v>-3734.07373899</v>
       </c>
       <c r="J96" t="n">
-        <v>-1052.89750497</v>
+        <v>-6830.49529395</v>
       </c>
       <c r="K96" t="n">
-        <v>-4051.10333506</v>
+        <v>-3911.573518109999</v>
       </c>
       <c r="L96" t="n">
-        <v>-1316.24999344</v>
+        <v>-4223.832838849999</v>
       </c>
       <c r="M96" t="n">
-        <v>-2562.04027985</v>
+        <v>128.9646278899999</v>
       </c>
     </row>
     <row r="97">
@@ -4412,37 +4412,37 @@
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>-390.66800273</v>
+        <v>-571.0470705499999</v>
       </c>
       <c r="D97" t="n">
-        <v>-572.8410040900001</v>
+        <v>-660.42543496</v>
       </c>
       <c r="E97" t="n">
-        <v>-662.76767952</v>
+        <v>-743.33638173</v>
       </c>
       <c r="F97" t="n">
-        <v>-743.89748664</v>
+        <v>-759.53682237</v>
       </c>
       <c r="G97" t="n">
-        <v>-758.00109288</v>
+        <v>-585.64289834</v>
       </c>
       <c r="H97" t="n">
-        <v>-582.72498698</v>
+        <v>-502.6904276</v>
       </c>
       <c r="I97" t="n">
-        <v>-492.98747729</v>
+        <v>-426.6017235</v>
       </c>
       <c r="J97" t="n">
-        <v>-394.5598874</v>
+        <v>-465.38007605</v>
       </c>
       <c r="K97" t="n">
-        <v>-450.82742394</v>
+        <v>-209.15082239</v>
       </c>
       <c r="L97" t="n">
-        <v>-195.19992286</v>
+        <v>-134.58597339</v>
       </c>
       <c r="M97" t="n">
-        <v>-103.30729146</v>
+        <v>368.88771678</v>
       </c>
     </row>
     <row r="98">
@@ -4453,37 +4453,37 @@
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
-        <v>1536.70366566</v>
+        <v>145.46712666</v>
       </c>
       <c r="D98" t="n">
-        <v>1218.6428156</v>
+        <v>-4.492891670000001</v>
       </c>
       <c r="E98" t="n">
-        <v>-314.7243752599999</v>
+        <v>95.88561462</v>
       </c>
       <c r="F98" t="n">
-        <v>-3281.55806913</v>
+        <v>-42.83531533000001</v>
       </c>
       <c r="G98" t="n">
-        <v>-3548.27561396</v>
+        <v>-164.25828058</v>
       </c>
       <c r="H98" t="n">
-        <v>-3621.3521157</v>
+        <v>-87.40913046</v>
       </c>
       <c r="I98" t="n">
-        <v>-3240.785810939999</v>
+        <v>25.19258487</v>
       </c>
       <c r="J98" t="n">
-        <v>-2688.02548525</v>
+        <v>-166.22357102</v>
       </c>
       <c r="K98" t="n">
-        <v>-2960.16818202</v>
+        <v>-51.52929649000001</v>
       </c>
       <c r="L98" t="n">
-        <v>-2660.80372069</v>
+        <v>-116.82267563</v>
       </c>
       <c r="M98" t="n">
-        <v>-1809.89391656</v>
+        <v>19.44349946</v>
       </c>
     </row>
     <row r="99">
@@ -4494,37 +4494,37 @@
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>2.43043327</v>
+        <v>3.42453723</v>
       </c>
       <c r="D99" t="n">
-        <v>3.42453723</v>
+        <v>20.0696195</v>
       </c>
       <c r="E99" t="n">
-        <v>20.0696195</v>
+        <v>29.27378089</v>
       </c>
       <c r="F99" t="n">
-        <v>29.27378089</v>
+        <v>17.24417347</v>
       </c>
       <c r="G99" t="n">
-        <v>17.24417347</v>
+        <v>24.68333282</v>
       </c>
       <c r="H99" t="n">
-        <v>24.68333282</v>
+        <v>34.23585004</v>
       </c>
       <c r="I99" t="n">
-        <v>34.23585004</v>
+        <v>36.69660673999999</v>
       </c>
       <c r="J99" t="n">
-        <v>36.69660673999999</v>
+        <v>25.24661327</v>
       </c>
       <c r="K99" t="n">
-        <v>25.24661327</v>
+        <v>13.11654365</v>
       </c>
       <c r="L99" t="n">
-        <v>13.11654365</v>
+        <v>-6.82524702</v>
       </c>
       <c r="M99" t="n">
-        <v>-6.82524702</v>
+        <v>-22.07105331</v>
       </c>
     </row>
     <row r="100">
@@ -4535,37 +4535,37 @@
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="n">
-        <v>-1.47041395</v>
+        <v>-12.68539322</v>
       </c>
       <c r="D100" t="n">
-        <v>-12.68523507</v>
+        <v>-16.25013197</v>
       </c>
       <c r="E100" t="n">
-        <v>-16.25005949</v>
+        <v>-10.87956181</v>
       </c>
       <c r="F100" t="n">
-        <v>-10.87937043</v>
+        <v>4.361418260000001</v>
       </c>
       <c r="G100" t="n">
-        <v>4.36138133</v>
+        <v>2.551020509999999</v>
       </c>
       <c r="H100" t="n">
-        <v>2.550761389999999</v>
+        <v>5.33199266</v>
       </c>
       <c r="I100" t="n">
-        <v>5.33204738</v>
+        <v>7.81839165</v>
       </c>
       <c r="J100" t="n">
-        <v>7.818490239999999</v>
+        <v>-4.54553314</v>
       </c>
       <c r="K100" t="n">
-        <v>-4.54547223</v>
+        <v>7.622740110000001</v>
       </c>
       <c r="L100" t="n">
-        <v>7.6226877</v>
+        <v>6.635783129999999</v>
       </c>
       <c r="M100" t="n">
-        <v>6.635682029999999</v>
+        <v>9.99111613</v>
       </c>
     </row>
     <row r="101">
@@ -4576,37 +4576,37 @@
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
-        <v>-218.54624147</v>
+        <v>-239.31343198</v>
       </c>
       <c r="D101" t="n">
-        <v>-239.31343198</v>
+        <v>-229.82111553</v>
       </c>
       <c r="E101" t="n">
-        <v>-229.82111553</v>
+        <v>-223.33650541</v>
       </c>
       <c r="F101" t="n">
-        <v>-223.33650541</v>
+        <v>-73.25820245</v>
       </c>
       <c r="G101" t="n">
-        <v>-73.25820245</v>
+        <v>16.35519561</v>
       </c>
       <c r="H101" t="n">
-        <v>16.35519561</v>
+        <v>-17.97346777</v>
       </c>
       <c r="I101" t="n">
-        <v>-17.97346777</v>
+        <v>-34.65812325</v>
       </c>
       <c r="J101" t="n">
-        <v>-34.65812325</v>
+        <v>-47.58972109</v>
       </c>
       <c r="K101" t="n">
-        <v>-47.58972109</v>
+        <v>62.04757827</v>
       </c>
       <c r="L101" t="n">
-        <v>62.04757827</v>
+        <v>17.0858512</v>
       </c>
       <c r="M101" t="n">
-        <v>17.0858512</v>
+        <v>85.30745282999999</v>
       </c>
     </row>
   </sheetData>

--- a/Result/analyze_2.xlsx
+++ b/Result/analyze_2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M101"/>
+  <dimension ref="A1:M100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
     </row>
@@ -503,37 +503,37 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>797.9680631</v>
+        <v>756.68650825</v>
       </c>
       <c r="D2" t="n">
-        <v>756.5434718099999</v>
+        <v>1794.74592754</v>
       </c>
       <c r="E2" t="n">
-        <v>1795.35936574</v>
+        <v>-150.38968488</v>
       </c>
       <c r="F2" t="n">
-        <v>-149.20933828</v>
+        <v>98.64851412999998</v>
       </c>
       <c r="G2" t="n">
-        <v>97.92280796</v>
+        <v>224.8790239</v>
       </c>
       <c r="H2" t="n">
-        <v>222.53991865</v>
+        <v>-93.22831414999997</v>
       </c>
       <c r="I2" t="n">
-        <v>-93.61492202999999</v>
+        <v>-892.089431</v>
       </c>
       <c r="J2" t="n">
-        <v>-894.43254129</v>
+        <v>-233.36954077</v>
       </c>
       <c r="K2" t="n">
-        <v>-234.40686299</v>
+        <v>-621.5591128899999</v>
       </c>
       <c r="L2" t="n">
-        <v>-620.9509553400001</v>
+        <v>548.97550104</v>
       </c>
       <c r="M2" t="n">
-        <v>552.3066825500001</v>
+        <v>287.70347311</v>
       </c>
     </row>
     <row r="3">
@@ -544,37 +544,37 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>32.44665509</v>
+        <v>121.68627221</v>
       </c>
       <c r="D3" t="n">
-        <v>126.68079483</v>
+        <v>125.42579632</v>
       </c>
       <c r="E3" t="n">
-        <v>127.30804794</v>
+        <v>101.45459925</v>
       </c>
       <c r="F3" t="n">
-        <v>106.12652779</v>
+        <v>177.69254748</v>
       </c>
       <c r="G3" t="n">
-        <v>194.37430686</v>
+        <v>265.54693157</v>
       </c>
       <c r="H3" t="n">
-        <v>285.69424378</v>
+        <v>205.61338718</v>
       </c>
       <c r="I3" t="n">
-        <v>221.28333162</v>
+        <v>-8.991332590000003</v>
       </c>
       <c r="J3" t="n">
-        <v>-8.367861130000001</v>
+        <v>267.62429922</v>
       </c>
       <c r="K3" t="n">
-        <v>278.79872496</v>
+        <v>-22.2832707</v>
       </c>
       <c r="L3" t="n">
-        <v>-8.181877210000003</v>
+        <v>55.74061373000001</v>
       </c>
       <c r="M3" t="n">
-        <v>64.78335676</v>
+        <v>-21.19819757</v>
       </c>
     </row>
     <row r="4">
@@ -585,37 +585,37 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>3.834606890000008</v>
+        <v>-53.51867572000001</v>
       </c>
       <c r="D4" t="n">
-        <v>-56.59616733000001</v>
+        <v>-70.54500037000001</v>
       </c>
       <c r="E4" t="n">
-        <v>-72.94745936000001</v>
+        <v>-151.84248622</v>
       </c>
       <c r="F4" t="n">
-        <v>-156.15998314</v>
+        <v>-158.6562986</v>
       </c>
       <c r="G4" t="n">
-        <v>-172.03063363</v>
+        <v>91.56319833999999</v>
       </c>
       <c r="H4" t="n">
-        <v>77.19033728999999</v>
+        <v>182.81530372</v>
       </c>
       <c r="I4" t="n">
-        <v>169.48177125</v>
+        <v>-123.30427425</v>
       </c>
       <c r="J4" t="n">
-        <v>-121.17329731</v>
+        <v>91.52964345000001</v>
       </c>
       <c r="K4" t="n">
-        <v>82.40051088</v>
+        <v>-46.82294983</v>
       </c>
       <c r="L4" t="n">
-        <v>-61.24672998</v>
+        <v>91.50523982</v>
       </c>
       <c r="M4" t="n">
-        <v>80.31131538</v>
+        <v>93.49837962000001</v>
       </c>
     </row>
     <row r="5">
@@ -626,37 +626,37 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>-428.94029793</v>
+        <v>-414.56281904</v>
       </c>
       <c r="D5" t="n">
-        <v>-414.56281904</v>
+        <v>-487.76732049</v>
       </c>
       <c r="E5" t="n">
-        <v>-487.76732049</v>
+        <v>-416.49802748</v>
       </c>
       <c r="F5" t="n">
-        <v>-416.49802748</v>
+        <v>-353.20717254</v>
       </c>
       <c r="G5" t="n">
-        <v>-353.20717254</v>
+        <v>-249.69010529</v>
       </c>
       <c r="H5" t="n">
-        <v>-249.69010529</v>
+        <v>-355.58396056</v>
       </c>
       <c r="I5" t="n">
-        <v>-355.58396056</v>
+        <v>-426.60047145</v>
       </c>
       <c r="J5" t="n">
-        <v>-426.60047145</v>
+        <v>-314.10521795</v>
       </c>
       <c r="K5" t="n">
-        <v>-314.10521795</v>
+        <v>246.88207098</v>
       </c>
       <c r="L5" t="n">
-        <v>246.88207098</v>
+        <v>389.30943271</v>
       </c>
       <c r="M5" t="n">
-        <v>389.30943271</v>
+        <v>538.2064277899999</v>
       </c>
     </row>
     <row r="6">
@@ -665,41 +665,39 @@
           <t>其他右下</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>71.53026682000001</v>
+        <v>62.17060529</v>
       </c>
       <c r="D6" t="n">
-        <v>61.95069416</v>
+        <v>150.89392396</v>
       </c>
       <c r="E6" t="n">
-        <v>149.95948194</v>
+        <v>196.74508554</v>
       </c>
       <c r="F6" t="n">
-        <v>189.86291641</v>
+        <v>-5.487039460000012</v>
       </c>
       <c r="G6" t="n">
-        <v>26.54005540999999</v>
+        <v>30.87101049999999</v>
       </c>
       <c r="H6" t="n">
-        <v>60.85894823</v>
+        <v>-33.62812604999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-16.84305672</v>
+        <v>-94.41604997999998</v>
       </c>
       <c r="J6" t="n">
-        <v>-82.56073731999999</v>
+        <v>16.34970049</v>
       </c>
       <c r="K6" t="n">
-        <v>19.95676215000001</v>
+        <v>-21.72633224</v>
       </c>
       <c r="L6" t="n">
-        <v>-20.10041905</v>
+        <v>80.54039675999999</v>
       </c>
       <c r="M6" t="n">
-        <v>79.89614155</v>
+        <v>-323.98824517</v>
       </c>
     </row>
     <row r="7">
@@ -710,37 +708,37 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>-31.47371011</v>
+        <v>-25.96269403</v>
       </c>
       <c r="D7" t="n">
-        <v>-25.89268865</v>
+        <v>-26.92285974</v>
       </c>
       <c r="E7" t="n">
-        <v>-25.98170246</v>
+        <v>-40.42271543</v>
       </c>
       <c r="F7" t="n">
-        <v>-33.37205148</v>
+        <v>-16.79846916</v>
       </c>
       <c r="G7" t="n">
-        <v>-48.86903072</v>
+        <v>7.528688150000001</v>
       </c>
       <c r="H7" t="n">
-        <v>-22.2992774</v>
+        <v>9.82962717</v>
       </c>
       <c r="I7" t="n">
-        <v>-6.911284380000001</v>
+        <v>-3.89752989</v>
       </c>
       <c r="J7" t="n">
-        <v>-15.80152208</v>
+        <v>16.29408498</v>
       </c>
       <c r="K7" t="n">
-        <v>12.60820129</v>
+        <v>26.33244564</v>
       </c>
       <c r="L7" t="n">
-        <v>24.45883667</v>
+        <v>15.9780071</v>
       </c>
       <c r="M7" t="n">
-        <v>16.33643048</v>
+        <v>7.275816900000001</v>
       </c>
     </row>
     <row r="8">
@@ -751,37 +749,37 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3796.85290555</v>
+        <v>879.34148613</v>
       </c>
       <c r="D8" t="n">
-        <v>879.34148613</v>
+        <v>2616.42912294</v>
       </c>
       <c r="E8" t="n">
-        <v>2616.42912294</v>
+        <v>2457.4736574</v>
       </c>
       <c r="F8" t="n">
-        <v>2457.4736574</v>
+        <v>3001.12265816</v>
       </c>
       <c r="G8" t="n">
-        <v>3001.12265816</v>
+        <v>2854.8874692</v>
       </c>
       <c r="H8" t="n">
-        <v>2854.8874692</v>
+        <v>-845.1834295299999</v>
       </c>
       <c r="I8" t="n">
-        <v>-845.1834295299999</v>
+        <v>-5232.13894658</v>
       </c>
       <c r="J8" t="n">
-        <v>-5232.13894658</v>
+        <v>-2467.22388111</v>
       </c>
       <c r="K8" t="n">
-        <v>-2467.22388111</v>
+        <v>-3623.44463932</v>
       </c>
       <c r="L8" t="n">
-        <v>-3623.44463932</v>
+        <v>-1265.08049358</v>
       </c>
       <c r="M8" t="n">
-        <v>-1265.08049358</v>
+        <v>1053.48564696</v>
       </c>
     </row>
     <row r="9">
@@ -792,37 +790,37 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>-182.47906743</v>
+        <v>-209.37100311</v>
       </c>
       <c r="D9" t="n">
-        <v>-209.37100311</v>
+        <v>-263.1047347</v>
       </c>
       <c r="E9" t="n">
-        <v>-263.1047347</v>
+        <v>-252.67459755</v>
       </c>
       <c r="F9" t="n">
-        <v>-252.67459755</v>
+        <v>-233.13082217</v>
       </c>
       <c r="G9" t="n">
-        <v>-233.13082217</v>
+        <v>-220.98118002</v>
       </c>
       <c r="H9" t="n">
-        <v>-220.98118002</v>
+        <v>-205.97982787</v>
       </c>
       <c r="I9" t="n">
-        <v>-205.97982787</v>
+        <v>-168.92762387</v>
       </c>
       <c r="J9" t="n">
-        <v>-168.92762387</v>
+        <v>-98.29998353999999</v>
       </c>
       <c r="K9" t="n">
-        <v>-98.29998353999999</v>
+        <v>-98.09675525</v>
       </c>
       <c r="L9" t="n">
-        <v>-98.09675525</v>
+        <v>64.11305131</v>
       </c>
       <c r="M9" t="n">
-        <v>64.11305131</v>
+        <v>59.17481488</v>
       </c>
     </row>
     <row r="10">
@@ -833,37 +831,37 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>-11.61784773</v>
+        <v>16.39353733</v>
       </c>
       <c r="D10" t="n">
-        <v>16.39353733</v>
+        <v>0.1845545600000026</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1845545600000026</v>
+        <v>22.13039961</v>
       </c>
       <c r="F10" t="n">
-        <v>22.13039961</v>
+        <v>58.61804813000001</v>
       </c>
       <c r="G10" t="n">
-        <v>58.61804813000001</v>
+        <v>132.59398889</v>
       </c>
       <c r="H10" t="n">
-        <v>132.59398889</v>
+        <v>32.55600085</v>
       </c>
       <c r="I10" t="n">
-        <v>32.55600085</v>
+        <v>-32.17047336</v>
       </c>
       <c r="J10" t="n">
-        <v>-32.17047336</v>
+        <v>-7.06750377</v>
       </c>
       <c r="K10" t="n">
-        <v>-7.06750377</v>
+        <v>-30.78226786</v>
       </c>
       <c r="L10" t="n">
-        <v>-30.78226786</v>
+        <v>-3.5616625</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.5616625</v>
+        <v>-7.561324500000001</v>
       </c>
     </row>
     <row r="11">
@@ -874,37 +872,37 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>-15.33443696000001</v>
+        <v>29.40305192000001</v>
       </c>
       <c r="D11" t="n">
-        <v>30.12201213</v>
+        <v>-182.4291296</v>
       </c>
       <c r="E11" t="n">
-        <v>-180.83661576</v>
+        <v>-30.5926886</v>
       </c>
       <c r="F11" t="n">
-        <v>-28.02151100000001</v>
+        <v>311.62520288</v>
       </c>
       <c r="G11" t="n">
-        <v>312.29508241</v>
+        <v>659.1886513100001</v>
       </c>
       <c r="H11" t="n">
-        <v>658.2697451700001</v>
+        <v>244.53322146</v>
       </c>
       <c r="I11" t="n">
-        <v>242.28540973</v>
+        <v>-26.44182122999998</v>
       </c>
       <c r="J11" t="n">
-        <v>-30.65988094999998</v>
+        <v>-50.99600907999999</v>
       </c>
       <c r="K11" t="n">
-        <v>-51.47565085999999</v>
+        <v>-119.42196126</v>
       </c>
       <c r="L11" t="n">
-        <v>-120.47050673</v>
+        <v>1.506050279999997</v>
       </c>
       <c r="M11" t="n">
-        <v>1.62506261000001</v>
+        <v>121.84324355</v>
       </c>
     </row>
     <row r="12">
@@ -915,37 +913,37 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>239.49127732</v>
+        <v>174.45539656</v>
       </c>
       <c r="D12" t="n">
-        <v>173.03005152</v>
+        <v>-44.77838671</v>
       </c>
       <c r="E12" t="n">
-        <v>-44.28253254</v>
+        <v>-24.94845069</v>
       </c>
       <c r="F12" t="n">
-        <v>-22.13244071</v>
+        <v>-1.646628819999999</v>
       </c>
       <c r="G12" t="n">
-        <v>2.708196700000001</v>
+        <v>48.42101496</v>
       </c>
       <c r="H12" t="n">
-        <v>58.76775105</v>
+        <v>-29.50507429</v>
       </c>
       <c r="I12" t="n">
-        <v>-14.08652773</v>
+        <v>-158.29390554</v>
       </c>
       <c r="J12" t="n">
-        <v>-152.03090199</v>
+        <v>-58.16087749</v>
       </c>
       <c r="K12" t="n">
-        <v>-52.54308368</v>
+        <v>-112.46891363</v>
       </c>
       <c r="L12" t="n">
-        <v>-111.04547971</v>
+        <v>30.29172928000001</v>
       </c>
       <c r="M12" t="n">
-        <v>31.86454527000001</v>
+        <v>-18.75832244999999</v>
       </c>
     </row>
     <row r="13">
@@ -956,37 +954,37 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>1.46647876</v>
+        <v>22.10749099</v>
       </c>
       <c r="D13" t="n">
-        <v>22.81387582</v>
+        <v>45.15335395</v>
       </c>
       <c r="E13" t="n">
-        <v>43.06498594</v>
+        <v>26.8574633</v>
       </c>
       <c r="F13" t="n">
-        <v>21.47027572</v>
+        <v>23.58722025</v>
       </c>
       <c r="G13" t="n">
-        <v>18.5625152</v>
+        <v>34.84612357</v>
       </c>
       <c r="H13" t="n">
-        <v>25.41829362</v>
+        <v>19.02833648</v>
       </c>
       <c r="I13" t="n">
-        <v>5.85760165</v>
+        <v>-7.29885986</v>
       </c>
       <c r="J13" t="n">
-        <v>-9.34380369</v>
+        <v>7.64136523</v>
       </c>
       <c r="K13" t="n">
-        <v>2.5032132</v>
+        <v>-5.876304530000001</v>
       </c>
       <c r="L13" t="n">
-        <v>-6.25119298</v>
+        <v>-2.12667614</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.81850446</v>
+        <v>-11.7179514</v>
       </c>
     </row>
     <row r="14">
@@ -997,37 +995,37 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>7318.33156405</v>
+        <v>4022.3160685</v>
       </c>
       <c r="D14" t="n">
-        <v>3930.5487168</v>
+        <v>7523.92096141</v>
       </c>
       <c r="E14" t="n">
-        <v>7257.10979524</v>
+        <v>3960.72905864</v>
       </c>
       <c r="F14" t="n">
-        <v>3296.08931944</v>
+        <v>4484.04050699</v>
       </c>
       <c r="G14" t="n">
-        <v>3704.13905733</v>
+        <v>1741.93120384</v>
       </c>
       <c r="H14" t="n">
-        <v>907.2646100900001</v>
+        <v>594.98097982</v>
       </c>
       <c r="I14" t="n">
-        <v>338.1748518900001</v>
+        <v>-9461.103020389999</v>
       </c>
       <c r="J14" t="n">
-        <v>-9605.48128622</v>
+        <v>-2730.51777282</v>
       </c>
       <c r="K14" t="n">
-        <v>-2731.88181618</v>
+        <v>-5333.40531922</v>
       </c>
       <c r="L14" t="n">
-        <v>-5124.80083696</v>
+        <v>503.47427672</v>
       </c>
       <c r="M14" t="n">
-        <v>504.54231106</v>
+        <v>5093.12992998</v>
       </c>
     </row>
     <row r="15">
@@ -1040,37 +1038,37 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>32.21266831</v>
+        <v>1013.55209997</v>
       </c>
       <c r="D15" t="n">
-        <v>977.8892039999999</v>
+        <v>634.50910672</v>
       </c>
       <c r="E15" t="n">
-        <v>547.21699911</v>
+        <v>863.5064051100001</v>
       </c>
       <c r="F15" t="n">
-        <v>777.07836709</v>
+        <v>928.77974017</v>
       </c>
       <c r="G15" t="n">
-        <v>749.1804924300001</v>
+        <v>438.7465631399999</v>
       </c>
       <c r="H15" t="n">
-        <v>348.7542246099999</v>
+        <v>171.74922036</v>
       </c>
       <c r="I15" t="n">
-        <v>122.71872522</v>
+        <v>257.18762437</v>
       </c>
       <c r="J15" t="n">
-        <v>194.04073046</v>
+        <v>594.36170499</v>
       </c>
       <c r="K15" t="n">
-        <v>571.22651807</v>
+        <v>221.33481986</v>
       </c>
       <c r="L15" t="n">
-        <v>228.89498795</v>
+        <v>653.0409554</v>
       </c>
       <c r="M15" t="n">
-        <v>670.29859247</v>
+        <v>1032.03089481</v>
       </c>
     </row>
     <row r="16">
@@ -1081,37 +1079,37 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>-489.76824849</v>
+        <v>-739.0281200000002</v>
       </c>
       <c r="D16" t="n">
-        <v>-701.90128036</v>
+        <v>-365.55829991</v>
       </c>
       <c r="E16" t="n">
-        <v>-287.33511213</v>
+        <v>-54.79259674999999</v>
       </c>
       <c r="F16" t="n">
-        <v>54.02991229000001</v>
+        <v>-619.90224225</v>
       </c>
       <c r="G16" t="n">
-        <v>-480.7713622000001</v>
+        <v>-313.05244077</v>
       </c>
       <c r="H16" t="n">
-        <v>-119.79053997</v>
+        <v>-562.63433833</v>
       </c>
       <c r="I16" t="n">
-        <v>-549.7267032</v>
+        <v>-977.38348374</v>
       </c>
       <c r="J16" t="n">
-        <v>-813.76362848</v>
+        <v>-635.43537988</v>
       </c>
       <c r="K16" t="n">
-        <v>-655.10622357</v>
+        <v>-161.83840645</v>
       </c>
       <c r="L16" t="n">
-        <v>-245.06034683</v>
+        <v>956.8410490100001</v>
       </c>
       <c r="M16" t="n">
-        <v>913.0013036900001</v>
+        <v>2015.53057677</v>
       </c>
     </row>
     <row r="17">
@@ -1122,37 +1120,37 @@
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
-        <v>0.0402896</v>
+        <v>-0.04455849</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.04455849</v>
+        <v>0.07666569000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>0.07666569000000001</v>
+        <v>0.07677364</v>
       </c>
       <c r="F17" t="n">
-        <v>0.07677364</v>
+        <v>0.0734079</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0734079</v>
+        <v>0.0220497</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0220497</v>
+        <v>-0.00882698</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.00882698</v>
+        <v>0.02347425</v>
       </c>
       <c r="J17" t="n">
-        <v>0.02347425</v>
+        <v>0.05612575</v>
       </c>
       <c r="K17" t="n">
-        <v>0.05612575</v>
+        <v>0.0005408300000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0005408300000000001</v>
+        <v>0.03166494</v>
       </c>
       <c r="M17" t="n">
-        <v>0.03166494</v>
+        <v>-0.0056103</v>
       </c>
     </row>
     <row r="18">
@@ -1163,37 +1161,37 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>-1.127325219999998</v>
+        <v>755.78596946</v>
       </c>
       <c r="D18" t="n">
-        <v>755.78596021</v>
+        <v>808.4195493899999</v>
       </c>
       <c r="E18" t="n">
-        <v>808.41952552</v>
+        <v>20.00700631</v>
       </c>
       <c r="F18" t="n">
-        <v>20.00698698</v>
+        <v>397.85692321</v>
       </c>
       <c r="G18" t="n">
-        <v>397.85688729</v>
+        <v>941.7539192499999</v>
       </c>
       <c r="H18" t="n">
-        <v>941.7538826699999</v>
+        <v>-199.19023425</v>
       </c>
       <c r="I18" t="n">
-        <v>-199.19026018</v>
+        <v>-682.8813279</v>
       </c>
       <c r="J18" t="n">
-        <v>-682.8813332799999</v>
+        <v>76.16105462000002</v>
       </c>
       <c r="K18" t="n">
-        <v>76.16105438000001</v>
+        <v>-50.12597775999999</v>
       </c>
       <c r="L18" t="n">
-        <v>-50.12597799999999</v>
+        <v>-19.45315685</v>
       </c>
       <c r="M18" t="n">
-        <v>-19.45313958</v>
+        <v>456.06068405</v>
       </c>
     </row>
     <row r="19">
@@ -1204,37 +1202,37 @@
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>-17.56692518</v>
+        <v>-10.88912333</v>
       </c>
       <c r="D19" t="n">
-        <v>-10.88911408</v>
+        <v>-2.39154094</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.39151707</v>
+        <v>3.08110632</v>
       </c>
       <c r="F19" t="n">
-        <v>3.08112565</v>
+        <v>6.265575350000001</v>
       </c>
       <c r="G19" t="n">
-        <v>6.265611270000001</v>
+        <v>0.6903576900000001</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6903942700000002</v>
+        <v>-1.0968434</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.09681747</v>
+        <v>-4.18859639</v>
       </c>
       <c r="J19" t="n">
-        <v>-4.188591010000001</v>
+        <v>1.13234285</v>
       </c>
       <c r="K19" t="n">
-        <v>1.13234309</v>
+        <v>-2.43509875</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.43509851</v>
+        <v>-3.15424531</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.15426258</v>
+        <v>-1.89528089</v>
       </c>
     </row>
     <row r="20">
@@ -1245,37 +1243,37 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>-34.65196079</v>
+        <v>-20.07586818</v>
       </c>
       <c r="D20" t="n">
-        <v>-20.07586818</v>
+        <v>37.03994246</v>
       </c>
       <c r="E20" t="n">
-        <v>37.03994246</v>
+        <v>61.97440654</v>
       </c>
       <c r="F20" t="n">
-        <v>61.97440654</v>
+        <v>4.784528130000001</v>
       </c>
       <c r="G20" t="n">
-        <v>4.784528130000001</v>
+        <v>-26.57971293</v>
       </c>
       <c r="H20" t="n">
-        <v>-26.57971293</v>
+        <v>-51.94192612000001</v>
       </c>
       <c r="I20" t="n">
-        <v>-51.94192612000001</v>
+        <v>-0.42173321</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.42173321</v>
+        <v>-23.83094442</v>
       </c>
       <c r="K20" t="n">
-        <v>-23.83094442</v>
+        <v>-44.06559479000001</v>
       </c>
       <c r="L20" t="n">
-        <v>-44.06559479000001</v>
+        <v>-16.18543155</v>
       </c>
       <c r="M20" t="n">
-        <v>-16.18543155</v>
+        <v>-36.8669311</v>
       </c>
     </row>
     <row r="21">
@@ -1286,37 +1284,37 @@
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
-        <v>-7.15899586</v>
+        <v>-1.9665216</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9665216</v>
+        <v>-1.02758461</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.02758461</v>
+        <v>2.7858135</v>
       </c>
       <c r="F21" t="n">
-        <v>2.7858135</v>
+        <v>1.57265017</v>
       </c>
       <c r="G21" t="n">
-        <v>1.57265017</v>
+        <v>-0.11769773</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.11769773</v>
+        <v>-1.28430574</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.28430574</v>
+        <v>-3.1636393</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.1636393</v>
+        <v>-3.19371817</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.19371817</v>
+        <v>-3.23149288</v>
       </c>
       <c r="L21" t="n">
-        <v>-3.23149288</v>
+        <v>-1.73988098</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.73988098</v>
+        <v>0.25646976</v>
       </c>
     </row>
     <row r="22">
@@ -1327,37 +1325,37 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>0.9927766899999999</v>
+        <v>-0.03595326999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.03595326999999999</v>
+        <v>0.96984157</v>
       </c>
       <c r="E22" t="n">
-        <v>0.96984157</v>
+        <v>1.21441183</v>
       </c>
       <c r="F22" t="n">
-        <v>1.21441183</v>
+        <v>2.1806725</v>
       </c>
       <c r="G22" t="n">
-        <v>2.1806725</v>
+        <v>0.27043521</v>
       </c>
       <c r="H22" t="n">
-        <v>0.27043521</v>
+        <v>0.97694012</v>
       </c>
       <c r="I22" t="n">
-        <v>0.97694012</v>
+        <v>-0.11805477</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.11805477</v>
+        <v>1.62020539</v>
       </c>
       <c r="K22" t="n">
-        <v>1.62020539</v>
+        <v>0.18215004</v>
       </c>
       <c r="L22" t="n">
-        <v>0.18215004</v>
+        <v>1.30186974</v>
       </c>
       <c r="M22" t="n">
-        <v>1.30186974</v>
+        <v>-0.31173102</v>
       </c>
     </row>
     <row r="23">
@@ -1368,37 +1366,37 @@
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
-        <v>29.79123508</v>
+        <v>65.34342972</v>
       </c>
       <c r="D23" t="n">
-        <v>65.34342972</v>
+        <v>67.63610528999999</v>
       </c>
       <c r="E23" t="n">
-        <v>67.63610528999999</v>
+        <v>69.97203975999999</v>
       </c>
       <c r="F23" t="n">
-        <v>69.97203975999999</v>
+        <v>133.0464327</v>
       </c>
       <c r="G23" t="n">
-        <v>133.0464327</v>
+        <v>130.6413759</v>
       </c>
       <c r="H23" t="n">
-        <v>130.6413759</v>
+        <v>58.89268668</v>
       </c>
       <c r="I23" t="n">
-        <v>58.89268668</v>
+        <v>0.1293569200000017</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1293569200000017</v>
+        <v>-20.18880538</v>
       </c>
       <c r="K23" t="n">
-        <v>-20.18880538</v>
+        <v>-29.74299028</v>
       </c>
       <c r="L23" t="n">
-        <v>-29.74299028</v>
+        <v>-68.75786970999999</v>
       </c>
       <c r="M23" t="n">
-        <v>-68.75786970999999</v>
+        <v>-62.90526295</v>
       </c>
     </row>
     <row r="24">
@@ -1409,37 +1407,37 @@
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
-        <v>-42.31824303</v>
+        <v>-57.8911487</v>
       </c>
       <c r="D24" t="n">
-        <v>-44.79656034000001</v>
+        <v>13.57766081</v>
       </c>
       <c r="E24" t="n">
-        <v>-22.37138071000001</v>
+        <v>28.53646346</v>
       </c>
       <c r="F24" t="n">
-        <v>16.04445966</v>
+        <v>32.38043983</v>
       </c>
       <c r="G24" t="n">
-        <v>30.46881979</v>
+        <v>25.60689783</v>
       </c>
       <c r="H24" t="n">
-        <v>33.51039145</v>
+        <v>-2.246864229999999</v>
       </c>
       <c r="I24" t="n">
-        <v>10.90981581</v>
+        <v>-49.41941372</v>
       </c>
       <c r="J24" t="n">
-        <v>-32.27587199</v>
+        <v>0.8974105799999965</v>
       </c>
       <c r="K24" t="n">
-        <v>6.558118359999997</v>
+        <v>-17.93332839</v>
       </c>
       <c r="L24" t="n">
-        <v>-11.25430171</v>
+        <v>-1.879133519999998</v>
       </c>
       <c r="M24" t="n">
-        <v>1.930407980000002</v>
+        <v>-23.74535507</v>
       </c>
     </row>
     <row r="25">
@@ -1450,37 +1448,37 @@
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>3.268189569999998</v>
+        <v>14.27351332</v>
       </c>
       <c r="D25" t="n">
-        <v>1.178924959999999</v>
+        <v>3.89314188</v>
       </c>
       <c r="E25" t="n">
-        <v>39.8421834</v>
+        <v>28.32196782</v>
       </c>
       <c r="F25" t="n">
-        <v>40.81397162</v>
+        <v>34.4410354</v>
       </c>
       <c r="G25" t="n">
-        <v>36.35265544</v>
+        <v>48.23688248</v>
       </c>
       <c r="H25" t="n">
-        <v>40.33338886</v>
+        <v>4.95570522</v>
       </c>
       <c r="I25" t="n">
-        <v>-8.200974820000001</v>
+        <v>-44.91641203</v>
       </c>
       <c r="J25" t="n">
-        <v>-62.05995376</v>
+        <v>-39.56430317</v>
       </c>
       <c r="K25" t="n">
-        <v>-45.22501095</v>
+        <v>-33.14800539</v>
       </c>
       <c r="L25" t="n">
-        <v>-39.82703207</v>
+        <v>-30.87213973</v>
       </c>
       <c r="M25" t="n">
-        <v>-34.68168123</v>
+        <v>-42.11488065</v>
       </c>
     </row>
     <row r="26">
@@ -1491,37 +1489,37 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>5.521821180000001</v>
+        <v>16.6409802</v>
       </c>
       <c r="D26" t="n">
-        <v>16.6409802</v>
+        <v>6.06098376</v>
       </c>
       <c r="E26" t="n">
-        <v>6.06098376</v>
+        <v>6.223655750000001</v>
       </c>
       <c r="F26" t="n">
-        <v>6.223655750000001</v>
+        <v>7.69451413</v>
       </c>
       <c r="G26" t="n">
-        <v>7.69451413</v>
+        <v>9.40402284</v>
       </c>
       <c r="H26" t="n">
-        <v>9.40402284</v>
+        <v>3.51569178</v>
       </c>
       <c r="I26" t="n">
-        <v>3.51569178</v>
+        <v>-0.84665852</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.84665852</v>
+        <v>-3.81098417</v>
       </c>
       <c r="K26" t="n">
-        <v>-3.81098417</v>
+        <v>3.2463298</v>
       </c>
       <c r="L26" t="n">
-        <v>3.2463298</v>
+        <v>10.10026982</v>
       </c>
       <c r="M26" t="n">
-        <v>10.10026982</v>
+        <v>-1.11573838</v>
       </c>
     </row>
     <row r="27">
@@ -1532,37 +1530,37 @@
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>22.18765775</v>
+        <v>32.00669278</v>
       </c>
       <c r="D27" t="n">
-        <v>32.00669278</v>
+        <v>32.90437347</v>
       </c>
       <c r="E27" t="n">
-        <v>32.90437347</v>
+        <v>31.89174097</v>
       </c>
       <c r="F27" t="n">
-        <v>31.89174097</v>
+        <v>15.84071661</v>
       </c>
       <c r="G27" t="n">
-        <v>15.84071661</v>
+        <v>15.49391241</v>
       </c>
       <c r="H27" t="n">
-        <v>15.49391241</v>
+        <v>7.17790168</v>
       </c>
       <c r="I27" t="n">
-        <v>7.17790168</v>
+        <v>-3.00251758</v>
       </c>
       <c r="J27" t="n">
-        <v>-3.00251758</v>
+        <v>-0.9558826999999984</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.9558826999999984</v>
+        <v>-3.047840899999999</v>
       </c>
       <c r="L27" t="n">
-        <v>-3.047840899999999</v>
+        <v>3.49603584</v>
       </c>
       <c r="M27" t="n">
-        <v>3.49603584</v>
+        <v>8.40225049</v>
       </c>
     </row>
     <row r="28">
@@ -1573,37 +1571,37 @@
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>-107.64209913</v>
+        <v>-100.87609465</v>
       </c>
       <c r="D28" t="n">
-        <v>-100.87609465</v>
+        <v>-89.11733212999999</v>
       </c>
       <c r="E28" t="n">
-        <v>-89.11733212999999</v>
+        <v>-74.32016209999999</v>
       </c>
       <c r="F28" t="n">
-        <v>-74.32016209999999</v>
+        <v>-60.25372348999999</v>
       </c>
       <c r="G28" t="n">
-        <v>-60.25372348999999</v>
+        <v>-34.00273959</v>
       </c>
       <c r="H28" t="n">
-        <v>-34.00273959</v>
+        <v>-31.31406694</v>
       </c>
       <c r="I28" t="n">
-        <v>-31.31406694</v>
+        <v>-34.43851073</v>
       </c>
       <c r="J28" t="n">
-        <v>-34.43851073</v>
+        <v>-6.507427059999999</v>
       </c>
       <c r="K28" t="n">
-        <v>-6.507427059999999</v>
+        <v>-9.892342220000002</v>
       </c>
       <c r="L28" t="n">
-        <v>-9.892342220000002</v>
+        <v>-10.52663957</v>
       </c>
       <c r="M28" t="n">
-        <v>-10.52663957</v>
+        <v>-22.50967457</v>
       </c>
     </row>
     <row r="29">
@@ -1614,37 +1612,37 @@
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>0.01277118</v>
+        <v>-0.00653676</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.00653676</v>
+        <v>-0.01623805</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.01623805</v>
+        <v>-0.01854561</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.01854561</v>
+        <v>-0.0214375</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.0214375</v>
+        <v>-0.00590779</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.00590779</v>
+        <v>0.007246020000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>0.007246020000000001</v>
+        <v>0.04125581</v>
       </c>
       <c r="J29" t="n">
-        <v>0.04125581</v>
+        <v>0.01170391</v>
       </c>
       <c r="K29" t="n">
-        <v>0.01170391</v>
+        <v>0.02586367</v>
       </c>
       <c r="L29" t="n">
-        <v>0.02586367</v>
+        <v>0.005801969999999999</v>
       </c>
       <c r="M29" t="n">
-        <v>0.005801969999999999</v>
+        <v>0.00582863</v>
       </c>
     </row>
     <row r="30">
@@ -1655,37 +1653,37 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>-0.00467908</v>
+        <v>-0.009399649999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.00565026</v>
+        <v>-0.00608247</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.00688049</v>
+        <v>0.01270172</v>
       </c>
       <c r="F30" t="n">
-        <v>0.01008529</v>
+        <v>0.00278657</v>
       </c>
       <c r="G30" t="n">
-        <v>0.00215091</v>
+        <v>0.00315456</v>
       </c>
       <c r="H30" t="n">
-        <v>0.003591480000000001</v>
+        <v>0.0003366700000000005</v>
       </c>
       <c r="I30" t="n">
-        <v>0.001555480000000001</v>
+        <v>-0.00315718</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.0007999199999999996</v>
+        <v>0.00399096</v>
       </c>
       <c r="K30" t="n">
-        <v>0.00545615</v>
+        <v>0.00596591</v>
       </c>
       <c r="L30" t="n">
-        <v>0.007495199999999999</v>
+        <v>0.000657989999999999</v>
       </c>
       <c r="M30" t="n">
-        <v>0.003162389999999999</v>
+        <v>0.00123295</v>
       </c>
     </row>
     <row r="31">
@@ -1696,37 +1694,37 @@
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>-0.05285173000000001</v>
+        <v>-0.09100522999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.09475462</v>
+        <v>-0.18580192</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.1850039</v>
+        <v>0.0009241699999999998</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0035406</v>
+        <v>-0.03760385</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.03696819</v>
+        <v>0.2104042</v>
       </c>
       <c r="H31" t="n">
-        <v>0.20996728</v>
+        <v>0.08392569</v>
       </c>
       <c r="I31" t="n">
-        <v>0.08270688000000001</v>
+        <v>-0.01734405</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.01970131</v>
+        <v>0.08931181000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0.08784662000000001</v>
+        <v>-0.01858694</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.02011623</v>
+        <v>-0.08233456</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.08483896</v>
+        <v>0.15470174</v>
       </c>
     </row>
     <row r="32">
@@ -1737,37 +1735,37 @@
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>-28.63820698</v>
+        <v>-10.76783712</v>
       </c>
       <c r="D32" t="n">
-        <v>-10.76783712</v>
+        <v>-20.0377565</v>
       </c>
       <c r="E32" t="n">
-        <v>-20.0377565</v>
+        <v>-6.47922948</v>
       </c>
       <c r="F32" t="n">
-        <v>-6.47922948</v>
+        <v>-21.67391496</v>
       </c>
       <c r="G32" t="n">
-        <v>-21.67391496</v>
+        <v>5.52792584</v>
       </c>
       <c r="H32" t="n">
-        <v>5.52792584</v>
+        <v>7.32848074</v>
       </c>
       <c r="I32" t="n">
-        <v>7.32848074</v>
+        <v>15.30775618</v>
       </c>
       <c r="J32" t="n">
-        <v>15.30775618</v>
+        <v>7.30639586</v>
       </c>
       <c r="K32" t="n">
-        <v>7.30639586</v>
+        <v>-11.85354807</v>
       </c>
       <c r="L32" t="n">
-        <v>-11.85354807</v>
+        <v>-0.6966225100000002</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.6966225100000002</v>
+        <v>-46.61611256</v>
       </c>
     </row>
     <row r="33">
@@ -1778,37 +1776,37 @@
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
-        <v>-14.85168894</v>
+        <v>-7.31165541</v>
       </c>
       <c r="D33" t="n">
-        <v>-7.31165541</v>
+        <v>-1.41149422</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.41149422</v>
+        <v>-7.85183825</v>
       </c>
       <c r="F33" t="n">
-        <v>-7.85183825</v>
+        <v>6.05615573</v>
       </c>
       <c r="G33" t="n">
-        <v>6.05615573</v>
+        <v>10.38013217</v>
       </c>
       <c r="H33" t="n">
-        <v>10.38013217</v>
+        <v>14.06584317</v>
       </c>
       <c r="I33" t="n">
-        <v>14.06584317</v>
+        <v>-5.77658342</v>
       </c>
       <c r="J33" t="n">
-        <v>-5.77658342</v>
+        <v>-11.60830516</v>
       </c>
       <c r="K33" t="n">
-        <v>-11.60830516</v>
+        <v>-5.47274894</v>
       </c>
       <c r="L33" t="n">
-        <v>-5.47274894</v>
+        <v>22.31044223</v>
       </c>
       <c r="M33" t="n">
-        <v>22.31044223</v>
+        <v>25.9601656</v>
       </c>
     </row>
     <row r="34">
@@ -1819,37 +1817,37 @@
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
-        <v>42.38292683</v>
+        <v>53.14078301</v>
       </c>
       <c r="D34" t="n">
-        <v>53.14078301</v>
+        <v>77.31264456</v>
       </c>
       <c r="E34" t="n">
-        <v>77.31264456</v>
+        <v>-99.06594910000001</v>
       </c>
       <c r="F34" t="n">
-        <v>-99.06594910000001</v>
+        <v>-137.71287059</v>
       </c>
       <c r="G34" t="n">
-        <v>-137.71287059</v>
+        <v>-36.98264507</v>
       </c>
       <c r="H34" t="n">
-        <v>-36.98264507</v>
+        <v>-110.28325571</v>
       </c>
       <c r="I34" t="n">
-        <v>-110.28325571</v>
+        <v>-29.94653585</v>
       </c>
       <c r="J34" t="n">
-        <v>-29.94653585</v>
+        <v>-75.37832121000001</v>
       </c>
       <c r="K34" t="n">
-        <v>-75.37832121000001</v>
+        <v>-140.33270771</v>
       </c>
       <c r="L34" t="n">
-        <v>-140.33270771</v>
+        <v>-13.10425446</v>
       </c>
       <c r="M34" t="n">
-        <v>-13.10425446</v>
+        <v>-100.77426828</v>
       </c>
     </row>
     <row r="35">
@@ -1860,37 +1858,37 @@
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
-        <v>-0.03013220000000001</v>
+        <v>3.18854859</v>
       </c>
       <c r="D35" t="n">
-        <v>3.18854859</v>
+        <v>2.605460190000001</v>
       </c>
       <c r="E35" t="n">
-        <v>2.605460190000001</v>
+        <v>4.13401164</v>
       </c>
       <c r="F35" t="n">
-        <v>4.13401164</v>
+        <v>4.72190981</v>
       </c>
       <c r="G35" t="n">
-        <v>4.72190981</v>
+        <v>5.98762434</v>
       </c>
       <c r="H35" t="n">
-        <v>5.98762434</v>
+        <v>2.37916882</v>
       </c>
       <c r="I35" t="n">
-        <v>2.37916882</v>
+        <v>-0.53526386</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.53526386</v>
+        <v>2.64361891</v>
       </c>
       <c r="K35" t="n">
-        <v>2.64361891</v>
+        <v>7.38655337</v>
       </c>
       <c r="L35" t="n">
-        <v>7.38655337</v>
+        <v>7.14443184</v>
       </c>
       <c r="M35" t="n">
-        <v>7.14443184</v>
+        <v>8.25474532</v>
       </c>
     </row>
     <row r="36">
@@ -1901,37 +1899,37 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>352.4427523</v>
+        <v>215.34440896</v>
       </c>
       <c r="D36" t="n">
-        <v>204.10822595</v>
+        <v>203.11277483</v>
       </c>
       <c r="E36" t="n">
-        <v>203.78321979</v>
+        <v>-9.032017559999998</v>
       </c>
       <c r="F36" t="n">
-        <v>-5.257925969999995</v>
+        <v>184.61897931</v>
       </c>
       <c r="G36" t="n">
-        <v>182.21045032</v>
+        <v>5.011323659999997</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8376441199999973</v>
+        <v>-98.44188990000001</v>
       </c>
       <c r="I36" t="n">
-        <v>-109.20080044</v>
+        <v>-118.62121267</v>
       </c>
       <c r="J36" t="n">
-        <v>-113.180397</v>
+        <v>-24.10902694</v>
       </c>
       <c r="K36" t="n">
-        <v>-28.44645008</v>
+        <v>-146.27039908</v>
       </c>
       <c r="L36" t="n">
-        <v>-140.59688302</v>
+        <v>-45.89729789999999</v>
       </c>
       <c r="M36" t="n">
-        <v>-31.58967633999999</v>
+        <v>39.49694426000001</v>
       </c>
     </row>
     <row r="37">
@@ -1942,37 +1940,37 @@
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>-8.201723510000004</v>
+        <v>35.11853209</v>
       </c>
       <c r="D37" t="n">
-        <v>36.93535253</v>
+        <v>8.366463559999998</v>
       </c>
       <c r="E37" t="n">
-        <v>10.60939206</v>
+        <v>18.71187082</v>
       </c>
       <c r="F37" t="n">
-        <v>14.43491196</v>
+        <v>6.856268900000002</v>
       </c>
       <c r="G37" t="n">
-        <v>-3.202828459999999</v>
+        <v>31.59423299</v>
       </c>
       <c r="H37" t="n">
-        <v>19.45456314</v>
+        <v>14.46818199</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.084996530000001</v>
+        <v>-50.35822645</v>
       </c>
       <c r="J37" t="n">
-        <v>-64.69088463</v>
+        <v>-16.95623388</v>
       </c>
       <c r="K37" t="n">
-        <v>-21.91433284</v>
+        <v>-42.66262531</v>
       </c>
       <c r="L37" t="n">
-        <v>-47.81949567</v>
+        <v>-1.491744379999999</v>
       </c>
       <c r="M37" t="n">
-        <v>-8.695576079999999</v>
+        <v>-38.93065039</v>
       </c>
     </row>
     <row r="38">
@@ -1983,37 +1981,37 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>9.36090752</v>
+        <v>30.11840382</v>
       </c>
       <c r="D38" t="n">
-        <v>39.53776639</v>
+        <v>37.00274245</v>
       </c>
       <c r="E38" t="n">
-        <v>34.08936899</v>
+        <v>-20.49456894</v>
       </c>
       <c r="F38" t="n">
-        <v>-19.99170167</v>
+        <v>2.79140924</v>
       </c>
       <c r="G38" t="n">
-        <v>15.25903559</v>
+        <v>-48.28613629</v>
       </c>
       <c r="H38" t="n">
-        <v>-31.9727869</v>
+        <v>-117.4094757</v>
       </c>
       <c r="I38" t="n">
-        <v>-91.09738664</v>
+        <v>-136.13917919</v>
       </c>
       <c r="J38" t="n">
-        <v>-127.24733668</v>
+        <v>-57.5016625</v>
       </c>
       <c r="K38" t="n">
-        <v>-48.2061404</v>
+        <v>-57.69474112</v>
       </c>
       <c r="L38" t="n">
-        <v>-58.21138682000001</v>
+        <v>-0.4677123500000031</v>
       </c>
       <c r="M38" t="n">
-        <v>-7.571502210000003</v>
+        <v>99.941777</v>
       </c>
     </row>
     <row r="39">
@@ -2024,37 +2022,37 @@
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
-        <v>24.80576117</v>
+        <v>21.99748971</v>
       </c>
       <c r="D39" t="n">
-        <v>21.99748971</v>
+        <v>7.5667577</v>
       </c>
       <c r="E39" t="n">
-        <v>7.5667577</v>
+        <v>-0.39082327</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.39082327</v>
+        <v>6.9156605</v>
       </c>
       <c r="G39" t="n">
-        <v>6.9156605</v>
+        <v>-3.65105099</v>
       </c>
       <c r="H39" t="n">
-        <v>-3.65105099</v>
+        <v>5.96885178</v>
       </c>
       <c r="I39" t="n">
-        <v>5.96885178</v>
+        <v>-4.14332239</v>
       </c>
       <c r="J39" t="n">
-        <v>-4.14332239</v>
+        <v>-1.8353452</v>
       </c>
       <c r="K39" t="n">
-        <v>-1.8353452</v>
+        <v>-7.62116679</v>
       </c>
       <c r="L39" t="n">
-        <v>-7.62116679</v>
+        <v>-5.07731053</v>
       </c>
       <c r="M39" t="n">
-        <v>-5.07731053</v>
+        <v>-2.26730802</v>
       </c>
     </row>
     <row r="40">
@@ -2065,37 +2063,37 @@
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>-18.29832132</v>
+        <v>16.51942199</v>
       </c>
       <c r="D40" t="n">
-        <v>16.51942199</v>
+        <v>-19.21069481</v>
       </c>
       <c r="E40" t="n">
-        <v>-19.21069481</v>
+        <v>-76.86549835</v>
       </c>
       <c r="F40" t="n">
-        <v>-76.86549835</v>
+        <v>-32.5970419</v>
       </c>
       <c r="G40" t="n">
-        <v>-32.5970419</v>
+        <v>-50.29811102</v>
       </c>
       <c r="H40" t="n">
-        <v>-50.29811102</v>
+        <v>-89.72822392</v>
       </c>
       <c r="I40" t="n">
-        <v>-89.72822392</v>
+        <v>-81.92920619</v>
       </c>
       <c r="J40" t="n">
-        <v>-81.92920619</v>
+        <v>5.598820609999998</v>
       </c>
       <c r="K40" t="n">
-        <v>5.598820609999998</v>
+        <v>45.96694628999999</v>
       </c>
       <c r="L40" t="n">
-        <v>45.96694628999999</v>
+        <v>5.63183572</v>
       </c>
       <c r="M40" t="n">
-        <v>5.63183572</v>
+        <v>-13.4108558</v>
       </c>
     </row>
     <row r="41">
@@ -2106,37 +2104,37 @@
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
-        <v>4.417e-05</v>
+        <v>9.085e-05</v>
       </c>
       <c r="D41" t="n">
-        <v>9.085e-05</v>
+        <v>-7.104999999999999e-05</v>
       </c>
       <c r="E41" t="n">
-        <v>-7.104999999999999e-05</v>
+        <v>-0.00022371</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.00022371</v>
+        <v>-0.00012</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.00012</v>
+        <v>-0.00023445</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.00023445</v>
+        <v>-0.00035108</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.00035108</v>
+        <v>-0.00043212</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.00043212</v>
+        <v>-0.00024149</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.00024149</v>
+        <v>-0.00030939</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.00030939</v>
+        <v>-0.00037094</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.00037094</v>
+        <v>-0.00043955</v>
       </c>
     </row>
     <row r="42">
@@ -2147,37 +2145,37 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>156.76665614</v>
+        <v>582.9563215699999</v>
       </c>
       <c r="D42" t="n">
-        <v>578.4989785</v>
+        <v>919.0814701600001</v>
       </c>
       <c r="E42" t="n">
-        <v>900.52032724</v>
+        <v>1187.41765549</v>
       </c>
       <c r="F42" t="n">
-        <v>1153.82319753</v>
+        <v>1289.85564071</v>
       </c>
       <c r="G42" t="n">
-        <v>1252.18441714</v>
+        <v>1322.24512202</v>
       </c>
       <c r="H42" t="n">
-        <v>1286.18806609</v>
+        <v>-584.51218126</v>
       </c>
       <c r="I42" t="n">
-        <v>-596.5809266700001</v>
+        <v>-826.4290825300001</v>
       </c>
       <c r="J42" t="n">
-        <v>-826.9752677900001</v>
+        <v>-645.921484</v>
       </c>
       <c r="K42" t="n">
-        <v>-639.5127566199999</v>
+        <v>-699.15563984</v>
       </c>
       <c r="L42" t="n">
-        <v>-688.69328325</v>
+        <v>-559.26777697</v>
       </c>
       <c r="M42" t="n">
-        <v>-546.8971442000001</v>
+        <v>-529.61274407</v>
       </c>
     </row>
     <row r="43">
@@ -2188,37 +2186,37 @@
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
-        <v>-2.72785007</v>
+        <v>-0.80378561</v>
       </c>
       <c r="D43" t="n">
-        <v>3.65355746</v>
+        <v>2.28745028</v>
       </c>
       <c r="E43" t="n">
-        <v>20.8485932</v>
+        <v>0.67277188</v>
       </c>
       <c r="F43" t="n">
-        <v>34.26722984000001</v>
+        <v>0.93779075</v>
       </c>
       <c r="G43" t="n">
-        <v>38.60901432</v>
+        <v>1.58338164</v>
       </c>
       <c r="H43" t="n">
-        <v>37.64043757</v>
+        <v>-0.03535392000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>12.03339149</v>
+        <v>-1.21772847</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.6715432099999999</v>
+        <v>-0.23402355</v>
       </c>
       <c r="K43" t="n">
-        <v>-6.64275093</v>
+        <v>-0.65173021</v>
       </c>
       <c r="L43" t="n">
-        <v>-11.1140868</v>
+        <v>-1.14842042</v>
       </c>
       <c r="M43" t="n">
-        <v>-13.51905319</v>
+        <v>-0.22527868</v>
       </c>
     </row>
     <row r="44">
@@ -2229,37 +2227,37 @@
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>11.62153488</v>
+        <v>12.81417435</v>
       </c>
       <c r="D44" t="n">
-        <v>12.52428829</v>
+        <v>-6.106026710000001</v>
       </c>
       <c r="E44" t="n">
-        <v>-6.29255899</v>
+        <v>-19.84500612</v>
       </c>
       <c r="F44" t="n">
-        <v>-19.82934299</v>
+        <v>-25.51124397</v>
       </c>
       <c r="G44" t="n">
-        <v>-25.38328077</v>
+        <v>-19.78262109</v>
       </c>
       <c r="H44" t="n">
-        <v>-19.68425024</v>
+        <v>-7.33561229</v>
       </c>
       <c r="I44" t="n">
-        <v>-7.2754713</v>
+        <v>-12.35542252</v>
       </c>
       <c r="J44" t="n">
-        <v>-12.29083748</v>
+        <v>9.283503610000002</v>
       </c>
       <c r="K44" t="n">
-        <v>0.4751900600000004</v>
+        <v>28.47411383</v>
       </c>
       <c r="L44" t="n">
-        <v>23.01384118</v>
+        <v>-13.29807724</v>
       </c>
       <c r="M44" t="n">
-        <v>-15.65109047</v>
+        <v>17.62521757</v>
       </c>
     </row>
     <row r="45">
@@ -2268,41 +2266,39 @@
           <t>生技醫療業右下</t>
         </is>
       </c>
-      <c r="B45" t="n">
-        <v>0</v>
-      </c>
+      <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
-        <v>97.33550386000002</v>
+        <v>184.27281155</v>
       </c>
       <c r="D45" t="n">
-        <v>184.27656159</v>
+        <v>198.71161434</v>
       </c>
       <c r="E45" t="n">
-        <v>198.713476</v>
+        <v>293.36449177</v>
       </c>
       <c r="F45" t="n">
-        <v>293.36701458</v>
+        <v>426.05303363</v>
       </c>
       <c r="G45" t="n">
-        <v>426.05552276</v>
+        <v>554.8878276999999</v>
       </c>
       <c r="H45" t="n">
-        <v>554.8971386100001</v>
+        <v>773.2213106000002</v>
       </c>
       <c r="I45" t="n">
-        <v>773.22111708</v>
+        <v>1235.00220317</v>
       </c>
       <c r="J45" t="n">
-        <v>1234.9986829</v>
+        <v>1393.17093556</v>
       </c>
       <c r="K45" t="n">
-        <v>1393.16834543</v>
+        <v>431.49255032</v>
       </c>
       <c r="L45" t="n">
-        <v>431.49039629</v>
+        <v>639.89453255</v>
       </c>
       <c r="M45" t="n">
-        <v>639.90180303</v>
+        <v>1909.63838393</v>
       </c>
     </row>
     <row r="46">
@@ -2313,37 +2309,37 @@
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>-59.50473491</v>
+        <v>73.33092348999999</v>
       </c>
       <c r="D46" t="n">
-        <v>73.61822776999999</v>
+        <v>103.1284493</v>
       </c>
       <c r="E46" t="n">
-        <v>103.31493801</v>
+        <v>247.06172803</v>
       </c>
       <c r="F46" t="n">
-        <v>247.04460891</v>
+        <v>66.79263655999999</v>
       </c>
       <c r="G46" t="n">
-        <v>66.66327029999999</v>
+        <v>-62.13504729</v>
       </c>
       <c r="H46" t="n">
-        <v>-62.24306832</v>
+        <v>-149.18986887</v>
       </c>
       <c r="I46" t="n">
-        <v>-149.25217461</v>
+        <v>-141.13778</v>
       </c>
       <c r="J46" t="n">
-        <v>-141.19945651</v>
+        <v>-93.13772162000001</v>
       </c>
       <c r="K46" t="n">
-        <v>-84.32757759</v>
+        <v>-118.46152752</v>
       </c>
       <c r="L46" t="n">
-        <v>-112.99791711</v>
+        <v>-51.9006511</v>
       </c>
       <c r="M46" t="n">
-        <v>-49.55242153000001</v>
+        <v>29.48658999</v>
       </c>
     </row>
     <row r="47">
@@ -2354,37 +2350,37 @@
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>-1.1655586</v>
+        <v>3.26496547</v>
       </c>
       <c r="D47" t="n">
-        <v>3.26496547</v>
+        <v>1.63752578</v>
       </c>
       <c r="E47" t="n">
-        <v>1.63752578</v>
+        <v>0.73957031</v>
       </c>
       <c r="F47" t="n">
-        <v>0.73957031</v>
+        <v>2.84248041</v>
       </c>
       <c r="G47" t="n">
-        <v>2.84248041</v>
+        <v>3.94012105</v>
       </c>
       <c r="H47" t="n">
-        <v>3.94012105</v>
+        <v>4.282697440000001</v>
       </c>
       <c r="I47" t="n">
-        <v>4.282697440000001</v>
+        <v>1.74059634</v>
       </c>
       <c r="J47" t="n">
-        <v>1.74059634</v>
+        <v>2.58832362</v>
       </c>
       <c r="K47" t="n">
-        <v>2.58832362</v>
+        <v>8.37476756</v>
       </c>
       <c r="L47" t="n">
-        <v>8.37476756</v>
+        <v>2.66770553</v>
       </c>
       <c r="M47" t="n">
-        <v>2.66770553</v>
+        <v>0.4382049700000001</v>
       </c>
     </row>
     <row r="48">
@@ -2395,37 +2391,37 @@
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
-        <v>-161.09871495</v>
+        <v>-138.91380902</v>
       </c>
       <c r="D48" t="n">
-        <v>-138.66368119</v>
+        <v>-65.78404603</v>
       </c>
       <c r="E48" t="n">
-        <v>-66.08023935999999</v>
+        <v>100.66743719</v>
       </c>
       <c r="F48" t="n">
-        <v>100.64913585</v>
+        <v>167.30677723</v>
       </c>
       <c r="G48" t="n">
-        <v>167.52132607</v>
+        <v>94.00985064999999</v>
       </c>
       <c r="H48" t="n">
-        <v>93.73160254999999</v>
+        <v>31.25876354</v>
       </c>
       <c r="I48" t="n">
-        <v>30.6499759</v>
+        <v>-9.365502470000003</v>
       </c>
       <c r="J48" t="n">
-        <v>-10.20388659</v>
+        <v>71.67941374999999</v>
       </c>
       <c r="K48" t="n">
-        <v>68.61116697</v>
+        <v>41.2511178</v>
       </c>
       <c r="L48" t="n">
-        <v>39.74779179999999</v>
+        <v>92.82611540000001</v>
       </c>
       <c r="M48" t="n">
-        <v>92.27023935000001</v>
+        <v>-19.17170454</v>
       </c>
     </row>
     <row r="49">
@@ -2436,37 +2432,37 @@
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>-3.14896068</v>
+        <v>-1.09712453</v>
       </c>
       <c r="D49" t="n">
-        <v>-1.09718438</v>
+        <v>13.15970596</v>
       </c>
       <c r="E49" t="n">
-        <v>13.15970829</v>
+        <v>60.53457304</v>
       </c>
       <c r="F49" t="n">
-        <v>60.53451084</v>
+        <v>92.00486252000002</v>
       </c>
       <c r="G49" t="n">
-        <v>92.00479023</v>
+        <v>197.5995706</v>
       </c>
       <c r="H49" t="n">
-        <v>197.5994527</v>
+        <v>309.54157822</v>
       </c>
       <c r="I49" t="n">
-        <v>309.54159402</v>
+        <v>124.4714987</v>
       </c>
       <c r="J49" t="n">
-        <v>124.47148492</v>
+        <v>114.35247406</v>
       </c>
       <c r="K49" t="n">
-        <v>114.35255789</v>
+        <v>8.71393535</v>
       </c>
       <c r="L49" t="n">
-        <v>8.714754710000001</v>
+        <v>10.69780672</v>
       </c>
       <c r="M49" t="n">
-        <v>10.6989212</v>
+        <v>-40.25523382</v>
       </c>
     </row>
     <row r="50">
@@ -2477,37 +2473,37 @@
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
-        <v>-49.9699323</v>
+        <v>-31.82754244</v>
       </c>
       <c r="D50" t="n">
-        <v>-34.87113519</v>
+        <v>-102.22663502</v>
       </c>
       <c r="E50" t="n">
-        <v>-101.83529897</v>
+        <v>-21.90695902999999</v>
       </c>
       <c r="F50" t="n">
-        <v>-20.18952884999999</v>
+        <v>59.43458161</v>
       </c>
       <c r="G50" t="n">
-        <v>60.03399915</v>
+        <v>46.92944569000001</v>
       </c>
       <c r="H50" t="n">
-        <v>46.57401195000001</v>
+        <v>93.53647359999999</v>
       </c>
       <c r="I50" t="n">
-        <v>94.33851032</v>
+        <v>-57.2281396</v>
       </c>
       <c r="J50" t="n">
-        <v>-55.45684779</v>
+        <v>94.25144478999999</v>
       </c>
       <c r="K50" t="n">
-        <v>95.27728619</v>
+        <v>350.5417956399999</v>
       </c>
       <c r="L50" t="n">
-        <v>351.9052843899999</v>
+        <v>-95.48533762999998</v>
       </c>
       <c r="M50" t="n">
-        <v>-93.63477472999999</v>
+        <v>-75.13389208999999</v>
       </c>
     </row>
     <row r="51">
@@ -2518,37 +2514,37 @@
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>-27.0028744</v>
+        <v>-37.85275138</v>
       </c>
       <c r="D51" t="n">
-        <v>-37.85275138</v>
+        <v>-40.22223143</v>
       </c>
       <c r="E51" t="n">
-        <v>-40.22223143</v>
+        <v>-40.80161921</v>
       </c>
       <c r="F51" t="n">
-        <v>-40.80161921</v>
+        <v>-105.72028086</v>
       </c>
       <c r="G51" t="n">
-        <v>-105.72028086</v>
+        <v>-88.20309210000001</v>
       </c>
       <c r="H51" t="n">
-        <v>-88.20309210000001</v>
+        <v>-78.58831128</v>
       </c>
       <c r="I51" t="n">
-        <v>-78.58831128</v>
+        <v>-59.1395146</v>
       </c>
       <c r="J51" t="n">
-        <v>-59.1395146</v>
+        <v>-20.76651212</v>
       </c>
       <c r="K51" t="n">
-        <v>-20.76651212</v>
+        <v>-9.090089680000002</v>
       </c>
       <c r="L51" t="n">
-        <v>-9.090089680000002</v>
+        <v>13.2654385</v>
       </c>
       <c r="M51" t="n">
-        <v>13.2654385</v>
+        <v>8.69171933</v>
       </c>
     </row>
     <row r="52">
@@ -2559,37 +2555,37 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>-7.091562979999999</v>
+        <v>0.7334171800000016</v>
       </c>
       <c r="D52" t="n">
-        <v>3.777009930000002</v>
+        <v>-0.2071407800000003</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.598476830000001</v>
+        <v>-23.60915228</v>
       </c>
       <c r="F52" t="n">
-        <v>-25.32658246</v>
+        <v>-24.72228361</v>
       </c>
       <c r="G52" t="n">
-        <v>-25.32170115</v>
+        <v>-3.24545701</v>
       </c>
       <c r="H52" t="n">
-        <v>-2.890023269999999</v>
+        <v>-7.89663786</v>
       </c>
       <c r="I52" t="n">
-        <v>-8.69867458</v>
+        <v>-16.75375442</v>
       </c>
       <c r="J52" t="n">
-        <v>-18.52504623</v>
+        <v>-0.45316842</v>
       </c>
       <c r="K52" t="n">
-        <v>-1.479009819999999</v>
+        <v>58.01540833999999</v>
       </c>
       <c r="L52" t="n">
-        <v>56.65191959</v>
+        <v>-5.32871971</v>
       </c>
       <c r="M52" t="n">
-        <v>-7.17928261</v>
+        <v>-61.7399726</v>
       </c>
     </row>
     <row r="53">
@@ -2600,37 +2596,37 @@
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>403.92137964</v>
+        <v>410.35100406</v>
       </c>
       <c r="D53" t="n">
-        <v>417.27355261</v>
+        <v>802.9857267199999</v>
       </c>
       <c r="E53" t="n">
-        <v>787.2843079599999</v>
+        <v>519.87731748</v>
       </c>
       <c r="F53" t="n">
-        <v>526.30884272</v>
+        <v>613.73624384</v>
       </c>
       <c r="G53" t="n">
-        <v>649.1520573</v>
+        <v>748.7605075600001</v>
       </c>
       <c r="H53" t="n">
-        <v>849.2582801599999</v>
+        <v>-8.159963869999991</v>
       </c>
       <c r="I53" t="n">
-        <v>141.52416834</v>
+        <v>31.91758276999999</v>
       </c>
       <c r="J53" t="n">
-        <v>78.86956287999999</v>
+        <v>-303.6822649</v>
       </c>
       <c r="K53" t="n">
-        <v>-258.40794319</v>
+        <v>-109.37130644</v>
       </c>
       <c r="L53" t="n">
-        <v>-109.78883045</v>
+        <v>50.02147404000002</v>
       </c>
       <c r="M53" t="n">
-        <v>57.96800567000002</v>
+        <v>-332.76618495</v>
       </c>
     </row>
     <row r="54">
@@ -2639,41 +2635,39 @@
           <t>航運業右下</t>
         </is>
       </c>
-      <c r="B54" t="n">
-        <v>0</v>
-      </c>
+      <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>26.53279652</v>
+        <v>54.34063408000001</v>
       </c>
       <c r="D54" t="n">
-        <v>54.26527661000001</v>
+        <v>25.31443511</v>
       </c>
       <c r="E54" t="n">
-        <v>28.46371281</v>
+        <v>34.39132101000001</v>
       </c>
       <c r="F54" t="n">
-        <v>28.93043279</v>
+        <v>18.56744093</v>
       </c>
       <c r="G54" t="n">
-        <v>7.67053865</v>
+        <v>21.46671996</v>
       </c>
       <c r="H54" t="n">
-        <v>4.52408931</v>
+        <v>23.00197572</v>
       </c>
       <c r="I54" t="n">
-        <v>-5.367082490000001</v>
+        <v>-17.39471921</v>
       </c>
       <c r="J54" t="n">
-        <v>-23.60115783</v>
+        <v>-8.649636150000001</v>
       </c>
       <c r="K54" t="n">
-        <v>-5.530258799999999</v>
+        <v>-31.66030534</v>
       </c>
       <c r="L54" t="n">
-        <v>-21.78297269</v>
+        <v>-41.52215639</v>
       </c>
       <c r="M54" t="n">
-        <v>-29.47139295</v>
+        <v>-38.28242024</v>
       </c>
     </row>
     <row r="55">
@@ -2684,37 +2678,37 @@
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>101.43027788</v>
+        <v>294.85277566</v>
       </c>
       <c r="D55" t="n">
-        <v>287.92907859</v>
+        <v>-84.13148952</v>
       </c>
       <c r="E55" t="n">
-        <v>-71.93683267999999</v>
+        <v>64.43398040000001</v>
       </c>
       <c r="F55" t="n">
-        <v>63.32587674999999</v>
+        <v>-102.7353956</v>
       </c>
       <c r="G55" t="n">
-        <v>-126.93757763</v>
+        <v>67.43969466999998</v>
       </c>
       <c r="H55" t="n">
-        <v>-15.79360724000001</v>
+        <v>-268.41588501</v>
       </c>
       <c r="I55" t="n">
-        <v>-389.3578205</v>
+        <v>-480.65601975</v>
       </c>
       <c r="J55" t="n">
-        <v>-521.33185575</v>
+        <v>-95.26212647</v>
       </c>
       <c r="K55" t="n">
-        <v>-143.61005651</v>
+        <v>-91.24660399</v>
       </c>
       <c r="L55" t="n">
-        <v>-100.5940344</v>
+        <v>-3.401105479999992</v>
       </c>
       <c r="M55" t="n">
-        <v>-23.22845730999999</v>
+        <v>-385.2342181</v>
       </c>
     </row>
     <row r="56">
@@ -2725,37 +2719,37 @@
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>-29.51420846</v>
+        <v>-37.83837768</v>
       </c>
       <c r="D56" t="n">
-        <v>-37.83837768</v>
+        <v>-21.37096288</v>
       </c>
       <c r="E56" t="n">
-        <v>-21.37096288</v>
+        <v>3.36146783</v>
       </c>
       <c r="F56" t="n">
-        <v>3.36146783</v>
+        <v>3.36226849</v>
       </c>
       <c r="G56" t="n">
-        <v>3.36226849</v>
+        <v>27.33139818</v>
       </c>
       <c r="H56" t="n">
-        <v>27.33139818</v>
+        <v>30.01617481</v>
       </c>
       <c r="I56" t="n">
-        <v>30.01617481</v>
+        <v>29.86061085</v>
       </c>
       <c r="J56" t="n">
-        <v>29.86061085</v>
+        <v>27.02228676</v>
       </c>
       <c r="K56" t="n">
-        <v>27.02228676</v>
+        <v>32.18990925</v>
       </c>
       <c r="L56" t="n">
-        <v>32.18990925</v>
+        <v>16.3956815</v>
       </c>
       <c r="M56" t="n">
-        <v>16.3956815</v>
+        <v>27.8735459</v>
       </c>
     </row>
     <row r="57">
@@ -2764,41 +2758,39 @@
           <t>觀光事業右下</t>
         </is>
       </c>
-      <c r="B57" t="n">
-        <v>0</v>
-      </c>
+      <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
-        <v>-31.28732159</v>
+        <v>-35.82230129</v>
       </c>
       <c r="D57" t="n">
-        <v>-35.82188406</v>
+        <v>-48.83644887</v>
       </c>
       <c r="E57" t="n">
-        <v>-48.83523693999999</v>
+        <v>-2.96099005</v>
       </c>
       <c r="F57" t="n">
-        <v>-2.96059799</v>
+        <v>-4.132907749999999</v>
       </c>
       <c r="G57" t="n">
-        <v>-4.132503679999999</v>
+        <v>-6.76113141</v>
       </c>
       <c r="H57" t="n">
-        <v>-6.760800140000001</v>
+        <v>-11.20169948</v>
       </c>
       <c r="I57" t="n">
-        <v>-11.20146937</v>
+        <v>-1.30357813</v>
       </c>
       <c r="J57" t="n">
-        <v>-1.30338222</v>
+        <v>12.02094224</v>
       </c>
       <c r="K57" t="n">
-        <v>12.0210239</v>
+        <v>1.93671805</v>
       </c>
       <c r="L57" t="n">
-        <v>1.93636077</v>
+        <v>5.15673921</v>
       </c>
       <c r="M57" t="n">
-        <v>5.156443139999999</v>
+        <v>2.68580058</v>
       </c>
     </row>
     <row r="58">
@@ -2809,37 +2801,37 @@
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>-0.01366196</v>
+        <v>-0.02535924</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.02528435</v>
+        <v>-0.01054632</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.01048862</v>
+        <v>-0.02853263</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.02850319</v>
+        <v>-0.03224291</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.03215644</v>
+        <v>-0.02415376</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.0241682</v>
+        <v>-0.01781416</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.01771963</v>
+        <v>-0.006898679999999999</v>
       </c>
       <c r="J58" t="n">
-        <v>-0.00682615</v>
+        <v>-0.00198091</v>
       </c>
       <c r="K58" t="n">
-        <v>-0.00195043</v>
+        <v>0.00017943</v>
       </c>
       <c r="L58" t="n">
-        <v>0.0001301400000000001</v>
+        <v>0.00362758</v>
       </c>
       <c r="M58" t="n">
-        <v>0.00370429</v>
+        <v>0.00741122</v>
       </c>
     </row>
     <row r="59">
@@ -2850,37 +2842,37 @@
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
-        <v>0.04099756</v>
+        <v>0.02809802</v>
       </c>
       <c r="D59" t="n">
-        <v>0.02809802</v>
+        <v>0.04076989</v>
       </c>
       <c r="E59" t="n">
-        <v>0.04076989</v>
+        <v>-0.02230235</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.02230235</v>
+        <v>0.0121624</v>
       </c>
       <c r="G59" t="n">
-        <v>0.0121624</v>
+        <v>-0.02442989</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.02442989</v>
+        <v>0.09452125</v>
       </c>
       <c r="I59" t="n">
-        <v>0.09452125</v>
+        <v>0.12390914</v>
       </c>
       <c r="J59" t="n">
-        <v>0.12390914</v>
+        <v>0.05750639</v>
       </c>
       <c r="K59" t="n">
-        <v>0.05750639</v>
+        <v>0.01196176</v>
       </c>
       <c r="L59" t="n">
-        <v>0.01196176</v>
+        <v>-0.03147701</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.03147701</v>
+        <v>-0.03227104</v>
       </c>
     </row>
     <row r="60">
@@ -2891,1722 +2883,1683 @@
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
-        <v>3.745202050000001</v>
+        <v>-27.10836733</v>
       </c>
       <c r="D60" t="n">
-        <v>-27.11462849</v>
+        <v>-14.55097783</v>
       </c>
       <c r="E60" t="n">
-        <v>-14.54311404</v>
+        <v>-20.19341195</v>
       </c>
       <c r="F60" t="n">
-        <v>-20.20816677</v>
+        <v>-48.79022895</v>
       </c>
       <c r="G60" t="n">
-        <v>-48.84269329</v>
+        <v>-21.4031845</v>
       </c>
       <c r="H60" t="n">
-        <v>-21.3959596</v>
+        <v>-29.01154994</v>
       </c>
       <c r="I60" t="n">
-        <v>-28.9827527</v>
+        <v>-29.79071027</v>
       </c>
       <c r="J60" t="n">
-        <v>-29.74134219</v>
+        <v>13.33956805</v>
       </c>
       <c r="K60" t="n">
-        <v>13.35674909</v>
+        <v>-5.238531109999999</v>
       </c>
       <c r="L60" t="n">
-        <v>-5.219705279999999</v>
+        <v>-5.193532859999999</v>
       </c>
       <c r="M60" t="n">
-        <v>-5.249354970000001</v>
+        <v>-51.10926124</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨平</t>
+          <t>資訊服務業右上</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
-        <v>-0.00852609</v>
+        <v>54.93877188</v>
       </c>
       <c r="D61" t="n">
-        <v>0.00626116</v>
+        <v>-22.98987321</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.007863790000000001</v>
+        <v>-39.61853198000001</v>
       </c>
       <c r="F61" t="n">
-        <v>0.01475482</v>
+        <v>-39.8328593</v>
       </c>
       <c r="G61" t="n">
-        <v>0.05246434</v>
+        <v>-53.46346058</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.007224899999999999</v>
+        <v>-44.29557809</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.02879724</v>
+        <v>-13.57506585000001</v>
       </c>
       <c r="J61" t="n">
-        <v>-0.04936808</v>
+        <v>170.54267959</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.01718104</v>
+        <v>174.65825153</v>
       </c>
       <c r="L61" t="n">
-        <v>-0.01882583</v>
+        <v>150.92617291</v>
       </c>
       <c r="M61" t="n">
-        <v>0.05582211</v>
+        <v>138.10057287</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右上</t>
+          <t>資訊服務業右下</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>16.52188788</v>
+        <v>0.008596049999999999</v>
       </c>
       <c r="D62" t="n">
-        <v>67.26936631000001</v>
+        <v>0.00958909</v>
       </c>
       <c r="E62" t="n">
-        <v>-16.93134559</v>
+        <v>0.00693968</v>
       </c>
       <c r="F62" t="n">
-        <v>-37.9880055</v>
+        <v>0.00426686</v>
       </c>
       <c r="G62" t="n">
-        <v>-34.65914282</v>
+        <v>-0.0024533</v>
       </c>
       <c r="H62" t="n">
-        <v>-52.24997314</v>
+        <v>-0.00572523</v>
       </c>
       <c r="I62" t="n">
-        <v>-39.37738686</v>
+        <v>0.002586119999999999</v>
       </c>
       <c r="J62" t="n">
-        <v>-4.033918470000014</v>
+        <v>-0.0010712</v>
       </c>
       <c r="K62" t="n">
-        <v>175.37682422</v>
+        <v>-0.00402686</v>
       </c>
       <c r="L62" t="n">
-        <v>175.90085929</v>
+        <v>0.00016534</v>
       </c>
       <c r="M62" t="n">
-        <v>136.82315401</v>
+        <v>-0.00129074</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右下</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>0</v>
-      </c>
+          <t>資訊服務業平</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>0.0165183</v>
+        <v>42.50717179</v>
       </c>
       <c r="D63" t="n">
-        <v>0.02079566</v>
+        <v>35.45605584</v>
       </c>
       <c r="E63" t="n">
-        <v>0.02295783</v>
+        <v>0.2650007999999996</v>
       </c>
       <c r="F63" t="n">
-        <v>0.01874305</v>
+        <v>-17.41268575</v>
       </c>
       <c r="G63" t="n">
-        <v>0.01366509</v>
+        <v>-16.33202341</v>
       </c>
       <c r="H63" t="n">
-        <v>0.00024416</v>
+        <v>-24.18827343</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.00657713</v>
+        <v>7.50544225</v>
       </c>
       <c r="J63" t="n">
-        <v>0.00399665</v>
+        <v>27.78330302</v>
       </c>
       <c r="K63" t="n">
-        <v>0.00442412</v>
+        <v>5.40527296</v>
       </c>
       <c r="L63" t="n">
-        <v>-0.00497683</v>
+        <v>21.18573445</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.0007074799999999999</v>
+        <v>27.97332206</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業平</t>
+          <t>農業科技業右上</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
-        <v>18.4390037</v>
+        <v>-0.00052996</v>
       </c>
       <c r="D64" t="n">
-        <v>30.16394224</v>
+        <v>-4.627e-05</v>
       </c>
       <c r="E64" t="n">
-        <v>29.38253063</v>
+        <v>0.00012135</v>
       </c>
       <c r="F64" t="n">
-        <v>-1.380576690000001</v>
+        <v>0.00033795</v>
       </c>
       <c r="G64" t="n">
-        <v>-22.5959879</v>
+        <v>0.0007966399999999999</v>
       </c>
       <c r="H64" t="n">
-        <v>-17.54958439</v>
+        <v>0.00094526</v>
       </c>
       <c r="I64" t="n">
-        <v>-29.10349154</v>
+        <v>0.00174454</v>
       </c>
       <c r="J64" t="n">
-        <v>-2.03398716</v>
+        <v>0.0028698</v>
       </c>
       <c r="K64" t="n">
-        <v>22.94496679</v>
+        <v>0.00067753</v>
       </c>
       <c r="L64" t="n">
-        <v>4.16137799</v>
+        <v>-0.00045384</v>
       </c>
       <c r="M64" t="n">
-        <v>35.28482904</v>
+        <v>-0.00127009</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右上</t>
+          <t>農業科技業右下</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
-        <v>-0.00126824</v>
+        <v>-0.00011783</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.00052996</v>
+        <v>-0.00038662</v>
       </c>
       <c r="E65" t="n">
-        <v>-4.627e-05</v>
+        <v>-0.00020338</v>
       </c>
       <c r="F65" t="n">
-        <v>0.00012135</v>
+        <v>2.062999999999999e-05</v>
       </c>
       <c r="G65" t="n">
-        <v>0.00033795</v>
+        <v>7.988999999999998e-05</v>
       </c>
       <c r="H65" t="n">
-        <v>0.0007966399999999999</v>
+        <v>-3.629999999999995e-06</v>
       </c>
       <c r="I65" t="n">
-        <v>0.00094526</v>
+        <v>0.00015752</v>
       </c>
       <c r="J65" t="n">
-        <v>0.00174454</v>
+        <v>0.00021599</v>
       </c>
       <c r="K65" t="n">
-        <v>0.0028698</v>
+        <v>0.00017486</v>
       </c>
       <c r="L65" t="n">
-        <v>0.00067753</v>
+        <v>3.101e-05</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.00045384</v>
+        <v>-6.934e-05</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右下</t>
+          <t>通信網路業右上</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>-0.00012853</v>
+        <v>881.77153263</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.00011783</v>
+        <v>977.3671055899999</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.00038662</v>
+        <v>1060.49052372</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.00020338</v>
+        <v>1028.22388811</v>
       </c>
       <c r="G66" t="n">
-        <v>2.062999999999999e-05</v>
+        <v>1598.98058583</v>
       </c>
       <c r="H66" t="n">
-        <v>7.988999999999998e-05</v>
+        <v>445.43210898</v>
       </c>
       <c r="I66" t="n">
-        <v>-3.629999999999995e-06</v>
+        <v>-2030.04348458</v>
       </c>
       <c r="J66" t="n">
-        <v>0.00015752</v>
+        <v>-1282.33180896</v>
       </c>
       <c r="K66" t="n">
-        <v>0.00021599</v>
+        <v>-1021.56479744</v>
       </c>
       <c r="L66" t="n">
-        <v>0.00017486</v>
+        <v>-789.8186694300001</v>
       </c>
       <c r="M66" t="n">
-        <v>3.101e-05</v>
+        <v>-331.9871849</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右上</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr"/>
+          <t>通信網路業右下</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>0</v>
+      </c>
       <c r="C67" t="n">
-        <v>922.2366730800001</v>
+        <v>-30.75372053</v>
       </c>
       <c r="D67" t="n">
-        <v>1025.05925974</v>
+        <v>-12.25361867</v>
       </c>
       <c r="E67" t="n">
-        <v>1121.3388571</v>
+        <v>-9.69304327</v>
       </c>
       <c r="F67" t="n">
-        <v>1091.38838137</v>
+        <v>-7.762195480000003</v>
       </c>
       <c r="G67" t="n">
-        <v>1194.63658561</v>
+        <v>18.69303842</v>
       </c>
       <c r="H67" t="n">
-        <v>1752.89016636</v>
+        <v>16.39838854</v>
       </c>
       <c r="I67" t="n">
-        <v>599.6728452000001</v>
+        <v>-15.73082077</v>
       </c>
       <c r="J67" t="n">
-        <v>-1800.9600182</v>
+        <v>-2.49606959</v>
       </c>
       <c r="K67" t="n">
-        <v>-1190.94781851</v>
+        <v>-12.86192467</v>
       </c>
       <c r="L67" t="n">
-        <v>-1025.3908286</v>
+        <v>11.9852251</v>
       </c>
       <c r="M67" t="n">
-        <v>-866.6814339</v>
+        <v>82.28392362000001</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右下</t>
+          <t>通信網路業平</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>-108.88423967</v>
+        <v>169.57787524</v>
       </c>
       <c r="D68" t="n">
-        <v>-49.34166707</v>
+        <v>86.01461866</v>
       </c>
       <c r="E68" t="n">
-        <v>-40.32357138</v>
+        <v>55.92458661</v>
       </c>
       <c r="F68" t="n">
-        <v>-39.00888978</v>
+        <v>155.36693196</v>
       </c>
       <c r="G68" t="n">
-        <v>-17.80951091</v>
+        <v>186.84559613</v>
       </c>
       <c r="H68" t="n">
-        <v>6.000725700000001</v>
+        <v>110.13981128</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.7707804100000024</v>
+        <v>-64.29805888</v>
       </c>
       <c r="J68" t="n">
-        <v>-37.88953521</v>
+        <v>77.9521532</v>
       </c>
       <c r="K68" t="n">
-        <v>-10.25797633</v>
+        <v>-47.30402968</v>
       </c>
       <c r="L68" t="n">
-        <v>-18.96683493</v>
+        <v>-75.44613013999999</v>
       </c>
       <c r="M68" t="n">
-        <v>16.33818648</v>
+        <v>110.13512589</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>通信網路業平</t>
+          <t>造紙工業右下</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>-43.12169323</v>
+        <v>-1.07992369</v>
       </c>
       <c r="D69" t="n">
-        <v>44.67736398</v>
+        <v>-8.13542947</v>
       </c>
       <c r="E69" t="n">
-        <v>-30.20987664</v>
+        <v>-6.112742610000001</v>
       </c>
       <c r="F69" t="n">
-        <v>53.93063466</v>
+        <v>0.62737845</v>
       </c>
       <c r="G69" t="n">
-        <v>-1.213785110000001</v>
+        <v>-1.39124728</v>
       </c>
       <c r="H69" t="n">
-        <v>45.57241802999999</v>
+        <v>-3.48094111</v>
       </c>
       <c r="I69" t="n">
-        <v>-27.11002662000001</v>
+        <v>-5.56892512</v>
       </c>
       <c r="J69" t="n">
-        <v>-271.4762455</v>
+        <v>1.72853993</v>
       </c>
       <c r="K69" t="n">
-        <v>-6.035967030000001</v>
+        <v>-2.4559021</v>
       </c>
       <c r="L69" t="n">
-        <v>-37.75509148</v>
+        <v>-1.44139782</v>
       </c>
       <c r="M69" t="n">
-        <v>-3.085999260000009</v>
+        <v>3.123593180000001</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>造紙工業右下</t>
+          <t>造紙工業平</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>0.8999840899999999</v>
+        <v>2.0141396</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.07992369</v>
+        <v>0.94456732</v>
       </c>
       <c r="E70" t="n">
-        <v>-8.13542947</v>
+        <v>1.31059385</v>
       </c>
       <c r="F70" t="n">
-        <v>-6.112742610000001</v>
+        <v>0.44808132</v>
       </c>
       <c r="G70" t="n">
-        <v>0.62737845</v>
+        <v>1.02481299</v>
       </c>
       <c r="H70" t="n">
-        <v>-1.39124728</v>
+        <v>0.39879786</v>
       </c>
       <c r="I70" t="n">
-        <v>-3.48094111</v>
+        <v>-0.4558637</v>
       </c>
       <c r="J70" t="n">
-        <v>-5.56892512</v>
+        <v>0.5983068499999999</v>
       </c>
       <c r="K70" t="n">
-        <v>1.72853993</v>
+        <v>3.41007278</v>
       </c>
       <c r="L70" t="n">
-        <v>-2.4559021</v>
+        <v>3.07970445</v>
       </c>
       <c r="M70" t="n">
-        <v>-1.44139782</v>
+        <v>1.5513345</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>造紙工業平</t>
+          <t>運動休閒右上</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
-        <v>0.15324129</v>
+        <v>-0.8933656799999999</v>
       </c>
       <c r="D71" t="n">
-        <v>2.0141396</v>
+        <v>-11.91034057</v>
       </c>
       <c r="E71" t="n">
-        <v>0.94456732</v>
+        <v>-6.11659849</v>
       </c>
       <c r="F71" t="n">
-        <v>1.31059385</v>
+        <v>-1.00781589</v>
       </c>
       <c r="G71" t="n">
-        <v>0.44808132</v>
+        <v>-14.19481265</v>
       </c>
       <c r="H71" t="n">
-        <v>1.02481299</v>
+        <v>-10.85873646</v>
       </c>
       <c r="I71" t="n">
-        <v>0.39879786</v>
+        <v>-12.55970872</v>
       </c>
       <c r="J71" t="n">
-        <v>-0.4558637</v>
+        <v>-11.07626771</v>
       </c>
       <c r="K71" t="n">
-        <v>0.5983068499999999</v>
+        <v>-10.07216436</v>
       </c>
       <c r="L71" t="n">
-        <v>3.41007278</v>
+        <v>1.9133612</v>
       </c>
       <c r="M71" t="n">
-        <v>3.07970445</v>
+        <v>13.79692213</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右上</t>
+          <t>運動休閒右下</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>34.17125779</v>
+        <v>-62.8772119</v>
       </c>
       <c r="D72" t="n">
-        <v>-3.0706811</v>
+        <v>-12.82282402</v>
       </c>
       <c r="E72" t="n">
-        <v>-7.127004649999999</v>
+        <v>98.85202981</v>
       </c>
       <c r="F72" t="n">
-        <v>-16.45539349</v>
+        <v>106.34325255</v>
       </c>
       <c r="G72" t="n">
-        <v>-1.46575611</v>
+        <v>-1.836550060000001</v>
       </c>
       <c r="H72" t="n">
-        <v>-28.70342079</v>
+        <v>-111.9755101</v>
       </c>
       <c r="I72" t="n">
-        <v>-30.10771701</v>
+        <v>-93.22314349</v>
       </c>
       <c r="J72" t="n">
-        <v>-17.75000963</v>
+        <v>24.62366161</v>
       </c>
       <c r="K72" t="n">
-        <v>-16.20229139</v>
+        <v>8.48404197</v>
       </c>
       <c r="L72" t="n">
-        <v>-16.02781221</v>
+        <v>92.84662886</v>
       </c>
       <c r="M72" t="n">
-        <v>1.12072129</v>
+        <v>-389.95554058</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右下</t>
+          <t>運動休閒平</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
-        <v>-112.44551461</v>
+        <v>-17.48223691</v>
       </c>
       <c r="D73" t="n">
-        <v>-90.06517006999999</v>
+        <v>-4.105024530000001</v>
       </c>
       <c r="E73" t="n">
-        <v>-43.46545776000001</v>
+        <v>10.44366532</v>
       </c>
       <c r="F73" t="n">
-        <v>51.29491169</v>
+        <v>-3.14555707</v>
       </c>
       <c r="G73" t="n">
-        <v>59.22804754</v>
+        <v>-37.77630811</v>
       </c>
       <c r="H73" t="n">
-        <v>-19.14230721</v>
+        <v>-56.73373307</v>
       </c>
       <c r="I73" t="n">
-        <v>-113.7462762</v>
+        <v>-26.26078099</v>
       </c>
       <c r="J73" t="n">
-        <v>-86.32584292</v>
+        <v>-2.46272056</v>
       </c>
       <c r="K73" t="n">
-        <v>28.64253698</v>
+        <v>-16.96599539</v>
       </c>
       <c r="L73" t="n">
-        <v>18.30188621</v>
+        <v>0.4629108499999997</v>
       </c>
       <c r="M73" t="n">
-        <v>99.68047403</v>
+        <v>-4.400991700000001</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>運動休閒平</t>
+          <t>金融保險右上</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
-        <v>-30.54986415</v>
+        <v>661.4475458300001</v>
       </c>
       <c r="D74" t="n">
-        <v>-15.30492149</v>
+        <v>920.3418781399999</v>
       </c>
       <c r="E74" t="n">
-        <v>-8.88836045</v>
+        <v>1337.23523276</v>
       </c>
       <c r="F74" t="n">
-        <v>20.78246032</v>
+        <v>440.87010388</v>
       </c>
       <c r="G74" t="n">
-        <v>-2.68761685</v>
+        <v>283.95405481</v>
       </c>
       <c r="H74" t="n">
-        <v>-23.26769997</v>
+        <v>-274.049699</v>
       </c>
       <c r="I74" t="n">
-        <v>-37.48475252</v>
+        <v>-976.53537891</v>
       </c>
       <c r="J74" t="n">
-        <v>-21.07048008</v>
+        <v>-778.0464094499999</v>
       </c>
       <c r="K74" t="n">
-        <v>2.66330312</v>
+        <v>-1079.02344502</v>
       </c>
       <c r="L74" t="n">
-        <v>-11.01034754</v>
+        <v>-667.03826437</v>
       </c>
       <c r="M74" t="n">
-        <v>1.25555076</v>
+        <v>-1429.5533131</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>金融保險右上</t>
+          <t>金融保險右下</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
-        <v>664.72535027</v>
+        <v>-487.8436765000001</v>
       </c>
       <c r="D75" t="n">
-        <v>656.9999549300001</v>
+        <v>-231.09819764</v>
       </c>
       <c r="E75" t="n">
-        <v>922.40805115</v>
+        <v>-6.482741509999999</v>
       </c>
       <c r="F75" t="n">
-        <v>1352.18679415</v>
+        <v>-64.07832381</v>
       </c>
       <c r="G75" t="n">
-        <v>443.55634693</v>
+        <v>54.92950557</v>
       </c>
       <c r="H75" t="n">
-        <v>296.15320315</v>
+        <v>3.986776439999998</v>
       </c>
       <c r="I75" t="n">
-        <v>-274.2499456</v>
+        <v>105.74435434</v>
       </c>
       <c r="J75" t="n">
-        <v>-985.81143814</v>
+        <v>173.2930186</v>
       </c>
       <c r="K75" t="n">
-        <v>-778.2785946499999</v>
+        <v>93.11041993999999</v>
       </c>
       <c r="L75" t="n">
-        <v>-1087.35782134</v>
+        <v>105.96609074</v>
       </c>
       <c r="M75" t="n">
-        <v>-684.8153055399999</v>
+        <v>-194.99342868</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>金融保險右下</t>
+          <t>金融保險平</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>-366.08115125</v>
+        <v>24.75472931</v>
       </c>
       <c r="D76" t="n">
-        <v>-487.8436765000001</v>
+        <v>39.42194512</v>
       </c>
       <c r="E76" t="n">
-        <v>-231.09819764</v>
+        <v>96.91018503000001</v>
       </c>
       <c r="F76" t="n">
-        <v>-6.482741509999999</v>
+        <v>53.64617351</v>
       </c>
       <c r="G76" t="n">
-        <v>-64.07832381</v>
+        <v>29.05103062</v>
       </c>
       <c r="H76" t="n">
-        <v>54.92950557</v>
+        <v>-13.93929361</v>
       </c>
       <c r="I76" t="n">
-        <v>3.986776439999998</v>
+        <v>-51.13679468000001</v>
       </c>
       <c r="J76" t="n">
-        <v>105.74435434</v>
+        <v>-27.00637503</v>
       </c>
       <c r="K76" t="n">
-        <v>173.2930186</v>
+        <v>-39.34154576</v>
       </c>
       <c r="L76" t="n">
-        <v>93.11041993999999</v>
+        <v>2.200812019999999</v>
       </c>
       <c r="M76" t="n">
-        <v>105.96609074</v>
+        <v>-62.79503133999999</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>金融保險平</t>
+          <t>金融業右上</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="n">
-        <v>43.59403532</v>
+        <v>0.00101082</v>
       </c>
       <c r="D77" t="n">
-        <v>29.20232021</v>
+        <v>9.988e-05</v>
       </c>
       <c r="E77" t="n">
-        <v>37.35577211</v>
+        <v>0.00032912</v>
       </c>
       <c r="F77" t="n">
-        <v>81.95862364</v>
+        <v>-0.00052438</v>
       </c>
       <c r="G77" t="n">
-        <v>50.95993046</v>
+        <v>-9.99e-05</v>
       </c>
       <c r="H77" t="n">
-        <v>16.85188228</v>
+        <v>-0.00069427</v>
       </c>
       <c r="I77" t="n">
-        <v>-13.73904701</v>
+        <v>-0.00100544</v>
       </c>
       <c r="J77" t="n">
-        <v>-41.86073545</v>
+        <v>-0.00044273</v>
       </c>
       <c r="K77" t="n">
-        <v>-26.77418983</v>
+        <v>-0.00079249</v>
       </c>
       <c r="L77" t="n">
-        <v>-31.00716944</v>
+        <v>-0.0010202</v>
       </c>
       <c r="M77" t="n">
-        <v>19.97785319</v>
+        <v>0.00077677</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>金融業右上</t>
+          <t>金融業右下</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
-        <v>0.00226234</v>
+        <v>9.011000000000007e-05</v>
       </c>
       <c r="D78" t="n">
-        <v>0.00101082</v>
+        <v>0.0004795100000000002</v>
       </c>
       <c r="E78" t="n">
-        <v>9.988e-05</v>
+        <v>0.00329986</v>
       </c>
       <c r="F78" t="n">
-        <v>0.00032912</v>
+        <v>0.0005099499999999999</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.00052438</v>
+        <v>-0.0007658099999999999</v>
       </c>
       <c r="H78" t="n">
-        <v>-9.99e-05</v>
+        <v>0.0034501</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.00069427</v>
+        <v>0.0005688300000000001</v>
       </c>
       <c r="J78" t="n">
-        <v>-0.00100544</v>
+        <v>0.00248966</v>
       </c>
       <c r="K78" t="n">
-        <v>-0.00044273</v>
+        <v>0.00048036</v>
       </c>
       <c r="L78" t="n">
-        <v>-0.00079249</v>
+        <v>0.00267611</v>
       </c>
       <c r="M78" t="n">
-        <v>-0.0010202</v>
+        <v>0.0017373</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>金融業右下</t>
+          <t>金融業平</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="n">
-        <v>0.00272902</v>
+        <v>0.00013897</v>
       </c>
       <c r="D79" t="n">
-        <v>9.011000000000007e-05</v>
+        <v>6.415e-05</v>
       </c>
       <c r="E79" t="n">
-        <v>0.0004795100000000002</v>
+        <v>-0.00029419</v>
       </c>
       <c r="F79" t="n">
-        <v>0.00329986</v>
+        <v>0.00019073</v>
       </c>
       <c r="G79" t="n">
-        <v>0.0005099499999999999</v>
+        <v>-2.111999999999998e-05</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.0007658099999999999</v>
+        <v>0.00040195</v>
       </c>
       <c r="I79" t="n">
-        <v>0.0034501</v>
+        <v>7.686999999999999e-05</v>
       </c>
       <c r="J79" t="n">
-        <v>0.0005688300000000001</v>
+        <v>-0.00026166</v>
       </c>
       <c r="K79" t="n">
-        <v>0.00248966</v>
+        <v>-0.0005340900000000001</v>
       </c>
       <c r="L79" t="n">
-        <v>0.00048036</v>
+        <v>-0.0005954199999999999</v>
       </c>
       <c r="M79" t="n">
-        <v>0.00267611</v>
+        <v>-0.00055956</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>金融業平</t>
+          <t>鋼鐵工業右上</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="n">
-        <v>9.465e-05</v>
+        <v>12.0470033</v>
       </c>
       <c r="D80" t="n">
-        <v>0.00013897</v>
+        <v>-4.75992293</v>
       </c>
       <c r="E80" t="n">
-        <v>6.415e-05</v>
+        <v>12.51950739</v>
       </c>
       <c r="F80" t="n">
-        <v>-0.00029419</v>
+        <v>17.68515502</v>
       </c>
       <c r="G80" t="n">
-        <v>0.00019073</v>
+        <v>13.03947844</v>
       </c>
       <c r="H80" t="n">
-        <v>-2.111999999999998e-05</v>
+        <v>10.19729045</v>
       </c>
       <c r="I80" t="n">
-        <v>0.00040195</v>
+        <v>-4.28183161</v>
       </c>
       <c r="J80" t="n">
-        <v>7.686999999999999e-05</v>
+        <v>-6.19425625</v>
       </c>
       <c r="K80" t="n">
-        <v>-0.00026166</v>
+        <v>6.76254038</v>
       </c>
       <c r="L80" t="n">
-        <v>-0.0005340900000000001</v>
+        <v>8.853421710000001</v>
       </c>
       <c r="M80" t="n">
-        <v>-0.0005954199999999999</v>
+        <v>25.21709696</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上</t>
+          <t>鋼鐵工業右下</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>4.868124629999999</v>
+        <v>33.03930102</v>
       </c>
       <c r="D81" t="n">
-        <v>12.18883922</v>
+       